--- a/BacklogGATEAutoCompleto.xlsx
+++ b/BacklogGATEAutoCompleto.xlsx
@@ -8169,7 +8169,7 @@
         <v>1357</v>
       </c>
       <c r="E2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="F2" t="s">
         <v>1569</v>
@@ -8204,7 +8204,7 @@
         <v>1358</v>
       </c>
       <c r="E3">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="F3" t="s">
         <v>1569</v>
@@ -8239,7 +8239,7 @@
         <v>1359</v>
       </c>
       <c r="E4">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="F4" t="s">
         <v>1569</v>
@@ -8274,7 +8274,7 @@
         <v>1360</v>
       </c>
       <c r="E5">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="F5" t="s">
         <v>1569</v>
@@ -8309,7 +8309,7 @@
         <v>1361</v>
       </c>
       <c r="E6">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="F6" t="s">
         <v>1569</v>
@@ -8344,7 +8344,7 @@
         <v>1362</v>
       </c>
       <c r="E7">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="F7" t="s">
         <v>1569</v>
@@ -8379,7 +8379,7 @@
         <v>1363</v>
       </c>
       <c r="E8">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="F8" t="s">
         <v>1569</v>
@@ -8414,7 +8414,7 @@
         <v>1364</v>
       </c>
       <c r="E9">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="F9" t="s">
         <v>1569</v>
@@ -8449,7 +8449,7 @@
         <v>1365</v>
       </c>
       <c r="E10">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="F10" t="s">
         <v>1569</v>
@@ -8484,7 +8484,7 @@
         <v>1365</v>
       </c>
       <c r="E11">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="F11" t="s">
         <v>1569</v>
@@ -8519,7 +8519,7 @@
         <v>1366</v>
       </c>
       <c r="E12">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="F12" t="s">
         <v>1569</v>
@@ -8554,7 +8554,7 @@
         <v>1367</v>
       </c>
       <c r="E13">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F13" t="s">
         <v>1569</v>
@@ -8589,7 +8589,7 @@
         <v>1368</v>
       </c>
       <c r="E14">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="F14" t="s">
         <v>1569</v>
@@ -8624,7 +8624,7 @@
         <v>1368</v>
       </c>
       <c r="E15">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="F15" t="s">
         <v>1569</v>
@@ -8659,7 +8659,7 @@
         <v>1369</v>
       </c>
       <c r="E16">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="F16" t="s">
         <v>1569</v>
@@ -8694,7 +8694,7 @@
         <v>1370</v>
       </c>
       <c r="E17">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="F17" t="s">
         <v>1569</v>
@@ -8729,7 +8729,7 @@
         <v>1370</v>
       </c>
       <c r="E18">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="F18" t="s">
         <v>1569</v>
@@ -8764,7 +8764,7 @@
         <v>1371</v>
       </c>
       <c r="E19">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F19" t="s">
         <v>1569</v>
@@ -8799,7 +8799,7 @@
         <v>1372</v>
       </c>
       <c r="E20">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="F20" t="s">
         <v>1569</v>
@@ -8834,7 +8834,7 @@
         <v>1373</v>
       </c>
       <c r="E21">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F21" t="s">
         <v>1569</v>
@@ -8869,7 +8869,7 @@
         <v>1374</v>
       </c>
       <c r="E22">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F22" t="s">
         <v>1569</v>
@@ -8904,7 +8904,7 @@
         <v>1375</v>
       </c>
       <c r="E23">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="F23" t="s">
         <v>1569</v>
@@ -8942,7 +8942,7 @@
         <v>1376</v>
       </c>
       <c r="E24">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F24" t="s">
         <v>1569</v>
@@ -8977,7 +8977,7 @@
         <v>1377</v>
       </c>
       <c r="E25">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="F25" t="s">
         <v>1569</v>
@@ -9012,7 +9012,7 @@
         <v>1378</v>
       </c>
       <c r="E26">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="F26" t="s">
         <v>1569</v>
@@ -9047,7 +9047,7 @@
         <v>1379</v>
       </c>
       <c r="E27">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F27" t="s">
         <v>1569</v>
@@ -9082,7 +9082,7 @@
         <v>1380</v>
       </c>
       <c r="E28">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F28" t="s">
         <v>1569</v>
@@ -9117,7 +9117,7 @@
         <v>1381</v>
       </c>
       <c r="E29">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F29" t="s">
         <v>1569</v>
@@ -9152,7 +9152,7 @@
         <v>1382</v>
       </c>
       <c r="E30">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F30" t="s">
         <v>1569</v>
@@ -9187,7 +9187,7 @@
         <v>1383</v>
       </c>
       <c r="E31">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F31" t="s">
         <v>1569</v>
@@ -9222,7 +9222,7 @@
         <v>1384</v>
       </c>
       <c r="E32">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F32" t="s">
         <v>1569</v>
@@ -9257,7 +9257,7 @@
         <v>1385</v>
       </c>
       <c r="E33">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F33" t="s">
         <v>1569</v>
@@ -9292,7 +9292,7 @@
         <v>1386</v>
       </c>
       <c r="E34">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F34" t="s">
         <v>1569</v>
@@ -9327,7 +9327,7 @@
         <v>1386</v>
       </c>
       <c r="E35">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F35" t="s">
         <v>1569</v>
@@ -9362,7 +9362,7 @@
         <v>1387</v>
       </c>
       <c r="E36">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="F36" t="s">
         <v>1569</v>
@@ -9397,7 +9397,7 @@
         <v>1388</v>
       </c>
       <c r="E37">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F37" t="s">
         <v>1569</v>
@@ -9432,7 +9432,7 @@
         <v>1389</v>
       </c>
       <c r="E38">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F38" t="s">
         <v>1569</v>
@@ -9467,7 +9467,7 @@
         <v>1390</v>
       </c>
       <c r="E39">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F39" t="s">
         <v>1569</v>
@@ -9502,7 +9502,7 @@
         <v>1391</v>
       </c>
       <c r="E40">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F40" t="s">
         <v>1569</v>
@@ -9537,7 +9537,7 @@
         <v>1391</v>
       </c>
       <c r="E41">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F41" t="s">
         <v>1569</v>
@@ -9572,7 +9572,7 @@
         <v>1392</v>
       </c>
       <c r="E42">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F42" t="s">
         <v>1569</v>
@@ -9607,7 +9607,7 @@
         <v>1393</v>
       </c>
       <c r="E43">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F43" t="s">
         <v>1569</v>
@@ -9642,7 +9642,7 @@
         <v>1394</v>
       </c>
       <c r="E44">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F44" t="s">
         <v>1569</v>
@@ -9677,7 +9677,7 @@
         <v>1394</v>
       </c>
       <c r="E45">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F45" t="s">
         <v>1569</v>
@@ -9712,7 +9712,7 @@
         <v>1395</v>
       </c>
       <c r="E46">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F46" t="s">
         <v>1569</v>
@@ -9747,7 +9747,7 @@
         <v>1395</v>
       </c>
       <c r="E47">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F47" t="s">
         <v>1569</v>
@@ -9782,7 +9782,7 @@
         <v>1396</v>
       </c>
       <c r="E48">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F48" t="s">
         <v>1569</v>
@@ -9817,7 +9817,7 @@
         <v>1397</v>
       </c>
       <c r="E49">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F49" t="s">
         <v>1569</v>
@@ -9852,7 +9852,7 @@
         <v>1398</v>
       </c>
       <c r="E50">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F50" t="s">
         <v>1569</v>
@@ -9887,7 +9887,7 @@
         <v>1399</v>
       </c>
       <c r="E51">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F51" t="s">
         <v>1569</v>
@@ -9922,7 +9922,7 @@
         <v>1399</v>
       </c>
       <c r="E52">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F52" t="s">
         <v>1569</v>
@@ -9957,7 +9957,7 @@
         <v>1400</v>
       </c>
       <c r="E53">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F53" t="s">
         <v>1569</v>
@@ -9992,7 +9992,7 @@
         <v>1401</v>
       </c>
       <c r="E54">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F54" t="s">
         <v>1569</v>
@@ -10027,7 +10027,7 @@
         <v>1402</v>
       </c>
       <c r="E55">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F55" t="s">
         <v>1569</v>
@@ -10062,7 +10062,7 @@
         <v>1403</v>
       </c>
       <c r="E56">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F56" t="s">
         <v>1569</v>
@@ -10097,7 +10097,7 @@
         <v>1404</v>
       </c>
       <c r="E57">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F57" t="s">
         <v>1569</v>
@@ -10132,7 +10132,7 @@
         <v>1405</v>
       </c>
       <c r="E58">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F58" t="s">
         <v>1569</v>
@@ -10167,7 +10167,7 @@
         <v>1406</v>
       </c>
       <c r="E59">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F59" t="s">
         <v>1569</v>
@@ -10202,7 +10202,7 @@
         <v>1406</v>
       </c>
       <c r="E60">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F60" t="s">
         <v>1569</v>
@@ -10237,7 +10237,7 @@
         <v>1406</v>
       </c>
       <c r="E61">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F61" t="s">
         <v>1569</v>
@@ -10272,7 +10272,7 @@
         <v>1407</v>
       </c>
       <c r="E62">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F62" t="s">
         <v>1569</v>
@@ -10307,7 +10307,7 @@
         <v>1408</v>
       </c>
       <c r="E63">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F63" t="s">
         <v>1569</v>
@@ -10342,7 +10342,7 @@
         <v>1409</v>
       </c>
       <c r="E64">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F64" t="s">
         <v>1569</v>
@@ -10377,7 +10377,7 @@
         <v>1409</v>
       </c>
       <c r="E65">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F65" t="s">
         <v>1569</v>
@@ -10412,7 +10412,7 @@
         <v>1409</v>
       </c>
       <c r="E66">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F66" t="s">
         <v>1569</v>
@@ -10447,7 +10447,7 @@
         <v>1410</v>
       </c>
       <c r="E67">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F67" t="s">
         <v>1569</v>
@@ -10482,7 +10482,7 @@
         <v>1411</v>
       </c>
       <c r="E68">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F68" t="s">
         <v>1569</v>
@@ -10517,7 +10517,7 @@
         <v>1412</v>
       </c>
       <c r="E69">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F69" t="s">
         <v>1569</v>
@@ -10552,7 +10552,7 @@
         <v>1412</v>
       </c>
       <c r="E70">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F70" t="s">
         <v>1569</v>
@@ -10587,7 +10587,7 @@
         <v>1412</v>
       </c>
       <c r="E71">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F71" t="s">
         <v>1569</v>
@@ -10622,7 +10622,7 @@
         <v>1413</v>
       </c>
       <c r="E72">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F72" t="s">
         <v>1569</v>
@@ -10657,7 +10657,7 @@
         <v>1414</v>
       </c>
       <c r="E73">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F73" t="s">
         <v>1569</v>
@@ -10692,7 +10692,7 @@
         <v>1414</v>
       </c>
       <c r="E74">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F74" t="s">
         <v>1569</v>
@@ -10727,7 +10727,7 @@
         <v>1414</v>
       </c>
       <c r="E75">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F75" t="s">
         <v>1570</v>
@@ -10762,7 +10762,7 @@
         <v>1414</v>
       </c>
       <c r="E76">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F76" t="s">
         <v>1569</v>
@@ -10797,7 +10797,7 @@
         <v>1415</v>
       </c>
       <c r="E77">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F77" t="s">
         <v>1569</v>
@@ -10832,7 +10832,7 @@
         <v>1416</v>
       </c>
       <c r="E78">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F78" t="s">
         <v>1569</v>
@@ -10867,7 +10867,7 @@
         <v>1416</v>
       </c>
       <c r="E79">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F79" t="s">
         <v>1569</v>
@@ -10902,7 +10902,7 @@
         <v>1417</v>
       </c>
       <c r="E80">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F80" t="s">
         <v>1569</v>
@@ -10937,7 +10937,7 @@
         <v>1418</v>
       </c>
       <c r="E81">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F81" t="s">
         <v>1569</v>
@@ -10972,7 +10972,7 @@
         <v>1419</v>
       </c>
       <c r="E82">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F82" t="s">
         <v>1569</v>
@@ -11007,7 +11007,7 @@
         <v>1420</v>
       </c>
       <c r="E83">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F83" t="s">
         <v>1569</v>
@@ -11042,7 +11042,7 @@
         <v>1420</v>
       </c>
       <c r="E84">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F84" t="s">
         <v>1569</v>
@@ -11077,7 +11077,7 @@
         <v>1420</v>
       </c>
       <c r="E85">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F85" t="s">
         <v>1569</v>
@@ -11112,7 +11112,7 @@
         <v>1420</v>
       </c>
       <c r="E86">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F86" t="s">
         <v>1569</v>
@@ -11147,7 +11147,7 @@
         <v>1420</v>
       </c>
       <c r="E87">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F87" t="s">
         <v>1569</v>
@@ -11182,7 +11182,7 @@
         <v>1420</v>
       </c>
       <c r="E88">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F88" t="s">
         <v>1569</v>
@@ -11217,7 +11217,7 @@
         <v>1421</v>
       </c>
       <c r="E89">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F89" t="s">
         <v>1569</v>
@@ -11252,7 +11252,7 @@
         <v>1422</v>
       </c>
       <c r="E90">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F90" t="s">
         <v>1569</v>
@@ -11287,7 +11287,7 @@
         <v>1423</v>
       </c>
       <c r="E91">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F91" t="s">
         <v>1569</v>
@@ -11322,7 +11322,7 @@
         <v>1423</v>
       </c>
       <c r="E92">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F92" t="s">
         <v>1569</v>
@@ -11357,7 +11357,7 @@
         <v>1424</v>
       </c>
       <c r="E93">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F93" t="s">
         <v>1571</v>
@@ -11392,7 +11392,7 @@
         <v>1425</v>
       </c>
       <c r="E94">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F94" t="s">
         <v>1569</v>
@@ -11427,7 +11427,7 @@
         <v>1426</v>
       </c>
       <c r="E95">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F95" t="s">
         <v>1569</v>
@@ -11462,7 +11462,7 @@
         <v>1426</v>
       </c>
       <c r="E96">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F96" t="s">
         <v>1569</v>
@@ -11497,7 +11497,7 @@
         <v>1427</v>
       </c>
       <c r="E97">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F97" t="s">
         <v>1569</v>
@@ -11532,7 +11532,7 @@
         <v>1428</v>
       </c>
       <c r="E98">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F98" t="s">
         <v>1569</v>
@@ -11567,7 +11567,7 @@
         <v>1429</v>
       </c>
       <c r="E99">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F99" t="s">
         <v>1569</v>
@@ -11602,7 +11602,7 @@
         <v>1430</v>
       </c>
       <c r="E100">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F100" t="s">
         <v>1569</v>
@@ -11637,7 +11637,7 @@
         <v>1431</v>
       </c>
       <c r="E101">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F101" t="s">
         <v>1569</v>
@@ -11672,7 +11672,7 @@
         <v>1431</v>
       </c>
       <c r="E102">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F102" t="s">
         <v>1569</v>
@@ -11707,7 +11707,7 @@
         <v>1432</v>
       </c>
       <c r="E103">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F103" t="s">
         <v>1569</v>
@@ -11742,7 +11742,7 @@
         <v>1432</v>
       </c>
       <c r="E104">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F104" t="s">
         <v>1569</v>
@@ -11777,7 +11777,7 @@
         <v>1432</v>
       </c>
       <c r="E105">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F105" t="s">
         <v>1569</v>
@@ -11812,7 +11812,7 @@
         <v>1433</v>
       </c>
       <c r="E106">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F106" t="s">
         <v>1569</v>
@@ -11847,7 +11847,7 @@
         <v>1433</v>
       </c>
       <c r="E107">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F107" t="s">
         <v>1569</v>
@@ -11882,7 +11882,7 @@
         <v>1433</v>
       </c>
       <c r="E108">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F108" t="s">
         <v>1569</v>
@@ -11917,7 +11917,7 @@
         <v>1433</v>
       </c>
       <c r="E109">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F109" t="s">
         <v>1569</v>
@@ -11952,7 +11952,7 @@
         <v>1434</v>
       </c>
       <c r="E110">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F110" t="s">
         <v>1569</v>
@@ -11987,7 +11987,7 @@
         <v>1435</v>
       </c>
       <c r="E111">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F111" t="s">
         <v>1569</v>
@@ -12022,7 +12022,7 @@
         <v>1435</v>
       </c>
       <c r="E112">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F112" t="s">
         <v>1569</v>
@@ -12057,7 +12057,7 @@
         <v>1436</v>
       </c>
       <c r="E113">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F113" t="s">
         <v>1569</v>
@@ -12092,7 +12092,7 @@
         <v>1436</v>
       </c>
       <c r="E114">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F114" t="s">
         <v>1569</v>
@@ -12127,7 +12127,7 @@
         <v>1436</v>
       </c>
       <c r="E115">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F115" t="s">
         <v>1569</v>
@@ -12162,7 +12162,7 @@
         <v>1437</v>
       </c>
       <c r="E116">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F116" t="s">
         <v>1569</v>
@@ -12197,7 +12197,7 @@
         <v>1437</v>
       </c>
       <c r="E117">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F117" t="s">
         <v>1569</v>
@@ -12232,7 +12232,7 @@
         <v>1438</v>
       </c>
       <c r="E118">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F118" t="s">
         <v>1569</v>
@@ -12267,7 +12267,7 @@
         <v>1438</v>
       </c>
       <c r="E119">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F119" t="s">
         <v>1569</v>
@@ -12302,7 +12302,7 @@
         <v>1439</v>
       </c>
       <c r="E120">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F120" t="s">
         <v>1569</v>
@@ -12337,7 +12337,7 @@
         <v>1439</v>
       </c>
       <c r="E121">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F121" t="s">
         <v>1569</v>
@@ -12372,7 +12372,7 @@
         <v>1440</v>
       </c>
       <c r="E122">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F122" t="s">
         <v>1569</v>
@@ -12407,7 +12407,7 @@
         <v>1441</v>
       </c>
       <c r="E123">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F123" t="s">
         <v>1569</v>
@@ -12442,7 +12442,7 @@
         <v>1441</v>
       </c>
       <c r="E124">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F124" t="s">
         <v>1569</v>
@@ -12477,7 +12477,7 @@
         <v>1442</v>
       </c>
       <c r="E125">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F125" t="s">
         <v>1569</v>
@@ -12512,7 +12512,7 @@
         <v>1443</v>
       </c>
       <c r="E126">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F126" t="s">
         <v>1569</v>
@@ -12550,7 +12550,7 @@
         <v>1443</v>
       </c>
       <c r="E127">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F127" t="s">
         <v>1569</v>
@@ -12585,7 +12585,7 @@
         <v>1443</v>
       </c>
       <c r="E128">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F128" t="s">
         <v>1569</v>
@@ -12620,7 +12620,7 @@
         <v>1443</v>
       </c>
       <c r="E129">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F129" t="s">
         <v>1569</v>
@@ -12655,7 +12655,7 @@
         <v>1444</v>
       </c>
       <c r="E130">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F130" t="s">
         <v>1569</v>
@@ -12690,7 +12690,7 @@
         <v>1445</v>
       </c>
       <c r="E131">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F131" t="s">
         <v>1570</v>
@@ -12725,7 +12725,7 @@
         <v>1446</v>
       </c>
       <c r="E132">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F132" t="s">
         <v>1569</v>
@@ -12760,7 +12760,7 @@
         <v>1446</v>
       </c>
       <c r="E133">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F133" t="s">
         <v>1569</v>
@@ -12795,7 +12795,7 @@
         <v>1446</v>
       </c>
       <c r="E134">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F134" t="s">
         <v>1569</v>
@@ -12830,7 +12830,7 @@
         <v>1446</v>
       </c>
       <c r="E135">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F135" t="s">
         <v>1569</v>
@@ -12865,7 +12865,7 @@
         <v>1447</v>
       </c>
       <c r="E136">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F136" t="s">
         <v>1569</v>
@@ -12900,7 +12900,7 @@
         <v>1447</v>
       </c>
       <c r="E137">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F137" t="s">
         <v>1569</v>
@@ -12935,7 +12935,7 @@
         <v>1447</v>
       </c>
       <c r="E138">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F138" t="s">
         <v>1569</v>
@@ -12970,7 +12970,7 @@
         <v>1447</v>
       </c>
       <c r="E139">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F139" t="s">
         <v>1569</v>
@@ -13005,7 +13005,7 @@
         <v>1447</v>
       </c>
       <c r="E140">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F140" t="s">
         <v>1569</v>
@@ -13040,7 +13040,7 @@
         <v>1447</v>
       </c>
       <c r="E141">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F141" t="s">
         <v>1569</v>
@@ -13075,7 +13075,7 @@
         <v>1447</v>
       </c>
       <c r="E142">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F142" t="s">
         <v>1569</v>
@@ -13110,7 +13110,7 @@
         <v>1448</v>
       </c>
       <c r="E143">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F143" t="s">
         <v>1569</v>
@@ -13145,7 +13145,7 @@
         <v>1448</v>
       </c>
       <c r="E144">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F144" t="s">
         <v>1569</v>
@@ -13180,7 +13180,7 @@
         <v>1449</v>
       </c>
       <c r="E145">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F145" t="s">
         <v>1569</v>
@@ -13215,7 +13215,7 @@
         <v>1450</v>
       </c>
       <c r="E146">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F146" t="s">
         <v>1569</v>
@@ -13250,7 +13250,7 @@
         <v>1450</v>
       </c>
       <c r="E147">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F147" t="s">
         <v>1569</v>
@@ -13285,7 +13285,7 @@
         <v>1450</v>
       </c>
       <c r="E148">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F148" t="s">
         <v>1569</v>
@@ -13320,7 +13320,7 @@
         <v>1451</v>
       </c>
       <c r="E149">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F149" t="s">
         <v>1569</v>
@@ -13355,7 +13355,7 @@
         <v>1451</v>
       </c>
       <c r="E150">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F150" t="s">
         <v>1569</v>
@@ -13390,7 +13390,7 @@
         <v>1451</v>
       </c>
       <c r="E151">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F151" t="s">
         <v>1569</v>
@@ -13425,7 +13425,7 @@
         <v>1451</v>
       </c>
       <c r="E152">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F152" t="s">
         <v>1569</v>
@@ -13460,7 +13460,7 @@
         <v>1451</v>
       </c>
       <c r="E153">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F153" t="s">
         <v>1569</v>
@@ -13495,7 +13495,7 @@
         <v>1451</v>
       </c>
       <c r="E154">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F154" t="s">
         <v>1569</v>
@@ -13530,7 +13530,7 @@
         <v>1451</v>
       </c>
       <c r="E155">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F155" t="s">
         <v>1569</v>
@@ -13565,7 +13565,7 @@
         <v>1451</v>
       </c>
       <c r="E156">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F156" t="s">
         <v>1569</v>
@@ -13600,7 +13600,7 @@
         <v>1451</v>
       </c>
       <c r="E157">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F157" t="s">
         <v>1569</v>
@@ -13635,7 +13635,7 @@
         <v>1451</v>
       </c>
       <c r="E158">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F158" t="s">
         <v>1569</v>
@@ -13670,7 +13670,7 @@
         <v>1452</v>
       </c>
       <c r="E159">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F159" t="s">
         <v>1569</v>
@@ -13705,7 +13705,7 @@
         <v>1452</v>
       </c>
       <c r="E160">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F160" t="s">
         <v>1569</v>
@@ -13740,7 +13740,7 @@
         <v>1452</v>
       </c>
       <c r="E161">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F161" t="s">
         <v>1569</v>
@@ -13775,7 +13775,7 @@
         <v>1453</v>
       </c>
       <c r="E162">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F162" t="s">
         <v>1569</v>
@@ -13810,7 +13810,7 @@
         <v>1453</v>
       </c>
       <c r="E163">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F163" t="s">
         <v>1570</v>
@@ -13845,7 +13845,7 @@
         <v>1453</v>
       </c>
       <c r="E164">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F164" t="s">
         <v>1569</v>
@@ -13880,7 +13880,7 @@
         <v>1454</v>
       </c>
       <c r="E165">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F165" t="s">
         <v>1569</v>
@@ -13915,7 +13915,7 @@
         <v>1454</v>
       </c>
       <c r="E166">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F166" t="s">
         <v>1569</v>
@@ -13950,7 +13950,7 @@
         <v>1455</v>
       </c>
       <c r="E167">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F167" t="s">
         <v>1569</v>
@@ -13985,7 +13985,7 @@
         <v>1455</v>
       </c>
       <c r="E168">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F168" t="s">
         <v>1569</v>
@@ -14020,7 +14020,7 @@
         <v>1456</v>
       </c>
       <c r="E169">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F169" t="s">
         <v>1569</v>
@@ -14055,7 +14055,7 @@
         <v>1456</v>
       </c>
       <c r="E170">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F170" t="s">
         <v>1569</v>
@@ -14090,7 +14090,7 @@
         <v>1457</v>
       </c>
       <c r="E171">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F171" t="s">
         <v>1569</v>
@@ -14125,7 +14125,7 @@
         <v>1457</v>
       </c>
       <c r="E172">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F172" t="s">
         <v>1569</v>
@@ -14160,7 +14160,7 @@
         <v>1457</v>
       </c>
       <c r="E173">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F173" t="s">
         <v>1569</v>
@@ -14195,7 +14195,7 @@
         <v>1457</v>
       </c>
       <c r="E174">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F174" t="s">
         <v>1569</v>
@@ -14230,7 +14230,7 @@
         <v>1458</v>
       </c>
       <c r="E175">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F175" t="s">
         <v>1569</v>
@@ -14265,7 +14265,7 @@
         <v>1458</v>
       </c>
       <c r="E176">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F176" t="s">
         <v>1569</v>
@@ -14300,7 +14300,7 @@
         <v>1459</v>
       </c>
       <c r="E177">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F177" t="s">
         <v>1569</v>
@@ -14335,7 +14335,7 @@
         <v>1460</v>
       </c>
       <c r="E178">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F178" t="s">
         <v>1569</v>
@@ -14370,7 +14370,7 @@
         <v>1460</v>
       </c>
       <c r="E179">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F179" t="s">
         <v>1569</v>
@@ -14405,7 +14405,7 @@
         <v>1460</v>
       </c>
       <c r="E180">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F180" t="s">
         <v>1569</v>
@@ -14440,7 +14440,7 @@
         <v>1460</v>
       </c>
       <c r="E181">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F181" t="s">
         <v>1569</v>
@@ -14475,7 +14475,7 @@
         <v>1461</v>
       </c>
       <c r="E182">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F182" t="s">
         <v>1569</v>
@@ -14510,7 +14510,7 @@
         <v>1462</v>
       </c>
       <c r="E183">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F183" t="s">
         <v>1569</v>
@@ -14545,7 +14545,7 @@
         <v>1462</v>
       </c>
       <c r="E184">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F184" t="s">
         <v>1569</v>
@@ -14580,7 +14580,7 @@
         <v>1462</v>
       </c>
       <c r="E185">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F185" t="s">
         <v>1569</v>
@@ -14615,7 +14615,7 @@
         <v>1462</v>
       </c>
       <c r="E186">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F186" t="s">
         <v>1569</v>
@@ -14650,7 +14650,7 @@
         <v>1462</v>
       </c>
       <c r="E187">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F187" t="s">
         <v>1569</v>
@@ -14685,7 +14685,7 @@
         <v>1463</v>
       </c>
       <c r="E188">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F188" t="s">
         <v>1569</v>
@@ -14720,7 +14720,7 @@
         <v>1463</v>
       </c>
       <c r="E189">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F189" t="s">
         <v>1569</v>
@@ -14755,7 +14755,7 @@
         <v>1463</v>
       </c>
       <c r="E190">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F190" t="s">
         <v>1569</v>
@@ -14790,7 +14790,7 @@
         <v>1463</v>
       </c>
       <c r="E191">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F191" t="s">
         <v>1569</v>
@@ -14825,7 +14825,7 @@
         <v>1463</v>
       </c>
       <c r="E192">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F192" t="s">
         <v>1569</v>
@@ -14860,7 +14860,7 @@
         <v>1463</v>
       </c>
       <c r="E193">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F193" t="s">
         <v>1569</v>
@@ -14895,7 +14895,7 @@
         <v>1463</v>
       </c>
       <c r="E194">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F194" t="s">
         <v>1569</v>
@@ -14930,7 +14930,7 @@
         <v>1464</v>
       </c>
       <c r="E195">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F195" t="s">
         <v>1569</v>
@@ -14965,7 +14965,7 @@
         <v>1464</v>
       </c>
       <c r="E196">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F196" t="s">
         <v>1569</v>
@@ -15000,7 +15000,7 @@
         <v>1464</v>
       </c>
       <c r="E197">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F197" t="s">
         <v>1569</v>
@@ -15035,7 +15035,7 @@
         <v>1464</v>
       </c>
       <c r="E198">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F198" t="s">
         <v>1569</v>
@@ -15070,7 +15070,7 @@
         <v>1465</v>
       </c>
       <c r="E199">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F199" t="s">
         <v>1569</v>
@@ -15105,7 +15105,7 @@
         <v>1465</v>
       </c>
       <c r="E200">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F200" t="s">
         <v>1569</v>
@@ -15140,7 +15140,7 @@
         <v>1466</v>
       </c>
       <c r="E201">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F201" t="s">
         <v>1569</v>
@@ -15175,7 +15175,7 @@
         <v>1466</v>
       </c>
       <c r="E202">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F202" t="s">
         <v>1569</v>
@@ -15210,7 +15210,7 @@
         <v>1467</v>
       </c>
       <c r="E203">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F203" t="s">
         <v>1569</v>
@@ -15245,7 +15245,7 @@
         <v>1467</v>
       </c>
       <c r="E204">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F204" t="s">
         <v>1569</v>
@@ -15280,7 +15280,7 @@
         <v>1468</v>
       </c>
       <c r="E205">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F205" t="s">
         <v>1569</v>
@@ -15315,7 +15315,7 @@
         <v>1469</v>
       </c>
       <c r="E206">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F206" t="s">
         <v>1569</v>
@@ -15350,7 +15350,7 @@
         <v>1469</v>
       </c>
       <c r="E207">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F207" t="s">
         <v>1569</v>
@@ -15385,7 +15385,7 @@
         <v>1470</v>
       </c>
       <c r="E208">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F208" t="s">
         <v>1569</v>
@@ -15420,7 +15420,7 @@
         <v>1470</v>
       </c>
       <c r="E209">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F209" t="s">
         <v>1569</v>
@@ -15455,7 +15455,7 @@
         <v>1471</v>
       </c>
       <c r="E210">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F210" t="s">
         <v>1569</v>
@@ -15490,7 +15490,7 @@
         <v>1472</v>
       </c>
       <c r="E211">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F211" t="s">
         <v>1569</v>
@@ -15525,7 +15525,7 @@
         <v>1472</v>
       </c>
       <c r="E212">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F212" t="s">
         <v>1569</v>
@@ -15560,7 +15560,7 @@
         <v>1472</v>
       </c>
       <c r="E213">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F213" t="s">
         <v>1569</v>
@@ -15595,7 +15595,7 @@
         <v>1473</v>
       </c>
       <c r="E214">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F214" t="s">
         <v>1569</v>
@@ -15630,7 +15630,7 @@
         <v>1473</v>
       </c>
       <c r="E215">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F215" t="s">
         <v>1569</v>
@@ -15665,7 +15665,7 @@
         <v>1474</v>
       </c>
       <c r="E216">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F216" t="s">
         <v>1569</v>
@@ -15700,7 +15700,7 @@
         <v>1475</v>
       </c>
       <c r="E217">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F217" t="s">
         <v>1569</v>
@@ -15735,7 +15735,7 @@
         <v>1475</v>
       </c>
       <c r="E218">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F218" t="s">
         <v>1569</v>
@@ -15770,7 +15770,7 @@
         <v>1475</v>
       </c>
       <c r="E219">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F219" t="s">
         <v>1569</v>
@@ -15805,7 +15805,7 @@
         <v>1476</v>
       </c>
       <c r="E220">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F220" t="s">
         <v>1569</v>
@@ -15840,7 +15840,7 @@
         <v>1476</v>
       </c>
       <c r="E221">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F221" t="s">
         <v>1569</v>
@@ -15875,7 +15875,7 @@
         <v>1477</v>
       </c>
       <c r="E222">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F222" t="s">
         <v>1569</v>
@@ -15910,7 +15910,7 @@
         <v>1477</v>
       </c>
       <c r="E223">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F223" t="s">
         <v>1569</v>
@@ -15945,7 +15945,7 @@
         <v>1477</v>
       </c>
       <c r="E224">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F224" t="s">
         <v>1571</v>
@@ -15980,7 +15980,7 @@
         <v>1477</v>
       </c>
       <c r="E225">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F225" t="s">
         <v>1569</v>
@@ -16015,7 +16015,7 @@
         <v>1478</v>
       </c>
       <c r="E226">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F226" t="s">
         <v>1569</v>
@@ -16050,7 +16050,7 @@
         <v>1478</v>
       </c>
       <c r="E227">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F227" t="s">
         <v>1569</v>
@@ -16088,7 +16088,7 @@
         <v>1478</v>
       </c>
       <c r="E228">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F228" t="s">
         <v>1569</v>
@@ -16123,7 +16123,7 @@
         <v>1478</v>
       </c>
       <c r="E229">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F229" t="s">
         <v>1569</v>
@@ -16158,7 +16158,7 @@
         <v>1478</v>
       </c>
       <c r="E230">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F230" t="s">
         <v>1569</v>
@@ -16193,7 +16193,7 @@
         <v>1478</v>
       </c>
       <c r="E231">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F231" t="s">
         <v>1569</v>
@@ -16228,7 +16228,7 @@
         <v>1479</v>
       </c>
       <c r="E232">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F232" t="s">
         <v>1569</v>
@@ -16263,7 +16263,7 @@
         <v>1479</v>
       </c>
       <c r="E233">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F233" t="s">
         <v>1569</v>
@@ -16298,7 +16298,7 @@
         <v>1479</v>
       </c>
       <c r="E234">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F234" t="s">
         <v>1569</v>
@@ -16333,7 +16333,7 @@
         <v>1480</v>
       </c>
       <c r="E235">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F235" t="s">
         <v>1569</v>
@@ -16368,7 +16368,7 @@
         <v>1480</v>
       </c>
       <c r="E236">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F236" t="s">
         <v>1569</v>
@@ -16403,7 +16403,7 @@
         <v>1480</v>
       </c>
       <c r="E237">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F237" t="s">
         <v>1569</v>
@@ -16438,7 +16438,7 @@
         <v>1480</v>
       </c>
       <c r="E238">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F238" t="s">
         <v>1569</v>
@@ -16473,7 +16473,7 @@
         <v>1481</v>
       </c>
       <c r="E239">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F239" t="s">
         <v>1569</v>
@@ -16508,7 +16508,7 @@
         <v>1481</v>
       </c>
       <c r="E240">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F240" t="s">
         <v>1569</v>
@@ -16543,7 +16543,7 @@
         <v>1481</v>
       </c>
       <c r="E241">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F241" t="s">
         <v>1569</v>
@@ -16578,7 +16578,7 @@
         <v>1481</v>
       </c>
       <c r="E242">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F242" t="s">
         <v>1569</v>
@@ -16613,7 +16613,7 @@
         <v>1482</v>
       </c>
       <c r="E243">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F243" t="s">
         <v>1569</v>
@@ -16648,7 +16648,7 @@
         <v>1482</v>
       </c>
       <c r="E244">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F244" t="s">
         <v>1569</v>
@@ -16683,7 +16683,7 @@
         <v>1482</v>
       </c>
       <c r="E245">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F245" t="s">
         <v>1569</v>
@@ -16718,7 +16718,7 @@
         <v>1482</v>
       </c>
       <c r="E246">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F246" t="s">
         <v>1569</v>
@@ -16753,7 +16753,7 @@
         <v>1482</v>
       </c>
       <c r="E247">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F247" t="s">
         <v>1569</v>
@@ -16788,7 +16788,7 @@
         <v>1482</v>
       </c>
       <c r="E248">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F248" t="s">
         <v>1569</v>
@@ -16823,7 +16823,7 @@
         <v>1483</v>
       </c>
       <c r="E249">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F249" t="s">
         <v>1569</v>
@@ -16858,7 +16858,7 @@
         <v>1484</v>
       </c>
       <c r="E250">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F250" t="s">
         <v>1570</v>
@@ -16893,7 +16893,7 @@
         <v>1484</v>
       </c>
       <c r="E251">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F251" t="s">
         <v>1569</v>
@@ -16928,7 +16928,7 @@
         <v>1484</v>
       </c>
       <c r="E252">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F252" t="s">
         <v>1572</v>
@@ -16963,7 +16963,7 @@
         <v>1484</v>
       </c>
       <c r="E253">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F253" t="s">
         <v>1569</v>
@@ -16998,7 +16998,7 @@
         <v>1484</v>
       </c>
       <c r="E254">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F254" t="s">
         <v>1569</v>
@@ -17033,7 +17033,7 @@
         <v>1484</v>
       </c>
       <c r="E255">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F255" t="s">
         <v>1569</v>
@@ -17068,7 +17068,7 @@
         <v>1485</v>
       </c>
       <c r="E256">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F256" t="s">
         <v>1569</v>
@@ -17103,7 +17103,7 @@
         <v>1485</v>
       </c>
       <c r="E257">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F257" t="s">
         <v>1569</v>
@@ -17138,7 +17138,7 @@
         <v>1485</v>
       </c>
       <c r="E258">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F258" t="s">
         <v>1569</v>
@@ -17173,7 +17173,7 @@
         <v>1485</v>
       </c>
       <c r="E259">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F259" t="s">
         <v>1569</v>
@@ -17208,7 +17208,7 @@
         <v>1486</v>
       </c>
       <c r="E260">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F260" t="s">
         <v>1569</v>
@@ -17243,7 +17243,7 @@
         <v>1487</v>
       </c>
       <c r="E261">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F261" t="s">
         <v>1569</v>
@@ -17281,7 +17281,7 @@
         <v>1488</v>
       </c>
       <c r="E262">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F262" t="s">
         <v>1569</v>
@@ -17316,7 +17316,7 @@
         <v>1488</v>
       </c>
       <c r="E263">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F263" t="s">
         <v>1569</v>
@@ -17351,7 +17351,7 @@
         <v>1488</v>
       </c>
       <c r="E264">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F264" t="s">
         <v>1569</v>
@@ -17386,7 +17386,7 @@
         <v>1488</v>
       </c>
       <c r="E265">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F265" t="s">
         <v>1569</v>
@@ -17424,7 +17424,7 @@
         <v>1488</v>
       </c>
       <c r="E266">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F266" t="s">
         <v>1569</v>
@@ -17459,7 +17459,7 @@
         <v>1489</v>
       </c>
       <c r="E267">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F267" t="s">
         <v>1569</v>
@@ -17494,7 +17494,7 @@
         <v>1489</v>
       </c>
       <c r="E268">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F268" t="s">
         <v>1569</v>
@@ -17529,7 +17529,7 @@
         <v>1490</v>
       </c>
       <c r="E269">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F269" t="s">
         <v>1569</v>
@@ -17564,7 +17564,7 @@
         <v>1490</v>
       </c>
       <c r="E270">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F270" t="s">
         <v>1569</v>
@@ -17599,7 +17599,7 @@
         <v>1491</v>
       </c>
       <c r="E271">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F271" t="s">
         <v>1569</v>
@@ -17634,7 +17634,7 @@
         <v>1491</v>
       </c>
       <c r="E272">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F272" t="s">
         <v>1569</v>
@@ -17669,7 +17669,7 @@
         <v>1491</v>
       </c>
       <c r="E273">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F273" t="s">
         <v>1569</v>
@@ -17704,7 +17704,7 @@
         <v>1492</v>
       </c>
       <c r="E274">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F274" t="s">
         <v>1569</v>
@@ -17739,7 +17739,7 @@
         <v>1492</v>
       </c>
       <c r="E275">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F275" t="s">
         <v>1569</v>
@@ -17774,7 +17774,7 @@
         <v>1492</v>
       </c>
       <c r="E276">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F276" t="s">
         <v>1569</v>
@@ -17809,7 +17809,7 @@
         <v>1492</v>
       </c>
       <c r="E277">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F277" t="s">
         <v>1569</v>
@@ -17844,7 +17844,7 @@
         <v>1493</v>
       </c>
       <c r="E278">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F278" t="s">
         <v>1569</v>
@@ -17879,7 +17879,7 @@
         <v>1494</v>
       </c>
       <c r="E279">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F279" t="s">
         <v>1569</v>
@@ -17914,7 +17914,7 @@
         <v>1494</v>
       </c>
       <c r="E280">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F280" t="s">
         <v>1569</v>
@@ -17949,7 +17949,7 @@
         <v>1494</v>
       </c>
       <c r="E281">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F281" t="s">
         <v>1569</v>
@@ -17984,7 +17984,7 @@
         <v>1494</v>
       </c>
       <c r="E282">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F282" t="s">
         <v>1569</v>
@@ -18019,7 +18019,7 @@
         <v>1495</v>
       </c>
       <c r="E283">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F283" t="s">
         <v>1569</v>
@@ -18054,7 +18054,7 @@
         <v>1495</v>
       </c>
       <c r="E284">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F284" t="s">
         <v>1569</v>
@@ -18089,7 +18089,7 @@
         <v>1495</v>
       </c>
       <c r="E285">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F285" t="s">
         <v>1569</v>
@@ -18124,7 +18124,7 @@
         <v>1496</v>
       </c>
       <c r="E286">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F286" t="s">
         <v>1569</v>
@@ -18159,7 +18159,7 @@
         <v>1496</v>
       </c>
       <c r="E287">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F287" t="s">
         <v>1569</v>
@@ -18194,7 +18194,7 @@
         <v>1497</v>
       </c>
       <c r="E288">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F288" t="s">
         <v>1569</v>
@@ -18229,7 +18229,7 @@
         <v>1497</v>
       </c>
       <c r="E289">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F289" t="s">
         <v>1569</v>
@@ -18264,7 +18264,7 @@
         <v>1497</v>
       </c>
       <c r="E290">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F290" t="s">
         <v>1569</v>
@@ -18299,7 +18299,7 @@
         <v>1497</v>
       </c>
       <c r="E291">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F291" t="s">
         <v>1569</v>
@@ -18334,7 +18334,7 @@
         <v>1497</v>
       </c>
       <c r="E292">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F292" t="s">
         <v>1569</v>
@@ -18369,7 +18369,7 @@
         <v>1498</v>
       </c>
       <c r="E293">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F293" t="s">
         <v>1569</v>
@@ -18404,7 +18404,7 @@
         <v>1498</v>
       </c>
       <c r="E294">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F294" t="s">
         <v>1569</v>
@@ -18439,7 +18439,7 @@
         <v>1498</v>
       </c>
       <c r="E295">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F295" t="s">
         <v>1569</v>
@@ -18474,7 +18474,7 @@
         <v>1499</v>
       </c>
       <c r="E296">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F296" t="s">
         <v>1569</v>
@@ -18509,7 +18509,7 @@
         <v>1500</v>
       </c>
       <c r="E297">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F297" t="s">
         <v>1569</v>
@@ -18544,7 +18544,7 @@
         <v>1501</v>
       </c>
       <c r="E298">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F298" t="s">
         <v>1569</v>
@@ -18579,7 +18579,7 @@
         <v>1501</v>
       </c>
       <c r="E299">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F299" t="s">
         <v>1569</v>
@@ -18614,7 +18614,7 @@
         <v>1501</v>
       </c>
       <c r="E300">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F300" t="s">
         <v>1569</v>
@@ -18649,7 +18649,7 @@
         <v>1501</v>
       </c>
       <c r="E301">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F301" t="s">
         <v>1569</v>
@@ -18684,7 +18684,7 @@
         <v>1501</v>
       </c>
       <c r="E302">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F302" t="s">
         <v>1569</v>
@@ -18719,7 +18719,7 @@
         <v>1502</v>
       </c>
       <c r="E303">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F303" t="s">
         <v>1569</v>
@@ -18754,7 +18754,7 @@
         <v>1502</v>
       </c>
       <c r="E304">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F304" t="s">
         <v>1569</v>
@@ -18789,7 +18789,7 @@
         <v>1503</v>
       </c>
       <c r="E305">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F305" t="s">
         <v>1569</v>
@@ -18824,7 +18824,7 @@
         <v>1503</v>
       </c>
       <c r="E306">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F306" t="s">
         <v>1569</v>
@@ -18859,7 +18859,7 @@
         <v>1504</v>
       </c>
       <c r="E307">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F307" t="s">
         <v>1569</v>
@@ -18894,7 +18894,7 @@
         <v>1505</v>
       </c>
       <c r="E308">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F308" t="s">
         <v>1569</v>
@@ -18929,7 +18929,7 @@
         <v>1506</v>
       </c>
       <c r="E309">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F309" t="s">
         <v>1569</v>
@@ -18964,7 +18964,7 @@
         <v>1506</v>
       </c>
       <c r="E310">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F310" t="s">
         <v>1569</v>
@@ -18999,7 +18999,7 @@
         <v>1507</v>
       </c>
       <c r="E311">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F311" t="s">
         <v>1569</v>
@@ -19034,7 +19034,7 @@
         <v>1507</v>
       </c>
       <c r="E312">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F312" t="s">
         <v>1569</v>
@@ -19069,7 +19069,7 @@
         <v>1507</v>
       </c>
       <c r="E313">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F313" t="s">
         <v>1569</v>
@@ -19104,7 +19104,7 @@
         <v>1508</v>
       </c>
       <c r="E314">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F314" t="s">
         <v>1569</v>
@@ -19139,7 +19139,7 @@
         <v>1508</v>
       </c>
       <c r="E315">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F315" t="s">
         <v>1569</v>
@@ -19174,7 +19174,7 @@
         <v>1508</v>
       </c>
       <c r="E316">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F316" t="s">
         <v>1569</v>
@@ -19209,7 +19209,7 @@
         <v>1508</v>
       </c>
       <c r="E317">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F317" t="s">
         <v>1569</v>
@@ -19244,7 +19244,7 @@
         <v>1508</v>
       </c>
       <c r="E318">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F318" t="s">
         <v>1569</v>
@@ -19279,7 +19279,7 @@
         <v>1508</v>
       </c>
       <c r="E319">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F319" t="s">
         <v>1569</v>
@@ -19314,7 +19314,7 @@
         <v>1508</v>
       </c>
       <c r="E320">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F320" t="s">
         <v>1569</v>
@@ -19349,7 +19349,7 @@
         <v>1508</v>
       </c>
       <c r="E321">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F321" t="s">
         <v>1569</v>
@@ -19384,7 +19384,7 @@
         <v>1508</v>
       </c>
       <c r="E322">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F322" t="s">
         <v>1569</v>
@@ -19419,7 +19419,7 @@
         <v>1509</v>
       </c>
       <c r="E323">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F323" t="s">
         <v>1569</v>
@@ -19454,7 +19454,7 @@
         <v>1509</v>
       </c>
       <c r="E324">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F324" t="s">
         <v>1569</v>
@@ -19489,7 +19489,7 @@
         <v>1509</v>
       </c>
       <c r="E325">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F325" t="s">
         <v>1569</v>
@@ -19524,7 +19524,7 @@
         <v>1510</v>
       </c>
       <c r="E326">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F326" t="s">
         <v>1569</v>
@@ -19559,7 +19559,7 @@
         <v>1511</v>
       </c>
       <c r="E327">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F327" t="s">
         <v>1569</v>
@@ -19594,7 +19594,7 @@
         <v>1511</v>
       </c>
       <c r="E328">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F328" t="s">
         <v>1569</v>
@@ -19629,7 +19629,7 @@
         <v>1511</v>
       </c>
       <c r="E329">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F329" t="s">
         <v>1569</v>
@@ -19664,7 +19664,7 @@
         <v>1511</v>
       </c>
       <c r="E330">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F330" t="s">
         <v>1569</v>
@@ -19699,7 +19699,7 @@
         <v>1511</v>
       </c>
       <c r="E331">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F331" t="s">
         <v>1573</v>
@@ -19737,7 +19737,7 @@
         <v>1511</v>
       </c>
       <c r="E332">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F332" t="s">
         <v>1569</v>
@@ -19772,7 +19772,7 @@
         <v>1511</v>
       </c>
       <c r="E333">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F333" t="s">
         <v>1569</v>
@@ -19807,7 +19807,7 @@
         <v>1512</v>
       </c>
       <c r="E334">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F334" t="s">
         <v>1569</v>
@@ -19842,7 +19842,7 @@
         <v>1512</v>
       </c>
       <c r="E335">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F335" t="s">
         <v>1569</v>
@@ -19877,7 +19877,7 @@
         <v>1512</v>
       </c>
       <c r="E336">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F336" t="s">
         <v>1569</v>
@@ -19912,7 +19912,7 @@
         <v>1512</v>
       </c>
       <c r="E337">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F337" t="s">
         <v>1569</v>
@@ -19950,7 +19950,7 @@
         <v>1512</v>
       </c>
       <c r="E338">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F338" t="s">
         <v>1569</v>
@@ -19985,7 +19985,7 @@
         <v>1512</v>
       </c>
       <c r="E339">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F339" t="s">
         <v>1569</v>
@@ -20020,7 +20020,7 @@
         <v>1512</v>
       </c>
       <c r="E340">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F340" t="s">
         <v>1569</v>
@@ -20055,7 +20055,7 @@
         <v>1512</v>
       </c>
       <c r="E341">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F341" t="s">
         <v>1569</v>
@@ -20090,7 +20090,7 @@
         <v>1512</v>
       </c>
       <c r="E342">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F342" t="s">
         <v>1569</v>
@@ -20125,7 +20125,7 @@
         <v>1513</v>
       </c>
       <c r="E343">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F343" t="s">
         <v>1570</v>
@@ -20160,7 +20160,7 @@
         <v>1514</v>
       </c>
       <c r="E344">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F344" t="s">
         <v>1573</v>
@@ -20195,7 +20195,7 @@
         <v>1515</v>
       </c>
       <c r="E345">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F345" t="s">
         <v>1569</v>
@@ -20230,7 +20230,7 @@
         <v>1516</v>
       </c>
       <c r="E346">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F346" t="s">
         <v>1569</v>
@@ -20265,7 +20265,7 @@
         <v>1516</v>
       </c>
       <c r="E347">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F347" t="s">
         <v>1569</v>
@@ -20300,7 +20300,7 @@
         <v>1517</v>
       </c>
       <c r="E348">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F348" t="s">
         <v>1569</v>
@@ -20335,7 +20335,7 @@
         <v>1518</v>
       </c>
       <c r="E349">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F349" t="s">
         <v>1572</v>
@@ -20370,7 +20370,7 @@
         <v>1518</v>
       </c>
       <c r="E350">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F350" t="s">
         <v>1569</v>
@@ -20405,7 +20405,7 @@
         <v>1518</v>
       </c>
       <c r="E351">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F351" t="s">
         <v>1569</v>
@@ -20440,7 +20440,7 @@
         <v>1518</v>
       </c>
       <c r="E352">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F352" t="s">
         <v>1569</v>
@@ -20475,7 +20475,7 @@
         <v>1518</v>
       </c>
       <c r="E353">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F353" t="s">
         <v>1569</v>
@@ -20510,7 +20510,7 @@
         <v>1518</v>
       </c>
       <c r="E354">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F354" t="s">
         <v>1569</v>
@@ -20545,7 +20545,7 @@
         <v>1519</v>
       </c>
       <c r="E355">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F355" t="s">
         <v>1569</v>
@@ -20580,7 +20580,7 @@
         <v>1519</v>
       </c>
       <c r="E356">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F356" t="s">
         <v>1569</v>
@@ -20615,7 +20615,7 @@
         <v>1519</v>
       </c>
       <c r="E357">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F357" t="s">
         <v>1569</v>
@@ -20650,7 +20650,7 @@
         <v>1520</v>
       </c>
       <c r="E358">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F358" t="s">
         <v>1569</v>
@@ -20685,7 +20685,7 @@
         <v>1520</v>
       </c>
       <c r="E359">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F359" t="s">
         <v>1569</v>
@@ -20720,7 +20720,7 @@
         <v>1520</v>
       </c>
       <c r="E360">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F360" t="s">
         <v>1569</v>
@@ -20758,7 +20758,7 @@
         <v>1520</v>
       </c>
       <c r="E361">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F361" t="s">
         <v>1569</v>
@@ -20793,7 +20793,7 @@
         <v>1521</v>
       </c>
       <c r="E362">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F362" t="s">
         <v>1569</v>
@@ -20828,7 +20828,7 @@
         <v>1521</v>
       </c>
       <c r="E363">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F363" t="s">
         <v>1569</v>
@@ -20863,7 +20863,7 @@
         <v>1521</v>
       </c>
       <c r="E364">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F364" t="s">
         <v>1569</v>
@@ -20898,7 +20898,7 @@
         <v>1521</v>
       </c>
       <c r="E365">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F365" t="s">
         <v>1569</v>
@@ -20933,7 +20933,7 @@
         <v>1521</v>
       </c>
       <c r="E366">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F366" t="s">
         <v>1569</v>
@@ -20968,7 +20968,7 @@
         <v>1522</v>
       </c>
       <c r="E367">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F367" t="s">
         <v>1569</v>
@@ -21003,7 +21003,7 @@
         <v>1522</v>
       </c>
       <c r="E368">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F368" t="s">
         <v>1569</v>
@@ -21038,7 +21038,7 @@
         <v>1523</v>
       </c>
       <c r="E369">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F369" t="s">
         <v>1569</v>
@@ -21073,7 +21073,7 @@
         <v>1523</v>
       </c>
       <c r="E370">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F370" t="s">
         <v>1569</v>
@@ -21108,7 +21108,7 @@
         <v>1523</v>
       </c>
       <c r="E371">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F371" t="s">
         <v>1569</v>
@@ -21143,7 +21143,7 @@
         <v>1523</v>
       </c>
       <c r="E372">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F372" t="s">
         <v>1569</v>
@@ -21178,7 +21178,7 @@
         <v>1523</v>
       </c>
       <c r="E373">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F373" t="s">
         <v>1569</v>
@@ -21213,7 +21213,7 @@
         <v>1523</v>
       </c>
       <c r="E374">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F374" t="s">
         <v>1569</v>
@@ -21248,7 +21248,7 @@
         <v>1523</v>
       </c>
       <c r="E375">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F375" t="s">
         <v>1569</v>
@@ -21283,7 +21283,7 @@
         <v>1523</v>
       </c>
       <c r="E376">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F376" t="s">
         <v>1569</v>
@@ -21318,7 +21318,7 @@
         <v>1523</v>
       </c>
       <c r="E377">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F377" t="s">
         <v>1569</v>
@@ -21353,7 +21353,7 @@
         <v>1523</v>
       </c>
       <c r="E378">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F378" t="s">
         <v>1569</v>
@@ -21388,7 +21388,7 @@
         <v>1524</v>
       </c>
       <c r="E379">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F379" t="s">
         <v>1569</v>
@@ -21423,7 +21423,7 @@
         <v>1524</v>
       </c>
       <c r="E380">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F380" t="s">
         <v>1569</v>
@@ -21458,7 +21458,7 @@
         <v>1524</v>
       </c>
       <c r="E381">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F381" t="s">
         <v>1570</v>
@@ -21493,7 +21493,7 @@
         <v>1525</v>
       </c>
       <c r="E382">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F382" t="s">
         <v>1569</v>
@@ -21528,7 +21528,7 @@
         <v>1525</v>
       </c>
       <c r="E383">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F383" t="s">
         <v>1569</v>
@@ -21563,7 +21563,7 @@
         <v>1525</v>
       </c>
       <c r="E384">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F384" t="s">
         <v>1569</v>
@@ -21598,7 +21598,7 @@
         <v>1525</v>
       </c>
       <c r="E385">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F385" t="s">
         <v>1569</v>
@@ -21633,7 +21633,7 @@
         <v>1525</v>
       </c>
       <c r="E386">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F386" t="s">
         <v>1569</v>
@@ -21668,7 +21668,7 @@
         <v>1525</v>
       </c>
       <c r="E387">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F387" t="s">
         <v>1569</v>
@@ -21703,7 +21703,7 @@
         <v>1525</v>
       </c>
       <c r="E388">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F388" t="s">
         <v>1572</v>
@@ -21738,7 +21738,7 @@
         <v>1526</v>
       </c>
       <c r="E389">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F389" t="s">
         <v>1569</v>
@@ -21773,7 +21773,7 @@
         <v>1526</v>
       </c>
       <c r="E390">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F390" t="s">
         <v>1569</v>
@@ -21808,7 +21808,7 @@
         <v>1526</v>
       </c>
       <c r="E391">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F391" t="s">
         <v>1569</v>
@@ -21843,7 +21843,7 @@
         <v>1526</v>
       </c>
       <c r="E392">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F392" t="s">
         <v>1569</v>
@@ -21878,7 +21878,7 @@
         <v>1527</v>
       </c>
       <c r="E393">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F393" t="s">
         <v>1572</v>
@@ -21913,7 +21913,7 @@
         <v>1527</v>
       </c>
       <c r="E394">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F394" t="s">
         <v>1569</v>
@@ -21948,7 +21948,7 @@
         <v>1527</v>
       </c>
       <c r="E395">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F395" t="s">
         <v>1569</v>
@@ -21983,7 +21983,7 @@
         <v>1527</v>
       </c>
       <c r="E396">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F396" t="s">
         <v>1569</v>
@@ -22018,7 +22018,7 @@
         <v>1527</v>
       </c>
       <c r="E397">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F397" t="s">
         <v>1569</v>
@@ -22053,7 +22053,7 @@
         <v>1527</v>
       </c>
       <c r="E398">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F398" t="s">
         <v>1569</v>
@@ -22088,7 +22088,7 @@
         <v>1528</v>
       </c>
       <c r="E399">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F399" t="s">
         <v>1569</v>
@@ -22123,7 +22123,7 @@
         <v>1528</v>
       </c>
       <c r="E400">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F400" t="s">
         <v>1569</v>
@@ -22158,7 +22158,7 @@
         <v>1528</v>
       </c>
       <c r="E401">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F401" t="s">
         <v>1569</v>
@@ -22193,7 +22193,7 @@
         <v>1528</v>
       </c>
       <c r="E402">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F402" t="s">
         <v>1569</v>
@@ -22228,7 +22228,7 @@
         <v>1528</v>
       </c>
       <c r="E403">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F403" t="s">
         <v>1571</v>
@@ -22263,7 +22263,7 @@
         <v>1528</v>
       </c>
       <c r="E404">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F404" t="s">
         <v>1569</v>
@@ -22298,7 +22298,7 @@
         <v>1528</v>
       </c>
       <c r="E405">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F405" t="s">
         <v>1569</v>
@@ -22333,7 +22333,7 @@
         <v>1529</v>
       </c>
       <c r="E406">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F406" t="s">
         <v>1569</v>
@@ -22368,7 +22368,7 @@
         <v>1529</v>
       </c>
       <c r="E407">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F407" t="s">
         <v>1569</v>
@@ -22403,7 +22403,7 @@
         <v>1529</v>
       </c>
       <c r="E408">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F408" t="s">
         <v>1569</v>
@@ -22438,7 +22438,7 @@
         <v>1529</v>
       </c>
       <c r="E409">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F409" t="s">
         <v>1569</v>
@@ -22473,7 +22473,7 @@
         <v>1529</v>
       </c>
       <c r="E410">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F410" t="s">
         <v>1569</v>
@@ -22508,7 +22508,7 @@
         <v>1530</v>
       </c>
       <c r="E411">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F411" t="s">
         <v>1569</v>
@@ -22543,7 +22543,7 @@
         <v>1530</v>
       </c>
       <c r="E412">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F412" t="s">
         <v>1569</v>
@@ -22578,7 +22578,7 @@
         <v>1530</v>
       </c>
       <c r="E413">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F413" t="s">
         <v>1569</v>
@@ -22613,7 +22613,7 @@
         <v>1530</v>
       </c>
       <c r="E414">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F414" t="s">
         <v>1569</v>
@@ -22648,7 +22648,7 @@
         <v>1530</v>
       </c>
       <c r="E415">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F415" t="s">
         <v>1569</v>
@@ -22686,7 +22686,7 @@
         <v>1531</v>
       </c>
       <c r="E416">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F416" t="s">
         <v>1569</v>
@@ -22721,7 +22721,7 @@
         <v>1531</v>
       </c>
       <c r="E417">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F417" t="s">
         <v>1569</v>
@@ -22756,7 +22756,7 @@
         <v>1531</v>
       </c>
       <c r="E418">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F418" t="s">
         <v>1569</v>
@@ -22791,7 +22791,7 @@
         <v>1531</v>
       </c>
       <c r="E419">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F419" t="s">
         <v>1569</v>
@@ -22826,7 +22826,7 @@
         <v>1531</v>
       </c>
       <c r="E420">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F420" t="s">
         <v>1569</v>
@@ -22861,7 +22861,7 @@
         <v>1531</v>
       </c>
       <c r="E421">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F421" t="s">
         <v>1569</v>
@@ -22896,7 +22896,7 @@
         <v>1532</v>
       </c>
       <c r="E422">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F422" t="s">
         <v>1570</v>
@@ -22931,7 +22931,7 @@
         <v>1532</v>
       </c>
       <c r="E423">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F423" t="s">
         <v>1569</v>
@@ -22966,7 +22966,7 @@
         <v>1533</v>
       </c>
       <c r="E424">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F424" t="s">
         <v>1569</v>
@@ -23001,7 +23001,7 @@
         <v>1534</v>
       </c>
       <c r="E425">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F425" t="s">
         <v>1569</v>
@@ -23036,7 +23036,7 @@
         <v>1534</v>
       </c>
       <c r="E426">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F426" t="s">
         <v>1569</v>
@@ -23071,7 +23071,7 @@
         <v>1534</v>
       </c>
       <c r="E427">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F427" t="s">
         <v>1571</v>
@@ -23109,7 +23109,7 @@
         <v>1534</v>
       </c>
       <c r="E428">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F428" t="s">
         <v>1569</v>
@@ -23144,7 +23144,7 @@
         <v>1535</v>
       </c>
       <c r="E429">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F429" t="s">
         <v>1569</v>
@@ -23179,7 +23179,7 @@
         <v>1535</v>
       </c>
       <c r="E430">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F430" t="s">
         <v>1569</v>
@@ -23214,7 +23214,7 @@
         <v>1535</v>
       </c>
       <c r="E431">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F431" t="s">
         <v>1569</v>
@@ -23249,7 +23249,7 @@
         <v>1535</v>
       </c>
       <c r="E432">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F432" t="s">
         <v>1569</v>
@@ -23284,7 +23284,7 @@
         <v>1536</v>
       </c>
       <c r="E433">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F433" t="s">
         <v>1569</v>
@@ -23319,7 +23319,7 @@
         <v>1536</v>
       </c>
       <c r="E434">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F434" t="s">
         <v>1569</v>
@@ -23354,7 +23354,7 @@
         <v>1536</v>
       </c>
       <c r="E435">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F435" t="s">
         <v>1569</v>
@@ -23389,7 +23389,7 @@
         <v>1536</v>
       </c>
       <c r="E436">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F436" t="s">
         <v>1569</v>
@@ -23424,7 +23424,7 @@
         <v>1536</v>
       </c>
       <c r="E437">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F437" t="s">
         <v>1569</v>
@@ -23459,7 +23459,7 @@
         <v>1536</v>
       </c>
       <c r="E438">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F438" t="s">
         <v>1569</v>
@@ -23494,7 +23494,7 @@
         <v>1536</v>
       </c>
       <c r="E439">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F439" t="s">
         <v>1569</v>
@@ -23529,7 +23529,7 @@
         <v>1536</v>
       </c>
       <c r="E440">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F440" t="s">
         <v>1569</v>
@@ -23564,7 +23564,7 @@
         <v>1537</v>
       </c>
       <c r="E441">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F441" t="s">
         <v>1569</v>
@@ -23599,7 +23599,7 @@
         <v>1537</v>
       </c>
       <c r="E442">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F442" t="s">
         <v>1569</v>
@@ -23634,7 +23634,7 @@
         <v>1538</v>
       </c>
       <c r="E443">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F443" t="s">
         <v>1569</v>
@@ -23669,7 +23669,7 @@
         <v>1538</v>
       </c>
       <c r="E444">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F444" t="s">
         <v>1569</v>
@@ -23704,7 +23704,7 @@
         <v>1538</v>
       </c>
       <c r="E445">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F445" t="s">
         <v>1569</v>
@@ -23739,7 +23739,7 @@
         <v>1538</v>
       </c>
       <c r="E446">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F446" t="s">
         <v>1573</v>
@@ -23777,7 +23777,7 @@
         <v>1538</v>
       </c>
       <c r="E447">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F447" t="s">
         <v>1569</v>
@@ -23812,7 +23812,7 @@
         <v>1538</v>
       </c>
       <c r="E448">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F448" t="s">
         <v>1573</v>
@@ -23847,7 +23847,7 @@
         <v>1539</v>
       </c>
       <c r="E449">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F449" t="s">
         <v>1569</v>
@@ -23882,7 +23882,7 @@
         <v>1540</v>
       </c>
       <c r="E450">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F450" t="s">
         <v>1569</v>
@@ -23917,7 +23917,7 @@
         <v>1540</v>
       </c>
       <c r="E451">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F451" t="s">
         <v>1569</v>
@@ -23952,7 +23952,7 @@
         <v>1540</v>
       </c>
       <c r="E452">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F452" t="s">
         <v>1569</v>
@@ -23987,7 +23987,7 @@
         <v>1540</v>
       </c>
       <c r="E453">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F453" t="s">
         <v>1569</v>
@@ -24022,7 +24022,7 @@
         <v>1541</v>
       </c>
       <c r="E454">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F454" t="s">
         <v>1569</v>
@@ -24057,7 +24057,7 @@
         <v>1541</v>
       </c>
       <c r="E455">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F455" t="s">
         <v>1573</v>
@@ -24092,7 +24092,7 @@
         <v>1541</v>
       </c>
       <c r="E456">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F456" t="s">
         <v>1569</v>
@@ -24127,7 +24127,7 @@
         <v>1541</v>
       </c>
       <c r="E457">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F457" t="s">
         <v>1569</v>
@@ -24162,7 +24162,7 @@
         <v>1541</v>
       </c>
       <c r="E458">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F458" t="s">
         <v>1569</v>
@@ -24197,7 +24197,7 @@
         <v>1542</v>
       </c>
       <c r="E459">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F459" t="s">
         <v>1569</v>
@@ -24232,7 +24232,7 @@
         <v>1542</v>
       </c>
       <c r="E460">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F460" t="s">
         <v>1569</v>
@@ -24267,7 +24267,7 @@
         <v>1542</v>
       </c>
       <c r="E461">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F461" t="s">
         <v>1569</v>
@@ -24302,7 +24302,7 @@
         <v>1543</v>
       </c>
       <c r="E462">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F462" t="s">
         <v>1569</v>
@@ -24337,7 +24337,7 @@
         <v>1543</v>
       </c>
       <c r="E463">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F463" t="s">
         <v>1569</v>
@@ -24372,7 +24372,7 @@
         <v>1543</v>
       </c>
       <c r="E464">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F464" t="s">
         <v>1569</v>
@@ -24407,7 +24407,7 @@
         <v>1543</v>
       </c>
       <c r="E465">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F465" t="s">
         <v>1569</v>
@@ -24442,7 +24442,7 @@
         <v>1543</v>
       </c>
       <c r="E466">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F466" t="s">
         <v>1569</v>
@@ -24477,7 +24477,7 @@
         <v>1543</v>
       </c>
       <c r="E467">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F467" t="s">
         <v>1569</v>
@@ -24512,7 +24512,7 @@
         <v>1544</v>
       </c>
       <c r="E468">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F468" t="s">
         <v>1569</v>
@@ -24547,7 +24547,7 @@
         <v>1544</v>
       </c>
       <c r="E469">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F469" t="s">
         <v>1569</v>
@@ -24582,7 +24582,7 @@
         <v>1544</v>
       </c>
       <c r="E470">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F470" t="s">
         <v>1569</v>
@@ -24617,7 +24617,7 @@
         <v>1544</v>
       </c>
       <c r="E471">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F471" t="s">
         <v>1569</v>
@@ -24652,7 +24652,7 @@
         <v>1544</v>
       </c>
       <c r="E472">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F472" t="s">
         <v>1569</v>
@@ -24687,7 +24687,7 @@
         <v>1544</v>
       </c>
       <c r="E473">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F473" t="s">
         <v>1569</v>
@@ -24722,7 +24722,7 @@
         <v>1544</v>
       </c>
       <c r="E474">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F474" t="s">
         <v>1569</v>
@@ -24757,7 +24757,7 @@
         <v>1544</v>
       </c>
       <c r="E475">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F475" t="s">
         <v>1569</v>
@@ -24792,7 +24792,7 @@
         <v>1544</v>
       </c>
       <c r="E476">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F476" t="s">
         <v>1569</v>
@@ -24827,7 +24827,7 @@
         <v>1544</v>
       </c>
       <c r="E477">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F477" t="s">
         <v>1569</v>
@@ -24862,7 +24862,7 @@
         <v>1544</v>
       </c>
       <c r="E478">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F478" t="s">
         <v>1569</v>
@@ -24897,7 +24897,7 @@
         <v>1544</v>
       </c>
       <c r="E479">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F479" t="s">
         <v>1569</v>
@@ -24932,7 +24932,7 @@
         <v>1544</v>
       </c>
       <c r="E480">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F480" t="s">
         <v>1569</v>
@@ -24967,7 +24967,7 @@
         <v>1544</v>
       </c>
       <c r="E481">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F481" t="s">
         <v>1569</v>
@@ -25002,7 +25002,7 @@
         <v>1544</v>
       </c>
       <c r="E482">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F482" t="s">
         <v>1569</v>
@@ -25037,7 +25037,7 @@
         <v>1544</v>
       </c>
       <c r="E483">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F483" t="s">
         <v>1569</v>
@@ -25072,7 +25072,7 @@
         <v>1544</v>
       </c>
       <c r="E484">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F484" t="s">
         <v>1569</v>
@@ -25107,7 +25107,7 @@
         <v>1544</v>
       </c>
       <c r="E485">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F485" t="s">
         <v>1569</v>
@@ -25142,7 +25142,7 @@
         <v>1544</v>
       </c>
       <c r="E486">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F486" t="s">
         <v>1569</v>
@@ -25177,7 +25177,7 @@
         <v>1544</v>
       </c>
       <c r="E487">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F487" t="s">
         <v>1569</v>
@@ -25212,7 +25212,7 @@
         <v>1544</v>
       </c>
       <c r="E488">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F488" t="s">
         <v>1569</v>
@@ -25247,7 +25247,7 @@
         <v>1544</v>
       </c>
       <c r="E489">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F489" t="s">
         <v>1569</v>
@@ -25282,7 +25282,7 @@
         <v>1544</v>
       </c>
       <c r="E490">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F490" t="s">
         <v>1569</v>
@@ -25317,7 +25317,7 @@
         <v>1544</v>
       </c>
       <c r="E491">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F491" t="s">
         <v>1569</v>
@@ -25352,7 +25352,7 @@
         <v>1544</v>
       </c>
       <c r="E492">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F492" t="s">
         <v>1569</v>
@@ -25387,7 +25387,7 @@
         <v>1545</v>
       </c>
       <c r="E493">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F493" t="s">
         <v>1569</v>
@@ -25422,7 +25422,7 @@
         <v>1545</v>
       </c>
       <c r="E494">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F494" t="s">
         <v>1569</v>
@@ -25457,7 +25457,7 @@
         <v>1545</v>
       </c>
       <c r="E495">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F495" t="s">
         <v>1569</v>
@@ -25492,7 +25492,7 @@
         <v>1545</v>
       </c>
       <c r="E496">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F496" t="s">
         <v>1569</v>
@@ -25527,7 +25527,7 @@
         <v>1545</v>
       </c>
       <c r="E497">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F497" t="s">
         <v>1569</v>
@@ -25562,7 +25562,7 @@
         <v>1545</v>
       </c>
       <c r="E498">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F498" t="s">
         <v>1569</v>
@@ -25597,7 +25597,7 @@
         <v>1545</v>
       </c>
       <c r="E499">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F499" t="s">
         <v>1573</v>
@@ -25632,7 +25632,7 @@
         <v>1545</v>
       </c>
       <c r="E500">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F500" t="s">
         <v>1569</v>
@@ -25667,7 +25667,7 @@
         <v>1546</v>
       </c>
       <c r="E501">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F501" t="s">
         <v>1569</v>
@@ -25702,7 +25702,7 @@
         <v>1546</v>
       </c>
       <c r="E502">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F502" t="s">
         <v>1571</v>
@@ -25740,7 +25740,7 @@
         <v>1547</v>
       </c>
       <c r="E503">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F503" t="s">
         <v>1571</v>
@@ -25778,7 +25778,7 @@
         <v>1547</v>
       </c>
       <c r="E504">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F504" t="s">
         <v>1569</v>
@@ -25813,7 +25813,7 @@
         <v>1547</v>
       </c>
       <c r="E505">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F505" t="s">
         <v>1571</v>
@@ -25851,7 +25851,7 @@
         <v>1547</v>
       </c>
       <c r="E506">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F506" t="s">
         <v>1569</v>
@@ -25886,7 +25886,7 @@
         <v>1547</v>
       </c>
       <c r="E507">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F507" t="s">
         <v>1569</v>
@@ -25921,7 +25921,7 @@
         <v>1547</v>
       </c>
       <c r="E508">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F508" t="s">
         <v>1569</v>
@@ -25956,7 +25956,7 @@
         <v>1547</v>
       </c>
       <c r="E509">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F509" t="s">
         <v>1569</v>
@@ -25991,7 +25991,7 @@
         <v>1548</v>
       </c>
       <c r="E510">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F510" t="s">
         <v>1569</v>
@@ -26029,7 +26029,7 @@
         <v>1548</v>
       </c>
       <c r="E511">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F511" t="s">
         <v>1573</v>
@@ -26064,7 +26064,7 @@
         <v>1548</v>
       </c>
       <c r="E512">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F512" t="s">
         <v>1571</v>
@@ -26099,7 +26099,7 @@
         <v>1548</v>
       </c>
       <c r="E513">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F513" t="s">
         <v>1569</v>
@@ -26134,7 +26134,7 @@
         <v>1548</v>
       </c>
       <c r="E514">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F514" t="s">
         <v>1569</v>
@@ -26169,7 +26169,7 @@
         <v>1548</v>
       </c>
       <c r="E515">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F515" t="s">
         <v>1569</v>
@@ -26204,7 +26204,7 @@
         <v>1548</v>
       </c>
       <c r="E516">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F516" t="s">
         <v>1569</v>
@@ -26239,7 +26239,7 @@
         <v>1548</v>
       </c>
       <c r="E517">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F517" t="s">
         <v>1569</v>
@@ -26274,7 +26274,7 @@
         <v>1548</v>
       </c>
       <c r="E518">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F518" t="s">
         <v>1569</v>
@@ -26309,7 +26309,7 @@
         <v>1549</v>
       </c>
       <c r="E519">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F519" t="s">
         <v>1569</v>
@@ -26347,7 +26347,7 @@
         <v>1549</v>
       </c>
       <c r="E520">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F520" t="s">
         <v>1569</v>
@@ -26382,7 +26382,7 @@
         <v>1550</v>
       </c>
       <c r="E521">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F521" t="s">
         <v>1569</v>
@@ -26417,7 +26417,7 @@
         <v>1550</v>
       </c>
       <c r="E522">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F522" t="s">
         <v>1569</v>
@@ -26452,7 +26452,7 @@
         <v>1550</v>
       </c>
       <c r="E523">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F523" t="s">
         <v>1569</v>
@@ -26487,7 +26487,7 @@
         <v>1550</v>
       </c>
       <c r="E524">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F524" t="s">
         <v>1569</v>
@@ -26522,7 +26522,7 @@
         <v>1550</v>
       </c>
       <c r="E525">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F525" t="s">
         <v>1569</v>
@@ -26557,7 +26557,7 @@
         <v>1550</v>
       </c>
       <c r="E526">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F526" t="s">
         <v>1569</v>
@@ -26592,7 +26592,7 @@
         <v>1550</v>
       </c>
       <c r="E527">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F527" t="s">
         <v>1569</v>
@@ -26627,7 +26627,7 @@
         <v>1551</v>
       </c>
       <c r="E528">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F528" t="s">
         <v>1569</v>
@@ -26662,7 +26662,7 @@
         <v>1551</v>
       </c>
       <c r="E529">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F529" t="s">
         <v>1569</v>
@@ -26697,7 +26697,7 @@
         <v>1551</v>
       </c>
       <c r="E530">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F530" t="s">
         <v>1569</v>
@@ -26732,7 +26732,7 @@
         <v>1551</v>
       </c>
       <c r="E531">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F531" t="s">
         <v>1569</v>
@@ -26767,7 +26767,7 @@
         <v>1551</v>
       </c>
       <c r="E532">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F532" t="s">
         <v>1569</v>
@@ -26802,7 +26802,7 @@
         <v>1551</v>
       </c>
       <c r="E533">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F533" t="s">
         <v>1569</v>
@@ -26837,7 +26837,7 @@
         <v>1551</v>
       </c>
       <c r="E534">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F534" t="s">
         <v>1569</v>
@@ -26872,7 +26872,7 @@
         <v>1551</v>
       </c>
       <c r="E535">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F535" t="s">
         <v>1569</v>
@@ -26907,7 +26907,7 @@
         <v>1551</v>
       </c>
       <c r="E536">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F536" t="s">
         <v>1571</v>
@@ -26942,7 +26942,7 @@
         <v>1551</v>
       </c>
       <c r="E537">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F537" t="s">
         <v>1569</v>
@@ -26977,7 +26977,7 @@
         <v>1551</v>
       </c>
       <c r="E538">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F538" t="s">
         <v>1573</v>
@@ -27012,7 +27012,7 @@
         <v>1551</v>
       </c>
       <c r="E539">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F539" t="s">
         <v>1569</v>
@@ -27047,7 +27047,7 @@
         <v>1552</v>
       </c>
       <c r="E540">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F540" t="s">
         <v>1569</v>
@@ -27082,7 +27082,7 @@
         <v>1552</v>
       </c>
       <c r="E541">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F541" t="s">
         <v>1569</v>
@@ -27117,7 +27117,7 @@
         <v>1552</v>
       </c>
       <c r="E542">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F542" t="s">
         <v>1569</v>
@@ -27152,7 +27152,7 @@
         <v>1552</v>
       </c>
       <c r="E543">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F543" t="s">
         <v>1569</v>
@@ -27187,7 +27187,7 @@
         <v>1552</v>
       </c>
       <c r="E544">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F544" t="s">
         <v>1569</v>
@@ -27222,7 +27222,7 @@
         <v>1552</v>
       </c>
       <c r="E545">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F545" t="s">
         <v>1569</v>
@@ -27257,7 +27257,7 @@
         <v>1552</v>
       </c>
       <c r="E546">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F546" t="s">
         <v>1569</v>
@@ -27292,7 +27292,7 @@
         <v>1552</v>
       </c>
       <c r="E547">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F547" t="s">
         <v>1569</v>
@@ -27330,7 +27330,7 @@
         <v>1552</v>
       </c>
       <c r="E548">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F548" t="s">
         <v>1571</v>
@@ -27368,7 +27368,7 @@
         <v>1552</v>
       </c>
       <c r="E549">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F549" t="s">
         <v>1571</v>
@@ -27403,7 +27403,7 @@
         <v>1552</v>
       </c>
       <c r="E550">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F550" t="s">
         <v>1569</v>
@@ -27438,7 +27438,7 @@
         <v>1553</v>
       </c>
       <c r="E551">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F551" t="s">
         <v>1569</v>
@@ -27473,7 +27473,7 @@
         <v>1553</v>
       </c>
       <c r="E552">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F552" t="s">
         <v>1569</v>
@@ -27508,7 +27508,7 @@
         <v>1553</v>
       </c>
       <c r="E553">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F553" t="s">
         <v>1569</v>
@@ -27543,7 +27543,7 @@
         <v>1553</v>
       </c>
       <c r="E554">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F554" t="s">
         <v>1569</v>
@@ -27578,7 +27578,7 @@
         <v>1553</v>
       </c>
       <c r="E555">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F555" t="s">
         <v>1569</v>
@@ -27613,7 +27613,7 @@
         <v>1553</v>
       </c>
       <c r="E556">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F556" t="s">
         <v>1569</v>
@@ -27648,7 +27648,7 @@
         <v>1553</v>
       </c>
       <c r="E557">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F557" t="s">
         <v>1569</v>
@@ -27683,7 +27683,7 @@
         <v>1553</v>
       </c>
       <c r="E558">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F558" t="s">
         <v>1569</v>
@@ -27721,7 +27721,7 @@
         <v>1554</v>
       </c>
       <c r="E559">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F559" t="s">
         <v>1569</v>
@@ -27756,7 +27756,7 @@
         <v>1555</v>
       </c>
       <c r="E560">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F560" t="s">
         <v>1569</v>
@@ -27794,7 +27794,7 @@
         <v>1555</v>
       </c>
       <c r="E561">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F561" t="s">
         <v>1569</v>
@@ -27829,7 +27829,7 @@
         <v>1555</v>
       </c>
       <c r="E562">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F562" t="s">
         <v>1569</v>
@@ -27864,7 +27864,7 @@
         <v>1555</v>
       </c>
       <c r="E563">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F563" t="s">
         <v>1571</v>
@@ -27902,7 +27902,7 @@
         <v>1555</v>
       </c>
       <c r="E564">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F564" t="s">
         <v>1571</v>
@@ -27940,7 +27940,7 @@
         <v>1555</v>
       </c>
       <c r="E565">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F565" t="s">
         <v>1569</v>
@@ -27975,7 +27975,7 @@
         <v>1555</v>
       </c>
       <c r="E566">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F566" t="s">
         <v>1569</v>
@@ -28010,7 +28010,7 @@
         <v>1555</v>
       </c>
       <c r="E567">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F567" t="s">
         <v>1569</v>
@@ -28045,7 +28045,7 @@
         <v>1556</v>
       </c>
       <c r="E568">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F568" t="s">
         <v>1569</v>
@@ -28080,7 +28080,7 @@
         <v>1556</v>
       </c>
       <c r="E569">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F569" t="s">
         <v>1569</v>
@@ -28115,7 +28115,7 @@
         <v>1556</v>
       </c>
       <c r="E570">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F570" t="s">
         <v>1569</v>
@@ -28150,7 +28150,7 @@
         <v>1556</v>
       </c>
       <c r="E571">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F571" t="s">
         <v>1569</v>
@@ -28185,7 +28185,7 @@
         <v>1556</v>
       </c>
       <c r="E572">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F572" t="s">
         <v>1569</v>
@@ -28220,7 +28220,7 @@
         <v>1556</v>
       </c>
       <c r="E573">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F573" t="s">
         <v>1569</v>
@@ -28255,7 +28255,7 @@
         <v>1556</v>
       </c>
       <c r="E574">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F574" t="s">
         <v>1569</v>
@@ -28290,7 +28290,7 @@
         <v>1556</v>
       </c>
       <c r="E575">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F575" t="s">
         <v>1569</v>
@@ -28325,7 +28325,7 @@
         <v>1556</v>
       </c>
       <c r="E576">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F576" t="s">
         <v>1569</v>
@@ -28360,7 +28360,7 @@
         <v>1556</v>
       </c>
       <c r="E577">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F577" t="s">
         <v>1569</v>
@@ -28398,7 +28398,7 @@
         <v>1556</v>
       </c>
       <c r="E578">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F578" t="s">
         <v>1569</v>
@@ -28433,7 +28433,7 @@
         <v>1557</v>
       </c>
       <c r="E579">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F579" t="s">
         <v>1569</v>
@@ -28468,7 +28468,7 @@
         <v>1557</v>
       </c>
       <c r="E580">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F580" t="s">
         <v>1571</v>
@@ -28506,7 +28506,7 @@
         <v>1557</v>
       </c>
       <c r="E581">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F581" t="s">
         <v>1569</v>
@@ -28541,7 +28541,7 @@
         <v>1557</v>
       </c>
       <c r="E582">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F582" t="s">
         <v>1569</v>
@@ -28576,7 +28576,7 @@
         <v>1558</v>
       </c>
       <c r="E583">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F583" t="s">
         <v>1569</v>
@@ -28611,7 +28611,7 @@
         <v>1558</v>
       </c>
       <c r="E584">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F584" t="s">
         <v>1571</v>
@@ -28646,7 +28646,7 @@
         <v>1558</v>
       </c>
       <c r="E585">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F585" t="s">
         <v>1569</v>
@@ -28681,7 +28681,7 @@
         <v>1558</v>
       </c>
       <c r="E586">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F586" t="s">
         <v>1569</v>
@@ -28716,7 +28716,7 @@
         <v>1558</v>
       </c>
       <c r="E587">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F587" t="s">
         <v>1571</v>
@@ -28754,7 +28754,7 @@
         <v>1558</v>
       </c>
       <c r="E588">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F588" t="s">
         <v>1569</v>
@@ -28789,7 +28789,7 @@
         <v>1558</v>
       </c>
       <c r="E589">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F589" t="s">
         <v>1569</v>
@@ -28824,7 +28824,7 @@
         <v>1558</v>
       </c>
       <c r="E590">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F590" t="s">
         <v>1569</v>
@@ -28859,7 +28859,7 @@
         <v>1558</v>
       </c>
       <c r="E591">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F591" t="s">
         <v>1569</v>
@@ -28894,7 +28894,7 @@
         <v>1558</v>
       </c>
       <c r="E592">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F592" t="s">
         <v>1569</v>
@@ -28929,7 +28929,7 @@
         <v>1558</v>
       </c>
       <c r="E593">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F593" t="s">
         <v>1569</v>
@@ -28964,7 +28964,7 @@
         <v>1558</v>
       </c>
       <c r="E594">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F594" t="s">
         <v>1569</v>
@@ -28999,7 +28999,7 @@
         <v>1559</v>
       </c>
       <c r="E595">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F595" t="s">
         <v>1573</v>
@@ -29034,7 +29034,7 @@
         <v>1559</v>
       </c>
       <c r="E596">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F596" t="s">
         <v>1569</v>
@@ -29069,7 +29069,7 @@
         <v>1559</v>
       </c>
       <c r="E597">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F597" t="s">
         <v>1569</v>
@@ -29104,7 +29104,7 @@
         <v>1559</v>
       </c>
       <c r="E598">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F598" t="s">
         <v>1569</v>
@@ -29139,7 +29139,7 @@
         <v>1559</v>
       </c>
       <c r="E599">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F599" t="s">
         <v>1571</v>
@@ -29174,7 +29174,7 @@
         <v>1559</v>
       </c>
       <c r="E600">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F600" t="s">
         <v>1569</v>
@@ -29209,7 +29209,7 @@
         <v>1559</v>
       </c>
       <c r="E601">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F601" t="s">
         <v>1569</v>
@@ -29244,7 +29244,7 @@
         <v>1560</v>
       </c>
       <c r="E602">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F602" t="s">
         <v>1569</v>
@@ -29282,7 +29282,7 @@
         <v>1560</v>
       </c>
       <c r="E603">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F603" t="s">
         <v>1569</v>
@@ -29317,7 +29317,7 @@
         <v>1560</v>
       </c>
       <c r="E604">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F604" t="s">
         <v>1569</v>
@@ -29352,7 +29352,7 @@
         <v>1560</v>
       </c>
       <c r="E605">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F605" t="s">
         <v>1569</v>
@@ -29387,7 +29387,7 @@
         <v>1560</v>
       </c>
       <c r="E606">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F606" t="s">
         <v>1571</v>
@@ -29425,7 +29425,7 @@
         <v>1561</v>
       </c>
       <c r="E607">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F607" t="s">
         <v>1569</v>
@@ -29460,7 +29460,7 @@
         <v>1561</v>
       </c>
       <c r="E608">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F608" t="s">
         <v>1573</v>
@@ -29498,7 +29498,7 @@
         <v>1561</v>
       </c>
       <c r="E609">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F609" t="s">
         <v>1571</v>
@@ -29536,7 +29536,7 @@
         <v>1561</v>
       </c>
       <c r="E610">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F610" t="s">
         <v>1569</v>
@@ -29571,7 +29571,7 @@
         <v>1561</v>
       </c>
       <c r="E611">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F611" t="s">
         <v>1569</v>
@@ -29606,7 +29606,7 @@
         <v>1562</v>
       </c>
       <c r="E612">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F612" t="s">
         <v>1569</v>
@@ -29641,7 +29641,7 @@
         <v>1562</v>
       </c>
       <c r="E613">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F613" t="s">
         <v>1569</v>
@@ -29676,7 +29676,7 @@
         <v>1562</v>
       </c>
       <c r="E614">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F614" t="s">
         <v>1569</v>
@@ -29711,7 +29711,7 @@
         <v>1562</v>
       </c>
       <c r="E615">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F615" t="s">
         <v>1571</v>
@@ -29746,7 +29746,7 @@
         <v>1562</v>
       </c>
       <c r="E616">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F616" t="s">
         <v>1569</v>
@@ -29781,7 +29781,7 @@
         <v>1562</v>
       </c>
       <c r="E617">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F617" t="s">
         <v>1569</v>
@@ -29816,7 +29816,7 @@
         <v>1562</v>
       </c>
       <c r="E618">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F618" t="s">
         <v>1569</v>
@@ -29851,7 +29851,7 @@
         <v>1562</v>
       </c>
       <c r="E619">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F619" t="s">
         <v>1571</v>
@@ -29889,7 +29889,7 @@
         <v>1562</v>
       </c>
       <c r="E620">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F620" t="s">
         <v>1569</v>
@@ -29924,7 +29924,7 @@
         <v>1562</v>
       </c>
       <c r="E621">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F621" t="s">
         <v>1569</v>
@@ -29959,7 +29959,7 @@
         <v>1562</v>
       </c>
       <c r="E622">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F622" t="s">
         <v>1569</v>
@@ -29994,7 +29994,7 @@
         <v>1563</v>
       </c>
       <c r="E623">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F623" t="s">
         <v>1573</v>
@@ -30029,7 +30029,7 @@
         <v>1563</v>
       </c>
       <c r="E624">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F624" t="s">
         <v>1569</v>
@@ -30067,7 +30067,7 @@
         <v>1563</v>
       </c>
       <c r="E625">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F625" t="s">
         <v>1569</v>
@@ -30102,7 +30102,7 @@
         <v>1563</v>
       </c>
       <c r="E626">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F626" t="s">
         <v>1571</v>
@@ -30137,7 +30137,7 @@
         <v>1563</v>
       </c>
       <c r="E627">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F627" t="s">
         <v>1569</v>
@@ -30172,7 +30172,7 @@
         <v>1564</v>
       </c>
       <c r="E628">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F628" t="s">
         <v>1571</v>
@@ -30210,7 +30210,7 @@
         <v>1564</v>
       </c>
       <c r="E629">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F629" t="s">
         <v>1571</v>
@@ -30248,7 +30248,7 @@
         <v>1564</v>
       </c>
       <c r="E630">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F630" t="s">
         <v>1571</v>
@@ -30286,7 +30286,7 @@
         <v>1564</v>
       </c>
       <c r="E631">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F631" t="s">
         <v>1569</v>
@@ -30321,7 +30321,7 @@
         <v>1564</v>
       </c>
       <c r="E632">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F632" t="s">
         <v>1569</v>
@@ -30356,7 +30356,7 @@
         <v>1564</v>
       </c>
       <c r="E633">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F633" t="s">
         <v>1569</v>
@@ -30391,7 +30391,7 @@
         <v>1565</v>
       </c>
       <c r="E634">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F634" t="s">
         <v>1571</v>
@@ -30429,7 +30429,7 @@
         <v>1565</v>
       </c>
       <c r="E635">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F635" t="s">
         <v>1569</v>
@@ -30464,7 +30464,7 @@
         <v>1566</v>
       </c>
       <c r="E636">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F636" t="s">
         <v>1569</v>
@@ -30499,7 +30499,7 @@
         <v>1566</v>
       </c>
       <c r="E637">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F637" t="s">
         <v>1569</v>
@@ -30534,7 +30534,7 @@
         <v>1566</v>
       </c>
       <c r="E638">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F638" t="s">
         <v>1569</v>
@@ -30569,7 +30569,7 @@
         <v>1566</v>
       </c>
       <c r="E639">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F639" t="s">
         <v>1569</v>
@@ -30604,7 +30604,7 @@
         <v>1566</v>
       </c>
       <c r="E640">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F640" t="s">
         <v>1569</v>
@@ -30639,7 +30639,7 @@
         <v>1566</v>
       </c>
       <c r="E641">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F641" t="s">
         <v>1569</v>
@@ -30674,7 +30674,7 @@
         <v>1566</v>
       </c>
       <c r="E642">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F642" t="s">
         <v>1569</v>
@@ -30709,7 +30709,7 @@
         <v>1566</v>
       </c>
       <c r="E643">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F643" t="s">
         <v>1569</v>
@@ -30744,7 +30744,7 @@
         <v>1566</v>
       </c>
       <c r="E644">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F644" t="s">
         <v>1569</v>
@@ -30779,7 +30779,7 @@
         <v>1566</v>
       </c>
       <c r="E645">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F645" t="s">
         <v>1569</v>
@@ -30817,7 +30817,7 @@
         <v>1567</v>
       </c>
       <c r="E646">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F646" t="s">
         <v>1569</v>
@@ -30852,7 +30852,7 @@
         <v>1567</v>
       </c>
       <c r="E647">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F647" t="s">
         <v>1569</v>
@@ -30887,7 +30887,7 @@
         <v>1567</v>
       </c>
       <c r="E648">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F648" t="s">
         <v>1569</v>
@@ -30922,7 +30922,7 @@
         <v>1567</v>
       </c>
       <c r="E649">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F649" t="s">
         <v>1569</v>
@@ -30957,7 +30957,7 @@
         <v>1567</v>
       </c>
       <c r="E650">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F650" t="s">
         <v>1569</v>
@@ -30995,7 +30995,7 @@
         <v>1567</v>
       </c>
       <c r="E651">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F651" t="s">
         <v>1571</v>
@@ -31033,7 +31033,7 @@
         <v>1567</v>
       </c>
       <c r="E652">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F652" t="s">
         <v>1569</v>
@@ -31068,7 +31068,7 @@
         <v>1567</v>
       </c>
       <c r="E653">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F653" t="s">
         <v>1571</v>
@@ -31106,7 +31106,7 @@
         <v>1567</v>
       </c>
       <c r="E654">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F654" t="s">
         <v>1569</v>
@@ -31141,7 +31141,7 @@
         <v>1567</v>
       </c>
       <c r="E655">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F655" t="s">
         <v>1569</v>
@@ -31176,7 +31176,7 @@
         <v>1567</v>
       </c>
       <c r="E656">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F656" t="s">
         <v>1569</v>
@@ -31211,7 +31211,7 @@
         <v>1568</v>
       </c>
       <c r="E657">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F657" t="s">
         <v>1569</v>
@@ -31246,7 +31246,7 @@
         <v>1568</v>
       </c>
       <c r="E658">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F658" t="s">
         <v>1569</v>
@@ -31284,7 +31284,7 @@
         <v>1568</v>
       </c>
       <c r="E659">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F659" t="s">
         <v>1569</v>
@@ -31322,7 +31322,7 @@
         <v>1568</v>
       </c>
       <c r="E660">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F660" t="s">
         <v>1569</v>

--- a/BacklogGATEAutoCompleto.xlsx
+++ b/BacklogGATEAutoCompleto.xlsx
@@ -8169,7 +8169,7 @@
         <v>1357</v>
       </c>
       <c r="E2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="F2" t="s">
         <v>1569</v>
@@ -8204,7 +8204,7 @@
         <v>1358</v>
       </c>
       <c r="E3">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="F3" t="s">
         <v>1569</v>
@@ -8239,7 +8239,7 @@
         <v>1359</v>
       </c>
       <c r="E4">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="F4" t="s">
         <v>1569</v>
@@ -8274,7 +8274,7 @@
         <v>1360</v>
       </c>
       <c r="E5">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="F5" t="s">
         <v>1569</v>
@@ -8309,7 +8309,7 @@
         <v>1361</v>
       </c>
       <c r="E6">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="F6" t="s">
         <v>1569</v>
@@ -8344,7 +8344,7 @@
         <v>1362</v>
       </c>
       <c r="E7">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="F7" t="s">
         <v>1569</v>
@@ -8379,7 +8379,7 @@
         <v>1363</v>
       </c>
       <c r="E8">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="F8" t="s">
         <v>1569</v>
@@ -8414,7 +8414,7 @@
         <v>1364</v>
       </c>
       <c r="E9">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="F9" t="s">
         <v>1569</v>
@@ -8449,7 +8449,7 @@
         <v>1365</v>
       </c>
       <c r="E10">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="F10" t="s">
         <v>1569</v>
@@ -8484,7 +8484,7 @@
         <v>1365</v>
       </c>
       <c r="E11">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="F11" t="s">
         <v>1569</v>
@@ -8519,7 +8519,7 @@
         <v>1366</v>
       </c>
       <c r="E12">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="F12" t="s">
         <v>1569</v>
@@ -8554,7 +8554,7 @@
         <v>1367</v>
       </c>
       <c r="E13">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="F13" t="s">
         <v>1569</v>
@@ -8589,7 +8589,7 @@
         <v>1368</v>
       </c>
       <c r="E14">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="F14" t="s">
         <v>1569</v>
@@ -8624,7 +8624,7 @@
         <v>1368</v>
       </c>
       <c r="E15">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="F15" t="s">
         <v>1569</v>
@@ -8659,7 +8659,7 @@
         <v>1369</v>
       </c>
       <c r="E16">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="F16" t="s">
         <v>1569</v>
@@ -8694,7 +8694,7 @@
         <v>1370</v>
       </c>
       <c r="E17">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F17" t="s">
         <v>1569</v>
@@ -8729,7 +8729,7 @@
         <v>1370</v>
       </c>
       <c r="E18">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F18" t="s">
         <v>1569</v>
@@ -8764,7 +8764,7 @@
         <v>1371</v>
       </c>
       <c r="E19">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="F19" t="s">
         <v>1569</v>
@@ -8799,7 +8799,7 @@
         <v>1372</v>
       </c>
       <c r="E20">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="F20" t="s">
         <v>1569</v>
@@ -8834,7 +8834,7 @@
         <v>1373</v>
       </c>
       <c r="E21">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="F21" t="s">
         <v>1569</v>
@@ -8869,7 +8869,7 @@
         <v>1374</v>
       </c>
       <c r="E22">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F22" t="s">
         <v>1569</v>
@@ -8904,7 +8904,7 @@
         <v>1375</v>
       </c>
       <c r="E23">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="F23" t="s">
         <v>1569</v>
@@ -8942,7 +8942,7 @@
         <v>1376</v>
       </c>
       <c r="E24">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="F24" t="s">
         <v>1569</v>
@@ -8977,7 +8977,7 @@
         <v>1377</v>
       </c>
       <c r="E25">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F25" t="s">
         <v>1569</v>
@@ -9012,7 +9012,7 @@
         <v>1378</v>
       </c>
       <c r="E26">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="F26" t="s">
         <v>1569</v>
@@ -9047,7 +9047,7 @@
         <v>1379</v>
       </c>
       <c r="E27">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F27" t="s">
         <v>1569</v>
@@ -9082,7 +9082,7 @@
         <v>1380</v>
       </c>
       <c r="E28">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F28" t="s">
         <v>1569</v>
@@ -9117,7 +9117,7 @@
         <v>1381</v>
       </c>
       <c r="E29">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F29" t="s">
         <v>1569</v>
@@ -9152,7 +9152,7 @@
         <v>1382</v>
       </c>
       <c r="E30">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F30" t="s">
         <v>1569</v>
@@ -9187,7 +9187,7 @@
         <v>1383</v>
       </c>
       <c r="E31">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F31" t="s">
         <v>1569</v>
@@ -9222,7 +9222,7 @@
         <v>1384</v>
       </c>
       <c r="E32">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F32" t="s">
         <v>1569</v>
@@ -9257,7 +9257,7 @@
         <v>1385</v>
       </c>
       <c r="E33">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F33" t="s">
         <v>1569</v>
@@ -9292,7 +9292,7 @@
         <v>1386</v>
       </c>
       <c r="E34">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F34" t="s">
         <v>1569</v>
@@ -9327,7 +9327,7 @@
         <v>1386</v>
       </c>
       <c r="E35">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F35" t="s">
         <v>1569</v>
@@ -9362,7 +9362,7 @@
         <v>1387</v>
       </c>
       <c r="E36">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F36" t="s">
         <v>1569</v>
@@ -9397,7 +9397,7 @@
         <v>1388</v>
       </c>
       <c r="E37">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F37" t="s">
         <v>1569</v>
@@ -9432,7 +9432,7 @@
         <v>1389</v>
       </c>
       <c r="E38">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F38" t="s">
         <v>1569</v>
@@ -9467,7 +9467,7 @@
         <v>1390</v>
       </c>
       <c r="E39">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F39" t="s">
         <v>1569</v>
@@ -9502,7 +9502,7 @@
         <v>1391</v>
       </c>
       <c r="E40">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F40" t="s">
         <v>1569</v>
@@ -9537,7 +9537,7 @@
         <v>1391</v>
       </c>
       <c r="E41">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F41" t="s">
         <v>1569</v>
@@ -9572,7 +9572,7 @@
         <v>1392</v>
       </c>
       <c r="E42">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F42" t="s">
         <v>1569</v>
@@ -9607,7 +9607,7 @@
         <v>1393</v>
       </c>
       <c r="E43">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F43" t="s">
         <v>1569</v>
@@ -9642,7 +9642,7 @@
         <v>1394</v>
       </c>
       <c r="E44">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F44" t="s">
         <v>1569</v>
@@ -9677,7 +9677,7 @@
         <v>1394</v>
       </c>
       <c r="E45">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F45" t="s">
         <v>1569</v>
@@ -9712,7 +9712,7 @@
         <v>1395</v>
       </c>
       <c r="E46">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F46" t="s">
         <v>1569</v>
@@ -9747,7 +9747,7 @@
         <v>1395</v>
       </c>
       <c r="E47">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F47" t="s">
         <v>1569</v>
@@ -9782,7 +9782,7 @@
         <v>1396</v>
       </c>
       <c r="E48">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F48" t="s">
         <v>1569</v>
@@ -9817,7 +9817,7 @@
         <v>1397</v>
       </c>
       <c r="E49">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F49" t="s">
         <v>1569</v>
@@ -9852,7 +9852,7 @@
         <v>1398</v>
       </c>
       <c r="E50">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F50" t="s">
         <v>1569</v>
@@ -9887,7 +9887,7 @@
         <v>1399</v>
       </c>
       <c r="E51">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F51" t="s">
         <v>1569</v>
@@ -9922,7 +9922,7 @@
         <v>1399</v>
       </c>
       <c r="E52">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F52" t="s">
         <v>1569</v>
@@ -9957,7 +9957,7 @@
         <v>1400</v>
       </c>
       <c r="E53">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F53" t="s">
         <v>1569</v>
@@ -9992,7 +9992,7 @@
         <v>1401</v>
       </c>
       <c r="E54">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F54" t="s">
         <v>1569</v>
@@ -10027,7 +10027,7 @@
         <v>1402</v>
       </c>
       <c r="E55">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F55" t="s">
         <v>1569</v>
@@ -10062,7 +10062,7 @@
         <v>1403</v>
       </c>
       <c r="E56">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F56" t="s">
         <v>1569</v>
@@ -10097,7 +10097,7 @@
         <v>1404</v>
       </c>
       <c r="E57">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F57" t="s">
         <v>1569</v>
@@ -10132,7 +10132,7 @@
         <v>1405</v>
       </c>
       <c r="E58">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F58" t="s">
         <v>1569</v>
@@ -10167,7 +10167,7 @@
         <v>1406</v>
       </c>
       <c r="E59">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F59" t="s">
         <v>1569</v>
@@ -10202,7 +10202,7 @@
         <v>1406</v>
       </c>
       <c r="E60">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F60" t="s">
         <v>1569</v>
@@ -10237,7 +10237,7 @@
         <v>1406</v>
       </c>
       <c r="E61">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F61" t="s">
         <v>1569</v>
@@ -10272,7 +10272,7 @@
         <v>1407</v>
       </c>
       <c r="E62">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F62" t="s">
         <v>1569</v>
@@ -10307,7 +10307,7 @@
         <v>1408</v>
       </c>
       <c r="E63">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F63" t="s">
         <v>1569</v>
@@ -10342,7 +10342,7 @@
         <v>1409</v>
       </c>
       <c r="E64">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F64" t="s">
         <v>1569</v>
@@ -10377,7 +10377,7 @@
         <v>1409</v>
       </c>
       <c r="E65">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F65" t="s">
         <v>1569</v>
@@ -10412,7 +10412,7 @@
         <v>1409</v>
       </c>
       <c r="E66">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F66" t="s">
         <v>1569</v>
@@ -10447,7 +10447,7 @@
         <v>1410</v>
       </c>
       <c r="E67">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F67" t="s">
         <v>1569</v>
@@ -10482,7 +10482,7 @@
         <v>1411</v>
       </c>
       <c r="E68">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F68" t="s">
         <v>1569</v>
@@ -10517,7 +10517,7 @@
         <v>1412</v>
       </c>
       <c r="E69">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F69" t="s">
         <v>1569</v>
@@ -10552,7 +10552,7 @@
         <v>1412</v>
       </c>
       <c r="E70">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F70" t="s">
         <v>1569</v>
@@ -10587,7 +10587,7 @@
         <v>1412</v>
       </c>
       <c r="E71">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F71" t="s">
         <v>1569</v>
@@ -10622,7 +10622,7 @@
         <v>1413</v>
       </c>
       <c r="E72">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F72" t="s">
         <v>1569</v>
@@ -10657,7 +10657,7 @@
         <v>1414</v>
       </c>
       <c r="E73">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F73" t="s">
         <v>1569</v>
@@ -10692,7 +10692,7 @@
         <v>1414</v>
       </c>
       <c r="E74">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F74" t="s">
         <v>1569</v>
@@ -10727,7 +10727,7 @@
         <v>1414</v>
       </c>
       <c r="E75">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F75" t="s">
         <v>1570</v>
@@ -10762,7 +10762,7 @@
         <v>1414</v>
       </c>
       <c r="E76">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F76" t="s">
         <v>1569</v>
@@ -10797,7 +10797,7 @@
         <v>1415</v>
       </c>
       <c r="E77">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F77" t="s">
         <v>1569</v>
@@ -10832,7 +10832,7 @@
         <v>1416</v>
       </c>
       <c r="E78">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F78" t="s">
         <v>1569</v>
@@ -10867,7 +10867,7 @@
         <v>1416</v>
       </c>
       <c r="E79">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F79" t="s">
         <v>1569</v>
@@ -10902,7 +10902,7 @@
         <v>1417</v>
       </c>
       <c r="E80">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F80" t="s">
         <v>1569</v>
@@ -10937,7 +10937,7 @@
         <v>1418</v>
       </c>
       <c r="E81">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F81" t="s">
         <v>1569</v>
@@ -10972,7 +10972,7 @@
         <v>1419</v>
       </c>
       <c r="E82">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F82" t="s">
         <v>1569</v>
@@ -11007,7 +11007,7 @@
         <v>1420</v>
       </c>
       <c r="E83">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F83" t="s">
         <v>1569</v>
@@ -11042,7 +11042,7 @@
         <v>1420</v>
       </c>
       <c r="E84">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F84" t="s">
         <v>1569</v>
@@ -11077,7 +11077,7 @@
         <v>1420</v>
       </c>
       <c r="E85">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F85" t="s">
         <v>1569</v>
@@ -11112,7 +11112,7 @@
         <v>1420</v>
       </c>
       <c r="E86">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F86" t="s">
         <v>1569</v>
@@ -11147,7 +11147,7 @@
         <v>1420</v>
       </c>
       <c r="E87">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F87" t="s">
         <v>1569</v>
@@ -11182,7 +11182,7 @@
         <v>1420</v>
       </c>
       <c r="E88">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F88" t="s">
         <v>1569</v>
@@ -11217,7 +11217,7 @@
         <v>1421</v>
       </c>
       <c r="E89">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F89" t="s">
         <v>1569</v>
@@ -11252,7 +11252,7 @@
         <v>1422</v>
       </c>
       <c r="E90">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F90" t="s">
         <v>1569</v>
@@ -11287,7 +11287,7 @@
         <v>1423</v>
       </c>
       <c r="E91">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F91" t="s">
         <v>1569</v>
@@ -11322,7 +11322,7 @@
         <v>1423</v>
       </c>
       <c r="E92">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F92" t="s">
         <v>1569</v>
@@ -11357,7 +11357,7 @@
         <v>1424</v>
       </c>
       <c r="E93">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F93" t="s">
         <v>1571</v>
@@ -11392,7 +11392,7 @@
         <v>1425</v>
       </c>
       <c r="E94">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F94" t="s">
         <v>1569</v>
@@ -11427,7 +11427,7 @@
         <v>1426</v>
       </c>
       <c r="E95">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F95" t="s">
         <v>1569</v>
@@ -11462,7 +11462,7 @@
         <v>1426</v>
       </c>
       <c r="E96">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F96" t="s">
         <v>1569</v>
@@ -11497,7 +11497,7 @@
         <v>1427</v>
       </c>
       <c r="E97">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F97" t="s">
         <v>1569</v>
@@ -11532,7 +11532,7 @@
         <v>1428</v>
       </c>
       <c r="E98">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F98" t="s">
         <v>1569</v>
@@ -11567,7 +11567,7 @@
         <v>1429</v>
       </c>
       <c r="E99">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F99" t="s">
         <v>1569</v>
@@ -11602,7 +11602,7 @@
         <v>1430</v>
       </c>
       <c r="E100">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F100" t="s">
         <v>1569</v>
@@ -11637,7 +11637,7 @@
         <v>1431</v>
       </c>
       <c r="E101">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F101" t="s">
         <v>1569</v>
@@ -11672,7 +11672,7 @@
         <v>1431</v>
       </c>
       <c r="E102">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F102" t="s">
         <v>1569</v>
@@ -11707,7 +11707,7 @@
         <v>1432</v>
       </c>
       <c r="E103">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F103" t="s">
         <v>1569</v>
@@ -11742,7 +11742,7 @@
         <v>1432</v>
       </c>
       <c r="E104">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F104" t="s">
         <v>1569</v>
@@ -11777,7 +11777,7 @@
         <v>1432</v>
       </c>
       <c r="E105">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F105" t="s">
         <v>1569</v>
@@ -11812,7 +11812,7 @@
         <v>1433</v>
       </c>
       <c r="E106">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F106" t="s">
         <v>1569</v>
@@ -11847,7 +11847,7 @@
         <v>1433</v>
       </c>
       <c r="E107">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F107" t="s">
         <v>1569</v>
@@ -11882,7 +11882,7 @@
         <v>1433</v>
       </c>
       <c r="E108">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F108" t="s">
         <v>1569</v>
@@ -11917,7 +11917,7 @@
         <v>1433</v>
       </c>
       <c r="E109">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F109" t="s">
         <v>1569</v>
@@ -11952,7 +11952,7 @@
         <v>1434</v>
       </c>
       <c r="E110">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F110" t="s">
         <v>1569</v>
@@ -11987,7 +11987,7 @@
         <v>1435</v>
       </c>
       <c r="E111">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F111" t="s">
         <v>1569</v>
@@ -12022,7 +12022,7 @@
         <v>1435</v>
       </c>
       <c r="E112">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F112" t="s">
         <v>1569</v>
@@ -12057,7 +12057,7 @@
         <v>1436</v>
       </c>
       <c r="E113">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F113" t="s">
         <v>1569</v>
@@ -12092,7 +12092,7 @@
         <v>1436</v>
       </c>
       <c r="E114">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F114" t="s">
         <v>1569</v>
@@ -12127,7 +12127,7 @@
         <v>1436</v>
       </c>
       <c r="E115">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F115" t="s">
         <v>1569</v>
@@ -12162,7 +12162,7 @@
         <v>1437</v>
       </c>
       <c r="E116">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F116" t="s">
         <v>1569</v>
@@ -12197,7 +12197,7 @@
         <v>1437</v>
       </c>
       <c r="E117">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F117" t="s">
         <v>1569</v>
@@ -12232,7 +12232,7 @@
         <v>1438</v>
       </c>
       <c r="E118">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F118" t="s">
         <v>1569</v>
@@ -12267,7 +12267,7 @@
         <v>1438</v>
       </c>
       <c r="E119">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F119" t="s">
         <v>1569</v>
@@ -12302,7 +12302,7 @@
         <v>1439</v>
       </c>
       <c r="E120">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F120" t="s">
         <v>1569</v>
@@ -12337,7 +12337,7 @@
         <v>1439</v>
       </c>
       <c r="E121">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F121" t="s">
         <v>1569</v>
@@ -12372,7 +12372,7 @@
         <v>1440</v>
       </c>
       <c r="E122">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F122" t="s">
         <v>1569</v>
@@ -12407,7 +12407,7 @@
         <v>1441</v>
       </c>
       <c r="E123">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F123" t="s">
         <v>1569</v>
@@ -12442,7 +12442,7 @@
         <v>1441</v>
       </c>
       <c r="E124">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F124" t="s">
         <v>1569</v>
@@ -12477,7 +12477,7 @@
         <v>1442</v>
       </c>
       <c r="E125">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F125" t="s">
         <v>1569</v>
@@ -12512,7 +12512,7 @@
         <v>1443</v>
       </c>
       <c r="E126">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F126" t="s">
         <v>1569</v>
@@ -12550,7 +12550,7 @@
         <v>1443</v>
       </c>
       <c r="E127">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F127" t="s">
         <v>1569</v>
@@ -12585,7 +12585,7 @@
         <v>1443</v>
       </c>
       <c r="E128">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F128" t="s">
         <v>1569</v>
@@ -12620,7 +12620,7 @@
         <v>1443</v>
       </c>
       <c r="E129">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F129" t="s">
         <v>1569</v>
@@ -12655,7 +12655,7 @@
         <v>1444</v>
       </c>
       <c r="E130">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F130" t="s">
         <v>1569</v>
@@ -12690,7 +12690,7 @@
         <v>1445</v>
       </c>
       <c r="E131">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F131" t="s">
         <v>1570</v>
@@ -12725,7 +12725,7 @@
         <v>1446</v>
       </c>
       <c r="E132">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F132" t="s">
         <v>1569</v>
@@ -12760,7 +12760,7 @@
         <v>1446</v>
       </c>
       <c r="E133">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F133" t="s">
         <v>1569</v>
@@ -12795,7 +12795,7 @@
         <v>1446</v>
       </c>
       <c r="E134">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F134" t="s">
         <v>1569</v>
@@ -12830,7 +12830,7 @@
         <v>1446</v>
       </c>
       <c r="E135">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F135" t="s">
         <v>1569</v>
@@ -12865,7 +12865,7 @@
         <v>1447</v>
       </c>
       <c r="E136">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F136" t="s">
         <v>1569</v>
@@ -12900,7 +12900,7 @@
         <v>1447</v>
       </c>
       <c r="E137">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F137" t="s">
         <v>1569</v>
@@ -12935,7 +12935,7 @@
         <v>1447</v>
       </c>
       <c r="E138">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F138" t="s">
         <v>1569</v>
@@ -12970,7 +12970,7 @@
         <v>1447</v>
       </c>
       <c r="E139">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F139" t="s">
         <v>1569</v>
@@ -13005,7 +13005,7 @@
         <v>1447</v>
       </c>
       <c r="E140">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F140" t="s">
         <v>1569</v>
@@ -13040,7 +13040,7 @@
         <v>1447</v>
       </c>
       <c r="E141">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F141" t="s">
         <v>1569</v>
@@ -13075,7 +13075,7 @@
         <v>1447</v>
       </c>
       <c r="E142">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F142" t="s">
         <v>1569</v>
@@ -13110,7 +13110,7 @@
         <v>1448</v>
       </c>
       <c r="E143">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F143" t="s">
         <v>1569</v>
@@ -13145,7 +13145,7 @@
         <v>1448</v>
       </c>
       <c r="E144">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F144" t="s">
         <v>1569</v>
@@ -13180,7 +13180,7 @@
         <v>1449</v>
       </c>
       <c r="E145">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F145" t="s">
         <v>1569</v>
@@ -13215,7 +13215,7 @@
         <v>1450</v>
       </c>
       <c r="E146">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F146" t="s">
         <v>1569</v>
@@ -13250,7 +13250,7 @@
         <v>1450</v>
       </c>
       <c r="E147">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F147" t="s">
         <v>1569</v>
@@ -13285,7 +13285,7 @@
         <v>1450</v>
       </c>
       <c r="E148">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F148" t="s">
         <v>1569</v>
@@ -13320,7 +13320,7 @@
         <v>1451</v>
       </c>
       <c r="E149">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F149" t="s">
         <v>1569</v>
@@ -13355,7 +13355,7 @@
         <v>1451</v>
       </c>
       <c r="E150">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F150" t="s">
         <v>1569</v>
@@ -13390,7 +13390,7 @@
         <v>1451</v>
       </c>
       <c r="E151">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F151" t="s">
         <v>1569</v>
@@ -13425,7 +13425,7 @@
         <v>1451</v>
       </c>
       <c r="E152">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F152" t="s">
         <v>1569</v>
@@ -13460,7 +13460,7 @@
         <v>1451</v>
       </c>
       <c r="E153">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F153" t="s">
         <v>1569</v>
@@ -13495,7 +13495,7 @@
         <v>1451</v>
       </c>
       <c r="E154">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F154" t="s">
         <v>1569</v>
@@ -13530,7 +13530,7 @@
         <v>1451</v>
       </c>
       <c r="E155">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F155" t="s">
         <v>1569</v>
@@ -13565,7 +13565,7 @@
         <v>1451</v>
       </c>
       <c r="E156">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F156" t="s">
         <v>1569</v>
@@ -13600,7 +13600,7 @@
         <v>1451</v>
       </c>
       <c r="E157">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F157" t="s">
         <v>1569</v>
@@ -13635,7 +13635,7 @@
         <v>1451</v>
       </c>
       <c r="E158">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F158" t="s">
         <v>1569</v>
@@ -13670,7 +13670,7 @@
         <v>1452</v>
       </c>
       <c r="E159">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F159" t="s">
         <v>1569</v>
@@ -13705,7 +13705,7 @@
         <v>1452</v>
       </c>
       <c r="E160">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F160" t="s">
         <v>1569</v>
@@ -13740,7 +13740,7 @@
         <v>1452</v>
       </c>
       <c r="E161">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F161" t="s">
         <v>1569</v>
@@ -13775,7 +13775,7 @@
         <v>1453</v>
       </c>
       <c r="E162">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F162" t="s">
         <v>1569</v>
@@ -13810,7 +13810,7 @@
         <v>1453</v>
       </c>
       <c r="E163">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F163" t="s">
         <v>1570</v>
@@ -13845,7 +13845,7 @@
         <v>1453</v>
       </c>
       <c r="E164">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F164" t="s">
         <v>1569</v>
@@ -13880,7 +13880,7 @@
         <v>1454</v>
       </c>
       <c r="E165">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F165" t="s">
         <v>1569</v>
@@ -13915,7 +13915,7 @@
         <v>1454</v>
       </c>
       <c r="E166">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F166" t="s">
         <v>1569</v>
@@ -13950,7 +13950,7 @@
         <v>1455</v>
       </c>
       <c r="E167">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F167" t="s">
         <v>1569</v>
@@ -13985,7 +13985,7 @@
         <v>1455</v>
       </c>
       <c r="E168">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F168" t="s">
         <v>1569</v>
@@ -14020,7 +14020,7 @@
         <v>1456</v>
       </c>
       <c r="E169">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F169" t="s">
         <v>1569</v>
@@ -14055,7 +14055,7 @@
         <v>1456</v>
       </c>
       <c r="E170">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F170" t="s">
         <v>1569</v>
@@ -14090,7 +14090,7 @@
         <v>1457</v>
       </c>
       <c r="E171">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F171" t="s">
         <v>1569</v>
@@ -14125,7 +14125,7 @@
         <v>1457</v>
       </c>
       <c r="E172">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F172" t="s">
         <v>1569</v>
@@ -14160,7 +14160,7 @@
         <v>1457</v>
       </c>
       <c r="E173">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F173" t="s">
         <v>1569</v>
@@ -14195,7 +14195,7 @@
         <v>1457</v>
       </c>
       <c r="E174">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F174" t="s">
         <v>1569</v>
@@ -14230,7 +14230,7 @@
         <v>1458</v>
       </c>
       <c r="E175">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F175" t="s">
         <v>1569</v>
@@ -14265,7 +14265,7 @@
         <v>1458</v>
       </c>
       <c r="E176">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F176" t="s">
         <v>1569</v>
@@ -14300,7 +14300,7 @@
         <v>1459</v>
       </c>
       <c r="E177">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F177" t="s">
         <v>1569</v>
@@ -14335,7 +14335,7 @@
         <v>1460</v>
       </c>
       <c r="E178">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F178" t="s">
         <v>1569</v>
@@ -14370,7 +14370,7 @@
         <v>1460</v>
       </c>
       <c r="E179">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F179" t="s">
         <v>1569</v>
@@ -14405,7 +14405,7 @@
         <v>1460</v>
       </c>
       <c r="E180">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F180" t="s">
         <v>1569</v>
@@ -14440,7 +14440,7 @@
         <v>1460</v>
       </c>
       <c r="E181">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F181" t="s">
         <v>1569</v>
@@ -14475,7 +14475,7 @@
         <v>1461</v>
       </c>
       <c r="E182">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F182" t="s">
         <v>1569</v>
@@ -14510,7 +14510,7 @@
         <v>1462</v>
       </c>
       <c r="E183">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F183" t="s">
         <v>1569</v>
@@ -14545,7 +14545,7 @@
         <v>1462</v>
       </c>
       <c r="E184">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F184" t="s">
         <v>1569</v>
@@ -14580,7 +14580,7 @@
         <v>1462</v>
       </c>
       <c r="E185">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F185" t="s">
         <v>1569</v>
@@ -14615,7 +14615,7 @@
         <v>1462</v>
       </c>
       <c r="E186">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F186" t="s">
         <v>1569</v>
@@ -14650,7 +14650,7 @@
         <v>1462</v>
       </c>
       <c r="E187">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F187" t="s">
         <v>1569</v>
@@ -14685,7 +14685,7 @@
         <v>1463</v>
       </c>
       <c r="E188">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F188" t="s">
         <v>1569</v>
@@ -14720,7 +14720,7 @@
         <v>1463</v>
       </c>
       <c r="E189">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F189" t="s">
         <v>1569</v>
@@ -14755,7 +14755,7 @@
         <v>1463</v>
       </c>
       <c r="E190">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F190" t="s">
         <v>1569</v>
@@ -14790,7 +14790,7 @@
         <v>1463</v>
       </c>
       <c r="E191">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F191" t="s">
         <v>1569</v>
@@ -14825,7 +14825,7 @@
         <v>1463</v>
       </c>
       <c r="E192">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F192" t="s">
         <v>1569</v>
@@ -14860,7 +14860,7 @@
         <v>1463</v>
       </c>
       <c r="E193">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F193" t="s">
         <v>1569</v>
@@ -14895,7 +14895,7 @@
         <v>1463</v>
       </c>
       <c r="E194">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F194" t="s">
         <v>1569</v>
@@ -14930,7 +14930,7 @@
         <v>1464</v>
       </c>
       <c r="E195">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F195" t="s">
         <v>1569</v>
@@ -14965,7 +14965,7 @@
         <v>1464</v>
       </c>
       <c r="E196">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F196" t="s">
         <v>1569</v>
@@ -15000,7 +15000,7 @@
         <v>1464</v>
       </c>
       <c r="E197">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F197" t="s">
         <v>1569</v>
@@ -15035,7 +15035,7 @@
         <v>1464</v>
       </c>
       <c r="E198">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F198" t="s">
         <v>1569</v>
@@ -15070,7 +15070,7 @@
         <v>1465</v>
       </c>
       <c r="E199">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F199" t="s">
         <v>1569</v>
@@ -15105,7 +15105,7 @@
         <v>1465</v>
       </c>
       <c r="E200">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F200" t="s">
         <v>1569</v>
@@ -15140,7 +15140,7 @@
         <v>1466</v>
       </c>
       <c r="E201">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F201" t="s">
         <v>1569</v>
@@ -15175,7 +15175,7 @@
         <v>1466</v>
       </c>
       <c r="E202">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F202" t="s">
         <v>1569</v>
@@ -15210,7 +15210,7 @@
         <v>1467</v>
       </c>
       <c r="E203">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F203" t="s">
         <v>1569</v>
@@ -15245,7 +15245,7 @@
         <v>1467</v>
       </c>
       <c r="E204">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F204" t="s">
         <v>1569</v>
@@ -15280,7 +15280,7 @@
         <v>1468</v>
       </c>
       <c r="E205">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F205" t="s">
         <v>1569</v>
@@ -15315,7 +15315,7 @@
         <v>1469</v>
       </c>
       <c r="E206">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F206" t="s">
         <v>1569</v>
@@ -15350,7 +15350,7 @@
         <v>1469</v>
       </c>
       <c r="E207">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F207" t="s">
         <v>1569</v>
@@ -15385,7 +15385,7 @@
         <v>1470</v>
       </c>
       <c r="E208">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F208" t="s">
         <v>1569</v>
@@ -15420,7 +15420,7 @@
         <v>1470</v>
       </c>
       <c r="E209">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F209" t="s">
         <v>1569</v>
@@ -15455,7 +15455,7 @@
         <v>1471</v>
       </c>
       <c r="E210">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F210" t="s">
         <v>1569</v>
@@ -15490,7 +15490,7 @@
         <v>1472</v>
       </c>
       <c r="E211">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F211" t="s">
         <v>1569</v>
@@ -15525,7 +15525,7 @@
         <v>1472</v>
       </c>
       <c r="E212">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F212" t="s">
         <v>1569</v>
@@ -15560,7 +15560,7 @@
         <v>1472</v>
       </c>
       <c r="E213">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F213" t="s">
         <v>1569</v>
@@ -15595,7 +15595,7 @@
         <v>1473</v>
       </c>
       <c r="E214">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F214" t="s">
         <v>1569</v>
@@ -15630,7 +15630,7 @@
         <v>1473</v>
       </c>
       <c r="E215">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F215" t="s">
         <v>1569</v>
@@ -15665,7 +15665,7 @@
         <v>1474</v>
       </c>
       <c r="E216">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F216" t="s">
         <v>1569</v>
@@ -15700,7 +15700,7 @@
         <v>1475</v>
       </c>
       <c r="E217">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F217" t="s">
         <v>1569</v>
@@ -15735,7 +15735,7 @@
         <v>1475</v>
       </c>
       <c r="E218">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F218" t="s">
         <v>1569</v>
@@ -15770,7 +15770,7 @@
         <v>1475</v>
       </c>
       <c r="E219">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F219" t="s">
         <v>1569</v>
@@ -15805,7 +15805,7 @@
         <v>1476</v>
       </c>
       <c r="E220">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F220" t="s">
         <v>1569</v>
@@ -15840,7 +15840,7 @@
         <v>1476</v>
       </c>
       <c r="E221">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F221" t="s">
         <v>1569</v>
@@ -15875,7 +15875,7 @@
         <v>1477</v>
       </c>
       <c r="E222">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F222" t="s">
         <v>1569</v>
@@ -15910,7 +15910,7 @@
         <v>1477</v>
       </c>
       <c r="E223">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F223" t="s">
         <v>1569</v>
@@ -15945,7 +15945,7 @@
         <v>1477</v>
       </c>
       <c r="E224">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F224" t="s">
         <v>1571</v>
@@ -15980,7 +15980,7 @@
         <v>1477</v>
       </c>
       <c r="E225">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F225" t="s">
         <v>1569</v>
@@ -16015,7 +16015,7 @@
         <v>1478</v>
       </c>
       <c r="E226">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F226" t="s">
         <v>1569</v>
@@ -16050,7 +16050,7 @@
         <v>1478</v>
       </c>
       <c r="E227">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F227" t="s">
         <v>1569</v>
@@ -16088,7 +16088,7 @@
         <v>1478</v>
       </c>
       <c r="E228">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F228" t="s">
         <v>1569</v>
@@ -16123,7 +16123,7 @@
         <v>1478</v>
       </c>
       <c r="E229">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F229" t="s">
         <v>1569</v>
@@ -16158,7 +16158,7 @@
         <v>1478</v>
       </c>
       <c r="E230">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F230" t="s">
         <v>1569</v>
@@ -16193,7 +16193,7 @@
         <v>1478</v>
       </c>
       <c r="E231">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F231" t="s">
         <v>1569</v>
@@ -16228,7 +16228,7 @@
         <v>1479</v>
       </c>
       <c r="E232">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F232" t="s">
         <v>1569</v>
@@ -16263,7 +16263,7 @@
         <v>1479</v>
       </c>
       <c r="E233">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F233" t="s">
         <v>1569</v>
@@ -16298,7 +16298,7 @@
         <v>1479</v>
       </c>
       <c r="E234">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F234" t="s">
         <v>1569</v>
@@ -16333,7 +16333,7 @@
         <v>1480</v>
       </c>
       <c r="E235">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F235" t="s">
         <v>1569</v>
@@ -16368,7 +16368,7 @@
         <v>1480</v>
       </c>
       <c r="E236">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F236" t="s">
         <v>1569</v>
@@ -16403,7 +16403,7 @@
         <v>1480</v>
       </c>
       <c r="E237">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F237" t="s">
         <v>1569</v>
@@ -16438,7 +16438,7 @@
         <v>1480</v>
       </c>
       <c r="E238">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F238" t="s">
         <v>1569</v>
@@ -16473,7 +16473,7 @@
         <v>1481</v>
       </c>
       <c r="E239">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F239" t="s">
         <v>1569</v>
@@ -16508,7 +16508,7 @@
         <v>1481</v>
       </c>
       <c r="E240">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F240" t="s">
         <v>1569</v>
@@ -16543,7 +16543,7 @@
         <v>1481</v>
       </c>
       <c r="E241">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F241" t="s">
         <v>1569</v>
@@ -16578,7 +16578,7 @@
         <v>1481</v>
       </c>
       <c r="E242">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F242" t="s">
         <v>1569</v>
@@ -16613,7 +16613,7 @@
         <v>1482</v>
       </c>
       <c r="E243">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F243" t="s">
         <v>1569</v>
@@ -16648,7 +16648,7 @@
         <v>1482</v>
       </c>
       <c r="E244">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F244" t="s">
         <v>1569</v>
@@ -16683,7 +16683,7 @@
         <v>1482</v>
       </c>
       <c r="E245">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F245" t="s">
         <v>1569</v>
@@ -16718,7 +16718,7 @@
         <v>1482</v>
       </c>
       <c r="E246">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F246" t="s">
         <v>1569</v>
@@ -16753,7 +16753,7 @@
         <v>1482</v>
       </c>
       <c r="E247">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F247" t="s">
         <v>1569</v>
@@ -16788,7 +16788,7 @@
         <v>1482</v>
       </c>
       <c r="E248">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F248" t="s">
         <v>1569</v>
@@ -16823,7 +16823,7 @@
         <v>1483</v>
       </c>
       <c r="E249">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F249" t="s">
         <v>1569</v>
@@ -16858,7 +16858,7 @@
         <v>1484</v>
       </c>
       <c r="E250">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F250" t="s">
         <v>1570</v>
@@ -16893,7 +16893,7 @@
         <v>1484</v>
       </c>
       <c r="E251">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F251" t="s">
         <v>1569</v>
@@ -16928,7 +16928,7 @@
         <v>1484</v>
       </c>
       <c r="E252">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F252" t="s">
         <v>1572</v>
@@ -16963,7 +16963,7 @@
         <v>1484</v>
       </c>
       <c r="E253">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F253" t="s">
         <v>1569</v>
@@ -16998,7 +16998,7 @@
         <v>1484</v>
       </c>
       <c r="E254">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F254" t="s">
         <v>1569</v>
@@ -17033,7 +17033,7 @@
         <v>1484</v>
       </c>
       <c r="E255">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F255" t="s">
         <v>1569</v>
@@ -17068,7 +17068,7 @@
         <v>1485</v>
       </c>
       <c r="E256">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F256" t="s">
         <v>1569</v>
@@ -17103,7 +17103,7 @@
         <v>1485</v>
       </c>
       <c r="E257">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F257" t="s">
         <v>1569</v>
@@ -17138,7 +17138,7 @@
         <v>1485</v>
       </c>
       <c r="E258">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F258" t="s">
         <v>1569</v>
@@ -17173,7 +17173,7 @@
         <v>1485</v>
       </c>
       <c r="E259">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F259" t="s">
         <v>1569</v>
@@ -17208,7 +17208,7 @@
         <v>1486</v>
       </c>
       <c r="E260">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F260" t="s">
         <v>1569</v>
@@ -17243,7 +17243,7 @@
         <v>1487</v>
       </c>
       <c r="E261">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F261" t="s">
         <v>1569</v>
@@ -17281,7 +17281,7 @@
         <v>1488</v>
       </c>
       <c r="E262">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F262" t="s">
         <v>1569</v>
@@ -17316,7 +17316,7 @@
         <v>1488</v>
       </c>
       <c r="E263">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F263" t="s">
         <v>1569</v>
@@ -17351,7 +17351,7 @@
         <v>1488</v>
       </c>
       <c r="E264">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F264" t="s">
         <v>1569</v>
@@ -17386,7 +17386,7 @@
         <v>1488</v>
       </c>
       <c r="E265">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F265" t="s">
         <v>1569</v>
@@ -17424,7 +17424,7 @@
         <v>1488</v>
       </c>
       <c r="E266">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F266" t="s">
         <v>1569</v>
@@ -17459,7 +17459,7 @@
         <v>1489</v>
       </c>
       <c r="E267">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F267" t="s">
         <v>1569</v>
@@ -17494,7 +17494,7 @@
         <v>1489</v>
       </c>
       <c r="E268">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F268" t="s">
         <v>1569</v>
@@ -17529,7 +17529,7 @@
         <v>1490</v>
       </c>
       <c r="E269">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F269" t="s">
         <v>1569</v>
@@ -17564,7 +17564,7 @@
         <v>1490</v>
       </c>
       <c r="E270">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F270" t="s">
         <v>1569</v>
@@ -17599,7 +17599,7 @@
         <v>1491</v>
       </c>
       <c r="E271">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F271" t="s">
         <v>1569</v>
@@ -17634,7 +17634,7 @@
         <v>1491</v>
       </c>
       <c r="E272">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F272" t="s">
         <v>1569</v>
@@ -17669,7 +17669,7 @@
         <v>1491</v>
       </c>
       <c r="E273">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F273" t="s">
         <v>1569</v>
@@ -17704,7 +17704,7 @@
         <v>1492</v>
       </c>
       <c r="E274">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F274" t="s">
         <v>1569</v>
@@ -17739,7 +17739,7 @@
         <v>1492</v>
       </c>
       <c r="E275">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F275" t="s">
         <v>1569</v>
@@ -17774,7 +17774,7 @@
         <v>1492</v>
       </c>
       <c r="E276">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F276" t="s">
         <v>1569</v>
@@ -17809,7 +17809,7 @@
         <v>1492</v>
       </c>
       <c r="E277">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F277" t="s">
         <v>1569</v>
@@ -17844,7 +17844,7 @@
         <v>1493</v>
       </c>
       <c r="E278">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F278" t="s">
         <v>1569</v>
@@ -17879,7 +17879,7 @@
         <v>1494</v>
       </c>
       <c r="E279">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F279" t="s">
         <v>1569</v>
@@ -17914,7 +17914,7 @@
         <v>1494</v>
       </c>
       <c r="E280">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F280" t="s">
         <v>1569</v>
@@ -17949,7 +17949,7 @@
         <v>1494</v>
       </c>
       <c r="E281">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F281" t="s">
         <v>1569</v>
@@ -17984,7 +17984,7 @@
         <v>1494</v>
       </c>
       <c r="E282">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F282" t="s">
         <v>1569</v>
@@ -18019,7 +18019,7 @@
         <v>1495</v>
       </c>
       <c r="E283">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F283" t="s">
         <v>1569</v>
@@ -18054,7 +18054,7 @@
         <v>1495</v>
       </c>
       <c r="E284">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F284" t="s">
         <v>1569</v>
@@ -18089,7 +18089,7 @@
         <v>1495</v>
       </c>
       <c r="E285">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F285" t="s">
         <v>1569</v>
@@ -18124,7 +18124,7 @@
         <v>1496</v>
       </c>
       <c r="E286">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F286" t="s">
         <v>1569</v>
@@ -18159,7 +18159,7 @@
         <v>1496</v>
       </c>
       <c r="E287">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F287" t="s">
         <v>1569</v>
@@ -18194,7 +18194,7 @@
         <v>1497</v>
       </c>
       <c r="E288">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F288" t="s">
         <v>1569</v>
@@ -18229,7 +18229,7 @@
         <v>1497</v>
       </c>
       <c r="E289">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F289" t="s">
         <v>1569</v>
@@ -18264,7 +18264,7 @@
         <v>1497</v>
       </c>
       <c r="E290">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F290" t="s">
         <v>1569</v>
@@ -18299,7 +18299,7 @@
         <v>1497</v>
       </c>
       <c r="E291">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F291" t="s">
         <v>1569</v>
@@ -18334,7 +18334,7 @@
         <v>1497</v>
       </c>
       <c r="E292">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F292" t="s">
         <v>1569</v>
@@ -18369,7 +18369,7 @@
         <v>1498</v>
       </c>
       <c r="E293">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F293" t="s">
         <v>1569</v>
@@ -18404,7 +18404,7 @@
         <v>1498</v>
       </c>
       <c r="E294">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F294" t="s">
         <v>1569</v>
@@ -18439,7 +18439,7 @@
         <v>1498</v>
       </c>
       <c r="E295">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F295" t="s">
         <v>1569</v>
@@ -18474,7 +18474,7 @@
         <v>1499</v>
       </c>
       <c r="E296">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F296" t="s">
         <v>1569</v>
@@ -18509,7 +18509,7 @@
         <v>1500</v>
       </c>
       <c r="E297">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F297" t="s">
         <v>1569</v>
@@ -18544,7 +18544,7 @@
         <v>1501</v>
       </c>
       <c r="E298">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F298" t="s">
         <v>1569</v>
@@ -18579,7 +18579,7 @@
         <v>1501</v>
       </c>
       <c r="E299">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F299" t="s">
         <v>1569</v>
@@ -18614,7 +18614,7 @@
         <v>1501</v>
       </c>
       <c r="E300">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F300" t="s">
         <v>1569</v>
@@ -18649,7 +18649,7 @@
         <v>1501</v>
       </c>
       <c r="E301">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F301" t="s">
         <v>1569</v>
@@ -18684,7 +18684,7 @@
         <v>1501</v>
       </c>
       <c r="E302">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F302" t="s">
         <v>1569</v>
@@ -18719,7 +18719,7 @@
         <v>1502</v>
       </c>
       <c r="E303">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F303" t="s">
         <v>1569</v>
@@ -18754,7 +18754,7 @@
         <v>1502</v>
       </c>
       <c r="E304">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F304" t="s">
         <v>1569</v>
@@ -18789,7 +18789,7 @@
         <v>1503</v>
       </c>
       <c r="E305">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F305" t="s">
         <v>1569</v>
@@ -18824,7 +18824,7 @@
         <v>1503</v>
       </c>
       <c r="E306">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F306" t="s">
         <v>1569</v>
@@ -18859,7 +18859,7 @@
         <v>1504</v>
       </c>
       <c r="E307">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F307" t="s">
         <v>1569</v>
@@ -18894,7 +18894,7 @@
         <v>1505</v>
       </c>
       <c r="E308">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F308" t="s">
         <v>1569</v>
@@ -18929,7 +18929,7 @@
         <v>1506</v>
       </c>
       <c r="E309">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F309" t="s">
         <v>1569</v>
@@ -18964,7 +18964,7 @@
         <v>1506</v>
       </c>
       <c r="E310">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F310" t="s">
         <v>1569</v>
@@ -18999,7 +18999,7 @@
         <v>1507</v>
       </c>
       <c r="E311">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F311" t="s">
         <v>1569</v>
@@ -19034,7 +19034,7 @@
         <v>1507</v>
       </c>
       <c r="E312">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F312" t="s">
         <v>1569</v>
@@ -19069,7 +19069,7 @@
         <v>1507</v>
       </c>
       <c r="E313">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F313" t="s">
         <v>1569</v>
@@ -19104,7 +19104,7 @@
         <v>1508</v>
       </c>
       <c r="E314">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F314" t="s">
         <v>1569</v>
@@ -19139,7 +19139,7 @@
         <v>1508</v>
       </c>
       <c r="E315">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F315" t="s">
         <v>1569</v>
@@ -19174,7 +19174,7 @@
         <v>1508</v>
       </c>
       <c r="E316">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F316" t="s">
         <v>1569</v>
@@ -19209,7 +19209,7 @@
         <v>1508</v>
       </c>
       <c r="E317">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F317" t="s">
         <v>1569</v>
@@ -19244,7 +19244,7 @@
         <v>1508</v>
       </c>
       <c r="E318">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F318" t="s">
         <v>1569</v>
@@ -19279,7 +19279,7 @@
         <v>1508</v>
       </c>
       <c r="E319">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F319" t="s">
         <v>1569</v>
@@ -19314,7 +19314,7 @@
         <v>1508</v>
       </c>
       <c r="E320">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F320" t="s">
         <v>1569</v>
@@ -19349,7 +19349,7 @@
         <v>1508</v>
       </c>
       <c r="E321">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F321" t="s">
         <v>1569</v>
@@ -19384,7 +19384,7 @@
         <v>1508</v>
       </c>
       <c r="E322">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F322" t="s">
         <v>1569</v>
@@ -19419,7 +19419,7 @@
         <v>1509</v>
       </c>
       <c r="E323">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F323" t="s">
         <v>1569</v>
@@ -19454,7 +19454,7 @@
         <v>1509</v>
       </c>
       <c r="E324">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F324" t="s">
         <v>1569</v>
@@ -19489,7 +19489,7 @@
         <v>1509</v>
       </c>
       <c r="E325">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F325" t="s">
         <v>1569</v>
@@ -19524,7 +19524,7 @@
         <v>1510</v>
       </c>
       <c r="E326">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F326" t="s">
         <v>1569</v>
@@ -19559,7 +19559,7 @@
         <v>1511</v>
       </c>
       <c r="E327">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F327" t="s">
         <v>1569</v>
@@ -19594,7 +19594,7 @@
         <v>1511</v>
       </c>
       <c r="E328">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F328" t="s">
         <v>1569</v>
@@ -19629,7 +19629,7 @@
         <v>1511</v>
       </c>
       <c r="E329">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F329" t="s">
         <v>1569</v>
@@ -19664,7 +19664,7 @@
         <v>1511</v>
       </c>
       <c r="E330">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F330" t="s">
         <v>1569</v>
@@ -19699,7 +19699,7 @@
         <v>1511</v>
       </c>
       <c r="E331">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F331" t="s">
         <v>1573</v>
@@ -19737,7 +19737,7 @@
         <v>1511</v>
       </c>
       <c r="E332">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F332" t="s">
         <v>1569</v>
@@ -19772,7 +19772,7 @@
         <v>1511</v>
       </c>
       <c r="E333">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F333" t="s">
         <v>1569</v>
@@ -19807,7 +19807,7 @@
         <v>1512</v>
       </c>
       <c r="E334">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F334" t="s">
         <v>1569</v>
@@ -19842,7 +19842,7 @@
         <v>1512</v>
       </c>
       <c r="E335">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F335" t="s">
         <v>1569</v>
@@ -19877,7 +19877,7 @@
         <v>1512</v>
       </c>
       <c r="E336">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F336" t="s">
         <v>1569</v>
@@ -19912,7 +19912,7 @@
         <v>1512</v>
       </c>
       <c r="E337">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F337" t="s">
         <v>1569</v>
@@ -19950,7 +19950,7 @@
         <v>1512</v>
       </c>
       <c r="E338">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F338" t="s">
         <v>1569</v>
@@ -19985,7 +19985,7 @@
         <v>1512</v>
       </c>
       <c r="E339">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F339" t="s">
         <v>1569</v>
@@ -20020,7 +20020,7 @@
         <v>1512</v>
       </c>
       <c r="E340">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F340" t="s">
         <v>1569</v>
@@ -20055,7 +20055,7 @@
         <v>1512</v>
       </c>
       <c r="E341">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F341" t="s">
         <v>1569</v>
@@ -20090,7 +20090,7 @@
         <v>1512</v>
       </c>
       <c r="E342">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F342" t="s">
         <v>1569</v>
@@ -20125,7 +20125,7 @@
         <v>1513</v>
       </c>
       <c r="E343">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F343" t="s">
         <v>1570</v>
@@ -20160,7 +20160,7 @@
         <v>1514</v>
       </c>
       <c r="E344">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F344" t="s">
         <v>1573</v>
@@ -20195,7 +20195,7 @@
         <v>1515</v>
       </c>
       <c r="E345">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F345" t="s">
         <v>1569</v>
@@ -20230,7 +20230,7 @@
         <v>1516</v>
       </c>
       <c r="E346">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F346" t="s">
         <v>1569</v>
@@ -20265,7 +20265,7 @@
         <v>1516</v>
       </c>
       <c r="E347">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F347" t="s">
         <v>1569</v>
@@ -20300,7 +20300,7 @@
         <v>1517</v>
       </c>
       <c r="E348">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F348" t="s">
         <v>1569</v>
@@ -20335,7 +20335,7 @@
         <v>1518</v>
       </c>
       <c r="E349">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F349" t="s">
         <v>1572</v>
@@ -20370,7 +20370,7 @@
         <v>1518</v>
       </c>
       <c r="E350">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F350" t="s">
         <v>1569</v>
@@ -20405,7 +20405,7 @@
         <v>1518</v>
       </c>
       <c r="E351">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F351" t="s">
         <v>1569</v>
@@ -20440,7 +20440,7 @@
         <v>1518</v>
       </c>
       <c r="E352">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F352" t="s">
         <v>1569</v>
@@ -20475,7 +20475,7 @@
         <v>1518</v>
       </c>
       <c r="E353">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F353" t="s">
         <v>1569</v>
@@ -20510,7 +20510,7 @@
         <v>1518</v>
       </c>
       <c r="E354">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F354" t="s">
         <v>1569</v>
@@ -20545,7 +20545,7 @@
         <v>1519</v>
       </c>
       <c r="E355">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F355" t="s">
         <v>1569</v>
@@ -20580,7 +20580,7 @@
         <v>1519</v>
       </c>
       <c r="E356">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F356" t="s">
         <v>1569</v>
@@ -20615,7 +20615,7 @@
         <v>1519</v>
       </c>
       <c r="E357">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F357" t="s">
         <v>1569</v>
@@ -20650,7 +20650,7 @@
         <v>1520</v>
       </c>
       <c r="E358">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F358" t="s">
         <v>1569</v>
@@ -20685,7 +20685,7 @@
         <v>1520</v>
       </c>
       <c r="E359">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F359" t="s">
         <v>1569</v>
@@ -20720,7 +20720,7 @@
         <v>1520</v>
       </c>
       <c r="E360">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F360" t="s">
         <v>1569</v>
@@ -20758,7 +20758,7 @@
         <v>1520</v>
       </c>
       <c r="E361">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F361" t="s">
         <v>1569</v>
@@ -20793,7 +20793,7 @@
         <v>1521</v>
       </c>
       <c r="E362">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F362" t="s">
         <v>1569</v>
@@ -20828,7 +20828,7 @@
         <v>1521</v>
       </c>
       <c r="E363">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F363" t="s">
         <v>1569</v>
@@ -20863,7 +20863,7 @@
         <v>1521</v>
       </c>
       <c r="E364">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F364" t="s">
         <v>1569</v>
@@ -20898,7 +20898,7 @@
         <v>1521</v>
       </c>
       <c r="E365">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F365" t="s">
         <v>1569</v>
@@ -20933,7 +20933,7 @@
         <v>1521</v>
       </c>
       <c r="E366">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F366" t="s">
         <v>1569</v>
@@ -20968,7 +20968,7 @@
         <v>1522</v>
       </c>
       <c r="E367">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F367" t="s">
         <v>1569</v>
@@ -21003,7 +21003,7 @@
         <v>1522</v>
       </c>
       <c r="E368">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F368" t="s">
         <v>1569</v>
@@ -21038,7 +21038,7 @@
         <v>1523</v>
       </c>
       <c r="E369">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F369" t="s">
         <v>1569</v>
@@ -21073,7 +21073,7 @@
         <v>1523</v>
       </c>
       <c r="E370">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F370" t="s">
         <v>1569</v>
@@ -21108,7 +21108,7 @@
         <v>1523</v>
       </c>
       <c r="E371">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F371" t="s">
         <v>1569</v>
@@ -21143,7 +21143,7 @@
         <v>1523</v>
       </c>
       <c r="E372">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F372" t="s">
         <v>1569</v>
@@ -21178,7 +21178,7 @@
         <v>1523</v>
       </c>
       <c r="E373">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F373" t="s">
         <v>1569</v>
@@ -21213,7 +21213,7 @@
         <v>1523</v>
       </c>
       <c r="E374">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F374" t="s">
         <v>1569</v>
@@ -21248,7 +21248,7 @@
         <v>1523</v>
       </c>
       <c r="E375">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F375" t="s">
         <v>1569</v>
@@ -21283,7 +21283,7 @@
         <v>1523</v>
       </c>
       <c r="E376">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F376" t="s">
         <v>1569</v>
@@ -21318,7 +21318,7 @@
         <v>1523</v>
       </c>
       <c r="E377">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F377" t="s">
         <v>1569</v>
@@ -21353,7 +21353,7 @@
         <v>1523</v>
       </c>
       <c r="E378">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F378" t="s">
         <v>1569</v>
@@ -21388,7 +21388,7 @@
         <v>1524</v>
       </c>
       <c r="E379">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F379" t="s">
         <v>1569</v>
@@ -21423,7 +21423,7 @@
         <v>1524</v>
       </c>
       <c r="E380">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F380" t="s">
         <v>1569</v>
@@ -21458,7 +21458,7 @@
         <v>1524</v>
       </c>
       <c r="E381">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F381" t="s">
         <v>1570</v>
@@ -21493,7 +21493,7 @@
         <v>1525</v>
       </c>
       <c r="E382">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F382" t="s">
         <v>1569</v>
@@ -21528,7 +21528,7 @@
         <v>1525</v>
       </c>
       <c r="E383">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F383" t="s">
         <v>1569</v>
@@ -21563,7 +21563,7 @@
         <v>1525</v>
       </c>
       <c r="E384">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F384" t="s">
         <v>1569</v>
@@ -21598,7 +21598,7 @@
         <v>1525</v>
       </c>
       <c r="E385">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F385" t="s">
         <v>1569</v>
@@ -21633,7 +21633,7 @@
         <v>1525</v>
       </c>
       <c r="E386">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F386" t="s">
         <v>1569</v>
@@ -21668,7 +21668,7 @@
         <v>1525</v>
       </c>
       <c r="E387">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F387" t="s">
         <v>1569</v>
@@ -21703,7 +21703,7 @@
         <v>1525</v>
       </c>
       <c r="E388">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F388" t="s">
         <v>1572</v>
@@ -21738,7 +21738,7 @@
         <v>1526</v>
       </c>
       <c r="E389">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F389" t="s">
         <v>1569</v>
@@ -21773,7 +21773,7 @@
         <v>1526</v>
       </c>
       <c r="E390">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F390" t="s">
         <v>1569</v>
@@ -21808,7 +21808,7 @@
         <v>1526</v>
       </c>
       <c r="E391">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F391" t="s">
         <v>1569</v>
@@ -21843,7 +21843,7 @@
         <v>1526</v>
       </c>
       <c r="E392">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F392" t="s">
         <v>1569</v>
@@ -21878,7 +21878,7 @@
         <v>1527</v>
       </c>
       <c r="E393">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F393" t="s">
         <v>1572</v>
@@ -21913,7 +21913,7 @@
         <v>1527</v>
       </c>
       <c r="E394">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F394" t="s">
         <v>1569</v>
@@ -21948,7 +21948,7 @@
         <v>1527</v>
       </c>
       <c r="E395">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F395" t="s">
         <v>1569</v>
@@ -21983,7 +21983,7 @@
         <v>1527</v>
       </c>
       <c r="E396">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F396" t="s">
         <v>1569</v>
@@ -22018,7 +22018,7 @@
         <v>1527</v>
       </c>
       <c r="E397">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F397" t="s">
         <v>1569</v>
@@ -22053,7 +22053,7 @@
         <v>1527</v>
       </c>
       <c r="E398">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F398" t="s">
         <v>1569</v>
@@ -22088,7 +22088,7 @@
         <v>1528</v>
       </c>
       <c r="E399">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F399" t="s">
         <v>1569</v>
@@ -22123,7 +22123,7 @@
         <v>1528</v>
       </c>
       <c r="E400">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F400" t="s">
         <v>1569</v>
@@ -22158,7 +22158,7 @@
         <v>1528</v>
       </c>
       <c r="E401">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F401" t="s">
         <v>1569</v>
@@ -22193,7 +22193,7 @@
         <v>1528</v>
       </c>
       <c r="E402">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F402" t="s">
         <v>1569</v>
@@ -22228,7 +22228,7 @@
         <v>1528</v>
       </c>
       <c r="E403">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F403" t="s">
         <v>1571</v>
@@ -22263,7 +22263,7 @@
         <v>1528</v>
       </c>
       <c r="E404">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F404" t="s">
         <v>1569</v>
@@ -22298,7 +22298,7 @@
         <v>1528</v>
       </c>
       <c r="E405">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F405" t="s">
         <v>1569</v>
@@ -22333,7 +22333,7 @@
         <v>1529</v>
       </c>
       <c r="E406">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F406" t="s">
         <v>1569</v>
@@ -22368,7 +22368,7 @@
         <v>1529</v>
       </c>
       <c r="E407">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F407" t="s">
         <v>1569</v>
@@ -22403,7 +22403,7 @@
         <v>1529</v>
       </c>
       <c r="E408">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F408" t="s">
         <v>1569</v>
@@ -22438,7 +22438,7 @@
         <v>1529</v>
       </c>
       <c r="E409">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F409" t="s">
         <v>1569</v>
@@ -22473,7 +22473,7 @@
         <v>1529</v>
       </c>
       <c r="E410">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F410" t="s">
         <v>1569</v>
@@ -22508,7 +22508,7 @@
         <v>1530</v>
       </c>
       <c r="E411">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F411" t="s">
         <v>1569</v>
@@ -22543,7 +22543,7 @@
         <v>1530</v>
       </c>
       <c r="E412">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F412" t="s">
         <v>1569</v>
@@ -22578,7 +22578,7 @@
         <v>1530</v>
       </c>
       <c r="E413">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F413" t="s">
         <v>1569</v>
@@ -22613,7 +22613,7 @@
         <v>1530</v>
       </c>
       <c r="E414">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F414" t="s">
         <v>1569</v>
@@ -22648,7 +22648,7 @@
         <v>1530</v>
       </c>
       <c r="E415">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F415" t="s">
         <v>1569</v>
@@ -22686,7 +22686,7 @@
         <v>1531</v>
       </c>
       <c r="E416">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F416" t="s">
         <v>1569</v>
@@ -22721,7 +22721,7 @@
         <v>1531</v>
       </c>
       <c r="E417">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F417" t="s">
         <v>1569</v>
@@ -22756,7 +22756,7 @@
         <v>1531</v>
       </c>
       <c r="E418">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F418" t="s">
         <v>1569</v>
@@ -22791,7 +22791,7 @@
         <v>1531</v>
       </c>
       <c r="E419">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F419" t="s">
         <v>1569</v>
@@ -22826,7 +22826,7 @@
         <v>1531</v>
       </c>
       <c r="E420">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F420" t="s">
         <v>1569</v>
@@ -22861,7 +22861,7 @@
         <v>1531</v>
       </c>
       <c r="E421">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F421" t="s">
         <v>1569</v>
@@ -22896,7 +22896,7 @@
         <v>1532</v>
       </c>
       <c r="E422">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F422" t="s">
         <v>1570</v>
@@ -22931,7 +22931,7 @@
         <v>1532</v>
       </c>
       <c r="E423">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F423" t="s">
         <v>1569</v>
@@ -22966,7 +22966,7 @@
         <v>1533</v>
       </c>
       <c r="E424">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F424" t="s">
         <v>1569</v>
@@ -23001,7 +23001,7 @@
         <v>1534</v>
       </c>
       <c r="E425">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F425" t="s">
         <v>1569</v>
@@ -23036,7 +23036,7 @@
         <v>1534</v>
       </c>
       <c r="E426">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F426" t="s">
         <v>1569</v>
@@ -23071,7 +23071,7 @@
         <v>1534</v>
       </c>
       <c r="E427">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F427" t="s">
         <v>1571</v>
@@ -23109,7 +23109,7 @@
         <v>1534</v>
       </c>
       <c r="E428">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F428" t="s">
         <v>1569</v>
@@ -23144,7 +23144,7 @@
         <v>1535</v>
       </c>
       <c r="E429">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F429" t="s">
         <v>1569</v>
@@ -23179,7 +23179,7 @@
         <v>1535</v>
       </c>
       <c r="E430">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F430" t="s">
         <v>1569</v>
@@ -23214,7 +23214,7 @@
         <v>1535</v>
       </c>
       <c r="E431">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F431" t="s">
         <v>1569</v>
@@ -23249,7 +23249,7 @@
         <v>1535</v>
       </c>
       <c r="E432">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F432" t="s">
         <v>1569</v>
@@ -23284,7 +23284,7 @@
         <v>1536</v>
       </c>
       <c r="E433">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F433" t="s">
         <v>1569</v>
@@ -23319,7 +23319,7 @@
         <v>1536</v>
       </c>
       <c r="E434">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F434" t="s">
         <v>1569</v>
@@ -23354,7 +23354,7 @@
         <v>1536</v>
       </c>
       <c r="E435">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F435" t="s">
         <v>1569</v>
@@ -23389,7 +23389,7 @@
         <v>1536</v>
       </c>
       <c r="E436">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F436" t="s">
         <v>1569</v>
@@ -23424,7 +23424,7 @@
         <v>1536</v>
       </c>
       <c r="E437">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F437" t="s">
         <v>1569</v>
@@ -23459,7 +23459,7 @@
         <v>1536</v>
       </c>
       <c r="E438">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F438" t="s">
         <v>1569</v>
@@ -23494,7 +23494,7 @@
         <v>1536</v>
       </c>
       <c r="E439">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F439" t="s">
         <v>1569</v>
@@ -23529,7 +23529,7 @@
         <v>1536</v>
       </c>
       <c r="E440">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F440" t="s">
         <v>1569</v>
@@ -23564,7 +23564,7 @@
         <v>1537</v>
       </c>
       <c r="E441">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F441" t="s">
         <v>1569</v>
@@ -23599,7 +23599,7 @@
         <v>1537</v>
       </c>
       <c r="E442">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F442" t="s">
         <v>1569</v>
@@ -23634,7 +23634,7 @@
         <v>1538</v>
       </c>
       <c r="E443">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F443" t="s">
         <v>1569</v>
@@ -23669,7 +23669,7 @@
         <v>1538</v>
       </c>
       <c r="E444">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F444" t="s">
         <v>1569</v>
@@ -23704,7 +23704,7 @@
         <v>1538</v>
       </c>
       <c r="E445">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F445" t="s">
         <v>1569</v>
@@ -23739,7 +23739,7 @@
         <v>1538</v>
       </c>
       <c r="E446">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F446" t="s">
         <v>1573</v>
@@ -23777,7 +23777,7 @@
         <v>1538</v>
       </c>
       <c r="E447">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F447" t="s">
         <v>1569</v>
@@ -23812,7 +23812,7 @@
         <v>1538</v>
       </c>
       <c r="E448">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F448" t="s">
         <v>1573</v>
@@ -23847,7 +23847,7 @@
         <v>1539</v>
       </c>
       <c r="E449">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F449" t="s">
         <v>1569</v>
@@ -23882,7 +23882,7 @@
         <v>1540</v>
       </c>
       <c r="E450">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F450" t="s">
         <v>1569</v>
@@ -23917,7 +23917,7 @@
         <v>1540</v>
       </c>
       <c r="E451">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F451" t="s">
         <v>1569</v>
@@ -23952,7 +23952,7 @@
         <v>1540</v>
       </c>
       <c r="E452">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F452" t="s">
         <v>1569</v>
@@ -23987,7 +23987,7 @@
         <v>1540</v>
       </c>
       <c r="E453">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F453" t="s">
         <v>1569</v>
@@ -24022,7 +24022,7 @@
         <v>1541</v>
       </c>
       <c r="E454">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F454" t="s">
         <v>1569</v>
@@ -24057,7 +24057,7 @@
         <v>1541</v>
       </c>
       <c r="E455">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F455" t="s">
         <v>1573</v>
@@ -24092,7 +24092,7 @@
         <v>1541</v>
       </c>
       <c r="E456">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F456" t="s">
         <v>1569</v>
@@ -24127,7 +24127,7 @@
         <v>1541</v>
       </c>
       <c r="E457">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F457" t="s">
         <v>1569</v>
@@ -24162,7 +24162,7 @@
         <v>1541</v>
       </c>
       <c r="E458">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F458" t="s">
         <v>1569</v>
@@ -24197,7 +24197,7 @@
         <v>1542</v>
       </c>
       <c r="E459">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F459" t="s">
         <v>1569</v>
@@ -24232,7 +24232,7 @@
         <v>1542</v>
       </c>
       <c r="E460">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F460" t="s">
         <v>1569</v>
@@ -24267,7 +24267,7 @@
         <v>1542</v>
       </c>
       <c r="E461">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F461" t="s">
         <v>1569</v>
@@ -24302,7 +24302,7 @@
         <v>1543</v>
       </c>
       <c r="E462">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F462" t="s">
         <v>1569</v>
@@ -24337,7 +24337,7 @@
         <v>1543</v>
       </c>
       <c r="E463">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F463" t="s">
         <v>1569</v>
@@ -24372,7 +24372,7 @@
         <v>1543</v>
       </c>
       <c r="E464">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F464" t="s">
         <v>1569</v>
@@ -24407,7 +24407,7 @@
         <v>1543</v>
       </c>
       <c r="E465">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F465" t="s">
         <v>1569</v>
@@ -24442,7 +24442,7 @@
         <v>1543</v>
       </c>
       <c r="E466">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F466" t="s">
         <v>1569</v>
@@ -24477,7 +24477,7 @@
         <v>1543</v>
       </c>
       <c r="E467">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F467" t="s">
         <v>1569</v>
@@ -24512,7 +24512,7 @@
         <v>1544</v>
       </c>
       <c r="E468">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F468" t="s">
         <v>1569</v>
@@ -24547,7 +24547,7 @@
         <v>1544</v>
       </c>
       <c r="E469">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F469" t="s">
         <v>1569</v>
@@ -24582,7 +24582,7 @@
         <v>1544</v>
       </c>
       <c r="E470">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F470" t="s">
         <v>1569</v>
@@ -24617,7 +24617,7 @@
         <v>1544</v>
       </c>
       <c r="E471">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F471" t="s">
         <v>1569</v>
@@ -24652,7 +24652,7 @@
         <v>1544</v>
       </c>
       <c r="E472">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F472" t="s">
         <v>1569</v>
@@ -24687,7 +24687,7 @@
         <v>1544</v>
       </c>
       <c r="E473">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F473" t="s">
         <v>1569</v>
@@ -24722,7 +24722,7 @@
         <v>1544</v>
       </c>
       <c r="E474">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F474" t="s">
         <v>1569</v>
@@ -24757,7 +24757,7 @@
         <v>1544</v>
       </c>
       <c r="E475">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F475" t="s">
         <v>1569</v>
@@ -24792,7 +24792,7 @@
         <v>1544</v>
       </c>
       <c r="E476">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F476" t="s">
         <v>1569</v>
@@ -24827,7 +24827,7 @@
         <v>1544</v>
       </c>
       <c r="E477">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F477" t="s">
         <v>1569</v>
@@ -24862,7 +24862,7 @@
         <v>1544</v>
       </c>
       <c r="E478">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F478" t="s">
         <v>1569</v>
@@ -24897,7 +24897,7 @@
         <v>1544</v>
       </c>
       <c r="E479">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F479" t="s">
         <v>1569</v>
@@ -24932,7 +24932,7 @@
         <v>1544</v>
       </c>
       <c r="E480">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F480" t="s">
         <v>1569</v>
@@ -24967,7 +24967,7 @@
         <v>1544</v>
       </c>
       <c r="E481">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F481" t="s">
         <v>1569</v>
@@ -25002,7 +25002,7 @@
         <v>1544</v>
       </c>
       <c r="E482">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F482" t="s">
         <v>1569</v>
@@ -25037,7 +25037,7 @@
         <v>1544</v>
       </c>
       <c r="E483">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F483" t="s">
         <v>1569</v>
@@ -25072,7 +25072,7 @@
         <v>1544</v>
       </c>
       <c r="E484">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F484" t="s">
         <v>1569</v>
@@ -25107,7 +25107,7 @@
         <v>1544</v>
       </c>
       <c r="E485">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F485" t="s">
         <v>1569</v>
@@ -25142,7 +25142,7 @@
         <v>1544</v>
       </c>
       <c r="E486">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F486" t="s">
         <v>1569</v>
@@ -25177,7 +25177,7 @@
         <v>1544</v>
       </c>
       <c r="E487">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F487" t="s">
         <v>1569</v>
@@ -25212,7 +25212,7 @@
         <v>1544</v>
       </c>
       <c r="E488">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F488" t="s">
         <v>1569</v>
@@ -25247,7 +25247,7 @@
         <v>1544</v>
       </c>
       <c r="E489">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F489" t="s">
         <v>1569</v>
@@ -25282,7 +25282,7 @@
         <v>1544</v>
       </c>
       <c r="E490">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F490" t="s">
         <v>1569</v>
@@ -25317,7 +25317,7 @@
         <v>1544</v>
       </c>
       <c r="E491">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F491" t="s">
         <v>1569</v>
@@ -25352,7 +25352,7 @@
         <v>1544</v>
       </c>
       <c r="E492">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F492" t="s">
         <v>1569</v>
@@ -25387,7 +25387,7 @@
         <v>1545</v>
       </c>
       <c r="E493">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F493" t="s">
         <v>1569</v>
@@ -25422,7 +25422,7 @@
         <v>1545</v>
       </c>
       <c r="E494">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F494" t="s">
         <v>1569</v>
@@ -25457,7 +25457,7 @@
         <v>1545</v>
       </c>
       <c r="E495">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F495" t="s">
         <v>1569</v>
@@ -25492,7 +25492,7 @@
         <v>1545</v>
       </c>
       <c r="E496">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F496" t="s">
         <v>1569</v>
@@ -25527,7 +25527,7 @@
         <v>1545</v>
       </c>
       <c r="E497">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F497" t="s">
         <v>1569</v>
@@ -25562,7 +25562,7 @@
         <v>1545</v>
       </c>
       <c r="E498">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F498" t="s">
         <v>1569</v>
@@ -25597,7 +25597,7 @@
         <v>1545</v>
       </c>
       <c r="E499">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F499" t="s">
         <v>1573</v>
@@ -25632,7 +25632,7 @@
         <v>1545</v>
       </c>
       <c r="E500">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F500" t="s">
         <v>1569</v>
@@ -25667,7 +25667,7 @@
         <v>1546</v>
       </c>
       <c r="E501">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F501" t="s">
         <v>1569</v>
@@ -25702,7 +25702,7 @@
         <v>1546</v>
       </c>
       <c r="E502">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F502" t="s">
         <v>1571</v>
@@ -25740,7 +25740,7 @@
         <v>1547</v>
       </c>
       <c r="E503">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F503" t="s">
         <v>1571</v>
@@ -25778,7 +25778,7 @@
         <v>1547</v>
       </c>
       <c r="E504">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F504" t="s">
         <v>1569</v>
@@ -25813,7 +25813,7 @@
         <v>1547</v>
       </c>
       <c r="E505">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F505" t="s">
         <v>1571</v>
@@ -25851,7 +25851,7 @@
         <v>1547</v>
       </c>
       <c r="E506">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F506" t="s">
         <v>1569</v>
@@ -25886,7 +25886,7 @@
         <v>1547</v>
       </c>
       <c r="E507">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F507" t="s">
         <v>1569</v>
@@ -25921,7 +25921,7 @@
         <v>1547</v>
       </c>
       <c r="E508">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F508" t="s">
         <v>1569</v>
@@ -25956,7 +25956,7 @@
         <v>1547</v>
       </c>
       <c r="E509">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F509" t="s">
         <v>1569</v>
@@ -25991,7 +25991,7 @@
         <v>1548</v>
       </c>
       <c r="E510">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F510" t="s">
         <v>1569</v>
@@ -26029,7 +26029,7 @@
         <v>1548</v>
       </c>
       <c r="E511">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F511" t="s">
         <v>1573</v>
@@ -26064,7 +26064,7 @@
         <v>1548</v>
       </c>
       <c r="E512">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F512" t="s">
         <v>1571</v>
@@ -26099,7 +26099,7 @@
         <v>1548</v>
       </c>
       <c r="E513">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F513" t="s">
         <v>1569</v>
@@ -26134,7 +26134,7 @@
         <v>1548</v>
       </c>
       <c r="E514">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F514" t="s">
         <v>1569</v>
@@ -26169,7 +26169,7 @@
         <v>1548</v>
       </c>
       <c r="E515">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F515" t="s">
         <v>1569</v>
@@ -26204,7 +26204,7 @@
         <v>1548</v>
       </c>
       <c r="E516">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F516" t="s">
         <v>1569</v>
@@ -26239,7 +26239,7 @@
         <v>1548</v>
       </c>
       <c r="E517">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F517" t="s">
         <v>1569</v>
@@ -26274,7 +26274,7 @@
         <v>1548</v>
       </c>
       <c r="E518">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F518" t="s">
         <v>1569</v>
@@ -26309,7 +26309,7 @@
         <v>1549</v>
       </c>
       <c r="E519">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F519" t="s">
         <v>1569</v>
@@ -26347,7 +26347,7 @@
         <v>1549</v>
       </c>
       <c r="E520">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F520" t="s">
         <v>1569</v>
@@ -26382,7 +26382,7 @@
         <v>1550</v>
       </c>
       <c r="E521">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F521" t="s">
         <v>1569</v>
@@ -26417,7 +26417,7 @@
         <v>1550</v>
       </c>
       <c r="E522">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F522" t="s">
         <v>1569</v>
@@ -26452,7 +26452,7 @@
         <v>1550</v>
       </c>
       <c r="E523">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F523" t="s">
         <v>1569</v>
@@ -26487,7 +26487,7 @@
         <v>1550</v>
       </c>
       <c r="E524">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F524" t="s">
         <v>1569</v>
@@ -26522,7 +26522,7 @@
         <v>1550</v>
       </c>
       <c r="E525">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F525" t="s">
         <v>1569</v>
@@ -26557,7 +26557,7 @@
         <v>1550</v>
       </c>
       <c r="E526">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F526" t="s">
         <v>1569</v>
@@ -26592,7 +26592,7 @@
         <v>1550</v>
       </c>
       <c r="E527">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F527" t="s">
         <v>1569</v>
@@ -26627,7 +26627,7 @@
         <v>1551</v>
       </c>
       <c r="E528">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F528" t="s">
         <v>1569</v>
@@ -26662,7 +26662,7 @@
         <v>1551</v>
       </c>
       <c r="E529">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F529" t="s">
         <v>1569</v>
@@ -26697,7 +26697,7 @@
         <v>1551</v>
       </c>
       <c r="E530">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F530" t="s">
         <v>1569</v>
@@ -26732,7 +26732,7 @@
         <v>1551</v>
       </c>
       <c r="E531">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F531" t="s">
         <v>1569</v>
@@ -26767,7 +26767,7 @@
         <v>1551</v>
       </c>
       <c r="E532">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F532" t="s">
         <v>1569</v>
@@ -26802,7 +26802,7 @@
         <v>1551</v>
       </c>
       <c r="E533">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F533" t="s">
         <v>1569</v>
@@ -26837,7 +26837,7 @@
         <v>1551</v>
       </c>
       <c r="E534">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F534" t="s">
         <v>1569</v>
@@ -26872,7 +26872,7 @@
         <v>1551</v>
       </c>
       <c r="E535">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F535" t="s">
         <v>1569</v>
@@ -26907,7 +26907,7 @@
         <v>1551</v>
       </c>
       <c r="E536">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F536" t="s">
         <v>1571</v>
@@ -26942,7 +26942,7 @@
         <v>1551</v>
       </c>
       <c r="E537">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F537" t="s">
         <v>1569</v>
@@ -26977,7 +26977,7 @@
         <v>1551</v>
       </c>
       <c r="E538">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F538" t="s">
         <v>1573</v>
@@ -27012,7 +27012,7 @@
         <v>1551</v>
       </c>
       <c r="E539">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F539" t="s">
         <v>1569</v>
@@ -27047,7 +27047,7 @@
         <v>1552</v>
       </c>
       <c r="E540">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F540" t="s">
         <v>1569</v>
@@ -27082,7 +27082,7 @@
         <v>1552</v>
       </c>
       <c r="E541">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F541" t="s">
         <v>1569</v>
@@ -27117,7 +27117,7 @@
         <v>1552</v>
       </c>
       <c r="E542">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F542" t="s">
         <v>1569</v>
@@ -27152,7 +27152,7 @@
         <v>1552</v>
       </c>
       <c r="E543">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F543" t="s">
         <v>1569</v>
@@ -27187,7 +27187,7 @@
         <v>1552</v>
       </c>
       <c r="E544">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F544" t="s">
         <v>1569</v>
@@ -27222,7 +27222,7 @@
         <v>1552</v>
       </c>
       <c r="E545">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F545" t="s">
         <v>1569</v>
@@ -27257,7 +27257,7 @@
         <v>1552</v>
       </c>
       <c r="E546">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F546" t="s">
         <v>1569</v>
@@ -27292,7 +27292,7 @@
         <v>1552</v>
       </c>
       <c r="E547">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F547" t="s">
         <v>1569</v>
@@ -27330,7 +27330,7 @@
         <v>1552</v>
       </c>
       <c r="E548">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F548" t="s">
         <v>1571</v>
@@ -27368,7 +27368,7 @@
         <v>1552</v>
       </c>
       <c r="E549">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F549" t="s">
         <v>1571</v>
@@ -27403,7 +27403,7 @@
         <v>1552</v>
       </c>
       <c r="E550">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F550" t="s">
         <v>1569</v>
@@ -27438,7 +27438,7 @@
         <v>1553</v>
       </c>
       <c r="E551">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F551" t="s">
         <v>1569</v>
@@ -27473,7 +27473,7 @@
         <v>1553</v>
       </c>
       <c r="E552">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F552" t="s">
         <v>1569</v>
@@ -27508,7 +27508,7 @@
         <v>1553</v>
       </c>
       <c r="E553">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F553" t="s">
         <v>1569</v>
@@ -27543,7 +27543,7 @@
         <v>1553</v>
       </c>
       <c r="E554">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F554" t="s">
         <v>1569</v>
@@ -27578,7 +27578,7 @@
         <v>1553</v>
       </c>
       <c r="E555">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F555" t="s">
         <v>1569</v>
@@ -27613,7 +27613,7 @@
         <v>1553</v>
       </c>
       <c r="E556">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F556" t="s">
         <v>1569</v>
@@ -27648,7 +27648,7 @@
         <v>1553</v>
       </c>
       <c r="E557">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F557" t="s">
         <v>1569</v>
@@ -27683,7 +27683,7 @@
         <v>1553</v>
       </c>
       <c r="E558">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F558" t="s">
         <v>1569</v>
@@ -27721,7 +27721,7 @@
         <v>1554</v>
       </c>
       <c r="E559">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F559" t="s">
         <v>1569</v>
@@ -27756,7 +27756,7 @@
         <v>1555</v>
       </c>
       <c r="E560">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F560" t="s">
         <v>1569</v>
@@ -27794,7 +27794,7 @@
         <v>1555</v>
       </c>
       <c r="E561">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F561" t="s">
         <v>1569</v>
@@ -27829,7 +27829,7 @@
         <v>1555</v>
       </c>
       <c r="E562">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F562" t="s">
         <v>1569</v>
@@ -27864,7 +27864,7 @@
         <v>1555</v>
       </c>
       <c r="E563">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F563" t="s">
         <v>1571</v>
@@ -27902,7 +27902,7 @@
         <v>1555</v>
       </c>
       <c r="E564">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F564" t="s">
         <v>1571</v>
@@ -27940,7 +27940,7 @@
         <v>1555</v>
       </c>
       <c r="E565">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F565" t="s">
         <v>1569</v>
@@ -27975,7 +27975,7 @@
         <v>1555</v>
       </c>
       <c r="E566">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F566" t="s">
         <v>1569</v>
@@ -28010,7 +28010,7 @@
         <v>1555</v>
       </c>
       <c r="E567">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F567" t="s">
         <v>1569</v>
@@ -28045,7 +28045,7 @@
         <v>1556</v>
       </c>
       <c r="E568">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F568" t="s">
         <v>1569</v>
@@ -28080,7 +28080,7 @@
         <v>1556</v>
       </c>
       <c r="E569">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F569" t="s">
         <v>1569</v>
@@ -28115,7 +28115,7 @@
         <v>1556</v>
       </c>
       <c r="E570">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F570" t="s">
         <v>1569</v>
@@ -28150,7 +28150,7 @@
         <v>1556</v>
       </c>
       <c r="E571">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F571" t="s">
         <v>1569</v>
@@ -28185,7 +28185,7 @@
         <v>1556</v>
       </c>
       <c r="E572">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F572" t="s">
         <v>1569</v>
@@ -28220,7 +28220,7 @@
         <v>1556</v>
       </c>
       <c r="E573">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F573" t="s">
         <v>1569</v>
@@ -28255,7 +28255,7 @@
         <v>1556</v>
       </c>
       <c r="E574">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F574" t="s">
         <v>1569</v>
@@ -28290,7 +28290,7 @@
         <v>1556</v>
       </c>
       <c r="E575">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F575" t="s">
         <v>1569</v>
@@ -28325,7 +28325,7 @@
         <v>1556</v>
       </c>
       <c r="E576">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F576" t="s">
         <v>1569</v>
@@ -28360,7 +28360,7 @@
         <v>1556</v>
       </c>
       <c r="E577">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F577" t="s">
         <v>1569</v>
@@ -28398,7 +28398,7 @@
         <v>1556</v>
       </c>
       <c r="E578">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F578" t="s">
         <v>1569</v>
@@ -28433,7 +28433,7 @@
         <v>1557</v>
       </c>
       <c r="E579">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F579" t="s">
         <v>1569</v>
@@ -28468,7 +28468,7 @@
         <v>1557</v>
       </c>
       <c r="E580">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F580" t="s">
         <v>1571</v>
@@ -28506,7 +28506,7 @@
         <v>1557</v>
       </c>
       <c r="E581">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F581" t="s">
         <v>1569</v>
@@ -28541,7 +28541,7 @@
         <v>1557</v>
       </c>
       <c r="E582">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F582" t="s">
         <v>1569</v>
@@ -28576,7 +28576,7 @@
         <v>1558</v>
       </c>
       <c r="E583">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F583" t="s">
         <v>1569</v>
@@ -28611,7 +28611,7 @@
         <v>1558</v>
       </c>
       <c r="E584">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F584" t="s">
         <v>1571</v>
@@ -28646,7 +28646,7 @@
         <v>1558</v>
       </c>
       <c r="E585">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F585" t="s">
         <v>1569</v>
@@ -28681,7 +28681,7 @@
         <v>1558</v>
       </c>
       <c r="E586">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F586" t="s">
         <v>1569</v>
@@ -28716,7 +28716,7 @@
         <v>1558</v>
       </c>
       <c r="E587">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F587" t="s">
         <v>1571</v>
@@ -28754,7 +28754,7 @@
         <v>1558</v>
       </c>
       <c r="E588">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F588" t="s">
         <v>1569</v>
@@ -28789,7 +28789,7 @@
         <v>1558</v>
       </c>
       <c r="E589">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F589" t="s">
         <v>1569</v>
@@ -28824,7 +28824,7 @@
         <v>1558</v>
       </c>
       <c r="E590">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F590" t="s">
         <v>1569</v>
@@ -28859,7 +28859,7 @@
         <v>1558</v>
       </c>
       <c r="E591">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F591" t="s">
         <v>1569</v>
@@ -28894,7 +28894,7 @@
         <v>1558</v>
       </c>
       <c r="E592">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F592" t="s">
         <v>1569</v>
@@ -28929,7 +28929,7 @@
         <v>1558</v>
       </c>
       <c r="E593">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F593" t="s">
         <v>1569</v>
@@ -28964,7 +28964,7 @@
         <v>1558</v>
       </c>
       <c r="E594">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F594" t="s">
         <v>1569</v>
@@ -28999,7 +28999,7 @@
         <v>1559</v>
       </c>
       <c r="E595">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F595" t="s">
         <v>1573</v>
@@ -29034,7 +29034,7 @@
         <v>1559</v>
       </c>
       <c r="E596">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F596" t="s">
         <v>1569</v>
@@ -29069,7 +29069,7 @@
         <v>1559</v>
       </c>
       <c r="E597">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F597" t="s">
         <v>1569</v>
@@ -29104,7 +29104,7 @@
         <v>1559</v>
       </c>
       <c r="E598">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F598" t="s">
         <v>1569</v>
@@ -29139,7 +29139,7 @@
         <v>1559</v>
       </c>
       <c r="E599">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F599" t="s">
         <v>1571</v>
@@ -29174,7 +29174,7 @@
         <v>1559</v>
       </c>
       <c r="E600">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F600" t="s">
         <v>1569</v>
@@ -29209,7 +29209,7 @@
         <v>1559</v>
       </c>
       <c r="E601">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F601" t="s">
         <v>1569</v>
@@ -29244,7 +29244,7 @@
         <v>1560</v>
       </c>
       <c r="E602">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F602" t="s">
         <v>1569</v>
@@ -29282,7 +29282,7 @@
         <v>1560</v>
       </c>
       <c r="E603">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F603" t="s">
         <v>1569</v>
@@ -29317,7 +29317,7 @@
         <v>1560</v>
       </c>
       <c r="E604">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F604" t="s">
         <v>1569</v>
@@ -29352,7 +29352,7 @@
         <v>1560</v>
       </c>
       <c r="E605">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F605" t="s">
         <v>1569</v>
@@ -29387,7 +29387,7 @@
         <v>1560</v>
       </c>
       <c r="E606">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F606" t="s">
         <v>1571</v>
@@ -29425,7 +29425,7 @@
         <v>1561</v>
       </c>
       <c r="E607">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F607" t="s">
         <v>1569</v>
@@ -29460,7 +29460,7 @@
         <v>1561</v>
       </c>
       <c r="E608">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F608" t="s">
         <v>1573</v>
@@ -29498,7 +29498,7 @@
         <v>1561</v>
       </c>
       <c r="E609">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F609" t="s">
         <v>1571</v>
@@ -29536,7 +29536,7 @@
         <v>1561</v>
       </c>
       <c r="E610">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F610" t="s">
         <v>1569</v>
@@ -29571,7 +29571,7 @@
         <v>1561</v>
       </c>
       <c r="E611">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F611" t="s">
         <v>1569</v>
@@ -29606,7 +29606,7 @@
         <v>1562</v>
       </c>
       <c r="E612">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F612" t="s">
         <v>1569</v>
@@ -29641,7 +29641,7 @@
         <v>1562</v>
       </c>
       <c r="E613">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F613" t="s">
         <v>1569</v>
@@ -29676,7 +29676,7 @@
         <v>1562</v>
       </c>
       <c r="E614">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F614" t="s">
         <v>1569</v>
@@ -29711,7 +29711,7 @@
         <v>1562</v>
       </c>
       <c r="E615">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F615" t="s">
         <v>1571</v>
@@ -29746,7 +29746,7 @@
         <v>1562</v>
       </c>
       <c r="E616">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F616" t="s">
         <v>1569</v>
@@ -29781,7 +29781,7 @@
         <v>1562</v>
       </c>
       <c r="E617">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F617" t="s">
         <v>1569</v>
@@ -29816,7 +29816,7 @@
         <v>1562</v>
       </c>
       <c r="E618">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F618" t="s">
         <v>1569</v>
@@ -29851,7 +29851,7 @@
         <v>1562</v>
       </c>
       <c r="E619">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F619" t="s">
         <v>1571</v>
@@ -29889,7 +29889,7 @@
         <v>1562</v>
       </c>
       <c r="E620">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F620" t="s">
         <v>1569</v>
@@ -29924,7 +29924,7 @@
         <v>1562</v>
       </c>
       <c r="E621">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F621" t="s">
         <v>1569</v>
@@ -29959,7 +29959,7 @@
         <v>1562</v>
       </c>
       <c r="E622">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F622" t="s">
         <v>1569</v>
@@ -29994,7 +29994,7 @@
         <v>1563</v>
       </c>
       <c r="E623">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F623" t="s">
         <v>1573</v>
@@ -30029,7 +30029,7 @@
         <v>1563</v>
       </c>
       <c r="E624">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F624" t="s">
         <v>1569</v>
@@ -30067,7 +30067,7 @@
         <v>1563</v>
       </c>
       <c r="E625">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F625" t="s">
         <v>1569</v>
@@ -30102,7 +30102,7 @@
         <v>1563</v>
       </c>
       <c r="E626">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F626" t="s">
         <v>1571</v>
@@ -30137,7 +30137,7 @@
         <v>1563</v>
       </c>
       <c r="E627">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F627" t="s">
         <v>1569</v>
@@ -30172,7 +30172,7 @@
         <v>1564</v>
       </c>
       <c r="E628">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F628" t="s">
         <v>1571</v>
@@ -30210,7 +30210,7 @@
         <v>1564</v>
       </c>
       <c r="E629">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F629" t="s">
         <v>1571</v>
@@ -30248,7 +30248,7 @@
         <v>1564</v>
       </c>
       <c r="E630">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F630" t="s">
         <v>1571</v>
@@ -30286,7 +30286,7 @@
         <v>1564</v>
       </c>
       <c r="E631">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F631" t="s">
         <v>1569</v>
@@ -30321,7 +30321,7 @@
         <v>1564</v>
       </c>
       <c r="E632">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F632" t="s">
         <v>1569</v>
@@ -30356,7 +30356,7 @@
         <v>1564</v>
       </c>
       <c r="E633">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F633" t="s">
         <v>1569</v>
@@ -30391,7 +30391,7 @@
         <v>1565</v>
       </c>
       <c r="E634">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F634" t="s">
         <v>1571</v>
@@ -30429,7 +30429,7 @@
         <v>1565</v>
       </c>
       <c r="E635">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F635" t="s">
         <v>1569</v>
@@ -30464,7 +30464,7 @@
         <v>1566</v>
       </c>
       <c r="E636">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F636" t="s">
         <v>1569</v>
@@ -30499,7 +30499,7 @@
         <v>1566</v>
       </c>
       <c r="E637">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F637" t="s">
         <v>1569</v>
@@ -30534,7 +30534,7 @@
         <v>1566</v>
       </c>
       <c r="E638">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F638" t="s">
         <v>1569</v>
@@ -30569,7 +30569,7 @@
         <v>1566</v>
       </c>
       <c r="E639">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F639" t="s">
         <v>1569</v>
@@ -30604,7 +30604,7 @@
         <v>1566</v>
       </c>
       <c r="E640">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F640" t="s">
         <v>1569</v>
@@ -30639,7 +30639,7 @@
         <v>1566</v>
       </c>
       <c r="E641">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F641" t="s">
         <v>1569</v>
@@ -30674,7 +30674,7 @@
         <v>1566</v>
       </c>
       <c r="E642">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F642" t="s">
         <v>1569</v>
@@ -30709,7 +30709,7 @@
         <v>1566</v>
       </c>
       <c r="E643">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F643" t="s">
         <v>1569</v>
@@ -30744,7 +30744,7 @@
         <v>1566</v>
       </c>
       <c r="E644">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F644" t="s">
         <v>1569</v>
@@ -30779,7 +30779,7 @@
         <v>1566</v>
       </c>
       <c r="E645">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F645" t="s">
         <v>1569</v>
@@ -30817,7 +30817,7 @@
         <v>1567</v>
       </c>
       <c r="E646">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F646" t="s">
         <v>1569</v>
@@ -30852,7 +30852,7 @@
         <v>1567</v>
       </c>
       <c r="E647">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F647" t="s">
         <v>1569</v>
@@ -30887,7 +30887,7 @@
         <v>1567</v>
       </c>
       <c r="E648">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F648" t="s">
         <v>1569</v>
@@ -30922,7 +30922,7 @@
         <v>1567</v>
       </c>
       <c r="E649">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F649" t="s">
         <v>1569</v>
@@ -30957,7 +30957,7 @@
         <v>1567</v>
       </c>
       <c r="E650">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F650" t="s">
         <v>1569</v>
@@ -30995,7 +30995,7 @@
         <v>1567</v>
       </c>
       <c r="E651">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F651" t="s">
         <v>1571</v>
@@ -31033,7 +31033,7 @@
         <v>1567</v>
       </c>
       <c r="E652">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F652" t="s">
         <v>1569</v>
@@ -31068,7 +31068,7 @@
         <v>1567</v>
       </c>
       <c r="E653">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F653" t="s">
         <v>1571</v>
@@ -31106,7 +31106,7 @@
         <v>1567</v>
       </c>
       <c r="E654">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F654" t="s">
         <v>1569</v>
@@ -31141,7 +31141,7 @@
         <v>1567</v>
       </c>
       <c r="E655">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F655" t="s">
         <v>1569</v>
@@ -31176,7 +31176,7 @@
         <v>1567</v>
       </c>
       <c r="E656">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F656" t="s">
         <v>1569</v>
@@ -31211,7 +31211,7 @@
         <v>1568</v>
       </c>
       <c r="E657">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F657" t="s">
         <v>1569</v>
@@ -31246,7 +31246,7 @@
         <v>1568</v>
       </c>
       <c r="E658">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F658" t="s">
         <v>1569</v>
@@ -31284,7 +31284,7 @@
         <v>1568</v>
       </c>
       <c r="E659">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F659" t="s">
         <v>1569</v>
@@ -31322,7 +31322,7 @@
         <v>1568</v>
       </c>
       <c r="E660">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F660" t="s">
         <v>1569</v>

--- a/BacklogGATEAutoCompleto.xlsx
+++ b/BacklogGATEAutoCompleto.xlsx
@@ -29775,7 +29775,7 @@
     </row>
     <row r="620" spans="1:12">
       <c r="A620" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="B620" t="s">
         <v>656</v>
@@ -29799,7 +29799,7 @@
         <v>1571</v>
       </c>
       <c r="I620" t="s">
-        <v>1645</v>
+        <v>1587</v>
       </c>
       <c r="J620" t="s">
         <v>2315</v>
@@ -29808,7 +29808,7 @@
         <v>2410</v>
       </c>
       <c r="L620" t="s">
-        <v>2528</v>
+        <v>2540</v>
       </c>
     </row>
     <row r="621" spans="1:12">

--- a/BacklogGATEAutoCompleto.xlsx
+++ b/BacklogGATEAutoCompleto.xlsx
@@ -8070,7 +8070,7 @@
         <v>1338</v>
       </c>
       <c r="E2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="F2" t="s">
         <v>1550</v>
@@ -8105,7 +8105,7 @@
         <v>1339</v>
       </c>
       <c r="E3">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="F3" t="s">
         <v>1550</v>
@@ -8140,7 +8140,7 @@
         <v>1340</v>
       </c>
       <c r="E4">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="F4" t="s">
         <v>1550</v>
@@ -8175,7 +8175,7 @@
         <v>1341</v>
       </c>
       <c r="E5">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="F5" t="s">
         <v>1550</v>
@@ -8210,7 +8210,7 @@
         <v>1342</v>
       </c>
       <c r="E6">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="F6" t="s">
         <v>1550</v>
@@ -8245,7 +8245,7 @@
         <v>1343</v>
       </c>
       <c r="E7">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="F7" t="s">
         <v>1550</v>
@@ -8280,7 +8280,7 @@
         <v>1344</v>
       </c>
       <c r="E8">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="F8" t="s">
         <v>1550</v>
@@ -8315,7 +8315,7 @@
         <v>1345</v>
       </c>
       <c r="E9">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="F9" t="s">
         <v>1550</v>
@@ -8350,7 +8350,7 @@
         <v>1346</v>
       </c>
       <c r="E10">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="F10" t="s">
         <v>1550</v>
@@ -8385,7 +8385,7 @@
         <v>1346</v>
       </c>
       <c r="E11">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="F11" t="s">
         <v>1550</v>
@@ -8420,7 +8420,7 @@
         <v>1347</v>
       </c>
       <c r="E12">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="F12" t="s">
         <v>1550</v>
@@ -8455,7 +8455,7 @@
         <v>1348</v>
       </c>
       <c r="E13">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="F13" t="s">
         <v>1550</v>
@@ -8490,7 +8490,7 @@
         <v>1349</v>
       </c>
       <c r="E14">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="F14" t="s">
         <v>1550</v>
@@ -8525,7 +8525,7 @@
         <v>1349</v>
       </c>
       <c r="E15">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="F15" t="s">
         <v>1550</v>
@@ -8560,7 +8560,7 @@
         <v>1350</v>
       </c>
       <c r="E16">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="F16" t="s">
         <v>1550</v>
@@ -8595,7 +8595,7 @@
         <v>1351</v>
       </c>
       <c r="E17">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="F17" t="s">
         <v>1550</v>
@@ -8630,7 +8630,7 @@
         <v>1351</v>
       </c>
       <c r="E18">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="F18" t="s">
         <v>1550</v>
@@ -8665,7 +8665,7 @@
         <v>1352</v>
       </c>
       <c r="E19">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="F19" t="s">
         <v>1550</v>
@@ -8700,7 +8700,7 @@
         <v>1353</v>
       </c>
       <c r="E20">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="F20" t="s">
         <v>1550</v>
@@ -8735,7 +8735,7 @@
         <v>1354</v>
       </c>
       <c r="E21">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="F21" t="s">
         <v>1550</v>
@@ -8770,7 +8770,7 @@
         <v>1355</v>
       </c>
       <c r="E22">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="F22" t="s">
         <v>1550</v>
@@ -8805,7 +8805,7 @@
         <v>1356</v>
       </c>
       <c r="E23">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="F23" t="s">
         <v>1550</v>
@@ -8843,7 +8843,7 @@
         <v>1357</v>
       </c>
       <c r="E24">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="F24" t="s">
         <v>1550</v>
@@ -8878,7 +8878,7 @@
         <v>1358</v>
       </c>
       <c r="E25">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F25" t="s">
         <v>1550</v>
@@ -8913,7 +8913,7 @@
         <v>1359</v>
       </c>
       <c r="E26">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F26" t="s">
         <v>1550</v>
@@ -8948,7 +8948,7 @@
         <v>1360</v>
       </c>
       <c r="E27">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F27" t="s">
         <v>1550</v>
@@ -8983,7 +8983,7 @@
         <v>1361</v>
       </c>
       <c r="E28">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F28" t="s">
         <v>1550</v>
@@ -9018,7 +9018,7 @@
         <v>1362</v>
       </c>
       <c r="E29">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F29" t="s">
         <v>1550</v>
@@ -9053,7 +9053,7 @@
         <v>1363</v>
       </c>
       <c r="E30">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F30" t="s">
         <v>1550</v>
@@ -9088,7 +9088,7 @@
         <v>1364</v>
       </c>
       <c r="E31">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F31" t="s">
         <v>1550</v>
@@ -9123,7 +9123,7 @@
         <v>1365</v>
       </c>
       <c r="E32">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F32" t="s">
         <v>1550</v>
@@ -9158,7 +9158,7 @@
         <v>1366</v>
       </c>
       <c r="E33">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F33" t="s">
         <v>1550</v>
@@ -9193,7 +9193,7 @@
         <v>1367</v>
       </c>
       <c r="E34">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F34" t="s">
         <v>1550</v>
@@ -9228,7 +9228,7 @@
         <v>1367</v>
       </c>
       <c r="E35">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F35" t="s">
         <v>1550</v>
@@ -9263,7 +9263,7 @@
         <v>1368</v>
       </c>
       <c r="E36">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F36" t="s">
         <v>1550</v>
@@ -9298,7 +9298,7 @@
         <v>1369</v>
       </c>
       <c r="E37">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="F37" t="s">
         <v>1550</v>
@@ -9333,7 +9333,7 @@
         <v>1370</v>
       </c>
       <c r="E38">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F38" t="s">
         <v>1550</v>
@@ -9368,7 +9368,7 @@
         <v>1371</v>
       </c>
       <c r="E39">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F39" t="s">
         <v>1550</v>
@@ -9403,7 +9403,7 @@
         <v>1372</v>
       </c>
       <c r="E40">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F40" t="s">
         <v>1550</v>
@@ -9438,7 +9438,7 @@
         <v>1372</v>
       </c>
       <c r="E41">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F41" t="s">
         <v>1550</v>
@@ -9473,7 +9473,7 @@
         <v>1373</v>
       </c>
       <c r="E42">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F42" t="s">
         <v>1550</v>
@@ -9508,7 +9508,7 @@
         <v>1374</v>
       </c>
       <c r="E43">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F43" t="s">
         <v>1550</v>
@@ -9543,7 +9543,7 @@
         <v>1375</v>
       </c>
       <c r="E44">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F44" t="s">
         <v>1550</v>
@@ -9578,7 +9578,7 @@
         <v>1375</v>
       </c>
       <c r="E45">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F45" t="s">
         <v>1550</v>
@@ -9613,7 +9613,7 @@
         <v>1376</v>
       </c>
       <c r="E46">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F46" t="s">
         <v>1550</v>
@@ -9648,7 +9648,7 @@
         <v>1376</v>
       </c>
       <c r="E47">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F47" t="s">
         <v>1550</v>
@@ -9683,7 +9683,7 @@
         <v>1377</v>
       </c>
       <c r="E48">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F48" t="s">
         <v>1550</v>
@@ -9718,7 +9718,7 @@
         <v>1378</v>
       </c>
       <c r="E49">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F49" t="s">
         <v>1550</v>
@@ -9753,7 +9753,7 @@
         <v>1379</v>
       </c>
       <c r="E50">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F50" t="s">
         <v>1550</v>
@@ -9788,7 +9788,7 @@
         <v>1380</v>
       </c>
       <c r="E51">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F51" t="s">
         <v>1550</v>
@@ -9823,7 +9823,7 @@
         <v>1380</v>
       </c>
       <c r="E52">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F52" t="s">
         <v>1550</v>
@@ -9858,7 +9858,7 @@
         <v>1381</v>
       </c>
       <c r="E53">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F53" t="s">
         <v>1550</v>
@@ -9893,7 +9893,7 @@
         <v>1382</v>
       </c>
       <c r="E54">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F54" t="s">
         <v>1550</v>
@@ -9928,7 +9928,7 @@
         <v>1383</v>
       </c>
       <c r="E55">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F55" t="s">
         <v>1550</v>
@@ -9963,7 +9963,7 @@
         <v>1384</v>
       </c>
       <c r="E56">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F56" t="s">
         <v>1550</v>
@@ -9998,7 +9998,7 @@
         <v>1385</v>
       </c>
       <c r="E57">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F57" t="s">
         <v>1550</v>
@@ -10033,7 +10033,7 @@
         <v>1386</v>
       </c>
       <c r="E58">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F58" t="s">
         <v>1550</v>
@@ -10068,7 +10068,7 @@
         <v>1387</v>
       </c>
       <c r="E59">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F59" t="s">
         <v>1550</v>
@@ -10103,7 +10103,7 @@
         <v>1387</v>
       </c>
       <c r="E60">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F60" t="s">
         <v>1550</v>
@@ -10138,7 +10138,7 @@
         <v>1387</v>
       </c>
       <c r="E61">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F61" t="s">
         <v>1550</v>
@@ -10173,7 +10173,7 @@
         <v>1388</v>
       </c>
       <c r="E62">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F62" t="s">
         <v>1550</v>
@@ -10208,7 +10208,7 @@
         <v>1389</v>
       </c>
       <c r="E63">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F63" t="s">
         <v>1550</v>
@@ -10243,7 +10243,7 @@
         <v>1390</v>
       </c>
       <c r="E64">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F64" t="s">
         <v>1550</v>
@@ -10278,7 +10278,7 @@
         <v>1390</v>
       </c>
       <c r="E65">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F65" t="s">
         <v>1550</v>
@@ -10313,7 +10313,7 @@
         <v>1390</v>
       </c>
       <c r="E66">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F66" t="s">
         <v>1550</v>
@@ -10348,7 +10348,7 @@
         <v>1391</v>
       </c>
       <c r="E67">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F67" t="s">
         <v>1550</v>
@@ -10383,7 +10383,7 @@
         <v>1392</v>
       </c>
       <c r="E68">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F68" t="s">
         <v>1550</v>
@@ -10418,7 +10418,7 @@
         <v>1392</v>
       </c>
       <c r="E69">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F69" t="s">
         <v>1550</v>
@@ -10453,7 +10453,7 @@
         <v>1392</v>
       </c>
       <c r="E70">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F70" t="s">
         <v>1550</v>
@@ -10488,7 +10488,7 @@
         <v>1393</v>
       </c>
       <c r="E71">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F71" t="s">
         <v>1550</v>
@@ -10523,7 +10523,7 @@
         <v>1394</v>
       </c>
       <c r="E72">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F72" t="s">
         <v>1550</v>
@@ -10558,7 +10558,7 @@
         <v>1394</v>
       </c>
       <c r="E73">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F73" t="s">
         <v>1550</v>
@@ -10593,7 +10593,7 @@
         <v>1394</v>
       </c>
       <c r="E74">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F74" t="s">
         <v>1551</v>
@@ -10628,7 +10628,7 @@
         <v>1394</v>
       </c>
       <c r="E75">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F75" t="s">
         <v>1550</v>
@@ -10663,7 +10663,7 @@
         <v>1395</v>
       </c>
       <c r="E76">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F76" t="s">
         <v>1550</v>
@@ -10698,7 +10698,7 @@
         <v>1396</v>
       </c>
       <c r="E77">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F77" t="s">
         <v>1550</v>
@@ -10733,7 +10733,7 @@
         <v>1396</v>
       </c>
       <c r="E78">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F78" t="s">
         <v>1550</v>
@@ -10768,7 +10768,7 @@
         <v>1397</v>
       </c>
       <c r="E79">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F79" t="s">
         <v>1550</v>
@@ -10803,7 +10803,7 @@
         <v>1398</v>
       </c>
       <c r="E80">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F80" t="s">
         <v>1550</v>
@@ -10838,7 +10838,7 @@
         <v>1399</v>
       </c>
       <c r="E81">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F81" t="s">
         <v>1550</v>
@@ -10873,7 +10873,7 @@
         <v>1400</v>
       </c>
       <c r="E82">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F82" t="s">
         <v>1550</v>
@@ -10908,7 +10908,7 @@
         <v>1400</v>
       </c>
       <c r="E83">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F83" t="s">
         <v>1550</v>
@@ -10943,7 +10943,7 @@
         <v>1400</v>
       </c>
       <c r="E84">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F84" t="s">
         <v>1550</v>
@@ -10978,7 +10978,7 @@
         <v>1400</v>
       </c>
       <c r="E85">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F85" t="s">
         <v>1550</v>
@@ -11013,7 +11013,7 @@
         <v>1400</v>
       </c>
       <c r="E86">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F86" t="s">
         <v>1550</v>
@@ -11048,7 +11048,7 @@
         <v>1400</v>
       </c>
       <c r="E87">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F87" t="s">
         <v>1550</v>
@@ -11083,7 +11083,7 @@
         <v>1401</v>
       </c>
       <c r="E88">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F88" t="s">
         <v>1550</v>
@@ -11118,7 +11118,7 @@
         <v>1402</v>
       </c>
       <c r="E89">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F89" t="s">
         <v>1550</v>
@@ -11153,7 +11153,7 @@
         <v>1403</v>
       </c>
       <c r="E90">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F90" t="s">
         <v>1550</v>
@@ -11188,7 +11188,7 @@
         <v>1403</v>
       </c>
       <c r="E91">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F91" t="s">
         <v>1550</v>
@@ -11223,7 +11223,7 @@
         <v>1404</v>
       </c>
       <c r="E92">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F92" t="s">
         <v>1552</v>
@@ -11258,7 +11258,7 @@
         <v>1405</v>
       </c>
       <c r="E93">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F93" t="s">
         <v>1550</v>
@@ -11293,7 +11293,7 @@
         <v>1406</v>
       </c>
       <c r="E94">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F94" t="s">
         <v>1550</v>
@@ -11328,7 +11328,7 @@
         <v>1406</v>
       </c>
       <c r="E95">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F95" t="s">
         <v>1550</v>
@@ -11363,7 +11363,7 @@
         <v>1407</v>
       </c>
       <c r="E96">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F96" t="s">
         <v>1550</v>
@@ -11398,7 +11398,7 @@
         <v>1408</v>
       </c>
       <c r="E97">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F97" t="s">
         <v>1550</v>
@@ -11433,7 +11433,7 @@
         <v>1409</v>
       </c>
       <c r="E98">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F98" t="s">
         <v>1550</v>
@@ -11468,7 +11468,7 @@
         <v>1410</v>
       </c>
       <c r="E99">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F99" t="s">
         <v>1550</v>
@@ -11503,7 +11503,7 @@
         <v>1411</v>
       </c>
       <c r="E100">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F100" t="s">
         <v>1550</v>
@@ -11538,7 +11538,7 @@
         <v>1411</v>
       </c>
       <c r="E101">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F101" t="s">
         <v>1550</v>
@@ -11573,7 +11573,7 @@
         <v>1412</v>
       </c>
       <c r="E102">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F102" t="s">
         <v>1550</v>
@@ -11608,7 +11608,7 @@
         <v>1412</v>
       </c>
       <c r="E103">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F103" t="s">
         <v>1550</v>
@@ -11643,7 +11643,7 @@
         <v>1412</v>
       </c>
       <c r="E104">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F104" t="s">
         <v>1550</v>
@@ -11678,7 +11678,7 @@
         <v>1413</v>
       </c>
       <c r="E105">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F105" t="s">
         <v>1550</v>
@@ -11713,7 +11713,7 @@
         <v>1413</v>
       </c>
       <c r="E106">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F106" t="s">
         <v>1550</v>
@@ -11748,7 +11748,7 @@
         <v>1413</v>
       </c>
       <c r="E107">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F107" t="s">
         <v>1550</v>
@@ -11783,7 +11783,7 @@
         <v>1414</v>
       </c>
       <c r="E108">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F108" t="s">
         <v>1550</v>
@@ -11818,7 +11818,7 @@
         <v>1415</v>
       </c>
       <c r="E109">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F109" t="s">
         <v>1550</v>
@@ -11853,7 +11853,7 @@
         <v>1415</v>
       </c>
       <c r="E110">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F110" t="s">
         <v>1550</v>
@@ -11888,7 +11888,7 @@
         <v>1416</v>
       </c>
       <c r="E111">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F111" t="s">
         <v>1550</v>
@@ -11923,7 +11923,7 @@
         <v>1416</v>
       </c>
       <c r="E112">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F112" t="s">
         <v>1550</v>
@@ -11958,7 +11958,7 @@
         <v>1417</v>
       </c>
       <c r="E113">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F113" t="s">
         <v>1550</v>
@@ -11993,7 +11993,7 @@
         <v>1417</v>
       </c>
       <c r="E114">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F114" t="s">
         <v>1550</v>
@@ -12028,7 +12028,7 @@
         <v>1418</v>
       </c>
       <c r="E115">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F115" t="s">
         <v>1550</v>
@@ -12063,7 +12063,7 @@
         <v>1418</v>
       </c>
       <c r="E116">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F116" t="s">
         <v>1550</v>
@@ -12098,7 +12098,7 @@
         <v>1419</v>
       </c>
       <c r="E117">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F117" t="s">
         <v>1550</v>
@@ -12133,7 +12133,7 @@
         <v>1419</v>
       </c>
       <c r="E118">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F118" t="s">
         <v>1550</v>
@@ -12168,7 +12168,7 @@
         <v>1420</v>
       </c>
       <c r="E119">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F119" t="s">
         <v>1550</v>
@@ -12203,7 +12203,7 @@
         <v>1421</v>
       </c>
       <c r="E120">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F120" t="s">
         <v>1550</v>
@@ -12238,7 +12238,7 @@
         <v>1421</v>
       </c>
       <c r="E121">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F121" t="s">
         <v>1550</v>
@@ -12273,7 +12273,7 @@
         <v>1422</v>
       </c>
       <c r="E122">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F122" t="s">
         <v>1550</v>
@@ -12308,7 +12308,7 @@
         <v>1423</v>
       </c>
       <c r="E123">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F123" t="s">
         <v>1550</v>
@@ -12346,7 +12346,7 @@
         <v>1423</v>
       </c>
       <c r="E124">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F124" t="s">
         <v>1550</v>
@@ -12381,7 +12381,7 @@
         <v>1423</v>
       </c>
       <c r="E125">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F125" t="s">
         <v>1550</v>
@@ -12416,7 +12416,7 @@
         <v>1423</v>
       </c>
       <c r="E126">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F126" t="s">
         <v>1550</v>
@@ -12451,7 +12451,7 @@
         <v>1424</v>
       </c>
       <c r="E127">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F127" t="s">
         <v>1550</v>
@@ -12486,7 +12486,7 @@
         <v>1425</v>
       </c>
       <c r="E128">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F128" t="s">
         <v>1551</v>
@@ -12521,7 +12521,7 @@
         <v>1426</v>
       </c>
       <c r="E129">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F129" t="s">
         <v>1550</v>
@@ -12556,7 +12556,7 @@
         <v>1426</v>
       </c>
       <c r="E130">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F130" t="s">
         <v>1550</v>
@@ -12591,7 +12591,7 @@
         <v>1426</v>
       </c>
       <c r="E131">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F131" t="s">
         <v>1550</v>
@@ -12626,7 +12626,7 @@
         <v>1426</v>
       </c>
       <c r="E132">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F132" t="s">
         <v>1550</v>
@@ -12661,7 +12661,7 @@
         <v>1427</v>
       </c>
       <c r="E133">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F133" t="s">
         <v>1550</v>
@@ -12696,7 +12696,7 @@
         <v>1427</v>
       </c>
       <c r="E134">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F134" t="s">
         <v>1550</v>
@@ -12731,7 +12731,7 @@
         <v>1427</v>
       </c>
       <c r="E135">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F135" t="s">
         <v>1550</v>
@@ -12766,7 +12766,7 @@
         <v>1427</v>
       </c>
       <c r="E136">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F136" t="s">
         <v>1550</v>
@@ -12801,7 +12801,7 @@
         <v>1427</v>
       </c>
       <c r="E137">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F137" t="s">
         <v>1550</v>
@@ -12836,7 +12836,7 @@
         <v>1427</v>
       </c>
       <c r="E138">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F138" t="s">
         <v>1550</v>
@@ -12871,7 +12871,7 @@
         <v>1427</v>
       </c>
       <c r="E139">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F139" t="s">
         <v>1550</v>
@@ -12906,7 +12906,7 @@
         <v>1428</v>
       </c>
       <c r="E140">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F140" t="s">
         <v>1550</v>
@@ -12941,7 +12941,7 @@
         <v>1428</v>
       </c>
       <c r="E141">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F141" t="s">
         <v>1550</v>
@@ -12976,7 +12976,7 @@
         <v>1429</v>
       </c>
       <c r="E142">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F142" t="s">
         <v>1550</v>
@@ -13011,7 +13011,7 @@
         <v>1430</v>
       </c>
       <c r="E143">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F143" t="s">
         <v>1550</v>
@@ -13046,7 +13046,7 @@
         <v>1430</v>
       </c>
       <c r="E144">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F144" t="s">
         <v>1550</v>
@@ -13081,7 +13081,7 @@
         <v>1430</v>
       </c>
       <c r="E145">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F145" t="s">
         <v>1550</v>
@@ -13116,7 +13116,7 @@
         <v>1431</v>
       </c>
       <c r="E146">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F146" t="s">
         <v>1550</v>
@@ -13151,7 +13151,7 @@
         <v>1431</v>
       </c>
       <c r="E147">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F147" t="s">
         <v>1550</v>
@@ -13186,7 +13186,7 @@
         <v>1431</v>
       </c>
       <c r="E148">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F148" t="s">
         <v>1550</v>
@@ -13221,7 +13221,7 @@
         <v>1431</v>
       </c>
       <c r="E149">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F149" t="s">
         <v>1550</v>
@@ -13256,7 +13256,7 @@
         <v>1431</v>
       </c>
       <c r="E150">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F150" t="s">
         <v>1550</v>
@@ -13291,7 +13291,7 @@
         <v>1431</v>
       </c>
       <c r="E151">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F151" t="s">
         <v>1550</v>
@@ -13326,7 +13326,7 @@
         <v>1431</v>
       </c>
       <c r="E152">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F152" t="s">
         <v>1550</v>
@@ -13361,7 +13361,7 @@
         <v>1431</v>
       </c>
       <c r="E153">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F153" t="s">
         <v>1550</v>
@@ -13396,7 +13396,7 @@
         <v>1431</v>
       </c>
       <c r="E154">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F154" t="s">
         <v>1550</v>
@@ -13431,7 +13431,7 @@
         <v>1431</v>
       </c>
       <c r="E155">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F155" t="s">
         <v>1550</v>
@@ -13466,7 +13466,7 @@
         <v>1432</v>
       </c>
       <c r="E156">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F156" t="s">
         <v>1550</v>
@@ -13501,7 +13501,7 @@
         <v>1432</v>
       </c>
       <c r="E157">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F157" t="s">
         <v>1550</v>
@@ -13536,7 +13536,7 @@
         <v>1432</v>
       </c>
       <c r="E158">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F158" t="s">
         <v>1550</v>
@@ -13571,7 +13571,7 @@
         <v>1433</v>
       </c>
       <c r="E159">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F159" t="s">
         <v>1550</v>
@@ -13606,7 +13606,7 @@
         <v>1433</v>
       </c>
       <c r="E160">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F160" t="s">
         <v>1551</v>
@@ -13641,7 +13641,7 @@
         <v>1433</v>
       </c>
       <c r="E161">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F161" t="s">
         <v>1550</v>
@@ -13676,7 +13676,7 @@
         <v>1434</v>
       </c>
       <c r="E162">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F162" t="s">
         <v>1550</v>
@@ -13711,7 +13711,7 @@
         <v>1434</v>
       </c>
       <c r="E163">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F163" t="s">
         <v>1550</v>
@@ -13746,7 +13746,7 @@
         <v>1435</v>
       </c>
       <c r="E164">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F164" t="s">
         <v>1550</v>
@@ -13781,7 +13781,7 @@
         <v>1435</v>
       </c>
       <c r="E165">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F165" t="s">
         <v>1550</v>
@@ -13816,7 +13816,7 @@
         <v>1436</v>
       </c>
       <c r="E166">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F166" t="s">
         <v>1550</v>
@@ -13851,7 +13851,7 @@
         <v>1436</v>
       </c>
       <c r="E167">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F167" t="s">
         <v>1550</v>
@@ -13886,7 +13886,7 @@
         <v>1437</v>
       </c>
       <c r="E168">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F168" t="s">
         <v>1550</v>
@@ -13921,7 +13921,7 @@
         <v>1437</v>
       </c>
       <c r="E169">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F169" t="s">
         <v>1550</v>
@@ -13956,7 +13956,7 @@
         <v>1437</v>
       </c>
       <c r="E170">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F170" t="s">
         <v>1550</v>
@@ -13991,7 +13991,7 @@
         <v>1438</v>
       </c>
       <c r="E171">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F171" t="s">
         <v>1550</v>
@@ -14026,7 +14026,7 @@
         <v>1438</v>
       </c>
       <c r="E172">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F172" t="s">
         <v>1550</v>
@@ -14061,7 +14061,7 @@
         <v>1439</v>
       </c>
       <c r="E173">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F173" t="s">
         <v>1550</v>
@@ -14096,7 +14096,7 @@
         <v>1440</v>
       </c>
       <c r="E174">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F174" t="s">
         <v>1550</v>
@@ -14131,7 +14131,7 @@
         <v>1440</v>
       </c>
       <c r="E175">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F175" t="s">
         <v>1550</v>
@@ -14166,7 +14166,7 @@
         <v>1440</v>
       </c>
       <c r="E176">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F176" t="s">
         <v>1550</v>
@@ -14201,7 +14201,7 @@
         <v>1440</v>
       </c>
       <c r="E177">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F177" t="s">
         <v>1550</v>
@@ -14236,7 +14236,7 @@
         <v>1441</v>
       </c>
       <c r="E178">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F178" t="s">
         <v>1550</v>
@@ -14271,7 +14271,7 @@
         <v>1442</v>
       </c>
       <c r="E179">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F179" t="s">
         <v>1550</v>
@@ -14306,7 +14306,7 @@
         <v>1442</v>
       </c>
       <c r="E180">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F180" t="s">
         <v>1550</v>
@@ -14341,7 +14341,7 @@
         <v>1442</v>
       </c>
       <c r="E181">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F181" t="s">
         <v>1550</v>
@@ -14376,7 +14376,7 @@
         <v>1442</v>
       </c>
       <c r="E182">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F182" t="s">
         <v>1550</v>
@@ -14411,7 +14411,7 @@
         <v>1442</v>
       </c>
       <c r="E183">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F183" t="s">
         <v>1550</v>
@@ -14446,7 +14446,7 @@
         <v>1443</v>
       </c>
       <c r="E184">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F184" t="s">
         <v>1550</v>
@@ -14481,7 +14481,7 @@
         <v>1443</v>
       </c>
       <c r="E185">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F185" t="s">
         <v>1550</v>
@@ -14516,7 +14516,7 @@
         <v>1443</v>
       </c>
       <c r="E186">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F186" t="s">
         <v>1550</v>
@@ -14551,7 +14551,7 @@
         <v>1443</v>
       </c>
       <c r="E187">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F187" t="s">
         <v>1550</v>
@@ -14586,7 +14586,7 @@
         <v>1443</v>
       </c>
       <c r="E188">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F188" t="s">
         <v>1550</v>
@@ -14621,7 +14621,7 @@
         <v>1443</v>
       </c>
       <c r="E189">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F189" t="s">
         <v>1550</v>
@@ -14656,7 +14656,7 @@
         <v>1443</v>
       </c>
       <c r="E190">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F190" t="s">
         <v>1550</v>
@@ -14691,7 +14691,7 @@
         <v>1444</v>
       </c>
       <c r="E191">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F191" t="s">
         <v>1550</v>
@@ -14726,7 +14726,7 @@
         <v>1444</v>
       </c>
       <c r="E192">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F192" t="s">
         <v>1550</v>
@@ -14761,7 +14761,7 @@
         <v>1444</v>
       </c>
       <c r="E193">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F193" t="s">
         <v>1550</v>
@@ -14796,7 +14796,7 @@
         <v>1444</v>
       </c>
       <c r="E194">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F194" t="s">
         <v>1550</v>
@@ -14831,7 +14831,7 @@
         <v>1445</v>
       </c>
       <c r="E195">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F195" t="s">
         <v>1550</v>
@@ -14866,7 +14866,7 @@
         <v>1445</v>
       </c>
       <c r="E196">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F196" t="s">
         <v>1550</v>
@@ -14901,7 +14901,7 @@
         <v>1446</v>
       </c>
       <c r="E197">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F197" t="s">
         <v>1550</v>
@@ -14936,7 +14936,7 @@
         <v>1446</v>
       </c>
       <c r="E198">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F198" t="s">
         <v>1550</v>
@@ -14971,7 +14971,7 @@
         <v>1447</v>
       </c>
       <c r="E199">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F199" t="s">
         <v>1550</v>
@@ -15006,7 +15006,7 @@
         <v>1447</v>
       </c>
       <c r="E200">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F200" t="s">
         <v>1550</v>
@@ -15041,7 +15041,7 @@
         <v>1448</v>
       </c>
       <c r="E201">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F201" t="s">
         <v>1550</v>
@@ -15076,7 +15076,7 @@
         <v>1449</v>
       </c>
       <c r="E202">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F202" t="s">
         <v>1550</v>
@@ -15111,7 +15111,7 @@
         <v>1449</v>
       </c>
       <c r="E203">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F203" t="s">
         <v>1550</v>
@@ -15146,7 +15146,7 @@
         <v>1450</v>
       </c>
       <c r="E204">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F204" t="s">
         <v>1550</v>
@@ -15181,7 +15181,7 @@
         <v>1450</v>
       </c>
       <c r="E205">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F205" t="s">
         <v>1550</v>
@@ -15216,7 +15216,7 @@
         <v>1451</v>
       </c>
       <c r="E206">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F206" t="s">
         <v>1550</v>
@@ -15251,7 +15251,7 @@
         <v>1452</v>
       </c>
       <c r="E207">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F207" t="s">
         <v>1550</v>
@@ -15286,7 +15286,7 @@
         <v>1452</v>
       </c>
       <c r="E208">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F208" t="s">
         <v>1550</v>
@@ -15321,7 +15321,7 @@
         <v>1452</v>
       </c>
       <c r="E209">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F209" t="s">
         <v>1550</v>
@@ -15356,7 +15356,7 @@
         <v>1453</v>
       </c>
       <c r="E210">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F210" t="s">
         <v>1550</v>
@@ -15391,7 +15391,7 @@
         <v>1453</v>
       </c>
       <c r="E211">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F211" t="s">
         <v>1550</v>
@@ -15426,7 +15426,7 @@
         <v>1454</v>
       </c>
       <c r="E212">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F212" t="s">
         <v>1550</v>
@@ -15461,7 +15461,7 @@
         <v>1455</v>
       </c>
       <c r="E213">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F213" t="s">
         <v>1550</v>
@@ -15496,7 +15496,7 @@
         <v>1455</v>
       </c>
       <c r="E214">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F214" t="s">
         <v>1550</v>
@@ -15531,7 +15531,7 @@
         <v>1455</v>
       </c>
       <c r="E215">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F215" t="s">
         <v>1550</v>
@@ -15566,7 +15566,7 @@
         <v>1456</v>
       </c>
       <c r="E216">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F216" t="s">
         <v>1550</v>
@@ -15601,7 +15601,7 @@
         <v>1456</v>
       </c>
       <c r="E217">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F217" t="s">
         <v>1550</v>
@@ -15636,7 +15636,7 @@
         <v>1457</v>
       </c>
       <c r="E218">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F218" t="s">
         <v>1550</v>
@@ -15671,7 +15671,7 @@
         <v>1457</v>
       </c>
       <c r="E219">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F219" t="s">
         <v>1550</v>
@@ -15706,7 +15706,7 @@
         <v>1457</v>
       </c>
       <c r="E220">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F220" t="s">
         <v>1552</v>
@@ -15741,7 +15741,7 @@
         <v>1457</v>
       </c>
       <c r="E221">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F221" t="s">
         <v>1550</v>
@@ -15776,7 +15776,7 @@
         <v>1458</v>
       </c>
       <c r="E222">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F222" t="s">
         <v>1550</v>
@@ -15811,7 +15811,7 @@
         <v>1458</v>
       </c>
       <c r="E223">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F223" t="s">
         <v>1550</v>
@@ -15849,7 +15849,7 @@
         <v>1458</v>
       </c>
       <c r="E224">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F224" t="s">
         <v>1550</v>
@@ -15884,7 +15884,7 @@
         <v>1458</v>
       </c>
       <c r="E225">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F225" t="s">
         <v>1550</v>
@@ -15919,7 +15919,7 @@
         <v>1458</v>
       </c>
       <c r="E226">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F226" t="s">
         <v>1550</v>
@@ -15954,7 +15954,7 @@
         <v>1458</v>
       </c>
       <c r="E227">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F227" t="s">
         <v>1550</v>
@@ -15989,7 +15989,7 @@
         <v>1459</v>
       </c>
       <c r="E228">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F228" t="s">
         <v>1550</v>
@@ -16024,7 +16024,7 @@
         <v>1459</v>
       </c>
       <c r="E229">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F229" t="s">
         <v>1550</v>
@@ -16059,7 +16059,7 @@
         <v>1459</v>
       </c>
       <c r="E230">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F230" t="s">
         <v>1550</v>
@@ -16094,7 +16094,7 @@
         <v>1460</v>
       </c>
       <c r="E231">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F231" t="s">
         <v>1550</v>
@@ -16129,7 +16129,7 @@
         <v>1460</v>
       </c>
       <c r="E232">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F232" t="s">
         <v>1550</v>
@@ -16164,7 +16164,7 @@
         <v>1460</v>
       </c>
       <c r="E233">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F233" t="s">
         <v>1550</v>
@@ -16199,7 +16199,7 @@
         <v>1460</v>
       </c>
       <c r="E234">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F234" t="s">
         <v>1550</v>
@@ -16234,7 +16234,7 @@
         <v>1461</v>
       </c>
       <c r="E235">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F235" t="s">
         <v>1550</v>
@@ -16269,7 +16269,7 @@
         <v>1461</v>
       </c>
       <c r="E236">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F236" t="s">
         <v>1550</v>
@@ -16304,7 +16304,7 @@
         <v>1461</v>
       </c>
       <c r="E237">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F237" t="s">
         <v>1550</v>
@@ -16339,7 +16339,7 @@
         <v>1461</v>
       </c>
       <c r="E238">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F238" t="s">
         <v>1550</v>
@@ -16374,7 +16374,7 @@
         <v>1462</v>
       </c>
       <c r="E239">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F239" t="s">
         <v>1550</v>
@@ -16409,7 +16409,7 @@
         <v>1462</v>
       </c>
       <c r="E240">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F240" t="s">
         <v>1550</v>
@@ -16444,7 +16444,7 @@
         <v>1462</v>
       </c>
       <c r="E241">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F241" t="s">
         <v>1550</v>
@@ -16479,7 +16479,7 @@
         <v>1462</v>
       </c>
       <c r="E242">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F242" t="s">
         <v>1550</v>
@@ -16514,7 +16514,7 @@
         <v>1462</v>
       </c>
       <c r="E243">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F243" t="s">
         <v>1550</v>
@@ -16549,7 +16549,7 @@
         <v>1462</v>
       </c>
       <c r="E244">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F244" t="s">
         <v>1550</v>
@@ -16584,7 +16584,7 @@
         <v>1463</v>
       </c>
       <c r="E245">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F245" t="s">
         <v>1550</v>
@@ -16619,7 +16619,7 @@
         <v>1464</v>
       </c>
       <c r="E246">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F246" t="s">
         <v>1550</v>
@@ -16654,7 +16654,7 @@
         <v>1464</v>
       </c>
       <c r="E247">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F247" t="s">
         <v>1553</v>
@@ -16689,7 +16689,7 @@
         <v>1464</v>
       </c>
       <c r="E248">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F248" t="s">
         <v>1550</v>
@@ -16724,7 +16724,7 @@
         <v>1464</v>
       </c>
       <c r="E249">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F249" t="s">
         <v>1550</v>
@@ -16759,7 +16759,7 @@
         <v>1464</v>
       </c>
       <c r="E250">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F250" t="s">
         <v>1550</v>
@@ -16794,7 +16794,7 @@
         <v>1465</v>
       </c>
       <c r="E251">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F251" t="s">
         <v>1550</v>
@@ -16829,7 +16829,7 @@
         <v>1465</v>
       </c>
       <c r="E252">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F252" t="s">
         <v>1550</v>
@@ -16864,7 +16864,7 @@
         <v>1465</v>
       </c>
       <c r="E253">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F253" t="s">
         <v>1550</v>
@@ -16899,7 +16899,7 @@
         <v>1465</v>
       </c>
       <c r="E254">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F254" t="s">
         <v>1550</v>
@@ -16934,7 +16934,7 @@
         <v>1466</v>
       </c>
       <c r="E255">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F255" t="s">
         <v>1550</v>
@@ -16969,7 +16969,7 @@
         <v>1467</v>
       </c>
       <c r="E256">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F256" t="s">
         <v>1550</v>
@@ -17007,7 +17007,7 @@
         <v>1468</v>
       </c>
       <c r="E257">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F257" t="s">
         <v>1550</v>
@@ -17042,7 +17042,7 @@
         <v>1468</v>
       </c>
       <c r="E258">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F258" t="s">
         <v>1550</v>
@@ -17077,7 +17077,7 @@
         <v>1468</v>
       </c>
       <c r="E259">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F259" t="s">
         <v>1550</v>
@@ -17112,7 +17112,7 @@
         <v>1468</v>
       </c>
       <c r="E260">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F260" t="s">
         <v>1550</v>
@@ -17150,7 +17150,7 @@
         <v>1468</v>
       </c>
       <c r="E261">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F261" t="s">
         <v>1550</v>
@@ -17185,7 +17185,7 @@
         <v>1469</v>
       </c>
       <c r="E262">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F262" t="s">
         <v>1550</v>
@@ -17220,7 +17220,7 @@
         <v>1469</v>
       </c>
       <c r="E263">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F263" t="s">
         <v>1550</v>
@@ -17255,7 +17255,7 @@
         <v>1470</v>
       </c>
       <c r="E264">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F264" t="s">
         <v>1550</v>
@@ -17290,7 +17290,7 @@
         <v>1470</v>
       </c>
       <c r="E265">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F265" t="s">
         <v>1550</v>
@@ -17325,7 +17325,7 @@
         <v>1471</v>
       </c>
       <c r="E266">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F266" t="s">
         <v>1550</v>
@@ -17360,7 +17360,7 @@
         <v>1471</v>
       </c>
       <c r="E267">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F267" t="s">
         <v>1550</v>
@@ -17395,7 +17395,7 @@
         <v>1471</v>
       </c>
       <c r="E268">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F268" t="s">
         <v>1550</v>
@@ -17430,7 +17430,7 @@
         <v>1472</v>
       </c>
       <c r="E269">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F269" t="s">
         <v>1550</v>
@@ -17465,7 +17465,7 @@
         <v>1472</v>
       </c>
       <c r="E270">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F270" t="s">
         <v>1550</v>
@@ -17500,7 +17500,7 @@
         <v>1472</v>
       </c>
       <c r="E271">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F271" t="s">
         <v>1550</v>
@@ -17535,7 +17535,7 @@
         <v>1472</v>
       </c>
       <c r="E272">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F272" t="s">
         <v>1550</v>
@@ -17570,7 +17570,7 @@
         <v>1473</v>
       </c>
       <c r="E273">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F273" t="s">
         <v>1550</v>
@@ -17605,7 +17605,7 @@
         <v>1474</v>
       </c>
       <c r="E274">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F274" t="s">
         <v>1550</v>
@@ -17640,7 +17640,7 @@
         <v>1474</v>
       </c>
       <c r="E275">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F275" t="s">
         <v>1550</v>
@@ -17675,7 +17675,7 @@
         <v>1474</v>
       </c>
       <c r="E276">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F276" t="s">
         <v>1550</v>
@@ -17710,7 +17710,7 @@
         <v>1474</v>
       </c>
       <c r="E277">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F277" t="s">
         <v>1550</v>
@@ -17745,7 +17745,7 @@
         <v>1475</v>
       </c>
       <c r="E278">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F278" t="s">
         <v>1550</v>
@@ -17780,7 +17780,7 @@
         <v>1475</v>
       </c>
       <c r="E279">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F279" t="s">
         <v>1550</v>
@@ -17815,7 +17815,7 @@
         <v>1475</v>
       </c>
       <c r="E280">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F280" t="s">
         <v>1550</v>
@@ -17850,7 +17850,7 @@
         <v>1476</v>
       </c>
       <c r="E281">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F281" t="s">
         <v>1550</v>
@@ -17885,7 +17885,7 @@
         <v>1476</v>
       </c>
       <c r="E282">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F282" t="s">
         <v>1550</v>
@@ -17920,7 +17920,7 @@
         <v>1477</v>
       </c>
       <c r="E283">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F283" t="s">
         <v>1550</v>
@@ -17955,7 +17955,7 @@
         <v>1477</v>
       </c>
       <c r="E284">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F284" t="s">
         <v>1550</v>
@@ -17990,7 +17990,7 @@
         <v>1477</v>
       </c>
       <c r="E285">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F285" t="s">
         <v>1550</v>
@@ -18025,7 +18025,7 @@
         <v>1477</v>
       </c>
       <c r="E286">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F286" t="s">
         <v>1550</v>
@@ -18060,7 +18060,7 @@
         <v>1477</v>
       </c>
       <c r="E287">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F287" t="s">
         <v>1550</v>
@@ -18095,7 +18095,7 @@
         <v>1478</v>
       </c>
       <c r="E288">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F288" t="s">
         <v>1550</v>
@@ -18130,7 +18130,7 @@
         <v>1478</v>
       </c>
       <c r="E289">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F289" t="s">
         <v>1550</v>
@@ -18165,7 +18165,7 @@
         <v>1478</v>
       </c>
       <c r="E290">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F290" t="s">
         <v>1550</v>
@@ -18200,7 +18200,7 @@
         <v>1479</v>
       </c>
       <c r="E291">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F291" t="s">
         <v>1550</v>
@@ -18235,7 +18235,7 @@
         <v>1480</v>
       </c>
       <c r="E292">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F292" t="s">
         <v>1550</v>
@@ -18270,7 +18270,7 @@
         <v>1481</v>
       </c>
       <c r="E293">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F293" t="s">
         <v>1550</v>
@@ -18305,7 +18305,7 @@
         <v>1481</v>
       </c>
       <c r="E294">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F294" t="s">
         <v>1550</v>
@@ -18340,7 +18340,7 @@
         <v>1481</v>
       </c>
       <c r="E295">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F295" t="s">
         <v>1550</v>
@@ -18375,7 +18375,7 @@
         <v>1481</v>
       </c>
       <c r="E296">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F296" t="s">
         <v>1550</v>
@@ -18410,7 +18410,7 @@
         <v>1481</v>
       </c>
       <c r="E297">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F297" t="s">
         <v>1550</v>
@@ -18445,7 +18445,7 @@
         <v>1482</v>
       </c>
       <c r="E298">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F298" t="s">
         <v>1550</v>
@@ -18480,7 +18480,7 @@
         <v>1482</v>
       </c>
       <c r="E299">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F299" t="s">
         <v>1550</v>
@@ -18515,7 +18515,7 @@
         <v>1483</v>
       </c>
       <c r="E300">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F300" t="s">
         <v>1550</v>
@@ -18550,7 +18550,7 @@
         <v>1483</v>
       </c>
       <c r="E301">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F301" t="s">
         <v>1550</v>
@@ -18585,7 +18585,7 @@
         <v>1484</v>
       </c>
       <c r="E302">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F302" t="s">
         <v>1550</v>
@@ -18620,7 +18620,7 @@
         <v>1485</v>
       </c>
       <c r="E303">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F303" t="s">
         <v>1550</v>
@@ -18655,7 +18655,7 @@
         <v>1486</v>
       </c>
       <c r="E304">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F304" t="s">
         <v>1550</v>
@@ -18690,7 +18690,7 @@
         <v>1486</v>
       </c>
       <c r="E305">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F305" t="s">
         <v>1550</v>
@@ -18725,7 +18725,7 @@
         <v>1487</v>
       </c>
       <c r="E306">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F306" t="s">
         <v>1550</v>
@@ -18760,7 +18760,7 @@
         <v>1487</v>
       </c>
       <c r="E307">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F307" t="s">
         <v>1550</v>
@@ -18795,7 +18795,7 @@
         <v>1487</v>
       </c>
       <c r="E308">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F308" t="s">
         <v>1550</v>
@@ -18830,7 +18830,7 @@
         <v>1488</v>
       </c>
       <c r="E309">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F309" t="s">
         <v>1550</v>
@@ -18865,7 +18865,7 @@
         <v>1488</v>
       </c>
       <c r="E310">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F310" t="s">
         <v>1550</v>
@@ -18900,7 +18900,7 @@
         <v>1488</v>
       </c>
       <c r="E311">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F311" t="s">
         <v>1550</v>
@@ -18935,7 +18935,7 @@
         <v>1488</v>
       </c>
       <c r="E312">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F312" t="s">
         <v>1550</v>
@@ -18970,7 +18970,7 @@
         <v>1488</v>
       </c>
       <c r="E313">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F313" t="s">
         <v>1550</v>
@@ -19005,7 +19005,7 @@
         <v>1488</v>
       </c>
       <c r="E314">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F314" t="s">
         <v>1550</v>
@@ -19040,7 +19040,7 @@
         <v>1488</v>
       </c>
       <c r="E315">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F315" t="s">
         <v>1550</v>
@@ -19075,7 +19075,7 @@
         <v>1488</v>
       </c>
       <c r="E316">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F316" t="s">
         <v>1550</v>
@@ -19110,7 +19110,7 @@
         <v>1488</v>
       </c>
       <c r="E317">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F317" t="s">
         <v>1550</v>
@@ -19145,7 +19145,7 @@
         <v>1489</v>
       </c>
       <c r="E318">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F318" t="s">
         <v>1550</v>
@@ -19180,7 +19180,7 @@
         <v>1489</v>
       </c>
       <c r="E319">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F319" t="s">
         <v>1550</v>
@@ -19215,7 +19215,7 @@
         <v>1489</v>
       </c>
       <c r="E320">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F320" t="s">
         <v>1550</v>
@@ -19250,7 +19250,7 @@
         <v>1490</v>
       </c>
       <c r="E321">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F321" t="s">
         <v>1550</v>
@@ -19285,7 +19285,7 @@
         <v>1491</v>
       </c>
       <c r="E322">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F322" t="s">
         <v>1550</v>
@@ -19320,7 +19320,7 @@
         <v>1491</v>
       </c>
       <c r="E323">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F323" t="s">
         <v>1550</v>
@@ -19355,7 +19355,7 @@
         <v>1491</v>
       </c>
       <c r="E324">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F324" t="s">
         <v>1550</v>
@@ -19390,7 +19390,7 @@
         <v>1491</v>
       </c>
       <c r="E325">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F325" t="s">
         <v>1550</v>
@@ -19425,7 +19425,7 @@
         <v>1491</v>
       </c>
       <c r="E326">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F326" t="s">
         <v>1554</v>
@@ -19463,7 +19463,7 @@
         <v>1491</v>
       </c>
       <c r="E327">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F327" t="s">
         <v>1550</v>
@@ -19498,7 +19498,7 @@
         <v>1491</v>
       </c>
       <c r="E328">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F328" t="s">
         <v>1550</v>
@@ -19533,7 +19533,7 @@
         <v>1492</v>
       </c>
       <c r="E329">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F329" t="s">
         <v>1550</v>
@@ -19568,7 +19568,7 @@
         <v>1492</v>
       </c>
       <c r="E330">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F330" t="s">
         <v>1550</v>
@@ -19603,7 +19603,7 @@
         <v>1492</v>
       </c>
       <c r="E331">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F331" t="s">
         <v>1550</v>
@@ -19638,7 +19638,7 @@
         <v>1492</v>
       </c>
       <c r="E332">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F332" t="s">
         <v>1550</v>
@@ -19676,7 +19676,7 @@
         <v>1492</v>
       </c>
       <c r="E333">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F333" t="s">
         <v>1550</v>
@@ -19711,7 +19711,7 @@
         <v>1492</v>
       </c>
       <c r="E334">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F334" t="s">
         <v>1550</v>
@@ -19746,7 +19746,7 @@
         <v>1492</v>
       </c>
       <c r="E335">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F335" t="s">
         <v>1550</v>
@@ -19781,7 +19781,7 @@
         <v>1492</v>
       </c>
       <c r="E336">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F336" t="s">
         <v>1550</v>
@@ -19816,7 +19816,7 @@
         <v>1492</v>
       </c>
       <c r="E337">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F337" t="s">
         <v>1550</v>
@@ -19851,7 +19851,7 @@
         <v>1493</v>
       </c>
       <c r="E338">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F338" t="s">
         <v>1551</v>
@@ -19886,7 +19886,7 @@
         <v>1494</v>
       </c>
       <c r="E339">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F339" t="s">
         <v>1554</v>
@@ -19921,7 +19921,7 @@
         <v>1495</v>
       </c>
       <c r="E340">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F340" t="s">
         <v>1550</v>
@@ -19956,7 +19956,7 @@
         <v>1496</v>
       </c>
       <c r="E341">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F341" t="s">
         <v>1550</v>
@@ -19991,7 +19991,7 @@
         <v>1496</v>
       </c>
       <c r="E342">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F342" t="s">
         <v>1550</v>
@@ -20026,7 +20026,7 @@
         <v>1497</v>
       </c>
       <c r="E343">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F343" t="s">
         <v>1550</v>
@@ -20061,7 +20061,7 @@
         <v>1498</v>
       </c>
       <c r="E344">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F344" t="s">
         <v>1553</v>
@@ -20096,7 +20096,7 @@
         <v>1498</v>
       </c>
       <c r="E345">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F345" t="s">
         <v>1550</v>
@@ -20131,7 +20131,7 @@
         <v>1498</v>
       </c>
       <c r="E346">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F346" t="s">
         <v>1550</v>
@@ -20166,7 +20166,7 @@
         <v>1498</v>
       </c>
       <c r="E347">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F347" t="s">
         <v>1550</v>
@@ -20201,7 +20201,7 @@
         <v>1498</v>
       </c>
       <c r="E348">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F348" t="s">
         <v>1550</v>
@@ -20236,7 +20236,7 @@
         <v>1498</v>
       </c>
       <c r="E349">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F349" t="s">
         <v>1550</v>
@@ -20271,7 +20271,7 @@
         <v>1499</v>
       </c>
       <c r="E350">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F350" t="s">
         <v>1550</v>
@@ -20306,7 +20306,7 @@
         <v>1499</v>
       </c>
       <c r="E351">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F351" t="s">
         <v>1550</v>
@@ -20341,7 +20341,7 @@
         <v>1499</v>
       </c>
       <c r="E352">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F352" t="s">
         <v>1550</v>
@@ -20376,7 +20376,7 @@
         <v>1500</v>
       </c>
       <c r="E353">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F353" t="s">
         <v>1550</v>
@@ -20411,7 +20411,7 @@
         <v>1500</v>
       </c>
       <c r="E354">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F354" t="s">
         <v>1550</v>
@@ -20446,7 +20446,7 @@
         <v>1500</v>
       </c>
       <c r="E355">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F355" t="s">
         <v>1550</v>
@@ -20484,7 +20484,7 @@
         <v>1500</v>
       </c>
       <c r="E356">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F356" t="s">
         <v>1550</v>
@@ -20519,7 +20519,7 @@
         <v>1501</v>
       </c>
       <c r="E357">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F357" t="s">
         <v>1550</v>
@@ -20554,7 +20554,7 @@
         <v>1501</v>
       </c>
       <c r="E358">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F358" t="s">
         <v>1550</v>
@@ -20589,7 +20589,7 @@
         <v>1501</v>
       </c>
       <c r="E359">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F359" t="s">
         <v>1550</v>
@@ -20624,7 +20624,7 @@
         <v>1501</v>
       </c>
       <c r="E360">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F360" t="s">
         <v>1550</v>
@@ -20659,7 +20659,7 @@
         <v>1501</v>
       </c>
       <c r="E361">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F361" t="s">
         <v>1550</v>
@@ -20694,7 +20694,7 @@
         <v>1502</v>
       </c>
       <c r="E362">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F362" t="s">
         <v>1550</v>
@@ -20729,7 +20729,7 @@
         <v>1502</v>
       </c>
       <c r="E363">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F363" t="s">
         <v>1550</v>
@@ -20764,7 +20764,7 @@
         <v>1503</v>
       </c>
       <c r="E364">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F364" t="s">
         <v>1550</v>
@@ -20799,7 +20799,7 @@
         <v>1503</v>
       </c>
       <c r="E365">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F365" t="s">
         <v>1550</v>
@@ -20834,7 +20834,7 @@
         <v>1503</v>
       </c>
       <c r="E366">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F366" t="s">
         <v>1550</v>
@@ -20869,7 +20869,7 @@
         <v>1503</v>
       </c>
       <c r="E367">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F367" t="s">
         <v>1550</v>
@@ -20904,7 +20904,7 @@
         <v>1503</v>
       </c>
       <c r="E368">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F368" t="s">
         <v>1550</v>
@@ -20939,7 +20939,7 @@
         <v>1503</v>
       </c>
       <c r="E369">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F369" t="s">
         <v>1550</v>
@@ -20974,7 +20974,7 @@
         <v>1503</v>
       </c>
       <c r="E370">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F370" t="s">
         <v>1550</v>
@@ -21009,7 +21009,7 @@
         <v>1503</v>
       </c>
       <c r="E371">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F371" t="s">
         <v>1550</v>
@@ -21044,7 +21044,7 @@
         <v>1503</v>
       </c>
       <c r="E372">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F372" t="s">
         <v>1550</v>
@@ -21079,7 +21079,7 @@
         <v>1503</v>
       </c>
       <c r="E373">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F373" t="s">
         <v>1550</v>
@@ -21114,7 +21114,7 @@
         <v>1504</v>
       </c>
       <c r="E374">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F374" t="s">
         <v>1550</v>
@@ -21149,7 +21149,7 @@
         <v>1504</v>
       </c>
       <c r="E375">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F375" t="s">
         <v>1550</v>
@@ -21184,7 +21184,7 @@
         <v>1504</v>
       </c>
       <c r="E376">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F376" t="s">
         <v>1551</v>
@@ -21219,7 +21219,7 @@
         <v>1505</v>
       </c>
       <c r="E377">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F377" t="s">
         <v>1550</v>
@@ -21254,7 +21254,7 @@
         <v>1505</v>
       </c>
       <c r="E378">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F378" t="s">
         <v>1550</v>
@@ -21289,7 +21289,7 @@
         <v>1505</v>
       </c>
       <c r="E379">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F379" t="s">
         <v>1550</v>
@@ -21324,7 +21324,7 @@
         <v>1505</v>
       </c>
       <c r="E380">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F380" t="s">
         <v>1550</v>
@@ -21359,7 +21359,7 @@
         <v>1505</v>
       </c>
       <c r="E381">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F381" t="s">
         <v>1550</v>
@@ -21394,7 +21394,7 @@
         <v>1505</v>
       </c>
       <c r="E382">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F382" t="s">
         <v>1550</v>
@@ -21429,7 +21429,7 @@
         <v>1505</v>
       </c>
       <c r="E383">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F383" t="s">
         <v>1553</v>
@@ -21464,7 +21464,7 @@
         <v>1506</v>
       </c>
       <c r="E384">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F384" t="s">
         <v>1550</v>
@@ -21499,7 +21499,7 @@
         <v>1506</v>
       </c>
       <c r="E385">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F385" t="s">
         <v>1550</v>
@@ -21534,7 +21534,7 @@
         <v>1506</v>
       </c>
       <c r="E386">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F386" t="s">
         <v>1550</v>
@@ -21569,7 +21569,7 @@
         <v>1506</v>
       </c>
       <c r="E387">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F387" t="s">
         <v>1550</v>
@@ -21604,7 +21604,7 @@
         <v>1507</v>
       </c>
       <c r="E388">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F388" t="s">
         <v>1553</v>
@@ -21639,7 +21639,7 @@
         <v>1507</v>
       </c>
       <c r="E389">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F389" t="s">
         <v>1550</v>
@@ -21674,7 +21674,7 @@
         <v>1507</v>
       </c>
       <c r="E390">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F390" t="s">
         <v>1550</v>
@@ -21709,7 +21709,7 @@
         <v>1507</v>
       </c>
       <c r="E391">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F391" t="s">
         <v>1550</v>
@@ -21744,7 +21744,7 @@
         <v>1507</v>
       </c>
       <c r="E392">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F392" t="s">
         <v>1550</v>
@@ -21779,7 +21779,7 @@
         <v>1507</v>
       </c>
       <c r="E393">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F393" t="s">
         <v>1550</v>
@@ -21814,7 +21814,7 @@
         <v>1508</v>
       </c>
       <c r="E394">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F394" t="s">
         <v>1550</v>
@@ -21849,7 +21849,7 @@
         <v>1508</v>
       </c>
       <c r="E395">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F395" t="s">
         <v>1550</v>
@@ -21884,7 +21884,7 @@
         <v>1508</v>
       </c>
       <c r="E396">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F396" t="s">
         <v>1550</v>
@@ -21919,7 +21919,7 @@
         <v>1508</v>
       </c>
       <c r="E397">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F397" t="s">
         <v>1550</v>
@@ -21954,7 +21954,7 @@
         <v>1508</v>
       </c>
       <c r="E398">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F398" t="s">
         <v>1552</v>
@@ -21989,7 +21989,7 @@
         <v>1508</v>
       </c>
       <c r="E399">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F399" t="s">
         <v>1550</v>
@@ -22024,7 +22024,7 @@
         <v>1508</v>
       </c>
       <c r="E400">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F400" t="s">
         <v>1550</v>
@@ -22059,7 +22059,7 @@
         <v>1509</v>
       </c>
       <c r="E401">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F401" t="s">
         <v>1550</v>
@@ -22094,7 +22094,7 @@
         <v>1509</v>
       </c>
       <c r="E402">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F402" t="s">
         <v>1550</v>
@@ -22129,7 +22129,7 @@
         <v>1509</v>
       </c>
       <c r="E403">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F403" t="s">
         <v>1550</v>
@@ -22164,7 +22164,7 @@
         <v>1509</v>
       </c>
       <c r="E404">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F404" t="s">
         <v>1550</v>
@@ -22199,7 +22199,7 @@
         <v>1509</v>
       </c>
       <c r="E405">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F405" t="s">
         <v>1550</v>
@@ -22234,7 +22234,7 @@
         <v>1510</v>
       </c>
       <c r="E406">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F406" t="s">
         <v>1550</v>
@@ -22269,7 +22269,7 @@
         <v>1510</v>
       </c>
       <c r="E407">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F407" t="s">
         <v>1550</v>
@@ -22304,7 +22304,7 @@
         <v>1510</v>
       </c>
       <c r="E408">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F408" t="s">
         <v>1550</v>
@@ -22339,7 +22339,7 @@
         <v>1510</v>
       </c>
       <c r="E409">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F409" t="s">
         <v>1550</v>
@@ -22374,7 +22374,7 @@
         <v>1510</v>
       </c>
       <c r="E410">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F410" t="s">
         <v>1550</v>
@@ -22412,7 +22412,7 @@
         <v>1511</v>
       </c>
       <c r="E411">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F411" t="s">
         <v>1550</v>
@@ -22447,7 +22447,7 @@
         <v>1511</v>
       </c>
       <c r="E412">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F412" t="s">
         <v>1550</v>
@@ -22482,7 +22482,7 @@
         <v>1511</v>
       </c>
       <c r="E413">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F413" t="s">
         <v>1550</v>
@@ -22517,7 +22517,7 @@
         <v>1511</v>
       </c>
       <c r="E414">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F414" t="s">
         <v>1550</v>
@@ -22552,7 +22552,7 @@
         <v>1511</v>
       </c>
       <c r="E415">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F415" t="s">
         <v>1550</v>
@@ -22587,7 +22587,7 @@
         <v>1511</v>
       </c>
       <c r="E416">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F416" t="s">
         <v>1550</v>
@@ -22622,7 +22622,7 @@
         <v>1512</v>
       </c>
       <c r="E417">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F417" t="s">
         <v>1551</v>
@@ -22657,7 +22657,7 @@
         <v>1512</v>
       </c>
       <c r="E418">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F418" t="s">
         <v>1550</v>
@@ -22692,7 +22692,7 @@
         <v>1513</v>
       </c>
       <c r="E419">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F419" t="s">
         <v>1550</v>
@@ -22727,7 +22727,7 @@
         <v>1514</v>
       </c>
       <c r="E420">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F420" t="s">
         <v>1550</v>
@@ -22762,7 +22762,7 @@
         <v>1514</v>
       </c>
       <c r="E421">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F421" t="s">
         <v>1550</v>
@@ -22797,7 +22797,7 @@
         <v>1514</v>
       </c>
       <c r="E422">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F422" t="s">
         <v>1552</v>
@@ -22835,7 +22835,7 @@
         <v>1514</v>
       </c>
       <c r="E423">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F423" t="s">
         <v>1550</v>
@@ -22870,7 +22870,7 @@
         <v>1515</v>
       </c>
       <c r="E424">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F424" t="s">
         <v>1550</v>
@@ -22905,7 +22905,7 @@
         <v>1515</v>
       </c>
       <c r="E425">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F425" t="s">
         <v>1550</v>
@@ -22940,7 +22940,7 @@
         <v>1515</v>
       </c>
       <c r="E426">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F426" t="s">
         <v>1550</v>
@@ -22975,7 +22975,7 @@
         <v>1515</v>
       </c>
       <c r="E427">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F427" t="s">
         <v>1550</v>
@@ -23010,7 +23010,7 @@
         <v>1516</v>
       </c>
       <c r="E428">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F428" t="s">
         <v>1550</v>
@@ -23045,7 +23045,7 @@
         <v>1516</v>
       </c>
       <c r="E429">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F429" t="s">
         <v>1550</v>
@@ -23080,7 +23080,7 @@
         <v>1516</v>
       </c>
       <c r="E430">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F430" t="s">
         <v>1550</v>
@@ -23115,7 +23115,7 @@
         <v>1516</v>
       </c>
       <c r="E431">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F431" t="s">
         <v>1550</v>
@@ -23150,7 +23150,7 @@
         <v>1516</v>
       </c>
       <c r="E432">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F432" t="s">
         <v>1550</v>
@@ -23185,7 +23185,7 @@
         <v>1516</v>
       </c>
       <c r="E433">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F433" t="s">
         <v>1550</v>
@@ -23220,7 +23220,7 @@
         <v>1516</v>
       </c>
       <c r="E434">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F434" t="s">
         <v>1550</v>
@@ -23255,7 +23255,7 @@
         <v>1516</v>
       </c>
       <c r="E435">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F435" t="s">
         <v>1550</v>
@@ -23290,7 +23290,7 @@
         <v>1517</v>
       </c>
       <c r="E436">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F436" t="s">
         <v>1550</v>
@@ -23325,7 +23325,7 @@
         <v>1518</v>
       </c>
       <c r="E437">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F437" t="s">
         <v>1550</v>
@@ -23360,7 +23360,7 @@
         <v>1518</v>
       </c>
       <c r="E438">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F438" t="s">
         <v>1550</v>
@@ -23395,7 +23395,7 @@
         <v>1518</v>
       </c>
       <c r="E439">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F439" t="s">
         <v>1550</v>
@@ -23430,7 +23430,7 @@
         <v>1518</v>
       </c>
       <c r="E440">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F440" t="s">
         <v>1554</v>
@@ -23468,7 +23468,7 @@
         <v>1518</v>
       </c>
       <c r="E441">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F441" t="s">
         <v>1550</v>
@@ -23503,7 +23503,7 @@
         <v>1518</v>
       </c>
       <c r="E442">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F442" t="s">
         <v>1554</v>
@@ -23538,7 +23538,7 @@
         <v>1519</v>
       </c>
       <c r="E443">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F443" t="s">
         <v>1550</v>
@@ -23573,7 +23573,7 @@
         <v>1520</v>
       </c>
       <c r="E444">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F444" t="s">
         <v>1550</v>
@@ -23608,7 +23608,7 @@
         <v>1520</v>
       </c>
       <c r="E445">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F445" t="s">
         <v>1550</v>
@@ -23643,7 +23643,7 @@
         <v>1520</v>
       </c>
       <c r="E446">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F446" t="s">
         <v>1550</v>
@@ -23678,7 +23678,7 @@
         <v>1520</v>
       </c>
       <c r="E447">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F447" t="s">
         <v>1550</v>
@@ -23713,7 +23713,7 @@
         <v>1521</v>
       </c>
       <c r="E448">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F448" t="s">
         <v>1550</v>
@@ -23748,7 +23748,7 @@
         <v>1521</v>
       </c>
       <c r="E449">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F449" t="s">
         <v>1554</v>
@@ -23783,7 +23783,7 @@
         <v>1521</v>
       </c>
       <c r="E450">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F450" t="s">
         <v>1550</v>
@@ -23818,7 +23818,7 @@
         <v>1521</v>
       </c>
       <c r="E451">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F451" t="s">
         <v>1550</v>
@@ -23853,7 +23853,7 @@
         <v>1521</v>
       </c>
       <c r="E452">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F452" t="s">
         <v>1550</v>
@@ -23888,7 +23888,7 @@
         <v>1522</v>
       </c>
       <c r="E453">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F453" t="s">
         <v>1550</v>
@@ -23923,7 +23923,7 @@
         <v>1522</v>
       </c>
       <c r="E454">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F454" t="s">
         <v>1550</v>
@@ -23958,7 +23958,7 @@
         <v>1522</v>
       </c>
       <c r="E455">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F455" t="s">
         <v>1550</v>
@@ -23993,7 +23993,7 @@
         <v>1523</v>
       </c>
       <c r="E456">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F456" t="s">
         <v>1550</v>
@@ -24028,7 +24028,7 @@
         <v>1523</v>
       </c>
       <c r="E457">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F457" t="s">
         <v>1550</v>
@@ -24063,7 +24063,7 @@
         <v>1523</v>
       </c>
       <c r="E458">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F458" t="s">
         <v>1550</v>
@@ -24098,7 +24098,7 @@
         <v>1523</v>
       </c>
       <c r="E459">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F459" t="s">
         <v>1550</v>
@@ -24133,7 +24133,7 @@
         <v>1523</v>
       </c>
       <c r="E460">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F460" t="s">
         <v>1550</v>
@@ -24168,7 +24168,7 @@
         <v>1523</v>
       </c>
       <c r="E461">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F461" t="s">
         <v>1550</v>
@@ -24203,7 +24203,7 @@
         <v>1524</v>
       </c>
       <c r="E462">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F462" t="s">
         <v>1550</v>
@@ -24238,7 +24238,7 @@
         <v>1524</v>
       </c>
       <c r="E463">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F463" t="s">
         <v>1550</v>
@@ -24273,7 +24273,7 @@
         <v>1524</v>
       </c>
       <c r="E464">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F464" t="s">
         <v>1550</v>
@@ -24308,7 +24308,7 @@
         <v>1524</v>
       </c>
       <c r="E465">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F465" t="s">
         <v>1550</v>
@@ -24343,7 +24343,7 @@
         <v>1524</v>
       </c>
       <c r="E466">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F466" t="s">
         <v>1550</v>
@@ -24378,7 +24378,7 @@
         <v>1524</v>
       </c>
       <c r="E467">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F467" t="s">
         <v>1550</v>
@@ -24413,7 +24413,7 @@
         <v>1524</v>
       </c>
       <c r="E468">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F468" t="s">
         <v>1550</v>
@@ -24448,7 +24448,7 @@
         <v>1524</v>
       </c>
       <c r="E469">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F469" t="s">
         <v>1550</v>
@@ -24483,7 +24483,7 @@
         <v>1524</v>
       </c>
       <c r="E470">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F470" t="s">
         <v>1550</v>
@@ -24518,7 +24518,7 @@
         <v>1524</v>
       </c>
       <c r="E471">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F471" t="s">
         <v>1550</v>
@@ -24553,7 +24553,7 @@
         <v>1524</v>
       </c>
       <c r="E472">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F472" t="s">
         <v>1550</v>
@@ -24588,7 +24588,7 @@
         <v>1524</v>
       </c>
       <c r="E473">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F473" t="s">
         <v>1550</v>
@@ -24623,7 +24623,7 @@
         <v>1524</v>
       </c>
       <c r="E474">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F474" t="s">
         <v>1550</v>
@@ -24658,7 +24658,7 @@
         <v>1524</v>
       </c>
       <c r="E475">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F475" t="s">
         <v>1550</v>
@@ -24693,7 +24693,7 @@
         <v>1524</v>
       </c>
       <c r="E476">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F476" t="s">
         <v>1550</v>
@@ -24728,7 +24728,7 @@
         <v>1524</v>
       </c>
       <c r="E477">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F477" t="s">
         <v>1550</v>
@@ -24763,7 +24763,7 @@
         <v>1524</v>
       </c>
       <c r="E478">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F478" t="s">
         <v>1550</v>
@@ -24798,7 +24798,7 @@
         <v>1524</v>
       </c>
       <c r="E479">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F479" t="s">
         <v>1550</v>
@@ -24833,7 +24833,7 @@
         <v>1524</v>
       </c>
       <c r="E480">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F480" t="s">
         <v>1550</v>
@@ -24868,7 +24868,7 @@
         <v>1524</v>
       </c>
       <c r="E481">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F481" t="s">
         <v>1550</v>
@@ -24903,7 +24903,7 @@
         <v>1524</v>
       </c>
       <c r="E482">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F482" t="s">
         <v>1550</v>
@@ -24938,7 +24938,7 @@
         <v>1524</v>
       </c>
       <c r="E483">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F483" t="s">
         <v>1550</v>
@@ -24973,7 +24973,7 @@
         <v>1524</v>
       </c>
       <c r="E484">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F484" t="s">
         <v>1550</v>
@@ -25008,7 +25008,7 @@
         <v>1524</v>
       </c>
       <c r="E485">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F485" t="s">
         <v>1550</v>
@@ -25043,7 +25043,7 @@
         <v>1524</v>
       </c>
       <c r="E486">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F486" t="s">
         <v>1550</v>
@@ -25078,7 +25078,7 @@
         <v>1525</v>
       </c>
       <c r="E487">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F487" t="s">
         <v>1550</v>
@@ -25113,7 +25113,7 @@
         <v>1525</v>
       </c>
       <c r="E488">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F488" t="s">
         <v>1550</v>
@@ -25148,7 +25148,7 @@
         <v>1525</v>
       </c>
       <c r="E489">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F489" t="s">
         <v>1550</v>
@@ -25183,7 +25183,7 @@
         <v>1525</v>
       </c>
       <c r="E490">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F490" t="s">
         <v>1550</v>
@@ -25218,7 +25218,7 @@
         <v>1525</v>
       </c>
       <c r="E491">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F491" t="s">
         <v>1550</v>
@@ -25253,7 +25253,7 @@
         <v>1525</v>
       </c>
       <c r="E492">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F492" t="s">
         <v>1550</v>
@@ -25288,7 +25288,7 @@
         <v>1525</v>
       </c>
       <c r="E493">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F493" t="s">
         <v>1554</v>
@@ -25323,7 +25323,7 @@
         <v>1525</v>
       </c>
       <c r="E494">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F494" t="s">
         <v>1550</v>
@@ -25358,7 +25358,7 @@
         <v>1526</v>
       </c>
       <c r="E495">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F495" t="s">
         <v>1550</v>
@@ -25393,7 +25393,7 @@
         <v>1526</v>
       </c>
       <c r="E496">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F496" t="s">
         <v>1552</v>
@@ -25431,7 +25431,7 @@
         <v>1527</v>
       </c>
       <c r="E497">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F497" t="s">
         <v>1552</v>
@@ -25469,7 +25469,7 @@
         <v>1527</v>
       </c>
       <c r="E498">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F498" t="s">
         <v>1550</v>
@@ -25504,7 +25504,7 @@
         <v>1527</v>
       </c>
       <c r="E499">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F499" t="s">
         <v>1550</v>
@@ -25539,7 +25539,7 @@
         <v>1527</v>
       </c>
       <c r="E500">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F500" t="s">
         <v>1550</v>
@@ -25574,7 +25574,7 @@
         <v>1527</v>
       </c>
       <c r="E501">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F501" t="s">
         <v>1550</v>
@@ -25609,7 +25609,7 @@
         <v>1527</v>
       </c>
       <c r="E502">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F502" t="s">
         <v>1550</v>
@@ -25644,7 +25644,7 @@
         <v>1528</v>
       </c>
       <c r="E503">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F503" t="s">
         <v>1550</v>
@@ -25682,7 +25682,7 @@
         <v>1528</v>
       </c>
       <c r="E504">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F504" t="s">
         <v>1554</v>
@@ -25717,7 +25717,7 @@
         <v>1528</v>
       </c>
       <c r="E505">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F505" t="s">
         <v>1552</v>
@@ -25752,7 +25752,7 @@
         <v>1528</v>
       </c>
       <c r="E506">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F506" t="s">
         <v>1550</v>
@@ -25787,7 +25787,7 @@
         <v>1528</v>
       </c>
       <c r="E507">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F507" t="s">
         <v>1550</v>
@@ -25822,7 +25822,7 @@
         <v>1528</v>
       </c>
       <c r="E508">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F508" t="s">
         <v>1550</v>
@@ -25857,7 +25857,7 @@
         <v>1528</v>
       </c>
       <c r="E509">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F509" t="s">
         <v>1550</v>
@@ -25892,7 +25892,7 @@
         <v>1528</v>
       </c>
       <c r="E510">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F510" t="s">
         <v>1550</v>
@@ -25927,7 +25927,7 @@
         <v>1528</v>
       </c>
       <c r="E511">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F511" t="s">
         <v>1550</v>
@@ -25962,7 +25962,7 @@
         <v>1529</v>
       </c>
       <c r="E512">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F512" t="s">
         <v>1554</v>
@@ -26000,7 +26000,7 @@
         <v>1529</v>
       </c>
       <c r="E513">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F513" t="s">
         <v>1550</v>
@@ -26035,7 +26035,7 @@
         <v>1530</v>
       </c>
       <c r="E514">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F514" t="s">
         <v>1550</v>
@@ -26070,7 +26070,7 @@
         <v>1530</v>
       </c>
       <c r="E515">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F515" t="s">
         <v>1550</v>
@@ -26105,7 +26105,7 @@
         <v>1530</v>
       </c>
       <c r="E516">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F516" t="s">
         <v>1550</v>
@@ -26140,7 +26140,7 @@
         <v>1530</v>
       </c>
       <c r="E517">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F517" t="s">
         <v>1550</v>
@@ -26175,7 +26175,7 @@
         <v>1530</v>
       </c>
       <c r="E518">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F518" t="s">
         <v>1550</v>
@@ -26210,7 +26210,7 @@
         <v>1530</v>
       </c>
       <c r="E519">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F519" t="s">
         <v>1550</v>
@@ -26245,7 +26245,7 @@
         <v>1530</v>
       </c>
       <c r="E520">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F520" t="s">
         <v>1550</v>
@@ -26280,7 +26280,7 @@
         <v>1531</v>
       </c>
       <c r="E521">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F521" t="s">
         <v>1550</v>
@@ -26315,7 +26315,7 @@
         <v>1531</v>
       </c>
       <c r="E522">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F522" t="s">
         <v>1550</v>
@@ -26350,7 +26350,7 @@
         <v>1531</v>
       </c>
       <c r="E523">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F523" t="s">
         <v>1550</v>
@@ -26385,7 +26385,7 @@
         <v>1531</v>
       </c>
       <c r="E524">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F524" t="s">
         <v>1550</v>
@@ -26420,7 +26420,7 @@
         <v>1531</v>
       </c>
       <c r="E525">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F525" t="s">
         <v>1550</v>
@@ -26455,7 +26455,7 @@
         <v>1531</v>
       </c>
       <c r="E526">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F526" t="s">
         <v>1550</v>
@@ -26490,7 +26490,7 @@
         <v>1531</v>
       </c>
       <c r="E527">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F527" t="s">
         <v>1552</v>
@@ -26525,7 +26525,7 @@
         <v>1531</v>
       </c>
       <c r="E528">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F528" t="s">
         <v>1550</v>
@@ -26560,7 +26560,7 @@
         <v>1531</v>
       </c>
       <c r="E529">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F529" t="s">
         <v>1554</v>
@@ -26595,7 +26595,7 @@
         <v>1531</v>
       </c>
       <c r="E530">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F530" t="s">
         <v>1550</v>
@@ -26630,7 +26630,7 @@
         <v>1532</v>
       </c>
       <c r="E531">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F531" t="s">
         <v>1550</v>
@@ -26665,7 +26665,7 @@
         <v>1532</v>
       </c>
       <c r="E532">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F532" t="s">
         <v>1550</v>
@@ -26700,7 +26700,7 @@
         <v>1532</v>
       </c>
       <c r="E533">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F533" t="s">
         <v>1550</v>
@@ -26735,7 +26735,7 @@
         <v>1532</v>
       </c>
       <c r="E534">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F534" t="s">
         <v>1550</v>
@@ -26770,7 +26770,7 @@
         <v>1532</v>
       </c>
       <c r="E535">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F535" t="s">
         <v>1550</v>
@@ -26805,7 +26805,7 @@
         <v>1532</v>
       </c>
       <c r="E536">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F536" t="s">
         <v>1550</v>
@@ -26840,7 +26840,7 @@
         <v>1532</v>
       </c>
       <c r="E537">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F537" t="s">
         <v>1550</v>
@@ -26875,7 +26875,7 @@
         <v>1532</v>
       </c>
       <c r="E538">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F538" t="s">
         <v>1550</v>
@@ -26913,7 +26913,7 @@
         <v>1532</v>
       </c>
       <c r="E539">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F539" t="s">
         <v>1552</v>
@@ -26951,7 +26951,7 @@
         <v>1532</v>
       </c>
       <c r="E540">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F540" t="s">
         <v>1552</v>
@@ -26986,7 +26986,7 @@
         <v>1532</v>
       </c>
       <c r="E541">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F541" t="s">
         <v>1550</v>
@@ -27021,7 +27021,7 @@
         <v>1533</v>
       </c>
       <c r="E542">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F542" t="s">
         <v>1550</v>
@@ -27056,7 +27056,7 @@
         <v>1533</v>
       </c>
       <c r="E543">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F543" t="s">
         <v>1550</v>
@@ -27091,7 +27091,7 @@
         <v>1533</v>
       </c>
       <c r="E544">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F544" t="s">
         <v>1550</v>
@@ -27126,7 +27126,7 @@
         <v>1533</v>
       </c>
       <c r="E545">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F545" t="s">
         <v>1550</v>
@@ -27161,7 +27161,7 @@
         <v>1533</v>
       </c>
       <c r="E546">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F546" t="s">
         <v>1550</v>
@@ -27196,7 +27196,7 @@
         <v>1533</v>
       </c>
       <c r="E547">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F547" t="s">
         <v>1550</v>
@@ -27231,7 +27231,7 @@
         <v>1533</v>
       </c>
       <c r="E548">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F548" t="s">
         <v>1550</v>
@@ -27266,7 +27266,7 @@
         <v>1534</v>
       </c>
       <c r="E549">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F549" t="s">
         <v>1550</v>
@@ -27301,7 +27301,7 @@
         <v>1535</v>
       </c>
       <c r="E550">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F550" t="s">
         <v>1550</v>
@@ -27339,7 +27339,7 @@
         <v>1535</v>
       </c>
       <c r="E551">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F551" t="s">
         <v>1550</v>
@@ -27374,7 +27374,7 @@
         <v>1535</v>
       </c>
       <c r="E552">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F552" t="s">
         <v>1550</v>
@@ -27409,7 +27409,7 @@
         <v>1535</v>
       </c>
       <c r="E553">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F553" t="s">
         <v>1552</v>
@@ -27447,7 +27447,7 @@
         <v>1535</v>
       </c>
       <c r="E554">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F554" t="s">
         <v>1552</v>
@@ -27485,7 +27485,7 @@
         <v>1535</v>
       </c>
       <c r="E555">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F555" t="s">
         <v>1550</v>
@@ -27520,7 +27520,7 @@
         <v>1535</v>
       </c>
       <c r="E556">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F556" t="s">
         <v>1550</v>
@@ -27555,7 +27555,7 @@
         <v>1535</v>
       </c>
       <c r="E557">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F557" t="s">
         <v>1550</v>
@@ -27590,7 +27590,7 @@
         <v>1536</v>
       </c>
       <c r="E558">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F558" t="s">
         <v>1550</v>
@@ -27625,7 +27625,7 @@
         <v>1536</v>
       </c>
       <c r="E559">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F559" t="s">
         <v>1550</v>
@@ -27660,7 +27660,7 @@
         <v>1536</v>
       </c>
       <c r="E560">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F560" t="s">
         <v>1550</v>
@@ -27695,7 +27695,7 @@
         <v>1536</v>
       </c>
       <c r="E561">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F561" t="s">
         <v>1550</v>
@@ -27730,7 +27730,7 @@
         <v>1536</v>
       </c>
       <c r="E562">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F562" t="s">
         <v>1550</v>
@@ -27765,7 +27765,7 @@
         <v>1536</v>
       </c>
       <c r="E563">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F563" t="s">
         <v>1550</v>
@@ -27800,7 +27800,7 @@
         <v>1536</v>
       </c>
       <c r="E564">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F564" t="s">
         <v>1550</v>
@@ -27835,7 +27835,7 @@
         <v>1536</v>
       </c>
       <c r="E565">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F565" t="s">
         <v>1550</v>
@@ -27870,7 +27870,7 @@
         <v>1536</v>
       </c>
       <c r="E566">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F566" t="s">
         <v>1550</v>
@@ -27908,7 +27908,7 @@
         <v>1536</v>
       </c>
       <c r="E567">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F567" t="s">
         <v>1550</v>
@@ -27943,7 +27943,7 @@
         <v>1537</v>
       </c>
       <c r="E568">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F568" t="s">
         <v>1550</v>
@@ -27978,7 +27978,7 @@
         <v>1537</v>
       </c>
       <c r="E569">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F569" t="s">
         <v>1552</v>
@@ -28016,7 +28016,7 @@
         <v>1537</v>
       </c>
       <c r="E570">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F570" t="s">
         <v>1550</v>
@@ -28051,7 +28051,7 @@
         <v>1537</v>
       </c>
       <c r="E571">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F571" t="s">
         <v>1550</v>
@@ -28086,7 +28086,7 @@
         <v>1538</v>
       </c>
       <c r="E572">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F572" t="s">
         <v>1550</v>
@@ -28121,7 +28121,7 @@
         <v>1538</v>
       </c>
       <c r="E573">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F573" t="s">
         <v>1552</v>
@@ -28156,7 +28156,7 @@
         <v>1538</v>
       </c>
       <c r="E574">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F574" t="s">
         <v>1550</v>
@@ -28191,7 +28191,7 @@
         <v>1538</v>
       </c>
       <c r="E575">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F575" t="s">
         <v>1550</v>
@@ -28226,7 +28226,7 @@
         <v>1538</v>
       </c>
       <c r="E576">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F576" t="s">
         <v>1552</v>
@@ -28264,7 +28264,7 @@
         <v>1538</v>
       </c>
       <c r="E577">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F577" t="s">
         <v>1550</v>
@@ -28299,7 +28299,7 @@
         <v>1538</v>
       </c>
       <c r="E578">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F578" t="s">
         <v>1550</v>
@@ -28334,7 +28334,7 @@
         <v>1538</v>
       </c>
       <c r="E579">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F579" t="s">
         <v>1550</v>
@@ -28369,7 +28369,7 @@
         <v>1538</v>
       </c>
       <c r="E580">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F580" t="s">
         <v>1550</v>
@@ -28404,7 +28404,7 @@
         <v>1538</v>
       </c>
       <c r="E581">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F581" t="s">
         <v>1550</v>
@@ -28439,7 +28439,7 @@
         <v>1538</v>
       </c>
       <c r="E582">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F582" t="s">
         <v>1550</v>
@@ -28474,7 +28474,7 @@
         <v>1538</v>
       </c>
       <c r="E583">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F583" t="s">
         <v>1550</v>
@@ -28509,7 +28509,7 @@
         <v>1539</v>
       </c>
       <c r="E584">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F584" t="s">
         <v>1554</v>
@@ -28544,7 +28544,7 @@
         <v>1539</v>
       </c>
       <c r="E585">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F585" t="s">
         <v>1550</v>
@@ -28579,7 +28579,7 @@
         <v>1539</v>
       </c>
       <c r="E586">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F586" t="s">
         <v>1550</v>
@@ -28614,7 +28614,7 @@
         <v>1539</v>
       </c>
       <c r="E587">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F587" t="s">
         <v>1550</v>
@@ -28649,7 +28649,7 @@
         <v>1539</v>
       </c>
       <c r="E588">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F588" t="s">
         <v>1552</v>
@@ -28684,7 +28684,7 @@
         <v>1539</v>
       </c>
       <c r="E589">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F589" t="s">
         <v>1550</v>
@@ -28719,7 +28719,7 @@
         <v>1539</v>
       </c>
       <c r="E590">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F590" t="s">
         <v>1550</v>
@@ -28754,7 +28754,7 @@
         <v>1540</v>
       </c>
       <c r="E591">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F591" t="s">
         <v>1550</v>
@@ -28789,7 +28789,7 @@
         <v>1540</v>
       </c>
       <c r="E592">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F592" t="s">
         <v>1550</v>
@@ -28824,7 +28824,7 @@
         <v>1540</v>
       </c>
       <c r="E593">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F593" t="s">
         <v>1550</v>
@@ -28859,7 +28859,7 @@
         <v>1540</v>
       </c>
       <c r="E594">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F594" t="s">
         <v>1552</v>
@@ -28897,7 +28897,7 @@
         <v>1541</v>
       </c>
       <c r="E595">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F595" t="s">
         <v>1550</v>
@@ -28932,7 +28932,7 @@
         <v>1541</v>
       </c>
       <c r="E596">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F596" t="s">
         <v>1554</v>
@@ -28970,7 +28970,7 @@
         <v>1541</v>
       </c>
       <c r="E597">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F597" t="s">
         <v>1550</v>
@@ -29005,7 +29005,7 @@
         <v>1541</v>
       </c>
       <c r="E598">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F598" t="s">
         <v>1550</v>
@@ -29040,7 +29040,7 @@
         <v>1542</v>
       </c>
       <c r="E599">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F599" t="s">
         <v>1550</v>
@@ -29075,7 +29075,7 @@
         <v>1542</v>
       </c>
       <c r="E600">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F600" t="s">
         <v>1550</v>
@@ -29110,7 +29110,7 @@
         <v>1542</v>
       </c>
       <c r="E601">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F601" t="s">
         <v>1550</v>
@@ -29145,7 +29145,7 @@
         <v>1542</v>
       </c>
       <c r="E602">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F602" t="s">
         <v>1552</v>
@@ -29180,7 +29180,7 @@
         <v>1542</v>
       </c>
       <c r="E603">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F603" t="s">
         <v>1550</v>
@@ -29215,7 +29215,7 @@
         <v>1542</v>
       </c>
       <c r="E604">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F604" t="s">
         <v>1550</v>
@@ -29250,7 +29250,7 @@
         <v>1542</v>
       </c>
       <c r="E605">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F605" t="s">
         <v>1550</v>
@@ -29285,7 +29285,7 @@
         <v>1542</v>
       </c>
       <c r="E606">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F606" t="s">
         <v>1552</v>
@@ -29323,7 +29323,7 @@
         <v>1542</v>
       </c>
       <c r="E607">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F607" t="s">
         <v>1550</v>
@@ -29358,7 +29358,7 @@
         <v>1542</v>
       </c>
       <c r="E608">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F608" t="s">
         <v>1550</v>
@@ -29393,7 +29393,7 @@
         <v>1542</v>
       </c>
       <c r="E609">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F609" t="s">
         <v>1550</v>
@@ -29428,7 +29428,7 @@
         <v>1543</v>
       </c>
       <c r="E610">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F610" t="s">
         <v>1554</v>
@@ -29463,7 +29463,7 @@
         <v>1543</v>
       </c>
       <c r="E611">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F611" t="s">
         <v>1550</v>
@@ -29501,7 +29501,7 @@
         <v>1543</v>
       </c>
       <c r="E612">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F612" t="s">
         <v>1550</v>
@@ -29536,7 +29536,7 @@
         <v>1543</v>
       </c>
       <c r="E613">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F613" t="s">
         <v>1552</v>
@@ -29571,7 +29571,7 @@
         <v>1543</v>
       </c>
       <c r="E614">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F614" t="s">
         <v>1550</v>
@@ -29606,7 +29606,7 @@
         <v>1544</v>
       </c>
       <c r="E615">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F615" t="s">
         <v>1552</v>
@@ -29644,7 +29644,7 @@
         <v>1544</v>
       </c>
       <c r="E616">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F616" t="s">
         <v>1552</v>
@@ -29682,7 +29682,7 @@
         <v>1544</v>
       </c>
       <c r="E617">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F617" t="s">
         <v>1550</v>
@@ -29717,7 +29717,7 @@
         <v>1544</v>
       </c>
       <c r="E618">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F618" t="s">
         <v>1550</v>
@@ -29752,7 +29752,7 @@
         <v>1544</v>
       </c>
       <c r="E619">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F619" t="s">
         <v>1550</v>
@@ -29787,7 +29787,7 @@
         <v>1545</v>
       </c>
       <c r="E620">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F620" t="s">
         <v>1552</v>
@@ -29825,7 +29825,7 @@
         <v>1545</v>
       </c>
       <c r="E621">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F621" t="s">
         <v>1550</v>
@@ -29860,7 +29860,7 @@
         <v>1546</v>
       </c>
       <c r="E622">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F622" t="s">
         <v>1550</v>
@@ -29895,7 +29895,7 @@
         <v>1546</v>
       </c>
       <c r="E623">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F623" t="s">
         <v>1550</v>
@@ -29930,7 +29930,7 @@
         <v>1546</v>
       </c>
       <c r="E624">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F624" t="s">
         <v>1550</v>
@@ -29965,7 +29965,7 @@
         <v>1546</v>
       </c>
       <c r="E625">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F625" t="s">
         <v>1550</v>
@@ -30000,7 +30000,7 @@
         <v>1546</v>
       </c>
       <c r="E626">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F626" t="s">
         <v>1550</v>
@@ -30035,7 +30035,7 @@
         <v>1546</v>
       </c>
       <c r="E627">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F627" t="s">
         <v>1550</v>
@@ -30070,7 +30070,7 @@
         <v>1546</v>
       </c>
       <c r="E628">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F628" t="s">
         <v>1550</v>
@@ -30105,7 +30105,7 @@
         <v>1546</v>
       </c>
       <c r="E629">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F629" t="s">
         <v>1550</v>
@@ -30140,7 +30140,7 @@
         <v>1546</v>
       </c>
       <c r="E630">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F630" t="s">
         <v>1550</v>
@@ -30175,7 +30175,7 @@
         <v>1546</v>
       </c>
       <c r="E631">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F631" t="s">
         <v>1552</v>
@@ -30213,7 +30213,7 @@
         <v>1547</v>
       </c>
       <c r="E632">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F632" t="s">
         <v>1550</v>
@@ -30248,7 +30248,7 @@
         <v>1547</v>
       </c>
       <c r="E633">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F633" t="s">
         <v>1550</v>
@@ -30283,7 +30283,7 @@
         <v>1547</v>
       </c>
       <c r="E634">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F634" t="s">
         <v>1550</v>
@@ -30318,7 +30318,7 @@
         <v>1547</v>
       </c>
       <c r="E635">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F635" t="s">
         <v>1550</v>
@@ -30353,7 +30353,7 @@
         <v>1547</v>
       </c>
       <c r="E636">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F636" t="s">
         <v>1552</v>
@@ -30391,7 +30391,7 @@
         <v>1547</v>
       </c>
       <c r="E637">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F637" t="s">
         <v>1552</v>
@@ -30429,7 +30429,7 @@
         <v>1547</v>
       </c>
       <c r="E638">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F638" t="s">
         <v>1550</v>
@@ -30464,7 +30464,7 @@
         <v>1547</v>
       </c>
       <c r="E639">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F639" t="s">
         <v>1552</v>
@@ -30502,7 +30502,7 @@
         <v>1547</v>
       </c>
       <c r="E640">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F640" t="s">
         <v>1550</v>
@@ -30537,7 +30537,7 @@
         <v>1547</v>
       </c>
       <c r="E641">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F641" t="s">
         <v>1550</v>
@@ -30572,7 +30572,7 @@
         <v>1547</v>
       </c>
       <c r="E642">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F642" t="s">
         <v>1550</v>
@@ -30607,7 +30607,7 @@
         <v>1548</v>
       </c>
       <c r="E643">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F643" t="s">
         <v>1550</v>
@@ -30642,7 +30642,7 @@
         <v>1548</v>
       </c>
       <c r="E644">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F644" t="s">
         <v>1550</v>
@@ -30680,7 +30680,7 @@
         <v>1548</v>
       </c>
       <c r="E645">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F645" t="s">
         <v>1552</v>
@@ -30718,7 +30718,7 @@
         <v>1548</v>
       </c>
       <c r="E646">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F646" t="s">
         <v>1550</v>
@@ -30753,7 +30753,7 @@
         <v>1549</v>
       </c>
       <c r="E647">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F647" t="s">
         <v>1550</v>
@@ -30791,7 +30791,7 @@
         <v>1549</v>
       </c>
       <c r="E648">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F648" t="s">
         <v>1550</v>
@@ -30826,7 +30826,7 @@
         <v>1549</v>
       </c>
       <c r="E649">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F649" t="s">
         <v>1550</v>
@@ -30864,7 +30864,7 @@
         <v>1549</v>
       </c>
       <c r="E650">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F650" t="s">
         <v>1550</v>

--- a/BacklogGATEAutoCompleto.xlsx
+++ b/BacklogGATEAutoCompleto.xlsx
@@ -8100,7 +8100,7 @@
         <v>1346</v>
       </c>
       <c r="E2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="F2" t="s">
         <v>1558</v>
@@ -8135,7 +8135,7 @@
         <v>1347</v>
       </c>
       <c r="E3">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="F3" t="s">
         <v>1558</v>
@@ -8170,7 +8170,7 @@
         <v>1348</v>
       </c>
       <c r="E4">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="F4" t="s">
         <v>1558</v>
@@ -8205,7 +8205,7 @@
         <v>1349</v>
       </c>
       <c r="E5">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F5" t="s">
         <v>1558</v>
@@ -8240,7 +8240,7 @@
         <v>1350</v>
       </c>
       <c r="E6">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="F6" t="s">
         <v>1558</v>
@@ -8275,7 +8275,7 @@
         <v>1351</v>
       </c>
       <c r="E7">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F7" t="s">
         <v>1558</v>
@@ -8310,7 +8310,7 @@
         <v>1352</v>
       </c>
       <c r="E8">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="F8" t="s">
         <v>1558</v>
@@ -8345,7 +8345,7 @@
         <v>1353</v>
       </c>
       <c r="E9">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="F9" t="s">
         <v>1558</v>
@@ -8380,7 +8380,7 @@
         <v>1354</v>
       </c>
       <c r="E10">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="F10" t="s">
         <v>1558</v>
@@ -8415,7 +8415,7 @@
         <v>1354</v>
       </c>
       <c r="E11">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="F11" t="s">
         <v>1558</v>
@@ -8450,7 +8450,7 @@
         <v>1355</v>
       </c>
       <c r="E12">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="F12" t="s">
         <v>1558</v>
@@ -8485,7 +8485,7 @@
         <v>1356</v>
       </c>
       <c r="E13">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F13" t="s">
         <v>1558</v>
@@ -8520,7 +8520,7 @@
         <v>1357</v>
       </c>
       <c r="E14">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F14" t="s">
         <v>1558</v>
@@ -8555,7 +8555,7 @@
         <v>1357</v>
       </c>
       <c r="E15">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F15" t="s">
         <v>1558</v>
@@ -8590,7 +8590,7 @@
         <v>1358</v>
       </c>
       <c r="E16">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="F16" t="s">
         <v>1558</v>
@@ -8625,7 +8625,7 @@
         <v>1359</v>
       </c>
       <c r="E17">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="F17" t="s">
         <v>1558</v>
@@ -8660,7 +8660,7 @@
         <v>1359</v>
       </c>
       <c r="E18">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="F18" t="s">
         <v>1558</v>
@@ -8695,7 +8695,7 @@
         <v>1360</v>
       </c>
       <c r="E19">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="F19" t="s">
         <v>1558</v>
@@ -8730,7 +8730,7 @@
         <v>1361</v>
       </c>
       <c r="E20">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="F20" t="s">
         <v>1558</v>
@@ -8765,7 +8765,7 @@
         <v>1362</v>
       </c>
       <c r="E21">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="F21" t="s">
         <v>1558</v>
@@ -8800,7 +8800,7 @@
         <v>1363</v>
       </c>
       <c r="E22">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="F22" t="s">
         <v>1558</v>
@@ -8835,7 +8835,7 @@
         <v>1364</v>
       </c>
       <c r="E23">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="F23" t="s">
         <v>1558</v>
@@ -8873,7 +8873,7 @@
         <v>1365</v>
       </c>
       <c r="E24">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F24" t="s">
         <v>1558</v>
@@ -8908,7 +8908,7 @@
         <v>1366</v>
       </c>
       <c r="E25">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F25" t="s">
         <v>1558</v>
@@ -8943,7 +8943,7 @@
         <v>1367</v>
       </c>
       <c r="E26">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F26" t="s">
         <v>1558</v>
@@ -8978,7 +8978,7 @@
         <v>1368</v>
       </c>
       <c r="E27">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F27" t="s">
         <v>1558</v>
@@ -9013,7 +9013,7 @@
         <v>1369</v>
       </c>
       <c r="E28">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F28" t="s">
         <v>1558</v>
@@ -9048,7 +9048,7 @@
         <v>1370</v>
       </c>
       <c r="E29">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F29" t="s">
         <v>1558</v>
@@ -9083,7 +9083,7 @@
         <v>1371</v>
       </c>
       <c r="E30">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F30" t="s">
         <v>1558</v>
@@ -9118,7 +9118,7 @@
         <v>1372</v>
       </c>
       <c r="E31">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F31" t="s">
         <v>1558</v>
@@ -9153,7 +9153,7 @@
         <v>1373</v>
       </c>
       <c r="E32">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F32" t="s">
         <v>1558</v>
@@ -9188,7 +9188,7 @@
         <v>1374</v>
       </c>
       <c r="E33">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F33" t="s">
         <v>1558</v>
@@ -9223,7 +9223,7 @@
         <v>1375</v>
       </c>
       <c r="E34">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F34" t="s">
         <v>1558</v>
@@ -9258,7 +9258,7 @@
         <v>1375</v>
       </c>
       <c r="E35">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F35" t="s">
         <v>1558</v>
@@ -9293,7 +9293,7 @@
         <v>1376</v>
       </c>
       <c r="E36">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F36" t="s">
         <v>1558</v>
@@ -9328,7 +9328,7 @@
         <v>1377</v>
       </c>
       <c r="E37">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F37" t="s">
         <v>1558</v>
@@ -9363,7 +9363,7 @@
         <v>1378</v>
       </c>
       <c r="E38">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F38" t="s">
         <v>1558</v>
@@ -9398,7 +9398,7 @@
         <v>1379</v>
       </c>
       <c r="E39">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F39" t="s">
         <v>1558</v>
@@ -9433,7 +9433,7 @@
         <v>1380</v>
       </c>
       <c r="E40">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F40" t="s">
         <v>1558</v>
@@ -9468,7 +9468,7 @@
         <v>1380</v>
       </c>
       <c r="E41">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F41" t="s">
         <v>1558</v>
@@ -9503,7 +9503,7 @@
         <v>1381</v>
       </c>
       <c r="E42">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F42" t="s">
         <v>1558</v>
@@ -9538,7 +9538,7 @@
         <v>1382</v>
       </c>
       <c r="E43">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F43" t="s">
         <v>1558</v>
@@ -9573,7 +9573,7 @@
         <v>1383</v>
       </c>
       <c r="E44">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F44" t="s">
         <v>1558</v>
@@ -9608,7 +9608,7 @@
         <v>1383</v>
       </c>
       <c r="E45">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F45" t="s">
         <v>1558</v>
@@ -9643,7 +9643,7 @@
         <v>1384</v>
       </c>
       <c r="E46">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F46" t="s">
         <v>1558</v>
@@ -9678,7 +9678,7 @@
         <v>1384</v>
       </c>
       <c r="E47">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F47" t="s">
         <v>1558</v>
@@ -9713,7 +9713,7 @@
         <v>1385</v>
       </c>
       <c r="E48">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F48" t="s">
         <v>1558</v>
@@ -9748,7 +9748,7 @@
         <v>1386</v>
       </c>
       <c r="E49">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F49" t="s">
         <v>1558</v>
@@ -9783,7 +9783,7 @@
         <v>1387</v>
       </c>
       <c r="E50">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F50" t="s">
         <v>1558</v>
@@ -9818,7 +9818,7 @@
         <v>1388</v>
       </c>
       <c r="E51">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F51" t="s">
         <v>1558</v>
@@ -9853,7 +9853,7 @@
         <v>1388</v>
       </c>
       <c r="E52">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F52" t="s">
         <v>1558</v>
@@ -9888,7 +9888,7 @@
         <v>1389</v>
       </c>
       <c r="E53">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F53" t="s">
         <v>1558</v>
@@ -9923,7 +9923,7 @@
         <v>1390</v>
       </c>
       <c r="E54">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F54" t="s">
         <v>1558</v>
@@ -9958,7 +9958,7 @@
         <v>1391</v>
       </c>
       <c r="E55">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F55" t="s">
         <v>1558</v>
@@ -9993,7 +9993,7 @@
         <v>1392</v>
       </c>
       <c r="E56">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F56" t="s">
         <v>1558</v>
@@ -10028,7 +10028,7 @@
         <v>1393</v>
       </c>
       <c r="E57">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F57" t="s">
         <v>1558</v>
@@ -10063,7 +10063,7 @@
         <v>1394</v>
       </c>
       <c r="E58">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F58" t="s">
         <v>1558</v>
@@ -10098,7 +10098,7 @@
         <v>1395</v>
       </c>
       <c r="E59">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F59" t="s">
         <v>1558</v>
@@ -10133,7 +10133,7 @@
         <v>1395</v>
       </c>
       <c r="E60">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F60" t="s">
         <v>1558</v>
@@ -10168,7 +10168,7 @@
         <v>1395</v>
       </c>
       <c r="E61">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F61" t="s">
         <v>1558</v>
@@ -10203,7 +10203,7 @@
         <v>1396</v>
       </c>
       <c r="E62">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F62" t="s">
         <v>1558</v>
@@ -10238,7 +10238,7 @@
         <v>1397</v>
       </c>
       <c r="E63">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F63" t="s">
         <v>1558</v>
@@ -10273,7 +10273,7 @@
         <v>1398</v>
       </c>
       <c r="E64">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F64" t="s">
         <v>1558</v>
@@ -10308,7 +10308,7 @@
         <v>1398</v>
       </c>
       <c r="E65">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F65" t="s">
         <v>1558</v>
@@ -10343,7 +10343,7 @@
         <v>1398</v>
       </c>
       <c r="E66">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F66" t="s">
         <v>1558</v>
@@ -10378,7 +10378,7 @@
         <v>1399</v>
       </c>
       <c r="E67">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F67" t="s">
         <v>1558</v>
@@ -10413,7 +10413,7 @@
         <v>1400</v>
       </c>
       <c r="E68">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F68" t="s">
         <v>1558</v>
@@ -10448,7 +10448,7 @@
         <v>1400</v>
       </c>
       <c r="E69">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F69" t="s">
         <v>1558</v>
@@ -10483,7 +10483,7 @@
         <v>1400</v>
       </c>
       <c r="E70">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F70" t="s">
         <v>1558</v>
@@ -10518,7 +10518,7 @@
         <v>1401</v>
       </c>
       <c r="E71">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F71" t="s">
         <v>1558</v>
@@ -10553,7 +10553,7 @@
         <v>1402</v>
       </c>
       <c r="E72">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F72" t="s">
         <v>1558</v>
@@ -10588,7 +10588,7 @@
         <v>1402</v>
       </c>
       <c r="E73">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F73" t="s">
         <v>1558</v>
@@ -10623,7 +10623,7 @@
         <v>1402</v>
       </c>
       <c r="E74">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F74" t="s">
         <v>1559</v>
@@ -10658,7 +10658,7 @@
         <v>1402</v>
       </c>
       <c r="E75">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F75" t="s">
         <v>1558</v>
@@ -10693,7 +10693,7 @@
         <v>1403</v>
       </c>
       <c r="E76">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F76" t="s">
         <v>1558</v>
@@ -10728,7 +10728,7 @@
         <v>1404</v>
       </c>
       <c r="E77">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F77" t="s">
         <v>1558</v>
@@ -10763,7 +10763,7 @@
         <v>1404</v>
       </c>
       <c r="E78">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F78" t="s">
         <v>1558</v>
@@ -10798,7 +10798,7 @@
         <v>1405</v>
       </c>
       <c r="E79">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F79" t="s">
         <v>1558</v>
@@ -10833,7 +10833,7 @@
         <v>1406</v>
       </c>
       <c r="E80">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F80" t="s">
         <v>1558</v>
@@ -10868,7 +10868,7 @@
         <v>1407</v>
       </c>
       <c r="E81">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F81" t="s">
         <v>1558</v>
@@ -10903,7 +10903,7 @@
         <v>1408</v>
       </c>
       <c r="E82">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F82" t="s">
         <v>1558</v>
@@ -10938,7 +10938,7 @@
         <v>1408</v>
       </c>
       <c r="E83">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F83" t="s">
         <v>1558</v>
@@ -10973,7 +10973,7 @@
         <v>1408</v>
       </c>
       <c r="E84">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F84" t="s">
         <v>1558</v>
@@ -11008,7 +11008,7 @@
         <v>1408</v>
       </c>
       <c r="E85">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F85" t="s">
         <v>1558</v>
@@ -11043,7 +11043,7 @@
         <v>1408</v>
       </c>
       <c r="E86">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F86" t="s">
         <v>1558</v>
@@ -11078,7 +11078,7 @@
         <v>1408</v>
       </c>
       <c r="E87">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F87" t="s">
         <v>1558</v>
@@ -11113,7 +11113,7 @@
         <v>1409</v>
       </c>
       <c r="E88">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F88" t="s">
         <v>1558</v>
@@ -11148,7 +11148,7 @@
         <v>1410</v>
       </c>
       <c r="E89">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F89" t="s">
         <v>1558</v>
@@ -11183,7 +11183,7 @@
         <v>1411</v>
       </c>
       <c r="E90">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F90" t="s">
         <v>1558</v>
@@ -11218,7 +11218,7 @@
         <v>1411</v>
       </c>
       <c r="E91">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F91" t="s">
         <v>1558</v>
@@ -11253,7 +11253,7 @@
         <v>1412</v>
       </c>
       <c r="E92">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F92" t="s">
         <v>1560</v>
@@ -11288,7 +11288,7 @@
         <v>1413</v>
       </c>
       <c r="E93">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F93" t="s">
         <v>1558</v>
@@ -11323,7 +11323,7 @@
         <v>1414</v>
       </c>
       <c r="E94">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F94" t="s">
         <v>1558</v>
@@ -11358,7 +11358,7 @@
         <v>1414</v>
       </c>
       <c r="E95">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F95" t="s">
         <v>1558</v>
@@ -11393,7 +11393,7 @@
         <v>1415</v>
       </c>
       <c r="E96">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F96" t="s">
         <v>1558</v>
@@ -11428,7 +11428,7 @@
         <v>1416</v>
       </c>
       <c r="E97">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F97" t="s">
         <v>1558</v>
@@ -11463,7 +11463,7 @@
         <v>1417</v>
       </c>
       <c r="E98">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F98" t="s">
         <v>1558</v>
@@ -11498,7 +11498,7 @@
         <v>1418</v>
       </c>
       <c r="E99">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F99" t="s">
         <v>1558</v>
@@ -11533,7 +11533,7 @@
         <v>1419</v>
       </c>
       <c r="E100">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F100" t="s">
         <v>1558</v>
@@ -11568,7 +11568,7 @@
         <v>1419</v>
       </c>
       <c r="E101">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F101" t="s">
         <v>1558</v>
@@ -11603,7 +11603,7 @@
         <v>1420</v>
       </c>
       <c r="E102">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F102" t="s">
         <v>1558</v>
@@ -11638,7 +11638,7 @@
         <v>1420</v>
       </c>
       <c r="E103">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F103" t="s">
         <v>1558</v>
@@ -11673,7 +11673,7 @@
         <v>1420</v>
       </c>
       <c r="E104">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F104" t="s">
         <v>1558</v>
@@ -11708,7 +11708,7 @@
         <v>1421</v>
       </c>
       <c r="E105">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F105" t="s">
         <v>1558</v>
@@ -11743,7 +11743,7 @@
         <v>1421</v>
       </c>
       <c r="E106">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F106" t="s">
         <v>1558</v>
@@ -11778,7 +11778,7 @@
         <v>1421</v>
       </c>
       <c r="E107">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F107" t="s">
         <v>1558</v>
@@ -11813,7 +11813,7 @@
         <v>1422</v>
       </c>
       <c r="E108">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F108" t="s">
         <v>1558</v>
@@ -11848,7 +11848,7 @@
         <v>1423</v>
       </c>
       <c r="E109">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F109" t="s">
         <v>1558</v>
@@ -11883,7 +11883,7 @@
         <v>1423</v>
       </c>
       <c r="E110">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F110" t="s">
         <v>1558</v>
@@ -11918,7 +11918,7 @@
         <v>1424</v>
       </c>
       <c r="E111">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F111" t="s">
         <v>1558</v>
@@ -11953,7 +11953,7 @@
         <v>1424</v>
       </c>
       <c r="E112">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F112" t="s">
         <v>1558</v>
@@ -11988,7 +11988,7 @@
         <v>1425</v>
       </c>
       <c r="E113">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F113" t="s">
         <v>1558</v>
@@ -12023,7 +12023,7 @@
         <v>1425</v>
       </c>
       <c r="E114">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F114" t="s">
         <v>1558</v>
@@ -12058,7 +12058,7 @@
         <v>1426</v>
       </c>
       <c r="E115">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F115" t="s">
         <v>1558</v>
@@ -12093,7 +12093,7 @@
         <v>1426</v>
       </c>
       <c r="E116">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F116" t="s">
         <v>1558</v>
@@ -12128,7 +12128,7 @@
         <v>1427</v>
       </c>
       <c r="E117">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F117" t="s">
         <v>1558</v>
@@ -12163,7 +12163,7 @@
         <v>1427</v>
       </c>
       <c r="E118">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F118" t="s">
         <v>1558</v>
@@ -12198,7 +12198,7 @@
         <v>1428</v>
       </c>
       <c r="E119">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F119" t="s">
         <v>1558</v>
@@ -12233,7 +12233,7 @@
         <v>1429</v>
       </c>
       <c r="E120">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F120" t="s">
         <v>1558</v>
@@ -12268,7 +12268,7 @@
         <v>1429</v>
       </c>
       <c r="E121">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F121" t="s">
         <v>1558</v>
@@ -12303,7 +12303,7 @@
         <v>1430</v>
       </c>
       <c r="E122">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F122" t="s">
         <v>1558</v>
@@ -12338,7 +12338,7 @@
         <v>1431</v>
       </c>
       <c r="E123">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F123" t="s">
         <v>1558</v>
@@ -12376,7 +12376,7 @@
         <v>1431</v>
       </c>
       <c r="E124">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F124" t="s">
         <v>1558</v>
@@ -12411,7 +12411,7 @@
         <v>1431</v>
       </c>
       <c r="E125">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F125" t="s">
         <v>1558</v>
@@ -12446,7 +12446,7 @@
         <v>1431</v>
       </c>
       <c r="E126">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F126" t="s">
         <v>1558</v>
@@ -12481,7 +12481,7 @@
         <v>1432</v>
       </c>
       <c r="E127">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F127" t="s">
         <v>1559</v>
@@ -12516,7 +12516,7 @@
         <v>1433</v>
       </c>
       <c r="E128">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F128" t="s">
         <v>1558</v>
@@ -12551,7 +12551,7 @@
         <v>1433</v>
       </c>
       <c r="E129">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F129" t="s">
         <v>1558</v>
@@ -12586,7 +12586,7 @@
         <v>1433</v>
       </c>
       <c r="E130">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F130" t="s">
         <v>1558</v>
@@ -12621,7 +12621,7 @@
         <v>1433</v>
       </c>
       <c r="E131">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F131" t="s">
         <v>1558</v>
@@ -12656,7 +12656,7 @@
         <v>1434</v>
       </c>
       <c r="E132">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F132" t="s">
         <v>1558</v>
@@ -12691,7 +12691,7 @@
         <v>1434</v>
       </c>
       <c r="E133">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F133" t="s">
         <v>1558</v>
@@ -12726,7 +12726,7 @@
         <v>1434</v>
       </c>
       <c r="E134">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F134" t="s">
         <v>1558</v>
@@ -12761,7 +12761,7 @@
         <v>1434</v>
       </c>
       <c r="E135">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F135" t="s">
         <v>1558</v>
@@ -12796,7 +12796,7 @@
         <v>1434</v>
       </c>
       <c r="E136">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F136" t="s">
         <v>1558</v>
@@ -12831,7 +12831,7 @@
         <v>1434</v>
       </c>
       <c r="E137">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F137" t="s">
         <v>1558</v>
@@ -12866,7 +12866,7 @@
         <v>1434</v>
       </c>
       <c r="E138">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F138" t="s">
         <v>1558</v>
@@ -12901,7 +12901,7 @@
         <v>1435</v>
       </c>
       <c r="E139">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F139" t="s">
         <v>1558</v>
@@ -12936,7 +12936,7 @@
         <v>1435</v>
       </c>
       <c r="E140">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F140" t="s">
         <v>1558</v>
@@ -12971,7 +12971,7 @@
         <v>1436</v>
       </c>
       <c r="E141">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F141" t="s">
         <v>1558</v>
@@ -13006,7 +13006,7 @@
         <v>1437</v>
       </c>
       <c r="E142">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F142" t="s">
         <v>1558</v>
@@ -13041,7 +13041,7 @@
         <v>1437</v>
       </c>
       <c r="E143">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F143" t="s">
         <v>1558</v>
@@ -13076,7 +13076,7 @@
         <v>1437</v>
       </c>
       <c r="E144">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F144" t="s">
         <v>1558</v>
@@ -13111,7 +13111,7 @@
         <v>1438</v>
       </c>
       <c r="E145">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F145" t="s">
         <v>1558</v>
@@ -13146,7 +13146,7 @@
         <v>1438</v>
       </c>
       <c r="E146">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F146" t="s">
         <v>1558</v>
@@ -13181,7 +13181,7 @@
         <v>1438</v>
       </c>
       <c r="E147">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F147" t="s">
         <v>1558</v>
@@ -13216,7 +13216,7 @@
         <v>1438</v>
       </c>
       <c r="E148">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F148" t="s">
         <v>1558</v>
@@ -13251,7 +13251,7 @@
         <v>1438</v>
       </c>
       <c r="E149">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F149" t="s">
         <v>1558</v>
@@ -13286,7 +13286,7 @@
         <v>1438</v>
       </c>
       <c r="E150">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F150" t="s">
         <v>1558</v>
@@ -13321,7 +13321,7 @@
         <v>1438</v>
       </c>
       <c r="E151">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F151" t="s">
         <v>1558</v>
@@ -13356,7 +13356,7 @@
         <v>1438</v>
       </c>
       <c r="E152">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F152" t="s">
         <v>1558</v>
@@ -13391,7 +13391,7 @@
         <v>1438</v>
       </c>
       <c r="E153">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F153" t="s">
         <v>1558</v>
@@ -13426,7 +13426,7 @@
         <v>1438</v>
       </c>
       <c r="E154">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F154" t="s">
         <v>1558</v>
@@ -13461,7 +13461,7 @@
         <v>1439</v>
       </c>
       <c r="E155">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F155" t="s">
         <v>1558</v>
@@ -13496,7 +13496,7 @@
         <v>1439</v>
       </c>
       <c r="E156">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F156" t="s">
         <v>1558</v>
@@ -13531,7 +13531,7 @@
         <v>1439</v>
       </c>
       <c r="E157">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F157" t="s">
         <v>1558</v>
@@ -13566,7 +13566,7 @@
         <v>1440</v>
       </c>
       <c r="E158">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F158" t="s">
         <v>1558</v>
@@ -13601,7 +13601,7 @@
         <v>1440</v>
       </c>
       <c r="E159">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F159" t="s">
         <v>1559</v>
@@ -13636,7 +13636,7 @@
         <v>1440</v>
       </c>
       <c r="E160">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F160" t="s">
         <v>1558</v>
@@ -13671,7 +13671,7 @@
         <v>1441</v>
       </c>
       <c r="E161">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F161" t="s">
         <v>1558</v>
@@ -13706,7 +13706,7 @@
         <v>1441</v>
       </c>
       <c r="E162">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F162" t="s">
         <v>1558</v>
@@ -13741,7 +13741,7 @@
         <v>1442</v>
       </c>
       <c r="E163">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F163" t="s">
         <v>1558</v>
@@ -13776,7 +13776,7 @@
         <v>1442</v>
       </c>
       <c r="E164">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F164" t="s">
         <v>1558</v>
@@ -13811,7 +13811,7 @@
         <v>1443</v>
       </c>
       <c r="E165">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F165" t="s">
         <v>1558</v>
@@ -13846,7 +13846,7 @@
         <v>1443</v>
       </c>
       <c r="E166">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F166" t="s">
         <v>1558</v>
@@ -13881,7 +13881,7 @@
         <v>1444</v>
       </c>
       <c r="E167">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F167" t="s">
         <v>1558</v>
@@ -13916,7 +13916,7 @@
         <v>1444</v>
       </c>
       <c r="E168">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F168" t="s">
         <v>1558</v>
@@ -13951,7 +13951,7 @@
         <v>1444</v>
       </c>
       <c r="E169">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F169" t="s">
         <v>1558</v>
@@ -13986,7 +13986,7 @@
         <v>1445</v>
       </c>
       <c r="E170">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F170" t="s">
         <v>1558</v>
@@ -14021,7 +14021,7 @@
         <v>1445</v>
       </c>
       <c r="E171">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F171" t="s">
         <v>1558</v>
@@ -14056,7 +14056,7 @@
         <v>1446</v>
       </c>
       <c r="E172">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F172" t="s">
         <v>1558</v>
@@ -14091,7 +14091,7 @@
         <v>1447</v>
       </c>
       <c r="E173">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F173" t="s">
         <v>1558</v>
@@ -14126,7 +14126,7 @@
         <v>1447</v>
       </c>
       <c r="E174">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F174" t="s">
         <v>1558</v>
@@ -14161,7 +14161,7 @@
         <v>1447</v>
       </c>
       <c r="E175">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F175" t="s">
         <v>1558</v>
@@ -14196,7 +14196,7 @@
         <v>1447</v>
       </c>
       <c r="E176">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F176" t="s">
         <v>1558</v>
@@ -14231,7 +14231,7 @@
         <v>1448</v>
       </c>
       <c r="E177">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F177" t="s">
         <v>1558</v>
@@ -14266,7 +14266,7 @@
         <v>1449</v>
       </c>
       <c r="E178">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F178" t="s">
         <v>1558</v>
@@ -14301,7 +14301,7 @@
         <v>1449</v>
       </c>
       <c r="E179">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F179" t="s">
         <v>1558</v>
@@ -14336,7 +14336,7 @@
         <v>1449</v>
       </c>
       <c r="E180">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F180" t="s">
         <v>1558</v>
@@ -14371,7 +14371,7 @@
         <v>1449</v>
       </c>
       <c r="E181">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F181" t="s">
         <v>1558</v>
@@ -14406,7 +14406,7 @@
         <v>1449</v>
       </c>
       <c r="E182">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F182" t="s">
         <v>1558</v>
@@ -14441,7 +14441,7 @@
         <v>1450</v>
       </c>
       <c r="E183">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F183" t="s">
         <v>1558</v>
@@ -14476,7 +14476,7 @@
         <v>1450</v>
       </c>
       <c r="E184">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F184" t="s">
         <v>1558</v>
@@ -14511,7 +14511,7 @@
         <v>1450</v>
       </c>
       <c r="E185">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F185" t="s">
         <v>1558</v>
@@ -14546,7 +14546,7 @@
         <v>1450</v>
       </c>
       <c r="E186">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F186" t="s">
         <v>1558</v>
@@ -14581,7 +14581,7 @@
         <v>1450</v>
       </c>
       <c r="E187">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F187" t="s">
         <v>1558</v>
@@ -14616,7 +14616,7 @@
         <v>1450</v>
       </c>
       <c r="E188">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F188" t="s">
         <v>1558</v>
@@ -14651,7 +14651,7 @@
         <v>1451</v>
       </c>
       <c r="E189">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F189" t="s">
         <v>1558</v>
@@ -14686,7 +14686,7 @@
         <v>1451</v>
       </c>
       <c r="E190">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F190" t="s">
         <v>1558</v>
@@ -14721,7 +14721,7 @@
         <v>1451</v>
       </c>
       <c r="E191">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F191" t="s">
         <v>1558</v>
@@ -14756,7 +14756,7 @@
         <v>1451</v>
       </c>
       <c r="E192">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F192" t="s">
         <v>1558</v>
@@ -14791,7 +14791,7 @@
         <v>1452</v>
       </c>
       <c r="E193">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F193" t="s">
         <v>1558</v>
@@ -14826,7 +14826,7 @@
         <v>1452</v>
       </c>
       <c r="E194">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F194" t="s">
         <v>1558</v>
@@ -14861,7 +14861,7 @@
         <v>1453</v>
       </c>
       <c r="E195">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F195" t="s">
         <v>1558</v>
@@ -14896,7 +14896,7 @@
         <v>1453</v>
       </c>
       <c r="E196">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F196" t="s">
         <v>1558</v>
@@ -14931,7 +14931,7 @@
         <v>1454</v>
       </c>
       <c r="E197">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F197" t="s">
         <v>1558</v>
@@ -14966,7 +14966,7 @@
         <v>1454</v>
       </c>
       <c r="E198">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F198" t="s">
         <v>1558</v>
@@ -15001,7 +15001,7 @@
         <v>1455</v>
       </c>
       <c r="E199">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F199" t="s">
         <v>1558</v>
@@ -15036,7 +15036,7 @@
         <v>1456</v>
       </c>
       <c r="E200">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F200" t="s">
         <v>1558</v>
@@ -15071,7 +15071,7 @@
         <v>1456</v>
       </c>
       <c r="E201">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F201" t="s">
         <v>1558</v>
@@ -15106,7 +15106,7 @@
         <v>1457</v>
       </c>
       <c r="E202">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F202" t="s">
         <v>1558</v>
@@ -15141,7 +15141,7 @@
         <v>1457</v>
       </c>
       <c r="E203">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F203" t="s">
         <v>1558</v>
@@ -15176,7 +15176,7 @@
         <v>1458</v>
       </c>
       <c r="E204">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F204" t="s">
         <v>1558</v>
@@ -15211,7 +15211,7 @@
         <v>1459</v>
       </c>
       <c r="E205">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F205" t="s">
         <v>1558</v>
@@ -15246,7 +15246,7 @@
         <v>1459</v>
       </c>
       <c r="E206">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F206" t="s">
         <v>1558</v>
@@ -15281,7 +15281,7 @@
         <v>1459</v>
       </c>
       <c r="E207">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F207" t="s">
         <v>1558</v>
@@ -15316,7 +15316,7 @@
         <v>1460</v>
       </c>
       <c r="E208">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F208" t="s">
         <v>1558</v>
@@ -15351,7 +15351,7 @@
         <v>1460</v>
       </c>
       <c r="E209">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F209" t="s">
         <v>1558</v>
@@ -15386,7 +15386,7 @@
         <v>1461</v>
       </c>
       <c r="E210">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F210" t="s">
         <v>1558</v>
@@ -15421,7 +15421,7 @@
         <v>1462</v>
       </c>
       <c r="E211">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F211" t="s">
         <v>1558</v>
@@ -15456,7 +15456,7 @@
         <v>1462</v>
       </c>
       <c r="E212">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F212" t="s">
         <v>1558</v>
@@ -15491,7 +15491,7 @@
         <v>1462</v>
       </c>
       <c r="E213">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F213" t="s">
         <v>1558</v>
@@ -15526,7 +15526,7 @@
         <v>1463</v>
       </c>
       <c r="E214">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F214" t="s">
         <v>1558</v>
@@ -15561,7 +15561,7 @@
         <v>1463</v>
       </c>
       <c r="E215">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F215" t="s">
         <v>1558</v>
@@ -15596,7 +15596,7 @@
         <v>1464</v>
       </c>
       <c r="E216">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F216" t="s">
         <v>1558</v>
@@ -15631,7 +15631,7 @@
         <v>1464</v>
       </c>
       <c r="E217">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F217" t="s">
         <v>1558</v>
@@ -15666,7 +15666,7 @@
         <v>1464</v>
       </c>
       <c r="E218">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F218" t="s">
         <v>1560</v>
@@ -15701,7 +15701,7 @@
         <v>1464</v>
       </c>
       <c r="E219">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F219" t="s">
         <v>1558</v>
@@ -15736,7 +15736,7 @@
         <v>1465</v>
       </c>
       <c r="E220">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F220" t="s">
         <v>1558</v>
@@ -15771,7 +15771,7 @@
         <v>1465</v>
       </c>
       <c r="E221">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F221" t="s">
         <v>1558</v>
@@ -15809,7 +15809,7 @@
         <v>1465</v>
       </c>
       <c r="E222">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F222" t="s">
         <v>1558</v>
@@ -15844,7 +15844,7 @@
         <v>1465</v>
       </c>
       <c r="E223">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F223" t="s">
         <v>1558</v>
@@ -15879,7 +15879,7 @@
         <v>1465</v>
       </c>
       <c r="E224">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F224" t="s">
         <v>1558</v>
@@ -15914,7 +15914,7 @@
         <v>1465</v>
       </c>
       <c r="E225">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F225" t="s">
         <v>1558</v>
@@ -15949,7 +15949,7 @@
         <v>1466</v>
       </c>
       <c r="E226">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F226" t="s">
         <v>1558</v>
@@ -15984,7 +15984,7 @@
         <v>1466</v>
       </c>
       <c r="E227">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F227" t="s">
         <v>1558</v>
@@ -16019,7 +16019,7 @@
         <v>1466</v>
       </c>
       <c r="E228">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F228" t="s">
         <v>1558</v>
@@ -16054,7 +16054,7 @@
         <v>1467</v>
       </c>
       <c r="E229">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F229" t="s">
         <v>1558</v>
@@ -16089,7 +16089,7 @@
         <v>1467</v>
       </c>
       <c r="E230">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F230" t="s">
         <v>1558</v>
@@ -16124,7 +16124,7 @@
         <v>1467</v>
       </c>
       <c r="E231">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F231" t="s">
         <v>1558</v>
@@ -16159,7 +16159,7 @@
         <v>1467</v>
       </c>
       <c r="E232">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F232" t="s">
         <v>1558</v>
@@ -16194,7 +16194,7 @@
         <v>1468</v>
       </c>
       <c r="E233">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F233" t="s">
         <v>1558</v>
@@ -16229,7 +16229,7 @@
         <v>1468</v>
       </c>
       <c r="E234">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F234" t="s">
         <v>1558</v>
@@ -16264,7 +16264,7 @@
         <v>1468</v>
       </c>
       <c r="E235">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F235" t="s">
         <v>1558</v>
@@ -16299,7 +16299,7 @@
         <v>1468</v>
       </c>
       <c r="E236">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F236" t="s">
         <v>1558</v>
@@ -16334,7 +16334,7 @@
         <v>1469</v>
       </c>
       <c r="E237">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F237" t="s">
         <v>1558</v>
@@ -16369,7 +16369,7 @@
         <v>1469</v>
       </c>
       <c r="E238">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F238" t="s">
         <v>1558</v>
@@ -16404,7 +16404,7 @@
         <v>1469</v>
       </c>
       <c r="E239">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F239" t="s">
         <v>1558</v>
@@ -16439,7 +16439,7 @@
         <v>1469</v>
       </c>
       <c r="E240">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F240" t="s">
         <v>1558</v>
@@ -16474,7 +16474,7 @@
         <v>1469</v>
       </c>
       <c r="E241">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F241" t="s">
         <v>1558</v>
@@ -16509,7 +16509,7 @@
         <v>1469</v>
       </c>
       <c r="E242">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F242" t="s">
         <v>1558</v>
@@ -16544,7 +16544,7 @@
         <v>1470</v>
       </c>
       <c r="E243">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F243" t="s">
         <v>1558</v>
@@ -16579,7 +16579,7 @@
         <v>1471</v>
       </c>
       <c r="E244">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F244" t="s">
         <v>1558</v>
@@ -16614,7 +16614,7 @@
         <v>1471</v>
       </c>
       <c r="E245">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F245" t="s">
         <v>1561</v>
@@ -16649,7 +16649,7 @@
         <v>1471</v>
       </c>
       <c r="E246">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F246" t="s">
         <v>1558</v>
@@ -16684,7 +16684,7 @@
         <v>1471</v>
       </c>
       <c r="E247">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F247" t="s">
         <v>1558</v>
@@ -16719,7 +16719,7 @@
         <v>1471</v>
       </c>
       <c r="E248">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F248" t="s">
         <v>1558</v>
@@ -16754,7 +16754,7 @@
         <v>1472</v>
       </c>
       <c r="E249">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F249" t="s">
         <v>1558</v>
@@ -16789,7 +16789,7 @@
         <v>1472</v>
       </c>
       <c r="E250">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F250" t="s">
         <v>1558</v>
@@ -16824,7 +16824,7 @@
         <v>1472</v>
       </c>
       <c r="E251">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F251" t="s">
         <v>1558</v>
@@ -16859,7 +16859,7 @@
         <v>1472</v>
       </c>
       <c r="E252">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F252" t="s">
         <v>1558</v>
@@ -16894,7 +16894,7 @@
         <v>1473</v>
       </c>
       <c r="E253">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F253" t="s">
         <v>1558</v>
@@ -16929,7 +16929,7 @@
         <v>1474</v>
       </c>
       <c r="E254">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F254" t="s">
         <v>1558</v>
@@ -16967,7 +16967,7 @@
         <v>1475</v>
       </c>
       <c r="E255">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F255" t="s">
         <v>1558</v>
@@ -17002,7 +17002,7 @@
         <v>1475</v>
       </c>
       <c r="E256">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F256" t="s">
         <v>1558</v>
@@ -17037,7 +17037,7 @@
         <v>1475</v>
       </c>
       <c r="E257">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F257" t="s">
         <v>1558</v>
@@ -17072,7 +17072,7 @@
         <v>1475</v>
       </c>
       <c r="E258">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F258" t="s">
         <v>1558</v>
@@ -17110,7 +17110,7 @@
         <v>1475</v>
       </c>
       <c r="E259">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F259" t="s">
         <v>1558</v>
@@ -17145,7 +17145,7 @@
         <v>1476</v>
       </c>
       <c r="E260">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F260" t="s">
         <v>1558</v>
@@ -17180,7 +17180,7 @@
         <v>1476</v>
       </c>
       <c r="E261">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F261" t="s">
         <v>1558</v>
@@ -17215,7 +17215,7 @@
         <v>1477</v>
       </c>
       <c r="E262">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F262" t="s">
         <v>1558</v>
@@ -17250,7 +17250,7 @@
         <v>1477</v>
       </c>
       <c r="E263">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F263" t="s">
         <v>1558</v>
@@ -17285,7 +17285,7 @@
         <v>1478</v>
       </c>
       <c r="E264">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F264" t="s">
         <v>1558</v>
@@ -17320,7 +17320,7 @@
         <v>1478</v>
       </c>
       <c r="E265">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F265" t="s">
         <v>1558</v>
@@ -17355,7 +17355,7 @@
         <v>1478</v>
       </c>
       <c r="E266">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F266" t="s">
         <v>1558</v>
@@ -17390,7 +17390,7 @@
         <v>1479</v>
       </c>
       <c r="E267">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F267" t="s">
         <v>1558</v>
@@ -17425,7 +17425,7 @@
         <v>1479</v>
       </c>
       <c r="E268">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F268" t="s">
         <v>1558</v>
@@ -17460,7 +17460,7 @@
         <v>1479</v>
       </c>
       <c r="E269">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F269" t="s">
         <v>1558</v>
@@ -17495,7 +17495,7 @@
         <v>1479</v>
       </c>
       <c r="E270">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F270" t="s">
         <v>1558</v>
@@ -17530,7 +17530,7 @@
         <v>1480</v>
       </c>
       <c r="E271">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F271" t="s">
         <v>1558</v>
@@ -17565,7 +17565,7 @@
         <v>1481</v>
       </c>
       <c r="E272">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F272" t="s">
         <v>1558</v>
@@ -17600,7 +17600,7 @@
         <v>1481</v>
       </c>
       <c r="E273">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F273" t="s">
         <v>1558</v>
@@ -17635,7 +17635,7 @@
         <v>1481</v>
       </c>
       <c r="E274">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F274" t="s">
         <v>1558</v>
@@ -17670,7 +17670,7 @@
         <v>1481</v>
       </c>
       <c r="E275">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F275" t="s">
         <v>1558</v>
@@ -17705,7 +17705,7 @@
         <v>1482</v>
       </c>
       <c r="E276">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F276" t="s">
         <v>1558</v>
@@ -17740,7 +17740,7 @@
         <v>1482</v>
       </c>
       <c r="E277">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F277" t="s">
         <v>1558</v>
@@ -17775,7 +17775,7 @@
         <v>1482</v>
       </c>
       <c r="E278">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F278" t="s">
         <v>1558</v>
@@ -17810,7 +17810,7 @@
         <v>1483</v>
       </c>
       <c r="E279">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F279" t="s">
         <v>1558</v>
@@ -17845,7 +17845,7 @@
         <v>1483</v>
       </c>
       <c r="E280">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F280" t="s">
         <v>1558</v>
@@ -17880,7 +17880,7 @@
         <v>1484</v>
       </c>
       <c r="E281">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F281" t="s">
         <v>1558</v>
@@ -17915,7 +17915,7 @@
         <v>1484</v>
       </c>
       <c r="E282">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F282" t="s">
         <v>1558</v>
@@ -17950,7 +17950,7 @@
         <v>1484</v>
       </c>
       <c r="E283">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F283" t="s">
         <v>1558</v>
@@ -17985,7 +17985,7 @@
         <v>1484</v>
       </c>
       <c r="E284">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F284" t="s">
         <v>1558</v>
@@ -18020,7 +18020,7 @@
         <v>1484</v>
       </c>
       <c r="E285">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F285" t="s">
         <v>1558</v>
@@ -18055,7 +18055,7 @@
         <v>1485</v>
       </c>
       <c r="E286">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F286" t="s">
         <v>1558</v>
@@ -18090,7 +18090,7 @@
         <v>1485</v>
       </c>
       <c r="E287">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F287" t="s">
         <v>1558</v>
@@ -18125,7 +18125,7 @@
         <v>1485</v>
       </c>
       <c r="E288">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F288" t="s">
         <v>1558</v>
@@ -18160,7 +18160,7 @@
         <v>1486</v>
       </c>
       <c r="E289">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F289" t="s">
         <v>1558</v>
@@ -18195,7 +18195,7 @@
         <v>1487</v>
       </c>
       <c r="E290">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F290" t="s">
         <v>1558</v>
@@ -18230,7 +18230,7 @@
         <v>1488</v>
       </c>
       <c r="E291">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F291" t="s">
         <v>1558</v>
@@ -18265,7 +18265,7 @@
         <v>1488</v>
       </c>
       <c r="E292">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F292" t="s">
         <v>1558</v>
@@ -18300,7 +18300,7 @@
         <v>1488</v>
       </c>
       <c r="E293">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F293" t="s">
         <v>1558</v>
@@ -18335,7 +18335,7 @@
         <v>1488</v>
       </c>
       <c r="E294">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F294" t="s">
         <v>1558</v>
@@ -18370,7 +18370,7 @@
         <v>1488</v>
       </c>
       <c r="E295">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F295" t="s">
         <v>1558</v>
@@ -18405,7 +18405,7 @@
         <v>1489</v>
       </c>
       <c r="E296">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F296" t="s">
         <v>1558</v>
@@ -18440,7 +18440,7 @@
         <v>1489</v>
       </c>
       <c r="E297">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F297" t="s">
         <v>1558</v>
@@ -18475,7 +18475,7 @@
         <v>1490</v>
       </c>
       <c r="E298">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F298" t="s">
         <v>1558</v>
@@ -18510,7 +18510,7 @@
         <v>1490</v>
       </c>
       <c r="E299">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F299" t="s">
         <v>1558</v>
@@ -18545,7 +18545,7 @@
         <v>1491</v>
       </c>
       <c r="E300">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F300" t="s">
         <v>1558</v>
@@ -18580,7 +18580,7 @@
         <v>1492</v>
       </c>
       <c r="E301">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F301" t="s">
         <v>1558</v>
@@ -18615,7 +18615,7 @@
         <v>1493</v>
       </c>
       <c r="E302">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F302" t="s">
         <v>1558</v>
@@ -18650,7 +18650,7 @@
         <v>1493</v>
       </c>
       <c r="E303">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F303" t="s">
         <v>1558</v>
@@ -18685,7 +18685,7 @@
         <v>1494</v>
       </c>
       <c r="E304">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F304" t="s">
         <v>1558</v>
@@ -18720,7 +18720,7 @@
         <v>1494</v>
       </c>
       <c r="E305">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F305" t="s">
         <v>1558</v>
@@ -18755,7 +18755,7 @@
         <v>1494</v>
       </c>
       <c r="E306">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F306" t="s">
         <v>1558</v>
@@ -18790,7 +18790,7 @@
         <v>1495</v>
       </c>
       <c r="E307">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F307" t="s">
         <v>1558</v>
@@ -18825,7 +18825,7 @@
         <v>1495</v>
       </c>
       <c r="E308">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F308" t="s">
         <v>1558</v>
@@ -18860,7 +18860,7 @@
         <v>1495</v>
       </c>
       <c r="E309">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F309" t="s">
         <v>1558</v>
@@ -18895,7 +18895,7 @@
         <v>1495</v>
       </c>
       <c r="E310">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F310" t="s">
         <v>1558</v>
@@ -18930,7 +18930,7 @@
         <v>1495</v>
       </c>
       <c r="E311">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F311" t="s">
         <v>1558</v>
@@ -18965,7 +18965,7 @@
         <v>1495</v>
       </c>
       <c r="E312">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F312" t="s">
         <v>1558</v>
@@ -19000,7 +19000,7 @@
         <v>1495</v>
       </c>
       <c r="E313">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F313" t="s">
         <v>1558</v>
@@ -19035,7 +19035,7 @@
         <v>1495</v>
       </c>
       <c r="E314">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F314" t="s">
         <v>1558</v>
@@ -19070,7 +19070,7 @@
         <v>1495</v>
       </c>
       <c r="E315">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F315" t="s">
         <v>1558</v>
@@ -19105,7 +19105,7 @@
         <v>1496</v>
       </c>
       <c r="E316">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F316" t="s">
         <v>1558</v>
@@ -19140,7 +19140,7 @@
         <v>1496</v>
       </c>
       <c r="E317">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F317" t="s">
         <v>1558</v>
@@ -19175,7 +19175,7 @@
         <v>1496</v>
       </c>
       <c r="E318">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F318" t="s">
         <v>1558</v>
@@ -19210,7 +19210,7 @@
         <v>1497</v>
       </c>
       <c r="E319">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F319" t="s">
         <v>1558</v>
@@ -19245,7 +19245,7 @@
         <v>1498</v>
       </c>
       <c r="E320">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F320" t="s">
         <v>1558</v>
@@ -19280,7 +19280,7 @@
         <v>1498</v>
       </c>
       <c r="E321">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F321" t="s">
         <v>1558</v>
@@ -19315,7 +19315,7 @@
         <v>1498</v>
       </c>
       <c r="E322">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F322" t="s">
         <v>1558</v>
@@ -19350,7 +19350,7 @@
         <v>1498</v>
       </c>
       <c r="E323">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F323" t="s">
         <v>1558</v>
@@ -19385,7 +19385,7 @@
         <v>1498</v>
       </c>
       <c r="E324">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F324" t="s">
         <v>1562</v>
@@ -19423,7 +19423,7 @@
         <v>1498</v>
       </c>
       <c r="E325">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F325" t="s">
         <v>1558</v>
@@ -19458,7 +19458,7 @@
         <v>1498</v>
       </c>
       <c r="E326">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F326" t="s">
         <v>1558</v>
@@ -19493,7 +19493,7 @@
         <v>1499</v>
       </c>
       <c r="E327">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F327" t="s">
         <v>1558</v>
@@ -19528,7 +19528,7 @@
         <v>1499</v>
       </c>
       <c r="E328">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F328" t="s">
         <v>1558</v>
@@ -19563,7 +19563,7 @@
         <v>1499</v>
       </c>
       <c r="E329">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F329" t="s">
         <v>1558</v>
@@ -19598,7 +19598,7 @@
         <v>1499</v>
       </c>
       <c r="E330">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F330" t="s">
         <v>1558</v>
@@ -19636,7 +19636,7 @@
         <v>1499</v>
       </c>
       <c r="E331">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F331" t="s">
         <v>1558</v>
@@ -19671,7 +19671,7 @@
         <v>1499</v>
       </c>
       <c r="E332">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F332" t="s">
         <v>1558</v>
@@ -19706,7 +19706,7 @@
         <v>1499</v>
       </c>
       <c r="E333">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F333" t="s">
         <v>1558</v>
@@ -19741,7 +19741,7 @@
         <v>1499</v>
       </c>
       <c r="E334">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F334" t="s">
         <v>1558</v>
@@ -19776,7 +19776,7 @@
         <v>1499</v>
       </c>
       <c r="E335">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F335" t="s">
         <v>1558</v>
@@ -19811,7 +19811,7 @@
         <v>1500</v>
       </c>
       <c r="E336">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F336" t="s">
         <v>1559</v>
@@ -19846,7 +19846,7 @@
         <v>1501</v>
       </c>
       <c r="E337">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F337" t="s">
         <v>1562</v>
@@ -19881,7 +19881,7 @@
         <v>1502</v>
       </c>
       <c r="E338">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F338" t="s">
         <v>1558</v>
@@ -19916,7 +19916,7 @@
         <v>1503</v>
       </c>
       <c r="E339">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F339" t="s">
         <v>1558</v>
@@ -19951,7 +19951,7 @@
         <v>1503</v>
       </c>
       <c r="E340">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F340" t="s">
         <v>1558</v>
@@ -19986,7 +19986,7 @@
         <v>1504</v>
       </c>
       <c r="E341">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F341" t="s">
         <v>1558</v>
@@ -20021,7 +20021,7 @@
         <v>1505</v>
       </c>
       <c r="E342">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F342" t="s">
         <v>1561</v>
@@ -20056,7 +20056,7 @@
         <v>1505</v>
       </c>
       <c r="E343">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F343" t="s">
         <v>1558</v>
@@ -20091,7 +20091,7 @@
         <v>1505</v>
       </c>
       <c r="E344">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F344" t="s">
         <v>1558</v>
@@ -20126,7 +20126,7 @@
         <v>1505</v>
       </c>
       <c r="E345">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F345" t="s">
         <v>1558</v>
@@ -20161,7 +20161,7 @@
         <v>1505</v>
       </c>
       <c r="E346">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F346" t="s">
         <v>1558</v>
@@ -20196,7 +20196,7 @@
         <v>1505</v>
       </c>
       <c r="E347">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F347" t="s">
         <v>1558</v>
@@ -20231,7 +20231,7 @@
         <v>1506</v>
       </c>
       <c r="E348">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F348" t="s">
         <v>1558</v>
@@ -20266,7 +20266,7 @@
         <v>1506</v>
       </c>
       <c r="E349">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F349" t="s">
         <v>1558</v>
@@ -20301,7 +20301,7 @@
         <v>1506</v>
       </c>
       <c r="E350">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F350" t="s">
         <v>1558</v>
@@ -20336,7 +20336,7 @@
         <v>1507</v>
       </c>
       <c r="E351">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F351" t="s">
         <v>1558</v>
@@ -20371,7 +20371,7 @@
         <v>1507</v>
       </c>
       <c r="E352">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F352" t="s">
         <v>1558</v>
@@ -20406,7 +20406,7 @@
         <v>1507</v>
       </c>
       <c r="E353">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F353" t="s">
         <v>1558</v>
@@ -20444,7 +20444,7 @@
         <v>1507</v>
       </c>
       <c r="E354">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F354" t="s">
         <v>1558</v>
@@ -20479,7 +20479,7 @@
         <v>1508</v>
       </c>
       <c r="E355">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F355" t="s">
         <v>1558</v>
@@ -20514,7 +20514,7 @@
         <v>1508</v>
       </c>
       <c r="E356">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F356" t="s">
         <v>1558</v>
@@ -20549,7 +20549,7 @@
         <v>1508</v>
       </c>
       <c r="E357">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F357" t="s">
         <v>1558</v>
@@ -20584,7 +20584,7 @@
         <v>1508</v>
       </c>
       <c r="E358">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F358" t="s">
         <v>1558</v>
@@ -20619,7 +20619,7 @@
         <v>1508</v>
       </c>
       <c r="E359">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F359" t="s">
         <v>1558</v>
@@ -20654,7 +20654,7 @@
         <v>1509</v>
       </c>
       <c r="E360">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F360" t="s">
         <v>1558</v>
@@ -20689,7 +20689,7 @@
         <v>1509</v>
       </c>
       <c r="E361">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F361" t="s">
         <v>1558</v>
@@ -20724,7 +20724,7 @@
         <v>1510</v>
       </c>
       <c r="E362">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F362" t="s">
         <v>1558</v>
@@ -20759,7 +20759,7 @@
         <v>1510</v>
       </c>
       <c r="E363">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F363" t="s">
         <v>1558</v>
@@ -20794,7 +20794,7 @@
         <v>1510</v>
       </c>
       <c r="E364">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F364" t="s">
         <v>1558</v>
@@ -20829,7 +20829,7 @@
         <v>1510</v>
       </c>
       <c r="E365">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F365" t="s">
         <v>1558</v>
@@ -20864,7 +20864,7 @@
         <v>1510</v>
       </c>
       <c r="E366">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F366" t="s">
         <v>1558</v>
@@ -20899,7 +20899,7 @@
         <v>1510</v>
       </c>
       <c r="E367">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F367" t="s">
         <v>1558</v>
@@ -20934,7 +20934,7 @@
         <v>1510</v>
       </c>
       <c r="E368">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F368" t="s">
         <v>1558</v>
@@ -20969,7 +20969,7 @@
         <v>1510</v>
       </c>
       <c r="E369">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F369" t="s">
         <v>1558</v>
@@ -21004,7 +21004,7 @@
         <v>1510</v>
       </c>
       <c r="E370">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F370" t="s">
         <v>1558</v>
@@ -21039,7 +21039,7 @@
         <v>1510</v>
       </c>
       <c r="E371">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F371" t="s">
         <v>1558</v>
@@ -21074,7 +21074,7 @@
         <v>1511</v>
       </c>
       <c r="E372">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F372" t="s">
         <v>1558</v>
@@ -21109,7 +21109,7 @@
         <v>1511</v>
       </c>
       <c r="E373">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F373" t="s">
         <v>1558</v>
@@ -21144,7 +21144,7 @@
         <v>1511</v>
       </c>
       <c r="E374">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F374" t="s">
         <v>1559</v>
@@ -21179,7 +21179,7 @@
         <v>1512</v>
       </c>
       <c r="E375">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F375" t="s">
         <v>1558</v>
@@ -21214,7 +21214,7 @@
         <v>1512</v>
       </c>
       <c r="E376">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F376" t="s">
         <v>1558</v>
@@ -21249,7 +21249,7 @@
         <v>1512</v>
       </c>
       <c r="E377">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F377" t="s">
         <v>1558</v>
@@ -21284,7 +21284,7 @@
         <v>1512</v>
       </c>
       <c r="E378">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F378" t="s">
         <v>1558</v>
@@ -21319,7 +21319,7 @@
         <v>1512</v>
       </c>
       <c r="E379">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F379" t="s">
         <v>1558</v>
@@ -21354,7 +21354,7 @@
         <v>1512</v>
       </c>
       <c r="E380">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F380" t="s">
         <v>1558</v>
@@ -21389,7 +21389,7 @@
         <v>1512</v>
       </c>
       <c r="E381">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F381" t="s">
         <v>1561</v>
@@ -21424,7 +21424,7 @@
         <v>1513</v>
       </c>
       <c r="E382">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F382" t="s">
         <v>1558</v>
@@ -21459,7 +21459,7 @@
         <v>1513</v>
       </c>
       <c r="E383">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F383" t="s">
         <v>1558</v>
@@ -21494,7 +21494,7 @@
         <v>1513</v>
       </c>
       <c r="E384">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F384" t="s">
         <v>1558</v>
@@ -21529,7 +21529,7 @@
         <v>1513</v>
       </c>
       <c r="E385">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F385" t="s">
         <v>1558</v>
@@ -21564,7 +21564,7 @@
         <v>1514</v>
       </c>
       <c r="E386">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F386" t="s">
         <v>1561</v>
@@ -21599,7 +21599,7 @@
         <v>1514</v>
       </c>
       <c r="E387">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F387" t="s">
         <v>1558</v>
@@ -21634,7 +21634,7 @@
         <v>1514</v>
       </c>
       <c r="E388">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F388" t="s">
         <v>1558</v>
@@ -21669,7 +21669,7 @@
         <v>1514</v>
       </c>
       <c r="E389">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F389" t="s">
         <v>1558</v>
@@ -21704,7 +21704,7 @@
         <v>1514</v>
       </c>
       <c r="E390">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F390" t="s">
         <v>1558</v>
@@ -21739,7 +21739,7 @@
         <v>1514</v>
       </c>
       <c r="E391">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F391" t="s">
         <v>1558</v>
@@ -21774,7 +21774,7 @@
         <v>1515</v>
       </c>
       <c r="E392">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F392" t="s">
         <v>1558</v>
@@ -21809,7 +21809,7 @@
         <v>1515</v>
       </c>
       <c r="E393">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F393" t="s">
         <v>1558</v>
@@ -21844,7 +21844,7 @@
         <v>1515</v>
       </c>
       <c r="E394">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F394" t="s">
         <v>1558</v>
@@ -21879,7 +21879,7 @@
         <v>1515</v>
       </c>
       <c r="E395">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F395" t="s">
         <v>1558</v>
@@ -21914,7 +21914,7 @@
         <v>1515</v>
       </c>
       <c r="E396">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F396" t="s">
         <v>1560</v>
@@ -21949,7 +21949,7 @@
         <v>1515</v>
       </c>
       <c r="E397">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F397" t="s">
         <v>1558</v>
@@ -21984,7 +21984,7 @@
         <v>1515</v>
       </c>
       <c r="E398">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F398" t="s">
         <v>1558</v>
@@ -22019,7 +22019,7 @@
         <v>1516</v>
       </c>
       <c r="E399">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F399" t="s">
         <v>1558</v>
@@ -22054,7 +22054,7 @@
         <v>1516</v>
       </c>
       <c r="E400">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F400" t="s">
         <v>1558</v>
@@ -22089,7 +22089,7 @@
         <v>1516</v>
       </c>
       <c r="E401">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F401" t="s">
         <v>1558</v>
@@ -22124,7 +22124,7 @@
         <v>1516</v>
       </c>
       <c r="E402">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F402" t="s">
         <v>1558</v>
@@ -22159,7 +22159,7 @@
         <v>1516</v>
       </c>
       <c r="E403">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F403" t="s">
         <v>1558</v>
@@ -22194,7 +22194,7 @@
         <v>1517</v>
       </c>
       <c r="E404">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F404" t="s">
         <v>1558</v>
@@ -22229,7 +22229,7 @@
         <v>1517</v>
       </c>
       <c r="E405">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F405" t="s">
         <v>1558</v>
@@ -22264,7 +22264,7 @@
         <v>1517</v>
       </c>
       <c r="E406">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F406" t="s">
         <v>1558</v>
@@ -22299,7 +22299,7 @@
         <v>1517</v>
       </c>
       <c r="E407">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F407" t="s">
         <v>1558</v>
@@ -22334,7 +22334,7 @@
         <v>1517</v>
       </c>
       <c r="E408">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F408" t="s">
         <v>1558</v>
@@ -22372,7 +22372,7 @@
         <v>1518</v>
       </c>
       <c r="E409">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F409" t="s">
         <v>1558</v>
@@ -22407,7 +22407,7 @@
         <v>1518</v>
       </c>
       <c r="E410">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F410" t="s">
         <v>1558</v>
@@ -22442,7 +22442,7 @@
         <v>1518</v>
       </c>
       <c r="E411">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F411" t="s">
         <v>1558</v>
@@ -22477,7 +22477,7 @@
         <v>1518</v>
       </c>
       <c r="E412">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F412" t="s">
         <v>1558</v>
@@ -22512,7 +22512,7 @@
         <v>1518</v>
       </c>
       <c r="E413">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F413" t="s">
         <v>1558</v>
@@ -22547,7 +22547,7 @@
         <v>1518</v>
       </c>
       <c r="E414">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F414" t="s">
         <v>1558</v>
@@ -22582,7 +22582,7 @@
         <v>1519</v>
       </c>
       <c r="E415">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F415" t="s">
         <v>1559</v>
@@ -22617,7 +22617,7 @@
         <v>1519</v>
       </c>
       <c r="E416">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F416" t="s">
         <v>1558</v>
@@ -22652,7 +22652,7 @@
         <v>1520</v>
       </c>
       <c r="E417">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F417" t="s">
         <v>1558</v>
@@ -22687,7 +22687,7 @@
         <v>1521</v>
       </c>
       <c r="E418">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F418" t="s">
         <v>1558</v>
@@ -22722,7 +22722,7 @@
         <v>1521</v>
       </c>
       <c r="E419">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F419" t="s">
         <v>1558</v>
@@ -22757,7 +22757,7 @@
         <v>1521</v>
       </c>
       <c r="E420">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F420" t="s">
         <v>1560</v>
@@ -22795,7 +22795,7 @@
         <v>1521</v>
       </c>
       <c r="E421">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F421" t="s">
         <v>1558</v>
@@ -22830,7 +22830,7 @@
         <v>1522</v>
       </c>
       <c r="E422">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F422" t="s">
         <v>1558</v>
@@ -22865,7 +22865,7 @@
         <v>1522</v>
       </c>
       <c r="E423">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F423" t="s">
         <v>1558</v>
@@ -22900,7 +22900,7 @@
         <v>1522</v>
       </c>
       <c r="E424">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F424" t="s">
         <v>1558</v>
@@ -22935,7 +22935,7 @@
         <v>1522</v>
       </c>
       <c r="E425">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F425" t="s">
         <v>1558</v>
@@ -22970,7 +22970,7 @@
         <v>1523</v>
       </c>
       <c r="E426">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F426" t="s">
         <v>1558</v>
@@ -23005,7 +23005,7 @@
         <v>1523</v>
       </c>
       <c r="E427">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F427" t="s">
         <v>1558</v>
@@ -23040,7 +23040,7 @@
         <v>1523</v>
       </c>
       <c r="E428">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F428" t="s">
         <v>1558</v>
@@ -23075,7 +23075,7 @@
         <v>1523</v>
       </c>
       <c r="E429">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F429" t="s">
         <v>1558</v>
@@ -23110,7 +23110,7 @@
         <v>1523</v>
       </c>
       <c r="E430">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F430" t="s">
         <v>1558</v>
@@ -23145,7 +23145,7 @@
         <v>1523</v>
       </c>
       <c r="E431">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F431" t="s">
         <v>1558</v>
@@ -23180,7 +23180,7 @@
         <v>1523</v>
       </c>
       <c r="E432">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F432" t="s">
         <v>1558</v>
@@ -23215,7 +23215,7 @@
         <v>1523</v>
       </c>
       <c r="E433">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F433" t="s">
         <v>1558</v>
@@ -23250,7 +23250,7 @@
         <v>1524</v>
       </c>
       <c r="E434">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F434" t="s">
         <v>1558</v>
@@ -23285,7 +23285,7 @@
         <v>1525</v>
       </c>
       <c r="E435">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F435" t="s">
         <v>1558</v>
@@ -23320,7 +23320,7 @@
         <v>1525</v>
       </c>
       <c r="E436">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F436" t="s">
         <v>1558</v>
@@ -23355,7 +23355,7 @@
         <v>1525</v>
       </c>
       <c r="E437">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F437" t="s">
         <v>1558</v>
@@ -23390,7 +23390,7 @@
         <v>1525</v>
       </c>
       <c r="E438">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F438" t="s">
         <v>1562</v>
@@ -23428,7 +23428,7 @@
         <v>1525</v>
       </c>
       <c r="E439">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F439" t="s">
         <v>1558</v>
@@ -23463,7 +23463,7 @@
         <v>1525</v>
       </c>
       <c r="E440">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F440" t="s">
         <v>1562</v>
@@ -23498,7 +23498,7 @@
         <v>1526</v>
       </c>
       <c r="E441">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F441" t="s">
         <v>1558</v>
@@ -23533,7 +23533,7 @@
         <v>1527</v>
       </c>
       <c r="E442">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F442" t="s">
         <v>1558</v>
@@ -23568,7 +23568,7 @@
         <v>1527</v>
       </c>
       <c r="E443">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F443" t="s">
         <v>1558</v>
@@ -23603,7 +23603,7 @@
         <v>1527</v>
       </c>
       <c r="E444">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F444" t="s">
         <v>1558</v>
@@ -23638,7 +23638,7 @@
         <v>1527</v>
       </c>
       <c r="E445">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F445" t="s">
         <v>1558</v>
@@ -23673,7 +23673,7 @@
         <v>1528</v>
       </c>
       <c r="E446">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F446" t="s">
         <v>1558</v>
@@ -23708,7 +23708,7 @@
         <v>1528</v>
       </c>
       <c r="E447">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F447" t="s">
         <v>1562</v>
@@ -23743,7 +23743,7 @@
         <v>1528</v>
       </c>
       <c r="E448">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F448" t="s">
         <v>1558</v>
@@ -23778,7 +23778,7 @@
         <v>1528</v>
       </c>
       <c r="E449">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F449" t="s">
         <v>1558</v>
@@ -23813,7 +23813,7 @@
         <v>1528</v>
       </c>
       <c r="E450">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F450" t="s">
         <v>1558</v>
@@ -23848,7 +23848,7 @@
         <v>1529</v>
       </c>
       <c r="E451">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F451" t="s">
         <v>1558</v>
@@ -23883,7 +23883,7 @@
         <v>1529</v>
       </c>
       <c r="E452">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F452" t="s">
         <v>1558</v>
@@ -23918,7 +23918,7 @@
         <v>1529</v>
       </c>
       <c r="E453">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F453" t="s">
         <v>1558</v>
@@ -23953,7 +23953,7 @@
         <v>1530</v>
       </c>
       <c r="E454">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F454" t="s">
         <v>1558</v>
@@ -23988,7 +23988,7 @@
         <v>1530</v>
       </c>
       <c r="E455">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F455" t="s">
         <v>1558</v>
@@ -24023,7 +24023,7 @@
         <v>1530</v>
       </c>
       <c r="E456">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F456" t="s">
         <v>1558</v>
@@ -24058,7 +24058,7 @@
         <v>1530</v>
       </c>
       <c r="E457">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F457" t="s">
         <v>1558</v>
@@ -24093,7 +24093,7 @@
         <v>1530</v>
       </c>
       <c r="E458">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F458" t="s">
         <v>1558</v>
@@ -24128,7 +24128,7 @@
         <v>1530</v>
       </c>
       <c r="E459">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F459" t="s">
         <v>1558</v>
@@ -24163,7 +24163,7 @@
         <v>1531</v>
       </c>
       <c r="E460">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F460" t="s">
         <v>1558</v>
@@ -24198,7 +24198,7 @@
         <v>1531</v>
       </c>
       <c r="E461">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F461" t="s">
         <v>1558</v>
@@ -24233,7 +24233,7 @@
         <v>1531</v>
       </c>
       <c r="E462">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F462" t="s">
         <v>1558</v>
@@ -24268,7 +24268,7 @@
         <v>1531</v>
       </c>
       <c r="E463">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F463" t="s">
         <v>1558</v>
@@ -24303,7 +24303,7 @@
         <v>1531</v>
       </c>
       <c r="E464">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F464" t="s">
         <v>1558</v>
@@ -24338,7 +24338,7 @@
         <v>1531</v>
       </c>
       <c r="E465">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F465" t="s">
         <v>1558</v>
@@ -24373,7 +24373,7 @@
         <v>1531</v>
       </c>
       <c r="E466">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F466" t="s">
         <v>1558</v>
@@ -24408,7 +24408,7 @@
         <v>1531</v>
       </c>
       <c r="E467">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F467" t="s">
         <v>1558</v>
@@ -24443,7 +24443,7 @@
         <v>1531</v>
       </c>
       <c r="E468">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F468" t="s">
         <v>1558</v>
@@ -24478,7 +24478,7 @@
         <v>1531</v>
       </c>
       <c r="E469">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F469" t="s">
         <v>1558</v>
@@ -24513,7 +24513,7 @@
         <v>1531</v>
       </c>
       <c r="E470">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F470" t="s">
         <v>1558</v>
@@ -24548,7 +24548,7 @@
         <v>1531</v>
       </c>
       <c r="E471">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F471" t="s">
         <v>1558</v>
@@ -24583,7 +24583,7 @@
         <v>1531</v>
       </c>
       <c r="E472">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F472" t="s">
         <v>1558</v>
@@ -24618,7 +24618,7 @@
         <v>1531</v>
       </c>
       <c r="E473">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F473" t="s">
         <v>1558</v>
@@ -24653,7 +24653,7 @@
         <v>1531</v>
       </c>
       <c r="E474">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F474" t="s">
         <v>1558</v>
@@ -24688,7 +24688,7 @@
         <v>1531</v>
       </c>
       <c r="E475">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F475" t="s">
         <v>1558</v>
@@ -24723,7 +24723,7 @@
         <v>1531</v>
       </c>
       <c r="E476">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F476" t="s">
         <v>1558</v>
@@ -24758,7 +24758,7 @@
         <v>1531</v>
       </c>
       <c r="E477">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F477" t="s">
         <v>1558</v>
@@ -24793,7 +24793,7 @@
         <v>1531</v>
       </c>
       <c r="E478">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F478" t="s">
         <v>1558</v>
@@ -24828,7 +24828,7 @@
         <v>1531</v>
       </c>
       <c r="E479">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F479" t="s">
         <v>1558</v>
@@ -24863,7 +24863,7 @@
         <v>1531</v>
       </c>
       <c r="E480">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F480" t="s">
         <v>1558</v>
@@ -24898,7 +24898,7 @@
         <v>1531</v>
       </c>
       <c r="E481">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F481" t="s">
         <v>1558</v>
@@ -24933,7 +24933,7 @@
         <v>1531</v>
       </c>
       <c r="E482">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F482" t="s">
         <v>1558</v>
@@ -24968,7 +24968,7 @@
         <v>1531</v>
       </c>
       <c r="E483">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F483" t="s">
         <v>1558</v>
@@ -25003,7 +25003,7 @@
         <v>1531</v>
       </c>
       <c r="E484">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F484" t="s">
         <v>1558</v>
@@ -25038,7 +25038,7 @@
         <v>1532</v>
       </c>
       <c r="E485">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F485" t="s">
         <v>1558</v>
@@ -25073,7 +25073,7 @@
         <v>1532</v>
       </c>
       <c r="E486">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F486" t="s">
         <v>1558</v>
@@ -25108,7 +25108,7 @@
         <v>1532</v>
       </c>
       <c r="E487">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F487" t="s">
         <v>1558</v>
@@ -25143,7 +25143,7 @@
         <v>1532</v>
       </c>
       <c r="E488">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F488" t="s">
         <v>1558</v>
@@ -25178,7 +25178,7 @@
         <v>1532</v>
       </c>
       <c r="E489">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F489" t="s">
         <v>1558</v>
@@ -25213,7 +25213,7 @@
         <v>1532</v>
       </c>
       <c r="E490">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F490" t="s">
         <v>1558</v>
@@ -25248,7 +25248,7 @@
         <v>1532</v>
       </c>
       <c r="E491">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F491" t="s">
         <v>1562</v>
@@ -25283,7 +25283,7 @@
         <v>1532</v>
       </c>
       <c r="E492">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F492" t="s">
         <v>1558</v>
@@ -25318,7 +25318,7 @@
         <v>1533</v>
       </c>
       <c r="E493">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F493" t="s">
         <v>1558</v>
@@ -25353,7 +25353,7 @@
         <v>1534</v>
       </c>
       <c r="E494">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F494" t="s">
         <v>1560</v>
@@ -25391,7 +25391,7 @@
         <v>1534</v>
       </c>
       <c r="E495">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F495" t="s">
         <v>1558</v>
@@ -25426,7 +25426,7 @@
         <v>1534</v>
       </c>
       <c r="E496">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F496" t="s">
         <v>1558</v>
@@ -25461,7 +25461,7 @@
         <v>1534</v>
       </c>
       <c r="E497">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F497" t="s">
         <v>1558</v>
@@ -25496,7 +25496,7 @@
         <v>1534</v>
       </c>
       <c r="E498">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F498" t="s">
         <v>1558</v>
@@ -25531,7 +25531,7 @@
         <v>1534</v>
       </c>
       <c r="E499">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F499" t="s">
         <v>1558</v>
@@ -25566,7 +25566,7 @@
         <v>1535</v>
       </c>
       <c r="E500">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F500" t="s">
         <v>1558</v>
@@ -25604,7 +25604,7 @@
         <v>1535</v>
       </c>
       <c r="E501">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F501" t="s">
         <v>1562</v>
@@ -25639,7 +25639,7 @@
         <v>1535</v>
       </c>
       <c r="E502">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F502" t="s">
         <v>1560</v>
@@ -25674,7 +25674,7 @@
         <v>1535</v>
       </c>
       <c r="E503">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F503" t="s">
         <v>1558</v>
@@ -25709,7 +25709,7 @@
         <v>1535</v>
       </c>
       <c r="E504">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F504" t="s">
         <v>1558</v>
@@ -25744,7 +25744,7 @@
         <v>1535</v>
       </c>
       <c r="E505">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F505" t="s">
         <v>1558</v>
@@ -25779,7 +25779,7 @@
         <v>1535</v>
       </c>
       <c r="E506">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F506" t="s">
         <v>1558</v>
@@ -25814,7 +25814,7 @@
         <v>1535</v>
       </c>
       <c r="E507">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F507" t="s">
         <v>1558</v>
@@ -25849,7 +25849,7 @@
         <v>1535</v>
       </c>
       <c r="E508">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F508" t="s">
         <v>1558</v>
@@ -25884,7 +25884,7 @@
         <v>1536</v>
       </c>
       <c r="E509">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F509" t="s">
         <v>1562</v>
@@ -25922,7 +25922,7 @@
         <v>1536</v>
       </c>
       <c r="E510">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F510" t="s">
         <v>1558</v>
@@ -25957,7 +25957,7 @@
         <v>1537</v>
       </c>
       <c r="E511">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F511" t="s">
         <v>1558</v>
@@ -25992,7 +25992,7 @@
         <v>1537</v>
       </c>
       <c r="E512">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F512" t="s">
         <v>1558</v>
@@ -26027,7 +26027,7 @@
         <v>1537</v>
       </c>
       <c r="E513">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F513" t="s">
         <v>1558</v>
@@ -26062,7 +26062,7 @@
         <v>1537</v>
       </c>
       <c r="E514">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F514" t="s">
         <v>1558</v>
@@ -26097,7 +26097,7 @@
         <v>1537</v>
       </c>
       <c r="E515">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F515" t="s">
         <v>1558</v>
@@ -26132,7 +26132,7 @@
         <v>1537</v>
       </c>
       <c r="E516">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F516" t="s">
         <v>1558</v>
@@ -26167,7 +26167,7 @@
         <v>1537</v>
       </c>
       <c r="E517">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F517" t="s">
         <v>1558</v>
@@ -26202,7 +26202,7 @@
         <v>1538</v>
       </c>
       <c r="E518">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F518" t="s">
         <v>1558</v>
@@ -26237,7 +26237,7 @@
         <v>1538</v>
       </c>
       <c r="E519">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F519" t="s">
         <v>1558</v>
@@ -26272,7 +26272,7 @@
         <v>1538</v>
       </c>
       <c r="E520">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F520" t="s">
         <v>1558</v>
@@ -26307,7 +26307,7 @@
         <v>1538</v>
       </c>
       <c r="E521">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F521" t="s">
         <v>1558</v>
@@ -26342,7 +26342,7 @@
         <v>1538</v>
       </c>
       <c r="E522">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F522" t="s">
         <v>1558</v>
@@ -26377,7 +26377,7 @@
         <v>1538</v>
       </c>
       <c r="E523">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F523" t="s">
         <v>1558</v>
@@ -26412,7 +26412,7 @@
         <v>1538</v>
       </c>
       <c r="E524">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F524" t="s">
         <v>1560</v>
@@ -26447,7 +26447,7 @@
         <v>1538</v>
       </c>
       <c r="E525">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F525" t="s">
         <v>1558</v>
@@ -26482,7 +26482,7 @@
         <v>1538</v>
       </c>
       <c r="E526">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F526" t="s">
         <v>1562</v>
@@ -26517,7 +26517,7 @@
         <v>1538</v>
       </c>
       <c r="E527">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F527" t="s">
         <v>1558</v>
@@ -26552,7 +26552,7 @@
         <v>1539</v>
       </c>
       <c r="E528">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F528" t="s">
         <v>1558</v>
@@ -26587,7 +26587,7 @@
         <v>1539</v>
       </c>
       <c r="E529">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F529" t="s">
         <v>1558</v>
@@ -26622,7 +26622,7 @@
         <v>1539</v>
       </c>
       <c r="E530">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F530" t="s">
         <v>1558</v>
@@ -26657,7 +26657,7 @@
         <v>1539</v>
       </c>
       <c r="E531">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F531" t="s">
         <v>1558</v>
@@ -26692,7 +26692,7 @@
         <v>1539</v>
       </c>
       <c r="E532">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F532" t="s">
         <v>1558</v>
@@ -26727,7 +26727,7 @@
         <v>1539</v>
       </c>
       <c r="E533">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F533" t="s">
         <v>1558</v>
@@ -26762,7 +26762,7 @@
         <v>1539</v>
       </c>
       <c r="E534">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F534" t="s">
         <v>1558</v>
@@ -26797,7 +26797,7 @@
         <v>1539</v>
       </c>
       <c r="E535">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F535" t="s">
         <v>1558</v>
@@ -26835,7 +26835,7 @@
         <v>1539</v>
       </c>
       <c r="E536">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F536" t="s">
         <v>1560</v>
@@ -26873,7 +26873,7 @@
         <v>1539</v>
       </c>
       <c r="E537">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F537" t="s">
         <v>1560</v>
@@ -26908,7 +26908,7 @@
         <v>1539</v>
       </c>
       <c r="E538">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F538" t="s">
         <v>1558</v>
@@ -26943,7 +26943,7 @@
         <v>1540</v>
       </c>
       <c r="E539">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F539" t="s">
         <v>1558</v>
@@ -26978,7 +26978,7 @@
         <v>1540</v>
       </c>
       <c r="E540">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F540" t="s">
         <v>1558</v>
@@ -27013,7 +27013,7 @@
         <v>1540</v>
       </c>
       <c r="E541">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F541" t="s">
         <v>1558</v>
@@ -27048,7 +27048,7 @@
         <v>1540</v>
       </c>
       <c r="E542">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F542" t="s">
         <v>1558</v>
@@ -27083,7 +27083,7 @@
         <v>1540</v>
       </c>
       <c r="E543">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F543" t="s">
         <v>1558</v>
@@ -27118,7 +27118,7 @@
         <v>1540</v>
       </c>
       <c r="E544">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F544" t="s">
         <v>1558</v>
@@ -27153,7 +27153,7 @@
         <v>1540</v>
       </c>
       <c r="E545">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F545" t="s">
         <v>1558</v>
@@ -27188,7 +27188,7 @@
         <v>1541</v>
       </c>
       <c r="E546">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F546" t="s">
         <v>1558</v>
@@ -27223,7 +27223,7 @@
         <v>1542</v>
       </c>
       <c r="E547">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F547" t="s">
         <v>1558</v>
@@ -27261,7 +27261,7 @@
         <v>1542</v>
       </c>
       <c r="E548">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F548" t="s">
         <v>1558</v>
@@ -27296,7 +27296,7 @@
         <v>1542</v>
       </c>
       <c r="E549">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F549" t="s">
         <v>1558</v>
@@ -27331,7 +27331,7 @@
         <v>1542</v>
       </c>
       <c r="E550">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F550" t="s">
         <v>1560</v>
@@ -27369,7 +27369,7 @@
         <v>1542</v>
       </c>
       <c r="E551">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F551" t="s">
         <v>1560</v>
@@ -27407,7 +27407,7 @@
         <v>1542</v>
       </c>
       <c r="E552">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F552" t="s">
         <v>1558</v>
@@ -27442,7 +27442,7 @@
         <v>1542</v>
       </c>
       <c r="E553">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F553" t="s">
         <v>1558</v>
@@ -27477,7 +27477,7 @@
         <v>1542</v>
       </c>
       <c r="E554">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F554" t="s">
         <v>1558</v>
@@ -27512,7 +27512,7 @@
         <v>1543</v>
       </c>
       <c r="E555">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F555" t="s">
         <v>1558</v>
@@ -27547,7 +27547,7 @@
         <v>1543</v>
       </c>
       <c r="E556">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F556" t="s">
         <v>1558</v>
@@ -27582,7 +27582,7 @@
         <v>1543</v>
       </c>
       <c r="E557">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F557" t="s">
         <v>1558</v>
@@ -27617,7 +27617,7 @@
         <v>1543</v>
       </c>
       <c r="E558">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F558" t="s">
         <v>1558</v>
@@ -27652,7 +27652,7 @@
         <v>1543</v>
       </c>
       <c r="E559">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F559" t="s">
         <v>1558</v>
@@ -27687,7 +27687,7 @@
         <v>1543</v>
       </c>
       <c r="E560">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F560" t="s">
         <v>1558</v>
@@ -27722,7 +27722,7 @@
         <v>1543</v>
       </c>
       <c r="E561">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F561" t="s">
         <v>1558</v>
@@ -27757,7 +27757,7 @@
         <v>1543</v>
       </c>
       <c r="E562">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F562" t="s">
         <v>1558</v>
@@ -27792,7 +27792,7 @@
         <v>1543</v>
       </c>
       <c r="E563">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F563" t="s">
         <v>1558</v>
@@ -27830,7 +27830,7 @@
         <v>1543</v>
       </c>
       <c r="E564">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F564" t="s">
         <v>1558</v>
@@ -27865,7 +27865,7 @@
         <v>1544</v>
       </c>
       <c r="E565">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F565" t="s">
         <v>1558</v>
@@ -27900,7 +27900,7 @@
         <v>1544</v>
       </c>
       <c r="E566">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F566" t="s">
         <v>1560</v>
@@ -27938,7 +27938,7 @@
         <v>1544</v>
       </c>
       <c r="E567">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F567" t="s">
         <v>1558</v>
@@ -27973,7 +27973,7 @@
         <v>1544</v>
       </c>
       <c r="E568">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F568" t="s">
         <v>1558</v>
@@ -28008,7 +28008,7 @@
         <v>1545</v>
       </c>
       <c r="E569">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F569" t="s">
         <v>1558</v>
@@ -28043,7 +28043,7 @@
         <v>1545</v>
       </c>
       <c r="E570">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F570" t="s">
         <v>1560</v>
@@ -28078,7 +28078,7 @@
         <v>1545</v>
       </c>
       <c r="E571">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F571" t="s">
         <v>1558</v>
@@ -28113,7 +28113,7 @@
         <v>1545</v>
       </c>
       <c r="E572">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F572" t="s">
         <v>1558</v>
@@ -28148,7 +28148,7 @@
         <v>1545</v>
       </c>
       <c r="E573">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F573" t="s">
         <v>1560</v>
@@ -28186,7 +28186,7 @@
         <v>1545</v>
       </c>
       <c r="E574">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F574" t="s">
         <v>1558</v>
@@ -28221,7 +28221,7 @@
         <v>1545</v>
       </c>
       <c r="E575">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F575" t="s">
         <v>1558</v>
@@ -28256,7 +28256,7 @@
         <v>1545</v>
       </c>
       <c r="E576">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F576" t="s">
         <v>1558</v>
@@ -28291,7 +28291,7 @@
         <v>1545</v>
       </c>
       <c r="E577">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F577" t="s">
         <v>1558</v>
@@ -28326,7 +28326,7 @@
         <v>1545</v>
       </c>
       <c r="E578">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F578" t="s">
         <v>1558</v>
@@ -28361,7 +28361,7 @@
         <v>1545</v>
       </c>
       <c r="E579">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F579" t="s">
         <v>1558</v>
@@ -28396,7 +28396,7 @@
         <v>1545</v>
       </c>
       <c r="E580">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F580" t="s">
         <v>1558</v>
@@ -28431,7 +28431,7 @@
         <v>1546</v>
       </c>
       <c r="E581">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F581" t="s">
         <v>1562</v>
@@ -28466,7 +28466,7 @@
         <v>1546</v>
       </c>
       <c r="E582">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F582" t="s">
         <v>1558</v>
@@ -28501,7 +28501,7 @@
         <v>1546</v>
       </c>
       <c r="E583">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F583" t="s">
         <v>1558</v>
@@ -28536,7 +28536,7 @@
         <v>1546</v>
       </c>
       <c r="E584">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F584" t="s">
         <v>1558</v>
@@ -28571,7 +28571,7 @@
         <v>1546</v>
       </c>
       <c r="E585">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F585" t="s">
         <v>1558</v>
@@ -28606,7 +28606,7 @@
         <v>1546</v>
       </c>
       <c r="E586">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F586" t="s">
         <v>1558</v>
@@ -28641,7 +28641,7 @@
         <v>1547</v>
       </c>
       <c r="E587">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F587" t="s">
         <v>1558</v>
@@ -28676,7 +28676,7 @@
         <v>1547</v>
       </c>
       <c r="E588">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F588" t="s">
         <v>1558</v>
@@ -28711,7 +28711,7 @@
         <v>1547</v>
       </c>
       <c r="E589">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F589" t="s">
         <v>1558</v>
@@ -28746,7 +28746,7 @@
         <v>1547</v>
       </c>
       <c r="E590">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F590" t="s">
         <v>1560</v>
@@ -28784,7 +28784,7 @@
         <v>1548</v>
       </c>
       <c r="E591">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F591" t="s">
         <v>1558</v>
@@ -28819,7 +28819,7 @@
         <v>1548</v>
       </c>
       <c r="E592">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F592" t="s">
         <v>1562</v>
@@ -28857,7 +28857,7 @@
         <v>1548</v>
       </c>
       <c r="E593">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F593" t="s">
         <v>1558</v>
@@ -28892,7 +28892,7 @@
         <v>1548</v>
       </c>
       <c r="E594">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F594" t="s">
         <v>1558</v>
@@ -28927,7 +28927,7 @@
         <v>1549</v>
       </c>
       <c r="E595">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F595" t="s">
         <v>1558</v>
@@ -28962,7 +28962,7 @@
         <v>1549</v>
       </c>
       <c r="E596">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F596" t="s">
         <v>1558</v>
@@ -28997,7 +28997,7 @@
         <v>1549</v>
       </c>
       <c r="E597">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F597" t="s">
         <v>1558</v>
@@ -29032,7 +29032,7 @@
         <v>1549</v>
       </c>
       <c r="E598">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F598" t="s">
         <v>1560</v>
@@ -29067,7 +29067,7 @@
         <v>1549</v>
       </c>
       <c r="E599">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F599" t="s">
         <v>1558</v>
@@ -29102,7 +29102,7 @@
         <v>1549</v>
       </c>
       <c r="E600">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F600" t="s">
         <v>1558</v>
@@ -29137,7 +29137,7 @@
         <v>1549</v>
       </c>
       <c r="E601">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F601" t="s">
         <v>1558</v>
@@ -29172,7 +29172,7 @@
         <v>1549</v>
       </c>
       <c r="E602">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F602" t="s">
         <v>1560</v>
@@ -29210,7 +29210,7 @@
         <v>1549</v>
       </c>
       <c r="E603">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F603" t="s">
         <v>1558</v>
@@ -29245,7 +29245,7 @@
         <v>1549</v>
       </c>
       <c r="E604">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F604" t="s">
         <v>1558</v>
@@ -29280,7 +29280,7 @@
         <v>1549</v>
       </c>
       <c r="E605">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F605" t="s">
         <v>1558</v>
@@ -29315,7 +29315,7 @@
         <v>1550</v>
       </c>
       <c r="E606">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F606" t="s">
         <v>1562</v>
@@ -29350,7 +29350,7 @@
         <v>1550</v>
       </c>
       <c r="E607">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F607" t="s">
         <v>1558</v>
@@ -29388,7 +29388,7 @@
         <v>1550</v>
       </c>
       <c r="E608">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F608" t="s">
         <v>1558</v>
@@ -29423,7 +29423,7 @@
         <v>1550</v>
       </c>
       <c r="E609">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F609" t="s">
         <v>1560</v>
@@ -29458,7 +29458,7 @@
         <v>1550</v>
       </c>
       <c r="E610">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F610" t="s">
         <v>1558</v>
@@ -29493,7 +29493,7 @@
         <v>1551</v>
       </c>
       <c r="E611">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F611" t="s">
         <v>1560</v>
@@ -29531,7 +29531,7 @@
         <v>1551</v>
       </c>
       <c r="E612">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F612" t="s">
         <v>1560</v>
@@ -29569,7 +29569,7 @@
         <v>1551</v>
       </c>
       <c r="E613">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F613" t="s">
         <v>1558</v>
@@ -29604,7 +29604,7 @@
         <v>1551</v>
       </c>
       <c r="E614">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F614" t="s">
         <v>1558</v>
@@ -29639,7 +29639,7 @@
         <v>1551</v>
       </c>
       <c r="E615">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F615" t="s">
         <v>1558</v>
@@ -29674,7 +29674,7 @@
         <v>1552</v>
       </c>
       <c r="E616">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F616" t="s">
         <v>1558</v>
@@ -29709,7 +29709,7 @@
         <v>1553</v>
       </c>
       <c r="E617">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F617" t="s">
         <v>1558</v>
@@ -29744,7 +29744,7 @@
         <v>1553</v>
       </c>
       <c r="E618">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F618" t="s">
         <v>1558</v>
@@ -29779,7 +29779,7 @@
         <v>1553</v>
       </c>
       <c r="E619">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F619" t="s">
         <v>1558</v>
@@ -29814,7 +29814,7 @@
         <v>1553</v>
       </c>
       <c r="E620">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F620" t="s">
         <v>1558</v>
@@ -29849,7 +29849,7 @@
         <v>1553</v>
       </c>
       <c r="E621">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F621" t="s">
         <v>1558</v>
@@ -29884,7 +29884,7 @@
         <v>1553</v>
       </c>
       <c r="E622">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F622" t="s">
         <v>1558</v>
@@ -29919,7 +29919,7 @@
         <v>1553</v>
       </c>
       <c r="E623">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F623" t="s">
         <v>1558</v>
@@ -29954,7 +29954,7 @@
         <v>1553</v>
       </c>
       <c r="E624">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F624" t="s">
         <v>1558</v>
@@ -29989,7 +29989,7 @@
         <v>1553</v>
       </c>
       <c r="E625">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F625" t="s">
         <v>1558</v>
@@ -30024,7 +30024,7 @@
         <v>1553</v>
       </c>
       <c r="E626">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F626" t="s">
         <v>1560</v>
@@ -30062,7 +30062,7 @@
         <v>1554</v>
       </c>
       <c r="E627">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F627" t="s">
         <v>1558</v>
@@ -30097,7 +30097,7 @@
         <v>1554</v>
       </c>
       <c r="E628">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F628" t="s">
         <v>1558</v>
@@ -30132,7 +30132,7 @@
         <v>1554</v>
       </c>
       <c r="E629">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F629" t="s">
         <v>1558</v>
@@ -30167,7 +30167,7 @@
         <v>1554</v>
       </c>
       <c r="E630">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F630" t="s">
         <v>1558</v>
@@ -30202,7 +30202,7 @@
         <v>1554</v>
       </c>
       <c r="E631">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F631" t="s">
         <v>1560</v>
@@ -30240,7 +30240,7 @@
         <v>1554</v>
       </c>
       <c r="E632">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F632" t="s">
         <v>1560</v>
@@ -30278,7 +30278,7 @@
         <v>1554</v>
       </c>
       <c r="E633">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F633" t="s">
         <v>1558</v>
@@ -30313,7 +30313,7 @@
         <v>1554</v>
       </c>
       <c r="E634">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F634" t="s">
         <v>1560</v>
@@ -30351,7 +30351,7 @@
         <v>1554</v>
       </c>
       <c r="E635">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F635" t="s">
         <v>1558</v>
@@ -30386,7 +30386,7 @@
         <v>1554</v>
       </c>
       <c r="E636">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F636" t="s">
         <v>1558</v>
@@ -30421,7 +30421,7 @@
         <v>1554</v>
       </c>
       <c r="E637">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F637" t="s">
         <v>1558</v>
@@ -30456,7 +30456,7 @@
         <v>1555</v>
       </c>
       <c r="E638">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F638" t="s">
         <v>1558</v>
@@ -30491,7 +30491,7 @@
         <v>1555</v>
       </c>
       <c r="E639">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F639" t="s">
         <v>1558</v>
@@ -30529,7 +30529,7 @@
         <v>1555</v>
       </c>
       <c r="E640">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F640" t="s">
         <v>1560</v>
@@ -30567,7 +30567,7 @@
         <v>1555</v>
       </c>
       <c r="E641">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F641" t="s">
         <v>1558</v>
@@ -30602,7 +30602,7 @@
         <v>1556</v>
       </c>
       <c r="E642">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F642" t="s">
         <v>1560</v>
@@ -30640,7 +30640,7 @@
         <v>1556</v>
       </c>
       <c r="E643">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F643" t="s">
         <v>1558</v>
@@ -30675,7 +30675,7 @@
         <v>1556</v>
       </c>
       <c r="E644">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F644" t="s">
         <v>1560</v>
@@ -30713,7 +30713,7 @@
         <v>1556</v>
       </c>
       <c r="E645">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F645" t="s">
         <v>1558</v>
@@ -30748,7 +30748,7 @@
         <v>1557</v>
       </c>
       <c r="E646">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F646" t="s">
         <v>1558</v>
@@ -30783,7 +30783,7 @@
         <v>1557</v>
       </c>
       <c r="E647">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F647" t="s">
         <v>1558</v>
@@ -30818,7 +30818,7 @@
         <v>1557</v>
       </c>
       <c r="E648">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F648" t="s">
         <v>1558</v>
@@ -30853,7 +30853,7 @@
         <v>1557</v>
       </c>
       <c r="E649">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F649" t="s">
         <v>1558</v>
@@ -30888,7 +30888,7 @@
         <v>1557</v>
       </c>
       <c r="E650">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F650" t="s">
         <v>1558</v>
@@ -30923,7 +30923,7 @@
         <v>1557</v>
       </c>
       <c r="E651">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F651" t="s">
         <v>1558</v>
@@ -30958,7 +30958,7 @@
         <v>1557</v>
       </c>
       <c r="E652">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F652" t="s">
         <v>1558</v>
@@ -30996,7 +30996,7 @@
         <v>1557</v>
       </c>
       <c r="E653">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F653" t="s">
         <v>1558</v>
@@ -31034,7 +31034,7 @@
         <v>1557</v>
       </c>
       <c r="E654">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F654" t="s">
         <v>1558</v>

--- a/BacklogGATEAutoCompleto.xlsx
+++ b/BacklogGATEAutoCompleto.xlsx
@@ -103,6 +103,9 @@
     <t>NÚCLEO TÉCNICO DE ENGENHARIA,NÚCLEO TÉCNICO DE CIÊNCIAS NATURAIS</t>
   </si>
   <si>
+    <t>SECRETARIA GERAL DO GATE</t>
+  </si>
+  <si>
     <t>ADMISSIBILIDADE DA SECRETARIA DO GATE</t>
   </si>
   <si>
@@ -124,9 +127,6 @@
     <t>NÚCLEO TÉCNICO DE CIÊNCIAS NATURAIS,NÚCLEO TÉCNICO DE ECONOMIA</t>
   </si>
   <si>
-    <t>SECRETARIA GERAL DO GATE</t>
-  </si>
-  <si>
     <t>NÚCLEO TÉCNICO DE ENGENHARIA, SECRETARIA GERAL DO GATE</t>
   </si>
   <si>
@@ -4966,106 +4966,106 @@
     <t>HUDSON DE OLIVEIRA SACRAMENTO</t>
   </si>
   <si>
+    <t>ALESSANDRA ALMEIDA DIAS DA SILVA,ALEXANDER MAGNO BORGES GOMES DA SILVA,VANESSA FERNANDES LEÃO</t>
+  </si>
+  <si>
+    <t>SUZAN NIGRI</t>
+  </si>
+  <si>
+    <t>PABLO GINIO VIMERCATI SIMAS</t>
+  </si>
+  <si>
+    <t>THIAGO JOSÉ DUPRAT FORTES</t>
+  </si>
+  <si>
+    <t>FERNANDA FERREIRA FONTES,JULIANA MARTINS BAHIENSE,RODRIGO VALENTE SERRA</t>
+  </si>
+  <si>
+    <t>PEDRO HENRIQUE DE MESQUITA MAGALHÃES</t>
+  </si>
+  <si>
+    <t>REINALDO DE SOUZA MACHADO</t>
+  </si>
+  <si>
+    <t>RODRIGO VENTURA MARRA,THIAGO JOSÉ DUPRAT FORTES</t>
+  </si>
+  <si>
+    <t>CHRISTIANA ROSA FERREIRA</t>
+  </si>
+  <si>
+    <t>HEITOR DE FÁTIMA BARBOSA DA SILVA</t>
+  </si>
+  <si>
+    <t>JULIANA MARTINS BAHIENSE,MARIA JOSÉ LOPES DE ARAUJO SAROLDI</t>
+  </si>
+  <si>
+    <t>CAROLINE OLIVEIRA DE MENEZES</t>
+  </si>
+  <si>
+    <t>PATRICIA PASSARO DA SILVA TOLEDO,VALÉRIA FERREIRA DA SILVA LÚCIO</t>
+  </si>
+  <si>
+    <t>JOELSON SANTANA DE CARVALHO</t>
+  </si>
+  <si>
+    <t>MARINA DE AQUINO PARREIRA XAVIER, _SEM USUARIO ATRIBUIDO</t>
+  </si>
+  <si>
+    <t>EDUARDO COUTO SOLEDADE</t>
+  </si>
+  <si>
+    <t>HELENA FERREIRA DE LIMA</t>
+  </si>
+  <si>
+    <t>LUIZ FRANCISCO PERALTA BRAGA,MARCELO SILVA DE AZEVEDO, _SEM USUARIO ATRIBUIDO</t>
+  </si>
+  <si>
+    <t>DIANA DELGADO DA COSTA DA SILVA</t>
+  </si>
+  <si>
+    <t>LEONARDO ARAÚJO DE SOUZA,MOEMA BELLONI SCHMIDT</t>
+  </si>
+  <si>
+    <t>MARCELO KOLBLINGER DE GODOY</t>
+  </si>
+  <si>
+    <t>IZABEL CHRISTINA DE ALCANTARA FIGUEIREDO PIMENTA</t>
+  </si>
+  <si>
+    <t>EDIWAN SOUSA DA SILVA,SEZISNANDO JOSE PRIMO PAES</t>
+  </si>
+  <si>
+    <t>EDIWAN SOUSA DA SILVA,ELIANA MIRANDA ARAUJO DA SILVA SOARES</t>
+  </si>
+  <si>
+    <t>FERNANDA ZUCOLOTTO</t>
+  </si>
+  <si>
+    <t>RAQUEL SILVA FERNANDES LYRA</t>
+  </si>
+  <si>
+    <t>RENATA DE ARAUJO RIOS</t>
+  </si>
+  <si>
+    <t>FERNANDA ZUCOLOTTO,MARINA DE AQUINO PARREIRA XAVIER</t>
+  </si>
+  <si>
+    <t>DAYSE BARBOSA DE ARAÚJO GÓIS</t>
+  </si>
+  <si>
+    <t>FLAVIA REIS RIBEIRO BASTOS, _SEM USUARIO ATRIBUIDO</t>
+  </si>
+  <si>
+    <t>SEZISNANDO JOSE PRIMO PAES</t>
+  </si>
+  <si>
+    <t>LEONARDO ARAÚJO DE SOUZA</t>
+  </si>
+  <si>
+    <t>RODRIGO VALENTE SERRA,VANESSA FERNANDES LEÃO</t>
+  </si>
+  <si>
     <t>GLAUCO CASTILHO DE ALMEIDA</t>
-  </si>
-  <si>
-    <t>ALESSANDRA ALMEIDA DIAS DA SILVA,ALEXANDER MAGNO BORGES GOMES DA SILVA,VANESSA FERNANDES LEÃO</t>
-  </si>
-  <si>
-    <t>SUZAN NIGRI</t>
-  </si>
-  <si>
-    <t>PABLO GINIO VIMERCATI SIMAS</t>
-  </si>
-  <si>
-    <t>THIAGO JOSÉ DUPRAT FORTES</t>
-  </si>
-  <si>
-    <t>FERNANDA FERREIRA FONTES,JULIANA MARTINS BAHIENSE,RODRIGO VALENTE SERRA</t>
-  </si>
-  <si>
-    <t>PEDRO HENRIQUE DE MESQUITA MAGALHÃES</t>
-  </si>
-  <si>
-    <t>REINALDO DE SOUZA MACHADO</t>
-  </si>
-  <si>
-    <t>RODRIGO VENTURA MARRA,THIAGO JOSÉ DUPRAT FORTES</t>
-  </si>
-  <si>
-    <t>CHRISTIANA ROSA FERREIRA</t>
-  </si>
-  <si>
-    <t>HEITOR DE FÁTIMA BARBOSA DA SILVA</t>
-  </si>
-  <si>
-    <t>JULIANA MARTINS BAHIENSE,MARIA JOSÉ LOPES DE ARAUJO SAROLDI</t>
-  </si>
-  <si>
-    <t>CAROLINE OLIVEIRA DE MENEZES</t>
-  </si>
-  <si>
-    <t>PATRICIA PASSARO DA SILVA TOLEDO,VALÉRIA FERREIRA DA SILVA LÚCIO</t>
-  </si>
-  <si>
-    <t>JOELSON SANTANA DE CARVALHO</t>
-  </si>
-  <si>
-    <t>MARINA DE AQUINO PARREIRA XAVIER, _SEM USUARIO ATRIBUIDO</t>
-  </si>
-  <si>
-    <t>EDUARDO COUTO SOLEDADE</t>
-  </si>
-  <si>
-    <t>HELENA FERREIRA DE LIMA</t>
-  </si>
-  <si>
-    <t>LUIZ FRANCISCO PERALTA BRAGA,MARCELO SILVA DE AZEVEDO, _SEM USUARIO ATRIBUIDO</t>
-  </si>
-  <si>
-    <t>DIANA DELGADO DA COSTA DA SILVA</t>
-  </si>
-  <si>
-    <t>LEONARDO ARAÚJO DE SOUZA,MOEMA BELLONI SCHMIDT</t>
-  </si>
-  <si>
-    <t>MARCELO KOLBLINGER DE GODOY</t>
-  </si>
-  <si>
-    <t>IZABEL CHRISTINA DE ALCANTARA FIGUEIREDO PIMENTA</t>
-  </si>
-  <si>
-    <t>EDIWAN SOUSA DA SILVA,SEZISNANDO JOSE PRIMO PAES</t>
-  </si>
-  <si>
-    <t>EDIWAN SOUSA DA SILVA,ELIANA MIRANDA ARAUJO DA SILVA SOARES</t>
-  </si>
-  <si>
-    <t>FERNANDA ZUCOLOTTO</t>
-  </si>
-  <si>
-    <t>RAQUEL SILVA FERNANDES LYRA</t>
-  </si>
-  <si>
-    <t>RENATA DE ARAUJO RIOS</t>
-  </si>
-  <si>
-    <t>FERNANDA ZUCOLOTTO,MARINA DE AQUINO PARREIRA XAVIER</t>
-  </si>
-  <si>
-    <t>DAYSE BARBOSA DE ARAÚJO GÓIS</t>
-  </si>
-  <si>
-    <t>FLAVIA REIS RIBEIRO BASTOS, _SEM USUARIO ATRIBUIDO</t>
-  </si>
-  <si>
-    <t>SEZISNANDO JOSE PRIMO PAES</t>
-  </si>
-  <si>
-    <t>LEONARDO ARAÚJO DE SOUZA</t>
-  </si>
-  <si>
-    <t>RODRIGO VALENTE SERRA,VANESSA FERNANDES LEÃO</t>
   </si>
   <si>
     <t>ANDRÉA SILVA ARAUJO DE MELLO</t>
@@ -9833,7 +9833,7 @@
         <v>1740</v>
       </c>
       <c r="K51" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="L51" t="s">
         <v>2477</v>
@@ -14884,7 +14884,7 @@
     </row>
     <row r="196" spans="1:12">
       <c r="A196" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="B196" t="s">
         <v>234</v>
@@ -14905,7 +14905,7 @@
         <v>1563</v>
       </c>
       <c r="I196" t="s">
-        <v>1650</v>
+        <v>1596</v>
       </c>
       <c r="J196" t="s">
         <v>1906</v>
@@ -15150,7 +15150,7 @@
         <v>1563</v>
       </c>
       <c r="I203" t="s">
-        <v>1651</v>
+        <v>1650</v>
       </c>
       <c r="J203" t="s">
         <v>1913</v>
@@ -15185,7 +15185,7 @@
         <v>1563</v>
       </c>
       <c r="I204" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
       <c r="J204" t="s">
         <v>1914</v>
@@ -15339,7 +15339,7 @@
     </row>
     <row r="209" spans="1:12">
       <c r="A209" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B209" t="s">
         <v>247</v>
@@ -15360,7 +15360,7 @@
         <v>1563</v>
       </c>
       <c r="I209" t="s">
-        <v>1653</v>
+        <v>1652</v>
       </c>
       <c r="J209" t="s">
         <v>1919</v>
@@ -15395,7 +15395,7 @@
         <v>1563</v>
       </c>
       <c r="I210" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="J210" t="s">
         <v>1920</v>
@@ -15514,7 +15514,7 @@
     </row>
     <row r="214" spans="1:12">
       <c r="A214" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B214" t="s">
         <v>252</v>
@@ -15535,7 +15535,7 @@
         <v>1563</v>
       </c>
       <c r="I214" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
       <c r="J214" t="s">
         <v>1924</v>
@@ -15584,7 +15584,7 @@
     </row>
     <row r="216" spans="1:12">
       <c r="A216" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B216" t="s">
         <v>254</v>
@@ -15605,7 +15605,7 @@
         <v>1563</v>
       </c>
       <c r="I216" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="J216" t="s">
         <v>1926</v>
@@ -15640,7 +15640,7 @@
         <v>1563</v>
       </c>
       <c r="I217" t="s">
-        <v>1657</v>
+        <v>1656</v>
       </c>
       <c r="J217" t="s">
         <v>1927</v>
@@ -15675,7 +15675,7 @@
         <v>1563</v>
       </c>
       <c r="I218" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
       <c r="J218" t="s">
         <v>1928</v>
@@ -15853,7 +15853,7 @@
         <v>1563</v>
       </c>
       <c r="I223" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
       <c r="J223" t="s">
         <v>1933</v>
@@ -15888,7 +15888,7 @@
         <v>1563</v>
       </c>
       <c r="I224" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
       <c r="J224" t="s">
         <v>1934</v>
@@ -15923,7 +15923,7 @@
         <v>1563</v>
       </c>
       <c r="I225" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
       <c r="J225" t="s">
         <v>1935</v>
@@ -16042,7 +16042,7 @@
     </row>
     <row r="229" spans="1:12">
       <c r="A229" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B229" t="s">
         <v>267</v>
@@ -16063,7 +16063,7 @@
         <v>1563</v>
       </c>
       <c r="I229" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
       <c r="J229" t="s">
         <v>1939</v>
@@ -16133,7 +16133,7 @@
         <v>1563</v>
       </c>
       <c r="I231" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
       <c r="J231" t="s">
         <v>1941</v>
@@ -16168,7 +16168,7 @@
         <v>1563</v>
       </c>
       <c r="I232" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
       <c r="J232" t="s">
         <v>1942</v>
@@ -16217,7 +16217,7 @@
     </row>
     <row r="234" spans="1:12">
       <c r="A234" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B234" t="s">
         <v>272</v>
@@ -16238,7 +16238,7 @@
         <v>1563</v>
       </c>
       <c r="I234" t="s">
-        <v>1665</v>
+        <v>1664</v>
       </c>
       <c r="J234" t="s">
         <v>1944</v>
@@ -16287,7 +16287,7 @@
     </row>
     <row r="236" spans="1:12">
       <c r="A236" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B236" t="s">
         <v>274</v>
@@ -16308,7 +16308,7 @@
         <v>1563</v>
       </c>
       <c r="I236" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="J236" t="s">
         <v>1946</v>
@@ -16343,7 +16343,7 @@
         <v>1563</v>
       </c>
       <c r="I237" t="s">
-        <v>1666</v>
+        <v>1665</v>
       </c>
       <c r="J237" t="s">
         <v>1947</v>
@@ -16497,7 +16497,7 @@
     </row>
     <row r="242" spans="1:12">
       <c r="A242" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B242" t="s">
         <v>280</v>
@@ -16518,7 +16518,7 @@
         <v>1563</v>
       </c>
       <c r="I242" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="J242" t="s">
         <v>1952</v>
@@ -16623,7 +16623,7 @@
         <v>1563</v>
       </c>
       <c r="I245" t="s">
-        <v>1667</v>
+        <v>1666</v>
       </c>
       <c r="J245" t="s">
         <v>1955</v>
@@ -16672,7 +16672,7 @@
     </row>
     <row r="247" spans="1:12">
       <c r="A247" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B247" t="s">
         <v>285</v>
@@ -16693,7 +16693,7 @@
         <v>1563</v>
       </c>
       <c r="I247" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="J247" t="s">
         <v>1957</v>
@@ -16707,7 +16707,7 @@
     </row>
     <row r="248" spans="1:12">
       <c r="A248" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B248" t="s">
         <v>286</v>
@@ -16728,7 +16728,7 @@
         <v>1563</v>
       </c>
       <c r="I248" t="s">
-        <v>1668</v>
+        <v>1667</v>
       </c>
       <c r="J248" t="s">
         <v>1958</v>
@@ -16882,7 +16882,7 @@
     </row>
     <row r="253" spans="1:12">
       <c r="A253" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B253" t="s">
         <v>291</v>
@@ -16903,7 +16903,7 @@
         <v>1563</v>
       </c>
       <c r="I253" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="J253" t="s">
         <v>1963</v>
@@ -17060,7 +17060,7 @@
     </row>
     <row r="258" spans="1:12">
       <c r="A258" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B258" t="s">
         <v>296</v>
@@ -17084,7 +17084,7 @@
         <v>1568</v>
       </c>
       <c r="I258" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="J258" t="s">
         <v>1968</v>
@@ -17203,7 +17203,7 @@
     </row>
     <row r="262" spans="1:12">
       <c r="A262" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B262" t="s">
         <v>300</v>
@@ -17224,7 +17224,7 @@
         <v>1563</v>
       </c>
       <c r="I262" t="s">
-        <v>1653</v>
+        <v>1652</v>
       </c>
       <c r="J262" t="s">
         <v>1972</v>
@@ -17238,7 +17238,7 @@
     </row>
     <row r="263" spans="1:12">
       <c r="A263" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B263" t="s">
         <v>301</v>
@@ -17259,7 +17259,7 @@
         <v>1563</v>
       </c>
       <c r="I263" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="J263" t="s">
         <v>1973</v>
@@ -17399,7 +17399,7 @@
         <v>1563</v>
       </c>
       <c r="I267" t="s">
-        <v>1669</v>
+        <v>1668</v>
       </c>
       <c r="J267" t="s">
         <v>1977</v>
@@ -17434,7 +17434,7 @@
         <v>1563</v>
       </c>
       <c r="I268" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
       <c r="J268" t="s">
         <v>1978</v>
@@ -17448,7 +17448,7 @@
     </row>
     <row r="269" spans="1:12">
       <c r="A269" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B269" t="s">
         <v>307</v>
@@ -17469,7 +17469,7 @@
         <v>1563</v>
       </c>
       <c r="I269" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="J269" t="s">
         <v>1979</v>
@@ -17504,7 +17504,7 @@
         <v>1563</v>
       </c>
       <c r="I270" t="s">
-        <v>1671</v>
+        <v>1670</v>
       </c>
       <c r="J270" t="s">
         <v>1980</v>
@@ -17798,7 +17798,7 @@
     </row>
     <row r="279" spans="1:12">
       <c r="A279" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B279" t="s">
         <v>317</v>
@@ -17819,7 +17819,7 @@
         <v>1563</v>
       </c>
       <c r="I279" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="J279" t="s">
         <v>1989</v>
@@ -17903,7 +17903,7 @@
     </row>
     <row r="282" spans="1:12">
       <c r="A282" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B282" t="s">
         <v>320</v>
@@ -17924,7 +17924,7 @@
         <v>1563</v>
       </c>
       <c r="I282" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
       <c r="J282" t="s">
         <v>1992</v>
@@ -17973,7 +17973,7 @@
     </row>
     <row r="284" spans="1:12">
       <c r="A284" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B284" t="s">
         <v>322</v>
@@ -17994,7 +17994,7 @@
         <v>1563</v>
       </c>
       <c r="I284" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="J284" t="s">
         <v>1994</v>
@@ -18148,7 +18148,7 @@
     </row>
     <row r="289" spans="1:12">
       <c r="A289" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B289" t="s">
         <v>327</v>
@@ -18169,7 +18169,7 @@
         <v>1563</v>
       </c>
       <c r="I289" t="s">
-        <v>1673</v>
+        <v>1672</v>
       </c>
       <c r="J289" t="s">
         <v>1999</v>
@@ -18239,7 +18239,7 @@
         <v>1563</v>
       </c>
       <c r="I291" t="s">
-        <v>1674</v>
+        <v>1673</v>
       </c>
       <c r="J291" t="s">
         <v>2001</v>
@@ -18323,7 +18323,7 @@
     </row>
     <row r="294" spans="1:12">
       <c r="A294" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B294" t="s">
         <v>332</v>
@@ -18344,7 +18344,7 @@
         <v>1563</v>
       </c>
       <c r="I294" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="J294" t="s">
         <v>2004</v>
@@ -18428,7 +18428,7 @@
     </row>
     <row r="297" spans="1:12">
       <c r="A297" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B297" t="s">
         <v>335</v>
@@ -18449,7 +18449,7 @@
         <v>1563</v>
       </c>
       <c r="I297" t="s">
-        <v>1653</v>
+        <v>1652</v>
       </c>
       <c r="J297" t="s">
         <v>2007</v>
@@ -18554,7 +18554,7 @@
         <v>1563</v>
       </c>
       <c r="I300" t="s">
-        <v>1669</v>
+        <v>1668</v>
       </c>
       <c r="J300" t="s">
         <v>2010</v>
@@ -18883,7 +18883,7 @@
     </row>
     <row r="310" spans="1:12">
       <c r="A310" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B310" t="s">
         <v>348</v>
@@ -18904,7 +18904,7 @@
         <v>1563</v>
       </c>
       <c r="I310" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="J310" t="s">
         <v>2020</v>
@@ -19303,7 +19303,7 @@
     </row>
     <row r="322" spans="1:12">
       <c r="A322" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B322" t="s">
         <v>360</v>
@@ -19324,7 +19324,7 @@
         <v>1563</v>
       </c>
       <c r="I322" t="s">
-        <v>1653</v>
+        <v>1652</v>
       </c>
       <c r="J322" t="s">
         <v>2032</v>
@@ -19397,7 +19397,7 @@
         <v>1514</v>
       </c>
       <c r="I324" t="s">
-        <v>1675</v>
+        <v>1674</v>
       </c>
       <c r="J324" t="s">
         <v>2034</v>
@@ -19481,7 +19481,7 @@
     </row>
     <row r="327" spans="1:12">
       <c r="A327" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B327" t="s">
         <v>365</v>
@@ -19502,7 +19502,7 @@
         <v>1563</v>
       </c>
       <c r="I327" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="J327" t="s">
         <v>2037</v>
@@ -19516,7 +19516,7 @@
     </row>
     <row r="328" spans="1:12">
       <c r="A328" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B328" t="s">
         <v>366</v>
@@ -19537,7 +19537,7 @@
         <v>1563</v>
       </c>
       <c r="I328" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
       <c r="J328" t="s">
         <v>2038</v>
@@ -19869,7 +19869,7 @@
     </row>
     <row r="338" spans="1:12">
       <c r="A338" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B338" t="s">
         <v>376</v>
@@ -19890,7 +19890,7 @@
         <v>1563</v>
       </c>
       <c r="I338" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="J338" t="s">
         <v>2048</v>
@@ -20044,7 +20044,7 @@
     </row>
     <row r="343" spans="1:12">
       <c r="A343" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B343" t="s">
         <v>381</v>
@@ -20065,7 +20065,7 @@
         <v>1563</v>
       </c>
       <c r="I343" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
       <c r="J343" t="s">
         <v>2053</v>
@@ -20149,7 +20149,7 @@
     </row>
     <row r="346" spans="1:12">
       <c r="A346" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B346" t="s">
         <v>384</v>
@@ -20170,7 +20170,7 @@
         <v>1563</v>
       </c>
       <c r="I346" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
       <c r="J346" t="s">
         <v>2056</v>
@@ -20184,7 +20184,7 @@
     </row>
     <row r="347" spans="1:12">
       <c r="A347" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B347" t="s">
         <v>385</v>
@@ -20205,7 +20205,7 @@
         <v>1563</v>
       </c>
       <c r="I347" t="s">
-        <v>1653</v>
+        <v>1652</v>
       </c>
       <c r="J347" t="s">
         <v>2057</v>
@@ -20219,7 +20219,7 @@
     </row>
     <row r="348" spans="1:12">
       <c r="A348" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B348" t="s">
         <v>386</v>
@@ -20240,7 +20240,7 @@
         <v>1563</v>
       </c>
       <c r="I348" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
       <c r="J348" t="s">
         <v>2058</v>
@@ -20289,7 +20289,7 @@
     </row>
     <row r="350" spans="1:12">
       <c r="A350" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B350" t="s">
         <v>388</v>
@@ -20310,7 +20310,7 @@
         <v>1563</v>
       </c>
       <c r="I350" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
       <c r="J350" t="s">
         <v>2060</v>
@@ -20324,7 +20324,7 @@
     </row>
     <row r="351" spans="1:12">
       <c r="A351" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B351" t="s">
         <v>389</v>
@@ -20345,7 +20345,7 @@
         <v>1563</v>
       </c>
       <c r="I351" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
       <c r="J351" t="s">
         <v>2061</v>
@@ -20394,7 +20394,7 @@
     </row>
     <row r="353" spans="1:12">
       <c r="A353" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B353" t="s">
         <v>391</v>
@@ -20418,7 +20418,7 @@
         <v>1570</v>
       </c>
       <c r="I353" t="s">
-        <v>1653</v>
+        <v>1652</v>
       </c>
       <c r="J353" t="s">
         <v>2063</v>
@@ -20453,7 +20453,7 @@
         <v>1563</v>
       </c>
       <c r="I354" t="s">
-        <v>1677</v>
+        <v>1676</v>
       </c>
       <c r="J354" t="s">
         <v>2064</v>
@@ -20467,7 +20467,7 @@
     </row>
     <row r="355" spans="1:12">
       <c r="A355" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B355" t="s">
         <v>393</v>
@@ -20488,7 +20488,7 @@
         <v>1563</v>
       </c>
       <c r="I355" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="J355" t="s">
         <v>2065</v>
@@ -20502,7 +20502,7 @@
     </row>
     <row r="356" spans="1:12">
       <c r="A356" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B356" t="s">
         <v>394</v>
@@ -20523,7 +20523,7 @@
         <v>1563</v>
       </c>
       <c r="I356" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="J356" t="s">
         <v>2066</v>
@@ -20537,7 +20537,7 @@
     </row>
     <row r="357" spans="1:12">
       <c r="A357" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B357" t="s">
         <v>395</v>
@@ -20558,7 +20558,7 @@
         <v>1563</v>
       </c>
       <c r="I357" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
       <c r="J357" t="s">
         <v>2067</v>
@@ -20607,7 +20607,7 @@
     </row>
     <row r="359" spans="1:12">
       <c r="A359" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B359" t="s">
         <v>397</v>
@@ -20628,7 +20628,7 @@
         <v>1563</v>
       </c>
       <c r="I359" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="J359" t="s">
         <v>2069</v>
@@ -20642,7 +20642,7 @@
     </row>
     <row r="360" spans="1:12">
       <c r="A360" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B360" t="s">
         <v>398</v>
@@ -20663,7 +20663,7 @@
         <v>1563</v>
       </c>
       <c r="I360" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
       <c r="J360" t="s">
         <v>2070</v>
@@ -20677,7 +20677,7 @@
     </row>
     <row r="361" spans="1:12">
       <c r="A361" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B361" t="s">
         <v>399</v>
@@ -20698,7 +20698,7 @@
         <v>1563</v>
       </c>
       <c r="I361" t="s">
-        <v>1653</v>
+        <v>1652</v>
       </c>
       <c r="J361" t="s">
         <v>2071</v>
@@ -20782,7 +20782,7 @@
     </row>
     <row r="364" spans="1:12">
       <c r="A364" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B364" t="s">
         <v>402</v>
@@ -20803,7 +20803,7 @@
         <v>1563</v>
       </c>
       <c r="I364" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="J364" t="s">
         <v>2074</v>
@@ -20887,7 +20887,7 @@
     </row>
     <row r="367" spans="1:12">
       <c r="A367" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B367" t="s">
         <v>405</v>
@@ -20908,7 +20908,7 @@
         <v>1563</v>
       </c>
       <c r="I367" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="J367" t="s">
         <v>2077</v>
@@ -20957,7 +20957,7 @@
     </row>
     <row r="369" spans="1:12">
       <c r="A369" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B369" t="s">
         <v>407</v>
@@ -20978,7 +20978,7 @@
         <v>1563</v>
       </c>
       <c r="I369" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
       <c r="J369" t="s">
         <v>2079</v>
@@ -21118,7 +21118,7 @@
         <v>1563</v>
       </c>
       <c r="I373" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
       <c r="J373" t="s">
         <v>2083</v>
@@ -21167,7 +21167,7 @@
     </row>
     <row r="375" spans="1:12">
       <c r="A375" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B375" t="s">
         <v>413</v>
@@ -21188,7 +21188,7 @@
         <v>1565</v>
       </c>
       <c r="I375" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
       <c r="J375" t="s">
         <v>2085</v>
@@ -21223,7 +21223,7 @@
         <v>1563</v>
       </c>
       <c r="I376" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
       <c r="J376" t="s">
         <v>2086</v>
@@ -21412,7 +21412,7 @@
     </row>
     <row r="382" spans="1:12">
       <c r="A382" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B382" t="s">
         <v>420</v>
@@ -21433,7 +21433,7 @@
         <v>1563</v>
       </c>
       <c r="I382" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
       <c r="J382" t="s">
         <v>2092</v>
@@ -21447,7 +21447,7 @@
     </row>
     <row r="383" spans="1:12">
       <c r="A383" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B383" t="s">
         <v>421</v>
@@ -21468,7 +21468,7 @@
         <v>1563</v>
       </c>
       <c r="I383" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
       <c r="J383" t="s">
         <v>2093</v>
@@ -21517,7 +21517,7 @@
     </row>
     <row r="385" spans="1:12">
       <c r="A385" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B385" t="s">
         <v>423</v>
@@ -21538,7 +21538,7 @@
         <v>1563</v>
       </c>
       <c r="I385" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
       <c r="J385" t="s">
         <v>2095</v>
@@ -21622,7 +21622,7 @@
     </row>
     <row r="388" spans="1:12">
       <c r="A388" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B388" t="s">
         <v>426</v>
@@ -21643,7 +21643,7 @@
         <v>1563</v>
       </c>
       <c r="I388" t="s">
-        <v>1653</v>
+        <v>1652</v>
       </c>
       <c r="J388" t="s">
         <v>2098</v>
@@ -21657,7 +21657,7 @@
     </row>
     <row r="389" spans="1:12">
       <c r="A389" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B389" t="s">
         <v>427</v>
@@ -21678,7 +21678,7 @@
         <v>1563</v>
       </c>
       <c r="I389" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
       <c r="J389" t="s">
         <v>2099</v>
@@ -21727,7 +21727,7 @@
     </row>
     <row r="391" spans="1:12">
       <c r="A391" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B391" t="s">
         <v>429</v>
@@ -21748,7 +21748,7 @@
         <v>1563</v>
       </c>
       <c r="I391" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="J391" t="s">
         <v>2101</v>
@@ -21853,7 +21853,7 @@
         <v>1563</v>
       </c>
       <c r="I394" t="s">
-        <v>1671</v>
+        <v>1670</v>
       </c>
       <c r="J394" t="s">
         <v>2104</v>
@@ -21937,7 +21937,7 @@
     </row>
     <row r="397" spans="1:12">
       <c r="A397" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B397" t="s">
         <v>435</v>
@@ -21958,7 +21958,7 @@
         <v>1563</v>
       </c>
       <c r="I397" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
       <c r="J397" t="s">
         <v>2107</v>
@@ -22063,7 +22063,7 @@
         <v>1563</v>
       </c>
       <c r="I400" t="s">
-        <v>1681</v>
+        <v>1680</v>
       </c>
       <c r="J400" t="s">
         <v>2110</v>
@@ -22112,7 +22112,7 @@
     </row>
     <row r="402" spans="1:12">
       <c r="A402" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B402" t="s">
         <v>440</v>
@@ -22133,7 +22133,7 @@
         <v>1563</v>
       </c>
       <c r="I402" t="s">
-        <v>1653</v>
+        <v>1652</v>
       </c>
       <c r="J402" t="s">
         <v>2112</v>
@@ -22168,7 +22168,7 @@
         <v>1563</v>
       </c>
       <c r="I403" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="J403" t="s">
         <v>2113</v>
@@ -22238,7 +22238,7 @@
         <v>1563</v>
       </c>
       <c r="I405" t="s">
-        <v>1682</v>
+        <v>1681</v>
       </c>
       <c r="J405" t="s">
         <v>2115</v>
@@ -22308,7 +22308,7 @@
         <v>1563</v>
       </c>
       <c r="I407" t="s">
-        <v>1681</v>
+        <v>1680</v>
       </c>
       <c r="J407" t="s">
         <v>2117</v>
@@ -22535,7 +22535,7 @@
     </row>
     <row r="414" spans="1:12">
       <c r="A414" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B414" t="s">
         <v>452</v>
@@ -22556,7 +22556,7 @@
         <v>1563</v>
       </c>
       <c r="I414" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="J414" t="s">
         <v>2124</v>
@@ -22605,7 +22605,7 @@
     </row>
     <row r="416" spans="1:12">
       <c r="A416" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B416" t="s">
         <v>454</v>
@@ -22626,7 +22626,7 @@
         <v>1563</v>
       </c>
       <c r="I416" t="s">
-        <v>1653</v>
+        <v>1652</v>
       </c>
       <c r="J416" t="s">
         <v>2126</v>
@@ -22675,7 +22675,7 @@
     </row>
     <row r="418" spans="1:12">
       <c r="A418" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B418" t="s">
         <v>456</v>
@@ -22696,7 +22696,7 @@
         <v>1563</v>
       </c>
       <c r="I418" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
       <c r="J418" t="s">
         <v>2128</v>
@@ -22710,7 +22710,7 @@
     </row>
     <row r="419" spans="1:12">
       <c r="A419" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B419" t="s">
         <v>457</v>
@@ -22731,7 +22731,7 @@
         <v>1563</v>
       </c>
       <c r="I419" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
       <c r="J419" t="s">
         <v>2129</v>
@@ -22769,7 +22769,7 @@
         <v>1538</v>
       </c>
       <c r="I420" t="s">
-        <v>1650</v>
+        <v>1683</v>
       </c>
       <c r="J420" t="s">
         <v>2130</v>
@@ -22783,7 +22783,7 @@
     </row>
     <row r="421" spans="1:12">
       <c r="A421" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="B421" t="s">
         <v>459</v>
@@ -22923,7 +22923,7 @@
     </row>
     <row r="425" spans="1:12">
       <c r="A425" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="B425" t="s">
         <v>463</v>
@@ -22958,7 +22958,7 @@
     </row>
     <row r="426" spans="1:12">
       <c r="A426" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B426" t="s">
         <v>464</v>
@@ -22979,7 +22979,7 @@
         <v>1563</v>
       </c>
       <c r="I426" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
       <c r="J426" t="s">
         <v>2136</v>
@@ -23028,7 +23028,7 @@
     </row>
     <row r="428" spans="1:12">
       <c r="A428" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B428" t="s">
         <v>466</v>
@@ -23049,7 +23049,7 @@
         <v>1563</v>
       </c>
       <c r="I428" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
       <c r="J428" t="s">
         <v>2138</v>
@@ -23098,7 +23098,7 @@
     </row>
     <row r="430" spans="1:12">
       <c r="A430" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B430" t="s">
         <v>468</v>
@@ -23119,7 +23119,7 @@
         <v>1563</v>
       </c>
       <c r="I430" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
       <c r="J430" t="s">
         <v>2140</v>
@@ -23133,7 +23133,7 @@
     </row>
     <row r="431" spans="1:12">
       <c r="A431" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B431" t="s">
         <v>469</v>
@@ -23154,7 +23154,7 @@
         <v>1563</v>
       </c>
       <c r="I431" t="s">
-        <v>1653</v>
+        <v>1652</v>
       </c>
       <c r="J431" t="s">
         <v>2141</v>
@@ -23189,7 +23189,7 @@
         <v>1563</v>
       </c>
       <c r="I432" t="s">
-        <v>1667</v>
+        <v>1666</v>
       </c>
       <c r="J432" t="s">
         <v>2142</v>
@@ -23203,7 +23203,7 @@
     </row>
     <row r="433" spans="1:12">
       <c r="A433" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B433" t="s">
         <v>471</v>
@@ -23224,7 +23224,7 @@
         <v>1563</v>
       </c>
       <c r="I433" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="J433" t="s">
         <v>2143</v>
@@ -23238,7 +23238,7 @@
     </row>
     <row r="434" spans="1:12">
       <c r="A434" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B434" t="s">
         <v>472</v>
@@ -23259,7 +23259,7 @@
         <v>1563</v>
       </c>
       <c r="I434" t="s">
-        <v>1653</v>
+        <v>1652</v>
       </c>
       <c r="J434" t="s">
         <v>2144</v>
@@ -23273,7 +23273,7 @@
     </row>
     <row r="435" spans="1:12">
       <c r="A435" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B435" t="s">
         <v>473</v>
@@ -23294,7 +23294,7 @@
         <v>1563</v>
       </c>
       <c r="I435" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="J435" t="s">
         <v>2145</v>
@@ -23308,7 +23308,7 @@
     </row>
     <row r="436" spans="1:12">
       <c r="A436" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B436" t="s">
         <v>474</v>
@@ -23329,7 +23329,7 @@
         <v>1563</v>
       </c>
       <c r="I436" t="s">
-        <v>1653</v>
+        <v>1652</v>
       </c>
       <c r="J436" t="s">
         <v>2112</v>
@@ -23591,7 +23591,7 @@
     </row>
     <row r="444" spans="1:12">
       <c r="A444" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B444" t="s">
         <v>482</v>
@@ -23612,7 +23612,7 @@
         <v>1563</v>
       </c>
       <c r="I444" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="J444" t="s">
         <v>2153</v>
@@ -23626,7 +23626,7 @@
     </row>
     <row r="445" spans="1:12">
       <c r="A445" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B445" t="s">
         <v>483</v>
@@ -23647,7 +23647,7 @@
         <v>1563</v>
       </c>
       <c r="I445" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
       <c r="J445" t="s">
         <v>2154</v>
@@ -23661,7 +23661,7 @@
     </row>
     <row r="446" spans="1:12">
       <c r="A446" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B446" t="s">
         <v>484</v>
@@ -23682,7 +23682,7 @@
         <v>1563</v>
       </c>
       <c r="I446" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
       <c r="J446" t="s">
         <v>2155</v>
@@ -23766,7 +23766,7 @@
     </row>
     <row r="449" spans="1:12">
       <c r="A449" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B449" t="s">
         <v>487</v>
@@ -23787,7 +23787,7 @@
         <v>1563</v>
       </c>
       <c r="I449" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
       <c r="J449" t="s">
         <v>2158</v>
@@ -23801,7 +23801,7 @@
     </row>
     <row r="450" spans="1:12">
       <c r="A450" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B450" t="s">
         <v>488</v>
@@ -23822,7 +23822,7 @@
         <v>1563</v>
       </c>
       <c r="I450" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
       <c r="J450" t="s">
         <v>2159</v>
@@ -23836,7 +23836,7 @@
     </row>
     <row r="451" spans="1:12">
       <c r="A451" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B451" t="s">
         <v>489</v>
@@ -23857,7 +23857,7 @@
         <v>1563</v>
       </c>
       <c r="I451" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="J451" t="s">
         <v>2160</v>
@@ -23871,7 +23871,7 @@
     </row>
     <row r="452" spans="1:12">
       <c r="A452" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B452" t="s">
         <v>490</v>
@@ -23892,7 +23892,7 @@
         <v>1563</v>
       </c>
       <c r="I452" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="J452" t="s">
         <v>2161</v>
@@ -23906,7 +23906,7 @@
     </row>
     <row r="453" spans="1:12">
       <c r="A453" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B453" t="s">
         <v>491</v>
@@ -23927,7 +23927,7 @@
         <v>1563</v>
       </c>
       <c r="I453" t="s">
-        <v>1653</v>
+        <v>1652</v>
       </c>
       <c r="J453" t="s">
         <v>2162</v>
@@ -23976,7 +23976,7 @@
     </row>
     <row r="455" spans="1:12">
       <c r="A455" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B455" t="s">
         <v>493</v>
@@ -23997,7 +23997,7 @@
         <v>1563</v>
       </c>
       <c r="I455" t="s">
-        <v>1653</v>
+        <v>1652</v>
       </c>
       <c r="J455" t="s">
         <v>2164</v>
@@ -24081,7 +24081,7 @@
     </row>
     <row r="458" spans="1:12">
       <c r="A458" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B458" t="s">
         <v>496</v>
@@ -24102,7 +24102,7 @@
         <v>1563</v>
       </c>
       <c r="I458" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
       <c r="J458" t="s">
         <v>2167</v>
@@ -24116,7 +24116,7 @@
     </row>
     <row r="459" spans="1:12">
       <c r="A459" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B459" t="s">
         <v>497</v>
@@ -24137,7 +24137,7 @@
         <v>1563</v>
       </c>
       <c r="I459" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
       <c r="J459" t="s">
         <v>2168</v>
@@ -24186,7 +24186,7 @@
     </row>
     <row r="461" spans="1:12">
       <c r="A461" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B461" t="s">
         <v>499</v>
@@ -24207,7 +24207,7 @@
         <v>1563</v>
       </c>
       <c r="I461" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
       <c r="J461" t="s">
         <v>2170</v>
@@ -24312,7 +24312,7 @@
         <v>1563</v>
       </c>
       <c r="I464" t="s">
-        <v>1667</v>
+        <v>1666</v>
       </c>
       <c r="J464" t="s">
         <v>2173</v>
@@ -24326,7 +24326,7 @@
     </row>
     <row r="465" spans="1:12">
       <c r="A465" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B465" t="s">
         <v>503</v>
@@ -24347,7 +24347,7 @@
         <v>1563</v>
       </c>
       <c r="I465" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
       <c r="J465" t="s">
         <v>2174</v>
@@ -24361,7 +24361,7 @@
     </row>
     <row r="466" spans="1:12">
       <c r="A466" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="B466" t="s">
         <v>504</v>
@@ -24396,7 +24396,7 @@
     </row>
     <row r="467" spans="1:12">
       <c r="A467" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="B467" t="s">
         <v>505</v>
@@ -24431,7 +24431,7 @@
     </row>
     <row r="468" spans="1:12">
       <c r="A468" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="B468" t="s">
         <v>506</v>
@@ -24466,7 +24466,7 @@
     </row>
     <row r="469" spans="1:12">
       <c r="A469" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="B469" t="s">
         <v>507</v>
@@ -24501,7 +24501,7 @@
     </row>
     <row r="470" spans="1:12">
       <c r="A470" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="B470" t="s">
         <v>508</v>
@@ -24536,7 +24536,7 @@
     </row>
     <row r="471" spans="1:12">
       <c r="A471" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="B471" t="s">
         <v>509</v>
@@ -24571,7 +24571,7 @@
     </row>
     <row r="472" spans="1:12">
       <c r="A472" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="B472" t="s">
         <v>510</v>
@@ -24606,7 +24606,7 @@
     </row>
     <row r="473" spans="1:12">
       <c r="A473" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="B473" t="s">
         <v>511</v>
@@ -24641,7 +24641,7 @@
     </row>
     <row r="474" spans="1:12">
       <c r="A474" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="B474" t="s">
         <v>512</v>
@@ -24676,7 +24676,7 @@
     </row>
     <row r="475" spans="1:12">
       <c r="A475" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="B475" t="s">
         <v>513</v>
@@ -24711,7 +24711,7 @@
     </row>
     <row r="476" spans="1:12">
       <c r="A476" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="B476" t="s">
         <v>514</v>
@@ -24746,7 +24746,7 @@
     </row>
     <row r="477" spans="1:12">
       <c r="A477" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="B477" t="s">
         <v>515</v>
@@ -24781,7 +24781,7 @@
     </row>
     <row r="478" spans="1:12">
       <c r="A478" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="B478" t="s">
         <v>516</v>
@@ -24816,7 +24816,7 @@
     </row>
     <row r="479" spans="1:12">
       <c r="A479" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="B479" t="s">
         <v>517</v>
@@ -24851,7 +24851,7 @@
     </row>
     <row r="480" spans="1:12">
       <c r="A480" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="B480" t="s">
         <v>518</v>
@@ -24886,7 +24886,7 @@
     </row>
     <row r="481" spans="1:12">
       <c r="A481" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="B481" t="s">
         <v>519</v>
@@ -24921,7 +24921,7 @@
     </row>
     <row r="482" spans="1:12">
       <c r="A482" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="B482" t="s">
         <v>520</v>
@@ -24956,7 +24956,7 @@
     </row>
     <row r="483" spans="1:12">
       <c r="A483" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="B483" t="s">
         <v>521</v>
@@ -24991,7 +24991,7 @@
     </row>
     <row r="484" spans="1:12">
       <c r="A484" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="B484" t="s">
         <v>522</v>
@@ -25026,7 +25026,7 @@
     </row>
     <row r="485" spans="1:12">
       <c r="A485" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B485" t="s">
         <v>523</v>
@@ -25047,7 +25047,7 @@
         <v>1563</v>
       </c>
       <c r="I485" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="J485" t="s">
         <v>2194</v>
@@ -25096,7 +25096,7 @@
     </row>
     <row r="487" spans="1:12">
       <c r="A487" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B487" t="s">
         <v>525</v>
@@ -25117,7 +25117,7 @@
         <v>1563</v>
       </c>
       <c r="I487" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
       <c r="J487" t="s">
         <v>2196</v>
@@ -25131,7 +25131,7 @@
     </row>
     <row r="488" spans="1:12">
       <c r="A488" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B488" t="s">
         <v>526</v>
@@ -25152,7 +25152,7 @@
         <v>1563</v>
       </c>
       <c r="I488" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
       <c r="J488" t="s">
         <v>2196</v>
@@ -25166,7 +25166,7 @@
     </row>
     <row r="489" spans="1:12">
       <c r="A489" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B489" t="s">
         <v>527</v>
@@ -25187,7 +25187,7 @@
         <v>1563</v>
       </c>
       <c r="I489" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
       <c r="J489" t="s">
         <v>2196</v>
@@ -25271,7 +25271,7 @@
     </row>
     <row r="492" spans="1:12">
       <c r="A492" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B492" t="s">
         <v>529</v>
@@ -25292,7 +25292,7 @@
         <v>1563</v>
       </c>
       <c r="I492" t="s">
-        <v>1653</v>
+        <v>1652</v>
       </c>
       <c r="J492" t="s">
         <v>2198</v>
@@ -25379,7 +25379,7 @@
     </row>
     <row r="495" spans="1:12">
       <c r="A495" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B495" t="s">
         <v>532</v>
@@ -25414,7 +25414,7 @@
     </row>
     <row r="496" spans="1:12">
       <c r="A496" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B496" t="s">
         <v>533</v>
@@ -25484,7 +25484,7 @@
     </row>
     <row r="498" spans="1:12">
       <c r="A498" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B498" t="s">
         <v>535</v>
@@ -25519,7 +25519,7 @@
     </row>
     <row r="499" spans="1:12">
       <c r="A499" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B499" t="s">
         <v>536</v>
@@ -25540,7 +25540,7 @@
         <v>1563</v>
       </c>
       <c r="I499" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="J499" t="s">
         <v>2205</v>
@@ -25648,7 +25648,7 @@
         <v>1563</v>
       </c>
       <c r="I502" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
       <c r="J502" t="s">
         <v>2208</v>
@@ -25697,7 +25697,7 @@
     </row>
     <row r="504" spans="1:12">
       <c r="A504" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B504" t="s">
         <v>541</v>
@@ -25718,7 +25718,7 @@
         <v>1563</v>
       </c>
       <c r="I504" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
       <c r="J504" t="s">
         <v>2210</v>
@@ -25802,7 +25802,7 @@
     </row>
     <row r="507" spans="1:12">
       <c r="A507" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B507" t="s">
         <v>544</v>
@@ -25823,7 +25823,7 @@
         <v>1563</v>
       </c>
       <c r="I507" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
       <c r="J507" t="s">
         <v>2213</v>
@@ -25837,7 +25837,7 @@
     </row>
     <row r="508" spans="1:12">
       <c r="A508" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B508" t="s">
         <v>545</v>
@@ -25896,7 +25896,7 @@
         <v>1572</v>
       </c>
       <c r="I509" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
       <c r="J509" t="s">
         <v>2215</v>
@@ -25910,7 +25910,7 @@
     </row>
     <row r="510" spans="1:12">
       <c r="A510" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B510" t="s">
         <v>547</v>
@@ -25931,7 +25931,7 @@
         <v>1563</v>
       </c>
       <c r="I510" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
       <c r="J510" t="s">
         <v>2216</v>
@@ -25945,7 +25945,7 @@
     </row>
     <row r="511" spans="1:12">
       <c r="A511" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B511" t="s">
         <v>548</v>
@@ -25966,7 +25966,7 @@
         <v>1563</v>
       </c>
       <c r="I511" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
       <c r="J511" t="s">
         <v>2217</v>
@@ -26015,7 +26015,7 @@
     </row>
     <row r="513" spans="1:12">
       <c r="A513" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B513" t="s">
         <v>550</v>
@@ -26085,7 +26085,7 @@
     </row>
     <row r="515" spans="1:12">
       <c r="A515" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B515" t="s">
         <v>552</v>
@@ -26120,7 +26120,7 @@
     </row>
     <row r="516" spans="1:12">
       <c r="A516" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B516" t="s">
         <v>553</v>
@@ -26225,7 +26225,7 @@
     </row>
     <row r="519" spans="1:12">
       <c r="A519" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B519" t="s">
         <v>556</v>
@@ -26260,7 +26260,7 @@
     </row>
     <row r="520" spans="1:12">
       <c r="A520" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="B520" t="s">
         <v>557</v>
@@ -26295,7 +26295,7 @@
     </row>
     <row r="521" spans="1:12">
       <c r="A521" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B521" t="s">
         <v>558</v>
@@ -26470,7 +26470,7 @@
     </row>
     <row r="526" spans="1:12">
       <c r="A526" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B526" t="s">
         <v>563</v>
@@ -26491,7 +26491,7 @@
         <v>1563</v>
       </c>
       <c r="I526" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
       <c r="J526" t="s">
         <v>2232</v>
@@ -26505,7 +26505,7 @@
     </row>
     <row r="527" spans="1:12">
       <c r="A527" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B527" t="s">
         <v>564</v>
@@ -26526,7 +26526,7 @@
         <v>1563</v>
       </c>
       <c r="I527" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="J527" t="s">
         <v>2233</v>
@@ -26610,7 +26610,7 @@
     </row>
     <row r="530" spans="1:12">
       <c r="A530" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B530" t="s">
         <v>567</v>
@@ -26631,7 +26631,7 @@
         <v>1563</v>
       </c>
       <c r="I530" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
       <c r="J530" t="s">
         <v>2236</v>
@@ -26645,7 +26645,7 @@
     </row>
     <row r="531" spans="1:12">
       <c r="A531" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B531" t="s">
         <v>568</v>
@@ -26666,7 +26666,7 @@
         <v>1563</v>
       </c>
       <c r="I531" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
       <c r="J531" t="s">
         <v>2237</v>
@@ -26680,7 +26680,7 @@
     </row>
     <row r="532" spans="1:12">
       <c r="A532" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B532" t="s">
         <v>569</v>
@@ -26701,7 +26701,7 @@
         <v>1563</v>
       </c>
       <c r="I532" t="s">
-        <v>1653</v>
+        <v>1652</v>
       </c>
       <c r="J532" t="s">
         <v>2238</v>
@@ -26736,7 +26736,7 @@
         <v>1563</v>
       </c>
       <c r="I533" t="s">
-        <v>1674</v>
+        <v>1673</v>
       </c>
       <c r="J533" t="s">
         <v>2239</v>
@@ -26861,7 +26861,7 @@
     </row>
     <row r="537" spans="1:12">
       <c r="A537" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B537" t="s">
         <v>573</v>
@@ -26896,7 +26896,7 @@
     </row>
     <row r="538" spans="1:12">
       <c r="A538" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B538" t="s">
         <v>574</v>
@@ -26917,7 +26917,7 @@
         <v>1563</v>
       </c>
       <c r="I538" t="s">
-        <v>1653</v>
+        <v>1652</v>
       </c>
       <c r="J538" t="s">
         <v>2243</v>
@@ -26966,7 +26966,7 @@
     </row>
     <row r="540" spans="1:12">
       <c r="A540" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B540" t="s">
         <v>576</v>
@@ -26987,7 +26987,7 @@
         <v>1563</v>
       </c>
       <c r="I540" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
       <c r="J540" t="s">
         <v>2245</v>
@@ -27001,7 +27001,7 @@
     </row>
     <row r="541" spans="1:12">
       <c r="A541" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B541" t="s">
         <v>577</v>
@@ -27022,7 +27022,7 @@
         <v>1563</v>
       </c>
       <c r="I541" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
       <c r="J541" t="s">
         <v>2246</v>
@@ -27071,7 +27071,7 @@
     </row>
     <row r="543" spans="1:12">
       <c r="A543" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B543" t="s">
         <v>579</v>
@@ -27092,7 +27092,7 @@
         <v>1563</v>
       </c>
       <c r="I543" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
       <c r="J543" t="s">
         <v>2248</v>
@@ -27141,7 +27141,7 @@
     </row>
     <row r="545" spans="1:12">
       <c r="A545" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B545" t="s">
         <v>581</v>
@@ -27162,7 +27162,7 @@
         <v>1563</v>
       </c>
       <c r="I545" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
       <c r="J545" t="s">
         <v>2250</v>
@@ -27211,7 +27211,7 @@
     </row>
     <row r="547" spans="1:12">
       <c r="A547" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B547" t="s">
         <v>583</v>
@@ -27235,7 +27235,7 @@
         <v>1575</v>
       </c>
       <c r="I547" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
       <c r="J547" t="s">
         <v>2252</v>
@@ -27395,7 +27395,7 @@
     </row>
     <row r="552" spans="1:12">
       <c r="A552" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B552" t="s">
         <v>588</v>
@@ -27416,7 +27416,7 @@
         <v>1563</v>
       </c>
       <c r="I552" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
       <c r="J552" t="s">
         <v>2257</v>
@@ -27465,7 +27465,7 @@
     </row>
     <row r="554" spans="1:12">
       <c r="A554" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B554" t="s">
         <v>590</v>
@@ -27486,7 +27486,7 @@
         <v>1563</v>
       </c>
       <c r="I554" t="s">
-        <v>1653</v>
+        <v>1652</v>
       </c>
       <c r="J554" t="s">
         <v>2259</v>
@@ -27500,7 +27500,7 @@
     </row>
     <row r="555" spans="1:12">
       <c r="A555" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B555" t="s">
         <v>591</v>
@@ -27535,7 +27535,7 @@
     </row>
     <row r="556" spans="1:12">
       <c r="A556" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B556" t="s">
         <v>592</v>
@@ -27556,7 +27556,7 @@
         <v>1563</v>
       </c>
       <c r="I556" t="s">
-        <v>1653</v>
+        <v>1652</v>
       </c>
       <c r="J556" t="s">
         <v>2261</v>
@@ -27570,7 +27570,7 @@
     </row>
     <row r="557" spans="1:12">
       <c r="A557" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B557" t="s">
         <v>593</v>
@@ -27605,7 +27605,7 @@
     </row>
     <row r="558" spans="1:12">
       <c r="A558" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B558" t="s">
         <v>594</v>
@@ -27626,7 +27626,7 @@
         <v>1563</v>
       </c>
       <c r="I558" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="J558" t="s">
         <v>2263</v>
@@ -27640,7 +27640,7 @@
     </row>
     <row r="559" spans="1:12">
       <c r="A559" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B559" t="s">
         <v>595</v>
@@ -27661,7 +27661,7 @@
         <v>1563</v>
       </c>
       <c r="I559" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
       <c r="J559" t="s">
         <v>2264</v>
@@ -27675,7 +27675,7 @@
     </row>
     <row r="560" spans="1:12">
       <c r="A560" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B560" t="s">
         <v>596</v>
@@ -27696,7 +27696,7 @@
         <v>1563</v>
       </c>
       <c r="I560" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
       <c r="J560" t="s">
         <v>2265</v>
@@ -27745,7 +27745,7 @@
     </row>
     <row r="562" spans="1:12">
       <c r="A562" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B562" t="s">
         <v>598</v>
@@ -27766,7 +27766,7 @@
         <v>1563</v>
       </c>
       <c r="I562" t="s">
-        <v>1653</v>
+        <v>1652</v>
       </c>
       <c r="J562" t="s">
         <v>2149</v>
@@ -27780,7 +27780,7 @@
     </row>
     <row r="563" spans="1:12">
       <c r="A563" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B563" t="s">
         <v>599</v>
@@ -27853,7 +27853,7 @@
     </row>
     <row r="565" spans="1:12">
       <c r="A565" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B565" t="s">
         <v>601</v>
@@ -27996,7 +27996,7 @@
     </row>
     <row r="569" spans="1:12">
       <c r="A569" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B569" t="s">
         <v>605</v>
@@ -28017,7 +28017,7 @@
         <v>1563</v>
       </c>
       <c r="I569" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="J569" t="s">
         <v>2273</v>
@@ -28101,7 +28101,7 @@
     </row>
     <row r="572" spans="1:12">
       <c r="A572" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B572" t="s">
         <v>608</v>
@@ -28122,7 +28122,7 @@
         <v>1563</v>
       </c>
       <c r="I572" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
       <c r="J572" t="s">
         <v>2276</v>
@@ -28195,7 +28195,7 @@
         <v>1563</v>
       </c>
       <c r="I574" t="s">
-        <v>1682</v>
+        <v>1681</v>
       </c>
       <c r="J574" t="s">
         <v>2278</v>
@@ -28244,7 +28244,7 @@
     </row>
     <row r="576" spans="1:12">
       <c r="A576" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B576" t="s">
         <v>612</v>
@@ -28279,7 +28279,7 @@
     </row>
     <row r="577" spans="1:12">
       <c r="A577" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B577" t="s">
         <v>613</v>
@@ -28314,7 +28314,7 @@
     </row>
     <row r="578" spans="1:12">
       <c r="A578" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B578" t="s">
         <v>614</v>
@@ -28349,7 +28349,7 @@
     </row>
     <row r="579" spans="1:12">
       <c r="A579" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B579" t="s">
         <v>615</v>
@@ -28370,7 +28370,7 @@
         <v>1563</v>
       </c>
       <c r="I579" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
       <c r="J579" t="s">
         <v>2283</v>
@@ -28384,7 +28384,7 @@
     </row>
     <row r="580" spans="1:12">
       <c r="A580" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B580" t="s">
         <v>616</v>
@@ -28405,7 +28405,7 @@
         <v>1563</v>
       </c>
       <c r="I580" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
       <c r="J580" t="s">
         <v>2284</v>
@@ -28524,7 +28524,7 @@
     </row>
     <row r="584" spans="1:12">
       <c r="A584" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B584" t="s">
         <v>620</v>
@@ -28594,7 +28594,7 @@
     </row>
     <row r="586" spans="1:12">
       <c r="A586" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B586" t="s">
         <v>622</v>
@@ -28985,7 +28985,7 @@
     </row>
     <row r="597" spans="1:12">
       <c r="A597" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="B597" t="s">
         <v>633</v>
@@ -29041,7 +29041,7 @@
         <v>1563</v>
       </c>
       <c r="I598" t="s">
-        <v>1666</v>
+        <v>1665</v>
       </c>
       <c r="J598" t="s">
         <v>2302</v>
@@ -29111,7 +29111,7 @@
         <v>1563</v>
       </c>
       <c r="I600" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
       <c r="J600" t="s">
         <v>2304</v>
@@ -29146,7 +29146,7 @@
         <v>1563</v>
       </c>
       <c r="I601" t="s">
-        <v>1667</v>
+        <v>1666</v>
       </c>
       <c r="J601" t="s">
         <v>2305</v>
@@ -29198,7 +29198,7 @@
     </row>
     <row r="603" spans="1:12">
       <c r="A603" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B603" t="s">
         <v>639</v>
@@ -29233,7 +29233,7 @@
     </row>
     <row r="604" spans="1:12">
       <c r="A604" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B604" t="s">
         <v>640</v>
@@ -29268,7 +29268,7 @@
     </row>
     <row r="605" spans="1:12">
       <c r="A605" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B605" t="s">
         <v>641</v>
@@ -29303,7 +29303,7 @@
     </row>
     <row r="606" spans="1:12">
       <c r="A606" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B606" t="s">
         <v>642</v>
@@ -29446,7 +29446,7 @@
     </row>
     <row r="610" spans="1:12">
       <c r="A610" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B610" t="s">
         <v>646</v>
@@ -29467,7 +29467,7 @@
         <v>1563</v>
       </c>
       <c r="I610" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
       <c r="J610" t="s">
         <v>2314</v>
@@ -29557,7 +29557,7 @@
     </row>
     <row r="613" spans="1:12">
       <c r="A613" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B613" t="s">
         <v>649</v>
@@ -29578,7 +29578,7 @@
         <v>1563</v>
       </c>
       <c r="I613" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
       <c r="J613" t="s">
         <v>2317</v>
@@ -29627,7 +29627,7 @@
     </row>
     <row r="615" spans="1:12">
       <c r="A615" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B615" t="s">
         <v>651</v>
@@ -29648,7 +29648,7 @@
         <v>1563</v>
       </c>
       <c r="I615" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
       <c r="J615" t="s">
         <v>2319</v>
@@ -29697,7 +29697,7 @@
     </row>
     <row r="617" spans="1:12">
       <c r="A617" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="B617" t="s">
         <v>653</v>
@@ -29732,7 +29732,7 @@
     </row>
     <row r="618" spans="1:12">
       <c r="A618" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="B618" t="s">
         <v>654</v>
@@ -29767,7 +29767,7 @@
     </row>
     <row r="619" spans="1:12">
       <c r="A619" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B619" t="s">
         <v>655</v>
@@ -29802,7 +29802,7 @@
     </row>
     <row r="620" spans="1:12">
       <c r="A620" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B620" t="s">
         <v>656</v>
@@ -29837,7 +29837,7 @@
     </row>
     <row r="621" spans="1:12">
       <c r="A621" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B621" t="s">
         <v>657</v>
@@ -29907,7 +29907,7 @@
     </row>
     <row r="623" spans="1:12">
       <c r="A623" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B623" t="s">
         <v>659</v>
@@ -29928,7 +29928,7 @@
         <v>1563</v>
       </c>
       <c r="I623" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="J623" t="s">
         <v>2326</v>
@@ -29942,7 +29942,7 @@
     </row>
     <row r="624" spans="1:12">
       <c r="A624" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="B624" t="s">
         <v>660</v>
@@ -29977,7 +29977,7 @@
     </row>
     <row r="625" spans="1:12">
       <c r="A625" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="B625" t="s">
         <v>661</v>
@@ -30036,7 +30036,7 @@
         <v>1551</v>
       </c>
       <c r="I626" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
       <c r="J626" t="s">
         <v>2329</v>
@@ -30050,7 +30050,7 @@
     </row>
     <row r="627" spans="1:12">
       <c r="A627" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B627" t="s">
         <v>663</v>
@@ -30071,7 +30071,7 @@
         <v>1563</v>
       </c>
       <c r="I627" t="s">
-        <v>1653</v>
+        <v>1652</v>
       </c>
       <c r="J627" t="s">
         <v>2330</v>
@@ -30120,7 +30120,7 @@
     </row>
     <row r="629" spans="1:12">
       <c r="A629" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B629" t="s">
         <v>665</v>
@@ -30141,7 +30141,7 @@
         <v>1563</v>
       </c>
       <c r="I629" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
       <c r="J629" t="s">
         <v>2332</v>
@@ -30266,7 +30266,7 @@
     </row>
     <row r="633" spans="1:12">
       <c r="A633" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B633" t="s">
         <v>669</v>
@@ -30287,7 +30287,7 @@
         <v>1563</v>
       </c>
       <c r="I633" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
       <c r="J633" t="s">
         <v>2336</v>
@@ -30339,7 +30339,7 @@
     </row>
     <row r="635" spans="1:12">
       <c r="A635" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B635" t="s">
         <v>671</v>
@@ -30374,7 +30374,7 @@
     </row>
     <row r="636" spans="1:12">
       <c r="A636" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="B636" t="s">
         <v>672</v>
@@ -30409,7 +30409,7 @@
     </row>
     <row r="637" spans="1:12">
       <c r="A637" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B637" t="s">
         <v>673</v>
@@ -30444,7 +30444,7 @@
     </row>
     <row r="638" spans="1:12">
       <c r="A638" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B638" t="s">
         <v>674</v>
@@ -30465,7 +30465,7 @@
         <v>1563</v>
       </c>
       <c r="I638" t="s">
-        <v>1653</v>
+        <v>1652</v>
       </c>
       <c r="J638" t="s">
         <v>2340</v>
@@ -30479,7 +30479,7 @@
     </row>
     <row r="639" spans="1:12">
       <c r="A639" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="B639" t="s">
         <v>675</v>
@@ -30555,7 +30555,7 @@
     </row>
     <row r="641" spans="1:12">
       <c r="A641" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B641" t="s">
         <v>677</v>
@@ -30576,7 +30576,7 @@
         <v>1563</v>
       </c>
       <c r="I641" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
       <c r="J641" t="s">
         <v>2343</v>
@@ -30628,7 +30628,7 @@
     </row>
     <row r="643" spans="1:12">
       <c r="A643" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B643" t="s">
         <v>679</v>
@@ -30701,7 +30701,7 @@
     </row>
     <row r="645" spans="1:12">
       <c r="A645" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="B645" t="s">
         <v>681</v>
@@ -30736,7 +30736,7 @@
     </row>
     <row r="646" spans="1:12">
       <c r="A646" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="B646" t="s">
         <v>682</v>
@@ -30771,7 +30771,7 @@
     </row>
     <row r="647" spans="1:12">
       <c r="A647" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B647" t="s">
         <v>683</v>
@@ -30806,7 +30806,7 @@
     </row>
     <row r="648" spans="1:12">
       <c r="A648" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B648" t="s">
         <v>684</v>
@@ -30827,7 +30827,7 @@
         <v>1563</v>
       </c>
       <c r="I648" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
       <c r="J648" t="s">
         <v>2350</v>
@@ -30841,7 +30841,7 @@
     </row>
     <row r="649" spans="1:12">
       <c r="A649" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B649" t="s">
         <v>685</v>
@@ -30862,7 +30862,7 @@
         <v>1563</v>
       </c>
       <c r="I649" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="J649" t="s">
         <v>2351</v>
@@ -30876,7 +30876,7 @@
     </row>
     <row r="650" spans="1:12">
       <c r="A650" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="B650" t="s">
         <v>686</v>
@@ -30911,7 +30911,7 @@
     </row>
     <row r="651" spans="1:12">
       <c r="A651" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B651" t="s">
         <v>687</v>
@@ -30946,7 +30946,7 @@
     </row>
     <row r="652" spans="1:12">
       <c r="A652" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="B652" t="s">
         <v>688</v>
@@ -30984,7 +30984,7 @@
     </row>
     <row r="653" spans="1:12">
       <c r="A653" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B653" t="s">
         <v>689</v>
@@ -31008,7 +31008,7 @@
         <v>1587</v>
       </c>
       <c r="I653" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
       <c r="J653" t="s">
         <v>2355</v>
@@ -31022,7 +31022,7 @@
     </row>
     <row r="654" spans="1:12">
       <c r="A654" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B654" t="s">
         <v>690</v>
@@ -31046,7 +31046,7 @@
         <v>1591</v>
       </c>
       <c r="I654" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
       <c r="J654" t="s">
         <v>2356</v>
@@ -31060,7 +31060,7 @@
     </row>
     <row r="655" spans="1:12">
       <c r="A655" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="B655" t="s">
         <v>691</v>
@@ -31092,7 +31092,7 @@
     </row>
     <row r="656" spans="1:12">
       <c r="A656" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="B656" t="s">
         <v>692</v>

--- a/BacklogGATEAutoCompleto.xlsx
+++ b/BacklogGATEAutoCompleto.xlsx
@@ -29732,7 +29732,7 @@
     </row>
     <row r="618" spans="1:12">
       <c r="A618" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="B618" t="s">
         <v>654</v>
@@ -29753,7 +29753,7 @@
         <v>1563</v>
       </c>
       <c r="I618" t="s">
-        <v>1707</v>
+        <v>1596</v>
       </c>
       <c r="J618" t="s">
         <v>2322</v>
@@ -30479,7 +30479,7 @@
     </row>
     <row r="639" spans="1:12">
       <c r="A639" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="B639" t="s">
         <v>675</v>
@@ -30494,7 +30494,7 @@
         <v>5</v>
       </c>
       <c r="F639" t="s">
-        <v>1558</v>
+        <v>1560</v>
       </c>
       <c r="G639" t="s">
         <v>1565</v>
@@ -30503,7 +30503,7 @@
         <v>1586</v>
       </c>
       <c r="I639" t="s">
-        <v>1707</v>
+        <v>1669</v>
       </c>
       <c r="J639" t="s">
         <v>2341</v>

--- a/BacklogGATEAutoCompleto.xlsx
+++ b/BacklogGATEAutoCompleto.xlsx
@@ -8052,7 +8052,7 @@
         <v>1338</v>
       </c>
       <c r="E2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="F2" t="s">
         <v>1549</v>
@@ -8087,7 +8087,7 @@
         <v>1339</v>
       </c>
       <c r="E3">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="F3" t="s">
         <v>1549</v>
@@ -8122,7 +8122,7 @@
         <v>1340</v>
       </c>
       <c r="E4">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="F4" t="s">
         <v>1549</v>
@@ -8157,7 +8157,7 @@
         <v>1341</v>
       </c>
       <c r="E5">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="F5" t="s">
         <v>1549</v>
@@ -8192,7 +8192,7 @@
         <v>1342</v>
       </c>
       <c r="E6">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F6" t="s">
         <v>1549</v>
@@ -8227,7 +8227,7 @@
         <v>1343</v>
       </c>
       <c r="E7">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F7" t="s">
         <v>1549</v>
@@ -8262,7 +8262,7 @@
         <v>1344</v>
       </c>
       <c r="E8">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="F8" t="s">
         <v>1549</v>
@@ -8297,7 +8297,7 @@
         <v>1345</v>
       </c>
       <c r="E9">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="F9" t="s">
         <v>1549</v>
@@ -8332,7 +8332,7 @@
         <v>1346</v>
       </c>
       <c r="E10">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="F10" t="s">
         <v>1549</v>
@@ -8367,7 +8367,7 @@
         <v>1346</v>
       </c>
       <c r="E11">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="F11" t="s">
         <v>1549</v>
@@ -8402,7 +8402,7 @@
         <v>1347</v>
       </c>
       <c r="E12">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="F12" t="s">
         <v>1549</v>
@@ -8437,7 +8437,7 @@
         <v>1348</v>
       </c>
       <c r="E13">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F13" t="s">
         <v>1549</v>
@@ -8472,7 +8472,7 @@
         <v>1349</v>
       </c>
       <c r="E14">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="F14" t="s">
         <v>1549</v>
@@ -8507,7 +8507,7 @@
         <v>1349</v>
       </c>
       <c r="E15">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="F15" t="s">
         <v>1549</v>
@@ -8542,7 +8542,7 @@
         <v>1350</v>
       </c>
       <c r="E16">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="F16" t="s">
         <v>1549</v>
@@ -8577,7 +8577,7 @@
         <v>1350</v>
       </c>
       <c r="E17">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="F17" t="s">
         <v>1549</v>
@@ -8612,7 +8612,7 @@
         <v>1351</v>
       </c>
       <c r="E18">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F18" t="s">
         <v>1549</v>
@@ -8647,7 +8647,7 @@
         <v>1352</v>
       </c>
       <c r="E19">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="F19" t="s">
         <v>1549</v>
@@ -8682,7 +8682,7 @@
         <v>1353</v>
       </c>
       <c r="E20">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="F20" t="s">
         <v>1549</v>
@@ -8717,7 +8717,7 @@
         <v>1354</v>
       </c>
       <c r="E21">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="F21" t="s">
         <v>1549</v>
@@ -8752,7 +8752,7 @@
         <v>1355</v>
       </c>
       <c r="E22">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F22" t="s">
         <v>1549</v>
@@ -8790,7 +8790,7 @@
         <v>1356</v>
       </c>
       <c r="E23">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F23" t="s">
         <v>1549</v>
@@ -8825,7 +8825,7 @@
         <v>1357</v>
       </c>
       <c r="E24">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F24" t="s">
         <v>1549</v>
@@ -8860,7 +8860,7 @@
         <v>1358</v>
       </c>
       <c r="E25">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F25" t="s">
         <v>1549</v>
@@ -8895,7 +8895,7 @@
         <v>1359</v>
       </c>
       <c r="E26">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="F26" t="s">
         <v>1549</v>
@@ -8930,7 +8930,7 @@
         <v>1360</v>
       </c>
       <c r="E27">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F27" t="s">
         <v>1549</v>
@@ -8965,7 +8965,7 @@
         <v>1361</v>
       </c>
       <c r="E28">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F28" t="s">
         <v>1549</v>
@@ -9000,7 +9000,7 @@
         <v>1362</v>
       </c>
       <c r="E29">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F29" t="s">
         <v>1549</v>
@@ -9035,7 +9035,7 @@
         <v>1363</v>
       </c>
       <c r="E30">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F30" t="s">
         <v>1549</v>
@@ -9070,7 +9070,7 @@
         <v>1364</v>
       </c>
       <c r="E31">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F31" t="s">
         <v>1549</v>
@@ -9105,7 +9105,7 @@
         <v>1365</v>
       </c>
       <c r="E32">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F32" t="s">
         <v>1549</v>
@@ -9140,7 +9140,7 @@
         <v>1366</v>
       </c>
       <c r="E33">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F33" t="s">
         <v>1549</v>
@@ -9175,7 +9175,7 @@
         <v>1366</v>
       </c>
       <c r="E34">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F34" t="s">
         <v>1549</v>
@@ -9210,7 +9210,7 @@
         <v>1367</v>
       </c>
       <c r="E35">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F35" t="s">
         <v>1549</v>
@@ -9245,7 +9245,7 @@
         <v>1368</v>
       </c>
       <c r="E36">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F36" t="s">
         <v>1549</v>
@@ -9280,7 +9280,7 @@
         <v>1369</v>
       </c>
       <c r="E37">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="F37" t="s">
         <v>1549</v>
@@ -9315,7 +9315,7 @@
         <v>1370</v>
       </c>
       <c r="E38">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F38" t="s">
         <v>1549</v>
@@ -9350,7 +9350,7 @@
         <v>1371</v>
       </c>
       <c r="E39">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F39" t="s">
         <v>1549</v>
@@ -9385,7 +9385,7 @@
         <v>1371</v>
       </c>
       <c r="E40">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F40" t="s">
         <v>1549</v>
@@ -9420,7 +9420,7 @@
         <v>1372</v>
       </c>
       <c r="E41">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F41" t="s">
         <v>1549</v>
@@ -9455,7 +9455,7 @@
         <v>1373</v>
       </c>
       <c r="E42">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F42" t="s">
         <v>1549</v>
@@ -9490,7 +9490,7 @@
         <v>1374</v>
       </c>
       <c r="E43">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F43" t="s">
         <v>1549</v>
@@ -9525,7 +9525,7 @@
         <v>1374</v>
       </c>
       <c r="E44">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F44" t="s">
         <v>1549</v>
@@ -9560,7 +9560,7 @@
         <v>1375</v>
       </c>
       <c r="E45">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F45" t="s">
         <v>1549</v>
@@ -9595,7 +9595,7 @@
         <v>1375</v>
       </c>
       <c r="E46">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F46" t="s">
         <v>1549</v>
@@ -9630,7 +9630,7 @@
         <v>1376</v>
       </c>
       <c r="E47">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F47" t="s">
         <v>1549</v>
@@ -9665,7 +9665,7 @@
         <v>1377</v>
       </c>
       <c r="E48">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F48" t="s">
         <v>1549</v>
@@ -9700,7 +9700,7 @@
         <v>1378</v>
       </c>
       <c r="E49">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F49" t="s">
         <v>1549</v>
@@ -9735,7 +9735,7 @@
         <v>1379</v>
       </c>
       <c r="E50">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F50" t="s">
         <v>1549</v>
@@ -9770,7 +9770,7 @@
         <v>1379</v>
       </c>
       <c r="E51">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F51" t="s">
         <v>1549</v>
@@ -9805,7 +9805,7 @@
         <v>1380</v>
       </c>
       <c r="E52">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F52" t="s">
         <v>1549</v>
@@ -9840,7 +9840,7 @@
         <v>1381</v>
       </c>
       <c r="E53">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F53" t="s">
         <v>1549</v>
@@ -9875,7 +9875,7 @@
         <v>1382</v>
       </c>
       <c r="E54">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F54" t="s">
         <v>1549</v>
@@ -9910,7 +9910,7 @@
         <v>1383</v>
       </c>
       <c r="E55">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F55" t="s">
         <v>1549</v>
@@ -9945,7 +9945,7 @@
         <v>1384</v>
       </c>
       <c r="E56">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F56" t="s">
         <v>1549</v>
@@ -9980,7 +9980,7 @@
         <v>1385</v>
       </c>
       <c r="E57">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F57" t="s">
         <v>1549</v>
@@ -10015,7 +10015,7 @@
         <v>1386</v>
       </c>
       <c r="E58">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F58" t="s">
         <v>1549</v>
@@ -10050,7 +10050,7 @@
         <v>1386</v>
       </c>
       <c r="E59">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F59" t="s">
         <v>1549</v>
@@ -10085,7 +10085,7 @@
         <v>1386</v>
       </c>
       <c r="E60">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F60" t="s">
         <v>1549</v>
@@ -10120,7 +10120,7 @@
         <v>1387</v>
       </c>
       <c r="E61">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F61" t="s">
         <v>1549</v>
@@ -10155,7 +10155,7 @@
         <v>1388</v>
       </c>
       <c r="E62">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F62" t="s">
         <v>1549</v>
@@ -10190,7 +10190,7 @@
         <v>1389</v>
       </c>
       <c r="E63">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F63" t="s">
         <v>1549</v>
@@ -10225,7 +10225,7 @@
         <v>1389</v>
       </c>
       <c r="E64">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F64" t="s">
         <v>1549</v>
@@ -10260,7 +10260,7 @@
         <v>1389</v>
       </c>
       <c r="E65">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F65" t="s">
         <v>1549</v>
@@ -10295,7 +10295,7 @@
         <v>1390</v>
       </c>
       <c r="E66">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F66" t="s">
         <v>1549</v>
@@ -10330,7 +10330,7 @@
         <v>1391</v>
       </c>
       <c r="E67">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F67" t="s">
         <v>1549</v>
@@ -10365,7 +10365,7 @@
         <v>1391</v>
       </c>
       <c r="E68">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F68" t="s">
         <v>1549</v>
@@ -10400,7 +10400,7 @@
         <v>1391</v>
       </c>
       <c r="E69">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F69" t="s">
         <v>1549</v>
@@ -10435,7 +10435,7 @@
         <v>1392</v>
       </c>
       <c r="E70">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F70" t="s">
         <v>1549</v>
@@ -10470,7 +10470,7 @@
         <v>1393</v>
       </c>
       <c r="E71">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F71" t="s">
         <v>1549</v>
@@ -10505,7 +10505,7 @@
         <v>1393</v>
       </c>
       <c r="E72">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F72" t="s">
         <v>1549</v>
@@ -10540,7 +10540,7 @@
         <v>1393</v>
       </c>
       <c r="E73">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F73" t="s">
         <v>1550</v>
@@ -10575,7 +10575,7 @@
         <v>1393</v>
       </c>
       <c r="E74">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F74" t="s">
         <v>1549</v>
@@ -10610,7 +10610,7 @@
         <v>1394</v>
       </c>
       <c r="E75">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F75" t="s">
         <v>1549</v>
@@ -10645,7 +10645,7 @@
         <v>1395</v>
       </c>
       <c r="E76">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F76" t="s">
         <v>1549</v>
@@ -10680,7 +10680,7 @@
         <v>1395</v>
       </c>
       <c r="E77">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F77" t="s">
         <v>1549</v>
@@ -10715,7 +10715,7 @@
         <v>1396</v>
       </c>
       <c r="E78">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F78" t="s">
         <v>1549</v>
@@ -10750,7 +10750,7 @@
         <v>1397</v>
       </c>
       <c r="E79">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F79" t="s">
         <v>1549</v>
@@ -10785,7 +10785,7 @@
         <v>1398</v>
       </c>
       <c r="E80">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F80" t="s">
         <v>1549</v>
@@ -10820,7 +10820,7 @@
         <v>1399</v>
       </c>
       <c r="E81">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F81" t="s">
         <v>1549</v>
@@ -10855,7 +10855,7 @@
         <v>1399</v>
       </c>
       <c r="E82">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F82" t="s">
         <v>1549</v>
@@ -10890,7 +10890,7 @@
         <v>1399</v>
       </c>
       <c r="E83">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F83" t="s">
         <v>1549</v>
@@ -10925,7 +10925,7 @@
         <v>1399</v>
       </c>
       <c r="E84">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F84" t="s">
         <v>1549</v>
@@ -10960,7 +10960,7 @@
         <v>1399</v>
       </c>
       <c r="E85">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F85" t="s">
         <v>1549</v>
@@ -10995,7 +10995,7 @@
         <v>1399</v>
       </c>
       <c r="E86">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F86" t="s">
         <v>1549</v>
@@ -11030,7 +11030,7 @@
         <v>1400</v>
       </c>
       <c r="E87">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F87" t="s">
         <v>1549</v>
@@ -11065,7 +11065,7 @@
         <v>1401</v>
       </c>
       <c r="E88">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F88" t="s">
         <v>1549</v>
@@ -11100,7 +11100,7 @@
         <v>1402</v>
       </c>
       <c r="E89">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F89" t="s">
         <v>1549</v>
@@ -11135,7 +11135,7 @@
         <v>1402</v>
       </c>
       <c r="E90">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F90" t="s">
         <v>1549</v>
@@ -11170,7 +11170,7 @@
         <v>1403</v>
       </c>
       <c r="E91">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F91" t="s">
         <v>1551</v>
@@ -11205,7 +11205,7 @@
         <v>1404</v>
       </c>
       <c r="E92">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F92" t="s">
         <v>1549</v>
@@ -11240,7 +11240,7 @@
         <v>1405</v>
       </c>
       <c r="E93">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F93" t="s">
         <v>1549</v>
@@ -11275,7 +11275,7 @@
         <v>1405</v>
       </c>
       <c r="E94">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F94" t="s">
         <v>1549</v>
@@ -11310,7 +11310,7 @@
         <v>1406</v>
       </c>
       <c r="E95">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F95" t="s">
         <v>1549</v>
@@ -11345,7 +11345,7 @@
         <v>1407</v>
       </c>
       <c r="E96">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F96" t="s">
         <v>1549</v>
@@ -11380,7 +11380,7 @@
         <v>1408</v>
       </c>
       <c r="E97">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F97" t="s">
         <v>1549</v>
@@ -11415,7 +11415,7 @@
         <v>1409</v>
       </c>
       <c r="E98">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F98" t="s">
         <v>1549</v>
@@ -11450,7 +11450,7 @@
         <v>1410</v>
       </c>
       <c r="E99">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F99" t="s">
         <v>1549</v>
@@ -11485,7 +11485,7 @@
         <v>1410</v>
       </c>
       <c r="E100">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F100" t="s">
         <v>1549</v>
@@ -11520,7 +11520,7 @@
         <v>1411</v>
       </c>
       <c r="E101">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F101" t="s">
         <v>1549</v>
@@ -11555,7 +11555,7 @@
         <v>1411</v>
       </c>
       <c r="E102">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F102" t="s">
         <v>1549</v>
@@ -11590,7 +11590,7 @@
         <v>1411</v>
       </c>
       <c r="E103">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F103" t="s">
         <v>1549</v>
@@ -11625,7 +11625,7 @@
         <v>1412</v>
       </c>
       <c r="E104">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F104" t="s">
         <v>1549</v>
@@ -11660,7 +11660,7 @@
         <v>1412</v>
       </c>
       <c r="E105">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F105" t="s">
         <v>1549</v>
@@ -11695,7 +11695,7 @@
         <v>1412</v>
       </c>
       <c r="E106">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F106" t="s">
         <v>1549</v>
@@ -11730,7 +11730,7 @@
         <v>1413</v>
       </c>
       <c r="E107">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F107" t="s">
         <v>1549</v>
@@ -11765,7 +11765,7 @@
         <v>1414</v>
       </c>
       <c r="E108">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F108" t="s">
         <v>1549</v>
@@ -11800,7 +11800,7 @@
         <v>1414</v>
       </c>
       <c r="E109">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F109" t="s">
         <v>1549</v>
@@ -11835,7 +11835,7 @@
         <v>1415</v>
       </c>
       <c r="E110">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F110" t="s">
         <v>1549</v>
@@ -11870,7 +11870,7 @@
         <v>1415</v>
       </c>
       <c r="E111">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F111" t="s">
         <v>1549</v>
@@ -11905,7 +11905,7 @@
         <v>1416</v>
       </c>
       <c r="E112">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F112" t="s">
         <v>1549</v>
@@ -11940,7 +11940,7 @@
         <v>1416</v>
       </c>
       <c r="E113">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F113" t="s">
         <v>1549</v>
@@ -11975,7 +11975,7 @@
         <v>1417</v>
       </c>
       <c r="E114">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F114" t="s">
         <v>1549</v>
@@ -12010,7 +12010,7 @@
         <v>1417</v>
       </c>
       <c r="E115">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F115" t="s">
         <v>1549</v>
@@ -12045,7 +12045,7 @@
         <v>1418</v>
       </c>
       <c r="E116">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F116" t="s">
         <v>1549</v>
@@ -12080,7 +12080,7 @@
         <v>1418</v>
       </c>
       <c r="E117">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F117" t="s">
         <v>1549</v>
@@ -12115,7 +12115,7 @@
         <v>1419</v>
       </c>
       <c r="E118">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F118" t="s">
         <v>1549</v>
@@ -12150,7 +12150,7 @@
         <v>1420</v>
       </c>
       <c r="E119">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F119" t="s">
         <v>1549</v>
@@ -12185,7 +12185,7 @@
         <v>1420</v>
       </c>
       <c r="E120">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F120" t="s">
         <v>1549</v>
@@ -12220,7 +12220,7 @@
         <v>1421</v>
       </c>
       <c r="E121">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F121" t="s">
         <v>1549</v>
@@ -12255,7 +12255,7 @@
         <v>1422</v>
       </c>
       <c r="E122">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F122" t="s">
         <v>1549</v>
@@ -12293,7 +12293,7 @@
         <v>1422</v>
       </c>
       <c r="E123">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F123" t="s">
         <v>1549</v>
@@ -12328,7 +12328,7 @@
         <v>1422</v>
       </c>
       <c r="E124">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F124" t="s">
         <v>1549</v>
@@ -12363,7 +12363,7 @@
         <v>1422</v>
       </c>
       <c r="E125">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F125" t="s">
         <v>1549</v>
@@ -12398,7 +12398,7 @@
         <v>1423</v>
       </c>
       <c r="E126">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F126" t="s">
         <v>1550</v>
@@ -12433,7 +12433,7 @@
         <v>1424</v>
       </c>
       <c r="E127">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F127" t="s">
         <v>1549</v>
@@ -12468,7 +12468,7 @@
         <v>1424</v>
       </c>
       <c r="E128">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F128" t="s">
         <v>1549</v>
@@ -12503,7 +12503,7 @@
         <v>1424</v>
       </c>
       <c r="E129">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F129" t="s">
         <v>1549</v>
@@ -12538,7 +12538,7 @@
         <v>1424</v>
       </c>
       <c r="E130">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F130" t="s">
         <v>1549</v>
@@ -12573,7 +12573,7 @@
         <v>1425</v>
       </c>
       <c r="E131">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F131" t="s">
         <v>1549</v>
@@ -12608,7 +12608,7 @@
         <v>1425</v>
       </c>
       <c r="E132">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F132" t="s">
         <v>1549</v>
@@ -12643,7 +12643,7 @@
         <v>1425</v>
       </c>
       <c r="E133">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F133" t="s">
         <v>1549</v>
@@ -12678,7 +12678,7 @@
         <v>1425</v>
       </c>
       <c r="E134">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F134" t="s">
         <v>1549</v>
@@ -12713,7 +12713,7 @@
         <v>1425</v>
       </c>
       <c r="E135">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F135" t="s">
         <v>1549</v>
@@ -12748,7 +12748,7 @@
         <v>1425</v>
       </c>
       <c r="E136">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F136" t="s">
         <v>1549</v>
@@ -12783,7 +12783,7 @@
         <v>1425</v>
       </c>
       <c r="E137">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F137" t="s">
         <v>1549</v>
@@ -12818,7 +12818,7 @@
         <v>1426</v>
       </c>
       <c r="E138">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F138" t="s">
         <v>1549</v>
@@ -12853,7 +12853,7 @@
         <v>1426</v>
       </c>
       <c r="E139">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F139" t="s">
         <v>1549</v>
@@ -12888,7 +12888,7 @@
         <v>1427</v>
       </c>
       <c r="E140">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F140" t="s">
         <v>1549</v>
@@ -12923,7 +12923,7 @@
         <v>1428</v>
       </c>
       <c r="E141">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F141" t="s">
         <v>1549</v>
@@ -12958,7 +12958,7 @@
         <v>1428</v>
       </c>
       <c r="E142">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F142" t="s">
         <v>1549</v>
@@ -12993,7 +12993,7 @@
         <v>1428</v>
       </c>
       <c r="E143">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F143" t="s">
         <v>1549</v>
@@ -13028,7 +13028,7 @@
         <v>1429</v>
       </c>
       <c r="E144">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F144" t="s">
         <v>1549</v>
@@ -13063,7 +13063,7 @@
         <v>1429</v>
       </c>
       <c r="E145">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F145" t="s">
         <v>1549</v>
@@ -13098,7 +13098,7 @@
         <v>1429</v>
       </c>
       <c r="E146">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F146" t="s">
         <v>1549</v>
@@ -13133,7 +13133,7 @@
         <v>1429</v>
       </c>
       <c r="E147">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F147" t="s">
         <v>1549</v>
@@ -13168,7 +13168,7 @@
         <v>1429</v>
       </c>
       <c r="E148">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F148" t="s">
         <v>1549</v>
@@ -13203,7 +13203,7 @@
         <v>1429</v>
       </c>
       <c r="E149">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F149" t="s">
         <v>1549</v>
@@ -13238,7 +13238,7 @@
         <v>1429</v>
       </c>
       <c r="E150">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F150" t="s">
         <v>1549</v>
@@ -13273,7 +13273,7 @@
         <v>1429</v>
       </c>
       <c r="E151">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F151" t="s">
         <v>1549</v>
@@ -13308,7 +13308,7 @@
         <v>1429</v>
       </c>
       <c r="E152">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F152" t="s">
         <v>1549</v>
@@ -13343,7 +13343,7 @@
         <v>1429</v>
       </c>
       <c r="E153">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F153" t="s">
         <v>1549</v>
@@ -13378,7 +13378,7 @@
         <v>1430</v>
       </c>
       <c r="E154">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F154" t="s">
         <v>1549</v>
@@ -13413,7 +13413,7 @@
         <v>1430</v>
       </c>
       <c r="E155">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F155" t="s">
         <v>1549</v>
@@ -13448,7 +13448,7 @@
         <v>1430</v>
       </c>
       <c r="E156">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F156" t="s">
         <v>1549</v>
@@ -13483,7 +13483,7 @@
         <v>1431</v>
       </c>
       <c r="E157">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F157" t="s">
         <v>1549</v>
@@ -13518,7 +13518,7 @@
         <v>1431</v>
       </c>
       <c r="E158">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F158" t="s">
         <v>1550</v>
@@ -13553,7 +13553,7 @@
         <v>1431</v>
       </c>
       <c r="E159">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F159" t="s">
         <v>1549</v>
@@ -13588,7 +13588,7 @@
         <v>1432</v>
       </c>
       <c r="E160">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F160" t="s">
         <v>1549</v>
@@ -13623,7 +13623,7 @@
         <v>1432</v>
       </c>
       <c r="E161">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F161" t="s">
         <v>1549</v>
@@ -13658,7 +13658,7 @@
         <v>1433</v>
       </c>
       <c r="E162">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F162" t="s">
         <v>1549</v>
@@ -13693,7 +13693,7 @@
         <v>1433</v>
       </c>
       <c r="E163">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F163" t="s">
         <v>1549</v>
@@ -13728,7 +13728,7 @@
         <v>1434</v>
       </c>
       <c r="E164">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F164" t="s">
         <v>1549</v>
@@ -13763,7 +13763,7 @@
         <v>1434</v>
       </c>
       <c r="E165">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F165" t="s">
         <v>1549</v>
@@ -13798,7 +13798,7 @@
         <v>1435</v>
       </c>
       <c r="E166">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F166" t="s">
         <v>1549</v>
@@ -13833,7 +13833,7 @@
         <v>1435</v>
       </c>
       <c r="E167">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F167" t="s">
         <v>1549</v>
@@ -13868,7 +13868,7 @@
         <v>1435</v>
       </c>
       <c r="E168">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F168" t="s">
         <v>1549</v>
@@ -13903,7 +13903,7 @@
         <v>1436</v>
       </c>
       <c r="E169">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F169" t="s">
         <v>1549</v>
@@ -13938,7 +13938,7 @@
         <v>1436</v>
       </c>
       <c r="E170">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F170" t="s">
         <v>1549</v>
@@ -13973,7 +13973,7 @@
         <v>1437</v>
       </c>
       <c r="E171">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F171" t="s">
         <v>1549</v>
@@ -14008,7 +14008,7 @@
         <v>1438</v>
       </c>
       <c r="E172">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F172" t="s">
         <v>1549</v>
@@ -14043,7 +14043,7 @@
         <v>1438</v>
       </c>
       <c r="E173">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F173" t="s">
         <v>1549</v>
@@ -14078,7 +14078,7 @@
         <v>1438</v>
       </c>
       <c r="E174">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F174" t="s">
         <v>1549</v>
@@ -14113,7 +14113,7 @@
         <v>1438</v>
       </c>
       <c r="E175">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F175" t="s">
         <v>1549</v>
@@ -14148,7 +14148,7 @@
         <v>1439</v>
       </c>
       <c r="E176">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F176" t="s">
         <v>1549</v>
@@ -14183,7 +14183,7 @@
         <v>1440</v>
       </c>
       <c r="E177">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F177" t="s">
         <v>1549</v>
@@ -14218,7 +14218,7 @@
         <v>1440</v>
       </c>
       <c r="E178">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F178" t="s">
         <v>1549</v>
@@ -14253,7 +14253,7 @@
         <v>1440</v>
       </c>
       <c r="E179">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F179" t="s">
         <v>1549</v>
@@ -14288,7 +14288,7 @@
         <v>1440</v>
       </c>
       <c r="E180">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F180" t="s">
         <v>1549</v>
@@ -14323,7 +14323,7 @@
         <v>1440</v>
       </c>
       <c r="E181">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F181" t="s">
         <v>1549</v>
@@ -14358,7 +14358,7 @@
         <v>1441</v>
       </c>
       <c r="E182">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F182" t="s">
         <v>1549</v>
@@ -14393,7 +14393,7 @@
         <v>1441</v>
       </c>
       <c r="E183">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F183" t="s">
         <v>1549</v>
@@ -14428,7 +14428,7 @@
         <v>1441</v>
       </c>
       <c r="E184">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F184" t="s">
         <v>1549</v>
@@ -14463,7 +14463,7 @@
         <v>1441</v>
       </c>
       <c r="E185">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F185" t="s">
         <v>1549</v>
@@ -14498,7 +14498,7 @@
         <v>1441</v>
       </c>
       <c r="E186">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F186" t="s">
         <v>1549</v>
@@ -14533,7 +14533,7 @@
         <v>1441</v>
       </c>
       <c r="E187">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F187" t="s">
         <v>1549</v>
@@ -14568,7 +14568,7 @@
         <v>1442</v>
       </c>
       <c r="E188">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F188" t="s">
         <v>1549</v>
@@ -14603,7 +14603,7 @@
         <v>1442</v>
       </c>
       <c r="E189">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F189" t="s">
         <v>1549</v>
@@ -14638,7 +14638,7 @@
         <v>1442</v>
       </c>
       <c r="E190">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F190" t="s">
         <v>1549</v>
@@ -14673,7 +14673,7 @@
         <v>1442</v>
       </c>
       <c r="E191">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F191" t="s">
         <v>1549</v>
@@ -14708,7 +14708,7 @@
         <v>1443</v>
       </c>
       <c r="E192">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F192" t="s">
         <v>1549</v>
@@ -14743,7 +14743,7 @@
         <v>1443</v>
       </c>
       <c r="E193">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F193" t="s">
         <v>1549</v>
@@ -14778,7 +14778,7 @@
         <v>1444</v>
       </c>
       <c r="E194">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F194" t="s">
         <v>1549</v>
@@ -14813,7 +14813,7 @@
         <v>1445</v>
       </c>
       <c r="E195">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F195" t="s">
         <v>1549</v>
@@ -14848,7 +14848,7 @@
         <v>1445</v>
       </c>
       <c r="E196">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F196" t="s">
         <v>1549</v>
@@ -14883,7 +14883,7 @@
         <v>1446</v>
       </c>
       <c r="E197">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F197" t="s">
         <v>1549</v>
@@ -14918,7 +14918,7 @@
         <v>1447</v>
       </c>
       <c r="E198">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F198" t="s">
         <v>1549</v>
@@ -14953,7 +14953,7 @@
         <v>1447</v>
       </c>
       <c r="E199">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F199" t="s">
         <v>1549</v>
@@ -14988,7 +14988,7 @@
         <v>1448</v>
       </c>
       <c r="E200">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F200" t="s">
         <v>1549</v>
@@ -15023,7 +15023,7 @@
         <v>1448</v>
       </c>
       <c r="E201">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F201" t="s">
         <v>1549</v>
@@ -15058,7 +15058,7 @@
         <v>1449</v>
       </c>
       <c r="E202">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F202" t="s">
         <v>1549</v>
@@ -15093,7 +15093,7 @@
         <v>1450</v>
       </c>
       <c r="E203">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F203" t="s">
         <v>1549</v>
@@ -15128,7 +15128,7 @@
         <v>1450</v>
       </c>
       <c r="E204">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F204" t="s">
         <v>1549</v>
@@ -15163,7 +15163,7 @@
         <v>1450</v>
       </c>
       <c r="E205">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F205" t="s">
         <v>1549</v>
@@ -15198,7 +15198,7 @@
         <v>1451</v>
       </c>
       <c r="E206">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F206" t="s">
         <v>1549</v>
@@ -15233,7 +15233,7 @@
         <v>1451</v>
       </c>
       <c r="E207">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F207" t="s">
         <v>1549</v>
@@ -15268,7 +15268,7 @@
         <v>1452</v>
       </c>
       <c r="E208">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F208" t="s">
         <v>1549</v>
@@ -15303,7 +15303,7 @@
         <v>1453</v>
       </c>
       <c r="E209">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F209" t="s">
         <v>1549</v>
@@ -15338,7 +15338,7 @@
         <v>1453</v>
       </c>
       <c r="E210">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F210" t="s">
         <v>1549</v>
@@ -15373,7 +15373,7 @@
         <v>1453</v>
       </c>
       <c r="E211">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F211" t="s">
         <v>1549</v>
@@ -15408,7 +15408,7 @@
         <v>1454</v>
       </c>
       <c r="E212">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F212" t="s">
         <v>1549</v>
@@ -15443,7 +15443,7 @@
         <v>1454</v>
       </c>
       <c r="E213">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F213" t="s">
         <v>1549</v>
@@ -15478,7 +15478,7 @@
         <v>1455</v>
       </c>
       <c r="E214">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F214" t="s">
         <v>1549</v>
@@ -15513,7 +15513,7 @@
         <v>1455</v>
       </c>
       <c r="E215">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F215" t="s">
         <v>1549</v>
@@ -15548,7 +15548,7 @@
         <v>1455</v>
       </c>
       <c r="E216">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F216" t="s">
         <v>1551</v>
@@ -15583,7 +15583,7 @@
         <v>1455</v>
       </c>
       <c r="E217">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F217" t="s">
         <v>1549</v>
@@ -15618,7 +15618,7 @@
         <v>1456</v>
       </c>
       <c r="E218">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F218" t="s">
         <v>1549</v>
@@ -15653,7 +15653,7 @@
         <v>1456</v>
       </c>
       <c r="E219">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F219" t="s">
         <v>1549</v>
@@ -15691,7 +15691,7 @@
         <v>1456</v>
       </c>
       <c r="E220">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F220" t="s">
         <v>1549</v>
@@ -15726,7 +15726,7 @@
         <v>1456</v>
       </c>
       <c r="E221">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F221" t="s">
         <v>1549</v>
@@ -15761,7 +15761,7 @@
         <v>1456</v>
       </c>
       <c r="E222">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F222" t="s">
         <v>1549</v>
@@ -15796,7 +15796,7 @@
         <v>1456</v>
       </c>
       <c r="E223">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F223" t="s">
         <v>1549</v>
@@ -15831,7 +15831,7 @@
         <v>1457</v>
       </c>
       <c r="E224">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F224" t="s">
         <v>1549</v>
@@ -15866,7 +15866,7 @@
         <v>1457</v>
       </c>
       <c r="E225">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F225" t="s">
         <v>1549</v>
@@ -15901,7 +15901,7 @@
         <v>1457</v>
       </c>
       <c r="E226">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F226" t="s">
         <v>1549</v>
@@ -15936,7 +15936,7 @@
         <v>1458</v>
       </c>
       <c r="E227">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F227" t="s">
         <v>1549</v>
@@ -15971,7 +15971,7 @@
         <v>1458</v>
       </c>
       <c r="E228">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F228" t="s">
         <v>1549</v>
@@ -16006,7 +16006,7 @@
         <v>1458</v>
       </c>
       <c r="E229">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F229" t="s">
         <v>1549</v>
@@ -16041,7 +16041,7 @@
         <v>1458</v>
       </c>
       <c r="E230">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F230" t="s">
         <v>1549</v>
@@ -16076,7 +16076,7 @@
         <v>1459</v>
       </c>
       <c r="E231">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F231" t="s">
         <v>1549</v>
@@ -16111,7 +16111,7 @@
         <v>1459</v>
       </c>
       <c r="E232">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F232" t="s">
         <v>1549</v>
@@ -16146,7 +16146,7 @@
         <v>1459</v>
       </c>
       <c r="E233">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F233" t="s">
         <v>1549</v>
@@ -16181,7 +16181,7 @@
         <v>1460</v>
       </c>
       <c r="E234">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F234" t="s">
         <v>1549</v>
@@ -16216,7 +16216,7 @@
         <v>1460</v>
       </c>
       <c r="E235">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F235" t="s">
         <v>1549</v>
@@ -16251,7 +16251,7 @@
         <v>1460</v>
       </c>
       <c r="E236">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F236" t="s">
         <v>1549</v>
@@ -16286,7 +16286,7 @@
         <v>1460</v>
       </c>
       <c r="E237">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F237" t="s">
         <v>1549</v>
@@ -16321,7 +16321,7 @@
         <v>1460</v>
       </c>
       <c r="E238">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F238" t="s">
         <v>1549</v>
@@ -16356,7 +16356,7 @@
         <v>1460</v>
       </c>
       <c r="E239">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F239" t="s">
         <v>1549</v>
@@ -16391,7 +16391,7 @@
         <v>1461</v>
       </c>
       <c r="E240">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F240" t="s">
         <v>1549</v>
@@ -16426,7 +16426,7 @@
         <v>1462</v>
       </c>
       <c r="E241">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F241" t="s">
         <v>1549</v>
@@ -16461,7 +16461,7 @@
         <v>1462</v>
       </c>
       <c r="E242">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F242" t="s">
         <v>1552</v>
@@ -16496,7 +16496,7 @@
         <v>1462</v>
       </c>
       <c r="E243">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F243" t="s">
         <v>1549</v>
@@ -16531,7 +16531,7 @@
         <v>1462</v>
       </c>
       <c r="E244">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F244" t="s">
         <v>1549</v>
@@ -16566,7 +16566,7 @@
         <v>1462</v>
       </c>
       <c r="E245">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F245" t="s">
         <v>1549</v>
@@ -16601,7 +16601,7 @@
         <v>1463</v>
       </c>
       <c r="E246">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F246" t="s">
         <v>1549</v>
@@ -16636,7 +16636,7 @@
         <v>1463</v>
       </c>
       <c r="E247">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F247" t="s">
         <v>1549</v>
@@ -16671,7 +16671,7 @@
         <v>1463</v>
       </c>
       <c r="E248">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F248" t="s">
         <v>1549</v>
@@ -16706,7 +16706,7 @@
         <v>1463</v>
       </c>
       <c r="E249">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F249" t="s">
         <v>1549</v>
@@ -16741,7 +16741,7 @@
         <v>1464</v>
       </c>
       <c r="E250">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F250" t="s">
         <v>1549</v>
@@ -16776,7 +16776,7 @@
         <v>1465</v>
       </c>
       <c r="E251">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F251" t="s">
         <v>1549</v>
@@ -16814,7 +16814,7 @@
         <v>1466</v>
       </c>
       <c r="E252">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F252" t="s">
         <v>1549</v>
@@ -16849,7 +16849,7 @@
         <v>1466</v>
       </c>
       <c r="E253">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F253" t="s">
         <v>1549</v>
@@ -16884,7 +16884,7 @@
         <v>1466</v>
       </c>
       <c r="E254">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F254" t="s">
         <v>1549</v>
@@ -16919,7 +16919,7 @@
         <v>1466</v>
       </c>
       <c r="E255">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F255" t="s">
         <v>1549</v>
@@ -16957,7 +16957,7 @@
         <v>1466</v>
       </c>
       <c r="E256">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F256" t="s">
         <v>1549</v>
@@ -16992,7 +16992,7 @@
         <v>1467</v>
       </c>
       <c r="E257">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F257" t="s">
         <v>1549</v>
@@ -17027,7 +17027,7 @@
         <v>1467</v>
       </c>
       <c r="E258">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F258" t="s">
         <v>1549</v>
@@ -17062,7 +17062,7 @@
         <v>1468</v>
       </c>
       <c r="E259">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F259" t="s">
         <v>1549</v>
@@ -17097,7 +17097,7 @@
         <v>1468</v>
       </c>
       <c r="E260">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F260" t="s">
         <v>1549</v>
@@ -17132,7 +17132,7 @@
         <v>1469</v>
       </c>
       <c r="E261">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F261" t="s">
         <v>1549</v>
@@ -17167,7 +17167,7 @@
         <v>1469</v>
       </c>
       <c r="E262">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F262" t="s">
         <v>1549</v>
@@ -17202,7 +17202,7 @@
         <v>1469</v>
       </c>
       <c r="E263">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F263" t="s">
         <v>1549</v>
@@ -17237,7 +17237,7 @@
         <v>1470</v>
       </c>
       <c r="E264">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F264" t="s">
         <v>1549</v>
@@ -17272,7 +17272,7 @@
         <v>1470</v>
       </c>
       <c r="E265">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F265" t="s">
         <v>1549</v>
@@ -17307,7 +17307,7 @@
         <v>1470</v>
       </c>
       <c r="E266">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F266" t="s">
         <v>1549</v>
@@ -17342,7 +17342,7 @@
         <v>1470</v>
       </c>
       <c r="E267">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F267" t="s">
         <v>1549</v>
@@ -17377,7 +17377,7 @@
         <v>1471</v>
       </c>
       <c r="E268">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F268" t="s">
         <v>1549</v>
@@ -17412,7 +17412,7 @@
         <v>1472</v>
       </c>
       <c r="E269">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F269" t="s">
         <v>1549</v>
@@ -17447,7 +17447,7 @@
         <v>1472</v>
       </c>
       <c r="E270">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F270" t="s">
         <v>1549</v>
@@ -17482,7 +17482,7 @@
         <v>1472</v>
       </c>
       <c r="E271">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F271" t="s">
         <v>1549</v>
@@ -17517,7 +17517,7 @@
         <v>1472</v>
       </c>
       <c r="E272">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F272" t="s">
         <v>1549</v>
@@ -17552,7 +17552,7 @@
         <v>1473</v>
       </c>
       <c r="E273">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F273" t="s">
         <v>1549</v>
@@ -17587,7 +17587,7 @@
         <v>1473</v>
       </c>
       <c r="E274">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F274" t="s">
         <v>1549</v>
@@ -17622,7 +17622,7 @@
         <v>1473</v>
       </c>
       <c r="E275">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F275" t="s">
         <v>1549</v>
@@ -17657,7 +17657,7 @@
         <v>1474</v>
       </c>
       <c r="E276">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F276" t="s">
         <v>1549</v>
@@ -17692,7 +17692,7 @@
         <v>1474</v>
       </c>
       <c r="E277">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F277" t="s">
         <v>1549</v>
@@ -17727,7 +17727,7 @@
         <v>1475</v>
       </c>
       <c r="E278">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F278" t="s">
         <v>1549</v>
@@ -17762,7 +17762,7 @@
         <v>1475</v>
       </c>
       <c r="E279">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F279" t="s">
         <v>1549</v>
@@ -17797,7 +17797,7 @@
         <v>1475</v>
       </c>
       <c r="E280">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F280" t="s">
         <v>1549</v>
@@ -17832,7 +17832,7 @@
         <v>1475</v>
       </c>
       <c r="E281">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F281" t="s">
         <v>1549</v>
@@ -17867,7 +17867,7 @@
         <v>1475</v>
       </c>
       <c r="E282">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F282" t="s">
         <v>1549</v>
@@ -17902,7 +17902,7 @@
         <v>1476</v>
       </c>
       <c r="E283">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F283" t="s">
         <v>1549</v>
@@ -17937,7 +17937,7 @@
         <v>1476</v>
       </c>
       <c r="E284">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F284" t="s">
         <v>1549</v>
@@ -17972,7 +17972,7 @@
         <v>1476</v>
       </c>
       <c r="E285">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F285" t="s">
         <v>1549</v>
@@ -18007,7 +18007,7 @@
         <v>1477</v>
       </c>
       <c r="E286">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F286" t="s">
         <v>1549</v>
@@ -18042,7 +18042,7 @@
         <v>1478</v>
       </c>
       <c r="E287">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F287" t="s">
         <v>1549</v>
@@ -18077,7 +18077,7 @@
         <v>1479</v>
       </c>
       <c r="E288">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F288" t="s">
         <v>1549</v>
@@ -18112,7 +18112,7 @@
         <v>1479</v>
       </c>
       <c r="E289">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F289" t="s">
         <v>1549</v>
@@ -18147,7 +18147,7 @@
         <v>1479</v>
       </c>
       <c r="E290">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F290" t="s">
         <v>1549</v>
@@ -18182,7 +18182,7 @@
         <v>1479</v>
       </c>
       <c r="E291">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F291" t="s">
         <v>1549</v>
@@ -18217,7 +18217,7 @@
         <v>1479</v>
       </c>
       <c r="E292">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F292" t="s">
         <v>1549</v>
@@ -18252,7 +18252,7 @@
         <v>1480</v>
       </c>
       <c r="E293">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F293" t="s">
         <v>1549</v>
@@ -18287,7 +18287,7 @@
         <v>1480</v>
       </c>
       <c r="E294">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F294" t="s">
         <v>1549</v>
@@ -18322,7 +18322,7 @@
         <v>1481</v>
       </c>
       <c r="E295">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F295" t="s">
         <v>1549</v>
@@ -18357,7 +18357,7 @@
         <v>1481</v>
       </c>
       <c r="E296">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F296" t="s">
         <v>1549</v>
@@ -18392,7 +18392,7 @@
         <v>1482</v>
       </c>
       <c r="E297">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F297" t="s">
         <v>1549</v>
@@ -18427,7 +18427,7 @@
         <v>1483</v>
       </c>
       <c r="E298">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F298" t="s">
         <v>1549</v>
@@ -18462,7 +18462,7 @@
         <v>1484</v>
       </c>
       <c r="E299">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F299" t="s">
         <v>1549</v>
@@ -18497,7 +18497,7 @@
         <v>1484</v>
       </c>
       <c r="E300">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F300" t="s">
         <v>1549</v>
@@ -18532,7 +18532,7 @@
         <v>1485</v>
       </c>
       <c r="E301">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F301" t="s">
         <v>1549</v>
@@ -18567,7 +18567,7 @@
         <v>1485</v>
       </c>
       <c r="E302">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F302" t="s">
         <v>1549</v>
@@ -18602,7 +18602,7 @@
         <v>1485</v>
       </c>
       <c r="E303">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F303" t="s">
         <v>1549</v>
@@ -18637,7 +18637,7 @@
         <v>1486</v>
       </c>
       <c r="E304">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F304" t="s">
         <v>1549</v>
@@ -18672,7 +18672,7 @@
         <v>1486</v>
       </c>
       <c r="E305">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F305" t="s">
         <v>1549</v>
@@ -18707,7 +18707,7 @@
         <v>1486</v>
       </c>
       <c r="E306">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F306" t="s">
         <v>1549</v>
@@ -18742,7 +18742,7 @@
         <v>1486</v>
       </c>
       <c r="E307">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F307" t="s">
         <v>1549</v>
@@ -18777,7 +18777,7 @@
         <v>1486</v>
       </c>
       <c r="E308">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F308" t="s">
         <v>1549</v>
@@ -18812,7 +18812,7 @@
         <v>1486</v>
       </c>
       <c r="E309">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F309" t="s">
         <v>1549</v>
@@ -18847,7 +18847,7 @@
         <v>1486</v>
       </c>
       <c r="E310">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F310" t="s">
         <v>1549</v>
@@ -18882,7 +18882,7 @@
         <v>1486</v>
       </c>
       <c r="E311">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F311" t="s">
         <v>1549</v>
@@ -18917,7 +18917,7 @@
         <v>1486</v>
       </c>
       <c r="E312">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F312" t="s">
         <v>1549</v>
@@ -18952,7 +18952,7 @@
         <v>1487</v>
       </c>
       <c r="E313">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F313" t="s">
         <v>1549</v>
@@ -18987,7 +18987,7 @@
         <v>1487</v>
       </c>
       <c r="E314">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F314" t="s">
         <v>1549</v>
@@ -19022,7 +19022,7 @@
         <v>1487</v>
       </c>
       <c r="E315">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F315" t="s">
         <v>1549</v>
@@ -19057,7 +19057,7 @@
         <v>1488</v>
       </c>
       <c r="E316">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F316" t="s">
         <v>1549</v>
@@ -19092,7 +19092,7 @@
         <v>1489</v>
       </c>
       <c r="E317">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F317" t="s">
         <v>1549</v>
@@ -19127,7 +19127,7 @@
         <v>1489</v>
       </c>
       <c r="E318">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F318" t="s">
         <v>1549</v>
@@ -19162,7 +19162,7 @@
         <v>1489</v>
       </c>
       <c r="E319">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F319" t="s">
         <v>1549</v>
@@ -19197,7 +19197,7 @@
         <v>1489</v>
       </c>
       <c r="E320">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F320" t="s">
         <v>1549</v>
@@ -19232,7 +19232,7 @@
         <v>1489</v>
       </c>
       <c r="E321">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F321" t="s">
         <v>1553</v>
@@ -19270,7 +19270,7 @@
         <v>1489</v>
       </c>
       <c r="E322">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F322" t="s">
         <v>1549</v>
@@ -19305,7 +19305,7 @@
         <v>1489</v>
       </c>
       <c r="E323">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F323" t="s">
         <v>1549</v>
@@ -19340,7 +19340,7 @@
         <v>1490</v>
       </c>
       <c r="E324">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F324" t="s">
         <v>1549</v>
@@ -19375,7 +19375,7 @@
         <v>1490</v>
       </c>
       <c r="E325">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F325" t="s">
         <v>1549</v>
@@ -19410,7 +19410,7 @@
         <v>1490</v>
       </c>
       <c r="E326">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F326" t="s">
         <v>1549</v>
@@ -19445,7 +19445,7 @@
         <v>1490</v>
       </c>
       <c r="E327">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F327" t="s">
         <v>1549</v>
@@ -19483,7 +19483,7 @@
         <v>1490</v>
       </c>
       <c r="E328">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F328" t="s">
         <v>1549</v>
@@ -19518,7 +19518,7 @@
         <v>1490</v>
       </c>
       <c r="E329">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F329" t="s">
         <v>1549</v>
@@ -19553,7 +19553,7 @@
         <v>1490</v>
       </c>
       <c r="E330">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F330" t="s">
         <v>1549</v>
@@ -19588,7 +19588,7 @@
         <v>1490</v>
       </c>
       <c r="E331">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F331" t="s">
         <v>1549</v>
@@ -19623,7 +19623,7 @@
         <v>1490</v>
       </c>
       <c r="E332">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F332" t="s">
         <v>1549</v>
@@ -19658,7 +19658,7 @@
         <v>1491</v>
       </c>
       <c r="E333">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F333" t="s">
         <v>1550</v>
@@ -19693,7 +19693,7 @@
         <v>1492</v>
       </c>
       <c r="E334">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F334" t="s">
         <v>1553</v>
@@ -19728,7 +19728,7 @@
         <v>1493</v>
       </c>
       <c r="E335">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F335" t="s">
         <v>1549</v>
@@ -19763,7 +19763,7 @@
         <v>1494</v>
       </c>
       <c r="E336">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F336" t="s">
         <v>1549</v>
@@ -19798,7 +19798,7 @@
         <v>1494</v>
       </c>
       <c r="E337">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F337" t="s">
         <v>1549</v>
@@ -19833,7 +19833,7 @@
         <v>1495</v>
       </c>
       <c r="E338">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F338" t="s">
         <v>1549</v>
@@ -19868,7 +19868,7 @@
         <v>1496</v>
       </c>
       <c r="E339">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F339" t="s">
         <v>1552</v>
@@ -19903,7 +19903,7 @@
         <v>1496</v>
       </c>
       <c r="E340">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F340" t="s">
         <v>1549</v>
@@ -19938,7 +19938,7 @@
         <v>1496</v>
       </c>
       <c r="E341">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F341" t="s">
         <v>1549</v>
@@ -19973,7 +19973,7 @@
         <v>1496</v>
       </c>
       <c r="E342">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F342" t="s">
         <v>1549</v>
@@ -20008,7 +20008,7 @@
         <v>1496</v>
       </c>
       <c r="E343">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F343" t="s">
         <v>1549</v>
@@ -20043,7 +20043,7 @@
         <v>1496</v>
       </c>
       <c r="E344">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F344" t="s">
         <v>1549</v>
@@ -20078,7 +20078,7 @@
         <v>1497</v>
       </c>
       <c r="E345">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F345" t="s">
         <v>1549</v>
@@ -20113,7 +20113,7 @@
         <v>1497</v>
       </c>
       <c r="E346">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F346" t="s">
         <v>1549</v>
@@ -20148,7 +20148,7 @@
         <v>1497</v>
       </c>
       <c r="E347">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F347" t="s">
         <v>1549</v>
@@ -20183,7 +20183,7 @@
         <v>1498</v>
       </c>
       <c r="E348">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F348" t="s">
         <v>1549</v>
@@ -20218,7 +20218,7 @@
         <v>1498</v>
       </c>
       <c r="E349">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F349" t="s">
         <v>1549</v>
@@ -20253,7 +20253,7 @@
         <v>1498</v>
       </c>
       <c r="E350">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F350" t="s">
         <v>1549</v>
@@ -20291,7 +20291,7 @@
         <v>1498</v>
       </c>
       <c r="E351">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F351" t="s">
         <v>1549</v>
@@ -20326,7 +20326,7 @@
         <v>1499</v>
       </c>
       <c r="E352">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F352" t="s">
         <v>1549</v>
@@ -20361,7 +20361,7 @@
         <v>1499</v>
       </c>
       <c r="E353">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F353" t="s">
         <v>1549</v>
@@ -20396,7 +20396,7 @@
         <v>1499</v>
       </c>
       <c r="E354">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F354" t="s">
         <v>1549</v>
@@ -20431,7 +20431,7 @@
         <v>1499</v>
       </c>
       <c r="E355">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F355" t="s">
         <v>1549</v>
@@ -20466,7 +20466,7 @@
         <v>1499</v>
       </c>
       <c r="E356">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F356" t="s">
         <v>1549</v>
@@ -20501,7 +20501,7 @@
         <v>1500</v>
       </c>
       <c r="E357">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F357" t="s">
         <v>1549</v>
@@ -20536,7 +20536,7 @@
         <v>1500</v>
       </c>
       <c r="E358">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F358" t="s">
         <v>1549</v>
@@ -20571,7 +20571,7 @@
         <v>1501</v>
       </c>
       <c r="E359">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F359" t="s">
         <v>1549</v>
@@ -20606,7 +20606,7 @@
         <v>1501</v>
       </c>
       <c r="E360">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F360" t="s">
         <v>1549</v>
@@ -20641,7 +20641,7 @@
         <v>1501</v>
       </c>
       <c r="E361">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F361" t="s">
         <v>1549</v>
@@ -20676,7 +20676,7 @@
         <v>1501</v>
       </c>
       <c r="E362">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F362" t="s">
         <v>1549</v>
@@ -20711,7 +20711,7 @@
         <v>1501</v>
       </c>
       <c r="E363">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F363" t="s">
         <v>1549</v>
@@ -20746,7 +20746,7 @@
         <v>1501</v>
       </c>
       <c r="E364">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F364" t="s">
         <v>1549</v>
@@ -20781,7 +20781,7 @@
         <v>1501</v>
       </c>
       <c r="E365">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F365" t="s">
         <v>1549</v>
@@ -20816,7 +20816,7 @@
         <v>1501</v>
       </c>
       <c r="E366">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F366" t="s">
         <v>1549</v>
@@ -20851,7 +20851,7 @@
         <v>1501</v>
       </c>
       <c r="E367">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F367" t="s">
         <v>1549</v>
@@ -20886,7 +20886,7 @@
         <v>1501</v>
       </c>
       <c r="E368">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F368" t="s">
         <v>1549</v>
@@ -20921,7 +20921,7 @@
         <v>1502</v>
       </c>
       <c r="E369">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F369" t="s">
         <v>1549</v>
@@ -20956,7 +20956,7 @@
         <v>1502</v>
       </c>
       <c r="E370">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F370" t="s">
         <v>1549</v>
@@ -20991,7 +20991,7 @@
         <v>1502</v>
       </c>
       <c r="E371">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F371" t="s">
         <v>1550</v>
@@ -21026,7 +21026,7 @@
         <v>1503</v>
       </c>
       <c r="E372">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F372" t="s">
         <v>1549</v>
@@ -21061,7 +21061,7 @@
         <v>1503</v>
       </c>
       <c r="E373">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F373" t="s">
         <v>1549</v>
@@ -21096,7 +21096,7 @@
         <v>1503</v>
       </c>
       <c r="E374">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F374" t="s">
         <v>1549</v>
@@ -21131,7 +21131,7 @@
         <v>1503</v>
       </c>
       <c r="E375">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F375" t="s">
         <v>1549</v>
@@ -21166,7 +21166,7 @@
         <v>1503</v>
       </c>
       <c r="E376">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F376" t="s">
         <v>1549</v>
@@ -21201,7 +21201,7 @@
         <v>1503</v>
       </c>
       <c r="E377">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F377" t="s">
         <v>1549</v>
@@ -21236,7 +21236,7 @@
         <v>1503</v>
       </c>
       <c r="E378">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F378" t="s">
         <v>1552</v>
@@ -21271,7 +21271,7 @@
         <v>1504</v>
       </c>
       <c r="E379">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F379" t="s">
         <v>1549</v>
@@ -21306,7 +21306,7 @@
         <v>1504</v>
       </c>
       <c r="E380">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F380" t="s">
         <v>1549</v>
@@ -21341,7 +21341,7 @@
         <v>1504</v>
       </c>
       <c r="E381">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F381" t="s">
         <v>1549</v>
@@ -21376,7 +21376,7 @@
         <v>1504</v>
       </c>
       <c r="E382">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F382" t="s">
         <v>1549</v>
@@ -21411,7 +21411,7 @@
         <v>1505</v>
       </c>
       <c r="E383">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F383" t="s">
         <v>1552</v>
@@ -21446,7 +21446,7 @@
         <v>1505</v>
       </c>
       <c r="E384">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F384" t="s">
         <v>1549</v>
@@ -21481,7 +21481,7 @@
         <v>1505</v>
       </c>
       <c r="E385">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F385" t="s">
         <v>1549</v>
@@ -21516,7 +21516,7 @@
         <v>1505</v>
       </c>
       <c r="E386">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F386" t="s">
         <v>1549</v>
@@ -21551,7 +21551,7 @@
         <v>1505</v>
       </c>
       <c r="E387">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F387" t="s">
         <v>1549</v>
@@ -21586,7 +21586,7 @@
         <v>1505</v>
       </c>
       <c r="E388">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F388" t="s">
         <v>1549</v>
@@ -21621,7 +21621,7 @@
         <v>1506</v>
       </c>
       <c r="E389">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F389" t="s">
         <v>1549</v>
@@ -21656,7 +21656,7 @@
         <v>1506</v>
       </c>
       <c r="E390">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F390" t="s">
         <v>1549</v>
@@ -21691,7 +21691,7 @@
         <v>1506</v>
       </c>
       <c r="E391">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F391" t="s">
         <v>1549</v>
@@ -21726,7 +21726,7 @@
         <v>1506</v>
       </c>
       <c r="E392">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F392" t="s">
         <v>1549</v>
@@ -21761,7 +21761,7 @@
         <v>1506</v>
       </c>
       <c r="E393">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F393" t="s">
         <v>1551</v>
@@ -21796,7 +21796,7 @@
         <v>1506</v>
       </c>
       <c r="E394">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F394" t="s">
         <v>1549</v>
@@ -21831,7 +21831,7 @@
         <v>1506</v>
       </c>
       <c r="E395">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F395" t="s">
         <v>1549</v>
@@ -21866,7 +21866,7 @@
         <v>1507</v>
       </c>
       <c r="E396">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F396" t="s">
         <v>1549</v>
@@ -21901,7 +21901,7 @@
         <v>1507</v>
       </c>
       <c r="E397">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F397" t="s">
         <v>1549</v>
@@ -21936,7 +21936,7 @@
         <v>1507</v>
       </c>
       <c r="E398">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F398" t="s">
         <v>1549</v>
@@ -21971,7 +21971,7 @@
         <v>1507</v>
       </c>
       <c r="E399">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F399" t="s">
         <v>1549</v>
@@ -22006,7 +22006,7 @@
         <v>1507</v>
       </c>
       <c r="E400">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F400" t="s">
         <v>1549</v>
@@ -22041,7 +22041,7 @@
         <v>1508</v>
       </c>
       <c r="E401">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F401" t="s">
         <v>1549</v>
@@ -22076,7 +22076,7 @@
         <v>1508</v>
       </c>
       <c r="E402">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F402" t="s">
         <v>1549</v>
@@ -22111,7 +22111,7 @@
         <v>1508</v>
       </c>
       <c r="E403">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F403" t="s">
         <v>1549</v>
@@ -22146,7 +22146,7 @@
         <v>1508</v>
       </c>
       <c r="E404">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F404" t="s">
         <v>1549</v>
@@ -22181,7 +22181,7 @@
         <v>1508</v>
       </c>
       <c r="E405">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F405" t="s">
         <v>1549</v>
@@ -22219,7 +22219,7 @@
         <v>1509</v>
       </c>
       <c r="E406">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F406" t="s">
         <v>1549</v>
@@ -22254,7 +22254,7 @@
         <v>1509</v>
       </c>
       <c r="E407">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F407" t="s">
         <v>1549</v>
@@ -22289,7 +22289,7 @@
         <v>1509</v>
       </c>
       <c r="E408">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F408" t="s">
         <v>1549</v>
@@ -22324,7 +22324,7 @@
         <v>1509</v>
       </c>
       <c r="E409">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F409" t="s">
         <v>1549</v>
@@ -22359,7 +22359,7 @@
         <v>1509</v>
       </c>
       <c r="E410">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F410" t="s">
         <v>1549</v>
@@ -22394,7 +22394,7 @@
         <v>1509</v>
       </c>
       <c r="E411">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F411" t="s">
         <v>1549</v>
@@ -22429,7 +22429,7 @@
         <v>1510</v>
       </c>
       <c r="E412">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F412" t="s">
         <v>1550</v>
@@ -22464,7 +22464,7 @@
         <v>1510</v>
       </c>
       <c r="E413">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F413" t="s">
         <v>1549</v>
@@ -22499,7 +22499,7 @@
         <v>1511</v>
       </c>
       <c r="E414">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F414" t="s">
         <v>1549</v>
@@ -22534,7 +22534,7 @@
         <v>1512</v>
       </c>
       <c r="E415">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F415" t="s">
         <v>1549</v>
@@ -22569,7 +22569,7 @@
         <v>1512</v>
       </c>
       <c r="E416">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F416" t="s">
         <v>1549</v>
@@ -22604,7 +22604,7 @@
         <v>1512</v>
       </c>
       <c r="E417">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F417" t="s">
         <v>1551</v>
@@ -22642,7 +22642,7 @@
         <v>1513</v>
       </c>
       <c r="E418">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F418" t="s">
         <v>1549</v>
@@ -22677,7 +22677,7 @@
         <v>1513</v>
       </c>
       <c r="E419">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F419" t="s">
         <v>1549</v>
@@ -22712,7 +22712,7 @@
         <v>1513</v>
       </c>
       <c r="E420">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F420" t="s">
         <v>1549</v>
@@ -22747,7 +22747,7 @@
         <v>1514</v>
       </c>
       <c r="E421">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F421" t="s">
         <v>1549</v>
@@ -22782,7 +22782,7 @@
         <v>1514</v>
       </c>
       <c r="E422">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F422" t="s">
         <v>1549</v>
@@ -22817,7 +22817,7 @@
         <v>1514</v>
       </c>
       <c r="E423">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F423" t="s">
         <v>1549</v>
@@ -22852,7 +22852,7 @@
         <v>1514</v>
       </c>
       <c r="E424">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F424" t="s">
         <v>1549</v>
@@ -22887,7 +22887,7 @@
         <v>1514</v>
       </c>
       <c r="E425">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F425" t="s">
         <v>1549</v>
@@ -22922,7 +22922,7 @@
         <v>1514</v>
       </c>
       <c r="E426">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F426" t="s">
         <v>1549</v>
@@ -22957,7 +22957,7 @@
         <v>1514</v>
       </c>
       <c r="E427">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F427" t="s">
         <v>1549</v>
@@ -22992,7 +22992,7 @@
         <v>1514</v>
       </c>
       <c r="E428">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F428" t="s">
         <v>1549</v>
@@ -23027,7 +23027,7 @@
         <v>1515</v>
       </c>
       <c r="E429">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F429" t="s">
         <v>1549</v>
@@ -23062,7 +23062,7 @@
         <v>1516</v>
       </c>
       <c r="E430">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F430" t="s">
         <v>1549</v>
@@ -23097,7 +23097,7 @@
         <v>1516</v>
       </c>
       <c r="E431">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F431" t="s">
         <v>1549</v>
@@ -23132,7 +23132,7 @@
         <v>1516</v>
       </c>
       <c r="E432">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F432" t="s">
         <v>1549</v>
@@ -23167,7 +23167,7 @@
         <v>1516</v>
       </c>
       <c r="E433">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F433" t="s">
         <v>1553</v>
@@ -23205,7 +23205,7 @@
         <v>1516</v>
       </c>
       <c r="E434">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F434" t="s">
         <v>1549</v>
@@ -23240,7 +23240,7 @@
         <v>1516</v>
       </c>
       <c r="E435">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F435" t="s">
         <v>1553</v>
@@ -23275,7 +23275,7 @@
         <v>1517</v>
       </c>
       <c r="E436">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F436" t="s">
         <v>1549</v>
@@ -23310,7 +23310,7 @@
         <v>1518</v>
       </c>
       <c r="E437">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F437" t="s">
         <v>1549</v>
@@ -23345,7 +23345,7 @@
         <v>1518</v>
       </c>
       <c r="E438">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F438" t="s">
         <v>1549</v>
@@ -23380,7 +23380,7 @@
         <v>1518</v>
       </c>
       <c r="E439">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F439" t="s">
         <v>1549</v>
@@ -23415,7 +23415,7 @@
         <v>1518</v>
       </c>
       <c r="E440">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F440" t="s">
         <v>1549</v>
@@ -23450,7 +23450,7 @@
         <v>1519</v>
       </c>
       <c r="E441">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F441" t="s">
         <v>1549</v>
@@ -23485,7 +23485,7 @@
         <v>1519</v>
       </c>
       <c r="E442">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F442" t="s">
         <v>1553</v>
@@ -23520,7 +23520,7 @@
         <v>1519</v>
       </c>
       <c r="E443">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F443" t="s">
         <v>1549</v>
@@ -23555,7 +23555,7 @@
         <v>1519</v>
       </c>
       <c r="E444">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F444" t="s">
         <v>1549</v>
@@ -23590,7 +23590,7 @@
         <v>1519</v>
       </c>
       <c r="E445">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F445" t="s">
         <v>1549</v>
@@ -23625,7 +23625,7 @@
         <v>1520</v>
       </c>
       <c r="E446">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F446" t="s">
         <v>1549</v>
@@ -23660,7 +23660,7 @@
         <v>1520</v>
       </c>
       <c r="E447">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F447" t="s">
         <v>1549</v>
@@ -23695,7 +23695,7 @@
         <v>1520</v>
       </c>
       <c r="E448">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F448" t="s">
         <v>1549</v>
@@ -23730,7 +23730,7 @@
         <v>1521</v>
       </c>
       <c r="E449">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F449" t="s">
         <v>1549</v>
@@ -23765,7 +23765,7 @@
         <v>1521</v>
       </c>
       <c r="E450">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F450" t="s">
         <v>1549</v>
@@ -23800,7 +23800,7 @@
         <v>1521</v>
       </c>
       <c r="E451">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F451" t="s">
         <v>1549</v>
@@ -23835,7 +23835,7 @@
         <v>1521</v>
       </c>
       <c r="E452">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F452" t="s">
         <v>1549</v>
@@ -23870,7 +23870,7 @@
         <v>1521</v>
       </c>
       <c r="E453">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F453" t="s">
         <v>1549</v>
@@ -23905,7 +23905,7 @@
         <v>1521</v>
       </c>
       <c r="E454">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F454" t="s">
         <v>1549</v>
@@ -23940,7 +23940,7 @@
         <v>1522</v>
       </c>
       <c r="E455">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F455" t="s">
         <v>1549</v>
@@ -23975,7 +23975,7 @@
         <v>1522</v>
       </c>
       <c r="E456">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F456" t="s">
         <v>1549</v>
@@ -24010,7 +24010,7 @@
         <v>1522</v>
       </c>
       <c r="E457">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F457" t="s">
         <v>1549</v>
@@ -24045,7 +24045,7 @@
         <v>1522</v>
       </c>
       <c r="E458">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F458" t="s">
         <v>1549</v>
@@ -24080,7 +24080,7 @@
         <v>1522</v>
       </c>
       <c r="E459">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F459" t="s">
         <v>1549</v>
@@ -24115,7 +24115,7 @@
         <v>1522</v>
       </c>
       <c r="E460">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F460" t="s">
         <v>1549</v>
@@ -24150,7 +24150,7 @@
         <v>1522</v>
       </c>
       <c r="E461">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F461" t="s">
         <v>1549</v>
@@ -24185,7 +24185,7 @@
         <v>1522</v>
       </c>
       <c r="E462">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F462" t="s">
         <v>1549</v>
@@ -24220,7 +24220,7 @@
         <v>1522</v>
       </c>
       <c r="E463">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F463" t="s">
         <v>1549</v>
@@ -24255,7 +24255,7 @@
         <v>1522</v>
       </c>
       <c r="E464">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F464" t="s">
         <v>1549</v>
@@ -24290,7 +24290,7 @@
         <v>1522</v>
       </c>
       <c r="E465">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F465" t="s">
         <v>1549</v>
@@ -24325,7 +24325,7 @@
         <v>1522</v>
       </c>
       <c r="E466">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F466" t="s">
         <v>1549</v>
@@ -24360,7 +24360,7 @@
         <v>1522</v>
       </c>
       <c r="E467">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F467" t="s">
         <v>1549</v>
@@ -24395,7 +24395,7 @@
         <v>1522</v>
       </c>
       <c r="E468">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F468" t="s">
         <v>1549</v>
@@ -24430,7 +24430,7 @@
         <v>1522</v>
       </c>
       <c r="E469">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F469" t="s">
         <v>1549</v>
@@ -24465,7 +24465,7 @@
         <v>1522</v>
       </c>
       <c r="E470">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F470" t="s">
         <v>1549</v>
@@ -24500,7 +24500,7 @@
         <v>1522</v>
       </c>
       <c r="E471">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F471" t="s">
         <v>1549</v>
@@ -24535,7 +24535,7 @@
         <v>1522</v>
       </c>
       <c r="E472">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F472" t="s">
         <v>1549</v>
@@ -24570,7 +24570,7 @@
         <v>1522</v>
       </c>
       <c r="E473">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F473" t="s">
         <v>1549</v>
@@ -24605,7 +24605,7 @@
         <v>1522</v>
       </c>
       <c r="E474">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F474" t="s">
         <v>1549</v>
@@ -24640,7 +24640,7 @@
         <v>1522</v>
       </c>
       <c r="E475">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F475" t="s">
         <v>1549</v>
@@ -24675,7 +24675,7 @@
         <v>1522</v>
       </c>
       <c r="E476">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F476" t="s">
         <v>1549</v>
@@ -24710,7 +24710,7 @@
         <v>1522</v>
       </c>
       <c r="E477">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F477" t="s">
         <v>1549</v>
@@ -24745,7 +24745,7 @@
         <v>1522</v>
       </c>
       <c r="E478">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F478" t="s">
         <v>1549</v>
@@ -24780,7 +24780,7 @@
         <v>1522</v>
       </c>
       <c r="E479">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F479" t="s">
         <v>1549</v>
@@ -24815,7 +24815,7 @@
         <v>1523</v>
       </c>
       <c r="E480">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F480" t="s">
         <v>1549</v>
@@ -24850,7 +24850,7 @@
         <v>1523</v>
       </c>
       <c r="E481">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F481" t="s">
         <v>1549</v>
@@ -24885,7 +24885,7 @@
         <v>1523</v>
       </c>
       <c r="E482">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F482" t="s">
         <v>1549</v>
@@ -24920,7 +24920,7 @@
         <v>1523</v>
       </c>
       <c r="E483">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F483" t="s">
         <v>1549</v>
@@ -24955,7 +24955,7 @@
         <v>1523</v>
       </c>
       <c r="E484">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F484" t="s">
         <v>1549</v>
@@ -24990,7 +24990,7 @@
         <v>1523</v>
       </c>
       <c r="E485">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F485" t="s">
         <v>1549</v>
@@ -25025,7 +25025,7 @@
         <v>1523</v>
       </c>
       <c r="E486">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F486" t="s">
         <v>1553</v>
@@ -25060,7 +25060,7 @@
         <v>1523</v>
       </c>
       <c r="E487">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F487" t="s">
         <v>1549</v>
@@ -25095,7 +25095,7 @@
         <v>1524</v>
       </c>
       <c r="E488">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F488" t="s">
         <v>1549</v>
@@ -25130,7 +25130,7 @@
         <v>1525</v>
       </c>
       <c r="E489">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F489" t="s">
         <v>1551</v>
@@ -25168,7 +25168,7 @@
         <v>1525</v>
       </c>
       <c r="E490">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F490" t="s">
         <v>1549</v>
@@ -25203,7 +25203,7 @@
         <v>1525</v>
       </c>
       <c r="E491">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F491" t="s">
         <v>1549</v>
@@ -25238,7 +25238,7 @@
         <v>1525</v>
       </c>
       <c r="E492">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F492" t="s">
         <v>1549</v>
@@ -25273,7 +25273,7 @@
         <v>1525</v>
       </c>
       <c r="E493">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F493" t="s">
         <v>1549</v>
@@ -25308,7 +25308,7 @@
         <v>1525</v>
       </c>
       <c r="E494">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F494" t="s">
         <v>1549</v>
@@ -25343,7 +25343,7 @@
         <v>1526</v>
       </c>
       <c r="E495">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F495" t="s">
         <v>1549</v>
@@ -25381,7 +25381,7 @@
         <v>1526</v>
       </c>
       <c r="E496">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F496" t="s">
         <v>1553</v>
@@ -25416,7 +25416,7 @@
         <v>1526</v>
       </c>
       <c r="E497">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F497" t="s">
         <v>1551</v>
@@ -25451,7 +25451,7 @@
         <v>1526</v>
       </c>
       <c r="E498">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F498" t="s">
         <v>1549</v>
@@ -25486,7 +25486,7 @@
         <v>1526</v>
       </c>
       <c r="E499">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F499" t="s">
         <v>1549</v>
@@ -25521,7 +25521,7 @@
         <v>1526</v>
       </c>
       <c r="E500">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F500" t="s">
         <v>1549</v>
@@ -25556,7 +25556,7 @@
         <v>1526</v>
       </c>
       <c r="E501">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F501" t="s">
         <v>1549</v>
@@ -25591,7 +25591,7 @@
         <v>1526</v>
       </c>
       <c r="E502">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F502" t="s">
         <v>1549</v>
@@ -25626,7 +25626,7 @@
         <v>1526</v>
       </c>
       <c r="E503">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F503" t="s">
         <v>1549</v>
@@ -25661,7 +25661,7 @@
         <v>1527</v>
       </c>
       <c r="E504">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F504" t="s">
         <v>1553</v>
@@ -25699,7 +25699,7 @@
         <v>1527</v>
       </c>
       <c r="E505">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F505" t="s">
         <v>1549</v>
@@ -25734,7 +25734,7 @@
         <v>1528</v>
       </c>
       <c r="E506">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F506" t="s">
         <v>1549</v>
@@ -25769,7 +25769,7 @@
         <v>1528</v>
       </c>
       <c r="E507">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F507" t="s">
         <v>1549</v>
@@ -25804,7 +25804,7 @@
         <v>1528</v>
       </c>
       <c r="E508">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F508" t="s">
         <v>1549</v>
@@ -25839,7 +25839,7 @@
         <v>1528</v>
       </c>
       <c r="E509">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F509" t="s">
         <v>1549</v>
@@ -25874,7 +25874,7 @@
         <v>1528</v>
       </c>
       <c r="E510">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F510" t="s">
         <v>1549</v>
@@ -25909,7 +25909,7 @@
         <v>1528</v>
       </c>
       <c r="E511">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F511" t="s">
         <v>1549</v>
@@ -25944,7 +25944,7 @@
         <v>1528</v>
       </c>
       <c r="E512">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F512" t="s">
         <v>1549</v>
@@ -25979,7 +25979,7 @@
         <v>1529</v>
       </c>
       <c r="E513">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F513" t="s">
         <v>1549</v>
@@ -26014,7 +26014,7 @@
         <v>1529</v>
       </c>
       <c r="E514">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F514" t="s">
         <v>1549</v>
@@ -26049,7 +26049,7 @@
         <v>1529</v>
       </c>
       <c r="E515">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F515" t="s">
         <v>1549</v>
@@ -26084,7 +26084,7 @@
         <v>1529</v>
       </c>
       <c r="E516">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F516" t="s">
         <v>1549</v>
@@ -26119,7 +26119,7 @@
         <v>1529</v>
       </c>
       <c r="E517">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F517" t="s">
         <v>1549</v>
@@ -26154,7 +26154,7 @@
         <v>1529</v>
       </c>
       <c r="E518">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F518" t="s">
         <v>1551</v>
@@ -26189,7 +26189,7 @@
         <v>1529</v>
       </c>
       <c r="E519">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F519" t="s">
         <v>1549</v>
@@ -26224,7 +26224,7 @@
         <v>1529</v>
       </c>
       <c r="E520">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F520" t="s">
         <v>1553</v>
@@ -26259,7 +26259,7 @@
         <v>1529</v>
       </c>
       <c r="E521">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F521" t="s">
         <v>1549</v>
@@ -26294,7 +26294,7 @@
         <v>1530</v>
       </c>
       <c r="E522">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F522" t="s">
         <v>1549</v>
@@ -26329,7 +26329,7 @@
         <v>1530</v>
       </c>
       <c r="E523">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F523" t="s">
         <v>1549</v>
@@ -26364,7 +26364,7 @@
         <v>1530</v>
       </c>
       <c r="E524">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F524" t="s">
         <v>1549</v>
@@ -26399,7 +26399,7 @@
         <v>1530</v>
       </c>
       <c r="E525">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F525" t="s">
         <v>1549</v>
@@ -26434,7 +26434,7 @@
         <v>1530</v>
       </c>
       <c r="E526">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F526" t="s">
         <v>1549</v>
@@ -26469,7 +26469,7 @@
         <v>1530</v>
       </c>
       <c r="E527">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F527" t="s">
         <v>1549</v>
@@ -26504,7 +26504,7 @@
         <v>1530</v>
       </c>
       <c r="E528">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F528" t="s">
         <v>1549</v>
@@ -26539,7 +26539,7 @@
         <v>1530</v>
       </c>
       <c r="E529">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F529" t="s">
         <v>1549</v>
@@ -26577,7 +26577,7 @@
         <v>1530</v>
       </c>
       <c r="E530">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F530" t="s">
         <v>1551</v>
@@ -26615,7 +26615,7 @@
         <v>1530</v>
       </c>
       <c r="E531">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F531" t="s">
         <v>1551</v>
@@ -26650,7 +26650,7 @@
         <v>1530</v>
       </c>
       <c r="E532">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F532" t="s">
         <v>1549</v>
@@ -26685,7 +26685,7 @@
         <v>1531</v>
       </c>
       <c r="E533">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F533" t="s">
         <v>1549</v>
@@ -26720,7 +26720,7 @@
         <v>1531</v>
       </c>
       <c r="E534">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F534" t="s">
         <v>1549</v>
@@ -26755,7 +26755,7 @@
         <v>1531</v>
       </c>
       <c r="E535">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F535" t="s">
         <v>1549</v>
@@ -26790,7 +26790,7 @@
         <v>1531</v>
       </c>
       <c r="E536">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F536" t="s">
         <v>1549</v>
@@ -26825,7 +26825,7 @@
         <v>1531</v>
       </c>
       <c r="E537">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F537" t="s">
         <v>1549</v>
@@ -26860,7 +26860,7 @@
         <v>1531</v>
       </c>
       <c r="E538">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F538" t="s">
         <v>1549</v>
@@ -26895,7 +26895,7 @@
         <v>1531</v>
       </c>
       <c r="E539">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F539" t="s">
         <v>1549</v>
@@ -26930,7 +26930,7 @@
         <v>1532</v>
       </c>
       <c r="E540">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F540" t="s">
         <v>1549</v>
@@ -26968,7 +26968,7 @@
         <v>1532</v>
       </c>
       <c r="E541">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F541" t="s">
         <v>1549</v>
@@ -27003,7 +27003,7 @@
         <v>1532</v>
       </c>
       <c r="E542">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F542" t="s">
         <v>1549</v>
@@ -27038,7 +27038,7 @@
         <v>1532</v>
       </c>
       <c r="E543">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F543" t="s">
         <v>1551</v>
@@ -27076,7 +27076,7 @@
         <v>1532</v>
       </c>
       <c r="E544">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F544" t="s">
         <v>1551</v>
@@ -27114,7 +27114,7 @@
         <v>1532</v>
       </c>
       <c r="E545">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F545" t="s">
         <v>1549</v>
@@ -27149,7 +27149,7 @@
         <v>1532</v>
       </c>
       <c r="E546">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F546" t="s">
         <v>1549</v>
@@ -27184,7 +27184,7 @@
         <v>1532</v>
       </c>
       <c r="E547">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F547" t="s">
         <v>1549</v>
@@ -27219,7 +27219,7 @@
         <v>1533</v>
       </c>
       <c r="E548">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F548" t="s">
         <v>1549</v>
@@ -27254,7 +27254,7 @@
         <v>1533</v>
       </c>
       <c r="E549">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F549" t="s">
         <v>1549</v>
@@ -27289,7 +27289,7 @@
         <v>1533</v>
       </c>
       <c r="E550">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F550" t="s">
         <v>1549</v>
@@ -27324,7 +27324,7 @@
         <v>1533</v>
       </c>
       <c r="E551">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F551" t="s">
         <v>1549</v>
@@ -27359,7 +27359,7 @@
         <v>1533</v>
       </c>
       <c r="E552">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F552" t="s">
         <v>1549</v>
@@ -27394,7 +27394,7 @@
         <v>1533</v>
       </c>
       <c r="E553">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F553" t="s">
         <v>1549</v>
@@ -27429,7 +27429,7 @@
         <v>1533</v>
       </c>
       <c r="E554">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F554" t="s">
         <v>1549</v>
@@ -27464,7 +27464,7 @@
         <v>1533</v>
       </c>
       <c r="E555">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F555" t="s">
         <v>1549</v>
@@ -27499,7 +27499,7 @@
         <v>1533</v>
       </c>
       <c r="E556">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F556" t="s">
         <v>1549</v>
@@ -27537,7 +27537,7 @@
         <v>1533</v>
       </c>
       <c r="E557">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F557" t="s">
         <v>1549</v>
@@ -27572,7 +27572,7 @@
         <v>1534</v>
       </c>
       <c r="E558">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F558" t="s">
         <v>1549</v>
@@ -27607,7 +27607,7 @@
         <v>1534</v>
       </c>
       <c r="E559">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F559" t="s">
         <v>1551</v>
@@ -27645,7 +27645,7 @@
         <v>1534</v>
       </c>
       <c r="E560">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F560" t="s">
         <v>1549</v>
@@ -27680,7 +27680,7 @@
         <v>1534</v>
       </c>
       <c r="E561">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F561" t="s">
         <v>1549</v>
@@ -27715,7 +27715,7 @@
         <v>1535</v>
       </c>
       <c r="E562">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F562" t="s">
         <v>1549</v>
@@ -27750,7 +27750,7 @@
         <v>1535</v>
       </c>
       <c r="E563">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F563" t="s">
         <v>1551</v>
@@ -27785,7 +27785,7 @@
         <v>1535</v>
       </c>
       <c r="E564">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F564" t="s">
         <v>1549</v>
@@ -27820,7 +27820,7 @@
         <v>1535</v>
       </c>
       <c r="E565">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F565" t="s">
         <v>1549</v>
@@ -27855,7 +27855,7 @@
         <v>1535</v>
       </c>
       <c r="E566">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F566" t="s">
         <v>1551</v>
@@ -27893,7 +27893,7 @@
         <v>1535</v>
       </c>
       <c r="E567">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F567" t="s">
         <v>1549</v>
@@ -27928,7 +27928,7 @@
         <v>1535</v>
       </c>
       <c r="E568">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F568" t="s">
         <v>1549</v>
@@ -27963,7 +27963,7 @@
         <v>1535</v>
       </c>
       <c r="E569">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F569" t="s">
         <v>1549</v>
@@ -27998,7 +27998,7 @@
         <v>1535</v>
       </c>
       <c r="E570">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F570" t="s">
         <v>1549</v>
@@ -28033,7 +28033,7 @@
         <v>1535</v>
       </c>
       <c r="E571">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F571" t="s">
         <v>1549</v>
@@ -28068,7 +28068,7 @@
         <v>1535</v>
       </c>
       <c r="E572">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F572" t="s">
         <v>1549</v>
@@ -28103,7 +28103,7 @@
         <v>1535</v>
       </c>
       <c r="E573">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F573" t="s">
         <v>1549</v>
@@ -28138,7 +28138,7 @@
         <v>1536</v>
       </c>
       <c r="E574">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F574" t="s">
         <v>1553</v>
@@ -28173,7 +28173,7 @@
         <v>1536</v>
       </c>
       <c r="E575">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F575" t="s">
         <v>1549</v>
@@ -28208,7 +28208,7 @@
         <v>1536</v>
       </c>
       <c r="E576">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F576" t="s">
         <v>1549</v>
@@ -28243,7 +28243,7 @@
         <v>1536</v>
       </c>
       <c r="E577">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F577" t="s">
         <v>1549</v>
@@ -28278,7 +28278,7 @@
         <v>1536</v>
       </c>
       <c r="E578">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F578" t="s">
         <v>1549</v>
@@ -28313,7 +28313,7 @@
         <v>1537</v>
       </c>
       <c r="E579">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F579" t="s">
         <v>1549</v>
@@ -28348,7 +28348,7 @@
         <v>1537</v>
       </c>
       <c r="E580">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F580" t="s">
         <v>1549</v>
@@ -28383,7 +28383,7 @@
         <v>1537</v>
       </c>
       <c r="E581">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F581" t="s">
         <v>1549</v>
@@ -28418,7 +28418,7 @@
         <v>1537</v>
       </c>
       <c r="E582">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F582" t="s">
         <v>1551</v>
@@ -28456,7 +28456,7 @@
         <v>1538</v>
       </c>
       <c r="E583">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F583" t="s">
         <v>1549</v>
@@ -28491,7 +28491,7 @@
         <v>1538</v>
       </c>
       <c r="E584">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F584" t="s">
         <v>1553</v>
@@ -28529,7 +28529,7 @@
         <v>1538</v>
       </c>
       <c r="E585">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F585" t="s">
         <v>1549</v>
@@ -28564,7 +28564,7 @@
         <v>1538</v>
       </c>
       <c r="E586">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F586" t="s">
         <v>1549</v>
@@ -28599,7 +28599,7 @@
         <v>1539</v>
       </c>
       <c r="E587">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F587" t="s">
         <v>1549</v>
@@ -28634,7 +28634,7 @@
         <v>1539</v>
       </c>
       <c r="E588">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F588" t="s">
         <v>1549</v>
@@ -28669,7 +28669,7 @@
         <v>1539</v>
       </c>
       <c r="E589">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F589" t="s">
         <v>1551</v>
@@ -28704,7 +28704,7 @@
         <v>1539</v>
       </c>
       <c r="E590">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F590" t="s">
         <v>1549</v>
@@ -28739,7 +28739,7 @@
         <v>1539</v>
       </c>
       <c r="E591">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F591" t="s">
         <v>1549</v>
@@ -28774,7 +28774,7 @@
         <v>1539</v>
       </c>
       <c r="E592">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F592" t="s">
         <v>1549</v>
@@ -28809,7 +28809,7 @@
         <v>1539</v>
       </c>
       <c r="E593">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F593" t="s">
         <v>1551</v>
@@ -28847,7 +28847,7 @@
         <v>1539</v>
       </c>
       <c r="E594">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F594" t="s">
         <v>1549</v>
@@ -28882,7 +28882,7 @@
         <v>1539</v>
       </c>
       <c r="E595">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F595" t="s">
         <v>1549</v>
@@ -28917,7 +28917,7 @@
         <v>1539</v>
       </c>
       <c r="E596">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F596" t="s">
         <v>1549</v>
@@ -28952,7 +28952,7 @@
         <v>1540</v>
       </c>
       <c r="E597">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F597" t="s">
         <v>1549</v>
@@ -28987,7 +28987,7 @@
         <v>1540</v>
       </c>
       <c r="E598">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F598" t="s">
         <v>1551</v>
@@ -29022,7 +29022,7 @@
         <v>1540</v>
       </c>
       <c r="E599">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F599" t="s">
         <v>1549</v>
@@ -29057,7 +29057,7 @@
         <v>1541</v>
       </c>
       <c r="E600">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F600" t="s">
         <v>1551</v>
@@ -29095,7 +29095,7 @@
         <v>1541</v>
       </c>
       <c r="E601">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F601" t="s">
         <v>1551</v>
@@ -29133,7 +29133,7 @@
         <v>1541</v>
       </c>
       <c r="E602">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F602" t="s">
         <v>1549</v>
@@ -29168,7 +29168,7 @@
         <v>1541</v>
       </c>
       <c r="E603">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F603" t="s">
         <v>1549</v>
@@ -29203,7 +29203,7 @@
         <v>1541</v>
       </c>
       <c r="E604">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F604" t="s">
         <v>1549</v>
@@ -29238,7 +29238,7 @@
         <v>1542</v>
       </c>
       <c r="E605">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F605" t="s">
         <v>1549</v>
@@ -29273,7 +29273,7 @@
         <v>1543</v>
       </c>
       <c r="E606">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F606" t="s">
         <v>1549</v>
@@ -29308,7 +29308,7 @@
         <v>1543</v>
       </c>
       <c r="E607">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F607" t="s">
         <v>1549</v>
@@ -29343,7 +29343,7 @@
         <v>1543</v>
       </c>
       <c r="E608">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F608" t="s">
         <v>1549</v>
@@ -29378,7 +29378,7 @@
         <v>1543</v>
       </c>
       <c r="E609">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F609" t="s">
         <v>1549</v>
@@ -29413,7 +29413,7 @@
         <v>1543</v>
       </c>
       <c r="E610">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F610" t="s">
         <v>1549</v>
@@ -29448,7 +29448,7 @@
         <v>1543</v>
       </c>
       <c r="E611">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F611" t="s">
         <v>1549</v>
@@ -29483,7 +29483,7 @@
         <v>1543</v>
       </c>
       <c r="E612">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F612" t="s">
         <v>1549</v>
@@ -29518,7 +29518,7 @@
         <v>1543</v>
       </c>
       <c r="E613">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F613" t="s">
         <v>1549</v>
@@ -29553,7 +29553,7 @@
         <v>1543</v>
       </c>
       <c r="E614">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F614" t="s">
         <v>1549</v>
@@ -29588,7 +29588,7 @@
         <v>1543</v>
       </c>
       <c r="E615">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F615" t="s">
         <v>1551</v>
@@ -29626,7 +29626,7 @@
         <v>1544</v>
       </c>
       <c r="E616">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F616" t="s">
         <v>1549</v>
@@ -29661,7 +29661,7 @@
         <v>1544</v>
       </c>
       <c r="E617">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F617" t="s">
         <v>1549</v>
@@ -29696,7 +29696,7 @@
         <v>1544</v>
       </c>
       <c r="E618">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F618" t="s">
         <v>1549</v>
@@ -29731,7 +29731,7 @@
         <v>1544</v>
       </c>
       <c r="E619">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F619" t="s">
         <v>1549</v>
@@ -29766,7 +29766,7 @@
         <v>1544</v>
       </c>
       <c r="E620">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F620" t="s">
         <v>1551</v>
@@ -29804,7 +29804,7 @@
         <v>1544</v>
       </c>
       <c r="E621">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F621" t="s">
         <v>1551</v>
@@ -29842,7 +29842,7 @@
         <v>1544</v>
       </c>
       <c r="E622">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F622" t="s">
         <v>1549</v>
@@ -29877,7 +29877,7 @@
         <v>1544</v>
       </c>
       <c r="E623">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F623" t="s">
         <v>1551</v>
@@ -29915,7 +29915,7 @@
         <v>1544</v>
       </c>
       <c r="E624">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F624" t="s">
         <v>1549</v>
@@ -29950,7 +29950,7 @@
         <v>1544</v>
       </c>
       <c r="E625">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F625" t="s">
         <v>1549</v>
@@ -29985,7 +29985,7 @@
         <v>1544</v>
       </c>
       <c r="E626">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F626" t="s">
         <v>1549</v>
@@ -30020,7 +30020,7 @@
         <v>1545</v>
       </c>
       <c r="E627">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F627" t="s">
         <v>1549</v>
@@ -30055,7 +30055,7 @@
         <v>1545</v>
       </c>
       <c r="E628">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F628" t="s">
         <v>1551</v>
@@ -30093,7 +30093,7 @@
         <v>1545</v>
       </c>
       <c r="E629">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F629" t="s">
         <v>1551</v>
@@ -30131,7 +30131,7 @@
         <v>1545</v>
       </c>
       <c r="E630">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F630" t="s">
         <v>1549</v>
@@ -30166,7 +30166,7 @@
         <v>1546</v>
       </c>
       <c r="E631">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F631" t="s">
         <v>1551</v>
@@ -30204,7 +30204,7 @@
         <v>1546</v>
       </c>
       <c r="E632">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F632" t="s">
         <v>1549</v>
@@ -30239,7 +30239,7 @@
         <v>1546</v>
       </c>
       <c r="E633">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F633" t="s">
         <v>1551</v>
@@ -30277,7 +30277,7 @@
         <v>1546</v>
       </c>
       <c r="E634">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F634" t="s">
         <v>1549</v>
@@ -30312,7 +30312,7 @@
         <v>1547</v>
       </c>
       <c r="E635">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F635" t="s">
         <v>1549</v>
@@ -30347,7 +30347,7 @@
         <v>1547</v>
       </c>
       <c r="E636">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F636" t="s">
         <v>1549</v>
@@ -30382,7 +30382,7 @@
         <v>1547</v>
       </c>
       <c r="E637">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F637" t="s">
         <v>1549</v>
@@ -30417,7 +30417,7 @@
         <v>1547</v>
       </c>
       <c r="E638">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F638" t="s">
         <v>1549</v>
@@ -30452,7 +30452,7 @@
         <v>1547</v>
       </c>
       <c r="E639">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F639" t="s">
         <v>1549</v>
@@ -30487,7 +30487,7 @@
         <v>1547</v>
       </c>
       <c r="E640">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F640" t="s">
         <v>1549</v>
@@ -30522,7 +30522,7 @@
         <v>1547</v>
       </c>
       <c r="E641">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F641" t="s">
         <v>1549</v>
@@ -30560,7 +30560,7 @@
         <v>1547</v>
       </c>
       <c r="E642">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F642" t="s">
         <v>1551</v>
@@ -30598,7 +30598,7 @@
         <v>1547</v>
       </c>
       <c r="E643">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F643" t="s">
         <v>1549</v>
@@ -30636,7 +30636,7 @@
         <v>1548</v>
       </c>
       <c r="E644">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F644" t="s">
         <v>1549</v>
@@ -30671,7 +30671,7 @@
         <v>1548</v>
       </c>
       <c r="E645">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F645" t="s">
         <v>1549</v>
@@ -30706,7 +30706,7 @@
         <v>1548</v>
       </c>
       <c r="E646">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F646" t="s">
         <v>1549</v>
@@ -30741,7 +30741,7 @@
         <v>1548</v>
       </c>
       <c r="E647">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F647" t="s">
         <v>1549</v>
@@ -30776,7 +30776,7 @@
         <v>1548</v>
       </c>
       <c r="E648">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F648" t="s">
         <v>1549</v>
@@ -30811,7 +30811,7 @@
         <v>1548</v>
       </c>
       <c r="E649">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F649" t="s">
         <v>1551</v>

--- a/BacklogGATEAutoCompleto.xlsx
+++ b/BacklogGATEAutoCompleto.xlsx
@@ -8085,7 +8085,7 @@
         <v>1341</v>
       </c>
       <c r="E2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="F2" t="s">
         <v>1552</v>
@@ -8120,7 +8120,7 @@
         <v>1342</v>
       </c>
       <c r="E3">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="F3" t="s">
         <v>1552</v>
@@ -8155,7 +8155,7 @@
         <v>1343</v>
       </c>
       <c r="E4">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="F4" t="s">
         <v>1552</v>
@@ -8190,7 +8190,7 @@
         <v>1344</v>
       </c>
       <c r="E5">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="F5" t="s">
         <v>1552</v>
@@ -8225,7 +8225,7 @@
         <v>1345</v>
       </c>
       <c r="E6">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="F6" t="s">
         <v>1552</v>
@@ -8260,7 +8260,7 @@
         <v>1346</v>
       </c>
       <c r="E7">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="F7" t="s">
         <v>1552</v>
@@ -8295,7 +8295,7 @@
         <v>1347</v>
       </c>
       <c r="E8">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="F8" t="s">
         <v>1552</v>
@@ -8330,7 +8330,7 @@
         <v>1348</v>
       </c>
       <c r="E9">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="F9" t="s">
         <v>1552</v>
@@ -8365,7 +8365,7 @@
         <v>1349</v>
       </c>
       <c r="E10">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="F10" t="s">
         <v>1552</v>
@@ -8400,7 +8400,7 @@
         <v>1349</v>
       </c>
       <c r="E11">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="F11" t="s">
         <v>1552</v>
@@ -8435,7 +8435,7 @@
         <v>1350</v>
       </c>
       <c r="E12">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="F12" t="s">
         <v>1552</v>
@@ -8470,7 +8470,7 @@
         <v>1351</v>
       </c>
       <c r="E13">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="F13" t="s">
         <v>1552</v>
@@ -8505,7 +8505,7 @@
         <v>1352</v>
       </c>
       <c r="E14">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="F14" t="s">
         <v>1552</v>
@@ -8540,7 +8540,7 @@
         <v>1352</v>
       </c>
       <c r="E15">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="F15" t="s">
         <v>1552</v>
@@ -8575,7 +8575,7 @@
         <v>1353</v>
       </c>
       <c r="E16">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="F16" t="s">
         <v>1552</v>
@@ -8610,7 +8610,7 @@
         <v>1353</v>
       </c>
       <c r="E17">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="F17" t="s">
         <v>1552</v>
@@ -8645,7 +8645,7 @@
         <v>1354</v>
       </c>
       <c r="E18">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F18" t="s">
         <v>1552</v>
@@ -8680,7 +8680,7 @@
         <v>1355</v>
       </c>
       <c r="E19">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="F19" t="s">
         <v>1552</v>
@@ -8715,7 +8715,7 @@
         <v>1356</v>
       </c>
       <c r="E20">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="F20" t="s">
         <v>1552</v>
@@ -8750,7 +8750,7 @@
         <v>1357</v>
       </c>
       <c r="E21">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F21" t="s">
         <v>1552</v>
@@ -8785,7 +8785,7 @@
         <v>1358</v>
       </c>
       <c r="E22">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="F22" t="s">
         <v>1552</v>
@@ -8823,7 +8823,7 @@
         <v>1359</v>
       </c>
       <c r="E23">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="F23" t="s">
         <v>1552</v>
@@ -8858,7 +8858,7 @@
         <v>1360</v>
       </c>
       <c r="E24">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F24" t="s">
         <v>1552</v>
@@ -8893,7 +8893,7 @@
         <v>1361</v>
       </c>
       <c r="E25">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F25" t="s">
         <v>1552</v>
@@ -8928,7 +8928,7 @@
         <v>1362</v>
       </c>
       <c r="E26">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F26" t="s">
         <v>1552</v>
@@ -8963,7 +8963,7 @@
         <v>1363</v>
       </c>
       <c r="E27">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F27" t="s">
         <v>1552</v>
@@ -8998,7 +8998,7 @@
         <v>1364</v>
       </c>
       <c r="E28">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F28" t="s">
         <v>1552</v>
@@ -9033,7 +9033,7 @@
         <v>1365</v>
       </c>
       <c r="E29">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F29" t="s">
         <v>1552</v>
@@ -9068,7 +9068,7 @@
         <v>1366</v>
       </c>
       <c r="E30">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F30" t="s">
         <v>1552</v>
@@ -9103,7 +9103,7 @@
         <v>1367</v>
       </c>
       <c r="E31">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F31" t="s">
         <v>1552</v>
@@ -9138,7 +9138,7 @@
         <v>1368</v>
       </c>
       <c r="E32">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F32" t="s">
         <v>1552</v>
@@ -9173,7 +9173,7 @@
         <v>1368</v>
       </c>
       <c r="E33">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F33" t="s">
         <v>1552</v>
@@ -9208,7 +9208,7 @@
         <v>1369</v>
       </c>
       <c r="E34">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F34" t="s">
         <v>1552</v>
@@ -9243,7 +9243,7 @@
         <v>1370</v>
       </c>
       <c r="E35">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F35" t="s">
         <v>1552</v>
@@ -9278,7 +9278,7 @@
         <v>1371</v>
       </c>
       <c r="E36">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F36" t="s">
         <v>1552</v>
@@ -9313,7 +9313,7 @@
         <v>1372</v>
       </c>
       <c r="E37">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F37" t="s">
         <v>1552</v>
@@ -9348,7 +9348,7 @@
         <v>1373</v>
       </c>
       <c r="E38">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F38" t="s">
         <v>1552</v>
@@ -9383,7 +9383,7 @@
         <v>1373</v>
       </c>
       <c r="E39">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F39" t="s">
         <v>1552</v>
@@ -9418,7 +9418,7 @@
         <v>1374</v>
       </c>
       <c r="E40">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F40" t="s">
         <v>1552</v>
@@ -9453,7 +9453,7 @@
         <v>1375</v>
       </c>
       <c r="E41">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F41" t="s">
         <v>1552</v>
@@ -9488,7 +9488,7 @@
         <v>1376</v>
       </c>
       <c r="E42">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F42" t="s">
         <v>1552</v>
@@ -9523,7 +9523,7 @@
         <v>1376</v>
       </c>
       <c r="E43">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F43" t="s">
         <v>1552</v>
@@ -9558,7 +9558,7 @@
         <v>1377</v>
       </c>
       <c r="E44">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F44" t="s">
         <v>1552</v>
@@ -9593,7 +9593,7 @@
         <v>1377</v>
       </c>
       <c r="E45">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F45" t="s">
         <v>1552</v>
@@ -9628,7 +9628,7 @@
         <v>1378</v>
       </c>
       <c r="E46">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F46" t="s">
         <v>1552</v>
@@ -9663,7 +9663,7 @@
         <v>1379</v>
       </c>
       <c r="E47">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F47" t="s">
         <v>1552</v>
@@ -9698,7 +9698,7 @@
         <v>1380</v>
       </c>
       <c r="E48">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F48" t="s">
         <v>1552</v>
@@ -9733,7 +9733,7 @@
         <v>1381</v>
       </c>
       <c r="E49">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F49" t="s">
         <v>1552</v>
@@ -9768,7 +9768,7 @@
         <v>1381</v>
       </c>
       <c r="E50">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F50" t="s">
         <v>1552</v>
@@ -9803,7 +9803,7 @@
         <v>1382</v>
       </c>
       <c r="E51">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F51" t="s">
         <v>1552</v>
@@ -9838,7 +9838,7 @@
         <v>1383</v>
       </c>
       <c r="E52">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F52" t="s">
         <v>1552</v>
@@ -9873,7 +9873,7 @@
         <v>1384</v>
       </c>
       <c r="E53">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F53" t="s">
         <v>1552</v>
@@ -9908,7 +9908,7 @@
         <v>1385</v>
       </c>
       <c r="E54">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F54" t="s">
         <v>1552</v>
@@ -9943,7 +9943,7 @@
         <v>1386</v>
       </c>
       <c r="E55">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F55" t="s">
         <v>1552</v>
@@ -9978,7 +9978,7 @@
         <v>1387</v>
       </c>
       <c r="E56">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F56" t="s">
         <v>1552</v>
@@ -10013,7 +10013,7 @@
         <v>1388</v>
       </c>
       <c r="E57">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F57" t="s">
         <v>1552</v>
@@ -10048,7 +10048,7 @@
         <v>1388</v>
       </c>
       <c r="E58">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F58" t="s">
         <v>1552</v>
@@ -10083,7 +10083,7 @@
         <v>1388</v>
       </c>
       <c r="E59">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F59" t="s">
         <v>1552</v>
@@ -10118,7 +10118,7 @@
         <v>1389</v>
       </c>
       <c r="E60">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F60" t="s">
         <v>1552</v>
@@ -10153,7 +10153,7 @@
         <v>1390</v>
       </c>
       <c r="E61">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F61" t="s">
         <v>1552</v>
@@ -10188,7 +10188,7 @@
         <v>1391</v>
       </c>
       <c r="E62">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F62" t="s">
         <v>1552</v>
@@ -10223,7 +10223,7 @@
         <v>1391</v>
       </c>
       <c r="E63">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F63" t="s">
         <v>1552</v>
@@ -10258,7 +10258,7 @@
         <v>1392</v>
       </c>
       <c r="E64">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F64" t="s">
         <v>1552</v>
@@ -10293,7 +10293,7 @@
         <v>1393</v>
       </c>
       <c r="E65">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F65" t="s">
         <v>1552</v>
@@ -10328,7 +10328,7 @@
         <v>1393</v>
       </c>
       <c r="E66">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F66" t="s">
         <v>1552</v>
@@ -10363,7 +10363,7 @@
         <v>1393</v>
       </c>
       <c r="E67">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F67" t="s">
         <v>1552</v>
@@ -10398,7 +10398,7 @@
         <v>1394</v>
       </c>
       <c r="E68">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F68" t="s">
         <v>1552</v>
@@ -10433,7 +10433,7 @@
         <v>1395</v>
       </c>
       <c r="E69">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F69" t="s">
         <v>1552</v>
@@ -10468,7 +10468,7 @@
         <v>1395</v>
       </c>
       <c r="E70">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F70" t="s">
         <v>1552</v>
@@ -10503,7 +10503,7 @@
         <v>1395</v>
       </c>
       <c r="E71">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F71" t="s">
         <v>1553</v>
@@ -10538,7 +10538,7 @@
         <v>1395</v>
       </c>
       <c r="E72">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F72" t="s">
         <v>1552</v>
@@ -10573,7 +10573,7 @@
         <v>1396</v>
       </c>
       <c r="E73">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F73" t="s">
         <v>1552</v>
@@ -10608,7 +10608,7 @@
         <v>1397</v>
       </c>
       <c r="E74">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F74" t="s">
         <v>1552</v>
@@ -10643,7 +10643,7 @@
         <v>1397</v>
       </c>
       <c r="E75">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F75" t="s">
         <v>1552</v>
@@ -10678,7 +10678,7 @@
         <v>1398</v>
       </c>
       <c r="E76">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F76" t="s">
         <v>1552</v>
@@ -10713,7 +10713,7 @@
         <v>1399</v>
       </c>
       <c r="E77">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F77" t="s">
         <v>1552</v>
@@ -10748,7 +10748,7 @@
         <v>1400</v>
       </c>
       <c r="E78">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F78" t="s">
         <v>1552</v>
@@ -10783,7 +10783,7 @@
         <v>1401</v>
       </c>
       <c r="E79">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F79" t="s">
         <v>1552</v>
@@ -10818,7 +10818,7 @@
         <v>1401</v>
       </c>
       <c r="E80">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F80" t="s">
         <v>1552</v>
@@ -10853,7 +10853,7 @@
         <v>1401</v>
       </c>
       <c r="E81">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F81" t="s">
         <v>1552</v>
@@ -10888,7 +10888,7 @@
         <v>1401</v>
       </c>
       <c r="E82">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F82" t="s">
         <v>1552</v>
@@ -10923,7 +10923,7 @@
         <v>1401</v>
       </c>
       <c r="E83">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F83" t="s">
         <v>1552</v>
@@ -10958,7 +10958,7 @@
         <v>1401</v>
       </c>
       <c r="E84">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F84" t="s">
         <v>1552</v>
@@ -10993,7 +10993,7 @@
         <v>1402</v>
       </c>
       <c r="E85">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F85" t="s">
         <v>1552</v>
@@ -11028,7 +11028,7 @@
         <v>1403</v>
       </c>
       <c r="E86">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F86" t="s">
         <v>1552</v>
@@ -11063,7 +11063,7 @@
         <v>1404</v>
       </c>
       <c r="E87">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F87" t="s">
         <v>1552</v>
@@ -11098,7 +11098,7 @@
         <v>1404</v>
       </c>
       <c r="E88">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F88" t="s">
         <v>1552</v>
@@ -11133,7 +11133,7 @@
         <v>1405</v>
       </c>
       <c r="E89">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F89" t="s">
         <v>1554</v>
@@ -11168,7 +11168,7 @@
         <v>1406</v>
       </c>
       <c r="E90">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F90" t="s">
         <v>1552</v>
@@ -11203,7 +11203,7 @@
         <v>1407</v>
       </c>
       <c r="E91">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F91" t="s">
         <v>1552</v>
@@ -11238,7 +11238,7 @@
         <v>1407</v>
       </c>
       <c r="E92">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F92" t="s">
         <v>1552</v>
@@ -11273,7 +11273,7 @@
         <v>1408</v>
       </c>
       <c r="E93">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F93" t="s">
         <v>1552</v>
@@ -11308,7 +11308,7 @@
         <v>1409</v>
       </c>
       <c r="E94">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F94" t="s">
         <v>1552</v>
@@ -11343,7 +11343,7 @@
         <v>1410</v>
       </c>
       <c r="E95">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F95" t="s">
         <v>1552</v>
@@ -11378,7 +11378,7 @@
         <v>1411</v>
       </c>
       <c r="E96">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F96" t="s">
         <v>1552</v>
@@ -11413,7 +11413,7 @@
         <v>1412</v>
       </c>
       <c r="E97">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F97" t="s">
         <v>1552</v>
@@ -11448,7 +11448,7 @@
         <v>1412</v>
       </c>
       <c r="E98">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F98" t="s">
         <v>1552</v>
@@ -11483,7 +11483,7 @@
         <v>1413</v>
       </c>
       <c r="E99">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F99" t="s">
         <v>1552</v>
@@ -11518,7 +11518,7 @@
         <v>1413</v>
       </c>
       <c r="E100">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F100" t="s">
         <v>1552</v>
@@ -11553,7 +11553,7 @@
         <v>1413</v>
       </c>
       <c r="E101">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F101" t="s">
         <v>1552</v>
@@ -11588,7 +11588,7 @@
         <v>1414</v>
       </c>
       <c r="E102">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F102" t="s">
         <v>1552</v>
@@ -11623,7 +11623,7 @@
         <v>1414</v>
       </c>
       <c r="E103">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F103" t="s">
         <v>1552</v>
@@ -11658,7 +11658,7 @@
         <v>1415</v>
       </c>
       <c r="E104">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F104" t="s">
         <v>1552</v>
@@ -11693,7 +11693,7 @@
         <v>1416</v>
       </c>
       <c r="E105">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F105" t="s">
         <v>1552</v>
@@ -11728,7 +11728,7 @@
         <v>1417</v>
       </c>
       <c r="E106">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F106" t="s">
         <v>1552</v>
@@ -11763,7 +11763,7 @@
         <v>1417</v>
       </c>
       <c r="E107">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F107" t="s">
         <v>1552</v>
@@ -11798,7 +11798,7 @@
         <v>1418</v>
       </c>
       <c r="E108">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F108" t="s">
         <v>1552</v>
@@ -11833,7 +11833,7 @@
         <v>1418</v>
       </c>
       <c r="E109">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F109" t="s">
         <v>1552</v>
@@ -11868,7 +11868,7 @@
         <v>1419</v>
       </c>
       <c r="E110">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F110" t="s">
         <v>1552</v>
@@ -11903,7 +11903,7 @@
         <v>1420</v>
       </c>
       <c r="E111">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F111" t="s">
         <v>1552</v>
@@ -11938,7 +11938,7 @@
         <v>1420</v>
       </c>
       <c r="E112">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F112" t="s">
         <v>1552</v>
@@ -11973,7 +11973,7 @@
         <v>1421</v>
       </c>
       <c r="E113">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F113" t="s">
         <v>1552</v>
@@ -12008,7 +12008,7 @@
         <v>1422</v>
       </c>
       <c r="E114">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F114" t="s">
         <v>1552</v>
@@ -12043,7 +12043,7 @@
         <v>1422</v>
       </c>
       <c r="E115">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F115" t="s">
         <v>1552</v>
@@ -12078,7 +12078,7 @@
         <v>1423</v>
       </c>
       <c r="E116">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F116" t="s">
         <v>1552</v>
@@ -12113,7 +12113,7 @@
         <v>1424</v>
       </c>
       <c r="E117">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F117" t="s">
         <v>1552</v>
@@ -12151,7 +12151,7 @@
         <v>1424</v>
       </c>
       <c r="E118">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F118" t="s">
         <v>1552</v>
@@ -12186,7 +12186,7 @@
         <v>1424</v>
       </c>
       <c r="E119">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F119" t="s">
         <v>1552</v>
@@ -12221,7 +12221,7 @@
         <v>1424</v>
       </c>
       <c r="E120">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F120" t="s">
         <v>1552</v>
@@ -12256,7 +12256,7 @@
         <v>1425</v>
       </c>
       <c r="E121">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F121" t="s">
         <v>1553</v>
@@ -12291,7 +12291,7 @@
         <v>1426</v>
       </c>
       <c r="E122">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F122" t="s">
         <v>1552</v>
@@ -12326,7 +12326,7 @@
         <v>1426</v>
       </c>
       <c r="E123">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F123" t="s">
         <v>1552</v>
@@ -12361,7 +12361,7 @@
         <v>1426</v>
       </c>
       <c r="E124">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F124" t="s">
         <v>1552</v>
@@ -12396,7 +12396,7 @@
         <v>1426</v>
       </c>
       <c r="E125">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F125" t="s">
         <v>1552</v>
@@ -12431,7 +12431,7 @@
         <v>1427</v>
       </c>
       <c r="E126">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F126" t="s">
         <v>1552</v>
@@ -12466,7 +12466,7 @@
         <v>1427</v>
       </c>
       <c r="E127">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F127" t="s">
         <v>1552</v>
@@ -12501,7 +12501,7 @@
         <v>1427</v>
       </c>
       <c r="E128">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F128" t="s">
         <v>1552</v>
@@ -12536,7 +12536,7 @@
         <v>1427</v>
       </c>
       <c r="E129">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F129" t="s">
         <v>1552</v>
@@ -12571,7 +12571,7 @@
         <v>1427</v>
       </c>
       <c r="E130">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F130" t="s">
         <v>1552</v>
@@ -12606,7 +12606,7 @@
         <v>1427</v>
       </c>
       <c r="E131">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F131" t="s">
         <v>1552</v>
@@ -12641,7 +12641,7 @@
         <v>1427</v>
       </c>
       <c r="E132">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F132" t="s">
         <v>1552</v>
@@ -12676,7 +12676,7 @@
         <v>1428</v>
       </c>
       <c r="E133">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F133" t="s">
         <v>1552</v>
@@ -12711,7 +12711,7 @@
         <v>1428</v>
       </c>
       <c r="E134">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F134" t="s">
         <v>1552</v>
@@ -12746,7 +12746,7 @@
         <v>1429</v>
       </c>
       <c r="E135">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F135" t="s">
         <v>1552</v>
@@ -12781,7 +12781,7 @@
         <v>1430</v>
       </c>
       <c r="E136">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F136" t="s">
         <v>1552</v>
@@ -12816,7 +12816,7 @@
         <v>1430</v>
       </c>
       <c r="E137">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F137" t="s">
         <v>1552</v>
@@ -12851,7 +12851,7 @@
         <v>1430</v>
       </c>
       <c r="E138">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F138" t="s">
         <v>1552</v>
@@ -12886,7 +12886,7 @@
         <v>1431</v>
       </c>
       <c r="E139">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F139" t="s">
         <v>1552</v>
@@ -12921,7 +12921,7 @@
         <v>1431</v>
       </c>
       <c r="E140">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F140" t="s">
         <v>1552</v>
@@ -12956,7 +12956,7 @@
         <v>1431</v>
       </c>
       <c r="E141">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F141" t="s">
         <v>1552</v>
@@ -12991,7 +12991,7 @@
         <v>1431</v>
       </c>
       <c r="E142">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F142" t="s">
         <v>1552</v>
@@ -13026,7 +13026,7 @@
         <v>1431</v>
       </c>
       <c r="E143">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F143" t="s">
         <v>1552</v>
@@ -13061,7 +13061,7 @@
         <v>1431</v>
       </c>
       <c r="E144">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F144" t="s">
         <v>1552</v>
@@ -13096,7 +13096,7 @@
         <v>1431</v>
       </c>
       <c r="E145">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F145" t="s">
         <v>1552</v>
@@ -13131,7 +13131,7 @@
         <v>1431</v>
       </c>
       <c r="E146">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F146" t="s">
         <v>1552</v>
@@ -13166,7 +13166,7 @@
         <v>1431</v>
       </c>
       <c r="E147">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F147" t="s">
         <v>1552</v>
@@ -13201,7 +13201,7 @@
         <v>1431</v>
       </c>
       <c r="E148">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F148" t="s">
         <v>1552</v>
@@ -13236,7 +13236,7 @@
         <v>1432</v>
       </c>
       <c r="E149">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F149" t="s">
         <v>1552</v>
@@ -13271,7 +13271,7 @@
         <v>1432</v>
       </c>
       <c r="E150">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F150" t="s">
         <v>1552</v>
@@ -13306,7 +13306,7 @@
         <v>1432</v>
       </c>
       <c r="E151">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F151" t="s">
         <v>1552</v>
@@ -13341,7 +13341,7 @@
         <v>1433</v>
       </c>
       <c r="E152">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F152" t="s">
         <v>1552</v>
@@ -13376,7 +13376,7 @@
         <v>1433</v>
       </c>
       <c r="E153">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F153" t="s">
         <v>1553</v>
@@ -13411,7 +13411,7 @@
         <v>1433</v>
       </c>
       <c r="E154">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F154" t="s">
         <v>1552</v>
@@ -13446,7 +13446,7 @@
         <v>1434</v>
       </c>
       <c r="E155">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F155" t="s">
         <v>1552</v>
@@ -13481,7 +13481,7 @@
         <v>1434</v>
       </c>
       <c r="E156">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F156" t="s">
         <v>1552</v>
@@ -13516,7 +13516,7 @@
         <v>1435</v>
       </c>
       <c r="E157">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F157" t="s">
         <v>1552</v>
@@ -13551,7 +13551,7 @@
         <v>1435</v>
       </c>
       <c r="E158">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F158" t="s">
         <v>1552</v>
@@ -13586,7 +13586,7 @@
         <v>1436</v>
       </c>
       <c r="E159">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F159" t="s">
         <v>1552</v>
@@ -13621,7 +13621,7 @@
         <v>1436</v>
       </c>
       <c r="E160">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F160" t="s">
         <v>1552</v>
@@ -13656,7 +13656,7 @@
         <v>1437</v>
       </c>
       <c r="E161">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F161" t="s">
         <v>1552</v>
@@ -13691,7 +13691,7 @@
         <v>1437</v>
       </c>
       <c r="E162">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F162" t="s">
         <v>1552</v>
@@ -13726,7 +13726,7 @@
         <v>1437</v>
       </c>
       <c r="E163">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F163" t="s">
         <v>1552</v>
@@ -13761,7 +13761,7 @@
         <v>1438</v>
       </c>
       <c r="E164">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F164" t="s">
         <v>1552</v>
@@ -13796,7 +13796,7 @@
         <v>1438</v>
       </c>
       <c r="E165">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F165" t="s">
         <v>1552</v>
@@ -13831,7 +13831,7 @@
         <v>1439</v>
       </c>
       <c r="E166">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F166" t="s">
         <v>1552</v>
@@ -13866,7 +13866,7 @@
         <v>1440</v>
       </c>
       <c r="E167">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F167" t="s">
         <v>1552</v>
@@ -13901,7 +13901,7 @@
         <v>1440</v>
       </c>
       <c r="E168">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F168" t="s">
         <v>1552</v>
@@ -13936,7 +13936,7 @@
         <v>1440</v>
       </c>
       <c r="E169">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F169" t="s">
         <v>1552</v>
@@ -13971,7 +13971,7 @@
         <v>1440</v>
       </c>
       <c r="E170">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F170" t="s">
         <v>1552</v>
@@ -14006,7 +14006,7 @@
         <v>1441</v>
       </c>
       <c r="E171">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F171" t="s">
         <v>1552</v>
@@ -14041,7 +14041,7 @@
         <v>1442</v>
       </c>
       <c r="E172">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F172" t="s">
         <v>1552</v>
@@ -14076,7 +14076,7 @@
         <v>1442</v>
       </c>
       <c r="E173">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F173" t="s">
         <v>1552</v>
@@ -14111,7 +14111,7 @@
         <v>1442</v>
       </c>
       <c r="E174">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F174" t="s">
         <v>1552</v>
@@ -14146,7 +14146,7 @@
         <v>1442</v>
       </c>
       <c r="E175">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F175" t="s">
         <v>1552</v>
@@ -14181,7 +14181,7 @@
         <v>1442</v>
       </c>
       <c r="E176">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F176" t="s">
         <v>1552</v>
@@ -14216,7 +14216,7 @@
         <v>1443</v>
       </c>
       <c r="E177">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F177" t="s">
         <v>1552</v>
@@ -14251,7 +14251,7 @@
         <v>1443</v>
       </c>
       <c r="E178">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F178" t="s">
         <v>1552</v>
@@ -14286,7 +14286,7 @@
         <v>1443</v>
       </c>
       <c r="E179">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F179" t="s">
         <v>1552</v>
@@ -14321,7 +14321,7 @@
         <v>1443</v>
       </c>
       <c r="E180">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F180" t="s">
         <v>1552</v>
@@ -14356,7 +14356,7 @@
         <v>1443</v>
       </c>
       <c r="E181">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F181" t="s">
         <v>1552</v>
@@ -14391,7 +14391,7 @@
         <v>1443</v>
       </c>
       <c r="E182">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F182" t="s">
         <v>1552</v>
@@ -14426,7 +14426,7 @@
         <v>1444</v>
       </c>
       <c r="E183">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F183" t="s">
         <v>1552</v>
@@ -14461,7 +14461,7 @@
         <v>1444</v>
       </c>
       <c r="E184">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F184" t="s">
         <v>1552</v>
@@ -14496,7 +14496,7 @@
         <v>1444</v>
       </c>
       <c r="E185">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F185" t="s">
         <v>1552</v>
@@ -14531,7 +14531,7 @@
         <v>1444</v>
       </c>
       <c r="E186">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F186" t="s">
         <v>1552</v>
@@ -14566,7 +14566,7 @@
         <v>1445</v>
       </c>
       <c r="E187">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F187" t="s">
         <v>1552</v>
@@ -14601,7 +14601,7 @@
         <v>1445</v>
       </c>
       <c r="E188">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F188" t="s">
         <v>1552</v>
@@ -14636,7 +14636,7 @@
         <v>1446</v>
       </c>
       <c r="E189">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F189" t="s">
         <v>1552</v>
@@ -14671,7 +14671,7 @@
         <v>1447</v>
       </c>
       <c r="E190">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F190" t="s">
         <v>1552</v>
@@ -14706,7 +14706,7 @@
         <v>1447</v>
       </c>
       <c r="E191">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F191" t="s">
         <v>1552</v>
@@ -14741,7 +14741,7 @@
         <v>1448</v>
       </c>
       <c r="E192">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F192" t="s">
         <v>1552</v>
@@ -14776,7 +14776,7 @@
         <v>1449</v>
       </c>
       <c r="E193">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F193" t="s">
         <v>1552</v>
@@ -14811,7 +14811,7 @@
         <v>1449</v>
       </c>
       <c r="E194">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F194" t="s">
         <v>1552</v>
@@ -14846,7 +14846,7 @@
         <v>1450</v>
       </c>
       <c r="E195">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F195" t="s">
         <v>1552</v>
@@ -14881,7 +14881,7 @@
         <v>1450</v>
       </c>
       <c r="E196">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F196" t="s">
         <v>1552</v>
@@ -14916,7 +14916,7 @@
         <v>1451</v>
       </c>
       <c r="E197">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F197" t="s">
         <v>1552</v>
@@ -14951,7 +14951,7 @@
         <v>1452</v>
       </c>
       <c r="E198">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F198" t="s">
         <v>1552</v>
@@ -14986,7 +14986,7 @@
         <v>1452</v>
       </c>
       <c r="E199">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F199" t="s">
         <v>1552</v>
@@ -15021,7 +15021,7 @@
         <v>1452</v>
       </c>
       <c r="E200">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F200" t="s">
         <v>1552</v>
@@ -15056,7 +15056,7 @@
         <v>1453</v>
       </c>
       <c r="E201">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F201" t="s">
         <v>1552</v>
@@ -15091,7 +15091,7 @@
         <v>1453</v>
       </c>
       <c r="E202">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F202" t="s">
         <v>1552</v>
@@ -15126,7 +15126,7 @@
         <v>1454</v>
       </c>
       <c r="E203">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F203" t="s">
         <v>1552</v>
@@ -15161,7 +15161,7 @@
         <v>1455</v>
       </c>
       <c r="E204">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F204" t="s">
         <v>1552</v>
@@ -15196,7 +15196,7 @@
         <v>1455</v>
       </c>
       <c r="E205">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F205" t="s">
         <v>1552</v>
@@ -15231,7 +15231,7 @@
         <v>1455</v>
       </c>
       <c r="E206">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F206" t="s">
         <v>1552</v>
@@ -15266,7 +15266,7 @@
         <v>1456</v>
       </c>
       <c r="E207">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F207" t="s">
         <v>1552</v>
@@ -15301,7 +15301,7 @@
         <v>1456</v>
       </c>
       <c r="E208">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F208" t="s">
         <v>1552</v>
@@ -15336,7 +15336,7 @@
         <v>1457</v>
       </c>
       <c r="E209">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F209" t="s">
         <v>1552</v>
@@ -15371,7 +15371,7 @@
         <v>1457</v>
       </c>
       <c r="E210">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F210" t="s">
         <v>1552</v>
@@ -15406,7 +15406,7 @@
         <v>1457</v>
       </c>
       <c r="E211">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F211" t="s">
         <v>1554</v>
@@ -15441,7 +15441,7 @@
         <v>1457</v>
       </c>
       <c r="E212">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F212" t="s">
         <v>1552</v>
@@ -15476,7 +15476,7 @@
         <v>1458</v>
       </c>
       <c r="E213">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F213" t="s">
         <v>1552</v>
@@ -15511,7 +15511,7 @@
         <v>1458</v>
       </c>
       <c r="E214">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F214" t="s">
         <v>1552</v>
@@ -15549,7 +15549,7 @@
         <v>1458</v>
       </c>
       <c r="E215">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F215" t="s">
         <v>1552</v>
@@ -15584,7 +15584,7 @@
         <v>1458</v>
       </c>
       <c r="E216">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F216" t="s">
         <v>1552</v>
@@ -15619,7 +15619,7 @@
         <v>1458</v>
       </c>
       <c r="E217">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F217" t="s">
         <v>1552</v>
@@ -15654,7 +15654,7 @@
         <v>1458</v>
       </c>
       <c r="E218">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F218" t="s">
         <v>1552</v>
@@ -15689,7 +15689,7 @@
         <v>1459</v>
       </c>
       <c r="E219">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F219" t="s">
         <v>1552</v>
@@ -15724,7 +15724,7 @@
         <v>1459</v>
       </c>
       <c r="E220">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F220" t="s">
         <v>1552</v>
@@ -15759,7 +15759,7 @@
         <v>1459</v>
       </c>
       <c r="E221">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F221" t="s">
         <v>1552</v>
@@ -15794,7 +15794,7 @@
         <v>1460</v>
       </c>
       <c r="E222">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F222" t="s">
         <v>1552</v>
@@ -15829,7 +15829,7 @@
         <v>1460</v>
       </c>
       <c r="E223">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F223" t="s">
         <v>1552</v>
@@ -15864,7 +15864,7 @@
         <v>1460</v>
       </c>
       <c r="E224">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F224" t="s">
         <v>1552</v>
@@ -15899,7 +15899,7 @@
         <v>1460</v>
       </c>
       <c r="E225">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F225" t="s">
         <v>1552</v>
@@ -15934,7 +15934,7 @@
         <v>1461</v>
       </c>
       <c r="E226">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F226" t="s">
         <v>1552</v>
@@ -15969,7 +15969,7 @@
         <v>1461</v>
       </c>
       <c r="E227">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F227" t="s">
         <v>1552</v>
@@ -16004,7 +16004,7 @@
         <v>1461</v>
       </c>
       <c r="E228">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F228" t="s">
         <v>1552</v>
@@ -16039,7 +16039,7 @@
         <v>1462</v>
       </c>
       <c r="E229">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F229" t="s">
         <v>1552</v>
@@ -16074,7 +16074,7 @@
         <v>1462</v>
       </c>
       <c r="E230">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F230" t="s">
         <v>1552</v>
@@ -16109,7 +16109,7 @@
         <v>1462</v>
       </c>
       <c r="E231">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F231" t="s">
         <v>1552</v>
@@ -16144,7 +16144,7 @@
         <v>1462</v>
       </c>
       <c r="E232">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F232" t="s">
         <v>1552</v>
@@ -16179,7 +16179,7 @@
         <v>1462</v>
       </c>
       <c r="E233">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F233" t="s">
         <v>1552</v>
@@ -16214,7 +16214,7 @@
         <v>1462</v>
       </c>
       <c r="E234">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F234" t="s">
         <v>1552</v>
@@ -16249,7 +16249,7 @@
         <v>1463</v>
       </c>
       <c r="E235">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F235" t="s">
         <v>1552</v>
@@ -16284,7 +16284,7 @@
         <v>1464</v>
       </c>
       <c r="E236">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F236" t="s">
         <v>1552</v>
@@ -16319,7 +16319,7 @@
         <v>1464</v>
       </c>
       <c r="E237">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F237" t="s">
         <v>1555</v>
@@ -16354,7 +16354,7 @@
         <v>1464</v>
       </c>
       <c r="E238">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F238" t="s">
         <v>1552</v>
@@ -16389,7 +16389,7 @@
         <v>1464</v>
       </c>
       <c r="E239">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F239" t="s">
         <v>1552</v>
@@ -16424,7 +16424,7 @@
         <v>1464</v>
       </c>
       <c r="E240">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F240" t="s">
         <v>1552</v>
@@ -16459,7 +16459,7 @@
         <v>1465</v>
       </c>
       <c r="E241">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F241" t="s">
         <v>1552</v>
@@ -16494,7 +16494,7 @@
         <v>1465</v>
       </c>
       <c r="E242">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F242" t="s">
         <v>1552</v>
@@ -16529,7 +16529,7 @@
         <v>1465</v>
       </c>
       <c r="E243">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F243" t="s">
         <v>1552</v>
@@ -16564,7 +16564,7 @@
         <v>1465</v>
       </c>
       <c r="E244">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F244" t="s">
         <v>1552</v>
@@ -16599,7 +16599,7 @@
         <v>1466</v>
       </c>
       <c r="E245">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F245" t="s">
         <v>1552</v>
@@ -16634,7 +16634,7 @@
         <v>1467</v>
       </c>
       <c r="E246">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F246" t="s">
         <v>1552</v>
@@ -16672,7 +16672,7 @@
         <v>1468</v>
       </c>
       <c r="E247">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F247" t="s">
         <v>1552</v>
@@ -16707,7 +16707,7 @@
         <v>1468</v>
       </c>
       <c r="E248">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F248" t="s">
         <v>1552</v>
@@ -16742,7 +16742,7 @@
         <v>1468</v>
       </c>
       <c r="E249">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F249" t="s">
         <v>1552</v>
@@ -16777,7 +16777,7 @@
         <v>1468</v>
       </c>
       <c r="E250">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F250" t="s">
         <v>1552</v>
@@ -16815,7 +16815,7 @@
         <v>1468</v>
       </c>
       <c r="E251">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F251" t="s">
         <v>1552</v>
@@ -16850,7 +16850,7 @@
         <v>1469</v>
       </c>
       <c r="E252">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F252" t="s">
         <v>1552</v>
@@ -16885,7 +16885,7 @@
         <v>1469</v>
       </c>
       <c r="E253">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F253" t="s">
         <v>1552</v>
@@ -16920,7 +16920,7 @@
         <v>1470</v>
       </c>
       <c r="E254">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F254" t="s">
         <v>1552</v>
@@ -16955,7 +16955,7 @@
         <v>1470</v>
       </c>
       <c r="E255">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F255" t="s">
         <v>1552</v>
@@ -16990,7 +16990,7 @@
         <v>1471</v>
       </c>
       <c r="E256">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F256" t="s">
         <v>1552</v>
@@ -17025,7 +17025,7 @@
         <v>1471</v>
       </c>
       <c r="E257">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F257" t="s">
         <v>1552</v>
@@ -17060,7 +17060,7 @@
         <v>1471</v>
       </c>
       <c r="E258">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F258" t="s">
         <v>1552</v>
@@ -17095,7 +17095,7 @@
         <v>1472</v>
       </c>
       <c r="E259">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F259" t="s">
         <v>1552</v>
@@ -17130,7 +17130,7 @@
         <v>1472</v>
       </c>
       <c r="E260">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F260" t="s">
         <v>1552</v>
@@ -17165,7 +17165,7 @@
         <v>1472</v>
       </c>
       <c r="E261">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F261" t="s">
         <v>1552</v>
@@ -17200,7 +17200,7 @@
         <v>1472</v>
       </c>
       <c r="E262">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F262" t="s">
         <v>1552</v>
@@ -17235,7 +17235,7 @@
         <v>1473</v>
       </c>
       <c r="E263">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F263" t="s">
         <v>1552</v>
@@ -17270,7 +17270,7 @@
         <v>1474</v>
       </c>
       <c r="E264">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F264" t="s">
         <v>1552</v>
@@ -17305,7 +17305,7 @@
         <v>1474</v>
       </c>
       <c r="E265">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F265" t="s">
         <v>1552</v>
@@ -17340,7 +17340,7 @@
         <v>1474</v>
       </c>
       <c r="E266">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F266" t="s">
         <v>1552</v>
@@ -17375,7 +17375,7 @@
         <v>1474</v>
       </c>
       <c r="E267">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F267" t="s">
         <v>1552</v>
@@ -17410,7 +17410,7 @@
         <v>1475</v>
       </c>
       <c r="E268">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F268" t="s">
         <v>1552</v>
@@ -17445,7 +17445,7 @@
         <v>1475</v>
       </c>
       <c r="E269">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F269" t="s">
         <v>1552</v>
@@ -17480,7 +17480,7 @@
         <v>1475</v>
       </c>
       <c r="E270">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F270" t="s">
         <v>1552</v>
@@ -17515,7 +17515,7 @@
         <v>1476</v>
       </c>
       <c r="E271">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F271" t="s">
         <v>1552</v>
@@ -17550,7 +17550,7 @@
         <v>1476</v>
       </c>
       <c r="E272">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F272" t="s">
         <v>1552</v>
@@ -17585,7 +17585,7 @@
         <v>1477</v>
       </c>
       <c r="E273">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F273" t="s">
         <v>1552</v>
@@ -17620,7 +17620,7 @@
         <v>1477</v>
       </c>
       <c r="E274">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F274" t="s">
         <v>1552</v>
@@ -17655,7 +17655,7 @@
         <v>1477</v>
       </c>
       <c r="E275">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F275" t="s">
         <v>1552</v>
@@ -17690,7 +17690,7 @@
         <v>1477</v>
       </c>
       <c r="E276">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F276" t="s">
         <v>1552</v>
@@ -17725,7 +17725,7 @@
         <v>1477</v>
       </c>
       <c r="E277">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F277" t="s">
         <v>1552</v>
@@ -17760,7 +17760,7 @@
         <v>1478</v>
       </c>
       <c r="E278">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F278" t="s">
         <v>1552</v>
@@ -17795,7 +17795,7 @@
         <v>1478</v>
       </c>
       <c r="E279">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F279" t="s">
         <v>1552</v>
@@ -17830,7 +17830,7 @@
         <v>1478</v>
       </c>
       <c r="E280">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F280" t="s">
         <v>1552</v>
@@ -17865,7 +17865,7 @@
         <v>1479</v>
       </c>
       <c r="E281">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F281" t="s">
         <v>1552</v>
@@ -17900,7 +17900,7 @@
         <v>1480</v>
       </c>
       <c r="E282">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F282" t="s">
         <v>1552</v>
@@ -17935,7 +17935,7 @@
         <v>1481</v>
       </c>
       <c r="E283">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F283" t="s">
         <v>1552</v>
@@ -17970,7 +17970,7 @@
         <v>1481</v>
       </c>
       <c r="E284">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F284" t="s">
         <v>1552</v>
@@ -18005,7 +18005,7 @@
         <v>1481</v>
       </c>
       <c r="E285">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F285" t="s">
         <v>1552</v>
@@ -18040,7 +18040,7 @@
         <v>1481</v>
       </c>
       <c r="E286">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F286" t="s">
         <v>1552</v>
@@ -18075,7 +18075,7 @@
         <v>1481</v>
       </c>
       <c r="E287">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F287" t="s">
         <v>1552</v>
@@ -18110,7 +18110,7 @@
         <v>1482</v>
       </c>
       <c r="E288">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F288" t="s">
         <v>1552</v>
@@ -18145,7 +18145,7 @@
         <v>1482</v>
       </c>
       <c r="E289">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F289" t="s">
         <v>1552</v>
@@ -18180,7 +18180,7 @@
         <v>1483</v>
       </c>
       <c r="E290">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F290" t="s">
         <v>1552</v>
@@ -18215,7 +18215,7 @@
         <v>1483</v>
       </c>
       <c r="E291">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F291" t="s">
         <v>1552</v>
@@ -18250,7 +18250,7 @@
         <v>1484</v>
       </c>
       <c r="E292">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F292" t="s">
         <v>1552</v>
@@ -18285,7 +18285,7 @@
         <v>1485</v>
       </c>
       <c r="E293">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F293" t="s">
         <v>1552</v>
@@ -18320,7 +18320,7 @@
         <v>1486</v>
       </c>
       <c r="E294">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F294" t="s">
         <v>1552</v>
@@ -18355,7 +18355,7 @@
         <v>1486</v>
       </c>
       <c r="E295">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F295" t="s">
         <v>1552</v>
@@ -18390,7 +18390,7 @@
         <v>1487</v>
       </c>
       <c r="E296">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F296" t="s">
         <v>1552</v>
@@ -18425,7 +18425,7 @@
         <v>1487</v>
       </c>
       <c r="E297">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F297" t="s">
         <v>1552</v>
@@ -18460,7 +18460,7 @@
         <v>1487</v>
       </c>
       <c r="E298">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F298" t="s">
         <v>1552</v>
@@ -18495,7 +18495,7 @@
         <v>1488</v>
       </c>
       <c r="E299">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F299" t="s">
         <v>1552</v>
@@ -18530,7 +18530,7 @@
         <v>1488</v>
       </c>
       <c r="E300">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F300" t="s">
         <v>1552</v>
@@ -18565,7 +18565,7 @@
         <v>1488</v>
       </c>
       <c r="E301">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F301" t="s">
         <v>1552</v>
@@ -18600,7 +18600,7 @@
         <v>1488</v>
       </c>
       <c r="E302">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F302" t="s">
         <v>1552</v>
@@ -18635,7 +18635,7 @@
         <v>1488</v>
       </c>
       <c r="E303">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F303" t="s">
         <v>1552</v>
@@ -18670,7 +18670,7 @@
         <v>1488</v>
       </c>
       <c r="E304">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F304" t="s">
         <v>1552</v>
@@ -18705,7 +18705,7 @@
         <v>1488</v>
       </c>
       <c r="E305">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F305" t="s">
         <v>1552</v>
@@ -18740,7 +18740,7 @@
         <v>1488</v>
       </c>
       <c r="E306">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F306" t="s">
         <v>1552</v>
@@ -18775,7 +18775,7 @@
         <v>1488</v>
       </c>
       <c r="E307">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F307" t="s">
         <v>1552</v>
@@ -18810,7 +18810,7 @@
         <v>1489</v>
       </c>
       <c r="E308">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F308" t="s">
         <v>1552</v>
@@ -18845,7 +18845,7 @@
         <v>1489</v>
       </c>
       <c r="E309">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F309" t="s">
         <v>1552</v>
@@ -18880,7 +18880,7 @@
         <v>1489</v>
       </c>
       <c r="E310">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F310" t="s">
         <v>1552</v>
@@ -18915,7 +18915,7 @@
         <v>1490</v>
       </c>
       <c r="E311">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F311" t="s">
         <v>1552</v>
@@ -18950,7 +18950,7 @@
         <v>1491</v>
       </c>
       <c r="E312">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F312" t="s">
         <v>1552</v>
@@ -18985,7 +18985,7 @@
         <v>1491</v>
       </c>
       <c r="E313">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F313" t="s">
         <v>1552</v>
@@ -19020,7 +19020,7 @@
         <v>1491</v>
       </c>
       <c r="E314">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F314" t="s">
         <v>1552</v>
@@ -19055,7 +19055,7 @@
         <v>1491</v>
       </c>
       <c r="E315">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F315" t="s">
         <v>1552</v>
@@ -19090,7 +19090,7 @@
         <v>1491</v>
       </c>
       <c r="E316">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F316" t="s">
         <v>1556</v>
@@ -19128,7 +19128,7 @@
         <v>1491</v>
       </c>
       <c r="E317">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F317" t="s">
         <v>1552</v>
@@ -19163,7 +19163,7 @@
         <v>1491</v>
       </c>
       <c r="E318">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F318" t="s">
         <v>1552</v>
@@ -19198,7 +19198,7 @@
         <v>1492</v>
       </c>
       <c r="E319">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F319" t="s">
         <v>1552</v>
@@ -19233,7 +19233,7 @@
         <v>1492</v>
       </c>
       <c r="E320">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F320" t="s">
         <v>1552</v>
@@ -19268,7 +19268,7 @@
         <v>1492</v>
       </c>
       <c r="E321">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F321" t="s">
         <v>1552</v>
@@ -19303,7 +19303,7 @@
         <v>1492</v>
       </c>
       <c r="E322">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F322" t="s">
         <v>1552</v>
@@ -19341,7 +19341,7 @@
         <v>1492</v>
       </c>
       <c r="E323">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F323" t="s">
         <v>1552</v>
@@ -19376,7 +19376,7 @@
         <v>1492</v>
       </c>
       <c r="E324">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F324" t="s">
         <v>1552</v>
@@ -19411,7 +19411,7 @@
         <v>1492</v>
       </c>
       <c r="E325">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F325" t="s">
         <v>1552</v>
@@ -19446,7 +19446,7 @@
         <v>1492</v>
       </c>
       <c r="E326">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F326" t="s">
         <v>1552</v>
@@ -19481,7 +19481,7 @@
         <v>1492</v>
       </c>
       <c r="E327">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F327" t="s">
         <v>1552</v>
@@ -19516,7 +19516,7 @@
         <v>1493</v>
       </c>
       <c r="E328">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F328" t="s">
         <v>1553</v>
@@ -19551,7 +19551,7 @@
         <v>1494</v>
       </c>
       <c r="E329">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F329" t="s">
         <v>1556</v>
@@ -19586,7 +19586,7 @@
         <v>1495</v>
       </c>
       <c r="E330">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F330" t="s">
         <v>1552</v>
@@ -19621,7 +19621,7 @@
         <v>1496</v>
       </c>
       <c r="E331">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F331" t="s">
         <v>1552</v>
@@ -19656,7 +19656,7 @@
         <v>1496</v>
       </c>
       <c r="E332">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F332" t="s">
         <v>1552</v>
@@ -19691,7 +19691,7 @@
         <v>1497</v>
       </c>
       <c r="E333">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F333" t="s">
         <v>1552</v>
@@ -19726,7 +19726,7 @@
         <v>1498</v>
       </c>
       <c r="E334">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F334" t="s">
         <v>1555</v>
@@ -19761,7 +19761,7 @@
         <v>1498</v>
       </c>
       <c r="E335">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F335" t="s">
         <v>1552</v>
@@ -19796,7 +19796,7 @@
         <v>1498</v>
       </c>
       <c r="E336">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F336" t="s">
         <v>1552</v>
@@ -19831,7 +19831,7 @@
         <v>1498</v>
       </c>
       <c r="E337">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F337" t="s">
         <v>1552</v>
@@ -19866,7 +19866,7 @@
         <v>1498</v>
       </c>
       <c r="E338">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F338" t="s">
         <v>1552</v>
@@ -19901,7 +19901,7 @@
         <v>1498</v>
       </c>
       <c r="E339">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F339" t="s">
         <v>1552</v>
@@ -19936,7 +19936,7 @@
         <v>1499</v>
       </c>
       <c r="E340">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F340" t="s">
         <v>1552</v>
@@ -19971,7 +19971,7 @@
         <v>1499</v>
       </c>
       <c r="E341">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F341" t="s">
         <v>1552</v>
@@ -20006,7 +20006,7 @@
         <v>1499</v>
       </c>
       <c r="E342">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F342" t="s">
         <v>1552</v>
@@ -20041,7 +20041,7 @@
         <v>1500</v>
       </c>
       <c r="E343">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F343" t="s">
         <v>1552</v>
@@ -20076,7 +20076,7 @@
         <v>1500</v>
       </c>
       <c r="E344">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F344" t="s">
         <v>1552</v>
@@ -20111,7 +20111,7 @@
         <v>1500</v>
       </c>
       <c r="E345">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F345" t="s">
         <v>1552</v>
@@ -20149,7 +20149,7 @@
         <v>1500</v>
       </c>
       <c r="E346">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F346" t="s">
         <v>1552</v>
@@ -20184,7 +20184,7 @@
         <v>1501</v>
       </c>
       <c r="E347">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F347" t="s">
         <v>1552</v>
@@ -20219,7 +20219,7 @@
         <v>1501</v>
       </c>
       <c r="E348">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F348" t="s">
         <v>1552</v>
@@ -20254,7 +20254,7 @@
         <v>1501</v>
       </c>
       <c r="E349">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F349" t="s">
         <v>1552</v>
@@ -20289,7 +20289,7 @@
         <v>1501</v>
       </c>
       <c r="E350">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F350" t="s">
         <v>1552</v>
@@ -20324,7 +20324,7 @@
         <v>1501</v>
       </c>
       <c r="E351">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F351" t="s">
         <v>1552</v>
@@ -20359,7 +20359,7 @@
         <v>1502</v>
       </c>
       <c r="E352">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F352" t="s">
         <v>1552</v>
@@ -20394,7 +20394,7 @@
         <v>1502</v>
       </c>
       <c r="E353">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F353" t="s">
         <v>1552</v>
@@ -20429,7 +20429,7 @@
         <v>1503</v>
       </c>
       <c r="E354">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F354" t="s">
         <v>1552</v>
@@ -20464,7 +20464,7 @@
         <v>1503</v>
       </c>
       <c r="E355">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F355" t="s">
         <v>1552</v>
@@ -20499,7 +20499,7 @@
         <v>1503</v>
       </c>
       <c r="E356">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F356" t="s">
         <v>1552</v>
@@ -20534,7 +20534,7 @@
         <v>1503</v>
       </c>
       <c r="E357">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F357" t="s">
         <v>1552</v>
@@ -20569,7 +20569,7 @@
         <v>1503</v>
       </c>
       <c r="E358">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F358" t="s">
         <v>1552</v>
@@ -20604,7 +20604,7 @@
         <v>1503</v>
       </c>
       <c r="E359">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F359" t="s">
         <v>1552</v>
@@ -20639,7 +20639,7 @@
         <v>1503</v>
       </c>
       <c r="E360">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F360" t="s">
         <v>1552</v>
@@ -20674,7 +20674,7 @@
         <v>1503</v>
       </c>
       <c r="E361">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F361" t="s">
         <v>1552</v>
@@ -20709,7 +20709,7 @@
         <v>1503</v>
       </c>
       <c r="E362">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F362" t="s">
         <v>1552</v>
@@ -20744,7 +20744,7 @@
         <v>1503</v>
       </c>
       <c r="E363">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F363" t="s">
         <v>1552</v>
@@ -20779,7 +20779,7 @@
         <v>1504</v>
       </c>
       <c r="E364">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F364" t="s">
         <v>1552</v>
@@ -20814,7 +20814,7 @@
         <v>1504</v>
       </c>
       <c r="E365">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F365" t="s">
         <v>1552</v>
@@ -20849,7 +20849,7 @@
         <v>1504</v>
       </c>
       <c r="E366">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F366" t="s">
         <v>1553</v>
@@ -20884,7 +20884,7 @@
         <v>1505</v>
       </c>
       <c r="E367">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F367" t="s">
         <v>1552</v>
@@ -20919,7 +20919,7 @@
         <v>1505</v>
       </c>
       <c r="E368">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F368" t="s">
         <v>1552</v>
@@ -20954,7 +20954,7 @@
         <v>1505</v>
       </c>
       <c r="E369">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F369" t="s">
         <v>1552</v>
@@ -20989,7 +20989,7 @@
         <v>1505</v>
       </c>
       <c r="E370">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F370" t="s">
         <v>1552</v>
@@ -21024,7 +21024,7 @@
         <v>1505</v>
       </c>
       <c r="E371">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F371" t="s">
         <v>1552</v>
@@ -21059,7 +21059,7 @@
         <v>1505</v>
       </c>
       <c r="E372">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F372" t="s">
         <v>1552</v>
@@ -21094,7 +21094,7 @@
         <v>1505</v>
       </c>
       <c r="E373">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F373" t="s">
         <v>1555</v>
@@ -21129,7 +21129,7 @@
         <v>1506</v>
       </c>
       <c r="E374">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F374" t="s">
         <v>1552</v>
@@ -21164,7 +21164,7 @@
         <v>1506</v>
       </c>
       <c r="E375">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F375" t="s">
         <v>1552</v>
@@ -21199,7 +21199,7 @@
         <v>1506</v>
       </c>
       <c r="E376">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F376" t="s">
         <v>1552</v>
@@ -21234,7 +21234,7 @@
         <v>1506</v>
       </c>
       <c r="E377">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F377" t="s">
         <v>1552</v>
@@ -21269,7 +21269,7 @@
         <v>1507</v>
       </c>
       <c r="E378">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F378" t="s">
         <v>1555</v>
@@ -21304,7 +21304,7 @@
         <v>1507</v>
       </c>
       <c r="E379">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F379" t="s">
         <v>1552</v>
@@ -21339,7 +21339,7 @@
         <v>1507</v>
       </c>
       <c r="E380">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F380" t="s">
         <v>1552</v>
@@ -21374,7 +21374,7 @@
         <v>1507</v>
       </c>
       <c r="E381">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F381" t="s">
         <v>1552</v>
@@ -21409,7 +21409,7 @@
         <v>1507</v>
       </c>
       <c r="E382">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F382" t="s">
         <v>1552</v>
@@ -21444,7 +21444,7 @@
         <v>1507</v>
       </c>
       <c r="E383">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F383" t="s">
         <v>1552</v>
@@ -21479,7 +21479,7 @@
         <v>1508</v>
       </c>
       <c r="E384">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F384" t="s">
         <v>1552</v>
@@ -21514,7 +21514,7 @@
         <v>1508</v>
       </c>
       <c r="E385">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F385" t="s">
         <v>1552</v>
@@ -21549,7 +21549,7 @@
         <v>1508</v>
       </c>
       <c r="E386">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F386" t="s">
         <v>1552</v>
@@ -21584,7 +21584,7 @@
         <v>1508</v>
       </c>
       <c r="E387">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F387" t="s">
         <v>1552</v>
@@ -21619,7 +21619,7 @@
         <v>1508</v>
       </c>
       <c r="E388">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F388" t="s">
         <v>1554</v>
@@ -21654,7 +21654,7 @@
         <v>1508</v>
       </c>
       <c r="E389">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F389" t="s">
         <v>1552</v>
@@ -21689,7 +21689,7 @@
         <v>1508</v>
       </c>
       <c r="E390">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F390" t="s">
         <v>1552</v>
@@ -21724,7 +21724,7 @@
         <v>1509</v>
       </c>
       <c r="E391">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F391" t="s">
         <v>1552</v>
@@ -21759,7 +21759,7 @@
         <v>1509</v>
       </c>
       <c r="E392">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F392" t="s">
         <v>1552</v>
@@ -21794,7 +21794,7 @@
         <v>1509</v>
       </c>
       <c r="E393">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F393" t="s">
         <v>1552</v>
@@ -21829,7 +21829,7 @@
         <v>1509</v>
       </c>
       <c r="E394">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F394" t="s">
         <v>1552</v>
@@ -21864,7 +21864,7 @@
         <v>1509</v>
       </c>
       <c r="E395">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F395" t="s">
         <v>1552</v>
@@ -21899,7 +21899,7 @@
         <v>1510</v>
       </c>
       <c r="E396">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F396" t="s">
         <v>1552</v>
@@ -21934,7 +21934,7 @@
         <v>1510</v>
       </c>
       <c r="E397">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F397" t="s">
         <v>1552</v>
@@ -21969,7 +21969,7 @@
         <v>1510</v>
       </c>
       <c r="E398">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F398" t="s">
         <v>1552</v>
@@ -22004,7 +22004,7 @@
         <v>1510</v>
       </c>
       <c r="E399">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F399" t="s">
         <v>1552</v>
@@ -22039,7 +22039,7 @@
         <v>1510</v>
       </c>
       <c r="E400">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F400" t="s">
         <v>1552</v>
@@ -22077,7 +22077,7 @@
         <v>1511</v>
       </c>
       <c r="E401">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F401" t="s">
         <v>1552</v>
@@ -22112,7 +22112,7 @@
         <v>1511</v>
       </c>
       <c r="E402">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F402" t="s">
         <v>1552</v>
@@ -22147,7 +22147,7 @@
         <v>1511</v>
       </c>
       <c r="E403">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F403" t="s">
         <v>1552</v>
@@ -22182,7 +22182,7 @@
         <v>1511</v>
       </c>
       <c r="E404">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F404" t="s">
         <v>1552</v>
@@ -22217,7 +22217,7 @@
         <v>1511</v>
       </c>
       <c r="E405">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F405" t="s">
         <v>1552</v>
@@ -22252,7 +22252,7 @@
         <v>1511</v>
       </c>
       <c r="E406">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F406" t="s">
         <v>1552</v>
@@ -22287,7 +22287,7 @@
         <v>1512</v>
       </c>
       <c r="E407">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F407" t="s">
         <v>1553</v>
@@ -22322,7 +22322,7 @@
         <v>1512</v>
       </c>
       <c r="E408">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F408" t="s">
         <v>1552</v>
@@ -22357,7 +22357,7 @@
         <v>1513</v>
       </c>
       <c r="E409">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F409" t="s">
         <v>1552</v>
@@ -22392,7 +22392,7 @@
         <v>1514</v>
       </c>
       <c r="E410">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F410" t="s">
         <v>1552</v>
@@ -22427,7 +22427,7 @@
         <v>1514</v>
       </c>
       <c r="E411">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F411" t="s">
         <v>1552</v>
@@ -22462,7 +22462,7 @@
         <v>1514</v>
       </c>
       <c r="E412">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F412" t="s">
         <v>1554</v>
@@ -22500,7 +22500,7 @@
         <v>1515</v>
       </c>
       <c r="E413">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F413" t="s">
         <v>1552</v>
@@ -22535,7 +22535,7 @@
         <v>1515</v>
       </c>
       <c r="E414">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F414" t="s">
         <v>1552</v>
@@ -22570,7 +22570,7 @@
         <v>1515</v>
       </c>
       <c r="E415">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F415" t="s">
         <v>1552</v>
@@ -22605,7 +22605,7 @@
         <v>1516</v>
       </c>
       <c r="E416">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F416" t="s">
         <v>1552</v>
@@ -22640,7 +22640,7 @@
         <v>1516</v>
       </c>
       <c r="E417">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F417" t="s">
         <v>1552</v>
@@ -22675,7 +22675,7 @@
         <v>1516</v>
       </c>
       <c r="E418">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F418" t="s">
         <v>1552</v>
@@ -22710,7 +22710,7 @@
         <v>1516</v>
       </c>
       <c r="E419">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F419" t="s">
         <v>1552</v>
@@ -22745,7 +22745,7 @@
         <v>1516</v>
       </c>
       <c r="E420">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F420" t="s">
         <v>1552</v>
@@ -22780,7 +22780,7 @@
         <v>1516</v>
       </c>
       <c r="E421">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F421" t="s">
         <v>1552</v>
@@ -22815,7 +22815,7 @@
         <v>1516</v>
       </c>
       <c r="E422">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F422" t="s">
         <v>1552</v>
@@ -22850,7 +22850,7 @@
         <v>1516</v>
       </c>
       <c r="E423">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F423" t="s">
         <v>1552</v>
@@ -22885,7 +22885,7 @@
         <v>1517</v>
       </c>
       <c r="E424">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F424" t="s">
         <v>1552</v>
@@ -22920,7 +22920,7 @@
         <v>1518</v>
       </c>
       <c r="E425">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F425" t="s">
         <v>1552</v>
@@ -22955,7 +22955,7 @@
         <v>1518</v>
       </c>
       <c r="E426">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F426" t="s">
         <v>1552</v>
@@ -22990,7 +22990,7 @@
         <v>1518</v>
       </c>
       <c r="E427">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F427" t="s">
         <v>1552</v>
@@ -23025,7 +23025,7 @@
         <v>1518</v>
       </c>
       <c r="E428">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F428" t="s">
         <v>1556</v>
@@ -23063,7 +23063,7 @@
         <v>1518</v>
       </c>
       <c r="E429">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F429" t="s">
         <v>1552</v>
@@ -23098,7 +23098,7 @@
         <v>1518</v>
       </c>
       <c r="E430">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F430" t="s">
         <v>1556</v>
@@ -23133,7 +23133,7 @@
         <v>1519</v>
       </c>
       <c r="E431">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F431" t="s">
         <v>1552</v>
@@ -23168,7 +23168,7 @@
         <v>1520</v>
       </c>
       <c r="E432">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F432" t="s">
         <v>1552</v>
@@ -23203,7 +23203,7 @@
         <v>1520</v>
       </c>
       <c r="E433">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F433" t="s">
         <v>1552</v>
@@ -23238,7 +23238,7 @@
         <v>1520</v>
       </c>
       <c r="E434">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F434" t="s">
         <v>1552</v>
@@ -23273,7 +23273,7 @@
         <v>1520</v>
       </c>
       <c r="E435">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F435" t="s">
         <v>1552</v>
@@ -23308,7 +23308,7 @@
         <v>1521</v>
       </c>
       <c r="E436">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F436" t="s">
         <v>1552</v>
@@ -23343,7 +23343,7 @@
         <v>1521</v>
       </c>
       <c r="E437">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F437" t="s">
         <v>1556</v>
@@ -23378,7 +23378,7 @@
         <v>1521</v>
       </c>
       <c r="E438">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F438" t="s">
         <v>1552</v>
@@ -23413,7 +23413,7 @@
         <v>1521</v>
       </c>
       <c r="E439">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F439" t="s">
         <v>1552</v>
@@ -23448,7 +23448,7 @@
         <v>1521</v>
       </c>
       <c r="E440">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F440" t="s">
         <v>1552</v>
@@ -23483,7 +23483,7 @@
         <v>1522</v>
       </c>
       <c r="E441">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F441" t="s">
         <v>1552</v>
@@ -23518,7 +23518,7 @@
         <v>1522</v>
       </c>
       <c r="E442">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F442" t="s">
         <v>1552</v>
@@ -23553,7 +23553,7 @@
         <v>1522</v>
       </c>
       <c r="E443">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F443" t="s">
         <v>1552</v>
@@ -23588,7 +23588,7 @@
         <v>1523</v>
       </c>
       <c r="E444">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F444" t="s">
         <v>1552</v>
@@ -23623,7 +23623,7 @@
         <v>1523</v>
       </c>
       <c r="E445">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F445" t="s">
         <v>1552</v>
@@ -23658,7 +23658,7 @@
         <v>1523</v>
       </c>
       <c r="E446">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F446" t="s">
         <v>1552</v>
@@ -23693,7 +23693,7 @@
         <v>1523</v>
       </c>
       <c r="E447">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F447" t="s">
         <v>1552</v>
@@ -23728,7 +23728,7 @@
         <v>1523</v>
       </c>
       <c r="E448">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F448" t="s">
         <v>1552</v>
@@ -23763,7 +23763,7 @@
         <v>1524</v>
       </c>
       <c r="E449">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F449" t="s">
         <v>1552</v>
@@ -23798,7 +23798,7 @@
         <v>1524</v>
       </c>
       <c r="E450">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F450" t="s">
         <v>1552</v>
@@ -23833,7 +23833,7 @@
         <v>1524</v>
       </c>
       <c r="E451">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F451" t="s">
         <v>1552</v>
@@ -23868,7 +23868,7 @@
         <v>1524</v>
       </c>
       <c r="E452">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F452" t="s">
         <v>1552</v>
@@ -23903,7 +23903,7 @@
         <v>1524</v>
       </c>
       <c r="E453">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F453" t="s">
         <v>1552</v>
@@ -23938,7 +23938,7 @@
         <v>1524</v>
       </c>
       <c r="E454">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F454" t="s">
         <v>1552</v>
@@ -23973,7 +23973,7 @@
         <v>1524</v>
       </c>
       <c r="E455">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F455" t="s">
         <v>1552</v>
@@ -24008,7 +24008,7 @@
         <v>1524</v>
       </c>
       <c r="E456">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F456" t="s">
         <v>1552</v>
@@ -24043,7 +24043,7 @@
         <v>1524</v>
       </c>
       <c r="E457">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F457" t="s">
         <v>1552</v>
@@ -24078,7 +24078,7 @@
         <v>1524</v>
       </c>
       <c r="E458">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F458" t="s">
         <v>1552</v>
@@ -24113,7 +24113,7 @@
         <v>1524</v>
       </c>
       <c r="E459">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F459" t="s">
         <v>1552</v>
@@ -24148,7 +24148,7 @@
         <v>1524</v>
       </c>
       <c r="E460">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F460" t="s">
         <v>1552</v>
@@ -24183,7 +24183,7 @@
         <v>1524</v>
       </c>
       <c r="E461">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F461" t="s">
         <v>1552</v>
@@ -24218,7 +24218,7 @@
         <v>1524</v>
       </c>
       <c r="E462">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F462" t="s">
         <v>1552</v>
@@ -24253,7 +24253,7 @@
         <v>1524</v>
       </c>
       <c r="E463">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F463" t="s">
         <v>1552</v>
@@ -24288,7 +24288,7 @@
         <v>1524</v>
       </c>
       <c r="E464">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F464" t="s">
         <v>1552</v>
@@ -24323,7 +24323,7 @@
         <v>1524</v>
       </c>
       <c r="E465">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F465" t="s">
         <v>1552</v>
@@ -24358,7 +24358,7 @@
         <v>1524</v>
       </c>
       <c r="E466">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F466" t="s">
         <v>1552</v>
@@ -24393,7 +24393,7 @@
         <v>1524</v>
       </c>
       <c r="E467">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F467" t="s">
         <v>1552</v>
@@ -24428,7 +24428,7 @@
         <v>1524</v>
       </c>
       <c r="E468">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F468" t="s">
         <v>1552</v>
@@ -24463,7 +24463,7 @@
         <v>1524</v>
       </c>
       <c r="E469">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F469" t="s">
         <v>1552</v>
@@ -24498,7 +24498,7 @@
         <v>1524</v>
       </c>
       <c r="E470">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F470" t="s">
         <v>1552</v>
@@ -24533,7 +24533,7 @@
         <v>1524</v>
       </c>
       <c r="E471">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F471" t="s">
         <v>1552</v>
@@ -24568,7 +24568,7 @@
         <v>1524</v>
       </c>
       <c r="E472">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F472" t="s">
         <v>1552</v>
@@ -24603,7 +24603,7 @@
         <v>1524</v>
       </c>
       <c r="E473">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F473" t="s">
         <v>1552</v>
@@ -24638,7 +24638,7 @@
         <v>1525</v>
       </c>
       <c r="E474">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F474" t="s">
         <v>1552</v>
@@ -24673,7 +24673,7 @@
         <v>1525</v>
       </c>
       <c r="E475">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F475" t="s">
         <v>1552</v>
@@ -24708,7 +24708,7 @@
         <v>1525</v>
       </c>
       <c r="E476">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F476" t="s">
         <v>1552</v>
@@ -24743,7 +24743,7 @@
         <v>1525</v>
       </c>
       <c r="E477">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F477" t="s">
         <v>1552</v>
@@ -24778,7 +24778,7 @@
         <v>1525</v>
       </c>
       <c r="E478">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F478" t="s">
         <v>1552</v>
@@ -24813,7 +24813,7 @@
         <v>1525</v>
       </c>
       <c r="E479">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F479" t="s">
         <v>1552</v>
@@ -24848,7 +24848,7 @@
         <v>1525</v>
       </c>
       <c r="E480">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F480" t="s">
         <v>1556</v>
@@ -24883,7 +24883,7 @@
         <v>1525</v>
       </c>
       <c r="E481">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F481" t="s">
         <v>1552</v>
@@ -24918,7 +24918,7 @@
         <v>1526</v>
       </c>
       <c r="E482">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F482" t="s">
         <v>1552</v>
@@ -24953,7 +24953,7 @@
         <v>1527</v>
       </c>
       <c r="E483">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F483" t="s">
         <v>1554</v>
@@ -24991,7 +24991,7 @@
         <v>1527</v>
       </c>
       <c r="E484">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F484" t="s">
         <v>1552</v>
@@ -25026,7 +25026,7 @@
         <v>1527</v>
       </c>
       <c r="E485">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F485" t="s">
         <v>1552</v>
@@ -25061,7 +25061,7 @@
         <v>1527</v>
       </c>
       <c r="E486">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F486" t="s">
         <v>1552</v>
@@ -25096,7 +25096,7 @@
         <v>1527</v>
       </c>
       <c r="E487">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F487" t="s">
         <v>1552</v>
@@ -25131,7 +25131,7 @@
         <v>1527</v>
       </c>
       <c r="E488">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F488" t="s">
         <v>1552</v>
@@ -25166,7 +25166,7 @@
         <v>1528</v>
       </c>
       <c r="E489">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F489" t="s">
         <v>1552</v>
@@ -25204,7 +25204,7 @@
         <v>1528</v>
       </c>
       <c r="E490">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F490" t="s">
         <v>1556</v>
@@ -25239,7 +25239,7 @@
         <v>1528</v>
       </c>
       <c r="E491">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F491" t="s">
         <v>1554</v>
@@ -25274,7 +25274,7 @@
         <v>1528</v>
       </c>
       <c r="E492">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F492" t="s">
         <v>1552</v>
@@ -25309,7 +25309,7 @@
         <v>1528</v>
       </c>
       <c r="E493">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F493" t="s">
         <v>1552</v>
@@ -25344,7 +25344,7 @@
         <v>1528</v>
       </c>
       <c r="E494">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F494" t="s">
         <v>1552</v>
@@ -25379,7 +25379,7 @@
         <v>1528</v>
       </c>
       <c r="E495">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F495" t="s">
         <v>1552</v>
@@ -25414,7 +25414,7 @@
         <v>1528</v>
       </c>
       <c r="E496">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F496" t="s">
         <v>1552</v>
@@ -25449,7 +25449,7 @@
         <v>1528</v>
       </c>
       <c r="E497">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F497" t="s">
         <v>1552</v>
@@ -25484,7 +25484,7 @@
         <v>1529</v>
       </c>
       <c r="E498">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F498" t="s">
         <v>1556</v>
@@ -25522,7 +25522,7 @@
         <v>1529</v>
       </c>
       <c r="E499">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F499" t="s">
         <v>1552</v>
@@ -25557,7 +25557,7 @@
         <v>1530</v>
       </c>
       <c r="E500">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F500" t="s">
         <v>1552</v>
@@ -25592,7 +25592,7 @@
         <v>1530</v>
       </c>
       <c r="E501">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F501" t="s">
         <v>1552</v>
@@ -25627,7 +25627,7 @@
         <v>1530</v>
       </c>
       <c r="E502">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F502" t="s">
         <v>1552</v>
@@ -25662,7 +25662,7 @@
         <v>1530</v>
       </c>
       <c r="E503">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F503" t="s">
         <v>1552</v>
@@ -25697,7 +25697,7 @@
         <v>1530</v>
       </c>
       <c r="E504">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F504" t="s">
         <v>1552</v>
@@ -25732,7 +25732,7 @@
         <v>1530</v>
       </c>
       <c r="E505">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F505" t="s">
         <v>1552</v>
@@ -25767,7 +25767,7 @@
         <v>1530</v>
       </c>
       <c r="E506">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F506" t="s">
         <v>1552</v>
@@ -25802,7 +25802,7 @@
         <v>1531</v>
       </c>
       <c r="E507">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F507" t="s">
         <v>1552</v>
@@ -25837,7 +25837,7 @@
         <v>1531</v>
       </c>
       <c r="E508">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F508" t="s">
         <v>1552</v>
@@ -25872,7 +25872,7 @@
         <v>1531</v>
       </c>
       <c r="E509">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F509" t="s">
         <v>1552</v>
@@ -25907,7 +25907,7 @@
         <v>1531</v>
       </c>
       <c r="E510">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F510" t="s">
         <v>1552</v>
@@ -25942,7 +25942,7 @@
         <v>1531</v>
       </c>
       <c r="E511">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F511" t="s">
         <v>1552</v>
@@ -25977,7 +25977,7 @@
         <v>1531</v>
       </c>
       <c r="E512">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F512" t="s">
         <v>1554</v>
@@ -26012,7 +26012,7 @@
         <v>1531</v>
       </c>
       <c r="E513">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F513" t="s">
         <v>1552</v>
@@ -26047,7 +26047,7 @@
         <v>1531</v>
       </c>
       <c r="E514">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F514" t="s">
         <v>1556</v>
@@ -26082,7 +26082,7 @@
         <v>1531</v>
       </c>
       <c r="E515">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F515" t="s">
         <v>1552</v>
@@ -26117,7 +26117,7 @@
         <v>1532</v>
       </c>
       <c r="E516">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F516" t="s">
         <v>1552</v>
@@ -26152,7 +26152,7 @@
         <v>1532</v>
       </c>
       <c r="E517">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F517" t="s">
         <v>1552</v>
@@ -26187,7 +26187,7 @@
         <v>1532</v>
       </c>
       <c r="E518">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F518" t="s">
         <v>1552</v>
@@ -26222,7 +26222,7 @@
         <v>1532</v>
       </c>
       <c r="E519">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F519" t="s">
         <v>1552</v>
@@ -26257,7 +26257,7 @@
         <v>1532</v>
       </c>
       <c r="E520">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F520" t="s">
         <v>1552</v>
@@ -26292,7 +26292,7 @@
         <v>1532</v>
       </c>
       <c r="E521">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F521" t="s">
         <v>1552</v>
@@ -26327,7 +26327,7 @@
         <v>1532</v>
       </c>
       <c r="E522">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F522" t="s">
         <v>1552</v>
@@ -26362,7 +26362,7 @@
         <v>1532</v>
       </c>
       <c r="E523">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F523" t="s">
         <v>1552</v>
@@ -26400,7 +26400,7 @@
         <v>1532</v>
       </c>
       <c r="E524">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F524" t="s">
         <v>1554</v>
@@ -26438,7 +26438,7 @@
         <v>1532</v>
       </c>
       <c r="E525">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F525" t="s">
         <v>1554</v>
@@ -26473,7 +26473,7 @@
         <v>1532</v>
       </c>
       <c r="E526">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F526" t="s">
         <v>1552</v>
@@ -26508,7 +26508,7 @@
         <v>1533</v>
       </c>
       <c r="E527">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F527" t="s">
         <v>1552</v>
@@ -26543,7 +26543,7 @@
         <v>1533</v>
       </c>
       <c r="E528">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F528" t="s">
         <v>1552</v>
@@ -26578,7 +26578,7 @@
         <v>1533</v>
       </c>
       <c r="E529">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F529" t="s">
         <v>1552</v>
@@ -26613,7 +26613,7 @@
         <v>1533</v>
       </c>
       <c r="E530">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F530" t="s">
         <v>1552</v>
@@ -26648,7 +26648,7 @@
         <v>1533</v>
       </c>
       <c r="E531">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F531" t="s">
         <v>1552</v>
@@ -26683,7 +26683,7 @@
         <v>1533</v>
       </c>
       <c r="E532">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F532" t="s">
         <v>1552</v>
@@ -26718,7 +26718,7 @@
         <v>1533</v>
       </c>
       <c r="E533">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F533" t="s">
         <v>1552</v>
@@ -26753,7 +26753,7 @@
         <v>1534</v>
       </c>
       <c r="E534">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F534" t="s">
         <v>1552</v>
@@ -26791,7 +26791,7 @@
         <v>1534</v>
       </c>
       <c r="E535">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F535" t="s">
         <v>1552</v>
@@ -26826,7 +26826,7 @@
         <v>1534</v>
       </c>
       <c r="E536">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F536" t="s">
         <v>1552</v>
@@ -26861,7 +26861,7 @@
         <v>1534</v>
       </c>
       <c r="E537">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F537" t="s">
         <v>1554</v>
@@ -26899,7 +26899,7 @@
         <v>1534</v>
       </c>
       <c r="E538">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F538" t="s">
         <v>1554</v>
@@ -26937,7 +26937,7 @@
         <v>1534</v>
       </c>
       <c r="E539">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F539" t="s">
         <v>1552</v>
@@ -26972,7 +26972,7 @@
         <v>1534</v>
       </c>
       <c r="E540">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F540" t="s">
         <v>1552</v>
@@ -27007,7 +27007,7 @@
         <v>1534</v>
       </c>
       <c r="E541">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F541" t="s">
         <v>1552</v>
@@ -27042,7 +27042,7 @@
         <v>1535</v>
       </c>
       <c r="E542">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F542" t="s">
         <v>1552</v>
@@ -27077,7 +27077,7 @@
         <v>1535</v>
       </c>
       <c r="E543">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F543" t="s">
         <v>1552</v>
@@ -27112,7 +27112,7 @@
         <v>1535</v>
       </c>
       <c r="E544">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F544" t="s">
         <v>1552</v>
@@ -27147,7 +27147,7 @@
         <v>1535</v>
       </c>
       <c r="E545">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F545" t="s">
         <v>1552</v>
@@ -27182,7 +27182,7 @@
         <v>1535</v>
       </c>
       <c r="E546">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F546" t="s">
         <v>1552</v>
@@ -27217,7 +27217,7 @@
         <v>1535</v>
       </c>
       <c r="E547">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F547" t="s">
         <v>1552</v>
@@ -27252,7 +27252,7 @@
         <v>1535</v>
       </c>
       <c r="E548">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F548" t="s">
         <v>1552</v>
@@ -27287,7 +27287,7 @@
         <v>1535</v>
       </c>
       <c r="E549">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F549" t="s">
         <v>1552</v>
@@ -27322,7 +27322,7 @@
         <v>1535</v>
       </c>
       <c r="E550">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F550" t="s">
         <v>1552</v>
@@ -27360,7 +27360,7 @@
         <v>1535</v>
       </c>
       <c r="E551">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F551" t="s">
         <v>1552</v>
@@ -27395,7 +27395,7 @@
         <v>1536</v>
       </c>
       <c r="E552">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F552" t="s">
         <v>1552</v>
@@ -27430,7 +27430,7 @@
         <v>1536</v>
       </c>
       <c r="E553">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F553" t="s">
         <v>1554</v>
@@ -27468,7 +27468,7 @@
         <v>1536</v>
       </c>
       <c r="E554">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F554" t="s">
         <v>1552</v>
@@ -27503,7 +27503,7 @@
         <v>1536</v>
       </c>
       <c r="E555">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F555" t="s">
         <v>1552</v>
@@ -27538,7 +27538,7 @@
         <v>1537</v>
       </c>
       <c r="E556">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F556" t="s">
         <v>1552</v>
@@ -27573,7 +27573,7 @@
         <v>1537</v>
       </c>
       <c r="E557">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F557" t="s">
         <v>1554</v>
@@ -27608,7 +27608,7 @@
         <v>1537</v>
       </c>
       <c r="E558">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F558" t="s">
         <v>1552</v>
@@ -27643,7 +27643,7 @@
         <v>1537</v>
       </c>
       <c r="E559">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F559" t="s">
         <v>1552</v>
@@ -27678,7 +27678,7 @@
         <v>1537</v>
       </c>
       <c r="E560">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F560" t="s">
         <v>1554</v>
@@ -27716,7 +27716,7 @@
         <v>1537</v>
       </c>
       <c r="E561">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F561" t="s">
         <v>1552</v>
@@ -27751,7 +27751,7 @@
         <v>1537</v>
       </c>
       <c r="E562">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F562" t="s">
         <v>1552</v>
@@ -27786,7 +27786,7 @@
         <v>1537</v>
       </c>
       <c r="E563">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F563" t="s">
         <v>1552</v>
@@ -27821,7 +27821,7 @@
         <v>1537</v>
       </c>
       <c r="E564">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F564" t="s">
         <v>1552</v>
@@ -27856,7 +27856,7 @@
         <v>1537</v>
       </c>
       <c r="E565">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F565" t="s">
         <v>1552</v>
@@ -27891,7 +27891,7 @@
         <v>1537</v>
       </c>
       <c r="E566">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F566" t="s">
         <v>1552</v>
@@ -27926,7 +27926,7 @@
         <v>1538</v>
       </c>
       <c r="E567">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F567" t="s">
         <v>1556</v>
@@ -27961,7 +27961,7 @@
         <v>1538</v>
       </c>
       <c r="E568">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F568" t="s">
         <v>1552</v>
@@ -27996,7 +27996,7 @@
         <v>1538</v>
       </c>
       <c r="E569">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F569" t="s">
         <v>1552</v>
@@ -28031,7 +28031,7 @@
         <v>1538</v>
       </c>
       <c r="E570">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F570" t="s">
         <v>1552</v>
@@ -28066,7 +28066,7 @@
         <v>1538</v>
       </c>
       <c r="E571">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F571" t="s">
         <v>1552</v>
@@ -28101,7 +28101,7 @@
         <v>1539</v>
       </c>
       <c r="E572">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F572" t="s">
         <v>1552</v>
@@ -28136,7 +28136,7 @@
         <v>1539</v>
       </c>
       <c r="E573">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F573" t="s">
         <v>1552</v>
@@ -28171,7 +28171,7 @@
         <v>1539</v>
       </c>
       <c r="E574">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F574" t="s">
         <v>1552</v>
@@ -28206,7 +28206,7 @@
         <v>1539</v>
       </c>
       <c r="E575">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F575" t="s">
         <v>1554</v>
@@ -28244,7 +28244,7 @@
         <v>1540</v>
       </c>
       <c r="E576">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F576" t="s">
         <v>1552</v>
@@ -28279,7 +28279,7 @@
         <v>1540</v>
       </c>
       <c r="E577">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F577" t="s">
         <v>1556</v>
@@ -28317,7 +28317,7 @@
         <v>1540</v>
       </c>
       <c r="E578">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F578" t="s">
         <v>1552</v>
@@ -28352,7 +28352,7 @@
         <v>1540</v>
       </c>
       <c r="E579">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F579" t="s">
         <v>1552</v>
@@ -28387,7 +28387,7 @@
         <v>1541</v>
       </c>
       <c r="E580">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F580" t="s">
         <v>1552</v>
@@ -28422,7 +28422,7 @@
         <v>1541</v>
       </c>
       <c r="E581">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F581" t="s">
         <v>1552</v>
@@ -28457,7 +28457,7 @@
         <v>1541</v>
       </c>
       <c r="E582">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F582" t="s">
         <v>1554</v>
@@ -28492,7 +28492,7 @@
         <v>1541</v>
       </c>
       <c r="E583">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F583" t="s">
         <v>1552</v>
@@ -28527,7 +28527,7 @@
         <v>1541</v>
       </c>
       <c r="E584">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F584" t="s">
         <v>1552</v>
@@ -28562,7 +28562,7 @@
         <v>1541</v>
       </c>
       <c r="E585">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F585" t="s">
         <v>1552</v>
@@ -28597,7 +28597,7 @@
         <v>1541</v>
       </c>
       <c r="E586">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F586" t="s">
         <v>1554</v>
@@ -28635,7 +28635,7 @@
         <v>1541</v>
       </c>
       <c r="E587">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F587" t="s">
         <v>1552</v>
@@ -28670,7 +28670,7 @@
         <v>1541</v>
       </c>
       <c r="E588">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F588" t="s">
         <v>1552</v>
@@ -28705,7 +28705,7 @@
         <v>1541</v>
       </c>
       <c r="E589">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F589" t="s">
         <v>1552</v>
@@ -28740,7 +28740,7 @@
         <v>1542</v>
       </c>
       <c r="E590">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F590" t="s">
         <v>1552</v>
@@ -28775,7 +28775,7 @@
         <v>1542</v>
       </c>
       <c r="E591">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F591" t="s">
         <v>1554</v>
@@ -28810,7 +28810,7 @@
         <v>1542</v>
       </c>
       <c r="E592">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F592" t="s">
         <v>1552</v>
@@ -28845,7 +28845,7 @@
         <v>1543</v>
       </c>
       <c r="E593">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F593" t="s">
         <v>1554</v>
@@ -28883,7 +28883,7 @@
         <v>1543</v>
       </c>
       <c r="E594">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F594" t="s">
         <v>1554</v>
@@ -28921,7 +28921,7 @@
         <v>1543</v>
       </c>
       <c r="E595">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F595" t="s">
         <v>1552</v>
@@ -28956,7 +28956,7 @@
         <v>1543</v>
       </c>
       <c r="E596">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F596" t="s">
         <v>1552</v>
@@ -28991,7 +28991,7 @@
         <v>1543</v>
       </c>
       <c r="E597">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F597" t="s">
         <v>1552</v>
@@ -29026,7 +29026,7 @@
         <v>1544</v>
       </c>
       <c r="E598">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F598" t="s">
         <v>1552</v>
@@ -29061,7 +29061,7 @@
         <v>1545</v>
       </c>
       <c r="E599">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F599" t="s">
         <v>1552</v>
@@ -29096,7 +29096,7 @@
         <v>1545</v>
       </c>
       <c r="E600">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F600" t="s">
         <v>1552</v>
@@ -29131,7 +29131,7 @@
         <v>1545</v>
       </c>
       <c r="E601">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F601" t="s">
         <v>1552</v>
@@ -29166,7 +29166,7 @@
         <v>1545</v>
       </c>
       <c r="E602">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F602" t="s">
         <v>1552</v>
@@ -29201,7 +29201,7 @@
         <v>1545</v>
       </c>
       <c r="E603">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F603" t="s">
         <v>1552</v>
@@ -29236,7 +29236,7 @@
         <v>1545</v>
       </c>
       <c r="E604">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F604" t="s">
         <v>1552</v>
@@ -29271,7 +29271,7 @@
         <v>1545</v>
       </c>
       <c r="E605">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F605" t="s">
         <v>1552</v>
@@ -29306,7 +29306,7 @@
         <v>1545</v>
       </c>
       <c r="E606">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F606" t="s">
         <v>1552</v>
@@ -29341,7 +29341,7 @@
         <v>1545</v>
       </c>
       <c r="E607">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F607" t="s">
         <v>1552</v>
@@ -29376,7 +29376,7 @@
         <v>1545</v>
       </c>
       <c r="E608">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F608" t="s">
         <v>1554</v>
@@ -29414,7 +29414,7 @@
         <v>1546</v>
       </c>
       <c r="E609">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F609" t="s">
         <v>1552</v>
@@ -29449,7 +29449,7 @@
         <v>1546</v>
       </c>
       <c r="E610">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F610" t="s">
         <v>1552</v>
@@ -29484,7 +29484,7 @@
         <v>1546</v>
       </c>
       <c r="E611">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F611" t="s">
         <v>1552</v>
@@ -29519,7 +29519,7 @@
         <v>1546</v>
       </c>
       <c r="E612">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F612" t="s">
         <v>1552</v>
@@ -29554,7 +29554,7 @@
         <v>1546</v>
       </c>
       <c r="E613">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F613" t="s">
         <v>1554</v>
@@ -29592,7 +29592,7 @@
         <v>1546</v>
       </c>
       <c r="E614">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F614" t="s">
         <v>1554</v>
@@ -29630,7 +29630,7 @@
         <v>1546</v>
       </c>
       <c r="E615">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F615" t="s">
         <v>1552</v>
@@ -29665,7 +29665,7 @@
         <v>1546</v>
       </c>
       <c r="E616">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F616" t="s">
         <v>1554</v>
@@ -29703,7 +29703,7 @@
         <v>1546</v>
       </c>
       <c r="E617">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F617" t="s">
         <v>1552</v>
@@ -29738,7 +29738,7 @@
         <v>1546</v>
       </c>
       <c r="E618">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F618" t="s">
         <v>1552</v>
@@ -29773,7 +29773,7 @@
         <v>1546</v>
       </c>
       <c r="E619">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F619" t="s">
         <v>1552</v>
@@ -29808,7 +29808,7 @@
         <v>1547</v>
       </c>
       <c r="E620">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F620" t="s">
         <v>1552</v>
@@ -29843,7 +29843,7 @@
         <v>1547</v>
       </c>
       <c r="E621">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F621" t="s">
         <v>1554</v>
@@ -29881,7 +29881,7 @@
         <v>1547</v>
       </c>
       <c r="E622">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F622" t="s">
         <v>1554</v>
@@ -29919,7 +29919,7 @@
         <v>1547</v>
       </c>
       <c r="E623">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F623" t="s">
         <v>1552</v>
@@ -29954,7 +29954,7 @@
         <v>1548</v>
       </c>
       <c r="E624">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F624" t="s">
         <v>1554</v>
@@ -29992,7 +29992,7 @@
         <v>1548</v>
       </c>
       <c r="E625">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F625" t="s">
         <v>1552</v>
@@ -30027,7 +30027,7 @@
         <v>1548</v>
       </c>
       <c r="E626">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F626" t="s">
         <v>1554</v>
@@ -30065,7 +30065,7 @@
         <v>1548</v>
       </c>
       <c r="E627">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F627" t="s">
         <v>1552</v>
@@ -30100,7 +30100,7 @@
         <v>1549</v>
       </c>
       <c r="E628">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F628" t="s">
         <v>1552</v>
@@ -30135,7 +30135,7 @@
         <v>1549</v>
       </c>
       <c r="E629">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F629" t="s">
         <v>1552</v>
@@ -30170,7 +30170,7 @@
         <v>1549</v>
       </c>
       <c r="E630">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F630" t="s">
         <v>1552</v>
@@ -30205,7 +30205,7 @@
         <v>1549</v>
       </c>
       <c r="E631">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F631" t="s">
         <v>1552</v>
@@ -30240,7 +30240,7 @@
         <v>1549</v>
       </c>
       <c r="E632">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F632" t="s">
         <v>1552</v>
@@ -30275,7 +30275,7 @@
         <v>1549</v>
       </c>
       <c r="E633">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F633" t="s">
         <v>1552</v>
@@ -30310,7 +30310,7 @@
         <v>1549</v>
       </c>
       <c r="E634">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F634" t="s">
         <v>1552</v>
@@ -30348,7 +30348,7 @@
         <v>1549</v>
       </c>
       <c r="E635">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F635" t="s">
         <v>1554</v>
@@ -30386,7 +30386,7 @@
         <v>1549</v>
       </c>
       <c r="E636">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F636" t="s">
         <v>1552</v>
@@ -30424,7 +30424,7 @@
         <v>1550</v>
       </c>
       <c r="E637">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F637" t="s">
         <v>1552</v>
@@ -30462,7 +30462,7 @@
         <v>1550</v>
       </c>
       <c r="E638">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F638" t="s">
         <v>1552</v>
@@ -30497,7 +30497,7 @@
         <v>1550</v>
       </c>
       <c r="E639">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F639" t="s">
         <v>1552</v>
@@ -30532,7 +30532,7 @@
         <v>1550</v>
       </c>
       <c r="E640">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F640" t="s">
         <v>1552</v>
@@ -30567,7 +30567,7 @@
         <v>1550</v>
       </c>
       <c r="E641">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F641" t="s">
         <v>1552</v>
@@ -30602,7 +30602,7 @@
         <v>1550</v>
       </c>
       <c r="E642">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F642" t="s">
         <v>1552</v>
@@ -30637,7 +30637,7 @@
         <v>1550</v>
       </c>
       <c r="E643">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F643" t="s">
         <v>1554</v>
@@ -30675,7 +30675,7 @@
         <v>1551</v>
       </c>
       <c r="E644">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F644" t="s">
         <v>1552</v>
@@ -30710,7 +30710,7 @@
         <v>1551</v>
       </c>
       <c r="E645">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F645" t="s">
         <v>1552</v>
@@ -30745,7 +30745,7 @@
         <v>1551</v>
       </c>
       <c r="E646">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F646" t="s">
         <v>1552</v>
@@ -30780,7 +30780,7 @@
         <v>1551</v>
       </c>
       <c r="E647">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F647" t="s">
         <v>1552</v>
@@ -30815,7 +30815,7 @@
         <v>1551</v>
       </c>
       <c r="E648">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F648" t="s">
         <v>1552</v>
@@ -30850,7 +30850,7 @@
         <v>1551</v>
       </c>
       <c r="E649">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F649" t="s">
         <v>1552</v>
@@ -30885,7 +30885,7 @@
         <v>1551</v>
       </c>
       <c r="E650">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F650" t="s">
         <v>1552</v>
@@ -30920,7 +30920,7 @@
         <v>1551</v>
       </c>
       <c r="E651">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F651" t="s">
         <v>1552</v>

--- a/BacklogGATEAutoCompleto.xlsx
+++ b/BacklogGATEAutoCompleto.xlsx
@@ -64,6 +64,9 @@
     <t>NÚCLEO TÉCNICO DE POLÍTICAS PÚBLICAS</t>
   </si>
   <si>
+    <t>SECRETARIA GERAL DO GATE</t>
+  </si>
+  <si>
     <t>NÚCLEO TÉCNICO DE CIÊNCIAS NATURAIS</t>
   </si>
   <si>
@@ -97,9 +100,6 @@
     <t>NÚCLEO TÉCNICO DE CIÊNCIA DE DADOS,NÚCLEO TÉCNICO DE CONTABILIDADE</t>
   </si>
   <si>
-    <t>SECRETARIA GERAL DO GATE</t>
-  </si>
-  <si>
     <t>GRUPO EXECUTIVO DE FISCALIZAÇÃO DE UNIDADES POLICIAIS E PRISIONAIS 18 - DES</t>
   </si>
   <si>
@@ -3973,15 +3973,18 @@
     <t>ITAMAR COSTA KALIL</t>
   </si>
   <si>
+    <t>_SEM USUARIO ATRIBUIDO</t>
+  </si>
+  <si>
+    <t>LILIAN ALVES DE ARAUJO</t>
+  </si>
+  <si>
+    <t>VANESSA TRINDADE CAMPOS DA SILVA</t>
+  </si>
+  <si>
     <t>MARCELO TEIXEIRA SANTANA</t>
   </si>
   <si>
-    <t>LILIAN ALVES DE ARAUJO</t>
-  </si>
-  <si>
-    <t>VANESSA TRINDADE CAMPOS DA SILVA</t>
-  </si>
-  <si>
     <t>VANESSA FERNANDES LEÃO</t>
   </si>
   <si>
@@ -4103,9 +4106,6 @@
   </si>
   <si>
     <t>ALESSANDRA ALMEIDA DIAS DA SILVA,SIMONE MANNHEIMER DE ALVARENGA</t>
-  </si>
-  <si>
-    <t>_SEM USUARIO ATRIBUIDO</t>
   </si>
   <si>
     <t>NIVANA DANIELLE SILVA COSTA</t>
@@ -8330,7 +8330,7 @@
     </row>
     <row r="45" spans="1:12">
       <c r="A45" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B45" t="s">
         <v>78</v>
@@ -8351,7 +8351,7 @@
         <v>1284</v>
       </c>
       <c r="I45" t="s">
-        <v>1319</v>
+        <v>1322</v>
       </c>
       <c r="J45" t="s">
         <v>1469</v>
@@ -8427,7 +8427,7 @@
         <v>1450</v>
       </c>
       <c r="K47" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="L47" t="s">
         <v>2057</v>
@@ -8435,7 +8435,7 @@
     </row>
     <row r="48" spans="1:12">
       <c r="A48" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B48" t="s">
         <v>81</v>
@@ -8456,7 +8456,7 @@
         <v>1284</v>
       </c>
       <c r="I48" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="J48" t="s">
         <v>1471</v>
@@ -8491,7 +8491,7 @@
         <v>1284</v>
       </c>
       <c r="I49" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="J49" t="s">
         <v>1472</v>
@@ -8505,7 +8505,7 @@
     </row>
     <row r="50" spans="1:12">
       <c r="A50" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B50" t="s">
         <v>83</v>
@@ -8526,7 +8526,7 @@
         <v>1284</v>
       </c>
       <c r="I50" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="J50" t="s">
         <v>1473</v>
@@ -8750,7 +8750,7 @@
     </row>
     <row r="57" spans="1:12">
       <c r="A57" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B57" t="s">
         <v>90</v>
@@ -8771,7 +8771,7 @@
         <v>1284</v>
       </c>
       <c r="I57" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="J57" t="s">
         <v>1480</v>
@@ -8841,7 +8841,7 @@
         <v>1284</v>
       </c>
       <c r="I59" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="J59" t="s">
         <v>1482</v>
@@ -8855,7 +8855,7 @@
     </row>
     <row r="60" spans="1:12">
       <c r="A60" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B60" t="s">
         <v>93</v>
@@ -8876,7 +8876,7 @@
         <v>1284</v>
       </c>
       <c r="I60" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="J60" t="s">
         <v>1483</v>
@@ -8890,7 +8890,7 @@
     </row>
     <row r="61" spans="1:12">
       <c r="A61" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B61" t="s">
         <v>94</v>
@@ -8911,7 +8911,7 @@
         <v>1284</v>
       </c>
       <c r="I61" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="J61" t="s">
         <v>1484</v>
@@ -9030,7 +9030,7 @@
     </row>
     <row r="65" spans="1:12">
       <c r="A65" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B65" t="s">
         <v>98</v>
@@ -9051,7 +9051,7 @@
         <v>1284</v>
       </c>
       <c r="I65" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="J65" t="s">
         <v>1488</v>
@@ -9135,7 +9135,7 @@
     </row>
     <row r="68" spans="1:12">
       <c r="A68" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B68" t="s">
         <v>101</v>
@@ -9275,7 +9275,7 @@
     </row>
     <row r="72" spans="1:12">
       <c r="A72" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B72" t="s">
         <v>105</v>
@@ -9380,7 +9380,7 @@
     </row>
     <row r="75" spans="1:12">
       <c r="A75" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B75" t="s">
         <v>108</v>
@@ -9401,7 +9401,7 @@
         <v>1284</v>
       </c>
       <c r="I75" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="J75" t="s">
         <v>1498</v>
@@ -9450,7 +9450,7 @@
     </row>
     <row r="77" spans="1:12">
       <c r="A77" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B77" t="s">
         <v>110</v>
@@ -9471,7 +9471,7 @@
         <v>1284</v>
       </c>
       <c r="I77" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="J77" t="s">
         <v>1500</v>
@@ -9520,7 +9520,7 @@
     </row>
     <row r="79" spans="1:12">
       <c r="A79" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B79" t="s">
         <v>112</v>
@@ -9576,7 +9576,7 @@
         <v>1284</v>
       </c>
       <c r="I80" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="J80" t="s">
         <v>1503</v>
@@ -9590,7 +9590,7 @@
     </row>
     <row r="81" spans="1:12">
       <c r="A81" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B81" t="s">
         <v>114</v>
@@ -9660,7 +9660,7 @@
     </row>
     <row r="83" spans="1:12">
       <c r="A83" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B83" t="s">
         <v>116</v>
@@ -9681,7 +9681,7 @@
         <v>1284</v>
       </c>
       <c r="I83" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="J83" t="s">
         <v>1506</v>
@@ -9730,7 +9730,7 @@
     </row>
     <row r="85" spans="1:12">
       <c r="A85" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B85" t="s">
         <v>118</v>
@@ -9751,7 +9751,7 @@
         <v>1284</v>
       </c>
       <c r="I85" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="J85" t="s">
         <v>1508</v>
@@ -9800,7 +9800,7 @@
     </row>
     <row r="87" spans="1:12">
       <c r="A87" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B87" t="s">
         <v>120</v>
@@ -9821,7 +9821,7 @@
         <v>1284</v>
       </c>
       <c r="I87" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="J87" t="s">
         <v>1510</v>
@@ -9856,7 +9856,7 @@
         <v>1284</v>
       </c>
       <c r="I88" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="J88" t="s">
         <v>1511</v>
@@ -9870,7 +9870,7 @@
     </row>
     <row r="89" spans="1:12">
       <c r="A89" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B89" t="s">
         <v>122</v>
@@ -9891,7 +9891,7 @@
         <v>1284</v>
       </c>
       <c r="I89" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="J89" t="s">
         <v>1512</v>
@@ -9905,7 +9905,7 @@
     </row>
     <row r="90" spans="1:12">
       <c r="A90" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B90" t="s">
         <v>123</v>
@@ -9926,7 +9926,7 @@
         <v>1284</v>
       </c>
       <c r="I90" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="J90" t="s">
         <v>1513</v>
@@ -9940,7 +9940,7 @@
     </row>
     <row r="91" spans="1:12">
       <c r="A91" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B91" t="s">
         <v>124</v>
@@ -10031,7 +10031,7 @@
         <v>1284</v>
       </c>
       <c r="I93" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="J93" t="s">
         <v>1516</v>
@@ -10045,7 +10045,7 @@
     </row>
     <row r="94" spans="1:12">
       <c r="A94" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B94" t="s">
         <v>127</v>
@@ -10066,7 +10066,7 @@
         <v>1284</v>
       </c>
       <c r="I94" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="J94" t="s">
         <v>1517</v>
@@ -10150,7 +10150,7 @@
     </row>
     <row r="97" spans="1:12">
       <c r="A97" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B97" t="s">
         <v>130</v>
@@ -10185,7 +10185,7 @@
     </row>
     <row r="98" spans="1:12">
       <c r="A98" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B98" t="s">
         <v>131</v>
@@ -10360,7 +10360,7 @@
     </row>
     <row r="103" spans="1:12">
       <c r="A103" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B103" t="s">
         <v>136</v>
@@ -10395,7 +10395,7 @@
     </row>
     <row r="104" spans="1:12">
       <c r="A104" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B104" t="s">
         <v>137</v>
@@ -10416,7 +10416,7 @@
         <v>1284</v>
       </c>
       <c r="I104" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="J104" t="s">
         <v>1527</v>
@@ -10451,7 +10451,7 @@
         <v>1284</v>
       </c>
       <c r="I105" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="J105" t="s">
         <v>1528</v>
@@ -10465,7 +10465,7 @@
     </row>
     <row r="106" spans="1:12">
       <c r="A106" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B106" t="s">
         <v>139</v>
@@ -10486,7 +10486,7 @@
         <v>1284</v>
       </c>
       <c r="I106" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="J106" t="s">
         <v>1529</v>
@@ -10521,7 +10521,7 @@
         <v>1284</v>
       </c>
       <c r="I107" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="J107" t="s">
         <v>1530</v>
@@ -10535,7 +10535,7 @@
     </row>
     <row r="108" spans="1:12">
       <c r="A108" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B108" t="s">
         <v>141</v>
@@ -10556,7 +10556,7 @@
         <v>1284</v>
       </c>
       <c r="I108" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="J108" t="s">
         <v>1531</v>
@@ -10605,7 +10605,7 @@
     </row>
     <row r="110" spans="1:12">
       <c r="A110" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B110" t="s">
         <v>143</v>
@@ -10766,7 +10766,7 @@
         <v>1284</v>
       </c>
       <c r="I114" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="J114" t="s">
         <v>1537</v>
@@ -10780,7 +10780,7 @@
     </row>
     <row r="115" spans="1:12">
       <c r="A115" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B115" t="s">
         <v>148</v>
@@ -10804,7 +10804,7 @@
         <v>1287</v>
       </c>
       <c r="I115" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="J115" t="s">
         <v>1538</v>
@@ -10839,7 +10839,7 @@
         <v>1284</v>
       </c>
       <c r="I116" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="J116" t="s">
         <v>1539</v>
@@ -10853,7 +10853,7 @@
     </row>
     <row r="117" spans="1:12">
       <c r="A117" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B117" t="s">
         <v>150</v>
@@ -10888,7 +10888,7 @@
     </row>
     <row r="118" spans="1:12">
       <c r="A118" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B118" t="s">
         <v>151</v>
@@ -10958,7 +10958,7 @@
     </row>
     <row r="120" spans="1:12">
       <c r="A120" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B120" t="s">
         <v>153</v>
@@ -10979,7 +10979,7 @@
         <v>1284</v>
       </c>
       <c r="I120" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="J120" t="s">
         <v>1543</v>
@@ -10993,7 +10993,7 @@
     </row>
     <row r="121" spans="1:12">
       <c r="A121" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B121" t="s">
         <v>154</v>
@@ -11014,7 +11014,7 @@
         <v>1284</v>
       </c>
       <c r="I121" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="J121" t="s">
         <v>1544</v>
@@ -11028,7 +11028,7 @@
     </row>
     <row r="122" spans="1:12">
       <c r="A122" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B122" t="s">
         <v>155</v>
@@ -11049,7 +11049,7 @@
         <v>1284</v>
       </c>
       <c r="I122" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="J122" t="s">
         <v>1545</v>
@@ -11063,7 +11063,7 @@
     </row>
     <row r="123" spans="1:12">
       <c r="A123" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B123" t="s">
         <v>156</v>
@@ -11098,7 +11098,7 @@
     </row>
     <row r="124" spans="1:12">
       <c r="A124" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B124" t="s">
         <v>157</v>
@@ -11119,7 +11119,7 @@
         <v>1284</v>
       </c>
       <c r="I124" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="J124" t="s">
         <v>1547</v>
@@ -11133,7 +11133,7 @@
     </row>
     <row r="125" spans="1:12">
       <c r="A125" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B125" t="s">
         <v>158</v>
@@ -11168,7 +11168,7 @@
     </row>
     <row r="126" spans="1:12">
       <c r="A126" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B126" t="s">
         <v>159</v>
@@ -11189,7 +11189,7 @@
         <v>1284</v>
       </c>
       <c r="I126" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="J126" t="s">
         <v>1549</v>
@@ -11203,7 +11203,7 @@
     </row>
     <row r="127" spans="1:12">
       <c r="A127" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B127" t="s">
         <v>160</v>
@@ -11224,7 +11224,7 @@
         <v>1284</v>
       </c>
       <c r="I127" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="J127" t="s">
         <v>1550</v>
@@ -11273,7 +11273,7 @@
     </row>
     <row r="129" spans="1:12">
       <c r="A129" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B129" t="s">
         <v>162</v>
@@ -11294,7 +11294,7 @@
         <v>1284</v>
       </c>
       <c r="I129" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="J129" t="s">
         <v>1552</v>
@@ -11308,7 +11308,7 @@
     </row>
     <row r="130" spans="1:12">
       <c r="A130" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B130" t="s">
         <v>163</v>
@@ -11329,7 +11329,7 @@
         <v>1284</v>
       </c>
       <c r="I130" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="J130" t="s">
         <v>1553</v>
@@ -11343,7 +11343,7 @@
     </row>
     <row r="131" spans="1:12">
       <c r="A131" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B131" t="s">
         <v>164</v>
@@ -11364,7 +11364,7 @@
         <v>1284</v>
       </c>
       <c r="I131" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="J131" t="s">
         <v>1554</v>
@@ -11378,7 +11378,7 @@
     </row>
     <row r="132" spans="1:12">
       <c r="A132" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B132" t="s">
         <v>165</v>
@@ -11399,7 +11399,7 @@
         <v>1284</v>
       </c>
       <c r="I132" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="J132" t="s">
         <v>1555</v>
@@ -11469,7 +11469,7 @@
         <v>1284</v>
       </c>
       <c r="I134" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="J134" t="s">
         <v>1557</v>
@@ -11553,7 +11553,7 @@
     </row>
     <row r="137" spans="1:12">
       <c r="A137" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B137" t="s">
         <v>170</v>
@@ -11609,7 +11609,7 @@
         <v>1284</v>
       </c>
       <c r="I138" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="J138" t="s">
         <v>1560</v>
@@ -11658,7 +11658,7 @@
     </row>
     <row r="140" spans="1:12">
       <c r="A140" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B140" t="s">
         <v>173</v>
@@ -11693,7 +11693,7 @@
     </row>
     <row r="141" spans="1:12">
       <c r="A141" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B141" t="s">
         <v>174</v>
@@ -11728,7 +11728,7 @@
     </row>
     <row r="142" spans="1:12">
       <c r="A142" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B142" t="s">
         <v>175</v>
@@ -11763,7 +11763,7 @@
     </row>
     <row r="143" spans="1:12">
       <c r="A143" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B143" t="s">
         <v>176</v>
@@ -11798,7 +11798,7 @@
     </row>
     <row r="144" spans="1:12">
       <c r="A144" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B144" t="s">
         <v>177</v>
@@ -11819,7 +11819,7 @@
         <v>1284</v>
       </c>
       <c r="I144" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="J144" t="s">
         <v>1566</v>
@@ -11868,7 +11868,7 @@
     </row>
     <row r="146" spans="1:12">
       <c r="A146" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B146" t="s">
         <v>179</v>
@@ -11889,7 +11889,7 @@
         <v>1284</v>
       </c>
       <c r="I146" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="J146" t="s">
         <v>1568</v>
@@ -11903,7 +11903,7 @@
     </row>
     <row r="147" spans="1:12">
       <c r="A147" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B147" t="s">
         <v>180</v>
@@ -11938,7 +11938,7 @@
     </row>
     <row r="148" spans="1:12">
       <c r="A148" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B148" t="s">
         <v>181</v>
@@ -11973,7 +11973,7 @@
     </row>
     <row r="149" spans="1:12">
       <c r="A149" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B149" t="s">
         <v>182</v>
@@ -12029,7 +12029,7 @@
         <v>1284</v>
       </c>
       <c r="I150" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="J150" t="s">
         <v>1572</v>
@@ -12134,7 +12134,7 @@
         <v>1284</v>
       </c>
       <c r="I153" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="J153" t="s">
         <v>1575</v>
@@ -12148,7 +12148,7 @@
     </row>
     <row r="154" spans="1:12">
       <c r="A154" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B154" t="s">
         <v>187</v>
@@ -12218,7 +12218,7 @@
     </row>
     <row r="156" spans="1:12">
       <c r="A156" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B156" t="s">
         <v>189</v>
@@ -12288,7 +12288,7 @@
     </row>
     <row r="158" spans="1:12">
       <c r="A158" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B158" t="s">
         <v>191</v>
@@ -12344,7 +12344,7 @@
         <v>1284</v>
       </c>
       <c r="I159" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="J159" t="s">
         <v>1581</v>
@@ -12358,7 +12358,7 @@
     </row>
     <row r="160" spans="1:12">
       <c r="A160" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B160" t="s">
         <v>193</v>
@@ -12449,7 +12449,7 @@
         <v>1284</v>
       </c>
       <c r="I162" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="J162" t="s">
         <v>1584</v>
@@ -12463,7 +12463,7 @@
     </row>
     <row r="163" spans="1:12">
       <c r="A163" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B163" t="s">
         <v>196</v>
@@ -12484,7 +12484,7 @@
         <v>1284</v>
       </c>
       <c r="I163" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="J163" t="s">
         <v>1585</v>
@@ -12498,7 +12498,7 @@
     </row>
     <row r="164" spans="1:12">
       <c r="A164" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B164" t="s">
         <v>197</v>
@@ -12533,7 +12533,7 @@
     </row>
     <row r="165" spans="1:12">
       <c r="A165" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B165" t="s">
         <v>198</v>
@@ -12638,7 +12638,7 @@
     </row>
     <row r="168" spans="1:12">
       <c r="A168" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B168" t="s">
         <v>201</v>
@@ -12708,7 +12708,7 @@
     </row>
     <row r="170" spans="1:12">
       <c r="A170" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B170" t="s">
         <v>203</v>
@@ -12764,7 +12764,7 @@
         <v>1284</v>
       </c>
       <c r="I171" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="J171" t="s">
         <v>1593</v>
@@ -12848,7 +12848,7 @@
     </row>
     <row r="174" spans="1:12">
       <c r="A174" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B174" t="s">
         <v>207</v>
@@ -12953,7 +12953,7 @@
     </row>
     <row r="177" spans="1:12">
       <c r="A177" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B177" t="s">
         <v>210</v>
@@ -12974,7 +12974,7 @@
         <v>1284</v>
       </c>
       <c r="I177" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="J177" t="s">
         <v>1599</v>
@@ -13009,7 +13009,7 @@
         <v>1284</v>
       </c>
       <c r="I178" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="J178" t="s">
         <v>1600</v>
@@ -13058,7 +13058,7 @@
     </row>
     <row r="180" spans="1:12">
       <c r="A180" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B180" t="s">
         <v>213</v>
@@ -13079,7 +13079,7 @@
         <v>1284</v>
       </c>
       <c r="I180" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="J180" t="s">
         <v>1602</v>
@@ -13128,7 +13128,7 @@
     </row>
     <row r="182" spans="1:12">
       <c r="A182" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="B182" t="s">
         <v>215</v>
@@ -13149,7 +13149,7 @@
         <v>1284</v>
       </c>
       <c r="I182" t="s">
-        <v>1363</v>
+        <v>1319</v>
       </c>
       <c r="J182" t="s">
         <v>1604</v>
@@ -13198,7 +13198,7 @@
     </row>
     <row r="184" spans="1:12">
       <c r="A184" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B184" t="s">
         <v>217</v>
@@ -13233,7 +13233,7 @@
     </row>
     <row r="185" spans="1:12">
       <c r="A185" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B185" t="s">
         <v>218</v>
@@ -13338,7 +13338,7 @@
     </row>
     <row r="188" spans="1:12">
       <c r="A188" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B188" t="s">
         <v>221</v>
@@ -13408,7 +13408,7 @@
     </row>
     <row r="190" spans="1:12">
       <c r="A190" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B190" t="s">
         <v>223</v>
@@ -13443,7 +13443,7 @@
     </row>
     <row r="191" spans="1:12">
       <c r="A191" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B191" t="s">
         <v>224</v>
@@ -13513,7 +13513,7 @@
     </row>
     <row r="193" spans="1:12">
       <c r="A193" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B193" t="s">
         <v>226</v>
@@ -13653,7 +13653,7 @@
     </row>
     <row r="197" spans="1:12">
       <c r="A197" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B197" t="s">
         <v>230</v>
@@ -14003,7 +14003,7 @@
     </row>
     <row r="207" spans="1:12">
       <c r="A207" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B207" t="s">
         <v>240</v>
@@ -14038,7 +14038,7 @@
     </row>
     <row r="208" spans="1:12">
       <c r="A208" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B208" t="s">
         <v>241</v>
@@ -14073,7 +14073,7 @@
     </row>
     <row r="209" spans="1:12">
       <c r="A209" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B209" t="s">
         <v>242</v>
@@ -14108,7 +14108,7 @@
     </row>
     <row r="210" spans="1:12">
       <c r="A210" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B210" t="s">
         <v>243</v>
@@ -14146,7 +14146,7 @@
     </row>
     <row r="211" spans="1:12">
       <c r="A211" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B211" t="s">
         <v>244</v>
@@ -14181,7 +14181,7 @@
     </row>
     <row r="212" spans="1:12">
       <c r="A212" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B212" t="s">
         <v>245</v>
@@ -14286,7 +14286,7 @@
     </row>
     <row r="215" spans="1:12">
       <c r="A215" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B215" t="s">
         <v>248</v>
@@ -14321,7 +14321,7 @@
     </row>
     <row r="216" spans="1:12">
       <c r="A216" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B216" t="s">
         <v>249</v>
@@ -14356,7 +14356,7 @@
     </row>
     <row r="217" spans="1:12">
       <c r="A217" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B217" t="s">
         <v>250</v>
@@ -14461,7 +14461,7 @@
     </row>
     <row r="220" spans="1:12">
       <c r="A220" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B220" t="s">
         <v>253</v>
@@ -14531,7 +14531,7 @@
     </row>
     <row r="222" spans="1:12">
       <c r="A222" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B222" t="s">
         <v>255</v>
@@ -14566,7 +14566,7 @@
     </row>
     <row r="223" spans="1:12">
       <c r="A223" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B223" t="s">
         <v>256</v>
@@ -14916,7 +14916,7 @@
     </row>
     <row r="233" spans="1:12">
       <c r="A233" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B233" t="s">
         <v>266</v>
@@ -14951,7 +14951,7 @@
     </row>
     <row r="234" spans="1:12">
       <c r="A234" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B234" t="s">
         <v>267</v>
@@ -15091,7 +15091,7 @@
     </row>
     <row r="238" spans="1:12">
       <c r="A238" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B238" t="s">
         <v>271</v>
@@ -15126,7 +15126,7 @@
     </row>
     <row r="239" spans="1:12">
       <c r="A239" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B239" t="s">
         <v>272</v>
@@ -15517,7 +15517,7 @@
     </row>
     <row r="250" spans="1:12">
       <c r="A250" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B250" t="s">
         <v>283</v>
@@ -15552,7 +15552,7 @@
     </row>
     <row r="251" spans="1:12">
       <c r="A251" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B251" t="s">
         <v>284</v>
@@ -15587,7 +15587,7 @@
     </row>
     <row r="252" spans="1:12">
       <c r="A252" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B252" t="s">
         <v>285</v>
@@ -15622,7 +15622,7 @@
     </row>
     <row r="253" spans="1:12">
       <c r="A253" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B253" t="s">
         <v>286</v>
@@ -15832,7 +15832,7 @@
     </row>
     <row r="259" spans="1:12">
       <c r="A259" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B259" t="s">
         <v>292</v>
@@ -15972,7 +15972,7 @@
     </row>
     <row r="263" spans="1:12">
       <c r="A263" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B263" t="s">
         <v>296</v>
@@ -16063,7 +16063,7 @@
         <v>1284</v>
       </c>
       <c r="I265" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="J265" t="s">
         <v>1687</v>
@@ -16182,7 +16182,7 @@
     </row>
     <row r="269" spans="1:12">
       <c r="A269" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B269" t="s">
         <v>302</v>
@@ -16287,7 +16287,7 @@
     </row>
     <row r="272" spans="1:12">
       <c r="A272" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B272" t="s">
         <v>305</v>
@@ -16553,7 +16553,7 @@
         <v>1284</v>
       </c>
       <c r="I279" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="J279" t="s">
         <v>1701</v>
@@ -16567,7 +16567,7 @@
     </row>
     <row r="280" spans="1:12">
       <c r="A280" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B280" t="s">
         <v>313</v>
@@ -16672,7 +16672,7 @@
     </row>
     <row r="283" spans="1:12">
       <c r="A283" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B283" t="s">
         <v>316</v>
@@ -16917,7 +16917,7 @@
     </row>
     <row r="290" spans="1:12">
       <c r="A290" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B290" t="s">
         <v>323</v>
@@ -16952,7 +16952,7 @@
     </row>
     <row r="291" spans="1:12">
       <c r="A291" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B291" t="s">
         <v>324</v>
@@ -16987,7 +16987,7 @@
     </row>
     <row r="292" spans="1:12">
       <c r="A292" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B292" t="s">
         <v>325</v>
@@ -17057,7 +17057,7 @@
     </row>
     <row r="294" spans="1:12">
       <c r="A294" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B294" t="s">
         <v>327</v>
@@ -17078,7 +17078,7 @@
         <v>1284</v>
       </c>
       <c r="I294" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="J294" t="s">
         <v>1716</v>
@@ -17340,7 +17340,7 @@
     </row>
     <row r="302" spans="1:12">
       <c r="A302" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B302" t="s">
         <v>335</v>
@@ -17361,7 +17361,7 @@
         <v>1284</v>
       </c>
       <c r="I302" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="J302" t="s">
         <v>1724</v>
@@ -17483,7 +17483,7 @@
     </row>
     <row r="306" spans="1:12">
       <c r="A306" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B306" t="s">
         <v>339</v>
@@ -17658,7 +17658,7 @@
     </row>
     <row r="311" spans="1:12">
       <c r="A311" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B311" t="s">
         <v>344</v>
@@ -17693,7 +17693,7 @@
     </row>
     <row r="312" spans="1:12">
       <c r="A312" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B312" t="s">
         <v>345</v>
@@ -18113,7 +18113,7 @@
     </row>
     <row r="324" spans="1:12">
       <c r="A324" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B324" t="s">
         <v>357</v>
@@ -18484,7 +18484,7 @@
         <v>1284</v>
       </c>
       <c r="I334" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="J334" t="s">
         <v>1756</v>
@@ -18603,7 +18603,7 @@
     </row>
     <row r="338" spans="1:12">
       <c r="A338" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="B338" t="s">
         <v>371</v>
@@ -18638,7 +18638,7 @@
     </row>
     <row r="339" spans="1:12">
       <c r="A339" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B339" t="s">
         <v>372</v>
@@ -18708,7 +18708,7 @@
     </row>
     <row r="341" spans="1:12">
       <c r="A341" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B341" t="s">
         <v>374</v>
@@ -18778,7 +18778,7 @@
     </row>
     <row r="343" spans="1:12">
       <c r="A343" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B343" t="s">
         <v>376</v>
@@ -18834,7 +18834,7 @@
         <v>1284</v>
       </c>
       <c r="I344" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="J344" t="s">
         <v>1766</v>
@@ -18883,7 +18883,7 @@
     </row>
     <row r="346" spans="1:12">
       <c r="A346" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B346" t="s">
         <v>379</v>
@@ -18953,7 +18953,7 @@
     </row>
     <row r="348" spans="1:12">
       <c r="A348" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B348" t="s">
         <v>381</v>
@@ -18974,7 +18974,7 @@
         <v>1284</v>
       </c>
       <c r="I348" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="J348" t="s">
         <v>1770</v>
@@ -19023,7 +19023,7 @@
     </row>
     <row r="350" spans="1:12">
       <c r="A350" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B350" t="s">
         <v>383</v>
@@ -19058,7 +19058,7 @@
     </row>
     <row r="351" spans="1:12">
       <c r="A351" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B351" t="s">
         <v>384</v>
@@ -19093,7 +19093,7 @@
     </row>
     <row r="352" spans="1:12">
       <c r="A352" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B352" t="s">
         <v>385</v>
@@ -19114,7 +19114,7 @@
         <v>1284</v>
       </c>
       <c r="I352" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="J352" t="s">
         <v>1774</v>
@@ -19198,7 +19198,7 @@
     </row>
     <row r="355" spans="1:12">
       <c r="A355" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B355" t="s">
         <v>388</v>
@@ -19233,7 +19233,7 @@
     </row>
     <row r="356" spans="1:12">
       <c r="A356" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B356" t="s">
         <v>389</v>
@@ -19268,7 +19268,7 @@
     </row>
     <row r="357" spans="1:12">
       <c r="A357" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B357" t="s">
         <v>390</v>
@@ -19376,7 +19376,7 @@
     </row>
     <row r="360" spans="1:12">
       <c r="A360" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B360" t="s">
         <v>393</v>
@@ -19446,7 +19446,7 @@
     </row>
     <row r="362" spans="1:12">
       <c r="A362" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B362" t="s">
         <v>395</v>
@@ -19586,7 +19586,7 @@
     </row>
     <row r="366" spans="1:12">
       <c r="A366" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B366" t="s">
         <v>399</v>
@@ -19659,7 +19659,7 @@
     </row>
     <row r="368" spans="1:12">
       <c r="A368" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B368" t="s">
         <v>401</v>
@@ -19694,7 +19694,7 @@
     </row>
     <row r="369" spans="1:12">
       <c r="A369" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B369" t="s">
         <v>402</v>
@@ -19764,7 +19764,7 @@
     </row>
     <row r="371" spans="1:12">
       <c r="A371" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B371" t="s">
         <v>404</v>
@@ -19799,7 +19799,7 @@
     </row>
     <row r="372" spans="1:12">
       <c r="A372" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B372" t="s">
         <v>405</v>
@@ -19869,7 +19869,7 @@
     </row>
     <row r="374" spans="1:12">
       <c r="A374" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B374" t="s">
         <v>407</v>
@@ -19893,7 +19893,7 @@
         <v>1292</v>
       </c>
       <c r="I374" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="J374" t="s">
         <v>1796</v>
@@ -19977,7 +19977,7 @@
     </row>
     <row r="377" spans="1:12">
       <c r="A377" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B377" t="s">
         <v>410</v>
@@ -20012,7 +20012,7 @@
     </row>
     <row r="378" spans="1:12">
       <c r="A378" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B378" t="s">
         <v>411</v>
@@ -20047,7 +20047,7 @@
     </row>
     <row r="379" spans="1:12">
       <c r="A379" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B379" t="s">
         <v>412</v>
@@ -20327,7 +20327,7 @@
     </row>
     <row r="387" spans="1:12">
       <c r="A387" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B387" t="s">
         <v>420</v>
@@ -20467,7 +20467,7 @@
     </row>
     <row r="391" spans="1:12">
       <c r="A391" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="B391" t="s">
         <v>424</v>
@@ -20502,7 +20502,7 @@
     </row>
     <row r="392" spans="1:12">
       <c r="A392" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="B392" t="s">
         <v>425</v>
@@ -20537,7 +20537,7 @@
     </row>
     <row r="393" spans="1:12">
       <c r="A393" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="B393" t="s">
         <v>426</v>
@@ -20572,7 +20572,7 @@
     </row>
     <row r="394" spans="1:12">
       <c r="A394" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="B394" t="s">
         <v>427</v>
@@ -20607,7 +20607,7 @@
     </row>
     <row r="395" spans="1:12">
       <c r="A395" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="B395" t="s">
         <v>428</v>
@@ -20642,7 +20642,7 @@
     </row>
     <row r="396" spans="1:12">
       <c r="A396" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="B396" t="s">
         <v>429</v>
@@ -20677,7 +20677,7 @@
     </row>
     <row r="397" spans="1:12">
       <c r="A397" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="B397" t="s">
         <v>430</v>
@@ -20712,7 +20712,7 @@
     </row>
     <row r="398" spans="1:12">
       <c r="A398" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="B398" t="s">
         <v>431</v>
@@ -20747,7 +20747,7 @@
     </row>
     <row r="399" spans="1:12">
       <c r="A399" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="B399" t="s">
         <v>432</v>
@@ -20782,7 +20782,7 @@
     </row>
     <row r="400" spans="1:12">
       <c r="A400" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="B400" t="s">
         <v>433</v>
@@ -20817,7 +20817,7 @@
     </row>
     <row r="401" spans="1:12">
       <c r="A401" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="B401" t="s">
         <v>434</v>
@@ -20852,7 +20852,7 @@
     </row>
     <row r="402" spans="1:12">
       <c r="A402" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="B402" t="s">
         <v>435</v>
@@ -20887,7 +20887,7 @@
     </row>
     <row r="403" spans="1:12">
       <c r="A403" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="B403" t="s">
         <v>436</v>
@@ -20922,7 +20922,7 @@
     </row>
     <row r="404" spans="1:12">
       <c r="A404" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="B404" t="s">
         <v>437</v>
@@ -20957,7 +20957,7 @@
     </row>
     <row r="405" spans="1:12">
       <c r="A405" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="B405" t="s">
         <v>438</v>
@@ -20992,7 +20992,7 @@
     </row>
     <row r="406" spans="1:12">
       <c r="A406" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="B406" t="s">
         <v>439</v>
@@ -21027,7 +21027,7 @@
     </row>
     <row r="407" spans="1:12">
       <c r="A407" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="B407" t="s">
         <v>440</v>
@@ -21062,7 +21062,7 @@
     </row>
     <row r="408" spans="1:12">
       <c r="A408" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="B408" t="s">
         <v>441</v>
@@ -21097,7 +21097,7 @@
     </row>
     <row r="409" spans="1:12">
       <c r="A409" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="B409" t="s">
         <v>442</v>
@@ -21132,7 +21132,7 @@
     </row>
     <row r="410" spans="1:12">
       <c r="A410" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B410" t="s">
         <v>443</v>
@@ -21167,7 +21167,7 @@
     </row>
     <row r="411" spans="1:12">
       <c r="A411" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B411" t="s">
         <v>444</v>
@@ -21202,7 +21202,7 @@
     </row>
     <row r="412" spans="1:12">
       <c r="A412" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B412" t="s">
         <v>444</v>
@@ -21272,7 +21272,7 @@
     </row>
     <row r="414" spans="1:12">
       <c r="A414" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B414" t="s">
         <v>446</v>
@@ -21380,7 +21380,7 @@
     </row>
     <row r="417" spans="1:12">
       <c r="A417" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B417" t="s">
         <v>449</v>
@@ -21415,7 +21415,7 @@
     </row>
     <row r="418" spans="1:12">
       <c r="A418" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B418" t="s">
         <v>450</v>
@@ -21488,7 +21488,7 @@
     </row>
     <row r="420" spans="1:12">
       <c r="A420" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B420" t="s">
         <v>452</v>
@@ -21523,7 +21523,7 @@
     </row>
     <row r="421" spans="1:12">
       <c r="A421" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B421" t="s">
         <v>453</v>
@@ -21701,7 +21701,7 @@
     </row>
     <row r="426" spans="1:12">
       <c r="A426" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B426" t="s">
         <v>458</v>
@@ -21806,7 +21806,7 @@
     </row>
     <row r="429" spans="1:12">
       <c r="A429" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B429" t="s">
         <v>461</v>
@@ -21981,7 +21981,7 @@
     </row>
     <row r="434" spans="1:12">
       <c r="A434" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B434" t="s">
         <v>466</v>
@@ -22016,7 +22016,7 @@
     </row>
     <row r="435" spans="1:12">
       <c r="A435" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B435" t="s">
         <v>467</v>
@@ -22051,7 +22051,7 @@
     </row>
     <row r="436" spans="1:12">
       <c r="A436" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B436" t="s">
         <v>468</v>
@@ -22121,7 +22121,7 @@
     </row>
     <row r="438" spans="1:12">
       <c r="A438" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B438" t="s">
         <v>470</v>
@@ -22159,7 +22159,7 @@
     </row>
     <row r="439" spans="1:12">
       <c r="A439" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B439" t="s">
         <v>470</v>
@@ -22197,7 +22197,7 @@
     </row>
     <row r="440" spans="1:12">
       <c r="A440" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="B440" t="s">
         <v>471</v>
@@ -22267,7 +22267,7 @@
     </row>
     <row r="442" spans="1:12">
       <c r="A442" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B442" t="s">
         <v>473</v>
@@ -22302,7 +22302,7 @@
     </row>
     <row r="443" spans="1:12">
       <c r="A443" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B443" t="s">
         <v>474</v>
@@ -22372,7 +22372,7 @@
     </row>
     <row r="445" spans="1:12">
       <c r="A445" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B445" t="s">
         <v>476</v>
@@ -22407,7 +22407,7 @@
     </row>
     <row r="446" spans="1:12">
       <c r="A446" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B446" t="s">
         <v>477</v>
@@ -22480,7 +22480,7 @@
     </row>
     <row r="448" spans="1:12">
       <c r="A448" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B448" t="s">
         <v>479</v>
@@ -22588,7 +22588,7 @@
     </row>
     <row r="451" spans="1:12">
       <c r="A451" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B451" t="s">
         <v>482</v>
@@ -22623,7 +22623,7 @@
     </row>
     <row r="452" spans="1:12">
       <c r="A452" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B452" t="s">
         <v>483</v>
@@ -22658,7 +22658,7 @@
     </row>
     <row r="453" spans="1:12">
       <c r="A453" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B453" t="s">
         <v>484</v>
@@ -22766,7 +22766,7 @@
     </row>
     <row r="456" spans="1:12">
       <c r="A456" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B456" t="s">
         <v>487</v>
@@ -22801,7 +22801,7 @@
     </row>
     <row r="457" spans="1:12">
       <c r="A457" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B457" t="s">
         <v>488</v>
@@ -22906,7 +22906,7 @@
     </row>
     <row r="460" spans="1:12">
       <c r="A460" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B460" t="s">
         <v>491</v>
@@ -23122,7 +23122,7 @@
     </row>
     <row r="466" spans="1:12">
       <c r="A466" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B466" t="s">
         <v>497</v>
@@ -23297,7 +23297,7 @@
     </row>
     <row r="471" spans="1:12">
       <c r="A471" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B471" t="s">
         <v>502</v>
@@ -23461,7 +23461,7 @@
         <v>1284</v>
       </c>
       <c r="I475" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="J475" t="s">
         <v>1895</v>
@@ -23475,7 +23475,7 @@
     </row>
     <row r="476" spans="1:12">
       <c r="A476" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B476" t="s">
         <v>507</v>
@@ -23513,7 +23513,7 @@
     </row>
     <row r="477" spans="1:12">
       <c r="A477" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B477" t="s">
         <v>508</v>
@@ -23817,7 +23817,7 @@
         <v>1284</v>
       </c>
       <c r="I485" t="s">
-        <v>1363</v>
+        <v>1319</v>
       </c>
       <c r="J485" t="s">
         <v>1904</v>
@@ -23831,7 +23831,7 @@
     </row>
     <row r="486" spans="1:12">
       <c r="A486" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="B486" t="s">
         <v>517</v>
@@ -23866,7 +23866,7 @@
     </row>
     <row r="487" spans="1:12">
       <c r="A487" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="B487" t="s">
         <v>518</v>
@@ -24144,7 +24144,7 @@
         <v>1301</v>
       </c>
       <c r="I494" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="J494" t="s">
         <v>1913</v>
@@ -24158,7 +24158,7 @@
     </row>
     <row r="495" spans="1:12">
       <c r="A495" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="B495" t="s">
         <v>526</v>
@@ -24193,7 +24193,7 @@
     </row>
     <row r="496" spans="1:12">
       <c r="A496" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B496" t="s">
         <v>527</v>
@@ -24269,7 +24269,7 @@
     </row>
     <row r="498" spans="1:12">
       <c r="A498" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B498" t="s">
         <v>529</v>
@@ -24293,7 +24293,7 @@
         <v>1304</v>
       </c>
       <c r="I498" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="J498" t="s">
         <v>1917</v>
@@ -24307,7 +24307,7 @@
     </row>
     <row r="499" spans="1:12">
       <c r="A499" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="B499" t="s">
         <v>530</v>
@@ -24377,7 +24377,7 @@
     </row>
     <row r="501" spans="1:12">
       <c r="A501" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="B501" t="s">
         <v>532</v>
@@ -24415,7 +24415,7 @@
     </row>
     <row r="502" spans="1:12">
       <c r="A502" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B502" t="s">
         <v>533</v>
@@ -24453,7 +24453,7 @@
     </row>
     <row r="503" spans="1:12">
       <c r="A503" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="B503" t="s">
         <v>534</v>
@@ -24526,7 +24526,7 @@
     </row>
     <row r="505" spans="1:12">
       <c r="A505" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="B505" t="s">
         <v>536</v>
@@ -24561,7 +24561,7 @@
     </row>
     <row r="506" spans="1:12">
       <c r="A506" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="B506" t="s">
         <v>537</v>
@@ -24704,7 +24704,7 @@
     </row>
     <row r="510" spans="1:12">
       <c r="A510" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="B510" t="s">
         <v>541</v>
@@ -24739,7 +24739,7 @@
     </row>
     <row r="511" spans="1:12">
       <c r="A511" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="B511" t="s">
         <v>542</v>
@@ -24809,7 +24809,7 @@
     </row>
     <row r="513" spans="1:12">
       <c r="A513" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B513" t="s">
         <v>544</v>
@@ -24844,7 +24844,7 @@
     </row>
     <row r="514" spans="1:12">
       <c r="A514" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="B514" t="s">
         <v>545</v>
@@ -24879,7 +24879,7 @@
     </row>
     <row r="515" spans="1:12">
       <c r="A515" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="B515" t="s">
         <v>546</v>
@@ -24917,7 +24917,7 @@
     </row>
     <row r="516" spans="1:12">
       <c r="A516" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="B516" t="s">
         <v>547</v>
@@ -24952,7 +24952,7 @@
     </row>
     <row r="517" spans="1:12">
       <c r="A517" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="B517" t="s">
         <v>548</v>
@@ -25060,7 +25060,7 @@
     </row>
     <row r="520" spans="1:12">
       <c r="A520" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="B520" t="s">
         <v>551</v>
@@ -25095,7 +25095,7 @@
     </row>
     <row r="521" spans="1:12">
       <c r="A521" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="B521" t="s">
         <v>552</v>
@@ -25127,7 +25127,7 @@
     </row>
     <row r="522" spans="1:12">
       <c r="A522" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="B522" t="s">
         <v>553</v>

--- a/BacklogGATEAutoCompleto.xlsx
+++ b/BacklogGATEAutoCompleto.xlsx
@@ -6834,7 +6834,7 @@
         <v>1073</v>
       </c>
       <c r="E2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="F2" t="s">
         <v>1279</v>
@@ -6869,7 +6869,7 @@
         <v>1074</v>
       </c>
       <c r="E3">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="F3" t="s">
         <v>1279</v>
@@ -6904,7 +6904,7 @@
         <v>1075</v>
       </c>
       <c r="E4">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="F4" t="s">
         <v>1279</v>
@@ -6939,7 +6939,7 @@
         <v>1076</v>
       </c>
       <c r="E5">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="F5" t="s">
         <v>1279</v>
@@ -6974,7 +6974,7 @@
         <v>1077</v>
       </c>
       <c r="E6">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="F6" t="s">
         <v>1279</v>
@@ -7009,7 +7009,7 @@
         <v>1078</v>
       </c>
       <c r="E7">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="F7" t="s">
         <v>1279</v>
@@ -7044,7 +7044,7 @@
         <v>1079</v>
       </c>
       <c r="E8">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="F8" t="s">
         <v>1279</v>
@@ -7079,7 +7079,7 @@
         <v>1080</v>
       </c>
       <c r="E9">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="F9" t="s">
         <v>1279</v>
@@ -7114,7 +7114,7 @@
         <v>1081</v>
       </c>
       <c r="E10">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="F10" t="s">
         <v>1279</v>
@@ -7149,7 +7149,7 @@
         <v>1081</v>
       </c>
       <c r="E11">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="F11" t="s">
         <v>1279</v>
@@ -7184,7 +7184,7 @@
         <v>1082</v>
       </c>
       <c r="E12">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="F12" t="s">
         <v>1279</v>
@@ -7219,7 +7219,7 @@
         <v>1083</v>
       </c>
       <c r="E13">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="F13" t="s">
         <v>1279</v>
@@ -7254,7 +7254,7 @@
         <v>1084</v>
       </c>
       <c r="E14">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F14" t="s">
         <v>1279</v>
@@ -7289,7 +7289,7 @@
         <v>1084</v>
       </c>
       <c r="E15">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F15" t="s">
         <v>1279</v>
@@ -7324,7 +7324,7 @@
         <v>1085</v>
       </c>
       <c r="E16">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F16" t="s">
         <v>1279</v>
@@ -7359,7 +7359,7 @@
         <v>1085</v>
       </c>
       <c r="E17">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F17" t="s">
         <v>1279</v>
@@ -7394,7 +7394,7 @@
         <v>1086</v>
       </c>
       <c r="E18">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="F18" t="s">
         <v>1279</v>
@@ -7429,7 +7429,7 @@
         <v>1087</v>
       </c>
       <c r="E19">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="F19" t="s">
         <v>1279</v>
@@ -7464,7 +7464,7 @@
         <v>1088</v>
       </c>
       <c r="E20">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="F20" t="s">
         <v>1279</v>
@@ -7499,7 +7499,7 @@
         <v>1089</v>
       </c>
       <c r="E21">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="F21" t="s">
         <v>1279</v>
@@ -7534,7 +7534,7 @@
         <v>1090</v>
       </c>
       <c r="E22">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F22" t="s">
         <v>1279</v>
@@ -7572,7 +7572,7 @@
         <v>1091</v>
       </c>
       <c r="E23">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="F23" t="s">
         <v>1279</v>
@@ -7607,7 +7607,7 @@
         <v>1092</v>
       </c>
       <c r="E24">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F24" t="s">
         <v>1279</v>
@@ -7642,7 +7642,7 @@
         <v>1093</v>
       </c>
       <c r="E25">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F25" t="s">
         <v>1279</v>
@@ -7677,7 +7677,7 @@
         <v>1094</v>
       </c>
       <c r="E26">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F26" t="s">
         <v>1279</v>
@@ -7712,7 +7712,7 @@
         <v>1095</v>
       </c>
       <c r="E27">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F27" t="s">
         <v>1279</v>
@@ -7747,7 +7747,7 @@
         <v>1096</v>
       </c>
       <c r="E28">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F28" t="s">
         <v>1279</v>
@@ -7782,7 +7782,7 @@
         <v>1097</v>
       </c>
       <c r="E29">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F29" t="s">
         <v>1279</v>
@@ -7817,7 +7817,7 @@
         <v>1098</v>
       </c>
       <c r="E30">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F30" t="s">
         <v>1279</v>
@@ -7852,7 +7852,7 @@
         <v>1099</v>
       </c>
       <c r="E31">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F31" t="s">
         <v>1279</v>
@@ -7887,7 +7887,7 @@
         <v>1100</v>
       </c>
       <c r="E32">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F32" t="s">
         <v>1279</v>
@@ -7922,7 +7922,7 @@
         <v>1101</v>
       </c>
       <c r="E33">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F33" t="s">
         <v>1279</v>
@@ -7957,7 +7957,7 @@
         <v>1102</v>
       </c>
       <c r="E34">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F34" t="s">
         <v>1279</v>
@@ -7992,7 +7992,7 @@
         <v>1103</v>
       </c>
       <c r="E35">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F35" t="s">
         <v>1279</v>
@@ -8027,7 +8027,7 @@
         <v>1104</v>
       </c>
       <c r="E36">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F36" t="s">
         <v>1279</v>
@@ -8062,7 +8062,7 @@
         <v>1104</v>
       </c>
       <c r="E37">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F37" t="s">
         <v>1279</v>
@@ -8097,7 +8097,7 @@
         <v>1105</v>
       </c>
       <c r="E38">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F38" t="s">
         <v>1279</v>
@@ -8132,7 +8132,7 @@
         <v>1106</v>
       </c>
       <c r="E39">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F39" t="s">
         <v>1279</v>
@@ -8167,7 +8167,7 @@
         <v>1107</v>
       </c>
       <c r="E40">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F40" t="s">
         <v>1279</v>
@@ -8202,7 +8202,7 @@
         <v>1107</v>
       </c>
       <c r="E41">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F41" t="s">
         <v>1279</v>
@@ -8237,7 +8237,7 @@
         <v>1108</v>
       </c>
       <c r="E42">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F42" t="s">
         <v>1279</v>
@@ -8272,7 +8272,7 @@
         <v>1108</v>
       </c>
       <c r="E43">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F43" t="s">
         <v>1279</v>
@@ -8307,7 +8307,7 @@
         <v>1109</v>
       </c>
       <c r="E44">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F44" t="s">
         <v>1279</v>
@@ -8342,7 +8342,7 @@
         <v>1110</v>
       </c>
       <c r="E45">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F45" t="s">
         <v>1279</v>
@@ -8377,7 +8377,7 @@
         <v>1111</v>
       </c>
       <c r="E46">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F46" t="s">
         <v>1279</v>
@@ -8412,7 +8412,7 @@
         <v>1112</v>
       </c>
       <c r="E47">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F47" t="s">
         <v>1279</v>
@@ -8447,7 +8447,7 @@
         <v>1112</v>
       </c>
       <c r="E48">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F48" t="s">
         <v>1279</v>
@@ -8482,7 +8482,7 @@
         <v>1113</v>
       </c>
       <c r="E49">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F49" t="s">
         <v>1279</v>
@@ -8517,7 +8517,7 @@
         <v>1114</v>
       </c>
       <c r="E50">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F50" t="s">
         <v>1279</v>
@@ -8552,7 +8552,7 @@
         <v>1115</v>
       </c>
       <c r="E51">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F51" t="s">
         <v>1279</v>
@@ -8587,7 +8587,7 @@
         <v>1116</v>
       </c>
       <c r="E52">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F52" t="s">
         <v>1279</v>
@@ -8622,7 +8622,7 @@
         <v>1117</v>
       </c>
       <c r="E53">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F53" t="s">
         <v>1279</v>
@@ -8657,7 +8657,7 @@
         <v>1118</v>
       </c>
       <c r="E54">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F54" t="s">
         <v>1279</v>
@@ -8692,7 +8692,7 @@
         <v>1119</v>
       </c>
       <c r="E55">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F55" t="s">
         <v>1279</v>
@@ -8727,7 +8727,7 @@
         <v>1119</v>
       </c>
       <c r="E56">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F56" t="s">
         <v>1279</v>
@@ -8762,7 +8762,7 @@
         <v>1119</v>
       </c>
       <c r="E57">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F57" t="s">
         <v>1279</v>
@@ -8797,7 +8797,7 @@
         <v>1120</v>
       </c>
       <c r="E58">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F58" t="s">
         <v>1279</v>
@@ -8832,7 +8832,7 @@
         <v>1121</v>
       </c>
       <c r="E59">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F59" t="s">
         <v>1279</v>
@@ -8867,7 +8867,7 @@
         <v>1122</v>
       </c>
       <c r="E60">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F60" t="s">
         <v>1279</v>
@@ -8902,7 +8902,7 @@
         <v>1122</v>
       </c>
       <c r="E61">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F61" t="s">
         <v>1279</v>
@@ -8937,7 +8937,7 @@
         <v>1123</v>
       </c>
       <c r="E62">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F62" t="s">
         <v>1279</v>
@@ -8972,7 +8972,7 @@
         <v>1124</v>
       </c>
       <c r="E63">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F63" t="s">
         <v>1279</v>
@@ -9007,7 +9007,7 @@
         <v>1124</v>
       </c>
       <c r="E64">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F64" t="s">
         <v>1279</v>
@@ -9042,7 +9042,7 @@
         <v>1124</v>
       </c>
       <c r="E65">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F65" t="s">
         <v>1279</v>
@@ -9077,7 +9077,7 @@
         <v>1125</v>
       </c>
       <c r="E66">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F66" t="s">
         <v>1279</v>
@@ -9112,7 +9112,7 @@
         <v>1126</v>
       </c>
       <c r="E67">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F67" t="s">
         <v>1279</v>
@@ -9147,7 +9147,7 @@
         <v>1126</v>
       </c>
       <c r="E68">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F68" t="s">
         <v>1279</v>
@@ -9182,7 +9182,7 @@
         <v>1126</v>
       </c>
       <c r="E69">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F69" t="s">
         <v>1280</v>
@@ -9217,7 +9217,7 @@
         <v>1126</v>
       </c>
       <c r="E70">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F70" t="s">
         <v>1279</v>
@@ -9252,7 +9252,7 @@
         <v>1127</v>
       </c>
       <c r="E71">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F71" t="s">
         <v>1279</v>
@@ -9287,7 +9287,7 @@
         <v>1128</v>
       </c>
       <c r="E72">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F72" t="s">
         <v>1279</v>
@@ -9322,7 +9322,7 @@
         <v>1128</v>
       </c>
       <c r="E73">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F73" t="s">
         <v>1279</v>
@@ -9357,7 +9357,7 @@
         <v>1129</v>
       </c>
       <c r="E74">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F74" t="s">
         <v>1279</v>
@@ -9392,7 +9392,7 @@
         <v>1130</v>
       </c>
       <c r="E75">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F75" t="s">
         <v>1279</v>
@@ -9427,7 +9427,7 @@
         <v>1131</v>
       </c>
       <c r="E76">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F76" t="s">
         <v>1279</v>
@@ -9462,7 +9462,7 @@
         <v>1132</v>
       </c>
       <c r="E77">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F77" t="s">
         <v>1279</v>
@@ -9497,7 +9497,7 @@
         <v>1132</v>
       </c>
       <c r="E78">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F78" t="s">
         <v>1279</v>
@@ -9532,7 +9532,7 @@
         <v>1132</v>
       </c>
       <c r="E79">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F79" t="s">
         <v>1279</v>
@@ -9567,7 +9567,7 @@
         <v>1132</v>
       </c>
       <c r="E80">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F80" t="s">
         <v>1279</v>
@@ -9602,7 +9602,7 @@
         <v>1132</v>
       </c>
       <c r="E81">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F81" t="s">
         <v>1279</v>
@@ -9637,7 +9637,7 @@
         <v>1132</v>
       </c>
       <c r="E82">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F82" t="s">
         <v>1279</v>
@@ -9672,7 +9672,7 @@
         <v>1133</v>
       </c>
       <c r="E83">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F83" t="s">
         <v>1279</v>
@@ -9707,7 +9707,7 @@
         <v>1134</v>
       </c>
       <c r="E84">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F84" t="s">
         <v>1279</v>
@@ -9742,7 +9742,7 @@
         <v>1135</v>
       </c>
       <c r="E85">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F85" t="s">
         <v>1279</v>
@@ -9777,7 +9777,7 @@
         <v>1135</v>
       </c>
       <c r="E86">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F86" t="s">
         <v>1279</v>
@@ -9812,7 +9812,7 @@
         <v>1136</v>
       </c>
       <c r="E87">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F87" t="s">
         <v>1281</v>
@@ -9847,7 +9847,7 @@
         <v>1137</v>
       </c>
       <c r="E88">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F88" t="s">
         <v>1279</v>
@@ -9882,7 +9882,7 @@
         <v>1138</v>
       </c>
       <c r="E89">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F89" t="s">
         <v>1279</v>
@@ -9917,7 +9917,7 @@
         <v>1138</v>
       </c>
       <c r="E90">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F90" t="s">
         <v>1279</v>
@@ -9952,7 +9952,7 @@
         <v>1139</v>
       </c>
       <c r="E91">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F91" t="s">
         <v>1279</v>
@@ -9987,7 +9987,7 @@
         <v>1140</v>
       </c>
       <c r="E92">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F92" t="s">
         <v>1279</v>
@@ -10022,7 +10022,7 @@
         <v>1141</v>
       </c>
       <c r="E93">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F93" t="s">
         <v>1279</v>
@@ -10057,7 +10057,7 @@
         <v>1142</v>
       </c>
       <c r="E94">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F94" t="s">
         <v>1279</v>
@@ -10092,7 +10092,7 @@
         <v>1143</v>
       </c>
       <c r="E95">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F95" t="s">
         <v>1279</v>
@@ -10127,7 +10127,7 @@
         <v>1143</v>
       </c>
       <c r="E96">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F96" t="s">
         <v>1279</v>
@@ -10162,7 +10162,7 @@
         <v>1144</v>
       </c>
       <c r="E97">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F97" t="s">
         <v>1279</v>
@@ -10197,7 +10197,7 @@
         <v>1144</v>
       </c>
       <c r="E98">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F98" t="s">
         <v>1279</v>
@@ -10232,7 +10232,7 @@
         <v>1144</v>
       </c>
       <c r="E99">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F99" t="s">
         <v>1279</v>
@@ -10267,7 +10267,7 @@
         <v>1145</v>
       </c>
       <c r="E100">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F100" t="s">
         <v>1279</v>
@@ -10302,7 +10302,7 @@
         <v>1145</v>
       </c>
       <c r="E101">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F101" t="s">
         <v>1279</v>
@@ -10337,7 +10337,7 @@
         <v>1146</v>
       </c>
       <c r="E102">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F102" t="s">
         <v>1279</v>
@@ -10372,7 +10372,7 @@
         <v>1147</v>
       </c>
       <c r="E103">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F103" t="s">
         <v>1279</v>
@@ -10407,7 +10407,7 @@
         <v>1148</v>
       </c>
       <c r="E104">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F104" t="s">
         <v>1279</v>
@@ -10442,7 +10442,7 @@
         <v>1148</v>
       </c>
       <c r="E105">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F105" t="s">
         <v>1279</v>
@@ -10477,7 +10477,7 @@
         <v>1149</v>
       </c>
       <c r="E106">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F106" t="s">
         <v>1279</v>
@@ -10512,7 +10512,7 @@
         <v>1149</v>
       </c>
       <c r="E107">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F107" t="s">
         <v>1279</v>
@@ -10547,7 +10547,7 @@
         <v>1150</v>
       </c>
       <c r="E108">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F108" t="s">
         <v>1279</v>
@@ -10582,7 +10582,7 @@
         <v>1151</v>
       </c>
       <c r="E109">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F109" t="s">
         <v>1279</v>
@@ -10617,7 +10617,7 @@
         <v>1151</v>
       </c>
       <c r="E110">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F110" t="s">
         <v>1279</v>
@@ -10652,7 +10652,7 @@
         <v>1152</v>
       </c>
       <c r="E111">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F111" t="s">
         <v>1279</v>
@@ -10687,7 +10687,7 @@
         <v>1153</v>
       </c>
       <c r="E112">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F112" t="s">
         <v>1279</v>
@@ -10722,7 +10722,7 @@
         <v>1153</v>
       </c>
       <c r="E113">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F113" t="s">
         <v>1279</v>
@@ -10757,7 +10757,7 @@
         <v>1154</v>
       </c>
       <c r="E114">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F114" t="s">
         <v>1279</v>
@@ -10792,7 +10792,7 @@
         <v>1155</v>
       </c>
       <c r="E115">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F115" t="s">
         <v>1279</v>
@@ -10830,7 +10830,7 @@
         <v>1155</v>
       </c>
       <c r="E116">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F116" t="s">
         <v>1279</v>
@@ -10865,7 +10865,7 @@
         <v>1155</v>
       </c>
       <c r="E117">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F117" t="s">
         <v>1279</v>
@@ -10900,7 +10900,7 @@
         <v>1155</v>
       </c>
       <c r="E118">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F118" t="s">
         <v>1279</v>
@@ -10935,7 +10935,7 @@
         <v>1156</v>
       </c>
       <c r="E119">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F119" t="s">
         <v>1280</v>
@@ -10970,7 +10970,7 @@
         <v>1157</v>
       </c>
       <c r="E120">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F120" t="s">
         <v>1279</v>
@@ -11005,7 +11005,7 @@
         <v>1157</v>
       </c>
       <c r="E121">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F121" t="s">
         <v>1279</v>
@@ -11040,7 +11040,7 @@
         <v>1157</v>
       </c>
       <c r="E122">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F122" t="s">
         <v>1279</v>
@@ -11075,7 +11075,7 @@
         <v>1157</v>
       </c>
       <c r="E123">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F123" t="s">
         <v>1279</v>
@@ -11110,7 +11110,7 @@
         <v>1158</v>
       </c>
       <c r="E124">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F124" t="s">
         <v>1279</v>
@@ -11145,7 +11145,7 @@
         <v>1158</v>
       </c>
       <c r="E125">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F125" t="s">
         <v>1279</v>
@@ -11180,7 +11180,7 @@
         <v>1158</v>
       </c>
       <c r="E126">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F126" t="s">
         <v>1279</v>
@@ -11215,7 +11215,7 @@
         <v>1158</v>
       </c>
       <c r="E127">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F127" t="s">
         <v>1279</v>
@@ -11250,7 +11250,7 @@
         <v>1158</v>
       </c>
       <c r="E128">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F128" t="s">
         <v>1279</v>
@@ -11285,7 +11285,7 @@
         <v>1158</v>
       </c>
       <c r="E129">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F129" t="s">
         <v>1279</v>
@@ -11320,7 +11320,7 @@
         <v>1158</v>
       </c>
       <c r="E130">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F130" t="s">
         <v>1279</v>
@@ -11355,7 +11355,7 @@
         <v>1159</v>
       </c>
       <c r="E131">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F131" t="s">
         <v>1279</v>
@@ -11390,7 +11390,7 @@
         <v>1159</v>
       </c>
       <c r="E132">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F132" t="s">
         <v>1279</v>
@@ -11425,7 +11425,7 @@
         <v>1160</v>
       </c>
       <c r="E133">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F133" t="s">
         <v>1279</v>
@@ -11460,7 +11460,7 @@
         <v>1161</v>
       </c>
       <c r="E134">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F134" t="s">
         <v>1279</v>
@@ -11495,7 +11495,7 @@
         <v>1161</v>
       </c>
       <c r="E135">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F135" t="s">
         <v>1279</v>
@@ -11530,7 +11530,7 @@
         <v>1161</v>
       </c>
       <c r="E136">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F136" t="s">
         <v>1279</v>
@@ -11565,7 +11565,7 @@
         <v>1162</v>
       </c>
       <c r="E137">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F137" t="s">
         <v>1279</v>
@@ -11600,7 +11600,7 @@
         <v>1162</v>
       </c>
       <c r="E138">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F138" t="s">
         <v>1279</v>
@@ -11635,7 +11635,7 @@
         <v>1162</v>
       </c>
       <c r="E139">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F139" t="s">
         <v>1279</v>
@@ -11670,7 +11670,7 @@
         <v>1162</v>
       </c>
       <c r="E140">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F140" t="s">
         <v>1279</v>
@@ -11705,7 +11705,7 @@
         <v>1162</v>
       </c>
       <c r="E141">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F141" t="s">
         <v>1279</v>
@@ -11740,7 +11740,7 @@
         <v>1162</v>
       </c>
       <c r="E142">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F142" t="s">
         <v>1279</v>
@@ -11775,7 +11775,7 @@
         <v>1162</v>
       </c>
       <c r="E143">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F143" t="s">
         <v>1279</v>
@@ -11810,7 +11810,7 @@
         <v>1162</v>
       </c>
       <c r="E144">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F144" t="s">
         <v>1279</v>
@@ -11845,7 +11845,7 @@
         <v>1162</v>
       </c>
       <c r="E145">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F145" t="s">
         <v>1279</v>
@@ -11880,7 +11880,7 @@
         <v>1163</v>
       </c>
       <c r="E146">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F146" t="s">
         <v>1279</v>
@@ -11915,7 +11915,7 @@
         <v>1163</v>
       </c>
       <c r="E147">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F147" t="s">
         <v>1279</v>
@@ -11950,7 +11950,7 @@
         <v>1163</v>
       </c>
       <c r="E148">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F148" t="s">
         <v>1279</v>
@@ -11985,7 +11985,7 @@
         <v>1164</v>
       </c>
       <c r="E149">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F149" t="s">
         <v>1279</v>
@@ -12020,7 +12020,7 @@
         <v>1164</v>
       </c>
       <c r="E150">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F150" t="s">
         <v>1280</v>
@@ -12055,7 +12055,7 @@
         <v>1164</v>
       </c>
       <c r="E151">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F151" t="s">
         <v>1279</v>
@@ -12090,7 +12090,7 @@
         <v>1165</v>
       </c>
       <c r="E152">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F152" t="s">
         <v>1279</v>
@@ -12125,7 +12125,7 @@
         <v>1165</v>
       </c>
       <c r="E153">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F153" t="s">
         <v>1279</v>
@@ -12160,7 +12160,7 @@
         <v>1166</v>
       </c>
       <c r="E154">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F154" t="s">
         <v>1279</v>
@@ -12195,7 +12195,7 @@
         <v>1166</v>
       </c>
       <c r="E155">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F155" t="s">
         <v>1279</v>
@@ -12230,7 +12230,7 @@
         <v>1167</v>
       </c>
       <c r="E156">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F156" t="s">
         <v>1279</v>
@@ -12265,7 +12265,7 @@
         <v>1167</v>
       </c>
       <c r="E157">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F157" t="s">
         <v>1279</v>
@@ -12300,7 +12300,7 @@
         <v>1168</v>
       </c>
       <c r="E158">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F158" t="s">
         <v>1279</v>
@@ -12335,7 +12335,7 @@
         <v>1168</v>
       </c>
       <c r="E159">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F159" t="s">
         <v>1279</v>
@@ -12370,7 +12370,7 @@
         <v>1168</v>
       </c>
       <c r="E160">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F160" t="s">
         <v>1279</v>
@@ -12405,7 +12405,7 @@
         <v>1169</v>
       </c>
       <c r="E161">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F161" t="s">
         <v>1279</v>
@@ -12440,7 +12440,7 @@
         <v>1169</v>
       </c>
       <c r="E162">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F162" t="s">
         <v>1279</v>
@@ -12475,7 +12475,7 @@
         <v>1170</v>
       </c>
       <c r="E163">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F163" t="s">
         <v>1279</v>
@@ -12510,7 +12510,7 @@
         <v>1171</v>
       </c>
       <c r="E164">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F164" t="s">
         <v>1279</v>
@@ -12545,7 +12545,7 @@
         <v>1171</v>
       </c>
       <c r="E165">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F165" t="s">
         <v>1279</v>
@@ -12580,7 +12580,7 @@
         <v>1171</v>
       </c>
       <c r="E166">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F166" t="s">
         <v>1279</v>
@@ -12615,7 +12615,7 @@
         <v>1171</v>
       </c>
       <c r="E167">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F167" t="s">
         <v>1279</v>
@@ -12650,7 +12650,7 @@
         <v>1172</v>
       </c>
       <c r="E168">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F168" t="s">
         <v>1279</v>
@@ -12685,7 +12685,7 @@
         <v>1173</v>
       </c>
       <c r="E169">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F169" t="s">
         <v>1279</v>
@@ -12720,7 +12720,7 @@
         <v>1173</v>
       </c>
       <c r="E170">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F170" t="s">
         <v>1279</v>
@@ -12755,7 +12755,7 @@
         <v>1173</v>
       </c>
       <c r="E171">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F171" t="s">
         <v>1279</v>
@@ -12790,7 +12790,7 @@
         <v>1173</v>
       </c>
       <c r="E172">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F172" t="s">
         <v>1279</v>
@@ -12825,7 +12825,7 @@
         <v>1173</v>
       </c>
       <c r="E173">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F173" t="s">
         <v>1279</v>
@@ -12860,7 +12860,7 @@
         <v>1174</v>
       </c>
       <c r="E174">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F174" t="s">
         <v>1279</v>
@@ -12895,7 +12895,7 @@
         <v>1174</v>
       </c>
       <c r="E175">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F175" t="s">
         <v>1279</v>
@@ -12930,7 +12930,7 @@
         <v>1174</v>
       </c>
       <c r="E176">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F176" t="s">
         <v>1279</v>
@@ -12965,7 +12965,7 @@
         <v>1174</v>
       </c>
       <c r="E177">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F177" t="s">
         <v>1279</v>
@@ -13000,7 +13000,7 @@
         <v>1174</v>
       </c>
       <c r="E178">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F178" t="s">
         <v>1279</v>
@@ -13035,7 +13035,7 @@
         <v>1174</v>
       </c>
       <c r="E179">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F179" t="s">
         <v>1279</v>
@@ -13070,7 +13070,7 @@
         <v>1175</v>
       </c>
       <c r="E180">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F180" t="s">
         <v>1279</v>
@@ -13105,7 +13105,7 @@
         <v>1175</v>
       </c>
       <c r="E181">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F181" t="s">
         <v>1279</v>
@@ -13140,7 +13140,7 @@
         <v>1175</v>
       </c>
       <c r="E182">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F182" t="s">
         <v>1279</v>
@@ -13175,7 +13175,7 @@
         <v>1175</v>
       </c>
       <c r="E183">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F183" t="s">
         <v>1279</v>
@@ -13210,7 +13210,7 @@
         <v>1176</v>
       </c>
       <c r="E184">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F184" t="s">
         <v>1279</v>
@@ -13245,7 +13245,7 @@
         <v>1176</v>
       </c>
       <c r="E185">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F185" t="s">
         <v>1279</v>
@@ -13280,7 +13280,7 @@
         <v>1177</v>
       </c>
       <c r="E186">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F186" t="s">
         <v>1279</v>
@@ -13315,7 +13315,7 @@
         <v>1178</v>
       </c>
       <c r="E187">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F187" t="s">
         <v>1279</v>
@@ -13350,7 +13350,7 @@
         <v>1178</v>
       </c>
       <c r="E188">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F188" t="s">
         <v>1279</v>
@@ -13385,7 +13385,7 @@
         <v>1179</v>
       </c>
       <c r="E189">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F189" t="s">
         <v>1279</v>
@@ -13420,7 +13420,7 @@
         <v>1180</v>
       </c>
       <c r="E190">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F190" t="s">
         <v>1279</v>
@@ -13455,7 +13455,7 @@
         <v>1180</v>
       </c>
       <c r="E191">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F191" t="s">
         <v>1279</v>
@@ -13490,7 +13490,7 @@
         <v>1181</v>
       </c>
       <c r="E192">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F192" t="s">
         <v>1279</v>
@@ -13525,7 +13525,7 @@
         <v>1181</v>
       </c>
       <c r="E193">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F193" t="s">
         <v>1279</v>
@@ -13560,7 +13560,7 @@
         <v>1182</v>
       </c>
       <c r="E194">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F194" t="s">
         <v>1279</v>
@@ -13595,7 +13595,7 @@
         <v>1183</v>
       </c>
       <c r="E195">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F195" t="s">
         <v>1279</v>
@@ -13630,7 +13630,7 @@
         <v>1183</v>
       </c>
       <c r="E196">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F196" t="s">
         <v>1279</v>
@@ -13665,7 +13665,7 @@
         <v>1183</v>
       </c>
       <c r="E197">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F197" t="s">
         <v>1279</v>
@@ -13700,7 +13700,7 @@
         <v>1184</v>
       </c>
       <c r="E198">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F198" t="s">
         <v>1279</v>
@@ -13735,7 +13735,7 @@
         <v>1184</v>
       </c>
       <c r="E199">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F199" t="s">
         <v>1279</v>
@@ -13770,7 +13770,7 @@
         <v>1185</v>
       </c>
       <c r="E200">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F200" t="s">
         <v>1279</v>
@@ -13805,7 +13805,7 @@
         <v>1186</v>
       </c>
       <c r="E201">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F201" t="s">
         <v>1279</v>
@@ -13840,7 +13840,7 @@
         <v>1186</v>
       </c>
       <c r="E202">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F202" t="s">
         <v>1279</v>
@@ -13875,7 +13875,7 @@
         <v>1186</v>
       </c>
       <c r="E203">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F203" t="s">
         <v>1279</v>
@@ -13910,7 +13910,7 @@
         <v>1187</v>
       </c>
       <c r="E204">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F204" t="s">
         <v>1279</v>
@@ -13945,7 +13945,7 @@
         <v>1187</v>
       </c>
       <c r="E205">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F205" t="s">
         <v>1279</v>
@@ -13980,7 +13980,7 @@
         <v>1188</v>
       </c>
       <c r="E206">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F206" t="s">
         <v>1279</v>
@@ -14015,7 +14015,7 @@
         <v>1188</v>
       </c>
       <c r="E207">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F207" t="s">
         <v>1281</v>
@@ -14050,7 +14050,7 @@
         <v>1188</v>
       </c>
       <c r="E208">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F208" t="s">
         <v>1279</v>
@@ -14085,7 +14085,7 @@
         <v>1189</v>
       </c>
       <c r="E209">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F209" t="s">
         <v>1279</v>
@@ -14120,7 +14120,7 @@
         <v>1189</v>
       </c>
       <c r="E210">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F210" t="s">
         <v>1279</v>
@@ -14158,7 +14158,7 @@
         <v>1189</v>
       </c>
       <c r="E211">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F211" t="s">
         <v>1279</v>
@@ -14193,7 +14193,7 @@
         <v>1189</v>
       </c>
       <c r="E212">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F212" t="s">
         <v>1279</v>
@@ -14228,7 +14228,7 @@
         <v>1189</v>
       </c>
       <c r="E213">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F213" t="s">
         <v>1279</v>
@@ -14263,7 +14263,7 @@
         <v>1189</v>
       </c>
       <c r="E214">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F214" t="s">
         <v>1279</v>
@@ -14298,7 +14298,7 @@
         <v>1190</v>
       </c>
       <c r="E215">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F215" t="s">
         <v>1279</v>
@@ -14333,7 +14333,7 @@
         <v>1190</v>
       </c>
       <c r="E216">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F216" t="s">
         <v>1279</v>
@@ -14368,7 +14368,7 @@
         <v>1190</v>
       </c>
       <c r="E217">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F217" t="s">
         <v>1279</v>
@@ -14403,7 +14403,7 @@
         <v>1191</v>
       </c>
       <c r="E218">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F218" t="s">
         <v>1279</v>
@@ -14438,7 +14438,7 @@
         <v>1191</v>
       </c>
       <c r="E219">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F219" t="s">
         <v>1279</v>
@@ -14473,7 +14473,7 @@
         <v>1191</v>
       </c>
       <c r="E220">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F220" t="s">
         <v>1279</v>
@@ -14508,7 +14508,7 @@
         <v>1192</v>
       </c>
       <c r="E221">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F221" t="s">
         <v>1279</v>
@@ -14543,7 +14543,7 @@
         <v>1192</v>
       </c>
       <c r="E222">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F222" t="s">
         <v>1279</v>
@@ -14578,7 +14578,7 @@
         <v>1192</v>
       </c>
       <c r="E223">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F223" t="s">
         <v>1279</v>
@@ -14613,7 +14613,7 @@
         <v>1193</v>
       </c>
       <c r="E224">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F224" t="s">
         <v>1279</v>
@@ -14648,7 +14648,7 @@
         <v>1193</v>
       </c>
       <c r="E225">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F225" t="s">
         <v>1279</v>
@@ -14683,7 +14683,7 @@
         <v>1193</v>
       </c>
       <c r="E226">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F226" t="s">
         <v>1279</v>
@@ -14718,7 +14718,7 @@
         <v>1193</v>
       </c>
       <c r="E227">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F227" t="s">
         <v>1279</v>
@@ -14753,7 +14753,7 @@
         <v>1193</v>
       </c>
       <c r="E228">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F228" t="s">
         <v>1279</v>
@@ -14788,7 +14788,7 @@
         <v>1193</v>
       </c>
       <c r="E229">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F229" t="s">
         <v>1279</v>
@@ -14823,7 +14823,7 @@
         <v>1194</v>
       </c>
       <c r="E230">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F230" t="s">
         <v>1279</v>
@@ -14858,7 +14858,7 @@
         <v>1195</v>
       </c>
       <c r="E231">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F231" t="s">
         <v>1279</v>
@@ -14893,7 +14893,7 @@
         <v>1195</v>
       </c>
       <c r="E232">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F232" t="s">
         <v>1282</v>
@@ -14928,7 +14928,7 @@
         <v>1195</v>
       </c>
       <c r="E233">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F233" t="s">
         <v>1279</v>
@@ -14963,7 +14963,7 @@
         <v>1195</v>
       </c>
       <c r="E234">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F234" t="s">
         <v>1279</v>
@@ -14998,7 +14998,7 @@
         <v>1196</v>
       </c>
       <c r="E235">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F235" t="s">
         <v>1279</v>
@@ -15033,7 +15033,7 @@
         <v>1196</v>
       </c>
       <c r="E236">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F236" t="s">
         <v>1279</v>
@@ -15068,7 +15068,7 @@
         <v>1196</v>
       </c>
       <c r="E237">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F237" t="s">
         <v>1279</v>
@@ -15103,7 +15103,7 @@
         <v>1196</v>
       </c>
       <c r="E238">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F238" t="s">
         <v>1279</v>
@@ -15138,7 +15138,7 @@
         <v>1197</v>
       </c>
       <c r="E239">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F239" t="s">
         <v>1279</v>
@@ -15176,7 +15176,7 @@
         <v>1198</v>
       </c>
       <c r="E240">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F240" t="s">
         <v>1279</v>
@@ -15211,7 +15211,7 @@
         <v>1198</v>
       </c>
       <c r="E241">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F241" t="s">
         <v>1279</v>
@@ -15246,7 +15246,7 @@
         <v>1198</v>
       </c>
       <c r="E242">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F242" t="s">
         <v>1279</v>
@@ -15281,7 +15281,7 @@
         <v>1198</v>
       </c>
       <c r="E243">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F243" t="s">
         <v>1279</v>
@@ -15319,7 +15319,7 @@
         <v>1198</v>
       </c>
       <c r="E244">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F244" t="s">
         <v>1279</v>
@@ -15354,7 +15354,7 @@
         <v>1199</v>
       </c>
       <c r="E245">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F245" t="s">
         <v>1279</v>
@@ -15389,7 +15389,7 @@
         <v>1199</v>
       </c>
       <c r="E246">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F246" t="s">
         <v>1279</v>
@@ -15424,7 +15424,7 @@
         <v>1200</v>
       </c>
       <c r="E247">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F247" t="s">
         <v>1279</v>
@@ -15459,7 +15459,7 @@
         <v>1200</v>
       </c>
       <c r="E248">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F248" t="s">
         <v>1279</v>
@@ -15494,7 +15494,7 @@
         <v>1200</v>
       </c>
       <c r="E249">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F249" t="s">
         <v>1279</v>
@@ -15529,7 +15529,7 @@
         <v>1201</v>
       </c>
       <c r="E250">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F250" t="s">
         <v>1279</v>
@@ -15564,7 +15564,7 @@
         <v>1201</v>
       </c>
       <c r="E251">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F251" t="s">
         <v>1279</v>
@@ -15599,7 +15599,7 @@
         <v>1202</v>
       </c>
       <c r="E252">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F252" t="s">
         <v>1279</v>
@@ -15634,7 +15634,7 @@
         <v>1203</v>
       </c>
       <c r="E253">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F253" t="s">
         <v>1279</v>
@@ -15669,7 +15669,7 @@
         <v>1203</v>
       </c>
       <c r="E254">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F254" t="s">
         <v>1279</v>
@@ -15704,7 +15704,7 @@
         <v>1203</v>
       </c>
       <c r="E255">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F255" t="s">
         <v>1279</v>
@@ -15739,7 +15739,7 @@
         <v>1203</v>
       </c>
       <c r="E256">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F256" t="s">
         <v>1279</v>
@@ -15774,7 +15774,7 @@
         <v>1204</v>
       </c>
       <c r="E257">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F257" t="s">
         <v>1279</v>
@@ -15809,7 +15809,7 @@
         <v>1204</v>
       </c>
       <c r="E258">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F258" t="s">
         <v>1279</v>
@@ -15844,7 +15844,7 @@
         <v>1204</v>
       </c>
       <c r="E259">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F259" t="s">
         <v>1279</v>
@@ -15879,7 +15879,7 @@
         <v>1205</v>
       </c>
       <c r="E260">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F260" t="s">
         <v>1279</v>
@@ -15914,7 +15914,7 @@
         <v>1206</v>
       </c>
       <c r="E261">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F261" t="s">
         <v>1279</v>
@@ -15949,7 +15949,7 @@
         <v>1206</v>
       </c>
       <c r="E262">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F262" t="s">
         <v>1279</v>
@@ -15984,7 +15984,7 @@
         <v>1206</v>
       </c>
       <c r="E263">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F263" t="s">
         <v>1279</v>
@@ -16019,7 +16019,7 @@
         <v>1207</v>
       </c>
       <c r="E264">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F264" t="s">
         <v>1279</v>
@@ -16054,7 +16054,7 @@
         <v>1207</v>
       </c>
       <c r="E265">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F265" t="s">
         <v>1279</v>
@@ -16089,7 +16089,7 @@
         <v>1207</v>
       </c>
       <c r="E266">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F266" t="s">
         <v>1279</v>
@@ -16124,7 +16124,7 @@
         <v>1208</v>
       </c>
       <c r="E267">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F267" t="s">
         <v>1279</v>
@@ -16159,7 +16159,7 @@
         <v>1209</v>
       </c>
       <c r="E268">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F268" t="s">
         <v>1279</v>
@@ -16194,7 +16194,7 @@
         <v>1210</v>
       </c>
       <c r="E269">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F269" t="s">
         <v>1279</v>
@@ -16229,7 +16229,7 @@
         <v>1210</v>
       </c>
       <c r="E270">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F270" t="s">
         <v>1279</v>
@@ -16264,7 +16264,7 @@
         <v>1210</v>
       </c>
       <c r="E271">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F271" t="s">
         <v>1279</v>
@@ -16299,7 +16299,7 @@
         <v>1210</v>
       </c>
       <c r="E272">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F272" t="s">
         <v>1279</v>
@@ -16334,7 +16334,7 @@
         <v>1211</v>
       </c>
       <c r="E273">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F273" t="s">
         <v>1279</v>
@@ -16369,7 +16369,7 @@
         <v>1212</v>
       </c>
       <c r="E274">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F274" t="s">
         <v>1279</v>
@@ -16404,7 +16404,7 @@
         <v>1212</v>
       </c>
       <c r="E275">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F275" t="s">
         <v>1279</v>
@@ -16439,7 +16439,7 @@
         <v>1213</v>
       </c>
       <c r="E276">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F276" t="s">
         <v>1279</v>
@@ -16474,7 +16474,7 @@
         <v>1214</v>
       </c>
       <c r="E277">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F277" t="s">
         <v>1279</v>
@@ -16509,7 +16509,7 @@
         <v>1215</v>
       </c>
       <c r="E278">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F278" t="s">
         <v>1279</v>
@@ -16544,7 +16544,7 @@
         <v>1215</v>
       </c>
       <c r="E279">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F279" t="s">
         <v>1279</v>
@@ -16579,7 +16579,7 @@
         <v>1216</v>
       </c>
       <c r="E280">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F280" t="s">
         <v>1279</v>
@@ -16614,7 +16614,7 @@
         <v>1216</v>
       </c>
       <c r="E281">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F281" t="s">
         <v>1279</v>
@@ -16649,7 +16649,7 @@
         <v>1216</v>
       </c>
       <c r="E282">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F282" t="s">
         <v>1279</v>
@@ -16684,7 +16684,7 @@
         <v>1217</v>
       </c>
       <c r="E283">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F283" t="s">
         <v>1279</v>
@@ -16719,7 +16719,7 @@
         <v>1217</v>
       </c>
       <c r="E284">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F284" t="s">
         <v>1279</v>
@@ -16754,7 +16754,7 @@
         <v>1217</v>
       </c>
       <c r="E285">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F285" t="s">
         <v>1279</v>
@@ -16789,7 +16789,7 @@
         <v>1217</v>
       </c>
       <c r="E286">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F286" t="s">
         <v>1279</v>
@@ -16824,7 +16824,7 @@
         <v>1217</v>
       </c>
       <c r="E287">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F287" t="s">
         <v>1279</v>
@@ -16859,7 +16859,7 @@
         <v>1217</v>
       </c>
       <c r="E288">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F288" t="s">
         <v>1279</v>
@@ -16894,7 +16894,7 @@
         <v>1217</v>
       </c>
       <c r="E289">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F289" t="s">
         <v>1279</v>
@@ -16929,7 +16929,7 @@
         <v>1217</v>
       </c>
       <c r="E290">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F290" t="s">
         <v>1279</v>
@@ -16964,7 +16964,7 @@
         <v>1218</v>
       </c>
       <c r="E291">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F291" t="s">
         <v>1279</v>
@@ -16999,7 +16999,7 @@
         <v>1218</v>
       </c>
       <c r="E292">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F292" t="s">
         <v>1279</v>
@@ -17034,7 +17034,7 @@
         <v>1218</v>
       </c>
       <c r="E293">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F293" t="s">
         <v>1279</v>
@@ -17069,7 +17069,7 @@
         <v>1219</v>
       </c>
       <c r="E294">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F294" t="s">
         <v>1279</v>
@@ -17104,7 +17104,7 @@
         <v>1220</v>
       </c>
       <c r="E295">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F295" t="s">
         <v>1279</v>
@@ -17139,7 +17139,7 @@
         <v>1220</v>
       </c>
       <c r="E296">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F296" t="s">
         <v>1279</v>
@@ -17174,7 +17174,7 @@
         <v>1220</v>
       </c>
       <c r="E297">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F297" t="s">
         <v>1279</v>
@@ -17209,7 +17209,7 @@
         <v>1220</v>
       </c>
       <c r="E298">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F298" t="s">
         <v>1283</v>
@@ -17247,7 +17247,7 @@
         <v>1220</v>
       </c>
       <c r="E299">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F299" t="s">
         <v>1279</v>
@@ -17282,7 +17282,7 @@
         <v>1220</v>
       </c>
       <c r="E300">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F300" t="s">
         <v>1279</v>
@@ -17317,7 +17317,7 @@
         <v>1221</v>
       </c>
       <c r="E301">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F301" t="s">
         <v>1279</v>
@@ -17352,7 +17352,7 @@
         <v>1221</v>
       </c>
       <c r="E302">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F302" t="s">
         <v>1279</v>
@@ -17387,7 +17387,7 @@
         <v>1221</v>
       </c>
       <c r="E303">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F303" t="s">
         <v>1279</v>
@@ -17425,7 +17425,7 @@
         <v>1221</v>
       </c>
       <c r="E304">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F304" t="s">
         <v>1279</v>
@@ -17460,7 +17460,7 @@
         <v>1221</v>
       </c>
       <c r="E305">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F305" t="s">
         <v>1279</v>
@@ -17495,7 +17495,7 @@
         <v>1221</v>
       </c>
       <c r="E306">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F306" t="s">
         <v>1279</v>
@@ -17530,7 +17530,7 @@
         <v>1221</v>
       </c>
       <c r="E307">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F307" t="s">
         <v>1279</v>
@@ -17565,7 +17565,7 @@
         <v>1221</v>
       </c>
       <c r="E308">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F308" t="s">
         <v>1279</v>
@@ -17600,7 +17600,7 @@
         <v>1222</v>
       </c>
       <c r="E309">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F309" t="s">
         <v>1280</v>
@@ -17635,7 +17635,7 @@
         <v>1223</v>
       </c>
       <c r="E310">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F310" t="s">
         <v>1283</v>
@@ -17670,7 +17670,7 @@
         <v>1224</v>
       </c>
       <c r="E311">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F311" t="s">
         <v>1279</v>
@@ -17705,7 +17705,7 @@
         <v>1224</v>
       </c>
       <c r="E312">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F312" t="s">
         <v>1279</v>
@@ -17740,7 +17740,7 @@
         <v>1225</v>
       </c>
       <c r="E313">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F313" t="s">
         <v>1279</v>
@@ -17775,7 +17775,7 @@
         <v>1226</v>
       </c>
       <c r="E314">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F314" t="s">
         <v>1282</v>
@@ -17810,7 +17810,7 @@
         <v>1226</v>
       </c>
       <c r="E315">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F315" t="s">
         <v>1279</v>
@@ -17845,7 +17845,7 @@
         <v>1226</v>
       </c>
       <c r="E316">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F316" t="s">
         <v>1279</v>
@@ -17880,7 +17880,7 @@
         <v>1226</v>
       </c>
       <c r="E317">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F317" t="s">
         <v>1279</v>
@@ -17915,7 +17915,7 @@
         <v>1227</v>
       </c>
       <c r="E318">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F318" t="s">
         <v>1279</v>
@@ -17950,7 +17950,7 @@
         <v>1228</v>
       </c>
       <c r="E319">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F319" t="s">
         <v>1279</v>
@@ -17985,7 +17985,7 @@
         <v>1228</v>
       </c>
       <c r="E320">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F320" t="s">
         <v>1279</v>
@@ -18020,7 +18020,7 @@
         <v>1229</v>
       </c>
       <c r="E321">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F321" t="s">
         <v>1279</v>
@@ -18055,7 +18055,7 @@
         <v>1230</v>
       </c>
       <c r="E322">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F322" t="s">
         <v>1279</v>
@@ -18090,7 +18090,7 @@
         <v>1230</v>
       </c>
       <c r="E323">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F323" t="s">
         <v>1279</v>
@@ -18125,7 +18125,7 @@
         <v>1230</v>
       </c>
       <c r="E324">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F324" t="s">
         <v>1279</v>
@@ -18160,7 +18160,7 @@
         <v>1230</v>
       </c>
       <c r="E325">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F325" t="s">
         <v>1279</v>
@@ -18195,7 +18195,7 @@
         <v>1230</v>
       </c>
       <c r="E326">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F326" t="s">
         <v>1279</v>
@@ -18230,7 +18230,7 @@
         <v>1230</v>
       </c>
       <c r="E327">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F327" t="s">
         <v>1279</v>
@@ -18265,7 +18265,7 @@
         <v>1230</v>
       </c>
       <c r="E328">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F328" t="s">
         <v>1279</v>
@@ -18300,7 +18300,7 @@
         <v>1231</v>
       </c>
       <c r="E329">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F329" t="s">
         <v>1279</v>
@@ -18335,7 +18335,7 @@
         <v>1231</v>
       </c>
       <c r="E330">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F330" t="s">
         <v>1279</v>
@@ -18370,7 +18370,7 @@
         <v>1231</v>
       </c>
       <c r="E331">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F331" t="s">
         <v>1280</v>
@@ -18405,7 +18405,7 @@
         <v>1232</v>
       </c>
       <c r="E332">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F332" t="s">
         <v>1279</v>
@@ -18440,7 +18440,7 @@
         <v>1232</v>
       </c>
       <c r="E333">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F333" t="s">
         <v>1279</v>
@@ -18475,7 +18475,7 @@
         <v>1232</v>
       </c>
       <c r="E334">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F334" t="s">
         <v>1279</v>
@@ -18510,7 +18510,7 @@
         <v>1232</v>
       </c>
       <c r="E335">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F335" t="s">
         <v>1279</v>
@@ -18545,7 +18545,7 @@
         <v>1232</v>
       </c>
       <c r="E336">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F336" t="s">
         <v>1279</v>
@@ -18580,7 +18580,7 @@
         <v>1232</v>
       </c>
       <c r="E337">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F337" t="s">
         <v>1282</v>
@@ -18615,7 +18615,7 @@
         <v>1233</v>
       </c>
       <c r="E338">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F338" t="s">
         <v>1279</v>
@@ -18650,7 +18650,7 @@
         <v>1233</v>
       </c>
       <c r="E339">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F339" t="s">
         <v>1279</v>
@@ -18685,7 +18685,7 @@
         <v>1233</v>
       </c>
       <c r="E340">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F340" t="s">
         <v>1279</v>
@@ -18720,7 +18720,7 @@
         <v>1234</v>
       </c>
       <c r="E341">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F341" t="s">
         <v>1282</v>
@@ -18755,7 +18755,7 @@
         <v>1234</v>
       </c>
       <c r="E342">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F342" t="s">
         <v>1279</v>
@@ -18790,7 +18790,7 @@
         <v>1234</v>
       </c>
       <c r="E343">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F343" t="s">
         <v>1279</v>
@@ -18825,7 +18825,7 @@
         <v>1235</v>
       </c>
       <c r="E344">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F344" t="s">
         <v>1279</v>
@@ -18860,7 +18860,7 @@
         <v>1235</v>
       </c>
       <c r="E345">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F345" t="s">
         <v>1279</v>
@@ -18895,7 +18895,7 @@
         <v>1235</v>
       </c>
       <c r="E346">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F346" t="s">
         <v>1279</v>
@@ -18930,7 +18930,7 @@
         <v>1235</v>
       </c>
       <c r="E347">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F347" t="s">
         <v>1279</v>
@@ -18965,7 +18965,7 @@
         <v>1235</v>
       </c>
       <c r="E348">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F348" t="s">
         <v>1281</v>
@@ -19000,7 +19000,7 @@
         <v>1235</v>
       </c>
       <c r="E349">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F349" t="s">
         <v>1279</v>
@@ -19035,7 +19035,7 @@
         <v>1236</v>
       </c>
       <c r="E350">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F350" t="s">
         <v>1279</v>
@@ -19070,7 +19070,7 @@
         <v>1236</v>
       </c>
       <c r="E351">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F351" t="s">
         <v>1279</v>
@@ -19105,7 +19105,7 @@
         <v>1236</v>
       </c>
       <c r="E352">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F352" t="s">
         <v>1279</v>
@@ -19140,7 +19140,7 @@
         <v>1236</v>
       </c>
       <c r="E353">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F353" t="s">
         <v>1279</v>
@@ -19175,7 +19175,7 @@
         <v>1237</v>
       </c>
       <c r="E354">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F354" t="s">
         <v>1279</v>
@@ -19210,7 +19210,7 @@
         <v>1237</v>
       </c>
       <c r="E355">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F355" t="s">
         <v>1279</v>
@@ -19245,7 +19245,7 @@
         <v>1237</v>
       </c>
       <c r="E356">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F356" t="s">
         <v>1279</v>
@@ -19280,7 +19280,7 @@
         <v>1237</v>
       </c>
       <c r="E357">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F357" t="s">
         <v>1279</v>
@@ -19315,7 +19315,7 @@
         <v>1237</v>
       </c>
       <c r="E358">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F358" t="s">
         <v>1279</v>
@@ -19353,7 +19353,7 @@
         <v>1238</v>
       </c>
       <c r="E359">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F359" t="s">
         <v>1279</v>
@@ -19388,7 +19388,7 @@
         <v>1238</v>
       </c>
       <c r="E360">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F360" t="s">
         <v>1279</v>
@@ -19423,7 +19423,7 @@
         <v>1238</v>
       </c>
       <c r="E361">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F361" t="s">
         <v>1279</v>
@@ -19458,7 +19458,7 @@
         <v>1238</v>
       </c>
       <c r="E362">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F362" t="s">
         <v>1279</v>
@@ -19493,7 +19493,7 @@
         <v>1238</v>
       </c>
       <c r="E363">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F363" t="s">
         <v>1279</v>
@@ -19528,7 +19528,7 @@
         <v>1238</v>
       </c>
       <c r="E364">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F364" t="s">
         <v>1279</v>
@@ -19563,7 +19563,7 @@
         <v>1239</v>
       </c>
       <c r="E365">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F365" t="s">
         <v>1280</v>
@@ -19598,7 +19598,7 @@
         <v>1240</v>
       </c>
       <c r="E366">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F366" t="s">
         <v>1279</v>
@@ -19633,7 +19633,7 @@
         <v>1241</v>
       </c>
       <c r="E367">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F367" t="s">
         <v>1281</v>
@@ -19671,7 +19671,7 @@
         <v>1242</v>
       </c>
       <c r="E368">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F368" t="s">
         <v>1279</v>
@@ -19706,7 +19706,7 @@
         <v>1242</v>
       </c>
       <c r="E369">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F369" t="s">
         <v>1279</v>
@@ -19741,7 +19741,7 @@
         <v>1242</v>
       </c>
       <c r="E370">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F370" t="s">
         <v>1279</v>
@@ -19776,7 +19776,7 @@
         <v>1243</v>
       </c>
       <c r="E371">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F371" t="s">
         <v>1279</v>
@@ -19811,7 +19811,7 @@
         <v>1243</v>
       </c>
       <c r="E372">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F372" t="s">
         <v>1279</v>
@@ -19846,7 +19846,7 @@
         <v>1244</v>
       </c>
       <c r="E373">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F373" t="s">
         <v>1279</v>
@@ -19881,7 +19881,7 @@
         <v>1244</v>
       </c>
       <c r="E374">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F374" t="s">
         <v>1283</v>
@@ -19919,7 +19919,7 @@
         <v>1244</v>
       </c>
       <c r="E375">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F375" t="s">
         <v>1279</v>
@@ -19954,7 +19954,7 @@
         <v>1244</v>
       </c>
       <c r="E376">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F376" t="s">
         <v>1283</v>
@@ -19989,7 +19989,7 @@
         <v>1245</v>
       </c>
       <c r="E377">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F377" t="s">
         <v>1279</v>
@@ -20024,7 +20024,7 @@
         <v>1246</v>
       </c>
       <c r="E378">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F378" t="s">
         <v>1279</v>
@@ -20059,7 +20059,7 @@
         <v>1246</v>
       </c>
       <c r="E379">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F379" t="s">
         <v>1279</v>
@@ -20094,7 +20094,7 @@
         <v>1246</v>
       </c>
       <c r="E380">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F380" t="s">
         <v>1279</v>
@@ -20129,7 +20129,7 @@
         <v>1246</v>
       </c>
       <c r="E381">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F381" t="s">
         <v>1279</v>
@@ -20164,7 +20164,7 @@
         <v>1247</v>
       </c>
       <c r="E382">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F382" t="s">
         <v>1283</v>
@@ -20199,7 +20199,7 @@
         <v>1247</v>
       </c>
       <c r="E383">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F383" t="s">
         <v>1279</v>
@@ -20234,7 +20234,7 @@
         <v>1247</v>
       </c>
       <c r="E384">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F384" t="s">
         <v>1279</v>
@@ -20269,7 +20269,7 @@
         <v>1248</v>
       </c>
       <c r="E385">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F385" t="s">
         <v>1279</v>
@@ -20304,7 +20304,7 @@
         <v>1249</v>
       </c>
       <c r="E386">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F386" t="s">
         <v>1279</v>
@@ -20339,7 +20339,7 @@
         <v>1249</v>
       </c>
       <c r="E387">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F387" t="s">
         <v>1279</v>
@@ -20374,7 +20374,7 @@
         <v>1250</v>
       </c>
       <c r="E388">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F388" t="s">
         <v>1279</v>
@@ -20409,7 +20409,7 @@
         <v>1250</v>
       </c>
       <c r="E389">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F389" t="s">
         <v>1279</v>
@@ -20444,7 +20444,7 @@
         <v>1250</v>
       </c>
       <c r="E390">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F390" t="s">
         <v>1279</v>
@@ -20479,7 +20479,7 @@
         <v>1250</v>
       </c>
       <c r="E391">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F391" t="s">
         <v>1279</v>
@@ -20514,7 +20514,7 @@
         <v>1250</v>
       </c>
       <c r="E392">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F392" t="s">
         <v>1279</v>
@@ -20549,7 +20549,7 @@
         <v>1250</v>
       </c>
       <c r="E393">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F393" t="s">
         <v>1279</v>
@@ -20584,7 +20584,7 @@
         <v>1250</v>
       </c>
       <c r="E394">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F394" t="s">
         <v>1279</v>
@@ -20619,7 +20619,7 @@
         <v>1250</v>
       </c>
       <c r="E395">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F395" t="s">
         <v>1279</v>
@@ -20654,7 +20654,7 @@
         <v>1250</v>
       </c>
       <c r="E396">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F396" t="s">
         <v>1279</v>
@@ -20689,7 +20689,7 @@
         <v>1250</v>
       </c>
       <c r="E397">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F397" t="s">
         <v>1279</v>
@@ -20724,7 +20724,7 @@
         <v>1250</v>
       </c>
       <c r="E398">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F398" t="s">
         <v>1279</v>
@@ -20759,7 +20759,7 @@
         <v>1250</v>
       </c>
       <c r="E399">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F399" t="s">
         <v>1279</v>
@@ -20794,7 +20794,7 @@
         <v>1250</v>
       </c>
       <c r="E400">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F400" t="s">
         <v>1279</v>
@@ -20829,7 +20829,7 @@
         <v>1250</v>
       </c>
       <c r="E401">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F401" t="s">
         <v>1279</v>
@@ -20864,7 +20864,7 @@
         <v>1250</v>
       </c>
       <c r="E402">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F402" t="s">
         <v>1279</v>
@@ -20899,7 +20899,7 @@
         <v>1250</v>
       </c>
       <c r="E403">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F403" t="s">
         <v>1279</v>
@@ -20934,7 +20934,7 @@
         <v>1250</v>
       </c>
       <c r="E404">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F404" t="s">
         <v>1279</v>
@@ -20969,7 +20969,7 @@
         <v>1250</v>
       </c>
       <c r="E405">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F405" t="s">
         <v>1279</v>
@@ -21004,7 +21004,7 @@
         <v>1250</v>
       </c>
       <c r="E406">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F406" t="s">
         <v>1279</v>
@@ -21039,7 +21039,7 @@
         <v>1250</v>
       </c>
       <c r="E407">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F407" t="s">
         <v>1279</v>
@@ -21074,7 +21074,7 @@
         <v>1250</v>
       </c>
       <c r="E408">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F408" t="s">
         <v>1279</v>
@@ -21109,7 +21109,7 @@
         <v>1250</v>
       </c>
       <c r="E409">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F409" t="s">
         <v>1279</v>
@@ -21144,7 +21144,7 @@
         <v>1251</v>
       </c>
       <c r="E410">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F410" t="s">
         <v>1279</v>
@@ -21179,7 +21179,7 @@
         <v>1251</v>
       </c>
       <c r="E411">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F411" t="s">
         <v>1279</v>
@@ -21214,7 +21214,7 @@
         <v>1251</v>
       </c>
       <c r="E412">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F412" t="s">
         <v>1283</v>
@@ -21249,7 +21249,7 @@
         <v>1252</v>
       </c>
       <c r="E413">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F413" t="s">
         <v>1279</v>
@@ -21284,7 +21284,7 @@
         <v>1253</v>
       </c>
       <c r="E414">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F414" t="s">
         <v>1281</v>
@@ -21322,7 +21322,7 @@
         <v>1253</v>
       </c>
       <c r="E415">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F415" t="s">
         <v>1279</v>
@@ -21357,7 +21357,7 @@
         <v>1253</v>
       </c>
       <c r="E416">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F416" t="s">
         <v>1279</v>
@@ -21392,7 +21392,7 @@
         <v>1253</v>
       </c>
       <c r="E417">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F417" t="s">
         <v>1279</v>
@@ -21427,7 +21427,7 @@
         <v>1254</v>
       </c>
       <c r="E418">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F418" t="s">
         <v>1279</v>
@@ -21465,7 +21465,7 @@
         <v>1254</v>
       </c>
       <c r="E419">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F419" t="s">
         <v>1283</v>
@@ -21500,7 +21500,7 @@
         <v>1254</v>
       </c>
       <c r="E420">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F420" t="s">
         <v>1281</v>
@@ -21535,7 +21535,7 @@
         <v>1254</v>
       </c>
       <c r="E421">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F421" t="s">
         <v>1279</v>
@@ -21570,7 +21570,7 @@
         <v>1254</v>
       </c>
       <c r="E422">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F422" t="s">
         <v>1279</v>
@@ -21605,7 +21605,7 @@
         <v>1254</v>
       </c>
       <c r="E423">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F423" t="s">
         <v>1279</v>
@@ -21640,7 +21640,7 @@
         <v>1254</v>
       </c>
       <c r="E424">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F424" t="s">
         <v>1279</v>
@@ -21675,7 +21675,7 @@
         <v>1255</v>
       </c>
       <c r="E425">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F425" t="s">
         <v>1283</v>
@@ -21713,7 +21713,7 @@
         <v>1256</v>
       </c>
       <c r="E426">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F426" t="s">
         <v>1279</v>
@@ -21748,7 +21748,7 @@
         <v>1256</v>
       </c>
       <c r="E427">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F427" t="s">
         <v>1279</v>
@@ -21783,7 +21783,7 @@
         <v>1256</v>
       </c>
       <c r="E428">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F428" t="s">
         <v>1279</v>
@@ -21818,7 +21818,7 @@
         <v>1257</v>
       </c>
       <c r="E429">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F429" t="s">
         <v>1279</v>
@@ -21853,7 +21853,7 @@
         <v>1257</v>
       </c>
       <c r="E430">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F430" t="s">
         <v>1279</v>
@@ -21888,7 +21888,7 @@
         <v>1257</v>
       </c>
       <c r="E431">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F431" t="s">
         <v>1279</v>
@@ -21923,7 +21923,7 @@
         <v>1257</v>
       </c>
       <c r="E432">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F432" t="s">
         <v>1281</v>
@@ -21958,7 +21958,7 @@
         <v>1257</v>
       </c>
       <c r="E433">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F433" t="s">
         <v>1279</v>
@@ -21993,7 +21993,7 @@
         <v>1258</v>
       </c>
       <c r="E434">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F434" t="s">
         <v>1279</v>
@@ -22028,7 +22028,7 @@
         <v>1258</v>
       </c>
       <c r="E435">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F435" t="s">
         <v>1279</v>
@@ -22063,7 +22063,7 @@
         <v>1258</v>
       </c>
       <c r="E436">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F436" t="s">
         <v>1279</v>
@@ -22098,7 +22098,7 @@
         <v>1258</v>
       </c>
       <c r="E437">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F437" t="s">
         <v>1279</v>
@@ -22133,7 +22133,7 @@
         <v>1258</v>
       </c>
       <c r="E438">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F438" t="s">
         <v>1279</v>
@@ -22171,7 +22171,7 @@
         <v>1258</v>
       </c>
       <c r="E439">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F439" t="s">
         <v>1281</v>
@@ -22209,7 +22209,7 @@
         <v>1258</v>
       </c>
       <c r="E440">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F440" t="s">
         <v>1281</v>
@@ -22244,7 +22244,7 @@
         <v>1259</v>
       </c>
       <c r="E441">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F441" t="s">
         <v>1279</v>
@@ -22279,7 +22279,7 @@
         <v>1259</v>
       </c>
       <c r="E442">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F442" t="s">
         <v>1279</v>
@@ -22314,7 +22314,7 @@
         <v>1259</v>
       </c>
       <c r="E443">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F443" t="s">
         <v>1279</v>
@@ -22349,7 +22349,7 @@
         <v>1260</v>
       </c>
       <c r="E444">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F444" t="s">
         <v>1279</v>
@@ -22384,7 +22384,7 @@
         <v>1260</v>
       </c>
       <c r="E445">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F445" t="s">
         <v>1279</v>
@@ -22419,7 +22419,7 @@
         <v>1260</v>
       </c>
       <c r="E446">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F446" t="s">
         <v>1281</v>
@@ -22457,7 +22457,7 @@
         <v>1260</v>
       </c>
       <c r="E447">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F447" t="s">
         <v>1279</v>
@@ -22492,7 +22492,7 @@
         <v>1261</v>
       </c>
       <c r="E448">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F448" t="s">
         <v>1279</v>
@@ -22527,7 +22527,7 @@
         <v>1261</v>
       </c>
       <c r="E449">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F449" t="s">
         <v>1279</v>
@@ -22562,7 +22562,7 @@
         <v>1262</v>
       </c>
       <c r="E450">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F450" t="s">
         <v>1281</v>
@@ -22600,7 +22600,7 @@
         <v>1262</v>
       </c>
       <c r="E451">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F451" t="s">
         <v>1279</v>
@@ -22635,7 +22635,7 @@
         <v>1262</v>
       </c>
       <c r="E452">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F452" t="s">
         <v>1279</v>
@@ -22670,7 +22670,7 @@
         <v>1263</v>
       </c>
       <c r="E453">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F453" t="s">
         <v>1281</v>
@@ -22705,7 +22705,7 @@
         <v>1263</v>
       </c>
       <c r="E454">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F454" t="s">
         <v>1279</v>
@@ -22740,7 +22740,7 @@
         <v>1263</v>
       </c>
       <c r="E455">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F455" t="s">
         <v>1281</v>
@@ -22778,7 +22778,7 @@
         <v>1263</v>
       </c>
       <c r="E456">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F456" t="s">
         <v>1279</v>
@@ -22813,7 +22813,7 @@
         <v>1263</v>
       </c>
       <c r="E457">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F457" t="s">
         <v>1279</v>
@@ -22848,7 +22848,7 @@
         <v>1264</v>
       </c>
       <c r="E458">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F458" t="s">
         <v>1279</v>
@@ -22883,7 +22883,7 @@
         <v>1264</v>
       </c>
       <c r="E459">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F459" t="s">
         <v>1279</v>
@@ -22918,7 +22918,7 @@
         <v>1265</v>
       </c>
       <c r="E460">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F460" t="s">
         <v>1279</v>
@@ -22953,7 +22953,7 @@
         <v>1265</v>
       </c>
       <c r="E461">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F461" t="s">
         <v>1279</v>
@@ -22988,7 +22988,7 @@
         <v>1265</v>
       </c>
       <c r="E462">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F462" t="s">
         <v>1279</v>
@@ -23023,7 +23023,7 @@
         <v>1265</v>
       </c>
       <c r="E463">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F463" t="s">
         <v>1281</v>
@@ -23061,7 +23061,7 @@
         <v>1266</v>
       </c>
       <c r="E464">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F464" t="s">
         <v>1279</v>
@@ -23096,7 +23096,7 @@
         <v>1266</v>
       </c>
       <c r="E465">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F465" t="s">
         <v>1283</v>
@@ -23134,7 +23134,7 @@
         <v>1266</v>
       </c>
       <c r="E466">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F466" t="s">
         <v>1279</v>
@@ -23169,7 +23169,7 @@
         <v>1266</v>
       </c>
       <c r="E467">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F467" t="s">
         <v>1279</v>
@@ -23204,7 +23204,7 @@
         <v>1267</v>
       </c>
       <c r="E468">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F468" t="s">
         <v>1279</v>
@@ -23239,7 +23239,7 @@
         <v>1267</v>
       </c>
       <c r="E469">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F469" t="s">
         <v>1279</v>
@@ -23274,7 +23274,7 @@
         <v>1267</v>
       </c>
       <c r="E470">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F470" t="s">
         <v>1279</v>
@@ -23309,7 +23309,7 @@
         <v>1267</v>
       </c>
       <c r="E471">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F471" t="s">
         <v>1279</v>
@@ -23344,7 +23344,7 @@
         <v>1267</v>
       </c>
       <c r="E472">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F472" t="s">
         <v>1279</v>
@@ -23379,7 +23379,7 @@
         <v>1267</v>
       </c>
       <c r="E473">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F473" t="s">
         <v>1281</v>
@@ -23417,7 +23417,7 @@
         <v>1268</v>
       </c>
       <c r="E474">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F474" t="s">
         <v>1279</v>
@@ -23452,7 +23452,7 @@
         <v>1268</v>
       </c>
       <c r="E475">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F475" t="s">
         <v>1281</v>
@@ -23487,7 +23487,7 @@
         <v>1269</v>
       </c>
       <c r="E476">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F476" t="s">
         <v>1281</v>
@@ -23525,7 +23525,7 @@
         <v>1269</v>
       </c>
       <c r="E477">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F477" t="s">
         <v>1281</v>
@@ -23563,7 +23563,7 @@
         <v>1269</v>
       </c>
       <c r="E478">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F478" t="s">
         <v>1279</v>
@@ -23598,7 +23598,7 @@
         <v>1269</v>
       </c>
       <c r="E479">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F479" t="s">
         <v>1279</v>
@@ -23633,7 +23633,7 @@
         <v>1270</v>
       </c>
       <c r="E480">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F480" t="s">
         <v>1279</v>
@@ -23668,7 +23668,7 @@
         <v>1271</v>
       </c>
       <c r="E481">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F481" t="s">
         <v>1279</v>
@@ -23703,7 +23703,7 @@
         <v>1271</v>
       </c>
       <c r="E482">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F482" t="s">
         <v>1279</v>
@@ -23738,7 +23738,7 @@
         <v>1271</v>
       </c>
       <c r="E483">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F483" t="s">
         <v>1279</v>
@@ -23773,7 +23773,7 @@
         <v>1271</v>
       </c>
       <c r="E484">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F484" t="s">
         <v>1279</v>
@@ -23808,7 +23808,7 @@
         <v>1271</v>
       </c>
       <c r="E485">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F485" t="s">
         <v>1279</v>
@@ -23843,7 +23843,7 @@
         <v>1271</v>
       </c>
       <c r="E486">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F486" t="s">
         <v>1279</v>
@@ -23878,7 +23878,7 @@
         <v>1271</v>
       </c>
       <c r="E487">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F487" t="s">
         <v>1279</v>
@@ -23913,7 +23913,7 @@
         <v>1271</v>
       </c>
       <c r="E488">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F488" t="s">
         <v>1281</v>
@@ -23951,7 +23951,7 @@
         <v>1272</v>
       </c>
       <c r="E489">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F489" t="s">
         <v>1279</v>
@@ -23986,7 +23986,7 @@
         <v>1272</v>
       </c>
       <c r="E490">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F490" t="s">
         <v>1279</v>
@@ -24021,7 +24021,7 @@
         <v>1272</v>
       </c>
       <c r="E491">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F491" t="s">
         <v>1279</v>
@@ -24056,7 +24056,7 @@
         <v>1272</v>
       </c>
       <c r="E492">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F492" t="s">
         <v>1281</v>
@@ -24094,7 +24094,7 @@
         <v>1272</v>
       </c>
       <c r="E493">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F493" t="s">
         <v>1281</v>
@@ -24132,7 +24132,7 @@
         <v>1272</v>
       </c>
       <c r="E494">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F494" t="s">
         <v>1281</v>
@@ -24170,7 +24170,7 @@
         <v>1272</v>
       </c>
       <c r="E495">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F495" t="s">
         <v>1279</v>
@@ -24205,7 +24205,7 @@
         <v>1273</v>
       </c>
       <c r="E496">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F496" t="s">
         <v>1281</v>
@@ -24243,7 +24243,7 @@
         <v>1273</v>
       </c>
       <c r="E497">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F497" t="s">
         <v>1281</v>
@@ -24281,7 +24281,7 @@
         <v>1274</v>
       </c>
       <c r="E498">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F498" t="s">
         <v>1281</v>
@@ -24319,7 +24319,7 @@
         <v>1274</v>
       </c>
       <c r="E499">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F499" t="s">
         <v>1279</v>
@@ -24354,7 +24354,7 @@
         <v>1275</v>
       </c>
       <c r="E500">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F500" t="s">
         <v>1279</v>
@@ -24389,7 +24389,7 @@
         <v>1275</v>
       </c>
       <c r="E501">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F501" t="s">
         <v>1279</v>
@@ -24427,7 +24427,7 @@
         <v>1275</v>
       </c>
       <c r="E502">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F502" t="s">
         <v>1281</v>
@@ -24465,7 +24465,7 @@
         <v>1276</v>
       </c>
       <c r="E503">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F503" t="s">
         <v>1279</v>
@@ -24503,7 +24503,7 @@
         <v>1276</v>
       </c>
       <c r="E504">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F504" t="s">
         <v>1279</v>
@@ -24538,7 +24538,7 @@
         <v>1276</v>
       </c>
       <c r="E505">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F505" t="s">
         <v>1279</v>
@@ -24573,7 +24573,7 @@
         <v>1276</v>
       </c>
       <c r="E506">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F506" t="s">
         <v>1279</v>
@@ -24608,7 +24608,7 @@
         <v>1276</v>
       </c>
       <c r="E507">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F507" t="s">
         <v>1279</v>
@@ -24643,7 +24643,7 @@
         <v>1276</v>
       </c>
       <c r="E508">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F508" t="s">
         <v>1281</v>
@@ -24681,7 +24681,7 @@
         <v>1277</v>
       </c>
       <c r="E509">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F509" t="s">
         <v>1279</v>
@@ -24716,7 +24716,7 @@
         <v>1277</v>
       </c>
       <c r="E510">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F510" t="s">
         <v>1279</v>
@@ -24751,7 +24751,7 @@
         <v>1277</v>
       </c>
       <c r="E511">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F511" t="s">
         <v>1279</v>
@@ -24786,7 +24786,7 @@
         <v>1277</v>
       </c>
       <c r="E512">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F512" t="s">
         <v>1279</v>
@@ -24821,7 +24821,7 @@
         <v>1277</v>
       </c>
       <c r="E513">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F513" t="s">
         <v>1279</v>
@@ -24856,7 +24856,7 @@
         <v>1277</v>
       </c>
       <c r="E514">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F514" t="s">
         <v>1279</v>
@@ -24891,7 +24891,7 @@
         <v>1278</v>
       </c>
       <c r="E515">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F515" t="s">
         <v>1279</v>
@@ -24929,7 +24929,7 @@
         <v>1278</v>
       </c>
       <c r="E516">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F516" t="s">
         <v>1279</v>
@@ -24964,7 +24964,7 @@
         <v>1278</v>
       </c>
       <c r="E517">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F517" t="s">
         <v>1279</v>
@@ -24999,7 +24999,7 @@
         <v>1278</v>
       </c>
       <c r="E518">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F518" t="s">
         <v>1279</v>
@@ -25037,7 +25037,7 @@
         <v>1278</v>
       </c>
       <c r="E519">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F519" t="s">
         <v>1279</v>
@@ -25072,7 +25072,7 @@
         <v>1278</v>
       </c>
       <c r="E520">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F520" t="s">
         <v>1281</v>

--- a/BacklogGATEAutoCompleto.xlsx
+++ b/BacklogGATEAutoCompleto.xlsx
@@ -6834,7 +6834,7 @@
         <v>1073</v>
       </c>
       <c r="E2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="F2" t="s">
         <v>1279</v>
@@ -6869,7 +6869,7 @@
         <v>1074</v>
       </c>
       <c r="E3">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="F3" t="s">
         <v>1279</v>
@@ -6904,7 +6904,7 @@
         <v>1075</v>
       </c>
       <c r="E4">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="F4" t="s">
         <v>1279</v>
@@ -6939,7 +6939,7 @@
         <v>1076</v>
       </c>
       <c r="E5">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="F5" t="s">
         <v>1279</v>
@@ -6974,7 +6974,7 @@
         <v>1077</v>
       </c>
       <c r="E6">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="F6" t="s">
         <v>1279</v>
@@ -7009,7 +7009,7 @@
         <v>1078</v>
       </c>
       <c r="E7">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="F7" t="s">
         <v>1279</v>
@@ -7044,7 +7044,7 @@
         <v>1079</v>
       </c>
       <c r="E8">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="F8" t="s">
         <v>1279</v>
@@ -7079,7 +7079,7 @@
         <v>1080</v>
       </c>
       <c r="E9">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="F9" t="s">
         <v>1279</v>
@@ -7114,7 +7114,7 @@
         <v>1081</v>
       </c>
       <c r="E10">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="F10" t="s">
         <v>1279</v>
@@ -7149,7 +7149,7 @@
         <v>1081</v>
       </c>
       <c r="E11">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="F11" t="s">
         <v>1279</v>
@@ -7184,7 +7184,7 @@
         <v>1082</v>
       </c>
       <c r="E12">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="F12" t="s">
         <v>1279</v>
@@ -7219,7 +7219,7 @@
         <v>1083</v>
       </c>
       <c r="E13">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="F13" t="s">
         <v>1279</v>
@@ -7254,7 +7254,7 @@
         <v>1084</v>
       </c>
       <c r="E14">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="F14" t="s">
         <v>1279</v>
@@ -7289,7 +7289,7 @@
         <v>1084</v>
       </c>
       <c r="E15">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="F15" t="s">
         <v>1279</v>
@@ -7324,7 +7324,7 @@
         <v>1085</v>
       </c>
       <c r="E16">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="F16" t="s">
         <v>1279</v>
@@ -7359,7 +7359,7 @@
         <v>1085</v>
       </c>
       <c r="E17">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="F17" t="s">
         <v>1279</v>
@@ -7394,7 +7394,7 @@
         <v>1086</v>
       </c>
       <c r="E18">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="F18" t="s">
         <v>1279</v>
@@ -7429,7 +7429,7 @@
         <v>1087</v>
       </c>
       <c r="E19">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="F19" t="s">
         <v>1279</v>
@@ -7464,7 +7464,7 @@
         <v>1088</v>
       </c>
       <c r="E20">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="F20" t="s">
         <v>1279</v>
@@ -7499,7 +7499,7 @@
         <v>1089</v>
       </c>
       <c r="E21">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="F21" t="s">
         <v>1279</v>
@@ -7534,7 +7534,7 @@
         <v>1090</v>
       </c>
       <c r="E22">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F22" t="s">
         <v>1279</v>
@@ -7572,7 +7572,7 @@
         <v>1091</v>
       </c>
       <c r="E23">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="F23" t="s">
         <v>1279</v>
@@ -7607,7 +7607,7 @@
         <v>1092</v>
       </c>
       <c r="E24">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="F24" t="s">
         <v>1279</v>
@@ -7642,7 +7642,7 @@
         <v>1093</v>
       </c>
       <c r="E25">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="F25" t="s">
         <v>1279</v>
@@ -7677,7 +7677,7 @@
         <v>1094</v>
       </c>
       <c r="E26">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="F26" t="s">
         <v>1279</v>
@@ -7712,7 +7712,7 @@
         <v>1095</v>
       </c>
       <c r="E27">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F27" t="s">
         <v>1279</v>
@@ -7747,7 +7747,7 @@
         <v>1096</v>
       </c>
       <c r="E28">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F28" t="s">
         <v>1279</v>
@@ -7782,7 +7782,7 @@
         <v>1097</v>
       </c>
       <c r="E29">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F29" t="s">
         <v>1279</v>
@@ -7817,7 +7817,7 @@
         <v>1098</v>
       </c>
       <c r="E30">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F30" t="s">
         <v>1279</v>
@@ -7852,7 +7852,7 @@
         <v>1099</v>
       </c>
       <c r="E31">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F31" t="s">
         <v>1279</v>
@@ -7887,7 +7887,7 @@
         <v>1100</v>
       </c>
       <c r="E32">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F32" t="s">
         <v>1279</v>
@@ -7922,7 +7922,7 @@
         <v>1101</v>
       </c>
       <c r="E33">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F33" t="s">
         <v>1279</v>
@@ -7957,7 +7957,7 @@
         <v>1102</v>
       </c>
       <c r="E34">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F34" t="s">
         <v>1279</v>
@@ -7992,7 +7992,7 @@
         <v>1103</v>
       </c>
       <c r="E35">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="F35" t="s">
         <v>1279</v>
@@ -8027,7 +8027,7 @@
         <v>1104</v>
       </c>
       <c r="E36">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F36" t="s">
         <v>1279</v>
@@ -8062,7 +8062,7 @@
         <v>1104</v>
       </c>
       <c r="E37">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F37" t="s">
         <v>1279</v>
@@ -8097,7 +8097,7 @@
         <v>1105</v>
       </c>
       <c r="E38">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F38" t="s">
         <v>1279</v>
@@ -8132,7 +8132,7 @@
         <v>1106</v>
       </c>
       <c r="E39">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F39" t="s">
         <v>1279</v>
@@ -8167,7 +8167,7 @@
         <v>1107</v>
       </c>
       <c r="E40">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F40" t="s">
         <v>1279</v>
@@ -8202,7 +8202,7 @@
         <v>1107</v>
       </c>
       <c r="E41">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F41" t="s">
         <v>1279</v>
@@ -8237,7 +8237,7 @@
         <v>1108</v>
       </c>
       <c r="E42">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F42" t="s">
         <v>1279</v>
@@ -8272,7 +8272,7 @@
         <v>1108</v>
       </c>
       <c r="E43">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F43" t="s">
         <v>1279</v>
@@ -8307,7 +8307,7 @@
         <v>1109</v>
       </c>
       <c r="E44">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F44" t="s">
         <v>1279</v>
@@ -8342,7 +8342,7 @@
         <v>1110</v>
       </c>
       <c r="E45">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F45" t="s">
         <v>1279</v>
@@ -8377,7 +8377,7 @@
         <v>1111</v>
       </c>
       <c r="E46">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F46" t="s">
         <v>1279</v>
@@ -8412,7 +8412,7 @@
         <v>1112</v>
       </c>
       <c r="E47">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F47" t="s">
         <v>1279</v>
@@ -8447,7 +8447,7 @@
         <v>1112</v>
       </c>
       <c r="E48">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F48" t="s">
         <v>1279</v>
@@ -8482,7 +8482,7 @@
         <v>1113</v>
       </c>
       <c r="E49">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F49" t="s">
         <v>1279</v>
@@ -8517,7 +8517,7 @@
         <v>1114</v>
       </c>
       <c r="E50">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F50" t="s">
         <v>1279</v>
@@ -8552,7 +8552,7 @@
         <v>1115</v>
       </c>
       <c r="E51">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F51" t="s">
         <v>1279</v>
@@ -8587,7 +8587,7 @@
         <v>1116</v>
       </c>
       <c r="E52">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F52" t="s">
         <v>1279</v>
@@ -8622,7 +8622,7 @@
         <v>1117</v>
       </c>
       <c r="E53">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F53" t="s">
         <v>1279</v>
@@ -8657,7 +8657,7 @@
         <v>1118</v>
       </c>
       <c r="E54">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F54" t="s">
         <v>1279</v>
@@ -8692,7 +8692,7 @@
         <v>1119</v>
       </c>
       <c r="E55">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F55" t="s">
         <v>1279</v>
@@ -8727,7 +8727,7 @@
         <v>1119</v>
       </c>
       <c r="E56">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F56" t="s">
         <v>1279</v>
@@ -8762,7 +8762,7 @@
         <v>1119</v>
       </c>
       <c r="E57">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F57" t="s">
         <v>1279</v>
@@ -8797,7 +8797,7 @@
         <v>1120</v>
       </c>
       <c r="E58">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F58" t="s">
         <v>1279</v>
@@ -8832,7 +8832,7 @@
         <v>1121</v>
       </c>
       <c r="E59">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F59" t="s">
         <v>1279</v>
@@ -8867,7 +8867,7 @@
         <v>1122</v>
       </c>
       <c r="E60">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F60" t="s">
         <v>1279</v>
@@ -8902,7 +8902,7 @@
         <v>1122</v>
       </c>
       <c r="E61">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F61" t="s">
         <v>1279</v>
@@ -8937,7 +8937,7 @@
         <v>1123</v>
       </c>
       <c r="E62">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F62" t="s">
         <v>1279</v>
@@ -8972,7 +8972,7 @@
         <v>1124</v>
       </c>
       <c r="E63">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F63" t="s">
         <v>1279</v>
@@ -9007,7 +9007,7 @@
         <v>1124</v>
       </c>
       <c r="E64">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F64" t="s">
         <v>1279</v>
@@ -9042,7 +9042,7 @@
         <v>1124</v>
       </c>
       <c r="E65">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F65" t="s">
         <v>1279</v>
@@ -9077,7 +9077,7 @@
         <v>1125</v>
       </c>
       <c r="E66">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F66" t="s">
         <v>1279</v>
@@ -9112,7 +9112,7 @@
         <v>1126</v>
       </c>
       <c r="E67">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F67" t="s">
         <v>1279</v>
@@ -9147,7 +9147,7 @@
         <v>1126</v>
       </c>
       <c r="E68">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F68" t="s">
         <v>1279</v>
@@ -9182,7 +9182,7 @@
         <v>1126</v>
       </c>
       <c r="E69">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F69" t="s">
         <v>1280</v>
@@ -9217,7 +9217,7 @@
         <v>1126</v>
       </c>
       <c r="E70">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F70" t="s">
         <v>1279</v>
@@ -9252,7 +9252,7 @@
         <v>1127</v>
       </c>
       <c r="E71">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F71" t="s">
         <v>1279</v>
@@ -9287,7 +9287,7 @@
         <v>1128</v>
       </c>
       <c r="E72">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F72" t="s">
         <v>1279</v>
@@ -9322,7 +9322,7 @@
         <v>1128</v>
       </c>
       <c r="E73">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F73" t="s">
         <v>1279</v>
@@ -9357,7 +9357,7 @@
         <v>1129</v>
       </c>
       <c r="E74">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F74" t="s">
         <v>1279</v>
@@ -9392,7 +9392,7 @@
         <v>1130</v>
       </c>
       <c r="E75">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F75" t="s">
         <v>1279</v>
@@ -9427,7 +9427,7 @@
         <v>1131</v>
       </c>
       <c r="E76">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F76" t="s">
         <v>1279</v>
@@ -9462,7 +9462,7 @@
         <v>1132</v>
       </c>
       <c r="E77">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F77" t="s">
         <v>1279</v>
@@ -9497,7 +9497,7 @@
         <v>1132</v>
       </c>
       <c r="E78">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F78" t="s">
         <v>1279</v>
@@ -9532,7 +9532,7 @@
         <v>1132</v>
       </c>
       <c r="E79">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F79" t="s">
         <v>1279</v>
@@ -9567,7 +9567,7 @@
         <v>1132</v>
       </c>
       <c r="E80">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F80" t="s">
         <v>1279</v>
@@ -9602,7 +9602,7 @@
         <v>1132</v>
       </c>
       <c r="E81">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F81" t="s">
         <v>1279</v>
@@ -9637,7 +9637,7 @@
         <v>1132</v>
       </c>
       <c r="E82">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F82" t="s">
         <v>1279</v>
@@ -9672,7 +9672,7 @@
         <v>1133</v>
       </c>
       <c r="E83">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F83" t="s">
         <v>1279</v>
@@ -9707,7 +9707,7 @@
         <v>1134</v>
       </c>
       <c r="E84">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F84" t="s">
         <v>1279</v>
@@ -9742,7 +9742,7 @@
         <v>1135</v>
       </c>
       <c r="E85">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F85" t="s">
         <v>1279</v>
@@ -9777,7 +9777,7 @@
         <v>1135</v>
       </c>
       <c r="E86">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F86" t="s">
         <v>1279</v>
@@ -9812,7 +9812,7 @@
         <v>1136</v>
       </c>
       <c r="E87">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F87" t="s">
         <v>1281</v>
@@ -9847,7 +9847,7 @@
         <v>1137</v>
       </c>
       <c r="E88">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F88" t="s">
         <v>1279</v>
@@ -9882,7 +9882,7 @@
         <v>1138</v>
       </c>
       <c r="E89">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F89" t="s">
         <v>1279</v>
@@ -9917,7 +9917,7 @@
         <v>1138</v>
       </c>
       <c r="E90">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F90" t="s">
         <v>1279</v>
@@ -9952,7 +9952,7 @@
         <v>1139</v>
       </c>
       <c r="E91">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F91" t="s">
         <v>1279</v>
@@ -9987,7 +9987,7 @@
         <v>1140</v>
       </c>
       <c r="E92">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F92" t="s">
         <v>1279</v>
@@ -10022,7 +10022,7 @@
         <v>1141</v>
       </c>
       <c r="E93">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F93" t="s">
         <v>1279</v>
@@ -10057,7 +10057,7 @@
         <v>1142</v>
       </c>
       <c r="E94">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F94" t="s">
         <v>1279</v>
@@ -10092,7 +10092,7 @@
         <v>1143</v>
       </c>
       <c r="E95">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F95" t="s">
         <v>1279</v>
@@ -10127,7 +10127,7 @@
         <v>1143</v>
       </c>
       <c r="E96">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F96" t="s">
         <v>1279</v>
@@ -10162,7 +10162,7 @@
         <v>1144</v>
       </c>
       <c r="E97">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F97" t="s">
         <v>1279</v>
@@ -10197,7 +10197,7 @@
         <v>1144</v>
       </c>
       <c r="E98">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F98" t="s">
         <v>1279</v>
@@ -10232,7 +10232,7 @@
         <v>1144</v>
       </c>
       <c r="E99">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F99" t="s">
         <v>1279</v>
@@ -10267,7 +10267,7 @@
         <v>1145</v>
       </c>
       <c r="E100">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F100" t="s">
         <v>1279</v>
@@ -10302,7 +10302,7 @@
         <v>1145</v>
       </c>
       <c r="E101">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F101" t="s">
         <v>1279</v>
@@ -10337,7 +10337,7 @@
         <v>1146</v>
       </c>
       <c r="E102">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F102" t="s">
         <v>1279</v>
@@ -10372,7 +10372,7 @@
         <v>1147</v>
       </c>
       <c r="E103">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F103" t="s">
         <v>1279</v>
@@ -10407,7 +10407,7 @@
         <v>1148</v>
       </c>
       <c r="E104">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F104" t="s">
         <v>1279</v>
@@ -10442,7 +10442,7 @@
         <v>1148</v>
       </c>
       <c r="E105">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F105" t="s">
         <v>1279</v>
@@ -10477,7 +10477,7 @@
         <v>1149</v>
       </c>
       <c r="E106">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F106" t="s">
         <v>1279</v>
@@ -10512,7 +10512,7 @@
         <v>1149</v>
       </c>
       <c r="E107">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F107" t="s">
         <v>1279</v>
@@ -10547,7 +10547,7 @@
         <v>1150</v>
       </c>
       <c r="E108">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F108" t="s">
         <v>1279</v>
@@ -10582,7 +10582,7 @@
         <v>1151</v>
       </c>
       <c r="E109">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F109" t="s">
         <v>1279</v>
@@ -10617,7 +10617,7 @@
         <v>1151</v>
       </c>
       <c r="E110">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F110" t="s">
         <v>1279</v>
@@ -10652,7 +10652,7 @@
         <v>1152</v>
       </c>
       <c r="E111">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F111" t="s">
         <v>1279</v>
@@ -10687,7 +10687,7 @@
         <v>1153</v>
       </c>
       <c r="E112">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F112" t="s">
         <v>1279</v>
@@ -10722,7 +10722,7 @@
         <v>1153</v>
       </c>
       <c r="E113">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F113" t="s">
         <v>1279</v>
@@ -10757,7 +10757,7 @@
         <v>1154</v>
       </c>
       <c r="E114">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F114" t="s">
         <v>1279</v>
@@ -10792,7 +10792,7 @@
         <v>1155</v>
       </c>
       <c r="E115">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F115" t="s">
         <v>1279</v>
@@ -10830,7 +10830,7 @@
         <v>1155</v>
       </c>
       <c r="E116">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F116" t="s">
         <v>1279</v>
@@ -10865,7 +10865,7 @@
         <v>1155</v>
       </c>
       <c r="E117">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F117" t="s">
         <v>1279</v>
@@ -10900,7 +10900,7 @@
         <v>1155</v>
       </c>
       <c r="E118">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F118" t="s">
         <v>1279</v>
@@ -10935,7 +10935,7 @@
         <v>1156</v>
       </c>
       <c r="E119">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F119" t="s">
         <v>1280</v>
@@ -10970,7 +10970,7 @@
         <v>1157</v>
       </c>
       <c r="E120">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F120" t="s">
         <v>1279</v>
@@ -11005,7 +11005,7 @@
         <v>1157</v>
       </c>
       <c r="E121">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F121" t="s">
         <v>1279</v>
@@ -11040,7 +11040,7 @@
         <v>1157</v>
       </c>
       <c r="E122">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F122" t="s">
         <v>1279</v>
@@ -11075,7 +11075,7 @@
         <v>1157</v>
       </c>
       <c r="E123">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F123" t="s">
         <v>1279</v>
@@ -11110,7 +11110,7 @@
         <v>1158</v>
       </c>
       <c r="E124">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F124" t="s">
         <v>1279</v>
@@ -11145,7 +11145,7 @@
         <v>1158</v>
       </c>
       <c r="E125">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F125" t="s">
         <v>1279</v>
@@ -11180,7 +11180,7 @@
         <v>1158</v>
       </c>
       <c r="E126">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F126" t="s">
         <v>1279</v>
@@ -11215,7 +11215,7 @@
         <v>1158</v>
       </c>
       <c r="E127">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F127" t="s">
         <v>1279</v>
@@ -11250,7 +11250,7 @@
         <v>1158</v>
       </c>
       <c r="E128">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F128" t="s">
         <v>1279</v>
@@ -11285,7 +11285,7 @@
         <v>1158</v>
       </c>
       <c r="E129">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F129" t="s">
         <v>1279</v>
@@ -11320,7 +11320,7 @@
         <v>1158</v>
       </c>
       <c r="E130">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F130" t="s">
         <v>1279</v>
@@ -11355,7 +11355,7 @@
         <v>1159</v>
       </c>
       <c r="E131">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F131" t="s">
         <v>1279</v>
@@ -11390,7 +11390,7 @@
         <v>1159</v>
       </c>
       <c r="E132">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F132" t="s">
         <v>1279</v>
@@ -11425,7 +11425,7 @@
         <v>1160</v>
       </c>
       <c r="E133">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F133" t="s">
         <v>1279</v>
@@ -11460,7 +11460,7 @@
         <v>1161</v>
       </c>
       <c r="E134">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F134" t="s">
         <v>1279</v>
@@ -11495,7 +11495,7 @@
         <v>1161</v>
       </c>
       <c r="E135">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F135" t="s">
         <v>1279</v>
@@ -11530,7 +11530,7 @@
         <v>1161</v>
       </c>
       <c r="E136">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F136" t="s">
         <v>1279</v>
@@ -11565,7 +11565,7 @@
         <v>1162</v>
       </c>
       <c r="E137">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F137" t="s">
         <v>1279</v>
@@ -11600,7 +11600,7 @@
         <v>1162</v>
       </c>
       <c r="E138">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F138" t="s">
         <v>1279</v>
@@ -11635,7 +11635,7 @@
         <v>1162</v>
       </c>
       <c r="E139">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F139" t="s">
         <v>1279</v>
@@ -11670,7 +11670,7 @@
         <v>1162</v>
       </c>
       <c r="E140">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F140" t="s">
         <v>1279</v>
@@ -11705,7 +11705,7 @@
         <v>1162</v>
       </c>
       <c r="E141">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F141" t="s">
         <v>1279</v>
@@ -11740,7 +11740,7 @@
         <v>1162</v>
       </c>
       <c r="E142">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F142" t="s">
         <v>1279</v>
@@ -11775,7 +11775,7 @@
         <v>1162</v>
       </c>
       <c r="E143">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F143" t="s">
         <v>1279</v>
@@ -11810,7 +11810,7 @@
         <v>1162</v>
       </c>
       <c r="E144">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F144" t="s">
         <v>1279</v>
@@ -11845,7 +11845,7 @@
         <v>1162</v>
       </c>
       <c r="E145">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F145" t="s">
         <v>1279</v>
@@ -11880,7 +11880,7 @@
         <v>1163</v>
       </c>
       <c r="E146">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F146" t="s">
         <v>1279</v>
@@ -11915,7 +11915,7 @@
         <v>1163</v>
       </c>
       <c r="E147">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F147" t="s">
         <v>1279</v>
@@ -11950,7 +11950,7 @@
         <v>1163</v>
       </c>
       <c r="E148">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F148" t="s">
         <v>1279</v>
@@ -11985,7 +11985,7 @@
         <v>1164</v>
       </c>
       <c r="E149">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F149" t="s">
         <v>1279</v>
@@ -12020,7 +12020,7 @@
         <v>1164</v>
       </c>
       <c r="E150">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F150" t="s">
         <v>1280</v>
@@ -12055,7 +12055,7 @@
         <v>1164</v>
       </c>
       <c r="E151">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F151" t="s">
         <v>1279</v>
@@ -12090,7 +12090,7 @@
         <v>1165</v>
       </c>
       <c r="E152">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F152" t="s">
         <v>1279</v>
@@ -12125,7 +12125,7 @@
         <v>1165</v>
       </c>
       <c r="E153">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F153" t="s">
         <v>1279</v>
@@ -12160,7 +12160,7 @@
         <v>1166</v>
       </c>
       <c r="E154">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F154" t="s">
         <v>1279</v>
@@ -12195,7 +12195,7 @@
         <v>1166</v>
       </c>
       <c r="E155">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F155" t="s">
         <v>1279</v>
@@ -12230,7 +12230,7 @@
         <v>1167</v>
       </c>
       <c r="E156">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F156" t="s">
         <v>1279</v>
@@ -12265,7 +12265,7 @@
         <v>1167</v>
       </c>
       <c r="E157">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F157" t="s">
         <v>1279</v>
@@ -12300,7 +12300,7 @@
         <v>1168</v>
       </c>
       <c r="E158">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F158" t="s">
         <v>1279</v>
@@ -12335,7 +12335,7 @@
         <v>1168</v>
       </c>
       <c r="E159">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F159" t="s">
         <v>1279</v>
@@ -12370,7 +12370,7 @@
         <v>1168</v>
       </c>
       <c r="E160">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F160" t="s">
         <v>1279</v>
@@ -12405,7 +12405,7 @@
         <v>1169</v>
       </c>
       <c r="E161">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F161" t="s">
         <v>1279</v>
@@ -12440,7 +12440,7 @@
         <v>1169</v>
       </c>
       <c r="E162">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F162" t="s">
         <v>1279</v>
@@ -12475,7 +12475,7 @@
         <v>1170</v>
       </c>
       <c r="E163">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F163" t="s">
         <v>1279</v>
@@ -12510,7 +12510,7 @@
         <v>1171</v>
       </c>
       <c r="E164">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F164" t="s">
         <v>1279</v>
@@ -12545,7 +12545,7 @@
         <v>1171</v>
       </c>
       <c r="E165">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F165" t="s">
         <v>1279</v>
@@ -12580,7 +12580,7 @@
         <v>1171</v>
       </c>
       <c r="E166">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F166" t="s">
         <v>1279</v>
@@ -12615,7 +12615,7 @@
         <v>1171</v>
       </c>
       <c r="E167">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F167" t="s">
         <v>1279</v>
@@ -12650,7 +12650,7 @@
         <v>1172</v>
       </c>
       <c r="E168">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F168" t="s">
         <v>1279</v>
@@ -12685,7 +12685,7 @@
         <v>1173</v>
       </c>
       <c r="E169">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F169" t="s">
         <v>1279</v>
@@ -12720,7 +12720,7 @@
         <v>1173</v>
       </c>
       <c r="E170">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F170" t="s">
         <v>1279</v>
@@ -12755,7 +12755,7 @@
         <v>1173</v>
       </c>
       <c r="E171">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F171" t="s">
         <v>1279</v>
@@ -12790,7 +12790,7 @@
         <v>1173</v>
       </c>
       <c r="E172">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F172" t="s">
         <v>1279</v>
@@ -12825,7 +12825,7 @@
         <v>1173</v>
       </c>
       <c r="E173">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F173" t="s">
         <v>1279</v>
@@ -12860,7 +12860,7 @@
         <v>1174</v>
       </c>
       <c r="E174">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F174" t="s">
         <v>1279</v>
@@ -12895,7 +12895,7 @@
         <v>1174</v>
       </c>
       <c r="E175">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F175" t="s">
         <v>1279</v>
@@ -12930,7 +12930,7 @@
         <v>1174</v>
       </c>
       <c r="E176">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F176" t="s">
         <v>1279</v>
@@ -12965,7 +12965,7 @@
         <v>1174</v>
       </c>
       <c r="E177">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F177" t="s">
         <v>1279</v>
@@ -13000,7 +13000,7 @@
         <v>1174</v>
       </c>
       <c r="E178">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F178" t="s">
         <v>1279</v>
@@ -13035,7 +13035,7 @@
         <v>1174</v>
       </c>
       <c r="E179">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F179" t="s">
         <v>1279</v>
@@ -13070,7 +13070,7 @@
         <v>1175</v>
       </c>
       <c r="E180">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F180" t="s">
         <v>1279</v>
@@ -13105,7 +13105,7 @@
         <v>1175</v>
       </c>
       <c r="E181">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F181" t="s">
         <v>1279</v>
@@ -13140,7 +13140,7 @@
         <v>1175</v>
       </c>
       <c r="E182">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F182" t="s">
         <v>1279</v>
@@ -13175,7 +13175,7 @@
         <v>1175</v>
       </c>
       <c r="E183">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F183" t="s">
         <v>1279</v>
@@ -13210,7 +13210,7 @@
         <v>1176</v>
       </c>
       <c r="E184">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F184" t="s">
         <v>1279</v>
@@ -13245,7 +13245,7 @@
         <v>1176</v>
       </c>
       <c r="E185">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F185" t="s">
         <v>1279</v>
@@ -13280,7 +13280,7 @@
         <v>1177</v>
       </c>
       <c r="E186">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F186" t="s">
         <v>1279</v>
@@ -13315,7 +13315,7 @@
         <v>1178</v>
       </c>
       <c r="E187">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F187" t="s">
         <v>1279</v>
@@ -13350,7 +13350,7 @@
         <v>1178</v>
       </c>
       <c r="E188">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F188" t="s">
         <v>1279</v>
@@ -13385,7 +13385,7 @@
         <v>1179</v>
       </c>
       <c r="E189">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F189" t="s">
         <v>1279</v>
@@ -13420,7 +13420,7 @@
         <v>1180</v>
       </c>
       <c r="E190">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F190" t="s">
         <v>1279</v>
@@ -13455,7 +13455,7 @@
         <v>1180</v>
       </c>
       <c r="E191">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F191" t="s">
         <v>1279</v>
@@ -13490,7 +13490,7 @@
         <v>1181</v>
       </c>
       <c r="E192">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F192" t="s">
         <v>1279</v>
@@ -13525,7 +13525,7 @@
         <v>1181</v>
       </c>
       <c r="E193">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F193" t="s">
         <v>1279</v>
@@ -13560,7 +13560,7 @@
         <v>1182</v>
       </c>
       <c r="E194">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F194" t="s">
         <v>1279</v>
@@ -13595,7 +13595,7 @@
         <v>1183</v>
       </c>
       <c r="E195">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F195" t="s">
         <v>1279</v>
@@ -13630,7 +13630,7 @@
         <v>1183</v>
       </c>
       <c r="E196">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F196" t="s">
         <v>1279</v>
@@ -13665,7 +13665,7 @@
         <v>1183</v>
       </c>
       <c r="E197">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F197" t="s">
         <v>1279</v>
@@ -13700,7 +13700,7 @@
         <v>1184</v>
       </c>
       <c r="E198">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F198" t="s">
         <v>1279</v>
@@ -13735,7 +13735,7 @@
         <v>1184</v>
       </c>
       <c r="E199">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F199" t="s">
         <v>1279</v>
@@ -13770,7 +13770,7 @@
         <v>1185</v>
       </c>
       <c r="E200">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F200" t="s">
         <v>1279</v>
@@ -13805,7 +13805,7 @@
         <v>1186</v>
       </c>
       <c r="E201">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F201" t="s">
         <v>1279</v>
@@ -13840,7 +13840,7 @@
         <v>1186</v>
       </c>
       <c r="E202">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F202" t="s">
         <v>1279</v>
@@ -13875,7 +13875,7 @@
         <v>1186</v>
       </c>
       <c r="E203">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F203" t="s">
         <v>1279</v>
@@ -13910,7 +13910,7 @@
         <v>1187</v>
       </c>
       <c r="E204">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F204" t="s">
         <v>1279</v>
@@ -13945,7 +13945,7 @@
         <v>1187</v>
       </c>
       <c r="E205">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F205" t="s">
         <v>1279</v>
@@ -13980,7 +13980,7 @@
         <v>1188</v>
       </c>
       <c r="E206">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F206" t="s">
         <v>1279</v>
@@ -14015,7 +14015,7 @@
         <v>1188</v>
       </c>
       <c r="E207">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F207" t="s">
         <v>1281</v>
@@ -14050,7 +14050,7 @@
         <v>1188</v>
       </c>
       <c r="E208">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F208" t="s">
         <v>1279</v>
@@ -14085,7 +14085,7 @@
         <v>1189</v>
       </c>
       <c r="E209">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F209" t="s">
         <v>1279</v>
@@ -14120,7 +14120,7 @@
         <v>1189</v>
       </c>
       <c r="E210">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F210" t="s">
         <v>1279</v>
@@ -14158,7 +14158,7 @@
         <v>1189</v>
       </c>
       <c r="E211">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F211" t="s">
         <v>1279</v>
@@ -14193,7 +14193,7 @@
         <v>1189</v>
       </c>
       <c r="E212">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F212" t="s">
         <v>1279</v>
@@ -14228,7 +14228,7 @@
         <v>1189</v>
       </c>
       <c r="E213">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F213" t="s">
         <v>1279</v>
@@ -14263,7 +14263,7 @@
         <v>1189</v>
       </c>
       <c r="E214">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F214" t="s">
         <v>1279</v>
@@ -14298,7 +14298,7 @@
         <v>1190</v>
       </c>
       <c r="E215">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F215" t="s">
         <v>1279</v>
@@ -14333,7 +14333,7 @@
         <v>1190</v>
       </c>
       <c r="E216">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F216" t="s">
         <v>1279</v>
@@ -14368,7 +14368,7 @@
         <v>1190</v>
       </c>
       <c r="E217">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F217" t="s">
         <v>1279</v>
@@ -14403,7 +14403,7 @@
         <v>1191</v>
       </c>
       <c r="E218">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F218" t="s">
         <v>1279</v>
@@ -14438,7 +14438,7 @@
         <v>1191</v>
       </c>
       <c r="E219">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F219" t="s">
         <v>1279</v>
@@ -14473,7 +14473,7 @@
         <v>1191</v>
       </c>
       <c r="E220">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F220" t="s">
         <v>1279</v>
@@ -14508,7 +14508,7 @@
         <v>1192</v>
       </c>
       <c r="E221">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F221" t="s">
         <v>1279</v>
@@ -14543,7 +14543,7 @@
         <v>1192</v>
       </c>
       <c r="E222">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F222" t="s">
         <v>1279</v>
@@ -14578,7 +14578,7 @@
         <v>1192</v>
       </c>
       <c r="E223">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F223" t="s">
         <v>1279</v>
@@ -14613,7 +14613,7 @@
         <v>1193</v>
       </c>
       <c r="E224">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F224" t="s">
         <v>1279</v>
@@ -14648,7 +14648,7 @@
         <v>1193</v>
       </c>
       <c r="E225">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F225" t="s">
         <v>1279</v>
@@ -14683,7 +14683,7 @@
         <v>1193</v>
       </c>
       <c r="E226">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F226" t="s">
         <v>1279</v>
@@ -14718,7 +14718,7 @@
         <v>1193</v>
       </c>
       <c r="E227">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F227" t="s">
         <v>1279</v>
@@ -14753,7 +14753,7 @@
         <v>1193</v>
       </c>
       <c r="E228">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F228" t="s">
         <v>1279</v>
@@ -14788,7 +14788,7 @@
         <v>1193</v>
       </c>
       <c r="E229">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F229" t="s">
         <v>1279</v>
@@ -14823,7 +14823,7 @@
         <v>1194</v>
       </c>
       <c r="E230">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F230" t="s">
         <v>1279</v>
@@ -14858,7 +14858,7 @@
         <v>1195</v>
       </c>
       <c r="E231">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F231" t="s">
         <v>1279</v>
@@ -14893,7 +14893,7 @@
         <v>1195</v>
       </c>
       <c r="E232">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F232" t="s">
         <v>1282</v>
@@ -14928,7 +14928,7 @@
         <v>1195</v>
       </c>
       <c r="E233">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F233" t="s">
         <v>1279</v>
@@ -14963,7 +14963,7 @@
         <v>1195</v>
       </c>
       <c r="E234">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F234" t="s">
         <v>1279</v>
@@ -14998,7 +14998,7 @@
         <v>1196</v>
       </c>
       <c r="E235">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F235" t="s">
         <v>1279</v>
@@ -15033,7 +15033,7 @@
         <v>1196</v>
       </c>
       <c r="E236">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F236" t="s">
         <v>1279</v>
@@ -15068,7 +15068,7 @@
         <v>1196</v>
       </c>
       <c r="E237">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F237" t="s">
         <v>1279</v>
@@ -15103,7 +15103,7 @@
         <v>1196</v>
       </c>
       <c r="E238">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F238" t="s">
         <v>1279</v>
@@ -15138,7 +15138,7 @@
         <v>1197</v>
       </c>
       <c r="E239">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F239" t="s">
         <v>1279</v>
@@ -15176,7 +15176,7 @@
         <v>1198</v>
       </c>
       <c r="E240">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F240" t="s">
         <v>1279</v>
@@ -15211,7 +15211,7 @@
         <v>1198</v>
       </c>
       <c r="E241">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F241" t="s">
         <v>1279</v>
@@ -15246,7 +15246,7 @@
         <v>1198</v>
       </c>
       <c r="E242">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F242" t="s">
         <v>1279</v>
@@ -15281,7 +15281,7 @@
         <v>1198</v>
       </c>
       <c r="E243">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F243" t="s">
         <v>1279</v>
@@ -15319,7 +15319,7 @@
         <v>1198</v>
       </c>
       <c r="E244">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F244" t="s">
         <v>1279</v>
@@ -15354,7 +15354,7 @@
         <v>1199</v>
       </c>
       <c r="E245">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F245" t="s">
         <v>1279</v>
@@ -15389,7 +15389,7 @@
         <v>1199</v>
       </c>
       <c r="E246">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F246" t="s">
         <v>1279</v>
@@ -15424,7 +15424,7 @@
         <v>1200</v>
       </c>
       <c r="E247">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F247" t="s">
         <v>1279</v>
@@ -15459,7 +15459,7 @@
         <v>1200</v>
       </c>
       <c r="E248">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F248" t="s">
         <v>1279</v>
@@ -15494,7 +15494,7 @@
         <v>1200</v>
       </c>
       <c r="E249">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F249" t="s">
         <v>1279</v>
@@ -15529,7 +15529,7 @@
         <v>1201</v>
       </c>
       <c r="E250">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F250" t="s">
         <v>1279</v>
@@ -15564,7 +15564,7 @@
         <v>1201</v>
       </c>
       <c r="E251">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F251" t="s">
         <v>1279</v>
@@ -15599,7 +15599,7 @@
         <v>1202</v>
       </c>
       <c r="E252">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F252" t="s">
         <v>1279</v>
@@ -15634,7 +15634,7 @@
         <v>1203</v>
       </c>
       <c r="E253">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F253" t="s">
         <v>1279</v>
@@ -15669,7 +15669,7 @@
         <v>1203</v>
       </c>
       <c r="E254">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F254" t="s">
         <v>1279</v>
@@ -15704,7 +15704,7 @@
         <v>1203</v>
       </c>
       <c r="E255">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F255" t="s">
         <v>1279</v>
@@ -15739,7 +15739,7 @@
         <v>1203</v>
       </c>
       <c r="E256">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F256" t="s">
         <v>1279</v>
@@ -15774,7 +15774,7 @@
         <v>1204</v>
       </c>
       <c r="E257">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F257" t="s">
         <v>1279</v>
@@ -15809,7 +15809,7 @@
         <v>1204</v>
       </c>
       <c r="E258">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F258" t="s">
         <v>1279</v>
@@ -15844,7 +15844,7 @@
         <v>1204</v>
       </c>
       <c r="E259">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F259" t="s">
         <v>1279</v>
@@ -15879,7 +15879,7 @@
         <v>1205</v>
       </c>
       <c r="E260">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F260" t="s">
         <v>1279</v>
@@ -15914,7 +15914,7 @@
         <v>1206</v>
       </c>
       <c r="E261">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F261" t="s">
         <v>1279</v>
@@ -15949,7 +15949,7 @@
         <v>1206</v>
       </c>
       <c r="E262">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F262" t="s">
         <v>1279</v>
@@ -15984,7 +15984,7 @@
         <v>1206</v>
       </c>
       <c r="E263">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F263" t="s">
         <v>1279</v>
@@ -16019,7 +16019,7 @@
         <v>1207</v>
       </c>
       <c r="E264">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F264" t="s">
         <v>1279</v>
@@ -16054,7 +16054,7 @@
         <v>1207</v>
       </c>
       <c r="E265">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F265" t="s">
         <v>1279</v>
@@ -16089,7 +16089,7 @@
         <v>1207</v>
       </c>
       <c r="E266">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F266" t="s">
         <v>1279</v>
@@ -16124,7 +16124,7 @@
         <v>1208</v>
       </c>
       <c r="E267">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F267" t="s">
         <v>1279</v>
@@ -16159,7 +16159,7 @@
         <v>1209</v>
       </c>
       <c r="E268">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F268" t="s">
         <v>1279</v>
@@ -16194,7 +16194,7 @@
         <v>1210</v>
       </c>
       <c r="E269">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F269" t="s">
         <v>1279</v>
@@ -16229,7 +16229,7 @@
         <v>1210</v>
       </c>
       <c r="E270">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F270" t="s">
         <v>1279</v>
@@ -16264,7 +16264,7 @@
         <v>1210</v>
       </c>
       <c r="E271">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F271" t="s">
         <v>1279</v>
@@ -16299,7 +16299,7 @@
         <v>1210</v>
       </c>
       <c r="E272">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F272" t="s">
         <v>1279</v>
@@ -16334,7 +16334,7 @@
         <v>1211</v>
       </c>
       <c r="E273">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F273" t="s">
         <v>1279</v>
@@ -16369,7 +16369,7 @@
         <v>1212</v>
       </c>
       <c r="E274">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F274" t="s">
         <v>1279</v>
@@ -16404,7 +16404,7 @@
         <v>1212</v>
       </c>
       <c r="E275">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F275" t="s">
         <v>1279</v>
@@ -16439,7 +16439,7 @@
         <v>1213</v>
       </c>
       <c r="E276">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F276" t="s">
         <v>1279</v>
@@ -16474,7 +16474,7 @@
         <v>1214</v>
       </c>
       <c r="E277">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F277" t="s">
         <v>1279</v>
@@ -16509,7 +16509,7 @@
         <v>1215</v>
       </c>
       <c r="E278">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F278" t="s">
         <v>1279</v>
@@ -16544,7 +16544,7 @@
         <v>1215</v>
       </c>
       <c r="E279">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F279" t="s">
         <v>1279</v>
@@ -16579,7 +16579,7 @@
         <v>1216</v>
       </c>
       <c r="E280">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F280" t="s">
         <v>1279</v>
@@ -16614,7 +16614,7 @@
         <v>1216</v>
       </c>
       <c r="E281">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F281" t="s">
         <v>1279</v>
@@ -16649,7 +16649,7 @@
         <v>1216</v>
       </c>
       <c r="E282">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F282" t="s">
         <v>1279</v>
@@ -16684,7 +16684,7 @@
         <v>1217</v>
       </c>
       <c r="E283">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F283" t="s">
         <v>1279</v>
@@ -16719,7 +16719,7 @@
         <v>1217</v>
       </c>
       <c r="E284">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F284" t="s">
         <v>1279</v>
@@ -16754,7 +16754,7 @@
         <v>1217</v>
       </c>
       <c r="E285">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F285" t="s">
         <v>1279</v>
@@ -16789,7 +16789,7 @@
         <v>1217</v>
       </c>
       <c r="E286">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F286" t="s">
         <v>1279</v>
@@ -16824,7 +16824,7 @@
         <v>1217</v>
       </c>
       <c r="E287">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F287" t="s">
         <v>1279</v>
@@ -16859,7 +16859,7 @@
         <v>1217</v>
       </c>
       <c r="E288">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F288" t="s">
         <v>1279</v>
@@ -16894,7 +16894,7 @@
         <v>1217</v>
       </c>
       <c r="E289">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F289" t="s">
         <v>1279</v>
@@ -16929,7 +16929,7 @@
         <v>1217</v>
       </c>
       <c r="E290">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F290" t="s">
         <v>1279</v>
@@ -16964,7 +16964,7 @@
         <v>1218</v>
       </c>
       <c r="E291">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F291" t="s">
         <v>1279</v>
@@ -16999,7 +16999,7 @@
         <v>1218</v>
       </c>
       <c r="E292">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F292" t="s">
         <v>1279</v>
@@ -17034,7 +17034,7 @@
         <v>1218</v>
       </c>
       <c r="E293">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F293" t="s">
         <v>1279</v>
@@ -17069,7 +17069,7 @@
         <v>1219</v>
       </c>
       <c r="E294">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F294" t="s">
         <v>1279</v>
@@ -17104,7 +17104,7 @@
         <v>1220</v>
       </c>
       <c r="E295">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F295" t="s">
         <v>1279</v>
@@ -17139,7 +17139,7 @@
         <v>1220</v>
       </c>
       <c r="E296">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F296" t="s">
         <v>1279</v>
@@ -17174,7 +17174,7 @@
         <v>1220</v>
       </c>
       <c r="E297">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F297" t="s">
         <v>1279</v>
@@ -17209,7 +17209,7 @@
         <v>1220</v>
       </c>
       <c r="E298">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F298" t="s">
         <v>1283</v>
@@ -17247,7 +17247,7 @@
         <v>1220</v>
       </c>
       <c r="E299">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F299" t="s">
         <v>1279</v>
@@ -17282,7 +17282,7 @@
         <v>1220</v>
       </c>
       <c r="E300">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F300" t="s">
         <v>1279</v>
@@ -17317,7 +17317,7 @@
         <v>1221</v>
       </c>
       <c r="E301">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F301" t="s">
         <v>1279</v>
@@ -17352,7 +17352,7 @@
         <v>1221</v>
       </c>
       <c r="E302">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F302" t="s">
         <v>1279</v>
@@ -17387,7 +17387,7 @@
         <v>1221</v>
       </c>
       <c r="E303">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F303" t="s">
         <v>1279</v>
@@ -17425,7 +17425,7 @@
         <v>1221</v>
       </c>
       <c r="E304">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F304" t="s">
         <v>1279</v>
@@ -17460,7 +17460,7 @@
         <v>1221</v>
       </c>
       <c r="E305">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F305" t="s">
         <v>1279</v>
@@ -17495,7 +17495,7 @@
         <v>1221</v>
       </c>
       <c r="E306">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F306" t="s">
         <v>1279</v>
@@ -17530,7 +17530,7 @@
         <v>1221</v>
       </c>
       <c r="E307">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F307" t="s">
         <v>1279</v>
@@ -17565,7 +17565,7 @@
         <v>1221</v>
       </c>
       <c r="E308">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F308" t="s">
         <v>1279</v>
@@ -17600,7 +17600,7 @@
         <v>1222</v>
       </c>
       <c r="E309">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F309" t="s">
         <v>1280</v>
@@ -17635,7 +17635,7 @@
         <v>1223</v>
       </c>
       <c r="E310">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F310" t="s">
         <v>1283</v>
@@ -17670,7 +17670,7 @@
         <v>1224</v>
       </c>
       <c r="E311">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F311" t="s">
         <v>1279</v>
@@ -17705,7 +17705,7 @@
         <v>1224</v>
       </c>
       <c r="E312">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F312" t="s">
         <v>1279</v>
@@ -17740,7 +17740,7 @@
         <v>1225</v>
       </c>
       <c r="E313">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F313" t="s">
         <v>1279</v>
@@ -17775,7 +17775,7 @@
         <v>1226</v>
       </c>
       <c r="E314">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F314" t="s">
         <v>1282</v>
@@ -17810,7 +17810,7 @@
         <v>1226</v>
       </c>
       <c r="E315">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F315" t="s">
         <v>1279</v>
@@ -17845,7 +17845,7 @@
         <v>1226</v>
       </c>
       <c r="E316">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F316" t="s">
         <v>1279</v>
@@ -17880,7 +17880,7 @@
         <v>1226</v>
       </c>
       <c r="E317">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F317" t="s">
         <v>1279</v>
@@ -17915,7 +17915,7 @@
         <v>1227</v>
       </c>
       <c r="E318">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F318" t="s">
         <v>1279</v>
@@ -17950,7 +17950,7 @@
         <v>1228</v>
       </c>
       <c r="E319">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F319" t="s">
         <v>1279</v>
@@ -17985,7 +17985,7 @@
         <v>1228</v>
       </c>
       <c r="E320">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F320" t="s">
         <v>1279</v>
@@ -18020,7 +18020,7 @@
         <v>1229</v>
       </c>
       <c r="E321">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F321" t="s">
         <v>1279</v>
@@ -18055,7 +18055,7 @@
         <v>1230</v>
       </c>
       <c r="E322">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F322" t="s">
         <v>1279</v>
@@ -18090,7 +18090,7 @@
         <v>1230</v>
       </c>
       <c r="E323">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F323" t="s">
         <v>1279</v>
@@ -18125,7 +18125,7 @@
         <v>1230</v>
       </c>
       <c r="E324">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F324" t="s">
         <v>1279</v>
@@ -18160,7 +18160,7 @@
         <v>1230</v>
       </c>
       <c r="E325">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F325" t="s">
         <v>1279</v>
@@ -18195,7 +18195,7 @@
         <v>1230</v>
       </c>
       <c r="E326">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F326" t="s">
         <v>1279</v>
@@ -18230,7 +18230,7 @@
         <v>1230</v>
       </c>
       <c r="E327">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F327" t="s">
         <v>1279</v>
@@ -18265,7 +18265,7 @@
         <v>1230</v>
       </c>
       <c r="E328">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F328" t="s">
         <v>1279</v>
@@ -18300,7 +18300,7 @@
         <v>1231</v>
       </c>
       <c r="E329">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F329" t="s">
         <v>1279</v>
@@ -18335,7 +18335,7 @@
         <v>1231</v>
       </c>
       <c r="E330">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F330" t="s">
         <v>1279</v>
@@ -18370,7 +18370,7 @@
         <v>1231</v>
       </c>
       <c r="E331">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F331" t="s">
         <v>1280</v>
@@ -18405,7 +18405,7 @@
         <v>1232</v>
       </c>
       <c r="E332">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F332" t="s">
         <v>1279</v>
@@ -18440,7 +18440,7 @@
         <v>1232</v>
       </c>
       <c r="E333">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F333" t="s">
         <v>1279</v>
@@ -18475,7 +18475,7 @@
         <v>1232</v>
       </c>
       <c r="E334">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F334" t="s">
         <v>1279</v>
@@ -18510,7 +18510,7 @@
         <v>1232</v>
       </c>
       <c r="E335">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F335" t="s">
         <v>1279</v>
@@ -18545,7 +18545,7 @@
         <v>1232</v>
       </c>
       <c r="E336">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F336" t="s">
         <v>1279</v>
@@ -18580,7 +18580,7 @@
         <v>1232</v>
       </c>
       <c r="E337">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F337" t="s">
         <v>1282</v>
@@ -18615,7 +18615,7 @@
         <v>1233</v>
       </c>
       <c r="E338">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F338" t="s">
         <v>1279</v>
@@ -18650,7 +18650,7 @@
         <v>1233</v>
       </c>
       <c r="E339">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F339" t="s">
         <v>1279</v>
@@ -18685,7 +18685,7 @@
         <v>1233</v>
       </c>
       <c r="E340">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F340" t="s">
         <v>1279</v>
@@ -18720,7 +18720,7 @@
         <v>1234</v>
       </c>
       <c r="E341">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F341" t="s">
         <v>1282</v>
@@ -18755,7 +18755,7 @@
         <v>1234</v>
       </c>
       <c r="E342">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F342" t="s">
         <v>1279</v>
@@ -18790,7 +18790,7 @@
         <v>1234</v>
       </c>
       <c r="E343">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F343" t="s">
         <v>1279</v>
@@ -18825,7 +18825,7 @@
         <v>1235</v>
       </c>
       <c r="E344">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F344" t="s">
         <v>1279</v>
@@ -18860,7 +18860,7 @@
         <v>1235</v>
       </c>
       <c r="E345">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F345" t="s">
         <v>1279</v>
@@ -18895,7 +18895,7 @@
         <v>1235</v>
       </c>
       <c r="E346">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F346" t="s">
         <v>1279</v>
@@ -18930,7 +18930,7 @@
         <v>1235</v>
       </c>
       <c r="E347">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F347" t="s">
         <v>1279</v>
@@ -18965,7 +18965,7 @@
         <v>1235</v>
       </c>
       <c r="E348">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F348" t="s">
         <v>1281</v>
@@ -19000,7 +19000,7 @@
         <v>1235</v>
       </c>
       <c r="E349">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F349" t="s">
         <v>1279</v>
@@ -19035,7 +19035,7 @@
         <v>1236</v>
       </c>
       <c r="E350">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F350" t="s">
         <v>1279</v>
@@ -19070,7 +19070,7 @@
         <v>1236</v>
       </c>
       <c r="E351">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F351" t="s">
         <v>1279</v>
@@ -19105,7 +19105,7 @@
         <v>1236</v>
       </c>
       <c r="E352">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F352" t="s">
         <v>1279</v>
@@ -19140,7 +19140,7 @@
         <v>1236</v>
       </c>
       <c r="E353">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F353" t="s">
         <v>1279</v>
@@ -19175,7 +19175,7 @@
         <v>1237</v>
       </c>
       <c r="E354">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F354" t="s">
         <v>1279</v>
@@ -19210,7 +19210,7 @@
         <v>1237</v>
       </c>
       <c r="E355">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F355" t="s">
         <v>1279</v>
@@ -19245,7 +19245,7 @@
         <v>1237</v>
       </c>
       <c r="E356">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F356" t="s">
         <v>1279</v>
@@ -19280,7 +19280,7 @@
         <v>1237</v>
       </c>
       <c r="E357">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F357" t="s">
         <v>1279</v>
@@ -19315,7 +19315,7 @@
         <v>1237</v>
       </c>
       <c r="E358">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F358" t="s">
         <v>1279</v>
@@ -19353,7 +19353,7 @@
         <v>1238</v>
       </c>
       <c r="E359">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F359" t="s">
         <v>1279</v>
@@ -19388,7 +19388,7 @@
         <v>1238</v>
       </c>
       <c r="E360">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F360" t="s">
         <v>1279</v>
@@ -19423,7 +19423,7 @@
         <v>1238</v>
       </c>
       <c r="E361">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F361" t="s">
         <v>1279</v>
@@ -19458,7 +19458,7 @@
         <v>1238</v>
       </c>
       <c r="E362">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F362" t="s">
         <v>1279</v>
@@ -19493,7 +19493,7 @@
         <v>1238</v>
       </c>
       <c r="E363">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F363" t="s">
         <v>1279</v>
@@ -19528,7 +19528,7 @@
         <v>1238</v>
       </c>
       <c r="E364">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F364" t="s">
         <v>1279</v>
@@ -19563,7 +19563,7 @@
         <v>1239</v>
       </c>
       <c r="E365">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F365" t="s">
         <v>1280</v>
@@ -19598,7 +19598,7 @@
         <v>1240</v>
       </c>
       <c r="E366">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F366" t="s">
         <v>1279</v>
@@ -19633,7 +19633,7 @@
         <v>1241</v>
       </c>
       <c r="E367">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F367" t="s">
         <v>1281</v>
@@ -19671,7 +19671,7 @@
         <v>1242</v>
       </c>
       <c r="E368">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F368" t="s">
         <v>1279</v>
@@ -19706,7 +19706,7 @@
         <v>1242</v>
       </c>
       <c r="E369">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F369" t="s">
         <v>1279</v>
@@ -19741,7 +19741,7 @@
         <v>1242</v>
       </c>
       <c r="E370">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F370" t="s">
         <v>1279</v>
@@ -19776,7 +19776,7 @@
         <v>1243</v>
       </c>
       <c r="E371">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F371" t="s">
         <v>1279</v>
@@ -19811,7 +19811,7 @@
         <v>1243</v>
       </c>
       <c r="E372">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F372" t="s">
         <v>1279</v>
@@ -19846,7 +19846,7 @@
         <v>1244</v>
       </c>
       <c r="E373">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F373" t="s">
         <v>1279</v>
@@ -19881,7 +19881,7 @@
         <v>1244</v>
       </c>
       <c r="E374">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F374" t="s">
         <v>1283</v>
@@ -19919,7 +19919,7 @@
         <v>1244</v>
       </c>
       <c r="E375">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F375" t="s">
         <v>1279</v>
@@ -19954,7 +19954,7 @@
         <v>1244</v>
       </c>
       <c r="E376">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F376" t="s">
         <v>1283</v>
@@ -19989,7 +19989,7 @@
         <v>1245</v>
       </c>
       <c r="E377">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F377" t="s">
         <v>1279</v>
@@ -20024,7 +20024,7 @@
         <v>1246</v>
       </c>
       <c r="E378">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F378" t="s">
         <v>1279</v>
@@ -20059,7 +20059,7 @@
         <v>1246</v>
       </c>
       <c r="E379">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F379" t="s">
         <v>1279</v>
@@ -20094,7 +20094,7 @@
         <v>1246</v>
       </c>
       <c r="E380">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F380" t="s">
         <v>1279</v>
@@ -20129,7 +20129,7 @@
         <v>1246</v>
       </c>
       <c r="E381">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F381" t="s">
         <v>1279</v>
@@ -20164,7 +20164,7 @@
         <v>1247</v>
       </c>
       <c r="E382">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F382" t="s">
         <v>1283</v>
@@ -20199,7 +20199,7 @@
         <v>1247</v>
       </c>
       <c r="E383">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F383" t="s">
         <v>1279</v>
@@ -20234,7 +20234,7 @@
         <v>1247</v>
       </c>
       <c r="E384">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F384" t="s">
         <v>1279</v>
@@ -20269,7 +20269,7 @@
         <v>1248</v>
       </c>
       <c r="E385">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F385" t="s">
         <v>1279</v>
@@ -20304,7 +20304,7 @@
         <v>1249</v>
       </c>
       <c r="E386">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F386" t="s">
         <v>1279</v>
@@ -20339,7 +20339,7 @@
         <v>1249</v>
       </c>
       <c r="E387">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F387" t="s">
         <v>1279</v>
@@ -20374,7 +20374,7 @@
         <v>1250</v>
       </c>
       <c r="E388">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F388" t="s">
         <v>1279</v>
@@ -20409,7 +20409,7 @@
         <v>1250</v>
       </c>
       <c r="E389">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F389" t="s">
         <v>1279</v>
@@ -20444,7 +20444,7 @@
         <v>1250</v>
       </c>
       <c r="E390">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F390" t="s">
         <v>1279</v>
@@ -20479,7 +20479,7 @@
         <v>1250</v>
       </c>
       <c r="E391">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F391" t="s">
         <v>1279</v>
@@ -20514,7 +20514,7 @@
         <v>1250</v>
       </c>
       <c r="E392">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F392" t="s">
         <v>1279</v>
@@ -20549,7 +20549,7 @@
         <v>1250</v>
       </c>
       <c r="E393">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F393" t="s">
         <v>1279</v>
@@ -20584,7 +20584,7 @@
         <v>1250</v>
       </c>
       <c r="E394">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F394" t="s">
         <v>1279</v>
@@ -20619,7 +20619,7 @@
         <v>1250</v>
       </c>
       <c r="E395">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F395" t="s">
         <v>1279</v>
@@ -20654,7 +20654,7 @@
         <v>1250</v>
       </c>
       <c r="E396">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F396" t="s">
         <v>1279</v>
@@ -20689,7 +20689,7 @@
         <v>1250</v>
       </c>
       <c r="E397">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F397" t="s">
         <v>1279</v>
@@ -20724,7 +20724,7 @@
         <v>1250</v>
       </c>
       <c r="E398">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F398" t="s">
         <v>1279</v>
@@ -20759,7 +20759,7 @@
         <v>1250</v>
       </c>
       <c r="E399">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F399" t="s">
         <v>1279</v>
@@ -20794,7 +20794,7 @@
         <v>1250</v>
       </c>
       <c r="E400">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F400" t="s">
         <v>1279</v>
@@ -20829,7 +20829,7 @@
         <v>1250</v>
       </c>
       <c r="E401">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F401" t="s">
         <v>1279</v>
@@ -20864,7 +20864,7 @@
         <v>1250</v>
       </c>
       <c r="E402">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F402" t="s">
         <v>1279</v>
@@ -20899,7 +20899,7 @@
         <v>1250</v>
       </c>
       <c r="E403">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F403" t="s">
         <v>1279</v>
@@ -20934,7 +20934,7 @@
         <v>1250</v>
       </c>
       <c r="E404">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F404" t="s">
         <v>1279</v>
@@ -20969,7 +20969,7 @@
         <v>1250</v>
       </c>
       <c r="E405">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F405" t="s">
         <v>1279</v>
@@ -21004,7 +21004,7 @@
         <v>1250</v>
       </c>
       <c r="E406">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F406" t="s">
         <v>1279</v>
@@ -21039,7 +21039,7 @@
         <v>1250</v>
       </c>
       <c r="E407">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F407" t="s">
         <v>1279</v>
@@ -21074,7 +21074,7 @@
         <v>1250</v>
       </c>
       <c r="E408">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F408" t="s">
         <v>1279</v>
@@ -21109,7 +21109,7 @@
         <v>1250</v>
       </c>
       <c r="E409">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F409" t="s">
         <v>1279</v>
@@ -21144,7 +21144,7 @@
         <v>1251</v>
       </c>
       <c r="E410">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F410" t="s">
         <v>1279</v>
@@ -21179,7 +21179,7 @@
         <v>1251</v>
       </c>
       <c r="E411">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F411" t="s">
         <v>1279</v>
@@ -21214,7 +21214,7 @@
         <v>1251</v>
       </c>
       <c r="E412">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F412" t="s">
         <v>1283</v>
@@ -21249,7 +21249,7 @@
         <v>1252</v>
       </c>
       <c r="E413">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F413" t="s">
         <v>1279</v>
@@ -21284,7 +21284,7 @@
         <v>1253</v>
       </c>
       <c r="E414">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F414" t="s">
         <v>1281</v>
@@ -21322,7 +21322,7 @@
         <v>1253</v>
       </c>
       <c r="E415">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F415" t="s">
         <v>1279</v>
@@ -21357,7 +21357,7 @@
         <v>1253</v>
       </c>
       <c r="E416">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F416" t="s">
         <v>1279</v>
@@ -21392,7 +21392,7 @@
         <v>1253</v>
       </c>
       <c r="E417">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F417" t="s">
         <v>1279</v>
@@ -21427,7 +21427,7 @@
         <v>1254</v>
       </c>
       <c r="E418">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F418" t="s">
         <v>1279</v>
@@ -21465,7 +21465,7 @@
         <v>1254</v>
       </c>
       <c r="E419">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F419" t="s">
         <v>1283</v>
@@ -21500,7 +21500,7 @@
         <v>1254</v>
       </c>
       <c r="E420">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F420" t="s">
         <v>1281</v>
@@ -21535,7 +21535,7 @@
         <v>1254</v>
       </c>
       <c r="E421">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F421" t="s">
         <v>1279</v>
@@ -21570,7 +21570,7 @@
         <v>1254</v>
       </c>
       <c r="E422">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F422" t="s">
         <v>1279</v>
@@ -21605,7 +21605,7 @@
         <v>1254</v>
       </c>
       <c r="E423">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F423" t="s">
         <v>1279</v>
@@ -21640,7 +21640,7 @@
         <v>1254</v>
       </c>
       <c r="E424">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F424" t="s">
         <v>1279</v>
@@ -21675,7 +21675,7 @@
         <v>1255</v>
       </c>
       <c r="E425">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F425" t="s">
         <v>1283</v>
@@ -21713,7 +21713,7 @@
         <v>1256</v>
       </c>
       <c r="E426">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F426" t="s">
         <v>1279</v>
@@ -21748,7 +21748,7 @@
         <v>1256</v>
       </c>
       <c r="E427">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F427" t="s">
         <v>1279</v>
@@ -21783,7 +21783,7 @@
         <v>1256</v>
       </c>
       <c r="E428">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F428" t="s">
         <v>1279</v>
@@ -21818,7 +21818,7 @@
         <v>1257</v>
       </c>
       <c r="E429">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F429" t="s">
         <v>1279</v>
@@ -21853,7 +21853,7 @@
         <v>1257</v>
       </c>
       <c r="E430">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F430" t="s">
         <v>1279</v>
@@ -21888,7 +21888,7 @@
         <v>1257</v>
       </c>
       <c r="E431">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F431" t="s">
         <v>1279</v>
@@ -21923,7 +21923,7 @@
         <v>1257</v>
       </c>
       <c r="E432">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F432" t="s">
         <v>1281</v>
@@ -21958,7 +21958,7 @@
         <v>1257</v>
       </c>
       <c r="E433">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F433" t="s">
         <v>1279</v>
@@ -21993,7 +21993,7 @@
         <v>1258</v>
       </c>
       <c r="E434">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F434" t="s">
         <v>1279</v>
@@ -22028,7 +22028,7 @@
         <v>1258</v>
       </c>
       <c r="E435">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F435" t="s">
         <v>1279</v>
@@ -22063,7 +22063,7 @@
         <v>1258</v>
       </c>
       <c r="E436">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F436" t="s">
         <v>1279</v>
@@ -22098,7 +22098,7 @@
         <v>1258</v>
       </c>
       <c r="E437">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F437" t="s">
         <v>1279</v>
@@ -22133,7 +22133,7 @@
         <v>1258</v>
       </c>
       <c r="E438">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F438" t="s">
         <v>1279</v>
@@ -22171,7 +22171,7 @@
         <v>1258</v>
       </c>
       <c r="E439">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F439" t="s">
         <v>1281</v>
@@ -22209,7 +22209,7 @@
         <v>1258</v>
       </c>
       <c r="E440">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F440" t="s">
         <v>1281</v>
@@ -22244,7 +22244,7 @@
         <v>1259</v>
       </c>
       <c r="E441">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F441" t="s">
         <v>1279</v>
@@ -22279,7 +22279,7 @@
         <v>1259</v>
       </c>
       <c r="E442">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F442" t="s">
         <v>1279</v>
@@ -22314,7 +22314,7 @@
         <v>1259</v>
       </c>
       <c r="E443">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F443" t="s">
         <v>1279</v>
@@ -22349,7 +22349,7 @@
         <v>1260</v>
       </c>
       <c r="E444">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F444" t="s">
         <v>1279</v>
@@ -22384,7 +22384,7 @@
         <v>1260</v>
       </c>
       <c r="E445">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F445" t="s">
         <v>1279</v>
@@ -22419,7 +22419,7 @@
         <v>1260</v>
       </c>
       <c r="E446">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F446" t="s">
         <v>1281</v>
@@ -22457,7 +22457,7 @@
         <v>1260</v>
       </c>
       <c r="E447">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F447" t="s">
         <v>1279</v>
@@ -22492,7 +22492,7 @@
         <v>1261</v>
       </c>
       <c r="E448">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F448" t="s">
         <v>1279</v>
@@ -22527,7 +22527,7 @@
         <v>1261</v>
       </c>
       <c r="E449">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F449" t="s">
         <v>1279</v>
@@ -22562,7 +22562,7 @@
         <v>1262</v>
       </c>
       <c r="E450">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F450" t="s">
         <v>1281</v>
@@ -22600,7 +22600,7 @@
         <v>1262</v>
       </c>
       <c r="E451">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F451" t="s">
         <v>1279</v>
@@ -22635,7 +22635,7 @@
         <v>1262</v>
       </c>
       <c r="E452">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F452" t="s">
         <v>1279</v>
@@ -22670,7 +22670,7 @@
         <v>1263</v>
       </c>
       <c r="E453">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F453" t="s">
         <v>1281</v>
@@ -22705,7 +22705,7 @@
         <v>1263</v>
       </c>
       <c r="E454">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F454" t="s">
         <v>1279</v>
@@ -22740,7 +22740,7 @@
         <v>1263</v>
       </c>
       <c r="E455">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F455" t="s">
         <v>1281</v>
@@ -22778,7 +22778,7 @@
         <v>1263</v>
       </c>
       <c r="E456">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F456" t="s">
         <v>1279</v>
@@ -22813,7 +22813,7 @@
         <v>1263</v>
       </c>
       <c r="E457">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F457" t="s">
         <v>1279</v>
@@ -22848,7 +22848,7 @@
         <v>1264</v>
       </c>
       <c r="E458">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F458" t="s">
         <v>1279</v>
@@ -22883,7 +22883,7 @@
         <v>1264</v>
       </c>
       <c r="E459">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F459" t="s">
         <v>1279</v>
@@ -22918,7 +22918,7 @@
         <v>1265</v>
       </c>
       <c r="E460">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F460" t="s">
         <v>1279</v>
@@ -22953,7 +22953,7 @@
         <v>1265</v>
       </c>
       <c r="E461">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F461" t="s">
         <v>1279</v>
@@ -22988,7 +22988,7 @@
         <v>1265</v>
       </c>
       <c r="E462">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F462" t="s">
         <v>1279</v>
@@ -23023,7 +23023,7 @@
         <v>1265</v>
       </c>
       <c r="E463">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F463" t="s">
         <v>1281</v>
@@ -23061,7 +23061,7 @@
         <v>1266</v>
       </c>
       <c r="E464">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F464" t="s">
         <v>1279</v>
@@ -23096,7 +23096,7 @@
         <v>1266</v>
       </c>
       <c r="E465">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F465" t="s">
         <v>1283</v>
@@ -23134,7 +23134,7 @@
         <v>1266</v>
       </c>
       <c r="E466">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F466" t="s">
         <v>1279</v>
@@ -23169,7 +23169,7 @@
         <v>1266</v>
       </c>
       <c r="E467">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F467" t="s">
         <v>1279</v>
@@ -23204,7 +23204,7 @@
         <v>1267</v>
       </c>
       <c r="E468">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F468" t="s">
         <v>1279</v>
@@ -23239,7 +23239,7 @@
         <v>1267</v>
       </c>
       <c r="E469">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F469" t="s">
         <v>1279</v>
@@ -23274,7 +23274,7 @@
         <v>1267</v>
       </c>
       <c r="E470">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F470" t="s">
         <v>1279</v>
@@ -23309,7 +23309,7 @@
         <v>1267</v>
       </c>
       <c r="E471">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F471" t="s">
         <v>1279</v>
@@ -23344,7 +23344,7 @@
         <v>1267</v>
       </c>
       <c r="E472">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F472" t="s">
         <v>1279</v>
@@ -23379,7 +23379,7 @@
         <v>1267</v>
       </c>
       <c r="E473">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F473" t="s">
         <v>1281</v>
@@ -23417,7 +23417,7 @@
         <v>1268</v>
       </c>
       <c r="E474">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F474" t="s">
         <v>1279</v>
@@ -23452,7 +23452,7 @@
         <v>1268</v>
       </c>
       <c r="E475">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F475" t="s">
         <v>1281</v>
@@ -23487,7 +23487,7 @@
         <v>1269</v>
       </c>
       <c r="E476">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F476" t="s">
         <v>1281</v>
@@ -23525,7 +23525,7 @@
         <v>1269</v>
       </c>
       <c r="E477">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F477" t="s">
         <v>1281</v>
@@ -23563,7 +23563,7 @@
         <v>1269</v>
       </c>
       <c r="E478">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F478" t="s">
         <v>1279</v>
@@ -23598,7 +23598,7 @@
         <v>1269</v>
       </c>
       <c r="E479">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F479" t="s">
         <v>1279</v>
@@ -23633,7 +23633,7 @@
         <v>1270</v>
       </c>
       <c r="E480">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F480" t="s">
         <v>1279</v>
@@ -23668,7 +23668,7 @@
         <v>1271</v>
       </c>
       <c r="E481">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F481" t="s">
         <v>1279</v>
@@ -23703,7 +23703,7 @@
         <v>1271</v>
       </c>
       <c r="E482">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F482" t="s">
         <v>1279</v>
@@ -23738,7 +23738,7 @@
         <v>1271</v>
       </c>
       <c r="E483">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F483" t="s">
         <v>1279</v>
@@ -23773,7 +23773,7 @@
         <v>1271</v>
       </c>
       <c r="E484">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F484" t="s">
         <v>1279</v>
@@ -23808,7 +23808,7 @@
         <v>1271</v>
       </c>
       <c r="E485">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F485" t="s">
         <v>1279</v>
@@ -23843,7 +23843,7 @@
         <v>1271</v>
       </c>
       <c r="E486">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F486" t="s">
         <v>1279</v>
@@ -23878,7 +23878,7 @@
         <v>1271</v>
       </c>
       <c r="E487">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F487" t="s">
         <v>1279</v>
@@ -23913,7 +23913,7 @@
         <v>1271</v>
       </c>
       <c r="E488">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F488" t="s">
         <v>1281</v>
@@ -23951,7 +23951,7 @@
         <v>1272</v>
       </c>
       <c r="E489">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F489" t="s">
         <v>1279</v>
@@ -23986,7 +23986,7 @@
         <v>1272</v>
       </c>
       <c r="E490">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F490" t="s">
         <v>1279</v>
@@ -24021,7 +24021,7 @@
         <v>1272</v>
       </c>
       <c r="E491">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F491" t="s">
         <v>1279</v>
@@ -24056,7 +24056,7 @@
         <v>1272</v>
       </c>
       <c r="E492">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F492" t="s">
         <v>1281</v>
@@ -24094,7 +24094,7 @@
         <v>1272</v>
       </c>
       <c r="E493">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F493" t="s">
         <v>1281</v>
@@ -24132,7 +24132,7 @@
         <v>1272</v>
       </c>
       <c r="E494">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F494" t="s">
         <v>1281</v>
@@ -24170,7 +24170,7 @@
         <v>1272</v>
       </c>
       <c r="E495">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F495" t="s">
         <v>1279</v>
@@ -24205,7 +24205,7 @@
         <v>1273</v>
       </c>
       <c r="E496">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F496" t="s">
         <v>1281</v>
@@ -24243,7 +24243,7 @@
         <v>1273</v>
       </c>
       <c r="E497">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F497" t="s">
         <v>1281</v>
@@ -24281,7 +24281,7 @@
         <v>1274</v>
       </c>
       <c r="E498">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F498" t="s">
         <v>1281</v>
@@ -24319,7 +24319,7 @@
         <v>1274</v>
       </c>
       <c r="E499">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F499" t="s">
         <v>1279</v>
@@ -24354,7 +24354,7 @@
         <v>1275</v>
       </c>
       <c r="E500">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F500" t="s">
         <v>1279</v>
@@ -24389,7 +24389,7 @@
         <v>1275</v>
       </c>
       <c r="E501">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F501" t="s">
         <v>1279</v>
@@ -24427,7 +24427,7 @@
         <v>1275</v>
       </c>
       <c r="E502">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F502" t="s">
         <v>1281</v>
@@ -24465,7 +24465,7 @@
         <v>1276</v>
       </c>
       <c r="E503">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F503" t="s">
         <v>1279</v>
@@ -24503,7 +24503,7 @@
         <v>1276</v>
       </c>
       <c r="E504">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F504" t="s">
         <v>1279</v>
@@ -24538,7 +24538,7 @@
         <v>1276</v>
       </c>
       <c r="E505">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F505" t="s">
         <v>1279</v>
@@ -24573,7 +24573,7 @@
         <v>1276</v>
       </c>
       <c r="E506">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F506" t="s">
         <v>1279</v>
@@ -24608,7 +24608,7 @@
         <v>1276</v>
       </c>
       <c r="E507">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F507" t="s">
         <v>1279</v>
@@ -24643,7 +24643,7 @@
         <v>1276</v>
       </c>
       <c r="E508">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F508" t="s">
         <v>1281</v>
@@ -24681,7 +24681,7 @@
         <v>1277</v>
       </c>
       <c r="E509">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F509" t="s">
         <v>1279</v>
@@ -24716,7 +24716,7 @@
         <v>1277</v>
       </c>
       <c r="E510">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F510" t="s">
         <v>1279</v>
@@ -24751,7 +24751,7 @@
         <v>1277</v>
       </c>
       <c r="E511">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F511" t="s">
         <v>1279</v>
@@ -24786,7 +24786,7 @@
         <v>1277</v>
       </c>
       <c r="E512">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F512" t="s">
         <v>1279</v>
@@ -24821,7 +24821,7 @@
         <v>1277</v>
       </c>
       <c r="E513">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F513" t="s">
         <v>1279</v>
@@ -24856,7 +24856,7 @@
         <v>1277</v>
       </c>
       <c r="E514">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F514" t="s">
         <v>1279</v>
@@ -24891,7 +24891,7 @@
         <v>1278</v>
       </c>
       <c r="E515">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F515" t="s">
         <v>1279</v>
@@ -24929,7 +24929,7 @@
         <v>1278</v>
       </c>
       <c r="E516">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F516" t="s">
         <v>1279</v>
@@ -24964,7 +24964,7 @@
         <v>1278</v>
       </c>
       <c r="E517">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F517" t="s">
         <v>1279</v>
@@ -24999,7 +24999,7 @@
         <v>1278</v>
       </c>
       <c r="E518">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F518" t="s">
         <v>1279</v>
@@ -25037,7 +25037,7 @@
         <v>1278</v>
       </c>
       <c r="E519">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F519" t="s">
         <v>1279</v>
@@ -25072,7 +25072,7 @@
         <v>1278</v>
       </c>
       <c r="E520">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F520" t="s">
         <v>1281</v>

--- a/BacklogGATEAutoCompleto.xlsx
+++ b/BacklogGATEAutoCompleto.xlsx
@@ -6834,7 +6834,7 @@
         <v>1073</v>
       </c>
       <c r="E2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="F2" t="s">
         <v>1279</v>
@@ -6869,7 +6869,7 @@
         <v>1074</v>
       </c>
       <c r="E3">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="F3" t="s">
         <v>1279</v>
@@ -6904,7 +6904,7 @@
         <v>1075</v>
       </c>
       <c r="E4">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="F4" t="s">
         <v>1279</v>
@@ -6939,7 +6939,7 @@
         <v>1076</v>
       </c>
       <c r="E5">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="F5" t="s">
         <v>1279</v>
@@ -6974,7 +6974,7 @@
         <v>1077</v>
       </c>
       <c r="E6">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="F6" t="s">
         <v>1279</v>
@@ -7009,7 +7009,7 @@
         <v>1078</v>
       </c>
       <c r="E7">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="F7" t="s">
         <v>1279</v>
@@ -7044,7 +7044,7 @@
         <v>1079</v>
       </c>
       <c r="E8">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F8" t="s">
         <v>1279</v>
@@ -7079,7 +7079,7 @@
         <v>1080</v>
       </c>
       <c r="E9">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="F9" t="s">
         <v>1279</v>
@@ -7114,7 +7114,7 @@
         <v>1081</v>
       </c>
       <c r="E10">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="F10" t="s">
         <v>1279</v>
@@ -7149,7 +7149,7 @@
         <v>1081</v>
       </c>
       <c r="E11">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="F11" t="s">
         <v>1279</v>
@@ -7184,7 +7184,7 @@
         <v>1082</v>
       </c>
       <c r="E12">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="F12" t="s">
         <v>1279</v>
@@ -7219,7 +7219,7 @@
         <v>1083</v>
       </c>
       <c r="E13">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="F13" t="s">
         <v>1279</v>
@@ -7254,7 +7254,7 @@
         <v>1084</v>
       </c>
       <c r="E14">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F14" t="s">
         <v>1279</v>
@@ -7289,7 +7289,7 @@
         <v>1084</v>
       </c>
       <c r="E15">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F15" t="s">
         <v>1279</v>
@@ -7324,7 +7324,7 @@
         <v>1085</v>
       </c>
       <c r="E16">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="F16" t="s">
         <v>1279</v>
@@ -7359,7 +7359,7 @@
         <v>1085</v>
       </c>
       <c r="E17">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="F17" t="s">
         <v>1279</v>
@@ -7394,7 +7394,7 @@
         <v>1086</v>
       </c>
       <c r="E18">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="F18" t="s">
         <v>1279</v>
@@ -7429,7 +7429,7 @@
         <v>1087</v>
       </c>
       <c r="E19">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="F19" t="s">
         <v>1279</v>
@@ -7464,7 +7464,7 @@
         <v>1088</v>
       </c>
       <c r="E20">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="F20" t="s">
         <v>1279</v>
@@ -7499,7 +7499,7 @@
         <v>1089</v>
       </c>
       <c r="E21">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F21" t="s">
         <v>1279</v>
@@ -7534,7 +7534,7 @@
         <v>1090</v>
       </c>
       <c r="E22">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F22" t="s">
         <v>1279</v>
@@ -7572,7 +7572,7 @@
         <v>1091</v>
       </c>
       <c r="E23">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="F23" t="s">
         <v>1279</v>
@@ -7607,7 +7607,7 @@
         <v>1092</v>
       </c>
       <c r="E24">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="F24" t="s">
         <v>1279</v>
@@ -7642,7 +7642,7 @@
         <v>1093</v>
       </c>
       <c r="E25">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="F25" t="s">
         <v>1279</v>
@@ -7677,7 +7677,7 @@
         <v>1094</v>
       </c>
       <c r="E26">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F26" t="s">
         <v>1279</v>
@@ -7712,7 +7712,7 @@
         <v>1095</v>
       </c>
       <c r="E27">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F27" t="s">
         <v>1279</v>
@@ -7747,7 +7747,7 @@
         <v>1096</v>
       </c>
       <c r="E28">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F28" t="s">
         <v>1279</v>
@@ -7782,7 +7782,7 @@
         <v>1097</v>
       </c>
       <c r="E29">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F29" t="s">
         <v>1279</v>
@@ -7817,7 +7817,7 @@
         <v>1098</v>
       </c>
       <c r="E30">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F30" t="s">
         <v>1279</v>
@@ -7852,7 +7852,7 @@
         <v>1099</v>
       </c>
       <c r="E31">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F31" t="s">
         <v>1279</v>
@@ -7887,7 +7887,7 @@
         <v>1100</v>
       </c>
       <c r="E32">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F32" t="s">
         <v>1279</v>
@@ -7922,7 +7922,7 @@
         <v>1101</v>
       </c>
       <c r="E33">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F33" t="s">
         <v>1279</v>
@@ -7957,7 +7957,7 @@
         <v>1102</v>
       </c>
       <c r="E34">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F34" t="s">
         <v>1279</v>
@@ -7992,7 +7992,7 @@
         <v>1103</v>
       </c>
       <c r="E35">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F35" t="s">
         <v>1279</v>
@@ -8027,7 +8027,7 @@
         <v>1104</v>
       </c>
       <c r="E36">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F36" t="s">
         <v>1279</v>
@@ -8062,7 +8062,7 @@
         <v>1104</v>
       </c>
       <c r="E37">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F37" t="s">
         <v>1279</v>
@@ -8097,7 +8097,7 @@
         <v>1105</v>
       </c>
       <c r="E38">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F38" t="s">
         <v>1279</v>
@@ -8132,7 +8132,7 @@
         <v>1106</v>
       </c>
       <c r="E39">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F39" t="s">
         <v>1279</v>
@@ -8167,7 +8167,7 @@
         <v>1107</v>
       </c>
       <c r="E40">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F40" t="s">
         <v>1279</v>
@@ -8202,7 +8202,7 @@
         <v>1107</v>
       </c>
       <c r="E41">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F41" t="s">
         <v>1279</v>
@@ -8237,7 +8237,7 @@
         <v>1108</v>
       </c>
       <c r="E42">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F42" t="s">
         <v>1279</v>
@@ -8272,7 +8272,7 @@
         <v>1108</v>
       </c>
       <c r="E43">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F43" t="s">
         <v>1279</v>
@@ -8307,7 +8307,7 @@
         <v>1109</v>
       </c>
       <c r="E44">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F44" t="s">
         <v>1279</v>
@@ -8342,7 +8342,7 @@
         <v>1110</v>
       </c>
       <c r="E45">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F45" t="s">
         <v>1279</v>
@@ -8377,7 +8377,7 @@
         <v>1111</v>
       </c>
       <c r="E46">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F46" t="s">
         <v>1279</v>
@@ -8412,7 +8412,7 @@
         <v>1112</v>
       </c>
       <c r="E47">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F47" t="s">
         <v>1279</v>
@@ -8447,7 +8447,7 @@
         <v>1112</v>
       </c>
       <c r="E48">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F48" t="s">
         <v>1279</v>
@@ -8482,7 +8482,7 @@
         <v>1113</v>
       </c>
       <c r="E49">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F49" t="s">
         <v>1279</v>
@@ -8517,7 +8517,7 @@
         <v>1114</v>
       </c>
       <c r="E50">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F50" t="s">
         <v>1279</v>
@@ -8552,7 +8552,7 @@
         <v>1115</v>
       </c>
       <c r="E51">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F51" t="s">
         <v>1279</v>
@@ -8587,7 +8587,7 @@
         <v>1116</v>
       </c>
       <c r="E52">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F52" t="s">
         <v>1279</v>
@@ -8622,7 +8622,7 @@
         <v>1117</v>
       </c>
       <c r="E53">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F53" t="s">
         <v>1279</v>
@@ -8657,7 +8657,7 @@
         <v>1118</v>
       </c>
       <c r="E54">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F54" t="s">
         <v>1279</v>
@@ -8692,7 +8692,7 @@
         <v>1119</v>
       </c>
       <c r="E55">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F55" t="s">
         <v>1279</v>
@@ -8727,7 +8727,7 @@
         <v>1119</v>
       </c>
       <c r="E56">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F56" t="s">
         <v>1279</v>
@@ -8762,7 +8762,7 @@
         <v>1119</v>
       </c>
       <c r="E57">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F57" t="s">
         <v>1279</v>
@@ -8797,7 +8797,7 @@
         <v>1120</v>
       </c>
       <c r="E58">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F58" t="s">
         <v>1279</v>
@@ -8832,7 +8832,7 @@
         <v>1121</v>
       </c>
       <c r="E59">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F59" t="s">
         <v>1279</v>
@@ -8867,7 +8867,7 @@
         <v>1122</v>
       </c>
       <c r="E60">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F60" t="s">
         <v>1279</v>
@@ -8902,7 +8902,7 @@
         <v>1122</v>
       </c>
       <c r="E61">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F61" t="s">
         <v>1279</v>
@@ -8937,7 +8937,7 @@
         <v>1123</v>
       </c>
       <c r="E62">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F62" t="s">
         <v>1279</v>
@@ -8972,7 +8972,7 @@
         <v>1124</v>
       </c>
       <c r="E63">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F63" t="s">
         <v>1279</v>
@@ -9007,7 +9007,7 @@
         <v>1124</v>
       </c>
       <c r="E64">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F64" t="s">
         <v>1279</v>
@@ -9042,7 +9042,7 @@
         <v>1124</v>
       </c>
       <c r="E65">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F65" t="s">
         <v>1279</v>
@@ -9077,7 +9077,7 @@
         <v>1125</v>
       </c>
       <c r="E66">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F66" t="s">
         <v>1279</v>
@@ -9112,7 +9112,7 @@
         <v>1126</v>
       </c>
       <c r="E67">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F67" t="s">
         <v>1279</v>
@@ -9147,7 +9147,7 @@
         <v>1126</v>
       </c>
       <c r="E68">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F68" t="s">
         <v>1279</v>
@@ -9182,7 +9182,7 @@
         <v>1126</v>
       </c>
       <c r="E69">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F69" t="s">
         <v>1280</v>
@@ -9217,7 +9217,7 @@
         <v>1126</v>
       </c>
       <c r="E70">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F70" t="s">
         <v>1279</v>
@@ -9252,7 +9252,7 @@
         <v>1127</v>
       </c>
       <c r="E71">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F71" t="s">
         <v>1279</v>
@@ -9287,7 +9287,7 @@
         <v>1128</v>
       </c>
       <c r="E72">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F72" t="s">
         <v>1279</v>
@@ -9322,7 +9322,7 @@
         <v>1128</v>
       </c>
       <c r="E73">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F73" t="s">
         <v>1279</v>
@@ -9357,7 +9357,7 @@
         <v>1129</v>
       </c>
       <c r="E74">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F74" t="s">
         <v>1279</v>
@@ -9392,7 +9392,7 @@
         <v>1130</v>
       </c>
       <c r="E75">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F75" t="s">
         <v>1279</v>
@@ -9427,7 +9427,7 @@
         <v>1131</v>
       </c>
       <c r="E76">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F76" t="s">
         <v>1279</v>
@@ -9462,7 +9462,7 @@
         <v>1132</v>
       </c>
       <c r="E77">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F77" t="s">
         <v>1279</v>
@@ -9497,7 +9497,7 @@
         <v>1132</v>
       </c>
       <c r="E78">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F78" t="s">
         <v>1279</v>
@@ -9532,7 +9532,7 @@
         <v>1132</v>
       </c>
       <c r="E79">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F79" t="s">
         <v>1279</v>
@@ -9567,7 +9567,7 @@
         <v>1132</v>
       </c>
       <c r="E80">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F80" t="s">
         <v>1279</v>
@@ -9602,7 +9602,7 @@
         <v>1132</v>
       </c>
       <c r="E81">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F81" t="s">
         <v>1279</v>
@@ -9637,7 +9637,7 @@
         <v>1132</v>
       </c>
       <c r="E82">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F82" t="s">
         <v>1279</v>
@@ -9672,7 +9672,7 @@
         <v>1133</v>
       </c>
       <c r="E83">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F83" t="s">
         <v>1279</v>
@@ -9707,7 +9707,7 @@
         <v>1134</v>
       </c>
       <c r="E84">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F84" t="s">
         <v>1279</v>
@@ -9742,7 +9742,7 @@
         <v>1135</v>
       </c>
       <c r="E85">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F85" t="s">
         <v>1279</v>
@@ -9777,7 +9777,7 @@
         <v>1135</v>
       </c>
       <c r="E86">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F86" t="s">
         <v>1279</v>
@@ -9812,7 +9812,7 @@
         <v>1136</v>
       </c>
       <c r="E87">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F87" t="s">
         <v>1281</v>
@@ -9847,7 +9847,7 @@
         <v>1137</v>
       </c>
       <c r="E88">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F88" t="s">
         <v>1279</v>
@@ -9882,7 +9882,7 @@
         <v>1138</v>
       </c>
       <c r="E89">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F89" t="s">
         <v>1279</v>
@@ -9917,7 +9917,7 @@
         <v>1138</v>
       </c>
       <c r="E90">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F90" t="s">
         <v>1279</v>
@@ -9952,7 +9952,7 @@
         <v>1139</v>
       </c>
       <c r="E91">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F91" t="s">
         <v>1279</v>
@@ -9987,7 +9987,7 @@
         <v>1140</v>
       </c>
       <c r="E92">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F92" t="s">
         <v>1279</v>
@@ -10022,7 +10022,7 @@
         <v>1141</v>
       </c>
       <c r="E93">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F93" t="s">
         <v>1279</v>
@@ -10057,7 +10057,7 @@
         <v>1142</v>
       </c>
       <c r="E94">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F94" t="s">
         <v>1279</v>
@@ -10092,7 +10092,7 @@
         <v>1143</v>
       </c>
       <c r="E95">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F95" t="s">
         <v>1279</v>
@@ -10127,7 +10127,7 @@
         <v>1143</v>
       </c>
       <c r="E96">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F96" t="s">
         <v>1279</v>
@@ -10162,7 +10162,7 @@
         <v>1144</v>
       </c>
       <c r="E97">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F97" t="s">
         <v>1279</v>
@@ -10197,7 +10197,7 @@
         <v>1144</v>
       </c>
       <c r="E98">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F98" t="s">
         <v>1279</v>
@@ -10232,7 +10232,7 @@
         <v>1144</v>
       </c>
       <c r="E99">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F99" t="s">
         <v>1279</v>
@@ -10267,7 +10267,7 @@
         <v>1145</v>
       </c>
       <c r="E100">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F100" t="s">
         <v>1279</v>
@@ -10302,7 +10302,7 @@
         <v>1145</v>
       </c>
       <c r="E101">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F101" t="s">
         <v>1279</v>
@@ -10337,7 +10337,7 @@
         <v>1146</v>
       </c>
       <c r="E102">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F102" t="s">
         <v>1279</v>
@@ -10372,7 +10372,7 @@
         <v>1147</v>
       </c>
       <c r="E103">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F103" t="s">
         <v>1279</v>
@@ -10407,7 +10407,7 @@
         <v>1148</v>
       </c>
       <c r="E104">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F104" t="s">
         <v>1279</v>
@@ -10442,7 +10442,7 @@
         <v>1148</v>
       </c>
       <c r="E105">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F105" t="s">
         <v>1279</v>
@@ -10477,7 +10477,7 @@
         <v>1149</v>
       </c>
       <c r="E106">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F106" t="s">
         <v>1279</v>
@@ -10512,7 +10512,7 @@
         <v>1149</v>
       </c>
       <c r="E107">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F107" t="s">
         <v>1279</v>
@@ -10547,7 +10547,7 @@
         <v>1150</v>
       </c>
       <c r="E108">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F108" t="s">
         <v>1279</v>
@@ -10582,7 +10582,7 @@
         <v>1151</v>
       </c>
       <c r="E109">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F109" t="s">
         <v>1279</v>
@@ -10617,7 +10617,7 @@
         <v>1151</v>
       </c>
       <c r="E110">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F110" t="s">
         <v>1279</v>
@@ -10652,7 +10652,7 @@
         <v>1152</v>
       </c>
       <c r="E111">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F111" t="s">
         <v>1279</v>
@@ -10687,7 +10687,7 @@
         <v>1153</v>
       </c>
       <c r="E112">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F112" t="s">
         <v>1279</v>
@@ -10722,7 +10722,7 @@
         <v>1153</v>
       </c>
       <c r="E113">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F113" t="s">
         <v>1279</v>
@@ -10757,7 +10757,7 @@
         <v>1154</v>
       </c>
       <c r="E114">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F114" t="s">
         <v>1279</v>
@@ -10792,7 +10792,7 @@
         <v>1155</v>
       </c>
       <c r="E115">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F115" t="s">
         <v>1279</v>
@@ -10830,7 +10830,7 @@
         <v>1155</v>
       </c>
       <c r="E116">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F116" t="s">
         <v>1279</v>
@@ -10865,7 +10865,7 @@
         <v>1155</v>
       </c>
       <c r="E117">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F117" t="s">
         <v>1279</v>
@@ -10900,7 +10900,7 @@
         <v>1155</v>
       </c>
       <c r="E118">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F118" t="s">
         <v>1279</v>
@@ -10935,7 +10935,7 @@
         <v>1156</v>
       </c>
       <c r="E119">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F119" t="s">
         <v>1280</v>
@@ -10970,7 +10970,7 @@
         <v>1157</v>
       </c>
       <c r="E120">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F120" t="s">
         <v>1279</v>
@@ -11005,7 +11005,7 @@
         <v>1157</v>
       </c>
       <c r="E121">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F121" t="s">
         <v>1279</v>
@@ -11040,7 +11040,7 @@
         <v>1157</v>
       </c>
       <c r="E122">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F122" t="s">
         <v>1279</v>
@@ -11075,7 +11075,7 @@
         <v>1157</v>
       </c>
       <c r="E123">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F123" t="s">
         <v>1279</v>
@@ -11110,7 +11110,7 @@
         <v>1158</v>
       </c>
       <c r="E124">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F124" t="s">
         <v>1279</v>
@@ -11145,7 +11145,7 @@
         <v>1158</v>
       </c>
       <c r="E125">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F125" t="s">
         <v>1279</v>
@@ -11180,7 +11180,7 @@
         <v>1158</v>
       </c>
       <c r="E126">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F126" t="s">
         <v>1279</v>
@@ -11215,7 +11215,7 @@
         <v>1158</v>
       </c>
       <c r="E127">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F127" t="s">
         <v>1279</v>
@@ -11250,7 +11250,7 @@
         <v>1158</v>
       </c>
       <c r="E128">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F128" t="s">
         <v>1279</v>
@@ -11285,7 +11285,7 @@
         <v>1158</v>
       </c>
       <c r="E129">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F129" t="s">
         <v>1279</v>
@@ -11320,7 +11320,7 @@
         <v>1158</v>
       </c>
       <c r="E130">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F130" t="s">
         <v>1279</v>
@@ -11355,7 +11355,7 @@
         <v>1159</v>
       </c>
       <c r="E131">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F131" t="s">
         <v>1279</v>
@@ -11390,7 +11390,7 @@
         <v>1159</v>
       </c>
       <c r="E132">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F132" t="s">
         <v>1279</v>
@@ -11425,7 +11425,7 @@
         <v>1160</v>
       </c>
       <c r="E133">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F133" t="s">
         <v>1279</v>
@@ -11460,7 +11460,7 @@
         <v>1161</v>
       </c>
       <c r="E134">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F134" t="s">
         <v>1279</v>
@@ -11495,7 +11495,7 @@
         <v>1161</v>
       </c>
       <c r="E135">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F135" t="s">
         <v>1279</v>
@@ -11530,7 +11530,7 @@
         <v>1161</v>
       </c>
       <c r="E136">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F136" t="s">
         <v>1279</v>
@@ -11565,7 +11565,7 @@
         <v>1162</v>
       </c>
       <c r="E137">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F137" t="s">
         <v>1279</v>
@@ -11600,7 +11600,7 @@
         <v>1162</v>
       </c>
       <c r="E138">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F138" t="s">
         <v>1279</v>
@@ -11635,7 +11635,7 @@
         <v>1162</v>
       </c>
       <c r="E139">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F139" t="s">
         <v>1279</v>
@@ -11670,7 +11670,7 @@
         <v>1162</v>
       </c>
       <c r="E140">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F140" t="s">
         <v>1279</v>
@@ -11705,7 +11705,7 @@
         <v>1162</v>
       </c>
       <c r="E141">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F141" t="s">
         <v>1279</v>
@@ -11740,7 +11740,7 @@
         <v>1162</v>
       </c>
       <c r="E142">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F142" t="s">
         <v>1279</v>
@@ -11775,7 +11775,7 @@
         <v>1162</v>
       </c>
       <c r="E143">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F143" t="s">
         <v>1279</v>
@@ -11810,7 +11810,7 @@
         <v>1162</v>
       </c>
       <c r="E144">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F144" t="s">
         <v>1279</v>
@@ -11845,7 +11845,7 @@
         <v>1162</v>
       </c>
       <c r="E145">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F145" t="s">
         <v>1279</v>
@@ -11880,7 +11880,7 @@
         <v>1163</v>
       </c>
       <c r="E146">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F146" t="s">
         <v>1279</v>
@@ -11915,7 +11915,7 @@
         <v>1163</v>
       </c>
       <c r="E147">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F147" t="s">
         <v>1279</v>
@@ -11950,7 +11950,7 @@
         <v>1163</v>
       </c>
       <c r="E148">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F148" t="s">
         <v>1279</v>
@@ -11985,7 +11985,7 @@
         <v>1164</v>
       </c>
       <c r="E149">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F149" t="s">
         <v>1279</v>
@@ -12020,7 +12020,7 @@
         <v>1164</v>
       </c>
       <c r="E150">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F150" t="s">
         <v>1280</v>
@@ -12055,7 +12055,7 @@
         <v>1164</v>
       </c>
       <c r="E151">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F151" t="s">
         <v>1279</v>
@@ -12090,7 +12090,7 @@
         <v>1165</v>
       </c>
       <c r="E152">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F152" t="s">
         <v>1279</v>
@@ -12125,7 +12125,7 @@
         <v>1165</v>
       </c>
       <c r="E153">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F153" t="s">
         <v>1279</v>
@@ -12160,7 +12160,7 @@
         <v>1166</v>
       </c>
       <c r="E154">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F154" t="s">
         <v>1279</v>
@@ -12195,7 +12195,7 @@
         <v>1166</v>
       </c>
       <c r="E155">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F155" t="s">
         <v>1279</v>
@@ -12230,7 +12230,7 @@
         <v>1167</v>
       </c>
       <c r="E156">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F156" t="s">
         <v>1279</v>
@@ -12265,7 +12265,7 @@
         <v>1167</v>
       </c>
       <c r="E157">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F157" t="s">
         <v>1279</v>
@@ -12300,7 +12300,7 @@
         <v>1168</v>
       </c>
       <c r="E158">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F158" t="s">
         <v>1279</v>
@@ -12335,7 +12335,7 @@
         <v>1168</v>
       </c>
       <c r="E159">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F159" t="s">
         <v>1279</v>
@@ -12370,7 +12370,7 @@
         <v>1168</v>
       </c>
       <c r="E160">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F160" t="s">
         <v>1279</v>
@@ -12405,7 +12405,7 @@
         <v>1169</v>
       </c>
       <c r="E161">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F161" t="s">
         <v>1279</v>
@@ -12440,7 +12440,7 @@
         <v>1169</v>
       </c>
       <c r="E162">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F162" t="s">
         <v>1279</v>
@@ -12475,7 +12475,7 @@
         <v>1170</v>
       </c>
       <c r="E163">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F163" t="s">
         <v>1279</v>
@@ -12510,7 +12510,7 @@
         <v>1171</v>
       </c>
       <c r="E164">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F164" t="s">
         <v>1279</v>
@@ -12545,7 +12545,7 @@
         <v>1171</v>
       </c>
       <c r="E165">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F165" t="s">
         <v>1279</v>
@@ -12580,7 +12580,7 @@
         <v>1171</v>
       </c>
       <c r="E166">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F166" t="s">
         <v>1279</v>
@@ -12615,7 +12615,7 @@
         <v>1171</v>
       </c>
       <c r="E167">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F167" t="s">
         <v>1279</v>
@@ -12650,7 +12650,7 @@
         <v>1172</v>
       </c>
       <c r="E168">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F168" t="s">
         <v>1279</v>
@@ -12685,7 +12685,7 @@
         <v>1173</v>
       </c>
       <c r="E169">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F169" t="s">
         <v>1279</v>
@@ -12720,7 +12720,7 @@
         <v>1173</v>
       </c>
       <c r="E170">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F170" t="s">
         <v>1279</v>
@@ -12755,7 +12755,7 @@
         <v>1173</v>
       </c>
       <c r="E171">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F171" t="s">
         <v>1279</v>
@@ -12790,7 +12790,7 @@
         <v>1173</v>
       </c>
       <c r="E172">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F172" t="s">
         <v>1279</v>
@@ -12825,7 +12825,7 @@
         <v>1173</v>
       </c>
       <c r="E173">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F173" t="s">
         <v>1279</v>
@@ -12860,7 +12860,7 @@
         <v>1174</v>
       </c>
       <c r="E174">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F174" t="s">
         <v>1279</v>
@@ -12895,7 +12895,7 @@
         <v>1174</v>
       </c>
       <c r="E175">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F175" t="s">
         <v>1279</v>
@@ -12930,7 +12930,7 @@
         <v>1174</v>
       </c>
       <c r="E176">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F176" t="s">
         <v>1279</v>
@@ -12965,7 +12965,7 @@
         <v>1174</v>
       </c>
       <c r="E177">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F177" t="s">
         <v>1279</v>
@@ -13000,7 +13000,7 @@
         <v>1174</v>
       </c>
       <c r="E178">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F178" t="s">
         <v>1279</v>
@@ -13035,7 +13035,7 @@
         <v>1174</v>
       </c>
       <c r="E179">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F179" t="s">
         <v>1279</v>
@@ -13070,7 +13070,7 @@
         <v>1175</v>
       </c>
       <c r="E180">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F180" t="s">
         <v>1279</v>
@@ -13105,7 +13105,7 @@
         <v>1175</v>
       </c>
       <c r="E181">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F181" t="s">
         <v>1279</v>
@@ -13140,7 +13140,7 @@
         <v>1175</v>
       </c>
       <c r="E182">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F182" t="s">
         <v>1279</v>
@@ -13175,7 +13175,7 @@
         <v>1175</v>
       </c>
       <c r="E183">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F183" t="s">
         <v>1279</v>
@@ -13210,7 +13210,7 @@
         <v>1176</v>
       </c>
       <c r="E184">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F184" t="s">
         <v>1279</v>
@@ -13245,7 +13245,7 @@
         <v>1176</v>
       </c>
       <c r="E185">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F185" t="s">
         <v>1279</v>
@@ -13280,7 +13280,7 @@
         <v>1177</v>
       </c>
       <c r="E186">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F186" t="s">
         <v>1279</v>
@@ -13315,7 +13315,7 @@
         <v>1178</v>
       </c>
       <c r="E187">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F187" t="s">
         <v>1279</v>
@@ -13350,7 +13350,7 @@
         <v>1178</v>
       </c>
       <c r="E188">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F188" t="s">
         <v>1279</v>
@@ -13385,7 +13385,7 @@
         <v>1179</v>
       </c>
       <c r="E189">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F189" t="s">
         <v>1279</v>
@@ -13420,7 +13420,7 @@
         <v>1180</v>
       </c>
       <c r="E190">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F190" t="s">
         <v>1279</v>
@@ -13455,7 +13455,7 @@
         <v>1180</v>
       </c>
       <c r="E191">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F191" t="s">
         <v>1279</v>
@@ -13490,7 +13490,7 @@
         <v>1181</v>
       </c>
       <c r="E192">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F192" t="s">
         <v>1279</v>
@@ -13525,7 +13525,7 @@
         <v>1181</v>
       </c>
       <c r="E193">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F193" t="s">
         <v>1279</v>
@@ -13560,7 +13560,7 @@
         <v>1182</v>
       </c>
       <c r="E194">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F194" t="s">
         <v>1279</v>
@@ -13595,7 +13595,7 @@
         <v>1183</v>
       </c>
       <c r="E195">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F195" t="s">
         <v>1279</v>
@@ -13630,7 +13630,7 @@
         <v>1183</v>
       </c>
       <c r="E196">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F196" t="s">
         <v>1279</v>
@@ -13665,7 +13665,7 @@
         <v>1183</v>
       </c>
       <c r="E197">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F197" t="s">
         <v>1279</v>
@@ -13700,7 +13700,7 @@
         <v>1184</v>
       </c>
       <c r="E198">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F198" t="s">
         <v>1279</v>
@@ -13735,7 +13735,7 @@
         <v>1184</v>
       </c>
       <c r="E199">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F199" t="s">
         <v>1279</v>
@@ -13770,7 +13770,7 @@
         <v>1185</v>
       </c>
       <c r="E200">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F200" t="s">
         <v>1279</v>
@@ -13805,7 +13805,7 @@
         <v>1186</v>
       </c>
       <c r="E201">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F201" t="s">
         <v>1279</v>
@@ -13840,7 +13840,7 @@
         <v>1186</v>
       </c>
       <c r="E202">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F202" t="s">
         <v>1279</v>
@@ -13875,7 +13875,7 @@
         <v>1186</v>
       </c>
       <c r="E203">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F203" t="s">
         <v>1279</v>
@@ -13910,7 +13910,7 @@
         <v>1187</v>
       </c>
       <c r="E204">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F204" t="s">
         <v>1279</v>
@@ -13945,7 +13945,7 @@
         <v>1187</v>
       </c>
       <c r="E205">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F205" t="s">
         <v>1279</v>
@@ -13980,7 +13980,7 @@
         <v>1188</v>
       </c>
       <c r="E206">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F206" t="s">
         <v>1279</v>
@@ -14015,7 +14015,7 @@
         <v>1188</v>
       </c>
       <c r="E207">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F207" t="s">
         <v>1281</v>
@@ -14050,7 +14050,7 @@
         <v>1188</v>
       </c>
       <c r="E208">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F208" t="s">
         <v>1279</v>
@@ -14085,7 +14085,7 @@
         <v>1189</v>
       </c>
       <c r="E209">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F209" t="s">
         <v>1279</v>
@@ -14120,7 +14120,7 @@
         <v>1189</v>
       </c>
       <c r="E210">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F210" t="s">
         <v>1279</v>
@@ -14158,7 +14158,7 @@
         <v>1189</v>
       </c>
       <c r="E211">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F211" t="s">
         <v>1279</v>
@@ -14193,7 +14193,7 @@
         <v>1189</v>
       </c>
       <c r="E212">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F212" t="s">
         <v>1279</v>
@@ -14228,7 +14228,7 @@
         <v>1189</v>
       </c>
       <c r="E213">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F213" t="s">
         <v>1279</v>
@@ -14263,7 +14263,7 @@
         <v>1189</v>
       </c>
       <c r="E214">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F214" t="s">
         <v>1279</v>
@@ -14298,7 +14298,7 @@
         <v>1190</v>
       </c>
       <c r="E215">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F215" t="s">
         <v>1279</v>
@@ -14333,7 +14333,7 @@
         <v>1190</v>
       </c>
       <c r="E216">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F216" t="s">
         <v>1279</v>
@@ -14368,7 +14368,7 @@
         <v>1190</v>
       </c>
       <c r="E217">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F217" t="s">
         <v>1279</v>
@@ -14403,7 +14403,7 @@
         <v>1191</v>
       </c>
       <c r="E218">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F218" t="s">
         <v>1279</v>
@@ -14438,7 +14438,7 @@
         <v>1191</v>
       </c>
       <c r="E219">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F219" t="s">
         <v>1279</v>
@@ -14473,7 +14473,7 @@
         <v>1191</v>
       </c>
       <c r="E220">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F220" t="s">
         <v>1279</v>
@@ -14508,7 +14508,7 @@
         <v>1192</v>
       </c>
       <c r="E221">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F221" t="s">
         <v>1279</v>
@@ -14543,7 +14543,7 @@
         <v>1192</v>
       </c>
       <c r="E222">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F222" t="s">
         <v>1279</v>
@@ -14578,7 +14578,7 @@
         <v>1192</v>
       </c>
       <c r="E223">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F223" t="s">
         <v>1279</v>
@@ -14613,7 +14613,7 @@
         <v>1193</v>
       </c>
       <c r="E224">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F224" t="s">
         <v>1279</v>
@@ -14648,7 +14648,7 @@
         <v>1193</v>
       </c>
       <c r="E225">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F225" t="s">
         <v>1279</v>
@@ -14683,7 +14683,7 @@
         <v>1193</v>
       </c>
       <c r="E226">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F226" t="s">
         <v>1279</v>
@@ -14718,7 +14718,7 @@
         <v>1193</v>
       </c>
       <c r="E227">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F227" t="s">
         <v>1279</v>
@@ -14753,7 +14753,7 @@
         <v>1193</v>
       </c>
       <c r="E228">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F228" t="s">
         <v>1279</v>
@@ -14788,7 +14788,7 @@
         <v>1193</v>
       </c>
       <c r="E229">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F229" t="s">
         <v>1279</v>
@@ -14823,7 +14823,7 @@
         <v>1194</v>
       </c>
       <c r="E230">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F230" t="s">
         <v>1279</v>
@@ -14858,7 +14858,7 @@
         <v>1195</v>
       </c>
       <c r="E231">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F231" t="s">
         <v>1279</v>
@@ -14893,7 +14893,7 @@
         <v>1195</v>
       </c>
       <c r="E232">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F232" t="s">
         <v>1282</v>
@@ -14928,7 +14928,7 @@
         <v>1195</v>
       </c>
       <c r="E233">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F233" t="s">
         <v>1279</v>
@@ -14963,7 +14963,7 @@
         <v>1195</v>
       </c>
       <c r="E234">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F234" t="s">
         <v>1279</v>
@@ -14998,7 +14998,7 @@
         <v>1196</v>
       </c>
       <c r="E235">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F235" t="s">
         <v>1279</v>
@@ -15033,7 +15033,7 @@
         <v>1196</v>
       </c>
       <c r="E236">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F236" t="s">
         <v>1279</v>
@@ -15068,7 +15068,7 @@
         <v>1196</v>
       </c>
       <c r="E237">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F237" t="s">
         <v>1279</v>
@@ -15103,7 +15103,7 @@
         <v>1196</v>
       </c>
       <c r="E238">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F238" t="s">
         <v>1279</v>
@@ -15138,7 +15138,7 @@
         <v>1197</v>
       </c>
       <c r="E239">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F239" t="s">
         <v>1279</v>
@@ -15176,7 +15176,7 @@
         <v>1198</v>
       </c>
       <c r="E240">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F240" t="s">
         <v>1279</v>
@@ -15211,7 +15211,7 @@
         <v>1198</v>
       </c>
       <c r="E241">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F241" t="s">
         <v>1279</v>
@@ -15246,7 +15246,7 @@
         <v>1198</v>
       </c>
       <c r="E242">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F242" t="s">
         <v>1279</v>
@@ -15281,7 +15281,7 @@
         <v>1198</v>
       </c>
       <c r="E243">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F243" t="s">
         <v>1279</v>
@@ -15319,7 +15319,7 @@
         <v>1198</v>
       </c>
       <c r="E244">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F244" t="s">
         <v>1279</v>
@@ -15354,7 +15354,7 @@
         <v>1199</v>
       </c>
       <c r="E245">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F245" t="s">
         <v>1279</v>
@@ -15389,7 +15389,7 @@
         <v>1199</v>
       </c>
       <c r="E246">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F246" t="s">
         <v>1279</v>
@@ -15424,7 +15424,7 @@
         <v>1200</v>
       </c>
       <c r="E247">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F247" t="s">
         <v>1279</v>
@@ -15459,7 +15459,7 @@
         <v>1200</v>
       </c>
       <c r="E248">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F248" t="s">
         <v>1279</v>
@@ -15494,7 +15494,7 @@
         <v>1200</v>
       </c>
       <c r="E249">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F249" t="s">
         <v>1279</v>
@@ -15529,7 +15529,7 @@
         <v>1201</v>
       </c>
       <c r="E250">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F250" t="s">
         <v>1279</v>
@@ -15564,7 +15564,7 @@
         <v>1201</v>
       </c>
       <c r="E251">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F251" t="s">
         <v>1279</v>
@@ -15599,7 +15599,7 @@
         <v>1202</v>
       </c>
       <c r="E252">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F252" t="s">
         <v>1279</v>
@@ -15634,7 +15634,7 @@
         <v>1203</v>
       </c>
       <c r="E253">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F253" t="s">
         <v>1279</v>
@@ -15669,7 +15669,7 @@
         <v>1203</v>
       </c>
       <c r="E254">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F254" t="s">
         <v>1279</v>
@@ -15704,7 +15704,7 @@
         <v>1203</v>
       </c>
       <c r="E255">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F255" t="s">
         <v>1279</v>
@@ -15739,7 +15739,7 @@
         <v>1203</v>
       </c>
       <c r="E256">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F256" t="s">
         <v>1279</v>
@@ -15774,7 +15774,7 @@
         <v>1204</v>
       </c>
       <c r="E257">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F257" t="s">
         <v>1279</v>
@@ -15809,7 +15809,7 @@
         <v>1204</v>
       </c>
       <c r="E258">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F258" t="s">
         <v>1279</v>
@@ -15844,7 +15844,7 @@
         <v>1204</v>
       </c>
       <c r="E259">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F259" t="s">
         <v>1279</v>
@@ -15879,7 +15879,7 @@
         <v>1205</v>
       </c>
       <c r="E260">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F260" t="s">
         <v>1279</v>
@@ -15914,7 +15914,7 @@
         <v>1206</v>
       </c>
       <c r="E261">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F261" t="s">
         <v>1279</v>
@@ -15949,7 +15949,7 @@
         <v>1206</v>
       </c>
       <c r="E262">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F262" t="s">
         <v>1279</v>
@@ -15984,7 +15984,7 @@
         <v>1206</v>
       </c>
       <c r="E263">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F263" t="s">
         <v>1279</v>
@@ -16019,7 +16019,7 @@
         <v>1207</v>
       </c>
       <c r="E264">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F264" t="s">
         <v>1279</v>
@@ -16054,7 +16054,7 @@
         <v>1207</v>
       </c>
       <c r="E265">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F265" t="s">
         <v>1279</v>
@@ -16089,7 +16089,7 @@
         <v>1207</v>
       </c>
       <c r="E266">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F266" t="s">
         <v>1279</v>
@@ -16124,7 +16124,7 @@
         <v>1208</v>
       </c>
       <c r="E267">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F267" t="s">
         <v>1279</v>
@@ -16159,7 +16159,7 @@
         <v>1209</v>
       </c>
       <c r="E268">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F268" t="s">
         <v>1279</v>
@@ -16194,7 +16194,7 @@
         <v>1210</v>
       </c>
       <c r="E269">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F269" t="s">
         <v>1279</v>
@@ -16229,7 +16229,7 @@
         <v>1210</v>
       </c>
       <c r="E270">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F270" t="s">
         <v>1279</v>
@@ -16264,7 +16264,7 @@
         <v>1210</v>
       </c>
       <c r="E271">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F271" t="s">
         <v>1279</v>
@@ -16299,7 +16299,7 @@
         <v>1210</v>
       </c>
       <c r="E272">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F272" t="s">
         <v>1279</v>
@@ -16334,7 +16334,7 @@
         <v>1211</v>
       </c>
       <c r="E273">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F273" t="s">
         <v>1279</v>
@@ -16369,7 +16369,7 @@
         <v>1212</v>
       </c>
       <c r="E274">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F274" t="s">
         <v>1279</v>
@@ -16404,7 +16404,7 @@
         <v>1212</v>
       </c>
       <c r="E275">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F275" t="s">
         <v>1279</v>
@@ -16439,7 +16439,7 @@
         <v>1213</v>
       </c>
       <c r="E276">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F276" t="s">
         <v>1279</v>
@@ -16474,7 +16474,7 @@
         <v>1214</v>
       </c>
       <c r="E277">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F277" t="s">
         <v>1279</v>
@@ -16509,7 +16509,7 @@
         <v>1215</v>
       </c>
       <c r="E278">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F278" t="s">
         <v>1279</v>
@@ -16544,7 +16544,7 @@
         <v>1215</v>
       </c>
       <c r="E279">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F279" t="s">
         <v>1279</v>
@@ -16579,7 +16579,7 @@
         <v>1216</v>
       </c>
       <c r="E280">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F280" t="s">
         <v>1279</v>
@@ -16614,7 +16614,7 @@
         <v>1216</v>
       </c>
       <c r="E281">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F281" t="s">
         <v>1279</v>
@@ -16649,7 +16649,7 @@
         <v>1216</v>
       </c>
       <c r="E282">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F282" t="s">
         <v>1279</v>
@@ -16684,7 +16684,7 @@
         <v>1217</v>
       </c>
       <c r="E283">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F283" t="s">
         <v>1279</v>
@@ -16719,7 +16719,7 @@
         <v>1217</v>
       </c>
       <c r="E284">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F284" t="s">
         <v>1279</v>
@@ -16754,7 +16754,7 @@
         <v>1217</v>
       </c>
       <c r="E285">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F285" t="s">
         <v>1279</v>
@@ -16789,7 +16789,7 @@
         <v>1217</v>
       </c>
       <c r="E286">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F286" t="s">
         <v>1279</v>
@@ -16824,7 +16824,7 @@
         <v>1217</v>
       </c>
       <c r="E287">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F287" t="s">
         <v>1279</v>
@@ -16859,7 +16859,7 @@
         <v>1217</v>
       </c>
       <c r="E288">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F288" t="s">
         <v>1279</v>
@@ -16894,7 +16894,7 @@
         <v>1217</v>
       </c>
       <c r="E289">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F289" t="s">
         <v>1279</v>
@@ -16929,7 +16929,7 @@
         <v>1217</v>
       </c>
       <c r="E290">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F290" t="s">
         <v>1279</v>
@@ -16964,7 +16964,7 @@
         <v>1218</v>
       </c>
       <c r="E291">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F291" t="s">
         <v>1279</v>
@@ -16999,7 +16999,7 @@
         <v>1218</v>
       </c>
       <c r="E292">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F292" t="s">
         <v>1279</v>
@@ -17034,7 +17034,7 @@
         <v>1218</v>
       </c>
       <c r="E293">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F293" t="s">
         <v>1279</v>
@@ -17069,7 +17069,7 @@
         <v>1219</v>
       </c>
       <c r="E294">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F294" t="s">
         <v>1279</v>
@@ -17104,7 +17104,7 @@
         <v>1220</v>
       </c>
       <c r="E295">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F295" t="s">
         <v>1279</v>
@@ -17139,7 +17139,7 @@
         <v>1220</v>
       </c>
       <c r="E296">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F296" t="s">
         <v>1279</v>
@@ -17174,7 +17174,7 @@
         <v>1220</v>
       </c>
       <c r="E297">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F297" t="s">
         <v>1279</v>
@@ -17209,7 +17209,7 @@
         <v>1220</v>
       </c>
       <c r="E298">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F298" t="s">
         <v>1283</v>
@@ -17247,7 +17247,7 @@
         <v>1220</v>
       </c>
       <c r="E299">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F299" t="s">
         <v>1279</v>
@@ -17282,7 +17282,7 @@
         <v>1220</v>
       </c>
       <c r="E300">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F300" t="s">
         <v>1279</v>
@@ -17317,7 +17317,7 @@
         <v>1221</v>
       </c>
       <c r="E301">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F301" t="s">
         <v>1279</v>
@@ -17352,7 +17352,7 @@
         <v>1221</v>
       </c>
       <c r="E302">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F302" t="s">
         <v>1279</v>
@@ -17387,7 +17387,7 @@
         <v>1221</v>
       </c>
       <c r="E303">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F303" t="s">
         <v>1279</v>
@@ -17425,7 +17425,7 @@
         <v>1221</v>
       </c>
       <c r="E304">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F304" t="s">
         <v>1279</v>
@@ -17460,7 +17460,7 @@
         <v>1221</v>
       </c>
       <c r="E305">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F305" t="s">
         <v>1279</v>
@@ -17495,7 +17495,7 @@
         <v>1221</v>
       </c>
       <c r="E306">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F306" t="s">
         <v>1279</v>
@@ -17530,7 +17530,7 @@
         <v>1221</v>
       </c>
       <c r="E307">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F307" t="s">
         <v>1279</v>
@@ -17565,7 +17565,7 @@
         <v>1221</v>
       </c>
       <c r="E308">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F308" t="s">
         <v>1279</v>
@@ -17600,7 +17600,7 @@
         <v>1222</v>
       </c>
       <c r="E309">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F309" t="s">
         <v>1280</v>
@@ -17635,7 +17635,7 @@
         <v>1223</v>
       </c>
       <c r="E310">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F310" t="s">
         <v>1283</v>
@@ -17670,7 +17670,7 @@
         <v>1224</v>
       </c>
       <c r="E311">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F311" t="s">
         <v>1279</v>
@@ -17705,7 +17705,7 @@
         <v>1224</v>
       </c>
       <c r="E312">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F312" t="s">
         <v>1279</v>
@@ -17740,7 +17740,7 @@
         <v>1225</v>
       </c>
       <c r="E313">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F313" t="s">
         <v>1279</v>
@@ -17775,7 +17775,7 @@
         <v>1226</v>
       </c>
       <c r="E314">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F314" t="s">
         <v>1282</v>
@@ -17810,7 +17810,7 @@
         <v>1226</v>
       </c>
       <c r="E315">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F315" t="s">
         <v>1279</v>
@@ -17845,7 +17845,7 @@
         <v>1226</v>
       </c>
       <c r="E316">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F316" t="s">
         <v>1279</v>
@@ -17880,7 +17880,7 @@
         <v>1226</v>
       </c>
       <c r="E317">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F317" t="s">
         <v>1279</v>
@@ -17915,7 +17915,7 @@
         <v>1227</v>
       </c>
       <c r="E318">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F318" t="s">
         <v>1279</v>
@@ -17950,7 +17950,7 @@
         <v>1228</v>
       </c>
       <c r="E319">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F319" t="s">
         <v>1279</v>
@@ -17985,7 +17985,7 @@
         <v>1228</v>
       </c>
       <c r="E320">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F320" t="s">
         <v>1279</v>
@@ -18020,7 +18020,7 @@
         <v>1229</v>
       </c>
       <c r="E321">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F321" t="s">
         <v>1279</v>
@@ -18055,7 +18055,7 @@
         <v>1230</v>
       </c>
       <c r="E322">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F322" t="s">
         <v>1279</v>
@@ -18090,7 +18090,7 @@
         <v>1230</v>
       </c>
       <c r="E323">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F323" t="s">
         <v>1279</v>
@@ -18125,7 +18125,7 @@
         <v>1230</v>
       </c>
       <c r="E324">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F324" t="s">
         <v>1279</v>
@@ -18160,7 +18160,7 @@
         <v>1230</v>
       </c>
       <c r="E325">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F325" t="s">
         <v>1279</v>
@@ -18195,7 +18195,7 @@
         <v>1230</v>
       </c>
       <c r="E326">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F326" t="s">
         <v>1279</v>
@@ -18230,7 +18230,7 @@
         <v>1230</v>
       </c>
       <c r="E327">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F327" t="s">
         <v>1279</v>
@@ -18265,7 +18265,7 @@
         <v>1230</v>
       </c>
       <c r="E328">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F328" t="s">
         <v>1279</v>
@@ -18300,7 +18300,7 @@
         <v>1231</v>
       </c>
       <c r="E329">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F329" t="s">
         <v>1279</v>
@@ -18335,7 +18335,7 @@
         <v>1231</v>
       </c>
       <c r="E330">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F330" t="s">
         <v>1279</v>
@@ -18370,7 +18370,7 @@
         <v>1231</v>
       </c>
       <c r="E331">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F331" t="s">
         <v>1280</v>
@@ -18405,7 +18405,7 @@
         <v>1232</v>
       </c>
       <c r="E332">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F332" t="s">
         <v>1279</v>
@@ -18440,7 +18440,7 @@
         <v>1232</v>
       </c>
       <c r="E333">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F333" t="s">
         <v>1279</v>
@@ -18475,7 +18475,7 @@
         <v>1232</v>
       </c>
       <c r="E334">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F334" t="s">
         <v>1279</v>
@@ -18510,7 +18510,7 @@
         <v>1232</v>
       </c>
       <c r="E335">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F335" t="s">
         <v>1279</v>
@@ -18545,7 +18545,7 @@
         <v>1232</v>
       </c>
       <c r="E336">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F336" t="s">
         <v>1279</v>
@@ -18580,7 +18580,7 @@
         <v>1232</v>
       </c>
       <c r="E337">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F337" t="s">
         <v>1282</v>
@@ -18615,7 +18615,7 @@
         <v>1233</v>
       </c>
       <c r="E338">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F338" t="s">
         <v>1279</v>
@@ -18650,7 +18650,7 @@
         <v>1233</v>
       </c>
       <c r="E339">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F339" t="s">
         <v>1279</v>
@@ -18685,7 +18685,7 @@
         <v>1233</v>
       </c>
       <c r="E340">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F340" t="s">
         <v>1279</v>
@@ -18720,7 +18720,7 @@
         <v>1234</v>
       </c>
       <c r="E341">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F341" t="s">
         <v>1282</v>
@@ -18755,7 +18755,7 @@
         <v>1234</v>
       </c>
       <c r="E342">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F342" t="s">
         <v>1279</v>
@@ -18790,7 +18790,7 @@
         <v>1234</v>
       </c>
       <c r="E343">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F343" t="s">
         <v>1279</v>
@@ -18825,7 +18825,7 @@
         <v>1235</v>
       </c>
       <c r="E344">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F344" t="s">
         <v>1279</v>
@@ -18860,7 +18860,7 @@
         <v>1235</v>
       </c>
       <c r="E345">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F345" t="s">
         <v>1279</v>
@@ -18895,7 +18895,7 @@
         <v>1235</v>
       </c>
       <c r="E346">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F346" t="s">
         <v>1279</v>
@@ -18930,7 +18930,7 @@
         <v>1235</v>
       </c>
       <c r="E347">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F347" t="s">
         <v>1279</v>
@@ -18965,7 +18965,7 @@
         <v>1235</v>
       </c>
       <c r="E348">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F348" t="s">
         <v>1281</v>
@@ -19000,7 +19000,7 @@
         <v>1235</v>
       </c>
       <c r="E349">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F349" t="s">
         <v>1279</v>
@@ -19035,7 +19035,7 @@
         <v>1236</v>
       </c>
       <c r="E350">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F350" t="s">
         <v>1279</v>
@@ -19070,7 +19070,7 @@
         <v>1236</v>
       </c>
       <c r="E351">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F351" t="s">
         <v>1279</v>
@@ -19105,7 +19105,7 @@
         <v>1236</v>
       </c>
       <c r="E352">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F352" t="s">
         <v>1279</v>
@@ -19140,7 +19140,7 @@
         <v>1236</v>
       </c>
       <c r="E353">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F353" t="s">
         <v>1279</v>
@@ -19175,7 +19175,7 @@
         <v>1237</v>
       </c>
       <c r="E354">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F354" t="s">
         <v>1279</v>
@@ -19210,7 +19210,7 @@
         <v>1237</v>
       </c>
       <c r="E355">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F355" t="s">
         <v>1279</v>
@@ -19245,7 +19245,7 @@
         <v>1237</v>
       </c>
       <c r="E356">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F356" t="s">
         <v>1279</v>
@@ -19280,7 +19280,7 @@
         <v>1237</v>
       </c>
       <c r="E357">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F357" t="s">
         <v>1279</v>
@@ -19315,7 +19315,7 @@
         <v>1237</v>
       </c>
       <c r="E358">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F358" t="s">
         <v>1279</v>
@@ -19353,7 +19353,7 @@
         <v>1238</v>
       </c>
       <c r="E359">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F359" t="s">
         <v>1279</v>
@@ -19388,7 +19388,7 @@
         <v>1238</v>
       </c>
       <c r="E360">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F360" t="s">
         <v>1279</v>
@@ -19423,7 +19423,7 @@
         <v>1238</v>
       </c>
       <c r="E361">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F361" t="s">
         <v>1279</v>
@@ -19458,7 +19458,7 @@
         <v>1238</v>
       </c>
       <c r="E362">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F362" t="s">
         <v>1279</v>
@@ -19493,7 +19493,7 @@
         <v>1238</v>
       </c>
       <c r="E363">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F363" t="s">
         <v>1279</v>
@@ -19528,7 +19528,7 @@
         <v>1238</v>
       </c>
       <c r="E364">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F364" t="s">
         <v>1279</v>
@@ -19563,7 +19563,7 @@
         <v>1239</v>
       </c>
       <c r="E365">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F365" t="s">
         <v>1280</v>
@@ -19598,7 +19598,7 @@
         <v>1240</v>
       </c>
       <c r="E366">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F366" t="s">
         <v>1279</v>
@@ -19633,7 +19633,7 @@
         <v>1241</v>
       </c>
       <c r="E367">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F367" t="s">
         <v>1281</v>
@@ -19671,7 +19671,7 @@
         <v>1242</v>
       </c>
       <c r="E368">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F368" t="s">
         <v>1279</v>
@@ -19706,7 +19706,7 @@
         <v>1242</v>
       </c>
       <c r="E369">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F369" t="s">
         <v>1279</v>
@@ -19741,7 +19741,7 @@
         <v>1242</v>
       </c>
       <c r="E370">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F370" t="s">
         <v>1279</v>
@@ -19776,7 +19776,7 @@
         <v>1243</v>
       </c>
       <c r="E371">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F371" t="s">
         <v>1279</v>
@@ -19811,7 +19811,7 @@
         <v>1243</v>
       </c>
       <c r="E372">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F372" t="s">
         <v>1279</v>
@@ -19846,7 +19846,7 @@
         <v>1244</v>
       </c>
       <c r="E373">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F373" t="s">
         <v>1279</v>
@@ -19881,7 +19881,7 @@
         <v>1244</v>
       </c>
       <c r="E374">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F374" t="s">
         <v>1283</v>
@@ -19919,7 +19919,7 @@
         <v>1244</v>
       </c>
       <c r="E375">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F375" t="s">
         <v>1279</v>
@@ -19954,7 +19954,7 @@
         <v>1244</v>
       </c>
       <c r="E376">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F376" t="s">
         <v>1283</v>
@@ -19989,7 +19989,7 @@
         <v>1245</v>
       </c>
       <c r="E377">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F377" t="s">
         <v>1279</v>
@@ -20024,7 +20024,7 @@
         <v>1246</v>
       </c>
       <c r="E378">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F378" t="s">
         <v>1279</v>
@@ -20059,7 +20059,7 @@
         <v>1246</v>
       </c>
       <c r="E379">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F379" t="s">
         <v>1279</v>
@@ -20094,7 +20094,7 @@
         <v>1246</v>
       </c>
       <c r="E380">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F380" t="s">
         <v>1279</v>
@@ -20129,7 +20129,7 @@
         <v>1246</v>
       </c>
       <c r="E381">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F381" t="s">
         <v>1279</v>
@@ -20164,7 +20164,7 @@
         <v>1247</v>
       </c>
       <c r="E382">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F382" t="s">
         <v>1283</v>
@@ -20199,7 +20199,7 @@
         <v>1247</v>
       </c>
       <c r="E383">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F383" t="s">
         <v>1279</v>
@@ -20234,7 +20234,7 @@
         <v>1247</v>
       </c>
       <c r="E384">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F384" t="s">
         <v>1279</v>
@@ -20269,7 +20269,7 @@
         <v>1248</v>
       </c>
       <c r="E385">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F385" t="s">
         <v>1279</v>
@@ -20304,7 +20304,7 @@
         <v>1249</v>
       </c>
       <c r="E386">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F386" t="s">
         <v>1279</v>
@@ -20339,7 +20339,7 @@
         <v>1249</v>
       </c>
       <c r="E387">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F387" t="s">
         <v>1279</v>
@@ -20374,7 +20374,7 @@
         <v>1250</v>
       </c>
       <c r="E388">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F388" t="s">
         <v>1279</v>
@@ -20409,7 +20409,7 @@
         <v>1250</v>
       </c>
       <c r="E389">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F389" t="s">
         <v>1279</v>
@@ -20444,7 +20444,7 @@
         <v>1250</v>
       </c>
       <c r="E390">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F390" t="s">
         <v>1279</v>
@@ -20479,7 +20479,7 @@
         <v>1250</v>
       </c>
       <c r="E391">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F391" t="s">
         <v>1279</v>
@@ -20514,7 +20514,7 @@
         <v>1250</v>
       </c>
       <c r="E392">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F392" t="s">
         <v>1279</v>
@@ -20549,7 +20549,7 @@
         <v>1250</v>
       </c>
       <c r="E393">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F393" t="s">
         <v>1279</v>
@@ -20584,7 +20584,7 @@
         <v>1250</v>
       </c>
       <c r="E394">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F394" t="s">
         <v>1279</v>
@@ -20619,7 +20619,7 @@
         <v>1250</v>
       </c>
       <c r="E395">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F395" t="s">
         <v>1279</v>
@@ -20654,7 +20654,7 @@
         <v>1250</v>
       </c>
       <c r="E396">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F396" t="s">
         <v>1279</v>
@@ -20689,7 +20689,7 @@
         <v>1250</v>
       </c>
       <c r="E397">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F397" t="s">
         <v>1279</v>
@@ -20724,7 +20724,7 @@
         <v>1250</v>
       </c>
       <c r="E398">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F398" t="s">
         <v>1279</v>
@@ -20759,7 +20759,7 @@
         <v>1250</v>
       </c>
       <c r="E399">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F399" t="s">
         <v>1279</v>
@@ -20794,7 +20794,7 @@
         <v>1250</v>
       </c>
       <c r="E400">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F400" t="s">
         <v>1279</v>
@@ -20829,7 +20829,7 @@
         <v>1250</v>
       </c>
       <c r="E401">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F401" t="s">
         <v>1279</v>
@@ -20864,7 +20864,7 @@
         <v>1250</v>
       </c>
       <c r="E402">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F402" t="s">
         <v>1279</v>
@@ -20899,7 +20899,7 @@
         <v>1250</v>
       </c>
       <c r="E403">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F403" t="s">
         <v>1279</v>
@@ -20934,7 +20934,7 @@
         <v>1250</v>
       </c>
       <c r="E404">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F404" t="s">
         <v>1279</v>
@@ -20969,7 +20969,7 @@
         <v>1250</v>
       </c>
       <c r="E405">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F405" t="s">
         <v>1279</v>
@@ -21004,7 +21004,7 @@
         <v>1250</v>
       </c>
       <c r="E406">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F406" t="s">
         <v>1279</v>
@@ -21039,7 +21039,7 @@
         <v>1250</v>
       </c>
       <c r="E407">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F407" t="s">
         <v>1279</v>
@@ -21074,7 +21074,7 @@
         <v>1250</v>
       </c>
       <c r="E408">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F408" t="s">
         <v>1279</v>
@@ -21109,7 +21109,7 @@
         <v>1250</v>
       </c>
       <c r="E409">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F409" t="s">
         <v>1279</v>
@@ -21144,7 +21144,7 @@
         <v>1251</v>
       </c>
       <c r="E410">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F410" t="s">
         <v>1279</v>
@@ -21179,7 +21179,7 @@
         <v>1251</v>
       </c>
       <c r="E411">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F411" t="s">
         <v>1279</v>
@@ -21214,7 +21214,7 @@
         <v>1251</v>
       </c>
       <c r="E412">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F412" t="s">
         <v>1283</v>
@@ -21249,7 +21249,7 @@
         <v>1252</v>
       </c>
       <c r="E413">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F413" t="s">
         <v>1279</v>
@@ -21284,7 +21284,7 @@
         <v>1253</v>
       </c>
       <c r="E414">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F414" t="s">
         <v>1281</v>
@@ -21322,7 +21322,7 @@
         <v>1253</v>
       </c>
       <c r="E415">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F415" t="s">
         <v>1279</v>
@@ -21357,7 +21357,7 @@
         <v>1253</v>
       </c>
       <c r="E416">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F416" t="s">
         <v>1279</v>
@@ -21392,7 +21392,7 @@
         <v>1253</v>
       </c>
       <c r="E417">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F417" t="s">
         <v>1279</v>
@@ -21427,7 +21427,7 @@
         <v>1254</v>
       </c>
       <c r="E418">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F418" t="s">
         <v>1279</v>
@@ -21465,7 +21465,7 @@
         <v>1254</v>
       </c>
       <c r="E419">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F419" t="s">
         <v>1283</v>
@@ -21500,7 +21500,7 @@
         <v>1254</v>
       </c>
       <c r="E420">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F420" t="s">
         <v>1281</v>
@@ -21535,7 +21535,7 @@
         <v>1254</v>
       </c>
       <c r="E421">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F421" t="s">
         <v>1279</v>
@@ -21570,7 +21570,7 @@
         <v>1254</v>
       </c>
       <c r="E422">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F422" t="s">
         <v>1279</v>
@@ -21605,7 +21605,7 @@
         <v>1254</v>
       </c>
       <c r="E423">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F423" t="s">
         <v>1279</v>
@@ -21640,7 +21640,7 @@
         <v>1254</v>
       </c>
       <c r="E424">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F424" t="s">
         <v>1279</v>
@@ -21675,7 +21675,7 @@
         <v>1255</v>
       </c>
       <c r="E425">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F425" t="s">
         <v>1283</v>
@@ -21713,7 +21713,7 @@
         <v>1256</v>
       </c>
       <c r="E426">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F426" t="s">
         <v>1279</v>
@@ -21748,7 +21748,7 @@
         <v>1256</v>
       </c>
       <c r="E427">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F427" t="s">
         <v>1279</v>
@@ -21783,7 +21783,7 @@
         <v>1256</v>
       </c>
       <c r="E428">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F428" t="s">
         <v>1279</v>
@@ -21818,7 +21818,7 @@
         <v>1257</v>
       </c>
       <c r="E429">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F429" t="s">
         <v>1279</v>
@@ -21853,7 +21853,7 @@
         <v>1257</v>
       </c>
       <c r="E430">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F430" t="s">
         <v>1279</v>
@@ -21888,7 +21888,7 @@
         <v>1257</v>
       </c>
       <c r="E431">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F431" t="s">
         <v>1279</v>
@@ -21923,7 +21923,7 @@
         <v>1257</v>
       </c>
       <c r="E432">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F432" t="s">
         <v>1281</v>
@@ -21958,7 +21958,7 @@
         <v>1257</v>
       </c>
       <c r="E433">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F433" t="s">
         <v>1279</v>
@@ -21993,7 +21993,7 @@
         <v>1258</v>
       </c>
       <c r="E434">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F434" t="s">
         <v>1279</v>
@@ -22028,7 +22028,7 @@
         <v>1258</v>
       </c>
       <c r="E435">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F435" t="s">
         <v>1279</v>
@@ -22063,7 +22063,7 @@
         <v>1258</v>
       </c>
       <c r="E436">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F436" t="s">
         <v>1279</v>
@@ -22098,7 +22098,7 @@
         <v>1258</v>
       </c>
       <c r="E437">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F437" t="s">
         <v>1279</v>
@@ -22133,7 +22133,7 @@
         <v>1258</v>
       </c>
       <c r="E438">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F438" t="s">
         <v>1279</v>
@@ -22171,7 +22171,7 @@
         <v>1258</v>
       </c>
       <c r="E439">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F439" t="s">
         <v>1281</v>
@@ -22209,7 +22209,7 @@
         <v>1258</v>
       </c>
       <c r="E440">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F440" t="s">
         <v>1281</v>
@@ -22244,7 +22244,7 @@
         <v>1259</v>
       </c>
       <c r="E441">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F441" t="s">
         <v>1279</v>
@@ -22279,7 +22279,7 @@
         <v>1259</v>
       </c>
       <c r="E442">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F442" t="s">
         <v>1279</v>
@@ -22314,7 +22314,7 @@
         <v>1259</v>
       </c>
       <c r="E443">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F443" t="s">
         <v>1279</v>
@@ -22349,7 +22349,7 @@
         <v>1260</v>
       </c>
       <c r="E444">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F444" t="s">
         <v>1279</v>
@@ -22384,7 +22384,7 @@
         <v>1260</v>
       </c>
       <c r="E445">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F445" t="s">
         <v>1279</v>
@@ -22419,7 +22419,7 @@
         <v>1260</v>
       </c>
       <c r="E446">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F446" t="s">
         <v>1281</v>
@@ -22457,7 +22457,7 @@
         <v>1260</v>
       </c>
       <c r="E447">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F447" t="s">
         <v>1279</v>
@@ -22492,7 +22492,7 @@
         <v>1261</v>
       </c>
       <c r="E448">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F448" t="s">
         <v>1279</v>
@@ -22527,7 +22527,7 @@
         <v>1261</v>
       </c>
       <c r="E449">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F449" t="s">
         <v>1279</v>
@@ -22562,7 +22562,7 @@
         <v>1262</v>
       </c>
       <c r="E450">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F450" t="s">
         <v>1281</v>
@@ -22600,7 +22600,7 @@
         <v>1262</v>
       </c>
       <c r="E451">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F451" t="s">
         <v>1279</v>
@@ -22635,7 +22635,7 @@
         <v>1262</v>
       </c>
       <c r="E452">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F452" t="s">
         <v>1279</v>
@@ -22670,7 +22670,7 @@
         <v>1263</v>
       </c>
       <c r="E453">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F453" t="s">
         <v>1281</v>
@@ -22705,7 +22705,7 @@
         <v>1263</v>
       </c>
       <c r="E454">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F454" t="s">
         <v>1279</v>
@@ -22740,7 +22740,7 @@
         <v>1263</v>
       </c>
       <c r="E455">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F455" t="s">
         <v>1281</v>
@@ -22778,7 +22778,7 @@
         <v>1263</v>
       </c>
       <c r="E456">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F456" t="s">
         <v>1279</v>
@@ -22813,7 +22813,7 @@
         <v>1263</v>
       </c>
       <c r="E457">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F457" t="s">
         <v>1279</v>
@@ -22848,7 +22848,7 @@
         <v>1264</v>
       </c>
       <c r="E458">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F458" t="s">
         <v>1279</v>
@@ -22883,7 +22883,7 @@
         <v>1264</v>
       </c>
       <c r="E459">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F459" t="s">
         <v>1279</v>
@@ -22918,7 +22918,7 @@
         <v>1265</v>
       </c>
       <c r="E460">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F460" t="s">
         <v>1279</v>
@@ -22953,7 +22953,7 @@
         <v>1265</v>
       </c>
       <c r="E461">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F461" t="s">
         <v>1279</v>
@@ -22988,7 +22988,7 @@
         <v>1265</v>
       </c>
       <c r="E462">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F462" t="s">
         <v>1279</v>
@@ -23023,7 +23023,7 @@
         <v>1265</v>
       </c>
       <c r="E463">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F463" t="s">
         <v>1281</v>
@@ -23061,7 +23061,7 @@
         <v>1266</v>
       </c>
       <c r="E464">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F464" t="s">
         <v>1279</v>
@@ -23096,7 +23096,7 @@
         <v>1266</v>
       </c>
       <c r="E465">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F465" t="s">
         <v>1283</v>
@@ -23134,7 +23134,7 @@
         <v>1266</v>
       </c>
       <c r="E466">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F466" t="s">
         <v>1279</v>
@@ -23169,7 +23169,7 @@
         <v>1266</v>
       </c>
       <c r="E467">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F467" t="s">
         <v>1279</v>
@@ -23204,7 +23204,7 @@
         <v>1267</v>
       </c>
       <c r="E468">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F468" t="s">
         <v>1279</v>
@@ -23239,7 +23239,7 @@
         <v>1267</v>
       </c>
       <c r="E469">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F469" t="s">
         <v>1279</v>
@@ -23274,7 +23274,7 @@
         <v>1267</v>
       </c>
       <c r="E470">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F470" t="s">
         <v>1279</v>
@@ -23309,7 +23309,7 @@
         <v>1267</v>
       </c>
       <c r="E471">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F471" t="s">
         <v>1279</v>
@@ -23344,7 +23344,7 @@
         <v>1267</v>
       </c>
       <c r="E472">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F472" t="s">
         <v>1279</v>
@@ -23379,7 +23379,7 @@
         <v>1267</v>
       </c>
       <c r="E473">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F473" t="s">
         <v>1281</v>
@@ -23417,7 +23417,7 @@
         <v>1268</v>
       </c>
       <c r="E474">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F474" t="s">
         <v>1279</v>
@@ -23452,7 +23452,7 @@
         <v>1268</v>
       </c>
       <c r="E475">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F475" t="s">
         <v>1281</v>
@@ -23487,7 +23487,7 @@
         <v>1269</v>
       </c>
       <c r="E476">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F476" t="s">
         <v>1281</v>
@@ -23525,7 +23525,7 @@
         <v>1269</v>
       </c>
       <c r="E477">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F477" t="s">
         <v>1281</v>
@@ -23563,7 +23563,7 @@
         <v>1269</v>
       </c>
       <c r="E478">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F478" t="s">
         <v>1279</v>
@@ -23598,7 +23598,7 @@
         <v>1269</v>
       </c>
       <c r="E479">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F479" t="s">
         <v>1279</v>
@@ -23633,7 +23633,7 @@
         <v>1270</v>
       </c>
       <c r="E480">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F480" t="s">
         <v>1279</v>
@@ -23668,7 +23668,7 @@
         <v>1271</v>
       </c>
       <c r="E481">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F481" t="s">
         <v>1279</v>
@@ -23703,7 +23703,7 @@
         <v>1271</v>
       </c>
       <c r="E482">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F482" t="s">
         <v>1279</v>
@@ -23738,7 +23738,7 @@
         <v>1271</v>
       </c>
       <c r="E483">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F483" t="s">
         <v>1279</v>
@@ -23773,7 +23773,7 @@
         <v>1271</v>
       </c>
       <c r="E484">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F484" t="s">
         <v>1279</v>
@@ -23808,7 +23808,7 @@
         <v>1271</v>
       </c>
       <c r="E485">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F485" t="s">
         <v>1279</v>
@@ -23843,7 +23843,7 @@
         <v>1271</v>
       </c>
       <c r="E486">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F486" t="s">
         <v>1279</v>
@@ -23878,7 +23878,7 @@
         <v>1271</v>
       </c>
       <c r="E487">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F487" t="s">
         <v>1279</v>
@@ -23913,7 +23913,7 @@
         <v>1271</v>
       </c>
       <c r="E488">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F488" t="s">
         <v>1281</v>
@@ -23951,7 +23951,7 @@
         <v>1272</v>
       </c>
       <c r="E489">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F489" t="s">
         <v>1279</v>
@@ -23986,7 +23986,7 @@
         <v>1272</v>
       </c>
       <c r="E490">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F490" t="s">
         <v>1279</v>
@@ -24021,7 +24021,7 @@
         <v>1272</v>
       </c>
       <c r="E491">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F491" t="s">
         <v>1279</v>
@@ -24056,7 +24056,7 @@
         <v>1272</v>
       </c>
       <c r="E492">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F492" t="s">
         <v>1281</v>
@@ -24094,7 +24094,7 @@
         <v>1272</v>
       </c>
       <c r="E493">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F493" t="s">
         <v>1281</v>
@@ -24132,7 +24132,7 @@
         <v>1272</v>
       </c>
       <c r="E494">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F494" t="s">
         <v>1281</v>
@@ -24170,7 +24170,7 @@
         <v>1272</v>
       </c>
       <c r="E495">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F495" t="s">
         <v>1279</v>
@@ -24205,7 +24205,7 @@
         <v>1273</v>
       </c>
       <c r="E496">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F496" t="s">
         <v>1281</v>
@@ -24243,7 +24243,7 @@
         <v>1273</v>
       </c>
       <c r="E497">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F497" t="s">
         <v>1281</v>
@@ -24281,7 +24281,7 @@
         <v>1274</v>
       </c>
       <c r="E498">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F498" t="s">
         <v>1281</v>
@@ -24319,7 +24319,7 @@
         <v>1274</v>
       </c>
       <c r="E499">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F499" t="s">
         <v>1279</v>
@@ -24354,7 +24354,7 @@
         <v>1275</v>
       </c>
       <c r="E500">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F500" t="s">
         <v>1279</v>
@@ -24389,7 +24389,7 @@
         <v>1275</v>
       </c>
       <c r="E501">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F501" t="s">
         <v>1279</v>
@@ -24427,7 +24427,7 @@
         <v>1275</v>
       </c>
       <c r="E502">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F502" t="s">
         <v>1281</v>
@@ -24465,7 +24465,7 @@
         <v>1276</v>
       </c>
       <c r="E503">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F503" t="s">
         <v>1279</v>
@@ -24503,7 +24503,7 @@
         <v>1276</v>
       </c>
       <c r="E504">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F504" t="s">
         <v>1279</v>
@@ -24538,7 +24538,7 @@
         <v>1276</v>
       </c>
       <c r="E505">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F505" t="s">
         <v>1279</v>
@@ -24573,7 +24573,7 @@
         <v>1276</v>
       </c>
       <c r="E506">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F506" t="s">
         <v>1279</v>
@@ -24608,7 +24608,7 @@
         <v>1276</v>
       </c>
       <c r="E507">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F507" t="s">
         <v>1279</v>
@@ -24643,7 +24643,7 @@
         <v>1276</v>
       </c>
       <c r="E508">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F508" t="s">
         <v>1281</v>
@@ -24681,7 +24681,7 @@
         <v>1277</v>
       </c>
       <c r="E509">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F509" t="s">
         <v>1279</v>
@@ -24716,7 +24716,7 @@
         <v>1277</v>
       </c>
       <c r="E510">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F510" t="s">
         <v>1279</v>
@@ -24751,7 +24751,7 @@
         <v>1277</v>
       </c>
       <c r="E511">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F511" t="s">
         <v>1279</v>
@@ -24786,7 +24786,7 @@
         <v>1277</v>
       </c>
       <c r="E512">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F512" t="s">
         <v>1279</v>
@@ -24821,7 +24821,7 @@
         <v>1277</v>
       </c>
       <c r="E513">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F513" t="s">
         <v>1279</v>
@@ -24856,7 +24856,7 @@
         <v>1277</v>
       </c>
       <c r="E514">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F514" t="s">
         <v>1279</v>
@@ -24891,7 +24891,7 @@
         <v>1278</v>
       </c>
       <c r="E515">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F515" t="s">
         <v>1279</v>
@@ -24929,7 +24929,7 @@
         <v>1278</v>
       </c>
       <c r="E516">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F516" t="s">
         <v>1279</v>
@@ -24964,7 +24964,7 @@
         <v>1278</v>
       </c>
       <c r="E517">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F517" t="s">
         <v>1279</v>
@@ -24999,7 +24999,7 @@
         <v>1278</v>
       </c>
       <c r="E518">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F518" t="s">
         <v>1279</v>
@@ -25037,7 +25037,7 @@
         <v>1278</v>
       </c>
       <c r="E519">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F519" t="s">
         <v>1279</v>
@@ -25072,7 +25072,7 @@
         <v>1278</v>
       </c>
       <c r="E520">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F520" t="s">
         <v>1281</v>

--- a/BacklogGATEAutoCompleto.xlsx
+++ b/BacklogGATEAutoCompleto.xlsx
@@ -7450,9 +7450,6 @@
     <t>ECONOMICIDADE OBRAS,MOBILIDADE E TRANSPORTE</t>
   </si>
   <si>
-    <t>MOBILIDADE E TRANSPORTE,ECONOMICIDADE OBRAS</t>
-  </si>
-  <si>
     <t>PATRIMÔNIO HISTÓRICO E CULTURAL,URBANISMO</t>
   </si>
   <si>
@@ -7474,40 +7471,43 @@
     <t>###   SEM TEMA   ###</t>
   </si>
   <si>
+    <t>ECONOMICIDADE OBRAS,ECONOMICIDADE CONTÁBIL</t>
+  </si>
+  <si>
+    <t>AVALIAÇÃO DE IMÓVEIS,GEOLOGIA</t>
+  </si>
+  <si>
+    <t>ENGENHARIA CIVIL,FENOMENOS DE ENERGIA E INFORMAÇÃO</t>
+  </si>
+  <si>
+    <t>ENGENHARIA CIVIL,ENGENHARIA QUÍMICA,FENOMENOS DE ENERGIA E INFORMAÇÃO</t>
+  </si>
+  <si>
+    <t>VALORAÇÃO DANOS AMBIENTAIS,RECURSOS HÍDRICOS</t>
+  </si>
+  <si>
+    <t>AVALIAÇÃO DE IMÓVEIS,ECONOMICIDADE OBRAS</t>
+  </si>
+  <si>
+    <t>ENGENHARIA FLORESTAL,URBANISMO</t>
+  </si>
+  <si>
+    <t>URBANISMO,BIOLOGIA</t>
+  </si>
+  <si>
+    <t>FARMÁCIA,SAÚDE</t>
+  </si>
+  <si>
+    <t>ENGENHARIA AMBIENTAL,BIOLOGIA</t>
+  </si>
+  <si>
     <t>ECONOMICIDADE CONTÁBIL,ECONOMICIDADE OBRAS</t>
   </si>
   <si>
-    <t>AVALIAÇÃO DE IMÓVEIS,GEOLOGIA</t>
-  </si>
-  <si>
-    <t>ENGENHARIA CIVIL,FENOMENOS DE ENERGIA E INFORMAÇÃO</t>
-  </si>
-  <si>
-    <t>ENGENHARIA CIVIL,ENGENHARIA QUÍMICA,FENOMENOS DE ENERGIA E INFORMAÇÃO</t>
-  </si>
-  <si>
-    <t>RECURSOS HÍDRICOS,VALORAÇÃO DANOS AMBIENTAIS</t>
-  </si>
-  <si>
-    <t>AVALIAÇÃO DE IMÓVEIS,ECONOMICIDADE OBRAS</t>
-  </si>
-  <si>
-    <t>ENGENHARIA FLORESTAL,URBANISMO</t>
-  </si>
-  <si>
-    <t>URBANISMO,BIOLOGIA</t>
-  </si>
-  <si>
-    <t>FARMÁCIA,SAÚDE</t>
-  </si>
-  <si>
-    <t>ENGENHARIA AMBIENTAL,BIOLOGIA</t>
-  </si>
-  <si>
     <t>BIOLOGIA,GEOLOGIA</t>
   </si>
   <si>
-    <t>BIOLOGIA,RECURSOS HÍDRICOS,MOBILIDADE E TRANSPORTE,URBANISMO</t>
+    <t>MOBILIDADE E TRANSPORTE,RECURSOS HÍDRICOS,BIOLOGIA,URBANISMO</t>
   </si>
   <si>
     <t>ENGENHARIA QUÍMICA,RESÍDUOS SÓLIDOS</t>
@@ -7516,16 +7516,16 @@
     <t>GEOLOGIA,ENGENHARIA QUÍMICA</t>
   </si>
   <si>
-    <t>BIOLOGIA,ENGENHARIA AMBIENTAL</t>
-  </si>
-  <si>
-    <t>ENGENHARIA CIVIL,MOBILIDADE E TRANSPORTE</t>
+    <t>MOBILIDADE E TRANSPORTE,ENGENHARIA CIVIL</t>
   </si>
   <si>
     <t>FENOMENOS DE ENERGIA E INFORMAÇÃO,ENGENHARIA CIVIL</t>
   </si>
   <si>
-    <t>AVALIAÇÃO DE IMÓVEIS,ORÇAMENTO,SAÚDE,PSICOLOGIA,SAÚDE MENTAL,MOBILIDADE E TRANSPORTE,ECONOMICIDADE CONTÁBIL,URBANISMO,ASSISTÊNCIA SOCIAL,ECONOMIA</t>
+    <t>GEOTECNIA,ENGENHARIA CIVIL</t>
+  </si>
+  <si>
+    <t>SAÚDE MENTAL,SAÚDE,ECONOMICIDADE CONTÁBIL,AVALIAÇÃO DE IMÓVEIS,ECONOMIA,URBANISMO,MOBILIDADE E TRANSPORTE,PSICOLOGIA,ASSISTÊNCIA SOCIAL,ORÇAMENTO</t>
   </si>
 </sst>
 </file>
@@ -19667,7 +19667,7 @@
         <v>2329</v>
       </c>
       <c r="L336" t="s">
-        <v>2478</v>
+        <v>2477</v>
       </c>
     </row>
     <row r="337" spans="1:12">
@@ -20440,7 +20440,7 @@
         <v>2327</v>
       </c>
       <c r="L358" t="s">
-        <v>2479</v>
+        <v>2478</v>
       </c>
     </row>
     <row r="359" spans="1:12">
@@ -20475,7 +20475,7 @@
         <v>2336</v>
       </c>
       <c r="L359" t="s">
-        <v>2480</v>
+        <v>2479</v>
       </c>
     </row>
     <row r="360" spans="1:12">
@@ -20580,7 +20580,7 @@
         <v>2318</v>
       </c>
       <c r="L362" t="s">
-        <v>2481</v>
+        <v>2480</v>
       </c>
     </row>
     <row r="363" spans="1:12">
@@ -20895,7 +20895,7 @@
         <v>2387</v>
       </c>
       <c r="L371" t="s">
-        <v>2482</v>
+        <v>2481</v>
       </c>
     </row>
     <row r="372" spans="1:12">
@@ -21490,7 +21490,7 @@
         <v>2335</v>
       </c>
       <c r="L388" t="s">
-        <v>2483</v>
+        <v>2482</v>
       </c>
     </row>
     <row r="389" spans="1:12">
@@ -21595,7 +21595,7 @@
         <v>2351</v>
       </c>
       <c r="L391" t="s">
-        <v>2484</v>
+        <v>2483</v>
       </c>
     </row>
     <row r="392" spans="1:12">
@@ -21913,7 +21913,7 @@
         <v>2336</v>
       </c>
       <c r="L400" t="s">
-        <v>2480</v>
+        <v>2479</v>
       </c>
     </row>
     <row r="401" spans="1:12">
@@ -23494,7 +23494,7 @@
         <v>2356</v>
       </c>
       <c r="L445" t="s">
-        <v>2485</v>
+        <v>2484</v>
       </c>
     </row>
     <row r="446" spans="1:12">
@@ -23529,7 +23529,7 @@
         <v>2399</v>
       </c>
       <c r="L446" t="s">
-        <v>2485</v>
+        <v>2484</v>
       </c>
     </row>
     <row r="447" spans="1:12">
@@ -23564,7 +23564,7 @@
         <v>2399</v>
       </c>
       <c r="L447" t="s">
-        <v>2485</v>
+        <v>2484</v>
       </c>
     </row>
     <row r="448" spans="1:12">
@@ -23599,7 +23599,7 @@
         <v>2399</v>
       </c>
       <c r="L448" t="s">
-        <v>2485</v>
+        <v>2484</v>
       </c>
     </row>
     <row r="449" spans="1:12">
@@ -23634,7 +23634,7 @@
         <v>2399</v>
       </c>
       <c r="L449" t="s">
-        <v>2485</v>
+        <v>2484</v>
       </c>
     </row>
     <row r="450" spans="1:12">
@@ -23669,7 +23669,7 @@
         <v>2399</v>
       </c>
       <c r="L450" t="s">
-        <v>2485</v>
+        <v>2484</v>
       </c>
     </row>
     <row r="451" spans="1:12">
@@ -23704,7 +23704,7 @@
         <v>2399</v>
       </c>
       <c r="L451" t="s">
-        <v>2485</v>
+        <v>2484</v>
       </c>
     </row>
     <row r="452" spans="1:12">
@@ -23739,7 +23739,7 @@
         <v>2399</v>
       </c>
       <c r="L452" t="s">
-        <v>2485</v>
+        <v>2484</v>
       </c>
     </row>
     <row r="453" spans="1:12">
@@ -23774,7 +23774,7 @@
         <v>2399</v>
       </c>
       <c r="L453" t="s">
-        <v>2485</v>
+        <v>2484</v>
       </c>
     </row>
     <row r="454" spans="1:12">
@@ -23809,7 +23809,7 @@
         <v>2399</v>
       </c>
       <c r="L454" t="s">
-        <v>2485</v>
+        <v>2484</v>
       </c>
     </row>
     <row r="455" spans="1:12">
@@ -23844,7 +23844,7 @@
         <v>2399</v>
       </c>
       <c r="L455" t="s">
-        <v>2485</v>
+        <v>2484</v>
       </c>
     </row>
     <row r="456" spans="1:12">
@@ -23879,7 +23879,7 @@
         <v>2399</v>
       </c>
       <c r="L456" t="s">
-        <v>2485</v>
+        <v>2484</v>
       </c>
     </row>
     <row r="457" spans="1:12">
@@ -23914,7 +23914,7 @@
         <v>2399</v>
       </c>
       <c r="L457" t="s">
-        <v>2485</v>
+        <v>2484</v>
       </c>
     </row>
     <row r="458" spans="1:12">
@@ -23949,7 +23949,7 @@
         <v>2399</v>
       </c>
       <c r="L458" t="s">
-        <v>2485</v>
+        <v>2484</v>
       </c>
     </row>
     <row r="459" spans="1:12">
@@ -23984,7 +23984,7 @@
         <v>2399</v>
       </c>
       <c r="L459" t="s">
-        <v>2485</v>
+        <v>2484</v>
       </c>
     </row>
     <row r="460" spans="1:12">
@@ -24019,7 +24019,7 @@
         <v>2399</v>
       </c>
       <c r="L460" t="s">
-        <v>2485</v>
+        <v>2484</v>
       </c>
     </row>
     <row r="461" spans="1:12">
@@ -24054,7 +24054,7 @@
         <v>2399</v>
       </c>
       <c r="L461" t="s">
-        <v>2485</v>
+        <v>2484</v>
       </c>
     </row>
     <row r="462" spans="1:12">
@@ -24089,7 +24089,7 @@
         <v>2399</v>
       </c>
       <c r="L462" t="s">
-        <v>2485</v>
+        <v>2484</v>
       </c>
     </row>
     <row r="463" spans="1:12">
@@ -24124,7 +24124,7 @@
         <v>2399</v>
       </c>
       <c r="L463" t="s">
-        <v>2485</v>
+        <v>2484</v>
       </c>
     </row>
     <row r="464" spans="1:12">
@@ -24299,7 +24299,7 @@
         <v>2388</v>
       </c>
       <c r="L468" t="s">
-        <v>2486</v>
+        <v>2485</v>
       </c>
     </row>
     <row r="469" spans="1:12">
@@ -24655,7 +24655,7 @@
         <v>2316</v>
       </c>
       <c r="L478" t="s">
-        <v>2487</v>
+        <v>2486</v>
       </c>
     </row>
     <row r="479" spans="1:12">
@@ -24690,7 +24690,7 @@
         <v>2356</v>
       </c>
       <c r="L479" t="s">
-        <v>2488</v>
+        <v>2487</v>
       </c>
     </row>
     <row r="480" spans="1:12">
@@ -25323,7 +25323,7 @@
         <v>2334</v>
       </c>
       <c r="L497" t="s">
-        <v>2432</v>
+        <v>2442</v>
       </c>
     </row>
     <row r="498" spans="1:12">
@@ -25428,7 +25428,7 @@
         <v>2357</v>
       </c>
       <c r="L500" t="s">
-        <v>2489</v>
+        <v>2488</v>
       </c>
     </row>
     <row r="501" spans="1:12">
@@ -25463,7 +25463,7 @@
         <v>2311</v>
       </c>
       <c r="L501" t="s">
-        <v>2488</v>
+        <v>2487</v>
       </c>
     </row>
     <row r="502" spans="1:12">
@@ -25854,7 +25854,7 @@
         <v>2307</v>
       </c>
       <c r="L512" t="s">
-        <v>2490</v>
+        <v>2489</v>
       </c>
     </row>
     <row r="513" spans="1:12">
@@ -26134,7 +26134,7 @@
         <v>2332</v>
       </c>
       <c r="L520" t="s">
-        <v>2491</v>
+        <v>2490</v>
       </c>
     </row>
     <row r="521" spans="1:12">
@@ -26169,7 +26169,7 @@
         <v>2326</v>
       </c>
       <c r="L521" t="s">
-        <v>2492</v>
+        <v>2491</v>
       </c>
     </row>
     <row r="522" spans="1:12">
@@ -26417,7 +26417,7 @@
         <v>2405</v>
       </c>
       <c r="L528" t="s">
-        <v>2493</v>
+        <v>2492</v>
       </c>
     </row>
     <row r="529" spans="1:12">
@@ -26557,7 +26557,7 @@
         <v>2344</v>
       </c>
       <c r="L532" t="s">
-        <v>2494</v>
+        <v>2493</v>
       </c>
     </row>
     <row r="533" spans="1:12">
@@ -27056,7 +27056,7 @@
         <v>2334</v>
       </c>
       <c r="L546" t="s">
-        <v>2434</v>
+        <v>2492</v>
       </c>
     </row>
     <row r="547" spans="1:12">
@@ -27126,7 +27126,7 @@
         <v>2334</v>
       </c>
       <c r="L548" t="s">
-        <v>2495</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="549" spans="1:12">
@@ -27196,7 +27196,7 @@
         <v>2338</v>
       </c>
       <c r="L550" t="s">
-        <v>2486</v>
+        <v>2495</v>
       </c>
     </row>
     <row r="551" spans="1:12">
@@ -27371,7 +27371,7 @@
         <v>2350</v>
       </c>
       <c r="L555" t="s">
-        <v>2485</v>
+        <v>2484</v>
       </c>
     </row>
     <row r="556" spans="1:12">
@@ -27657,7 +27657,7 @@
         <v>2409</v>
       </c>
       <c r="L563" t="s">
-        <v>2481</v>
+        <v>2480</v>
       </c>
     </row>
     <row r="564" spans="1:12">
@@ -27692,7 +27692,7 @@
         <v>2409</v>
       </c>
       <c r="L564" t="s">
-        <v>2488</v>
+        <v>2487</v>
       </c>
     </row>
     <row r="565" spans="1:12">
@@ -27940,7 +27940,7 @@
         <v>2323</v>
       </c>
       <c r="L571" t="s">
-        <v>2492</v>
+        <v>2491</v>
       </c>
     </row>
     <row r="572" spans="1:12">
@@ -29192,7 +29192,7 @@
         <v>2323</v>
       </c>
       <c r="L606" t="s">
-        <v>2481</v>
+        <v>2480</v>
       </c>
     </row>
     <row r="607" spans="1:12">
@@ -29227,7 +29227,7 @@
         <v>2349</v>
       </c>
       <c r="L607" t="s">
-        <v>2485</v>
+        <v>2484</v>
       </c>
     </row>
     <row r="608" spans="1:12">
@@ -29691,7 +29691,7 @@
         <v>2412</v>
       </c>
       <c r="L620" t="s">
-        <v>2485</v>
+        <v>2484</v>
       </c>
     </row>
     <row r="621" spans="1:12">
@@ -29726,7 +29726,7 @@
         <v>2336</v>
       </c>
       <c r="L621" t="s">
-        <v>2500</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="622" spans="1:12">
@@ -29764,7 +29764,7 @@
         <v>2413</v>
       </c>
       <c r="L622" t="s">
-        <v>2481</v>
+        <v>2480</v>
       </c>
     </row>
     <row r="623" spans="1:12">
@@ -29834,7 +29834,7 @@
         <v>2414</v>
       </c>
       <c r="L624" t="s">
-        <v>2501</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="625" spans="1:12">
@@ -29869,7 +29869,7 @@
         <v>2346</v>
       </c>
       <c r="L625" t="s">
-        <v>2485</v>
+        <v>2484</v>
       </c>
     </row>
     <row r="626" spans="1:12">
@@ -30044,7 +30044,7 @@
         <v>2416</v>
       </c>
       <c r="L630" t="s">
-        <v>2485</v>
+        <v>2484</v>
       </c>
     </row>
     <row r="631" spans="1:12">
@@ -30082,7 +30082,7 @@
         <v>2417</v>
       </c>
       <c r="L631" t="s">
-        <v>2485</v>
+        <v>2484</v>
       </c>
     </row>
     <row r="632" spans="1:12">
@@ -30117,7 +30117,7 @@
         <v>2308</v>
       </c>
       <c r="L632" t="s">
-        <v>2485</v>
+        <v>2484</v>
       </c>
     </row>
     <row r="633" spans="1:12">
@@ -30152,7 +30152,7 @@
         <v>2308</v>
       </c>
       <c r="L633" t="s">
-        <v>2485</v>
+        <v>2484</v>
       </c>
     </row>
     <row r="634" spans="1:12">
@@ -30260,7 +30260,7 @@
         <v>2418</v>
       </c>
       <c r="L636" t="s">
-        <v>2502</v>
+        <v>2501</v>
       </c>
     </row>
     <row r="637" spans="1:12">
@@ -30295,7 +30295,7 @@
         <v>2353</v>
       </c>
       <c r="L637" t="s">
-        <v>2485</v>
+        <v>2484</v>
       </c>
     </row>
     <row r="638" spans="1:12">
@@ -30327,7 +30327,7 @@
         <v>2419</v>
       </c>
       <c r="L638" t="s">
-        <v>2438</v>
+        <v>2502</v>
       </c>
     </row>
     <row r="639" spans="1:12">

--- a/BacklogGATEAutoCompleto.xlsx
+++ b/BacklogGATEAutoCompleto.xlsx
@@ -7935,7 +7935,7 @@
         <v>1320</v>
       </c>
       <c r="E2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="F2" t="s">
         <v>1532</v>
@@ -7970,7 +7970,7 @@
         <v>1321</v>
       </c>
       <c r="E3">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="F3" t="s">
         <v>1532</v>
@@ -8005,7 +8005,7 @@
         <v>1322</v>
       </c>
       <c r="E4">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="F4" t="s">
         <v>1532</v>
@@ -8040,7 +8040,7 @@
         <v>1323</v>
       </c>
       <c r="E5">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="F5" t="s">
         <v>1532</v>
@@ -8075,7 +8075,7 @@
         <v>1324</v>
       </c>
       <c r="E6">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="F6" t="s">
         <v>1532</v>
@@ -8110,7 +8110,7 @@
         <v>1325</v>
       </c>
       <c r="E7">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F7" t="s">
         <v>1532</v>
@@ -8145,7 +8145,7 @@
         <v>1326</v>
       </c>
       <c r="E8">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="F8" t="s">
         <v>1532</v>
@@ -8180,7 +8180,7 @@
         <v>1327</v>
       </c>
       <c r="E9">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F9" t="s">
         <v>1532</v>
@@ -8215,7 +8215,7 @@
         <v>1328</v>
       </c>
       <c r="E10">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="F10" t="s">
         <v>1532</v>
@@ -8250,7 +8250,7 @@
         <v>1328</v>
       </c>
       <c r="E11">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="F11" t="s">
         <v>1532</v>
@@ -8285,7 +8285,7 @@
         <v>1329</v>
       </c>
       <c r="E12">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="F12" t="s">
         <v>1532</v>
@@ -8320,7 +8320,7 @@
         <v>1330</v>
       </c>
       <c r="E13">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="F13" t="s">
         <v>1532</v>
@@ -8355,7 +8355,7 @@
         <v>1331</v>
       </c>
       <c r="E14">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="F14" t="s">
         <v>1532</v>
@@ -8390,7 +8390,7 @@
         <v>1331</v>
       </c>
       <c r="E15">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="F15" t="s">
         <v>1532</v>
@@ -8425,7 +8425,7 @@
         <v>1332</v>
       </c>
       <c r="E16">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="F16" t="s">
         <v>1532</v>
@@ -8460,7 +8460,7 @@
         <v>1332</v>
       </c>
       <c r="E17">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="F17" t="s">
         <v>1532</v>
@@ -8495,7 +8495,7 @@
         <v>1333</v>
       </c>
       <c r="E18">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F18" t="s">
         <v>1532</v>
@@ -8530,7 +8530,7 @@
         <v>1334</v>
       </c>
       <c r="E19">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="F19" t="s">
         <v>1532</v>
@@ -8565,7 +8565,7 @@
         <v>1335</v>
       </c>
       <c r="E20">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="F20" t="s">
         <v>1532</v>
@@ -8600,7 +8600,7 @@
         <v>1336</v>
       </c>
       <c r="E21">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F21" t="s">
         <v>1532</v>
@@ -8635,7 +8635,7 @@
         <v>1337</v>
       </c>
       <c r="E22">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="F22" t="s">
         <v>1532</v>
@@ -8673,7 +8673,7 @@
         <v>1338</v>
       </c>
       <c r="E23">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F23" t="s">
         <v>1532</v>
@@ -8708,7 +8708,7 @@
         <v>1339</v>
       </c>
       <c r="E24">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F24" t="s">
         <v>1532</v>
@@ -8743,7 +8743,7 @@
         <v>1340</v>
       </c>
       <c r="E25">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F25" t="s">
         <v>1532</v>
@@ -8778,7 +8778,7 @@
         <v>1341</v>
       </c>
       <c r="E26">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F26" t="s">
         <v>1532</v>
@@ -8813,7 +8813,7 @@
         <v>1342</v>
       </c>
       <c r="E27">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F27" t="s">
         <v>1532</v>
@@ -8848,7 +8848,7 @@
         <v>1343</v>
       </c>
       <c r="E28">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F28" t="s">
         <v>1532</v>
@@ -8883,7 +8883,7 @@
         <v>1344</v>
       </c>
       <c r="E29">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F29" t="s">
         <v>1532</v>
@@ -8918,7 +8918,7 @@
         <v>1345</v>
       </c>
       <c r="E30">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F30" t="s">
         <v>1532</v>
@@ -8953,7 +8953,7 @@
         <v>1346</v>
       </c>
       <c r="E31">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F31" t="s">
         <v>1532</v>
@@ -8988,7 +8988,7 @@
         <v>1347</v>
       </c>
       <c r="E32">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F32" t="s">
         <v>1532</v>
@@ -9023,7 +9023,7 @@
         <v>1348</v>
       </c>
       <c r="E33">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F33" t="s">
         <v>1532</v>
@@ -9058,7 +9058,7 @@
         <v>1349</v>
       </c>
       <c r="E34">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F34" t="s">
         <v>1532</v>
@@ -9093,7 +9093,7 @@
         <v>1350</v>
       </c>
       <c r="E35">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="F35" t="s">
         <v>1532</v>
@@ -9128,7 +9128,7 @@
         <v>1350</v>
       </c>
       <c r="E36">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="F36" t="s">
         <v>1532</v>
@@ -9163,7 +9163,7 @@
         <v>1351</v>
       </c>
       <c r="E37">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F37" t="s">
         <v>1532</v>
@@ -9198,7 +9198,7 @@
         <v>1352</v>
       </c>
       <c r="E38">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F38" t="s">
         <v>1532</v>
@@ -9233,7 +9233,7 @@
         <v>1353</v>
       </c>
       <c r="E39">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F39" t="s">
         <v>1532</v>
@@ -9268,7 +9268,7 @@
         <v>1353</v>
       </c>
       <c r="E40">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F40" t="s">
         <v>1532</v>
@@ -9303,7 +9303,7 @@
         <v>1354</v>
       </c>
       <c r="E41">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F41" t="s">
         <v>1532</v>
@@ -9338,7 +9338,7 @@
         <v>1354</v>
       </c>
       <c r="E42">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F42" t="s">
         <v>1532</v>
@@ -9373,7 +9373,7 @@
         <v>1355</v>
       </c>
       <c r="E43">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F43" t="s">
         <v>1532</v>
@@ -9408,7 +9408,7 @@
         <v>1356</v>
       </c>
       <c r="E44">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F44" t="s">
         <v>1532</v>
@@ -9443,7 +9443,7 @@
         <v>1357</v>
       </c>
       <c r="E45">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F45" t="s">
         <v>1532</v>
@@ -9478,7 +9478,7 @@
         <v>1358</v>
       </c>
       <c r="E46">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F46" t="s">
         <v>1532</v>
@@ -9513,7 +9513,7 @@
         <v>1358</v>
       </c>
       <c r="E47">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F47" t="s">
         <v>1532</v>
@@ -9548,7 +9548,7 @@
         <v>1359</v>
       </c>
       <c r="E48">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F48" t="s">
         <v>1532</v>
@@ -9583,7 +9583,7 @@
         <v>1360</v>
       </c>
       <c r="E49">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F49" t="s">
         <v>1532</v>
@@ -9618,7 +9618,7 @@
         <v>1361</v>
       </c>
       <c r="E50">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F50" t="s">
         <v>1532</v>
@@ -9653,7 +9653,7 @@
         <v>1362</v>
       </c>
       <c r="E51">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F51" t="s">
         <v>1532</v>
@@ -9688,7 +9688,7 @@
         <v>1363</v>
       </c>
       <c r="E52">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F52" t="s">
         <v>1532</v>
@@ -9723,7 +9723,7 @@
         <v>1364</v>
       </c>
       <c r="E53">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F53" t="s">
         <v>1532</v>
@@ -9758,7 +9758,7 @@
         <v>1365</v>
       </c>
       <c r="E54">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F54" t="s">
         <v>1532</v>
@@ -9793,7 +9793,7 @@
         <v>1365</v>
       </c>
       <c r="E55">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F55" t="s">
         <v>1532</v>
@@ -9828,7 +9828,7 @@
         <v>1365</v>
       </c>
       <c r="E56">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F56" t="s">
         <v>1532</v>
@@ -9863,7 +9863,7 @@
         <v>1366</v>
       </c>
       <c r="E57">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F57" t="s">
         <v>1532</v>
@@ -9898,7 +9898,7 @@
         <v>1367</v>
       </c>
       <c r="E58">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F58" t="s">
         <v>1532</v>
@@ -9933,7 +9933,7 @@
         <v>1368</v>
       </c>
       <c r="E59">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F59" t="s">
         <v>1532</v>
@@ -9968,7 +9968,7 @@
         <v>1369</v>
       </c>
       <c r="E60">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F60" t="s">
         <v>1532</v>
@@ -10003,7 +10003,7 @@
         <v>1370</v>
       </c>
       <c r="E61">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F61" t="s">
         <v>1532</v>
@@ -10038,7 +10038,7 @@
         <v>1370</v>
       </c>
       <c r="E62">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F62" t="s">
         <v>1532</v>
@@ -10073,7 +10073,7 @@
         <v>1370</v>
       </c>
       <c r="E63">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F63" t="s">
         <v>1532</v>
@@ -10108,7 +10108,7 @@
         <v>1371</v>
       </c>
       <c r="E64">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F64" t="s">
         <v>1532</v>
@@ -10143,7 +10143,7 @@
         <v>1372</v>
       </c>
       <c r="E65">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F65" t="s">
         <v>1532</v>
@@ -10178,7 +10178,7 @@
         <v>1372</v>
       </c>
       <c r="E66">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F66" t="s">
         <v>1532</v>
@@ -10213,7 +10213,7 @@
         <v>1372</v>
       </c>
       <c r="E67">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F67" t="s">
         <v>1533</v>
@@ -10248,7 +10248,7 @@
         <v>1372</v>
       </c>
       <c r="E68">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F68" t="s">
         <v>1532</v>
@@ -10283,7 +10283,7 @@
         <v>1373</v>
       </c>
       <c r="E69">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F69" t="s">
         <v>1532</v>
@@ -10318,7 +10318,7 @@
         <v>1374</v>
       </c>
       <c r="E70">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F70" t="s">
         <v>1532</v>
@@ -10353,7 +10353,7 @@
         <v>1374</v>
       </c>
       <c r="E71">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F71" t="s">
         <v>1532</v>
@@ -10388,7 +10388,7 @@
         <v>1375</v>
       </c>
       <c r="E72">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F72" t="s">
         <v>1532</v>
@@ -10423,7 +10423,7 @@
         <v>1376</v>
       </c>
       <c r="E73">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F73" t="s">
         <v>1532</v>
@@ -10458,7 +10458,7 @@
         <v>1377</v>
       </c>
       <c r="E74">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F74" t="s">
         <v>1532</v>
@@ -10493,7 +10493,7 @@
         <v>1378</v>
       </c>
       <c r="E75">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F75" t="s">
         <v>1532</v>
@@ -10528,7 +10528,7 @@
         <v>1378</v>
       </c>
       <c r="E76">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F76" t="s">
         <v>1532</v>
@@ -10563,7 +10563,7 @@
         <v>1378</v>
       </c>
       <c r="E77">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F77" t="s">
         <v>1532</v>
@@ -10598,7 +10598,7 @@
         <v>1378</v>
       </c>
       <c r="E78">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F78" t="s">
         <v>1532</v>
@@ -10633,7 +10633,7 @@
         <v>1378</v>
       </c>
       <c r="E79">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F79" t="s">
         <v>1532</v>
@@ -10668,7 +10668,7 @@
         <v>1378</v>
       </c>
       <c r="E80">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F80" t="s">
         <v>1532</v>
@@ -10703,7 +10703,7 @@
         <v>1379</v>
       </c>
       <c r="E81">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F81" t="s">
         <v>1532</v>
@@ -10738,7 +10738,7 @@
         <v>1380</v>
       </c>
       <c r="E82">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F82" t="s">
         <v>1532</v>
@@ -10773,7 +10773,7 @@
         <v>1381</v>
       </c>
       <c r="E83">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F83" t="s">
         <v>1532</v>
@@ -10808,7 +10808,7 @@
         <v>1381</v>
       </c>
       <c r="E84">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F84" t="s">
         <v>1532</v>
@@ -10843,7 +10843,7 @@
         <v>1382</v>
       </c>
       <c r="E85">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F85" t="s">
         <v>1534</v>
@@ -10878,7 +10878,7 @@
         <v>1383</v>
       </c>
       <c r="E86">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F86" t="s">
         <v>1532</v>
@@ -10913,7 +10913,7 @@
         <v>1384</v>
       </c>
       <c r="E87">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F87" t="s">
         <v>1532</v>
@@ -10948,7 +10948,7 @@
         <v>1384</v>
       </c>
       <c r="E88">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F88" t="s">
         <v>1532</v>
@@ -10983,7 +10983,7 @@
         <v>1385</v>
       </c>
       <c r="E89">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F89" t="s">
         <v>1532</v>
@@ -11018,7 +11018,7 @@
         <v>1386</v>
       </c>
       <c r="E90">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F90" t="s">
         <v>1532</v>
@@ -11053,7 +11053,7 @@
         <v>1387</v>
       </c>
       <c r="E91">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F91" t="s">
         <v>1532</v>
@@ -11088,7 +11088,7 @@
         <v>1388</v>
       </c>
       <c r="E92">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F92" t="s">
         <v>1532</v>
@@ -11123,7 +11123,7 @@
         <v>1389</v>
       </c>
       <c r="E93">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F93" t="s">
         <v>1532</v>
@@ -11158,7 +11158,7 @@
         <v>1389</v>
       </c>
       <c r="E94">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F94" t="s">
         <v>1532</v>
@@ -11193,7 +11193,7 @@
         <v>1390</v>
       </c>
       <c r="E95">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F95" t="s">
         <v>1532</v>
@@ -11228,7 +11228,7 @@
         <v>1390</v>
       </c>
       <c r="E96">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F96" t="s">
         <v>1532</v>
@@ -11263,7 +11263,7 @@
         <v>1390</v>
       </c>
       <c r="E97">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F97" t="s">
         <v>1532</v>
@@ -11298,7 +11298,7 @@
         <v>1391</v>
       </c>
       <c r="E98">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F98" t="s">
         <v>1532</v>
@@ -11333,7 +11333,7 @@
         <v>1391</v>
       </c>
       <c r="E99">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F99" t="s">
         <v>1532</v>
@@ -11368,7 +11368,7 @@
         <v>1392</v>
       </c>
       <c r="E100">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F100" t="s">
         <v>1532</v>
@@ -11403,7 +11403,7 @@
         <v>1393</v>
       </c>
       <c r="E101">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F101" t="s">
         <v>1532</v>
@@ -11438,7 +11438,7 @@
         <v>1394</v>
       </c>
       <c r="E102">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F102" t="s">
         <v>1532</v>
@@ -11473,7 +11473,7 @@
         <v>1394</v>
       </c>
       <c r="E103">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F103" t="s">
         <v>1532</v>
@@ -11508,7 +11508,7 @@
         <v>1395</v>
       </c>
       <c r="E104">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F104" t="s">
         <v>1532</v>
@@ -11543,7 +11543,7 @@
         <v>1395</v>
       </c>
       <c r="E105">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F105" t="s">
         <v>1532</v>
@@ -11578,7 +11578,7 @@
         <v>1396</v>
       </c>
       <c r="E106">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F106" t="s">
         <v>1532</v>
@@ -11613,7 +11613,7 @@
         <v>1397</v>
       </c>
       <c r="E107">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F107" t="s">
         <v>1532</v>
@@ -11648,7 +11648,7 @@
         <v>1397</v>
       </c>
       <c r="E108">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F108" t="s">
         <v>1532</v>
@@ -11683,7 +11683,7 @@
         <v>1398</v>
       </c>
       <c r="E109">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F109" t="s">
         <v>1532</v>
@@ -11718,7 +11718,7 @@
         <v>1399</v>
       </c>
       <c r="E110">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F110" t="s">
         <v>1532</v>
@@ -11753,7 +11753,7 @@
         <v>1399</v>
       </c>
       <c r="E111">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F111" t="s">
         <v>1532</v>
@@ -11788,7 +11788,7 @@
         <v>1400</v>
       </c>
       <c r="E112">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F112" t="s">
         <v>1532</v>
@@ -11823,7 +11823,7 @@
         <v>1401</v>
       </c>
       <c r="E113">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F113" t="s">
         <v>1532</v>
@@ -11861,7 +11861,7 @@
         <v>1401</v>
       </c>
       <c r="E114">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F114" t="s">
         <v>1532</v>
@@ -11896,7 +11896,7 @@
         <v>1401</v>
       </c>
       <c r="E115">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F115" t="s">
         <v>1532</v>
@@ -11931,7 +11931,7 @@
         <v>1401</v>
       </c>
       <c r="E116">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F116" t="s">
         <v>1532</v>
@@ -11966,7 +11966,7 @@
         <v>1402</v>
       </c>
       <c r="E117">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F117" t="s">
         <v>1533</v>
@@ -12001,7 +12001,7 @@
         <v>1403</v>
       </c>
       <c r="E118">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F118" t="s">
         <v>1532</v>
@@ -12036,7 +12036,7 @@
         <v>1403</v>
       </c>
       <c r="E119">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F119" t="s">
         <v>1532</v>
@@ -12071,7 +12071,7 @@
         <v>1403</v>
       </c>
       <c r="E120">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F120" t="s">
         <v>1532</v>
@@ -12106,7 +12106,7 @@
         <v>1403</v>
       </c>
       <c r="E121">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F121" t="s">
         <v>1532</v>
@@ -12141,7 +12141,7 @@
         <v>1404</v>
       </c>
       <c r="E122">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F122" t="s">
         <v>1532</v>
@@ -12176,7 +12176,7 @@
         <v>1404</v>
       </c>
       <c r="E123">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F123" t="s">
         <v>1532</v>
@@ -12211,7 +12211,7 @@
         <v>1404</v>
       </c>
       <c r="E124">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F124" t="s">
         <v>1532</v>
@@ -12246,7 +12246,7 @@
         <v>1404</v>
       </c>
       <c r="E125">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F125" t="s">
         <v>1532</v>
@@ -12281,7 +12281,7 @@
         <v>1404</v>
       </c>
       <c r="E126">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F126" t="s">
         <v>1532</v>
@@ -12316,7 +12316,7 @@
         <v>1404</v>
       </c>
       <c r="E127">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F127" t="s">
         <v>1532</v>
@@ -12351,7 +12351,7 @@
         <v>1404</v>
       </c>
       <c r="E128">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F128" t="s">
         <v>1532</v>
@@ -12386,7 +12386,7 @@
         <v>1405</v>
       </c>
       <c r="E129">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F129" t="s">
         <v>1532</v>
@@ -12421,7 +12421,7 @@
         <v>1405</v>
       </c>
       <c r="E130">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F130" t="s">
         <v>1532</v>
@@ -12456,7 +12456,7 @@
         <v>1406</v>
       </c>
       <c r="E131">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F131" t="s">
         <v>1532</v>
@@ -12491,7 +12491,7 @@
         <v>1407</v>
       </c>
       <c r="E132">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F132" t="s">
         <v>1532</v>
@@ -12526,7 +12526,7 @@
         <v>1407</v>
       </c>
       <c r="E133">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F133" t="s">
         <v>1532</v>
@@ -12561,7 +12561,7 @@
         <v>1407</v>
       </c>
       <c r="E134">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F134" t="s">
         <v>1532</v>
@@ -12596,7 +12596,7 @@
         <v>1408</v>
       </c>
       <c r="E135">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F135" t="s">
         <v>1532</v>
@@ -12631,7 +12631,7 @@
         <v>1408</v>
       </c>
       <c r="E136">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F136" t="s">
         <v>1532</v>
@@ -12666,7 +12666,7 @@
         <v>1408</v>
       </c>
       <c r="E137">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F137" t="s">
         <v>1532</v>
@@ -12701,7 +12701,7 @@
         <v>1408</v>
       </c>
       <c r="E138">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F138" t="s">
         <v>1532</v>
@@ -12736,7 +12736,7 @@
         <v>1408</v>
       </c>
       <c r="E139">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F139" t="s">
         <v>1532</v>
@@ -12771,7 +12771,7 @@
         <v>1408</v>
       </c>
       <c r="E140">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F140" t="s">
         <v>1532</v>
@@ -12806,7 +12806,7 @@
         <v>1408</v>
       </c>
       <c r="E141">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F141" t="s">
         <v>1532</v>
@@ -12841,7 +12841,7 @@
         <v>1408</v>
       </c>
       <c r="E142">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F142" t="s">
         <v>1532</v>
@@ -12876,7 +12876,7 @@
         <v>1408</v>
       </c>
       <c r="E143">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F143" t="s">
         <v>1532</v>
@@ -12911,7 +12911,7 @@
         <v>1409</v>
       </c>
       <c r="E144">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F144" t="s">
         <v>1532</v>
@@ -12946,7 +12946,7 @@
         <v>1409</v>
       </c>
       <c r="E145">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F145" t="s">
         <v>1532</v>
@@ -12981,7 +12981,7 @@
         <v>1409</v>
       </c>
       <c r="E146">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F146" t="s">
         <v>1532</v>
@@ -13016,7 +13016,7 @@
         <v>1410</v>
       </c>
       <c r="E147">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F147" t="s">
         <v>1532</v>
@@ -13051,7 +13051,7 @@
         <v>1410</v>
       </c>
       <c r="E148">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F148" t="s">
         <v>1533</v>
@@ -13086,7 +13086,7 @@
         <v>1410</v>
       </c>
       <c r="E149">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F149" t="s">
         <v>1532</v>
@@ -13121,7 +13121,7 @@
         <v>1411</v>
       </c>
       <c r="E150">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F150" t="s">
         <v>1532</v>
@@ -13156,7 +13156,7 @@
         <v>1411</v>
       </c>
       <c r="E151">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F151" t="s">
         <v>1532</v>
@@ -13191,7 +13191,7 @@
         <v>1412</v>
       </c>
       <c r="E152">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F152" t="s">
         <v>1532</v>
@@ -13226,7 +13226,7 @@
         <v>1412</v>
       </c>
       <c r="E153">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F153" t="s">
         <v>1532</v>
@@ -13261,7 +13261,7 @@
         <v>1413</v>
       </c>
       <c r="E154">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F154" t="s">
         <v>1532</v>
@@ -13296,7 +13296,7 @@
         <v>1413</v>
       </c>
       <c r="E155">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F155" t="s">
         <v>1532</v>
@@ -13331,7 +13331,7 @@
         <v>1414</v>
       </c>
       <c r="E156">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F156" t="s">
         <v>1532</v>
@@ -13366,7 +13366,7 @@
         <v>1414</v>
       </c>
       <c r="E157">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F157" t="s">
         <v>1532</v>
@@ -13401,7 +13401,7 @@
         <v>1414</v>
       </c>
       <c r="E158">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F158" t="s">
         <v>1532</v>
@@ -13436,7 +13436,7 @@
         <v>1415</v>
       </c>
       <c r="E159">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F159" t="s">
         <v>1532</v>
@@ -13471,7 +13471,7 @@
         <v>1415</v>
       </c>
       <c r="E160">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F160" t="s">
         <v>1532</v>
@@ -13506,7 +13506,7 @@
         <v>1416</v>
       </c>
       <c r="E161">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F161" t="s">
         <v>1532</v>
@@ -13541,7 +13541,7 @@
         <v>1417</v>
       </c>
       <c r="E162">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F162" t="s">
         <v>1532</v>
@@ -13576,7 +13576,7 @@
         <v>1417</v>
       </c>
       <c r="E163">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F163" t="s">
         <v>1532</v>
@@ -13611,7 +13611,7 @@
         <v>1417</v>
       </c>
       <c r="E164">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F164" t="s">
         <v>1532</v>
@@ -13646,7 +13646,7 @@
         <v>1417</v>
       </c>
       <c r="E165">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F165" t="s">
         <v>1532</v>
@@ -13681,7 +13681,7 @@
         <v>1418</v>
       </c>
       <c r="E166">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F166" t="s">
         <v>1532</v>
@@ -13716,7 +13716,7 @@
         <v>1419</v>
       </c>
       <c r="E167">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F167" t="s">
         <v>1532</v>
@@ -13751,7 +13751,7 @@
         <v>1419</v>
       </c>
       <c r="E168">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F168" t="s">
         <v>1532</v>
@@ -13786,7 +13786,7 @@
         <v>1419</v>
       </c>
       <c r="E169">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F169" t="s">
         <v>1532</v>
@@ -13821,7 +13821,7 @@
         <v>1419</v>
       </c>
       <c r="E170">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F170" t="s">
         <v>1532</v>
@@ -13856,7 +13856,7 @@
         <v>1419</v>
       </c>
       <c r="E171">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F171" t="s">
         <v>1532</v>
@@ -13891,7 +13891,7 @@
         <v>1420</v>
       </c>
       <c r="E172">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F172" t="s">
         <v>1532</v>
@@ -13926,7 +13926,7 @@
         <v>1420</v>
       </c>
       <c r="E173">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F173" t="s">
         <v>1532</v>
@@ -13961,7 +13961,7 @@
         <v>1420</v>
       </c>
       <c r="E174">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F174" t="s">
         <v>1532</v>
@@ -13996,7 +13996,7 @@
         <v>1420</v>
       </c>
       <c r="E175">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F175" t="s">
         <v>1532</v>
@@ -14031,7 +14031,7 @@
         <v>1420</v>
       </c>
       <c r="E176">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F176" t="s">
         <v>1532</v>
@@ -14066,7 +14066,7 @@
         <v>1420</v>
       </c>
       <c r="E177">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F177" t="s">
         <v>1532</v>
@@ -14101,7 +14101,7 @@
         <v>1421</v>
       </c>
       <c r="E178">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F178" t="s">
         <v>1532</v>
@@ -14136,7 +14136,7 @@
         <v>1421</v>
       </c>
       <c r="E179">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F179" t="s">
         <v>1532</v>
@@ -14171,7 +14171,7 @@
         <v>1421</v>
       </c>
       <c r="E180">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F180" t="s">
         <v>1532</v>
@@ -14206,7 +14206,7 @@
         <v>1422</v>
       </c>
       <c r="E181">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F181" t="s">
         <v>1532</v>
@@ -14241,7 +14241,7 @@
         <v>1422</v>
       </c>
       <c r="E182">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F182" t="s">
         <v>1532</v>
@@ -14276,7 +14276,7 @@
         <v>1423</v>
       </c>
       <c r="E183">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F183" t="s">
         <v>1532</v>
@@ -14311,7 +14311,7 @@
         <v>1424</v>
       </c>
       <c r="E184">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F184" t="s">
         <v>1532</v>
@@ -14346,7 +14346,7 @@
         <v>1424</v>
       </c>
       <c r="E185">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F185" t="s">
         <v>1532</v>
@@ -14381,7 +14381,7 @@
         <v>1425</v>
       </c>
       <c r="E186">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F186" t="s">
         <v>1532</v>
@@ -14416,7 +14416,7 @@
         <v>1426</v>
       </c>
       <c r="E187">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F187" t="s">
         <v>1532</v>
@@ -14451,7 +14451,7 @@
         <v>1426</v>
       </c>
       <c r="E188">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F188" t="s">
         <v>1532</v>
@@ -14486,7 +14486,7 @@
         <v>1427</v>
       </c>
       <c r="E189">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F189" t="s">
         <v>1532</v>
@@ -14521,7 +14521,7 @@
         <v>1427</v>
       </c>
       <c r="E190">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F190" t="s">
         <v>1532</v>
@@ -14556,7 +14556,7 @@
         <v>1428</v>
       </c>
       <c r="E191">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F191" t="s">
         <v>1532</v>
@@ -14591,7 +14591,7 @@
         <v>1429</v>
       </c>
       <c r="E192">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F192" t="s">
         <v>1532</v>
@@ -14626,7 +14626,7 @@
         <v>1429</v>
       </c>
       <c r="E193">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F193" t="s">
         <v>1532</v>
@@ -14661,7 +14661,7 @@
         <v>1429</v>
       </c>
       <c r="E194">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F194" t="s">
         <v>1532</v>
@@ -14696,7 +14696,7 @@
         <v>1430</v>
       </c>
       <c r="E195">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F195" t="s">
         <v>1532</v>
@@ -14731,7 +14731,7 @@
         <v>1430</v>
       </c>
       <c r="E196">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F196" t="s">
         <v>1532</v>
@@ -14766,7 +14766,7 @@
         <v>1431</v>
       </c>
       <c r="E197">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F197" t="s">
         <v>1532</v>
@@ -14801,7 +14801,7 @@
         <v>1432</v>
       </c>
       <c r="E198">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F198" t="s">
         <v>1532</v>
@@ -14836,7 +14836,7 @@
         <v>1432</v>
       </c>
       <c r="E199">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F199" t="s">
         <v>1532</v>
@@ -14871,7 +14871,7 @@
         <v>1432</v>
       </c>
       <c r="E200">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F200" t="s">
         <v>1532</v>
@@ -14906,7 +14906,7 @@
         <v>1433</v>
       </c>
       <c r="E201">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F201" t="s">
         <v>1532</v>
@@ -14941,7 +14941,7 @@
         <v>1433</v>
       </c>
       <c r="E202">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F202" t="s">
         <v>1532</v>
@@ -14976,7 +14976,7 @@
         <v>1434</v>
       </c>
       <c r="E203">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F203" t="s">
         <v>1532</v>
@@ -15011,7 +15011,7 @@
         <v>1434</v>
       </c>
       <c r="E204">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F204" t="s">
         <v>1534</v>
@@ -15046,7 +15046,7 @@
         <v>1434</v>
       </c>
       <c r="E205">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F205" t="s">
         <v>1532</v>
@@ -15081,7 +15081,7 @@
         <v>1435</v>
       </c>
       <c r="E206">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F206" t="s">
         <v>1532</v>
@@ -15116,7 +15116,7 @@
         <v>1435</v>
       </c>
       <c r="E207">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F207" t="s">
         <v>1532</v>
@@ -15154,7 +15154,7 @@
         <v>1435</v>
       </c>
       <c r="E208">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F208" t="s">
         <v>1532</v>
@@ -15189,7 +15189,7 @@
         <v>1435</v>
       </c>
       <c r="E209">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F209" t="s">
         <v>1532</v>
@@ -15224,7 +15224,7 @@
         <v>1435</v>
       </c>
       <c r="E210">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F210" t="s">
         <v>1532</v>
@@ -15259,7 +15259,7 @@
         <v>1435</v>
       </c>
       <c r="E211">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F211" t="s">
         <v>1532</v>
@@ -15294,7 +15294,7 @@
         <v>1436</v>
       </c>
       <c r="E212">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F212" t="s">
         <v>1532</v>
@@ -15329,7 +15329,7 @@
         <v>1436</v>
       </c>
       <c r="E213">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F213" t="s">
         <v>1532</v>
@@ -15364,7 +15364,7 @@
         <v>1436</v>
       </c>
       <c r="E214">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F214" t="s">
         <v>1532</v>
@@ -15399,7 +15399,7 @@
         <v>1437</v>
       </c>
       <c r="E215">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F215" t="s">
         <v>1532</v>
@@ -15434,7 +15434,7 @@
         <v>1437</v>
       </c>
       <c r="E216">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F216" t="s">
         <v>1532</v>
@@ -15469,7 +15469,7 @@
         <v>1437</v>
       </c>
       <c r="E217">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F217" t="s">
         <v>1532</v>
@@ -15504,7 +15504,7 @@
         <v>1438</v>
       </c>
       <c r="E218">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F218" t="s">
         <v>1532</v>
@@ -15539,7 +15539,7 @@
         <v>1438</v>
       </c>
       <c r="E219">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F219" t="s">
         <v>1532</v>
@@ -15574,7 +15574,7 @@
         <v>1438</v>
       </c>
       <c r="E220">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F220" t="s">
         <v>1532</v>
@@ -15609,7 +15609,7 @@
         <v>1439</v>
       </c>
       <c r="E221">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F221" t="s">
         <v>1532</v>
@@ -15644,7 +15644,7 @@
         <v>1439</v>
       </c>
       <c r="E222">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F222" t="s">
         <v>1532</v>
@@ -15679,7 +15679,7 @@
         <v>1439</v>
       </c>
       <c r="E223">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F223" t="s">
         <v>1532</v>
@@ -15714,7 +15714,7 @@
         <v>1439</v>
       </c>
       <c r="E224">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F224" t="s">
         <v>1532</v>
@@ -15749,7 +15749,7 @@
         <v>1439</v>
       </c>
       <c r="E225">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F225" t="s">
         <v>1532</v>
@@ -15784,7 +15784,7 @@
         <v>1439</v>
       </c>
       <c r="E226">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F226" t="s">
         <v>1532</v>
@@ -15819,7 +15819,7 @@
         <v>1440</v>
       </c>
       <c r="E227">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F227" t="s">
         <v>1532</v>
@@ -15854,7 +15854,7 @@
         <v>1441</v>
       </c>
       <c r="E228">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F228" t="s">
         <v>1532</v>
@@ -15889,7 +15889,7 @@
         <v>1441</v>
       </c>
       <c r="E229">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F229" t="s">
         <v>1535</v>
@@ -15924,7 +15924,7 @@
         <v>1441</v>
       </c>
       <c r="E230">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F230" t="s">
         <v>1532</v>
@@ -15959,7 +15959,7 @@
         <v>1441</v>
       </c>
       <c r="E231">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F231" t="s">
         <v>1532</v>
@@ -15994,7 +15994,7 @@
         <v>1441</v>
       </c>
       <c r="E232">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F232" t="s">
         <v>1532</v>
@@ -16029,7 +16029,7 @@
         <v>1442</v>
       </c>
       <c r="E233">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F233" t="s">
         <v>1532</v>
@@ -16064,7 +16064,7 @@
         <v>1442</v>
       </c>
       <c r="E234">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F234" t="s">
         <v>1532</v>
@@ -16099,7 +16099,7 @@
         <v>1442</v>
       </c>
       <c r="E235">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F235" t="s">
         <v>1532</v>
@@ -16134,7 +16134,7 @@
         <v>1442</v>
       </c>
       <c r="E236">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F236" t="s">
         <v>1532</v>
@@ -16169,7 +16169,7 @@
         <v>1443</v>
       </c>
       <c r="E237">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F237" t="s">
         <v>1532</v>
@@ -16204,7 +16204,7 @@
         <v>1444</v>
       </c>
       <c r="E238">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F238" t="s">
         <v>1532</v>
@@ -16242,7 +16242,7 @@
         <v>1445</v>
       </c>
       <c r="E239">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F239" t="s">
         <v>1532</v>
@@ -16277,7 +16277,7 @@
         <v>1445</v>
       </c>
       <c r="E240">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F240" t="s">
         <v>1532</v>
@@ -16312,7 +16312,7 @@
         <v>1445</v>
       </c>
       <c r="E241">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F241" t="s">
         <v>1532</v>
@@ -16347,7 +16347,7 @@
         <v>1445</v>
       </c>
       <c r="E242">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F242" t="s">
         <v>1532</v>
@@ -16385,7 +16385,7 @@
         <v>1445</v>
       </c>
       <c r="E243">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F243" t="s">
         <v>1532</v>
@@ -16420,7 +16420,7 @@
         <v>1446</v>
       </c>
       <c r="E244">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F244" t="s">
         <v>1532</v>
@@ -16455,7 +16455,7 @@
         <v>1446</v>
       </c>
       <c r="E245">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F245" t="s">
         <v>1532</v>
@@ -16490,7 +16490,7 @@
         <v>1447</v>
       </c>
       <c r="E246">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F246" t="s">
         <v>1532</v>
@@ -16525,7 +16525,7 @@
         <v>1447</v>
       </c>
       <c r="E247">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F247" t="s">
         <v>1532</v>
@@ -16560,7 +16560,7 @@
         <v>1448</v>
       </c>
       <c r="E248">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F248" t="s">
         <v>1532</v>
@@ -16595,7 +16595,7 @@
         <v>1448</v>
       </c>
       <c r="E249">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F249" t="s">
         <v>1532</v>
@@ -16630,7 +16630,7 @@
         <v>1448</v>
       </c>
       <c r="E250">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F250" t="s">
         <v>1532</v>
@@ -16665,7 +16665,7 @@
         <v>1449</v>
       </c>
       <c r="E251">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F251" t="s">
         <v>1532</v>
@@ -16700,7 +16700,7 @@
         <v>1449</v>
       </c>
       <c r="E252">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F252" t="s">
         <v>1532</v>
@@ -16735,7 +16735,7 @@
         <v>1449</v>
       </c>
       <c r="E253">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F253" t="s">
         <v>1532</v>
@@ -16770,7 +16770,7 @@
         <v>1449</v>
       </c>
       <c r="E254">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F254" t="s">
         <v>1532</v>
@@ -16805,7 +16805,7 @@
         <v>1450</v>
       </c>
       <c r="E255">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F255" t="s">
         <v>1532</v>
@@ -16840,7 +16840,7 @@
         <v>1451</v>
       </c>
       <c r="E256">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F256" t="s">
         <v>1532</v>
@@ -16875,7 +16875,7 @@
         <v>1451</v>
       </c>
       <c r="E257">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F257" t="s">
         <v>1532</v>
@@ -16910,7 +16910,7 @@
         <v>1451</v>
       </c>
       <c r="E258">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F258" t="s">
         <v>1532</v>
@@ -16945,7 +16945,7 @@
         <v>1451</v>
       </c>
       <c r="E259">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F259" t="s">
         <v>1532</v>
@@ -16980,7 +16980,7 @@
         <v>1452</v>
       </c>
       <c r="E260">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F260" t="s">
         <v>1532</v>
@@ -17015,7 +17015,7 @@
         <v>1452</v>
       </c>
       <c r="E261">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F261" t="s">
         <v>1532</v>
@@ -17050,7 +17050,7 @@
         <v>1452</v>
       </c>
       <c r="E262">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F262" t="s">
         <v>1532</v>
@@ -17085,7 +17085,7 @@
         <v>1453</v>
       </c>
       <c r="E263">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F263" t="s">
         <v>1532</v>
@@ -17120,7 +17120,7 @@
         <v>1453</v>
       </c>
       <c r="E264">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F264" t="s">
         <v>1532</v>
@@ -17155,7 +17155,7 @@
         <v>1454</v>
       </c>
       <c r="E265">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F265" t="s">
         <v>1532</v>
@@ -17190,7 +17190,7 @@
         <v>1454</v>
       </c>
       <c r="E266">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F266" t="s">
         <v>1532</v>
@@ -17225,7 +17225,7 @@
         <v>1454</v>
       </c>
       <c r="E267">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F267" t="s">
         <v>1532</v>
@@ -17260,7 +17260,7 @@
         <v>1454</v>
       </c>
       <c r="E268">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F268" t="s">
         <v>1532</v>
@@ -17295,7 +17295,7 @@
         <v>1454</v>
       </c>
       <c r="E269">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F269" t="s">
         <v>1532</v>
@@ -17330,7 +17330,7 @@
         <v>1455</v>
       </c>
       <c r="E270">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F270" t="s">
         <v>1532</v>
@@ -17365,7 +17365,7 @@
         <v>1455</v>
       </c>
       <c r="E271">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F271" t="s">
         <v>1532</v>
@@ -17400,7 +17400,7 @@
         <v>1455</v>
       </c>
       <c r="E272">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F272" t="s">
         <v>1532</v>
@@ -17435,7 +17435,7 @@
         <v>1456</v>
       </c>
       <c r="E273">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F273" t="s">
         <v>1532</v>
@@ -17470,7 +17470,7 @@
         <v>1457</v>
       </c>
       <c r="E274">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F274" t="s">
         <v>1532</v>
@@ -17505,7 +17505,7 @@
         <v>1458</v>
       </c>
       <c r="E275">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F275" t="s">
         <v>1532</v>
@@ -17540,7 +17540,7 @@
         <v>1458</v>
       </c>
       <c r="E276">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F276" t="s">
         <v>1532</v>
@@ -17575,7 +17575,7 @@
         <v>1458</v>
       </c>
       <c r="E277">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F277" t="s">
         <v>1532</v>
@@ -17610,7 +17610,7 @@
         <v>1458</v>
       </c>
       <c r="E278">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F278" t="s">
         <v>1532</v>
@@ -17645,7 +17645,7 @@
         <v>1458</v>
       </c>
       <c r="E279">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F279" t="s">
         <v>1532</v>
@@ -17680,7 +17680,7 @@
         <v>1459</v>
       </c>
       <c r="E280">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F280" t="s">
         <v>1532</v>
@@ -17715,7 +17715,7 @@
         <v>1459</v>
       </c>
       <c r="E281">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F281" t="s">
         <v>1532</v>
@@ -17750,7 +17750,7 @@
         <v>1460</v>
       </c>
       <c r="E282">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F282" t="s">
         <v>1532</v>
@@ -17785,7 +17785,7 @@
         <v>1460</v>
       </c>
       <c r="E283">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F283" t="s">
         <v>1532</v>
@@ -17820,7 +17820,7 @@
         <v>1461</v>
       </c>
       <c r="E284">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F284" t="s">
         <v>1532</v>
@@ -17855,7 +17855,7 @@
         <v>1462</v>
       </c>
       <c r="E285">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F285" t="s">
         <v>1532</v>
@@ -17890,7 +17890,7 @@
         <v>1463</v>
       </c>
       <c r="E286">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F286" t="s">
         <v>1532</v>
@@ -17925,7 +17925,7 @@
         <v>1463</v>
       </c>
       <c r="E287">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F287" t="s">
         <v>1532</v>
@@ -17960,7 +17960,7 @@
         <v>1464</v>
       </c>
       <c r="E288">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F288" t="s">
         <v>1532</v>
@@ -17995,7 +17995,7 @@
         <v>1464</v>
       </c>
       <c r="E289">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F289" t="s">
         <v>1532</v>
@@ -18030,7 +18030,7 @@
         <v>1464</v>
       </c>
       <c r="E290">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F290" t="s">
         <v>1532</v>
@@ -18065,7 +18065,7 @@
         <v>1465</v>
       </c>
       <c r="E291">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F291" t="s">
         <v>1532</v>
@@ -18100,7 +18100,7 @@
         <v>1465</v>
       </c>
       <c r="E292">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F292" t="s">
         <v>1532</v>
@@ -18135,7 +18135,7 @@
         <v>1465</v>
       </c>
       <c r="E293">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F293" t="s">
         <v>1532</v>
@@ -18170,7 +18170,7 @@
         <v>1465</v>
       </c>
       <c r="E294">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F294" t="s">
         <v>1532</v>
@@ -18205,7 +18205,7 @@
         <v>1465</v>
       </c>
       <c r="E295">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F295" t="s">
         <v>1532</v>
@@ -18240,7 +18240,7 @@
         <v>1465</v>
       </c>
       <c r="E296">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F296" t="s">
         <v>1532</v>
@@ -18275,7 +18275,7 @@
         <v>1465</v>
       </c>
       <c r="E297">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F297" t="s">
         <v>1532</v>
@@ -18310,7 +18310,7 @@
         <v>1465</v>
       </c>
       <c r="E298">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F298" t="s">
         <v>1532</v>
@@ -18345,7 +18345,7 @@
         <v>1465</v>
       </c>
       <c r="E299">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F299" t="s">
         <v>1532</v>
@@ -18380,7 +18380,7 @@
         <v>1466</v>
       </c>
       <c r="E300">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F300" t="s">
         <v>1532</v>
@@ -18415,7 +18415,7 @@
         <v>1466</v>
       </c>
       <c r="E301">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F301" t="s">
         <v>1532</v>
@@ -18450,7 +18450,7 @@
         <v>1466</v>
       </c>
       <c r="E302">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F302" t="s">
         <v>1532</v>
@@ -18485,7 +18485,7 @@
         <v>1467</v>
       </c>
       <c r="E303">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F303" t="s">
         <v>1532</v>
@@ -18520,7 +18520,7 @@
         <v>1468</v>
       </c>
       <c r="E304">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F304" t="s">
         <v>1532</v>
@@ -18555,7 +18555,7 @@
         <v>1468</v>
       </c>
       <c r="E305">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F305" t="s">
         <v>1532</v>
@@ -18590,7 +18590,7 @@
         <v>1468</v>
       </c>
       <c r="E306">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F306" t="s">
         <v>1532</v>
@@ -18625,7 +18625,7 @@
         <v>1468</v>
       </c>
       <c r="E307">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F307" t="s">
         <v>1532</v>
@@ -18660,7 +18660,7 @@
         <v>1468</v>
       </c>
       <c r="E308">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F308" t="s">
         <v>1536</v>
@@ -18698,7 +18698,7 @@
         <v>1468</v>
       </c>
       <c r="E309">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F309" t="s">
         <v>1532</v>
@@ -18733,7 +18733,7 @@
         <v>1468</v>
       </c>
       <c r="E310">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F310" t="s">
         <v>1532</v>
@@ -18768,7 +18768,7 @@
         <v>1469</v>
       </c>
       <c r="E311">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F311" t="s">
         <v>1532</v>
@@ -18803,7 +18803,7 @@
         <v>1469</v>
       </c>
       <c r="E312">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F312" t="s">
         <v>1532</v>
@@ -18838,7 +18838,7 @@
         <v>1469</v>
       </c>
       <c r="E313">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F313" t="s">
         <v>1532</v>
@@ -18873,7 +18873,7 @@
         <v>1469</v>
       </c>
       <c r="E314">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F314" t="s">
         <v>1532</v>
@@ -18911,7 +18911,7 @@
         <v>1469</v>
       </c>
       <c r="E315">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F315" t="s">
         <v>1532</v>
@@ -18946,7 +18946,7 @@
         <v>1469</v>
       </c>
       <c r="E316">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F316" t="s">
         <v>1532</v>
@@ -18981,7 +18981,7 @@
         <v>1469</v>
       </c>
       <c r="E317">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F317" t="s">
         <v>1532</v>
@@ -19016,7 +19016,7 @@
         <v>1469</v>
       </c>
       <c r="E318">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F318" t="s">
         <v>1532</v>
@@ -19051,7 +19051,7 @@
         <v>1469</v>
       </c>
       <c r="E319">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F319" t="s">
         <v>1532</v>
@@ -19086,7 +19086,7 @@
         <v>1470</v>
       </c>
       <c r="E320">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F320" t="s">
         <v>1533</v>
@@ -19121,7 +19121,7 @@
         <v>1471</v>
       </c>
       <c r="E321">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F321" t="s">
         <v>1536</v>
@@ -19156,7 +19156,7 @@
         <v>1472</v>
       </c>
       <c r="E322">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F322" t="s">
         <v>1532</v>
@@ -19191,7 +19191,7 @@
         <v>1473</v>
       </c>
       <c r="E323">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F323" t="s">
         <v>1532</v>
@@ -19226,7 +19226,7 @@
         <v>1473</v>
       </c>
       <c r="E324">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F324" t="s">
         <v>1532</v>
@@ -19261,7 +19261,7 @@
         <v>1474</v>
       </c>
       <c r="E325">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F325" t="s">
         <v>1532</v>
@@ -19296,7 +19296,7 @@
         <v>1475</v>
       </c>
       <c r="E326">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F326" t="s">
         <v>1535</v>
@@ -19331,7 +19331,7 @@
         <v>1475</v>
       </c>
       <c r="E327">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F327" t="s">
         <v>1532</v>
@@ -19366,7 +19366,7 @@
         <v>1475</v>
       </c>
       <c r="E328">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F328" t="s">
         <v>1532</v>
@@ -19401,7 +19401,7 @@
         <v>1475</v>
       </c>
       <c r="E329">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F329" t="s">
         <v>1532</v>
@@ -19436,7 +19436,7 @@
         <v>1475</v>
       </c>
       <c r="E330">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F330" t="s">
         <v>1532</v>
@@ -19471,7 +19471,7 @@
         <v>1475</v>
       </c>
       <c r="E331">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F331" t="s">
         <v>1532</v>
@@ -19506,7 +19506,7 @@
         <v>1476</v>
       </c>
       <c r="E332">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F332" t="s">
         <v>1532</v>
@@ -19541,7 +19541,7 @@
         <v>1477</v>
       </c>
       <c r="E333">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F333" t="s">
         <v>1532</v>
@@ -19576,7 +19576,7 @@
         <v>1477</v>
       </c>
       <c r="E334">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F334" t="s">
         <v>1532</v>
@@ -19611,7 +19611,7 @@
         <v>1477</v>
       </c>
       <c r="E335">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F335" t="s">
         <v>1532</v>
@@ -19649,7 +19649,7 @@
         <v>1477</v>
       </c>
       <c r="E336">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F336" t="s">
         <v>1532</v>
@@ -19684,7 +19684,7 @@
         <v>1478</v>
       </c>
       <c r="E337">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F337" t="s">
         <v>1532</v>
@@ -19719,7 +19719,7 @@
         <v>1478</v>
       </c>
       <c r="E338">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F338" t="s">
         <v>1532</v>
@@ -19754,7 +19754,7 @@
         <v>1478</v>
       </c>
       <c r="E339">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F339" t="s">
         <v>1532</v>
@@ -19789,7 +19789,7 @@
         <v>1478</v>
       </c>
       <c r="E340">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F340" t="s">
         <v>1532</v>
@@ -19824,7 +19824,7 @@
         <v>1478</v>
       </c>
       <c r="E341">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F341" t="s">
         <v>1532</v>
@@ -19859,7 +19859,7 @@
         <v>1479</v>
       </c>
       <c r="E342">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F342" t="s">
         <v>1532</v>
@@ -19894,7 +19894,7 @@
         <v>1479</v>
       </c>
       <c r="E343">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F343" t="s">
         <v>1532</v>
@@ -19929,7 +19929,7 @@
         <v>1480</v>
       </c>
       <c r="E344">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F344" t="s">
         <v>1532</v>
@@ -19964,7 +19964,7 @@
         <v>1480</v>
       </c>
       <c r="E345">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F345" t="s">
         <v>1532</v>
@@ -19999,7 +19999,7 @@
         <v>1480</v>
       </c>
       <c r="E346">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F346" t="s">
         <v>1532</v>
@@ -20034,7 +20034,7 @@
         <v>1480</v>
       </c>
       <c r="E347">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F347" t="s">
         <v>1532</v>
@@ -20069,7 +20069,7 @@
         <v>1480</v>
       </c>
       <c r="E348">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F348" t="s">
         <v>1532</v>
@@ -20104,7 +20104,7 @@
         <v>1480</v>
       </c>
       <c r="E349">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F349" t="s">
         <v>1532</v>
@@ -20139,7 +20139,7 @@
         <v>1480</v>
       </c>
       <c r="E350">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F350" t="s">
         <v>1532</v>
@@ -20174,7 +20174,7 @@
         <v>1480</v>
       </c>
       <c r="E351">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F351" t="s">
         <v>1532</v>
@@ -20209,7 +20209,7 @@
         <v>1480</v>
       </c>
       <c r="E352">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F352" t="s">
         <v>1532</v>
@@ -20244,7 +20244,7 @@
         <v>1480</v>
       </c>
       <c r="E353">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F353" t="s">
         <v>1532</v>
@@ -20279,7 +20279,7 @@
         <v>1481</v>
       </c>
       <c r="E354">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F354" t="s">
         <v>1532</v>
@@ -20314,7 +20314,7 @@
         <v>1481</v>
       </c>
       <c r="E355">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F355" t="s">
         <v>1532</v>
@@ -20349,7 +20349,7 @@
         <v>1481</v>
       </c>
       <c r="E356">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F356" t="s">
         <v>1533</v>
@@ -20384,7 +20384,7 @@
         <v>1482</v>
       </c>
       <c r="E357">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F357" t="s">
         <v>1532</v>
@@ -20419,7 +20419,7 @@
         <v>1482</v>
       </c>
       <c r="E358">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F358" t="s">
         <v>1532</v>
@@ -20454,7 +20454,7 @@
         <v>1482</v>
       </c>
       <c r="E359">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F359" t="s">
         <v>1532</v>
@@ -20489,7 +20489,7 @@
         <v>1482</v>
       </c>
       <c r="E360">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F360" t="s">
         <v>1532</v>
@@ -20524,7 +20524,7 @@
         <v>1482</v>
       </c>
       <c r="E361">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F361" t="s">
         <v>1532</v>
@@ -20559,7 +20559,7 @@
         <v>1482</v>
       </c>
       <c r="E362">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F362" t="s">
         <v>1532</v>
@@ -20594,7 +20594,7 @@
         <v>1482</v>
       </c>
       <c r="E363">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F363" t="s">
         <v>1535</v>
@@ -20629,7 +20629,7 @@
         <v>1483</v>
       </c>
       <c r="E364">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F364" t="s">
         <v>1532</v>
@@ -20664,7 +20664,7 @@
         <v>1483</v>
       </c>
       <c r="E365">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F365" t="s">
         <v>1532</v>
@@ -20699,7 +20699,7 @@
         <v>1483</v>
       </c>
       <c r="E366">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F366" t="s">
         <v>1532</v>
@@ -20734,7 +20734,7 @@
         <v>1483</v>
       </c>
       <c r="E367">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F367" t="s">
         <v>1532</v>
@@ -20769,7 +20769,7 @@
         <v>1484</v>
       </c>
       <c r="E368">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F368" t="s">
         <v>1535</v>
@@ -20804,7 +20804,7 @@
         <v>1484</v>
       </c>
       <c r="E369">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F369" t="s">
         <v>1532</v>
@@ -20839,7 +20839,7 @@
         <v>1484</v>
       </c>
       <c r="E370">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F370" t="s">
         <v>1532</v>
@@ -20874,7 +20874,7 @@
         <v>1484</v>
       </c>
       <c r="E371">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F371" t="s">
         <v>1532</v>
@@ -20909,7 +20909,7 @@
         <v>1484</v>
       </c>
       <c r="E372">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F372" t="s">
         <v>1532</v>
@@ -20944,7 +20944,7 @@
         <v>1484</v>
       </c>
       <c r="E373">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F373" t="s">
         <v>1532</v>
@@ -20979,7 +20979,7 @@
         <v>1485</v>
       </c>
       <c r="E374">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F374" t="s">
         <v>1532</v>
@@ -21014,7 +21014,7 @@
         <v>1485</v>
       </c>
       <c r="E375">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F375" t="s">
         <v>1532</v>
@@ -21049,7 +21049,7 @@
         <v>1485</v>
       </c>
       <c r="E376">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F376" t="s">
         <v>1532</v>
@@ -21084,7 +21084,7 @@
         <v>1485</v>
       </c>
       <c r="E377">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F377" t="s">
         <v>1534</v>
@@ -21119,7 +21119,7 @@
         <v>1485</v>
       </c>
       <c r="E378">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F378" t="s">
         <v>1532</v>
@@ -21154,7 +21154,7 @@
         <v>1485</v>
       </c>
       <c r="E379">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F379" t="s">
         <v>1532</v>
@@ -21189,7 +21189,7 @@
         <v>1486</v>
       </c>
       <c r="E380">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F380" t="s">
         <v>1532</v>
@@ -21224,7 +21224,7 @@
         <v>1486</v>
       </c>
       <c r="E381">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F381" t="s">
         <v>1532</v>
@@ -21259,7 +21259,7 @@
         <v>1486</v>
       </c>
       <c r="E382">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F382" t="s">
         <v>1532</v>
@@ -21294,7 +21294,7 @@
         <v>1486</v>
       </c>
       <c r="E383">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F383" t="s">
         <v>1532</v>
@@ -21329,7 +21329,7 @@
         <v>1486</v>
       </c>
       <c r="E384">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F384" t="s">
         <v>1532</v>
@@ -21364,7 +21364,7 @@
         <v>1487</v>
       </c>
       <c r="E385">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F385" t="s">
         <v>1532</v>
@@ -21399,7 +21399,7 @@
         <v>1487</v>
       </c>
       <c r="E386">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F386" t="s">
         <v>1532</v>
@@ -21434,7 +21434,7 @@
         <v>1487</v>
       </c>
       <c r="E387">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F387" t="s">
         <v>1532</v>
@@ -21469,7 +21469,7 @@
         <v>1487</v>
       </c>
       <c r="E388">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F388" t="s">
         <v>1532</v>
@@ -21507,7 +21507,7 @@
         <v>1488</v>
       </c>
       <c r="E389">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F389" t="s">
         <v>1532</v>
@@ -21542,7 +21542,7 @@
         <v>1488</v>
       </c>
       <c r="E390">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F390" t="s">
         <v>1532</v>
@@ -21577,7 +21577,7 @@
         <v>1488</v>
       </c>
       <c r="E391">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F391" t="s">
         <v>1532</v>
@@ -21612,7 +21612,7 @@
         <v>1488</v>
       </c>
       <c r="E392">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F392" t="s">
         <v>1532</v>
@@ -21647,7 +21647,7 @@
         <v>1488</v>
       </c>
       <c r="E393">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F393" t="s">
         <v>1532</v>
@@ -21682,7 +21682,7 @@
         <v>1488</v>
       </c>
       <c r="E394">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F394" t="s">
         <v>1532</v>
@@ -21717,7 +21717,7 @@
         <v>1489</v>
       </c>
       <c r="E395">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F395" t="s">
         <v>1533</v>
@@ -21752,7 +21752,7 @@
         <v>1489</v>
       </c>
       <c r="E396">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F396" t="s">
         <v>1532</v>
@@ -21787,7 +21787,7 @@
         <v>1490</v>
       </c>
       <c r="E397">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F397" t="s">
         <v>1532</v>
@@ -21822,7 +21822,7 @@
         <v>1491</v>
       </c>
       <c r="E398">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F398" t="s">
         <v>1532</v>
@@ -21857,7 +21857,7 @@
         <v>1491</v>
       </c>
       <c r="E399">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F399" t="s">
         <v>1532</v>
@@ -21892,7 +21892,7 @@
         <v>1491</v>
       </c>
       <c r="E400">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F400" t="s">
         <v>1534</v>
@@ -21930,7 +21930,7 @@
         <v>1492</v>
       </c>
       <c r="E401">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F401" t="s">
         <v>1532</v>
@@ -21965,7 +21965,7 @@
         <v>1492</v>
       </c>
       <c r="E402">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F402" t="s">
         <v>1532</v>
@@ -22000,7 +22000,7 @@
         <v>1492</v>
       </c>
       <c r="E403">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F403" t="s">
         <v>1532</v>
@@ -22035,7 +22035,7 @@
         <v>1493</v>
       </c>
       <c r="E404">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F404" t="s">
         <v>1532</v>
@@ -22070,7 +22070,7 @@
         <v>1493</v>
       </c>
       <c r="E405">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F405" t="s">
         <v>1532</v>
@@ -22105,7 +22105,7 @@
         <v>1493</v>
       </c>
       <c r="E406">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F406" t="s">
         <v>1532</v>
@@ -22140,7 +22140,7 @@
         <v>1493</v>
       </c>
       <c r="E407">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F407" t="s">
         <v>1532</v>
@@ -22175,7 +22175,7 @@
         <v>1493</v>
       </c>
       <c r="E408">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F408" t="s">
         <v>1532</v>
@@ -22210,7 +22210,7 @@
         <v>1493</v>
       </c>
       <c r="E409">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F409" t="s">
         <v>1532</v>
@@ -22245,7 +22245,7 @@
         <v>1493</v>
       </c>
       <c r="E410">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F410" t="s">
         <v>1532</v>
@@ -22280,7 +22280,7 @@
         <v>1493</v>
       </c>
       <c r="E411">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F411" t="s">
         <v>1532</v>
@@ -22315,7 +22315,7 @@
         <v>1494</v>
       </c>
       <c r="E412">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F412" t="s">
         <v>1532</v>
@@ -22350,7 +22350,7 @@
         <v>1495</v>
       </c>
       <c r="E413">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F413" t="s">
         <v>1532</v>
@@ -22385,7 +22385,7 @@
         <v>1495</v>
       </c>
       <c r="E414">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F414" t="s">
         <v>1532</v>
@@ -22420,7 +22420,7 @@
         <v>1495</v>
       </c>
       <c r="E415">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F415" t="s">
         <v>1532</v>
@@ -22455,7 +22455,7 @@
         <v>1495</v>
       </c>
       <c r="E416">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F416" t="s">
         <v>1536</v>
@@ -22493,7 +22493,7 @@
         <v>1495</v>
       </c>
       <c r="E417">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F417" t="s">
         <v>1532</v>
@@ -22528,7 +22528,7 @@
         <v>1495</v>
       </c>
       <c r="E418">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F418" t="s">
         <v>1536</v>
@@ -22563,7 +22563,7 @@
         <v>1496</v>
       </c>
       <c r="E419">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F419" t="s">
         <v>1532</v>
@@ -22598,7 +22598,7 @@
         <v>1497</v>
       </c>
       <c r="E420">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F420" t="s">
         <v>1532</v>
@@ -22633,7 +22633,7 @@
         <v>1497</v>
       </c>
       <c r="E421">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F421" t="s">
         <v>1532</v>
@@ -22668,7 +22668,7 @@
         <v>1497</v>
       </c>
       <c r="E422">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F422" t="s">
         <v>1532</v>
@@ -22703,7 +22703,7 @@
         <v>1497</v>
       </c>
       <c r="E423">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F423" t="s">
         <v>1532</v>
@@ -22738,7 +22738,7 @@
         <v>1498</v>
       </c>
       <c r="E424">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F424" t="s">
         <v>1536</v>
@@ -22773,7 +22773,7 @@
         <v>1498</v>
       </c>
       <c r="E425">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F425" t="s">
         <v>1532</v>
@@ -22808,7 +22808,7 @@
         <v>1498</v>
       </c>
       <c r="E426">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F426" t="s">
         <v>1532</v>
@@ -22843,7 +22843,7 @@
         <v>1498</v>
       </c>
       <c r="E427">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F427" t="s">
         <v>1532</v>
@@ -22878,7 +22878,7 @@
         <v>1499</v>
       </c>
       <c r="E428">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F428" t="s">
         <v>1532</v>
@@ -22913,7 +22913,7 @@
         <v>1499</v>
       </c>
       <c r="E429">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F429" t="s">
         <v>1532</v>
@@ -22948,7 +22948,7 @@
         <v>1499</v>
       </c>
       <c r="E430">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F430" t="s">
         <v>1532</v>
@@ -22983,7 +22983,7 @@
         <v>1500</v>
       </c>
       <c r="E431">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F431" t="s">
         <v>1532</v>
@@ -23018,7 +23018,7 @@
         <v>1500</v>
       </c>
       <c r="E432">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F432" t="s">
         <v>1532</v>
@@ -23053,7 +23053,7 @@
         <v>1500</v>
       </c>
       <c r="E433">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F433" t="s">
         <v>1532</v>
@@ -23088,7 +23088,7 @@
         <v>1500</v>
       </c>
       <c r="E434">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F434" t="s">
         <v>1532</v>
@@ -23123,7 +23123,7 @@
         <v>1500</v>
       </c>
       <c r="E435">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F435" t="s">
         <v>1532</v>
@@ -23158,7 +23158,7 @@
         <v>1501</v>
       </c>
       <c r="E436">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F436" t="s">
         <v>1532</v>
@@ -23193,7 +23193,7 @@
         <v>1501</v>
       </c>
       <c r="E437">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F437" t="s">
         <v>1532</v>
@@ -23228,7 +23228,7 @@
         <v>1501</v>
       </c>
       <c r="E438">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F438" t="s">
         <v>1532</v>
@@ -23263,7 +23263,7 @@
         <v>1501</v>
       </c>
       <c r="E439">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F439" t="s">
         <v>1532</v>
@@ -23298,7 +23298,7 @@
         <v>1501</v>
       </c>
       <c r="E440">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F440" t="s">
         <v>1532</v>
@@ -23333,7 +23333,7 @@
         <v>1501</v>
       </c>
       <c r="E441">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F441" t="s">
         <v>1532</v>
@@ -23368,7 +23368,7 @@
         <v>1501</v>
       </c>
       <c r="E442">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F442" t="s">
         <v>1532</v>
@@ -23403,7 +23403,7 @@
         <v>1501</v>
       </c>
       <c r="E443">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F443" t="s">
         <v>1532</v>
@@ -23438,7 +23438,7 @@
         <v>1501</v>
       </c>
       <c r="E444">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F444" t="s">
         <v>1532</v>
@@ -23473,7 +23473,7 @@
         <v>1501</v>
       </c>
       <c r="E445">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F445" t="s">
         <v>1532</v>
@@ -23508,7 +23508,7 @@
         <v>1501</v>
       </c>
       <c r="E446">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F446" t="s">
         <v>1532</v>
@@ -23543,7 +23543,7 @@
         <v>1501</v>
       </c>
       <c r="E447">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F447" t="s">
         <v>1532</v>
@@ -23578,7 +23578,7 @@
         <v>1501</v>
       </c>
       <c r="E448">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F448" t="s">
         <v>1532</v>
@@ -23613,7 +23613,7 @@
         <v>1501</v>
       </c>
       <c r="E449">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F449" t="s">
         <v>1532</v>
@@ -23648,7 +23648,7 @@
         <v>1501</v>
       </c>
       <c r="E450">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F450" t="s">
         <v>1532</v>
@@ -23683,7 +23683,7 @@
         <v>1501</v>
       </c>
       <c r="E451">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F451" t="s">
         <v>1532</v>
@@ -23718,7 +23718,7 @@
         <v>1501</v>
       </c>
       <c r="E452">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F452" t="s">
         <v>1532</v>
@@ -23753,7 +23753,7 @@
         <v>1501</v>
       </c>
       <c r="E453">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F453" t="s">
         <v>1532</v>
@@ -23788,7 +23788,7 @@
         <v>1501</v>
       </c>
       <c r="E454">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F454" t="s">
         <v>1532</v>
@@ -23823,7 +23823,7 @@
         <v>1501</v>
       </c>
       <c r="E455">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F455" t="s">
         <v>1532</v>
@@ -23858,7 +23858,7 @@
         <v>1501</v>
       </c>
       <c r="E456">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F456" t="s">
         <v>1532</v>
@@ -23893,7 +23893,7 @@
         <v>1501</v>
       </c>
       <c r="E457">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F457" t="s">
         <v>1532</v>
@@ -23928,7 +23928,7 @@
         <v>1501</v>
       </c>
       <c r="E458">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F458" t="s">
         <v>1532</v>
@@ -23963,7 +23963,7 @@
         <v>1501</v>
       </c>
       <c r="E459">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F459" t="s">
         <v>1532</v>
@@ -23998,7 +23998,7 @@
         <v>1502</v>
       </c>
       <c r="E460">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F460" t="s">
         <v>1532</v>
@@ -24033,7 +24033,7 @@
         <v>1502</v>
       </c>
       <c r="E461">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F461" t="s">
         <v>1532</v>
@@ -24068,7 +24068,7 @@
         <v>1502</v>
       </c>
       <c r="E462">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F462" t="s">
         <v>1532</v>
@@ -24103,7 +24103,7 @@
         <v>1502</v>
       </c>
       <c r="E463">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F463" t="s">
         <v>1532</v>
@@ -24138,7 +24138,7 @@
         <v>1502</v>
       </c>
       <c r="E464">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F464" t="s">
         <v>1532</v>
@@ -24173,7 +24173,7 @@
         <v>1502</v>
       </c>
       <c r="E465">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F465" t="s">
         <v>1532</v>
@@ -24208,7 +24208,7 @@
         <v>1502</v>
       </c>
       <c r="E466">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F466" t="s">
         <v>1536</v>
@@ -24243,7 +24243,7 @@
         <v>1502</v>
       </c>
       <c r="E467">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F467" t="s">
         <v>1532</v>
@@ -24278,7 +24278,7 @@
         <v>1503</v>
       </c>
       <c r="E468">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F468" t="s">
         <v>1532</v>
@@ -24313,7 +24313,7 @@
         <v>1504</v>
       </c>
       <c r="E469">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F469" t="s">
         <v>1534</v>
@@ -24351,7 +24351,7 @@
         <v>1504</v>
       </c>
       <c r="E470">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F470" t="s">
         <v>1532</v>
@@ -24386,7 +24386,7 @@
         <v>1504</v>
       </c>
       <c r="E471">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F471" t="s">
         <v>1532</v>
@@ -24421,7 +24421,7 @@
         <v>1504</v>
       </c>
       <c r="E472">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F472" t="s">
         <v>1532</v>
@@ -24456,7 +24456,7 @@
         <v>1504</v>
       </c>
       <c r="E473">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F473" t="s">
         <v>1532</v>
@@ -24491,7 +24491,7 @@
         <v>1505</v>
       </c>
       <c r="E474">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F474" t="s">
         <v>1532</v>
@@ -24529,7 +24529,7 @@
         <v>1505</v>
       </c>
       <c r="E475">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F475" t="s">
         <v>1536</v>
@@ -24564,7 +24564,7 @@
         <v>1505</v>
       </c>
       <c r="E476">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F476" t="s">
         <v>1534</v>
@@ -24599,7 +24599,7 @@
         <v>1505</v>
       </c>
       <c r="E477">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F477" t="s">
         <v>1532</v>
@@ -24634,7 +24634,7 @@
         <v>1505</v>
       </c>
       <c r="E478">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F478" t="s">
         <v>1532</v>
@@ -24669,7 +24669,7 @@
         <v>1505</v>
       </c>
       <c r="E479">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F479" t="s">
         <v>1532</v>
@@ -24704,7 +24704,7 @@
         <v>1505</v>
       </c>
       <c r="E480">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F480" t="s">
         <v>1532</v>
@@ -24739,7 +24739,7 @@
         <v>1505</v>
       </c>
       <c r="E481">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F481" t="s">
         <v>1532</v>
@@ -24774,7 +24774,7 @@
         <v>1505</v>
       </c>
       <c r="E482">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F482" t="s">
         <v>1532</v>
@@ -24809,7 +24809,7 @@
         <v>1506</v>
       </c>
       <c r="E483">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F483" t="s">
         <v>1536</v>
@@ -24847,7 +24847,7 @@
         <v>1506</v>
       </c>
       <c r="E484">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F484" t="s">
         <v>1532</v>
@@ -24882,7 +24882,7 @@
         <v>1507</v>
       </c>
       <c r="E485">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F485" t="s">
         <v>1532</v>
@@ -24917,7 +24917,7 @@
         <v>1507</v>
       </c>
       <c r="E486">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F486" t="s">
         <v>1532</v>
@@ -24952,7 +24952,7 @@
         <v>1507</v>
       </c>
       <c r="E487">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F487" t="s">
         <v>1532</v>
@@ -24987,7 +24987,7 @@
         <v>1507</v>
       </c>
       <c r="E488">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F488" t="s">
         <v>1532</v>
@@ -25022,7 +25022,7 @@
         <v>1507</v>
       </c>
       <c r="E489">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F489" t="s">
         <v>1532</v>
@@ -25057,7 +25057,7 @@
         <v>1507</v>
       </c>
       <c r="E490">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F490" t="s">
         <v>1532</v>
@@ -25092,7 +25092,7 @@
         <v>1508</v>
       </c>
       <c r="E491">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F491" t="s">
         <v>1532</v>
@@ -25127,7 +25127,7 @@
         <v>1508</v>
       </c>
       <c r="E492">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F492" t="s">
         <v>1532</v>
@@ -25162,7 +25162,7 @@
         <v>1508</v>
       </c>
       <c r="E493">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F493" t="s">
         <v>1532</v>
@@ -25197,7 +25197,7 @@
         <v>1508</v>
       </c>
       <c r="E494">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F494" t="s">
         <v>1532</v>
@@ -25232,7 +25232,7 @@
         <v>1508</v>
       </c>
       <c r="E495">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F495" t="s">
         <v>1532</v>
@@ -25267,7 +25267,7 @@
         <v>1508</v>
       </c>
       <c r="E496">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F496" t="s">
         <v>1534</v>
@@ -25302,7 +25302,7 @@
         <v>1508</v>
       </c>
       <c r="E497">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F497" t="s">
         <v>1532</v>
@@ -25337,7 +25337,7 @@
         <v>1508</v>
       </c>
       <c r="E498">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F498" t="s">
         <v>1532</v>
@@ -25372,7 +25372,7 @@
         <v>1509</v>
       </c>
       <c r="E499">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F499" t="s">
         <v>1532</v>
@@ -25407,7 +25407,7 @@
         <v>1509</v>
       </c>
       <c r="E500">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F500" t="s">
         <v>1532</v>
@@ -25442,7 +25442,7 @@
         <v>1509</v>
       </c>
       <c r="E501">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F501" t="s">
         <v>1532</v>
@@ -25477,7 +25477,7 @@
         <v>1509</v>
       </c>
       <c r="E502">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F502" t="s">
         <v>1532</v>
@@ -25512,7 +25512,7 @@
         <v>1509</v>
       </c>
       <c r="E503">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F503" t="s">
         <v>1532</v>
@@ -25547,7 +25547,7 @@
         <v>1509</v>
       </c>
       <c r="E504">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F504" t="s">
         <v>1532</v>
@@ -25582,7 +25582,7 @@
         <v>1509</v>
       </c>
       <c r="E505">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F505" t="s">
         <v>1532</v>
@@ -25617,7 +25617,7 @@
         <v>1509</v>
       </c>
       <c r="E506">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F506" t="s">
         <v>1532</v>
@@ -25652,7 +25652,7 @@
         <v>1510</v>
       </c>
       <c r="E507">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F507" t="s">
         <v>1532</v>
@@ -25687,7 +25687,7 @@
         <v>1510</v>
       </c>
       <c r="E508">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F508" t="s">
         <v>1532</v>
@@ -25722,7 +25722,7 @@
         <v>1510</v>
       </c>
       <c r="E509">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F509" t="s">
         <v>1532</v>
@@ -25757,7 +25757,7 @@
         <v>1510</v>
       </c>
       <c r="E510">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F510" t="s">
         <v>1532</v>
@@ -25792,7 +25792,7 @@
         <v>1510</v>
       </c>
       <c r="E511">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F511" t="s">
         <v>1532</v>
@@ -25827,7 +25827,7 @@
         <v>1510</v>
       </c>
       <c r="E512">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F512" t="s">
         <v>1532</v>
@@ -25862,7 +25862,7 @@
         <v>1511</v>
       </c>
       <c r="E513">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F513" t="s">
         <v>1532</v>
@@ -25897,7 +25897,7 @@
         <v>1511</v>
       </c>
       <c r="E514">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F514" t="s">
         <v>1532</v>
@@ -25932,7 +25932,7 @@
         <v>1511</v>
       </c>
       <c r="E515">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F515" t="s">
         <v>1534</v>
@@ -25970,7 +25970,7 @@
         <v>1511</v>
       </c>
       <c r="E516">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F516" t="s">
         <v>1532</v>
@@ -26005,7 +26005,7 @@
         <v>1511</v>
       </c>
       <c r="E517">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F517" t="s">
         <v>1532</v>
@@ -26040,7 +26040,7 @@
         <v>1511</v>
       </c>
       <c r="E518">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F518" t="s">
         <v>1532</v>
@@ -26075,7 +26075,7 @@
         <v>1512</v>
       </c>
       <c r="E519">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F519" t="s">
         <v>1532</v>
@@ -26110,7 +26110,7 @@
         <v>1512</v>
       </c>
       <c r="E520">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F520" t="s">
         <v>1532</v>
@@ -26145,7 +26145,7 @@
         <v>1512</v>
       </c>
       <c r="E521">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F521" t="s">
         <v>1532</v>
@@ -26180,7 +26180,7 @@
         <v>1512</v>
       </c>
       <c r="E522">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F522" t="s">
         <v>1532</v>
@@ -26215,7 +26215,7 @@
         <v>1512</v>
       </c>
       <c r="E523">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F523" t="s">
         <v>1532</v>
@@ -26250,7 +26250,7 @@
         <v>1512</v>
       </c>
       <c r="E524">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F524" t="s">
         <v>1532</v>
@@ -26285,7 +26285,7 @@
         <v>1512</v>
       </c>
       <c r="E525">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F525" t="s">
         <v>1532</v>
@@ -26320,7 +26320,7 @@
         <v>1512</v>
       </c>
       <c r="E526">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F526" t="s">
         <v>1532</v>
@@ -26355,7 +26355,7 @@
         <v>1512</v>
       </c>
       <c r="E527">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F527" t="s">
         <v>1532</v>
@@ -26393,7 +26393,7 @@
         <v>1512</v>
       </c>
       <c r="E528">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F528" t="s">
         <v>1532</v>
@@ -26428,7 +26428,7 @@
         <v>1513</v>
       </c>
       <c r="E529">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F529" t="s">
         <v>1532</v>
@@ -26463,7 +26463,7 @@
         <v>1513</v>
       </c>
       <c r="E530">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F530" t="s">
         <v>1534</v>
@@ -26501,7 +26501,7 @@
         <v>1513</v>
       </c>
       <c r="E531">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F531" t="s">
         <v>1532</v>
@@ -26536,7 +26536,7 @@
         <v>1513</v>
       </c>
       <c r="E532">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F532" t="s">
         <v>1532</v>
@@ -26571,7 +26571,7 @@
         <v>1514</v>
       </c>
       <c r="E533">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F533" t="s">
         <v>1532</v>
@@ -26606,7 +26606,7 @@
         <v>1514</v>
       </c>
       <c r="E534">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F534" t="s">
         <v>1532</v>
@@ -26641,7 +26641,7 @@
         <v>1514</v>
       </c>
       <c r="E535">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F535" t="s">
         <v>1532</v>
@@ -26676,7 +26676,7 @@
         <v>1514</v>
       </c>
       <c r="E536">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F536" t="s">
         <v>1534</v>
@@ -26714,7 +26714,7 @@
         <v>1514</v>
       </c>
       <c r="E537">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F537" t="s">
         <v>1532</v>
@@ -26749,7 +26749,7 @@
         <v>1514</v>
       </c>
       <c r="E538">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F538" t="s">
         <v>1532</v>
@@ -26784,7 +26784,7 @@
         <v>1514</v>
       </c>
       <c r="E539">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F539" t="s">
         <v>1532</v>
@@ -26819,7 +26819,7 @@
         <v>1514</v>
       </c>
       <c r="E540">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F540" t="s">
         <v>1532</v>
@@ -26854,7 +26854,7 @@
         <v>1514</v>
       </c>
       <c r="E541">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F541" t="s">
         <v>1532</v>
@@ -26889,7 +26889,7 @@
         <v>1514</v>
       </c>
       <c r="E542">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F542" t="s">
         <v>1532</v>
@@ -26924,7 +26924,7 @@
         <v>1515</v>
       </c>
       <c r="E543">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F543" t="s">
         <v>1532</v>
@@ -26959,7 +26959,7 @@
         <v>1515</v>
       </c>
       <c r="E544">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F544" t="s">
         <v>1532</v>
@@ -26994,7 +26994,7 @@
         <v>1515</v>
       </c>
       <c r="E545">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F545" t="s">
         <v>1532</v>
@@ -27029,7 +27029,7 @@
         <v>1515</v>
       </c>
       <c r="E546">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F546" t="s">
         <v>1532</v>
@@ -27064,7 +27064,7 @@
         <v>1516</v>
       </c>
       <c r="E547">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F547" t="s">
         <v>1532</v>
@@ -27099,7 +27099,7 @@
         <v>1516</v>
       </c>
       <c r="E548">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F548" t="s">
         <v>1532</v>
@@ -27134,7 +27134,7 @@
         <v>1516</v>
       </c>
       <c r="E549">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F549" t="s">
         <v>1532</v>
@@ -27169,7 +27169,7 @@
         <v>1516</v>
       </c>
       <c r="E550">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F550" t="s">
         <v>1534</v>
@@ -27207,7 +27207,7 @@
         <v>1517</v>
       </c>
       <c r="E551">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F551" t="s">
         <v>1532</v>
@@ -27242,7 +27242,7 @@
         <v>1517</v>
       </c>
       <c r="E552">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F552" t="s">
         <v>1536</v>
@@ -27280,7 +27280,7 @@
         <v>1517</v>
       </c>
       <c r="E553">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F553" t="s">
         <v>1532</v>
@@ -27315,7 +27315,7 @@
         <v>1517</v>
       </c>
       <c r="E554">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F554" t="s">
         <v>1532</v>
@@ -27350,7 +27350,7 @@
         <v>1518</v>
       </c>
       <c r="E555">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F555" t="s">
         <v>1532</v>
@@ -27385,7 +27385,7 @@
         <v>1518</v>
       </c>
       <c r="E556">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F556" t="s">
         <v>1532</v>
@@ -27420,7 +27420,7 @@
         <v>1518</v>
       </c>
       <c r="E557">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F557" t="s">
         <v>1532</v>
@@ -27455,7 +27455,7 @@
         <v>1518</v>
       </c>
       <c r="E558">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F558" t="s">
         <v>1532</v>
@@ -27490,7 +27490,7 @@
         <v>1518</v>
       </c>
       <c r="E559">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F559" t="s">
         <v>1532</v>
@@ -27525,7 +27525,7 @@
         <v>1518</v>
       </c>
       <c r="E560">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F560" t="s">
         <v>1534</v>
@@ -27563,7 +27563,7 @@
         <v>1518</v>
       </c>
       <c r="E561">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F561" t="s">
         <v>1532</v>
@@ -27598,7 +27598,7 @@
         <v>1518</v>
       </c>
       <c r="E562">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F562" t="s">
         <v>1532</v>
@@ -27633,7 +27633,7 @@
         <v>1518</v>
       </c>
       <c r="E563">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F563" t="s">
         <v>1532</v>
@@ -27668,7 +27668,7 @@
         <v>1519</v>
       </c>
       <c r="E564">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F564" t="s">
         <v>1532</v>
@@ -27703,7 +27703,7 @@
         <v>1519</v>
       </c>
       <c r="E565">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F565" t="s">
         <v>1532</v>
@@ -27738,7 +27738,7 @@
         <v>1520</v>
       </c>
       <c r="E566">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F566" t="s">
         <v>1534</v>
@@ -27776,7 +27776,7 @@
         <v>1520</v>
       </c>
       <c r="E567">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F567" t="s">
         <v>1534</v>
@@ -27814,7 +27814,7 @@
         <v>1520</v>
       </c>
       <c r="E568">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F568" t="s">
         <v>1532</v>
@@ -27849,7 +27849,7 @@
         <v>1520</v>
       </c>
       <c r="E569">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F569" t="s">
         <v>1532</v>
@@ -27884,7 +27884,7 @@
         <v>1520</v>
       </c>
       <c r="E570">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F570" t="s">
         <v>1532</v>
@@ -27919,7 +27919,7 @@
         <v>1521</v>
       </c>
       <c r="E571">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F571" t="s">
         <v>1532</v>
@@ -27954,7 +27954,7 @@
         <v>1522</v>
       </c>
       <c r="E572">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F572" t="s">
         <v>1532</v>
@@ -27989,7 +27989,7 @@
         <v>1522</v>
       </c>
       <c r="E573">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F573" t="s">
         <v>1532</v>
@@ -28024,7 +28024,7 @@
         <v>1522</v>
       </c>
       <c r="E574">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F574" t="s">
         <v>1532</v>
@@ -28059,7 +28059,7 @@
         <v>1522</v>
       </c>
       <c r="E575">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F575" t="s">
         <v>1532</v>
@@ -28094,7 +28094,7 @@
         <v>1522</v>
       </c>
       <c r="E576">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F576" t="s">
         <v>1532</v>
@@ -28129,7 +28129,7 @@
         <v>1522</v>
       </c>
       <c r="E577">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F577" t="s">
         <v>1532</v>
@@ -28164,7 +28164,7 @@
         <v>1522</v>
       </c>
       <c r="E578">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F578" t="s">
         <v>1532</v>
@@ -28199,7 +28199,7 @@
         <v>1522</v>
       </c>
       <c r="E579">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F579" t="s">
         <v>1532</v>
@@ -28234,7 +28234,7 @@
         <v>1522</v>
       </c>
       <c r="E580">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F580" t="s">
         <v>1532</v>
@@ -28269,7 +28269,7 @@
         <v>1522</v>
       </c>
       <c r="E581">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F581" t="s">
         <v>1534</v>
@@ -28307,7 +28307,7 @@
         <v>1523</v>
       </c>
       <c r="E582">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F582" t="s">
         <v>1532</v>
@@ -28342,7 +28342,7 @@
         <v>1523</v>
       </c>
       <c r="E583">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F583" t="s">
         <v>1532</v>
@@ -28377,7 +28377,7 @@
         <v>1523</v>
       </c>
       <c r="E584">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F584" t="s">
         <v>1532</v>
@@ -28412,7 +28412,7 @@
         <v>1523</v>
       </c>
       <c r="E585">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F585" t="s">
         <v>1532</v>
@@ -28447,7 +28447,7 @@
         <v>1523</v>
       </c>
       <c r="E586">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F586" t="s">
         <v>1534</v>
@@ -28485,7 +28485,7 @@
         <v>1523</v>
       </c>
       <c r="E587">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F587" t="s">
         <v>1534</v>
@@ -28523,7 +28523,7 @@
         <v>1523</v>
       </c>
       <c r="E588">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F588" t="s">
         <v>1532</v>
@@ -28558,7 +28558,7 @@
         <v>1523</v>
       </c>
       <c r="E589">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F589" t="s">
         <v>1532</v>
@@ -28593,7 +28593,7 @@
         <v>1523</v>
       </c>
       <c r="E590">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F590" t="s">
         <v>1532</v>
@@ -28628,7 +28628,7 @@
         <v>1524</v>
       </c>
       <c r="E591">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F591" t="s">
         <v>1532</v>
@@ -28663,7 +28663,7 @@
         <v>1524</v>
       </c>
       <c r="E592">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F592" t="s">
         <v>1534</v>
@@ -28701,7 +28701,7 @@
         <v>1524</v>
       </c>
       <c r="E593">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F593" t="s">
         <v>1534</v>
@@ -28739,7 +28739,7 @@
         <v>1524</v>
       </c>
       <c r="E594">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F594" t="s">
         <v>1532</v>
@@ -28774,7 +28774,7 @@
         <v>1525</v>
       </c>
       <c r="E595">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F595" t="s">
         <v>1534</v>
@@ -28812,7 +28812,7 @@
         <v>1525</v>
       </c>
       <c r="E596">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F596" t="s">
         <v>1532</v>
@@ -28847,7 +28847,7 @@
         <v>1525</v>
       </c>
       <c r="E597">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F597" t="s">
         <v>1532</v>
@@ -28882,7 +28882,7 @@
         <v>1526</v>
       </c>
       <c r="E598">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F598" t="s">
         <v>1532</v>
@@ -28917,7 +28917,7 @@
         <v>1526</v>
       </c>
       <c r="E599">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F599" t="s">
         <v>1532</v>
@@ -28952,7 +28952,7 @@
         <v>1526</v>
       </c>
       <c r="E600">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F600" t="s">
         <v>1532</v>
@@ -28987,7 +28987,7 @@
         <v>1526</v>
       </c>
       <c r="E601">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F601" t="s">
         <v>1532</v>
@@ -29022,7 +29022,7 @@
         <v>1526</v>
       </c>
       <c r="E602">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F602" t="s">
         <v>1532</v>
@@ -29057,7 +29057,7 @@
         <v>1526</v>
       </c>
       <c r="E603">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F603" t="s">
         <v>1532</v>
@@ -29092,7 +29092,7 @@
         <v>1526</v>
       </c>
       <c r="E604">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F604" t="s">
         <v>1532</v>
@@ -29130,7 +29130,7 @@
         <v>1526</v>
       </c>
       <c r="E605">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F605" t="s">
         <v>1534</v>
@@ -29168,7 +29168,7 @@
         <v>1527</v>
       </c>
       <c r="E606">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F606" t="s">
         <v>1532</v>
@@ -29206,7 +29206,7 @@
         <v>1527</v>
       </c>
       <c r="E607">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F607" t="s">
         <v>1532</v>
@@ -29241,7 +29241,7 @@
         <v>1527</v>
       </c>
       <c r="E608">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F608" t="s">
         <v>1534</v>
@@ -29276,7 +29276,7 @@
         <v>1527</v>
       </c>
       <c r="E609">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F609" t="s">
         <v>1532</v>
@@ -29311,7 +29311,7 @@
         <v>1527</v>
       </c>
       <c r="E610">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F610" t="s">
         <v>1532</v>
@@ -29346,7 +29346,7 @@
         <v>1527</v>
       </c>
       <c r="E611">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F611" t="s">
         <v>1532</v>
@@ -29381,7 +29381,7 @@
         <v>1527</v>
       </c>
       <c r="E612">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F612" t="s">
         <v>1532</v>
@@ -29416,7 +29416,7 @@
         <v>1527</v>
       </c>
       <c r="E613">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F613" t="s">
         <v>1534</v>
@@ -29454,7 +29454,7 @@
         <v>1528</v>
       </c>
       <c r="E614">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F614" t="s">
         <v>1532</v>
@@ -29489,7 +29489,7 @@
         <v>1528</v>
       </c>
       <c r="E615">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F615" t="s">
         <v>1532</v>
@@ -29524,7 +29524,7 @@
         <v>1528</v>
       </c>
       <c r="E616">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F616" t="s">
         <v>1532</v>
@@ -29559,7 +29559,7 @@
         <v>1528</v>
       </c>
       <c r="E617">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F617" t="s">
         <v>1532</v>
@@ -29594,7 +29594,7 @@
         <v>1528</v>
       </c>
       <c r="E618">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F618" t="s">
         <v>1532</v>
@@ -29629,7 +29629,7 @@
         <v>1528</v>
       </c>
       <c r="E619">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F619" t="s">
         <v>1532</v>
@@ -29664,7 +29664,7 @@
         <v>1528</v>
       </c>
       <c r="E620">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F620" t="s">
         <v>1532</v>
@@ -29699,7 +29699,7 @@
         <v>1529</v>
       </c>
       <c r="E621">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F621" t="s">
         <v>1532</v>
@@ -29737,7 +29737,7 @@
         <v>1529</v>
       </c>
       <c r="E622">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F622" t="s">
         <v>1532</v>
@@ -29772,7 +29772,7 @@
         <v>1529</v>
       </c>
       <c r="E623">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F623" t="s">
         <v>1532</v>
@@ -29807,7 +29807,7 @@
         <v>1529</v>
       </c>
       <c r="E624">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F624" t="s">
         <v>1532</v>
@@ -29845,7 +29845,7 @@
         <v>1529</v>
       </c>
       <c r="E625">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F625" t="s">
         <v>1532</v>
@@ -29880,7 +29880,7 @@
         <v>1530</v>
       </c>
       <c r="E626">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F626" t="s">
         <v>1532</v>
@@ -29915,7 +29915,7 @@
         <v>1531</v>
       </c>
       <c r="E627">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F627" t="s">
         <v>1532</v>
@@ -29950,7 +29950,7 @@
         <v>1531</v>
       </c>
       <c r="E628">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F628" t="s">
         <v>1532</v>
@@ -29985,7 +29985,7 @@
         <v>1531</v>
       </c>
       <c r="E629">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F629" t="s">
         <v>1532</v>
@@ -30020,7 +30020,7 @@
         <v>1531</v>
       </c>
       <c r="E630">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F630" t="s">
         <v>1532</v>
@@ -30058,7 +30058,7 @@
         <v>1531</v>
       </c>
       <c r="E631">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F631" t="s">
         <v>1532</v>
@@ -30093,7 +30093,7 @@
         <v>1531</v>
       </c>
       <c r="E632">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F632" t="s">
         <v>1532</v>
@@ -30128,7 +30128,7 @@
         <v>1531</v>
       </c>
       <c r="E633">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F633" t="s">
         <v>1532</v>
@@ -30163,7 +30163,7 @@
         <v>1531</v>
       </c>
       <c r="E634">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F634" t="s">
         <v>1532</v>
@@ -30198,7 +30198,7 @@
         <v>1531</v>
       </c>
       <c r="E635">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F635" t="s">
         <v>1532</v>
@@ -30233,7 +30233,7 @@
         <v>1531</v>
       </c>
       <c r="E636">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F636" t="s">
         <v>1532</v>
@@ -30268,7 +30268,7 @@
         <v>1531</v>
       </c>
       <c r="E637">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F637" t="s">
         <v>1532</v>
@@ -30306,7 +30306,7 @@
         <v>1531</v>
       </c>
       <c r="E638">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F638" t="s">
         <v>1532</v>
@@ -30341,7 +30341,7 @@
         <v>1531</v>
       </c>
       <c r="E639">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F639" t="s">
         <v>1532</v>
@@ -30376,7 +30376,7 @@
         <v>1531</v>
       </c>
       <c r="E640">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F640" t="s">
         <v>1532</v>
@@ -30411,7 +30411,7 @@
         <v>1531</v>
       </c>
       <c r="E641">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F641" t="s">
         <v>1536</v>
@@ -30446,7 +30446,7 @@
         <v>1531</v>
       </c>
       <c r="E642">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F642" t="s">
         <v>1532</v>

--- a/BacklogGATEAutoCompleto.xlsx
+++ b/BacklogGATEAutoCompleto.xlsx
@@ -7953,7 +7953,7 @@
         <v>1325</v>
       </c>
       <c r="E2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="F2" t="s">
         <v>1537</v>
@@ -7988,7 +7988,7 @@
         <v>1326</v>
       </c>
       <c r="E3">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="F3" t="s">
         <v>1537</v>
@@ -8023,7 +8023,7 @@
         <v>1327</v>
       </c>
       <c r="E4">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="F4" t="s">
         <v>1537</v>
@@ -8058,7 +8058,7 @@
         <v>1328</v>
       </c>
       <c r="E5">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="F5" t="s">
         <v>1537</v>
@@ -8093,7 +8093,7 @@
         <v>1329</v>
       </c>
       <c r="E6">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="F6" t="s">
         <v>1537</v>
@@ -8128,7 +8128,7 @@
         <v>1330</v>
       </c>
       <c r="E7">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="F7" t="s">
         <v>1537</v>
@@ -8163,7 +8163,7 @@
         <v>1331</v>
       </c>
       <c r="E8">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="F8" t="s">
         <v>1537</v>
@@ -8198,7 +8198,7 @@
         <v>1332</v>
       </c>
       <c r="E9">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="F9" t="s">
         <v>1537</v>
@@ -8233,7 +8233,7 @@
         <v>1333</v>
       </c>
       <c r="E10">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F10" t="s">
         <v>1537</v>
@@ -8268,7 +8268,7 @@
         <v>1333</v>
       </c>
       <c r="E11">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F11" t="s">
         <v>1537</v>
@@ -8303,7 +8303,7 @@
         <v>1334</v>
       </c>
       <c r="E12">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="F12" t="s">
         <v>1537</v>
@@ -8338,7 +8338,7 @@
         <v>1335</v>
       </c>
       <c r="E13">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="F13" t="s">
         <v>1537</v>
@@ -8373,7 +8373,7 @@
         <v>1336</v>
       </c>
       <c r="E14">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="F14" t="s">
         <v>1537</v>
@@ -8408,7 +8408,7 @@
         <v>1336</v>
       </c>
       <c r="E15">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="F15" t="s">
         <v>1537</v>
@@ -8443,7 +8443,7 @@
         <v>1337</v>
       </c>
       <c r="E16">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="F16" t="s">
         <v>1537</v>
@@ -8478,7 +8478,7 @@
         <v>1337</v>
       </c>
       <c r="E17">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="F17" t="s">
         <v>1537</v>
@@ -8513,7 +8513,7 @@
         <v>1338</v>
       </c>
       <c r="E18">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="F18" t="s">
         <v>1537</v>
@@ -8548,7 +8548,7 @@
         <v>1339</v>
       </c>
       <c r="E19">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F19" t="s">
         <v>1537</v>
@@ -8583,7 +8583,7 @@
         <v>1340</v>
       </c>
       <c r="E20">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="F20" t="s">
         <v>1537</v>
@@ -8618,7 +8618,7 @@
         <v>1341</v>
       </c>
       <c r="E21">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F21" t="s">
         <v>1537</v>
@@ -8653,7 +8653,7 @@
         <v>1342</v>
       </c>
       <c r="E22">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="F22" t="s">
         <v>1537</v>
@@ -8691,7 +8691,7 @@
         <v>1343</v>
       </c>
       <c r="E23">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="F23" t="s">
         <v>1537</v>
@@ -8726,7 +8726,7 @@
         <v>1344</v>
       </c>
       <c r="E24">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F24" t="s">
         <v>1537</v>
@@ -8761,7 +8761,7 @@
         <v>1345</v>
       </c>
       <c r="E25">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F25" t="s">
         <v>1537</v>
@@ -8796,7 +8796,7 @@
         <v>1346</v>
       </c>
       <c r="E26">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="F26" t="s">
         <v>1537</v>
@@ -8831,7 +8831,7 @@
         <v>1347</v>
       </c>
       <c r="E27">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F27" t="s">
         <v>1537</v>
@@ -8866,7 +8866,7 @@
         <v>1348</v>
       </c>
       <c r="E28">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F28" t="s">
         <v>1537</v>
@@ -8901,7 +8901,7 @@
         <v>1349</v>
       </c>
       <c r="E29">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F29" t="s">
         <v>1537</v>
@@ -8936,7 +8936,7 @@
         <v>1350</v>
       </c>
       <c r="E30">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F30" t="s">
         <v>1537</v>
@@ -8971,7 +8971,7 @@
         <v>1351</v>
       </c>
       <c r="E31">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F31" t="s">
         <v>1537</v>
@@ -9006,7 +9006,7 @@
         <v>1352</v>
       </c>
       <c r="E32">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F32" t="s">
         <v>1537</v>
@@ -9041,7 +9041,7 @@
         <v>1353</v>
       </c>
       <c r="E33">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F33" t="s">
         <v>1537</v>
@@ -9076,7 +9076,7 @@
         <v>1354</v>
       </c>
       <c r="E34">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F34" t="s">
         <v>1537</v>
@@ -9111,7 +9111,7 @@
         <v>1355</v>
       </c>
       <c r="E35">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F35" t="s">
         <v>1537</v>
@@ -9146,7 +9146,7 @@
         <v>1355</v>
       </c>
       <c r="E36">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F36" t="s">
         <v>1537</v>
@@ -9181,7 +9181,7 @@
         <v>1356</v>
       </c>
       <c r="E37">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="F37" t="s">
         <v>1537</v>
@@ -9216,7 +9216,7 @@
         <v>1357</v>
       </c>
       <c r="E38">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F38" t="s">
         <v>1537</v>
@@ -9251,7 +9251,7 @@
         <v>1357</v>
       </c>
       <c r="E39">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F39" t="s">
         <v>1537</v>
@@ -9286,7 +9286,7 @@
         <v>1358</v>
       </c>
       <c r="E40">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F40" t="s">
         <v>1537</v>
@@ -9321,7 +9321,7 @@
         <v>1358</v>
       </c>
       <c r="E41">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F41" t="s">
         <v>1537</v>
@@ -9356,7 +9356,7 @@
         <v>1359</v>
       </c>
       <c r="E42">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F42" t="s">
         <v>1537</v>
@@ -9391,7 +9391,7 @@
         <v>1360</v>
       </c>
       <c r="E43">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F43" t="s">
         <v>1537</v>
@@ -9426,7 +9426,7 @@
         <v>1361</v>
       </c>
       <c r="E44">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F44" t="s">
         <v>1537</v>
@@ -9461,7 +9461,7 @@
         <v>1362</v>
       </c>
       <c r="E45">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F45" t="s">
         <v>1537</v>
@@ -9496,7 +9496,7 @@
         <v>1362</v>
       </c>
       <c r="E46">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F46" t="s">
         <v>1537</v>
@@ -9531,7 +9531,7 @@
         <v>1363</v>
       </c>
       <c r="E47">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F47" t="s">
         <v>1537</v>
@@ -9566,7 +9566,7 @@
         <v>1364</v>
       </c>
       <c r="E48">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F48" t="s">
         <v>1537</v>
@@ -9601,7 +9601,7 @@
         <v>1365</v>
       </c>
       <c r="E49">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F49" t="s">
         <v>1537</v>
@@ -9636,7 +9636,7 @@
         <v>1366</v>
       </c>
       <c r="E50">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F50" t="s">
         <v>1537</v>
@@ -9671,7 +9671,7 @@
         <v>1367</v>
       </c>
       <c r="E51">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F51" t="s">
         <v>1537</v>
@@ -9706,7 +9706,7 @@
         <v>1368</v>
       </c>
       <c r="E52">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F52" t="s">
         <v>1537</v>
@@ -9741,7 +9741,7 @@
         <v>1369</v>
       </c>
       <c r="E53">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F53" t="s">
         <v>1537</v>
@@ -9776,7 +9776,7 @@
         <v>1369</v>
       </c>
       <c r="E54">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F54" t="s">
         <v>1537</v>
@@ -9811,7 +9811,7 @@
         <v>1369</v>
       </c>
       <c r="E55">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F55" t="s">
         <v>1537</v>
@@ -9846,7 +9846,7 @@
         <v>1370</v>
       </c>
       <c r="E56">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F56" t="s">
         <v>1537</v>
@@ -9881,7 +9881,7 @@
         <v>1371</v>
       </c>
       <c r="E57">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F57" t="s">
         <v>1537</v>
@@ -9916,7 +9916,7 @@
         <v>1372</v>
       </c>
       <c r="E58">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F58" t="s">
         <v>1537</v>
@@ -9951,7 +9951,7 @@
         <v>1373</v>
       </c>
       <c r="E59">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F59" t="s">
         <v>1537</v>
@@ -9986,7 +9986,7 @@
         <v>1374</v>
       </c>
       <c r="E60">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F60" t="s">
         <v>1537</v>
@@ -10021,7 +10021,7 @@
         <v>1374</v>
       </c>
       <c r="E61">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F61" t="s">
         <v>1537</v>
@@ -10056,7 +10056,7 @@
         <v>1374</v>
       </c>
       <c r="E62">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F62" t="s">
         <v>1537</v>
@@ -10091,7 +10091,7 @@
         <v>1375</v>
       </c>
       <c r="E63">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F63" t="s">
         <v>1537</v>
@@ -10126,7 +10126,7 @@
         <v>1376</v>
       </c>
       <c r="E64">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F64" t="s">
         <v>1537</v>
@@ -10161,7 +10161,7 @@
         <v>1376</v>
       </c>
       <c r="E65">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F65" t="s">
         <v>1537</v>
@@ -10196,7 +10196,7 @@
         <v>1376</v>
       </c>
       <c r="E66">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F66" t="s">
         <v>1538</v>
@@ -10231,7 +10231,7 @@
         <v>1376</v>
       </c>
       <c r="E67">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F67" t="s">
         <v>1537</v>
@@ -10266,7 +10266,7 @@
         <v>1377</v>
       </c>
       <c r="E68">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F68" t="s">
         <v>1537</v>
@@ -10301,7 +10301,7 @@
         <v>1378</v>
       </c>
       <c r="E69">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F69" t="s">
         <v>1537</v>
@@ -10336,7 +10336,7 @@
         <v>1378</v>
       </c>
       <c r="E70">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F70" t="s">
         <v>1537</v>
@@ -10371,7 +10371,7 @@
         <v>1379</v>
       </c>
       <c r="E71">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F71" t="s">
         <v>1537</v>
@@ -10406,7 +10406,7 @@
         <v>1380</v>
       </c>
       <c r="E72">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F72" t="s">
         <v>1537</v>
@@ -10441,7 +10441,7 @@
         <v>1381</v>
       </c>
       <c r="E73">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F73" t="s">
         <v>1537</v>
@@ -10476,7 +10476,7 @@
         <v>1382</v>
       </c>
       <c r="E74">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F74" t="s">
         <v>1537</v>
@@ -10511,7 +10511,7 @@
         <v>1382</v>
       </c>
       <c r="E75">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F75" t="s">
         <v>1537</v>
@@ -10546,7 +10546,7 @@
         <v>1382</v>
       </c>
       <c r="E76">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F76" t="s">
         <v>1537</v>
@@ -10581,7 +10581,7 @@
         <v>1382</v>
       </c>
       <c r="E77">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F77" t="s">
         <v>1537</v>
@@ -10616,7 +10616,7 @@
         <v>1382</v>
       </c>
       <c r="E78">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F78" t="s">
         <v>1537</v>
@@ -10651,7 +10651,7 @@
         <v>1382</v>
       </c>
       <c r="E79">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F79" t="s">
         <v>1537</v>
@@ -10686,7 +10686,7 @@
         <v>1383</v>
       </c>
       <c r="E80">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F80" t="s">
         <v>1537</v>
@@ -10721,7 +10721,7 @@
         <v>1384</v>
       </c>
       <c r="E81">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F81" t="s">
         <v>1537</v>
@@ -10756,7 +10756,7 @@
         <v>1385</v>
       </c>
       <c r="E82">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F82" t="s">
         <v>1537</v>
@@ -10791,7 +10791,7 @@
         <v>1385</v>
       </c>
       <c r="E83">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F83" t="s">
         <v>1537</v>
@@ -10826,7 +10826,7 @@
         <v>1386</v>
       </c>
       <c r="E84">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F84" t="s">
         <v>1539</v>
@@ -10861,7 +10861,7 @@
         <v>1387</v>
       </c>
       <c r="E85">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F85" t="s">
         <v>1537</v>
@@ -10896,7 +10896,7 @@
         <v>1388</v>
       </c>
       <c r="E86">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F86" t="s">
         <v>1537</v>
@@ -10931,7 +10931,7 @@
         <v>1388</v>
       </c>
       <c r="E87">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F87" t="s">
         <v>1537</v>
@@ -10966,7 +10966,7 @@
         <v>1389</v>
       </c>
       <c r="E88">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F88" t="s">
         <v>1537</v>
@@ -11001,7 +11001,7 @@
         <v>1390</v>
       </c>
       <c r="E89">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F89" t="s">
         <v>1537</v>
@@ -11036,7 +11036,7 @@
         <v>1391</v>
       </c>
       <c r="E90">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F90" t="s">
         <v>1537</v>
@@ -11071,7 +11071,7 @@
         <v>1392</v>
       </c>
       <c r="E91">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F91" t="s">
         <v>1537</v>
@@ -11106,7 +11106,7 @@
         <v>1393</v>
       </c>
       <c r="E92">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F92" t="s">
         <v>1537</v>
@@ -11141,7 +11141,7 @@
         <v>1393</v>
       </c>
       <c r="E93">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F93" t="s">
         <v>1537</v>
@@ -11176,7 +11176,7 @@
         <v>1394</v>
       </c>
       <c r="E94">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F94" t="s">
         <v>1537</v>
@@ -11211,7 +11211,7 @@
         <v>1394</v>
       </c>
       <c r="E95">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F95" t="s">
         <v>1537</v>
@@ -11246,7 +11246,7 @@
         <v>1394</v>
       </c>
       <c r="E96">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F96" t="s">
         <v>1537</v>
@@ -11281,7 +11281,7 @@
         <v>1395</v>
       </c>
       <c r="E97">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F97" t="s">
         <v>1537</v>
@@ -11316,7 +11316,7 @@
         <v>1395</v>
       </c>
       <c r="E98">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F98" t="s">
         <v>1537</v>
@@ -11351,7 +11351,7 @@
         <v>1396</v>
       </c>
       <c r="E99">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F99" t="s">
         <v>1537</v>
@@ -11386,7 +11386,7 @@
         <v>1397</v>
       </c>
       <c r="E100">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F100" t="s">
         <v>1537</v>
@@ -11421,7 +11421,7 @@
         <v>1398</v>
       </c>
       <c r="E101">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F101" t="s">
         <v>1537</v>
@@ -11456,7 +11456,7 @@
         <v>1398</v>
       </c>
       <c r="E102">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F102" t="s">
         <v>1537</v>
@@ -11491,7 +11491,7 @@
         <v>1399</v>
       </c>
       <c r="E103">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F103" t="s">
         <v>1537</v>
@@ -11526,7 +11526,7 @@
         <v>1399</v>
       </c>
       <c r="E104">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F104" t="s">
         <v>1537</v>
@@ -11561,7 +11561,7 @@
         <v>1400</v>
       </c>
       <c r="E105">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F105" t="s">
         <v>1537</v>
@@ -11596,7 +11596,7 @@
         <v>1401</v>
       </c>
       <c r="E106">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F106" t="s">
         <v>1537</v>
@@ -11631,7 +11631,7 @@
         <v>1401</v>
       </c>
       <c r="E107">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F107" t="s">
         <v>1537</v>
@@ -11666,7 +11666,7 @@
         <v>1402</v>
       </c>
       <c r="E108">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F108" t="s">
         <v>1537</v>
@@ -11701,7 +11701,7 @@
         <v>1403</v>
       </c>
       <c r="E109">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F109" t="s">
         <v>1537</v>
@@ -11736,7 +11736,7 @@
         <v>1403</v>
       </c>
       <c r="E110">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F110" t="s">
         <v>1537</v>
@@ -11771,7 +11771,7 @@
         <v>1404</v>
       </c>
       <c r="E111">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F111" t="s">
         <v>1537</v>
@@ -11806,7 +11806,7 @@
         <v>1405</v>
       </c>
       <c r="E112">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F112" t="s">
         <v>1537</v>
@@ -11844,7 +11844,7 @@
         <v>1405</v>
       </c>
       <c r="E113">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F113" t="s">
         <v>1537</v>
@@ -11879,7 +11879,7 @@
         <v>1405</v>
       </c>
       <c r="E114">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F114" t="s">
         <v>1537</v>
@@ -11914,7 +11914,7 @@
         <v>1405</v>
       </c>
       <c r="E115">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F115" t="s">
         <v>1537</v>
@@ -11949,7 +11949,7 @@
         <v>1406</v>
       </c>
       <c r="E116">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F116" t="s">
         <v>1538</v>
@@ -11984,7 +11984,7 @@
         <v>1407</v>
       </c>
       <c r="E117">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F117" t="s">
         <v>1537</v>
@@ -12019,7 +12019,7 @@
         <v>1407</v>
       </c>
       <c r="E118">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F118" t="s">
         <v>1537</v>
@@ -12054,7 +12054,7 @@
         <v>1407</v>
       </c>
       <c r="E119">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F119" t="s">
         <v>1537</v>
@@ -12089,7 +12089,7 @@
         <v>1407</v>
       </c>
       <c r="E120">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F120" t="s">
         <v>1537</v>
@@ -12124,7 +12124,7 @@
         <v>1408</v>
       </c>
       <c r="E121">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F121" t="s">
         <v>1537</v>
@@ -12159,7 +12159,7 @@
         <v>1408</v>
       </c>
       <c r="E122">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F122" t="s">
         <v>1537</v>
@@ -12194,7 +12194,7 @@
         <v>1408</v>
       </c>
       <c r="E123">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F123" t="s">
         <v>1537</v>
@@ -12229,7 +12229,7 @@
         <v>1408</v>
       </c>
       <c r="E124">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F124" t="s">
         <v>1537</v>
@@ -12264,7 +12264,7 @@
         <v>1408</v>
       </c>
       <c r="E125">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F125" t="s">
         <v>1537</v>
@@ -12299,7 +12299,7 @@
         <v>1408</v>
       </c>
       <c r="E126">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F126" t="s">
         <v>1537</v>
@@ -12334,7 +12334,7 @@
         <v>1408</v>
       </c>
       <c r="E127">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F127" t="s">
         <v>1537</v>
@@ -12369,7 +12369,7 @@
         <v>1409</v>
       </c>
       <c r="E128">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F128" t="s">
         <v>1537</v>
@@ -12404,7 +12404,7 @@
         <v>1409</v>
       </c>
       <c r="E129">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F129" t="s">
         <v>1537</v>
@@ -12439,7 +12439,7 @@
         <v>1410</v>
       </c>
       <c r="E130">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F130" t="s">
         <v>1537</v>
@@ -12474,7 +12474,7 @@
         <v>1411</v>
       </c>
       <c r="E131">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F131" t="s">
         <v>1537</v>
@@ -12509,7 +12509,7 @@
         <v>1411</v>
       </c>
       <c r="E132">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F132" t="s">
         <v>1537</v>
@@ -12544,7 +12544,7 @@
         <v>1411</v>
       </c>
       <c r="E133">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F133" t="s">
         <v>1537</v>
@@ -12579,7 +12579,7 @@
         <v>1412</v>
       </c>
       <c r="E134">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F134" t="s">
         <v>1537</v>
@@ -12614,7 +12614,7 @@
         <v>1412</v>
       </c>
       <c r="E135">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F135" t="s">
         <v>1537</v>
@@ -12649,7 +12649,7 @@
         <v>1412</v>
       </c>
       <c r="E136">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F136" t="s">
         <v>1537</v>
@@ -12684,7 +12684,7 @@
         <v>1412</v>
       </c>
       <c r="E137">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F137" t="s">
         <v>1537</v>
@@ -12719,7 +12719,7 @@
         <v>1412</v>
       </c>
       <c r="E138">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F138" t="s">
         <v>1537</v>
@@ -12754,7 +12754,7 @@
         <v>1412</v>
       </c>
       <c r="E139">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F139" t="s">
         <v>1537</v>
@@ -12789,7 +12789,7 @@
         <v>1412</v>
       </c>
       <c r="E140">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F140" t="s">
         <v>1537</v>
@@ -12824,7 +12824,7 @@
         <v>1412</v>
       </c>
       <c r="E141">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F141" t="s">
         <v>1537</v>
@@ -12859,7 +12859,7 @@
         <v>1412</v>
       </c>
       <c r="E142">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F142" t="s">
         <v>1537</v>
@@ -12894,7 +12894,7 @@
         <v>1413</v>
       </c>
       <c r="E143">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F143" t="s">
         <v>1537</v>
@@ -12929,7 +12929,7 @@
         <v>1413</v>
       </c>
       <c r="E144">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F144" t="s">
         <v>1537</v>
@@ -12964,7 +12964,7 @@
         <v>1413</v>
       </c>
       <c r="E145">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F145" t="s">
         <v>1537</v>
@@ -12999,7 +12999,7 @@
         <v>1414</v>
       </c>
       <c r="E146">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F146" t="s">
         <v>1537</v>
@@ -13034,7 +13034,7 @@
         <v>1414</v>
       </c>
       <c r="E147">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F147" t="s">
         <v>1538</v>
@@ -13069,7 +13069,7 @@
         <v>1414</v>
       </c>
       <c r="E148">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F148" t="s">
         <v>1537</v>
@@ -13104,7 +13104,7 @@
         <v>1415</v>
       </c>
       <c r="E149">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F149" t="s">
         <v>1537</v>
@@ -13139,7 +13139,7 @@
         <v>1415</v>
       </c>
       <c r="E150">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F150" t="s">
         <v>1537</v>
@@ -13174,7 +13174,7 @@
         <v>1416</v>
       </c>
       <c r="E151">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F151" t="s">
         <v>1537</v>
@@ -13209,7 +13209,7 @@
         <v>1416</v>
       </c>
       <c r="E152">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F152" t="s">
         <v>1537</v>
@@ -13244,7 +13244,7 @@
         <v>1417</v>
       </c>
       <c r="E153">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F153" t="s">
         <v>1537</v>
@@ -13279,7 +13279,7 @@
         <v>1417</v>
       </c>
       <c r="E154">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F154" t="s">
         <v>1537</v>
@@ -13314,7 +13314,7 @@
         <v>1418</v>
       </c>
       <c r="E155">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F155" t="s">
         <v>1537</v>
@@ -13349,7 +13349,7 @@
         <v>1418</v>
       </c>
       <c r="E156">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F156" t="s">
         <v>1537</v>
@@ -13384,7 +13384,7 @@
         <v>1418</v>
       </c>
       <c r="E157">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F157" t="s">
         <v>1537</v>
@@ -13419,7 +13419,7 @@
         <v>1419</v>
       </c>
       <c r="E158">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F158" t="s">
         <v>1537</v>
@@ -13454,7 +13454,7 @@
         <v>1419</v>
       </c>
       <c r="E159">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F159" t="s">
         <v>1537</v>
@@ -13489,7 +13489,7 @@
         <v>1420</v>
       </c>
       <c r="E160">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F160" t="s">
         <v>1537</v>
@@ -13524,7 +13524,7 @@
         <v>1421</v>
       </c>
       <c r="E161">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F161" t="s">
         <v>1537</v>
@@ -13559,7 +13559,7 @@
         <v>1421</v>
       </c>
       <c r="E162">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F162" t="s">
         <v>1537</v>
@@ -13594,7 +13594,7 @@
         <v>1421</v>
       </c>
       <c r="E163">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F163" t="s">
         <v>1537</v>
@@ -13629,7 +13629,7 @@
         <v>1421</v>
       </c>
       <c r="E164">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F164" t="s">
         <v>1537</v>
@@ -13664,7 +13664,7 @@
         <v>1422</v>
       </c>
       <c r="E165">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F165" t="s">
         <v>1537</v>
@@ -13699,7 +13699,7 @@
         <v>1423</v>
       </c>
       <c r="E166">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F166" t="s">
         <v>1537</v>
@@ -13734,7 +13734,7 @@
         <v>1423</v>
       </c>
       <c r="E167">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F167" t="s">
         <v>1537</v>
@@ -13769,7 +13769,7 @@
         <v>1423</v>
       </c>
       <c r="E168">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F168" t="s">
         <v>1537</v>
@@ -13804,7 +13804,7 @@
         <v>1423</v>
       </c>
       <c r="E169">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F169" t="s">
         <v>1537</v>
@@ -13839,7 +13839,7 @@
         <v>1423</v>
       </c>
       <c r="E170">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F170" t="s">
         <v>1537</v>
@@ -13874,7 +13874,7 @@
         <v>1424</v>
       </c>
       <c r="E171">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F171" t="s">
         <v>1537</v>
@@ -13909,7 +13909,7 @@
         <v>1424</v>
       </c>
       <c r="E172">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F172" t="s">
         <v>1537</v>
@@ -13944,7 +13944,7 @@
         <v>1424</v>
       </c>
       <c r="E173">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F173" t="s">
         <v>1537</v>
@@ -13979,7 +13979,7 @@
         <v>1424</v>
       </c>
       <c r="E174">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F174" t="s">
         <v>1537</v>
@@ -14014,7 +14014,7 @@
         <v>1424</v>
       </c>
       <c r="E175">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F175" t="s">
         <v>1537</v>
@@ -14049,7 +14049,7 @@
         <v>1424</v>
       </c>
       <c r="E176">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F176" t="s">
         <v>1537</v>
@@ -14084,7 +14084,7 @@
         <v>1425</v>
       </c>
       <c r="E177">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F177" t="s">
         <v>1537</v>
@@ -14119,7 +14119,7 @@
         <v>1425</v>
       </c>
       <c r="E178">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F178" t="s">
         <v>1537</v>
@@ -14154,7 +14154,7 @@
         <v>1425</v>
       </c>
       <c r="E179">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F179" t="s">
         <v>1537</v>
@@ -14189,7 +14189,7 @@
         <v>1426</v>
       </c>
       <c r="E180">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F180" t="s">
         <v>1537</v>
@@ -14224,7 +14224,7 @@
         <v>1426</v>
       </c>
       <c r="E181">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F181" t="s">
         <v>1537</v>
@@ -14259,7 +14259,7 @@
         <v>1427</v>
       </c>
       <c r="E182">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F182" t="s">
         <v>1537</v>
@@ -14294,7 +14294,7 @@
         <v>1428</v>
       </c>
       <c r="E183">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F183" t="s">
         <v>1537</v>
@@ -14329,7 +14329,7 @@
         <v>1428</v>
       </c>
       <c r="E184">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F184" t="s">
         <v>1537</v>
@@ -14364,7 +14364,7 @@
         <v>1429</v>
       </c>
       <c r="E185">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F185" t="s">
         <v>1537</v>
@@ -14399,7 +14399,7 @@
         <v>1430</v>
       </c>
       <c r="E186">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F186" t="s">
         <v>1537</v>
@@ -14434,7 +14434,7 @@
         <v>1430</v>
       </c>
       <c r="E187">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F187" t="s">
         <v>1537</v>
@@ -14469,7 +14469,7 @@
         <v>1431</v>
       </c>
       <c r="E188">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F188" t="s">
         <v>1537</v>
@@ -14504,7 +14504,7 @@
         <v>1431</v>
       </c>
       <c r="E189">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F189" t="s">
         <v>1537</v>
@@ -14539,7 +14539,7 @@
         <v>1432</v>
       </c>
       <c r="E190">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F190" t="s">
         <v>1537</v>
@@ -14574,7 +14574,7 @@
         <v>1433</v>
       </c>
       <c r="E191">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F191" t="s">
         <v>1537</v>
@@ -14609,7 +14609,7 @@
         <v>1433</v>
       </c>
       <c r="E192">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F192" t="s">
         <v>1537</v>
@@ -14644,7 +14644,7 @@
         <v>1433</v>
       </c>
       <c r="E193">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F193" t="s">
         <v>1537</v>
@@ -14679,7 +14679,7 @@
         <v>1434</v>
       </c>
       <c r="E194">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F194" t="s">
         <v>1537</v>
@@ -14714,7 +14714,7 @@
         <v>1434</v>
       </c>
       <c r="E195">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F195" t="s">
         <v>1537</v>
@@ -14749,7 +14749,7 @@
         <v>1435</v>
       </c>
       <c r="E196">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F196" t="s">
         <v>1537</v>
@@ -14784,7 +14784,7 @@
         <v>1436</v>
       </c>
       <c r="E197">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F197" t="s">
         <v>1537</v>
@@ -14819,7 +14819,7 @@
         <v>1436</v>
       </c>
       <c r="E198">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F198" t="s">
         <v>1537</v>
@@ -14854,7 +14854,7 @@
         <v>1436</v>
       </c>
       <c r="E199">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F199" t="s">
         <v>1537</v>
@@ -14889,7 +14889,7 @@
         <v>1437</v>
       </c>
       <c r="E200">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F200" t="s">
         <v>1537</v>
@@ -14924,7 +14924,7 @@
         <v>1437</v>
       </c>
       <c r="E201">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F201" t="s">
         <v>1537</v>
@@ -14959,7 +14959,7 @@
         <v>1438</v>
       </c>
       <c r="E202">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F202" t="s">
         <v>1537</v>
@@ -14994,7 +14994,7 @@
         <v>1438</v>
       </c>
       <c r="E203">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F203" t="s">
         <v>1539</v>
@@ -15029,7 +15029,7 @@
         <v>1438</v>
       </c>
       <c r="E204">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F204" t="s">
         <v>1537</v>
@@ -15064,7 +15064,7 @@
         <v>1439</v>
       </c>
       <c r="E205">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F205" t="s">
         <v>1537</v>
@@ -15099,7 +15099,7 @@
         <v>1439</v>
       </c>
       <c r="E206">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F206" t="s">
         <v>1537</v>
@@ -15137,7 +15137,7 @@
         <v>1439</v>
       </c>
       <c r="E207">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F207" t="s">
         <v>1537</v>
@@ -15172,7 +15172,7 @@
         <v>1439</v>
       </c>
       <c r="E208">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F208" t="s">
         <v>1537</v>
@@ -15207,7 +15207,7 @@
         <v>1439</v>
       </c>
       <c r="E209">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F209" t="s">
         <v>1537</v>
@@ -15242,7 +15242,7 @@
         <v>1439</v>
       </c>
       <c r="E210">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F210" t="s">
         <v>1537</v>
@@ -15277,7 +15277,7 @@
         <v>1440</v>
       </c>
       <c r="E211">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F211" t="s">
         <v>1537</v>
@@ -15312,7 +15312,7 @@
         <v>1440</v>
       </c>
       <c r="E212">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F212" t="s">
         <v>1537</v>
@@ -15347,7 +15347,7 @@
         <v>1440</v>
       </c>
       <c r="E213">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F213" t="s">
         <v>1537</v>
@@ -15382,7 +15382,7 @@
         <v>1441</v>
       </c>
       <c r="E214">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F214" t="s">
         <v>1537</v>
@@ -15417,7 +15417,7 @@
         <v>1441</v>
       </c>
       <c r="E215">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F215" t="s">
         <v>1537</v>
@@ -15452,7 +15452,7 @@
         <v>1441</v>
       </c>
       <c r="E216">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F216" t="s">
         <v>1537</v>
@@ -15487,7 +15487,7 @@
         <v>1442</v>
       </c>
       <c r="E217">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F217" t="s">
         <v>1537</v>
@@ -15522,7 +15522,7 @@
         <v>1442</v>
       </c>
       <c r="E218">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F218" t="s">
         <v>1537</v>
@@ -15557,7 +15557,7 @@
         <v>1442</v>
       </c>
       <c r="E219">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F219" t="s">
         <v>1537</v>
@@ -15592,7 +15592,7 @@
         <v>1443</v>
       </c>
       <c r="E220">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F220" t="s">
         <v>1537</v>
@@ -15627,7 +15627,7 @@
         <v>1443</v>
       </c>
       <c r="E221">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F221" t="s">
         <v>1537</v>
@@ -15662,7 +15662,7 @@
         <v>1443</v>
       </c>
       <c r="E222">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F222" t="s">
         <v>1537</v>
@@ -15697,7 +15697,7 @@
         <v>1443</v>
       </c>
       <c r="E223">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F223" t="s">
         <v>1537</v>
@@ -15732,7 +15732,7 @@
         <v>1443</v>
       </c>
       <c r="E224">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F224" t="s">
         <v>1537</v>
@@ -15767,7 +15767,7 @@
         <v>1443</v>
       </c>
       <c r="E225">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F225" t="s">
         <v>1537</v>
@@ -15802,7 +15802,7 @@
         <v>1444</v>
       </c>
       <c r="E226">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F226" t="s">
         <v>1537</v>
@@ -15837,7 +15837,7 @@
         <v>1445</v>
       </c>
       <c r="E227">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F227" t="s">
         <v>1537</v>
@@ -15872,7 +15872,7 @@
         <v>1445</v>
       </c>
       <c r="E228">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F228" t="s">
         <v>1540</v>
@@ -15907,7 +15907,7 @@
         <v>1445</v>
       </c>
       <c r="E229">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F229" t="s">
         <v>1537</v>
@@ -15942,7 +15942,7 @@
         <v>1445</v>
       </c>
       <c r="E230">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F230" t="s">
         <v>1537</v>
@@ -15977,7 +15977,7 @@
         <v>1445</v>
       </c>
       <c r="E231">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F231" t="s">
         <v>1537</v>
@@ -16012,7 +16012,7 @@
         <v>1446</v>
       </c>
       <c r="E232">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F232" t="s">
         <v>1537</v>
@@ -16047,7 +16047,7 @@
         <v>1446</v>
       </c>
       <c r="E233">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F233" t="s">
         <v>1537</v>
@@ -16082,7 +16082,7 @@
         <v>1446</v>
       </c>
       <c r="E234">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F234" t="s">
         <v>1537</v>
@@ -16117,7 +16117,7 @@
         <v>1446</v>
       </c>
       <c r="E235">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F235" t="s">
         <v>1537</v>
@@ -16152,7 +16152,7 @@
         <v>1447</v>
       </c>
       <c r="E236">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F236" t="s">
         <v>1537</v>
@@ -16187,7 +16187,7 @@
         <v>1448</v>
       </c>
       <c r="E237">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F237" t="s">
         <v>1537</v>
@@ -16225,7 +16225,7 @@
         <v>1449</v>
       </c>
       <c r="E238">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F238" t="s">
         <v>1537</v>
@@ -16260,7 +16260,7 @@
         <v>1449</v>
       </c>
       <c r="E239">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F239" t="s">
         <v>1537</v>
@@ -16295,7 +16295,7 @@
         <v>1449</v>
       </c>
       <c r="E240">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F240" t="s">
         <v>1537</v>
@@ -16330,7 +16330,7 @@
         <v>1449</v>
       </c>
       <c r="E241">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F241" t="s">
         <v>1537</v>
@@ -16368,7 +16368,7 @@
         <v>1449</v>
       </c>
       <c r="E242">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F242" t="s">
         <v>1537</v>
@@ -16403,7 +16403,7 @@
         <v>1450</v>
       </c>
       <c r="E243">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F243" t="s">
         <v>1537</v>
@@ -16438,7 +16438,7 @@
         <v>1450</v>
       </c>
       <c r="E244">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F244" t="s">
         <v>1537</v>
@@ -16473,7 +16473,7 @@
         <v>1451</v>
       </c>
       <c r="E245">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F245" t="s">
         <v>1537</v>
@@ -16508,7 +16508,7 @@
         <v>1451</v>
       </c>
       <c r="E246">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F246" t="s">
         <v>1537</v>
@@ -16543,7 +16543,7 @@
         <v>1452</v>
       </c>
       <c r="E247">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F247" t="s">
         <v>1537</v>
@@ -16578,7 +16578,7 @@
         <v>1452</v>
       </c>
       <c r="E248">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F248" t="s">
         <v>1537</v>
@@ -16613,7 +16613,7 @@
         <v>1452</v>
       </c>
       <c r="E249">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F249" t="s">
         <v>1537</v>
@@ -16648,7 +16648,7 @@
         <v>1453</v>
       </c>
       <c r="E250">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F250" t="s">
         <v>1537</v>
@@ -16683,7 +16683,7 @@
         <v>1453</v>
       </c>
       <c r="E251">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F251" t="s">
         <v>1537</v>
@@ -16718,7 +16718,7 @@
         <v>1453</v>
       </c>
       <c r="E252">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F252" t="s">
         <v>1537</v>
@@ -16753,7 +16753,7 @@
         <v>1453</v>
       </c>
       <c r="E253">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F253" t="s">
         <v>1537</v>
@@ -16788,7 +16788,7 @@
         <v>1454</v>
       </c>
       <c r="E254">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F254" t="s">
         <v>1537</v>
@@ -16823,7 +16823,7 @@
         <v>1455</v>
       </c>
       <c r="E255">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F255" t="s">
         <v>1537</v>
@@ -16858,7 +16858,7 @@
         <v>1455</v>
       </c>
       <c r="E256">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F256" t="s">
         <v>1537</v>
@@ -16893,7 +16893,7 @@
         <v>1455</v>
       </c>
       <c r="E257">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F257" t="s">
         <v>1537</v>
@@ -16928,7 +16928,7 @@
         <v>1455</v>
       </c>
       <c r="E258">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F258" t="s">
         <v>1537</v>
@@ -16963,7 +16963,7 @@
         <v>1456</v>
       </c>
       <c r="E259">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F259" t="s">
         <v>1537</v>
@@ -16998,7 +16998,7 @@
         <v>1456</v>
       </c>
       <c r="E260">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F260" t="s">
         <v>1537</v>
@@ -17033,7 +17033,7 @@
         <v>1456</v>
       </c>
       <c r="E261">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F261" t="s">
         <v>1537</v>
@@ -17068,7 +17068,7 @@
         <v>1457</v>
       </c>
       <c r="E262">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F262" t="s">
         <v>1537</v>
@@ -17103,7 +17103,7 @@
         <v>1457</v>
       </c>
       <c r="E263">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F263" t="s">
         <v>1537</v>
@@ -17138,7 +17138,7 @@
         <v>1458</v>
       </c>
       <c r="E264">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F264" t="s">
         <v>1537</v>
@@ -17173,7 +17173,7 @@
         <v>1458</v>
       </c>
       <c r="E265">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F265" t="s">
         <v>1537</v>
@@ -17208,7 +17208,7 @@
         <v>1458</v>
       </c>
       <c r="E266">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F266" t="s">
         <v>1537</v>
@@ -17243,7 +17243,7 @@
         <v>1458</v>
       </c>
       <c r="E267">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F267" t="s">
         <v>1537</v>
@@ -17278,7 +17278,7 @@
         <v>1458</v>
       </c>
       <c r="E268">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F268" t="s">
         <v>1537</v>
@@ -17313,7 +17313,7 @@
         <v>1459</v>
       </c>
       <c r="E269">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F269" t="s">
         <v>1537</v>
@@ -17348,7 +17348,7 @@
         <v>1459</v>
       </c>
       <c r="E270">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F270" t="s">
         <v>1537</v>
@@ -17383,7 +17383,7 @@
         <v>1459</v>
       </c>
       <c r="E271">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F271" t="s">
         <v>1537</v>
@@ -17418,7 +17418,7 @@
         <v>1460</v>
       </c>
       <c r="E272">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F272" t="s">
         <v>1537</v>
@@ -17453,7 +17453,7 @@
         <v>1461</v>
       </c>
       <c r="E273">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F273" t="s">
         <v>1537</v>
@@ -17488,7 +17488,7 @@
         <v>1462</v>
       </c>
       <c r="E274">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F274" t="s">
         <v>1537</v>
@@ -17523,7 +17523,7 @@
         <v>1462</v>
       </c>
       <c r="E275">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F275" t="s">
         <v>1537</v>
@@ -17558,7 +17558,7 @@
         <v>1462</v>
       </c>
       <c r="E276">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F276" t="s">
         <v>1537</v>
@@ -17593,7 +17593,7 @@
         <v>1462</v>
       </c>
       <c r="E277">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F277" t="s">
         <v>1537</v>
@@ -17628,7 +17628,7 @@
         <v>1462</v>
       </c>
       <c r="E278">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F278" t="s">
         <v>1537</v>
@@ -17663,7 +17663,7 @@
         <v>1463</v>
       </c>
       <c r="E279">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F279" t="s">
         <v>1537</v>
@@ -17698,7 +17698,7 @@
         <v>1463</v>
       </c>
       <c r="E280">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F280" t="s">
         <v>1537</v>
@@ -17733,7 +17733,7 @@
         <v>1464</v>
       </c>
       <c r="E281">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F281" t="s">
         <v>1537</v>
@@ -17768,7 +17768,7 @@
         <v>1464</v>
       </c>
       <c r="E282">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F282" t="s">
         <v>1537</v>
@@ -17803,7 +17803,7 @@
         <v>1465</v>
       </c>
       <c r="E283">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F283" t="s">
         <v>1537</v>
@@ -17838,7 +17838,7 @@
         <v>1466</v>
       </c>
       <c r="E284">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F284" t="s">
         <v>1537</v>
@@ -17873,7 +17873,7 @@
         <v>1467</v>
       </c>
       <c r="E285">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F285" t="s">
         <v>1537</v>
@@ -17908,7 +17908,7 @@
         <v>1467</v>
       </c>
       <c r="E286">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F286" t="s">
         <v>1537</v>
@@ -17943,7 +17943,7 @@
         <v>1468</v>
       </c>
       <c r="E287">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F287" t="s">
         <v>1537</v>
@@ -17978,7 +17978,7 @@
         <v>1468</v>
       </c>
       <c r="E288">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F288" t="s">
         <v>1537</v>
@@ -18013,7 +18013,7 @@
         <v>1468</v>
       </c>
       <c r="E289">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F289" t="s">
         <v>1537</v>
@@ -18048,7 +18048,7 @@
         <v>1469</v>
       </c>
       <c r="E290">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F290" t="s">
         <v>1537</v>
@@ -18083,7 +18083,7 @@
         <v>1469</v>
       </c>
       <c r="E291">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F291" t="s">
         <v>1537</v>
@@ -18118,7 +18118,7 @@
         <v>1469</v>
       </c>
       <c r="E292">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F292" t="s">
         <v>1537</v>
@@ -18153,7 +18153,7 @@
         <v>1469</v>
       </c>
       <c r="E293">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F293" t="s">
         <v>1537</v>
@@ -18188,7 +18188,7 @@
         <v>1469</v>
       </c>
       <c r="E294">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F294" t="s">
         <v>1537</v>
@@ -18223,7 +18223,7 @@
         <v>1469</v>
       </c>
       <c r="E295">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F295" t="s">
         <v>1537</v>
@@ -18258,7 +18258,7 @@
         <v>1469</v>
       </c>
       <c r="E296">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F296" t="s">
         <v>1537</v>
@@ -18293,7 +18293,7 @@
         <v>1469</v>
       </c>
       <c r="E297">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F297" t="s">
         <v>1537</v>
@@ -18328,7 +18328,7 @@
         <v>1469</v>
       </c>
       <c r="E298">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F298" t="s">
         <v>1537</v>
@@ -18363,7 +18363,7 @@
         <v>1470</v>
       </c>
       <c r="E299">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F299" t="s">
         <v>1537</v>
@@ -18398,7 +18398,7 @@
         <v>1470</v>
       </c>
       <c r="E300">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F300" t="s">
         <v>1537</v>
@@ -18433,7 +18433,7 @@
         <v>1470</v>
       </c>
       <c r="E301">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F301" t="s">
         <v>1537</v>
@@ -18468,7 +18468,7 @@
         <v>1471</v>
       </c>
       <c r="E302">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F302" t="s">
         <v>1537</v>
@@ -18503,7 +18503,7 @@
         <v>1472</v>
       </c>
       <c r="E303">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F303" t="s">
         <v>1537</v>
@@ -18538,7 +18538,7 @@
         <v>1472</v>
       </c>
       <c r="E304">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F304" t="s">
         <v>1537</v>
@@ -18573,7 +18573,7 @@
         <v>1472</v>
       </c>
       <c r="E305">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F305" t="s">
         <v>1537</v>
@@ -18608,7 +18608,7 @@
         <v>1472</v>
       </c>
       <c r="E306">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F306" t="s">
         <v>1537</v>
@@ -18643,7 +18643,7 @@
         <v>1472</v>
       </c>
       <c r="E307">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F307" t="s">
         <v>1537</v>
@@ -18678,7 +18678,7 @@
         <v>1472</v>
       </c>
       <c r="E308">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F308" t="s">
         <v>1537</v>
@@ -18713,7 +18713,7 @@
         <v>1473</v>
       </c>
       <c r="E309">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F309" t="s">
         <v>1537</v>
@@ -18748,7 +18748,7 @@
         <v>1473</v>
       </c>
       <c r="E310">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F310" t="s">
         <v>1537</v>
@@ -18783,7 +18783,7 @@
         <v>1473</v>
       </c>
       <c r="E311">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F311" t="s">
         <v>1537</v>
@@ -18818,7 +18818,7 @@
         <v>1473</v>
       </c>
       <c r="E312">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F312" t="s">
         <v>1537</v>
@@ -18856,7 +18856,7 @@
         <v>1473</v>
       </c>
       <c r="E313">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F313" t="s">
         <v>1537</v>
@@ -18891,7 +18891,7 @@
         <v>1473</v>
       </c>
       <c r="E314">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F314" t="s">
         <v>1537</v>
@@ -18926,7 +18926,7 @@
         <v>1473</v>
       </c>
       <c r="E315">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F315" t="s">
         <v>1537</v>
@@ -18961,7 +18961,7 @@
         <v>1473</v>
       </c>
       <c r="E316">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F316" t="s">
         <v>1537</v>
@@ -18996,7 +18996,7 @@
         <v>1473</v>
       </c>
       <c r="E317">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F317" t="s">
         <v>1537</v>
@@ -19031,7 +19031,7 @@
         <v>1474</v>
       </c>
       <c r="E318">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F318" t="s">
         <v>1538</v>
@@ -19066,7 +19066,7 @@
         <v>1475</v>
       </c>
       <c r="E319">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F319" t="s">
         <v>1541</v>
@@ -19101,7 +19101,7 @@
         <v>1476</v>
       </c>
       <c r="E320">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F320" t="s">
         <v>1537</v>
@@ -19136,7 +19136,7 @@
         <v>1477</v>
       </c>
       <c r="E321">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F321" t="s">
         <v>1537</v>
@@ -19171,7 +19171,7 @@
         <v>1477</v>
       </c>
       <c r="E322">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F322" t="s">
         <v>1537</v>
@@ -19206,7 +19206,7 @@
         <v>1478</v>
       </c>
       <c r="E323">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F323" t="s">
         <v>1537</v>
@@ -19241,7 +19241,7 @@
         <v>1479</v>
       </c>
       <c r="E324">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F324" t="s">
         <v>1540</v>
@@ -19276,7 +19276,7 @@
         <v>1479</v>
       </c>
       <c r="E325">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F325" t="s">
         <v>1537</v>
@@ -19311,7 +19311,7 @@
         <v>1479</v>
       </c>
       <c r="E326">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F326" t="s">
         <v>1537</v>
@@ -19346,7 +19346,7 @@
         <v>1479</v>
       </c>
       <c r="E327">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F327" t="s">
         <v>1537</v>
@@ -19381,7 +19381,7 @@
         <v>1479</v>
       </c>
       <c r="E328">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F328" t="s">
         <v>1537</v>
@@ -19416,7 +19416,7 @@
         <v>1479</v>
       </c>
       <c r="E329">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F329" t="s">
         <v>1537</v>
@@ -19451,7 +19451,7 @@
         <v>1480</v>
       </c>
       <c r="E330">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F330" t="s">
         <v>1537</v>
@@ -19486,7 +19486,7 @@
         <v>1481</v>
       </c>
       <c r="E331">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F331" t="s">
         <v>1537</v>
@@ -19521,7 +19521,7 @@
         <v>1481</v>
       </c>
       <c r="E332">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F332" t="s">
         <v>1537</v>
@@ -19556,7 +19556,7 @@
         <v>1481</v>
       </c>
       <c r="E333">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F333" t="s">
         <v>1537</v>
@@ -19594,7 +19594,7 @@
         <v>1481</v>
       </c>
       <c r="E334">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F334" t="s">
         <v>1537</v>
@@ -19629,7 +19629,7 @@
         <v>1482</v>
       </c>
       <c r="E335">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F335" t="s">
         <v>1537</v>
@@ -19664,7 +19664,7 @@
         <v>1482</v>
       </c>
       <c r="E336">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F336" t="s">
         <v>1537</v>
@@ -19699,7 +19699,7 @@
         <v>1482</v>
       </c>
       <c r="E337">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F337" t="s">
         <v>1537</v>
@@ -19734,7 +19734,7 @@
         <v>1482</v>
       </c>
       <c r="E338">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F338" t="s">
         <v>1537</v>
@@ -19769,7 +19769,7 @@
         <v>1482</v>
       </c>
       <c r="E339">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F339" t="s">
         <v>1537</v>
@@ -19804,7 +19804,7 @@
         <v>1483</v>
       </c>
       <c r="E340">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F340" t="s">
         <v>1537</v>
@@ -19839,7 +19839,7 @@
         <v>1483</v>
       </c>
       <c r="E341">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F341" t="s">
         <v>1537</v>
@@ -19874,7 +19874,7 @@
         <v>1484</v>
       </c>
       <c r="E342">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F342" t="s">
         <v>1537</v>
@@ -19909,7 +19909,7 @@
         <v>1484</v>
       </c>
       <c r="E343">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F343" t="s">
         <v>1537</v>
@@ -19944,7 +19944,7 @@
         <v>1484</v>
       </c>
       <c r="E344">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F344" t="s">
         <v>1537</v>
@@ -19979,7 +19979,7 @@
         <v>1484</v>
       </c>
       <c r="E345">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F345" t="s">
         <v>1537</v>
@@ -20014,7 +20014,7 @@
         <v>1484</v>
       </c>
       <c r="E346">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F346" t="s">
         <v>1537</v>
@@ -20049,7 +20049,7 @@
         <v>1484</v>
       </c>
       <c r="E347">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F347" t="s">
         <v>1537</v>
@@ -20084,7 +20084,7 @@
         <v>1484</v>
       </c>
       <c r="E348">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F348" t="s">
         <v>1537</v>
@@ -20119,7 +20119,7 @@
         <v>1484</v>
       </c>
       <c r="E349">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F349" t="s">
         <v>1537</v>
@@ -20154,7 +20154,7 @@
         <v>1484</v>
       </c>
       <c r="E350">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F350" t="s">
         <v>1537</v>
@@ -20189,7 +20189,7 @@
         <v>1484</v>
       </c>
       <c r="E351">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F351" t="s">
         <v>1537</v>
@@ -20224,7 +20224,7 @@
         <v>1485</v>
       </c>
       <c r="E352">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F352" t="s">
         <v>1537</v>
@@ -20259,7 +20259,7 @@
         <v>1485</v>
       </c>
       <c r="E353">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F353" t="s">
         <v>1537</v>
@@ -20294,7 +20294,7 @@
         <v>1485</v>
       </c>
       <c r="E354">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F354" t="s">
         <v>1538</v>
@@ -20329,7 +20329,7 @@
         <v>1486</v>
       </c>
       <c r="E355">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F355" t="s">
         <v>1537</v>
@@ -20364,7 +20364,7 @@
         <v>1486</v>
       </c>
       <c r="E356">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F356" t="s">
         <v>1537</v>
@@ -20399,7 +20399,7 @@
         <v>1486</v>
       </c>
       <c r="E357">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F357" t="s">
         <v>1537</v>
@@ -20434,7 +20434,7 @@
         <v>1486</v>
       </c>
       <c r="E358">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F358" t="s">
         <v>1537</v>
@@ -20469,7 +20469,7 @@
         <v>1486</v>
       </c>
       <c r="E359">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F359" t="s">
         <v>1537</v>
@@ -20504,7 +20504,7 @@
         <v>1486</v>
       </c>
       <c r="E360">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F360" t="s">
         <v>1537</v>
@@ -20539,7 +20539,7 @@
         <v>1486</v>
       </c>
       <c r="E361">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F361" t="s">
         <v>1540</v>
@@ -20574,7 +20574,7 @@
         <v>1487</v>
       </c>
       <c r="E362">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F362" t="s">
         <v>1537</v>
@@ -20609,7 +20609,7 @@
         <v>1487</v>
       </c>
       <c r="E363">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F363" t="s">
         <v>1537</v>
@@ -20644,7 +20644,7 @@
         <v>1487</v>
       </c>
       <c r="E364">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F364" t="s">
         <v>1537</v>
@@ -20679,7 +20679,7 @@
         <v>1487</v>
       </c>
       <c r="E365">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F365" t="s">
         <v>1537</v>
@@ -20714,7 +20714,7 @@
         <v>1488</v>
       </c>
       <c r="E366">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F366" t="s">
         <v>1540</v>
@@ -20749,7 +20749,7 @@
         <v>1488</v>
       </c>
       <c r="E367">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F367" t="s">
         <v>1537</v>
@@ -20784,7 +20784,7 @@
         <v>1488</v>
       </c>
       <c r="E368">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F368" t="s">
         <v>1537</v>
@@ -20819,7 +20819,7 @@
         <v>1488</v>
       </c>
       <c r="E369">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F369" t="s">
         <v>1537</v>
@@ -20854,7 +20854,7 @@
         <v>1488</v>
       </c>
       <c r="E370">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F370" t="s">
         <v>1537</v>
@@ -20889,7 +20889,7 @@
         <v>1488</v>
       </c>
       <c r="E371">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F371" t="s">
         <v>1537</v>
@@ -20924,7 +20924,7 @@
         <v>1489</v>
       </c>
       <c r="E372">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F372" t="s">
         <v>1537</v>
@@ -20959,7 +20959,7 @@
         <v>1489</v>
       </c>
       <c r="E373">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F373" t="s">
         <v>1537</v>
@@ -20994,7 +20994,7 @@
         <v>1489</v>
       </c>
       <c r="E374">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F374" t="s">
         <v>1537</v>
@@ -21029,7 +21029,7 @@
         <v>1489</v>
       </c>
       <c r="E375">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F375" t="s">
         <v>1539</v>
@@ -21064,7 +21064,7 @@
         <v>1489</v>
       </c>
       <c r="E376">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F376" t="s">
         <v>1537</v>
@@ -21099,7 +21099,7 @@
         <v>1489</v>
       </c>
       <c r="E377">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F377" t="s">
         <v>1537</v>
@@ -21134,7 +21134,7 @@
         <v>1490</v>
       </c>
       <c r="E378">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F378" t="s">
         <v>1537</v>
@@ -21169,7 +21169,7 @@
         <v>1490</v>
       </c>
       <c r="E379">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F379" t="s">
         <v>1537</v>
@@ -21204,7 +21204,7 @@
         <v>1490</v>
       </c>
       <c r="E380">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F380" t="s">
         <v>1537</v>
@@ -21239,7 +21239,7 @@
         <v>1490</v>
       </c>
       <c r="E381">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F381" t="s">
         <v>1537</v>
@@ -21274,7 +21274,7 @@
         <v>1490</v>
       </c>
       <c r="E382">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F382" t="s">
         <v>1537</v>
@@ -21309,7 +21309,7 @@
         <v>1491</v>
       </c>
       <c r="E383">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F383" t="s">
         <v>1537</v>
@@ -21344,7 +21344,7 @@
         <v>1491</v>
       </c>
       <c r="E384">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F384" t="s">
         <v>1537</v>
@@ -21379,7 +21379,7 @@
         <v>1491</v>
       </c>
       <c r="E385">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F385" t="s">
         <v>1537</v>
@@ -21414,7 +21414,7 @@
         <v>1491</v>
       </c>
       <c r="E386">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F386" t="s">
         <v>1537</v>
@@ -21452,7 +21452,7 @@
         <v>1492</v>
       </c>
       <c r="E387">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F387" t="s">
         <v>1537</v>
@@ -21487,7 +21487,7 @@
         <v>1492</v>
       </c>
       <c r="E388">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F388" t="s">
         <v>1537</v>
@@ -21522,7 +21522,7 @@
         <v>1492</v>
       </c>
       <c r="E389">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F389" t="s">
         <v>1537</v>
@@ -21557,7 +21557,7 @@
         <v>1492</v>
       </c>
       <c r="E390">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F390" t="s">
         <v>1537</v>
@@ -21592,7 +21592,7 @@
         <v>1492</v>
       </c>
       <c r="E391">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F391" t="s">
         <v>1537</v>
@@ -21627,7 +21627,7 @@
         <v>1492</v>
       </c>
       <c r="E392">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F392" t="s">
         <v>1537</v>
@@ -21662,7 +21662,7 @@
         <v>1493</v>
       </c>
       <c r="E393">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F393" t="s">
         <v>1538</v>
@@ -21697,7 +21697,7 @@
         <v>1493</v>
       </c>
       <c r="E394">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F394" t="s">
         <v>1537</v>
@@ -21732,7 +21732,7 @@
         <v>1494</v>
       </c>
       <c r="E395">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F395" t="s">
         <v>1537</v>
@@ -21767,7 +21767,7 @@
         <v>1495</v>
       </c>
       <c r="E396">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F396" t="s">
         <v>1537</v>
@@ -21802,7 +21802,7 @@
         <v>1495</v>
       </c>
       <c r="E397">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F397" t="s">
         <v>1537</v>
@@ -21837,7 +21837,7 @@
         <v>1495</v>
       </c>
       <c r="E398">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F398" t="s">
         <v>1539</v>
@@ -21875,7 +21875,7 @@
         <v>1496</v>
       </c>
       <c r="E399">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F399" t="s">
         <v>1537</v>
@@ -21910,7 +21910,7 @@
         <v>1496</v>
       </c>
       <c r="E400">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F400" t="s">
         <v>1537</v>
@@ -21945,7 +21945,7 @@
         <v>1496</v>
       </c>
       <c r="E401">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F401" t="s">
         <v>1537</v>
@@ -21980,7 +21980,7 @@
         <v>1497</v>
       </c>
       <c r="E402">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F402" t="s">
         <v>1537</v>
@@ -22015,7 +22015,7 @@
         <v>1497</v>
       </c>
       <c r="E403">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F403" t="s">
         <v>1537</v>
@@ -22050,7 +22050,7 @@
         <v>1497</v>
       </c>
       <c r="E404">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F404" t="s">
         <v>1537</v>
@@ -22085,7 +22085,7 @@
         <v>1497</v>
       </c>
       <c r="E405">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F405" t="s">
         <v>1537</v>
@@ -22120,7 +22120,7 @@
         <v>1497</v>
       </c>
       <c r="E406">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F406" t="s">
         <v>1537</v>
@@ -22155,7 +22155,7 @@
         <v>1497</v>
       </c>
       <c r="E407">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F407" t="s">
         <v>1537</v>
@@ -22190,7 +22190,7 @@
         <v>1497</v>
       </c>
       <c r="E408">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F408" t="s">
         <v>1537</v>
@@ -22225,7 +22225,7 @@
         <v>1498</v>
       </c>
       <c r="E409">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F409" t="s">
         <v>1537</v>
@@ -22260,7 +22260,7 @@
         <v>1499</v>
       </c>
       <c r="E410">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F410" t="s">
         <v>1537</v>
@@ -22295,7 +22295,7 @@
         <v>1499</v>
       </c>
       <c r="E411">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F411" t="s">
         <v>1537</v>
@@ -22330,7 +22330,7 @@
         <v>1499</v>
       </c>
       <c r="E412">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F412" t="s">
         <v>1537</v>
@@ -22365,7 +22365,7 @@
         <v>1499</v>
       </c>
       <c r="E413">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F413" t="s">
         <v>1541</v>
@@ -22403,7 +22403,7 @@
         <v>1499</v>
       </c>
       <c r="E414">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F414" t="s">
         <v>1537</v>
@@ -22438,7 +22438,7 @@
         <v>1499</v>
       </c>
       <c r="E415">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F415" t="s">
         <v>1541</v>
@@ -22473,7 +22473,7 @@
         <v>1500</v>
       </c>
       <c r="E416">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F416" t="s">
         <v>1537</v>
@@ -22508,7 +22508,7 @@
         <v>1501</v>
       </c>
       <c r="E417">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F417" t="s">
         <v>1537</v>
@@ -22543,7 +22543,7 @@
         <v>1501</v>
       </c>
       <c r="E418">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F418" t="s">
         <v>1537</v>
@@ -22578,7 +22578,7 @@
         <v>1501</v>
       </c>
       <c r="E419">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F419" t="s">
         <v>1537</v>
@@ -22613,7 +22613,7 @@
         <v>1501</v>
       </c>
       <c r="E420">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F420" t="s">
         <v>1537</v>
@@ -22648,7 +22648,7 @@
         <v>1502</v>
       </c>
       <c r="E421">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F421" t="s">
         <v>1541</v>
@@ -22683,7 +22683,7 @@
         <v>1502</v>
       </c>
       <c r="E422">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F422" t="s">
         <v>1537</v>
@@ -22718,7 +22718,7 @@
         <v>1502</v>
       </c>
       <c r="E423">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F423" t="s">
         <v>1537</v>
@@ -22753,7 +22753,7 @@
         <v>1502</v>
       </c>
       <c r="E424">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F424" t="s">
         <v>1537</v>
@@ -22788,7 +22788,7 @@
         <v>1503</v>
       </c>
       <c r="E425">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F425" t="s">
         <v>1537</v>
@@ -22823,7 +22823,7 @@
         <v>1503</v>
       </c>
       <c r="E426">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F426" t="s">
         <v>1537</v>
@@ -22858,7 +22858,7 @@
         <v>1503</v>
       </c>
       <c r="E427">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F427" t="s">
         <v>1537</v>
@@ -22893,7 +22893,7 @@
         <v>1504</v>
       </c>
       <c r="E428">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F428" t="s">
         <v>1537</v>
@@ -22928,7 +22928,7 @@
         <v>1504</v>
       </c>
       <c r="E429">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F429" t="s">
         <v>1537</v>
@@ -22963,7 +22963,7 @@
         <v>1504</v>
       </c>
       <c r="E430">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F430" t="s">
         <v>1537</v>
@@ -22998,7 +22998,7 @@
         <v>1504</v>
       </c>
       <c r="E431">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F431" t="s">
         <v>1537</v>
@@ -23033,7 +23033,7 @@
         <v>1504</v>
       </c>
       <c r="E432">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F432" t="s">
         <v>1537</v>
@@ -23068,7 +23068,7 @@
         <v>1505</v>
       </c>
       <c r="E433">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F433" t="s">
         <v>1537</v>
@@ -23103,7 +23103,7 @@
         <v>1505</v>
       </c>
       <c r="E434">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F434" t="s">
         <v>1537</v>
@@ -23138,7 +23138,7 @@
         <v>1505</v>
       </c>
       <c r="E435">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F435" t="s">
         <v>1537</v>
@@ -23173,7 +23173,7 @@
         <v>1505</v>
       </c>
       <c r="E436">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F436" t="s">
         <v>1537</v>
@@ -23208,7 +23208,7 @@
         <v>1505</v>
       </c>
       <c r="E437">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F437" t="s">
         <v>1537</v>
@@ -23243,7 +23243,7 @@
         <v>1505</v>
       </c>
       <c r="E438">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F438" t="s">
         <v>1537</v>
@@ -23278,7 +23278,7 @@
         <v>1505</v>
       </c>
       <c r="E439">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F439" t="s">
         <v>1537</v>
@@ -23313,7 +23313,7 @@
         <v>1505</v>
       </c>
       <c r="E440">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F440" t="s">
         <v>1537</v>
@@ -23348,7 +23348,7 @@
         <v>1505</v>
       </c>
       <c r="E441">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F441" t="s">
         <v>1537</v>
@@ -23383,7 +23383,7 @@
         <v>1505</v>
       </c>
       <c r="E442">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F442" t="s">
         <v>1537</v>
@@ -23418,7 +23418,7 @@
         <v>1505</v>
       </c>
       <c r="E443">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F443" t="s">
         <v>1537</v>
@@ -23453,7 +23453,7 @@
         <v>1505</v>
       </c>
       <c r="E444">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F444" t="s">
         <v>1537</v>
@@ -23488,7 +23488,7 @@
         <v>1505</v>
       </c>
       <c r="E445">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F445" t="s">
         <v>1537</v>
@@ -23523,7 +23523,7 @@
         <v>1505</v>
       </c>
       <c r="E446">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F446" t="s">
         <v>1537</v>
@@ -23558,7 +23558,7 @@
         <v>1505</v>
       </c>
       <c r="E447">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F447" t="s">
         <v>1537</v>
@@ -23593,7 +23593,7 @@
         <v>1505</v>
       </c>
       <c r="E448">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F448" t="s">
         <v>1537</v>
@@ -23628,7 +23628,7 @@
         <v>1505</v>
       </c>
       <c r="E449">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F449" t="s">
         <v>1537</v>
@@ -23663,7 +23663,7 @@
         <v>1505</v>
       </c>
       <c r="E450">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F450" t="s">
         <v>1537</v>
@@ -23698,7 +23698,7 @@
         <v>1505</v>
       </c>
       <c r="E451">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F451" t="s">
         <v>1537</v>
@@ -23733,7 +23733,7 @@
         <v>1505</v>
       </c>
       <c r="E452">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F452" t="s">
         <v>1537</v>
@@ -23768,7 +23768,7 @@
         <v>1505</v>
       </c>
       <c r="E453">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F453" t="s">
         <v>1537</v>
@@ -23803,7 +23803,7 @@
         <v>1505</v>
       </c>
       <c r="E454">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F454" t="s">
         <v>1537</v>
@@ -23838,7 +23838,7 @@
         <v>1505</v>
       </c>
       <c r="E455">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F455" t="s">
         <v>1537</v>
@@ -23873,7 +23873,7 @@
         <v>1505</v>
       </c>
       <c r="E456">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F456" t="s">
         <v>1537</v>
@@ -23908,7 +23908,7 @@
         <v>1506</v>
       </c>
       <c r="E457">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F457" t="s">
         <v>1537</v>
@@ -23943,7 +23943,7 @@
         <v>1506</v>
       </c>
       <c r="E458">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F458" t="s">
         <v>1537</v>
@@ -23978,7 +23978,7 @@
         <v>1506</v>
       </c>
       <c r="E459">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F459" t="s">
         <v>1537</v>
@@ -24013,7 +24013,7 @@
         <v>1506</v>
       </c>
       <c r="E460">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F460" t="s">
         <v>1537</v>
@@ -24048,7 +24048,7 @@
         <v>1506</v>
       </c>
       <c r="E461">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F461" t="s">
         <v>1537</v>
@@ -24083,7 +24083,7 @@
         <v>1506</v>
       </c>
       <c r="E462">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F462" t="s">
         <v>1537</v>
@@ -24118,7 +24118,7 @@
         <v>1506</v>
       </c>
       <c r="E463">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F463" t="s">
         <v>1541</v>
@@ -24153,7 +24153,7 @@
         <v>1506</v>
       </c>
       <c r="E464">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F464" t="s">
         <v>1537</v>
@@ -24188,7 +24188,7 @@
         <v>1507</v>
       </c>
       <c r="E465">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F465" t="s">
         <v>1537</v>
@@ -24223,7 +24223,7 @@
         <v>1508</v>
       </c>
       <c r="E466">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F466" t="s">
         <v>1539</v>
@@ -24261,7 +24261,7 @@
         <v>1508</v>
       </c>
       <c r="E467">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F467" t="s">
         <v>1537</v>
@@ -24296,7 +24296,7 @@
         <v>1508</v>
       </c>
       <c r="E468">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F468" t="s">
         <v>1537</v>
@@ -24331,7 +24331,7 @@
         <v>1508</v>
       </c>
       <c r="E469">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F469" t="s">
         <v>1537</v>
@@ -24366,7 +24366,7 @@
         <v>1508</v>
       </c>
       <c r="E470">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F470" t="s">
         <v>1537</v>
@@ -24401,7 +24401,7 @@
         <v>1509</v>
       </c>
       <c r="E471">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F471" t="s">
         <v>1537</v>
@@ -24439,7 +24439,7 @@
         <v>1509</v>
       </c>
       <c r="E472">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F472" t="s">
         <v>1541</v>
@@ -24474,7 +24474,7 @@
         <v>1509</v>
       </c>
       <c r="E473">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F473" t="s">
         <v>1539</v>
@@ -24509,7 +24509,7 @@
         <v>1509</v>
       </c>
       <c r="E474">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F474" t="s">
         <v>1537</v>
@@ -24544,7 +24544,7 @@
         <v>1509</v>
       </c>
       <c r="E475">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F475" t="s">
         <v>1537</v>
@@ -24579,7 +24579,7 @@
         <v>1509</v>
       </c>
       <c r="E476">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F476" t="s">
         <v>1537</v>
@@ -24614,7 +24614,7 @@
         <v>1509</v>
       </c>
       <c r="E477">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F477" t="s">
         <v>1537</v>
@@ -24649,7 +24649,7 @@
         <v>1509</v>
       </c>
       <c r="E478">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F478" t="s">
         <v>1537</v>
@@ -24684,7 +24684,7 @@
         <v>1509</v>
       </c>
       <c r="E479">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F479" t="s">
         <v>1537</v>
@@ -24719,7 +24719,7 @@
         <v>1510</v>
       </c>
       <c r="E480">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F480" t="s">
         <v>1541</v>
@@ -24757,7 +24757,7 @@
         <v>1510</v>
       </c>
       <c r="E481">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F481" t="s">
         <v>1537</v>
@@ -24792,7 +24792,7 @@
         <v>1511</v>
       </c>
       <c r="E482">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F482" t="s">
         <v>1537</v>
@@ -24827,7 +24827,7 @@
         <v>1511</v>
       </c>
       <c r="E483">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F483" t="s">
         <v>1537</v>
@@ -24862,7 +24862,7 @@
         <v>1511</v>
       </c>
       <c r="E484">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F484" t="s">
         <v>1537</v>
@@ -24897,7 +24897,7 @@
         <v>1511</v>
       </c>
       <c r="E485">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F485" t="s">
         <v>1537</v>
@@ -24932,7 +24932,7 @@
         <v>1511</v>
       </c>
       <c r="E486">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F486" t="s">
         <v>1537</v>
@@ -24967,7 +24967,7 @@
         <v>1511</v>
       </c>
       <c r="E487">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F487" t="s">
         <v>1537</v>
@@ -25002,7 +25002,7 @@
         <v>1512</v>
       </c>
       <c r="E488">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F488" t="s">
         <v>1537</v>
@@ -25037,7 +25037,7 @@
         <v>1512</v>
       </c>
       <c r="E489">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F489" t="s">
         <v>1537</v>
@@ -25072,7 +25072,7 @@
         <v>1512</v>
       </c>
       <c r="E490">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F490" t="s">
         <v>1537</v>
@@ -25107,7 +25107,7 @@
         <v>1512</v>
       </c>
       <c r="E491">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F491" t="s">
         <v>1537</v>
@@ -25142,7 +25142,7 @@
         <v>1512</v>
       </c>
       <c r="E492">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F492" t="s">
         <v>1537</v>
@@ -25177,7 +25177,7 @@
         <v>1512</v>
       </c>
       <c r="E493">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F493" t="s">
         <v>1539</v>
@@ -25212,7 +25212,7 @@
         <v>1512</v>
       </c>
       <c r="E494">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F494" t="s">
         <v>1537</v>
@@ -25247,7 +25247,7 @@
         <v>1512</v>
       </c>
       <c r="E495">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F495" t="s">
         <v>1537</v>
@@ -25282,7 +25282,7 @@
         <v>1513</v>
       </c>
       <c r="E496">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F496" t="s">
         <v>1537</v>
@@ -25317,7 +25317,7 @@
         <v>1513</v>
       </c>
       <c r="E497">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F497" t="s">
         <v>1537</v>
@@ -25352,7 +25352,7 @@
         <v>1513</v>
       </c>
       <c r="E498">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F498" t="s">
         <v>1537</v>
@@ -25387,7 +25387,7 @@
         <v>1513</v>
       </c>
       <c r="E499">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F499" t="s">
         <v>1537</v>
@@ -25422,7 +25422,7 @@
         <v>1513</v>
       </c>
       <c r="E500">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F500" t="s">
         <v>1537</v>
@@ -25457,7 +25457,7 @@
         <v>1513</v>
       </c>
       <c r="E501">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F501" t="s">
         <v>1537</v>
@@ -25492,7 +25492,7 @@
         <v>1513</v>
       </c>
       <c r="E502">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F502" t="s">
         <v>1537</v>
@@ -25527,7 +25527,7 @@
         <v>1513</v>
       </c>
       <c r="E503">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F503" t="s">
         <v>1537</v>
@@ -25562,7 +25562,7 @@
         <v>1514</v>
       </c>
       <c r="E504">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F504" t="s">
         <v>1537</v>
@@ -25597,7 +25597,7 @@
         <v>1514</v>
       </c>
       <c r="E505">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F505" t="s">
         <v>1537</v>
@@ -25632,7 +25632,7 @@
         <v>1514</v>
       </c>
       <c r="E506">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F506" t="s">
         <v>1537</v>
@@ -25667,7 +25667,7 @@
         <v>1514</v>
       </c>
       <c r="E507">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F507" t="s">
         <v>1537</v>
@@ -25702,7 +25702,7 @@
         <v>1514</v>
       </c>
       <c r="E508">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F508" t="s">
         <v>1537</v>
@@ -25737,7 +25737,7 @@
         <v>1514</v>
       </c>
       <c r="E509">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F509" t="s">
         <v>1537</v>
@@ -25772,7 +25772,7 @@
         <v>1515</v>
       </c>
       <c r="E510">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F510" t="s">
         <v>1537</v>
@@ -25807,7 +25807,7 @@
         <v>1515</v>
       </c>
       <c r="E511">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F511" t="s">
         <v>1537</v>
@@ -25842,7 +25842,7 @@
         <v>1515</v>
       </c>
       <c r="E512">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F512" t="s">
         <v>1537</v>
@@ -25877,7 +25877,7 @@
         <v>1515</v>
       </c>
       <c r="E513">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F513" t="s">
         <v>1537</v>
@@ -25912,7 +25912,7 @@
         <v>1515</v>
       </c>
       <c r="E514">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F514" t="s">
         <v>1537</v>
@@ -25947,7 +25947,7 @@
         <v>1516</v>
       </c>
       <c r="E515">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F515" t="s">
         <v>1537</v>
@@ -25982,7 +25982,7 @@
         <v>1516</v>
       </c>
       <c r="E516">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F516" t="s">
         <v>1537</v>
@@ -26017,7 +26017,7 @@
         <v>1516</v>
       </c>
       <c r="E517">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F517" t="s">
         <v>1537</v>
@@ -26052,7 +26052,7 @@
         <v>1516</v>
       </c>
       <c r="E518">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F518" t="s">
         <v>1537</v>
@@ -26087,7 +26087,7 @@
         <v>1516</v>
       </c>
       <c r="E519">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F519" t="s">
         <v>1537</v>
@@ -26122,7 +26122,7 @@
         <v>1516</v>
       </c>
       <c r="E520">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F520" t="s">
         <v>1537</v>
@@ -26157,7 +26157,7 @@
         <v>1516</v>
       </c>
       <c r="E521">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F521" t="s">
         <v>1537</v>
@@ -26192,7 +26192,7 @@
         <v>1516</v>
       </c>
       <c r="E522">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F522" t="s">
         <v>1537</v>
@@ -26227,7 +26227,7 @@
         <v>1516</v>
       </c>
       <c r="E523">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F523" t="s">
         <v>1537</v>
@@ -26265,7 +26265,7 @@
         <v>1516</v>
       </c>
       <c r="E524">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F524" t="s">
         <v>1537</v>
@@ -26300,7 +26300,7 @@
         <v>1517</v>
       </c>
       <c r="E525">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F525" t="s">
         <v>1537</v>
@@ -26335,7 +26335,7 @@
         <v>1517</v>
       </c>
       <c r="E526">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F526" t="s">
         <v>1539</v>
@@ -26373,7 +26373,7 @@
         <v>1517</v>
       </c>
       <c r="E527">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F527" t="s">
         <v>1537</v>
@@ -26408,7 +26408,7 @@
         <v>1517</v>
       </c>
       <c r="E528">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F528" t="s">
         <v>1537</v>
@@ -26443,7 +26443,7 @@
         <v>1518</v>
       </c>
       <c r="E529">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F529" t="s">
         <v>1537</v>
@@ -26478,7 +26478,7 @@
         <v>1518</v>
       </c>
       <c r="E530">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F530" t="s">
         <v>1537</v>
@@ -26513,7 +26513,7 @@
         <v>1518</v>
       </c>
       <c r="E531">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F531" t="s">
         <v>1537</v>
@@ -26548,7 +26548,7 @@
         <v>1518</v>
       </c>
       <c r="E532">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F532" t="s">
         <v>1539</v>
@@ -26586,7 +26586,7 @@
         <v>1518</v>
       </c>
       <c r="E533">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F533" t="s">
         <v>1537</v>
@@ -26621,7 +26621,7 @@
         <v>1518</v>
       </c>
       <c r="E534">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F534" t="s">
         <v>1537</v>
@@ -26656,7 +26656,7 @@
         <v>1518</v>
       </c>
       <c r="E535">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F535" t="s">
         <v>1537</v>
@@ -26691,7 +26691,7 @@
         <v>1518</v>
       </c>
       <c r="E536">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F536" t="s">
         <v>1537</v>
@@ -26726,7 +26726,7 @@
         <v>1518</v>
       </c>
       <c r="E537">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F537" t="s">
         <v>1537</v>
@@ -26761,7 +26761,7 @@
         <v>1518</v>
       </c>
       <c r="E538">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F538" t="s">
         <v>1537</v>
@@ -26796,7 +26796,7 @@
         <v>1519</v>
       </c>
       <c r="E539">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F539" t="s">
         <v>1537</v>
@@ -26831,7 +26831,7 @@
         <v>1519</v>
       </c>
       <c r="E540">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F540" t="s">
         <v>1537</v>
@@ -26866,7 +26866,7 @@
         <v>1519</v>
       </c>
       <c r="E541">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F541" t="s">
         <v>1537</v>
@@ -26901,7 +26901,7 @@
         <v>1519</v>
       </c>
       <c r="E542">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F542" t="s">
         <v>1537</v>
@@ -26936,7 +26936,7 @@
         <v>1520</v>
       </c>
       <c r="E543">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F543" t="s">
         <v>1537</v>
@@ -26971,7 +26971,7 @@
         <v>1520</v>
       </c>
       <c r="E544">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F544" t="s">
         <v>1537</v>
@@ -27006,7 +27006,7 @@
         <v>1520</v>
       </c>
       <c r="E545">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F545" t="s">
         <v>1537</v>
@@ -27041,7 +27041,7 @@
         <v>1520</v>
       </c>
       <c r="E546">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F546" t="s">
         <v>1539</v>
@@ -27079,7 +27079,7 @@
         <v>1521</v>
       </c>
       <c r="E547">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F547" t="s">
         <v>1537</v>
@@ -27114,7 +27114,7 @@
         <v>1521</v>
       </c>
       <c r="E548">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F548" t="s">
         <v>1541</v>
@@ -27152,7 +27152,7 @@
         <v>1521</v>
       </c>
       <c r="E549">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F549" t="s">
         <v>1537</v>
@@ -27187,7 +27187,7 @@
         <v>1521</v>
       </c>
       <c r="E550">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F550" t="s">
         <v>1537</v>
@@ -27222,7 +27222,7 @@
         <v>1522</v>
       </c>
       <c r="E551">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F551" t="s">
         <v>1537</v>
@@ -27257,7 +27257,7 @@
         <v>1522</v>
       </c>
       <c r="E552">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F552" t="s">
         <v>1537</v>
@@ -27292,7 +27292,7 @@
         <v>1522</v>
       </c>
       <c r="E553">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F553" t="s">
         <v>1537</v>
@@ -27327,7 +27327,7 @@
         <v>1522</v>
       </c>
       <c r="E554">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F554" t="s">
         <v>1537</v>
@@ -27362,7 +27362,7 @@
         <v>1522</v>
       </c>
       <c r="E555">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F555" t="s">
         <v>1539</v>
@@ -27400,7 +27400,7 @@
         <v>1522</v>
       </c>
       <c r="E556">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F556" t="s">
         <v>1537</v>
@@ -27435,7 +27435,7 @@
         <v>1522</v>
       </c>
       <c r="E557">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F557" t="s">
         <v>1537</v>
@@ -27470,7 +27470,7 @@
         <v>1522</v>
       </c>
       <c r="E558">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F558" t="s">
         <v>1537</v>
@@ -27505,7 +27505,7 @@
         <v>1523</v>
       </c>
       <c r="E559">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F559" t="s">
         <v>1537</v>
@@ -27540,7 +27540,7 @@
         <v>1523</v>
       </c>
       <c r="E560">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F560" t="s">
         <v>1537</v>
@@ -27575,7 +27575,7 @@
         <v>1524</v>
       </c>
       <c r="E561">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F561" t="s">
         <v>1539</v>
@@ -27613,7 +27613,7 @@
         <v>1524</v>
       </c>
       <c r="E562">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F562" t="s">
         <v>1539</v>
@@ -27651,7 +27651,7 @@
         <v>1524</v>
       </c>
       <c r="E563">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F563" t="s">
         <v>1537</v>
@@ -27686,7 +27686,7 @@
         <v>1524</v>
       </c>
       <c r="E564">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F564" t="s">
         <v>1537</v>
@@ -27721,7 +27721,7 @@
         <v>1524</v>
       </c>
       <c r="E565">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F565" t="s">
         <v>1537</v>
@@ -27756,7 +27756,7 @@
         <v>1525</v>
       </c>
       <c r="E566">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F566" t="s">
         <v>1537</v>
@@ -27791,7 +27791,7 @@
         <v>1526</v>
       </c>
       <c r="E567">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F567" t="s">
         <v>1537</v>
@@ -27826,7 +27826,7 @@
         <v>1526</v>
       </c>
       <c r="E568">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F568" t="s">
         <v>1537</v>
@@ -27861,7 +27861,7 @@
         <v>1526</v>
       </c>
       <c r="E569">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F569" t="s">
         <v>1537</v>
@@ -27896,7 +27896,7 @@
         <v>1526</v>
       </c>
       <c r="E570">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F570" t="s">
         <v>1537</v>
@@ -27931,7 +27931,7 @@
         <v>1526</v>
       </c>
       <c r="E571">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F571" t="s">
         <v>1537</v>
@@ -27966,7 +27966,7 @@
         <v>1526</v>
       </c>
       <c r="E572">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F572" t="s">
         <v>1537</v>
@@ -28001,7 +28001,7 @@
         <v>1526</v>
       </c>
       <c r="E573">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F573" t="s">
         <v>1537</v>
@@ -28036,7 +28036,7 @@
         <v>1526</v>
       </c>
       <c r="E574">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F574" t="s">
         <v>1537</v>
@@ -28071,7 +28071,7 @@
         <v>1526</v>
       </c>
       <c r="E575">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F575" t="s">
         <v>1537</v>
@@ -28106,7 +28106,7 @@
         <v>1526</v>
       </c>
       <c r="E576">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F576" t="s">
         <v>1539</v>
@@ -28144,7 +28144,7 @@
         <v>1527</v>
       </c>
       <c r="E577">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F577" t="s">
         <v>1537</v>
@@ -28179,7 +28179,7 @@
         <v>1527</v>
       </c>
       <c r="E578">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F578" t="s">
         <v>1537</v>
@@ -28214,7 +28214,7 @@
         <v>1527</v>
       </c>
       <c r="E579">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F579" t="s">
         <v>1537</v>
@@ -28249,7 +28249,7 @@
         <v>1527</v>
       </c>
       <c r="E580">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F580" t="s">
         <v>1537</v>
@@ -28284,7 +28284,7 @@
         <v>1527</v>
       </c>
       <c r="E581">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F581" t="s">
         <v>1539</v>
@@ -28322,7 +28322,7 @@
         <v>1527</v>
       </c>
       <c r="E582">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F582" t="s">
         <v>1539</v>
@@ -28360,7 +28360,7 @@
         <v>1527</v>
       </c>
       <c r="E583">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F583" t="s">
         <v>1537</v>
@@ -28395,7 +28395,7 @@
         <v>1527</v>
       </c>
       <c r="E584">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F584" t="s">
         <v>1537</v>
@@ -28430,7 +28430,7 @@
         <v>1527</v>
       </c>
       <c r="E585">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F585" t="s">
         <v>1537</v>
@@ -28465,7 +28465,7 @@
         <v>1528</v>
       </c>
       <c r="E586">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F586" t="s">
         <v>1537</v>
@@ -28500,7 +28500,7 @@
         <v>1528</v>
       </c>
       <c r="E587">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F587" t="s">
         <v>1539</v>
@@ -28538,7 +28538,7 @@
         <v>1528</v>
       </c>
       <c r="E588">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F588" t="s">
         <v>1539</v>
@@ -28576,7 +28576,7 @@
         <v>1528</v>
       </c>
       <c r="E589">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F589" t="s">
         <v>1537</v>
@@ -28611,7 +28611,7 @@
         <v>1529</v>
       </c>
       <c r="E590">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F590" t="s">
         <v>1539</v>
@@ -28649,7 +28649,7 @@
         <v>1529</v>
       </c>
       <c r="E591">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F591" t="s">
         <v>1537</v>
@@ -28684,7 +28684,7 @@
         <v>1529</v>
       </c>
       <c r="E592">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F592" t="s">
         <v>1537</v>
@@ -28719,7 +28719,7 @@
         <v>1530</v>
       </c>
       <c r="E593">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F593" t="s">
         <v>1537</v>
@@ -28754,7 +28754,7 @@
         <v>1530</v>
       </c>
       <c r="E594">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F594" t="s">
         <v>1537</v>
@@ -28789,7 +28789,7 @@
         <v>1530</v>
       </c>
       <c r="E595">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F595" t="s">
         <v>1537</v>
@@ -28824,7 +28824,7 @@
         <v>1530</v>
       </c>
       <c r="E596">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F596" t="s">
         <v>1537</v>
@@ -28859,7 +28859,7 @@
         <v>1530</v>
       </c>
       <c r="E597">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F597" t="s">
         <v>1537</v>
@@ -28894,7 +28894,7 @@
         <v>1530</v>
       </c>
       <c r="E598">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F598" t="s">
         <v>1537</v>
@@ -28929,7 +28929,7 @@
         <v>1530</v>
       </c>
       <c r="E599">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F599" t="s">
         <v>1539</v>
@@ -28967,7 +28967,7 @@
         <v>1530</v>
       </c>
       <c r="E600">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F600" t="s">
         <v>1539</v>
@@ -29005,7 +29005,7 @@
         <v>1531</v>
       </c>
       <c r="E601">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F601" t="s">
         <v>1539</v>
@@ -29043,7 +29043,7 @@
         <v>1531</v>
       </c>
       <c r="E602">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F602" t="s">
         <v>1539</v>
@@ -29078,7 +29078,7 @@
         <v>1531</v>
       </c>
       <c r="E603">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F603" t="s">
         <v>1537</v>
@@ -29113,7 +29113,7 @@
         <v>1531</v>
       </c>
       <c r="E604">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F604" t="s">
         <v>1537</v>
@@ -29148,7 +29148,7 @@
         <v>1531</v>
       </c>
       <c r="E605">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F605" t="s">
         <v>1537</v>
@@ -29183,7 +29183,7 @@
         <v>1531</v>
       </c>
       <c r="E606">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F606" t="s">
         <v>1537</v>
@@ -29218,7 +29218,7 @@
         <v>1531</v>
       </c>
       <c r="E607">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F607" t="s">
         <v>1539</v>
@@ -29256,7 +29256,7 @@
         <v>1532</v>
       </c>
       <c r="E608">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F608" t="s">
         <v>1537</v>
@@ -29291,7 +29291,7 @@
         <v>1532</v>
       </c>
       <c r="E609">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F609" t="s">
         <v>1537</v>
@@ -29326,7 +29326,7 @@
         <v>1532</v>
       </c>
       <c r="E610">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F610" t="s">
         <v>1537</v>
@@ -29361,7 +29361,7 @@
         <v>1532</v>
       </c>
       <c r="E611">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F611" t="s">
         <v>1537</v>
@@ -29396,7 +29396,7 @@
         <v>1532</v>
       </c>
       <c r="E612">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F612" t="s">
         <v>1537</v>
@@ -29431,7 +29431,7 @@
         <v>1532</v>
       </c>
       <c r="E613">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F613" t="s">
         <v>1537</v>
@@ -29466,7 +29466,7 @@
         <v>1532</v>
       </c>
       <c r="E614">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F614" t="s">
         <v>1537</v>
@@ -29501,7 +29501,7 @@
         <v>1533</v>
       </c>
       <c r="E615">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F615" t="s">
         <v>1537</v>
@@ -29539,7 +29539,7 @@
         <v>1533</v>
       </c>
       <c r="E616">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F616" t="s">
         <v>1537</v>
@@ -29574,7 +29574,7 @@
         <v>1533</v>
       </c>
       <c r="E617">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F617" t="s">
         <v>1537</v>
@@ -29609,7 +29609,7 @@
         <v>1533</v>
       </c>
       <c r="E618">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F618" t="s">
         <v>1537</v>
@@ -29647,7 +29647,7 @@
         <v>1533</v>
       </c>
       <c r="E619">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F619" t="s">
         <v>1537</v>
@@ -29682,7 +29682,7 @@
         <v>1534</v>
       </c>
       <c r="E620">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F620" t="s">
         <v>1537</v>
@@ -29717,7 +29717,7 @@
         <v>1535</v>
       </c>
       <c r="E621">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F621" t="s">
         <v>1537</v>
@@ -29752,7 +29752,7 @@
         <v>1535</v>
       </c>
       <c r="E622">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F622" t="s">
         <v>1537</v>
@@ -29787,7 +29787,7 @@
         <v>1535</v>
       </c>
       <c r="E623">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F623" t="s">
         <v>1537</v>
@@ -29822,7 +29822,7 @@
         <v>1535</v>
       </c>
       <c r="E624">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F624" t="s">
         <v>1537</v>
@@ -29860,7 +29860,7 @@
         <v>1535</v>
       </c>
       <c r="E625">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F625" t="s">
         <v>1537</v>
@@ -29895,7 +29895,7 @@
         <v>1535</v>
       </c>
       <c r="E626">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F626" t="s">
         <v>1537</v>
@@ -29930,7 +29930,7 @@
         <v>1535</v>
       </c>
       <c r="E627">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F627" t="s">
         <v>1537</v>
@@ -29965,7 +29965,7 @@
         <v>1535</v>
       </c>
       <c r="E628">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F628" t="s">
         <v>1537</v>
@@ -30000,7 +30000,7 @@
         <v>1535</v>
       </c>
       <c r="E629">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F629" t="s">
         <v>1537</v>
@@ -30035,7 +30035,7 @@
         <v>1535</v>
       </c>
       <c r="E630">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F630" t="s">
         <v>1537</v>
@@ -30070,7 +30070,7 @@
         <v>1535</v>
       </c>
       <c r="E631">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F631" t="s">
         <v>1537</v>
@@ -30108,7 +30108,7 @@
         <v>1535</v>
       </c>
       <c r="E632">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F632" t="s">
         <v>1537</v>
@@ -30143,7 +30143,7 @@
         <v>1535</v>
       </c>
       <c r="E633">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F633" t="s">
         <v>1537</v>
@@ -30178,7 +30178,7 @@
         <v>1535</v>
       </c>
       <c r="E634">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F634" t="s">
         <v>1541</v>
@@ -30213,7 +30213,7 @@
         <v>1535</v>
       </c>
       <c r="E635">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F635" t="s">
         <v>1537</v>
@@ -30251,7 +30251,7 @@
         <v>1536</v>
       </c>
       <c r="E636">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F636" t="s">
         <v>1537</v>
@@ -30286,7 +30286,7 @@
         <v>1536</v>
       </c>
       <c r="E637">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F637" t="s">
         <v>1537</v>
@@ -30321,7 +30321,7 @@
         <v>1536</v>
       </c>
       <c r="E638">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F638" t="s">
         <v>1537</v>
@@ -30359,7 +30359,7 @@
         <v>1536</v>
       </c>
       <c r="E639">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F639" t="s">
         <v>1537</v>
@@ -30394,7 +30394,7 @@
         <v>1536</v>
       </c>
       <c r="E640">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F640" t="s">
         <v>1539</v>
@@ -30432,7 +30432,7 @@
         <v>1536</v>
       </c>
       <c r="E641">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F641" t="s">
         <v>1539</v>
@@ -30470,7 +30470,7 @@
         <v>1536</v>
       </c>
       <c r="E642">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F642" t="s">
         <v>1537</v>
@@ -30508,7 +30508,7 @@
         <v>1536</v>
       </c>
       <c r="E643">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F643" t="s">
         <v>1537</v>

--- a/BacklogGATEAutoCompleto.xlsx
+++ b/BacklogGATEAutoCompleto.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6490" uniqueCount="2509">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6490" uniqueCount="2512">
   <si>
     <t>NUCLEO</t>
   </si>
@@ -7498,49 +7498,58 @@
     <t>###   SEM TEMA   ###</t>
   </si>
   <si>
+    <t>ECONOMICIDADE OBRAS,ECONOMICIDADE CONTÁBIL</t>
+  </si>
+  <si>
+    <t>AVALIAÇÃO DE IMÓVEIS,GEOLOGIA</t>
+  </si>
+  <si>
+    <t>ENGENHARIA CIVIL,FENOMENOS DE ENERGIA E INFORMAÇÃO</t>
+  </si>
+  <si>
+    <t>ENGENHARIA CIVIL,ENGENHARIA QUÍMICA,FENOMENOS DE ENERGIA E INFORMAÇÃO</t>
+  </si>
+  <si>
+    <t>AVALIAÇÃO DE IMÓVEIS,ECONOMICIDADE OBRAS</t>
+  </si>
+  <si>
+    <t>ENGENHARIA FLORESTAL,URBANISMO</t>
+  </si>
+  <si>
+    <t>FARMÁCIA,SAÚDE</t>
+  </si>
+  <si>
+    <t>URBANISMO,BIOLOGIA</t>
+  </si>
+  <si>
+    <t>ENGENHARIA AMBIENTAL,BIOLOGIA</t>
+  </si>
+  <si>
     <t>ECONOMICIDADE CONTÁBIL,ECONOMICIDADE OBRAS</t>
   </si>
   <si>
-    <t>AVALIAÇÃO DE IMÓVEIS,GEOLOGIA</t>
-  </si>
-  <si>
-    <t>ENGENHARIA CIVIL,FENOMENOS DE ENERGIA E INFORMAÇÃO</t>
-  </si>
-  <si>
-    <t>ENGENHARIA CIVIL,ENGENHARIA QUÍMICA,FENOMENOS DE ENERGIA E INFORMAÇÃO</t>
-  </si>
-  <si>
-    <t>AVALIAÇÃO DE IMÓVEIS,ECONOMICIDADE OBRAS</t>
-  </si>
-  <si>
-    <t>ENGENHARIA FLORESTAL,URBANISMO</t>
-  </si>
-  <si>
-    <t>FARMÁCIA,SAÚDE</t>
-  </si>
-  <si>
-    <t>URBANISMO,BIOLOGIA</t>
+    <t>BIOLOGIA,GEOLOGIA</t>
+  </si>
+  <si>
+    <t>URBANISMO,MOBILIDADE E TRANSPORTE,RECURSOS HÍDRICOS,BIOLOGIA</t>
+  </si>
+  <si>
+    <t>ENGENHARIA QUÍMICA,RESÍDUOS SÓLIDOS</t>
   </si>
   <si>
     <t>BIOLOGIA,ENGENHARIA AMBIENTAL</t>
   </si>
   <si>
-    <t>BIOLOGIA,GEOLOGIA</t>
-  </si>
-  <si>
-    <t>BIOLOGIA,URBANISMO,MOBILIDADE E TRANSPORTE,RECURSOS HÍDRICOS</t>
-  </si>
-  <si>
-    <t>ENGENHARIA QUÍMICA,RESÍDUOS SÓLIDOS</t>
-  </si>
-  <si>
-    <t>ENGENHARIA AMBIENTAL,BIOLOGIA</t>
-  </si>
-  <si>
     <t>ENGENHARIA CIVIL,MOBILIDADE E TRANSPORTE</t>
   </si>
   <si>
-    <t>ECONOMICIDADE CONTÁBIL,ASSISTÊNCIA SOCIAL,SAÚDE,URBANISMO,AVALIAÇÃO DE IMÓVEIS,PSICOLOGIA,MOBILIDADE E TRANSPORTE,ECONOMIA,SAÚDE MENTAL,ORÇAMENTO</t>
+    <t>ENGENHARIA FLORESTAL,BIOLOGIA</t>
+  </si>
+  <si>
+    <t>GEOTECNIA,ENGENHARIA CIVIL</t>
+  </si>
+  <si>
+    <t>PSICOLOGIA,URBANISMO,ASSISTÊNCIA SOCIAL,SAÚDE,MOBILIDADE E TRANSPORTE,ORÇAMENTO,AVALIAÇÃO DE IMÓVEIS,SAÚDE MENTAL,ECONOMIA,ECONOMICIDADE CONTÁBIL</t>
   </si>
 </sst>
 </file>
@@ -15755,7 +15764,7 @@
     </row>
     <row r="225" spans="1:12">
       <c r="A225" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="B225" t="s">
         <v>264</v>
@@ -15776,7 +15785,7 @@
         <v>1542</v>
       </c>
       <c r="I225" t="s">
-        <v>1632</v>
+        <v>1574</v>
       </c>
       <c r="J225" t="s">
         <v>1903</v>
@@ -16318,7 +16327,7 @@
     </row>
     <row r="241" spans="1:12">
       <c r="A241" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="B241" t="s">
         <v>280</v>
@@ -16342,7 +16351,7 @@
         <v>1547</v>
       </c>
       <c r="I241" t="s">
-        <v>1632</v>
+        <v>1574</v>
       </c>
       <c r="J241" t="s">
         <v>1919</v>
@@ -26779,7 +26788,7 @@
         <v>2348</v>
       </c>
       <c r="L538" t="s">
-        <v>2494</v>
+        <v>2503</v>
       </c>
     </row>
     <row r="539" spans="1:12">
@@ -27634,7 +27643,7 @@
         <v>2352</v>
       </c>
       <c r="L562" t="s">
-        <v>2503</v>
+        <v>2504</v>
       </c>
     </row>
     <row r="563" spans="1:12">
@@ -27914,7 +27923,7 @@
         <v>2319</v>
       </c>
       <c r="L570" t="s">
-        <v>2504</v>
+        <v>2505</v>
       </c>
     </row>
     <row r="571" spans="1:12">
@@ -28197,7 +28206,7 @@
         <v>2314</v>
       </c>
       <c r="L578" t="s">
-        <v>2505</v>
+        <v>2506</v>
       </c>
     </row>
     <row r="579" spans="1:12">
@@ -29201,7 +29210,7 @@
         <v>2346</v>
       </c>
       <c r="L606" t="s">
-        <v>2506</v>
+        <v>2507</v>
       </c>
     </row>
     <row r="607" spans="1:12">
@@ -29309,7 +29318,7 @@
         <v>2424</v>
       </c>
       <c r="L609" t="s">
-        <v>2507</v>
+        <v>2508</v>
       </c>
     </row>
     <row r="610" spans="1:12">
@@ -29983,7 +29992,7 @@
         <v>2364</v>
       </c>
       <c r="L628" t="s">
-        <v>2493</v>
+        <v>2467</v>
       </c>
     </row>
     <row r="629" spans="1:12">
@@ -30453,7 +30462,7 @@
         <v>2314</v>
       </c>
       <c r="L641" t="s">
-        <v>2484</v>
+        <v>2509</v>
       </c>
     </row>
     <row r="642" spans="1:12">
@@ -30558,7 +30567,7 @@
         <v>2428</v>
       </c>
       <c r="L644" t="s">
-        <v>2447</v>
+        <v>2510</v>
       </c>
     </row>
     <row r="645" spans="1:12">
@@ -30590,7 +30599,7 @@
         <v>2428</v>
       </c>
       <c r="L645" t="s">
-        <v>2508</v>
+        <v>2511</v>
       </c>
     </row>
   </sheetData>

--- a/BacklogGATEAutoCompleto.xlsx
+++ b/BacklogGATEAutoCompleto.xlsx
@@ -7854,7 +7854,7 @@
         <v>1308</v>
       </c>
       <c r="E2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="F2" t="s">
         <v>1519</v>
@@ -7889,7 +7889,7 @@
         <v>1309</v>
       </c>
       <c r="E3">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="F3" t="s">
         <v>1519</v>
@@ -7924,7 +7924,7 @@
         <v>1310</v>
       </c>
       <c r="E4">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="F4" t="s">
         <v>1519</v>
@@ -7959,7 +7959,7 @@
         <v>1311</v>
       </c>
       <c r="E5">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="F5" t="s">
         <v>1519</v>
@@ -7994,7 +7994,7 @@
         <v>1312</v>
       </c>
       <c r="E6">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="F6" t="s">
         <v>1519</v>
@@ -8029,7 +8029,7 @@
         <v>1313</v>
       </c>
       <c r="E7">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="F7" t="s">
         <v>1519</v>
@@ -8064,7 +8064,7 @@
         <v>1314</v>
       </c>
       <c r="E8">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="F8" t="s">
         <v>1519</v>
@@ -8099,7 +8099,7 @@
         <v>1315</v>
       </c>
       <c r="E9">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="F9" t="s">
         <v>1519</v>
@@ -8134,7 +8134,7 @@
         <v>1315</v>
       </c>
       <c r="E10">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="F10" t="s">
         <v>1519</v>
@@ -8169,7 +8169,7 @@
         <v>1316</v>
       </c>
       <c r="E11">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="F11" t="s">
         <v>1519</v>
@@ -8204,7 +8204,7 @@
         <v>1317</v>
       </c>
       <c r="E12">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="F12" t="s">
         <v>1519</v>
@@ -8239,7 +8239,7 @@
         <v>1318</v>
       </c>
       <c r="E13">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F13" t="s">
         <v>1519</v>
@@ -8274,7 +8274,7 @@
         <v>1318</v>
       </c>
       <c r="E14">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F14" t="s">
         <v>1519</v>
@@ -8309,7 +8309,7 @@
         <v>1319</v>
       </c>
       <c r="E15">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="F15" t="s">
         <v>1519</v>
@@ -8344,7 +8344,7 @@
         <v>1319</v>
       </c>
       <c r="E16">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="F16" t="s">
         <v>1519</v>
@@ -8379,7 +8379,7 @@
         <v>1320</v>
       </c>
       <c r="E17">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="F17" t="s">
         <v>1519</v>
@@ -8414,7 +8414,7 @@
         <v>1321</v>
       </c>
       <c r="E18">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="F18" t="s">
         <v>1519</v>
@@ -8449,7 +8449,7 @@
         <v>1322</v>
       </c>
       <c r="E19">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F19" t="s">
         <v>1519</v>
@@ -8484,7 +8484,7 @@
         <v>1323</v>
       </c>
       <c r="E20">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="F20" t="s">
         <v>1519</v>
@@ -8519,7 +8519,7 @@
         <v>1324</v>
       </c>
       <c r="E21">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="F21" t="s">
         <v>1519</v>
@@ -8557,7 +8557,7 @@
         <v>1325</v>
       </c>
       <c r="E22">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F22" t="s">
         <v>1519</v>
@@ -8592,7 +8592,7 @@
         <v>1326</v>
       </c>
       <c r="E23">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="F23" t="s">
         <v>1519</v>
@@ -8627,7 +8627,7 @@
         <v>1327</v>
       </c>
       <c r="E24">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F24" t="s">
         <v>1519</v>
@@ -8662,7 +8662,7 @@
         <v>1328</v>
       </c>
       <c r="E25">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="F25" t="s">
         <v>1519</v>
@@ -8697,7 +8697,7 @@
         <v>1329</v>
       </c>
       <c r="E26">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="F26" t="s">
         <v>1519</v>
@@ -8732,7 +8732,7 @@
         <v>1330</v>
       </c>
       <c r="E27">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F27" t="s">
         <v>1519</v>
@@ -8767,7 +8767,7 @@
         <v>1331</v>
       </c>
       <c r="E28">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F28" t="s">
         <v>1519</v>
@@ -8802,7 +8802,7 @@
         <v>1332</v>
       </c>
       <c r="E29">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F29" t="s">
         <v>1519</v>
@@ -8837,7 +8837,7 @@
         <v>1333</v>
       </c>
       <c r="E30">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F30" t="s">
         <v>1519</v>
@@ -8872,7 +8872,7 @@
         <v>1334</v>
       </c>
       <c r="E31">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F31" t="s">
         <v>1519</v>
@@ -8907,7 +8907,7 @@
         <v>1335</v>
       </c>
       <c r="E32">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F32" t="s">
         <v>1519</v>
@@ -8942,7 +8942,7 @@
         <v>1336</v>
       </c>
       <c r="E33">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F33" t="s">
         <v>1519</v>
@@ -8977,7 +8977,7 @@
         <v>1337</v>
       </c>
       <c r="E34">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F34" t="s">
         <v>1519</v>
@@ -9012,7 +9012,7 @@
         <v>1337</v>
       </c>
       <c r="E35">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F35" t="s">
         <v>1519</v>
@@ -9047,7 +9047,7 @@
         <v>1338</v>
       </c>
       <c r="E36">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F36" t="s">
         <v>1519</v>
@@ -9082,7 +9082,7 @@
         <v>1339</v>
       </c>
       <c r="E37">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F37" t="s">
         <v>1519</v>
@@ -9117,7 +9117,7 @@
         <v>1339</v>
       </c>
       <c r="E38">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F38" t="s">
         <v>1519</v>
@@ -9152,7 +9152,7 @@
         <v>1340</v>
       </c>
       <c r="E39">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F39" t="s">
         <v>1519</v>
@@ -9187,7 +9187,7 @@
         <v>1340</v>
       </c>
       <c r="E40">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F40" t="s">
         <v>1519</v>
@@ -9222,7 +9222,7 @@
         <v>1341</v>
       </c>
       <c r="E41">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F41" t="s">
         <v>1519</v>
@@ -9257,7 +9257,7 @@
         <v>1342</v>
       </c>
       <c r="E42">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F42" t="s">
         <v>1519</v>
@@ -9292,7 +9292,7 @@
         <v>1343</v>
       </c>
       <c r="E43">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F43" t="s">
         <v>1519</v>
@@ -9327,7 +9327,7 @@
         <v>1344</v>
       </c>
       <c r="E44">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F44" t="s">
         <v>1519</v>
@@ -9362,7 +9362,7 @@
         <v>1345</v>
       </c>
       <c r="E45">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F45" t="s">
         <v>1519</v>
@@ -9397,7 +9397,7 @@
         <v>1346</v>
       </c>
       <c r="E46">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F46" t="s">
         <v>1519</v>
@@ -9432,7 +9432,7 @@
         <v>1347</v>
       </c>
       <c r="E47">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F47" t="s">
         <v>1519</v>
@@ -9467,7 +9467,7 @@
         <v>1348</v>
       </c>
       <c r="E48">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F48" t="s">
         <v>1519</v>
@@ -9502,7 +9502,7 @@
         <v>1349</v>
       </c>
       <c r="E49">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F49" t="s">
         <v>1519</v>
@@ -9537,7 +9537,7 @@
         <v>1350</v>
       </c>
       <c r="E50">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F50" t="s">
         <v>1519</v>
@@ -9572,7 +9572,7 @@
         <v>1351</v>
       </c>
       <c r="E51">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F51" t="s">
         <v>1519</v>
@@ -9607,7 +9607,7 @@
         <v>1351</v>
       </c>
       <c r="E52">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F52" t="s">
         <v>1519</v>
@@ -9642,7 +9642,7 @@
         <v>1351</v>
       </c>
       <c r="E53">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F53" t="s">
         <v>1519</v>
@@ -9677,7 +9677,7 @@
         <v>1352</v>
       </c>
       <c r="E54">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F54" t="s">
         <v>1519</v>
@@ -9712,7 +9712,7 @@
         <v>1353</v>
       </c>
       <c r="E55">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F55" t="s">
         <v>1519</v>
@@ -9747,7 +9747,7 @@
         <v>1354</v>
       </c>
       <c r="E56">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F56" t="s">
         <v>1519</v>
@@ -9782,7 +9782,7 @@
         <v>1355</v>
       </c>
       <c r="E57">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F57" t="s">
         <v>1519</v>
@@ -9817,7 +9817,7 @@
         <v>1356</v>
       </c>
       <c r="E58">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F58" t="s">
         <v>1519</v>
@@ -9852,7 +9852,7 @@
         <v>1356</v>
       </c>
       <c r="E59">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F59" t="s">
         <v>1519</v>
@@ -9887,7 +9887,7 @@
         <v>1357</v>
       </c>
       <c r="E60">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F60" t="s">
         <v>1519</v>
@@ -9922,7 +9922,7 @@
         <v>1358</v>
       </c>
       <c r="E61">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F61" t="s">
         <v>1519</v>
@@ -9957,7 +9957,7 @@
         <v>1358</v>
       </c>
       <c r="E62">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F62" t="s">
         <v>1519</v>
@@ -9992,7 +9992,7 @@
         <v>1358</v>
       </c>
       <c r="E63">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F63" t="s">
         <v>1520</v>
@@ -10027,7 +10027,7 @@
         <v>1358</v>
       </c>
       <c r="E64">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F64" t="s">
         <v>1519</v>
@@ -10062,7 +10062,7 @@
         <v>1359</v>
       </c>
       <c r="E65">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F65" t="s">
         <v>1519</v>
@@ -10097,7 +10097,7 @@
         <v>1360</v>
       </c>
       <c r="E66">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F66" t="s">
         <v>1519</v>
@@ -10132,7 +10132,7 @@
         <v>1360</v>
       </c>
       <c r="E67">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F67" t="s">
         <v>1519</v>
@@ -10167,7 +10167,7 @@
         <v>1361</v>
       </c>
       <c r="E68">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F68" t="s">
         <v>1519</v>
@@ -10202,7 +10202,7 @@
         <v>1362</v>
       </c>
       <c r="E69">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F69" t="s">
         <v>1519</v>
@@ -10237,7 +10237,7 @@
         <v>1363</v>
       </c>
       <c r="E70">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F70" t="s">
         <v>1519</v>
@@ -10272,7 +10272,7 @@
         <v>1364</v>
       </c>
       <c r="E71">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F71" t="s">
         <v>1519</v>
@@ -10307,7 +10307,7 @@
         <v>1364</v>
       </c>
       <c r="E72">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F72" t="s">
         <v>1519</v>
@@ -10342,7 +10342,7 @@
         <v>1364</v>
       </c>
       <c r="E73">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F73" t="s">
         <v>1519</v>
@@ -10377,7 +10377,7 @@
         <v>1364</v>
       </c>
       <c r="E74">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F74" t="s">
         <v>1519</v>
@@ -10412,7 +10412,7 @@
         <v>1364</v>
       </c>
       <c r="E75">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F75" t="s">
         <v>1519</v>
@@ -10447,7 +10447,7 @@
         <v>1364</v>
       </c>
       <c r="E76">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F76" t="s">
         <v>1519</v>
@@ -10482,7 +10482,7 @@
         <v>1365</v>
       </c>
       <c r="E77">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F77" t="s">
         <v>1519</v>
@@ -10517,7 +10517,7 @@
         <v>1366</v>
       </c>
       <c r="E78">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F78" t="s">
         <v>1519</v>
@@ -10552,7 +10552,7 @@
         <v>1367</v>
       </c>
       <c r="E79">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F79" t="s">
         <v>1519</v>
@@ -10587,7 +10587,7 @@
         <v>1367</v>
       </c>
       <c r="E80">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F80" t="s">
         <v>1519</v>
@@ -10622,7 +10622,7 @@
         <v>1368</v>
       </c>
       <c r="E81">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F81" t="s">
         <v>1521</v>
@@ -10657,7 +10657,7 @@
         <v>1369</v>
       </c>
       <c r="E82">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F82" t="s">
         <v>1519</v>
@@ -10692,7 +10692,7 @@
         <v>1370</v>
       </c>
       <c r="E83">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F83" t="s">
         <v>1519</v>
@@ -10727,7 +10727,7 @@
         <v>1370</v>
       </c>
       <c r="E84">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F84" t="s">
         <v>1519</v>
@@ -10762,7 +10762,7 @@
         <v>1371</v>
       </c>
       <c r="E85">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F85" t="s">
         <v>1519</v>
@@ -10797,7 +10797,7 @@
         <v>1372</v>
       </c>
       <c r="E86">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F86" t="s">
         <v>1519</v>
@@ -10832,7 +10832,7 @@
         <v>1373</v>
       </c>
       <c r="E87">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F87" t="s">
         <v>1519</v>
@@ -10867,7 +10867,7 @@
         <v>1374</v>
       </c>
       <c r="E88">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F88" t="s">
         <v>1519</v>
@@ -10902,7 +10902,7 @@
         <v>1375</v>
       </c>
       <c r="E89">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F89" t="s">
         <v>1519</v>
@@ -10937,7 +10937,7 @@
         <v>1375</v>
       </c>
       <c r="E90">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F90" t="s">
         <v>1519</v>
@@ -10972,7 +10972,7 @@
         <v>1376</v>
       </c>
       <c r="E91">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F91" t="s">
         <v>1519</v>
@@ -11007,7 +11007,7 @@
         <v>1376</v>
       </c>
       <c r="E92">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F92" t="s">
         <v>1519</v>
@@ -11042,7 +11042,7 @@
         <v>1376</v>
       </c>
       <c r="E93">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F93" t="s">
         <v>1519</v>
@@ -11077,7 +11077,7 @@
         <v>1377</v>
       </c>
       <c r="E94">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F94" t="s">
         <v>1519</v>
@@ -11112,7 +11112,7 @@
         <v>1377</v>
       </c>
       <c r="E95">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F95" t="s">
         <v>1519</v>
@@ -11147,7 +11147,7 @@
         <v>1378</v>
       </c>
       <c r="E96">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F96" t="s">
         <v>1519</v>
@@ -11182,7 +11182,7 @@
         <v>1379</v>
       </c>
       <c r="E97">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F97" t="s">
         <v>1519</v>
@@ -11217,7 +11217,7 @@
         <v>1380</v>
       </c>
       <c r="E98">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F98" t="s">
         <v>1519</v>
@@ -11252,7 +11252,7 @@
         <v>1380</v>
       </c>
       <c r="E99">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F99" t="s">
         <v>1519</v>
@@ -11287,7 +11287,7 @@
         <v>1381</v>
       </c>
       <c r="E100">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F100" t="s">
         <v>1519</v>
@@ -11322,7 +11322,7 @@
         <v>1381</v>
       </c>
       <c r="E101">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F101" t="s">
         <v>1519</v>
@@ -11357,7 +11357,7 @@
         <v>1382</v>
       </c>
       <c r="E102">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F102" t="s">
         <v>1519</v>
@@ -11392,7 +11392,7 @@
         <v>1383</v>
       </c>
       <c r="E103">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F103" t="s">
         <v>1519</v>
@@ -11427,7 +11427,7 @@
         <v>1383</v>
       </c>
       <c r="E104">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F104" t="s">
         <v>1519</v>
@@ -11462,7 +11462,7 @@
         <v>1384</v>
       </c>
       <c r="E105">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F105" t="s">
         <v>1519</v>
@@ -11497,7 +11497,7 @@
         <v>1385</v>
       </c>
       <c r="E106">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F106" t="s">
         <v>1519</v>
@@ -11532,7 +11532,7 @@
         <v>1385</v>
       </c>
       <c r="E107">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F107" t="s">
         <v>1519</v>
@@ -11567,7 +11567,7 @@
         <v>1386</v>
       </c>
       <c r="E108">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F108" t="s">
         <v>1519</v>
@@ -11602,7 +11602,7 @@
         <v>1387</v>
       </c>
       <c r="E109">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F109" t="s">
         <v>1519</v>
@@ -11640,7 +11640,7 @@
         <v>1387</v>
       </c>
       <c r="E110">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F110" t="s">
         <v>1519</v>
@@ -11675,7 +11675,7 @@
         <v>1387</v>
       </c>
       <c r="E111">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F111" t="s">
         <v>1519</v>
@@ -11710,7 +11710,7 @@
         <v>1387</v>
       </c>
       <c r="E112">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F112" t="s">
         <v>1519</v>
@@ -11745,7 +11745,7 @@
         <v>1388</v>
       </c>
       <c r="E113">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F113" t="s">
         <v>1520</v>
@@ -11780,7 +11780,7 @@
         <v>1389</v>
       </c>
       <c r="E114">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F114" t="s">
         <v>1519</v>
@@ -11815,7 +11815,7 @@
         <v>1389</v>
       </c>
       <c r="E115">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F115" t="s">
         <v>1519</v>
@@ -11850,7 +11850,7 @@
         <v>1389</v>
       </c>
       <c r="E116">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F116" t="s">
         <v>1519</v>
@@ -11885,7 +11885,7 @@
         <v>1389</v>
       </c>
       <c r="E117">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F117" t="s">
         <v>1519</v>
@@ -11920,7 +11920,7 @@
         <v>1390</v>
       </c>
       <c r="E118">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F118" t="s">
         <v>1519</v>
@@ -11955,7 +11955,7 @@
         <v>1390</v>
       </c>
       <c r="E119">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F119" t="s">
         <v>1519</v>
@@ -11990,7 +11990,7 @@
         <v>1390</v>
       </c>
       <c r="E120">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F120" t="s">
         <v>1519</v>
@@ -12025,7 +12025,7 @@
         <v>1390</v>
       </c>
       <c r="E121">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F121" t="s">
         <v>1519</v>
@@ -12060,7 +12060,7 @@
         <v>1390</v>
       </c>
       <c r="E122">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F122" t="s">
         <v>1519</v>
@@ -12095,7 +12095,7 @@
         <v>1390</v>
       </c>
       <c r="E123">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F123" t="s">
         <v>1519</v>
@@ -12130,7 +12130,7 @@
         <v>1390</v>
       </c>
       <c r="E124">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F124" t="s">
         <v>1519</v>
@@ -12165,7 +12165,7 @@
         <v>1391</v>
       </c>
       <c r="E125">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F125" t="s">
         <v>1519</v>
@@ -12200,7 +12200,7 @@
         <v>1392</v>
       </c>
       <c r="E126">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F126" t="s">
         <v>1519</v>
@@ -12235,7 +12235,7 @@
         <v>1393</v>
       </c>
       <c r="E127">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F127" t="s">
         <v>1519</v>
@@ -12270,7 +12270,7 @@
         <v>1393</v>
       </c>
       <c r="E128">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F128" t="s">
         <v>1519</v>
@@ -12305,7 +12305,7 @@
         <v>1393</v>
       </c>
       <c r="E129">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F129" t="s">
         <v>1519</v>
@@ -12340,7 +12340,7 @@
         <v>1394</v>
       </c>
       <c r="E130">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F130" t="s">
         <v>1519</v>
@@ -12375,7 +12375,7 @@
         <v>1394</v>
       </c>
       <c r="E131">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F131" t="s">
         <v>1519</v>
@@ -12410,7 +12410,7 @@
         <v>1394</v>
       </c>
       <c r="E132">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F132" t="s">
         <v>1519</v>
@@ -12445,7 +12445,7 @@
         <v>1394</v>
       </c>
       <c r="E133">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F133" t="s">
         <v>1519</v>
@@ -12480,7 +12480,7 @@
         <v>1394</v>
       </c>
       <c r="E134">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F134" t="s">
         <v>1519</v>
@@ -12515,7 +12515,7 @@
         <v>1394</v>
       </c>
       <c r="E135">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F135" t="s">
         <v>1519</v>
@@ -12550,7 +12550,7 @@
         <v>1394</v>
       </c>
       <c r="E136">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F136" t="s">
         <v>1519</v>
@@ -12585,7 +12585,7 @@
         <v>1394</v>
       </c>
       <c r="E137">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F137" t="s">
         <v>1519</v>
@@ -12620,7 +12620,7 @@
         <v>1394</v>
       </c>
       <c r="E138">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F138" t="s">
         <v>1519</v>
@@ -12655,7 +12655,7 @@
         <v>1395</v>
       </c>
       <c r="E139">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F139" t="s">
         <v>1519</v>
@@ -12690,7 +12690,7 @@
         <v>1395</v>
       </c>
       <c r="E140">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F140" t="s">
         <v>1519</v>
@@ -12725,7 +12725,7 @@
         <v>1395</v>
       </c>
       <c r="E141">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F141" t="s">
         <v>1519</v>
@@ -12760,7 +12760,7 @@
         <v>1396</v>
       </c>
       <c r="E142">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F142" t="s">
         <v>1519</v>
@@ -12795,7 +12795,7 @@
         <v>1396</v>
       </c>
       <c r="E143">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F143" t="s">
         <v>1520</v>
@@ -12830,7 +12830,7 @@
         <v>1396</v>
       </c>
       <c r="E144">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F144" t="s">
         <v>1519</v>
@@ -12865,7 +12865,7 @@
         <v>1397</v>
       </c>
       <c r="E145">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F145" t="s">
         <v>1519</v>
@@ -12900,7 +12900,7 @@
         <v>1397</v>
       </c>
       <c r="E146">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F146" t="s">
         <v>1519</v>
@@ -12935,7 +12935,7 @@
         <v>1398</v>
       </c>
       <c r="E147">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F147" t="s">
         <v>1519</v>
@@ -12970,7 +12970,7 @@
         <v>1398</v>
       </c>
       <c r="E148">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F148" t="s">
         <v>1519</v>
@@ -13005,7 +13005,7 @@
         <v>1399</v>
       </c>
       <c r="E149">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F149" t="s">
         <v>1519</v>
@@ -13040,7 +13040,7 @@
         <v>1399</v>
       </c>
       <c r="E150">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F150" t="s">
         <v>1519</v>
@@ -13075,7 +13075,7 @@
         <v>1400</v>
       </c>
       <c r="E151">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F151" t="s">
         <v>1519</v>
@@ -13110,7 +13110,7 @@
         <v>1400</v>
       </c>
       <c r="E152">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F152" t="s">
         <v>1519</v>
@@ -13145,7 +13145,7 @@
         <v>1400</v>
       </c>
       <c r="E153">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F153" t="s">
         <v>1519</v>
@@ -13180,7 +13180,7 @@
         <v>1401</v>
       </c>
       <c r="E154">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F154" t="s">
         <v>1519</v>
@@ -13215,7 +13215,7 @@
         <v>1401</v>
       </c>
       <c r="E155">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F155" t="s">
         <v>1519</v>
@@ -13250,7 +13250,7 @@
         <v>1402</v>
       </c>
       <c r="E156">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F156" t="s">
         <v>1519</v>
@@ -13285,7 +13285,7 @@
         <v>1403</v>
       </c>
       <c r="E157">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F157" t="s">
         <v>1519</v>
@@ -13320,7 +13320,7 @@
         <v>1403</v>
       </c>
       <c r="E158">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F158" t="s">
         <v>1519</v>
@@ -13355,7 +13355,7 @@
         <v>1403</v>
       </c>
       <c r="E159">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F159" t="s">
         <v>1519</v>
@@ -13390,7 +13390,7 @@
         <v>1403</v>
       </c>
       <c r="E160">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F160" t="s">
         <v>1519</v>
@@ -13425,7 +13425,7 @@
         <v>1404</v>
       </c>
       <c r="E161">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F161" t="s">
         <v>1519</v>
@@ -13460,7 +13460,7 @@
         <v>1405</v>
       </c>
       <c r="E162">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F162" t="s">
         <v>1519</v>
@@ -13495,7 +13495,7 @@
         <v>1405</v>
       </c>
       <c r="E163">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F163" t="s">
         <v>1519</v>
@@ -13530,7 +13530,7 @@
         <v>1405</v>
       </c>
       <c r="E164">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F164" t="s">
         <v>1519</v>
@@ -13565,7 +13565,7 @@
         <v>1405</v>
       </c>
       <c r="E165">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F165" t="s">
         <v>1519</v>
@@ -13600,7 +13600,7 @@
         <v>1405</v>
       </c>
       <c r="E166">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F166" t="s">
         <v>1519</v>
@@ -13635,7 +13635,7 @@
         <v>1406</v>
       </c>
       <c r="E167">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F167" t="s">
         <v>1519</v>
@@ -13670,7 +13670,7 @@
         <v>1406</v>
       </c>
       <c r="E168">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F168" t="s">
         <v>1519</v>
@@ -13705,7 +13705,7 @@
         <v>1406</v>
       </c>
       <c r="E169">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F169" t="s">
         <v>1519</v>
@@ -13740,7 +13740,7 @@
         <v>1406</v>
       </c>
       <c r="E170">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F170" t="s">
         <v>1519</v>
@@ -13775,7 +13775,7 @@
         <v>1406</v>
       </c>
       <c r="E171">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F171" t="s">
         <v>1519</v>
@@ -13810,7 +13810,7 @@
         <v>1406</v>
       </c>
       <c r="E172">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F172" t="s">
         <v>1519</v>
@@ -13845,7 +13845,7 @@
         <v>1407</v>
       </c>
       <c r="E173">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F173" t="s">
         <v>1519</v>
@@ -13880,7 +13880,7 @@
         <v>1407</v>
       </c>
       <c r="E174">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F174" t="s">
         <v>1519</v>
@@ -13915,7 +13915,7 @@
         <v>1407</v>
       </c>
       <c r="E175">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F175" t="s">
         <v>1519</v>
@@ -13950,7 +13950,7 @@
         <v>1408</v>
       </c>
       <c r="E176">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F176" t="s">
         <v>1519</v>
@@ -13985,7 +13985,7 @@
         <v>1408</v>
       </c>
       <c r="E177">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F177" t="s">
         <v>1519</v>
@@ -14020,7 +14020,7 @@
         <v>1409</v>
       </c>
       <c r="E178">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F178" t="s">
         <v>1519</v>
@@ -14055,7 +14055,7 @@
         <v>1410</v>
       </c>
       <c r="E179">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F179" t="s">
         <v>1519</v>
@@ -14090,7 +14090,7 @@
         <v>1410</v>
       </c>
       <c r="E180">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F180" t="s">
         <v>1519</v>
@@ -14125,7 +14125,7 @@
         <v>1411</v>
       </c>
       <c r="E181">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F181" t="s">
         <v>1519</v>
@@ -14160,7 +14160,7 @@
         <v>1412</v>
       </c>
       <c r="E182">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F182" t="s">
         <v>1519</v>
@@ -14195,7 +14195,7 @@
         <v>1412</v>
       </c>
       <c r="E183">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F183" t="s">
         <v>1519</v>
@@ -14230,7 +14230,7 @@
         <v>1413</v>
       </c>
       <c r="E184">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F184" t="s">
         <v>1519</v>
@@ -14265,7 +14265,7 @@
         <v>1413</v>
       </c>
       <c r="E185">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F185" t="s">
         <v>1519</v>
@@ -14300,7 +14300,7 @@
         <v>1414</v>
       </c>
       <c r="E186">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F186" t="s">
         <v>1519</v>
@@ -14335,7 +14335,7 @@
         <v>1414</v>
       </c>
       <c r="E187">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F187" t="s">
         <v>1519</v>
@@ -14370,7 +14370,7 @@
         <v>1414</v>
       </c>
       <c r="E188">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F188" t="s">
         <v>1519</v>
@@ -14405,7 +14405,7 @@
         <v>1415</v>
       </c>
       <c r="E189">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F189" t="s">
         <v>1519</v>
@@ -14440,7 +14440,7 @@
         <v>1415</v>
       </c>
       <c r="E190">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F190" t="s">
         <v>1519</v>
@@ -14475,7 +14475,7 @@
         <v>1416</v>
       </c>
       <c r="E191">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F191" t="s">
         <v>1519</v>
@@ -14510,7 +14510,7 @@
         <v>1417</v>
       </c>
       <c r="E192">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F192" t="s">
         <v>1519</v>
@@ -14545,7 +14545,7 @@
         <v>1417</v>
       </c>
       <c r="E193">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F193" t="s">
         <v>1519</v>
@@ -14580,7 +14580,7 @@
         <v>1417</v>
       </c>
       <c r="E194">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F194" t="s">
         <v>1519</v>
@@ -14615,7 +14615,7 @@
         <v>1418</v>
       </c>
       <c r="E195">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F195" t="s">
         <v>1519</v>
@@ -14650,7 +14650,7 @@
         <v>1418</v>
       </c>
       <c r="E196">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F196" t="s">
         <v>1519</v>
@@ -14685,7 +14685,7 @@
         <v>1419</v>
       </c>
       <c r="E197">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F197" t="s">
         <v>1519</v>
@@ -14720,7 +14720,7 @@
         <v>1419</v>
       </c>
       <c r="E198">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F198" t="s">
         <v>1521</v>
@@ -14755,7 +14755,7 @@
         <v>1419</v>
       </c>
       <c r="E199">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F199" t="s">
         <v>1519</v>
@@ -14790,7 +14790,7 @@
         <v>1420</v>
       </c>
       <c r="E200">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F200" t="s">
         <v>1519</v>
@@ -14825,7 +14825,7 @@
         <v>1420</v>
       </c>
       <c r="E201">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F201" t="s">
         <v>1519</v>
@@ -14863,7 +14863,7 @@
         <v>1420</v>
       </c>
       <c r="E202">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F202" t="s">
         <v>1519</v>
@@ -14898,7 +14898,7 @@
         <v>1420</v>
       </c>
       <c r="E203">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F203" t="s">
         <v>1519</v>
@@ -14933,7 +14933,7 @@
         <v>1420</v>
       </c>
       <c r="E204">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F204" t="s">
         <v>1519</v>
@@ -14968,7 +14968,7 @@
         <v>1420</v>
       </c>
       <c r="E205">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F205" t="s">
         <v>1519</v>
@@ -15003,7 +15003,7 @@
         <v>1421</v>
       </c>
       <c r="E206">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F206" t="s">
         <v>1519</v>
@@ -15038,7 +15038,7 @@
         <v>1421</v>
       </c>
       <c r="E207">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F207" t="s">
         <v>1519</v>
@@ -15073,7 +15073,7 @@
         <v>1421</v>
       </c>
       <c r="E208">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F208" t="s">
         <v>1519</v>
@@ -15108,7 +15108,7 @@
         <v>1422</v>
       </c>
       <c r="E209">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F209" t="s">
         <v>1519</v>
@@ -15143,7 +15143,7 @@
         <v>1422</v>
       </c>
       <c r="E210">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F210" t="s">
         <v>1519</v>
@@ -15178,7 +15178,7 @@
         <v>1422</v>
       </c>
       <c r="E211">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F211" t="s">
         <v>1519</v>
@@ -15213,7 +15213,7 @@
         <v>1423</v>
       </c>
       <c r="E212">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F212" t="s">
         <v>1519</v>
@@ -15248,7 +15248,7 @@
         <v>1423</v>
       </c>
       <c r="E213">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F213" t="s">
         <v>1519</v>
@@ -15283,7 +15283,7 @@
         <v>1423</v>
       </c>
       <c r="E214">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F214" t="s">
         <v>1519</v>
@@ -15318,7 +15318,7 @@
         <v>1424</v>
       </c>
       <c r="E215">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F215" t="s">
         <v>1519</v>
@@ -15353,7 +15353,7 @@
         <v>1424</v>
       </c>
       <c r="E216">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F216" t="s">
         <v>1519</v>
@@ -15388,7 +15388,7 @@
         <v>1424</v>
       </c>
       <c r="E217">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F217" t="s">
         <v>1519</v>
@@ -15423,7 +15423,7 @@
         <v>1424</v>
       </c>
       <c r="E218">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F218" t="s">
         <v>1519</v>
@@ -15458,7 +15458,7 @@
         <v>1424</v>
       </c>
       <c r="E219">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F219" t="s">
         <v>1519</v>
@@ -15493,7 +15493,7 @@
         <v>1425</v>
       </c>
       <c r="E220">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F220" t="s">
         <v>1519</v>
@@ -15528,7 +15528,7 @@
         <v>1426</v>
       </c>
       <c r="E221">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F221" t="s">
         <v>1519</v>
@@ -15563,7 +15563,7 @@
         <v>1426</v>
       </c>
       <c r="E222">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F222" t="s">
         <v>1522</v>
@@ -15598,7 +15598,7 @@
         <v>1426</v>
       </c>
       <c r="E223">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F223" t="s">
         <v>1519</v>
@@ -15633,7 +15633,7 @@
         <v>1426</v>
       </c>
       <c r="E224">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F224" t="s">
         <v>1519</v>
@@ -15668,7 +15668,7 @@
         <v>1426</v>
       </c>
       <c r="E225">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F225" t="s">
         <v>1519</v>
@@ -15703,7 +15703,7 @@
         <v>1427</v>
       </c>
       <c r="E226">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F226" t="s">
         <v>1519</v>
@@ -15738,7 +15738,7 @@
         <v>1427</v>
       </c>
       <c r="E227">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F227" t="s">
         <v>1519</v>
@@ -15773,7 +15773,7 @@
         <v>1427</v>
       </c>
       <c r="E228">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F228" t="s">
         <v>1519</v>
@@ -15808,7 +15808,7 @@
         <v>1427</v>
       </c>
       <c r="E229">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F229" t="s">
         <v>1519</v>
@@ -15843,7 +15843,7 @@
         <v>1428</v>
       </c>
       <c r="E230">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F230" t="s">
         <v>1519</v>
@@ -15878,7 +15878,7 @@
         <v>1429</v>
       </c>
       <c r="E231">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F231" t="s">
         <v>1519</v>
@@ -15916,7 +15916,7 @@
         <v>1430</v>
       </c>
       <c r="E232">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F232" t="s">
         <v>1519</v>
@@ -15951,7 +15951,7 @@
         <v>1430</v>
       </c>
       <c r="E233">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F233" t="s">
         <v>1519</v>
@@ -15986,7 +15986,7 @@
         <v>1430</v>
       </c>
       <c r="E234">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F234" t="s">
         <v>1519</v>
@@ -16021,7 +16021,7 @@
         <v>1430</v>
       </c>
       <c r="E235">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F235" t="s">
         <v>1519</v>
@@ -16056,7 +16056,7 @@
         <v>1431</v>
       </c>
       <c r="E236">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F236" t="s">
         <v>1519</v>
@@ -16091,7 +16091,7 @@
         <v>1431</v>
       </c>
       <c r="E237">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F237" t="s">
         <v>1519</v>
@@ -16126,7 +16126,7 @@
         <v>1432</v>
       </c>
       <c r="E238">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F238" t="s">
         <v>1519</v>
@@ -16161,7 +16161,7 @@
         <v>1432</v>
       </c>
       <c r="E239">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F239" t="s">
         <v>1519</v>
@@ -16196,7 +16196,7 @@
         <v>1433</v>
       </c>
       <c r="E240">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F240" t="s">
         <v>1519</v>
@@ -16231,7 +16231,7 @@
         <v>1433</v>
       </c>
       <c r="E241">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F241" t="s">
         <v>1519</v>
@@ -16266,7 +16266,7 @@
         <v>1433</v>
       </c>
       <c r="E242">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F242" t="s">
         <v>1519</v>
@@ -16301,7 +16301,7 @@
         <v>1434</v>
       </c>
       <c r="E243">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F243" t="s">
         <v>1519</v>
@@ -16336,7 +16336,7 @@
         <v>1434</v>
       </c>
       <c r="E244">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F244" t="s">
         <v>1519</v>
@@ -16371,7 +16371,7 @@
         <v>1434</v>
       </c>
       <c r="E245">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F245" t="s">
         <v>1519</v>
@@ -16406,7 +16406,7 @@
         <v>1435</v>
       </c>
       <c r="E246">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F246" t="s">
         <v>1519</v>
@@ -16441,7 +16441,7 @@
         <v>1436</v>
       </c>
       <c r="E247">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F247" t="s">
         <v>1519</v>
@@ -16476,7 +16476,7 @@
         <v>1436</v>
       </c>
       <c r="E248">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F248" t="s">
         <v>1519</v>
@@ -16511,7 +16511,7 @@
         <v>1436</v>
       </c>
       <c r="E249">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F249" t="s">
         <v>1519</v>
@@ -16546,7 +16546,7 @@
         <v>1436</v>
       </c>
       <c r="E250">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F250" t="s">
         <v>1519</v>
@@ -16581,7 +16581,7 @@
         <v>1437</v>
       </c>
       <c r="E251">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F251" t="s">
         <v>1519</v>
@@ -16616,7 +16616,7 @@
         <v>1437</v>
       </c>
       <c r="E252">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F252" t="s">
         <v>1519</v>
@@ -16651,7 +16651,7 @@
         <v>1437</v>
       </c>
       <c r="E253">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F253" t="s">
         <v>1519</v>
@@ -16686,7 +16686,7 @@
         <v>1438</v>
       </c>
       <c r="E254">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F254" t="s">
         <v>1519</v>
@@ -16721,7 +16721,7 @@
         <v>1438</v>
       </c>
       <c r="E255">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F255" t="s">
         <v>1519</v>
@@ -16756,7 +16756,7 @@
         <v>1439</v>
       </c>
       <c r="E256">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F256" t="s">
         <v>1519</v>
@@ -16791,7 +16791,7 @@
         <v>1439</v>
       </c>
       <c r="E257">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F257" t="s">
         <v>1519</v>
@@ -16826,7 +16826,7 @@
         <v>1439</v>
       </c>
       <c r="E258">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F258" t="s">
         <v>1519</v>
@@ -16861,7 +16861,7 @@
         <v>1439</v>
       </c>
       <c r="E259">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F259" t="s">
         <v>1519</v>
@@ -16896,7 +16896,7 @@
         <v>1439</v>
       </c>
       <c r="E260">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F260" t="s">
         <v>1519</v>
@@ -16931,7 +16931,7 @@
         <v>1440</v>
       </c>
       <c r="E261">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F261" t="s">
         <v>1519</v>
@@ -16966,7 +16966,7 @@
         <v>1440</v>
       </c>
       <c r="E262">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F262" t="s">
         <v>1519</v>
@@ -17001,7 +17001,7 @@
         <v>1440</v>
       </c>
       <c r="E263">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F263" t="s">
         <v>1519</v>
@@ -17036,7 +17036,7 @@
         <v>1441</v>
       </c>
       <c r="E264">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F264" t="s">
         <v>1519</v>
@@ -17071,7 +17071,7 @@
         <v>1442</v>
       </c>
       <c r="E265">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F265" t="s">
         <v>1519</v>
@@ -17106,7 +17106,7 @@
         <v>1443</v>
       </c>
       <c r="E266">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F266" t="s">
         <v>1519</v>
@@ -17141,7 +17141,7 @@
         <v>1443</v>
       </c>
       <c r="E267">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F267" t="s">
         <v>1519</v>
@@ -17176,7 +17176,7 @@
         <v>1443</v>
       </c>
       <c r="E268">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F268" t="s">
         <v>1519</v>
@@ -17211,7 +17211,7 @@
         <v>1443</v>
       </c>
       <c r="E269">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F269" t="s">
         <v>1519</v>
@@ -17246,7 +17246,7 @@
         <v>1443</v>
       </c>
       <c r="E270">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F270" t="s">
         <v>1519</v>
@@ -17281,7 +17281,7 @@
         <v>1444</v>
       </c>
       <c r="E271">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F271" t="s">
         <v>1519</v>
@@ -17316,7 +17316,7 @@
         <v>1444</v>
       </c>
       <c r="E272">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F272" t="s">
         <v>1519</v>
@@ -17351,7 +17351,7 @@
         <v>1445</v>
       </c>
       <c r="E273">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F273" t="s">
         <v>1519</v>
@@ -17386,7 +17386,7 @@
         <v>1445</v>
       </c>
       <c r="E274">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F274" t="s">
         <v>1519</v>
@@ -17421,7 +17421,7 @@
         <v>1446</v>
       </c>
       <c r="E275">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F275" t="s">
         <v>1519</v>
@@ -17456,7 +17456,7 @@
         <v>1447</v>
       </c>
       <c r="E276">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F276" t="s">
         <v>1519</v>
@@ -17491,7 +17491,7 @@
         <v>1448</v>
       </c>
       <c r="E277">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F277" t="s">
         <v>1519</v>
@@ -17526,7 +17526,7 @@
         <v>1448</v>
       </c>
       <c r="E278">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F278" t="s">
         <v>1519</v>
@@ -17561,7 +17561,7 @@
         <v>1449</v>
       </c>
       <c r="E279">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F279" t="s">
         <v>1519</v>
@@ -17596,7 +17596,7 @@
         <v>1449</v>
       </c>
       <c r="E280">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F280" t="s">
         <v>1519</v>
@@ -17631,7 +17631,7 @@
         <v>1449</v>
       </c>
       <c r="E281">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F281" t="s">
         <v>1519</v>
@@ -17666,7 +17666,7 @@
         <v>1450</v>
       </c>
       <c r="E282">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F282" t="s">
         <v>1519</v>
@@ -17701,7 +17701,7 @@
         <v>1450</v>
       </c>
       <c r="E283">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F283" t="s">
         <v>1519</v>
@@ -17736,7 +17736,7 @@
         <v>1450</v>
       </c>
       <c r="E284">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F284" t="s">
         <v>1519</v>
@@ -17771,7 +17771,7 @@
         <v>1450</v>
       </c>
       <c r="E285">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F285" t="s">
         <v>1519</v>
@@ -17806,7 +17806,7 @@
         <v>1450</v>
       </c>
       <c r="E286">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F286" t="s">
         <v>1519</v>
@@ -17841,7 +17841,7 @@
         <v>1450</v>
       </c>
       <c r="E287">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F287" t="s">
         <v>1519</v>
@@ -17876,7 +17876,7 @@
         <v>1450</v>
       </c>
       <c r="E288">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F288" t="s">
         <v>1519</v>
@@ -17911,7 +17911,7 @@
         <v>1450</v>
       </c>
       <c r="E289">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F289" t="s">
         <v>1519</v>
@@ -17946,7 +17946,7 @@
         <v>1450</v>
       </c>
       <c r="E290">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F290" t="s">
         <v>1519</v>
@@ -17981,7 +17981,7 @@
         <v>1451</v>
       </c>
       <c r="E291">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F291" t="s">
         <v>1519</v>
@@ -18016,7 +18016,7 @@
         <v>1451</v>
       </c>
       <c r="E292">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F292" t="s">
         <v>1519</v>
@@ -18051,7 +18051,7 @@
         <v>1451</v>
       </c>
       <c r="E293">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F293" t="s">
         <v>1519</v>
@@ -18086,7 +18086,7 @@
         <v>1452</v>
       </c>
       <c r="E294">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F294" t="s">
         <v>1519</v>
@@ -18121,7 +18121,7 @@
         <v>1453</v>
       </c>
       <c r="E295">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F295" t="s">
         <v>1519</v>
@@ -18156,7 +18156,7 @@
         <v>1453</v>
       </c>
       <c r="E296">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F296" t="s">
         <v>1519</v>
@@ -18191,7 +18191,7 @@
         <v>1453</v>
       </c>
       <c r="E297">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F297" t="s">
         <v>1519</v>
@@ -18226,7 +18226,7 @@
         <v>1453</v>
       </c>
       <c r="E298">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F298" t="s">
         <v>1519</v>
@@ -18261,7 +18261,7 @@
         <v>1453</v>
       </c>
       <c r="E299">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F299" t="s">
         <v>1519</v>
@@ -18296,7 +18296,7 @@
         <v>1453</v>
       </c>
       <c r="E300">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F300" t="s">
         <v>1519</v>
@@ -18331,7 +18331,7 @@
         <v>1454</v>
       </c>
       <c r="E301">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F301" t="s">
         <v>1519</v>
@@ -18366,7 +18366,7 @@
         <v>1454</v>
       </c>
       <c r="E302">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F302" t="s">
         <v>1519</v>
@@ -18401,7 +18401,7 @@
         <v>1454</v>
       </c>
       <c r="E303">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F303" t="s">
         <v>1519</v>
@@ -18436,7 +18436,7 @@
         <v>1454</v>
       </c>
       <c r="E304">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F304" t="s">
         <v>1519</v>
@@ -18474,7 +18474,7 @@
         <v>1454</v>
       </c>
       <c r="E305">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F305" t="s">
         <v>1519</v>
@@ -18509,7 +18509,7 @@
         <v>1454</v>
       </c>
       <c r="E306">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F306" t="s">
         <v>1519</v>
@@ -18544,7 +18544,7 @@
         <v>1454</v>
       </c>
       <c r="E307">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F307" t="s">
         <v>1519</v>
@@ -18579,7 +18579,7 @@
         <v>1454</v>
       </c>
       <c r="E308">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F308" t="s">
         <v>1519</v>
@@ -18614,7 +18614,7 @@
         <v>1454</v>
       </c>
       <c r="E309">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F309" t="s">
         <v>1519</v>
@@ -18649,7 +18649,7 @@
         <v>1455</v>
       </c>
       <c r="E310">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F310" t="s">
         <v>1520</v>
@@ -18684,7 +18684,7 @@
         <v>1456</v>
       </c>
       <c r="E311">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F311" t="s">
         <v>1523</v>
@@ -18719,7 +18719,7 @@
         <v>1457</v>
       </c>
       <c r="E312">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F312" t="s">
         <v>1519</v>
@@ -18754,7 +18754,7 @@
         <v>1458</v>
       </c>
       <c r="E313">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F313" t="s">
         <v>1519</v>
@@ -18789,7 +18789,7 @@
         <v>1458</v>
       </c>
       <c r="E314">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F314" t="s">
         <v>1519</v>
@@ -18824,7 +18824,7 @@
         <v>1459</v>
       </c>
       <c r="E315">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F315" t="s">
         <v>1519</v>
@@ -18859,7 +18859,7 @@
         <v>1460</v>
       </c>
       <c r="E316">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F316" t="s">
         <v>1522</v>
@@ -18894,7 +18894,7 @@
         <v>1460</v>
       </c>
       <c r="E317">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F317" t="s">
         <v>1519</v>
@@ -18929,7 +18929,7 @@
         <v>1460</v>
       </c>
       <c r="E318">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F318" t="s">
         <v>1519</v>
@@ -18964,7 +18964,7 @@
         <v>1460</v>
       </c>
       <c r="E319">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F319" t="s">
         <v>1519</v>
@@ -18999,7 +18999,7 @@
         <v>1460</v>
       </c>
       <c r="E320">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F320" t="s">
         <v>1519</v>
@@ -19034,7 +19034,7 @@
         <v>1460</v>
       </c>
       <c r="E321">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F321" t="s">
         <v>1519</v>
@@ -19069,7 +19069,7 @@
         <v>1461</v>
       </c>
       <c r="E322">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F322" t="s">
         <v>1519</v>
@@ -19104,7 +19104,7 @@
         <v>1462</v>
       </c>
       <c r="E323">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F323" t="s">
         <v>1519</v>
@@ -19139,7 +19139,7 @@
         <v>1462</v>
       </c>
       <c r="E324">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F324" t="s">
         <v>1519</v>
@@ -19174,7 +19174,7 @@
         <v>1462</v>
       </c>
       <c r="E325">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F325" t="s">
         <v>1519</v>
@@ -19212,7 +19212,7 @@
         <v>1462</v>
       </c>
       <c r="E326">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F326" t="s">
         <v>1519</v>
@@ -19247,7 +19247,7 @@
         <v>1463</v>
       </c>
       <c r="E327">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F327" t="s">
         <v>1519</v>
@@ -19282,7 +19282,7 @@
         <v>1463</v>
       </c>
       <c r="E328">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F328" t="s">
         <v>1519</v>
@@ -19317,7 +19317,7 @@
         <v>1463</v>
       </c>
       <c r="E329">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F329" t="s">
         <v>1519</v>
@@ -19352,7 +19352,7 @@
         <v>1463</v>
       </c>
       <c r="E330">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F330" t="s">
         <v>1519</v>
@@ -19387,7 +19387,7 @@
         <v>1463</v>
       </c>
       <c r="E331">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F331" t="s">
         <v>1519</v>
@@ -19422,7 +19422,7 @@
         <v>1464</v>
       </c>
       <c r="E332">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F332" t="s">
         <v>1519</v>
@@ -19457,7 +19457,7 @@
         <v>1464</v>
       </c>
       <c r="E333">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F333" t="s">
         <v>1519</v>
@@ -19492,7 +19492,7 @@
         <v>1465</v>
       </c>
       <c r="E334">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F334" t="s">
         <v>1519</v>
@@ -19527,7 +19527,7 @@
         <v>1465</v>
       </c>
       <c r="E335">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F335" t="s">
         <v>1519</v>
@@ -19562,7 +19562,7 @@
         <v>1465</v>
       </c>
       <c r="E336">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F336" t="s">
         <v>1519</v>
@@ -19597,7 +19597,7 @@
         <v>1465</v>
       </c>
       <c r="E337">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F337" t="s">
         <v>1519</v>
@@ -19632,7 +19632,7 @@
         <v>1465</v>
       </c>
       <c r="E338">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F338" t="s">
         <v>1519</v>
@@ -19667,7 +19667,7 @@
         <v>1465</v>
       </c>
       <c r="E339">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F339" t="s">
         <v>1519</v>
@@ -19702,7 +19702,7 @@
         <v>1465</v>
       </c>
       <c r="E340">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F340" t="s">
         <v>1519</v>
@@ -19737,7 +19737,7 @@
         <v>1465</v>
       </c>
       <c r="E341">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F341" t="s">
         <v>1519</v>
@@ -19772,7 +19772,7 @@
         <v>1465</v>
       </c>
       <c r="E342">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F342" t="s">
         <v>1519</v>
@@ -19807,7 +19807,7 @@
         <v>1465</v>
       </c>
       <c r="E343">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F343" t="s">
         <v>1519</v>
@@ -19842,7 +19842,7 @@
         <v>1466</v>
       </c>
       <c r="E344">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F344" t="s">
         <v>1519</v>
@@ -19877,7 +19877,7 @@
         <v>1466</v>
       </c>
       <c r="E345">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F345" t="s">
         <v>1519</v>
@@ -19912,7 +19912,7 @@
         <v>1466</v>
       </c>
       <c r="E346">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F346" t="s">
         <v>1520</v>
@@ -19947,7 +19947,7 @@
         <v>1467</v>
       </c>
       <c r="E347">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F347" t="s">
         <v>1519</v>
@@ -19982,7 +19982,7 @@
         <v>1467</v>
       </c>
       <c r="E348">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F348" t="s">
         <v>1519</v>
@@ -20017,7 +20017,7 @@
         <v>1467</v>
       </c>
       <c r="E349">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F349" t="s">
         <v>1519</v>
@@ -20052,7 +20052,7 @@
         <v>1467</v>
       </c>
       <c r="E350">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F350" t="s">
         <v>1519</v>
@@ -20087,7 +20087,7 @@
         <v>1467</v>
       </c>
       <c r="E351">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F351" t="s">
         <v>1519</v>
@@ -20122,7 +20122,7 @@
         <v>1467</v>
       </c>
       <c r="E352">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F352" t="s">
         <v>1519</v>
@@ -20157,7 +20157,7 @@
         <v>1467</v>
       </c>
       <c r="E353">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F353" t="s">
         <v>1522</v>
@@ -20192,7 +20192,7 @@
         <v>1468</v>
       </c>
       <c r="E354">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F354" t="s">
         <v>1519</v>
@@ -20227,7 +20227,7 @@
         <v>1468</v>
       </c>
       <c r="E355">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F355" t="s">
         <v>1519</v>
@@ -20262,7 +20262,7 @@
         <v>1468</v>
       </c>
       <c r="E356">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F356" t="s">
         <v>1519</v>
@@ -20297,7 +20297,7 @@
         <v>1468</v>
       </c>
       <c r="E357">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F357" t="s">
         <v>1519</v>
@@ -20332,7 +20332,7 @@
         <v>1469</v>
       </c>
       <c r="E358">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F358" t="s">
         <v>1522</v>
@@ -20367,7 +20367,7 @@
         <v>1469</v>
       </c>
       <c r="E359">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F359" t="s">
         <v>1519</v>
@@ -20402,7 +20402,7 @@
         <v>1469</v>
       </c>
       <c r="E360">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F360" t="s">
         <v>1519</v>
@@ -20437,7 +20437,7 @@
         <v>1469</v>
       </c>
       <c r="E361">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F361" t="s">
         <v>1519</v>
@@ -20472,7 +20472,7 @@
         <v>1469</v>
       </c>
       <c r="E362">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F362" t="s">
         <v>1519</v>
@@ -20507,7 +20507,7 @@
         <v>1470</v>
       </c>
       <c r="E363">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F363" t="s">
         <v>1519</v>
@@ -20542,7 +20542,7 @@
         <v>1470</v>
       </c>
       <c r="E364">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F364" t="s">
         <v>1519</v>
@@ -20577,7 +20577,7 @@
         <v>1470</v>
       </c>
       <c r="E365">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F365" t="s">
         <v>1521</v>
@@ -20612,7 +20612,7 @@
         <v>1470</v>
       </c>
       <c r="E366">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F366" t="s">
         <v>1519</v>
@@ -20647,7 +20647,7 @@
         <v>1470</v>
       </c>
       <c r="E367">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F367" t="s">
         <v>1519</v>
@@ -20682,7 +20682,7 @@
         <v>1471</v>
       </c>
       <c r="E368">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F368" t="s">
         <v>1519</v>
@@ -20717,7 +20717,7 @@
         <v>1471</v>
       </c>
       <c r="E369">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F369" t="s">
         <v>1519</v>
@@ -20752,7 +20752,7 @@
         <v>1471</v>
       </c>
       <c r="E370">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F370" t="s">
         <v>1519</v>
@@ -20787,7 +20787,7 @@
         <v>1471</v>
       </c>
       <c r="E371">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F371" t="s">
         <v>1519</v>
@@ -20822,7 +20822,7 @@
         <v>1471</v>
       </c>
       <c r="E372">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F372" t="s">
         <v>1519</v>
@@ -20857,7 +20857,7 @@
         <v>1472</v>
       </c>
       <c r="E373">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F373" t="s">
         <v>1519</v>
@@ -20892,7 +20892,7 @@
         <v>1472</v>
       </c>
       <c r="E374">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F374" t="s">
         <v>1519</v>
@@ -20927,7 +20927,7 @@
         <v>1472</v>
       </c>
       <c r="E375">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F375" t="s">
         <v>1519</v>
@@ -20962,7 +20962,7 @@
         <v>1472</v>
       </c>
       <c r="E376">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F376" t="s">
         <v>1519</v>
@@ -21000,7 +21000,7 @@
         <v>1473</v>
       </c>
       <c r="E377">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F377" t="s">
         <v>1519</v>
@@ -21035,7 +21035,7 @@
         <v>1473</v>
       </c>
       <c r="E378">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F378" t="s">
         <v>1519</v>
@@ -21070,7 +21070,7 @@
         <v>1473</v>
       </c>
       <c r="E379">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F379" t="s">
         <v>1519</v>
@@ -21105,7 +21105,7 @@
         <v>1473</v>
       </c>
       <c r="E380">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F380" t="s">
         <v>1519</v>
@@ -21140,7 +21140,7 @@
         <v>1473</v>
       </c>
       <c r="E381">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F381" t="s">
         <v>1519</v>
@@ -21175,7 +21175,7 @@
         <v>1473</v>
       </c>
       <c r="E382">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F382" t="s">
         <v>1519</v>
@@ -21210,7 +21210,7 @@
         <v>1474</v>
       </c>
       <c r="E383">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F383" t="s">
         <v>1520</v>
@@ -21245,7 +21245,7 @@
         <v>1474</v>
       </c>
       <c r="E384">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F384" t="s">
         <v>1519</v>
@@ -21280,7 +21280,7 @@
         <v>1475</v>
       </c>
       <c r="E385">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F385" t="s">
         <v>1519</v>
@@ -21315,7 +21315,7 @@
         <v>1476</v>
       </c>
       <c r="E386">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F386" t="s">
         <v>1519</v>
@@ -21350,7 +21350,7 @@
         <v>1476</v>
       </c>
       <c r="E387">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F387" t="s">
         <v>1519</v>
@@ -21385,7 +21385,7 @@
         <v>1476</v>
       </c>
       <c r="E388">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F388" t="s">
         <v>1521</v>
@@ -21423,7 +21423,7 @@
         <v>1477</v>
       </c>
       <c r="E389">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F389" t="s">
         <v>1519</v>
@@ -21458,7 +21458,7 @@
         <v>1477</v>
       </c>
       <c r="E390">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F390" t="s">
         <v>1519</v>
@@ -21493,7 +21493,7 @@
         <v>1477</v>
       </c>
       <c r="E391">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F391" t="s">
         <v>1519</v>
@@ -21528,7 +21528,7 @@
         <v>1478</v>
       </c>
       <c r="E392">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F392" t="s">
         <v>1519</v>
@@ -21563,7 +21563,7 @@
         <v>1478</v>
       </c>
       <c r="E393">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F393" t="s">
         <v>1519</v>
@@ -21598,7 +21598,7 @@
         <v>1478</v>
       </c>
       <c r="E394">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F394" t="s">
         <v>1519</v>
@@ -21633,7 +21633,7 @@
         <v>1478</v>
       </c>
       <c r="E395">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F395" t="s">
         <v>1519</v>
@@ -21668,7 +21668,7 @@
         <v>1478</v>
       </c>
       <c r="E396">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F396" t="s">
         <v>1519</v>
@@ -21703,7 +21703,7 @@
         <v>1478</v>
       </c>
       <c r="E397">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F397" t="s">
         <v>1519</v>
@@ -21738,7 +21738,7 @@
         <v>1478</v>
       </c>
       <c r="E398">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F398" t="s">
         <v>1519</v>
@@ -21773,7 +21773,7 @@
         <v>1479</v>
       </c>
       <c r="E399">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F399" t="s">
         <v>1519</v>
@@ -21808,7 +21808,7 @@
         <v>1480</v>
       </c>
       <c r="E400">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F400" t="s">
         <v>1519</v>
@@ -21843,7 +21843,7 @@
         <v>1480</v>
       </c>
       <c r="E401">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F401" t="s">
         <v>1519</v>
@@ -21878,7 +21878,7 @@
         <v>1480</v>
       </c>
       <c r="E402">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F402" t="s">
         <v>1519</v>
@@ -21913,7 +21913,7 @@
         <v>1480</v>
       </c>
       <c r="E403">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F403" t="s">
         <v>1523</v>
@@ -21951,7 +21951,7 @@
         <v>1480</v>
       </c>
       <c r="E404">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F404" t="s">
         <v>1519</v>
@@ -21986,7 +21986,7 @@
         <v>1480</v>
       </c>
       <c r="E405">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F405" t="s">
         <v>1523</v>
@@ -22021,7 +22021,7 @@
         <v>1481</v>
       </c>
       <c r="E406">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F406" t="s">
         <v>1519</v>
@@ -22056,7 +22056,7 @@
         <v>1482</v>
       </c>
       <c r="E407">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F407" t="s">
         <v>1519</v>
@@ -22091,7 +22091,7 @@
         <v>1482</v>
       </c>
       <c r="E408">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F408" t="s">
         <v>1519</v>
@@ -22126,7 +22126,7 @@
         <v>1482</v>
       </c>
       <c r="E409">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F409" t="s">
         <v>1519</v>
@@ -22161,7 +22161,7 @@
         <v>1483</v>
       </c>
       <c r="E410">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F410" t="s">
         <v>1523</v>
@@ -22196,7 +22196,7 @@
         <v>1483</v>
       </c>
       <c r="E411">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F411" t="s">
         <v>1519</v>
@@ -22231,7 +22231,7 @@
         <v>1483</v>
       </c>
       <c r="E412">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F412" t="s">
         <v>1519</v>
@@ -22266,7 +22266,7 @@
         <v>1483</v>
       </c>
       <c r="E413">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F413" t="s">
         <v>1519</v>
@@ -22301,7 +22301,7 @@
         <v>1484</v>
       </c>
       <c r="E414">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F414" t="s">
         <v>1519</v>
@@ -22336,7 +22336,7 @@
         <v>1484</v>
       </c>
       <c r="E415">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F415" t="s">
         <v>1519</v>
@@ -22371,7 +22371,7 @@
         <v>1484</v>
       </c>
       <c r="E416">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F416" t="s">
         <v>1519</v>
@@ -22406,7 +22406,7 @@
         <v>1485</v>
       </c>
       <c r="E417">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F417" t="s">
         <v>1519</v>
@@ -22441,7 +22441,7 @@
         <v>1485</v>
       </c>
       <c r="E418">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F418" t="s">
         <v>1519</v>
@@ -22476,7 +22476,7 @@
         <v>1485</v>
       </c>
       <c r="E419">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F419" t="s">
         <v>1519</v>
@@ -22511,7 +22511,7 @@
         <v>1485</v>
       </c>
       <c r="E420">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F420" t="s">
         <v>1519</v>
@@ -22546,7 +22546,7 @@
         <v>1485</v>
       </c>
       <c r="E421">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F421" t="s">
         <v>1519</v>
@@ -22581,7 +22581,7 @@
         <v>1486</v>
       </c>
       <c r="E422">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F422" t="s">
         <v>1519</v>
@@ -22616,7 +22616,7 @@
         <v>1486</v>
       </c>
       <c r="E423">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F423" t="s">
         <v>1519</v>
@@ -22651,7 +22651,7 @@
         <v>1486</v>
       </c>
       <c r="E424">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F424" t="s">
         <v>1519</v>
@@ -22686,7 +22686,7 @@
         <v>1486</v>
       </c>
       <c r="E425">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F425" t="s">
         <v>1519</v>
@@ -22721,7 +22721,7 @@
         <v>1486</v>
       </c>
       <c r="E426">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F426" t="s">
         <v>1519</v>
@@ -22756,7 +22756,7 @@
         <v>1486</v>
       </c>
       <c r="E427">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F427" t="s">
         <v>1519</v>
@@ -22791,7 +22791,7 @@
         <v>1486</v>
       </c>
       <c r="E428">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F428" t="s">
         <v>1519</v>
@@ -22826,7 +22826,7 @@
         <v>1486</v>
       </c>
       <c r="E429">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F429" t="s">
         <v>1519</v>
@@ -22861,7 +22861,7 @@
         <v>1486</v>
       </c>
       <c r="E430">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F430" t="s">
         <v>1519</v>
@@ -22896,7 +22896,7 @@
         <v>1486</v>
       </c>
       <c r="E431">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F431" t="s">
         <v>1519</v>
@@ -22931,7 +22931,7 @@
         <v>1486</v>
       </c>
       <c r="E432">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F432" t="s">
         <v>1519</v>
@@ -22966,7 +22966,7 @@
         <v>1486</v>
       </c>
       <c r="E433">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F433" t="s">
         <v>1519</v>
@@ -23001,7 +23001,7 @@
         <v>1486</v>
       </c>
       <c r="E434">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F434" t="s">
         <v>1519</v>
@@ -23036,7 +23036,7 @@
         <v>1486</v>
       </c>
       <c r="E435">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F435" t="s">
         <v>1519</v>
@@ -23071,7 +23071,7 @@
         <v>1486</v>
       </c>
       <c r="E436">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F436" t="s">
         <v>1519</v>
@@ -23106,7 +23106,7 @@
         <v>1486</v>
       </c>
       <c r="E437">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F437" t="s">
         <v>1519</v>
@@ -23141,7 +23141,7 @@
         <v>1486</v>
       </c>
       <c r="E438">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F438" t="s">
         <v>1519</v>
@@ -23176,7 +23176,7 @@
         <v>1486</v>
       </c>
       <c r="E439">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F439" t="s">
         <v>1519</v>
@@ -23211,7 +23211,7 @@
         <v>1486</v>
       </c>
       <c r="E440">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F440" t="s">
         <v>1519</v>
@@ -23246,7 +23246,7 @@
         <v>1486</v>
       </c>
       <c r="E441">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F441" t="s">
         <v>1519</v>
@@ -23281,7 +23281,7 @@
         <v>1486</v>
       </c>
       <c r="E442">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F442" t="s">
         <v>1519</v>
@@ -23316,7 +23316,7 @@
         <v>1486</v>
       </c>
       <c r="E443">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F443" t="s">
         <v>1519</v>
@@ -23351,7 +23351,7 @@
         <v>1486</v>
       </c>
       <c r="E444">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F444" t="s">
         <v>1519</v>
@@ -23386,7 +23386,7 @@
         <v>1486</v>
       </c>
       <c r="E445">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F445" t="s">
         <v>1519</v>
@@ -23421,7 +23421,7 @@
         <v>1487</v>
       </c>
       <c r="E446">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F446" t="s">
         <v>1519</v>
@@ -23456,7 +23456,7 @@
         <v>1487</v>
       </c>
       <c r="E447">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F447" t="s">
         <v>1519</v>
@@ -23491,7 +23491,7 @@
         <v>1487</v>
       </c>
       <c r="E448">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F448" t="s">
         <v>1519</v>
@@ -23526,7 +23526,7 @@
         <v>1487</v>
       </c>
       <c r="E449">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F449" t="s">
         <v>1519</v>
@@ -23561,7 +23561,7 @@
         <v>1487</v>
       </c>
       <c r="E450">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F450" t="s">
         <v>1519</v>
@@ -23596,7 +23596,7 @@
         <v>1487</v>
       </c>
       <c r="E451">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F451" t="s">
         <v>1519</v>
@@ -23631,7 +23631,7 @@
         <v>1487</v>
       </c>
       <c r="E452">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F452" t="s">
         <v>1523</v>
@@ -23666,7 +23666,7 @@
         <v>1487</v>
       </c>
       <c r="E453">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F453" t="s">
         <v>1519</v>
@@ -23701,7 +23701,7 @@
         <v>1488</v>
       </c>
       <c r="E454">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F454" t="s">
         <v>1519</v>
@@ -23736,7 +23736,7 @@
         <v>1489</v>
       </c>
       <c r="E455">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F455" t="s">
         <v>1521</v>
@@ -23774,7 +23774,7 @@
         <v>1489</v>
       </c>
       <c r="E456">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F456" t="s">
         <v>1519</v>
@@ -23809,7 +23809,7 @@
         <v>1489</v>
       </c>
       <c r="E457">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F457" t="s">
         <v>1519</v>
@@ -23844,7 +23844,7 @@
         <v>1489</v>
       </c>
       <c r="E458">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F458" t="s">
         <v>1519</v>
@@ -23879,7 +23879,7 @@
         <v>1489</v>
       </c>
       <c r="E459">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F459" t="s">
         <v>1519</v>
@@ -23914,7 +23914,7 @@
         <v>1490</v>
       </c>
       <c r="E460">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F460" t="s">
         <v>1519</v>
@@ -23952,7 +23952,7 @@
         <v>1490</v>
       </c>
       <c r="E461">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F461" t="s">
         <v>1523</v>
@@ -23987,7 +23987,7 @@
         <v>1490</v>
       </c>
       <c r="E462">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F462" t="s">
         <v>1521</v>
@@ -24022,7 +24022,7 @@
         <v>1490</v>
       </c>
       <c r="E463">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F463" t="s">
         <v>1519</v>
@@ -24057,7 +24057,7 @@
         <v>1490</v>
       </c>
       <c r="E464">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F464" t="s">
         <v>1519</v>
@@ -24092,7 +24092,7 @@
         <v>1490</v>
       </c>
       <c r="E465">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F465" t="s">
         <v>1519</v>
@@ -24127,7 +24127,7 @@
         <v>1490</v>
       </c>
       <c r="E466">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F466" t="s">
         <v>1519</v>
@@ -24162,7 +24162,7 @@
         <v>1490</v>
       </c>
       <c r="E467">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F467" t="s">
         <v>1519</v>
@@ -24197,7 +24197,7 @@
         <v>1490</v>
       </c>
       <c r="E468">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F468" t="s">
         <v>1519</v>
@@ -24232,7 +24232,7 @@
         <v>1491</v>
       </c>
       <c r="E469">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F469" t="s">
         <v>1523</v>
@@ -24270,7 +24270,7 @@
         <v>1491</v>
       </c>
       <c r="E470">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F470" t="s">
         <v>1519</v>
@@ -24305,7 +24305,7 @@
         <v>1492</v>
       </c>
       <c r="E471">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F471" t="s">
         <v>1519</v>
@@ -24340,7 +24340,7 @@
         <v>1492</v>
       </c>
       <c r="E472">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F472" t="s">
         <v>1519</v>
@@ -24375,7 +24375,7 @@
         <v>1492</v>
       </c>
       <c r="E473">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F473" t="s">
         <v>1519</v>
@@ -24410,7 +24410,7 @@
         <v>1492</v>
       </c>
       <c r="E474">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F474" t="s">
         <v>1519</v>
@@ -24445,7 +24445,7 @@
         <v>1492</v>
       </c>
       <c r="E475">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F475" t="s">
         <v>1519</v>
@@ -24480,7 +24480,7 @@
         <v>1492</v>
       </c>
       <c r="E476">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F476" t="s">
         <v>1519</v>
@@ -24515,7 +24515,7 @@
         <v>1493</v>
       </c>
       <c r="E477">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F477" t="s">
         <v>1519</v>
@@ -24550,7 +24550,7 @@
         <v>1493</v>
       </c>
       <c r="E478">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F478" t="s">
         <v>1519</v>
@@ -24585,7 +24585,7 @@
         <v>1493</v>
       </c>
       <c r="E479">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F479" t="s">
         <v>1519</v>
@@ -24620,7 +24620,7 @@
         <v>1493</v>
       </c>
       <c r="E480">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F480" t="s">
         <v>1519</v>
@@ -24655,7 +24655,7 @@
         <v>1493</v>
       </c>
       <c r="E481">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F481" t="s">
         <v>1519</v>
@@ -24690,7 +24690,7 @@
         <v>1493</v>
       </c>
       <c r="E482">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F482" t="s">
         <v>1521</v>
@@ -24725,7 +24725,7 @@
         <v>1493</v>
       </c>
       <c r="E483">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F483" t="s">
         <v>1519</v>
@@ -24760,7 +24760,7 @@
         <v>1493</v>
       </c>
       <c r="E484">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F484" t="s">
         <v>1519</v>
@@ -24795,7 +24795,7 @@
         <v>1494</v>
       </c>
       <c r="E485">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F485" t="s">
         <v>1519</v>
@@ -24830,7 +24830,7 @@
         <v>1494</v>
       </c>
       <c r="E486">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F486" t="s">
         <v>1519</v>
@@ -24865,7 +24865,7 @@
         <v>1494</v>
       </c>
       <c r="E487">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F487" t="s">
         <v>1519</v>
@@ -24900,7 +24900,7 @@
         <v>1494</v>
       </c>
       <c r="E488">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F488" t="s">
         <v>1519</v>
@@ -24935,7 +24935,7 @@
         <v>1494</v>
       </c>
       <c r="E489">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F489" t="s">
         <v>1519</v>
@@ -24970,7 +24970,7 @@
         <v>1494</v>
       </c>
       <c r="E490">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F490" t="s">
         <v>1519</v>
@@ -25005,7 +25005,7 @@
         <v>1494</v>
       </c>
       <c r="E491">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F491" t="s">
         <v>1519</v>
@@ -25040,7 +25040,7 @@
         <v>1494</v>
       </c>
       <c r="E492">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F492" t="s">
         <v>1519</v>
@@ -25075,7 +25075,7 @@
         <v>1495</v>
       </c>
       <c r="E493">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F493" t="s">
         <v>1519</v>
@@ -25110,7 +25110,7 @@
         <v>1495</v>
       </c>
       <c r="E494">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F494" t="s">
         <v>1519</v>
@@ -25145,7 +25145,7 @@
         <v>1495</v>
       </c>
       <c r="E495">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F495" t="s">
         <v>1519</v>
@@ -25180,7 +25180,7 @@
         <v>1495</v>
       </c>
       <c r="E496">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F496" t="s">
         <v>1519</v>
@@ -25215,7 +25215,7 @@
         <v>1495</v>
       </c>
       <c r="E497">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F497" t="s">
         <v>1519</v>
@@ -25250,7 +25250,7 @@
         <v>1495</v>
       </c>
       <c r="E498">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F498" t="s">
         <v>1519</v>
@@ -25285,7 +25285,7 @@
         <v>1496</v>
       </c>
       <c r="E499">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F499" t="s">
         <v>1519</v>
@@ -25320,7 +25320,7 @@
         <v>1496</v>
       </c>
       <c r="E500">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F500" t="s">
         <v>1519</v>
@@ -25355,7 +25355,7 @@
         <v>1496</v>
       </c>
       <c r="E501">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F501" t="s">
         <v>1519</v>
@@ -25390,7 +25390,7 @@
         <v>1496</v>
       </c>
       <c r="E502">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F502" t="s">
         <v>1519</v>
@@ -25425,7 +25425,7 @@
         <v>1496</v>
       </c>
       <c r="E503">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F503" t="s">
         <v>1519</v>
@@ -25460,7 +25460,7 @@
         <v>1497</v>
       </c>
       <c r="E504">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F504" t="s">
         <v>1519</v>
@@ -25495,7 +25495,7 @@
         <v>1497</v>
       </c>
       <c r="E505">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F505" t="s">
         <v>1519</v>
@@ -25530,7 +25530,7 @@
         <v>1497</v>
       </c>
       <c r="E506">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F506" t="s">
         <v>1519</v>
@@ -25565,7 +25565,7 @@
         <v>1497</v>
       </c>
       <c r="E507">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F507" t="s">
         <v>1519</v>
@@ -25600,7 +25600,7 @@
         <v>1497</v>
       </c>
       <c r="E508">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F508" t="s">
         <v>1519</v>
@@ -25635,7 +25635,7 @@
         <v>1497</v>
       </c>
       <c r="E509">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F509" t="s">
         <v>1519</v>
@@ -25670,7 +25670,7 @@
         <v>1497</v>
       </c>
       <c r="E510">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F510" t="s">
         <v>1519</v>
@@ -25705,7 +25705,7 @@
         <v>1497</v>
       </c>
       <c r="E511">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F511" t="s">
         <v>1519</v>
@@ -25740,7 +25740,7 @@
         <v>1497</v>
       </c>
       <c r="E512">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F512" t="s">
         <v>1519</v>
@@ -25778,7 +25778,7 @@
         <v>1497</v>
       </c>
       <c r="E513">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F513" t="s">
         <v>1519</v>
@@ -25813,7 +25813,7 @@
         <v>1498</v>
       </c>
       <c r="E514">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F514" t="s">
         <v>1519</v>
@@ -25848,7 +25848,7 @@
         <v>1498</v>
       </c>
       <c r="E515">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F515" t="s">
         <v>1521</v>
@@ -25886,7 +25886,7 @@
         <v>1498</v>
       </c>
       <c r="E516">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F516" t="s">
         <v>1519</v>
@@ -25921,7 +25921,7 @@
         <v>1498</v>
       </c>
       <c r="E517">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F517" t="s">
         <v>1519</v>
@@ -25956,7 +25956,7 @@
         <v>1499</v>
       </c>
       <c r="E518">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F518" t="s">
         <v>1519</v>
@@ -25991,7 +25991,7 @@
         <v>1499</v>
       </c>
       <c r="E519">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F519" t="s">
         <v>1519</v>
@@ -26026,7 +26026,7 @@
         <v>1499</v>
       </c>
       <c r="E520">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F520" t="s">
         <v>1519</v>
@@ -26061,7 +26061,7 @@
         <v>1499</v>
       </c>
       <c r="E521">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F521" t="s">
         <v>1521</v>
@@ -26099,7 +26099,7 @@
         <v>1499</v>
       </c>
       <c r="E522">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F522" t="s">
         <v>1519</v>
@@ -26134,7 +26134,7 @@
         <v>1499</v>
       </c>
       <c r="E523">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F523" t="s">
         <v>1519</v>
@@ -26169,7 +26169,7 @@
         <v>1499</v>
       </c>
       <c r="E524">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F524" t="s">
         <v>1519</v>
@@ -26204,7 +26204,7 @@
         <v>1499</v>
       </c>
       <c r="E525">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F525" t="s">
         <v>1519</v>
@@ -26239,7 +26239,7 @@
         <v>1499</v>
       </c>
       <c r="E526">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F526" t="s">
         <v>1519</v>
@@ -26274,7 +26274,7 @@
         <v>1499</v>
       </c>
       <c r="E527">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F527" t="s">
         <v>1519</v>
@@ -26309,7 +26309,7 @@
         <v>1500</v>
       </c>
       <c r="E528">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F528" t="s">
         <v>1519</v>
@@ -26344,7 +26344,7 @@
         <v>1500</v>
       </c>
       <c r="E529">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F529" t="s">
         <v>1519</v>
@@ -26379,7 +26379,7 @@
         <v>1500</v>
       </c>
       <c r="E530">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F530" t="s">
         <v>1519</v>
@@ -26414,7 +26414,7 @@
         <v>1500</v>
       </c>
       <c r="E531">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F531" t="s">
         <v>1519</v>
@@ -26449,7 +26449,7 @@
         <v>1501</v>
       </c>
       <c r="E532">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F532" t="s">
         <v>1519</v>
@@ -26484,7 +26484,7 @@
         <v>1501</v>
       </c>
       <c r="E533">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F533" t="s">
         <v>1519</v>
@@ -26519,7 +26519,7 @@
         <v>1501</v>
       </c>
       <c r="E534">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F534" t="s">
         <v>1519</v>
@@ -26554,7 +26554,7 @@
         <v>1501</v>
       </c>
       <c r="E535">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F535" t="s">
         <v>1521</v>
@@ -26592,7 +26592,7 @@
         <v>1502</v>
       </c>
       <c r="E536">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F536" t="s">
         <v>1519</v>
@@ -26627,7 +26627,7 @@
         <v>1502</v>
       </c>
       <c r="E537">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F537" t="s">
         <v>1523</v>
@@ -26665,7 +26665,7 @@
         <v>1502</v>
       </c>
       <c r="E538">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F538" t="s">
         <v>1519</v>
@@ -26700,7 +26700,7 @@
         <v>1502</v>
       </c>
       <c r="E539">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F539" t="s">
         <v>1519</v>
@@ -26735,7 +26735,7 @@
         <v>1503</v>
       </c>
       <c r="E540">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F540" t="s">
         <v>1519</v>
@@ -26770,7 +26770,7 @@
         <v>1503</v>
       </c>
       <c r="E541">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F541" t="s">
         <v>1519</v>
@@ -26805,7 +26805,7 @@
         <v>1503</v>
       </c>
       <c r="E542">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F542" t="s">
         <v>1519</v>
@@ -26840,7 +26840,7 @@
         <v>1503</v>
       </c>
       <c r="E543">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F543" t="s">
         <v>1519</v>
@@ -26875,7 +26875,7 @@
         <v>1503</v>
       </c>
       <c r="E544">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F544" t="s">
         <v>1521</v>
@@ -26913,7 +26913,7 @@
         <v>1503</v>
       </c>
       <c r="E545">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F545" t="s">
         <v>1519</v>
@@ -26948,7 +26948,7 @@
         <v>1503</v>
       </c>
       <c r="E546">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F546" t="s">
         <v>1519</v>
@@ -26983,7 +26983,7 @@
         <v>1503</v>
       </c>
       <c r="E547">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F547" t="s">
         <v>1519</v>
@@ -27018,7 +27018,7 @@
         <v>1504</v>
       </c>
       <c r="E548">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F548" t="s">
         <v>1519</v>
@@ -27053,7 +27053,7 @@
         <v>1504</v>
       </c>
       <c r="E549">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F549" t="s">
         <v>1519</v>
@@ -27088,7 +27088,7 @@
         <v>1505</v>
       </c>
       <c r="E550">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F550" t="s">
         <v>1521</v>
@@ -27126,7 +27126,7 @@
         <v>1505</v>
       </c>
       <c r="E551">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F551" t="s">
         <v>1521</v>
@@ -27164,7 +27164,7 @@
         <v>1505</v>
       </c>
       <c r="E552">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F552" t="s">
         <v>1519</v>
@@ -27199,7 +27199,7 @@
         <v>1505</v>
       </c>
       <c r="E553">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F553" t="s">
         <v>1519</v>
@@ -27234,7 +27234,7 @@
         <v>1505</v>
       </c>
       <c r="E554">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F554" t="s">
         <v>1519</v>
@@ -27269,7 +27269,7 @@
         <v>1506</v>
       </c>
       <c r="E555">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F555" t="s">
         <v>1519</v>
@@ -27304,7 +27304,7 @@
         <v>1507</v>
       </c>
       <c r="E556">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F556" t="s">
         <v>1519</v>
@@ -27339,7 +27339,7 @@
         <v>1507</v>
       </c>
       <c r="E557">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F557" t="s">
         <v>1519</v>
@@ -27374,7 +27374,7 @@
         <v>1507</v>
       </c>
       <c r="E558">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F558" t="s">
         <v>1519</v>
@@ -27409,7 +27409,7 @@
         <v>1507</v>
       </c>
       <c r="E559">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F559" t="s">
         <v>1519</v>
@@ -27444,7 +27444,7 @@
         <v>1507</v>
       </c>
       <c r="E560">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F560" t="s">
         <v>1519</v>
@@ -27479,7 +27479,7 @@
         <v>1507</v>
       </c>
       <c r="E561">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F561" t="s">
         <v>1519</v>
@@ -27514,7 +27514,7 @@
         <v>1507</v>
       </c>
       <c r="E562">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F562" t="s">
         <v>1519</v>
@@ -27549,7 +27549,7 @@
         <v>1507</v>
       </c>
       <c r="E563">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F563" t="s">
         <v>1519</v>
@@ -27584,7 +27584,7 @@
         <v>1507</v>
       </c>
       <c r="E564">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F564" t="s">
         <v>1519</v>
@@ -27619,7 +27619,7 @@
         <v>1507</v>
       </c>
       <c r="E565">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F565" t="s">
         <v>1521</v>
@@ -27657,7 +27657,7 @@
         <v>1508</v>
       </c>
       <c r="E566">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F566" t="s">
         <v>1519</v>
@@ -27692,7 +27692,7 @@
         <v>1508</v>
       </c>
       <c r="E567">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F567" t="s">
         <v>1519</v>
@@ -27727,7 +27727,7 @@
         <v>1508</v>
       </c>
       <c r="E568">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F568" t="s">
         <v>1519</v>
@@ -27762,7 +27762,7 @@
         <v>1508</v>
       </c>
       <c r="E569">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F569" t="s">
         <v>1519</v>
@@ -27797,7 +27797,7 @@
         <v>1508</v>
       </c>
       <c r="E570">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F570" t="s">
         <v>1521</v>
@@ -27835,7 +27835,7 @@
         <v>1508</v>
       </c>
       <c r="E571">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F571" t="s">
         <v>1521</v>
@@ -27873,7 +27873,7 @@
         <v>1508</v>
       </c>
       <c r="E572">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F572" t="s">
         <v>1519</v>
@@ -27908,7 +27908,7 @@
         <v>1508</v>
       </c>
       <c r="E573">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F573" t="s">
         <v>1519</v>
@@ -27943,7 +27943,7 @@
         <v>1508</v>
       </c>
       <c r="E574">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F574" t="s">
         <v>1519</v>
@@ -27978,7 +27978,7 @@
         <v>1509</v>
       </c>
       <c r="E575">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F575" t="s">
         <v>1519</v>
@@ -28013,7 +28013,7 @@
         <v>1509</v>
       </c>
       <c r="E576">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F576" t="s">
         <v>1521</v>
@@ -28051,7 +28051,7 @@
         <v>1509</v>
       </c>
       <c r="E577">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F577" t="s">
         <v>1521</v>
@@ -28089,7 +28089,7 @@
         <v>1509</v>
       </c>
       <c r="E578">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F578" t="s">
         <v>1519</v>
@@ -28124,7 +28124,7 @@
         <v>1510</v>
       </c>
       <c r="E579">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F579" t="s">
         <v>1521</v>
@@ -28162,7 +28162,7 @@
         <v>1510</v>
       </c>
       <c r="E580">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F580" t="s">
         <v>1519</v>
@@ -28197,7 +28197,7 @@
         <v>1510</v>
       </c>
       <c r="E581">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F581" t="s">
         <v>1519</v>
@@ -28232,7 +28232,7 @@
         <v>1511</v>
       </c>
       <c r="E582">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F582" t="s">
         <v>1519</v>
@@ -28267,7 +28267,7 @@
         <v>1511</v>
       </c>
       <c r="E583">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F583" t="s">
         <v>1519</v>
@@ -28302,7 +28302,7 @@
         <v>1511</v>
       </c>
       <c r="E584">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F584" t="s">
         <v>1519</v>
@@ -28337,7 +28337,7 @@
         <v>1511</v>
       </c>
       <c r="E585">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F585" t="s">
         <v>1519</v>
@@ -28372,7 +28372,7 @@
         <v>1511</v>
       </c>
       <c r="E586">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F586" t="s">
         <v>1519</v>
@@ -28407,7 +28407,7 @@
         <v>1511</v>
       </c>
       <c r="E587">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F587" t="s">
         <v>1519</v>
@@ -28442,7 +28442,7 @@
         <v>1511</v>
       </c>
       <c r="E588">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F588" t="s">
         <v>1521</v>
@@ -28480,7 +28480,7 @@
         <v>1511</v>
       </c>
       <c r="E589">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F589" t="s">
         <v>1521</v>
@@ -28518,7 +28518,7 @@
         <v>1512</v>
       </c>
       <c r="E590">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F590" t="s">
         <v>1521</v>
@@ -28556,7 +28556,7 @@
         <v>1512</v>
       </c>
       <c r="E591">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F591" t="s">
         <v>1521</v>
@@ -28591,7 +28591,7 @@
         <v>1512</v>
       </c>
       <c r="E592">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F592" t="s">
         <v>1519</v>
@@ -28626,7 +28626,7 @@
         <v>1512</v>
       </c>
       <c r="E593">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F593" t="s">
         <v>1519</v>
@@ -28661,7 +28661,7 @@
         <v>1512</v>
       </c>
       <c r="E594">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F594" t="s">
         <v>1519</v>
@@ -28696,7 +28696,7 @@
         <v>1512</v>
       </c>
       <c r="E595">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F595" t="s">
         <v>1519</v>
@@ -28731,7 +28731,7 @@
         <v>1513</v>
       </c>
       <c r="E596">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F596" t="s">
         <v>1519</v>
@@ -28766,7 +28766,7 @@
         <v>1513</v>
       </c>
       <c r="E597">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F597" t="s">
         <v>1519</v>
@@ -28801,7 +28801,7 @@
         <v>1513</v>
       </c>
       <c r="E598">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F598" t="s">
         <v>1519</v>
@@ -28836,7 +28836,7 @@
         <v>1513</v>
       </c>
       <c r="E599">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F599" t="s">
         <v>1519</v>
@@ -28871,7 +28871,7 @@
         <v>1513</v>
       </c>
       <c r="E600">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F600" t="s">
         <v>1519</v>
@@ -28906,7 +28906,7 @@
         <v>1513</v>
       </c>
       <c r="E601">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F601" t="s">
         <v>1519</v>
@@ -28941,7 +28941,7 @@
         <v>1513</v>
       </c>
       <c r="E602">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F602" t="s">
         <v>1519</v>
@@ -28976,7 +28976,7 @@
         <v>1514</v>
       </c>
       <c r="E603">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F603" t="s">
         <v>1519</v>
@@ -29014,7 +29014,7 @@
         <v>1514</v>
       </c>
       <c r="E604">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F604" t="s">
         <v>1519</v>
@@ -29049,7 +29049,7 @@
         <v>1514</v>
       </c>
       <c r="E605">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F605" t="s">
         <v>1519</v>
@@ -29084,7 +29084,7 @@
         <v>1514</v>
       </c>
       <c r="E606">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F606" t="s">
         <v>1519</v>
@@ -29122,7 +29122,7 @@
         <v>1514</v>
       </c>
       <c r="E607">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F607" t="s">
         <v>1519</v>
@@ -29157,7 +29157,7 @@
         <v>1515</v>
       </c>
       <c r="E608">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F608" t="s">
         <v>1519</v>
@@ -29192,7 +29192,7 @@
         <v>1516</v>
       </c>
       <c r="E609">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F609" t="s">
         <v>1519</v>
@@ -29227,7 +29227,7 @@
         <v>1516</v>
       </c>
       <c r="E610">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F610" t="s">
         <v>1519</v>
@@ -29262,7 +29262,7 @@
         <v>1516</v>
       </c>
       <c r="E611">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F611" t="s">
         <v>1519</v>
@@ -29297,7 +29297,7 @@
         <v>1516</v>
       </c>
       <c r="E612">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F612" t="s">
         <v>1519</v>
@@ -29335,7 +29335,7 @@
         <v>1516</v>
       </c>
       <c r="E613">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F613" t="s">
         <v>1519</v>
@@ -29370,7 +29370,7 @@
         <v>1516</v>
       </c>
       <c r="E614">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F614" t="s">
         <v>1519</v>
@@ -29405,7 +29405,7 @@
         <v>1516</v>
       </c>
       <c r="E615">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F615" t="s">
         <v>1519</v>
@@ -29440,7 +29440,7 @@
         <v>1516</v>
       </c>
       <c r="E616">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F616" t="s">
         <v>1519</v>
@@ -29475,7 +29475,7 @@
         <v>1516</v>
       </c>
       <c r="E617">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F617" t="s">
         <v>1519</v>
@@ -29510,7 +29510,7 @@
         <v>1516</v>
       </c>
       <c r="E618">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F618" t="s">
         <v>1519</v>
@@ -29545,7 +29545,7 @@
         <v>1516</v>
       </c>
       <c r="E619">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F619" t="s">
         <v>1519</v>
@@ -29583,7 +29583,7 @@
         <v>1516</v>
       </c>
       <c r="E620">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F620" t="s">
         <v>1519</v>
@@ -29618,7 +29618,7 @@
         <v>1516</v>
       </c>
       <c r="E621">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F621" t="s">
         <v>1519</v>
@@ -29653,7 +29653,7 @@
         <v>1516</v>
       </c>
       <c r="E622">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F622" t="s">
         <v>1523</v>
@@ -29688,7 +29688,7 @@
         <v>1517</v>
       </c>
       <c r="E623">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F623" t="s">
         <v>1519</v>
@@ -29723,7 +29723,7 @@
         <v>1517</v>
       </c>
       <c r="E624">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F624" t="s">
         <v>1521</v>
@@ -29761,7 +29761,7 @@
         <v>1517</v>
       </c>
       <c r="E625">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F625" t="s">
         <v>1519</v>
@@ -29796,7 +29796,7 @@
         <v>1517</v>
       </c>
       <c r="E626">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F626" t="s">
         <v>1521</v>
@@ -29834,7 +29834,7 @@
         <v>1517</v>
       </c>
       <c r="E627">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F627" t="s">
         <v>1519</v>
@@ -29869,7 +29869,7 @@
         <v>1518</v>
       </c>
       <c r="E628">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F628" t="s">
         <v>1519</v>
@@ -29904,7 +29904,7 @@
         <v>1518</v>
       </c>
       <c r="E629">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F629" t="s">
         <v>1519</v>
@@ -29939,7 +29939,7 @@
         <v>1518</v>
       </c>
       <c r="E630">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F630" t="s">
         <v>1519</v>
@@ -29974,7 +29974,7 @@
         <v>1518</v>
       </c>
       <c r="E631">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F631" t="s">
         <v>1519</v>
@@ -30009,7 +30009,7 @@
         <v>1518</v>
       </c>
       <c r="E632">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F632" t="s">
         <v>1519</v>
@@ -30044,7 +30044,7 @@
         <v>1518</v>
       </c>
       <c r="E633">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F633" t="s">
         <v>1519</v>
@@ -30079,7 +30079,7 @@
         <v>1518</v>
       </c>
       <c r="E634">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F634" t="s">
         <v>1519</v>

--- a/BacklogGATEAutoCompleto.xlsx
+++ b/BacklogGATEAutoCompleto.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6395" uniqueCount="2476">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6395" uniqueCount="2474">
   <si>
     <t>NUCLEO</t>
   </si>
@@ -7369,9 +7369,6 @@
     <t>ECONOMICIDADE OBRAS,MOBILIDADE E TRANSPORTE</t>
   </si>
   <si>
-    <t>MOBILIDADE E TRANSPORTE,ECONOMICIDADE OBRAS</t>
-  </si>
-  <si>
     <t>PATRIMÔNIO HISTÓRICO E CULTURAL,URBANISMO</t>
   </si>
   <si>
@@ -7405,6 +7402,9 @@
     <t>ENGENHARIA CIVIL,FENOMENOS DE ENERGIA E INFORMAÇÃO</t>
   </si>
   <si>
+    <t>URBANISMO,BIOLOGIA</t>
+  </si>
+  <si>
     <t>ENGENHARIA CIVIL,ENGENHARIA QUÍMICA,FENOMENOS DE ENERGIA E INFORMAÇÃO</t>
   </si>
   <si>
@@ -7414,34 +7414,28 @@
     <t>ENGENHARIA FLORESTAL,URBANISMO</t>
   </si>
   <si>
-    <t>URBANISMO,BIOLOGIA</t>
-  </si>
-  <si>
     <t>FARMÁCIA,SAÚDE</t>
   </si>
   <si>
     <t>BIOLOGIA,ENGENHARIA AMBIENTAL</t>
   </si>
   <si>
-    <t>URBANISMO,ENGENHARIA FLORESTAL</t>
-  </si>
-  <si>
     <t>BIOLOGIA,GEOLOGIA</t>
   </si>
   <si>
-    <t>RECURSOS HÍDRICOS,BIOLOGIA,URBANISMO,MOBILIDADE E TRANSPORTE</t>
+    <t>MOBILIDADE E TRANSPORTE,BIOLOGIA,URBANISMO,RECURSOS HÍDRICOS</t>
   </si>
   <si>
     <t>ENGENHARIA QUÍMICA,RESÍDUOS SÓLIDOS</t>
   </si>
   <si>
-    <t>ENGENHARIA AMBIENTAL,BIOLOGIA</t>
-  </si>
-  <si>
-    <t>ENGENHARIA CIVIL,MOBILIDADE E TRANSPORTE</t>
-  </si>
-  <si>
-    <t>SAÚDE MENTAL,MOBILIDADE E TRANSPORTE,SAÚDE,ASSISTÊNCIA SOCIAL,ORÇAMENTO,AVALIAÇÃO DE IMÓVEIS,PSICOLOGIA,URBANISMO,ECONOMIA,ECONOMICIDADE CONTÁBIL</t>
+    <t>MOBILIDADE E TRANSPORTE,ENGENHARIA CIVIL</t>
+  </si>
+  <si>
+    <t>GEOTECNIA,ENGENHARIA CIVIL</t>
+  </si>
+  <si>
+    <t>MOBILIDADE E TRANSPORTE,SAÚDE MENTAL,ASSISTÊNCIA SOCIAL,AVALIAÇÃO DE IMÓVEIS,URBANISMO,ORÇAMENTO,ECONOMICIDADE CONTÁBIL,ECONOMIA,SAÚDE,PSICOLOGIA</t>
   </si>
 </sst>
 </file>
@@ -19122,7 +19116,7 @@
         <v>2306</v>
       </c>
       <c r="L323" t="s">
-        <v>2451</v>
+        <v>2450</v>
       </c>
     </row>
     <row r="324" spans="1:12">
@@ -19895,7 +19889,7 @@
         <v>2304</v>
       </c>
       <c r="L345" t="s">
-        <v>2452</v>
+        <v>2451</v>
       </c>
     </row>
     <row r="346" spans="1:12">
@@ -19930,7 +19924,7 @@
         <v>2312</v>
       </c>
       <c r="L346" t="s">
-        <v>2453</v>
+        <v>2452</v>
       </c>
     </row>
     <row r="347" spans="1:12">
@@ -20035,7 +20029,7 @@
         <v>2297</v>
       </c>
       <c r="L349" t="s">
-        <v>2454</v>
+        <v>2453</v>
       </c>
     </row>
     <row r="350" spans="1:12">
@@ -20350,7 +20344,7 @@
         <v>2365</v>
       </c>
       <c r="L358" t="s">
-        <v>2455</v>
+        <v>2454</v>
       </c>
     </row>
     <row r="359" spans="1:12">
@@ -20735,7 +20729,7 @@
         <v>2358</v>
       </c>
       <c r="L369" t="s">
-        <v>2456</v>
+        <v>2455</v>
       </c>
     </row>
     <row r="370" spans="1:12">
@@ -20840,7 +20834,7 @@
         <v>2341</v>
       </c>
       <c r="L372" t="s">
-        <v>2457</v>
+        <v>2456</v>
       </c>
     </row>
     <row r="373" spans="1:12">
@@ -20945,7 +20939,7 @@
         <v>2328</v>
       </c>
       <c r="L375" t="s">
-        <v>2458</v>
+        <v>2457</v>
       </c>
     </row>
     <row r="376" spans="1:12">
@@ -21228,7 +21222,7 @@
         <v>2312</v>
       </c>
       <c r="L383" t="s">
-        <v>2453</v>
+        <v>2452</v>
       </c>
     </row>
     <row r="384" spans="1:12">
@@ -21298,7 +21292,7 @@
         <v>2371</v>
       </c>
       <c r="L385" t="s">
-        <v>2456</v>
+        <v>2455</v>
       </c>
     </row>
     <row r="386" spans="1:12">
@@ -21581,7 +21575,7 @@
         <v>2372</v>
       </c>
       <c r="L393" t="s">
-        <v>2456</v>
+        <v>2455</v>
       </c>
     </row>
     <row r="394" spans="1:12">
@@ -21651,7 +21645,7 @@
         <v>2372</v>
       </c>
       <c r="L395" t="s">
-        <v>2456</v>
+        <v>2455</v>
       </c>
     </row>
     <row r="396" spans="1:12">
@@ -22774,7 +22768,7 @@
         <v>2334</v>
       </c>
       <c r="L427" t="s">
-        <v>2459</v>
+        <v>2458</v>
       </c>
     </row>
     <row r="428" spans="1:12">
@@ -22809,7 +22803,7 @@
         <v>2375</v>
       </c>
       <c r="L428" t="s">
-        <v>2459</v>
+        <v>2458</v>
       </c>
     </row>
     <row r="429" spans="1:12">
@@ -22844,7 +22838,7 @@
         <v>2375</v>
       </c>
       <c r="L429" t="s">
-        <v>2459</v>
+        <v>2458</v>
       </c>
     </row>
     <row r="430" spans="1:12">
@@ -22879,7 +22873,7 @@
         <v>2375</v>
       </c>
       <c r="L430" t="s">
-        <v>2459</v>
+        <v>2458</v>
       </c>
     </row>
     <row r="431" spans="1:12">
@@ -22914,7 +22908,7 @@
         <v>2375</v>
       </c>
       <c r="L431" t="s">
-        <v>2459</v>
+        <v>2458</v>
       </c>
     </row>
     <row r="432" spans="1:12">
@@ -22949,7 +22943,7 @@
         <v>2375</v>
       </c>
       <c r="L432" t="s">
-        <v>2459</v>
+        <v>2458</v>
       </c>
     </row>
     <row r="433" spans="1:12">
@@ -22984,7 +22978,7 @@
         <v>2375</v>
       </c>
       <c r="L433" t="s">
-        <v>2459</v>
+        <v>2458</v>
       </c>
     </row>
     <row r="434" spans="1:12">
@@ -23019,7 +23013,7 @@
         <v>2375</v>
       </c>
       <c r="L434" t="s">
-        <v>2459</v>
+        <v>2458</v>
       </c>
     </row>
     <row r="435" spans="1:12">
@@ -23054,7 +23048,7 @@
         <v>2375</v>
       </c>
       <c r="L435" t="s">
-        <v>2459</v>
+        <v>2458</v>
       </c>
     </row>
     <row r="436" spans="1:12">
@@ -23089,7 +23083,7 @@
         <v>2375</v>
       </c>
       <c r="L436" t="s">
-        <v>2459</v>
+        <v>2458</v>
       </c>
     </row>
     <row r="437" spans="1:12">
@@ -23124,7 +23118,7 @@
         <v>2375</v>
       </c>
       <c r="L437" t="s">
-        <v>2459</v>
+        <v>2458</v>
       </c>
     </row>
     <row r="438" spans="1:12">
@@ -23159,7 +23153,7 @@
         <v>2375</v>
       </c>
       <c r="L438" t="s">
-        <v>2459</v>
+        <v>2458</v>
       </c>
     </row>
     <row r="439" spans="1:12">
@@ -23194,7 +23188,7 @@
         <v>2375</v>
       </c>
       <c r="L439" t="s">
-        <v>2459</v>
+        <v>2458</v>
       </c>
     </row>
     <row r="440" spans="1:12">
@@ -23229,7 +23223,7 @@
         <v>2375</v>
       </c>
       <c r="L440" t="s">
-        <v>2459</v>
+        <v>2458</v>
       </c>
     </row>
     <row r="441" spans="1:12">
@@ -23264,7 +23258,7 @@
         <v>2375</v>
       </c>
       <c r="L441" t="s">
-        <v>2459</v>
+        <v>2458</v>
       </c>
     </row>
     <row r="442" spans="1:12">
@@ -23299,7 +23293,7 @@
         <v>2375</v>
       </c>
       <c r="L442" t="s">
-        <v>2459</v>
+        <v>2458</v>
       </c>
     </row>
     <row r="443" spans="1:12">
@@ -23334,7 +23328,7 @@
         <v>2375</v>
       </c>
       <c r="L443" t="s">
-        <v>2459</v>
+        <v>2458</v>
       </c>
     </row>
     <row r="444" spans="1:12">
@@ -23369,7 +23363,7 @@
         <v>2375</v>
       </c>
       <c r="L444" t="s">
-        <v>2459</v>
+        <v>2458</v>
       </c>
     </row>
     <row r="445" spans="1:12">
@@ -23404,7 +23398,7 @@
         <v>2375</v>
       </c>
       <c r="L445" t="s">
-        <v>2459</v>
+        <v>2458</v>
       </c>
     </row>
     <row r="446" spans="1:12">
@@ -23474,7 +23468,7 @@
         <v>2376</v>
       </c>
       <c r="L447" t="s">
-        <v>2456</v>
+        <v>2455</v>
       </c>
     </row>
     <row r="448" spans="1:12">
@@ -23579,7 +23573,7 @@
         <v>2366</v>
       </c>
       <c r="L450" t="s">
-        <v>2460</v>
+        <v>2459</v>
       </c>
     </row>
     <row r="451" spans="1:12">
@@ -23935,7 +23929,7 @@
         <v>2295</v>
       </c>
       <c r="L460" t="s">
-        <v>2461</v>
+        <v>2460</v>
       </c>
     </row>
     <row r="461" spans="1:12">
@@ -23970,7 +23964,7 @@
         <v>2334</v>
       </c>
       <c r="L461" t="s">
-        <v>2462</v>
+        <v>2461</v>
       </c>
     </row>
     <row r="462" spans="1:12">
@@ -24040,7 +24034,7 @@
         <v>2378</v>
       </c>
       <c r="L463" t="s">
-        <v>2456</v>
+        <v>2455</v>
       </c>
     </row>
     <row r="464" spans="1:12">
@@ -24358,7 +24352,7 @@
         <v>2379</v>
       </c>
       <c r="L472" t="s">
-        <v>2456</v>
+        <v>2455</v>
       </c>
     </row>
     <row r="473" spans="1:12">
@@ -24463,7 +24457,7 @@
         <v>2291</v>
       </c>
       <c r="L475" t="s">
-        <v>2447</v>
+        <v>2403</v>
       </c>
     </row>
     <row r="476" spans="1:12">
@@ -24533,7 +24527,7 @@
         <v>2319</v>
       </c>
       <c r="L477" t="s">
-        <v>2431</v>
+        <v>2462</v>
       </c>
     </row>
     <row r="478" spans="1:12">
@@ -24568,7 +24562,7 @@
         <v>2358</v>
       </c>
       <c r="L478" t="s">
-        <v>2456</v>
+        <v>2455</v>
       </c>
     </row>
     <row r="479" spans="1:12">
@@ -24743,7 +24737,7 @@
         <v>2290</v>
       </c>
       <c r="L483" t="s">
-        <v>2462</v>
+        <v>2461</v>
       </c>
     </row>
     <row r="484" spans="1:12">
@@ -24813,7 +24807,7 @@
         <v>2380</v>
       </c>
       <c r="L485" t="s">
-        <v>2456</v>
+        <v>2455</v>
       </c>
     </row>
     <row r="486" spans="1:12">
@@ -25548,7 +25542,7 @@
         <v>2382</v>
       </c>
       <c r="L506" t="s">
-        <v>2466</v>
+        <v>2462</v>
       </c>
     </row>
     <row r="507" spans="1:12">
@@ -25688,7 +25682,7 @@
         <v>2321</v>
       </c>
       <c r="L510" t="s">
-        <v>2467</v>
+        <v>2466</v>
       </c>
     </row>
     <row r="511" spans="1:12">
@@ -26152,7 +26146,7 @@
         <v>2310</v>
       </c>
       <c r="L523" t="s">
-        <v>2466</v>
+        <v>2406</v>
       </c>
     </row>
     <row r="524" spans="1:12">
@@ -26222,7 +26216,7 @@
         <v>2310</v>
       </c>
       <c r="L525" t="s">
-        <v>2468</v>
+        <v>2467</v>
       </c>
     </row>
     <row r="526" spans="1:12">
@@ -26292,7 +26286,7 @@
         <v>2314</v>
       </c>
       <c r="L527" t="s">
-        <v>2460</v>
+        <v>2459</v>
       </c>
     </row>
     <row r="528" spans="1:12">
@@ -26467,7 +26461,7 @@
         <v>2327</v>
       </c>
       <c r="L532" t="s">
-        <v>2459</v>
+        <v>2458</v>
       </c>
     </row>
     <row r="533" spans="1:12">
@@ -26683,7 +26677,7 @@
         <v>2378</v>
       </c>
       <c r="L538" t="s">
-        <v>2456</v>
+        <v>2455</v>
       </c>
     </row>
     <row r="539" spans="1:12">
@@ -26753,7 +26747,7 @@
         <v>2386</v>
       </c>
       <c r="L540" t="s">
-        <v>2454</v>
+        <v>2453</v>
       </c>
     </row>
     <row r="541" spans="1:12">
@@ -27001,7 +26995,7 @@
         <v>2316</v>
       </c>
       <c r="L547" t="s">
-        <v>2469</v>
+        <v>2465</v>
       </c>
     </row>
     <row r="548" spans="1:12">
@@ -27147,7 +27141,7 @@
         <v>2318</v>
       </c>
       <c r="L551" t="s">
-        <v>2470</v>
+        <v>2468</v>
       </c>
     </row>
     <row r="552" spans="1:12">
@@ -27427,7 +27421,7 @@
         <v>2286</v>
       </c>
       <c r="L559" t="s">
-        <v>2471</v>
+        <v>2469</v>
       </c>
     </row>
     <row r="560" spans="1:12">
@@ -27710,7 +27704,7 @@
         <v>2281</v>
       </c>
       <c r="L567" t="s">
-        <v>2472</v>
+        <v>2470</v>
       </c>
     </row>
     <row r="568" spans="1:12">
@@ -28180,7 +28174,7 @@
         <v>2316</v>
       </c>
       <c r="L580" t="s">
-        <v>2454</v>
+        <v>2453</v>
       </c>
     </row>
     <row r="581" spans="1:12">
@@ -28215,7 +28209,7 @@
         <v>2326</v>
       </c>
       <c r="L581" t="s">
-        <v>2459</v>
+        <v>2458</v>
       </c>
     </row>
     <row r="582" spans="1:12">
@@ -28539,7 +28533,7 @@
         <v>2388</v>
       </c>
       <c r="L590" t="s">
-        <v>2456</v>
+        <v>2455</v>
       </c>
     </row>
     <row r="591" spans="1:12">
@@ -28679,7 +28673,7 @@
         <v>2389</v>
       </c>
       <c r="L594" t="s">
-        <v>2456</v>
+        <v>2455</v>
       </c>
     </row>
     <row r="595" spans="1:12">
@@ -28714,7 +28708,7 @@
         <v>2312</v>
       </c>
       <c r="L595" t="s">
-        <v>2473</v>
+        <v>2467</v>
       </c>
     </row>
     <row r="596" spans="1:12">
@@ -28784,7 +28778,7 @@
         <v>2390</v>
       </c>
       <c r="L597" t="s">
-        <v>2474</v>
+        <v>2471</v>
       </c>
     </row>
     <row r="598" spans="1:12">
@@ -28819,7 +28813,7 @@
         <v>2323</v>
       </c>
       <c r="L598" t="s">
-        <v>2459</v>
+        <v>2458</v>
       </c>
     </row>
     <row r="599" spans="1:12">
@@ -28959,7 +28953,7 @@
         <v>2391</v>
       </c>
       <c r="L602" t="s">
-        <v>2459</v>
+        <v>2458</v>
       </c>
     </row>
     <row r="603" spans="1:12">
@@ -28997,7 +28991,7 @@
         <v>2392</v>
       </c>
       <c r="L603" t="s">
-        <v>2459</v>
+        <v>2458</v>
       </c>
     </row>
     <row r="604" spans="1:12">
@@ -29175,7 +29169,7 @@
         <v>2330</v>
       </c>
       <c r="L608" t="s">
-        <v>2459</v>
+        <v>2458</v>
       </c>
     </row>
     <row r="609" spans="1:12">
@@ -29210,7 +29204,7 @@
         <v>2353</v>
       </c>
       <c r="L609" t="s">
-        <v>2459</v>
+        <v>2458</v>
       </c>
     </row>
     <row r="610" spans="1:12">
@@ -30129,7 +30123,7 @@
         <v>2393</v>
       </c>
       <c r="L635" t="s">
-        <v>2412</v>
+        <v>2472</v>
       </c>
     </row>
     <row r="636" spans="1:12">
@@ -30161,7 +30155,7 @@
         <v>2393</v>
       </c>
       <c r="L636" t="s">
-        <v>2475</v>
+        <v>2473</v>
       </c>
     </row>
   </sheetData>

--- a/BacklogGATEAutoCompleto.xlsx
+++ b/BacklogGATEAutoCompleto.xlsx
@@ -7893,7 +7893,7 @@
         <v>1313</v>
       </c>
       <c r="E2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="F2" t="s">
         <v>1524</v>
@@ -7928,7 +7928,7 @@
         <v>1314</v>
       </c>
       <c r="E3">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="F3" t="s">
         <v>1524</v>
@@ -7963,7 +7963,7 @@
         <v>1315</v>
       </c>
       <c r="E4">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="F4" t="s">
         <v>1524</v>
@@ -7998,7 +7998,7 @@
         <v>1316</v>
       </c>
       <c r="E5">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="F5" t="s">
         <v>1524</v>
@@ -8033,7 +8033,7 @@
         <v>1317</v>
       </c>
       <c r="E6">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F6" t="s">
         <v>1524</v>
@@ -8068,7 +8068,7 @@
         <v>1318</v>
       </c>
       <c r="E7">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="F7" t="s">
         <v>1524</v>
@@ -8103,7 +8103,7 @@
         <v>1319</v>
       </c>
       <c r="E8">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="F8" t="s">
         <v>1524</v>
@@ -8138,7 +8138,7 @@
         <v>1319</v>
       </c>
       <c r="E9">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="F9" t="s">
         <v>1524</v>
@@ -8173,7 +8173,7 @@
         <v>1320</v>
       </c>
       <c r="E10">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="F10" t="s">
         <v>1524</v>
@@ -8208,7 +8208,7 @@
         <v>1321</v>
       </c>
       <c r="E11">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="F11" t="s">
         <v>1524</v>
@@ -8243,7 +8243,7 @@
         <v>1322</v>
       </c>
       <c r="E12">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="F12" t="s">
         <v>1524</v>
@@ -8278,7 +8278,7 @@
         <v>1322</v>
       </c>
       <c r="E13">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="F13" t="s">
         <v>1524</v>
@@ -8313,7 +8313,7 @@
         <v>1323</v>
       </c>
       <c r="E14">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="F14" t="s">
         <v>1524</v>
@@ -8348,7 +8348,7 @@
         <v>1323</v>
       </c>
       <c r="E15">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="F15" t="s">
         <v>1524</v>
@@ -8383,7 +8383,7 @@
         <v>1324</v>
       </c>
       <c r="E16">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="F16" t="s">
         <v>1524</v>
@@ -8418,7 +8418,7 @@
         <v>1325</v>
       </c>
       <c r="E17">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="F17" t="s">
         <v>1524</v>
@@ -8453,7 +8453,7 @@
         <v>1326</v>
       </c>
       <c r="E18">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="F18" t="s">
         <v>1524</v>
@@ -8488,7 +8488,7 @@
         <v>1327</v>
       </c>
       <c r="E19">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="F19" t="s">
         <v>1524</v>
@@ -8523,7 +8523,7 @@
         <v>1328</v>
       </c>
       <c r="E20">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F20" t="s">
         <v>1524</v>
@@ -8561,7 +8561,7 @@
         <v>1329</v>
       </c>
       <c r="E21">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F21" t="s">
         <v>1524</v>
@@ -8596,7 +8596,7 @@
         <v>1330</v>
       </c>
       <c r="E22">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="F22" t="s">
         <v>1524</v>
@@ -8631,7 +8631,7 @@
         <v>1331</v>
       </c>
       <c r="E23">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F23" t="s">
         <v>1524</v>
@@ -8666,7 +8666,7 @@
         <v>1332</v>
       </c>
       <c r="E24">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F24" t="s">
         <v>1524</v>
@@ -8701,7 +8701,7 @@
         <v>1333</v>
       </c>
       <c r="E25">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F25" t="s">
         <v>1524</v>
@@ -8736,7 +8736,7 @@
         <v>1334</v>
       </c>
       <c r="E26">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F26" t="s">
         <v>1524</v>
@@ -8771,7 +8771,7 @@
         <v>1335</v>
       </c>
       <c r="E27">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F27" t="s">
         <v>1524</v>
@@ -8806,7 +8806,7 @@
         <v>1336</v>
       </c>
       <c r="E28">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F28" t="s">
         <v>1524</v>
@@ -8841,7 +8841,7 @@
         <v>1337</v>
       </c>
       <c r="E29">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F29" t="s">
         <v>1524</v>
@@ -8876,7 +8876,7 @@
         <v>1338</v>
       </c>
       <c r="E30">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F30" t="s">
         <v>1524</v>
@@ -8911,7 +8911,7 @@
         <v>1339</v>
       </c>
       <c r="E31">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F31" t="s">
         <v>1524</v>
@@ -8946,7 +8946,7 @@
         <v>1340</v>
       </c>
       <c r="E32">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F32" t="s">
         <v>1524</v>
@@ -8981,7 +8981,7 @@
         <v>1341</v>
       </c>
       <c r="E33">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F33" t="s">
         <v>1524</v>
@@ -9016,7 +9016,7 @@
         <v>1341</v>
       </c>
       <c r="E34">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F34" t="s">
         <v>1524</v>
@@ -9051,7 +9051,7 @@
         <v>1342</v>
       </c>
       <c r="E35">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F35" t="s">
         <v>1524</v>
@@ -9086,7 +9086,7 @@
         <v>1343</v>
       </c>
       <c r="E36">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F36" t="s">
         <v>1524</v>
@@ -9121,7 +9121,7 @@
         <v>1343</v>
       </c>
       <c r="E37">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F37" t="s">
         <v>1524</v>
@@ -9156,7 +9156,7 @@
         <v>1344</v>
       </c>
       <c r="E38">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F38" t="s">
         <v>1524</v>
@@ -9191,7 +9191,7 @@
         <v>1344</v>
       </c>
       <c r="E39">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F39" t="s">
         <v>1524</v>
@@ -9226,7 +9226,7 @@
         <v>1345</v>
       </c>
       <c r="E40">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F40" t="s">
         <v>1524</v>
@@ -9261,7 +9261,7 @@
         <v>1346</v>
       </c>
       <c r="E41">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F41" t="s">
         <v>1524</v>
@@ -9296,7 +9296,7 @@
         <v>1347</v>
       </c>
       <c r="E42">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F42" t="s">
         <v>1524</v>
@@ -9331,7 +9331,7 @@
         <v>1348</v>
       </c>
       <c r="E43">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F43" t="s">
         <v>1524</v>
@@ -9366,7 +9366,7 @@
         <v>1349</v>
       </c>
       <c r="E44">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F44" t="s">
         <v>1524</v>
@@ -9401,7 +9401,7 @@
         <v>1350</v>
       </c>
       <c r="E45">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F45" t="s">
         <v>1524</v>
@@ -9436,7 +9436,7 @@
         <v>1351</v>
       </c>
       <c r="E46">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F46" t="s">
         <v>1524</v>
@@ -9471,7 +9471,7 @@
         <v>1352</v>
       </c>
       <c r="E47">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F47" t="s">
         <v>1524</v>
@@ -9506,7 +9506,7 @@
         <v>1353</v>
       </c>
       <c r="E48">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F48" t="s">
         <v>1524</v>
@@ -9541,7 +9541,7 @@
         <v>1354</v>
       </c>
       <c r="E49">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F49" t="s">
         <v>1524</v>
@@ -9576,7 +9576,7 @@
         <v>1355</v>
       </c>
       <c r="E50">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F50" t="s">
         <v>1524</v>
@@ -9611,7 +9611,7 @@
         <v>1355</v>
       </c>
       <c r="E51">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F51" t="s">
         <v>1524</v>
@@ -9646,7 +9646,7 @@
         <v>1355</v>
       </c>
       <c r="E52">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F52" t="s">
         <v>1524</v>
@@ -9681,7 +9681,7 @@
         <v>1356</v>
       </c>
       <c r="E53">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F53" t="s">
         <v>1524</v>
@@ -9716,7 +9716,7 @@
         <v>1357</v>
       </c>
       <c r="E54">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F54" t="s">
         <v>1524</v>
@@ -9751,7 +9751,7 @@
         <v>1358</v>
       </c>
       <c r="E55">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F55" t="s">
         <v>1524</v>
@@ -9786,7 +9786,7 @@
         <v>1359</v>
       </c>
       <c r="E56">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F56" t="s">
         <v>1524</v>
@@ -9821,7 +9821,7 @@
         <v>1360</v>
       </c>
       <c r="E57">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F57" t="s">
         <v>1524</v>
@@ -9856,7 +9856,7 @@
         <v>1360</v>
       </c>
       <c r="E58">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F58" t="s">
         <v>1524</v>
@@ -9891,7 +9891,7 @@
         <v>1361</v>
       </c>
       <c r="E59">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F59" t="s">
         <v>1524</v>
@@ -9926,7 +9926,7 @@
         <v>1362</v>
       </c>
       <c r="E60">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F60" t="s">
         <v>1524</v>
@@ -9961,7 +9961,7 @@
         <v>1362</v>
       </c>
       <c r="E61">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F61" t="s">
         <v>1524</v>
@@ -9996,7 +9996,7 @@
         <v>1362</v>
       </c>
       <c r="E62">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F62" t="s">
         <v>1525</v>
@@ -10031,7 +10031,7 @@
         <v>1362</v>
       </c>
       <c r="E63">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F63" t="s">
         <v>1524</v>
@@ -10066,7 +10066,7 @@
         <v>1363</v>
       </c>
       <c r="E64">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F64" t="s">
         <v>1524</v>
@@ -10101,7 +10101,7 @@
         <v>1364</v>
       </c>
       <c r="E65">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F65" t="s">
         <v>1524</v>
@@ -10136,7 +10136,7 @@
         <v>1364</v>
       </c>
       <c r="E66">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F66" t="s">
         <v>1524</v>
@@ -10171,7 +10171,7 @@
         <v>1365</v>
       </c>
       <c r="E67">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F67" t="s">
         <v>1524</v>
@@ -10206,7 +10206,7 @@
         <v>1366</v>
       </c>
       <c r="E68">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F68" t="s">
         <v>1524</v>
@@ -10241,7 +10241,7 @@
         <v>1367</v>
       </c>
       <c r="E69">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F69" t="s">
         <v>1524</v>
@@ -10276,7 +10276,7 @@
         <v>1368</v>
       </c>
       <c r="E70">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F70" t="s">
         <v>1524</v>
@@ -10311,7 +10311,7 @@
         <v>1368</v>
       </c>
       <c r="E71">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F71" t="s">
         <v>1524</v>
@@ -10346,7 +10346,7 @@
         <v>1368</v>
       </c>
       <c r="E72">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F72" t="s">
         <v>1524</v>
@@ -10381,7 +10381,7 @@
         <v>1368</v>
       </c>
       <c r="E73">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F73" t="s">
         <v>1524</v>
@@ -10416,7 +10416,7 @@
         <v>1368</v>
       </c>
       <c r="E74">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F74" t="s">
         <v>1524</v>
@@ -10451,7 +10451,7 @@
         <v>1368</v>
       </c>
       <c r="E75">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F75" t="s">
         <v>1524</v>
@@ -10486,7 +10486,7 @@
         <v>1369</v>
       </c>
       <c r="E76">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F76" t="s">
         <v>1524</v>
@@ -10521,7 +10521,7 @@
         <v>1370</v>
       </c>
       <c r="E77">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F77" t="s">
         <v>1524</v>
@@ -10556,7 +10556,7 @@
         <v>1371</v>
       </c>
       <c r="E78">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F78" t="s">
         <v>1524</v>
@@ -10591,7 +10591,7 @@
         <v>1371</v>
       </c>
       <c r="E79">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F79" t="s">
         <v>1524</v>
@@ -10626,7 +10626,7 @@
         <v>1372</v>
       </c>
       <c r="E80">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F80" t="s">
         <v>1526</v>
@@ -10661,7 +10661,7 @@
         <v>1373</v>
       </c>
       <c r="E81">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F81" t="s">
         <v>1524</v>
@@ -10696,7 +10696,7 @@
         <v>1374</v>
       </c>
       <c r="E82">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F82" t="s">
         <v>1524</v>
@@ -10731,7 +10731,7 @@
         <v>1375</v>
       </c>
       <c r="E83">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F83" t="s">
         <v>1524</v>
@@ -10766,7 +10766,7 @@
         <v>1376</v>
       </c>
       <c r="E84">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F84" t="s">
         <v>1524</v>
@@ -10801,7 +10801,7 @@
         <v>1377</v>
       </c>
       <c r="E85">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F85" t="s">
         <v>1524</v>
@@ -10836,7 +10836,7 @@
         <v>1378</v>
       </c>
       <c r="E86">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F86" t="s">
         <v>1524</v>
@@ -10871,7 +10871,7 @@
         <v>1379</v>
       </c>
       <c r="E87">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F87" t="s">
         <v>1524</v>
@@ -10906,7 +10906,7 @@
         <v>1379</v>
       </c>
       <c r="E88">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F88" t="s">
         <v>1524</v>
@@ -10941,7 +10941,7 @@
         <v>1380</v>
       </c>
       <c r="E89">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F89" t="s">
         <v>1524</v>
@@ -10976,7 +10976,7 @@
         <v>1380</v>
       </c>
       <c r="E90">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F90" t="s">
         <v>1524</v>
@@ -11011,7 +11011,7 @@
         <v>1380</v>
       </c>
       <c r="E91">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F91" t="s">
         <v>1524</v>
@@ -11046,7 +11046,7 @@
         <v>1381</v>
       </c>
       <c r="E92">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F92" t="s">
         <v>1524</v>
@@ -11081,7 +11081,7 @@
         <v>1381</v>
       </c>
       <c r="E93">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F93" t="s">
         <v>1524</v>
@@ -11116,7 +11116,7 @@
         <v>1382</v>
       </c>
       <c r="E94">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F94" t="s">
         <v>1524</v>
@@ -11151,7 +11151,7 @@
         <v>1383</v>
       </c>
       <c r="E95">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F95" t="s">
         <v>1524</v>
@@ -11186,7 +11186,7 @@
         <v>1384</v>
       </c>
       <c r="E96">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F96" t="s">
         <v>1524</v>
@@ -11221,7 +11221,7 @@
         <v>1384</v>
       </c>
       <c r="E97">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F97" t="s">
         <v>1524</v>
@@ -11256,7 +11256,7 @@
         <v>1385</v>
       </c>
       <c r="E98">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F98" t="s">
         <v>1524</v>
@@ -11291,7 +11291,7 @@
         <v>1385</v>
       </c>
       <c r="E99">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F99" t="s">
         <v>1524</v>
@@ -11326,7 +11326,7 @@
         <v>1386</v>
       </c>
       <c r="E100">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F100" t="s">
         <v>1524</v>
@@ -11361,7 +11361,7 @@
         <v>1387</v>
       </c>
       <c r="E101">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F101" t="s">
         <v>1524</v>
@@ -11396,7 +11396,7 @@
         <v>1387</v>
       </c>
       <c r="E102">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F102" t="s">
         <v>1524</v>
@@ -11431,7 +11431,7 @@
         <v>1388</v>
       </c>
       <c r="E103">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F103" t="s">
         <v>1524</v>
@@ -11466,7 +11466,7 @@
         <v>1389</v>
       </c>
       <c r="E104">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F104" t="s">
         <v>1524</v>
@@ -11501,7 +11501,7 @@
         <v>1389</v>
       </c>
       <c r="E105">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F105" t="s">
         <v>1524</v>
@@ -11536,7 +11536,7 @@
         <v>1390</v>
       </c>
       <c r="E106">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F106" t="s">
         <v>1524</v>
@@ -11571,7 +11571,7 @@
         <v>1391</v>
       </c>
       <c r="E107">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F107" t="s">
         <v>1524</v>
@@ -11609,7 +11609,7 @@
         <v>1391</v>
       </c>
       <c r="E108">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F108" t="s">
         <v>1524</v>
@@ -11644,7 +11644,7 @@
         <v>1391</v>
       </c>
       <c r="E109">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F109" t="s">
         <v>1524</v>
@@ -11679,7 +11679,7 @@
         <v>1391</v>
       </c>
       <c r="E110">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F110" t="s">
         <v>1524</v>
@@ -11714,7 +11714,7 @@
         <v>1392</v>
       </c>
       <c r="E111">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F111" t="s">
         <v>1525</v>
@@ -11749,7 +11749,7 @@
         <v>1393</v>
       </c>
       <c r="E112">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F112" t="s">
         <v>1524</v>
@@ -11784,7 +11784,7 @@
         <v>1393</v>
       </c>
       <c r="E113">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F113" t="s">
         <v>1524</v>
@@ -11819,7 +11819,7 @@
         <v>1393</v>
       </c>
       <c r="E114">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F114" t="s">
         <v>1524</v>
@@ -11854,7 +11854,7 @@
         <v>1393</v>
       </c>
       <c r="E115">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F115" t="s">
         <v>1524</v>
@@ -11889,7 +11889,7 @@
         <v>1394</v>
       </c>
       <c r="E116">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F116" t="s">
         <v>1524</v>
@@ -11924,7 +11924,7 @@
         <v>1394</v>
       </c>
       <c r="E117">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F117" t="s">
         <v>1524</v>
@@ -11959,7 +11959,7 @@
         <v>1394</v>
       </c>
       <c r="E118">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F118" t="s">
         <v>1524</v>
@@ -11994,7 +11994,7 @@
         <v>1394</v>
       </c>
       <c r="E119">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F119" t="s">
         <v>1524</v>
@@ -12029,7 +12029,7 @@
         <v>1394</v>
       </c>
       <c r="E120">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F120" t="s">
         <v>1524</v>
@@ -12064,7 +12064,7 @@
         <v>1394</v>
       </c>
       <c r="E121">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F121" t="s">
         <v>1524</v>
@@ -12099,7 +12099,7 @@
         <v>1394</v>
       </c>
       <c r="E122">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F122" t="s">
         <v>1524</v>
@@ -12134,7 +12134,7 @@
         <v>1395</v>
       </c>
       <c r="E123">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F123" t="s">
         <v>1524</v>
@@ -12169,7 +12169,7 @@
         <v>1396</v>
       </c>
       <c r="E124">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F124" t="s">
         <v>1524</v>
@@ -12204,7 +12204,7 @@
         <v>1397</v>
       </c>
       <c r="E125">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F125" t="s">
         <v>1524</v>
@@ -12239,7 +12239,7 @@
         <v>1397</v>
       </c>
       <c r="E126">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F126" t="s">
         <v>1524</v>
@@ -12274,7 +12274,7 @@
         <v>1397</v>
       </c>
       <c r="E127">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F127" t="s">
         <v>1524</v>
@@ -12309,7 +12309,7 @@
         <v>1398</v>
       </c>
       <c r="E128">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F128" t="s">
         <v>1524</v>
@@ -12344,7 +12344,7 @@
         <v>1398</v>
       </c>
       <c r="E129">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F129" t="s">
         <v>1524</v>
@@ -12379,7 +12379,7 @@
         <v>1398</v>
       </c>
       <c r="E130">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F130" t="s">
         <v>1524</v>
@@ -12414,7 +12414,7 @@
         <v>1398</v>
       </c>
       <c r="E131">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F131" t="s">
         <v>1524</v>
@@ -12449,7 +12449,7 @@
         <v>1398</v>
       </c>
       <c r="E132">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F132" t="s">
         <v>1524</v>
@@ -12484,7 +12484,7 @@
         <v>1398</v>
       </c>
       <c r="E133">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F133" t="s">
         <v>1524</v>
@@ -12519,7 +12519,7 @@
         <v>1398</v>
       </c>
       <c r="E134">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F134" t="s">
         <v>1524</v>
@@ -12554,7 +12554,7 @@
         <v>1398</v>
       </c>
       <c r="E135">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F135" t="s">
         <v>1524</v>
@@ -12589,7 +12589,7 @@
         <v>1398</v>
       </c>
       <c r="E136">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F136" t="s">
         <v>1524</v>
@@ -12624,7 +12624,7 @@
         <v>1399</v>
       </c>
       <c r="E137">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F137" t="s">
         <v>1524</v>
@@ -12659,7 +12659,7 @@
         <v>1399</v>
       </c>
       <c r="E138">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F138" t="s">
         <v>1524</v>
@@ -12694,7 +12694,7 @@
         <v>1399</v>
       </c>
       <c r="E139">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F139" t="s">
         <v>1524</v>
@@ -12729,7 +12729,7 @@
         <v>1400</v>
       </c>
       <c r="E140">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F140" t="s">
         <v>1524</v>
@@ -12764,7 +12764,7 @@
         <v>1400</v>
       </c>
       <c r="E141">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F141" t="s">
         <v>1525</v>
@@ -12799,7 +12799,7 @@
         <v>1400</v>
       </c>
       <c r="E142">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F142" t="s">
         <v>1524</v>
@@ -12834,7 +12834,7 @@
         <v>1401</v>
       </c>
       <c r="E143">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F143" t="s">
         <v>1524</v>
@@ -12869,7 +12869,7 @@
         <v>1401</v>
       </c>
       <c r="E144">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F144" t="s">
         <v>1524</v>
@@ -12904,7 +12904,7 @@
         <v>1402</v>
       </c>
       <c r="E145">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F145" t="s">
         <v>1524</v>
@@ -12939,7 +12939,7 @@
         <v>1402</v>
       </c>
       <c r="E146">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F146" t="s">
         <v>1524</v>
@@ -12974,7 +12974,7 @@
         <v>1403</v>
       </c>
       <c r="E147">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F147" t="s">
         <v>1524</v>
@@ -13009,7 +13009,7 @@
         <v>1403</v>
       </c>
       <c r="E148">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F148" t="s">
         <v>1524</v>
@@ -13044,7 +13044,7 @@
         <v>1404</v>
       </c>
       <c r="E149">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F149" t="s">
         <v>1524</v>
@@ -13079,7 +13079,7 @@
         <v>1404</v>
       </c>
       <c r="E150">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F150" t="s">
         <v>1524</v>
@@ -13114,7 +13114,7 @@
         <v>1404</v>
       </c>
       <c r="E151">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F151" t="s">
         <v>1524</v>
@@ -13149,7 +13149,7 @@
         <v>1405</v>
       </c>
       <c r="E152">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F152" t="s">
         <v>1524</v>
@@ -13184,7 +13184,7 @@
         <v>1405</v>
       </c>
       <c r="E153">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F153" t="s">
         <v>1524</v>
@@ -13219,7 +13219,7 @@
         <v>1406</v>
       </c>
       <c r="E154">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F154" t="s">
         <v>1524</v>
@@ -13254,7 +13254,7 @@
         <v>1407</v>
       </c>
       <c r="E155">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F155" t="s">
         <v>1524</v>
@@ -13289,7 +13289,7 @@
         <v>1407</v>
       </c>
       <c r="E156">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F156" t="s">
         <v>1524</v>
@@ -13324,7 +13324,7 @@
         <v>1407</v>
       </c>
       <c r="E157">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F157" t="s">
         <v>1524</v>
@@ -13359,7 +13359,7 @@
         <v>1407</v>
       </c>
       <c r="E158">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F158" t="s">
         <v>1524</v>
@@ -13394,7 +13394,7 @@
         <v>1408</v>
       </c>
       <c r="E159">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F159" t="s">
         <v>1524</v>
@@ -13429,7 +13429,7 @@
         <v>1409</v>
       </c>
       <c r="E160">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F160" t="s">
         <v>1524</v>
@@ -13464,7 +13464,7 @@
         <v>1409</v>
       </c>
       <c r="E161">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F161" t="s">
         <v>1524</v>
@@ -13499,7 +13499,7 @@
         <v>1409</v>
       </c>
       <c r="E162">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F162" t="s">
         <v>1524</v>
@@ -13534,7 +13534,7 @@
         <v>1409</v>
       </c>
       <c r="E163">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F163" t="s">
         <v>1524</v>
@@ -13569,7 +13569,7 @@
         <v>1409</v>
       </c>
       <c r="E164">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F164" t="s">
         <v>1524</v>
@@ -13604,7 +13604,7 @@
         <v>1410</v>
       </c>
       <c r="E165">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F165" t="s">
         <v>1524</v>
@@ -13639,7 +13639,7 @@
         <v>1410</v>
       </c>
       <c r="E166">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F166" t="s">
         <v>1524</v>
@@ -13674,7 +13674,7 @@
         <v>1410</v>
       </c>
       <c r="E167">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F167" t="s">
         <v>1524</v>
@@ -13709,7 +13709,7 @@
         <v>1410</v>
       </c>
       <c r="E168">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F168" t="s">
         <v>1524</v>
@@ -13744,7 +13744,7 @@
         <v>1410</v>
       </c>
       <c r="E169">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F169" t="s">
         <v>1524</v>
@@ -13779,7 +13779,7 @@
         <v>1410</v>
       </c>
       <c r="E170">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F170" t="s">
         <v>1524</v>
@@ -13814,7 +13814,7 @@
         <v>1411</v>
       </c>
       <c r="E171">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F171" t="s">
         <v>1524</v>
@@ -13849,7 +13849,7 @@
         <v>1411</v>
       </c>
       <c r="E172">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F172" t="s">
         <v>1524</v>
@@ -13884,7 +13884,7 @@
         <v>1411</v>
       </c>
       <c r="E173">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F173" t="s">
         <v>1524</v>
@@ -13919,7 +13919,7 @@
         <v>1412</v>
       </c>
       <c r="E174">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F174" t="s">
         <v>1524</v>
@@ -13954,7 +13954,7 @@
         <v>1412</v>
       </c>
       <c r="E175">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F175" t="s">
         <v>1524</v>
@@ -13989,7 +13989,7 @@
         <v>1413</v>
       </c>
       <c r="E176">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F176" t="s">
         <v>1524</v>
@@ -14024,7 +14024,7 @@
         <v>1414</v>
       </c>
       <c r="E177">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F177" t="s">
         <v>1524</v>
@@ -14059,7 +14059,7 @@
         <v>1414</v>
       </c>
       <c r="E178">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F178" t="s">
         <v>1524</v>
@@ -14094,7 +14094,7 @@
         <v>1415</v>
       </c>
       <c r="E179">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F179" t="s">
         <v>1524</v>
@@ -14129,7 +14129,7 @@
         <v>1416</v>
       </c>
       <c r="E180">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F180" t="s">
         <v>1524</v>
@@ -14164,7 +14164,7 @@
         <v>1416</v>
       </c>
       <c r="E181">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F181" t="s">
         <v>1524</v>
@@ -14199,7 +14199,7 @@
         <v>1417</v>
       </c>
       <c r="E182">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F182" t="s">
         <v>1524</v>
@@ -14234,7 +14234,7 @@
         <v>1417</v>
       </c>
       <c r="E183">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F183" t="s">
         <v>1524</v>
@@ -14269,7 +14269,7 @@
         <v>1418</v>
       </c>
       <c r="E184">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F184" t="s">
         <v>1524</v>
@@ -14304,7 +14304,7 @@
         <v>1418</v>
       </c>
       <c r="E185">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F185" t="s">
         <v>1524</v>
@@ -14339,7 +14339,7 @@
         <v>1418</v>
       </c>
       <c r="E186">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F186" t="s">
         <v>1524</v>
@@ -14374,7 +14374,7 @@
         <v>1419</v>
       </c>
       <c r="E187">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F187" t="s">
         <v>1524</v>
@@ -14409,7 +14409,7 @@
         <v>1419</v>
       </c>
       <c r="E188">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F188" t="s">
         <v>1524</v>
@@ -14444,7 +14444,7 @@
         <v>1420</v>
       </c>
       <c r="E189">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F189" t="s">
         <v>1524</v>
@@ -14479,7 +14479,7 @@
         <v>1421</v>
       </c>
       <c r="E190">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F190" t="s">
         <v>1524</v>
@@ -14514,7 +14514,7 @@
         <v>1421</v>
       </c>
       <c r="E191">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F191" t="s">
         <v>1524</v>
@@ -14549,7 +14549,7 @@
         <v>1421</v>
       </c>
       <c r="E192">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F192" t="s">
         <v>1524</v>
@@ -14584,7 +14584,7 @@
         <v>1422</v>
       </c>
       <c r="E193">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F193" t="s">
         <v>1524</v>
@@ -14619,7 +14619,7 @@
         <v>1422</v>
       </c>
       <c r="E194">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F194" t="s">
         <v>1524</v>
@@ -14654,7 +14654,7 @@
         <v>1423</v>
       </c>
       <c r="E195">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F195" t="s">
         <v>1524</v>
@@ -14689,7 +14689,7 @@
         <v>1423</v>
       </c>
       <c r="E196">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F196" t="s">
         <v>1526</v>
@@ -14724,7 +14724,7 @@
         <v>1423</v>
       </c>
       <c r="E197">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F197" t="s">
         <v>1524</v>
@@ -14759,7 +14759,7 @@
         <v>1424</v>
       </c>
       <c r="E198">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F198" t="s">
         <v>1524</v>
@@ -14794,7 +14794,7 @@
         <v>1424</v>
       </c>
       <c r="E199">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F199" t="s">
         <v>1524</v>
@@ -14832,7 +14832,7 @@
         <v>1424</v>
       </c>
       <c r="E200">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F200" t="s">
         <v>1524</v>
@@ -14867,7 +14867,7 @@
         <v>1424</v>
       </c>
       <c r="E201">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F201" t="s">
         <v>1524</v>
@@ -14902,7 +14902,7 @@
         <v>1424</v>
       </c>
       <c r="E202">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F202" t="s">
         <v>1524</v>
@@ -14937,7 +14937,7 @@
         <v>1424</v>
       </c>
       <c r="E203">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F203" t="s">
         <v>1524</v>
@@ -14972,7 +14972,7 @@
         <v>1425</v>
       </c>
       <c r="E204">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F204" t="s">
         <v>1524</v>
@@ -15007,7 +15007,7 @@
         <v>1425</v>
       </c>
       <c r="E205">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F205" t="s">
         <v>1524</v>
@@ -15042,7 +15042,7 @@
         <v>1425</v>
       </c>
       <c r="E206">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F206" t="s">
         <v>1524</v>
@@ -15077,7 +15077,7 @@
         <v>1426</v>
       </c>
       <c r="E207">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F207" t="s">
         <v>1524</v>
@@ -15112,7 +15112,7 @@
         <v>1426</v>
       </c>
       <c r="E208">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F208" t="s">
         <v>1524</v>
@@ -15147,7 +15147,7 @@
         <v>1426</v>
       </c>
       <c r="E209">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F209" t="s">
         <v>1524</v>
@@ -15182,7 +15182,7 @@
         <v>1427</v>
       </c>
       <c r="E210">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F210" t="s">
         <v>1524</v>
@@ -15217,7 +15217,7 @@
         <v>1427</v>
       </c>
       <c r="E211">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F211" t="s">
         <v>1524</v>
@@ -15252,7 +15252,7 @@
         <v>1427</v>
       </c>
       <c r="E212">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F212" t="s">
         <v>1524</v>
@@ -15287,7 +15287,7 @@
         <v>1428</v>
       </c>
       <c r="E213">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F213" t="s">
         <v>1524</v>
@@ -15322,7 +15322,7 @@
         <v>1428</v>
       </c>
       <c r="E214">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F214" t="s">
         <v>1524</v>
@@ -15357,7 +15357,7 @@
         <v>1428</v>
       </c>
       <c r="E215">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F215" t="s">
         <v>1524</v>
@@ -15392,7 +15392,7 @@
         <v>1428</v>
       </c>
       <c r="E216">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F216" t="s">
         <v>1524</v>
@@ -15427,7 +15427,7 @@
         <v>1428</v>
       </c>
       <c r="E217">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F217" t="s">
         <v>1524</v>
@@ -15462,7 +15462,7 @@
         <v>1428</v>
       </c>
       <c r="E218">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F218" t="s">
         <v>1524</v>
@@ -15497,7 +15497,7 @@
         <v>1429</v>
       </c>
       <c r="E219">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F219" t="s">
         <v>1524</v>
@@ -15532,7 +15532,7 @@
         <v>1430</v>
       </c>
       <c r="E220">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F220" t="s">
         <v>1524</v>
@@ -15567,7 +15567,7 @@
         <v>1430</v>
       </c>
       <c r="E221">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F221" t="s">
         <v>1527</v>
@@ -15602,7 +15602,7 @@
         <v>1430</v>
       </c>
       <c r="E222">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F222" t="s">
         <v>1524</v>
@@ -15637,7 +15637,7 @@
         <v>1430</v>
       </c>
       <c r="E223">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F223" t="s">
         <v>1524</v>
@@ -15672,7 +15672,7 @@
         <v>1430</v>
       </c>
       <c r="E224">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F224" t="s">
         <v>1524</v>
@@ -15707,7 +15707,7 @@
         <v>1431</v>
       </c>
       <c r="E225">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F225" t="s">
         <v>1524</v>
@@ -15742,7 +15742,7 @@
         <v>1431</v>
       </c>
       <c r="E226">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F226" t="s">
         <v>1524</v>
@@ -15777,7 +15777,7 @@
         <v>1431</v>
       </c>
       <c r="E227">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F227" t="s">
         <v>1524</v>
@@ -15812,7 +15812,7 @@
         <v>1431</v>
       </c>
       <c r="E228">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F228" t="s">
         <v>1524</v>
@@ -15847,7 +15847,7 @@
         <v>1432</v>
       </c>
       <c r="E229">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F229" t="s">
         <v>1524</v>
@@ -15882,7 +15882,7 @@
         <v>1433</v>
       </c>
       <c r="E230">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F230" t="s">
         <v>1524</v>
@@ -15920,7 +15920,7 @@
         <v>1434</v>
       </c>
       <c r="E231">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F231" t="s">
         <v>1524</v>
@@ -15955,7 +15955,7 @@
         <v>1434</v>
       </c>
       <c r="E232">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F232" t="s">
         <v>1524</v>
@@ -15990,7 +15990,7 @@
         <v>1434</v>
       </c>
       <c r="E233">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F233" t="s">
         <v>1524</v>
@@ -16025,7 +16025,7 @@
         <v>1434</v>
       </c>
       <c r="E234">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F234" t="s">
         <v>1524</v>
@@ -16060,7 +16060,7 @@
         <v>1435</v>
       </c>
       <c r="E235">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F235" t="s">
         <v>1524</v>
@@ -16095,7 +16095,7 @@
         <v>1435</v>
       </c>
       <c r="E236">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F236" t="s">
         <v>1524</v>
@@ -16130,7 +16130,7 @@
         <v>1436</v>
       </c>
       <c r="E237">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F237" t="s">
         <v>1524</v>
@@ -16165,7 +16165,7 @@
         <v>1436</v>
       </c>
       <c r="E238">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F238" t="s">
         <v>1524</v>
@@ -16200,7 +16200,7 @@
         <v>1437</v>
       </c>
       <c r="E239">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F239" t="s">
         <v>1524</v>
@@ -16235,7 +16235,7 @@
         <v>1437</v>
       </c>
       <c r="E240">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F240" t="s">
         <v>1524</v>
@@ -16270,7 +16270,7 @@
         <v>1437</v>
       </c>
       <c r="E241">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F241" t="s">
         <v>1524</v>
@@ -16305,7 +16305,7 @@
         <v>1438</v>
       </c>
       <c r="E242">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F242" t="s">
         <v>1524</v>
@@ -16340,7 +16340,7 @@
         <v>1438</v>
       </c>
       <c r="E243">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F243" t="s">
         <v>1524</v>
@@ -16375,7 +16375,7 @@
         <v>1438</v>
       </c>
       <c r="E244">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F244" t="s">
         <v>1524</v>
@@ -16410,7 +16410,7 @@
         <v>1439</v>
       </c>
       <c r="E245">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F245" t="s">
         <v>1524</v>
@@ -16445,7 +16445,7 @@
         <v>1440</v>
       </c>
       <c r="E246">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F246" t="s">
         <v>1524</v>
@@ -16480,7 +16480,7 @@
         <v>1440</v>
       </c>
       <c r="E247">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F247" t="s">
         <v>1524</v>
@@ -16515,7 +16515,7 @@
         <v>1440</v>
       </c>
       <c r="E248">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F248" t="s">
         <v>1524</v>
@@ -16550,7 +16550,7 @@
         <v>1440</v>
       </c>
       <c r="E249">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F249" t="s">
         <v>1524</v>
@@ -16585,7 +16585,7 @@
         <v>1441</v>
       </c>
       <c r="E250">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F250" t="s">
         <v>1524</v>
@@ -16620,7 +16620,7 @@
         <v>1441</v>
       </c>
       <c r="E251">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F251" t="s">
         <v>1524</v>
@@ -16655,7 +16655,7 @@
         <v>1441</v>
       </c>
       <c r="E252">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F252" t="s">
         <v>1524</v>
@@ -16690,7 +16690,7 @@
         <v>1442</v>
       </c>
       <c r="E253">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F253" t="s">
         <v>1524</v>
@@ -16725,7 +16725,7 @@
         <v>1442</v>
       </c>
       <c r="E254">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F254" t="s">
         <v>1524</v>
@@ -16760,7 +16760,7 @@
         <v>1443</v>
       </c>
       <c r="E255">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F255" t="s">
         <v>1524</v>
@@ -16795,7 +16795,7 @@
         <v>1443</v>
       </c>
       <c r="E256">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F256" t="s">
         <v>1524</v>
@@ -16830,7 +16830,7 @@
         <v>1443</v>
       </c>
       <c r="E257">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F257" t="s">
         <v>1524</v>
@@ -16865,7 +16865,7 @@
         <v>1443</v>
       </c>
       <c r="E258">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F258" t="s">
         <v>1524</v>
@@ -16900,7 +16900,7 @@
         <v>1443</v>
       </c>
       <c r="E259">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F259" t="s">
         <v>1524</v>
@@ -16935,7 +16935,7 @@
         <v>1444</v>
       </c>
       <c r="E260">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F260" t="s">
         <v>1524</v>
@@ -16970,7 +16970,7 @@
         <v>1444</v>
       </c>
       <c r="E261">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F261" t="s">
         <v>1524</v>
@@ -17005,7 +17005,7 @@
         <v>1444</v>
       </c>
       <c r="E262">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F262" t="s">
         <v>1524</v>
@@ -17040,7 +17040,7 @@
         <v>1445</v>
       </c>
       <c r="E263">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F263" t="s">
         <v>1524</v>
@@ -17075,7 +17075,7 @@
         <v>1446</v>
       </c>
       <c r="E264">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F264" t="s">
         <v>1524</v>
@@ -17110,7 +17110,7 @@
         <v>1447</v>
       </c>
       <c r="E265">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F265" t="s">
         <v>1524</v>
@@ -17145,7 +17145,7 @@
         <v>1447</v>
       </c>
       <c r="E266">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F266" t="s">
         <v>1524</v>
@@ -17180,7 +17180,7 @@
         <v>1447</v>
       </c>
       <c r="E267">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F267" t="s">
         <v>1524</v>
@@ -17215,7 +17215,7 @@
         <v>1447</v>
       </c>
       <c r="E268">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F268" t="s">
         <v>1524</v>
@@ -17250,7 +17250,7 @@
         <v>1447</v>
       </c>
       <c r="E269">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F269" t="s">
         <v>1524</v>
@@ -17285,7 +17285,7 @@
         <v>1448</v>
       </c>
       <c r="E270">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F270" t="s">
         <v>1524</v>
@@ -17320,7 +17320,7 @@
         <v>1448</v>
       </c>
       <c r="E271">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F271" t="s">
         <v>1524</v>
@@ -17355,7 +17355,7 @@
         <v>1449</v>
       </c>
       <c r="E272">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F272" t="s">
         <v>1524</v>
@@ -17390,7 +17390,7 @@
         <v>1449</v>
       </c>
       <c r="E273">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F273" t="s">
         <v>1524</v>
@@ -17425,7 +17425,7 @@
         <v>1450</v>
       </c>
       <c r="E274">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F274" t="s">
         <v>1524</v>
@@ -17460,7 +17460,7 @@
         <v>1451</v>
       </c>
       <c r="E275">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F275" t="s">
         <v>1524</v>
@@ -17495,7 +17495,7 @@
         <v>1452</v>
       </c>
       <c r="E276">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F276" t="s">
         <v>1524</v>
@@ -17530,7 +17530,7 @@
         <v>1452</v>
       </c>
       <c r="E277">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F277" t="s">
         <v>1524</v>
@@ -17565,7 +17565,7 @@
         <v>1453</v>
       </c>
       <c r="E278">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F278" t="s">
         <v>1524</v>
@@ -17600,7 +17600,7 @@
         <v>1453</v>
       </c>
       <c r="E279">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F279" t="s">
         <v>1524</v>
@@ -17635,7 +17635,7 @@
         <v>1453</v>
       </c>
       <c r="E280">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F280" t="s">
         <v>1524</v>
@@ -17670,7 +17670,7 @@
         <v>1454</v>
       </c>
       <c r="E281">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F281" t="s">
         <v>1524</v>
@@ -17705,7 +17705,7 @@
         <v>1454</v>
       </c>
       <c r="E282">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F282" t="s">
         <v>1524</v>
@@ -17740,7 +17740,7 @@
         <v>1454</v>
       </c>
       <c r="E283">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F283" t="s">
         <v>1524</v>
@@ -17775,7 +17775,7 @@
         <v>1454</v>
       </c>
       <c r="E284">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F284" t="s">
         <v>1524</v>
@@ -17810,7 +17810,7 @@
         <v>1454</v>
       </c>
       <c r="E285">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F285" t="s">
         <v>1524</v>
@@ -17845,7 +17845,7 @@
         <v>1454</v>
       </c>
       <c r="E286">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F286" t="s">
         <v>1524</v>
@@ -17880,7 +17880,7 @@
         <v>1454</v>
       </c>
       <c r="E287">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F287" t="s">
         <v>1524</v>
@@ -17915,7 +17915,7 @@
         <v>1454</v>
       </c>
       <c r="E288">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F288" t="s">
         <v>1524</v>
@@ -17950,7 +17950,7 @@
         <v>1454</v>
       </c>
       <c r="E289">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F289" t="s">
         <v>1524</v>
@@ -17985,7 +17985,7 @@
         <v>1455</v>
       </c>
       <c r="E290">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F290" t="s">
         <v>1524</v>
@@ -18020,7 +18020,7 @@
         <v>1455</v>
       </c>
       <c r="E291">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F291" t="s">
         <v>1524</v>
@@ -18055,7 +18055,7 @@
         <v>1455</v>
       </c>
       <c r="E292">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F292" t="s">
         <v>1524</v>
@@ -18090,7 +18090,7 @@
         <v>1456</v>
       </c>
       <c r="E293">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F293" t="s">
         <v>1524</v>
@@ -18125,7 +18125,7 @@
         <v>1457</v>
       </c>
       <c r="E294">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F294" t="s">
         <v>1524</v>
@@ -18160,7 +18160,7 @@
         <v>1457</v>
       </c>
       <c r="E295">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F295" t="s">
         <v>1524</v>
@@ -18195,7 +18195,7 @@
         <v>1457</v>
       </c>
       <c r="E296">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F296" t="s">
         <v>1524</v>
@@ -18230,7 +18230,7 @@
         <v>1457</v>
       </c>
       <c r="E297">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F297" t="s">
         <v>1524</v>
@@ -18265,7 +18265,7 @@
         <v>1457</v>
       </c>
       <c r="E298">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F298" t="s">
         <v>1524</v>
@@ -18300,7 +18300,7 @@
         <v>1457</v>
       </c>
       <c r="E299">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F299" t="s">
         <v>1524</v>
@@ -18335,7 +18335,7 @@
         <v>1458</v>
       </c>
       <c r="E300">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F300" t="s">
         <v>1524</v>
@@ -18370,7 +18370,7 @@
         <v>1458</v>
       </c>
       <c r="E301">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F301" t="s">
         <v>1524</v>
@@ -18405,7 +18405,7 @@
         <v>1458</v>
       </c>
       <c r="E302">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F302" t="s">
         <v>1524</v>
@@ -18440,7 +18440,7 @@
         <v>1458</v>
       </c>
       <c r="E303">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F303" t="s">
         <v>1524</v>
@@ -18478,7 +18478,7 @@
         <v>1458</v>
       </c>
       <c r="E304">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F304" t="s">
         <v>1524</v>
@@ -18513,7 +18513,7 @@
         <v>1458</v>
       </c>
       <c r="E305">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F305" t="s">
         <v>1524</v>
@@ -18548,7 +18548,7 @@
         <v>1458</v>
       </c>
       <c r="E306">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F306" t="s">
         <v>1524</v>
@@ -18583,7 +18583,7 @@
         <v>1458</v>
       </c>
       <c r="E307">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F307" t="s">
         <v>1524</v>
@@ -18618,7 +18618,7 @@
         <v>1458</v>
       </c>
       <c r="E308">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F308" t="s">
         <v>1524</v>
@@ -18653,7 +18653,7 @@
         <v>1459</v>
       </c>
       <c r="E309">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F309" t="s">
         <v>1525</v>
@@ -18688,7 +18688,7 @@
         <v>1460</v>
       </c>
       <c r="E310">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F310" t="s">
         <v>1528</v>
@@ -18723,7 +18723,7 @@
         <v>1461</v>
       </c>
       <c r="E311">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F311" t="s">
         <v>1524</v>
@@ -18758,7 +18758,7 @@
         <v>1462</v>
       </c>
       <c r="E312">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F312" t="s">
         <v>1524</v>
@@ -18793,7 +18793,7 @@
         <v>1462</v>
       </c>
       <c r="E313">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F313" t="s">
         <v>1524</v>
@@ -18828,7 +18828,7 @@
         <v>1463</v>
       </c>
       <c r="E314">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F314" t="s">
         <v>1524</v>
@@ -18863,7 +18863,7 @@
         <v>1464</v>
       </c>
       <c r="E315">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F315" t="s">
         <v>1527</v>
@@ -18898,7 +18898,7 @@
         <v>1464</v>
       </c>
       <c r="E316">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F316" t="s">
         <v>1524</v>
@@ -18933,7 +18933,7 @@
         <v>1464</v>
       </c>
       <c r="E317">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F317" t="s">
         <v>1524</v>
@@ -18968,7 +18968,7 @@
         <v>1464</v>
       </c>
       <c r="E318">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F318" t="s">
         <v>1524</v>
@@ -19003,7 +19003,7 @@
         <v>1464</v>
       </c>
       <c r="E319">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F319" t="s">
         <v>1524</v>
@@ -19038,7 +19038,7 @@
         <v>1464</v>
       </c>
       <c r="E320">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F320" t="s">
         <v>1524</v>
@@ -19073,7 +19073,7 @@
         <v>1465</v>
       </c>
       <c r="E321">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F321" t="s">
         <v>1524</v>
@@ -19108,7 +19108,7 @@
         <v>1466</v>
       </c>
       <c r="E322">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F322" t="s">
         <v>1524</v>
@@ -19143,7 +19143,7 @@
         <v>1466</v>
       </c>
       <c r="E323">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F323" t="s">
         <v>1524</v>
@@ -19178,7 +19178,7 @@
         <v>1466</v>
       </c>
       <c r="E324">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F324" t="s">
         <v>1524</v>
@@ -19216,7 +19216,7 @@
         <v>1466</v>
       </c>
       <c r="E325">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F325" t="s">
         <v>1524</v>
@@ -19251,7 +19251,7 @@
         <v>1467</v>
       </c>
       <c r="E326">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F326" t="s">
         <v>1524</v>
@@ -19286,7 +19286,7 @@
         <v>1467</v>
       </c>
       <c r="E327">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F327" t="s">
         <v>1524</v>
@@ -19321,7 +19321,7 @@
         <v>1467</v>
       </c>
       <c r="E328">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F328" t="s">
         <v>1524</v>
@@ -19356,7 +19356,7 @@
         <v>1467</v>
       </c>
       <c r="E329">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F329" t="s">
         <v>1524</v>
@@ -19391,7 +19391,7 @@
         <v>1467</v>
       </c>
       <c r="E330">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F330" t="s">
         <v>1524</v>
@@ -19426,7 +19426,7 @@
         <v>1468</v>
       </c>
       <c r="E331">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F331" t="s">
         <v>1524</v>
@@ -19461,7 +19461,7 @@
         <v>1468</v>
       </c>
       <c r="E332">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F332" t="s">
         <v>1524</v>
@@ -19496,7 +19496,7 @@
         <v>1469</v>
       </c>
       <c r="E333">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F333" t="s">
         <v>1524</v>
@@ -19531,7 +19531,7 @@
         <v>1469</v>
       </c>
       <c r="E334">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F334" t="s">
         <v>1524</v>
@@ -19566,7 +19566,7 @@
         <v>1469</v>
       </c>
       <c r="E335">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F335" t="s">
         <v>1524</v>
@@ -19601,7 +19601,7 @@
         <v>1469</v>
       </c>
       <c r="E336">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F336" t="s">
         <v>1524</v>
@@ -19636,7 +19636,7 @@
         <v>1469</v>
       </c>
       <c r="E337">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F337" t="s">
         <v>1524</v>
@@ -19671,7 +19671,7 @@
         <v>1469</v>
       </c>
       <c r="E338">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F338" t="s">
         <v>1524</v>
@@ -19706,7 +19706,7 @@
         <v>1469</v>
       </c>
       <c r="E339">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F339" t="s">
         <v>1524</v>
@@ -19741,7 +19741,7 @@
         <v>1469</v>
       </c>
       <c r="E340">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F340" t="s">
         <v>1524</v>
@@ -19776,7 +19776,7 @@
         <v>1469</v>
       </c>
       <c r="E341">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F341" t="s">
         <v>1524</v>
@@ -19811,7 +19811,7 @@
         <v>1469</v>
       </c>
       <c r="E342">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F342" t="s">
         <v>1524</v>
@@ -19846,7 +19846,7 @@
         <v>1470</v>
       </c>
       <c r="E343">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F343" t="s">
         <v>1524</v>
@@ -19881,7 +19881,7 @@
         <v>1470</v>
       </c>
       <c r="E344">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F344" t="s">
         <v>1524</v>
@@ -19916,7 +19916,7 @@
         <v>1470</v>
       </c>
       <c r="E345">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F345" t="s">
         <v>1525</v>
@@ -19951,7 +19951,7 @@
         <v>1471</v>
       </c>
       <c r="E346">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F346" t="s">
         <v>1524</v>
@@ -19986,7 +19986,7 @@
         <v>1471</v>
       </c>
       <c r="E347">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F347" t="s">
         <v>1524</v>
@@ -20021,7 +20021,7 @@
         <v>1471</v>
       </c>
       <c r="E348">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F348" t="s">
         <v>1524</v>
@@ -20056,7 +20056,7 @@
         <v>1471</v>
       </c>
       <c r="E349">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F349" t="s">
         <v>1524</v>
@@ -20091,7 +20091,7 @@
         <v>1471</v>
       </c>
       <c r="E350">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F350" t="s">
         <v>1524</v>
@@ -20126,7 +20126,7 @@
         <v>1471</v>
       </c>
       <c r="E351">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F351" t="s">
         <v>1524</v>
@@ -20161,7 +20161,7 @@
         <v>1471</v>
       </c>
       <c r="E352">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F352" t="s">
         <v>1527</v>
@@ -20196,7 +20196,7 @@
         <v>1472</v>
       </c>
       <c r="E353">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F353" t="s">
         <v>1524</v>
@@ -20231,7 +20231,7 @@
         <v>1472</v>
       </c>
       <c r="E354">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F354" t="s">
         <v>1524</v>
@@ -20266,7 +20266,7 @@
         <v>1472</v>
       </c>
       <c r="E355">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F355" t="s">
         <v>1524</v>
@@ -20301,7 +20301,7 @@
         <v>1472</v>
       </c>
       <c r="E356">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F356" t="s">
         <v>1524</v>
@@ -20336,7 +20336,7 @@
         <v>1473</v>
       </c>
       <c r="E357">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F357" t="s">
         <v>1527</v>
@@ -20371,7 +20371,7 @@
         <v>1473</v>
       </c>
       <c r="E358">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F358" t="s">
         <v>1524</v>
@@ -20406,7 +20406,7 @@
         <v>1473</v>
       </c>
       <c r="E359">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F359" t="s">
         <v>1524</v>
@@ -20441,7 +20441,7 @@
         <v>1473</v>
       </c>
       <c r="E360">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F360" t="s">
         <v>1524</v>
@@ -20476,7 +20476,7 @@
         <v>1473</v>
       </c>
       <c r="E361">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F361" t="s">
         <v>1524</v>
@@ -20511,7 +20511,7 @@
         <v>1474</v>
       </c>
       <c r="E362">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F362" t="s">
         <v>1524</v>
@@ -20546,7 +20546,7 @@
         <v>1474</v>
       </c>
       <c r="E363">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F363" t="s">
         <v>1524</v>
@@ -20581,7 +20581,7 @@
         <v>1474</v>
       </c>
       <c r="E364">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F364" t="s">
         <v>1526</v>
@@ -20616,7 +20616,7 @@
         <v>1474</v>
       </c>
       <c r="E365">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F365" t="s">
         <v>1524</v>
@@ -20651,7 +20651,7 @@
         <v>1474</v>
       </c>
       <c r="E366">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F366" t="s">
         <v>1524</v>
@@ -20686,7 +20686,7 @@
         <v>1475</v>
       </c>
       <c r="E367">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F367" t="s">
         <v>1524</v>
@@ -20721,7 +20721,7 @@
         <v>1475</v>
       </c>
       <c r="E368">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F368" t="s">
         <v>1524</v>
@@ -20756,7 +20756,7 @@
         <v>1475</v>
       </c>
       <c r="E369">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F369" t="s">
         <v>1524</v>
@@ -20791,7 +20791,7 @@
         <v>1475</v>
       </c>
       <c r="E370">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F370" t="s">
         <v>1524</v>
@@ -20826,7 +20826,7 @@
         <v>1475</v>
       </c>
       <c r="E371">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F371" t="s">
         <v>1524</v>
@@ -20861,7 +20861,7 @@
         <v>1476</v>
       </c>
       <c r="E372">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F372" t="s">
         <v>1524</v>
@@ -20896,7 +20896,7 @@
         <v>1476</v>
       </c>
       <c r="E373">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F373" t="s">
         <v>1524</v>
@@ -20931,7 +20931,7 @@
         <v>1476</v>
       </c>
       <c r="E374">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F374" t="s">
         <v>1524</v>
@@ -20966,7 +20966,7 @@
         <v>1476</v>
       </c>
       <c r="E375">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F375" t="s">
         <v>1524</v>
@@ -21004,7 +21004,7 @@
         <v>1477</v>
       </c>
       <c r="E376">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F376" t="s">
         <v>1524</v>
@@ -21039,7 +21039,7 @@
         <v>1477</v>
       </c>
       <c r="E377">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F377" t="s">
         <v>1524</v>
@@ -21074,7 +21074,7 @@
         <v>1477</v>
       </c>
       <c r="E378">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F378" t="s">
         <v>1524</v>
@@ -21109,7 +21109,7 @@
         <v>1477</v>
       </c>
       <c r="E379">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F379" t="s">
         <v>1524</v>
@@ -21144,7 +21144,7 @@
         <v>1477</v>
       </c>
       <c r="E380">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F380" t="s">
         <v>1524</v>
@@ -21179,7 +21179,7 @@
         <v>1477</v>
       </c>
       <c r="E381">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F381" t="s">
         <v>1524</v>
@@ -21214,7 +21214,7 @@
         <v>1478</v>
       </c>
       <c r="E382">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F382" t="s">
         <v>1525</v>
@@ -21249,7 +21249,7 @@
         <v>1478</v>
       </c>
       <c r="E383">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F383" t="s">
         <v>1524</v>
@@ -21284,7 +21284,7 @@
         <v>1479</v>
       </c>
       <c r="E384">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F384" t="s">
         <v>1524</v>
@@ -21319,7 +21319,7 @@
         <v>1480</v>
       </c>
       <c r="E385">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F385" t="s">
         <v>1524</v>
@@ -21354,7 +21354,7 @@
         <v>1480</v>
       </c>
       <c r="E386">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F386" t="s">
         <v>1524</v>
@@ -21389,7 +21389,7 @@
         <v>1480</v>
       </c>
       <c r="E387">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F387" t="s">
         <v>1526</v>
@@ -21427,7 +21427,7 @@
         <v>1481</v>
       </c>
       <c r="E388">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F388" t="s">
         <v>1524</v>
@@ -21462,7 +21462,7 @@
         <v>1481</v>
       </c>
       <c r="E389">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F389" t="s">
         <v>1524</v>
@@ -21497,7 +21497,7 @@
         <v>1481</v>
       </c>
       <c r="E390">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F390" t="s">
         <v>1524</v>
@@ -21532,7 +21532,7 @@
         <v>1482</v>
       </c>
       <c r="E391">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F391" t="s">
         <v>1524</v>
@@ -21567,7 +21567,7 @@
         <v>1482</v>
       </c>
       <c r="E392">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F392" t="s">
         <v>1524</v>
@@ -21602,7 +21602,7 @@
         <v>1482</v>
       </c>
       <c r="E393">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F393" t="s">
         <v>1524</v>
@@ -21637,7 +21637,7 @@
         <v>1482</v>
       </c>
       <c r="E394">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F394" t="s">
         <v>1524</v>
@@ -21672,7 +21672,7 @@
         <v>1482</v>
       </c>
       <c r="E395">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F395" t="s">
         <v>1524</v>
@@ -21707,7 +21707,7 @@
         <v>1482</v>
       </c>
       <c r="E396">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F396" t="s">
         <v>1524</v>
@@ -21742,7 +21742,7 @@
         <v>1482</v>
       </c>
       <c r="E397">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F397" t="s">
         <v>1524</v>
@@ -21777,7 +21777,7 @@
         <v>1483</v>
       </c>
       <c r="E398">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F398" t="s">
         <v>1524</v>
@@ -21812,7 +21812,7 @@
         <v>1484</v>
       </c>
       <c r="E399">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F399" t="s">
         <v>1524</v>
@@ -21847,7 +21847,7 @@
         <v>1484</v>
       </c>
       <c r="E400">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F400" t="s">
         <v>1524</v>
@@ -21882,7 +21882,7 @@
         <v>1484</v>
       </c>
       <c r="E401">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F401" t="s">
         <v>1524</v>
@@ -21917,7 +21917,7 @@
         <v>1484</v>
       </c>
       <c r="E402">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F402" t="s">
         <v>1528</v>
@@ -21955,7 +21955,7 @@
         <v>1484</v>
       </c>
       <c r="E403">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F403" t="s">
         <v>1524</v>
@@ -21990,7 +21990,7 @@
         <v>1484</v>
       </c>
       <c r="E404">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F404" t="s">
         <v>1528</v>
@@ -22025,7 +22025,7 @@
         <v>1485</v>
       </c>
       <c r="E405">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F405" t="s">
         <v>1524</v>
@@ -22060,7 +22060,7 @@
         <v>1486</v>
       </c>
       <c r="E406">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F406" t="s">
         <v>1524</v>
@@ -22095,7 +22095,7 @@
         <v>1486</v>
       </c>
       <c r="E407">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F407" t="s">
         <v>1524</v>
@@ -22130,7 +22130,7 @@
         <v>1486</v>
       </c>
       <c r="E408">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F408" t="s">
         <v>1524</v>
@@ -22165,7 +22165,7 @@
         <v>1487</v>
       </c>
       <c r="E409">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F409" t="s">
         <v>1528</v>
@@ -22200,7 +22200,7 @@
         <v>1487</v>
       </c>
       <c r="E410">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F410" t="s">
         <v>1524</v>
@@ -22235,7 +22235,7 @@
         <v>1487</v>
       </c>
       <c r="E411">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F411" t="s">
         <v>1524</v>
@@ -22270,7 +22270,7 @@
         <v>1487</v>
       </c>
       <c r="E412">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F412" t="s">
         <v>1524</v>
@@ -22305,7 +22305,7 @@
         <v>1488</v>
       </c>
       <c r="E413">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F413" t="s">
         <v>1524</v>
@@ -22340,7 +22340,7 @@
         <v>1488</v>
       </c>
       <c r="E414">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F414" t="s">
         <v>1524</v>
@@ -22375,7 +22375,7 @@
         <v>1488</v>
       </c>
       <c r="E415">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F415" t="s">
         <v>1524</v>
@@ -22410,7 +22410,7 @@
         <v>1489</v>
       </c>
       <c r="E416">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F416" t="s">
         <v>1524</v>
@@ -22445,7 +22445,7 @@
         <v>1489</v>
       </c>
       <c r="E417">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F417" t="s">
         <v>1524</v>
@@ -22480,7 +22480,7 @@
         <v>1489</v>
       </c>
       <c r="E418">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F418" t="s">
         <v>1524</v>
@@ -22515,7 +22515,7 @@
         <v>1489</v>
       </c>
       <c r="E419">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F419" t="s">
         <v>1524</v>
@@ -22550,7 +22550,7 @@
         <v>1489</v>
       </c>
       <c r="E420">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F420" t="s">
         <v>1524</v>
@@ -22585,7 +22585,7 @@
         <v>1490</v>
       </c>
       <c r="E421">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F421" t="s">
         <v>1524</v>
@@ -22620,7 +22620,7 @@
         <v>1490</v>
       </c>
       <c r="E422">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F422" t="s">
         <v>1524</v>
@@ -22655,7 +22655,7 @@
         <v>1490</v>
       </c>
       <c r="E423">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F423" t="s">
         <v>1524</v>
@@ -22690,7 +22690,7 @@
         <v>1490</v>
       </c>
       <c r="E424">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F424" t="s">
         <v>1524</v>
@@ -22725,7 +22725,7 @@
         <v>1490</v>
       </c>
       <c r="E425">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F425" t="s">
         <v>1524</v>
@@ -22760,7 +22760,7 @@
         <v>1490</v>
       </c>
       <c r="E426">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F426" t="s">
         <v>1524</v>
@@ -22795,7 +22795,7 @@
         <v>1490</v>
       </c>
       <c r="E427">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F427" t="s">
         <v>1524</v>
@@ -22830,7 +22830,7 @@
         <v>1490</v>
       </c>
       <c r="E428">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F428" t="s">
         <v>1524</v>
@@ -22865,7 +22865,7 @@
         <v>1490</v>
       </c>
       <c r="E429">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F429" t="s">
         <v>1524</v>
@@ -22900,7 +22900,7 @@
         <v>1490</v>
       </c>
       <c r="E430">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F430" t="s">
         <v>1524</v>
@@ -22935,7 +22935,7 @@
         <v>1490</v>
       </c>
       <c r="E431">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F431" t="s">
         <v>1524</v>
@@ -22970,7 +22970,7 @@
         <v>1490</v>
       </c>
       <c r="E432">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F432" t="s">
         <v>1524</v>
@@ -23005,7 +23005,7 @@
         <v>1490</v>
       </c>
       <c r="E433">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F433" t="s">
         <v>1524</v>
@@ -23040,7 +23040,7 @@
         <v>1490</v>
       </c>
       <c r="E434">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F434" t="s">
         <v>1524</v>
@@ -23075,7 +23075,7 @@
         <v>1490</v>
       </c>
       <c r="E435">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F435" t="s">
         <v>1524</v>
@@ -23110,7 +23110,7 @@
         <v>1490</v>
       </c>
       <c r="E436">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F436" t="s">
         <v>1524</v>
@@ -23145,7 +23145,7 @@
         <v>1490</v>
       </c>
       <c r="E437">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F437" t="s">
         <v>1524</v>
@@ -23180,7 +23180,7 @@
         <v>1490</v>
       </c>
       <c r="E438">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F438" t="s">
         <v>1524</v>
@@ -23215,7 +23215,7 @@
         <v>1490</v>
       </c>
       <c r="E439">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F439" t="s">
         <v>1524</v>
@@ -23250,7 +23250,7 @@
         <v>1490</v>
       </c>
       <c r="E440">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F440" t="s">
         <v>1524</v>
@@ -23285,7 +23285,7 @@
         <v>1490</v>
       </c>
       <c r="E441">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F441" t="s">
         <v>1524</v>
@@ -23320,7 +23320,7 @@
         <v>1490</v>
       </c>
       <c r="E442">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F442" t="s">
         <v>1524</v>
@@ -23355,7 +23355,7 @@
         <v>1490</v>
       </c>
       <c r="E443">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F443" t="s">
         <v>1524</v>
@@ -23390,7 +23390,7 @@
         <v>1490</v>
       </c>
       <c r="E444">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F444" t="s">
         <v>1524</v>
@@ -23425,7 +23425,7 @@
         <v>1491</v>
       </c>
       <c r="E445">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F445" t="s">
         <v>1524</v>
@@ -23460,7 +23460,7 @@
         <v>1491</v>
       </c>
       <c r="E446">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F446" t="s">
         <v>1524</v>
@@ -23495,7 +23495,7 @@
         <v>1491</v>
       </c>
       <c r="E447">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F447" t="s">
         <v>1524</v>
@@ -23530,7 +23530,7 @@
         <v>1491</v>
       </c>
       <c r="E448">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F448" t="s">
         <v>1524</v>
@@ -23565,7 +23565,7 @@
         <v>1491</v>
       </c>
       <c r="E449">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F449" t="s">
         <v>1524</v>
@@ -23600,7 +23600,7 @@
         <v>1491</v>
       </c>
       <c r="E450">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F450" t="s">
         <v>1524</v>
@@ -23635,7 +23635,7 @@
         <v>1491</v>
       </c>
       <c r="E451">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F451" t="s">
         <v>1528</v>
@@ -23670,7 +23670,7 @@
         <v>1491</v>
       </c>
       <c r="E452">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F452" t="s">
         <v>1524</v>
@@ -23705,7 +23705,7 @@
         <v>1492</v>
       </c>
       <c r="E453">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F453" t="s">
         <v>1524</v>
@@ -23740,7 +23740,7 @@
         <v>1493</v>
       </c>
       <c r="E454">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F454" t="s">
         <v>1526</v>
@@ -23778,7 +23778,7 @@
         <v>1493</v>
       </c>
       <c r="E455">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F455" t="s">
         <v>1524</v>
@@ -23813,7 +23813,7 @@
         <v>1493</v>
       </c>
       <c r="E456">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F456" t="s">
         <v>1524</v>
@@ -23848,7 +23848,7 @@
         <v>1493</v>
       </c>
       <c r="E457">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F457" t="s">
         <v>1524</v>
@@ -23883,7 +23883,7 @@
         <v>1493</v>
       </c>
       <c r="E458">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F458" t="s">
         <v>1524</v>
@@ -23918,7 +23918,7 @@
         <v>1494</v>
       </c>
       <c r="E459">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F459" t="s">
         <v>1524</v>
@@ -23956,7 +23956,7 @@
         <v>1494</v>
       </c>
       <c r="E460">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F460" t="s">
         <v>1528</v>
@@ -23991,7 +23991,7 @@
         <v>1494</v>
       </c>
       <c r="E461">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F461" t="s">
         <v>1526</v>
@@ -24026,7 +24026,7 @@
         <v>1494</v>
       </c>
       <c r="E462">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F462" t="s">
         <v>1524</v>
@@ -24061,7 +24061,7 @@
         <v>1494</v>
       </c>
       <c r="E463">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F463" t="s">
         <v>1524</v>
@@ -24096,7 +24096,7 @@
         <v>1494</v>
       </c>
       <c r="E464">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F464" t="s">
         <v>1524</v>
@@ -24131,7 +24131,7 @@
         <v>1494</v>
       </c>
       <c r="E465">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F465" t="s">
         <v>1524</v>
@@ -24166,7 +24166,7 @@
         <v>1494</v>
       </c>
       <c r="E466">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F466" t="s">
         <v>1524</v>
@@ -24201,7 +24201,7 @@
         <v>1494</v>
       </c>
       <c r="E467">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F467" t="s">
         <v>1524</v>
@@ -24236,7 +24236,7 @@
         <v>1495</v>
       </c>
       <c r="E468">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F468" t="s">
         <v>1528</v>
@@ -24274,7 +24274,7 @@
         <v>1495</v>
       </c>
       <c r="E469">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F469" t="s">
         <v>1524</v>
@@ -24309,7 +24309,7 @@
         <v>1496</v>
       </c>
       <c r="E470">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F470" t="s">
         <v>1524</v>
@@ -24344,7 +24344,7 @@
         <v>1496</v>
       </c>
       <c r="E471">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F471" t="s">
         <v>1524</v>
@@ -24379,7 +24379,7 @@
         <v>1496</v>
       </c>
       <c r="E472">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F472" t="s">
         <v>1524</v>
@@ -24414,7 +24414,7 @@
         <v>1496</v>
       </c>
       <c r="E473">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F473" t="s">
         <v>1524</v>
@@ -24449,7 +24449,7 @@
         <v>1496</v>
       </c>
       <c r="E474">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F474" t="s">
         <v>1524</v>
@@ -24484,7 +24484,7 @@
         <v>1496</v>
       </c>
       <c r="E475">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F475" t="s">
         <v>1524</v>
@@ -24519,7 +24519,7 @@
         <v>1497</v>
       </c>
       <c r="E476">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F476" t="s">
         <v>1524</v>
@@ -24554,7 +24554,7 @@
         <v>1497</v>
       </c>
       <c r="E477">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F477" t="s">
         <v>1524</v>
@@ -24589,7 +24589,7 @@
         <v>1497</v>
       </c>
       <c r="E478">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F478" t="s">
         <v>1524</v>
@@ -24624,7 +24624,7 @@
         <v>1497</v>
       </c>
       <c r="E479">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F479" t="s">
         <v>1524</v>
@@ -24659,7 +24659,7 @@
         <v>1497</v>
       </c>
       <c r="E480">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F480" t="s">
         <v>1524</v>
@@ -24694,7 +24694,7 @@
         <v>1497</v>
       </c>
       <c r="E481">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F481" t="s">
         <v>1526</v>
@@ -24729,7 +24729,7 @@
         <v>1497</v>
       </c>
       <c r="E482">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F482" t="s">
         <v>1524</v>
@@ -24764,7 +24764,7 @@
         <v>1497</v>
       </c>
       <c r="E483">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F483" t="s">
         <v>1524</v>
@@ -24799,7 +24799,7 @@
         <v>1498</v>
       </c>
       <c r="E484">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F484" t="s">
         <v>1524</v>
@@ -24834,7 +24834,7 @@
         <v>1498</v>
       </c>
       <c r="E485">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F485" t="s">
         <v>1524</v>
@@ -24869,7 +24869,7 @@
         <v>1498</v>
       </c>
       <c r="E486">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F486" t="s">
         <v>1524</v>
@@ -24904,7 +24904,7 @@
         <v>1498</v>
       </c>
       <c r="E487">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F487" t="s">
         <v>1524</v>
@@ -24939,7 +24939,7 @@
         <v>1498</v>
       </c>
       <c r="E488">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F488" t="s">
         <v>1524</v>
@@ -24974,7 +24974,7 @@
         <v>1498</v>
       </c>
       <c r="E489">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F489" t="s">
         <v>1524</v>
@@ -25009,7 +25009,7 @@
         <v>1498</v>
       </c>
       <c r="E490">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F490" t="s">
         <v>1524</v>
@@ -25044,7 +25044,7 @@
         <v>1498</v>
       </c>
       <c r="E491">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F491" t="s">
         <v>1524</v>
@@ -25079,7 +25079,7 @@
         <v>1499</v>
       </c>
       <c r="E492">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F492" t="s">
         <v>1524</v>
@@ -25114,7 +25114,7 @@
         <v>1499</v>
       </c>
       <c r="E493">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F493" t="s">
         <v>1524</v>
@@ -25149,7 +25149,7 @@
         <v>1499</v>
       </c>
       <c r="E494">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F494" t="s">
         <v>1524</v>
@@ -25184,7 +25184,7 @@
         <v>1499</v>
       </c>
       <c r="E495">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F495" t="s">
         <v>1524</v>
@@ -25219,7 +25219,7 @@
         <v>1499</v>
       </c>
       <c r="E496">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F496" t="s">
         <v>1524</v>
@@ -25254,7 +25254,7 @@
         <v>1499</v>
       </c>
       <c r="E497">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F497" t="s">
         <v>1524</v>
@@ -25289,7 +25289,7 @@
         <v>1500</v>
       </c>
       <c r="E498">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F498" t="s">
         <v>1524</v>
@@ -25324,7 +25324,7 @@
         <v>1500</v>
       </c>
       <c r="E499">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F499" t="s">
         <v>1524</v>
@@ -25359,7 +25359,7 @@
         <v>1500</v>
       </c>
       <c r="E500">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F500" t="s">
         <v>1524</v>
@@ -25394,7 +25394,7 @@
         <v>1500</v>
       </c>
       <c r="E501">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F501" t="s">
         <v>1524</v>
@@ -25429,7 +25429,7 @@
         <v>1500</v>
       </c>
       <c r="E502">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F502" t="s">
         <v>1524</v>
@@ -25464,7 +25464,7 @@
         <v>1501</v>
       </c>
       <c r="E503">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F503" t="s">
         <v>1524</v>
@@ -25499,7 +25499,7 @@
         <v>1501</v>
       </c>
       <c r="E504">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F504" t="s">
         <v>1524</v>
@@ -25534,7 +25534,7 @@
         <v>1501</v>
       </c>
       <c r="E505">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F505" t="s">
         <v>1524</v>
@@ -25569,7 +25569,7 @@
         <v>1501</v>
       </c>
       <c r="E506">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F506" t="s">
         <v>1524</v>
@@ -25604,7 +25604,7 @@
         <v>1501</v>
       </c>
       <c r="E507">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F507" t="s">
         <v>1524</v>
@@ -25639,7 +25639,7 @@
         <v>1501</v>
       </c>
       <c r="E508">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F508" t="s">
         <v>1524</v>
@@ -25674,7 +25674,7 @@
         <v>1501</v>
       </c>
       <c r="E509">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F509" t="s">
         <v>1524</v>
@@ -25709,7 +25709,7 @@
         <v>1501</v>
       </c>
       <c r="E510">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F510" t="s">
         <v>1524</v>
@@ -25744,7 +25744,7 @@
         <v>1501</v>
       </c>
       <c r="E511">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F511" t="s">
         <v>1524</v>
@@ -25782,7 +25782,7 @@
         <v>1501</v>
       </c>
       <c r="E512">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F512" t="s">
         <v>1524</v>
@@ -25817,7 +25817,7 @@
         <v>1502</v>
       </c>
       <c r="E513">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F513" t="s">
         <v>1524</v>
@@ -25852,7 +25852,7 @@
         <v>1502</v>
       </c>
       <c r="E514">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F514" t="s">
         <v>1526</v>
@@ -25890,7 +25890,7 @@
         <v>1502</v>
       </c>
       <c r="E515">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F515" t="s">
         <v>1524</v>
@@ -25925,7 +25925,7 @@
         <v>1502</v>
       </c>
       <c r="E516">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F516" t="s">
         <v>1524</v>
@@ -25960,7 +25960,7 @@
         <v>1503</v>
       </c>
       <c r="E517">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F517" t="s">
         <v>1524</v>
@@ -25995,7 +25995,7 @@
         <v>1503</v>
       </c>
       <c r="E518">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F518" t="s">
         <v>1524</v>
@@ -26030,7 +26030,7 @@
         <v>1503</v>
       </c>
       <c r="E519">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F519" t="s">
         <v>1524</v>
@@ -26065,7 +26065,7 @@
         <v>1503</v>
       </c>
       <c r="E520">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F520" t="s">
         <v>1526</v>
@@ -26103,7 +26103,7 @@
         <v>1503</v>
       </c>
       <c r="E521">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F521" t="s">
         <v>1524</v>
@@ -26138,7 +26138,7 @@
         <v>1503</v>
       </c>
       <c r="E522">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F522" t="s">
         <v>1524</v>
@@ -26173,7 +26173,7 @@
         <v>1503</v>
       </c>
       <c r="E523">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F523" t="s">
         <v>1524</v>
@@ -26208,7 +26208,7 @@
         <v>1503</v>
       </c>
       <c r="E524">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F524" t="s">
         <v>1524</v>
@@ -26243,7 +26243,7 @@
         <v>1503</v>
       </c>
       <c r="E525">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F525" t="s">
         <v>1524</v>
@@ -26278,7 +26278,7 @@
         <v>1503</v>
       </c>
       <c r="E526">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F526" t="s">
         <v>1524</v>
@@ -26313,7 +26313,7 @@
         <v>1504</v>
       </c>
       <c r="E527">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F527" t="s">
         <v>1524</v>
@@ -26348,7 +26348,7 @@
         <v>1504</v>
       </c>
       <c r="E528">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F528" t="s">
         <v>1524</v>
@@ -26383,7 +26383,7 @@
         <v>1504</v>
       </c>
       <c r="E529">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F529" t="s">
         <v>1524</v>
@@ -26418,7 +26418,7 @@
         <v>1504</v>
       </c>
       <c r="E530">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F530" t="s">
         <v>1524</v>
@@ -26453,7 +26453,7 @@
         <v>1505</v>
       </c>
       <c r="E531">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F531" t="s">
         <v>1524</v>
@@ -26488,7 +26488,7 @@
         <v>1505</v>
       </c>
       <c r="E532">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F532" t="s">
         <v>1524</v>
@@ -26523,7 +26523,7 @@
         <v>1505</v>
       </c>
       <c r="E533">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F533" t="s">
         <v>1524</v>
@@ -26558,7 +26558,7 @@
         <v>1505</v>
       </c>
       <c r="E534">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F534" t="s">
         <v>1526</v>
@@ -26596,7 +26596,7 @@
         <v>1506</v>
       </c>
       <c r="E535">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F535" t="s">
         <v>1524</v>
@@ -26631,7 +26631,7 @@
         <v>1506</v>
       </c>
       <c r="E536">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F536" t="s">
         <v>1528</v>
@@ -26669,7 +26669,7 @@
         <v>1506</v>
       </c>
       <c r="E537">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F537" t="s">
         <v>1524</v>
@@ -26704,7 +26704,7 @@
         <v>1506</v>
       </c>
       <c r="E538">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F538" t="s">
         <v>1524</v>
@@ -26739,7 +26739,7 @@
         <v>1507</v>
       </c>
       <c r="E539">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F539" t="s">
         <v>1524</v>
@@ -26774,7 +26774,7 @@
         <v>1507</v>
       </c>
       <c r="E540">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F540" t="s">
         <v>1524</v>
@@ -26809,7 +26809,7 @@
         <v>1507</v>
       </c>
       <c r="E541">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F541" t="s">
         <v>1524</v>
@@ -26844,7 +26844,7 @@
         <v>1507</v>
       </c>
       <c r="E542">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F542" t="s">
         <v>1524</v>
@@ -26879,7 +26879,7 @@
         <v>1507</v>
       </c>
       <c r="E543">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F543" t="s">
         <v>1526</v>
@@ -26917,7 +26917,7 @@
         <v>1507</v>
       </c>
       <c r="E544">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F544" t="s">
         <v>1524</v>
@@ -26952,7 +26952,7 @@
         <v>1507</v>
       </c>
       <c r="E545">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F545" t="s">
         <v>1524</v>
@@ -26987,7 +26987,7 @@
         <v>1507</v>
       </c>
       <c r="E546">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F546" t="s">
         <v>1524</v>
@@ -27022,7 +27022,7 @@
         <v>1508</v>
       </c>
       <c r="E547">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F547" t="s">
         <v>1524</v>
@@ -27057,7 +27057,7 @@
         <v>1508</v>
       </c>
       <c r="E548">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F548" t="s">
         <v>1524</v>
@@ -27092,7 +27092,7 @@
         <v>1509</v>
       </c>
       <c r="E549">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F549" t="s">
         <v>1526</v>
@@ -27130,7 +27130,7 @@
         <v>1509</v>
       </c>
       <c r="E550">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F550" t="s">
         <v>1526</v>
@@ -27168,7 +27168,7 @@
         <v>1509</v>
       </c>
       <c r="E551">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F551" t="s">
         <v>1524</v>
@@ -27203,7 +27203,7 @@
         <v>1509</v>
       </c>
       <c r="E552">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F552" t="s">
         <v>1524</v>
@@ -27238,7 +27238,7 @@
         <v>1509</v>
       </c>
       <c r="E553">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F553" t="s">
         <v>1524</v>
@@ -27273,7 +27273,7 @@
         <v>1510</v>
       </c>
       <c r="E554">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F554" t="s">
         <v>1524</v>
@@ -27308,7 +27308,7 @@
         <v>1511</v>
       </c>
       <c r="E555">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F555" t="s">
         <v>1524</v>
@@ -27343,7 +27343,7 @@
         <v>1511</v>
       </c>
       <c r="E556">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F556" t="s">
         <v>1524</v>
@@ -27378,7 +27378,7 @@
         <v>1511</v>
       </c>
       <c r="E557">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F557" t="s">
         <v>1524</v>
@@ -27413,7 +27413,7 @@
         <v>1511</v>
       </c>
       <c r="E558">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F558" t="s">
         <v>1524</v>
@@ -27448,7 +27448,7 @@
         <v>1511</v>
       </c>
       <c r="E559">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F559" t="s">
         <v>1524</v>
@@ -27483,7 +27483,7 @@
         <v>1511</v>
       </c>
       <c r="E560">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F560" t="s">
         <v>1524</v>
@@ -27518,7 +27518,7 @@
         <v>1511</v>
       </c>
       <c r="E561">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F561" t="s">
         <v>1524</v>
@@ -27553,7 +27553,7 @@
         <v>1511</v>
       </c>
       <c r="E562">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F562" t="s">
         <v>1524</v>
@@ -27588,7 +27588,7 @@
         <v>1511</v>
       </c>
       <c r="E563">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F563" t="s">
         <v>1524</v>
@@ -27623,7 +27623,7 @@
         <v>1511</v>
       </c>
       <c r="E564">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F564" t="s">
         <v>1526</v>
@@ -27661,7 +27661,7 @@
         <v>1512</v>
       </c>
       <c r="E565">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F565" t="s">
         <v>1524</v>
@@ -27696,7 +27696,7 @@
         <v>1512</v>
       </c>
       <c r="E566">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F566" t="s">
         <v>1524</v>
@@ -27731,7 +27731,7 @@
         <v>1512</v>
       </c>
       <c r="E567">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F567" t="s">
         <v>1524</v>
@@ -27766,7 +27766,7 @@
         <v>1512</v>
       </c>
       <c r="E568">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F568" t="s">
         <v>1524</v>
@@ -27801,7 +27801,7 @@
         <v>1512</v>
       </c>
       <c r="E569">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F569" t="s">
         <v>1526</v>
@@ -27839,7 +27839,7 @@
         <v>1512</v>
       </c>
       <c r="E570">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F570" t="s">
         <v>1526</v>
@@ -27877,7 +27877,7 @@
         <v>1512</v>
       </c>
       <c r="E571">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F571" t="s">
         <v>1524</v>
@@ -27912,7 +27912,7 @@
         <v>1512</v>
       </c>
       <c r="E572">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F572" t="s">
         <v>1524</v>
@@ -27947,7 +27947,7 @@
         <v>1512</v>
       </c>
       <c r="E573">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F573" t="s">
         <v>1524</v>
@@ -27982,7 +27982,7 @@
         <v>1513</v>
       </c>
       <c r="E574">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F574" t="s">
         <v>1524</v>
@@ -28017,7 +28017,7 @@
         <v>1513</v>
       </c>
       <c r="E575">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F575" t="s">
         <v>1526</v>
@@ -28055,7 +28055,7 @@
         <v>1513</v>
       </c>
       <c r="E576">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F576" t="s">
         <v>1524</v>
@@ -28090,7 +28090,7 @@
         <v>1514</v>
       </c>
       <c r="E577">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F577" t="s">
         <v>1526</v>
@@ -28128,7 +28128,7 @@
         <v>1514</v>
       </c>
       <c r="E578">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F578" t="s">
         <v>1524</v>
@@ -28163,7 +28163,7 @@
         <v>1514</v>
       </c>
       <c r="E579">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F579" t="s">
         <v>1524</v>
@@ -28198,7 +28198,7 @@
         <v>1515</v>
       </c>
       <c r="E580">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F580" t="s">
         <v>1524</v>
@@ -28233,7 +28233,7 @@
         <v>1515</v>
       </c>
       <c r="E581">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F581" t="s">
         <v>1524</v>
@@ -28268,7 +28268,7 @@
         <v>1515</v>
       </c>
       <c r="E582">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F582" t="s">
         <v>1524</v>
@@ -28303,7 +28303,7 @@
         <v>1515</v>
       </c>
       <c r="E583">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F583" t="s">
         <v>1524</v>
@@ -28338,7 +28338,7 @@
         <v>1515</v>
       </c>
       <c r="E584">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F584" t="s">
         <v>1524</v>
@@ -28373,7 +28373,7 @@
         <v>1515</v>
       </c>
       <c r="E585">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F585" t="s">
         <v>1524</v>
@@ -28408,7 +28408,7 @@
         <v>1515</v>
       </c>
       <c r="E586">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F586" t="s">
         <v>1526</v>
@@ -28446,7 +28446,7 @@
         <v>1515</v>
       </c>
       <c r="E587">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F587" t="s">
         <v>1526</v>
@@ -28484,7 +28484,7 @@
         <v>1516</v>
       </c>
       <c r="E588">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F588" t="s">
         <v>1526</v>
@@ -28522,7 +28522,7 @@
         <v>1516</v>
       </c>
       <c r="E589">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F589" t="s">
         <v>1526</v>
@@ -28557,7 +28557,7 @@
         <v>1516</v>
       </c>
       <c r="E590">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F590" t="s">
         <v>1524</v>
@@ -28592,7 +28592,7 @@
         <v>1516</v>
       </c>
       <c r="E591">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F591" t="s">
         <v>1524</v>
@@ -28627,7 +28627,7 @@
         <v>1516</v>
       </c>
       <c r="E592">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F592" t="s">
         <v>1524</v>
@@ -28662,7 +28662,7 @@
         <v>1516</v>
       </c>
       <c r="E593">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F593" t="s">
         <v>1524</v>
@@ -28697,7 +28697,7 @@
         <v>1517</v>
       </c>
       <c r="E594">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F594" t="s">
         <v>1524</v>
@@ -28732,7 +28732,7 @@
         <v>1517</v>
       </c>
       <c r="E595">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F595" t="s">
         <v>1524</v>
@@ -28767,7 +28767,7 @@
         <v>1517</v>
       </c>
       <c r="E596">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F596" t="s">
         <v>1524</v>
@@ -28802,7 +28802,7 @@
         <v>1517</v>
       </c>
       <c r="E597">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F597" t="s">
         <v>1524</v>
@@ -28837,7 +28837,7 @@
         <v>1517</v>
       </c>
       <c r="E598">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F598" t="s">
         <v>1524</v>
@@ -28872,7 +28872,7 @@
         <v>1517</v>
       </c>
       <c r="E599">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F599" t="s">
         <v>1524</v>
@@ -28907,7 +28907,7 @@
         <v>1517</v>
       </c>
       <c r="E600">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F600" t="s">
         <v>1524</v>
@@ -28942,7 +28942,7 @@
         <v>1518</v>
       </c>
       <c r="E601">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F601" t="s">
         <v>1524</v>
@@ -28980,7 +28980,7 @@
         <v>1518</v>
       </c>
       <c r="E602">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F602" t="s">
         <v>1524</v>
@@ -29015,7 +29015,7 @@
         <v>1518</v>
       </c>
       <c r="E603">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F603" t="s">
         <v>1524</v>
@@ -29050,7 +29050,7 @@
         <v>1518</v>
       </c>
       <c r="E604">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F604" t="s">
         <v>1524</v>
@@ -29088,7 +29088,7 @@
         <v>1518</v>
       </c>
       <c r="E605">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F605" t="s">
         <v>1524</v>
@@ -29123,7 +29123,7 @@
         <v>1519</v>
       </c>
       <c r="E606">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F606" t="s">
         <v>1524</v>
@@ -29158,7 +29158,7 @@
         <v>1520</v>
       </c>
       <c r="E607">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F607" t="s">
         <v>1524</v>
@@ -29193,7 +29193,7 @@
         <v>1520</v>
       </c>
       <c r="E608">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F608" t="s">
         <v>1524</v>
@@ -29228,7 +29228,7 @@
         <v>1520</v>
       </c>
       <c r="E609">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F609" t="s">
         <v>1526</v>
@@ -29263,7 +29263,7 @@
         <v>1520</v>
       </c>
       <c r="E610">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F610" t="s">
         <v>1526</v>
@@ -29301,7 +29301,7 @@
         <v>1520</v>
       </c>
       <c r="E611">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F611" t="s">
         <v>1524</v>
@@ -29336,7 +29336,7 @@
         <v>1520</v>
       </c>
       <c r="E612">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F612" t="s">
         <v>1524</v>
@@ -29371,7 +29371,7 @@
         <v>1520</v>
       </c>
       <c r="E613">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F613" t="s">
         <v>1524</v>
@@ -29406,7 +29406,7 @@
         <v>1520</v>
       </c>
       <c r="E614">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F614" t="s">
         <v>1524</v>
@@ -29441,7 +29441,7 @@
         <v>1520</v>
       </c>
       <c r="E615">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F615" t="s">
         <v>1524</v>
@@ -29476,7 +29476,7 @@
         <v>1520</v>
       </c>
       <c r="E616">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F616" t="s">
         <v>1524</v>
@@ -29511,7 +29511,7 @@
         <v>1520</v>
       </c>
       <c r="E617">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F617" t="s">
         <v>1524</v>
@@ -29549,7 +29549,7 @@
         <v>1520</v>
       </c>
       <c r="E618">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F618" t="s">
         <v>1524</v>
@@ -29584,7 +29584,7 @@
         <v>1520</v>
       </c>
       <c r="E619">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F619" t="s">
         <v>1524</v>
@@ -29619,7 +29619,7 @@
         <v>1520</v>
       </c>
       <c r="E620">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F620" t="s">
         <v>1528</v>
@@ -29654,7 +29654,7 @@
         <v>1521</v>
       </c>
       <c r="E621">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F621" t="s">
         <v>1524</v>
@@ -29689,7 +29689,7 @@
         <v>1521</v>
       </c>
       <c r="E622">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F622" t="s">
         <v>1526</v>
@@ -29727,7 +29727,7 @@
         <v>1521</v>
       </c>
       <c r="E623">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F623" t="s">
         <v>1524</v>
@@ -29762,7 +29762,7 @@
         <v>1521</v>
       </c>
       <c r="E624">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F624" t="s">
         <v>1526</v>
@@ -29800,7 +29800,7 @@
         <v>1521</v>
       </c>
       <c r="E625">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F625" t="s">
         <v>1524</v>
@@ -29835,7 +29835,7 @@
         <v>1522</v>
       </c>
       <c r="E626">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F626" t="s">
         <v>1524</v>
@@ -29870,7 +29870,7 @@
         <v>1522</v>
       </c>
       <c r="E627">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F627" t="s">
         <v>1524</v>
@@ -29905,7 +29905,7 @@
         <v>1522</v>
       </c>
       <c r="E628">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F628" t="s">
         <v>1524</v>
@@ -29940,7 +29940,7 @@
         <v>1522</v>
       </c>
       <c r="E629">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F629" t="s">
         <v>1524</v>
@@ -29975,7 +29975,7 @@
         <v>1522</v>
       </c>
       <c r="E630">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F630" t="s">
         <v>1524</v>
@@ -30010,7 +30010,7 @@
         <v>1522</v>
       </c>
       <c r="E631">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F631" t="s">
         <v>1524</v>
@@ -30045,7 +30045,7 @@
         <v>1522</v>
       </c>
       <c r="E632">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F632" t="s">
         <v>1524</v>
@@ -30080,7 +30080,7 @@
         <v>1523</v>
       </c>
       <c r="E633">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F633" t="s">
         <v>1524</v>
@@ -30115,7 +30115,7 @@
         <v>1523</v>
       </c>
       <c r="E634">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F634" t="s">
         <v>1524</v>
@@ -30150,7 +30150,7 @@
         <v>1523</v>
       </c>
       <c r="E635">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F635" t="s">
         <v>1524</v>
@@ -30185,7 +30185,7 @@
         <v>1523</v>
       </c>
       <c r="E636">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F636" t="s">
         <v>1524</v>
@@ -30220,7 +30220,7 @@
         <v>1523</v>
       </c>
       <c r="E637">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F637" t="s">
         <v>1524</v>

--- a/BacklogGATEAutoCompleto.xlsx
+++ b/BacklogGATEAutoCompleto.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6391" uniqueCount="2477">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6391" uniqueCount="2479">
   <si>
     <t>NUCLEO</t>
   </si>
@@ -7402,49 +7402,55 @@
     <t>###   SEM TEMA   ###</t>
   </si>
   <si>
+    <t>ECONOMICIDADE OBRAS,ECONOMICIDADE CONTÁBIL</t>
+  </si>
+  <si>
+    <t>AVALIAÇÃO DE IMÓVEIS,GEOLOGIA</t>
+  </si>
+  <si>
+    <t>ENGENHARIA CIVIL,FENOMENOS DE ENERGIA E INFORMAÇÃO</t>
+  </si>
+  <si>
+    <t>ENGENHARIA CIVIL,ENGENHARIA QUÍMICA,FENOMENOS DE ENERGIA E INFORMAÇÃO</t>
+  </si>
+  <si>
+    <t>AVALIAÇÃO DE IMÓVEIS,ECONOMICIDADE OBRAS</t>
+  </si>
+  <si>
+    <t>ENGENHARIA FLORESTAL,URBANISMO</t>
+  </si>
+  <si>
+    <t>FARMÁCIA,SAÚDE</t>
+  </si>
+  <si>
+    <t>URBANISMO,BIOLOGIA</t>
+  </si>
+  <si>
+    <t>BIOLOGIA,ENGENHARIA AMBIENTAL</t>
+  </si>
+  <si>
     <t>ECONOMICIDADE CONTÁBIL,ECONOMICIDADE OBRAS</t>
   </si>
   <si>
-    <t>AVALIAÇÃO DE IMÓVEIS,GEOLOGIA</t>
-  </si>
-  <si>
-    <t>ENGENHARIA CIVIL,FENOMENOS DE ENERGIA E INFORMAÇÃO</t>
-  </si>
-  <si>
-    <t>ENGENHARIA CIVIL,ENGENHARIA QUÍMICA,FENOMENOS DE ENERGIA E INFORMAÇÃO</t>
-  </si>
-  <si>
-    <t>AVALIAÇÃO DE IMÓVEIS,ECONOMICIDADE OBRAS</t>
-  </si>
-  <si>
-    <t>ENGENHARIA FLORESTAL,URBANISMO</t>
-  </si>
-  <si>
-    <t>URBANISMO,BIOLOGIA</t>
-  </si>
-  <si>
-    <t>FARMÁCIA,SAÚDE</t>
-  </si>
-  <si>
-    <t>BIOLOGIA,ENGENHARIA AMBIENTAL</t>
-  </si>
-  <si>
-    <t>MOBILIDADE E TRANSPORTE,URBANISMO,BIOLOGIA,RECURSOS HÍDRICOS</t>
+    <t>URBANISMO,ENGENHARIA FLORESTAL</t>
+  </si>
+  <si>
+    <t>URBANISMO,BIOLOGIA,MOBILIDADE E TRANSPORTE,RECURSOS HÍDRICOS</t>
   </si>
   <si>
     <t>ENGENHARIA QUÍMICA,RESÍDUOS SÓLIDOS</t>
   </si>
   <si>
-    <t>ENGENHARIA AMBIENTAL,BIOLOGIA</t>
-  </si>
-  <si>
     <t>ENGENHARIA CIVIL,MOBILIDADE E TRANSPORTE</t>
   </si>
   <si>
+    <t>ECONOMICIDADE CONTÁBIL,MOBILIDADE E TRANSPORTE</t>
+  </si>
+  <si>
     <t>GEOTECNIA,ENGENHARIA CIVIL</t>
   </si>
   <si>
-    <t>ORÇAMENTO,ECONOMICIDADE CONTÁBIL,AVALIAÇÃO DE IMÓVEIS,SAÚDE,SAÚDE MENTAL,URBANISMO,ECONOMIA,PSICOLOGIA,MOBILIDADE E TRANSPORTE,ASSISTÊNCIA SOCIAL</t>
+    <t>ASSISTÊNCIA SOCIAL,MOBILIDADE E TRANSPORTE,AVALIAÇÃO DE IMÓVEIS,ECONOMICIDADE CONTÁBIL,SAÚDE,ECONOMIA,SAÚDE MENTAL,PSICOLOGIA,URBANISMO,ORÇAMENTO</t>
   </si>
 </sst>
 </file>
@@ -25411,7 +25417,7 @@
         <v>2383</v>
       </c>
       <c r="L502" t="s">
-        <v>2468</v>
+        <v>2407</v>
       </c>
     </row>
     <row r="503" spans="1:12">
@@ -25551,7 +25557,7 @@
         <v>2321</v>
       </c>
       <c r="L506" t="s">
-        <v>2469</v>
+        <v>2468</v>
       </c>
     </row>
     <row r="507" spans="1:12">
@@ -25977,7 +25983,7 @@
         <v>2310</v>
       </c>
       <c r="L518" t="s">
-        <v>2407</v>
+        <v>2469</v>
       </c>
     </row>
     <row r="519" spans="1:12">
@@ -26117,7 +26123,7 @@
         <v>2315</v>
       </c>
       <c r="L522" t="s">
-        <v>2462</v>
+        <v>2471</v>
       </c>
     </row>
     <row r="523" spans="1:12">
@@ -26826,7 +26832,7 @@
         <v>2317</v>
       </c>
       <c r="L542" t="s">
-        <v>2467</v>
+        <v>2472</v>
       </c>
     </row>
     <row r="543" spans="1:12">
@@ -27214,7 +27220,7 @@
         <v>2286</v>
       </c>
       <c r="L553" t="s">
-        <v>2471</v>
+        <v>2473</v>
       </c>
     </row>
     <row r="554" spans="1:12">
@@ -27497,7 +27503,7 @@
         <v>2281</v>
       </c>
       <c r="L561" t="s">
-        <v>2472</v>
+        <v>2474</v>
       </c>
     </row>
     <row r="562" spans="1:12">
@@ -28387,7 +28393,7 @@
         <v>2312</v>
       </c>
       <c r="L586" t="s">
-        <v>2473</v>
+        <v>2470</v>
       </c>
     </row>
     <row r="587" spans="1:12">
@@ -28457,7 +28463,7 @@
         <v>2391</v>
       </c>
       <c r="L588" t="s">
-        <v>2474</v>
+        <v>2475</v>
       </c>
     </row>
     <row r="589" spans="1:12">
@@ -29875,7 +29881,7 @@
         <v>2325</v>
       </c>
       <c r="L628" t="s">
-        <v>2432</v>
+        <v>2476</v>
       </c>
     </row>
     <row r="629" spans="1:12">
@@ -30120,7 +30126,7 @@
         <v>2394</v>
       </c>
       <c r="L635" t="s">
-        <v>2475</v>
+        <v>2477</v>
       </c>
     </row>
     <row r="636" spans="1:12">
@@ -30152,7 +30158,7 @@
         <v>2394</v>
       </c>
       <c r="L636" t="s">
-        <v>2476</v>
+        <v>2478</v>
       </c>
     </row>
   </sheetData>

--- a/BacklogGATEAutoCompleto.xlsx
+++ b/BacklogGATEAutoCompleto.xlsx
@@ -7863,7 +7863,7 @@
         <v>1307</v>
       </c>
       <c r="E2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="F2" t="s">
         <v>1518</v>
@@ -7898,7 +7898,7 @@
         <v>1308</v>
       </c>
       <c r="E3">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="F3" t="s">
         <v>1518</v>
@@ -7933,7 +7933,7 @@
         <v>1309</v>
       </c>
       <c r="E4">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="F4" t="s">
         <v>1518</v>
@@ -7968,7 +7968,7 @@
         <v>1310</v>
       </c>
       <c r="E5">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="F5" t="s">
         <v>1518</v>
@@ -8003,7 +8003,7 @@
         <v>1311</v>
       </c>
       <c r="E6">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="F6" t="s">
         <v>1518</v>
@@ -8038,7 +8038,7 @@
         <v>1312</v>
       </c>
       <c r="E7">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F7" t="s">
         <v>1518</v>
@@ -8073,7 +8073,7 @@
         <v>1313</v>
       </c>
       <c r="E8">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="F8" t="s">
         <v>1518</v>
@@ -8108,7 +8108,7 @@
         <v>1313</v>
       </c>
       <c r="E9">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="F9" t="s">
         <v>1518</v>
@@ -8143,7 +8143,7 @@
         <v>1314</v>
       </c>
       <c r="E10">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F10" t="s">
         <v>1518</v>
@@ -8178,7 +8178,7 @@
         <v>1315</v>
       </c>
       <c r="E11">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="F11" t="s">
         <v>1518</v>
@@ -8213,7 +8213,7 @@
         <v>1316</v>
       </c>
       <c r="E12">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F12" t="s">
         <v>1518</v>
@@ -8248,7 +8248,7 @@
         <v>1316</v>
       </c>
       <c r="E13">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F13" t="s">
         <v>1518</v>
@@ -8283,7 +8283,7 @@
         <v>1317</v>
       </c>
       <c r="E14">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="F14" t="s">
         <v>1518</v>
@@ -8318,7 +8318,7 @@
         <v>1317</v>
       </c>
       <c r="E15">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="F15" t="s">
         <v>1518</v>
@@ -8353,7 +8353,7 @@
         <v>1318</v>
       </c>
       <c r="E16">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="F16" t="s">
         <v>1518</v>
@@ -8388,7 +8388,7 @@
         <v>1319</v>
       </c>
       <c r="E17">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="F17" t="s">
         <v>1518</v>
@@ -8423,7 +8423,7 @@
         <v>1320</v>
       </c>
       <c r="E18">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="F18" t="s">
         <v>1518</v>
@@ -8458,7 +8458,7 @@
         <v>1321</v>
       </c>
       <c r="E19">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="F19" t="s">
         <v>1518</v>
@@ -8493,7 +8493,7 @@
         <v>1322</v>
       </c>
       <c r="E20">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="F20" t="s">
         <v>1518</v>
@@ -8531,7 +8531,7 @@
         <v>1323</v>
       </c>
       <c r="E21">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="F21" t="s">
         <v>1518</v>
@@ -8566,7 +8566,7 @@
         <v>1324</v>
       </c>
       <c r="E22">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F22" t="s">
         <v>1518</v>
@@ -8601,7 +8601,7 @@
         <v>1325</v>
       </c>
       <c r="E23">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F23" t="s">
         <v>1518</v>
@@ -8636,7 +8636,7 @@
         <v>1326</v>
       </c>
       <c r="E24">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F24" t="s">
         <v>1518</v>
@@ -8671,7 +8671,7 @@
         <v>1327</v>
       </c>
       <c r="E25">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="F25" t="s">
         <v>1518</v>
@@ -8706,7 +8706,7 @@
         <v>1328</v>
       </c>
       <c r="E26">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F26" t="s">
         <v>1518</v>
@@ -8741,7 +8741,7 @@
         <v>1329</v>
       </c>
       <c r="E27">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F27" t="s">
         <v>1518</v>
@@ -8776,7 +8776,7 @@
         <v>1330</v>
       </c>
       <c r="E28">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F28" t="s">
         <v>1518</v>
@@ -8811,7 +8811,7 @@
         <v>1331</v>
       </c>
       <c r="E29">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F29" t="s">
         <v>1518</v>
@@ -8846,7 +8846,7 @@
         <v>1332</v>
       </c>
       <c r="E30">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F30" t="s">
         <v>1518</v>
@@ -8881,7 +8881,7 @@
         <v>1333</v>
       </c>
       <c r="E31">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F31" t="s">
         <v>1518</v>
@@ -8916,7 +8916,7 @@
         <v>1334</v>
       </c>
       <c r="E32">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F32" t="s">
         <v>1518</v>
@@ -8951,7 +8951,7 @@
         <v>1334</v>
       </c>
       <c r="E33">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F33" t="s">
         <v>1518</v>
@@ -8986,7 +8986,7 @@
         <v>1335</v>
       </c>
       <c r="E34">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F34" t="s">
         <v>1518</v>
@@ -9021,7 +9021,7 @@
         <v>1336</v>
       </c>
       <c r="E35">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F35" t="s">
         <v>1518</v>
@@ -9056,7 +9056,7 @@
         <v>1336</v>
       </c>
       <c r="E36">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F36" t="s">
         <v>1518</v>
@@ -9091,7 +9091,7 @@
         <v>1337</v>
       </c>
       <c r="E37">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F37" t="s">
         <v>1518</v>
@@ -9126,7 +9126,7 @@
         <v>1337</v>
       </c>
       <c r="E38">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F38" t="s">
         <v>1518</v>
@@ -9161,7 +9161,7 @@
         <v>1338</v>
       </c>
       <c r="E39">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F39" t="s">
         <v>1518</v>
@@ -9196,7 +9196,7 @@
         <v>1339</v>
       </c>
       <c r="E40">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F40" t="s">
         <v>1518</v>
@@ -9231,7 +9231,7 @@
         <v>1340</v>
       </c>
       <c r="E41">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F41" t="s">
         <v>1518</v>
@@ -9266,7 +9266,7 @@
         <v>1341</v>
       </c>
       <c r="E42">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F42" t="s">
         <v>1518</v>
@@ -9301,7 +9301,7 @@
         <v>1342</v>
       </c>
       <c r="E43">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F43" t="s">
         <v>1518</v>
@@ -9336,7 +9336,7 @@
         <v>1343</v>
       </c>
       <c r="E44">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F44" t="s">
         <v>1518</v>
@@ -9371,7 +9371,7 @@
         <v>1344</v>
       </c>
       <c r="E45">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F45" t="s">
         <v>1518</v>
@@ -9406,7 +9406,7 @@
         <v>1345</v>
       </c>
       <c r="E46">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F46" t="s">
         <v>1518</v>
@@ -9441,7 +9441,7 @@
         <v>1346</v>
       </c>
       <c r="E47">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F47" t="s">
         <v>1518</v>
@@ -9476,7 +9476,7 @@
         <v>1347</v>
       </c>
       <c r="E48">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F48" t="s">
         <v>1518</v>
@@ -9511,7 +9511,7 @@
         <v>1348</v>
       </c>
       <c r="E49">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F49" t="s">
         <v>1518</v>
@@ -9546,7 +9546,7 @@
         <v>1348</v>
       </c>
       <c r="E50">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F50" t="s">
         <v>1518</v>
@@ -9581,7 +9581,7 @@
         <v>1348</v>
       </c>
       <c r="E51">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F51" t="s">
         <v>1518</v>
@@ -9616,7 +9616,7 @@
         <v>1349</v>
       </c>
       <c r="E52">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F52" t="s">
         <v>1518</v>
@@ -9651,7 +9651,7 @@
         <v>1350</v>
       </c>
       <c r="E53">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F53" t="s">
         <v>1518</v>
@@ -9686,7 +9686,7 @@
         <v>1351</v>
       </c>
       <c r="E54">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F54" t="s">
         <v>1518</v>
@@ -9721,7 +9721,7 @@
         <v>1352</v>
       </c>
       <c r="E55">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F55" t="s">
         <v>1518</v>
@@ -9756,7 +9756,7 @@
         <v>1353</v>
       </c>
       <c r="E56">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F56" t="s">
         <v>1518</v>
@@ -9791,7 +9791,7 @@
         <v>1353</v>
       </c>
       <c r="E57">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F57" t="s">
         <v>1518</v>
@@ -9826,7 +9826,7 @@
         <v>1354</v>
       </c>
       <c r="E58">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F58" t="s">
         <v>1518</v>
@@ -9861,7 +9861,7 @@
         <v>1355</v>
       </c>
       <c r="E59">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F59" t="s">
         <v>1518</v>
@@ -9896,7 +9896,7 @@
         <v>1355</v>
       </c>
       <c r="E60">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F60" t="s">
         <v>1518</v>
@@ -9931,7 +9931,7 @@
         <v>1355</v>
       </c>
       <c r="E61">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F61" t="s">
         <v>1519</v>
@@ -9966,7 +9966,7 @@
         <v>1355</v>
       </c>
       <c r="E62">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F62" t="s">
         <v>1518</v>
@@ -10001,7 +10001,7 @@
         <v>1356</v>
       </c>
       <c r="E63">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F63" t="s">
         <v>1518</v>
@@ -10036,7 +10036,7 @@
         <v>1357</v>
       </c>
       <c r="E64">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F64" t="s">
         <v>1518</v>
@@ -10071,7 +10071,7 @@
         <v>1357</v>
       </c>
       <c r="E65">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F65" t="s">
         <v>1518</v>
@@ -10106,7 +10106,7 @@
         <v>1358</v>
       </c>
       <c r="E66">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F66" t="s">
         <v>1518</v>
@@ -10141,7 +10141,7 @@
         <v>1359</v>
       </c>
       <c r="E67">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F67" t="s">
         <v>1518</v>
@@ -10176,7 +10176,7 @@
         <v>1360</v>
       </c>
       <c r="E68">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F68" t="s">
         <v>1518</v>
@@ -10211,7 +10211,7 @@
         <v>1361</v>
       </c>
       <c r="E69">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F69" t="s">
         <v>1518</v>
@@ -10246,7 +10246,7 @@
         <v>1361</v>
       </c>
       <c r="E70">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F70" t="s">
         <v>1518</v>
@@ -10281,7 +10281,7 @@
         <v>1361</v>
       </c>
       <c r="E71">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F71" t="s">
         <v>1518</v>
@@ -10316,7 +10316,7 @@
         <v>1361</v>
       </c>
       <c r="E72">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F72" t="s">
         <v>1518</v>
@@ -10351,7 +10351,7 @@
         <v>1361</v>
       </c>
       <c r="E73">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F73" t="s">
         <v>1518</v>
@@ -10386,7 +10386,7 @@
         <v>1361</v>
       </c>
       <c r="E74">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F74" t="s">
         <v>1518</v>
@@ -10421,7 +10421,7 @@
         <v>1362</v>
       </c>
       <c r="E75">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F75" t="s">
         <v>1518</v>
@@ -10456,7 +10456,7 @@
         <v>1363</v>
       </c>
       <c r="E76">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F76" t="s">
         <v>1518</v>
@@ -10491,7 +10491,7 @@
         <v>1364</v>
       </c>
       <c r="E77">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F77" t="s">
         <v>1518</v>
@@ -10526,7 +10526,7 @@
         <v>1364</v>
       </c>
       <c r="E78">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F78" t="s">
         <v>1518</v>
@@ -10561,7 +10561,7 @@
         <v>1365</v>
       </c>
       <c r="E79">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F79" t="s">
         <v>1520</v>
@@ -10596,7 +10596,7 @@
         <v>1366</v>
       </c>
       <c r="E80">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F80" t="s">
         <v>1518</v>
@@ -10631,7 +10631,7 @@
         <v>1367</v>
       </c>
       <c r="E81">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F81" t="s">
         <v>1518</v>
@@ -10666,7 +10666,7 @@
         <v>1368</v>
       </c>
       <c r="E82">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F82" t="s">
         <v>1518</v>
@@ -10701,7 +10701,7 @@
         <v>1369</v>
       </c>
       <c r="E83">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F83" t="s">
         <v>1518</v>
@@ -10736,7 +10736,7 @@
         <v>1370</v>
       </c>
       <c r="E84">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F84" t="s">
         <v>1518</v>
@@ -10771,7 +10771,7 @@
         <v>1371</v>
       </c>
       <c r="E85">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F85" t="s">
         <v>1518</v>
@@ -10806,7 +10806,7 @@
         <v>1372</v>
       </c>
       <c r="E86">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F86" t="s">
         <v>1518</v>
@@ -10841,7 +10841,7 @@
         <v>1372</v>
       </c>
       <c r="E87">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F87" t="s">
         <v>1518</v>
@@ -10876,7 +10876,7 @@
         <v>1373</v>
       </c>
       <c r="E88">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F88" t="s">
         <v>1518</v>
@@ -10911,7 +10911,7 @@
         <v>1373</v>
       </c>
       <c r="E89">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F89" t="s">
         <v>1518</v>
@@ -10946,7 +10946,7 @@
         <v>1373</v>
       </c>
       <c r="E90">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F90" t="s">
         <v>1518</v>
@@ -10981,7 +10981,7 @@
         <v>1374</v>
       </c>
       <c r="E91">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F91" t="s">
         <v>1518</v>
@@ -11016,7 +11016,7 @@
         <v>1374</v>
       </c>
       <c r="E92">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F92" t="s">
         <v>1518</v>
@@ -11051,7 +11051,7 @@
         <v>1375</v>
       </c>
       <c r="E93">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F93" t="s">
         <v>1518</v>
@@ -11086,7 +11086,7 @@
         <v>1376</v>
       </c>
       <c r="E94">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F94" t="s">
         <v>1518</v>
@@ -11121,7 +11121,7 @@
         <v>1377</v>
       </c>
       <c r="E95">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F95" t="s">
         <v>1518</v>
@@ -11156,7 +11156,7 @@
         <v>1377</v>
       </c>
       <c r="E96">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F96" t="s">
         <v>1518</v>
@@ -11191,7 +11191,7 @@
         <v>1378</v>
       </c>
       <c r="E97">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F97" t="s">
         <v>1518</v>
@@ -11226,7 +11226,7 @@
         <v>1378</v>
       </c>
       <c r="E98">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F98" t="s">
         <v>1518</v>
@@ -11261,7 +11261,7 @@
         <v>1379</v>
       </c>
       <c r="E99">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F99" t="s">
         <v>1518</v>
@@ -11296,7 +11296,7 @@
         <v>1380</v>
       </c>
       <c r="E100">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F100" t="s">
         <v>1518</v>
@@ -11331,7 +11331,7 @@
         <v>1380</v>
       </c>
       <c r="E101">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F101" t="s">
         <v>1518</v>
@@ -11366,7 +11366,7 @@
         <v>1381</v>
       </c>
       <c r="E102">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F102" t="s">
         <v>1518</v>
@@ -11401,7 +11401,7 @@
         <v>1382</v>
       </c>
       <c r="E103">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F103" t="s">
         <v>1518</v>
@@ -11436,7 +11436,7 @@
         <v>1382</v>
       </c>
       <c r="E104">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F104" t="s">
         <v>1518</v>
@@ -11471,7 +11471,7 @@
         <v>1383</v>
       </c>
       <c r="E105">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F105" t="s">
         <v>1518</v>
@@ -11506,7 +11506,7 @@
         <v>1384</v>
       </c>
       <c r="E106">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F106" t="s">
         <v>1518</v>
@@ -11544,7 +11544,7 @@
         <v>1384</v>
       </c>
       <c r="E107">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F107" t="s">
         <v>1518</v>
@@ -11579,7 +11579,7 @@
         <v>1384</v>
       </c>
       <c r="E108">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F108" t="s">
         <v>1518</v>
@@ -11614,7 +11614,7 @@
         <v>1384</v>
       </c>
       <c r="E109">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F109" t="s">
         <v>1518</v>
@@ -11649,7 +11649,7 @@
         <v>1385</v>
       </c>
       <c r="E110">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F110" t="s">
         <v>1519</v>
@@ -11684,7 +11684,7 @@
         <v>1386</v>
       </c>
       <c r="E111">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F111" t="s">
         <v>1518</v>
@@ -11719,7 +11719,7 @@
         <v>1386</v>
       </c>
       <c r="E112">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F112" t="s">
         <v>1518</v>
@@ -11754,7 +11754,7 @@
         <v>1386</v>
       </c>
       <c r="E113">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F113" t="s">
         <v>1518</v>
@@ -11789,7 +11789,7 @@
         <v>1386</v>
       </c>
       <c r="E114">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F114" t="s">
         <v>1518</v>
@@ -11824,7 +11824,7 @@
         <v>1387</v>
       </c>
       <c r="E115">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F115" t="s">
         <v>1518</v>
@@ -11859,7 +11859,7 @@
         <v>1387</v>
       </c>
       <c r="E116">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F116" t="s">
         <v>1518</v>
@@ -11894,7 +11894,7 @@
         <v>1387</v>
       </c>
       <c r="E117">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F117" t="s">
         <v>1518</v>
@@ -11929,7 +11929,7 @@
         <v>1387</v>
       </c>
       <c r="E118">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F118" t="s">
         <v>1518</v>
@@ -11964,7 +11964,7 @@
         <v>1387</v>
       </c>
       <c r="E119">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F119" t="s">
         <v>1518</v>
@@ -11999,7 +11999,7 @@
         <v>1387</v>
       </c>
       <c r="E120">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F120" t="s">
         <v>1518</v>
@@ -12034,7 +12034,7 @@
         <v>1387</v>
       </c>
       <c r="E121">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F121" t="s">
         <v>1518</v>
@@ -12069,7 +12069,7 @@
         <v>1388</v>
       </c>
       <c r="E122">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F122" t="s">
         <v>1518</v>
@@ -12104,7 +12104,7 @@
         <v>1389</v>
       </c>
       <c r="E123">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F123" t="s">
         <v>1518</v>
@@ -12139,7 +12139,7 @@
         <v>1390</v>
       </c>
       <c r="E124">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F124" t="s">
         <v>1518</v>
@@ -12174,7 +12174,7 @@
         <v>1390</v>
       </c>
       <c r="E125">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F125" t="s">
         <v>1518</v>
@@ -12209,7 +12209,7 @@
         <v>1390</v>
       </c>
       <c r="E126">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F126" t="s">
         <v>1518</v>
@@ -12244,7 +12244,7 @@
         <v>1391</v>
       </c>
       <c r="E127">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F127" t="s">
         <v>1518</v>
@@ -12279,7 +12279,7 @@
         <v>1391</v>
       </c>
       <c r="E128">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F128" t="s">
         <v>1518</v>
@@ -12314,7 +12314,7 @@
         <v>1391</v>
       </c>
       <c r="E129">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F129" t="s">
         <v>1518</v>
@@ -12349,7 +12349,7 @@
         <v>1391</v>
       </c>
       <c r="E130">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F130" t="s">
         <v>1518</v>
@@ -12384,7 +12384,7 @@
         <v>1391</v>
       </c>
       <c r="E131">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F131" t="s">
         <v>1518</v>
@@ -12419,7 +12419,7 @@
         <v>1391</v>
       </c>
       <c r="E132">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F132" t="s">
         <v>1518</v>
@@ -12454,7 +12454,7 @@
         <v>1391</v>
       </c>
       <c r="E133">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F133" t="s">
         <v>1518</v>
@@ -12489,7 +12489,7 @@
         <v>1391</v>
       </c>
       <c r="E134">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F134" t="s">
         <v>1518</v>
@@ -12524,7 +12524,7 @@
         <v>1391</v>
       </c>
       <c r="E135">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F135" t="s">
         <v>1518</v>
@@ -12559,7 +12559,7 @@
         <v>1392</v>
       </c>
       <c r="E136">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F136" t="s">
         <v>1518</v>
@@ -12594,7 +12594,7 @@
         <v>1392</v>
       </c>
       <c r="E137">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F137" t="s">
         <v>1518</v>
@@ -12629,7 +12629,7 @@
         <v>1392</v>
       </c>
       <c r="E138">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F138" t="s">
         <v>1518</v>
@@ -12664,7 +12664,7 @@
         <v>1393</v>
       </c>
       <c r="E139">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F139" t="s">
         <v>1518</v>
@@ -12699,7 +12699,7 @@
         <v>1393</v>
       </c>
       <c r="E140">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F140" t="s">
         <v>1519</v>
@@ -12734,7 +12734,7 @@
         <v>1393</v>
       </c>
       <c r="E141">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F141" t="s">
         <v>1518</v>
@@ -12769,7 +12769,7 @@
         <v>1394</v>
       </c>
       <c r="E142">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F142" t="s">
         <v>1518</v>
@@ -12804,7 +12804,7 @@
         <v>1394</v>
       </c>
       <c r="E143">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F143" t="s">
         <v>1518</v>
@@ -12839,7 +12839,7 @@
         <v>1395</v>
       </c>
       <c r="E144">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F144" t="s">
         <v>1518</v>
@@ -12874,7 +12874,7 @@
         <v>1395</v>
       </c>
       <c r="E145">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F145" t="s">
         <v>1518</v>
@@ -12909,7 +12909,7 @@
         <v>1396</v>
       </c>
       <c r="E146">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F146" t="s">
         <v>1518</v>
@@ -12944,7 +12944,7 @@
         <v>1396</v>
       </c>
       <c r="E147">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F147" t="s">
         <v>1518</v>
@@ -12979,7 +12979,7 @@
         <v>1397</v>
       </c>
       <c r="E148">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F148" t="s">
         <v>1518</v>
@@ -13014,7 +13014,7 @@
         <v>1397</v>
       </c>
       <c r="E149">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F149" t="s">
         <v>1518</v>
@@ -13049,7 +13049,7 @@
         <v>1397</v>
       </c>
       <c r="E150">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F150" t="s">
         <v>1518</v>
@@ -13084,7 +13084,7 @@
         <v>1398</v>
       </c>
       <c r="E151">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F151" t="s">
         <v>1518</v>
@@ -13119,7 +13119,7 @@
         <v>1398</v>
       </c>
       <c r="E152">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F152" t="s">
         <v>1518</v>
@@ -13154,7 +13154,7 @@
         <v>1399</v>
       </c>
       <c r="E153">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F153" t="s">
         <v>1518</v>
@@ -13189,7 +13189,7 @@
         <v>1400</v>
       </c>
       <c r="E154">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F154" t="s">
         <v>1518</v>
@@ -13224,7 +13224,7 @@
         <v>1400</v>
       </c>
       <c r="E155">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F155" t="s">
         <v>1518</v>
@@ -13259,7 +13259,7 @@
         <v>1400</v>
       </c>
       <c r="E156">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F156" t="s">
         <v>1518</v>
@@ -13294,7 +13294,7 @@
         <v>1400</v>
       </c>
       <c r="E157">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F157" t="s">
         <v>1518</v>
@@ -13329,7 +13329,7 @@
         <v>1401</v>
       </c>
       <c r="E158">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F158" t="s">
         <v>1518</v>
@@ -13364,7 +13364,7 @@
         <v>1402</v>
       </c>
       <c r="E159">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F159" t="s">
         <v>1518</v>
@@ -13399,7 +13399,7 @@
         <v>1402</v>
       </c>
       <c r="E160">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F160" t="s">
         <v>1518</v>
@@ -13434,7 +13434,7 @@
         <v>1402</v>
       </c>
       <c r="E161">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F161" t="s">
         <v>1518</v>
@@ -13469,7 +13469,7 @@
         <v>1402</v>
       </c>
       <c r="E162">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F162" t="s">
         <v>1518</v>
@@ -13504,7 +13504,7 @@
         <v>1402</v>
       </c>
       <c r="E163">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F163" t="s">
         <v>1518</v>
@@ -13539,7 +13539,7 @@
         <v>1403</v>
       </c>
       <c r="E164">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F164" t="s">
         <v>1518</v>
@@ -13574,7 +13574,7 @@
         <v>1403</v>
       </c>
       <c r="E165">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F165" t="s">
         <v>1518</v>
@@ -13609,7 +13609,7 @@
         <v>1403</v>
       </c>
       <c r="E166">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F166" t="s">
         <v>1518</v>
@@ -13644,7 +13644,7 @@
         <v>1403</v>
       </c>
       <c r="E167">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F167" t="s">
         <v>1518</v>
@@ -13679,7 +13679,7 @@
         <v>1403</v>
       </c>
       <c r="E168">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F168" t="s">
         <v>1518</v>
@@ -13714,7 +13714,7 @@
         <v>1403</v>
       </c>
       <c r="E169">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F169" t="s">
         <v>1518</v>
@@ -13749,7 +13749,7 @@
         <v>1404</v>
       </c>
       <c r="E170">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F170" t="s">
         <v>1518</v>
@@ -13784,7 +13784,7 @@
         <v>1404</v>
       </c>
       <c r="E171">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F171" t="s">
         <v>1518</v>
@@ -13819,7 +13819,7 @@
         <v>1404</v>
       </c>
       <c r="E172">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F172" t="s">
         <v>1518</v>
@@ -13854,7 +13854,7 @@
         <v>1405</v>
       </c>
       <c r="E173">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F173" t="s">
         <v>1518</v>
@@ -13889,7 +13889,7 @@
         <v>1405</v>
       </c>
       <c r="E174">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F174" t="s">
         <v>1518</v>
@@ -13924,7 +13924,7 @@
         <v>1406</v>
       </c>
       <c r="E175">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F175" t="s">
         <v>1518</v>
@@ -13959,7 +13959,7 @@
         <v>1407</v>
       </c>
       <c r="E176">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F176" t="s">
         <v>1518</v>
@@ -13994,7 +13994,7 @@
         <v>1407</v>
       </c>
       <c r="E177">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F177" t="s">
         <v>1518</v>
@@ -14029,7 +14029,7 @@
         <v>1408</v>
       </c>
       <c r="E178">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F178" t="s">
         <v>1518</v>
@@ -14064,7 +14064,7 @@
         <v>1409</v>
       </c>
       <c r="E179">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F179" t="s">
         <v>1518</v>
@@ -14099,7 +14099,7 @@
         <v>1409</v>
       </c>
       <c r="E180">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F180" t="s">
         <v>1518</v>
@@ -14134,7 +14134,7 @@
         <v>1410</v>
       </c>
       <c r="E181">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F181" t="s">
         <v>1518</v>
@@ -14169,7 +14169,7 @@
         <v>1410</v>
       </c>
       <c r="E182">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F182" t="s">
         <v>1518</v>
@@ -14204,7 +14204,7 @@
         <v>1411</v>
       </c>
       <c r="E183">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F183" t="s">
         <v>1518</v>
@@ -14239,7 +14239,7 @@
         <v>1411</v>
       </c>
       <c r="E184">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F184" t="s">
         <v>1518</v>
@@ -14274,7 +14274,7 @@
         <v>1411</v>
       </c>
       <c r="E185">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F185" t="s">
         <v>1518</v>
@@ -14309,7 +14309,7 @@
         <v>1412</v>
       </c>
       <c r="E186">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F186" t="s">
         <v>1518</v>
@@ -14344,7 +14344,7 @@
         <v>1412</v>
       </c>
       <c r="E187">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F187" t="s">
         <v>1518</v>
@@ -14379,7 +14379,7 @@
         <v>1413</v>
       </c>
       <c r="E188">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F188" t="s">
         <v>1518</v>
@@ -14414,7 +14414,7 @@
         <v>1414</v>
       </c>
       <c r="E189">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F189" t="s">
         <v>1518</v>
@@ -14449,7 +14449,7 @@
         <v>1414</v>
       </c>
       <c r="E190">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F190" t="s">
         <v>1518</v>
@@ -14484,7 +14484,7 @@
         <v>1414</v>
       </c>
       <c r="E191">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F191" t="s">
         <v>1518</v>
@@ -14519,7 +14519,7 @@
         <v>1415</v>
       </c>
       <c r="E192">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F192" t="s">
         <v>1518</v>
@@ -14554,7 +14554,7 @@
         <v>1415</v>
       </c>
       <c r="E193">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F193" t="s">
         <v>1518</v>
@@ -14589,7 +14589,7 @@
         <v>1416</v>
       </c>
       <c r="E194">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F194" t="s">
         <v>1518</v>
@@ -14624,7 +14624,7 @@
         <v>1416</v>
       </c>
       <c r="E195">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F195" t="s">
         <v>1520</v>
@@ -14659,7 +14659,7 @@
         <v>1416</v>
       </c>
       <c r="E196">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F196" t="s">
         <v>1518</v>
@@ -14694,7 +14694,7 @@
         <v>1417</v>
       </c>
       <c r="E197">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F197" t="s">
         <v>1518</v>
@@ -14729,7 +14729,7 @@
         <v>1417</v>
       </c>
       <c r="E198">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F198" t="s">
         <v>1518</v>
@@ -14767,7 +14767,7 @@
         <v>1417</v>
       </c>
       <c r="E199">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F199" t="s">
         <v>1518</v>
@@ -14802,7 +14802,7 @@
         <v>1417</v>
       </c>
       <c r="E200">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F200" t="s">
         <v>1518</v>
@@ -14837,7 +14837,7 @@
         <v>1417</v>
       </c>
       <c r="E201">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F201" t="s">
         <v>1518</v>
@@ -14872,7 +14872,7 @@
         <v>1417</v>
       </c>
       <c r="E202">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F202" t="s">
         <v>1518</v>
@@ -14907,7 +14907,7 @@
         <v>1418</v>
       </c>
       <c r="E203">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F203" t="s">
         <v>1518</v>
@@ -14942,7 +14942,7 @@
         <v>1418</v>
       </c>
       <c r="E204">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F204" t="s">
         <v>1518</v>
@@ -14977,7 +14977,7 @@
         <v>1418</v>
       </c>
       <c r="E205">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F205" t="s">
         <v>1518</v>
@@ -15012,7 +15012,7 @@
         <v>1419</v>
       </c>
       <c r="E206">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F206" t="s">
         <v>1518</v>
@@ -15047,7 +15047,7 @@
         <v>1419</v>
       </c>
       <c r="E207">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F207" t="s">
         <v>1518</v>
@@ -15082,7 +15082,7 @@
         <v>1419</v>
       </c>
       <c r="E208">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F208" t="s">
         <v>1518</v>
@@ -15117,7 +15117,7 @@
         <v>1420</v>
       </c>
       <c r="E209">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F209" t="s">
         <v>1518</v>
@@ -15152,7 +15152,7 @@
         <v>1420</v>
       </c>
       <c r="E210">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F210" t="s">
         <v>1518</v>
@@ -15187,7 +15187,7 @@
         <v>1420</v>
       </c>
       <c r="E211">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F211" t="s">
         <v>1518</v>
@@ -15222,7 +15222,7 @@
         <v>1421</v>
       </c>
       <c r="E212">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F212" t="s">
         <v>1518</v>
@@ -15257,7 +15257,7 @@
         <v>1421</v>
       </c>
       <c r="E213">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F213" t="s">
         <v>1518</v>
@@ -15292,7 +15292,7 @@
         <v>1421</v>
       </c>
       <c r="E214">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F214" t="s">
         <v>1518</v>
@@ -15327,7 +15327,7 @@
         <v>1421</v>
       </c>
       <c r="E215">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F215" t="s">
         <v>1518</v>
@@ -15362,7 +15362,7 @@
         <v>1421</v>
       </c>
       <c r="E216">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F216" t="s">
         <v>1518</v>
@@ -15397,7 +15397,7 @@
         <v>1422</v>
       </c>
       <c r="E217">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F217" t="s">
         <v>1518</v>
@@ -15432,7 +15432,7 @@
         <v>1423</v>
       </c>
       <c r="E218">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F218" t="s">
         <v>1518</v>
@@ -15467,7 +15467,7 @@
         <v>1423</v>
       </c>
       <c r="E219">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F219" t="s">
         <v>1521</v>
@@ -15502,7 +15502,7 @@
         <v>1423</v>
       </c>
       <c r="E220">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F220" t="s">
         <v>1518</v>
@@ -15537,7 +15537,7 @@
         <v>1423</v>
       </c>
       <c r="E221">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F221" t="s">
         <v>1518</v>
@@ -15572,7 +15572,7 @@
         <v>1423</v>
       </c>
       <c r="E222">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F222" t="s">
         <v>1518</v>
@@ -15607,7 +15607,7 @@
         <v>1424</v>
       </c>
       <c r="E223">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F223" t="s">
         <v>1518</v>
@@ -15642,7 +15642,7 @@
         <v>1424</v>
       </c>
       <c r="E224">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F224" t="s">
         <v>1518</v>
@@ -15677,7 +15677,7 @@
         <v>1424</v>
       </c>
       <c r="E225">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F225" t="s">
         <v>1518</v>
@@ -15712,7 +15712,7 @@
         <v>1424</v>
       </c>
       <c r="E226">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F226" t="s">
         <v>1518</v>
@@ -15747,7 +15747,7 @@
         <v>1425</v>
       </c>
       <c r="E227">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F227" t="s">
         <v>1518</v>
@@ -15782,7 +15782,7 @@
         <v>1426</v>
       </c>
       <c r="E228">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F228" t="s">
         <v>1518</v>
@@ -15820,7 +15820,7 @@
         <v>1427</v>
       </c>
       <c r="E229">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F229" t="s">
         <v>1518</v>
@@ -15855,7 +15855,7 @@
         <v>1427</v>
       </c>
       <c r="E230">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F230" t="s">
         <v>1518</v>
@@ -15890,7 +15890,7 @@
         <v>1427</v>
       </c>
       <c r="E231">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F231" t="s">
         <v>1518</v>
@@ -15925,7 +15925,7 @@
         <v>1427</v>
       </c>
       <c r="E232">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F232" t="s">
         <v>1518</v>
@@ -15960,7 +15960,7 @@
         <v>1428</v>
       </c>
       <c r="E233">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F233" t="s">
         <v>1518</v>
@@ -15995,7 +15995,7 @@
         <v>1428</v>
       </c>
       <c r="E234">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F234" t="s">
         <v>1518</v>
@@ -16030,7 +16030,7 @@
         <v>1429</v>
       </c>
       <c r="E235">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F235" t="s">
         <v>1518</v>
@@ -16065,7 +16065,7 @@
         <v>1429</v>
       </c>
       <c r="E236">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F236" t="s">
         <v>1518</v>
@@ -16100,7 +16100,7 @@
         <v>1430</v>
       </c>
       <c r="E237">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F237" t="s">
         <v>1518</v>
@@ -16135,7 +16135,7 @@
         <v>1430</v>
       </c>
       <c r="E238">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F238" t="s">
         <v>1518</v>
@@ -16170,7 +16170,7 @@
         <v>1430</v>
       </c>
       <c r="E239">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F239" t="s">
         <v>1518</v>
@@ -16205,7 +16205,7 @@
         <v>1431</v>
       </c>
       <c r="E240">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F240" t="s">
         <v>1518</v>
@@ -16240,7 +16240,7 @@
         <v>1431</v>
       </c>
       <c r="E241">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F241" t="s">
         <v>1518</v>
@@ -16275,7 +16275,7 @@
         <v>1431</v>
       </c>
       <c r="E242">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F242" t="s">
         <v>1518</v>
@@ -16310,7 +16310,7 @@
         <v>1432</v>
       </c>
       <c r="E243">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F243" t="s">
         <v>1518</v>
@@ -16345,7 +16345,7 @@
         <v>1433</v>
       </c>
       <c r="E244">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F244" t="s">
         <v>1518</v>
@@ -16380,7 +16380,7 @@
         <v>1433</v>
       </c>
       <c r="E245">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F245" t="s">
         <v>1518</v>
@@ -16415,7 +16415,7 @@
         <v>1433</v>
       </c>
       <c r="E246">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F246" t="s">
         <v>1518</v>
@@ -16450,7 +16450,7 @@
         <v>1433</v>
       </c>
       <c r="E247">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F247" t="s">
         <v>1518</v>
@@ -16485,7 +16485,7 @@
         <v>1434</v>
       </c>
       <c r="E248">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F248" t="s">
         <v>1518</v>
@@ -16520,7 +16520,7 @@
         <v>1434</v>
       </c>
       <c r="E249">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F249" t="s">
         <v>1518</v>
@@ -16555,7 +16555,7 @@
         <v>1434</v>
       </c>
       <c r="E250">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F250" t="s">
         <v>1518</v>
@@ -16590,7 +16590,7 @@
         <v>1435</v>
       </c>
       <c r="E251">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F251" t="s">
         <v>1518</v>
@@ -16625,7 +16625,7 @@
         <v>1435</v>
       </c>
       <c r="E252">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F252" t="s">
         <v>1518</v>
@@ -16660,7 +16660,7 @@
         <v>1436</v>
       </c>
       <c r="E253">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F253" t="s">
         <v>1518</v>
@@ -16695,7 +16695,7 @@
         <v>1436</v>
       </c>
       <c r="E254">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F254" t="s">
         <v>1518</v>
@@ -16730,7 +16730,7 @@
         <v>1436</v>
       </c>
       <c r="E255">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F255" t="s">
         <v>1518</v>
@@ -16765,7 +16765,7 @@
         <v>1436</v>
       </c>
       <c r="E256">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F256" t="s">
         <v>1518</v>
@@ -16800,7 +16800,7 @@
         <v>1436</v>
       </c>
       <c r="E257">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F257" t="s">
         <v>1518</v>
@@ -16835,7 +16835,7 @@
         <v>1437</v>
       </c>
       <c r="E258">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F258" t="s">
         <v>1518</v>
@@ -16870,7 +16870,7 @@
         <v>1437</v>
       </c>
       <c r="E259">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F259" t="s">
         <v>1518</v>
@@ -16905,7 +16905,7 @@
         <v>1437</v>
       </c>
       <c r="E260">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F260" t="s">
         <v>1518</v>
@@ -16940,7 +16940,7 @@
         <v>1438</v>
       </c>
       <c r="E261">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F261" t="s">
         <v>1518</v>
@@ -16975,7 +16975,7 @@
         <v>1439</v>
       </c>
       <c r="E262">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F262" t="s">
         <v>1518</v>
@@ -17010,7 +17010,7 @@
         <v>1440</v>
       </c>
       <c r="E263">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F263" t="s">
         <v>1518</v>
@@ -17045,7 +17045,7 @@
         <v>1440</v>
       </c>
       <c r="E264">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F264" t="s">
         <v>1518</v>
@@ -17080,7 +17080,7 @@
         <v>1440</v>
       </c>
       <c r="E265">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F265" t="s">
         <v>1518</v>
@@ -17115,7 +17115,7 @@
         <v>1440</v>
       </c>
       <c r="E266">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F266" t="s">
         <v>1518</v>
@@ -17150,7 +17150,7 @@
         <v>1440</v>
       </c>
       <c r="E267">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F267" t="s">
         <v>1518</v>
@@ -17185,7 +17185,7 @@
         <v>1441</v>
       </c>
       <c r="E268">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F268" t="s">
         <v>1518</v>
@@ -17220,7 +17220,7 @@
         <v>1441</v>
       </c>
       <c r="E269">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F269" t="s">
         <v>1518</v>
@@ -17255,7 +17255,7 @@
         <v>1442</v>
       </c>
       <c r="E270">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F270" t="s">
         <v>1518</v>
@@ -17290,7 +17290,7 @@
         <v>1442</v>
       </c>
       <c r="E271">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F271" t="s">
         <v>1518</v>
@@ -17325,7 +17325,7 @@
         <v>1443</v>
       </c>
       <c r="E272">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F272" t="s">
         <v>1518</v>
@@ -17360,7 +17360,7 @@
         <v>1444</v>
       </c>
       <c r="E273">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F273" t="s">
         <v>1518</v>
@@ -17395,7 +17395,7 @@
         <v>1445</v>
       </c>
       <c r="E274">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F274" t="s">
         <v>1518</v>
@@ -17430,7 +17430,7 @@
         <v>1445</v>
       </c>
       <c r="E275">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F275" t="s">
         <v>1518</v>
@@ -17465,7 +17465,7 @@
         <v>1446</v>
       </c>
       <c r="E276">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F276" t="s">
         <v>1518</v>
@@ -17500,7 +17500,7 @@
         <v>1446</v>
       </c>
       <c r="E277">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F277" t="s">
         <v>1518</v>
@@ -17535,7 +17535,7 @@
         <v>1446</v>
       </c>
       <c r="E278">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F278" t="s">
         <v>1518</v>
@@ -17570,7 +17570,7 @@
         <v>1447</v>
       </c>
       <c r="E279">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F279" t="s">
         <v>1518</v>
@@ -17605,7 +17605,7 @@
         <v>1447</v>
       </c>
       <c r="E280">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F280" t="s">
         <v>1518</v>
@@ -17640,7 +17640,7 @@
         <v>1447</v>
       </c>
       <c r="E281">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F281" t="s">
         <v>1518</v>
@@ -17675,7 +17675,7 @@
         <v>1447</v>
       </c>
       <c r="E282">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F282" t="s">
         <v>1518</v>
@@ -17710,7 +17710,7 @@
         <v>1447</v>
       </c>
       <c r="E283">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F283" t="s">
         <v>1518</v>
@@ -17745,7 +17745,7 @@
         <v>1447</v>
       </c>
       <c r="E284">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F284" t="s">
         <v>1518</v>
@@ -17780,7 +17780,7 @@
         <v>1447</v>
       </c>
       <c r="E285">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F285" t="s">
         <v>1518</v>
@@ -17815,7 +17815,7 @@
         <v>1447</v>
       </c>
       <c r="E286">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F286" t="s">
         <v>1518</v>
@@ -17850,7 +17850,7 @@
         <v>1447</v>
       </c>
       <c r="E287">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F287" t="s">
         <v>1518</v>
@@ -17885,7 +17885,7 @@
         <v>1448</v>
       </c>
       <c r="E288">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F288" t="s">
         <v>1518</v>
@@ -17920,7 +17920,7 @@
         <v>1448</v>
       </c>
       <c r="E289">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F289" t="s">
         <v>1518</v>
@@ -17955,7 +17955,7 @@
         <v>1448</v>
       </c>
       <c r="E290">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F290" t="s">
         <v>1518</v>
@@ -17990,7 +17990,7 @@
         <v>1449</v>
       </c>
       <c r="E291">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F291" t="s">
         <v>1518</v>
@@ -18025,7 +18025,7 @@
         <v>1450</v>
       </c>
       <c r="E292">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F292" t="s">
         <v>1518</v>
@@ -18060,7 +18060,7 @@
         <v>1450</v>
       </c>
       <c r="E293">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F293" t="s">
         <v>1518</v>
@@ -18095,7 +18095,7 @@
         <v>1450</v>
       </c>
       <c r="E294">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F294" t="s">
         <v>1518</v>
@@ -18130,7 +18130,7 @@
         <v>1450</v>
       </c>
       <c r="E295">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F295" t="s">
         <v>1518</v>
@@ -18165,7 +18165,7 @@
         <v>1450</v>
       </c>
       <c r="E296">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F296" t="s">
         <v>1518</v>
@@ -18200,7 +18200,7 @@
         <v>1450</v>
       </c>
       <c r="E297">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F297" t="s">
         <v>1518</v>
@@ -18235,7 +18235,7 @@
         <v>1451</v>
       </c>
       <c r="E298">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F298" t="s">
         <v>1518</v>
@@ -18270,7 +18270,7 @@
         <v>1451</v>
       </c>
       <c r="E299">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F299" t="s">
         <v>1518</v>
@@ -18305,7 +18305,7 @@
         <v>1451</v>
       </c>
       <c r="E300">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F300" t="s">
         <v>1518</v>
@@ -18340,7 +18340,7 @@
         <v>1451</v>
       </c>
       <c r="E301">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F301" t="s">
         <v>1518</v>
@@ -18378,7 +18378,7 @@
         <v>1451</v>
       </c>
       <c r="E302">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F302" t="s">
         <v>1518</v>
@@ -18413,7 +18413,7 @@
         <v>1451</v>
       </c>
       <c r="E303">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F303" t="s">
         <v>1518</v>
@@ -18448,7 +18448,7 @@
         <v>1451</v>
       </c>
       <c r="E304">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F304" t="s">
         <v>1518</v>
@@ -18483,7 +18483,7 @@
         <v>1451</v>
       </c>
       <c r="E305">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F305" t="s">
         <v>1518</v>
@@ -18518,7 +18518,7 @@
         <v>1451</v>
       </c>
       <c r="E306">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F306" t="s">
         <v>1518</v>
@@ -18553,7 +18553,7 @@
         <v>1452</v>
       </c>
       <c r="E307">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F307" t="s">
         <v>1519</v>
@@ -18588,7 +18588,7 @@
         <v>1453</v>
       </c>
       <c r="E308">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F308" t="s">
         <v>1522</v>
@@ -18623,7 +18623,7 @@
         <v>1454</v>
       </c>
       <c r="E309">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F309" t="s">
         <v>1518</v>
@@ -18658,7 +18658,7 @@
         <v>1455</v>
       </c>
       <c r="E310">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F310" t="s">
         <v>1518</v>
@@ -18693,7 +18693,7 @@
         <v>1455</v>
       </c>
       <c r="E311">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F311" t="s">
         <v>1518</v>
@@ -18728,7 +18728,7 @@
         <v>1456</v>
       </c>
       <c r="E312">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F312" t="s">
         <v>1518</v>
@@ -18763,7 +18763,7 @@
         <v>1457</v>
       </c>
       <c r="E313">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F313" t="s">
         <v>1521</v>
@@ -18798,7 +18798,7 @@
         <v>1457</v>
       </c>
       <c r="E314">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F314" t="s">
         <v>1518</v>
@@ -18833,7 +18833,7 @@
         <v>1457</v>
       </c>
       <c r="E315">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F315" t="s">
         <v>1518</v>
@@ -18868,7 +18868,7 @@
         <v>1457</v>
       </c>
       <c r="E316">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F316" t="s">
         <v>1518</v>
@@ -18903,7 +18903,7 @@
         <v>1457</v>
       </c>
       <c r="E317">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F317" t="s">
         <v>1518</v>
@@ -18938,7 +18938,7 @@
         <v>1457</v>
       </c>
       <c r="E318">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F318" t="s">
         <v>1518</v>
@@ -18973,7 +18973,7 @@
         <v>1458</v>
       </c>
       <c r="E319">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F319" t="s">
         <v>1518</v>
@@ -19008,7 +19008,7 @@
         <v>1459</v>
       </c>
       <c r="E320">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F320" t="s">
         <v>1518</v>
@@ -19043,7 +19043,7 @@
         <v>1459</v>
       </c>
       <c r="E321">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F321" t="s">
         <v>1518</v>
@@ -19078,7 +19078,7 @@
         <v>1459</v>
       </c>
       <c r="E322">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F322" t="s">
         <v>1518</v>
@@ -19116,7 +19116,7 @@
         <v>1459</v>
       </c>
       <c r="E323">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F323" t="s">
         <v>1518</v>
@@ -19151,7 +19151,7 @@
         <v>1460</v>
       </c>
       <c r="E324">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F324" t="s">
         <v>1518</v>
@@ -19186,7 +19186,7 @@
         <v>1460</v>
       </c>
       <c r="E325">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F325" t="s">
         <v>1518</v>
@@ -19221,7 +19221,7 @@
         <v>1460</v>
       </c>
       <c r="E326">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F326" t="s">
         <v>1518</v>
@@ -19256,7 +19256,7 @@
         <v>1460</v>
       </c>
       <c r="E327">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F327" t="s">
         <v>1518</v>
@@ -19291,7 +19291,7 @@
         <v>1460</v>
       </c>
       <c r="E328">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F328" t="s">
         <v>1518</v>
@@ -19326,7 +19326,7 @@
         <v>1461</v>
       </c>
       <c r="E329">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F329" t="s">
         <v>1518</v>
@@ -19361,7 +19361,7 @@
         <v>1461</v>
       </c>
       <c r="E330">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F330" t="s">
         <v>1518</v>
@@ -19396,7 +19396,7 @@
         <v>1462</v>
       </c>
       <c r="E331">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F331" t="s">
         <v>1518</v>
@@ -19431,7 +19431,7 @@
         <v>1462</v>
       </c>
       <c r="E332">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F332" t="s">
         <v>1518</v>
@@ -19466,7 +19466,7 @@
         <v>1462</v>
       </c>
       <c r="E333">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F333" t="s">
         <v>1518</v>
@@ -19501,7 +19501,7 @@
         <v>1462</v>
       </c>
       <c r="E334">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F334" t="s">
         <v>1518</v>
@@ -19536,7 +19536,7 @@
         <v>1462</v>
       </c>
       <c r="E335">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F335" t="s">
         <v>1518</v>
@@ -19571,7 +19571,7 @@
         <v>1462</v>
       </c>
       <c r="E336">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F336" t="s">
         <v>1518</v>
@@ -19606,7 +19606,7 @@
         <v>1462</v>
       </c>
       <c r="E337">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F337" t="s">
         <v>1518</v>
@@ -19641,7 +19641,7 @@
         <v>1462</v>
       </c>
       <c r="E338">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F338" t="s">
         <v>1518</v>
@@ -19676,7 +19676,7 @@
         <v>1462</v>
       </c>
       <c r="E339">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F339" t="s">
         <v>1518</v>
@@ -19711,7 +19711,7 @@
         <v>1462</v>
       </c>
       <c r="E340">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F340" t="s">
         <v>1518</v>
@@ -19746,7 +19746,7 @@
         <v>1463</v>
       </c>
       <c r="E341">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F341" t="s">
         <v>1518</v>
@@ -19781,7 +19781,7 @@
         <v>1463</v>
       </c>
       <c r="E342">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F342" t="s">
         <v>1518</v>
@@ -19816,7 +19816,7 @@
         <v>1463</v>
       </c>
       <c r="E343">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F343" t="s">
         <v>1519</v>
@@ -19851,7 +19851,7 @@
         <v>1464</v>
       </c>
       <c r="E344">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F344" t="s">
         <v>1518</v>
@@ -19886,7 +19886,7 @@
         <v>1464</v>
       </c>
       <c r="E345">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F345" t="s">
         <v>1518</v>
@@ -19921,7 +19921,7 @@
         <v>1464</v>
       </c>
       <c r="E346">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F346" t="s">
         <v>1518</v>
@@ -19956,7 +19956,7 @@
         <v>1464</v>
       </c>
       <c r="E347">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F347" t="s">
         <v>1518</v>
@@ -19991,7 +19991,7 @@
         <v>1464</v>
       </c>
       <c r="E348">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F348" t="s">
         <v>1518</v>
@@ -20026,7 +20026,7 @@
         <v>1464</v>
       </c>
       <c r="E349">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F349" t="s">
         <v>1518</v>
@@ -20061,7 +20061,7 @@
         <v>1464</v>
       </c>
       <c r="E350">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F350" t="s">
         <v>1521</v>
@@ -20096,7 +20096,7 @@
         <v>1465</v>
       </c>
       <c r="E351">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F351" t="s">
         <v>1518</v>
@@ -20131,7 +20131,7 @@
         <v>1465</v>
       </c>
       <c r="E352">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F352" t="s">
         <v>1518</v>
@@ -20166,7 +20166,7 @@
         <v>1465</v>
       </c>
       <c r="E353">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F353" t="s">
         <v>1518</v>
@@ -20201,7 +20201,7 @@
         <v>1465</v>
       </c>
       <c r="E354">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F354" t="s">
         <v>1518</v>
@@ -20236,7 +20236,7 @@
         <v>1466</v>
       </c>
       <c r="E355">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F355" t="s">
         <v>1521</v>
@@ -20271,7 +20271,7 @@
         <v>1466</v>
       </c>
       <c r="E356">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F356" t="s">
         <v>1518</v>
@@ -20306,7 +20306,7 @@
         <v>1466</v>
       </c>
       <c r="E357">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F357" t="s">
         <v>1518</v>
@@ -20341,7 +20341,7 @@
         <v>1466</v>
       </c>
       <c r="E358">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F358" t="s">
         <v>1518</v>
@@ -20376,7 +20376,7 @@
         <v>1466</v>
       </c>
       <c r="E359">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F359" t="s">
         <v>1518</v>
@@ -20411,7 +20411,7 @@
         <v>1467</v>
       </c>
       <c r="E360">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F360" t="s">
         <v>1518</v>
@@ -20446,7 +20446,7 @@
         <v>1467</v>
       </c>
       <c r="E361">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F361" t="s">
         <v>1518</v>
@@ -20481,7 +20481,7 @@
         <v>1467</v>
       </c>
       <c r="E362">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F362" t="s">
         <v>1520</v>
@@ -20516,7 +20516,7 @@
         <v>1467</v>
       </c>
       <c r="E363">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F363" t="s">
         <v>1518</v>
@@ -20551,7 +20551,7 @@
         <v>1467</v>
       </c>
       <c r="E364">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F364" t="s">
         <v>1518</v>
@@ -20586,7 +20586,7 @@
         <v>1468</v>
       </c>
       <c r="E365">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F365" t="s">
         <v>1518</v>
@@ -20621,7 +20621,7 @@
         <v>1468</v>
       </c>
       <c r="E366">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F366" t="s">
         <v>1518</v>
@@ -20656,7 +20656,7 @@
         <v>1468</v>
       </c>
       <c r="E367">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F367" t="s">
         <v>1518</v>
@@ -20691,7 +20691,7 @@
         <v>1468</v>
       </c>
       <c r="E368">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F368" t="s">
         <v>1518</v>
@@ -20726,7 +20726,7 @@
         <v>1469</v>
       </c>
       <c r="E369">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F369" t="s">
         <v>1518</v>
@@ -20761,7 +20761,7 @@
         <v>1469</v>
       </c>
       <c r="E370">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F370" t="s">
         <v>1518</v>
@@ -20796,7 +20796,7 @@
         <v>1469</v>
       </c>
       <c r="E371">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F371" t="s">
         <v>1518</v>
@@ -20831,7 +20831,7 @@
         <v>1469</v>
       </c>
       <c r="E372">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F372" t="s">
         <v>1518</v>
@@ -20869,7 +20869,7 @@
         <v>1470</v>
       </c>
       <c r="E373">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F373" t="s">
         <v>1518</v>
@@ -20904,7 +20904,7 @@
         <v>1470</v>
       </c>
       <c r="E374">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F374" t="s">
         <v>1518</v>
@@ -20939,7 +20939,7 @@
         <v>1470</v>
       </c>
       <c r="E375">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F375" t="s">
         <v>1518</v>
@@ -20974,7 +20974,7 @@
         <v>1470</v>
       </c>
       <c r="E376">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F376" t="s">
         <v>1518</v>
@@ -21009,7 +21009,7 @@
         <v>1470</v>
       </c>
       <c r="E377">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F377" t="s">
         <v>1518</v>
@@ -21044,7 +21044,7 @@
         <v>1470</v>
       </c>
       <c r="E378">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F378" t="s">
         <v>1518</v>
@@ -21079,7 +21079,7 @@
         <v>1471</v>
       </c>
       <c r="E379">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F379" t="s">
         <v>1519</v>
@@ -21114,7 +21114,7 @@
         <v>1471</v>
       </c>
       <c r="E380">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F380" t="s">
         <v>1518</v>
@@ -21149,7 +21149,7 @@
         <v>1472</v>
       </c>
       <c r="E381">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F381" t="s">
         <v>1518</v>
@@ -21184,7 +21184,7 @@
         <v>1473</v>
       </c>
       <c r="E382">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F382" t="s">
         <v>1518</v>
@@ -21219,7 +21219,7 @@
         <v>1473</v>
       </c>
       <c r="E383">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F383" t="s">
         <v>1518</v>
@@ -21254,7 +21254,7 @@
         <v>1473</v>
       </c>
       <c r="E384">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F384" t="s">
         <v>1520</v>
@@ -21292,7 +21292,7 @@
         <v>1474</v>
       </c>
       <c r="E385">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F385" t="s">
         <v>1518</v>
@@ -21327,7 +21327,7 @@
         <v>1474</v>
       </c>
       <c r="E386">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F386" t="s">
         <v>1518</v>
@@ -21362,7 +21362,7 @@
         <v>1474</v>
       </c>
       <c r="E387">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F387" t="s">
         <v>1518</v>
@@ -21397,7 +21397,7 @@
         <v>1475</v>
       </c>
       <c r="E388">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F388" t="s">
         <v>1518</v>
@@ -21432,7 +21432,7 @@
         <v>1475</v>
       </c>
       <c r="E389">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F389" t="s">
         <v>1518</v>
@@ -21467,7 +21467,7 @@
         <v>1475</v>
       </c>
       <c r="E390">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F390" t="s">
         <v>1518</v>
@@ -21502,7 +21502,7 @@
         <v>1475</v>
       </c>
       <c r="E391">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F391" t="s">
         <v>1518</v>
@@ -21537,7 +21537,7 @@
         <v>1475</v>
       </c>
       <c r="E392">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F392" t="s">
         <v>1518</v>
@@ -21572,7 +21572,7 @@
         <v>1475</v>
       </c>
       <c r="E393">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F393" t="s">
         <v>1518</v>
@@ -21607,7 +21607,7 @@
         <v>1475</v>
       </c>
       <c r="E394">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F394" t="s">
         <v>1518</v>
@@ -21642,7 +21642,7 @@
         <v>1476</v>
       </c>
       <c r="E395">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F395" t="s">
         <v>1518</v>
@@ -21677,7 +21677,7 @@
         <v>1477</v>
       </c>
       <c r="E396">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F396" t="s">
         <v>1518</v>
@@ -21712,7 +21712,7 @@
         <v>1477</v>
       </c>
       <c r="E397">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F397" t="s">
         <v>1518</v>
@@ -21747,7 +21747,7 @@
         <v>1477</v>
       </c>
       <c r="E398">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F398" t="s">
         <v>1518</v>
@@ -21782,7 +21782,7 @@
         <v>1477</v>
       </c>
       <c r="E399">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F399" t="s">
         <v>1522</v>
@@ -21820,7 +21820,7 @@
         <v>1477</v>
       </c>
       <c r="E400">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F400" t="s">
         <v>1518</v>
@@ -21855,7 +21855,7 @@
         <v>1477</v>
       </c>
       <c r="E401">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F401" t="s">
         <v>1522</v>
@@ -21890,7 +21890,7 @@
         <v>1478</v>
       </c>
       <c r="E402">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F402" t="s">
         <v>1518</v>
@@ -21925,7 +21925,7 @@
         <v>1479</v>
       </c>
       <c r="E403">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F403" t="s">
         <v>1518</v>
@@ -21960,7 +21960,7 @@
         <v>1479</v>
       </c>
       <c r="E404">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F404" t="s">
         <v>1518</v>
@@ -21995,7 +21995,7 @@
         <v>1479</v>
       </c>
       <c r="E405">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F405" t="s">
         <v>1518</v>
@@ -22030,7 +22030,7 @@
         <v>1480</v>
       </c>
       <c r="E406">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F406" t="s">
         <v>1522</v>
@@ -22065,7 +22065,7 @@
         <v>1480</v>
       </c>
       <c r="E407">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F407" t="s">
         <v>1518</v>
@@ -22100,7 +22100,7 @@
         <v>1480</v>
       </c>
       <c r="E408">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F408" t="s">
         <v>1518</v>
@@ -22135,7 +22135,7 @@
         <v>1480</v>
       </c>
       <c r="E409">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F409" t="s">
         <v>1518</v>
@@ -22170,7 +22170,7 @@
         <v>1481</v>
       </c>
       <c r="E410">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F410" t="s">
         <v>1518</v>
@@ -22205,7 +22205,7 @@
         <v>1481</v>
       </c>
       <c r="E411">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F411" t="s">
         <v>1518</v>
@@ -22240,7 +22240,7 @@
         <v>1481</v>
       </c>
       <c r="E412">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F412" t="s">
         <v>1518</v>
@@ -22275,7 +22275,7 @@
         <v>1482</v>
       </c>
       <c r="E413">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F413" t="s">
         <v>1518</v>
@@ -22310,7 +22310,7 @@
         <v>1482</v>
       </c>
       <c r="E414">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F414" t="s">
         <v>1518</v>
@@ -22345,7 +22345,7 @@
         <v>1482</v>
       </c>
       <c r="E415">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F415" t="s">
         <v>1518</v>
@@ -22380,7 +22380,7 @@
         <v>1482</v>
       </c>
       <c r="E416">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F416" t="s">
         <v>1518</v>
@@ -22415,7 +22415,7 @@
         <v>1482</v>
       </c>
       <c r="E417">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F417" t="s">
         <v>1518</v>
@@ -22450,7 +22450,7 @@
         <v>1483</v>
       </c>
       <c r="E418">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F418" t="s">
         <v>1518</v>
@@ -22485,7 +22485,7 @@
         <v>1483</v>
       </c>
       <c r="E419">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F419" t="s">
         <v>1518</v>
@@ -22520,7 +22520,7 @@
         <v>1483</v>
       </c>
       <c r="E420">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F420" t="s">
         <v>1518</v>
@@ -22555,7 +22555,7 @@
         <v>1483</v>
       </c>
       <c r="E421">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F421" t="s">
         <v>1518</v>
@@ -22590,7 +22590,7 @@
         <v>1483</v>
       </c>
       <c r="E422">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F422" t="s">
         <v>1518</v>
@@ -22625,7 +22625,7 @@
         <v>1483</v>
       </c>
       <c r="E423">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F423" t="s">
         <v>1518</v>
@@ -22660,7 +22660,7 @@
         <v>1483</v>
       </c>
       <c r="E424">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F424" t="s">
         <v>1518</v>
@@ -22695,7 +22695,7 @@
         <v>1483</v>
       </c>
       <c r="E425">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F425" t="s">
         <v>1518</v>
@@ -22730,7 +22730,7 @@
         <v>1483</v>
       </c>
       <c r="E426">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F426" t="s">
         <v>1518</v>
@@ -22765,7 +22765,7 @@
         <v>1483</v>
       </c>
       <c r="E427">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F427" t="s">
         <v>1518</v>
@@ -22800,7 +22800,7 @@
         <v>1483</v>
       </c>
       <c r="E428">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F428" t="s">
         <v>1518</v>
@@ -22835,7 +22835,7 @@
         <v>1483</v>
       </c>
       <c r="E429">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F429" t="s">
         <v>1518</v>
@@ -22870,7 +22870,7 @@
         <v>1483</v>
       </c>
       <c r="E430">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F430" t="s">
         <v>1518</v>
@@ -22905,7 +22905,7 @@
         <v>1483</v>
       </c>
       <c r="E431">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F431" t="s">
         <v>1518</v>
@@ -22940,7 +22940,7 @@
         <v>1483</v>
       </c>
       <c r="E432">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F432" t="s">
         <v>1518</v>
@@ -22975,7 +22975,7 @@
         <v>1483</v>
       </c>
       <c r="E433">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F433" t="s">
         <v>1518</v>
@@ -23010,7 +23010,7 @@
         <v>1483</v>
       </c>
       <c r="E434">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F434" t="s">
         <v>1518</v>
@@ -23045,7 +23045,7 @@
         <v>1483</v>
       </c>
       <c r="E435">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F435" t="s">
         <v>1518</v>
@@ -23080,7 +23080,7 @@
         <v>1483</v>
       </c>
       <c r="E436">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F436" t="s">
         <v>1518</v>
@@ -23115,7 +23115,7 @@
         <v>1483</v>
       </c>
       <c r="E437">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F437" t="s">
         <v>1518</v>
@@ -23150,7 +23150,7 @@
         <v>1483</v>
       </c>
       <c r="E438">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F438" t="s">
         <v>1518</v>
@@ -23185,7 +23185,7 @@
         <v>1483</v>
       </c>
       <c r="E439">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F439" t="s">
         <v>1518</v>
@@ -23220,7 +23220,7 @@
         <v>1483</v>
       </c>
       <c r="E440">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F440" t="s">
         <v>1518</v>
@@ -23255,7 +23255,7 @@
         <v>1483</v>
       </c>
       <c r="E441">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F441" t="s">
         <v>1518</v>
@@ -23290,7 +23290,7 @@
         <v>1484</v>
       </c>
       <c r="E442">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F442" t="s">
         <v>1518</v>
@@ -23325,7 +23325,7 @@
         <v>1484</v>
       </c>
       <c r="E443">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F443" t="s">
         <v>1518</v>
@@ -23360,7 +23360,7 @@
         <v>1484</v>
       </c>
       <c r="E444">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F444" t="s">
         <v>1518</v>
@@ -23395,7 +23395,7 @@
         <v>1484</v>
       </c>
       <c r="E445">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F445" t="s">
         <v>1518</v>
@@ -23430,7 +23430,7 @@
         <v>1484</v>
       </c>
       <c r="E446">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F446" t="s">
         <v>1518</v>
@@ -23465,7 +23465,7 @@
         <v>1484</v>
       </c>
       <c r="E447">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F447" t="s">
         <v>1518</v>
@@ -23500,7 +23500,7 @@
         <v>1484</v>
       </c>
       <c r="E448">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F448" t="s">
         <v>1522</v>
@@ -23535,7 +23535,7 @@
         <v>1484</v>
       </c>
       <c r="E449">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F449" t="s">
         <v>1518</v>
@@ -23570,7 +23570,7 @@
         <v>1485</v>
       </c>
       <c r="E450">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F450" t="s">
         <v>1518</v>
@@ -23605,7 +23605,7 @@
         <v>1486</v>
       </c>
       <c r="E451">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F451" t="s">
         <v>1520</v>
@@ -23643,7 +23643,7 @@
         <v>1486</v>
       </c>
       <c r="E452">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F452" t="s">
         <v>1518</v>
@@ -23678,7 +23678,7 @@
         <v>1486</v>
       </c>
       <c r="E453">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F453" t="s">
         <v>1518</v>
@@ -23713,7 +23713,7 @@
         <v>1486</v>
       </c>
       <c r="E454">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F454" t="s">
         <v>1518</v>
@@ -23748,7 +23748,7 @@
         <v>1486</v>
       </c>
       <c r="E455">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F455" t="s">
         <v>1518</v>
@@ -23783,7 +23783,7 @@
         <v>1487</v>
       </c>
       <c r="E456">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F456" t="s">
         <v>1518</v>
@@ -23821,7 +23821,7 @@
         <v>1487</v>
       </c>
       <c r="E457">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F457" t="s">
         <v>1522</v>
@@ -23856,7 +23856,7 @@
         <v>1487</v>
       </c>
       <c r="E458">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F458" t="s">
         <v>1520</v>
@@ -23891,7 +23891,7 @@
         <v>1487</v>
       </c>
       <c r="E459">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F459" t="s">
         <v>1518</v>
@@ -23926,7 +23926,7 @@
         <v>1487</v>
       </c>
       <c r="E460">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F460" t="s">
         <v>1518</v>
@@ -23961,7 +23961,7 @@
         <v>1487</v>
       </c>
       <c r="E461">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F461" t="s">
         <v>1518</v>
@@ -23996,7 +23996,7 @@
         <v>1487</v>
       </c>
       <c r="E462">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F462" t="s">
         <v>1518</v>
@@ -24031,7 +24031,7 @@
         <v>1487</v>
       </c>
       <c r="E463">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F463" t="s">
         <v>1518</v>
@@ -24066,7 +24066,7 @@
         <v>1487</v>
       </c>
       <c r="E464">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F464" t="s">
         <v>1518</v>
@@ -24101,7 +24101,7 @@
         <v>1488</v>
       </c>
       <c r="E465">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F465" t="s">
         <v>1522</v>
@@ -24139,7 +24139,7 @@
         <v>1488</v>
       </c>
       <c r="E466">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F466" t="s">
         <v>1518</v>
@@ -24174,7 +24174,7 @@
         <v>1489</v>
       </c>
       <c r="E467">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F467" t="s">
         <v>1518</v>
@@ -24209,7 +24209,7 @@
         <v>1489</v>
       </c>
       <c r="E468">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F468" t="s">
         <v>1518</v>
@@ -24244,7 +24244,7 @@
         <v>1489</v>
       </c>
       <c r="E469">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F469" t="s">
         <v>1518</v>
@@ -24279,7 +24279,7 @@
         <v>1489</v>
       </c>
       <c r="E470">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F470" t="s">
         <v>1518</v>
@@ -24314,7 +24314,7 @@
         <v>1489</v>
       </c>
       <c r="E471">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F471" t="s">
         <v>1518</v>
@@ -24349,7 +24349,7 @@
         <v>1489</v>
       </c>
       <c r="E472">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F472" t="s">
         <v>1518</v>
@@ -24384,7 +24384,7 @@
         <v>1490</v>
       </c>
       <c r="E473">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F473" t="s">
         <v>1518</v>
@@ -24419,7 +24419,7 @@
         <v>1490</v>
       </c>
       <c r="E474">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F474" t="s">
         <v>1518</v>
@@ -24454,7 +24454,7 @@
         <v>1490</v>
       </c>
       <c r="E475">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F475" t="s">
         <v>1518</v>
@@ -24489,7 +24489,7 @@
         <v>1490</v>
       </c>
       <c r="E476">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F476" t="s">
         <v>1518</v>
@@ -24524,7 +24524,7 @@
         <v>1490</v>
       </c>
       <c r="E477">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F477" t="s">
         <v>1518</v>
@@ -24559,7 +24559,7 @@
         <v>1490</v>
       </c>
       <c r="E478">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F478" t="s">
         <v>1520</v>
@@ -24594,7 +24594,7 @@
         <v>1490</v>
       </c>
       <c r="E479">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F479" t="s">
         <v>1518</v>
@@ -24629,7 +24629,7 @@
         <v>1490</v>
       </c>
       <c r="E480">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F480" t="s">
         <v>1518</v>
@@ -24664,7 +24664,7 @@
         <v>1491</v>
       </c>
       <c r="E481">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F481" t="s">
         <v>1518</v>
@@ -24699,7 +24699,7 @@
         <v>1491</v>
       </c>
       <c r="E482">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F482" t="s">
         <v>1518</v>
@@ -24734,7 +24734,7 @@
         <v>1491</v>
       </c>
       <c r="E483">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F483" t="s">
         <v>1518</v>
@@ -24769,7 +24769,7 @@
         <v>1491</v>
       </c>
       <c r="E484">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F484" t="s">
         <v>1518</v>
@@ -24804,7 +24804,7 @@
         <v>1491</v>
       </c>
       <c r="E485">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F485" t="s">
         <v>1518</v>
@@ -24839,7 +24839,7 @@
         <v>1491</v>
       </c>
       <c r="E486">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F486" t="s">
         <v>1518</v>
@@ -24874,7 +24874,7 @@
         <v>1491</v>
       </c>
       <c r="E487">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F487" t="s">
         <v>1518</v>
@@ -24909,7 +24909,7 @@
         <v>1491</v>
       </c>
       <c r="E488">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F488" t="s">
         <v>1518</v>
@@ -24944,7 +24944,7 @@
         <v>1492</v>
       </c>
       <c r="E489">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F489" t="s">
         <v>1518</v>
@@ -24979,7 +24979,7 @@
         <v>1492</v>
       </c>
       <c r="E490">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F490" t="s">
         <v>1518</v>
@@ -25014,7 +25014,7 @@
         <v>1492</v>
       </c>
       <c r="E491">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F491" t="s">
         <v>1518</v>
@@ -25049,7 +25049,7 @@
         <v>1492</v>
       </c>
       <c r="E492">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F492" t="s">
         <v>1518</v>
@@ -25084,7 +25084,7 @@
         <v>1492</v>
       </c>
       <c r="E493">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F493" t="s">
         <v>1518</v>
@@ -25119,7 +25119,7 @@
         <v>1492</v>
       </c>
       <c r="E494">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F494" t="s">
         <v>1518</v>
@@ -25154,7 +25154,7 @@
         <v>1493</v>
       </c>
       <c r="E495">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F495" t="s">
         <v>1518</v>
@@ -25189,7 +25189,7 @@
         <v>1493</v>
       </c>
       <c r="E496">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F496" t="s">
         <v>1518</v>
@@ -25224,7 +25224,7 @@
         <v>1493</v>
       </c>
       <c r="E497">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F497" t="s">
         <v>1518</v>
@@ -25259,7 +25259,7 @@
         <v>1493</v>
       </c>
       <c r="E498">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F498" t="s">
         <v>1518</v>
@@ -25294,7 +25294,7 @@
         <v>1493</v>
       </c>
       <c r="E499">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F499" t="s">
         <v>1518</v>
@@ -25329,7 +25329,7 @@
         <v>1494</v>
       </c>
       <c r="E500">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F500" t="s">
         <v>1518</v>
@@ -25364,7 +25364,7 @@
         <v>1494</v>
       </c>
       <c r="E501">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F501" t="s">
         <v>1518</v>
@@ -25399,7 +25399,7 @@
         <v>1494</v>
       </c>
       <c r="E502">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F502" t="s">
         <v>1518</v>
@@ -25434,7 +25434,7 @@
         <v>1494</v>
       </c>
       <c r="E503">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F503" t="s">
         <v>1518</v>
@@ -25469,7 +25469,7 @@
         <v>1494</v>
       </c>
       <c r="E504">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F504" t="s">
         <v>1518</v>
@@ -25504,7 +25504,7 @@
         <v>1494</v>
       </c>
       <c r="E505">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F505" t="s">
         <v>1518</v>
@@ -25539,7 +25539,7 @@
         <v>1494</v>
       </c>
       <c r="E506">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F506" t="s">
         <v>1518</v>
@@ -25574,7 +25574,7 @@
         <v>1494</v>
       </c>
       <c r="E507">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F507" t="s">
         <v>1518</v>
@@ -25609,7 +25609,7 @@
         <v>1494</v>
       </c>
       <c r="E508">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F508" t="s">
         <v>1518</v>
@@ -25647,7 +25647,7 @@
         <v>1494</v>
       </c>
       <c r="E509">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F509" t="s">
         <v>1518</v>
@@ -25682,7 +25682,7 @@
         <v>1495</v>
       </c>
       <c r="E510">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F510" t="s">
         <v>1518</v>
@@ -25717,7 +25717,7 @@
         <v>1495</v>
       </c>
       <c r="E511">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F511" t="s">
         <v>1520</v>
@@ -25755,7 +25755,7 @@
         <v>1495</v>
       </c>
       <c r="E512">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F512" t="s">
         <v>1518</v>
@@ -25790,7 +25790,7 @@
         <v>1495</v>
       </c>
       <c r="E513">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F513" t="s">
         <v>1518</v>
@@ -25825,7 +25825,7 @@
         <v>1496</v>
       </c>
       <c r="E514">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F514" t="s">
         <v>1518</v>
@@ -25860,7 +25860,7 @@
         <v>1496</v>
       </c>
       <c r="E515">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F515" t="s">
         <v>1518</v>
@@ -25895,7 +25895,7 @@
         <v>1496</v>
       </c>
       <c r="E516">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F516" t="s">
         <v>1518</v>
@@ -25930,7 +25930,7 @@
         <v>1496</v>
       </c>
       <c r="E517">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F517" t="s">
         <v>1518</v>
@@ -25965,7 +25965,7 @@
         <v>1496</v>
       </c>
       <c r="E518">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F518" t="s">
         <v>1518</v>
@@ -26000,7 +26000,7 @@
         <v>1496</v>
       </c>
       <c r="E519">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F519" t="s">
         <v>1518</v>
@@ -26035,7 +26035,7 @@
         <v>1496</v>
       </c>
       <c r="E520">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F520" t="s">
         <v>1518</v>
@@ -26070,7 +26070,7 @@
         <v>1496</v>
       </c>
       <c r="E521">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F521" t="s">
         <v>1518</v>
@@ -26105,7 +26105,7 @@
         <v>1496</v>
       </c>
       <c r="E522">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F522" t="s">
         <v>1518</v>
@@ -26140,7 +26140,7 @@
         <v>1497</v>
       </c>
       <c r="E523">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F523" t="s">
         <v>1518</v>
@@ -26175,7 +26175,7 @@
         <v>1497</v>
       </c>
       <c r="E524">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F524" t="s">
         <v>1518</v>
@@ -26210,7 +26210,7 @@
         <v>1497</v>
       </c>
       <c r="E525">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F525" t="s">
         <v>1518</v>
@@ -26245,7 +26245,7 @@
         <v>1497</v>
       </c>
       <c r="E526">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F526" t="s">
         <v>1518</v>
@@ -26280,7 +26280,7 @@
         <v>1498</v>
       </c>
       <c r="E527">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F527" t="s">
         <v>1518</v>
@@ -26315,7 +26315,7 @@
         <v>1498</v>
       </c>
       <c r="E528">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F528" t="s">
         <v>1518</v>
@@ -26350,7 +26350,7 @@
         <v>1498</v>
       </c>
       <c r="E529">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F529" t="s">
         <v>1518</v>
@@ -26385,7 +26385,7 @@
         <v>1498</v>
       </c>
       <c r="E530">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F530" t="s">
         <v>1520</v>
@@ -26423,7 +26423,7 @@
         <v>1499</v>
       </c>
       <c r="E531">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F531" t="s">
         <v>1518</v>
@@ -26458,7 +26458,7 @@
         <v>1499</v>
       </c>
       <c r="E532">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F532" t="s">
         <v>1522</v>
@@ -26496,7 +26496,7 @@
         <v>1499</v>
       </c>
       <c r="E533">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F533" t="s">
         <v>1518</v>
@@ -26531,7 +26531,7 @@
         <v>1499</v>
       </c>
       <c r="E534">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F534" t="s">
         <v>1518</v>
@@ -26566,7 +26566,7 @@
         <v>1500</v>
       </c>
       <c r="E535">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F535" t="s">
         <v>1518</v>
@@ -26601,7 +26601,7 @@
         <v>1500</v>
       </c>
       <c r="E536">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F536" t="s">
         <v>1518</v>
@@ -26636,7 +26636,7 @@
         <v>1500</v>
       </c>
       <c r="E537">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F537" t="s">
         <v>1518</v>
@@ -26671,7 +26671,7 @@
         <v>1500</v>
       </c>
       <c r="E538">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F538" t="s">
         <v>1518</v>
@@ -26706,7 +26706,7 @@
         <v>1500</v>
       </c>
       <c r="E539">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F539" t="s">
         <v>1520</v>
@@ -26744,7 +26744,7 @@
         <v>1500</v>
       </c>
       <c r="E540">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F540" t="s">
         <v>1518</v>
@@ -26779,7 +26779,7 @@
         <v>1500</v>
       </c>
       <c r="E541">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F541" t="s">
         <v>1518</v>
@@ -26814,7 +26814,7 @@
         <v>1500</v>
       </c>
       <c r="E542">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F542" t="s">
         <v>1518</v>
@@ -26849,7 +26849,7 @@
         <v>1501</v>
       </c>
       <c r="E543">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F543" t="s">
         <v>1518</v>
@@ -26884,7 +26884,7 @@
         <v>1501</v>
       </c>
       <c r="E544">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F544" t="s">
         <v>1518</v>
@@ -26919,7 +26919,7 @@
         <v>1502</v>
       </c>
       <c r="E545">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F545" t="s">
         <v>1520</v>
@@ -26957,7 +26957,7 @@
         <v>1502</v>
       </c>
       <c r="E546">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F546" t="s">
         <v>1518</v>
@@ -26992,7 +26992,7 @@
         <v>1502</v>
       </c>
       <c r="E547">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F547" t="s">
         <v>1518</v>
@@ -27027,7 +27027,7 @@
         <v>1502</v>
       </c>
       <c r="E548">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F548" t="s">
         <v>1518</v>
@@ -27062,7 +27062,7 @@
         <v>1503</v>
       </c>
       <c r="E549">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F549" t="s">
         <v>1518</v>
@@ -27097,7 +27097,7 @@
         <v>1504</v>
       </c>
       <c r="E550">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F550" t="s">
         <v>1518</v>
@@ -27132,7 +27132,7 @@
         <v>1504</v>
       </c>
       <c r="E551">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F551" t="s">
         <v>1518</v>
@@ -27167,7 +27167,7 @@
         <v>1504</v>
       </c>
       <c r="E552">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F552" t="s">
         <v>1518</v>
@@ -27202,7 +27202,7 @@
         <v>1504</v>
       </c>
       <c r="E553">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F553" t="s">
         <v>1518</v>
@@ -27237,7 +27237,7 @@
         <v>1504</v>
       </c>
       <c r="E554">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F554" t="s">
         <v>1518</v>
@@ -27272,7 +27272,7 @@
         <v>1504</v>
       </c>
       <c r="E555">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F555" t="s">
         <v>1518</v>
@@ -27307,7 +27307,7 @@
         <v>1504</v>
       </c>
       <c r="E556">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F556" t="s">
         <v>1518</v>
@@ -27342,7 +27342,7 @@
         <v>1504</v>
       </c>
       <c r="E557">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F557" t="s">
         <v>1518</v>
@@ -27377,7 +27377,7 @@
         <v>1504</v>
       </c>
       <c r="E558">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F558" t="s">
         <v>1518</v>
@@ -27412,7 +27412,7 @@
         <v>1504</v>
       </c>
       <c r="E559">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F559" t="s">
         <v>1520</v>
@@ -27450,7 +27450,7 @@
         <v>1505</v>
       </c>
       <c r="E560">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F560" t="s">
         <v>1518</v>
@@ -27485,7 +27485,7 @@
         <v>1505</v>
       </c>
       <c r="E561">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F561" t="s">
         <v>1518</v>
@@ -27520,7 +27520,7 @@
         <v>1505</v>
       </c>
       <c r="E562">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F562" t="s">
         <v>1518</v>
@@ -27555,7 +27555,7 @@
         <v>1505</v>
       </c>
       <c r="E563">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F563" t="s">
         <v>1518</v>
@@ -27590,7 +27590,7 @@
         <v>1505</v>
       </c>
       <c r="E564">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F564" t="s">
         <v>1520</v>
@@ -27628,7 +27628,7 @@
         <v>1505</v>
       </c>
       <c r="E565">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F565" t="s">
         <v>1518</v>
@@ -27663,7 +27663,7 @@
         <v>1505</v>
       </c>
       <c r="E566">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F566" t="s">
         <v>1518</v>
@@ -27698,7 +27698,7 @@
         <v>1505</v>
       </c>
       <c r="E567">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F567" t="s">
         <v>1518</v>
@@ -27733,7 +27733,7 @@
         <v>1506</v>
       </c>
       <c r="E568">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F568" t="s">
         <v>1518</v>
@@ -27768,7 +27768,7 @@
         <v>1506</v>
       </c>
       <c r="E569">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F569" t="s">
         <v>1520</v>
@@ -27806,7 +27806,7 @@
         <v>1506</v>
       </c>
       <c r="E570">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F570" t="s">
         <v>1518</v>
@@ -27841,7 +27841,7 @@
         <v>1507</v>
       </c>
       <c r="E571">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F571" t="s">
         <v>1520</v>
@@ -27879,7 +27879,7 @@
         <v>1507</v>
       </c>
       <c r="E572">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F572" t="s">
         <v>1518</v>
@@ -27914,7 +27914,7 @@
         <v>1507</v>
       </c>
       <c r="E573">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F573" t="s">
         <v>1518</v>
@@ -27949,7 +27949,7 @@
         <v>1508</v>
       </c>
       <c r="E574">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F574" t="s">
         <v>1518</v>
@@ -27984,7 +27984,7 @@
         <v>1508</v>
       </c>
       <c r="E575">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F575" t="s">
         <v>1518</v>
@@ -28019,7 +28019,7 @@
         <v>1508</v>
       </c>
       <c r="E576">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F576" t="s">
         <v>1518</v>
@@ -28054,7 +28054,7 @@
         <v>1508</v>
       </c>
       <c r="E577">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F577" t="s">
         <v>1518</v>
@@ -28089,7 +28089,7 @@
         <v>1508</v>
       </c>
       <c r="E578">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F578" t="s">
         <v>1518</v>
@@ -28124,7 +28124,7 @@
         <v>1508</v>
       </c>
       <c r="E579">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F579" t="s">
         <v>1518</v>
@@ -28159,7 +28159,7 @@
         <v>1508</v>
       </c>
       <c r="E580">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F580" t="s">
         <v>1520</v>
@@ -28197,7 +28197,7 @@
         <v>1509</v>
       </c>
       <c r="E581">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F581" t="s">
         <v>1520</v>
@@ -28235,7 +28235,7 @@
         <v>1509</v>
       </c>
       <c r="E582">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F582" t="s">
         <v>1520</v>
@@ -28270,7 +28270,7 @@
         <v>1509</v>
       </c>
       <c r="E583">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F583" t="s">
         <v>1518</v>
@@ -28305,7 +28305,7 @@
         <v>1509</v>
       </c>
       <c r="E584">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F584" t="s">
         <v>1518</v>
@@ -28340,7 +28340,7 @@
         <v>1509</v>
       </c>
       <c r="E585">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F585" t="s">
         <v>1518</v>
@@ -28375,7 +28375,7 @@
         <v>1509</v>
       </c>
       <c r="E586">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F586" t="s">
         <v>1518</v>
@@ -28410,7 +28410,7 @@
         <v>1510</v>
       </c>
       <c r="E587">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F587" t="s">
         <v>1518</v>
@@ -28445,7 +28445,7 @@
         <v>1510</v>
       </c>
       <c r="E588">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F588" t="s">
         <v>1518</v>
@@ -28480,7 +28480,7 @@
         <v>1510</v>
       </c>
       <c r="E589">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F589" t="s">
         <v>1518</v>
@@ -28515,7 +28515,7 @@
         <v>1510</v>
       </c>
       <c r="E590">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F590" t="s">
         <v>1518</v>
@@ -28550,7 +28550,7 @@
         <v>1510</v>
       </c>
       <c r="E591">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F591" t="s">
         <v>1518</v>
@@ -28585,7 +28585,7 @@
         <v>1510</v>
       </c>
       <c r="E592">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F592" t="s">
         <v>1518</v>
@@ -28620,7 +28620,7 @@
         <v>1510</v>
       </c>
       <c r="E593">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F593" t="s">
         <v>1518</v>
@@ -28655,7 +28655,7 @@
         <v>1511</v>
       </c>
       <c r="E594">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F594" t="s">
         <v>1518</v>
@@ -28693,7 +28693,7 @@
         <v>1511</v>
       </c>
       <c r="E595">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F595" t="s">
         <v>1518</v>
@@ -28728,7 +28728,7 @@
         <v>1511</v>
       </c>
       <c r="E596">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F596" t="s">
         <v>1518</v>
@@ -28763,7 +28763,7 @@
         <v>1511</v>
       </c>
       <c r="E597">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F597" t="s">
         <v>1518</v>
@@ -28801,7 +28801,7 @@
         <v>1511</v>
       </c>
       <c r="E598">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F598" t="s">
         <v>1518</v>
@@ -28836,7 +28836,7 @@
         <v>1512</v>
       </c>
       <c r="E599">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F599" t="s">
         <v>1518</v>
@@ -28871,7 +28871,7 @@
         <v>1513</v>
       </c>
       <c r="E600">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F600" t="s">
         <v>1518</v>
@@ -28906,7 +28906,7 @@
         <v>1513</v>
       </c>
       <c r="E601">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F601" t="s">
         <v>1518</v>
@@ -28941,7 +28941,7 @@
         <v>1513</v>
       </c>
       <c r="E602">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F602" t="s">
         <v>1520</v>
@@ -28976,7 +28976,7 @@
         <v>1513</v>
       </c>
       <c r="E603">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F603" t="s">
         <v>1520</v>
@@ -29014,7 +29014,7 @@
         <v>1513</v>
       </c>
       <c r="E604">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F604" t="s">
         <v>1518</v>
@@ -29049,7 +29049,7 @@
         <v>1513</v>
       </c>
       <c r="E605">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F605" t="s">
         <v>1518</v>
@@ -29084,7 +29084,7 @@
         <v>1513</v>
       </c>
       <c r="E606">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F606" t="s">
         <v>1518</v>
@@ -29119,7 +29119,7 @@
         <v>1513</v>
       </c>
       <c r="E607">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F607" t="s">
         <v>1518</v>
@@ -29154,7 +29154,7 @@
         <v>1513</v>
       </c>
       <c r="E608">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F608" t="s">
         <v>1518</v>
@@ -29189,7 +29189,7 @@
         <v>1513</v>
       </c>
       <c r="E609">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F609" t="s">
         <v>1518</v>
@@ -29224,7 +29224,7 @@
         <v>1513</v>
       </c>
       <c r="E610">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F610" t="s">
         <v>1518</v>
@@ -29262,7 +29262,7 @@
         <v>1513</v>
       </c>
       <c r="E611">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F611" t="s">
         <v>1518</v>
@@ -29297,7 +29297,7 @@
         <v>1513</v>
       </c>
       <c r="E612">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F612" t="s">
         <v>1518</v>
@@ -29332,7 +29332,7 @@
         <v>1513</v>
       </c>
       <c r="E613">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F613" t="s">
         <v>1522</v>
@@ -29367,7 +29367,7 @@
         <v>1514</v>
       </c>
       <c r="E614">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F614" t="s">
         <v>1518</v>
@@ -29402,7 +29402,7 @@
         <v>1514</v>
       </c>
       <c r="E615">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F615" t="s">
         <v>1520</v>
@@ -29440,7 +29440,7 @@
         <v>1514</v>
       </c>
       <c r="E616">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F616" t="s">
         <v>1518</v>
@@ -29475,7 +29475,7 @@
         <v>1514</v>
       </c>
       <c r="E617">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F617" t="s">
         <v>1520</v>
@@ -29513,7 +29513,7 @@
         <v>1514</v>
       </c>
       <c r="E618">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F618" t="s">
         <v>1518</v>
@@ -29548,7 +29548,7 @@
         <v>1515</v>
       </c>
       <c r="E619">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F619" t="s">
         <v>1518</v>
@@ -29583,7 +29583,7 @@
         <v>1515</v>
       </c>
       <c r="E620">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F620" t="s">
         <v>1518</v>
@@ -29618,7 +29618,7 @@
         <v>1515</v>
       </c>
       <c r="E621">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F621" t="s">
         <v>1518</v>
@@ -29653,7 +29653,7 @@
         <v>1515</v>
       </c>
       <c r="E622">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F622" t="s">
         <v>1518</v>
@@ -29688,7 +29688,7 @@
         <v>1515</v>
       </c>
       <c r="E623">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F623" t="s">
         <v>1518</v>
@@ -29723,7 +29723,7 @@
         <v>1515</v>
       </c>
       <c r="E624">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F624" t="s">
         <v>1518</v>
@@ -29758,7 +29758,7 @@
         <v>1515</v>
       </c>
       <c r="E625">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F625" t="s">
         <v>1518</v>
@@ -29793,7 +29793,7 @@
         <v>1516</v>
       </c>
       <c r="E626">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F626" t="s">
         <v>1518</v>
@@ -29828,7 +29828,7 @@
         <v>1516</v>
       </c>
       <c r="E627">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F627" t="s">
         <v>1518</v>
@@ -29863,7 +29863,7 @@
         <v>1516</v>
       </c>
       <c r="E628">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F628" t="s">
         <v>1518</v>
@@ -29898,7 +29898,7 @@
         <v>1516</v>
       </c>
       <c r="E629">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F629" t="s">
         <v>1518</v>
@@ -29933,7 +29933,7 @@
         <v>1516</v>
       </c>
       <c r="E630">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F630" t="s">
         <v>1518</v>
@@ -29968,7 +29968,7 @@
         <v>1517</v>
       </c>
       <c r="E631">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F631" t="s">
         <v>1518</v>
@@ -30006,7 +30006,7 @@
         <v>1517</v>
       </c>
       <c r="E632">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F632" t="s">
         <v>1518</v>
@@ -30041,7 +30041,7 @@
         <v>1517</v>
       </c>
       <c r="E633">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F633" t="s">
         <v>1518</v>
@@ -30076,7 +30076,7 @@
         <v>1517</v>
       </c>
       <c r="E634">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F634" t="s">
         <v>1518</v>

--- a/BacklogGATEAutoCompleto.xlsx
+++ b/BacklogGATEAutoCompleto.xlsx
@@ -7863,7 +7863,7 @@
         <v>1307</v>
       </c>
       <c r="E2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="F2" t="s">
         <v>1518</v>
@@ -7898,7 +7898,7 @@
         <v>1308</v>
       </c>
       <c r="E3">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="F3" t="s">
         <v>1518</v>
@@ -7933,7 +7933,7 @@
         <v>1309</v>
       </c>
       <c r="E4">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="F4" t="s">
         <v>1518</v>
@@ -7968,7 +7968,7 @@
         <v>1310</v>
       </c>
       <c r="E5">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="F5" t="s">
         <v>1518</v>
@@ -8003,7 +8003,7 @@
         <v>1311</v>
       </c>
       <c r="E6">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="F6" t="s">
         <v>1518</v>
@@ -8038,7 +8038,7 @@
         <v>1312</v>
       </c>
       <c r="E7">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="F7" t="s">
         <v>1518</v>
@@ -8073,7 +8073,7 @@
         <v>1313</v>
       </c>
       <c r="E8">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F8" t="s">
         <v>1518</v>
@@ -8108,7 +8108,7 @@
         <v>1313</v>
       </c>
       <c r="E9">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F9" t="s">
         <v>1518</v>
@@ -8143,7 +8143,7 @@
         <v>1314</v>
       </c>
       <c r="E10">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="F10" t="s">
         <v>1518</v>
@@ -8178,7 +8178,7 @@
         <v>1315</v>
       </c>
       <c r="E11">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="F11" t="s">
         <v>1518</v>
@@ -8213,7 +8213,7 @@
         <v>1316</v>
       </c>
       <c r="E12">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="F12" t="s">
         <v>1518</v>
@@ -8248,7 +8248,7 @@
         <v>1316</v>
       </c>
       <c r="E13">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="F13" t="s">
         <v>1518</v>
@@ -8283,7 +8283,7 @@
         <v>1317</v>
       </c>
       <c r="E14">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="F14" t="s">
         <v>1518</v>
@@ -8318,7 +8318,7 @@
         <v>1317</v>
       </c>
       <c r="E15">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="F15" t="s">
         <v>1518</v>
@@ -8353,7 +8353,7 @@
         <v>1318</v>
       </c>
       <c r="E16">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F16" t="s">
         <v>1518</v>
@@ -8388,7 +8388,7 @@
         <v>1319</v>
       </c>
       <c r="E17">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F17" t="s">
         <v>1518</v>
@@ -8423,7 +8423,7 @@
         <v>1320</v>
       </c>
       <c r="E18">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="F18" t="s">
         <v>1518</v>
@@ -8458,7 +8458,7 @@
         <v>1321</v>
       </c>
       <c r="E19">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="F19" t="s">
         <v>1518</v>
@@ -8493,7 +8493,7 @@
         <v>1322</v>
       </c>
       <c r="E20">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="F20" t="s">
         <v>1518</v>
@@ -8531,7 +8531,7 @@
         <v>1323</v>
       </c>
       <c r="E21">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="F21" t="s">
         <v>1518</v>
@@ -8566,7 +8566,7 @@
         <v>1324</v>
       </c>
       <c r="E22">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="F22" t="s">
         <v>1518</v>
@@ -8601,7 +8601,7 @@
         <v>1325</v>
       </c>
       <c r="E23">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F23" t="s">
         <v>1518</v>
@@ -8636,7 +8636,7 @@
         <v>1326</v>
       </c>
       <c r="E24">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="F24" t="s">
         <v>1518</v>
@@ -8671,7 +8671,7 @@
         <v>1327</v>
       </c>
       <c r="E25">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F25" t="s">
         <v>1518</v>
@@ -8706,7 +8706,7 @@
         <v>1328</v>
       </c>
       <c r="E26">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F26" t="s">
         <v>1518</v>
@@ -8741,7 +8741,7 @@
         <v>1329</v>
       </c>
       <c r="E27">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F27" t="s">
         <v>1518</v>
@@ -8776,7 +8776,7 @@
         <v>1330</v>
       </c>
       <c r="E28">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F28" t="s">
         <v>1518</v>
@@ -8811,7 +8811,7 @@
         <v>1331</v>
       </c>
       <c r="E29">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F29" t="s">
         <v>1518</v>
@@ -8846,7 +8846,7 @@
         <v>1332</v>
       </c>
       <c r="E30">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F30" t="s">
         <v>1518</v>
@@ -8881,7 +8881,7 @@
         <v>1333</v>
       </c>
       <c r="E31">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F31" t="s">
         <v>1518</v>
@@ -8916,7 +8916,7 @@
         <v>1334</v>
       </c>
       <c r="E32">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F32" t="s">
         <v>1518</v>
@@ -8951,7 +8951,7 @@
         <v>1334</v>
       </c>
       <c r="E33">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F33" t="s">
         <v>1518</v>
@@ -8986,7 +8986,7 @@
         <v>1335</v>
       </c>
       <c r="E34">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F34" t="s">
         <v>1518</v>
@@ -9021,7 +9021,7 @@
         <v>1336</v>
       </c>
       <c r="E35">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F35" t="s">
         <v>1518</v>
@@ -9056,7 +9056,7 @@
         <v>1336</v>
       </c>
       <c r="E36">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F36" t="s">
         <v>1518</v>
@@ -9091,7 +9091,7 @@
         <v>1337</v>
       </c>
       <c r="E37">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F37" t="s">
         <v>1518</v>
@@ -9126,7 +9126,7 @@
         <v>1337</v>
       </c>
       <c r="E38">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F38" t="s">
         <v>1518</v>
@@ -9161,7 +9161,7 @@
         <v>1338</v>
       </c>
       <c r="E39">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F39" t="s">
         <v>1518</v>
@@ -9196,7 +9196,7 @@
         <v>1339</v>
       </c>
       <c r="E40">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F40" t="s">
         <v>1518</v>
@@ -9231,7 +9231,7 @@
         <v>1340</v>
       </c>
       <c r="E41">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F41" t="s">
         <v>1518</v>
@@ -9266,7 +9266,7 @@
         <v>1341</v>
       </c>
       <c r="E42">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F42" t="s">
         <v>1518</v>
@@ -9301,7 +9301,7 @@
         <v>1342</v>
       </c>
       <c r="E43">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F43" t="s">
         <v>1518</v>
@@ -9336,7 +9336,7 @@
         <v>1343</v>
       </c>
       <c r="E44">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F44" t="s">
         <v>1518</v>
@@ -9371,7 +9371,7 @@
         <v>1344</v>
       </c>
       <c r="E45">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F45" t="s">
         <v>1518</v>
@@ -9406,7 +9406,7 @@
         <v>1345</v>
       </c>
       <c r="E46">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F46" t="s">
         <v>1518</v>
@@ -9441,7 +9441,7 @@
         <v>1346</v>
       </c>
       <c r="E47">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F47" t="s">
         <v>1518</v>
@@ -9476,7 +9476,7 @@
         <v>1347</v>
       </c>
       <c r="E48">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F48" t="s">
         <v>1518</v>
@@ -9511,7 +9511,7 @@
         <v>1348</v>
       </c>
       <c r="E49">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F49" t="s">
         <v>1518</v>
@@ -9546,7 +9546,7 @@
         <v>1348</v>
       </c>
       <c r="E50">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F50" t="s">
         <v>1518</v>
@@ -9581,7 +9581,7 @@
         <v>1348</v>
       </c>
       <c r="E51">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F51" t="s">
         <v>1518</v>
@@ -9616,7 +9616,7 @@
         <v>1349</v>
       </c>
       <c r="E52">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F52" t="s">
         <v>1518</v>
@@ -9651,7 +9651,7 @@
         <v>1350</v>
       </c>
       <c r="E53">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F53" t="s">
         <v>1518</v>
@@ -9686,7 +9686,7 @@
         <v>1351</v>
       </c>
       <c r="E54">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F54" t="s">
         <v>1518</v>
@@ -9721,7 +9721,7 @@
         <v>1352</v>
       </c>
       <c r="E55">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F55" t="s">
         <v>1518</v>
@@ -9756,7 +9756,7 @@
         <v>1353</v>
       </c>
       <c r="E56">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F56" t="s">
         <v>1518</v>
@@ -9791,7 +9791,7 @@
         <v>1353</v>
       </c>
       <c r="E57">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F57" t="s">
         <v>1518</v>
@@ -9826,7 +9826,7 @@
         <v>1354</v>
       </c>
       <c r="E58">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F58" t="s">
         <v>1518</v>
@@ -9861,7 +9861,7 @@
         <v>1355</v>
       </c>
       <c r="E59">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F59" t="s">
         <v>1518</v>
@@ -9896,7 +9896,7 @@
         <v>1355</v>
       </c>
       <c r="E60">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F60" t="s">
         <v>1518</v>
@@ -9931,7 +9931,7 @@
         <v>1355</v>
       </c>
       <c r="E61">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F61" t="s">
         <v>1519</v>
@@ -9966,7 +9966,7 @@
         <v>1355</v>
       </c>
       <c r="E62">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F62" t="s">
         <v>1518</v>
@@ -10001,7 +10001,7 @@
         <v>1356</v>
       </c>
       <c r="E63">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F63" t="s">
         <v>1518</v>
@@ -10036,7 +10036,7 @@
         <v>1357</v>
       </c>
       <c r="E64">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F64" t="s">
         <v>1518</v>
@@ -10071,7 +10071,7 @@
         <v>1357</v>
       </c>
       <c r="E65">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F65" t="s">
         <v>1518</v>
@@ -10106,7 +10106,7 @@
         <v>1358</v>
       </c>
       <c r="E66">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F66" t="s">
         <v>1518</v>
@@ -10141,7 +10141,7 @@
         <v>1359</v>
       </c>
       <c r="E67">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F67" t="s">
         <v>1518</v>
@@ -10176,7 +10176,7 @@
         <v>1360</v>
       </c>
       <c r="E68">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F68" t="s">
         <v>1518</v>
@@ -10211,7 +10211,7 @@
         <v>1361</v>
       </c>
       <c r="E69">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F69" t="s">
         <v>1518</v>
@@ -10246,7 +10246,7 @@
         <v>1361</v>
       </c>
       <c r="E70">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F70" t="s">
         <v>1518</v>
@@ -10281,7 +10281,7 @@
         <v>1361</v>
       </c>
       <c r="E71">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F71" t="s">
         <v>1518</v>
@@ -10316,7 +10316,7 @@
         <v>1361</v>
       </c>
       <c r="E72">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F72" t="s">
         <v>1518</v>
@@ -10351,7 +10351,7 @@
         <v>1361</v>
       </c>
       <c r="E73">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F73" t="s">
         <v>1518</v>
@@ -10386,7 +10386,7 @@
         <v>1361</v>
       </c>
       <c r="E74">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F74" t="s">
         <v>1518</v>
@@ -10421,7 +10421,7 @@
         <v>1362</v>
       </c>
       <c r="E75">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F75" t="s">
         <v>1518</v>
@@ -10456,7 +10456,7 @@
         <v>1363</v>
       </c>
       <c r="E76">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F76" t="s">
         <v>1518</v>
@@ -10491,7 +10491,7 @@
         <v>1364</v>
       </c>
       <c r="E77">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F77" t="s">
         <v>1518</v>
@@ -10526,7 +10526,7 @@
         <v>1364</v>
       </c>
       <c r="E78">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F78" t="s">
         <v>1518</v>
@@ -10561,7 +10561,7 @@
         <v>1365</v>
       </c>
       <c r="E79">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F79" t="s">
         <v>1520</v>
@@ -10596,7 +10596,7 @@
         <v>1366</v>
       </c>
       <c r="E80">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F80" t="s">
         <v>1518</v>
@@ -10631,7 +10631,7 @@
         <v>1367</v>
       </c>
       <c r="E81">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F81" t="s">
         <v>1518</v>
@@ -10666,7 +10666,7 @@
         <v>1368</v>
       </c>
       <c r="E82">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F82" t="s">
         <v>1518</v>
@@ -10701,7 +10701,7 @@
         <v>1369</v>
       </c>
       <c r="E83">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F83" t="s">
         <v>1518</v>
@@ -10736,7 +10736,7 @@
         <v>1370</v>
       </c>
       <c r="E84">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F84" t="s">
         <v>1518</v>
@@ -10771,7 +10771,7 @@
         <v>1371</v>
       </c>
       <c r="E85">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F85" t="s">
         <v>1518</v>
@@ -10806,7 +10806,7 @@
         <v>1372</v>
       </c>
       <c r="E86">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F86" t="s">
         <v>1518</v>
@@ -10841,7 +10841,7 @@
         <v>1372</v>
       </c>
       <c r="E87">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F87" t="s">
         <v>1518</v>
@@ -10876,7 +10876,7 @@
         <v>1373</v>
       </c>
       <c r="E88">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F88" t="s">
         <v>1518</v>
@@ -10911,7 +10911,7 @@
         <v>1373</v>
       </c>
       <c r="E89">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F89" t="s">
         <v>1518</v>
@@ -10946,7 +10946,7 @@
         <v>1373</v>
       </c>
       <c r="E90">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F90" t="s">
         <v>1518</v>
@@ -10981,7 +10981,7 @@
         <v>1374</v>
       </c>
       <c r="E91">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F91" t="s">
         <v>1518</v>
@@ -11016,7 +11016,7 @@
         <v>1374</v>
       </c>
       <c r="E92">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F92" t="s">
         <v>1518</v>
@@ -11051,7 +11051,7 @@
         <v>1375</v>
       </c>
       <c r="E93">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F93" t="s">
         <v>1518</v>
@@ -11086,7 +11086,7 @@
         <v>1376</v>
       </c>
       <c r="E94">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F94" t="s">
         <v>1518</v>
@@ -11121,7 +11121,7 @@
         <v>1377</v>
       </c>
       <c r="E95">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F95" t="s">
         <v>1518</v>
@@ -11156,7 +11156,7 @@
         <v>1377</v>
       </c>
       <c r="E96">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F96" t="s">
         <v>1518</v>
@@ -11191,7 +11191,7 @@
         <v>1378</v>
       </c>
       <c r="E97">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F97" t="s">
         <v>1518</v>
@@ -11226,7 +11226,7 @@
         <v>1378</v>
       </c>
       <c r="E98">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F98" t="s">
         <v>1518</v>
@@ -11261,7 +11261,7 @@
         <v>1379</v>
       </c>
       <c r="E99">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F99" t="s">
         <v>1518</v>
@@ -11296,7 +11296,7 @@
         <v>1380</v>
       </c>
       <c r="E100">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F100" t="s">
         <v>1518</v>
@@ -11331,7 +11331,7 @@
         <v>1380</v>
       </c>
       <c r="E101">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F101" t="s">
         <v>1518</v>
@@ -11366,7 +11366,7 @@
         <v>1381</v>
       </c>
       <c r="E102">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F102" t="s">
         <v>1518</v>
@@ -11401,7 +11401,7 @@
         <v>1382</v>
       </c>
       <c r="E103">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F103" t="s">
         <v>1518</v>
@@ -11436,7 +11436,7 @@
         <v>1382</v>
       </c>
       <c r="E104">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F104" t="s">
         <v>1518</v>
@@ -11471,7 +11471,7 @@
         <v>1383</v>
       </c>
       <c r="E105">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F105" t="s">
         <v>1518</v>
@@ -11506,7 +11506,7 @@
         <v>1384</v>
       </c>
       <c r="E106">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F106" t="s">
         <v>1518</v>
@@ -11544,7 +11544,7 @@
         <v>1384</v>
       </c>
       <c r="E107">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F107" t="s">
         <v>1518</v>
@@ -11579,7 +11579,7 @@
         <v>1384</v>
       </c>
       <c r="E108">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F108" t="s">
         <v>1518</v>
@@ -11614,7 +11614,7 @@
         <v>1384</v>
       </c>
       <c r="E109">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F109" t="s">
         <v>1518</v>
@@ -11649,7 +11649,7 @@
         <v>1385</v>
       </c>
       <c r="E110">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F110" t="s">
         <v>1519</v>
@@ -11684,7 +11684,7 @@
         <v>1386</v>
       </c>
       <c r="E111">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F111" t="s">
         <v>1518</v>
@@ -11719,7 +11719,7 @@
         <v>1386</v>
       </c>
       <c r="E112">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F112" t="s">
         <v>1518</v>
@@ -11754,7 +11754,7 @@
         <v>1386</v>
       </c>
       <c r="E113">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F113" t="s">
         <v>1518</v>
@@ -11789,7 +11789,7 @@
         <v>1386</v>
       </c>
       <c r="E114">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F114" t="s">
         <v>1518</v>
@@ -11824,7 +11824,7 @@
         <v>1387</v>
       </c>
       <c r="E115">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F115" t="s">
         <v>1518</v>
@@ -11859,7 +11859,7 @@
         <v>1387</v>
       </c>
       <c r="E116">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F116" t="s">
         <v>1518</v>
@@ -11894,7 +11894,7 @@
         <v>1387</v>
       </c>
       <c r="E117">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F117" t="s">
         <v>1518</v>
@@ -11929,7 +11929,7 @@
         <v>1387</v>
       </c>
       <c r="E118">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F118" t="s">
         <v>1518</v>
@@ -11964,7 +11964,7 @@
         <v>1387</v>
       </c>
       <c r="E119">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F119" t="s">
         <v>1518</v>
@@ -11999,7 +11999,7 @@
         <v>1387</v>
       </c>
       <c r="E120">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F120" t="s">
         <v>1518</v>
@@ -12034,7 +12034,7 @@
         <v>1387</v>
       </c>
       <c r="E121">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F121" t="s">
         <v>1518</v>
@@ -12069,7 +12069,7 @@
         <v>1388</v>
       </c>
       <c r="E122">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F122" t="s">
         <v>1518</v>
@@ -12104,7 +12104,7 @@
         <v>1389</v>
       </c>
       <c r="E123">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F123" t="s">
         <v>1518</v>
@@ -12139,7 +12139,7 @@
         <v>1390</v>
       </c>
       <c r="E124">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F124" t="s">
         <v>1518</v>
@@ -12174,7 +12174,7 @@
         <v>1390</v>
       </c>
       <c r="E125">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F125" t="s">
         <v>1518</v>
@@ -12209,7 +12209,7 @@
         <v>1390</v>
       </c>
       <c r="E126">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F126" t="s">
         <v>1518</v>
@@ -12244,7 +12244,7 @@
         <v>1391</v>
       </c>
       <c r="E127">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F127" t="s">
         <v>1518</v>
@@ -12279,7 +12279,7 @@
         <v>1391</v>
       </c>
       <c r="E128">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F128" t="s">
         <v>1518</v>
@@ -12314,7 +12314,7 @@
         <v>1391</v>
       </c>
       <c r="E129">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F129" t="s">
         <v>1518</v>
@@ -12349,7 +12349,7 @@
         <v>1391</v>
       </c>
       <c r="E130">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F130" t="s">
         <v>1518</v>
@@ -12384,7 +12384,7 @@
         <v>1391</v>
       </c>
       <c r="E131">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F131" t="s">
         <v>1518</v>
@@ -12419,7 +12419,7 @@
         <v>1391</v>
       </c>
       <c r="E132">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F132" t="s">
         <v>1518</v>
@@ -12454,7 +12454,7 @@
         <v>1391</v>
       </c>
       <c r="E133">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F133" t="s">
         <v>1518</v>
@@ -12489,7 +12489,7 @@
         <v>1391</v>
       </c>
       <c r="E134">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F134" t="s">
         <v>1518</v>
@@ -12524,7 +12524,7 @@
         <v>1391</v>
       </c>
       <c r="E135">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F135" t="s">
         <v>1518</v>
@@ -12559,7 +12559,7 @@
         <v>1392</v>
       </c>
       <c r="E136">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F136" t="s">
         <v>1518</v>
@@ -12594,7 +12594,7 @@
         <v>1392</v>
       </c>
       <c r="E137">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F137" t="s">
         <v>1518</v>
@@ -12629,7 +12629,7 @@
         <v>1392</v>
       </c>
       <c r="E138">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F138" t="s">
         <v>1518</v>
@@ -12664,7 +12664,7 @@
         <v>1393</v>
       </c>
       <c r="E139">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F139" t="s">
         <v>1518</v>
@@ -12699,7 +12699,7 @@
         <v>1393</v>
       </c>
       <c r="E140">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F140" t="s">
         <v>1519</v>
@@ -12734,7 +12734,7 @@
         <v>1393</v>
       </c>
       <c r="E141">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F141" t="s">
         <v>1518</v>
@@ -12769,7 +12769,7 @@
         <v>1394</v>
       </c>
       <c r="E142">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F142" t="s">
         <v>1518</v>
@@ -12804,7 +12804,7 @@
         <v>1394</v>
       </c>
       <c r="E143">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F143" t="s">
         <v>1518</v>
@@ -12839,7 +12839,7 @@
         <v>1395</v>
       </c>
       <c r="E144">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F144" t="s">
         <v>1518</v>
@@ -12874,7 +12874,7 @@
         <v>1395</v>
       </c>
       <c r="E145">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F145" t="s">
         <v>1518</v>
@@ -12909,7 +12909,7 @@
         <v>1396</v>
       </c>
       <c r="E146">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F146" t="s">
         <v>1518</v>
@@ -12944,7 +12944,7 @@
         <v>1396</v>
       </c>
       <c r="E147">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F147" t="s">
         <v>1518</v>
@@ -12979,7 +12979,7 @@
         <v>1397</v>
       </c>
       <c r="E148">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F148" t="s">
         <v>1518</v>
@@ -13014,7 +13014,7 @@
         <v>1397</v>
       </c>
       <c r="E149">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F149" t="s">
         <v>1518</v>
@@ -13049,7 +13049,7 @@
         <v>1397</v>
       </c>
       <c r="E150">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F150" t="s">
         <v>1518</v>
@@ -13084,7 +13084,7 @@
         <v>1398</v>
       </c>
       <c r="E151">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F151" t="s">
         <v>1518</v>
@@ -13119,7 +13119,7 @@
         <v>1398</v>
       </c>
       <c r="E152">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F152" t="s">
         <v>1518</v>
@@ -13154,7 +13154,7 @@
         <v>1399</v>
       </c>
       <c r="E153">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F153" t="s">
         <v>1518</v>
@@ -13189,7 +13189,7 @@
         <v>1400</v>
       </c>
       <c r="E154">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F154" t="s">
         <v>1518</v>
@@ -13224,7 +13224,7 @@
         <v>1400</v>
       </c>
       <c r="E155">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F155" t="s">
         <v>1518</v>
@@ -13259,7 +13259,7 @@
         <v>1400</v>
       </c>
       <c r="E156">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F156" t="s">
         <v>1518</v>
@@ -13294,7 +13294,7 @@
         <v>1400</v>
       </c>
       <c r="E157">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F157" t="s">
         <v>1518</v>
@@ -13329,7 +13329,7 @@
         <v>1401</v>
       </c>
       <c r="E158">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F158" t="s">
         <v>1518</v>
@@ -13364,7 +13364,7 @@
         <v>1402</v>
       </c>
       <c r="E159">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F159" t="s">
         <v>1518</v>
@@ -13399,7 +13399,7 @@
         <v>1402</v>
       </c>
       <c r="E160">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F160" t="s">
         <v>1518</v>
@@ -13434,7 +13434,7 @@
         <v>1402</v>
       </c>
       <c r="E161">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F161" t="s">
         <v>1518</v>
@@ -13469,7 +13469,7 @@
         <v>1402</v>
       </c>
       <c r="E162">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F162" t="s">
         <v>1518</v>
@@ -13504,7 +13504,7 @@
         <v>1402</v>
       </c>
       <c r="E163">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F163" t="s">
         <v>1518</v>
@@ -13539,7 +13539,7 @@
         <v>1403</v>
       </c>
       <c r="E164">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F164" t="s">
         <v>1518</v>
@@ -13574,7 +13574,7 @@
         <v>1403</v>
       </c>
       <c r="E165">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F165" t="s">
         <v>1518</v>
@@ -13609,7 +13609,7 @@
         <v>1403</v>
       </c>
       <c r="E166">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F166" t="s">
         <v>1518</v>
@@ -13644,7 +13644,7 @@
         <v>1403</v>
       </c>
       <c r="E167">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F167" t="s">
         <v>1518</v>
@@ -13679,7 +13679,7 @@
         <v>1403</v>
       </c>
       <c r="E168">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F168" t="s">
         <v>1518</v>
@@ -13714,7 +13714,7 @@
         <v>1403</v>
       </c>
       <c r="E169">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F169" t="s">
         <v>1518</v>
@@ -13749,7 +13749,7 @@
         <v>1404</v>
       </c>
       <c r="E170">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F170" t="s">
         <v>1518</v>
@@ -13784,7 +13784,7 @@
         <v>1404</v>
       </c>
       <c r="E171">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F171" t="s">
         <v>1518</v>
@@ -13819,7 +13819,7 @@
         <v>1404</v>
       </c>
       <c r="E172">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F172" t="s">
         <v>1518</v>
@@ -13854,7 +13854,7 @@
         <v>1405</v>
       </c>
       <c r="E173">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F173" t="s">
         <v>1518</v>
@@ -13889,7 +13889,7 @@
         <v>1405</v>
       </c>
       <c r="E174">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F174" t="s">
         <v>1518</v>
@@ -13924,7 +13924,7 @@
         <v>1406</v>
       </c>
       <c r="E175">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F175" t="s">
         <v>1518</v>
@@ -13959,7 +13959,7 @@
         <v>1407</v>
       </c>
       <c r="E176">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F176" t="s">
         <v>1518</v>
@@ -13994,7 +13994,7 @@
         <v>1407</v>
       </c>
       <c r="E177">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F177" t="s">
         <v>1518</v>
@@ -14029,7 +14029,7 @@
         <v>1408</v>
       </c>
       <c r="E178">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F178" t="s">
         <v>1518</v>
@@ -14064,7 +14064,7 @@
         <v>1409</v>
       </c>
       <c r="E179">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F179" t="s">
         <v>1518</v>
@@ -14099,7 +14099,7 @@
         <v>1409</v>
       </c>
       <c r="E180">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F180" t="s">
         <v>1518</v>
@@ -14134,7 +14134,7 @@
         <v>1410</v>
       </c>
       <c r="E181">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F181" t="s">
         <v>1518</v>
@@ -14169,7 +14169,7 @@
         <v>1410</v>
       </c>
       <c r="E182">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F182" t="s">
         <v>1518</v>
@@ -14204,7 +14204,7 @@
         <v>1411</v>
       </c>
       <c r="E183">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F183" t="s">
         <v>1518</v>
@@ -14239,7 +14239,7 @@
         <v>1411</v>
       </c>
       <c r="E184">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F184" t="s">
         <v>1518</v>
@@ -14274,7 +14274,7 @@
         <v>1411</v>
       </c>
       <c r="E185">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F185" t="s">
         <v>1518</v>
@@ -14309,7 +14309,7 @@
         <v>1412</v>
       </c>
       <c r="E186">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F186" t="s">
         <v>1518</v>
@@ -14344,7 +14344,7 @@
         <v>1412</v>
       </c>
       <c r="E187">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F187" t="s">
         <v>1518</v>
@@ -14379,7 +14379,7 @@
         <v>1413</v>
       </c>
       <c r="E188">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F188" t="s">
         <v>1518</v>
@@ -14414,7 +14414,7 @@
         <v>1414</v>
       </c>
       <c r="E189">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F189" t="s">
         <v>1518</v>
@@ -14449,7 +14449,7 @@
         <v>1414</v>
       </c>
       <c r="E190">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F190" t="s">
         <v>1518</v>
@@ -14484,7 +14484,7 @@
         <v>1414</v>
       </c>
       <c r="E191">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F191" t="s">
         <v>1518</v>
@@ -14519,7 +14519,7 @@
         <v>1415</v>
       </c>
       <c r="E192">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F192" t="s">
         <v>1518</v>
@@ -14554,7 +14554,7 @@
         <v>1415</v>
       </c>
       <c r="E193">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F193" t="s">
         <v>1518</v>
@@ -14589,7 +14589,7 @@
         <v>1416</v>
       </c>
       <c r="E194">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F194" t="s">
         <v>1518</v>
@@ -14624,7 +14624,7 @@
         <v>1416</v>
       </c>
       <c r="E195">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F195" t="s">
         <v>1520</v>
@@ -14659,7 +14659,7 @@
         <v>1416</v>
       </c>
       <c r="E196">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F196" t="s">
         <v>1518</v>
@@ -14694,7 +14694,7 @@
         <v>1417</v>
       </c>
       <c r="E197">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F197" t="s">
         <v>1518</v>
@@ -14729,7 +14729,7 @@
         <v>1417</v>
       </c>
       <c r="E198">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F198" t="s">
         <v>1518</v>
@@ -14767,7 +14767,7 @@
         <v>1417</v>
       </c>
       <c r="E199">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F199" t="s">
         <v>1518</v>
@@ -14802,7 +14802,7 @@
         <v>1417</v>
       </c>
       <c r="E200">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F200" t="s">
         <v>1518</v>
@@ -14837,7 +14837,7 @@
         <v>1417</v>
       </c>
       <c r="E201">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F201" t="s">
         <v>1518</v>
@@ -14872,7 +14872,7 @@
         <v>1417</v>
       </c>
       <c r="E202">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F202" t="s">
         <v>1518</v>
@@ -14907,7 +14907,7 @@
         <v>1418</v>
       </c>
       <c r="E203">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F203" t="s">
         <v>1518</v>
@@ -14942,7 +14942,7 @@
         <v>1418</v>
       </c>
       <c r="E204">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F204" t="s">
         <v>1518</v>
@@ -14977,7 +14977,7 @@
         <v>1418</v>
       </c>
       <c r="E205">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F205" t="s">
         <v>1518</v>
@@ -15012,7 +15012,7 @@
         <v>1419</v>
       </c>
       <c r="E206">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F206" t="s">
         <v>1518</v>
@@ -15047,7 +15047,7 @@
         <v>1419</v>
       </c>
       <c r="E207">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F207" t="s">
         <v>1518</v>
@@ -15082,7 +15082,7 @@
         <v>1419</v>
       </c>
       <c r="E208">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F208" t="s">
         <v>1518</v>
@@ -15117,7 +15117,7 @@
         <v>1420</v>
       </c>
       <c r="E209">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F209" t="s">
         <v>1518</v>
@@ -15152,7 +15152,7 @@
         <v>1420</v>
       </c>
       <c r="E210">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F210" t="s">
         <v>1518</v>
@@ -15187,7 +15187,7 @@
         <v>1420</v>
       </c>
       <c r="E211">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F211" t="s">
         <v>1518</v>
@@ -15222,7 +15222,7 @@
         <v>1421</v>
       </c>
       <c r="E212">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F212" t="s">
         <v>1518</v>
@@ -15257,7 +15257,7 @@
         <v>1421</v>
       </c>
       <c r="E213">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F213" t="s">
         <v>1518</v>
@@ -15292,7 +15292,7 @@
         <v>1421</v>
       </c>
       <c r="E214">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F214" t="s">
         <v>1518</v>
@@ -15327,7 +15327,7 @@
         <v>1421</v>
       </c>
       <c r="E215">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F215" t="s">
         <v>1518</v>
@@ -15362,7 +15362,7 @@
         <v>1421</v>
       </c>
       <c r="E216">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F216" t="s">
         <v>1518</v>
@@ -15397,7 +15397,7 @@
         <v>1422</v>
       </c>
       <c r="E217">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F217" t="s">
         <v>1518</v>
@@ -15432,7 +15432,7 @@
         <v>1423</v>
       </c>
       <c r="E218">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F218" t="s">
         <v>1518</v>
@@ -15467,7 +15467,7 @@
         <v>1423</v>
       </c>
       <c r="E219">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F219" t="s">
         <v>1521</v>
@@ -15502,7 +15502,7 @@
         <v>1423</v>
       </c>
       <c r="E220">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F220" t="s">
         <v>1518</v>
@@ -15537,7 +15537,7 @@
         <v>1423</v>
       </c>
       <c r="E221">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F221" t="s">
         <v>1518</v>
@@ -15572,7 +15572,7 @@
         <v>1423</v>
       </c>
       <c r="E222">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F222" t="s">
         <v>1518</v>
@@ -15607,7 +15607,7 @@
         <v>1424</v>
       </c>
       <c r="E223">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F223" t="s">
         <v>1518</v>
@@ -15642,7 +15642,7 @@
         <v>1424</v>
       </c>
       <c r="E224">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F224" t="s">
         <v>1518</v>
@@ -15677,7 +15677,7 @@
         <v>1424</v>
       </c>
       <c r="E225">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F225" t="s">
         <v>1518</v>
@@ -15712,7 +15712,7 @@
         <v>1424</v>
       </c>
       <c r="E226">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F226" t="s">
         <v>1518</v>
@@ -15747,7 +15747,7 @@
         <v>1425</v>
       </c>
       <c r="E227">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F227" t="s">
         <v>1518</v>
@@ -15782,7 +15782,7 @@
         <v>1426</v>
       </c>
       <c r="E228">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F228" t="s">
         <v>1518</v>
@@ -15820,7 +15820,7 @@
         <v>1427</v>
       </c>
       <c r="E229">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F229" t="s">
         <v>1518</v>
@@ -15855,7 +15855,7 @@
         <v>1427</v>
       </c>
       <c r="E230">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F230" t="s">
         <v>1518</v>
@@ -15890,7 +15890,7 @@
         <v>1427</v>
       </c>
       <c r="E231">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F231" t="s">
         <v>1518</v>
@@ -15925,7 +15925,7 @@
         <v>1427</v>
       </c>
       <c r="E232">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F232" t="s">
         <v>1518</v>
@@ -15960,7 +15960,7 @@
         <v>1428</v>
       </c>
       <c r="E233">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F233" t="s">
         <v>1518</v>
@@ -15995,7 +15995,7 @@
         <v>1428</v>
       </c>
       <c r="E234">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F234" t="s">
         <v>1518</v>
@@ -16030,7 +16030,7 @@
         <v>1429</v>
       </c>
       <c r="E235">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F235" t="s">
         <v>1518</v>
@@ -16065,7 +16065,7 @@
         <v>1429</v>
       </c>
       <c r="E236">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F236" t="s">
         <v>1518</v>
@@ -16100,7 +16100,7 @@
         <v>1430</v>
       </c>
       <c r="E237">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F237" t="s">
         <v>1518</v>
@@ -16135,7 +16135,7 @@
         <v>1430</v>
       </c>
       <c r="E238">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F238" t="s">
         <v>1518</v>
@@ -16170,7 +16170,7 @@
         <v>1430</v>
       </c>
       <c r="E239">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F239" t="s">
         <v>1518</v>
@@ -16205,7 +16205,7 @@
         <v>1431</v>
       </c>
       <c r="E240">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F240" t="s">
         <v>1518</v>
@@ -16240,7 +16240,7 @@
         <v>1431</v>
       </c>
       <c r="E241">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F241" t="s">
         <v>1518</v>
@@ -16275,7 +16275,7 @@
         <v>1431</v>
       </c>
       <c r="E242">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F242" t="s">
         <v>1518</v>
@@ -16310,7 +16310,7 @@
         <v>1432</v>
       </c>
       <c r="E243">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F243" t="s">
         <v>1518</v>
@@ -16345,7 +16345,7 @@
         <v>1433</v>
       </c>
       <c r="E244">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F244" t="s">
         <v>1518</v>
@@ -16380,7 +16380,7 @@
         <v>1433</v>
       </c>
       <c r="E245">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F245" t="s">
         <v>1518</v>
@@ -16415,7 +16415,7 @@
         <v>1433</v>
       </c>
       <c r="E246">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F246" t="s">
         <v>1518</v>
@@ -16450,7 +16450,7 @@
         <v>1433</v>
       </c>
       <c r="E247">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F247" t="s">
         <v>1518</v>
@@ -16485,7 +16485,7 @@
         <v>1434</v>
       </c>
       <c r="E248">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F248" t="s">
         <v>1518</v>
@@ -16520,7 +16520,7 @@
         <v>1434</v>
       </c>
       <c r="E249">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F249" t="s">
         <v>1518</v>
@@ -16555,7 +16555,7 @@
         <v>1434</v>
       </c>
       <c r="E250">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F250" t="s">
         <v>1518</v>
@@ -16590,7 +16590,7 @@
         <v>1435</v>
       </c>
       <c r="E251">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F251" t="s">
         <v>1518</v>
@@ -16625,7 +16625,7 @@
         <v>1435</v>
       </c>
       <c r="E252">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F252" t="s">
         <v>1518</v>
@@ -16660,7 +16660,7 @@
         <v>1436</v>
       </c>
       <c r="E253">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F253" t="s">
         <v>1518</v>
@@ -16695,7 +16695,7 @@
         <v>1436</v>
       </c>
       <c r="E254">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F254" t="s">
         <v>1518</v>
@@ -16730,7 +16730,7 @@
         <v>1436</v>
       </c>
       <c r="E255">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F255" t="s">
         <v>1518</v>
@@ -16765,7 +16765,7 @@
         <v>1436</v>
       </c>
       <c r="E256">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F256" t="s">
         <v>1518</v>
@@ -16800,7 +16800,7 @@
         <v>1436</v>
       </c>
       <c r="E257">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F257" t="s">
         <v>1518</v>
@@ -16835,7 +16835,7 @@
         <v>1437</v>
       </c>
       <c r="E258">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F258" t="s">
         <v>1518</v>
@@ -16870,7 +16870,7 @@
         <v>1437</v>
       </c>
       <c r="E259">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F259" t="s">
         <v>1518</v>
@@ -16905,7 +16905,7 @@
         <v>1437</v>
       </c>
       <c r="E260">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F260" t="s">
         <v>1518</v>
@@ -16940,7 +16940,7 @@
         <v>1438</v>
       </c>
       <c r="E261">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F261" t="s">
         <v>1518</v>
@@ -16975,7 +16975,7 @@
         <v>1439</v>
       </c>
       <c r="E262">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F262" t="s">
         <v>1518</v>
@@ -17010,7 +17010,7 @@
         <v>1440</v>
       </c>
       <c r="E263">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F263" t="s">
         <v>1518</v>
@@ -17045,7 +17045,7 @@
         <v>1440</v>
       </c>
       <c r="E264">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F264" t="s">
         <v>1518</v>
@@ -17080,7 +17080,7 @@
         <v>1440</v>
       </c>
       <c r="E265">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F265" t="s">
         <v>1518</v>
@@ -17115,7 +17115,7 @@
         <v>1440</v>
       </c>
       <c r="E266">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F266" t="s">
         <v>1518</v>
@@ -17150,7 +17150,7 @@
         <v>1440</v>
       </c>
       <c r="E267">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F267" t="s">
         <v>1518</v>
@@ -17185,7 +17185,7 @@
         <v>1441</v>
       </c>
       <c r="E268">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F268" t="s">
         <v>1518</v>
@@ -17220,7 +17220,7 @@
         <v>1441</v>
       </c>
       <c r="E269">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F269" t="s">
         <v>1518</v>
@@ -17255,7 +17255,7 @@
         <v>1442</v>
       </c>
       <c r="E270">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F270" t="s">
         <v>1518</v>
@@ -17290,7 +17290,7 @@
         <v>1442</v>
       </c>
       <c r="E271">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F271" t="s">
         <v>1518</v>
@@ -17325,7 +17325,7 @@
         <v>1443</v>
       </c>
       <c r="E272">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F272" t="s">
         <v>1518</v>
@@ -17360,7 +17360,7 @@
         <v>1444</v>
       </c>
       <c r="E273">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F273" t="s">
         <v>1518</v>
@@ -17395,7 +17395,7 @@
         <v>1445</v>
       </c>
       <c r="E274">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F274" t="s">
         <v>1518</v>
@@ -17430,7 +17430,7 @@
         <v>1445</v>
       </c>
       <c r="E275">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F275" t="s">
         <v>1518</v>
@@ -17465,7 +17465,7 @@
         <v>1446</v>
       </c>
       <c r="E276">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F276" t="s">
         <v>1518</v>
@@ -17500,7 +17500,7 @@
         <v>1446</v>
       </c>
       <c r="E277">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F277" t="s">
         <v>1518</v>
@@ -17535,7 +17535,7 @@
         <v>1446</v>
       </c>
       <c r="E278">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F278" t="s">
         <v>1518</v>
@@ -17570,7 +17570,7 @@
         <v>1447</v>
       </c>
       <c r="E279">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F279" t="s">
         <v>1518</v>
@@ -17605,7 +17605,7 @@
         <v>1447</v>
       </c>
       <c r="E280">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F280" t="s">
         <v>1518</v>
@@ -17640,7 +17640,7 @@
         <v>1447</v>
       </c>
       <c r="E281">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F281" t="s">
         <v>1518</v>
@@ -17675,7 +17675,7 @@
         <v>1447</v>
       </c>
       <c r="E282">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F282" t="s">
         <v>1518</v>
@@ -17710,7 +17710,7 @@
         <v>1447</v>
       </c>
       <c r="E283">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F283" t="s">
         <v>1518</v>
@@ -17745,7 +17745,7 @@
         <v>1447</v>
       </c>
       <c r="E284">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F284" t="s">
         <v>1518</v>
@@ -17780,7 +17780,7 @@
         <v>1447</v>
       </c>
       <c r="E285">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F285" t="s">
         <v>1518</v>
@@ -17815,7 +17815,7 @@
         <v>1447</v>
       </c>
       <c r="E286">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F286" t="s">
         <v>1518</v>
@@ -17850,7 +17850,7 @@
         <v>1447</v>
       </c>
       <c r="E287">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F287" t="s">
         <v>1518</v>
@@ -17885,7 +17885,7 @@
         <v>1448</v>
       </c>
       <c r="E288">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F288" t="s">
         <v>1518</v>
@@ -17920,7 +17920,7 @@
         <v>1448</v>
       </c>
       <c r="E289">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F289" t="s">
         <v>1518</v>
@@ -17955,7 +17955,7 @@
         <v>1448</v>
       </c>
       <c r="E290">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F290" t="s">
         <v>1518</v>
@@ -17990,7 +17990,7 @@
         <v>1449</v>
       </c>
       <c r="E291">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F291" t="s">
         <v>1518</v>
@@ -18025,7 +18025,7 @@
         <v>1450</v>
       </c>
       <c r="E292">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F292" t="s">
         <v>1518</v>
@@ -18060,7 +18060,7 @@
         <v>1450</v>
       </c>
       <c r="E293">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F293" t="s">
         <v>1518</v>
@@ -18095,7 +18095,7 @@
         <v>1450</v>
       </c>
       <c r="E294">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F294" t="s">
         <v>1518</v>
@@ -18130,7 +18130,7 @@
         <v>1450</v>
       </c>
       <c r="E295">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F295" t="s">
         <v>1518</v>
@@ -18165,7 +18165,7 @@
         <v>1450</v>
       </c>
       <c r="E296">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F296" t="s">
         <v>1518</v>
@@ -18200,7 +18200,7 @@
         <v>1450</v>
       </c>
       <c r="E297">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F297" t="s">
         <v>1518</v>
@@ -18235,7 +18235,7 @@
         <v>1451</v>
       </c>
       <c r="E298">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F298" t="s">
         <v>1518</v>
@@ -18270,7 +18270,7 @@
         <v>1451</v>
       </c>
       <c r="E299">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F299" t="s">
         <v>1518</v>
@@ -18305,7 +18305,7 @@
         <v>1451</v>
       </c>
       <c r="E300">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F300" t="s">
         <v>1518</v>
@@ -18340,7 +18340,7 @@
         <v>1451</v>
       </c>
       <c r="E301">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F301" t="s">
         <v>1518</v>
@@ -18378,7 +18378,7 @@
         <v>1451</v>
       </c>
       <c r="E302">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F302" t="s">
         <v>1518</v>
@@ -18413,7 +18413,7 @@
         <v>1451</v>
       </c>
       <c r="E303">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F303" t="s">
         <v>1518</v>
@@ -18448,7 +18448,7 @@
         <v>1451</v>
       </c>
       <c r="E304">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F304" t="s">
         <v>1518</v>
@@ -18483,7 +18483,7 @@
         <v>1451</v>
       </c>
       <c r="E305">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F305" t="s">
         <v>1518</v>
@@ -18518,7 +18518,7 @@
         <v>1451</v>
       </c>
       <c r="E306">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F306" t="s">
         <v>1518</v>
@@ -18553,7 +18553,7 @@
         <v>1452</v>
       </c>
       <c r="E307">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F307" t="s">
         <v>1519</v>
@@ -18588,7 +18588,7 @@
         <v>1453</v>
       </c>
       <c r="E308">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F308" t="s">
         <v>1522</v>
@@ -18623,7 +18623,7 @@
         <v>1454</v>
       </c>
       <c r="E309">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F309" t="s">
         <v>1518</v>
@@ -18658,7 +18658,7 @@
         <v>1455</v>
       </c>
       <c r="E310">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F310" t="s">
         <v>1518</v>
@@ -18693,7 +18693,7 @@
         <v>1455</v>
       </c>
       <c r="E311">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F311" t="s">
         <v>1518</v>
@@ -18728,7 +18728,7 @@
         <v>1456</v>
       </c>
       <c r="E312">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F312" t="s">
         <v>1518</v>
@@ -18763,7 +18763,7 @@
         <v>1457</v>
       </c>
       <c r="E313">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F313" t="s">
         <v>1521</v>
@@ -18798,7 +18798,7 @@
         <v>1457</v>
       </c>
       <c r="E314">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F314" t="s">
         <v>1518</v>
@@ -18833,7 +18833,7 @@
         <v>1457</v>
       </c>
       <c r="E315">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F315" t="s">
         <v>1518</v>
@@ -18868,7 +18868,7 @@
         <v>1457</v>
       </c>
       <c r="E316">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F316" t="s">
         <v>1518</v>
@@ -18903,7 +18903,7 @@
         <v>1457</v>
       </c>
       <c r="E317">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F317" t="s">
         <v>1518</v>
@@ -18938,7 +18938,7 @@
         <v>1457</v>
       </c>
       <c r="E318">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F318" t="s">
         <v>1518</v>
@@ -18973,7 +18973,7 @@
         <v>1458</v>
       </c>
       <c r="E319">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F319" t="s">
         <v>1518</v>
@@ -19008,7 +19008,7 @@
         <v>1459</v>
       </c>
       <c r="E320">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F320" t="s">
         <v>1518</v>
@@ -19043,7 +19043,7 @@
         <v>1459</v>
       </c>
       <c r="E321">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F321" t="s">
         <v>1518</v>
@@ -19078,7 +19078,7 @@
         <v>1459</v>
       </c>
       <c r="E322">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F322" t="s">
         <v>1518</v>
@@ -19116,7 +19116,7 @@
         <v>1459</v>
       </c>
       <c r="E323">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F323" t="s">
         <v>1518</v>
@@ -19151,7 +19151,7 @@
         <v>1460</v>
       </c>
       <c r="E324">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F324" t="s">
         <v>1518</v>
@@ -19186,7 +19186,7 @@
         <v>1460</v>
       </c>
       <c r="E325">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F325" t="s">
         <v>1518</v>
@@ -19221,7 +19221,7 @@
         <v>1460</v>
       </c>
       <c r="E326">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F326" t="s">
         <v>1518</v>
@@ -19256,7 +19256,7 @@
         <v>1460</v>
       </c>
       <c r="E327">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F327" t="s">
         <v>1518</v>
@@ -19291,7 +19291,7 @@
         <v>1460</v>
       </c>
       <c r="E328">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F328" t="s">
         <v>1518</v>
@@ -19326,7 +19326,7 @@
         <v>1461</v>
       </c>
       <c r="E329">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F329" t="s">
         <v>1518</v>
@@ -19361,7 +19361,7 @@
         <v>1461</v>
       </c>
       <c r="E330">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F330" t="s">
         <v>1518</v>
@@ -19396,7 +19396,7 @@
         <v>1462</v>
       </c>
       <c r="E331">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F331" t="s">
         <v>1518</v>
@@ -19431,7 +19431,7 @@
         <v>1462</v>
       </c>
       <c r="E332">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F332" t="s">
         <v>1518</v>
@@ -19466,7 +19466,7 @@
         <v>1462</v>
       </c>
       <c r="E333">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F333" t="s">
         <v>1518</v>
@@ -19501,7 +19501,7 @@
         <v>1462</v>
       </c>
       <c r="E334">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F334" t="s">
         <v>1518</v>
@@ -19536,7 +19536,7 @@
         <v>1462</v>
       </c>
       <c r="E335">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F335" t="s">
         <v>1518</v>
@@ -19571,7 +19571,7 @@
         <v>1462</v>
       </c>
       <c r="E336">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F336" t="s">
         <v>1518</v>
@@ -19606,7 +19606,7 @@
         <v>1462</v>
       </c>
       <c r="E337">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F337" t="s">
         <v>1518</v>
@@ -19641,7 +19641,7 @@
         <v>1462</v>
       </c>
       <c r="E338">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F338" t="s">
         <v>1518</v>
@@ -19676,7 +19676,7 @@
         <v>1462</v>
       </c>
       <c r="E339">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F339" t="s">
         <v>1518</v>
@@ -19711,7 +19711,7 @@
         <v>1462</v>
       </c>
       <c r="E340">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F340" t="s">
         <v>1518</v>
@@ -19746,7 +19746,7 @@
         <v>1463</v>
       </c>
       <c r="E341">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F341" t="s">
         <v>1518</v>
@@ -19781,7 +19781,7 @@
         <v>1463</v>
       </c>
       <c r="E342">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F342" t="s">
         <v>1518</v>
@@ -19816,7 +19816,7 @@
         <v>1463</v>
       </c>
       <c r="E343">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F343" t="s">
         <v>1519</v>
@@ -19851,7 +19851,7 @@
         <v>1464</v>
       </c>
       <c r="E344">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F344" t="s">
         <v>1518</v>
@@ -19886,7 +19886,7 @@
         <v>1464</v>
       </c>
       <c r="E345">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F345" t="s">
         <v>1518</v>
@@ -19921,7 +19921,7 @@
         <v>1464</v>
       </c>
       <c r="E346">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F346" t="s">
         <v>1518</v>
@@ -19956,7 +19956,7 @@
         <v>1464</v>
       </c>
       <c r="E347">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F347" t="s">
         <v>1518</v>
@@ -19991,7 +19991,7 @@
         <v>1464</v>
       </c>
       <c r="E348">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F348" t="s">
         <v>1518</v>
@@ -20026,7 +20026,7 @@
         <v>1464</v>
       </c>
       <c r="E349">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F349" t="s">
         <v>1518</v>
@@ -20061,7 +20061,7 @@
         <v>1464</v>
       </c>
       <c r="E350">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F350" t="s">
         <v>1521</v>
@@ -20096,7 +20096,7 @@
         <v>1465</v>
       </c>
       <c r="E351">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F351" t="s">
         <v>1518</v>
@@ -20131,7 +20131,7 @@
         <v>1465</v>
       </c>
       <c r="E352">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F352" t="s">
         <v>1518</v>
@@ -20166,7 +20166,7 @@
         <v>1465</v>
       </c>
       <c r="E353">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F353" t="s">
         <v>1518</v>
@@ -20201,7 +20201,7 @@
         <v>1465</v>
       </c>
       <c r="E354">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F354" t="s">
         <v>1518</v>
@@ -20236,7 +20236,7 @@
         <v>1466</v>
       </c>
       <c r="E355">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F355" t="s">
         <v>1521</v>
@@ -20271,7 +20271,7 @@
         <v>1466</v>
       </c>
       <c r="E356">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F356" t="s">
         <v>1518</v>
@@ -20306,7 +20306,7 @@
         <v>1466</v>
       </c>
       <c r="E357">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F357" t="s">
         <v>1518</v>
@@ -20341,7 +20341,7 @@
         <v>1466</v>
       </c>
       <c r="E358">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F358" t="s">
         <v>1518</v>
@@ -20376,7 +20376,7 @@
         <v>1466</v>
       </c>
       <c r="E359">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F359" t="s">
         <v>1518</v>
@@ -20411,7 +20411,7 @@
         <v>1467</v>
       </c>
       <c r="E360">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F360" t="s">
         <v>1518</v>
@@ -20446,7 +20446,7 @@
         <v>1467</v>
       </c>
       <c r="E361">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F361" t="s">
         <v>1518</v>
@@ -20481,7 +20481,7 @@
         <v>1467</v>
       </c>
       <c r="E362">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F362" t="s">
         <v>1520</v>
@@ -20516,7 +20516,7 @@
         <v>1467</v>
       </c>
       <c r="E363">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F363" t="s">
         <v>1518</v>
@@ -20551,7 +20551,7 @@
         <v>1467</v>
       </c>
       <c r="E364">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F364" t="s">
         <v>1518</v>
@@ -20586,7 +20586,7 @@
         <v>1468</v>
       </c>
       <c r="E365">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F365" t="s">
         <v>1518</v>
@@ -20621,7 +20621,7 @@
         <v>1468</v>
       </c>
       <c r="E366">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F366" t="s">
         <v>1518</v>
@@ -20656,7 +20656,7 @@
         <v>1468</v>
       </c>
       <c r="E367">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F367" t="s">
         <v>1518</v>
@@ -20691,7 +20691,7 @@
         <v>1468</v>
       </c>
       <c r="E368">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F368" t="s">
         <v>1518</v>
@@ -20726,7 +20726,7 @@
         <v>1469</v>
       </c>
       <c r="E369">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F369" t="s">
         <v>1518</v>
@@ -20761,7 +20761,7 @@
         <v>1469</v>
       </c>
       <c r="E370">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F370" t="s">
         <v>1518</v>
@@ -20796,7 +20796,7 @@
         <v>1469</v>
       </c>
       <c r="E371">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F371" t="s">
         <v>1518</v>
@@ -20831,7 +20831,7 @@
         <v>1469</v>
       </c>
       <c r="E372">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F372" t="s">
         <v>1518</v>
@@ -20869,7 +20869,7 @@
         <v>1470</v>
       </c>
       <c r="E373">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F373" t="s">
         <v>1518</v>
@@ -20904,7 +20904,7 @@
         <v>1470</v>
       </c>
       <c r="E374">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F374" t="s">
         <v>1518</v>
@@ -20939,7 +20939,7 @@
         <v>1470</v>
       </c>
       <c r="E375">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F375" t="s">
         <v>1518</v>
@@ -20974,7 +20974,7 @@
         <v>1470</v>
       </c>
       <c r="E376">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F376" t="s">
         <v>1518</v>
@@ -21009,7 +21009,7 @@
         <v>1470</v>
       </c>
       <c r="E377">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F377" t="s">
         <v>1518</v>
@@ -21044,7 +21044,7 @@
         <v>1470</v>
       </c>
       <c r="E378">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F378" t="s">
         <v>1518</v>
@@ -21079,7 +21079,7 @@
         <v>1471</v>
       </c>
       <c r="E379">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F379" t="s">
         <v>1519</v>
@@ -21114,7 +21114,7 @@
         <v>1471</v>
       </c>
       <c r="E380">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F380" t="s">
         <v>1518</v>
@@ -21149,7 +21149,7 @@
         <v>1472</v>
       </c>
       <c r="E381">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F381" t="s">
         <v>1518</v>
@@ -21184,7 +21184,7 @@
         <v>1473</v>
       </c>
       <c r="E382">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F382" t="s">
         <v>1518</v>
@@ -21219,7 +21219,7 @@
         <v>1473</v>
       </c>
       <c r="E383">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F383" t="s">
         <v>1518</v>
@@ -21254,7 +21254,7 @@
         <v>1473</v>
       </c>
       <c r="E384">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F384" t="s">
         <v>1520</v>
@@ -21292,7 +21292,7 @@
         <v>1474</v>
       </c>
       <c r="E385">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F385" t="s">
         <v>1518</v>
@@ -21327,7 +21327,7 @@
         <v>1474</v>
       </c>
       <c r="E386">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F386" t="s">
         <v>1518</v>
@@ -21362,7 +21362,7 @@
         <v>1474</v>
       </c>
       <c r="E387">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F387" t="s">
         <v>1518</v>
@@ -21397,7 +21397,7 @@
         <v>1475</v>
       </c>
       <c r="E388">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F388" t="s">
         <v>1518</v>
@@ -21432,7 +21432,7 @@
         <v>1475</v>
       </c>
       <c r="E389">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F389" t="s">
         <v>1518</v>
@@ -21467,7 +21467,7 @@
         <v>1475</v>
       </c>
       <c r="E390">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F390" t="s">
         <v>1518</v>
@@ -21502,7 +21502,7 @@
         <v>1475</v>
       </c>
       <c r="E391">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F391" t="s">
         <v>1518</v>
@@ -21537,7 +21537,7 @@
         <v>1475</v>
       </c>
       <c r="E392">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F392" t="s">
         <v>1518</v>
@@ -21572,7 +21572,7 @@
         <v>1475</v>
       </c>
       <c r="E393">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F393" t="s">
         <v>1518</v>
@@ -21607,7 +21607,7 @@
         <v>1475</v>
       </c>
       <c r="E394">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F394" t="s">
         <v>1518</v>
@@ -21642,7 +21642,7 @@
         <v>1476</v>
       </c>
       <c r="E395">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F395" t="s">
         <v>1518</v>
@@ -21677,7 +21677,7 @@
         <v>1477</v>
       </c>
       <c r="E396">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F396" t="s">
         <v>1518</v>
@@ -21712,7 +21712,7 @@
         <v>1477</v>
       </c>
       <c r="E397">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F397" t="s">
         <v>1518</v>
@@ -21747,7 +21747,7 @@
         <v>1477</v>
       </c>
       <c r="E398">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F398" t="s">
         <v>1518</v>
@@ -21782,7 +21782,7 @@
         <v>1477</v>
       </c>
       <c r="E399">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F399" t="s">
         <v>1522</v>
@@ -21820,7 +21820,7 @@
         <v>1477</v>
       </c>
       <c r="E400">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F400" t="s">
         <v>1518</v>
@@ -21855,7 +21855,7 @@
         <v>1477</v>
       </c>
       <c r="E401">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F401" t="s">
         <v>1522</v>
@@ -21890,7 +21890,7 @@
         <v>1478</v>
       </c>
       <c r="E402">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F402" t="s">
         <v>1518</v>
@@ -21925,7 +21925,7 @@
         <v>1479</v>
       </c>
       <c r="E403">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F403" t="s">
         <v>1518</v>
@@ -21960,7 +21960,7 @@
         <v>1479</v>
       </c>
       <c r="E404">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F404" t="s">
         <v>1518</v>
@@ -21995,7 +21995,7 @@
         <v>1479</v>
       </c>
       <c r="E405">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F405" t="s">
         <v>1518</v>
@@ -22030,7 +22030,7 @@
         <v>1480</v>
       </c>
       <c r="E406">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F406" t="s">
         <v>1522</v>
@@ -22065,7 +22065,7 @@
         <v>1480</v>
       </c>
       <c r="E407">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F407" t="s">
         <v>1518</v>
@@ -22100,7 +22100,7 @@
         <v>1480</v>
       </c>
       <c r="E408">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F408" t="s">
         <v>1518</v>
@@ -22135,7 +22135,7 @@
         <v>1480</v>
       </c>
       <c r="E409">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F409" t="s">
         <v>1518</v>
@@ -22170,7 +22170,7 @@
         <v>1481</v>
       </c>
       <c r="E410">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F410" t="s">
         <v>1518</v>
@@ -22205,7 +22205,7 @@
         <v>1481</v>
       </c>
       <c r="E411">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F411" t="s">
         <v>1518</v>
@@ -22240,7 +22240,7 @@
         <v>1481</v>
       </c>
       <c r="E412">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F412" t="s">
         <v>1518</v>
@@ -22275,7 +22275,7 @@
         <v>1482</v>
       </c>
       <c r="E413">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F413" t="s">
         <v>1518</v>
@@ -22310,7 +22310,7 @@
         <v>1482</v>
       </c>
       <c r="E414">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F414" t="s">
         <v>1518</v>
@@ -22345,7 +22345,7 @@
         <v>1482</v>
       </c>
       <c r="E415">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F415" t="s">
         <v>1518</v>
@@ -22380,7 +22380,7 @@
         <v>1482</v>
       </c>
       <c r="E416">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F416" t="s">
         <v>1518</v>
@@ -22415,7 +22415,7 @@
         <v>1482</v>
       </c>
       <c r="E417">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F417" t="s">
         <v>1518</v>
@@ -22450,7 +22450,7 @@
         <v>1483</v>
       </c>
       <c r="E418">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F418" t="s">
         <v>1518</v>
@@ -22485,7 +22485,7 @@
         <v>1483</v>
       </c>
       <c r="E419">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F419" t="s">
         <v>1518</v>
@@ -22520,7 +22520,7 @@
         <v>1483</v>
       </c>
       <c r="E420">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F420" t="s">
         <v>1518</v>
@@ -22555,7 +22555,7 @@
         <v>1483</v>
       </c>
       <c r="E421">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F421" t="s">
         <v>1518</v>
@@ -22590,7 +22590,7 @@
         <v>1483</v>
       </c>
       <c r="E422">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F422" t="s">
         <v>1518</v>
@@ -22625,7 +22625,7 @@
         <v>1483</v>
       </c>
       <c r="E423">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F423" t="s">
         <v>1518</v>
@@ -22660,7 +22660,7 @@
         <v>1483</v>
       </c>
       <c r="E424">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F424" t="s">
         <v>1518</v>
@@ -22695,7 +22695,7 @@
         <v>1483</v>
       </c>
       <c r="E425">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F425" t="s">
         <v>1518</v>
@@ -22730,7 +22730,7 @@
         <v>1483</v>
       </c>
       <c r="E426">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F426" t="s">
         <v>1518</v>
@@ -22765,7 +22765,7 @@
         <v>1483</v>
       </c>
       <c r="E427">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F427" t="s">
         <v>1518</v>
@@ -22800,7 +22800,7 @@
         <v>1483</v>
       </c>
       <c r="E428">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F428" t="s">
         <v>1518</v>
@@ -22835,7 +22835,7 @@
         <v>1483</v>
       </c>
       <c r="E429">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F429" t="s">
         <v>1518</v>
@@ -22870,7 +22870,7 @@
         <v>1483</v>
       </c>
       <c r="E430">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F430" t="s">
         <v>1518</v>
@@ -22905,7 +22905,7 @@
         <v>1483</v>
       </c>
       <c r="E431">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F431" t="s">
         <v>1518</v>
@@ -22940,7 +22940,7 @@
         <v>1483</v>
       </c>
       <c r="E432">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F432" t="s">
         <v>1518</v>
@@ -22975,7 +22975,7 @@
         <v>1483</v>
       </c>
       <c r="E433">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F433" t="s">
         <v>1518</v>
@@ -23010,7 +23010,7 @@
         <v>1483</v>
       </c>
       <c r="E434">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F434" t="s">
         <v>1518</v>
@@ -23045,7 +23045,7 @@
         <v>1483</v>
       </c>
       <c r="E435">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F435" t="s">
         <v>1518</v>
@@ -23080,7 +23080,7 @@
         <v>1483</v>
       </c>
       <c r="E436">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F436" t="s">
         <v>1518</v>
@@ -23115,7 +23115,7 @@
         <v>1483</v>
       </c>
       <c r="E437">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F437" t="s">
         <v>1518</v>
@@ -23150,7 +23150,7 @@
         <v>1483</v>
       </c>
       <c r="E438">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F438" t="s">
         <v>1518</v>
@@ -23185,7 +23185,7 @@
         <v>1483</v>
       </c>
       <c r="E439">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F439" t="s">
         <v>1518</v>
@@ -23220,7 +23220,7 @@
         <v>1483</v>
       </c>
       <c r="E440">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F440" t="s">
         <v>1518</v>
@@ -23255,7 +23255,7 @@
         <v>1483</v>
       </c>
       <c r="E441">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F441" t="s">
         <v>1518</v>
@@ -23290,7 +23290,7 @@
         <v>1484</v>
       </c>
       <c r="E442">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F442" t="s">
         <v>1518</v>
@@ -23325,7 +23325,7 @@
         <v>1484</v>
       </c>
       <c r="E443">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F443" t="s">
         <v>1518</v>
@@ -23360,7 +23360,7 @@
         <v>1484</v>
       </c>
       <c r="E444">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F444" t="s">
         <v>1518</v>
@@ -23395,7 +23395,7 @@
         <v>1484</v>
       </c>
       <c r="E445">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F445" t="s">
         <v>1518</v>
@@ -23430,7 +23430,7 @@
         <v>1484</v>
       </c>
       <c r="E446">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F446" t="s">
         <v>1518</v>
@@ -23465,7 +23465,7 @@
         <v>1484</v>
       </c>
       <c r="E447">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F447" t="s">
         <v>1518</v>
@@ -23500,7 +23500,7 @@
         <v>1484</v>
       </c>
       <c r="E448">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F448" t="s">
         <v>1522</v>
@@ -23535,7 +23535,7 @@
         <v>1484</v>
       </c>
       <c r="E449">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F449" t="s">
         <v>1518</v>
@@ -23570,7 +23570,7 @@
         <v>1485</v>
       </c>
       <c r="E450">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F450" t="s">
         <v>1518</v>
@@ -23605,7 +23605,7 @@
         <v>1486</v>
       </c>
       <c r="E451">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F451" t="s">
         <v>1520</v>
@@ -23643,7 +23643,7 @@
         <v>1486</v>
       </c>
       <c r="E452">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F452" t="s">
         <v>1518</v>
@@ -23678,7 +23678,7 @@
         <v>1486</v>
       </c>
       <c r="E453">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F453" t="s">
         <v>1518</v>
@@ -23713,7 +23713,7 @@
         <v>1486</v>
       </c>
       <c r="E454">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F454" t="s">
         <v>1518</v>
@@ -23748,7 +23748,7 @@
         <v>1486</v>
       </c>
       <c r="E455">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F455" t="s">
         <v>1518</v>
@@ -23783,7 +23783,7 @@
         <v>1487</v>
       </c>
       <c r="E456">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F456" t="s">
         <v>1518</v>
@@ -23821,7 +23821,7 @@
         <v>1487</v>
       </c>
       <c r="E457">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F457" t="s">
         <v>1522</v>
@@ -23856,7 +23856,7 @@
         <v>1487</v>
       </c>
       <c r="E458">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F458" t="s">
         <v>1520</v>
@@ -23891,7 +23891,7 @@
         <v>1487</v>
       </c>
       <c r="E459">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F459" t="s">
         <v>1518</v>
@@ -23926,7 +23926,7 @@
         <v>1487</v>
       </c>
       <c r="E460">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F460" t="s">
         <v>1518</v>
@@ -23961,7 +23961,7 @@
         <v>1487</v>
       </c>
       <c r="E461">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F461" t="s">
         <v>1518</v>
@@ -23996,7 +23996,7 @@
         <v>1487</v>
       </c>
       <c r="E462">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F462" t="s">
         <v>1518</v>
@@ -24031,7 +24031,7 @@
         <v>1487</v>
       </c>
       <c r="E463">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F463" t="s">
         <v>1518</v>
@@ -24066,7 +24066,7 @@
         <v>1487</v>
       </c>
       <c r="E464">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F464" t="s">
         <v>1518</v>
@@ -24101,7 +24101,7 @@
         <v>1488</v>
       </c>
       <c r="E465">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F465" t="s">
         <v>1522</v>
@@ -24139,7 +24139,7 @@
         <v>1488</v>
       </c>
       <c r="E466">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F466" t="s">
         <v>1518</v>
@@ -24174,7 +24174,7 @@
         <v>1489</v>
       </c>
       <c r="E467">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F467" t="s">
         <v>1518</v>
@@ -24209,7 +24209,7 @@
         <v>1489</v>
       </c>
       <c r="E468">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F468" t="s">
         <v>1518</v>
@@ -24244,7 +24244,7 @@
         <v>1489</v>
       </c>
       <c r="E469">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F469" t="s">
         <v>1518</v>
@@ -24279,7 +24279,7 @@
         <v>1489</v>
       </c>
       <c r="E470">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F470" t="s">
         <v>1518</v>
@@ -24314,7 +24314,7 @@
         <v>1489</v>
       </c>
       <c r="E471">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F471" t="s">
         <v>1518</v>
@@ -24349,7 +24349,7 @@
         <v>1489</v>
       </c>
       <c r="E472">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F472" t="s">
         <v>1518</v>
@@ -24384,7 +24384,7 @@
         <v>1490</v>
       </c>
       <c r="E473">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F473" t="s">
         <v>1518</v>
@@ -24419,7 +24419,7 @@
         <v>1490</v>
       </c>
       <c r="E474">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F474" t="s">
         <v>1518</v>
@@ -24454,7 +24454,7 @@
         <v>1490</v>
       </c>
       <c r="E475">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F475" t="s">
         <v>1518</v>
@@ -24489,7 +24489,7 @@
         <v>1490</v>
       </c>
       <c r="E476">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F476" t="s">
         <v>1518</v>
@@ -24524,7 +24524,7 @@
         <v>1490</v>
       </c>
       <c r="E477">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F477" t="s">
         <v>1518</v>
@@ -24559,7 +24559,7 @@
         <v>1490</v>
       </c>
       <c r="E478">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F478" t="s">
         <v>1520</v>
@@ -24594,7 +24594,7 @@
         <v>1490</v>
       </c>
       <c r="E479">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F479" t="s">
         <v>1518</v>
@@ -24629,7 +24629,7 @@
         <v>1490</v>
       </c>
       <c r="E480">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F480" t="s">
         <v>1518</v>
@@ -24664,7 +24664,7 @@
         <v>1491</v>
       </c>
       <c r="E481">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F481" t="s">
         <v>1518</v>
@@ -24699,7 +24699,7 @@
         <v>1491</v>
       </c>
       <c r="E482">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F482" t="s">
         <v>1518</v>
@@ -24734,7 +24734,7 @@
         <v>1491</v>
       </c>
       <c r="E483">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F483" t="s">
         <v>1518</v>
@@ -24769,7 +24769,7 @@
         <v>1491</v>
       </c>
       <c r="E484">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F484" t="s">
         <v>1518</v>
@@ -24804,7 +24804,7 @@
         <v>1491</v>
       </c>
       <c r="E485">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F485" t="s">
         <v>1518</v>
@@ -24839,7 +24839,7 @@
         <v>1491</v>
       </c>
       <c r="E486">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F486" t="s">
         <v>1518</v>
@@ -24874,7 +24874,7 @@
         <v>1491</v>
       </c>
       <c r="E487">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F487" t="s">
         <v>1518</v>
@@ -24909,7 +24909,7 @@
         <v>1491</v>
       </c>
       <c r="E488">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F488" t="s">
         <v>1518</v>
@@ -24944,7 +24944,7 @@
         <v>1492</v>
       </c>
       <c r="E489">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F489" t="s">
         <v>1518</v>
@@ -24979,7 +24979,7 @@
         <v>1492</v>
       </c>
       <c r="E490">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F490" t="s">
         <v>1518</v>
@@ -25014,7 +25014,7 @@
         <v>1492</v>
       </c>
       <c r="E491">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F491" t="s">
         <v>1518</v>
@@ -25049,7 +25049,7 @@
         <v>1492</v>
       </c>
       <c r="E492">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F492" t="s">
         <v>1518</v>
@@ -25084,7 +25084,7 @@
         <v>1492</v>
       </c>
       <c r="E493">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F493" t="s">
         <v>1518</v>
@@ -25119,7 +25119,7 @@
         <v>1492</v>
       </c>
       <c r="E494">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F494" t="s">
         <v>1518</v>
@@ -25154,7 +25154,7 @@
         <v>1493</v>
       </c>
       <c r="E495">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F495" t="s">
         <v>1518</v>
@@ -25189,7 +25189,7 @@
         <v>1493</v>
       </c>
       <c r="E496">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F496" t="s">
         <v>1518</v>
@@ -25224,7 +25224,7 @@
         <v>1493</v>
       </c>
       <c r="E497">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F497" t="s">
         <v>1518</v>
@@ -25259,7 +25259,7 @@
         <v>1493</v>
       </c>
       <c r="E498">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F498" t="s">
         <v>1518</v>
@@ -25294,7 +25294,7 @@
         <v>1493</v>
       </c>
       <c r="E499">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F499" t="s">
         <v>1518</v>
@@ -25329,7 +25329,7 @@
         <v>1494</v>
       </c>
       <c r="E500">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F500" t="s">
         <v>1518</v>
@@ -25364,7 +25364,7 @@
         <v>1494</v>
       </c>
       <c r="E501">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F501" t="s">
         <v>1518</v>
@@ -25399,7 +25399,7 @@
         <v>1494</v>
       </c>
       <c r="E502">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F502" t="s">
         <v>1518</v>
@@ -25434,7 +25434,7 @@
         <v>1494</v>
       </c>
       <c r="E503">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F503" t="s">
         <v>1518</v>
@@ -25469,7 +25469,7 @@
         <v>1494</v>
       </c>
       <c r="E504">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F504" t="s">
         <v>1518</v>
@@ -25504,7 +25504,7 @@
         <v>1494</v>
       </c>
       <c r="E505">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F505" t="s">
         <v>1518</v>
@@ -25539,7 +25539,7 @@
         <v>1494</v>
       </c>
       <c r="E506">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F506" t="s">
         <v>1518</v>
@@ -25574,7 +25574,7 @@
         <v>1494</v>
       </c>
       <c r="E507">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F507" t="s">
         <v>1518</v>
@@ -25609,7 +25609,7 @@
         <v>1494</v>
       </c>
       <c r="E508">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F508" t="s">
         <v>1518</v>
@@ -25647,7 +25647,7 @@
         <v>1494</v>
       </c>
       <c r="E509">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F509" t="s">
         <v>1518</v>
@@ -25682,7 +25682,7 @@
         <v>1495</v>
       </c>
       <c r="E510">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F510" t="s">
         <v>1518</v>
@@ -25717,7 +25717,7 @@
         <v>1495</v>
       </c>
       <c r="E511">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F511" t="s">
         <v>1520</v>
@@ -25755,7 +25755,7 @@
         <v>1495</v>
       </c>
       <c r="E512">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F512" t="s">
         <v>1518</v>
@@ -25790,7 +25790,7 @@
         <v>1495</v>
       </c>
       <c r="E513">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F513" t="s">
         <v>1518</v>
@@ -25825,7 +25825,7 @@
         <v>1496</v>
       </c>
       <c r="E514">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F514" t="s">
         <v>1518</v>
@@ -25860,7 +25860,7 @@
         <v>1496</v>
       </c>
       <c r="E515">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F515" t="s">
         <v>1518</v>
@@ -25895,7 +25895,7 @@
         <v>1496</v>
       </c>
       <c r="E516">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F516" t="s">
         <v>1518</v>
@@ -25930,7 +25930,7 @@
         <v>1496</v>
       </c>
       <c r="E517">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F517" t="s">
         <v>1518</v>
@@ -25965,7 +25965,7 @@
         <v>1496</v>
       </c>
       <c r="E518">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F518" t="s">
         <v>1518</v>
@@ -26000,7 +26000,7 @@
         <v>1496</v>
       </c>
       <c r="E519">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F519" t="s">
         <v>1518</v>
@@ -26035,7 +26035,7 @@
         <v>1496</v>
       </c>
       <c r="E520">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F520" t="s">
         <v>1518</v>
@@ -26070,7 +26070,7 @@
         <v>1496</v>
       </c>
       <c r="E521">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F521" t="s">
         <v>1518</v>
@@ -26105,7 +26105,7 @@
         <v>1496</v>
       </c>
       <c r="E522">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F522" t="s">
         <v>1518</v>
@@ -26140,7 +26140,7 @@
         <v>1497</v>
       </c>
       <c r="E523">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F523" t="s">
         <v>1518</v>
@@ -26175,7 +26175,7 @@
         <v>1497</v>
       </c>
       <c r="E524">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F524" t="s">
         <v>1518</v>
@@ -26210,7 +26210,7 @@
         <v>1497</v>
       </c>
       <c r="E525">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F525" t="s">
         <v>1518</v>
@@ -26245,7 +26245,7 @@
         <v>1497</v>
       </c>
       <c r="E526">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F526" t="s">
         <v>1518</v>
@@ -26280,7 +26280,7 @@
         <v>1498</v>
       </c>
       <c r="E527">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F527" t="s">
         <v>1518</v>
@@ -26315,7 +26315,7 @@
         <v>1498</v>
       </c>
       <c r="E528">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F528" t="s">
         <v>1518</v>
@@ -26350,7 +26350,7 @@
         <v>1498</v>
       </c>
       <c r="E529">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F529" t="s">
         <v>1518</v>
@@ -26385,7 +26385,7 @@
         <v>1498</v>
       </c>
       <c r="E530">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F530" t="s">
         <v>1520</v>
@@ -26423,7 +26423,7 @@
         <v>1499</v>
       </c>
       <c r="E531">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F531" t="s">
         <v>1518</v>
@@ -26458,7 +26458,7 @@
         <v>1499</v>
       </c>
       <c r="E532">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F532" t="s">
         <v>1522</v>
@@ -26496,7 +26496,7 @@
         <v>1499</v>
       </c>
       <c r="E533">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F533" t="s">
         <v>1518</v>
@@ -26531,7 +26531,7 @@
         <v>1499</v>
       </c>
       <c r="E534">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F534" t="s">
         <v>1518</v>
@@ -26566,7 +26566,7 @@
         <v>1500</v>
       </c>
       <c r="E535">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F535" t="s">
         <v>1518</v>
@@ -26601,7 +26601,7 @@
         <v>1500</v>
       </c>
       <c r="E536">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F536" t="s">
         <v>1518</v>
@@ -26636,7 +26636,7 @@
         <v>1500</v>
       </c>
       <c r="E537">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F537" t="s">
         <v>1518</v>
@@ -26671,7 +26671,7 @@
         <v>1500</v>
       </c>
       <c r="E538">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F538" t="s">
         <v>1518</v>
@@ -26706,7 +26706,7 @@
         <v>1500</v>
       </c>
       <c r="E539">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F539" t="s">
         <v>1520</v>
@@ -26744,7 +26744,7 @@
         <v>1500</v>
       </c>
       <c r="E540">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F540" t="s">
         <v>1518</v>
@@ -26779,7 +26779,7 @@
         <v>1500</v>
       </c>
       <c r="E541">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F541" t="s">
         <v>1518</v>
@@ -26814,7 +26814,7 @@
         <v>1500</v>
       </c>
       <c r="E542">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F542" t="s">
         <v>1518</v>
@@ -26849,7 +26849,7 @@
         <v>1501</v>
       </c>
       <c r="E543">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F543" t="s">
         <v>1518</v>
@@ -26884,7 +26884,7 @@
         <v>1501</v>
       </c>
       <c r="E544">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F544" t="s">
         <v>1518</v>
@@ -26919,7 +26919,7 @@
         <v>1502</v>
       </c>
       <c r="E545">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F545" t="s">
         <v>1520</v>
@@ -26957,7 +26957,7 @@
         <v>1502</v>
       </c>
       <c r="E546">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F546" t="s">
         <v>1518</v>
@@ -26992,7 +26992,7 @@
         <v>1502</v>
       </c>
       <c r="E547">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F547" t="s">
         <v>1518</v>
@@ -27027,7 +27027,7 @@
         <v>1502</v>
       </c>
       <c r="E548">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F548" t="s">
         <v>1518</v>
@@ -27062,7 +27062,7 @@
         <v>1503</v>
       </c>
       <c r="E549">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F549" t="s">
         <v>1518</v>
@@ -27097,7 +27097,7 @@
         <v>1504</v>
       </c>
       <c r="E550">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F550" t="s">
         <v>1518</v>
@@ -27132,7 +27132,7 @@
         <v>1504</v>
       </c>
       <c r="E551">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F551" t="s">
         <v>1518</v>
@@ -27167,7 +27167,7 @@
         <v>1504</v>
       </c>
       <c r="E552">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F552" t="s">
         <v>1518</v>
@@ -27202,7 +27202,7 @@
         <v>1504</v>
       </c>
       <c r="E553">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F553" t="s">
         <v>1518</v>
@@ -27237,7 +27237,7 @@
         <v>1504</v>
       </c>
       <c r="E554">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F554" t="s">
         <v>1518</v>
@@ -27272,7 +27272,7 @@
         <v>1504</v>
       </c>
       <c r="E555">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F555" t="s">
         <v>1518</v>
@@ -27307,7 +27307,7 @@
         <v>1504</v>
       </c>
       <c r="E556">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F556" t="s">
         <v>1518</v>
@@ -27342,7 +27342,7 @@
         <v>1504</v>
       </c>
       <c r="E557">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F557" t="s">
         <v>1518</v>
@@ -27377,7 +27377,7 @@
         <v>1504</v>
       </c>
       <c r="E558">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F558" t="s">
         <v>1518</v>
@@ -27412,7 +27412,7 @@
         <v>1504</v>
       </c>
       <c r="E559">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F559" t="s">
         <v>1520</v>
@@ -27450,7 +27450,7 @@
         <v>1505</v>
       </c>
       <c r="E560">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F560" t="s">
         <v>1518</v>
@@ -27485,7 +27485,7 @@
         <v>1505</v>
       </c>
       <c r="E561">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F561" t="s">
         <v>1518</v>
@@ -27520,7 +27520,7 @@
         <v>1505</v>
       </c>
       <c r="E562">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F562" t="s">
         <v>1518</v>
@@ -27555,7 +27555,7 @@
         <v>1505</v>
       </c>
       <c r="E563">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F563" t="s">
         <v>1518</v>
@@ -27590,7 +27590,7 @@
         <v>1505</v>
       </c>
       <c r="E564">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F564" t="s">
         <v>1520</v>
@@ -27628,7 +27628,7 @@
         <v>1505</v>
       </c>
       <c r="E565">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F565" t="s">
         <v>1518</v>
@@ -27663,7 +27663,7 @@
         <v>1505</v>
       </c>
       <c r="E566">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F566" t="s">
         <v>1518</v>
@@ -27698,7 +27698,7 @@
         <v>1505</v>
       </c>
       <c r="E567">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F567" t="s">
         <v>1518</v>
@@ -27733,7 +27733,7 @@
         <v>1506</v>
       </c>
       <c r="E568">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F568" t="s">
         <v>1518</v>
@@ -27768,7 +27768,7 @@
         <v>1506</v>
       </c>
       <c r="E569">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F569" t="s">
         <v>1520</v>
@@ -27806,7 +27806,7 @@
         <v>1506</v>
       </c>
       <c r="E570">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F570" t="s">
         <v>1518</v>
@@ -27841,7 +27841,7 @@
         <v>1507</v>
       </c>
       <c r="E571">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F571" t="s">
         <v>1520</v>
@@ -27879,7 +27879,7 @@
         <v>1507</v>
       </c>
       <c r="E572">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F572" t="s">
         <v>1518</v>
@@ -27914,7 +27914,7 @@
         <v>1507</v>
       </c>
       <c r="E573">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F573" t="s">
         <v>1518</v>
@@ -27949,7 +27949,7 @@
         <v>1508</v>
       </c>
       <c r="E574">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F574" t="s">
         <v>1518</v>
@@ -27984,7 +27984,7 @@
         <v>1508</v>
       </c>
       <c r="E575">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F575" t="s">
         <v>1518</v>
@@ -28019,7 +28019,7 @@
         <v>1508</v>
       </c>
       <c r="E576">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F576" t="s">
         <v>1518</v>
@@ -28054,7 +28054,7 @@
         <v>1508</v>
       </c>
       <c r="E577">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F577" t="s">
         <v>1518</v>
@@ -28089,7 +28089,7 @@
         <v>1508</v>
       </c>
       <c r="E578">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F578" t="s">
         <v>1518</v>
@@ -28124,7 +28124,7 @@
         <v>1508</v>
       </c>
       <c r="E579">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F579" t="s">
         <v>1518</v>
@@ -28159,7 +28159,7 @@
         <v>1508</v>
       </c>
       <c r="E580">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F580" t="s">
         <v>1520</v>
@@ -28197,7 +28197,7 @@
         <v>1509</v>
       </c>
       <c r="E581">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F581" t="s">
         <v>1520</v>
@@ -28235,7 +28235,7 @@
         <v>1509</v>
       </c>
       <c r="E582">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F582" t="s">
         <v>1520</v>
@@ -28270,7 +28270,7 @@
         <v>1509</v>
       </c>
       <c r="E583">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F583" t="s">
         <v>1518</v>
@@ -28305,7 +28305,7 @@
         <v>1509</v>
       </c>
       <c r="E584">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F584" t="s">
         <v>1518</v>
@@ -28340,7 +28340,7 @@
         <v>1509</v>
       </c>
       <c r="E585">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F585" t="s">
         <v>1518</v>
@@ -28375,7 +28375,7 @@
         <v>1509</v>
       </c>
       <c r="E586">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F586" t="s">
         <v>1518</v>
@@ -28410,7 +28410,7 @@
         <v>1510</v>
       </c>
       <c r="E587">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F587" t="s">
         <v>1518</v>
@@ -28445,7 +28445,7 @@
         <v>1510</v>
       </c>
       <c r="E588">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F588" t="s">
         <v>1518</v>
@@ -28480,7 +28480,7 @@
         <v>1510</v>
       </c>
       <c r="E589">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F589" t="s">
         <v>1518</v>
@@ -28515,7 +28515,7 @@
         <v>1510</v>
       </c>
       <c r="E590">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F590" t="s">
         <v>1518</v>
@@ -28550,7 +28550,7 @@
         <v>1510</v>
       </c>
       <c r="E591">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F591" t="s">
         <v>1518</v>
@@ -28585,7 +28585,7 @@
         <v>1510</v>
       </c>
       <c r="E592">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F592" t="s">
         <v>1518</v>
@@ -28620,7 +28620,7 @@
         <v>1510</v>
       </c>
       <c r="E593">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F593" t="s">
         <v>1518</v>
@@ -28655,7 +28655,7 @@
         <v>1511</v>
       </c>
       <c r="E594">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F594" t="s">
         <v>1518</v>
@@ -28693,7 +28693,7 @@
         <v>1511</v>
       </c>
       <c r="E595">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F595" t="s">
         <v>1518</v>
@@ -28728,7 +28728,7 @@
         <v>1511</v>
       </c>
       <c r="E596">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F596" t="s">
         <v>1518</v>
@@ -28763,7 +28763,7 @@
         <v>1511</v>
       </c>
       <c r="E597">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F597" t="s">
         <v>1518</v>
@@ -28801,7 +28801,7 @@
         <v>1511</v>
       </c>
       <c r="E598">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F598" t="s">
         <v>1518</v>
@@ -28836,7 +28836,7 @@
         <v>1512</v>
       </c>
       <c r="E599">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F599" t="s">
         <v>1518</v>
@@ -28871,7 +28871,7 @@
         <v>1513</v>
       </c>
       <c r="E600">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F600" t="s">
         <v>1518</v>
@@ -28906,7 +28906,7 @@
         <v>1513</v>
       </c>
       <c r="E601">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F601" t="s">
         <v>1518</v>
@@ -28941,7 +28941,7 @@
         <v>1513</v>
       </c>
       <c r="E602">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F602" t="s">
         <v>1520</v>
@@ -28976,7 +28976,7 @@
         <v>1513</v>
       </c>
       <c r="E603">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F603" t="s">
         <v>1520</v>
@@ -29014,7 +29014,7 @@
         <v>1513</v>
       </c>
       <c r="E604">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F604" t="s">
         <v>1518</v>
@@ -29049,7 +29049,7 @@
         <v>1513</v>
       </c>
       <c r="E605">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F605" t="s">
         <v>1518</v>
@@ -29084,7 +29084,7 @@
         <v>1513</v>
       </c>
       <c r="E606">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F606" t="s">
         <v>1518</v>
@@ -29119,7 +29119,7 @@
         <v>1513</v>
       </c>
       <c r="E607">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F607" t="s">
         <v>1518</v>
@@ -29154,7 +29154,7 @@
         <v>1513</v>
       </c>
       <c r="E608">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F608" t="s">
         <v>1518</v>
@@ -29189,7 +29189,7 @@
         <v>1513</v>
       </c>
       <c r="E609">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F609" t="s">
         <v>1518</v>
@@ -29224,7 +29224,7 @@
         <v>1513</v>
       </c>
       <c r="E610">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F610" t="s">
         <v>1518</v>
@@ -29262,7 +29262,7 @@
         <v>1513</v>
       </c>
       <c r="E611">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F611" t="s">
         <v>1518</v>
@@ -29297,7 +29297,7 @@
         <v>1513</v>
       </c>
       <c r="E612">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F612" t="s">
         <v>1518</v>
@@ -29332,7 +29332,7 @@
         <v>1513</v>
       </c>
       <c r="E613">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F613" t="s">
         <v>1522</v>
@@ -29367,7 +29367,7 @@
         <v>1514</v>
       </c>
       <c r="E614">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F614" t="s">
         <v>1518</v>
@@ -29402,7 +29402,7 @@
         <v>1514</v>
       </c>
       <c r="E615">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F615" t="s">
         <v>1520</v>
@@ -29440,7 +29440,7 @@
         <v>1514</v>
       </c>
       <c r="E616">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F616" t="s">
         <v>1518</v>
@@ -29475,7 +29475,7 @@
         <v>1514</v>
       </c>
       <c r="E617">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F617" t="s">
         <v>1520</v>
@@ -29513,7 +29513,7 @@
         <v>1514</v>
       </c>
       <c r="E618">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F618" t="s">
         <v>1518</v>
@@ -29548,7 +29548,7 @@
         <v>1515</v>
       </c>
       <c r="E619">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F619" t="s">
         <v>1518</v>
@@ -29583,7 +29583,7 @@
         <v>1515</v>
       </c>
       <c r="E620">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F620" t="s">
         <v>1518</v>
@@ -29618,7 +29618,7 @@
         <v>1515</v>
       </c>
       <c r="E621">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F621" t="s">
         <v>1518</v>
@@ -29653,7 +29653,7 @@
         <v>1515</v>
       </c>
       <c r="E622">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F622" t="s">
         <v>1518</v>
@@ -29688,7 +29688,7 @@
         <v>1515</v>
       </c>
       <c r="E623">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F623" t="s">
         <v>1518</v>
@@ -29723,7 +29723,7 @@
         <v>1515</v>
       </c>
       <c r="E624">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F624" t="s">
         <v>1518</v>
@@ -29758,7 +29758,7 @@
         <v>1515</v>
       </c>
       <c r="E625">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F625" t="s">
         <v>1518</v>
@@ -29793,7 +29793,7 @@
         <v>1516</v>
       </c>
       <c r="E626">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F626" t="s">
         <v>1518</v>
@@ -29828,7 +29828,7 @@
         <v>1516</v>
       </c>
       <c r="E627">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F627" t="s">
         <v>1518</v>
@@ -29863,7 +29863,7 @@
         <v>1516</v>
       </c>
       <c r="E628">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F628" t="s">
         <v>1518</v>
@@ -29898,7 +29898,7 @@
         <v>1516</v>
       </c>
       <c r="E629">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F629" t="s">
         <v>1518</v>
@@ -29933,7 +29933,7 @@
         <v>1516</v>
       </c>
       <c r="E630">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F630" t="s">
         <v>1518</v>
@@ -29968,7 +29968,7 @@
         <v>1517</v>
       </c>
       <c r="E631">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F631" t="s">
         <v>1518</v>
@@ -30006,7 +30006,7 @@
         <v>1517</v>
       </c>
       <c r="E632">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F632" t="s">
         <v>1518</v>
@@ -30041,7 +30041,7 @@
         <v>1517</v>
       </c>
       <c r="E633">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F633" t="s">
         <v>1518</v>
@@ -30076,7 +30076,7 @@
         <v>1517</v>
       </c>
       <c r="E634">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F634" t="s">
         <v>1518</v>

--- a/BacklogGATEAutoCompleto.xlsx
+++ b/BacklogGATEAutoCompleto.xlsx
@@ -7863,7 +7863,7 @@
         <v>1307</v>
       </c>
       <c r="E2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="F2" t="s">
         <v>1518</v>
@@ -7898,7 +7898,7 @@
         <v>1308</v>
       </c>
       <c r="E3">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="F3" t="s">
         <v>1518</v>
@@ -7933,7 +7933,7 @@
         <v>1309</v>
       </c>
       <c r="E4">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="F4" t="s">
         <v>1518</v>
@@ -7968,7 +7968,7 @@
         <v>1310</v>
       </c>
       <c r="E5">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F5" t="s">
         <v>1518</v>
@@ -8003,7 +8003,7 @@
         <v>1311</v>
       </c>
       <c r="E6">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="F6" t="s">
         <v>1518</v>
@@ -8038,7 +8038,7 @@
         <v>1312</v>
       </c>
       <c r="E7">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="F7" t="s">
         <v>1518</v>
@@ -8073,7 +8073,7 @@
         <v>1313</v>
       </c>
       <c r="E8">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="F8" t="s">
         <v>1518</v>
@@ -8108,7 +8108,7 @@
         <v>1313</v>
       </c>
       <c r="E9">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="F9" t="s">
         <v>1518</v>
@@ -8143,7 +8143,7 @@
         <v>1314</v>
       </c>
       <c r="E10">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="F10" t="s">
         <v>1518</v>
@@ -8178,7 +8178,7 @@
         <v>1315</v>
       </c>
       <c r="E11">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="F11" t="s">
         <v>1518</v>
@@ -8213,7 +8213,7 @@
         <v>1316</v>
       </c>
       <c r="E12">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="F12" t="s">
         <v>1518</v>
@@ -8248,7 +8248,7 @@
         <v>1316</v>
       </c>
       <c r="E13">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="F13" t="s">
         <v>1518</v>
@@ -8283,7 +8283,7 @@
         <v>1317</v>
       </c>
       <c r="E14">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="F14" t="s">
         <v>1518</v>
@@ -8318,7 +8318,7 @@
         <v>1317</v>
       </c>
       <c r="E15">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="F15" t="s">
         <v>1518</v>
@@ -8353,7 +8353,7 @@
         <v>1318</v>
       </c>
       <c r="E16">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="F16" t="s">
         <v>1518</v>
@@ -8388,7 +8388,7 @@
         <v>1319</v>
       </c>
       <c r="E17">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F17" t="s">
         <v>1518</v>
@@ -8423,7 +8423,7 @@
         <v>1320</v>
       </c>
       <c r="E18">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F18" t="s">
         <v>1518</v>
@@ -8458,7 +8458,7 @@
         <v>1321</v>
       </c>
       <c r="E19">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="F19" t="s">
         <v>1518</v>
@@ -8493,7 +8493,7 @@
         <v>1322</v>
       </c>
       <c r="E20">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F20" t="s">
         <v>1518</v>
@@ -8531,7 +8531,7 @@
         <v>1323</v>
       </c>
       <c r="E21">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F21" t="s">
         <v>1518</v>
@@ -8566,7 +8566,7 @@
         <v>1324</v>
       </c>
       <c r="E22">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="F22" t="s">
         <v>1518</v>
@@ -8601,7 +8601,7 @@
         <v>1325</v>
       </c>
       <c r="E23">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F23" t="s">
         <v>1518</v>
@@ -8636,7 +8636,7 @@
         <v>1326</v>
       </c>
       <c r="E24">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="F24" t="s">
         <v>1518</v>
@@ -8671,7 +8671,7 @@
         <v>1327</v>
       </c>
       <c r="E25">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F25" t="s">
         <v>1518</v>
@@ -8706,7 +8706,7 @@
         <v>1328</v>
       </c>
       <c r="E26">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F26" t="s">
         <v>1518</v>
@@ -8741,7 +8741,7 @@
         <v>1329</v>
       </c>
       <c r="E27">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F27" t="s">
         <v>1518</v>
@@ -8776,7 +8776,7 @@
         <v>1330</v>
       </c>
       <c r="E28">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F28" t="s">
         <v>1518</v>
@@ -8811,7 +8811,7 @@
         <v>1331</v>
       </c>
       <c r="E29">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F29" t="s">
         <v>1518</v>
@@ -8846,7 +8846,7 @@
         <v>1332</v>
       </c>
       <c r="E30">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F30" t="s">
         <v>1518</v>
@@ -8881,7 +8881,7 @@
         <v>1333</v>
       </c>
       <c r="E31">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F31" t="s">
         <v>1518</v>
@@ -8916,7 +8916,7 @@
         <v>1334</v>
       </c>
       <c r="E32">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F32" t="s">
         <v>1518</v>
@@ -8951,7 +8951,7 @@
         <v>1334</v>
       </c>
       <c r="E33">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F33" t="s">
         <v>1518</v>
@@ -8986,7 +8986,7 @@
         <v>1335</v>
       </c>
       <c r="E34">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F34" t="s">
         <v>1518</v>
@@ -9021,7 +9021,7 @@
         <v>1336</v>
       </c>
       <c r="E35">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F35" t="s">
         <v>1518</v>
@@ -9056,7 +9056,7 @@
         <v>1336</v>
       </c>
       <c r="E36">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F36" t="s">
         <v>1518</v>
@@ -9091,7 +9091,7 @@
         <v>1337</v>
       </c>
       <c r="E37">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F37" t="s">
         <v>1518</v>
@@ -9126,7 +9126,7 @@
         <v>1337</v>
       </c>
       <c r="E38">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F38" t="s">
         <v>1518</v>
@@ -9161,7 +9161,7 @@
         <v>1338</v>
       </c>
       <c r="E39">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F39" t="s">
         <v>1518</v>
@@ -9196,7 +9196,7 @@
         <v>1339</v>
       </c>
       <c r="E40">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F40" t="s">
         <v>1518</v>
@@ -9231,7 +9231,7 @@
         <v>1340</v>
       </c>
       <c r="E41">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F41" t="s">
         <v>1518</v>
@@ -9266,7 +9266,7 @@
         <v>1341</v>
       </c>
       <c r="E42">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F42" t="s">
         <v>1518</v>
@@ -9301,7 +9301,7 @@
         <v>1342</v>
       </c>
       <c r="E43">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F43" t="s">
         <v>1518</v>
@@ -9336,7 +9336,7 @@
         <v>1343</v>
       </c>
       <c r="E44">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F44" t="s">
         <v>1518</v>
@@ -9371,7 +9371,7 @@
         <v>1344</v>
       </c>
       <c r="E45">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F45" t="s">
         <v>1518</v>
@@ -9406,7 +9406,7 @@
         <v>1345</v>
       </c>
       <c r="E46">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F46" t="s">
         <v>1518</v>
@@ -9441,7 +9441,7 @@
         <v>1346</v>
       </c>
       <c r="E47">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F47" t="s">
         <v>1518</v>
@@ -9476,7 +9476,7 @@
         <v>1347</v>
       </c>
       <c r="E48">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F48" t="s">
         <v>1518</v>
@@ -9511,7 +9511,7 @@
         <v>1348</v>
       </c>
       <c r="E49">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F49" t="s">
         <v>1518</v>
@@ -9546,7 +9546,7 @@
         <v>1348</v>
       </c>
       <c r="E50">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F50" t="s">
         <v>1518</v>
@@ -9581,7 +9581,7 @@
         <v>1348</v>
       </c>
       <c r="E51">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F51" t="s">
         <v>1518</v>
@@ -9616,7 +9616,7 @@
         <v>1349</v>
       </c>
       <c r="E52">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F52" t="s">
         <v>1518</v>
@@ -9651,7 +9651,7 @@
         <v>1350</v>
       </c>
       <c r="E53">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F53" t="s">
         <v>1518</v>
@@ -9686,7 +9686,7 @@
         <v>1351</v>
       </c>
       <c r="E54">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F54" t="s">
         <v>1518</v>
@@ -9721,7 +9721,7 @@
         <v>1352</v>
       </c>
       <c r="E55">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F55" t="s">
         <v>1518</v>
@@ -9756,7 +9756,7 @@
         <v>1353</v>
       </c>
       <c r="E56">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F56" t="s">
         <v>1518</v>
@@ -9791,7 +9791,7 @@
         <v>1353</v>
       </c>
       <c r="E57">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F57" t="s">
         <v>1518</v>
@@ -9826,7 +9826,7 @@
         <v>1354</v>
       </c>
       <c r="E58">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F58" t="s">
         <v>1518</v>
@@ -9861,7 +9861,7 @@
         <v>1355</v>
       </c>
       <c r="E59">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F59" t="s">
         <v>1518</v>
@@ -9896,7 +9896,7 @@
         <v>1355</v>
       </c>
       <c r="E60">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F60" t="s">
         <v>1518</v>
@@ -9931,7 +9931,7 @@
         <v>1355</v>
       </c>
       <c r="E61">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F61" t="s">
         <v>1519</v>
@@ -9966,7 +9966,7 @@
         <v>1355</v>
       </c>
       <c r="E62">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F62" t="s">
         <v>1518</v>
@@ -10001,7 +10001,7 @@
         <v>1356</v>
       </c>
       <c r="E63">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F63" t="s">
         <v>1518</v>
@@ -10036,7 +10036,7 @@
         <v>1357</v>
       </c>
       <c r="E64">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F64" t="s">
         <v>1518</v>
@@ -10071,7 +10071,7 @@
         <v>1357</v>
       </c>
       <c r="E65">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F65" t="s">
         <v>1518</v>
@@ -10106,7 +10106,7 @@
         <v>1358</v>
       </c>
       <c r="E66">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F66" t="s">
         <v>1518</v>
@@ -10141,7 +10141,7 @@
         <v>1359</v>
       </c>
       <c r="E67">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F67" t="s">
         <v>1518</v>
@@ -10176,7 +10176,7 @@
         <v>1360</v>
       </c>
       <c r="E68">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F68" t="s">
         <v>1518</v>
@@ -10211,7 +10211,7 @@
         <v>1361</v>
       </c>
       <c r="E69">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F69" t="s">
         <v>1518</v>
@@ -10246,7 +10246,7 @@
         <v>1361</v>
       </c>
       <c r="E70">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F70" t="s">
         <v>1518</v>
@@ -10281,7 +10281,7 @@
         <v>1361</v>
       </c>
       <c r="E71">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F71" t="s">
         <v>1518</v>
@@ -10316,7 +10316,7 @@
         <v>1361</v>
       </c>
       <c r="E72">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F72" t="s">
         <v>1518</v>
@@ -10351,7 +10351,7 @@
         <v>1361</v>
       </c>
       <c r="E73">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F73" t="s">
         <v>1518</v>
@@ -10386,7 +10386,7 @@
         <v>1361</v>
       </c>
       <c r="E74">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F74" t="s">
         <v>1518</v>
@@ -10421,7 +10421,7 @@
         <v>1362</v>
       </c>
       <c r="E75">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F75" t="s">
         <v>1518</v>
@@ -10456,7 +10456,7 @@
         <v>1363</v>
       </c>
       <c r="E76">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F76" t="s">
         <v>1518</v>
@@ -10491,7 +10491,7 @@
         <v>1364</v>
       </c>
       <c r="E77">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F77" t="s">
         <v>1518</v>
@@ -10526,7 +10526,7 @@
         <v>1364</v>
       </c>
       <c r="E78">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F78" t="s">
         <v>1518</v>
@@ -10561,7 +10561,7 @@
         <v>1365</v>
       </c>
       <c r="E79">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F79" t="s">
         <v>1520</v>
@@ -10596,7 +10596,7 @@
         <v>1366</v>
       </c>
       <c r="E80">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F80" t="s">
         <v>1518</v>
@@ -10631,7 +10631,7 @@
         <v>1367</v>
       </c>
       <c r="E81">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F81" t="s">
         <v>1518</v>
@@ -10666,7 +10666,7 @@
         <v>1368</v>
       </c>
       <c r="E82">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F82" t="s">
         <v>1518</v>
@@ -10701,7 +10701,7 @@
         <v>1369</v>
       </c>
       <c r="E83">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F83" t="s">
         <v>1518</v>
@@ -10736,7 +10736,7 @@
         <v>1370</v>
       </c>
       <c r="E84">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F84" t="s">
         <v>1518</v>
@@ -10771,7 +10771,7 @@
         <v>1371</v>
       </c>
       <c r="E85">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F85" t="s">
         <v>1518</v>
@@ -10806,7 +10806,7 @@
         <v>1372</v>
       </c>
       <c r="E86">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F86" t="s">
         <v>1518</v>
@@ -10841,7 +10841,7 @@
         <v>1372</v>
       </c>
       <c r="E87">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F87" t="s">
         <v>1518</v>
@@ -10876,7 +10876,7 @@
         <v>1373</v>
       </c>
       <c r="E88">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F88" t="s">
         <v>1518</v>
@@ -10911,7 +10911,7 @@
         <v>1373</v>
       </c>
       <c r="E89">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F89" t="s">
         <v>1518</v>
@@ -10946,7 +10946,7 @@
         <v>1373</v>
       </c>
       <c r="E90">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F90" t="s">
         <v>1518</v>
@@ -10981,7 +10981,7 @@
         <v>1374</v>
       </c>
       <c r="E91">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F91" t="s">
         <v>1518</v>
@@ -11016,7 +11016,7 @@
         <v>1374</v>
       </c>
       <c r="E92">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F92" t="s">
         <v>1518</v>
@@ -11051,7 +11051,7 @@
         <v>1375</v>
       </c>
       <c r="E93">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F93" t="s">
         <v>1518</v>
@@ -11086,7 +11086,7 @@
         <v>1376</v>
       </c>
       <c r="E94">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F94" t="s">
         <v>1518</v>
@@ -11121,7 +11121,7 @@
         <v>1377</v>
       </c>
       <c r="E95">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F95" t="s">
         <v>1518</v>
@@ -11156,7 +11156,7 @@
         <v>1377</v>
       </c>
       <c r="E96">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F96" t="s">
         <v>1518</v>
@@ -11191,7 +11191,7 @@
         <v>1378</v>
       </c>
       <c r="E97">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F97" t="s">
         <v>1518</v>
@@ -11226,7 +11226,7 @@
         <v>1378</v>
       </c>
       <c r="E98">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F98" t="s">
         <v>1518</v>
@@ -11261,7 +11261,7 @@
         <v>1379</v>
       </c>
       <c r="E99">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F99" t="s">
         <v>1518</v>
@@ -11296,7 +11296,7 @@
         <v>1380</v>
       </c>
       <c r="E100">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F100" t="s">
         <v>1518</v>
@@ -11331,7 +11331,7 @@
         <v>1380</v>
       </c>
       <c r="E101">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F101" t="s">
         <v>1518</v>
@@ -11366,7 +11366,7 @@
         <v>1381</v>
       </c>
       <c r="E102">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F102" t="s">
         <v>1518</v>
@@ -11401,7 +11401,7 @@
         <v>1382</v>
       </c>
       <c r="E103">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F103" t="s">
         <v>1518</v>
@@ -11436,7 +11436,7 @@
         <v>1382</v>
       </c>
       <c r="E104">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F104" t="s">
         <v>1518</v>
@@ -11471,7 +11471,7 @@
         <v>1383</v>
       </c>
       <c r="E105">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F105" t="s">
         <v>1518</v>
@@ -11506,7 +11506,7 @@
         <v>1384</v>
       </c>
       <c r="E106">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F106" t="s">
         <v>1518</v>
@@ -11544,7 +11544,7 @@
         <v>1384</v>
       </c>
       <c r="E107">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F107" t="s">
         <v>1518</v>
@@ -11579,7 +11579,7 @@
         <v>1384</v>
       </c>
       <c r="E108">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F108" t="s">
         <v>1518</v>
@@ -11614,7 +11614,7 @@
         <v>1384</v>
       </c>
       <c r="E109">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F109" t="s">
         <v>1518</v>
@@ -11649,7 +11649,7 @@
         <v>1385</v>
       </c>
       <c r="E110">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F110" t="s">
         <v>1519</v>
@@ -11684,7 +11684,7 @@
         <v>1386</v>
       </c>
       <c r="E111">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F111" t="s">
         <v>1518</v>
@@ -11719,7 +11719,7 @@
         <v>1386</v>
       </c>
       <c r="E112">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F112" t="s">
         <v>1518</v>
@@ -11754,7 +11754,7 @@
         <v>1386</v>
       </c>
       <c r="E113">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F113" t="s">
         <v>1518</v>
@@ -11789,7 +11789,7 @@
         <v>1386</v>
       </c>
       <c r="E114">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F114" t="s">
         <v>1518</v>
@@ -11824,7 +11824,7 @@
         <v>1387</v>
       </c>
       <c r="E115">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F115" t="s">
         <v>1518</v>
@@ -11859,7 +11859,7 @@
         <v>1387</v>
       </c>
       <c r="E116">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F116" t="s">
         <v>1518</v>
@@ -11894,7 +11894,7 @@
         <v>1387</v>
       </c>
       <c r="E117">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F117" t="s">
         <v>1518</v>
@@ -11929,7 +11929,7 @@
         <v>1387</v>
       </c>
       <c r="E118">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F118" t="s">
         <v>1518</v>
@@ -11964,7 +11964,7 @@
         <v>1387</v>
       </c>
       <c r="E119">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F119" t="s">
         <v>1518</v>
@@ -11999,7 +11999,7 @@
         <v>1387</v>
       </c>
       <c r="E120">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F120" t="s">
         <v>1518</v>
@@ -12034,7 +12034,7 @@
         <v>1387</v>
       </c>
       <c r="E121">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F121" t="s">
         <v>1518</v>
@@ -12069,7 +12069,7 @@
         <v>1388</v>
       </c>
       <c r="E122">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F122" t="s">
         <v>1518</v>
@@ -12104,7 +12104,7 @@
         <v>1389</v>
       </c>
       <c r="E123">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F123" t="s">
         <v>1518</v>
@@ -12139,7 +12139,7 @@
         <v>1390</v>
       </c>
       <c r="E124">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F124" t="s">
         <v>1518</v>
@@ -12174,7 +12174,7 @@
         <v>1390</v>
       </c>
       <c r="E125">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F125" t="s">
         <v>1518</v>
@@ -12209,7 +12209,7 @@
         <v>1390</v>
       </c>
       <c r="E126">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F126" t="s">
         <v>1518</v>
@@ -12244,7 +12244,7 @@
         <v>1391</v>
       </c>
       <c r="E127">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F127" t="s">
         <v>1518</v>
@@ -12279,7 +12279,7 @@
         <v>1391</v>
       </c>
       <c r="E128">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F128" t="s">
         <v>1518</v>
@@ -12314,7 +12314,7 @@
         <v>1391</v>
       </c>
       <c r="E129">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F129" t="s">
         <v>1518</v>
@@ -12349,7 +12349,7 @@
         <v>1391</v>
       </c>
       <c r="E130">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F130" t="s">
         <v>1518</v>
@@ -12384,7 +12384,7 @@
         <v>1391</v>
       </c>
       <c r="E131">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F131" t="s">
         <v>1518</v>
@@ -12419,7 +12419,7 @@
         <v>1391</v>
       </c>
       <c r="E132">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F132" t="s">
         <v>1518</v>
@@ -12454,7 +12454,7 @@
         <v>1391</v>
       </c>
       <c r="E133">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F133" t="s">
         <v>1518</v>
@@ -12489,7 +12489,7 @@
         <v>1391</v>
       </c>
       <c r="E134">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F134" t="s">
         <v>1518</v>
@@ -12524,7 +12524,7 @@
         <v>1391</v>
       </c>
       <c r="E135">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F135" t="s">
         <v>1518</v>
@@ -12559,7 +12559,7 @@
         <v>1392</v>
       </c>
       <c r="E136">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F136" t="s">
         <v>1518</v>
@@ -12594,7 +12594,7 @@
         <v>1392</v>
       </c>
       <c r="E137">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F137" t="s">
         <v>1518</v>
@@ -12629,7 +12629,7 @@
         <v>1392</v>
       </c>
       <c r="E138">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F138" t="s">
         <v>1518</v>
@@ -12664,7 +12664,7 @@
         <v>1393</v>
       </c>
       <c r="E139">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F139" t="s">
         <v>1518</v>
@@ -12699,7 +12699,7 @@
         <v>1393</v>
       </c>
       <c r="E140">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F140" t="s">
         <v>1519</v>
@@ -12734,7 +12734,7 @@
         <v>1393</v>
       </c>
       <c r="E141">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F141" t="s">
         <v>1518</v>
@@ -12769,7 +12769,7 @@
         <v>1394</v>
       </c>
       <c r="E142">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F142" t="s">
         <v>1518</v>
@@ -12804,7 +12804,7 @@
         <v>1394</v>
       </c>
       <c r="E143">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F143" t="s">
         <v>1518</v>
@@ -12839,7 +12839,7 @@
         <v>1395</v>
       </c>
       <c r="E144">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F144" t="s">
         <v>1518</v>
@@ -12874,7 +12874,7 @@
         <v>1395</v>
       </c>
       <c r="E145">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F145" t="s">
         <v>1518</v>
@@ -12909,7 +12909,7 @@
         <v>1396</v>
       </c>
       <c r="E146">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F146" t="s">
         <v>1518</v>
@@ -12944,7 +12944,7 @@
         <v>1396</v>
       </c>
       <c r="E147">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F147" t="s">
         <v>1518</v>
@@ -12979,7 +12979,7 @@
         <v>1397</v>
       </c>
       <c r="E148">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F148" t="s">
         <v>1518</v>
@@ -13014,7 +13014,7 @@
         <v>1397</v>
       </c>
       <c r="E149">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F149" t="s">
         <v>1518</v>
@@ -13049,7 +13049,7 @@
         <v>1397</v>
       </c>
       <c r="E150">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F150" t="s">
         <v>1518</v>
@@ -13084,7 +13084,7 @@
         <v>1398</v>
       </c>
       <c r="E151">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F151" t="s">
         <v>1518</v>
@@ -13119,7 +13119,7 @@
         <v>1398</v>
       </c>
       <c r="E152">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F152" t="s">
         <v>1518</v>
@@ -13154,7 +13154,7 @@
         <v>1399</v>
       </c>
       <c r="E153">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F153" t="s">
         <v>1518</v>
@@ -13189,7 +13189,7 @@
         <v>1400</v>
       </c>
       <c r="E154">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F154" t="s">
         <v>1518</v>
@@ -13224,7 +13224,7 @@
         <v>1400</v>
       </c>
       <c r="E155">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F155" t="s">
         <v>1518</v>
@@ -13259,7 +13259,7 @@
         <v>1400</v>
       </c>
       <c r="E156">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F156" t="s">
         <v>1518</v>
@@ -13294,7 +13294,7 @@
         <v>1400</v>
       </c>
       <c r="E157">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F157" t="s">
         <v>1518</v>
@@ -13329,7 +13329,7 @@
         <v>1401</v>
       </c>
       <c r="E158">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F158" t="s">
         <v>1518</v>
@@ -13364,7 +13364,7 @@
         <v>1402</v>
       </c>
       <c r="E159">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F159" t="s">
         <v>1518</v>
@@ -13399,7 +13399,7 @@
         <v>1402</v>
       </c>
       <c r="E160">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F160" t="s">
         <v>1518</v>
@@ -13434,7 +13434,7 @@
         <v>1402</v>
       </c>
       <c r="E161">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F161" t="s">
         <v>1518</v>
@@ -13469,7 +13469,7 @@
         <v>1402</v>
       </c>
       <c r="E162">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F162" t="s">
         <v>1518</v>
@@ -13504,7 +13504,7 @@
         <v>1402</v>
       </c>
       <c r="E163">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F163" t="s">
         <v>1518</v>
@@ -13539,7 +13539,7 @@
         <v>1403</v>
       </c>
       <c r="E164">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F164" t="s">
         <v>1518</v>
@@ -13574,7 +13574,7 @@
         <v>1403</v>
       </c>
       <c r="E165">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F165" t="s">
         <v>1518</v>
@@ -13609,7 +13609,7 @@
         <v>1403</v>
       </c>
       <c r="E166">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F166" t="s">
         <v>1518</v>
@@ -13644,7 +13644,7 @@
         <v>1403</v>
       </c>
       <c r="E167">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F167" t="s">
         <v>1518</v>
@@ -13679,7 +13679,7 @@
         <v>1403</v>
       </c>
       <c r="E168">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F168" t="s">
         <v>1518</v>
@@ -13714,7 +13714,7 @@
         <v>1403</v>
       </c>
       <c r="E169">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F169" t="s">
         <v>1518</v>
@@ -13749,7 +13749,7 @@
         <v>1404</v>
       </c>
       <c r="E170">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F170" t="s">
         <v>1518</v>
@@ -13784,7 +13784,7 @@
         <v>1404</v>
       </c>
       <c r="E171">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F171" t="s">
         <v>1518</v>
@@ -13819,7 +13819,7 @@
         <v>1404</v>
       </c>
       <c r="E172">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F172" t="s">
         <v>1518</v>
@@ -13854,7 +13854,7 @@
         <v>1405</v>
       </c>
       <c r="E173">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F173" t="s">
         <v>1518</v>
@@ -13889,7 +13889,7 @@
         <v>1405</v>
       </c>
       <c r="E174">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F174" t="s">
         <v>1518</v>
@@ -13924,7 +13924,7 @@
         <v>1406</v>
       </c>
       <c r="E175">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F175" t="s">
         <v>1518</v>
@@ -13959,7 +13959,7 @@
         <v>1407</v>
       </c>
       <c r="E176">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F176" t="s">
         <v>1518</v>
@@ -13994,7 +13994,7 @@
         <v>1407</v>
       </c>
       <c r="E177">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F177" t="s">
         <v>1518</v>
@@ -14029,7 +14029,7 @@
         <v>1408</v>
       </c>
       <c r="E178">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F178" t="s">
         <v>1518</v>
@@ -14064,7 +14064,7 @@
         <v>1409</v>
       </c>
       <c r="E179">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F179" t="s">
         <v>1518</v>
@@ -14099,7 +14099,7 @@
         <v>1409</v>
       </c>
       <c r="E180">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F180" t="s">
         <v>1518</v>
@@ -14134,7 +14134,7 @@
         <v>1410</v>
       </c>
       <c r="E181">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F181" t="s">
         <v>1518</v>
@@ -14169,7 +14169,7 @@
         <v>1410</v>
       </c>
       <c r="E182">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F182" t="s">
         <v>1518</v>
@@ -14204,7 +14204,7 @@
         <v>1411</v>
       </c>
       <c r="E183">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F183" t="s">
         <v>1518</v>
@@ -14239,7 +14239,7 @@
         <v>1411</v>
       </c>
       <c r="E184">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F184" t="s">
         <v>1518</v>
@@ -14274,7 +14274,7 @@
         <v>1411</v>
       </c>
       <c r="E185">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F185" t="s">
         <v>1518</v>
@@ -14309,7 +14309,7 @@
         <v>1412</v>
       </c>
       <c r="E186">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F186" t="s">
         <v>1518</v>
@@ -14344,7 +14344,7 @@
         <v>1412</v>
       </c>
       <c r="E187">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F187" t="s">
         <v>1518</v>
@@ -14379,7 +14379,7 @@
         <v>1413</v>
       </c>
       <c r="E188">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F188" t="s">
         <v>1518</v>
@@ -14414,7 +14414,7 @@
         <v>1414</v>
       </c>
       <c r="E189">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F189" t="s">
         <v>1518</v>
@@ -14449,7 +14449,7 @@
         <v>1414</v>
       </c>
       <c r="E190">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F190" t="s">
         <v>1518</v>
@@ -14484,7 +14484,7 @@
         <v>1414</v>
       </c>
       <c r="E191">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F191" t="s">
         <v>1518</v>
@@ -14519,7 +14519,7 @@
         <v>1415</v>
       </c>
       <c r="E192">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F192" t="s">
         <v>1518</v>
@@ -14554,7 +14554,7 @@
         <v>1415</v>
       </c>
       <c r="E193">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F193" t="s">
         <v>1518</v>
@@ -14589,7 +14589,7 @@
         <v>1416</v>
       </c>
       <c r="E194">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F194" t="s">
         <v>1518</v>
@@ -14624,7 +14624,7 @@
         <v>1416</v>
       </c>
       <c r="E195">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F195" t="s">
         <v>1520</v>
@@ -14659,7 +14659,7 @@
         <v>1416</v>
       </c>
       <c r="E196">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F196" t="s">
         <v>1518</v>
@@ -14694,7 +14694,7 @@
         <v>1417</v>
       </c>
       <c r="E197">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F197" t="s">
         <v>1518</v>
@@ -14729,7 +14729,7 @@
         <v>1417</v>
       </c>
       <c r="E198">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F198" t="s">
         <v>1518</v>
@@ -14767,7 +14767,7 @@
         <v>1417</v>
       </c>
       <c r="E199">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F199" t="s">
         <v>1518</v>
@@ -14802,7 +14802,7 @@
         <v>1417</v>
       </c>
       <c r="E200">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F200" t="s">
         <v>1518</v>
@@ -14837,7 +14837,7 @@
         <v>1417</v>
       </c>
       <c r="E201">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F201" t="s">
         <v>1518</v>
@@ -14872,7 +14872,7 @@
         <v>1417</v>
       </c>
       <c r="E202">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F202" t="s">
         <v>1518</v>
@@ -14907,7 +14907,7 @@
         <v>1418</v>
       </c>
       <c r="E203">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F203" t="s">
         <v>1518</v>
@@ -14942,7 +14942,7 @@
         <v>1418</v>
       </c>
       <c r="E204">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F204" t="s">
         <v>1518</v>
@@ -14977,7 +14977,7 @@
         <v>1418</v>
       </c>
       <c r="E205">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F205" t="s">
         <v>1518</v>
@@ -15012,7 +15012,7 @@
         <v>1419</v>
       </c>
       <c r="E206">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F206" t="s">
         <v>1518</v>
@@ -15047,7 +15047,7 @@
         <v>1419</v>
       </c>
       <c r="E207">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F207" t="s">
         <v>1518</v>
@@ -15082,7 +15082,7 @@
         <v>1419</v>
       </c>
       <c r="E208">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F208" t="s">
         <v>1518</v>
@@ -15117,7 +15117,7 @@
         <v>1420</v>
       </c>
       <c r="E209">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F209" t="s">
         <v>1518</v>
@@ -15152,7 +15152,7 @@
         <v>1420</v>
       </c>
       <c r="E210">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F210" t="s">
         <v>1518</v>
@@ -15187,7 +15187,7 @@
         <v>1420</v>
       </c>
       <c r="E211">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F211" t="s">
         <v>1518</v>
@@ -15222,7 +15222,7 @@
         <v>1421</v>
       </c>
       <c r="E212">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F212" t="s">
         <v>1518</v>
@@ -15257,7 +15257,7 @@
         <v>1421</v>
       </c>
       <c r="E213">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F213" t="s">
         <v>1518</v>
@@ -15292,7 +15292,7 @@
         <v>1421</v>
       </c>
       <c r="E214">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F214" t="s">
         <v>1518</v>
@@ -15327,7 +15327,7 @@
         <v>1421</v>
       </c>
       <c r="E215">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F215" t="s">
         <v>1518</v>
@@ -15362,7 +15362,7 @@
         <v>1421</v>
       </c>
       <c r="E216">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F216" t="s">
         <v>1518</v>
@@ -15397,7 +15397,7 @@
         <v>1422</v>
       </c>
       <c r="E217">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F217" t="s">
         <v>1518</v>
@@ -15432,7 +15432,7 @@
         <v>1423</v>
       </c>
       <c r="E218">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F218" t="s">
         <v>1518</v>
@@ -15467,7 +15467,7 @@
         <v>1423</v>
       </c>
       <c r="E219">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F219" t="s">
         <v>1521</v>
@@ -15502,7 +15502,7 @@
         <v>1423</v>
       </c>
       <c r="E220">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F220" t="s">
         <v>1518</v>
@@ -15537,7 +15537,7 @@
         <v>1423</v>
       </c>
       <c r="E221">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F221" t="s">
         <v>1518</v>
@@ -15572,7 +15572,7 @@
         <v>1423</v>
       </c>
       <c r="E222">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F222" t="s">
         <v>1518</v>
@@ -15607,7 +15607,7 @@
         <v>1424</v>
       </c>
       <c r="E223">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F223" t="s">
         <v>1518</v>
@@ -15642,7 +15642,7 @@
         <v>1424</v>
       </c>
       <c r="E224">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F224" t="s">
         <v>1518</v>
@@ -15677,7 +15677,7 @@
         <v>1424</v>
       </c>
       <c r="E225">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F225" t="s">
         <v>1518</v>
@@ -15712,7 +15712,7 @@
         <v>1424</v>
       </c>
       <c r="E226">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F226" t="s">
         <v>1518</v>
@@ -15747,7 +15747,7 @@
         <v>1425</v>
       </c>
       <c r="E227">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F227" t="s">
         <v>1518</v>
@@ -15782,7 +15782,7 @@
         <v>1426</v>
       </c>
       <c r="E228">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F228" t="s">
         <v>1518</v>
@@ -15820,7 +15820,7 @@
         <v>1427</v>
       </c>
       <c r="E229">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F229" t="s">
         <v>1518</v>
@@ -15855,7 +15855,7 @@
         <v>1427</v>
       </c>
       <c r="E230">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F230" t="s">
         <v>1518</v>
@@ -15890,7 +15890,7 @@
         <v>1427</v>
       </c>
       <c r="E231">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F231" t="s">
         <v>1518</v>
@@ -15925,7 +15925,7 @@
         <v>1427</v>
       </c>
       <c r="E232">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F232" t="s">
         <v>1518</v>
@@ -15960,7 +15960,7 @@
         <v>1428</v>
       </c>
       <c r="E233">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F233" t="s">
         <v>1518</v>
@@ -15995,7 +15995,7 @@
         <v>1428</v>
       </c>
       <c r="E234">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F234" t="s">
         <v>1518</v>
@@ -16030,7 +16030,7 @@
         <v>1429</v>
       </c>
       <c r="E235">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F235" t="s">
         <v>1518</v>
@@ -16065,7 +16065,7 @@
         <v>1429</v>
       </c>
       <c r="E236">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F236" t="s">
         <v>1518</v>
@@ -16100,7 +16100,7 @@
         <v>1430</v>
       </c>
       <c r="E237">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F237" t="s">
         <v>1518</v>
@@ -16135,7 +16135,7 @@
         <v>1430</v>
       </c>
       <c r="E238">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F238" t="s">
         <v>1518</v>
@@ -16170,7 +16170,7 @@
         <v>1430</v>
       </c>
       <c r="E239">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F239" t="s">
         <v>1518</v>
@@ -16205,7 +16205,7 @@
         <v>1431</v>
       </c>
       <c r="E240">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F240" t="s">
         <v>1518</v>
@@ -16240,7 +16240,7 @@
         <v>1431</v>
       </c>
       <c r="E241">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F241" t="s">
         <v>1518</v>
@@ -16275,7 +16275,7 @@
         <v>1431</v>
       </c>
       <c r="E242">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F242" t="s">
         <v>1518</v>
@@ -16310,7 +16310,7 @@
         <v>1432</v>
       </c>
       <c r="E243">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F243" t="s">
         <v>1518</v>
@@ -16345,7 +16345,7 @@
         <v>1433</v>
       </c>
       <c r="E244">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F244" t="s">
         <v>1518</v>
@@ -16380,7 +16380,7 @@
         <v>1433</v>
       </c>
       <c r="E245">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F245" t="s">
         <v>1518</v>
@@ -16415,7 +16415,7 @@
         <v>1433</v>
       </c>
       <c r="E246">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F246" t="s">
         <v>1518</v>
@@ -16450,7 +16450,7 @@
         <v>1433</v>
       </c>
       <c r="E247">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F247" t="s">
         <v>1518</v>
@@ -16485,7 +16485,7 @@
         <v>1434</v>
       </c>
       <c r="E248">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F248" t="s">
         <v>1518</v>
@@ -16520,7 +16520,7 @@
         <v>1434</v>
       </c>
       <c r="E249">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F249" t="s">
         <v>1518</v>
@@ -16555,7 +16555,7 @@
         <v>1434</v>
       </c>
       <c r="E250">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F250" t="s">
         <v>1518</v>
@@ -16590,7 +16590,7 @@
         <v>1435</v>
       </c>
       <c r="E251">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F251" t="s">
         <v>1518</v>
@@ -16625,7 +16625,7 @@
         <v>1435</v>
       </c>
       <c r="E252">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F252" t="s">
         <v>1518</v>
@@ -16660,7 +16660,7 @@
         <v>1436</v>
       </c>
       <c r="E253">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F253" t="s">
         <v>1518</v>
@@ -16695,7 +16695,7 @@
         <v>1436</v>
       </c>
       <c r="E254">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F254" t="s">
         <v>1518</v>
@@ -16730,7 +16730,7 @@
         <v>1436</v>
       </c>
       <c r="E255">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F255" t="s">
         <v>1518</v>
@@ -16765,7 +16765,7 @@
         <v>1436</v>
       </c>
       <c r="E256">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F256" t="s">
         <v>1518</v>
@@ -16800,7 +16800,7 @@
         <v>1436</v>
       </c>
       <c r="E257">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F257" t="s">
         <v>1518</v>
@@ -16835,7 +16835,7 @@
         <v>1437</v>
       </c>
       <c r="E258">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F258" t="s">
         <v>1518</v>
@@ -16870,7 +16870,7 @@
         <v>1437</v>
       </c>
       <c r="E259">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F259" t="s">
         <v>1518</v>
@@ -16905,7 +16905,7 @@
         <v>1437</v>
       </c>
       <c r="E260">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F260" t="s">
         <v>1518</v>
@@ -16940,7 +16940,7 @@
         <v>1438</v>
       </c>
       <c r="E261">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F261" t="s">
         <v>1518</v>
@@ -16975,7 +16975,7 @@
         <v>1439</v>
       </c>
       <c r="E262">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F262" t="s">
         <v>1518</v>
@@ -17010,7 +17010,7 @@
         <v>1440</v>
       </c>
       <c r="E263">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F263" t="s">
         <v>1518</v>
@@ -17045,7 +17045,7 @@
         <v>1440</v>
       </c>
       <c r="E264">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F264" t="s">
         <v>1518</v>
@@ -17080,7 +17080,7 @@
         <v>1440</v>
       </c>
       <c r="E265">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F265" t="s">
         <v>1518</v>
@@ -17115,7 +17115,7 @@
         <v>1440</v>
       </c>
       <c r="E266">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F266" t="s">
         <v>1518</v>
@@ -17150,7 +17150,7 @@
         <v>1440</v>
       </c>
       <c r="E267">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F267" t="s">
         <v>1518</v>
@@ -17185,7 +17185,7 @@
         <v>1441</v>
       </c>
       <c r="E268">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F268" t="s">
         <v>1518</v>
@@ -17220,7 +17220,7 @@
         <v>1441</v>
       </c>
       <c r="E269">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F269" t="s">
         <v>1518</v>
@@ -17255,7 +17255,7 @@
         <v>1442</v>
       </c>
       <c r="E270">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F270" t="s">
         <v>1518</v>
@@ -17290,7 +17290,7 @@
         <v>1442</v>
       </c>
       <c r="E271">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F271" t="s">
         <v>1518</v>
@@ -17325,7 +17325,7 @@
         <v>1443</v>
       </c>
       <c r="E272">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F272" t="s">
         <v>1518</v>
@@ -17360,7 +17360,7 @@
         <v>1444</v>
       </c>
       <c r="E273">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F273" t="s">
         <v>1518</v>
@@ -17395,7 +17395,7 @@
         <v>1445</v>
       </c>
       <c r="E274">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F274" t="s">
         <v>1518</v>
@@ -17430,7 +17430,7 @@
         <v>1445</v>
       </c>
       <c r="E275">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F275" t="s">
         <v>1518</v>
@@ -17465,7 +17465,7 @@
         <v>1446</v>
       </c>
       <c r="E276">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F276" t="s">
         <v>1518</v>
@@ -17500,7 +17500,7 @@
         <v>1446</v>
       </c>
       <c r="E277">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F277" t="s">
         <v>1518</v>
@@ -17535,7 +17535,7 @@
         <v>1446</v>
       </c>
       <c r="E278">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F278" t="s">
         <v>1518</v>
@@ -17570,7 +17570,7 @@
         <v>1447</v>
       </c>
       <c r="E279">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F279" t="s">
         <v>1518</v>
@@ -17605,7 +17605,7 @@
         <v>1447</v>
       </c>
       <c r="E280">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F280" t="s">
         <v>1518</v>
@@ -17640,7 +17640,7 @@
         <v>1447</v>
       </c>
       <c r="E281">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F281" t="s">
         <v>1518</v>
@@ -17675,7 +17675,7 @@
         <v>1447</v>
       </c>
       <c r="E282">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F282" t="s">
         <v>1518</v>
@@ -17710,7 +17710,7 @@
         <v>1447</v>
       </c>
       <c r="E283">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F283" t="s">
         <v>1518</v>
@@ -17745,7 +17745,7 @@
         <v>1447</v>
       </c>
       <c r="E284">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F284" t="s">
         <v>1518</v>
@@ -17780,7 +17780,7 @@
         <v>1447</v>
       </c>
       <c r="E285">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F285" t="s">
         <v>1518</v>
@@ -17815,7 +17815,7 @@
         <v>1447</v>
       </c>
       <c r="E286">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F286" t="s">
         <v>1518</v>
@@ -17850,7 +17850,7 @@
         <v>1447</v>
       </c>
       <c r="E287">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F287" t="s">
         <v>1518</v>
@@ -17885,7 +17885,7 @@
         <v>1448</v>
       </c>
       <c r="E288">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F288" t="s">
         <v>1518</v>
@@ -17920,7 +17920,7 @@
         <v>1448</v>
       </c>
       <c r="E289">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F289" t="s">
         <v>1518</v>
@@ -17955,7 +17955,7 @@
         <v>1448</v>
       </c>
       <c r="E290">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F290" t="s">
         <v>1518</v>
@@ -17990,7 +17990,7 @@
         <v>1449</v>
       </c>
       <c r="E291">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F291" t="s">
         <v>1518</v>
@@ -18025,7 +18025,7 @@
         <v>1450</v>
       </c>
       <c r="E292">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F292" t="s">
         <v>1518</v>
@@ -18060,7 +18060,7 @@
         <v>1450</v>
       </c>
       <c r="E293">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F293" t="s">
         <v>1518</v>
@@ -18095,7 +18095,7 @@
         <v>1450</v>
       </c>
       <c r="E294">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F294" t="s">
         <v>1518</v>
@@ -18130,7 +18130,7 @@
         <v>1450</v>
       </c>
       <c r="E295">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F295" t="s">
         <v>1518</v>
@@ -18165,7 +18165,7 @@
         <v>1450</v>
       </c>
       <c r="E296">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F296" t="s">
         <v>1518</v>
@@ -18200,7 +18200,7 @@
         <v>1450</v>
       </c>
       <c r="E297">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F297" t="s">
         <v>1518</v>
@@ -18235,7 +18235,7 @@
         <v>1451</v>
       </c>
       <c r="E298">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F298" t="s">
         <v>1518</v>
@@ -18270,7 +18270,7 @@
         <v>1451</v>
       </c>
       <c r="E299">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F299" t="s">
         <v>1518</v>
@@ -18305,7 +18305,7 @@
         <v>1451</v>
       </c>
       <c r="E300">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F300" t="s">
         <v>1518</v>
@@ -18340,7 +18340,7 @@
         <v>1451</v>
       </c>
       <c r="E301">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F301" t="s">
         <v>1518</v>
@@ -18378,7 +18378,7 @@
         <v>1451</v>
       </c>
       <c r="E302">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F302" t="s">
         <v>1518</v>
@@ -18413,7 +18413,7 @@
         <v>1451</v>
       </c>
       <c r="E303">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F303" t="s">
         <v>1518</v>
@@ -18448,7 +18448,7 @@
         <v>1451</v>
       </c>
       <c r="E304">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F304" t="s">
         <v>1518</v>
@@ -18483,7 +18483,7 @@
         <v>1451</v>
       </c>
       <c r="E305">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F305" t="s">
         <v>1518</v>
@@ -18518,7 +18518,7 @@
         <v>1451</v>
       </c>
       <c r="E306">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F306" t="s">
         <v>1518</v>
@@ -18553,7 +18553,7 @@
         <v>1452</v>
       </c>
       <c r="E307">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F307" t="s">
         <v>1519</v>
@@ -18588,7 +18588,7 @@
         <v>1453</v>
       </c>
       <c r="E308">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F308" t="s">
         <v>1522</v>
@@ -18623,7 +18623,7 @@
         <v>1454</v>
       </c>
       <c r="E309">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F309" t="s">
         <v>1518</v>
@@ -18658,7 +18658,7 @@
         <v>1455</v>
       </c>
       <c r="E310">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F310" t="s">
         <v>1518</v>
@@ -18693,7 +18693,7 @@
         <v>1455</v>
       </c>
       <c r="E311">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F311" t="s">
         <v>1518</v>
@@ -18728,7 +18728,7 @@
         <v>1456</v>
       </c>
       <c r="E312">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F312" t="s">
         <v>1518</v>
@@ -18763,7 +18763,7 @@
         <v>1457</v>
       </c>
       <c r="E313">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F313" t="s">
         <v>1521</v>
@@ -18798,7 +18798,7 @@
         <v>1457</v>
       </c>
       <c r="E314">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F314" t="s">
         <v>1518</v>
@@ -18833,7 +18833,7 @@
         <v>1457</v>
       </c>
       <c r="E315">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F315" t="s">
         <v>1518</v>
@@ -18868,7 +18868,7 @@
         <v>1457</v>
       </c>
       <c r="E316">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F316" t="s">
         <v>1518</v>
@@ -18903,7 +18903,7 @@
         <v>1457</v>
       </c>
       <c r="E317">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F317" t="s">
         <v>1518</v>
@@ -18938,7 +18938,7 @@
         <v>1457</v>
       </c>
       <c r="E318">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F318" t="s">
         <v>1518</v>
@@ -18973,7 +18973,7 @@
         <v>1458</v>
       </c>
       <c r="E319">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F319" t="s">
         <v>1518</v>
@@ -19008,7 +19008,7 @@
         <v>1459</v>
       </c>
       <c r="E320">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F320" t="s">
         <v>1518</v>
@@ -19043,7 +19043,7 @@
         <v>1459</v>
       </c>
       <c r="E321">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F321" t="s">
         <v>1518</v>
@@ -19078,7 +19078,7 @@
         <v>1459</v>
       </c>
       <c r="E322">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F322" t="s">
         <v>1518</v>
@@ -19116,7 +19116,7 @@
         <v>1459</v>
       </c>
       <c r="E323">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F323" t="s">
         <v>1518</v>
@@ -19151,7 +19151,7 @@
         <v>1460</v>
       </c>
       <c r="E324">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F324" t="s">
         <v>1518</v>
@@ -19186,7 +19186,7 @@
         <v>1460</v>
       </c>
       <c r="E325">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F325" t="s">
         <v>1518</v>
@@ -19221,7 +19221,7 @@
         <v>1460</v>
       </c>
       <c r="E326">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F326" t="s">
         <v>1518</v>
@@ -19256,7 +19256,7 @@
         <v>1460</v>
       </c>
       <c r="E327">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F327" t="s">
         <v>1518</v>
@@ -19291,7 +19291,7 @@
         <v>1460</v>
       </c>
       <c r="E328">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F328" t="s">
         <v>1518</v>
@@ -19326,7 +19326,7 @@
         <v>1461</v>
       </c>
       <c r="E329">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F329" t="s">
         <v>1518</v>
@@ -19361,7 +19361,7 @@
         <v>1461</v>
       </c>
       <c r="E330">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F330" t="s">
         <v>1518</v>
@@ -19396,7 +19396,7 @@
         <v>1462</v>
       </c>
       <c r="E331">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F331" t="s">
         <v>1518</v>
@@ -19431,7 +19431,7 @@
         <v>1462</v>
       </c>
       <c r="E332">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F332" t="s">
         <v>1518</v>
@@ -19466,7 +19466,7 @@
         <v>1462</v>
       </c>
       <c r="E333">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F333" t="s">
         <v>1518</v>
@@ -19501,7 +19501,7 @@
         <v>1462</v>
       </c>
       <c r="E334">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F334" t="s">
         <v>1518</v>
@@ -19536,7 +19536,7 @@
         <v>1462</v>
       </c>
       <c r="E335">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F335" t="s">
         <v>1518</v>
@@ -19571,7 +19571,7 @@
         <v>1462</v>
       </c>
       <c r="E336">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F336" t="s">
         <v>1518</v>
@@ -19606,7 +19606,7 @@
         <v>1462</v>
       </c>
       <c r="E337">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F337" t="s">
         <v>1518</v>
@@ -19641,7 +19641,7 @@
         <v>1462</v>
       </c>
       <c r="E338">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F338" t="s">
         <v>1518</v>
@@ -19676,7 +19676,7 @@
         <v>1462</v>
       </c>
       <c r="E339">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F339" t="s">
         <v>1518</v>
@@ -19711,7 +19711,7 @@
         <v>1462</v>
       </c>
       <c r="E340">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F340" t="s">
         <v>1518</v>
@@ -19746,7 +19746,7 @@
         <v>1463</v>
       </c>
       <c r="E341">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F341" t="s">
         <v>1518</v>
@@ -19781,7 +19781,7 @@
         <v>1463</v>
       </c>
       <c r="E342">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F342" t="s">
         <v>1518</v>
@@ -19816,7 +19816,7 @@
         <v>1463</v>
       </c>
       <c r="E343">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F343" t="s">
         <v>1519</v>
@@ -19851,7 +19851,7 @@
         <v>1464</v>
       </c>
       <c r="E344">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F344" t="s">
         <v>1518</v>
@@ -19886,7 +19886,7 @@
         <v>1464</v>
       </c>
       <c r="E345">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F345" t="s">
         <v>1518</v>
@@ -19921,7 +19921,7 @@
         <v>1464</v>
       </c>
       <c r="E346">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F346" t="s">
         <v>1518</v>
@@ -19956,7 +19956,7 @@
         <v>1464</v>
       </c>
       <c r="E347">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F347" t="s">
         <v>1518</v>
@@ -19991,7 +19991,7 @@
         <v>1464</v>
       </c>
       <c r="E348">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F348" t="s">
         <v>1518</v>
@@ -20026,7 +20026,7 @@
         <v>1464</v>
       </c>
       <c r="E349">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F349" t="s">
         <v>1518</v>
@@ -20061,7 +20061,7 @@
         <v>1464</v>
       </c>
       <c r="E350">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F350" t="s">
         <v>1521</v>
@@ -20096,7 +20096,7 @@
         <v>1465</v>
       </c>
       <c r="E351">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F351" t="s">
         <v>1518</v>
@@ -20131,7 +20131,7 @@
         <v>1465</v>
       </c>
       <c r="E352">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F352" t="s">
         <v>1518</v>
@@ -20166,7 +20166,7 @@
         <v>1465</v>
       </c>
       <c r="E353">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F353" t="s">
         <v>1518</v>
@@ -20201,7 +20201,7 @@
         <v>1465</v>
       </c>
       <c r="E354">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F354" t="s">
         <v>1518</v>
@@ -20236,7 +20236,7 @@
         <v>1466</v>
       </c>
       <c r="E355">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F355" t="s">
         <v>1521</v>
@@ -20271,7 +20271,7 @@
         <v>1466</v>
       </c>
       <c r="E356">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F356" t="s">
         <v>1518</v>
@@ -20306,7 +20306,7 @@
         <v>1466</v>
       </c>
       <c r="E357">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F357" t="s">
         <v>1518</v>
@@ -20341,7 +20341,7 @@
         <v>1466</v>
       </c>
       <c r="E358">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F358" t="s">
         <v>1518</v>
@@ -20376,7 +20376,7 @@
         <v>1466</v>
       </c>
       <c r="E359">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F359" t="s">
         <v>1518</v>
@@ -20411,7 +20411,7 @@
         <v>1467</v>
       </c>
       <c r="E360">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F360" t="s">
         <v>1518</v>
@@ -20446,7 +20446,7 @@
         <v>1467</v>
       </c>
       <c r="E361">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F361" t="s">
         <v>1518</v>
@@ -20481,7 +20481,7 @@
         <v>1467</v>
       </c>
       <c r="E362">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F362" t="s">
         <v>1520</v>
@@ -20516,7 +20516,7 @@
         <v>1467</v>
       </c>
       <c r="E363">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F363" t="s">
         <v>1518</v>
@@ -20551,7 +20551,7 @@
         <v>1467</v>
       </c>
       <c r="E364">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F364" t="s">
         <v>1518</v>
@@ -20586,7 +20586,7 @@
         <v>1468</v>
       </c>
       <c r="E365">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F365" t="s">
         <v>1518</v>
@@ -20621,7 +20621,7 @@
         <v>1468</v>
       </c>
       <c r="E366">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F366" t="s">
         <v>1518</v>
@@ -20656,7 +20656,7 @@
         <v>1468</v>
       </c>
       <c r="E367">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F367" t="s">
         <v>1518</v>
@@ -20691,7 +20691,7 @@
         <v>1468</v>
       </c>
       <c r="E368">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F368" t="s">
         <v>1518</v>
@@ -20726,7 +20726,7 @@
         <v>1469</v>
       </c>
       <c r="E369">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F369" t="s">
         <v>1518</v>
@@ -20761,7 +20761,7 @@
         <v>1469</v>
       </c>
       <c r="E370">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F370" t="s">
         <v>1518</v>
@@ -20796,7 +20796,7 @@
         <v>1469</v>
       </c>
       <c r="E371">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F371" t="s">
         <v>1518</v>
@@ -20831,7 +20831,7 @@
         <v>1469</v>
       </c>
       <c r="E372">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F372" t="s">
         <v>1518</v>
@@ -20869,7 +20869,7 @@
         <v>1470</v>
       </c>
       <c r="E373">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F373" t="s">
         <v>1518</v>
@@ -20904,7 +20904,7 @@
         <v>1470</v>
       </c>
       <c r="E374">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F374" t="s">
         <v>1518</v>
@@ -20939,7 +20939,7 @@
         <v>1470</v>
       </c>
       <c r="E375">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F375" t="s">
         <v>1518</v>
@@ -20974,7 +20974,7 @@
         <v>1470</v>
       </c>
       <c r="E376">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F376" t="s">
         <v>1518</v>
@@ -21009,7 +21009,7 @@
         <v>1470</v>
       </c>
       <c r="E377">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F377" t="s">
         <v>1518</v>
@@ -21044,7 +21044,7 @@
         <v>1470</v>
       </c>
       <c r="E378">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F378" t="s">
         <v>1518</v>
@@ -21079,7 +21079,7 @@
         <v>1471</v>
       </c>
       <c r="E379">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F379" t="s">
         <v>1519</v>
@@ -21114,7 +21114,7 @@
         <v>1471</v>
       </c>
       <c r="E380">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F380" t="s">
         <v>1518</v>
@@ -21149,7 +21149,7 @@
         <v>1472</v>
       </c>
       <c r="E381">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F381" t="s">
         <v>1518</v>
@@ -21184,7 +21184,7 @@
         <v>1473</v>
       </c>
       <c r="E382">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F382" t="s">
         <v>1518</v>
@@ -21219,7 +21219,7 @@
         <v>1473</v>
       </c>
       <c r="E383">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F383" t="s">
         <v>1518</v>
@@ -21254,7 +21254,7 @@
         <v>1473</v>
       </c>
       <c r="E384">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F384" t="s">
         <v>1520</v>
@@ -21292,7 +21292,7 @@
         <v>1474</v>
       </c>
       <c r="E385">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F385" t="s">
         <v>1518</v>
@@ -21327,7 +21327,7 @@
         <v>1474</v>
       </c>
       <c r="E386">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F386" t="s">
         <v>1518</v>
@@ -21362,7 +21362,7 @@
         <v>1474</v>
       </c>
       <c r="E387">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F387" t="s">
         <v>1518</v>
@@ -21397,7 +21397,7 @@
         <v>1475</v>
       </c>
       <c r="E388">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F388" t="s">
         <v>1518</v>
@@ -21432,7 +21432,7 @@
         <v>1475</v>
       </c>
       <c r="E389">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F389" t="s">
         <v>1518</v>
@@ -21467,7 +21467,7 @@
         <v>1475</v>
       </c>
       <c r="E390">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F390" t="s">
         <v>1518</v>
@@ -21502,7 +21502,7 @@
         <v>1475</v>
       </c>
       <c r="E391">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F391" t="s">
         <v>1518</v>
@@ -21537,7 +21537,7 @@
         <v>1475</v>
       </c>
       <c r="E392">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F392" t="s">
         <v>1518</v>
@@ -21572,7 +21572,7 @@
         <v>1475</v>
       </c>
       <c r="E393">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F393" t="s">
         <v>1518</v>
@@ -21607,7 +21607,7 @@
         <v>1475</v>
       </c>
       <c r="E394">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F394" t="s">
         <v>1518</v>
@@ -21642,7 +21642,7 @@
         <v>1476</v>
       </c>
       <c r="E395">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F395" t="s">
         <v>1518</v>
@@ -21677,7 +21677,7 @@
         <v>1477</v>
       </c>
       <c r="E396">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F396" t="s">
         <v>1518</v>
@@ -21712,7 +21712,7 @@
         <v>1477</v>
       </c>
       <c r="E397">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F397" t="s">
         <v>1518</v>
@@ -21747,7 +21747,7 @@
         <v>1477</v>
       </c>
       <c r="E398">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F398" t="s">
         <v>1518</v>
@@ -21782,7 +21782,7 @@
         <v>1477</v>
       </c>
       <c r="E399">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F399" t="s">
         <v>1522</v>
@@ -21820,7 +21820,7 @@
         <v>1477</v>
       </c>
       <c r="E400">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F400" t="s">
         <v>1518</v>
@@ -21855,7 +21855,7 @@
         <v>1477</v>
       </c>
       <c r="E401">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F401" t="s">
         <v>1522</v>
@@ -21890,7 +21890,7 @@
         <v>1478</v>
       </c>
       <c r="E402">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F402" t="s">
         <v>1518</v>
@@ -21925,7 +21925,7 @@
         <v>1479</v>
       </c>
       <c r="E403">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F403" t="s">
         <v>1518</v>
@@ -21960,7 +21960,7 @@
         <v>1479</v>
       </c>
       <c r="E404">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F404" t="s">
         <v>1518</v>
@@ -21995,7 +21995,7 @@
         <v>1479</v>
       </c>
       <c r="E405">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F405" t="s">
         <v>1518</v>
@@ -22030,7 +22030,7 @@
         <v>1480</v>
       </c>
       <c r="E406">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F406" t="s">
         <v>1522</v>
@@ -22065,7 +22065,7 @@
         <v>1480</v>
       </c>
       <c r="E407">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F407" t="s">
         <v>1518</v>
@@ -22100,7 +22100,7 @@
         <v>1480</v>
       </c>
       <c r="E408">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F408" t="s">
         <v>1518</v>
@@ -22135,7 +22135,7 @@
         <v>1480</v>
       </c>
       <c r="E409">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F409" t="s">
         <v>1518</v>
@@ -22170,7 +22170,7 @@
         <v>1481</v>
       </c>
       <c r="E410">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F410" t="s">
         <v>1518</v>
@@ -22205,7 +22205,7 @@
         <v>1481</v>
       </c>
       <c r="E411">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F411" t="s">
         <v>1518</v>
@@ -22240,7 +22240,7 @@
         <v>1481</v>
       </c>
       <c r="E412">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F412" t="s">
         <v>1518</v>
@@ -22275,7 +22275,7 @@
         <v>1482</v>
       </c>
       <c r="E413">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F413" t="s">
         <v>1518</v>
@@ -22310,7 +22310,7 @@
         <v>1482</v>
       </c>
       <c r="E414">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F414" t="s">
         <v>1518</v>
@@ -22345,7 +22345,7 @@
         <v>1482</v>
       </c>
       <c r="E415">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F415" t="s">
         <v>1518</v>
@@ -22380,7 +22380,7 @@
         <v>1482</v>
       </c>
       <c r="E416">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F416" t="s">
         <v>1518</v>
@@ -22415,7 +22415,7 @@
         <v>1482</v>
       </c>
       <c r="E417">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F417" t="s">
         <v>1518</v>
@@ -22450,7 +22450,7 @@
         <v>1483</v>
       </c>
       <c r="E418">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F418" t="s">
         <v>1518</v>
@@ -22485,7 +22485,7 @@
         <v>1483</v>
       </c>
       <c r="E419">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F419" t="s">
         <v>1518</v>
@@ -22520,7 +22520,7 @@
         <v>1483</v>
       </c>
       <c r="E420">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F420" t="s">
         <v>1518</v>
@@ -22555,7 +22555,7 @@
         <v>1483</v>
       </c>
       <c r="E421">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F421" t="s">
         <v>1518</v>
@@ -22590,7 +22590,7 @@
         <v>1483</v>
       </c>
       <c r="E422">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F422" t="s">
         <v>1518</v>
@@ -22625,7 +22625,7 @@
         <v>1483</v>
       </c>
       <c r="E423">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F423" t="s">
         <v>1518</v>
@@ -22660,7 +22660,7 @@
         <v>1483</v>
       </c>
       <c r="E424">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F424" t="s">
         <v>1518</v>
@@ -22695,7 +22695,7 @@
         <v>1483</v>
       </c>
       <c r="E425">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F425" t="s">
         <v>1518</v>
@@ -22730,7 +22730,7 @@
         <v>1483</v>
       </c>
       <c r="E426">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F426" t="s">
         <v>1518</v>
@@ -22765,7 +22765,7 @@
         <v>1483</v>
       </c>
       <c r="E427">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F427" t="s">
         <v>1518</v>
@@ -22800,7 +22800,7 @@
         <v>1483</v>
       </c>
       <c r="E428">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F428" t="s">
         <v>1518</v>
@@ -22835,7 +22835,7 @@
         <v>1483</v>
       </c>
       <c r="E429">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F429" t="s">
         <v>1518</v>
@@ -22870,7 +22870,7 @@
         <v>1483</v>
       </c>
       <c r="E430">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F430" t="s">
         <v>1518</v>
@@ -22905,7 +22905,7 @@
         <v>1483</v>
       </c>
       <c r="E431">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F431" t="s">
         <v>1518</v>
@@ -22940,7 +22940,7 @@
         <v>1483</v>
       </c>
       <c r="E432">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F432" t="s">
         <v>1518</v>
@@ -22975,7 +22975,7 @@
         <v>1483</v>
       </c>
       <c r="E433">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F433" t="s">
         <v>1518</v>
@@ -23010,7 +23010,7 @@
         <v>1483</v>
       </c>
       <c r="E434">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F434" t="s">
         <v>1518</v>
@@ -23045,7 +23045,7 @@
         <v>1483</v>
       </c>
       <c r="E435">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F435" t="s">
         <v>1518</v>
@@ -23080,7 +23080,7 @@
         <v>1483</v>
       </c>
       <c r="E436">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F436" t="s">
         <v>1518</v>
@@ -23115,7 +23115,7 @@
         <v>1483</v>
       </c>
       <c r="E437">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F437" t="s">
         <v>1518</v>
@@ -23150,7 +23150,7 @@
         <v>1483</v>
       </c>
       <c r="E438">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F438" t="s">
         <v>1518</v>
@@ -23185,7 +23185,7 @@
         <v>1483</v>
       </c>
       <c r="E439">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F439" t="s">
         <v>1518</v>
@@ -23220,7 +23220,7 @@
         <v>1483</v>
       </c>
       <c r="E440">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F440" t="s">
         <v>1518</v>
@@ -23255,7 +23255,7 @@
         <v>1483</v>
       </c>
       <c r="E441">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F441" t="s">
         <v>1518</v>
@@ -23290,7 +23290,7 @@
         <v>1484</v>
       </c>
       <c r="E442">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F442" t="s">
         <v>1518</v>
@@ -23325,7 +23325,7 @@
         <v>1484</v>
       </c>
       <c r="E443">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F443" t="s">
         <v>1518</v>
@@ -23360,7 +23360,7 @@
         <v>1484</v>
       </c>
       <c r="E444">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F444" t="s">
         <v>1518</v>
@@ -23395,7 +23395,7 @@
         <v>1484</v>
       </c>
       <c r="E445">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F445" t="s">
         <v>1518</v>
@@ -23430,7 +23430,7 @@
         <v>1484</v>
       </c>
       <c r="E446">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F446" t="s">
         <v>1518</v>
@@ -23465,7 +23465,7 @@
         <v>1484</v>
       </c>
       <c r="E447">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F447" t="s">
         <v>1518</v>
@@ -23500,7 +23500,7 @@
         <v>1484</v>
       </c>
       <c r="E448">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F448" t="s">
         <v>1522</v>
@@ -23535,7 +23535,7 @@
         <v>1484</v>
       </c>
       <c r="E449">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F449" t="s">
         <v>1518</v>
@@ -23570,7 +23570,7 @@
         <v>1485</v>
       </c>
       <c r="E450">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F450" t="s">
         <v>1518</v>
@@ -23605,7 +23605,7 @@
         <v>1486</v>
       </c>
       <c r="E451">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F451" t="s">
         <v>1520</v>
@@ -23643,7 +23643,7 @@
         <v>1486</v>
       </c>
       <c r="E452">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F452" t="s">
         <v>1518</v>
@@ -23678,7 +23678,7 @@
         <v>1486</v>
       </c>
       <c r="E453">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F453" t="s">
         <v>1518</v>
@@ -23713,7 +23713,7 @@
         <v>1486</v>
       </c>
       <c r="E454">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F454" t="s">
         <v>1518</v>
@@ -23748,7 +23748,7 @@
         <v>1486</v>
       </c>
       <c r="E455">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F455" t="s">
         <v>1518</v>
@@ -23783,7 +23783,7 @@
         <v>1487</v>
       </c>
       <c r="E456">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F456" t="s">
         <v>1518</v>
@@ -23821,7 +23821,7 @@
         <v>1487</v>
       </c>
       <c r="E457">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F457" t="s">
         <v>1522</v>
@@ -23856,7 +23856,7 @@
         <v>1487</v>
       </c>
       <c r="E458">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F458" t="s">
         <v>1520</v>
@@ -23891,7 +23891,7 @@
         <v>1487</v>
       </c>
       <c r="E459">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F459" t="s">
         <v>1518</v>
@@ -23926,7 +23926,7 @@
         <v>1487</v>
       </c>
       <c r="E460">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F460" t="s">
         <v>1518</v>
@@ -23961,7 +23961,7 @@
         <v>1487</v>
       </c>
       <c r="E461">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F461" t="s">
         <v>1518</v>
@@ -23996,7 +23996,7 @@
         <v>1487</v>
       </c>
       <c r="E462">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F462" t="s">
         <v>1518</v>
@@ -24031,7 +24031,7 @@
         <v>1487</v>
       </c>
       <c r="E463">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F463" t="s">
         <v>1518</v>
@@ -24066,7 +24066,7 @@
         <v>1487</v>
       </c>
       <c r="E464">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F464" t="s">
         <v>1518</v>
@@ -24101,7 +24101,7 @@
         <v>1488</v>
       </c>
       <c r="E465">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F465" t="s">
         <v>1522</v>
@@ -24139,7 +24139,7 @@
         <v>1488</v>
       </c>
       <c r="E466">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F466" t="s">
         <v>1518</v>
@@ -24174,7 +24174,7 @@
         <v>1489</v>
       </c>
       <c r="E467">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F467" t="s">
         <v>1518</v>
@@ -24209,7 +24209,7 @@
         <v>1489</v>
       </c>
       <c r="E468">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F468" t="s">
         <v>1518</v>
@@ -24244,7 +24244,7 @@
         <v>1489</v>
       </c>
       <c r="E469">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F469" t="s">
         <v>1518</v>
@@ -24279,7 +24279,7 @@
         <v>1489</v>
       </c>
       <c r="E470">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F470" t="s">
         <v>1518</v>
@@ -24314,7 +24314,7 @@
         <v>1489</v>
       </c>
       <c r="E471">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F471" t="s">
         <v>1518</v>
@@ -24349,7 +24349,7 @@
         <v>1489</v>
       </c>
       <c r="E472">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F472" t="s">
         <v>1518</v>
@@ -24384,7 +24384,7 @@
         <v>1490</v>
       </c>
       <c r="E473">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F473" t="s">
         <v>1518</v>
@@ -24419,7 +24419,7 @@
         <v>1490</v>
       </c>
       <c r="E474">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F474" t="s">
         <v>1518</v>
@@ -24454,7 +24454,7 @@
         <v>1490</v>
       </c>
       <c r="E475">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F475" t="s">
         <v>1518</v>
@@ -24489,7 +24489,7 @@
         <v>1490</v>
       </c>
       <c r="E476">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F476" t="s">
         <v>1518</v>
@@ -24524,7 +24524,7 @@
         <v>1490</v>
       </c>
       <c r="E477">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F477" t="s">
         <v>1518</v>
@@ -24559,7 +24559,7 @@
         <v>1490</v>
       </c>
       <c r="E478">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F478" t="s">
         <v>1520</v>
@@ -24594,7 +24594,7 @@
         <v>1490</v>
       </c>
       <c r="E479">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F479" t="s">
         <v>1518</v>
@@ -24629,7 +24629,7 @@
         <v>1490</v>
       </c>
       <c r="E480">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F480" t="s">
         <v>1518</v>
@@ -24664,7 +24664,7 @@
         <v>1491</v>
       </c>
       <c r="E481">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F481" t="s">
         <v>1518</v>
@@ -24699,7 +24699,7 @@
         <v>1491</v>
       </c>
       <c r="E482">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F482" t="s">
         <v>1518</v>
@@ -24734,7 +24734,7 @@
         <v>1491</v>
       </c>
       <c r="E483">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F483" t="s">
         <v>1518</v>
@@ -24769,7 +24769,7 @@
         <v>1491</v>
       </c>
       <c r="E484">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F484" t="s">
         <v>1518</v>
@@ -24804,7 +24804,7 @@
         <v>1491</v>
       </c>
       <c r="E485">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F485" t="s">
         <v>1518</v>
@@ -24839,7 +24839,7 @@
         <v>1491</v>
       </c>
       <c r="E486">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F486" t="s">
         <v>1518</v>
@@ -24874,7 +24874,7 @@
         <v>1491</v>
       </c>
       <c r="E487">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F487" t="s">
         <v>1518</v>
@@ -24909,7 +24909,7 @@
         <v>1491</v>
       </c>
       <c r="E488">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F488" t="s">
         <v>1518</v>
@@ -24944,7 +24944,7 @@
         <v>1492</v>
       </c>
       <c r="E489">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F489" t="s">
         <v>1518</v>
@@ -24979,7 +24979,7 @@
         <v>1492</v>
       </c>
       <c r="E490">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F490" t="s">
         <v>1518</v>
@@ -25014,7 +25014,7 @@
         <v>1492</v>
       </c>
       <c r="E491">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F491" t="s">
         <v>1518</v>
@@ -25049,7 +25049,7 @@
         <v>1492</v>
       </c>
       <c r="E492">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F492" t="s">
         <v>1518</v>
@@ -25084,7 +25084,7 @@
         <v>1492</v>
       </c>
       <c r="E493">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F493" t="s">
         <v>1518</v>
@@ -25119,7 +25119,7 @@
         <v>1492</v>
       </c>
       <c r="E494">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F494" t="s">
         <v>1518</v>
@@ -25154,7 +25154,7 @@
         <v>1493</v>
       </c>
       <c r="E495">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F495" t="s">
         <v>1518</v>
@@ -25189,7 +25189,7 @@
         <v>1493</v>
       </c>
       <c r="E496">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F496" t="s">
         <v>1518</v>
@@ -25224,7 +25224,7 @@
         <v>1493</v>
       </c>
       <c r="E497">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F497" t="s">
         <v>1518</v>
@@ -25259,7 +25259,7 @@
         <v>1493</v>
       </c>
       <c r="E498">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F498" t="s">
         <v>1518</v>
@@ -25294,7 +25294,7 @@
         <v>1493</v>
       </c>
       <c r="E499">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F499" t="s">
         <v>1518</v>
@@ -25329,7 +25329,7 @@
         <v>1494</v>
       </c>
       <c r="E500">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F500" t="s">
         <v>1518</v>
@@ -25364,7 +25364,7 @@
         <v>1494</v>
       </c>
       <c r="E501">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F501" t="s">
         <v>1518</v>
@@ -25399,7 +25399,7 @@
         <v>1494</v>
       </c>
       <c r="E502">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F502" t="s">
         <v>1518</v>
@@ -25434,7 +25434,7 @@
         <v>1494</v>
       </c>
       <c r="E503">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F503" t="s">
         <v>1518</v>
@@ -25469,7 +25469,7 @@
         <v>1494</v>
       </c>
       <c r="E504">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F504" t="s">
         <v>1518</v>
@@ -25504,7 +25504,7 @@
         <v>1494</v>
       </c>
       <c r="E505">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F505" t="s">
         <v>1518</v>
@@ -25539,7 +25539,7 @@
         <v>1494</v>
       </c>
       <c r="E506">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F506" t="s">
         <v>1518</v>
@@ -25574,7 +25574,7 @@
         <v>1494</v>
       </c>
       <c r="E507">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F507" t="s">
         <v>1518</v>
@@ -25609,7 +25609,7 @@
         <v>1494</v>
       </c>
       <c r="E508">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F508" t="s">
         <v>1518</v>
@@ -25647,7 +25647,7 @@
         <v>1494</v>
       </c>
       <c r="E509">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F509" t="s">
         <v>1518</v>
@@ -25682,7 +25682,7 @@
         <v>1495</v>
       </c>
       <c r="E510">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F510" t="s">
         <v>1518</v>
@@ -25717,7 +25717,7 @@
         <v>1495</v>
       </c>
       <c r="E511">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F511" t="s">
         <v>1520</v>
@@ -25755,7 +25755,7 @@
         <v>1495</v>
       </c>
       <c r="E512">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F512" t="s">
         <v>1518</v>
@@ -25790,7 +25790,7 @@
         <v>1495</v>
       </c>
       <c r="E513">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F513" t="s">
         <v>1518</v>
@@ -25825,7 +25825,7 @@
         <v>1496</v>
       </c>
       <c r="E514">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F514" t="s">
         <v>1518</v>
@@ -25860,7 +25860,7 @@
         <v>1496</v>
       </c>
       <c r="E515">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F515" t="s">
         <v>1518</v>
@@ -25895,7 +25895,7 @@
         <v>1496</v>
       </c>
       <c r="E516">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F516" t="s">
         <v>1518</v>
@@ -25930,7 +25930,7 @@
         <v>1496</v>
       </c>
       <c r="E517">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F517" t="s">
         <v>1518</v>
@@ -25965,7 +25965,7 @@
         <v>1496</v>
       </c>
       <c r="E518">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F518" t="s">
         <v>1518</v>
@@ -26000,7 +26000,7 @@
         <v>1496</v>
       </c>
       <c r="E519">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F519" t="s">
         <v>1518</v>
@@ -26035,7 +26035,7 @@
         <v>1496</v>
       </c>
       <c r="E520">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F520" t="s">
         <v>1518</v>
@@ -26070,7 +26070,7 @@
         <v>1496</v>
       </c>
       <c r="E521">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F521" t="s">
         <v>1518</v>
@@ -26105,7 +26105,7 @@
         <v>1496</v>
       </c>
       <c r="E522">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F522" t="s">
         <v>1518</v>
@@ -26140,7 +26140,7 @@
         <v>1497</v>
       </c>
       <c r="E523">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F523" t="s">
         <v>1518</v>
@@ -26175,7 +26175,7 @@
         <v>1497</v>
       </c>
       <c r="E524">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F524" t="s">
         <v>1518</v>
@@ -26210,7 +26210,7 @@
         <v>1497</v>
       </c>
       <c r="E525">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F525" t="s">
         <v>1518</v>
@@ -26245,7 +26245,7 @@
         <v>1497</v>
       </c>
       <c r="E526">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F526" t="s">
         <v>1518</v>
@@ -26280,7 +26280,7 @@
         <v>1498</v>
       </c>
       <c r="E527">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F527" t="s">
         <v>1518</v>
@@ -26315,7 +26315,7 @@
         <v>1498</v>
       </c>
       <c r="E528">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F528" t="s">
         <v>1518</v>
@@ -26350,7 +26350,7 @@
         <v>1498</v>
       </c>
       <c r="E529">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F529" t="s">
         <v>1518</v>
@@ -26385,7 +26385,7 @@
         <v>1498</v>
       </c>
       <c r="E530">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F530" t="s">
         <v>1520</v>
@@ -26423,7 +26423,7 @@
         <v>1499</v>
       </c>
       <c r="E531">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F531" t="s">
         <v>1518</v>
@@ -26458,7 +26458,7 @@
         <v>1499</v>
       </c>
       <c r="E532">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F532" t="s">
         <v>1522</v>
@@ -26496,7 +26496,7 @@
         <v>1499</v>
       </c>
       <c r="E533">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F533" t="s">
         <v>1518</v>
@@ -26531,7 +26531,7 @@
         <v>1499</v>
       </c>
       <c r="E534">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F534" t="s">
         <v>1518</v>
@@ -26566,7 +26566,7 @@
         <v>1500</v>
       </c>
       <c r="E535">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F535" t="s">
         <v>1518</v>
@@ -26601,7 +26601,7 @@
         <v>1500</v>
       </c>
       <c r="E536">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F536" t="s">
         <v>1518</v>
@@ -26636,7 +26636,7 @@
         <v>1500</v>
       </c>
       <c r="E537">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F537" t="s">
         <v>1518</v>
@@ -26671,7 +26671,7 @@
         <v>1500</v>
       </c>
       <c r="E538">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F538" t="s">
         <v>1518</v>
@@ -26706,7 +26706,7 @@
         <v>1500</v>
       </c>
       <c r="E539">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F539" t="s">
         <v>1520</v>
@@ -26744,7 +26744,7 @@
         <v>1500</v>
       </c>
       <c r="E540">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F540" t="s">
         <v>1518</v>
@@ -26779,7 +26779,7 @@
         <v>1500</v>
       </c>
       <c r="E541">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F541" t="s">
         <v>1518</v>
@@ -26814,7 +26814,7 @@
         <v>1500</v>
       </c>
       <c r="E542">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F542" t="s">
         <v>1518</v>
@@ -26849,7 +26849,7 @@
         <v>1501</v>
       </c>
       <c r="E543">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F543" t="s">
         <v>1518</v>
@@ -26884,7 +26884,7 @@
         <v>1501</v>
       </c>
       <c r="E544">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F544" t="s">
         <v>1518</v>
@@ -26919,7 +26919,7 @@
         <v>1502</v>
       </c>
       <c r="E545">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F545" t="s">
         <v>1520</v>
@@ -26957,7 +26957,7 @@
         <v>1502</v>
       </c>
       <c r="E546">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F546" t="s">
         <v>1518</v>
@@ -26992,7 +26992,7 @@
         <v>1502</v>
       </c>
       <c r="E547">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F547" t="s">
         <v>1518</v>
@@ -27027,7 +27027,7 @@
         <v>1502</v>
       </c>
       <c r="E548">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F548" t="s">
         <v>1518</v>
@@ -27062,7 +27062,7 @@
         <v>1503</v>
       </c>
       <c r="E549">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F549" t="s">
         <v>1518</v>
@@ -27097,7 +27097,7 @@
         <v>1504</v>
       </c>
       <c r="E550">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F550" t="s">
         <v>1518</v>
@@ -27132,7 +27132,7 @@
         <v>1504</v>
       </c>
       <c r="E551">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F551" t="s">
         <v>1518</v>
@@ -27167,7 +27167,7 @@
         <v>1504</v>
       </c>
       <c r="E552">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F552" t="s">
         <v>1518</v>
@@ -27202,7 +27202,7 @@
         <v>1504</v>
       </c>
       <c r="E553">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F553" t="s">
         <v>1518</v>
@@ -27237,7 +27237,7 @@
         <v>1504</v>
       </c>
       <c r="E554">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F554" t="s">
         <v>1518</v>
@@ -27272,7 +27272,7 @@
         <v>1504</v>
       </c>
       <c r="E555">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F555" t="s">
         <v>1518</v>
@@ -27307,7 +27307,7 @@
         <v>1504</v>
       </c>
       <c r="E556">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F556" t="s">
         <v>1518</v>
@@ -27342,7 +27342,7 @@
         <v>1504</v>
       </c>
       <c r="E557">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F557" t="s">
         <v>1518</v>
@@ -27377,7 +27377,7 @@
         <v>1504</v>
       </c>
       <c r="E558">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F558" t="s">
         <v>1518</v>
@@ -27412,7 +27412,7 @@
         <v>1504</v>
       </c>
       <c r="E559">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F559" t="s">
         <v>1520</v>
@@ -27450,7 +27450,7 @@
         <v>1505</v>
       </c>
       <c r="E560">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F560" t="s">
         <v>1518</v>
@@ -27485,7 +27485,7 @@
         <v>1505</v>
       </c>
       <c r="E561">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F561" t="s">
         <v>1518</v>
@@ -27520,7 +27520,7 @@
         <v>1505</v>
       </c>
       <c r="E562">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F562" t="s">
         <v>1518</v>
@@ -27555,7 +27555,7 @@
         <v>1505</v>
       </c>
       <c r="E563">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F563" t="s">
         <v>1518</v>
@@ -27590,7 +27590,7 @@
         <v>1505</v>
       </c>
       <c r="E564">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F564" t="s">
         <v>1520</v>
@@ -27628,7 +27628,7 @@
         <v>1505</v>
       </c>
       <c r="E565">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F565" t="s">
         <v>1518</v>
@@ -27663,7 +27663,7 @@
         <v>1505</v>
       </c>
       <c r="E566">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F566" t="s">
         <v>1518</v>
@@ -27698,7 +27698,7 @@
         <v>1505</v>
       </c>
       <c r="E567">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F567" t="s">
         <v>1518</v>
@@ -27733,7 +27733,7 @@
         <v>1506</v>
       </c>
       <c r="E568">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F568" t="s">
         <v>1518</v>
@@ -27768,7 +27768,7 @@
         <v>1506</v>
       </c>
       <c r="E569">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F569" t="s">
         <v>1520</v>
@@ -27806,7 +27806,7 @@
         <v>1506</v>
       </c>
       <c r="E570">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F570" t="s">
         <v>1518</v>
@@ -27841,7 +27841,7 @@
         <v>1507</v>
       </c>
       <c r="E571">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F571" t="s">
         <v>1520</v>
@@ -27879,7 +27879,7 @@
         <v>1507</v>
       </c>
       <c r="E572">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F572" t="s">
         <v>1518</v>
@@ -27914,7 +27914,7 @@
         <v>1507</v>
       </c>
       <c r="E573">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F573" t="s">
         <v>1518</v>
@@ -27949,7 +27949,7 @@
         <v>1508</v>
       </c>
       <c r="E574">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F574" t="s">
         <v>1518</v>
@@ -27984,7 +27984,7 @@
         <v>1508</v>
       </c>
       <c r="E575">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F575" t="s">
         <v>1518</v>
@@ -28019,7 +28019,7 @@
         <v>1508</v>
       </c>
       <c r="E576">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F576" t="s">
         <v>1518</v>
@@ -28054,7 +28054,7 @@
         <v>1508</v>
       </c>
       <c r="E577">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F577" t="s">
         <v>1518</v>
@@ -28089,7 +28089,7 @@
         <v>1508</v>
       </c>
       <c r="E578">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F578" t="s">
         <v>1518</v>
@@ -28124,7 +28124,7 @@
         <v>1508</v>
       </c>
       <c r="E579">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F579" t="s">
         <v>1518</v>
@@ -28159,7 +28159,7 @@
         <v>1508</v>
       </c>
       <c r="E580">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F580" t="s">
         <v>1520</v>
@@ -28197,7 +28197,7 @@
         <v>1509</v>
       </c>
       <c r="E581">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F581" t="s">
         <v>1520</v>
@@ -28235,7 +28235,7 @@
         <v>1509</v>
       </c>
       <c r="E582">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F582" t="s">
         <v>1520</v>
@@ -28270,7 +28270,7 @@
         <v>1509</v>
       </c>
       <c r="E583">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F583" t="s">
         <v>1518</v>
@@ -28305,7 +28305,7 @@
         <v>1509</v>
       </c>
       <c r="E584">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F584" t="s">
         <v>1518</v>
@@ -28340,7 +28340,7 @@
         <v>1509</v>
       </c>
       <c r="E585">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F585" t="s">
         <v>1518</v>
@@ -28375,7 +28375,7 @@
         <v>1509</v>
       </c>
       <c r="E586">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F586" t="s">
         <v>1518</v>
@@ -28410,7 +28410,7 @@
         <v>1510</v>
       </c>
       <c r="E587">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F587" t="s">
         <v>1518</v>
@@ -28445,7 +28445,7 @@
         <v>1510</v>
       </c>
       <c r="E588">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F588" t="s">
         <v>1518</v>
@@ -28480,7 +28480,7 @@
         <v>1510</v>
       </c>
       <c r="E589">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F589" t="s">
         <v>1518</v>
@@ -28515,7 +28515,7 @@
         <v>1510</v>
       </c>
       <c r="E590">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F590" t="s">
         <v>1518</v>
@@ -28550,7 +28550,7 @@
         <v>1510</v>
       </c>
       <c r="E591">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F591" t="s">
         <v>1518</v>
@@ -28585,7 +28585,7 @@
         <v>1510</v>
       </c>
       <c r="E592">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F592" t="s">
         <v>1518</v>
@@ -28620,7 +28620,7 @@
         <v>1510</v>
       </c>
       <c r="E593">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F593" t="s">
         <v>1518</v>
@@ -28655,7 +28655,7 @@
         <v>1511</v>
       </c>
       <c r="E594">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F594" t="s">
         <v>1518</v>
@@ -28693,7 +28693,7 @@
         <v>1511</v>
       </c>
       <c r="E595">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F595" t="s">
         <v>1518</v>
@@ -28728,7 +28728,7 @@
         <v>1511</v>
       </c>
       <c r="E596">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F596" t="s">
         <v>1518</v>
@@ -28763,7 +28763,7 @@
         <v>1511</v>
       </c>
       <c r="E597">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F597" t="s">
         <v>1518</v>
@@ -28801,7 +28801,7 @@
         <v>1511</v>
       </c>
       <c r="E598">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F598" t="s">
         <v>1518</v>
@@ -28836,7 +28836,7 @@
         <v>1512</v>
       </c>
       <c r="E599">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F599" t="s">
         <v>1518</v>
@@ -28871,7 +28871,7 @@
         <v>1513</v>
       </c>
       <c r="E600">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F600" t="s">
         <v>1518</v>
@@ -28906,7 +28906,7 @@
         <v>1513</v>
       </c>
       <c r="E601">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F601" t="s">
         <v>1518</v>
@@ -28941,7 +28941,7 @@
         <v>1513</v>
       </c>
       <c r="E602">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F602" t="s">
         <v>1520</v>
@@ -28976,7 +28976,7 @@
         <v>1513</v>
       </c>
       <c r="E603">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F603" t="s">
         <v>1520</v>
@@ -29014,7 +29014,7 @@
         <v>1513</v>
       </c>
       <c r="E604">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F604" t="s">
         <v>1518</v>
@@ -29049,7 +29049,7 @@
         <v>1513</v>
       </c>
       <c r="E605">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F605" t="s">
         <v>1518</v>
@@ -29084,7 +29084,7 @@
         <v>1513</v>
       </c>
       <c r="E606">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F606" t="s">
         <v>1518</v>
@@ -29119,7 +29119,7 @@
         <v>1513</v>
       </c>
       <c r="E607">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F607" t="s">
         <v>1518</v>
@@ -29154,7 +29154,7 @@
         <v>1513</v>
       </c>
       <c r="E608">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F608" t="s">
         <v>1518</v>
@@ -29189,7 +29189,7 @@
         <v>1513</v>
       </c>
       <c r="E609">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F609" t="s">
         <v>1518</v>
@@ -29224,7 +29224,7 @@
         <v>1513</v>
       </c>
       <c r="E610">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F610" t="s">
         <v>1518</v>
@@ -29262,7 +29262,7 @@
         <v>1513</v>
       </c>
       <c r="E611">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F611" t="s">
         <v>1518</v>
@@ -29297,7 +29297,7 @@
         <v>1513</v>
       </c>
       <c r="E612">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F612" t="s">
         <v>1518</v>
@@ -29332,7 +29332,7 @@
         <v>1513</v>
       </c>
       <c r="E613">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F613" t="s">
         <v>1522</v>
@@ -29367,7 +29367,7 @@
         <v>1514</v>
       </c>
       <c r="E614">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F614" t="s">
         <v>1518</v>
@@ -29402,7 +29402,7 @@
         <v>1514</v>
       </c>
       <c r="E615">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F615" t="s">
         <v>1520</v>
@@ -29440,7 +29440,7 @@
         <v>1514</v>
       </c>
       <c r="E616">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F616" t="s">
         <v>1518</v>
@@ -29475,7 +29475,7 @@
         <v>1514</v>
       </c>
       <c r="E617">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F617" t="s">
         <v>1520</v>
@@ -29513,7 +29513,7 @@
         <v>1514</v>
       </c>
       <c r="E618">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F618" t="s">
         <v>1518</v>
@@ -29548,7 +29548,7 @@
         <v>1515</v>
       </c>
       <c r="E619">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F619" t="s">
         <v>1518</v>
@@ -29583,7 +29583,7 @@
         <v>1515</v>
       </c>
       <c r="E620">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F620" t="s">
         <v>1518</v>
@@ -29618,7 +29618,7 @@
         <v>1515</v>
       </c>
       <c r="E621">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F621" t="s">
         <v>1518</v>
@@ -29653,7 +29653,7 @@
         <v>1515</v>
       </c>
       <c r="E622">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F622" t="s">
         <v>1518</v>
@@ -29688,7 +29688,7 @@
         <v>1515</v>
       </c>
       <c r="E623">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F623" t="s">
         <v>1518</v>
@@ -29723,7 +29723,7 @@
         <v>1515</v>
       </c>
       <c r="E624">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F624" t="s">
         <v>1518</v>
@@ -29758,7 +29758,7 @@
         <v>1515</v>
       </c>
       <c r="E625">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F625" t="s">
         <v>1518</v>
@@ -29793,7 +29793,7 @@
         <v>1516</v>
       </c>
       <c r="E626">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F626" t="s">
         <v>1518</v>
@@ -29828,7 +29828,7 @@
         <v>1516</v>
       </c>
       <c r="E627">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F627" t="s">
         <v>1518</v>
@@ -29863,7 +29863,7 @@
         <v>1516</v>
       </c>
       <c r="E628">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F628" t="s">
         <v>1518</v>
@@ -29898,7 +29898,7 @@
         <v>1516</v>
       </c>
       <c r="E629">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F629" t="s">
         <v>1518</v>
@@ -29933,7 +29933,7 @@
         <v>1516</v>
       </c>
       <c r="E630">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F630" t="s">
         <v>1518</v>
@@ -29968,7 +29968,7 @@
         <v>1517</v>
       </c>
       <c r="E631">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F631" t="s">
         <v>1518</v>
@@ -30006,7 +30006,7 @@
         <v>1517</v>
       </c>
       <c r="E632">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F632" t="s">
         <v>1518</v>
@@ -30041,7 +30041,7 @@
         <v>1517</v>
       </c>
       <c r="E633">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F633" t="s">
         <v>1518</v>
@@ -30076,7 +30076,7 @@
         <v>1517</v>
       </c>
       <c r="E634">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F634" t="s">
         <v>1518</v>

--- a/BacklogGATEAutoCompleto.xlsx
+++ b/BacklogGATEAutoCompleto.xlsx
@@ -4822,64 +4822,64 @@
     <t>HUDSON DE OLIVEIRA SACRAMENTO</t>
   </si>
   <si>
+    <t>LUIZ FRANCISCO PERALTA BRAGA</t>
+  </si>
+  <si>
+    <t>ALESSANDRA ALMEIDA DIAS DA SILVA,ALEXANDER MAGNO BORGES GOMES DA SILVA,VANESSA FERNANDES LEÃO</t>
+  </si>
+  <si>
+    <t>PABLO GINIO VIMERCATI SIMAS</t>
+  </si>
+  <si>
+    <t>THIAGO JOSÉ DUPRAT FORTES</t>
+  </si>
+  <si>
+    <t>FERNANDA FERREIRA FONTES,JULIANA MARTINS BAHIENSE,RODRIGO VALENTE SERRA</t>
+  </si>
+  <si>
+    <t>PEDRO HENRIQUE DE MESQUITA MAGALHÃES</t>
+  </si>
+  <si>
+    <t>RODRIGO VENTURA MARRA,THIAGO JOSÉ DUPRAT FORTES</t>
+  </si>
+  <si>
+    <t>CHRISTIANA ROSA FERREIRA</t>
+  </si>
+  <si>
+    <t>HEITOR DE FÁTIMA BARBOSA DA SILVA</t>
+  </si>
+  <si>
+    <t>JULIANA MARTINS BAHIENSE,MARIA JOSÉ LOPES DE ARAUJO SAROLDI</t>
+  </si>
+  <si>
+    <t>MARINA DE AQUINO PARREIRA XAVIER, _SEM USUARIO ATRIBUIDO</t>
+  </si>
+  <si>
+    <t>EDUARDO COUTO SOLEDADE</t>
+  </si>
+  <si>
+    <t>HELENA FERREIRA DE LIMA</t>
+  </si>
+  <si>
+    <t>LUIZ FRANCISCO PERALTA BRAGA,MARCELO SILVA DE AZEVEDO, _SEM USUARIO ATRIBUIDO</t>
+  </si>
+  <si>
+    <t>SEZISNANDO JOSE PRIMO PAES</t>
+  </si>
+  <si>
+    <t>JOELSON SANTANA DE CARVALHO</t>
+  </si>
+  <si>
+    <t>DIANA DELGADO DA COSTA DA SILVA,RENATA DE ARAUJO RIOS</t>
+  </si>
+  <si>
+    <t>DIANA DELGADO DA COSTA DA SILVA</t>
+  </si>
+  <si>
+    <t>RANAILLA LIMA BANDEIRA DOS SANTOS, _SEM USUARIO ATRIBUIDO</t>
+  </si>
+  <si>
     <t>GLAUCO CASTILHO DE ALMEIDA</t>
-  </si>
-  <si>
-    <t>LUIZ FRANCISCO PERALTA BRAGA</t>
-  </si>
-  <si>
-    <t>ALESSANDRA ALMEIDA DIAS DA SILVA,ALEXANDER MAGNO BORGES GOMES DA SILVA,VANESSA FERNANDES LEÃO</t>
-  </si>
-  <si>
-    <t>PABLO GINIO VIMERCATI SIMAS</t>
-  </si>
-  <si>
-    <t>THIAGO JOSÉ DUPRAT FORTES</t>
-  </si>
-  <si>
-    <t>FERNANDA FERREIRA FONTES,JULIANA MARTINS BAHIENSE,RODRIGO VALENTE SERRA</t>
-  </si>
-  <si>
-    <t>PEDRO HENRIQUE DE MESQUITA MAGALHÃES</t>
-  </si>
-  <si>
-    <t>RODRIGO VENTURA MARRA,THIAGO JOSÉ DUPRAT FORTES</t>
-  </si>
-  <si>
-    <t>CHRISTIANA ROSA FERREIRA</t>
-  </si>
-  <si>
-    <t>HEITOR DE FÁTIMA BARBOSA DA SILVA</t>
-  </si>
-  <si>
-    <t>JULIANA MARTINS BAHIENSE,MARIA JOSÉ LOPES DE ARAUJO SAROLDI</t>
-  </si>
-  <si>
-    <t>MARINA DE AQUINO PARREIRA XAVIER, _SEM USUARIO ATRIBUIDO</t>
-  </si>
-  <si>
-    <t>EDUARDO COUTO SOLEDADE</t>
-  </si>
-  <si>
-    <t>HELENA FERREIRA DE LIMA</t>
-  </si>
-  <si>
-    <t>LUIZ FRANCISCO PERALTA BRAGA,MARCELO SILVA DE AZEVEDO, _SEM USUARIO ATRIBUIDO</t>
-  </si>
-  <si>
-    <t>SEZISNANDO JOSE PRIMO PAES</t>
-  </si>
-  <si>
-    <t>JOELSON SANTANA DE CARVALHO</t>
-  </si>
-  <si>
-    <t>DIANA DELGADO DA COSTA DA SILVA,RENATA DE ARAUJO RIOS</t>
-  </si>
-  <si>
-    <t>DIANA DELGADO DA COSTA DA SILVA</t>
-  </si>
-  <si>
-    <t>RANAILLA LIMA BANDEIRA DOS SANTOS, _SEM USUARIO ATRIBUIDO</t>
   </si>
   <si>
     <t>IZABEL CHRISTINA DE ALCANTARA FIGUEIREDO PIMENTA</t>
@@ -13751,7 +13751,7 @@
     </row>
     <row r="171" spans="1:12">
       <c r="A171" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B171" t="s">
         <v>211</v>
@@ -13772,7 +13772,7 @@
         <v>1514</v>
       </c>
       <c r="I171" t="s">
-        <v>1602</v>
+        <v>1546</v>
       </c>
       <c r="J171" t="s">
         <v>1822</v>
@@ -13947,7 +13947,7 @@
         <v>1514</v>
       </c>
       <c r="I176" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="J176" t="s">
         <v>1827</v>
@@ -13982,7 +13982,7 @@
         <v>1514</v>
       </c>
       <c r="I177" t="s">
-        <v>1604</v>
+        <v>1603</v>
       </c>
       <c r="J177" t="s">
         <v>1828</v>
@@ -14157,7 +14157,7 @@
         <v>1514</v>
       </c>
       <c r="I182" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="J182" t="s">
         <v>1833</v>
@@ -14192,7 +14192,7 @@
         <v>1514</v>
       </c>
       <c r="I183" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
       <c r="J183" t="s">
         <v>1834</v>
@@ -14332,7 +14332,7 @@
         <v>1514</v>
       </c>
       <c r="I187" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
       <c r="J187" t="s">
         <v>1838</v>
@@ -14402,7 +14402,7 @@
         <v>1514</v>
       </c>
       <c r="I189" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="J189" t="s">
         <v>1840</v>
@@ -14437,7 +14437,7 @@
         <v>1514</v>
       </c>
       <c r="I190" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
       <c r="J190" t="s">
         <v>1841</v>
@@ -14615,7 +14615,7 @@
         <v>1514</v>
       </c>
       <c r="I195" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="J195" t="s">
         <v>1846</v>
@@ -14650,7 +14650,7 @@
         <v>1514</v>
       </c>
       <c r="I196" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="J196" t="s">
         <v>1847</v>
@@ -14685,7 +14685,7 @@
         <v>1514</v>
       </c>
       <c r="I197" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
       <c r="J197" t="s">
         <v>1848</v>
@@ -14965,7 +14965,7 @@
         <v>1514</v>
       </c>
       <c r="I205" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="J205" t="s">
         <v>1856</v>
@@ -15035,7 +15035,7 @@
         <v>1514</v>
       </c>
       <c r="I207" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="J207" t="s">
         <v>1858</v>
@@ -15245,7 +15245,7 @@
         <v>1514</v>
       </c>
       <c r="I213" t="s">
-        <v>1615</v>
+        <v>1614</v>
       </c>
       <c r="J213" t="s">
         <v>1864</v>
@@ -15315,7 +15315,7 @@
         <v>1514</v>
       </c>
       <c r="I215" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="J215" t="s">
         <v>1866</v>
@@ -15350,7 +15350,7 @@
         <v>1514</v>
       </c>
       <c r="I216" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
       <c r="J216" t="s">
         <v>1867</v>
@@ -15525,7 +15525,7 @@
         <v>1514</v>
       </c>
       <c r="I221" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="J221" t="s">
         <v>1872</v>
@@ -15563,7 +15563,7 @@
         <v>1436</v>
       </c>
       <c r="I222" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="J222" t="s">
         <v>1873</v>
@@ -15633,7 +15633,7 @@
         <v>1514</v>
       </c>
       <c r="I224" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="J224" t="s">
         <v>1875</v>
@@ -15773,7 +15773,7 @@
         <v>1514</v>
       </c>
       <c r="I228" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="J228" t="s">
         <v>1879</v>
@@ -15808,7 +15808,7 @@
         <v>1514</v>
       </c>
       <c r="I229" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="J229" t="s">
         <v>1880</v>
@@ -15878,7 +15878,7 @@
         <v>1514</v>
       </c>
       <c r="I231" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="J231" t="s">
         <v>1882</v>
@@ -15948,7 +15948,7 @@
         <v>1514</v>
       </c>
       <c r="I233" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="J233" t="s">
         <v>1884</v>
@@ -15983,7 +15983,7 @@
         <v>1514</v>
       </c>
       <c r="I234" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="J234" t="s">
         <v>1885</v>
@@ -16018,7 +16018,7 @@
         <v>1514</v>
       </c>
       <c r="I235" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="J235" t="s">
         <v>1886</v>
@@ -16333,7 +16333,7 @@
         <v>1514</v>
       </c>
       <c r="I244" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="J244" t="s">
         <v>1895</v>
@@ -16403,7 +16403,7 @@
         <v>1514</v>
       </c>
       <c r="I246" t="s">
-        <v>1602</v>
+        <v>1621</v>
       </c>
       <c r="J246" t="s">
         <v>1897</v>
@@ -16473,7 +16473,7 @@
         <v>1514</v>
       </c>
       <c r="I248" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="J248" t="s">
         <v>1899</v>
@@ -16823,7 +16823,7 @@
         <v>1514</v>
       </c>
       <c r="I258" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="J258" t="s">
         <v>1909</v>
@@ -16928,7 +16928,7 @@
         <v>1514</v>
       </c>
       <c r="I261" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="J261" t="s">
         <v>1912</v>
@@ -17033,7 +17033,7 @@
         <v>1514</v>
       </c>
       <c r="I264" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="J264" t="s">
         <v>1915</v>
@@ -17383,7 +17383,7 @@
         <v>1514</v>
       </c>
       <c r="I274" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="J274" t="s">
         <v>1925</v>
@@ -17768,7 +17768,7 @@
         <v>1514</v>
       </c>
       <c r="I285" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="J285" t="s">
         <v>1936</v>
@@ -17908,7 +17908,7 @@
         <v>1514</v>
       </c>
       <c r="I289" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="J289" t="s">
         <v>1940</v>
@@ -18296,7 +18296,7 @@
         <v>1514</v>
       </c>
       <c r="I300" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="J300" t="s">
         <v>1951</v>
@@ -18611,7 +18611,7 @@
         <v>1514</v>
       </c>
       <c r="I309" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="J309" t="s">
         <v>1960</v>
@@ -18754,7 +18754,7 @@
         <v>1520</v>
       </c>
       <c r="I313" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="J313" t="s">
         <v>1964</v>
@@ -18824,7 +18824,7 @@
         <v>1514</v>
       </c>
       <c r="I315" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="J315" t="s">
         <v>1966</v>
@@ -18859,7 +18859,7 @@
         <v>1514</v>
       </c>
       <c r="I316" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="J316" t="s">
         <v>1967</v>
@@ -18964,7 +18964,7 @@
         <v>1514</v>
       </c>
       <c r="I319" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="J319" t="s">
         <v>1970</v>
@@ -19034,7 +19034,7 @@
         <v>1514</v>
       </c>
       <c r="I321" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="J321" t="s">
         <v>1972</v>
@@ -19139,7 +19139,7 @@
         <v>1514</v>
       </c>
       <c r="I324" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="J324" t="s">
         <v>1975</v>
@@ -19244,7 +19244,7 @@
         <v>1514</v>
       </c>
       <c r="I327" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="J327" t="s">
         <v>1978</v>
@@ -19979,7 +19979,7 @@
         <v>1514</v>
       </c>
       <c r="I348" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="J348" t="s">
         <v>1999</v>
@@ -20049,7 +20049,7 @@
         <v>1514</v>
       </c>
       <c r="I350" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="J350" t="s">
         <v>2001</v>
@@ -20329,7 +20329,7 @@
         <v>1514</v>
       </c>
       <c r="I358" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="J358" t="s">
         <v>2009</v>
@@ -20364,7 +20364,7 @@
         <v>1514</v>
       </c>
       <c r="I359" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
       <c r="J359" t="s">
         <v>2010</v>
@@ -20787,7 +20787,7 @@
         <v>1514</v>
       </c>
       <c r="I371" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="J371" t="s">
         <v>2022</v>
@@ -20930,7 +20930,7 @@
         <v>1480</v>
       </c>
       <c r="I375" t="s">
-        <v>1602</v>
+        <v>1621</v>
       </c>
       <c r="J375" t="s">
         <v>2026</v>
@@ -21245,7 +21245,7 @@
         <v>1514</v>
       </c>
       <c r="I384" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="J384" t="s">
         <v>2035</v>
@@ -21280,7 +21280,7 @@
         <v>1514</v>
       </c>
       <c r="I385" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="J385" t="s">
         <v>2036</v>
@@ -21315,7 +21315,7 @@
         <v>1514</v>
       </c>
       <c r="I386" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="J386" t="s">
         <v>2037</v>
@@ -21350,7 +21350,7 @@
         <v>1514</v>
       </c>
       <c r="I387" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="J387" t="s">
         <v>2038</v>
@@ -21385,7 +21385,7 @@
         <v>1514</v>
       </c>
       <c r="I388" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="J388" t="s">
         <v>2009</v>
@@ -21668,7 +21668,7 @@
         <v>1514</v>
       </c>
       <c r="I396" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="J396" t="s">
         <v>2046</v>
@@ -21843,7 +21843,7 @@
         <v>1514</v>
       </c>
       <c r="I401" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="J401" t="s">
         <v>2051</v>
@@ -21878,7 +21878,7 @@
         <v>1514</v>
       </c>
       <c r="I402" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="J402" t="s">
         <v>2052</v>
@@ -21913,7 +21913,7 @@
         <v>1514</v>
       </c>
       <c r="I403" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="J403" t="s">
         <v>2053</v>
@@ -21948,7 +21948,7 @@
         <v>1514</v>
       </c>
       <c r="I404" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="J404" t="s">
         <v>2054</v>
@@ -22963,7 +22963,7 @@
         <v>1514</v>
       </c>
       <c r="I433" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="J433" t="s">
         <v>2083</v>
@@ -23208,7 +23208,7 @@
         <v>1514</v>
       </c>
       <c r="I440" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="J440" t="s">
         <v>2087</v>
@@ -23421,7 +23421,7 @@
         <v>1514</v>
       </c>
       <c r="I446" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="J446" t="s">
         <v>2093</v>
@@ -23777,7 +23777,7 @@
         <v>1522</v>
       </c>
       <c r="I456" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="J456" t="s">
         <v>2103</v>
@@ -24302,7 +24302,7 @@
         <v>1514</v>
       </c>
       <c r="I471" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="J471" t="s">
         <v>2118</v>
@@ -24477,7 +24477,7 @@
         <v>1514</v>
       </c>
       <c r="I476" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="J476" t="s">
         <v>2123</v>
@@ -24582,7 +24582,7 @@
         <v>1514</v>
       </c>
       <c r="I479" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="J479" t="s">
         <v>2126</v>
@@ -24967,7 +24967,7 @@
         <v>1514</v>
       </c>
       <c r="I490" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="J490" t="s">
         <v>2137</v>
@@ -25037,7 +25037,7 @@
         <v>1514</v>
       </c>
       <c r="I492" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="J492" t="s">
         <v>2139</v>
@@ -25107,7 +25107,7 @@
         <v>1514</v>
       </c>
       <c r="I494" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="J494" t="s">
         <v>2141</v>
@@ -25247,7 +25247,7 @@
         <v>1514</v>
       </c>
       <c r="I498" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="J498" t="s">
         <v>2042</v>
@@ -25460,7 +25460,7 @@
         <v>1514</v>
       </c>
       <c r="I504" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="J504" t="s">
         <v>2150</v>
@@ -26907,7 +26907,7 @@
         <v>1514</v>
       </c>
       <c r="I545" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="J545" t="s">
         <v>2190</v>
@@ -27050,7 +27050,7 @@
         <v>1514</v>
       </c>
       <c r="I549" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="J549" t="s">
         <v>2194</v>
@@ -27333,7 +27333,7 @@
         <v>1514</v>
       </c>
       <c r="I557" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="J557" t="s">
         <v>2201</v>
@@ -27549,7 +27549,7 @@
         <v>1514</v>
       </c>
       <c r="I563" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="J563" t="s">
         <v>2207</v>
@@ -27654,7 +27654,7 @@
         <v>1514</v>
       </c>
       <c r="I566" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="J566" t="s">
         <v>2210</v>
@@ -27870,7 +27870,7 @@
         <v>1514</v>
       </c>
       <c r="I572" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="J572" t="s">
         <v>2216</v>
@@ -28220,7 +28220,7 @@
         <v>1514</v>
       </c>
       <c r="I582" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="J582" t="s">
         <v>2226</v>
@@ -28401,7 +28401,7 @@
         <v>1514</v>
       </c>
       <c r="I587" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="J587" t="s">
         <v>2229</v>
@@ -28827,7 +28827,7 @@
         <v>1534</v>
       </c>
       <c r="I599" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="J599" t="s">
         <v>2241</v>
@@ -28862,7 +28862,7 @@
         <v>1514</v>
       </c>
       <c r="I600" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="J600" t="s">
         <v>2242</v>
@@ -28967,7 +28967,7 @@
         <v>1514</v>
       </c>
       <c r="I603" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="J603" t="s">
         <v>2244</v>
@@ -29145,7 +29145,7 @@
         <v>1514</v>
       </c>
       <c r="I608" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="J608" t="s">
         <v>2248</v>
@@ -29215,7 +29215,7 @@
         <v>1514</v>
       </c>
       <c r="I610" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="J610" t="s">
         <v>2250</v>
@@ -29250,7 +29250,7 @@
         <v>1514</v>
       </c>
       <c r="I611" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="J611" t="s">
         <v>2251</v>
@@ -29495,7 +29495,7 @@
         <v>1514</v>
       </c>
       <c r="I618" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="J618" t="s">
         <v>2258</v>

--- a/BacklogGATEAutoCompleto.xlsx
+++ b/BacklogGATEAutoCompleto.xlsx
@@ -7842,7 +7842,7 @@
         <v>1302</v>
       </c>
       <c r="E2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="F2" t="s">
         <v>1509</v>
@@ -7877,7 +7877,7 @@
         <v>1303</v>
       </c>
       <c r="E3">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="F3" t="s">
         <v>1509</v>
@@ -7912,7 +7912,7 @@
         <v>1304</v>
       </c>
       <c r="E4">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="F4" t="s">
         <v>1509</v>
@@ -7947,7 +7947,7 @@
         <v>1305</v>
       </c>
       <c r="E5">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="F5" t="s">
         <v>1509</v>
@@ -7982,7 +7982,7 @@
         <v>1306</v>
       </c>
       <c r="E6">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="F6" t="s">
         <v>1509</v>
@@ -8017,7 +8017,7 @@
         <v>1307</v>
       </c>
       <c r="E7">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="F7" t="s">
         <v>1509</v>
@@ -8052,7 +8052,7 @@
         <v>1308</v>
       </c>
       <c r="E8">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="F8" t="s">
         <v>1509</v>
@@ -8087,7 +8087,7 @@
         <v>1308</v>
       </c>
       <c r="E9">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="F9" t="s">
         <v>1509</v>
@@ -8122,7 +8122,7 @@
         <v>1309</v>
       </c>
       <c r="E10">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="F10" t="s">
         <v>1509</v>
@@ -8157,7 +8157,7 @@
         <v>1310</v>
       </c>
       <c r="E11">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="F11" t="s">
         <v>1509</v>
@@ -8192,7 +8192,7 @@
         <v>1311</v>
       </c>
       <c r="E12">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F12" t="s">
         <v>1509</v>
@@ -8227,7 +8227,7 @@
         <v>1311</v>
       </c>
       <c r="E13">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F13" t="s">
         <v>1509</v>
@@ -8262,7 +8262,7 @@
         <v>1312</v>
       </c>
       <c r="E14">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="F14" t="s">
         <v>1509</v>
@@ -8297,7 +8297,7 @@
         <v>1312</v>
       </c>
       <c r="E15">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="F15" t="s">
         <v>1509</v>
@@ -8332,7 +8332,7 @@
         <v>1313</v>
       </c>
       <c r="E16">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="F16" t="s">
         <v>1509</v>
@@ -8367,7 +8367,7 @@
         <v>1314</v>
       </c>
       <c r="E17">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="F17" t="s">
         <v>1509</v>
@@ -8402,7 +8402,7 @@
         <v>1315</v>
       </c>
       <c r="E18">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F18" t="s">
         <v>1509</v>
@@ -8437,7 +8437,7 @@
         <v>1316</v>
       </c>
       <c r="E19">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="F19" t="s">
         <v>1509</v>
@@ -8472,7 +8472,7 @@
         <v>1317</v>
       </c>
       <c r="E20">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F20" t="s">
         <v>1509</v>
@@ -8510,7 +8510,7 @@
         <v>1318</v>
       </c>
       <c r="E21">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="F21" t="s">
         <v>1509</v>
@@ -8545,7 +8545,7 @@
         <v>1319</v>
       </c>
       <c r="E22">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F22" t="s">
         <v>1509</v>
@@ -8580,7 +8580,7 @@
         <v>1320</v>
       </c>
       <c r="E23">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F23" t="s">
         <v>1509</v>
@@ -8615,7 +8615,7 @@
         <v>1321</v>
       </c>
       <c r="E24">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F24" t="s">
         <v>1509</v>
@@ -8650,7 +8650,7 @@
         <v>1322</v>
       </c>
       <c r="E25">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="F25" t="s">
         <v>1509</v>
@@ -8685,7 +8685,7 @@
         <v>1323</v>
       </c>
       <c r="E26">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F26" t="s">
         <v>1509</v>
@@ -8720,7 +8720,7 @@
         <v>1324</v>
       </c>
       <c r="E27">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F27" t="s">
         <v>1509</v>
@@ -8755,7 +8755,7 @@
         <v>1325</v>
       </c>
       <c r="E28">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F28" t="s">
         <v>1509</v>
@@ -8790,7 +8790,7 @@
         <v>1326</v>
       </c>
       <c r="E29">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F29" t="s">
         <v>1509</v>
@@ -8825,7 +8825,7 @@
         <v>1327</v>
       </c>
       <c r="E30">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F30" t="s">
         <v>1509</v>
@@ -8860,7 +8860,7 @@
         <v>1328</v>
       </c>
       <c r="E31">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F31" t="s">
         <v>1509</v>
@@ -8895,7 +8895,7 @@
         <v>1329</v>
       </c>
       <c r="E32">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F32" t="s">
         <v>1509</v>
@@ -8930,7 +8930,7 @@
         <v>1329</v>
       </c>
       <c r="E33">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F33" t="s">
         <v>1509</v>
@@ -8965,7 +8965,7 @@
         <v>1330</v>
       </c>
       <c r="E34">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F34" t="s">
         <v>1509</v>
@@ -9000,7 +9000,7 @@
         <v>1331</v>
       </c>
       <c r="E35">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="F35" t="s">
         <v>1509</v>
@@ -9035,7 +9035,7 @@
         <v>1331</v>
       </c>
       <c r="E36">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="F36" t="s">
         <v>1509</v>
@@ -9070,7 +9070,7 @@
         <v>1332</v>
       </c>
       <c r="E37">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F37" t="s">
         <v>1509</v>
@@ -9105,7 +9105,7 @@
         <v>1332</v>
       </c>
       <c r="E38">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F38" t="s">
         <v>1509</v>
@@ -9140,7 +9140,7 @@
         <v>1333</v>
       </c>
       <c r="E39">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F39" t="s">
         <v>1509</v>
@@ -9175,7 +9175,7 @@
         <v>1334</v>
       </c>
       <c r="E40">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F40" t="s">
         <v>1509</v>
@@ -9210,7 +9210,7 @@
         <v>1335</v>
       </c>
       <c r="E41">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F41" t="s">
         <v>1509</v>
@@ -9245,7 +9245,7 @@
         <v>1336</v>
       </c>
       <c r="E42">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F42" t="s">
         <v>1509</v>
@@ -9280,7 +9280,7 @@
         <v>1337</v>
       </c>
       <c r="E43">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F43" t="s">
         <v>1509</v>
@@ -9315,7 +9315,7 @@
         <v>1338</v>
       </c>
       <c r="E44">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F44" t="s">
         <v>1509</v>
@@ -9350,7 +9350,7 @@
         <v>1339</v>
       </c>
       <c r="E45">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F45" t="s">
         <v>1509</v>
@@ -9385,7 +9385,7 @@
         <v>1340</v>
       </c>
       <c r="E46">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F46" t="s">
         <v>1509</v>
@@ -9420,7 +9420,7 @@
         <v>1341</v>
       </c>
       <c r="E47">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F47" t="s">
         <v>1509</v>
@@ -9455,7 +9455,7 @@
         <v>1342</v>
       </c>
       <c r="E48">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F48" t="s">
         <v>1509</v>
@@ -9490,7 +9490,7 @@
         <v>1343</v>
       </c>
       <c r="E49">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F49" t="s">
         <v>1509</v>
@@ -9525,7 +9525,7 @@
         <v>1343</v>
       </c>
       <c r="E50">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F50" t="s">
         <v>1509</v>
@@ -9560,7 +9560,7 @@
         <v>1343</v>
       </c>
       <c r="E51">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F51" t="s">
         <v>1509</v>
@@ -9595,7 +9595,7 @@
         <v>1344</v>
       </c>
       <c r="E52">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F52" t="s">
         <v>1509</v>
@@ -9630,7 +9630,7 @@
         <v>1345</v>
       </c>
       <c r="E53">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F53" t="s">
         <v>1509</v>
@@ -9665,7 +9665,7 @@
         <v>1346</v>
       </c>
       <c r="E54">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F54" t="s">
         <v>1509</v>
@@ -9700,7 +9700,7 @@
         <v>1347</v>
       </c>
       <c r="E55">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F55" t="s">
         <v>1509</v>
@@ -9735,7 +9735,7 @@
         <v>1347</v>
       </c>
       <c r="E56">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F56" t="s">
         <v>1509</v>
@@ -9770,7 +9770,7 @@
         <v>1348</v>
       </c>
       <c r="E57">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F57" t="s">
         <v>1509</v>
@@ -9805,7 +9805,7 @@
         <v>1349</v>
       </c>
       <c r="E58">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F58" t="s">
         <v>1509</v>
@@ -9840,7 +9840,7 @@
         <v>1349</v>
       </c>
       <c r="E59">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F59" t="s">
         <v>1509</v>
@@ -9875,7 +9875,7 @@
         <v>1349</v>
       </c>
       <c r="E60">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F60" t="s">
         <v>1510</v>
@@ -9910,7 +9910,7 @@
         <v>1349</v>
       </c>
       <c r="E61">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F61" t="s">
         <v>1509</v>
@@ -9945,7 +9945,7 @@
         <v>1350</v>
       </c>
       <c r="E62">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F62" t="s">
         <v>1509</v>
@@ -9980,7 +9980,7 @@
         <v>1351</v>
       </c>
       <c r="E63">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F63" t="s">
         <v>1509</v>
@@ -10015,7 +10015,7 @@
         <v>1351</v>
       </c>
       <c r="E64">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F64" t="s">
         <v>1509</v>
@@ -10050,7 +10050,7 @@
         <v>1352</v>
       </c>
       <c r="E65">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F65" t="s">
         <v>1509</v>
@@ -10085,7 +10085,7 @@
         <v>1353</v>
       </c>
       <c r="E66">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F66" t="s">
         <v>1509</v>
@@ -10120,7 +10120,7 @@
         <v>1354</v>
       </c>
       <c r="E67">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F67" t="s">
         <v>1509</v>
@@ -10155,7 +10155,7 @@
         <v>1354</v>
       </c>
       <c r="E68">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F68" t="s">
         <v>1509</v>
@@ -10190,7 +10190,7 @@
         <v>1354</v>
       </c>
       <c r="E69">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F69" t="s">
         <v>1509</v>
@@ -10225,7 +10225,7 @@
         <v>1354</v>
       </c>
       <c r="E70">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F70" t="s">
         <v>1509</v>
@@ -10260,7 +10260,7 @@
         <v>1354</v>
       </c>
       <c r="E71">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F71" t="s">
         <v>1509</v>
@@ -10295,7 +10295,7 @@
         <v>1354</v>
       </c>
       <c r="E72">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F72" t="s">
         <v>1509</v>
@@ -10330,7 +10330,7 @@
         <v>1355</v>
       </c>
       <c r="E73">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F73" t="s">
         <v>1509</v>
@@ -10365,7 +10365,7 @@
         <v>1356</v>
       </c>
       <c r="E74">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F74" t="s">
         <v>1509</v>
@@ -10400,7 +10400,7 @@
         <v>1356</v>
       </c>
       <c r="E75">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F75" t="s">
         <v>1509</v>
@@ -10435,7 +10435,7 @@
         <v>1357</v>
       </c>
       <c r="E76">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F76" t="s">
         <v>1511</v>
@@ -10470,7 +10470,7 @@
         <v>1358</v>
       </c>
       <c r="E77">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F77" t="s">
         <v>1509</v>
@@ -10505,7 +10505,7 @@
         <v>1359</v>
       </c>
       <c r="E78">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F78" t="s">
         <v>1509</v>
@@ -10540,7 +10540,7 @@
         <v>1360</v>
       </c>
       <c r="E79">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F79" t="s">
         <v>1509</v>
@@ -10575,7 +10575,7 @@
         <v>1361</v>
       </c>
       <c r="E80">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F80" t="s">
         <v>1509</v>
@@ -10610,7 +10610,7 @@
         <v>1362</v>
       </c>
       <c r="E81">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F81" t="s">
         <v>1509</v>
@@ -10645,7 +10645,7 @@
         <v>1363</v>
       </c>
       <c r="E82">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F82" t="s">
         <v>1509</v>
@@ -10680,7 +10680,7 @@
         <v>1364</v>
       </c>
       <c r="E83">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F83" t="s">
         <v>1509</v>
@@ -10715,7 +10715,7 @@
         <v>1364</v>
       </c>
       <c r="E84">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F84" t="s">
         <v>1509</v>
@@ -10750,7 +10750,7 @@
         <v>1365</v>
       </c>
       <c r="E85">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F85" t="s">
         <v>1509</v>
@@ -10785,7 +10785,7 @@
         <v>1365</v>
       </c>
       <c r="E86">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F86" t="s">
         <v>1509</v>
@@ -10820,7 +10820,7 @@
         <v>1365</v>
       </c>
       <c r="E87">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F87" t="s">
         <v>1509</v>
@@ -10855,7 +10855,7 @@
         <v>1366</v>
       </c>
       <c r="E88">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F88" t="s">
         <v>1509</v>
@@ -10890,7 +10890,7 @@
         <v>1366</v>
       </c>
       <c r="E89">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F89" t="s">
         <v>1509</v>
@@ -10925,7 +10925,7 @@
         <v>1367</v>
       </c>
       <c r="E90">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F90" t="s">
         <v>1509</v>
@@ -10960,7 +10960,7 @@
         <v>1368</v>
       </c>
       <c r="E91">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F91" t="s">
         <v>1509</v>
@@ -10995,7 +10995,7 @@
         <v>1369</v>
       </c>
       <c r="E92">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F92" t="s">
         <v>1509</v>
@@ -11030,7 +11030,7 @@
         <v>1369</v>
       </c>
       <c r="E93">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F93" t="s">
         <v>1509</v>
@@ -11065,7 +11065,7 @@
         <v>1370</v>
       </c>
       <c r="E94">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F94" t="s">
         <v>1509</v>
@@ -11100,7 +11100,7 @@
         <v>1370</v>
       </c>
       <c r="E95">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F95" t="s">
         <v>1509</v>
@@ -11135,7 +11135,7 @@
         <v>1371</v>
       </c>
       <c r="E96">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F96" t="s">
         <v>1509</v>
@@ -11170,7 +11170,7 @@
         <v>1372</v>
       </c>
       <c r="E97">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F97" t="s">
         <v>1509</v>
@@ -11205,7 +11205,7 @@
         <v>1372</v>
       </c>
       <c r="E98">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F98" t="s">
         <v>1509</v>
@@ -11240,7 +11240,7 @@
         <v>1373</v>
       </c>
       <c r="E99">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F99" t="s">
         <v>1509</v>
@@ -11275,7 +11275,7 @@
         <v>1374</v>
       </c>
       <c r="E100">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F100" t="s">
         <v>1509</v>
@@ -11310,7 +11310,7 @@
         <v>1374</v>
       </c>
       <c r="E101">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F101" t="s">
         <v>1509</v>
@@ -11345,7 +11345,7 @@
         <v>1375</v>
       </c>
       <c r="E102">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F102" t="s">
         <v>1509</v>
@@ -11380,7 +11380,7 @@
         <v>1376</v>
       </c>
       <c r="E103">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F103" t="s">
         <v>1509</v>
@@ -11418,7 +11418,7 @@
         <v>1376</v>
       </c>
       <c r="E104">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F104" t="s">
         <v>1509</v>
@@ -11453,7 +11453,7 @@
         <v>1376</v>
       </c>
       <c r="E105">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F105" t="s">
         <v>1509</v>
@@ -11488,7 +11488,7 @@
         <v>1376</v>
       </c>
       <c r="E106">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F106" t="s">
         <v>1509</v>
@@ -11523,7 +11523,7 @@
         <v>1377</v>
       </c>
       <c r="E107">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F107" t="s">
         <v>1510</v>
@@ -11558,7 +11558,7 @@
         <v>1378</v>
       </c>
       <c r="E108">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F108" t="s">
         <v>1509</v>
@@ -11593,7 +11593,7 @@
         <v>1378</v>
       </c>
       <c r="E109">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F109" t="s">
         <v>1509</v>
@@ -11628,7 +11628,7 @@
         <v>1378</v>
       </c>
       <c r="E110">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F110" t="s">
         <v>1509</v>
@@ -11663,7 +11663,7 @@
         <v>1379</v>
       </c>
       <c r="E111">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F111" t="s">
         <v>1509</v>
@@ -11698,7 +11698,7 @@
         <v>1379</v>
       </c>
       <c r="E112">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F112" t="s">
         <v>1509</v>
@@ -11733,7 +11733,7 @@
         <v>1379</v>
       </c>
       <c r="E113">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F113" t="s">
         <v>1509</v>
@@ -11768,7 +11768,7 @@
         <v>1379</v>
       </c>
       <c r="E114">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F114" t="s">
         <v>1509</v>
@@ -11803,7 +11803,7 @@
         <v>1379</v>
       </c>
       <c r="E115">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F115" t="s">
         <v>1509</v>
@@ -11838,7 +11838,7 @@
         <v>1379</v>
       </c>
       <c r="E116">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F116" t="s">
         <v>1509</v>
@@ -11873,7 +11873,7 @@
         <v>1379</v>
       </c>
       <c r="E117">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F117" t="s">
         <v>1509</v>
@@ -11908,7 +11908,7 @@
         <v>1380</v>
       </c>
       <c r="E118">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F118" t="s">
         <v>1509</v>
@@ -11943,7 +11943,7 @@
         <v>1381</v>
       </c>
       <c r="E119">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F119" t="s">
         <v>1509</v>
@@ -11978,7 +11978,7 @@
         <v>1382</v>
       </c>
       <c r="E120">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F120" t="s">
         <v>1509</v>
@@ -12013,7 +12013,7 @@
         <v>1382</v>
       </c>
       <c r="E121">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F121" t="s">
         <v>1509</v>
@@ -12048,7 +12048,7 @@
         <v>1382</v>
       </c>
       <c r="E122">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F122" t="s">
         <v>1509</v>
@@ -12083,7 +12083,7 @@
         <v>1383</v>
       </c>
       <c r="E123">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F123" t="s">
         <v>1509</v>
@@ -12118,7 +12118,7 @@
         <v>1383</v>
       </c>
       <c r="E124">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F124" t="s">
         <v>1509</v>
@@ -12153,7 +12153,7 @@
         <v>1383</v>
       </c>
       <c r="E125">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F125" t="s">
         <v>1509</v>
@@ -12188,7 +12188,7 @@
         <v>1383</v>
       </c>
       <c r="E126">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F126" t="s">
         <v>1509</v>
@@ -12223,7 +12223,7 @@
         <v>1383</v>
       </c>
       <c r="E127">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F127" t="s">
         <v>1509</v>
@@ -12258,7 +12258,7 @@
         <v>1383</v>
       </c>
       <c r="E128">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F128" t="s">
         <v>1509</v>
@@ -12293,7 +12293,7 @@
         <v>1383</v>
       </c>
       <c r="E129">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F129" t="s">
         <v>1509</v>
@@ -12328,7 +12328,7 @@
         <v>1383</v>
       </c>
       <c r="E130">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F130" t="s">
         <v>1509</v>
@@ -12363,7 +12363,7 @@
         <v>1383</v>
       </c>
       <c r="E131">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F131" t="s">
         <v>1509</v>
@@ -12398,7 +12398,7 @@
         <v>1384</v>
       </c>
       <c r="E132">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F132" t="s">
         <v>1509</v>
@@ -12433,7 +12433,7 @@
         <v>1384</v>
       </c>
       <c r="E133">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F133" t="s">
         <v>1509</v>
@@ -12468,7 +12468,7 @@
         <v>1384</v>
       </c>
       <c r="E134">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F134" t="s">
         <v>1509</v>
@@ -12503,7 +12503,7 @@
         <v>1385</v>
       </c>
       <c r="E135">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F135" t="s">
         <v>1509</v>
@@ -12538,7 +12538,7 @@
         <v>1385</v>
       </c>
       <c r="E136">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F136" t="s">
         <v>1510</v>
@@ -12573,7 +12573,7 @@
         <v>1385</v>
       </c>
       <c r="E137">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F137" t="s">
         <v>1509</v>
@@ -12608,7 +12608,7 @@
         <v>1386</v>
       </c>
       <c r="E138">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F138" t="s">
         <v>1509</v>
@@ -12643,7 +12643,7 @@
         <v>1386</v>
       </c>
       <c r="E139">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F139" t="s">
         <v>1509</v>
@@ -12678,7 +12678,7 @@
         <v>1387</v>
       </c>
       <c r="E140">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F140" t="s">
         <v>1509</v>
@@ -12713,7 +12713,7 @@
         <v>1387</v>
       </c>
       <c r="E141">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F141" t="s">
         <v>1509</v>
@@ -12748,7 +12748,7 @@
         <v>1388</v>
       </c>
       <c r="E142">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F142" t="s">
         <v>1509</v>
@@ -12783,7 +12783,7 @@
         <v>1388</v>
       </c>
       <c r="E143">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F143" t="s">
         <v>1509</v>
@@ -12818,7 +12818,7 @@
         <v>1389</v>
       </c>
       <c r="E144">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F144" t="s">
         <v>1509</v>
@@ -12853,7 +12853,7 @@
         <v>1389</v>
       </c>
       <c r="E145">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F145" t="s">
         <v>1509</v>
@@ -12888,7 +12888,7 @@
         <v>1390</v>
       </c>
       <c r="E146">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F146" t="s">
         <v>1509</v>
@@ -12923,7 +12923,7 @@
         <v>1390</v>
       </c>
       <c r="E147">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F147" t="s">
         <v>1509</v>
@@ -12958,7 +12958,7 @@
         <v>1391</v>
       </c>
       <c r="E148">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F148" t="s">
         <v>1509</v>
@@ -12993,7 +12993,7 @@
         <v>1392</v>
       </c>
       <c r="E149">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F149" t="s">
         <v>1509</v>
@@ -13028,7 +13028,7 @@
         <v>1392</v>
       </c>
       <c r="E150">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F150" t="s">
         <v>1509</v>
@@ -13063,7 +13063,7 @@
         <v>1392</v>
       </c>
       <c r="E151">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F151" t="s">
         <v>1509</v>
@@ -13098,7 +13098,7 @@
         <v>1392</v>
       </c>
       <c r="E152">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F152" t="s">
         <v>1509</v>
@@ -13133,7 +13133,7 @@
         <v>1393</v>
       </c>
       <c r="E153">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F153" t="s">
         <v>1509</v>
@@ -13168,7 +13168,7 @@
         <v>1394</v>
       </c>
       <c r="E154">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F154" t="s">
         <v>1509</v>
@@ -13203,7 +13203,7 @@
         <v>1394</v>
       </c>
       <c r="E155">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F155" t="s">
         <v>1509</v>
@@ -13238,7 +13238,7 @@
         <v>1394</v>
       </c>
       <c r="E156">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F156" t="s">
         <v>1509</v>
@@ -13273,7 +13273,7 @@
         <v>1394</v>
       </c>
       <c r="E157">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F157" t="s">
         <v>1509</v>
@@ -13308,7 +13308,7 @@
         <v>1394</v>
       </c>
       <c r="E158">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F158" t="s">
         <v>1509</v>
@@ -13343,7 +13343,7 @@
         <v>1395</v>
       </c>
       <c r="E159">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F159" t="s">
         <v>1509</v>
@@ -13378,7 +13378,7 @@
         <v>1395</v>
       </c>
       <c r="E160">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F160" t="s">
         <v>1509</v>
@@ -13413,7 +13413,7 @@
         <v>1395</v>
       </c>
       <c r="E161">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F161" t="s">
         <v>1509</v>
@@ -13448,7 +13448,7 @@
         <v>1395</v>
       </c>
       <c r="E162">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F162" t="s">
         <v>1509</v>
@@ -13483,7 +13483,7 @@
         <v>1395</v>
       </c>
       <c r="E163">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F163" t="s">
         <v>1509</v>
@@ -13518,7 +13518,7 @@
         <v>1395</v>
       </c>
       <c r="E164">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F164" t="s">
         <v>1509</v>
@@ -13553,7 +13553,7 @@
         <v>1396</v>
       </c>
       <c r="E165">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F165" t="s">
         <v>1509</v>
@@ -13588,7 +13588,7 @@
         <v>1396</v>
       </c>
       <c r="E166">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F166" t="s">
         <v>1509</v>
@@ -13623,7 +13623,7 @@
         <v>1396</v>
       </c>
       <c r="E167">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F167" t="s">
         <v>1509</v>
@@ -13658,7 +13658,7 @@
         <v>1397</v>
       </c>
       <c r="E168">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F168" t="s">
         <v>1509</v>
@@ -13693,7 +13693,7 @@
         <v>1397</v>
       </c>
       <c r="E169">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F169" t="s">
         <v>1509</v>
@@ -13728,7 +13728,7 @@
         <v>1398</v>
       </c>
       <c r="E170">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F170" t="s">
         <v>1509</v>
@@ -13763,7 +13763,7 @@
         <v>1399</v>
       </c>
       <c r="E171">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F171" t="s">
         <v>1509</v>
@@ -13798,7 +13798,7 @@
         <v>1399</v>
       </c>
       <c r="E172">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F172" t="s">
         <v>1509</v>
@@ -13833,7 +13833,7 @@
         <v>1400</v>
       </c>
       <c r="E173">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F173" t="s">
         <v>1509</v>
@@ -13868,7 +13868,7 @@
         <v>1401</v>
       </c>
       <c r="E174">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F174" t="s">
         <v>1509</v>
@@ -13903,7 +13903,7 @@
         <v>1401</v>
       </c>
       <c r="E175">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F175" t="s">
         <v>1509</v>
@@ -13938,7 +13938,7 @@
         <v>1402</v>
       </c>
       <c r="E176">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F176" t="s">
         <v>1509</v>
@@ -13973,7 +13973,7 @@
         <v>1402</v>
       </c>
       <c r="E177">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F177" t="s">
         <v>1509</v>
@@ -14008,7 +14008,7 @@
         <v>1403</v>
       </c>
       <c r="E178">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F178" t="s">
         <v>1509</v>
@@ -14043,7 +14043,7 @@
         <v>1403</v>
       </c>
       <c r="E179">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F179" t="s">
         <v>1509</v>
@@ -14078,7 +14078,7 @@
         <v>1403</v>
       </c>
       <c r="E180">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F180" t="s">
         <v>1509</v>
@@ -14113,7 +14113,7 @@
         <v>1404</v>
       </c>
       <c r="E181">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F181" t="s">
         <v>1509</v>
@@ -14148,7 +14148,7 @@
         <v>1404</v>
       </c>
       <c r="E182">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F182" t="s">
         <v>1509</v>
@@ -14183,7 +14183,7 @@
         <v>1405</v>
       </c>
       <c r="E183">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F183" t="s">
         <v>1509</v>
@@ -14218,7 +14218,7 @@
         <v>1406</v>
       </c>
       <c r="E184">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F184" t="s">
         <v>1509</v>
@@ -14253,7 +14253,7 @@
         <v>1406</v>
       </c>
       <c r="E185">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F185" t="s">
         <v>1509</v>
@@ -14288,7 +14288,7 @@
         <v>1406</v>
       </c>
       <c r="E186">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F186" t="s">
         <v>1509</v>
@@ -14323,7 +14323,7 @@
         <v>1407</v>
       </c>
       <c r="E187">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F187" t="s">
         <v>1509</v>
@@ -14358,7 +14358,7 @@
         <v>1407</v>
       </c>
       <c r="E188">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F188" t="s">
         <v>1509</v>
@@ -14393,7 +14393,7 @@
         <v>1408</v>
       </c>
       <c r="E189">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F189" t="s">
         <v>1509</v>
@@ -14428,7 +14428,7 @@
         <v>1408</v>
       </c>
       <c r="E190">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F190" t="s">
         <v>1511</v>
@@ -14463,7 +14463,7 @@
         <v>1408</v>
       </c>
       <c r="E191">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F191" t="s">
         <v>1509</v>
@@ -14498,7 +14498,7 @@
         <v>1409</v>
       </c>
       <c r="E192">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F192" t="s">
         <v>1509</v>
@@ -14533,7 +14533,7 @@
         <v>1409</v>
       </c>
       <c r="E193">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F193" t="s">
         <v>1509</v>
@@ -14571,7 +14571,7 @@
         <v>1409</v>
       </c>
       <c r="E194">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F194" t="s">
         <v>1509</v>
@@ -14606,7 +14606,7 @@
         <v>1409</v>
       </c>
       <c r="E195">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F195" t="s">
         <v>1509</v>
@@ -14641,7 +14641,7 @@
         <v>1409</v>
       </c>
       <c r="E196">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F196" t="s">
         <v>1509</v>
@@ -14676,7 +14676,7 @@
         <v>1409</v>
       </c>
       <c r="E197">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F197" t="s">
         <v>1509</v>
@@ -14711,7 +14711,7 @@
         <v>1410</v>
       </c>
       <c r="E198">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F198" t="s">
         <v>1509</v>
@@ -14746,7 +14746,7 @@
         <v>1410</v>
       </c>
       <c r="E199">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F199" t="s">
         <v>1509</v>
@@ -14781,7 +14781,7 @@
         <v>1410</v>
       </c>
       <c r="E200">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F200" t="s">
         <v>1509</v>
@@ -14816,7 +14816,7 @@
         <v>1411</v>
       </c>
       <c r="E201">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F201" t="s">
         <v>1509</v>
@@ -14851,7 +14851,7 @@
         <v>1411</v>
       </c>
       <c r="E202">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F202" t="s">
         <v>1509</v>
@@ -14886,7 +14886,7 @@
         <v>1411</v>
       </c>
       <c r="E203">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F203" t="s">
         <v>1509</v>
@@ -14921,7 +14921,7 @@
         <v>1412</v>
       </c>
       <c r="E204">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F204" t="s">
         <v>1509</v>
@@ -14956,7 +14956,7 @@
         <v>1412</v>
       </c>
       <c r="E205">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F205" t="s">
         <v>1509</v>
@@ -14991,7 +14991,7 @@
         <v>1412</v>
       </c>
       <c r="E206">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F206" t="s">
         <v>1509</v>
@@ -15026,7 +15026,7 @@
         <v>1413</v>
       </c>
       <c r="E207">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F207" t="s">
         <v>1509</v>
@@ -15061,7 +15061,7 @@
         <v>1413</v>
       </c>
       <c r="E208">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F208" t="s">
         <v>1509</v>
@@ -15096,7 +15096,7 @@
         <v>1413</v>
       </c>
       <c r="E209">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F209" t="s">
         <v>1509</v>
@@ -15131,7 +15131,7 @@
         <v>1413</v>
       </c>
       <c r="E210">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F210" t="s">
         <v>1509</v>
@@ -15166,7 +15166,7 @@
         <v>1413</v>
       </c>
       <c r="E211">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F211" t="s">
         <v>1509</v>
@@ -15201,7 +15201,7 @@
         <v>1414</v>
       </c>
       <c r="E212">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F212" t="s">
         <v>1509</v>
@@ -15236,7 +15236,7 @@
         <v>1414</v>
       </c>
       <c r="E213">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F213" t="s">
         <v>1512</v>
@@ -15271,7 +15271,7 @@
         <v>1414</v>
       </c>
       <c r="E214">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F214" t="s">
         <v>1509</v>
@@ -15306,7 +15306,7 @@
         <v>1414</v>
       </c>
       <c r="E215">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F215" t="s">
         <v>1509</v>
@@ -15341,7 +15341,7 @@
         <v>1414</v>
       </c>
       <c r="E216">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F216" t="s">
         <v>1509</v>
@@ -15376,7 +15376,7 @@
         <v>1415</v>
       </c>
       <c r="E217">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F217" t="s">
         <v>1509</v>
@@ -15411,7 +15411,7 @@
         <v>1415</v>
       </c>
       <c r="E218">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F218" t="s">
         <v>1509</v>
@@ -15446,7 +15446,7 @@
         <v>1415</v>
       </c>
       <c r="E219">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F219" t="s">
         <v>1509</v>
@@ -15481,7 +15481,7 @@
         <v>1415</v>
       </c>
       <c r="E220">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F220" t="s">
         <v>1509</v>
@@ -15516,7 +15516,7 @@
         <v>1416</v>
       </c>
       <c r="E221">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F221" t="s">
         <v>1509</v>
@@ -15551,7 +15551,7 @@
         <v>1417</v>
       </c>
       <c r="E222">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F222" t="s">
         <v>1509</v>
@@ -15589,7 +15589,7 @@
         <v>1418</v>
       </c>
       <c r="E223">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F223" t="s">
         <v>1509</v>
@@ -15624,7 +15624,7 @@
         <v>1418</v>
       </c>
       <c r="E224">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F224" t="s">
         <v>1509</v>
@@ -15659,7 +15659,7 @@
         <v>1418</v>
       </c>
       <c r="E225">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F225" t="s">
         <v>1509</v>
@@ -15694,7 +15694,7 @@
         <v>1419</v>
       </c>
       <c r="E226">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F226" t="s">
         <v>1509</v>
@@ -15729,7 +15729,7 @@
         <v>1419</v>
       </c>
       <c r="E227">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F227" t="s">
         <v>1509</v>
@@ -15764,7 +15764,7 @@
         <v>1420</v>
       </c>
       <c r="E228">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F228" t="s">
         <v>1509</v>
@@ -15799,7 +15799,7 @@
         <v>1420</v>
       </c>
       <c r="E229">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F229" t="s">
         <v>1509</v>
@@ -15834,7 +15834,7 @@
         <v>1421</v>
       </c>
       <c r="E230">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F230" t="s">
         <v>1509</v>
@@ -15869,7 +15869,7 @@
         <v>1421</v>
       </c>
       <c r="E231">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F231" t="s">
         <v>1509</v>
@@ -15904,7 +15904,7 @@
         <v>1421</v>
       </c>
       <c r="E232">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F232" t="s">
         <v>1509</v>
@@ -15939,7 +15939,7 @@
         <v>1422</v>
       </c>
       <c r="E233">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F233" t="s">
         <v>1509</v>
@@ -15974,7 +15974,7 @@
         <v>1422</v>
       </c>
       <c r="E234">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F234" t="s">
         <v>1509</v>
@@ -16009,7 +16009,7 @@
         <v>1422</v>
       </c>
       <c r="E235">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F235" t="s">
         <v>1509</v>
@@ -16044,7 +16044,7 @@
         <v>1423</v>
       </c>
       <c r="E236">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F236" t="s">
         <v>1509</v>
@@ -16079,7 +16079,7 @@
         <v>1424</v>
       </c>
       <c r="E237">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F237" t="s">
         <v>1509</v>
@@ -16114,7 +16114,7 @@
         <v>1424</v>
       </c>
       <c r="E238">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F238" t="s">
         <v>1509</v>
@@ -16149,7 +16149,7 @@
         <v>1424</v>
       </c>
       <c r="E239">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F239" t="s">
         <v>1509</v>
@@ -16184,7 +16184,7 @@
         <v>1424</v>
       </c>
       <c r="E240">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F240" t="s">
         <v>1509</v>
@@ -16219,7 +16219,7 @@
         <v>1425</v>
       </c>
       <c r="E241">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F241" t="s">
         <v>1509</v>
@@ -16254,7 +16254,7 @@
         <v>1425</v>
       </c>
       <c r="E242">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F242" t="s">
         <v>1509</v>
@@ -16289,7 +16289,7 @@
         <v>1425</v>
       </c>
       <c r="E243">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F243" t="s">
         <v>1509</v>
@@ -16324,7 +16324,7 @@
         <v>1426</v>
       </c>
       <c r="E244">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F244" t="s">
         <v>1509</v>
@@ -16359,7 +16359,7 @@
         <v>1426</v>
       </c>
       <c r="E245">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F245" t="s">
         <v>1509</v>
@@ -16394,7 +16394,7 @@
         <v>1427</v>
       </c>
       <c r="E246">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F246" t="s">
         <v>1509</v>
@@ -16429,7 +16429,7 @@
         <v>1427</v>
       </c>
       <c r="E247">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F247" t="s">
         <v>1509</v>
@@ -16464,7 +16464,7 @@
         <v>1427</v>
       </c>
       <c r="E248">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F248" t="s">
         <v>1509</v>
@@ -16499,7 +16499,7 @@
         <v>1427</v>
       </c>
       <c r="E249">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F249" t="s">
         <v>1509</v>
@@ -16534,7 +16534,7 @@
         <v>1428</v>
       </c>
       <c r="E250">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F250" t="s">
         <v>1509</v>
@@ -16569,7 +16569,7 @@
         <v>1428</v>
       </c>
       <c r="E251">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F251" t="s">
         <v>1509</v>
@@ -16604,7 +16604,7 @@
         <v>1428</v>
       </c>
       <c r="E252">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F252" t="s">
         <v>1509</v>
@@ -16639,7 +16639,7 @@
         <v>1429</v>
       </c>
       <c r="E253">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F253" t="s">
         <v>1509</v>
@@ -16674,7 +16674,7 @@
         <v>1430</v>
       </c>
       <c r="E254">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F254" t="s">
         <v>1509</v>
@@ -16709,7 +16709,7 @@
         <v>1431</v>
       </c>
       <c r="E255">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F255" t="s">
         <v>1509</v>
@@ -16744,7 +16744,7 @@
         <v>1431</v>
       </c>
       <c r="E256">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F256" t="s">
         <v>1509</v>
@@ -16779,7 +16779,7 @@
         <v>1431</v>
       </c>
       <c r="E257">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F257" t="s">
         <v>1509</v>
@@ -16814,7 +16814,7 @@
         <v>1431</v>
       </c>
       <c r="E258">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F258" t="s">
         <v>1509</v>
@@ -16849,7 +16849,7 @@
         <v>1431</v>
       </c>
       <c r="E259">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F259" t="s">
         <v>1509</v>
@@ -16884,7 +16884,7 @@
         <v>1432</v>
       </c>
       <c r="E260">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F260" t="s">
         <v>1509</v>
@@ -16919,7 +16919,7 @@
         <v>1432</v>
       </c>
       <c r="E261">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F261" t="s">
         <v>1509</v>
@@ -16954,7 +16954,7 @@
         <v>1433</v>
       </c>
       <c r="E262">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F262" t="s">
         <v>1509</v>
@@ -16989,7 +16989,7 @@
         <v>1433</v>
       </c>
       <c r="E263">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F263" t="s">
         <v>1509</v>
@@ -17024,7 +17024,7 @@
         <v>1434</v>
       </c>
       <c r="E264">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F264" t="s">
         <v>1509</v>
@@ -17059,7 +17059,7 @@
         <v>1435</v>
       </c>
       <c r="E265">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F265" t="s">
         <v>1509</v>
@@ -17094,7 +17094,7 @@
         <v>1436</v>
       </c>
       <c r="E266">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F266" t="s">
         <v>1509</v>
@@ -17129,7 +17129,7 @@
         <v>1436</v>
       </c>
       <c r="E267">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F267" t="s">
         <v>1509</v>
@@ -17164,7 +17164,7 @@
         <v>1437</v>
       </c>
       <c r="E268">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F268" t="s">
         <v>1509</v>
@@ -17199,7 +17199,7 @@
         <v>1437</v>
       </c>
       <c r="E269">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F269" t="s">
         <v>1509</v>
@@ -17234,7 +17234,7 @@
         <v>1437</v>
       </c>
       <c r="E270">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F270" t="s">
         <v>1509</v>
@@ -17269,7 +17269,7 @@
         <v>1438</v>
       </c>
       <c r="E271">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F271" t="s">
         <v>1509</v>
@@ -17304,7 +17304,7 @@
         <v>1438</v>
       </c>
       <c r="E272">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F272" t="s">
         <v>1509</v>
@@ -17339,7 +17339,7 @@
         <v>1438</v>
       </c>
       <c r="E273">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F273" t="s">
         <v>1509</v>
@@ -17374,7 +17374,7 @@
         <v>1438</v>
       </c>
       <c r="E274">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F274" t="s">
         <v>1509</v>
@@ -17409,7 +17409,7 @@
         <v>1438</v>
       </c>
       <c r="E275">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F275" t="s">
         <v>1509</v>
@@ -17444,7 +17444,7 @@
         <v>1438</v>
       </c>
       <c r="E276">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F276" t="s">
         <v>1509</v>
@@ -17479,7 +17479,7 @@
         <v>1438</v>
       </c>
       <c r="E277">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F277" t="s">
         <v>1509</v>
@@ -17514,7 +17514,7 @@
         <v>1438</v>
       </c>
       <c r="E278">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F278" t="s">
         <v>1509</v>
@@ -17549,7 +17549,7 @@
         <v>1438</v>
       </c>
       <c r="E279">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F279" t="s">
         <v>1509</v>
@@ -17584,7 +17584,7 @@
         <v>1439</v>
       </c>
       <c r="E280">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F280" t="s">
         <v>1509</v>
@@ -17619,7 +17619,7 @@
         <v>1439</v>
       </c>
       <c r="E281">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F281" t="s">
         <v>1509</v>
@@ -17654,7 +17654,7 @@
         <v>1439</v>
       </c>
       <c r="E282">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F282" t="s">
         <v>1509</v>
@@ -17689,7 +17689,7 @@
         <v>1440</v>
       </c>
       <c r="E283">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F283" t="s">
         <v>1509</v>
@@ -17724,7 +17724,7 @@
         <v>1440</v>
       </c>
       <c r="E284">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F284" t="s">
         <v>1509</v>
@@ -17759,7 +17759,7 @@
         <v>1440</v>
       </c>
       <c r="E285">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F285" t="s">
         <v>1509</v>
@@ -17794,7 +17794,7 @@
         <v>1440</v>
       </c>
       <c r="E286">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F286" t="s">
         <v>1509</v>
@@ -17829,7 +17829,7 @@
         <v>1440</v>
       </c>
       <c r="E287">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F287" t="s">
         <v>1509</v>
@@ -17864,7 +17864,7 @@
         <v>1440</v>
       </c>
       <c r="E288">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F288" t="s">
         <v>1509</v>
@@ -17899,7 +17899,7 @@
         <v>1441</v>
       </c>
       <c r="E289">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F289" t="s">
         <v>1509</v>
@@ -17934,7 +17934,7 @@
         <v>1441</v>
       </c>
       <c r="E290">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F290" t="s">
         <v>1509</v>
@@ -17969,7 +17969,7 @@
         <v>1441</v>
       </c>
       <c r="E291">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F291" t="s">
         <v>1509</v>
@@ -18004,7 +18004,7 @@
         <v>1441</v>
       </c>
       <c r="E292">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F292" t="s">
         <v>1509</v>
@@ -18042,7 +18042,7 @@
         <v>1441</v>
       </c>
       <c r="E293">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F293" t="s">
         <v>1509</v>
@@ -18077,7 +18077,7 @@
         <v>1441</v>
       </c>
       <c r="E294">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F294" t="s">
         <v>1509</v>
@@ -18112,7 +18112,7 @@
         <v>1441</v>
       </c>
       <c r="E295">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F295" t="s">
         <v>1509</v>
@@ -18147,7 +18147,7 @@
         <v>1441</v>
       </c>
       <c r="E296">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F296" t="s">
         <v>1509</v>
@@ -18182,7 +18182,7 @@
         <v>1441</v>
       </c>
       <c r="E297">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F297" t="s">
         <v>1509</v>
@@ -18217,7 +18217,7 @@
         <v>1442</v>
       </c>
       <c r="E298">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F298" t="s">
         <v>1510</v>
@@ -18252,7 +18252,7 @@
         <v>1443</v>
       </c>
       <c r="E299">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F299" t="s">
         <v>1513</v>
@@ -18287,7 +18287,7 @@
         <v>1444</v>
       </c>
       <c r="E300">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F300" t="s">
         <v>1509</v>
@@ -18322,7 +18322,7 @@
         <v>1445</v>
       </c>
       <c r="E301">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F301" t="s">
         <v>1509</v>
@@ -18357,7 +18357,7 @@
         <v>1445</v>
       </c>
       <c r="E302">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F302" t="s">
         <v>1509</v>
@@ -18392,7 +18392,7 @@
         <v>1446</v>
       </c>
       <c r="E303">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F303" t="s">
         <v>1509</v>
@@ -18427,7 +18427,7 @@
         <v>1447</v>
       </c>
       <c r="E304">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F304" t="s">
         <v>1512</v>
@@ -18462,7 +18462,7 @@
         <v>1447</v>
       </c>
       <c r="E305">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F305" t="s">
         <v>1509</v>
@@ -18497,7 +18497,7 @@
         <v>1447</v>
       </c>
       <c r="E306">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F306" t="s">
         <v>1509</v>
@@ -18532,7 +18532,7 @@
         <v>1447</v>
       </c>
       <c r="E307">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F307" t="s">
         <v>1509</v>
@@ -18567,7 +18567,7 @@
         <v>1447</v>
       </c>
       <c r="E308">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F308" t="s">
         <v>1509</v>
@@ -18602,7 +18602,7 @@
         <v>1447</v>
       </c>
       <c r="E309">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F309" t="s">
         <v>1509</v>
@@ -18637,7 +18637,7 @@
         <v>1448</v>
       </c>
       <c r="E310">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F310" t="s">
         <v>1509</v>
@@ -18672,7 +18672,7 @@
         <v>1449</v>
       </c>
       <c r="E311">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F311" t="s">
         <v>1509</v>
@@ -18707,7 +18707,7 @@
         <v>1449</v>
       </c>
       <c r="E312">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F312" t="s">
         <v>1509</v>
@@ -18742,7 +18742,7 @@
         <v>1449</v>
       </c>
       <c r="E313">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F313" t="s">
         <v>1509</v>
@@ -18780,7 +18780,7 @@
         <v>1449</v>
       </c>
       <c r="E314">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F314" t="s">
         <v>1509</v>
@@ -18815,7 +18815,7 @@
         <v>1450</v>
       </c>
       <c r="E315">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F315" t="s">
         <v>1509</v>
@@ -18850,7 +18850,7 @@
         <v>1450</v>
       </c>
       <c r="E316">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F316" t="s">
         <v>1509</v>
@@ -18885,7 +18885,7 @@
         <v>1450</v>
       </c>
       <c r="E317">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F317" t="s">
         <v>1509</v>
@@ -18920,7 +18920,7 @@
         <v>1450</v>
       </c>
       <c r="E318">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F318" t="s">
         <v>1509</v>
@@ -18955,7 +18955,7 @@
         <v>1450</v>
       </c>
       <c r="E319">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F319" t="s">
         <v>1509</v>
@@ -18990,7 +18990,7 @@
         <v>1451</v>
       </c>
       <c r="E320">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F320" t="s">
         <v>1509</v>
@@ -19025,7 +19025,7 @@
         <v>1451</v>
       </c>
       <c r="E321">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F321" t="s">
         <v>1509</v>
@@ -19060,7 +19060,7 @@
         <v>1452</v>
       </c>
       <c r="E322">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F322" t="s">
         <v>1509</v>
@@ -19095,7 +19095,7 @@
         <v>1452</v>
       </c>
       <c r="E323">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F323" t="s">
         <v>1509</v>
@@ -19130,7 +19130,7 @@
         <v>1452</v>
       </c>
       <c r="E324">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F324" t="s">
         <v>1509</v>
@@ -19165,7 +19165,7 @@
         <v>1452</v>
       </c>
       <c r="E325">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F325" t="s">
         <v>1509</v>
@@ -19200,7 +19200,7 @@
         <v>1452</v>
       </c>
       <c r="E326">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F326" t="s">
         <v>1509</v>
@@ -19235,7 +19235,7 @@
         <v>1452</v>
       </c>
       <c r="E327">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F327" t="s">
         <v>1509</v>
@@ -19270,7 +19270,7 @@
         <v>1452</v>
       </c>
       <c r="E328">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F328" t="s">
         <v>1509</v>
@@ -19305,7 +19305,7 @@
         <v>1452</v>
       </c>
       <c r="E329">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F329" t="s">
         <v>1509</v>
@@ -19340,7 +19340,7 @@
         <v>1452</v>
       </c>
       <c r="E330">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F330" t="s">
         <v>1509</v>
@@ -19375,7 +19375,7 @@
         <v>1452</v>
       </c>
       <c r="E331">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F331" t="s">
         <v>1509</v>
@@ -19410,7 +19410,7 @@
         <v>1453</v>
       </c>
       <c r="E332">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F332" t="s">
         <v>1509</v>
@@ -19445,7 +19445,7 @@
         <v>1453</v>
       </c>
       <c r="E333">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F333" t="s">
         <v>1509</v>
@@ -19480,7 +19480,7 @@
         <v>1453</v>
       </c>
       <c r="E334">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F334" t="s">
         <v>1510</v>
@@ -19515,7 +19515,7 @@
         <v>1454</v>
       </c>
       <c r="E335">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F335" t="s">
         <v>1509</v>
@@ -19550,7 +19550,7 @@
         <v>1454</v>
       </c>
       <c r="E336">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F336" t="s">
         <v>1509</v>
@@ -19585,7 +19585,7 @@
         <v>1454</v>
       </c>
       <c r="E337">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F337" t="s">
         <v>1509</v>
@@ -19620,7 +19620,7 @@
         <v>1454</v>
       </c>
       <c r="E338">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F338" t="s">
         <v>1509</v>
@@ -19655,7 +19655,7 @@
         <v>1454</v>
       </c>
       <c r="E339">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F339" t="s">
         <v>1509</v>
@@ -19690,7 +19690,7 @@
         <v>1454</v>
       </c>
       <c r="E340">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F340" t="s">
         <v>1509</v>
@@ -19725,7 +19725,7 @@
         <v>1454</v>
       </c>
       <c r="E341">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F341" t="s">
         <v>1512</v>
@@ -19760,7 +19760,7 @@
         <v>1455</v>
       </c>
       <c r="E342">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F342" t="s">
         <v>1509</v>
@@ -19795,7 +19795,7 @@
         <v>1455</v>
       </c>
       <c r="E343">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F343" t="s">
         <v>1509</v>
@@ -19830,7 +19830,7 @@
         <v>1455</v>
       </c>
       <c r="E344">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F344" t="s">
         <v>1509</v>
@@ -19865,7 +19865,7 @@
         <v>1455</v>
       </c>
       <c r="E345">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F345" t="s">
         <v>1509</v>
@@ -19900,7 +19900,7 @@
         <v>1456</v>
       </c>
       <c r="E346">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F346" t="s">
         <v>1512</v>
@@ -19935,7 +19935,7 @@
         <v>1456</v>
       </c>
       <c r="E347">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F347" t="s">
         <v>1509</v>
@@ -19970,7 +19970,7 @@
         <v>1456</v>
       </c>
       <c r="E348">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F348" t="s">
         <v>1509</v>
@@ -20005,7 +20005,7 @@
         <v>1456</v>
       </c>
       <c r="E349">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F349" t="s">
         <v>1509</v>
@@ -20040,7 +20040,7 @@
         <v>1456</v>
       </c>
       <c r="E350">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F350" t="s">
         <v>1509</v>
@@ -20075,7 +20075,7 @@
         <v>1457</v>
       </c>
       <c r="E351">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F351" t="s">
         <v>1509</v>
@@ -20110,7 +20110,7 @@
         <v>1457</v>
       </c>
       <c r="E352">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F352" t="s">
         <v>1509</v>
@@ -20145,7 +20145,7 @@
         <v>1457</v>
       </c>
       <c r="E353">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F353" t="s">
         <v>1511</v>
@@ -20180,7 +20180,7 @@
         <v>1457</v>
       </c>
       <c r="E354">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F354" t="s">
         <v>1509</v>
@@ -20215,7 +20215,7 @@
         <v>1457</v>
       </c>
       <c r="E355">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F355" t="s">
         <v>1509</v>
@@ -20250,7 +20250,7 @@
         <v>1458</v>
       </c>
       <c r="E356">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F356" t="s">
         <v>1509</v>
@@ -20285,7 +20285,7 @@
         <v>1458</v>
       </c>
       <c r="E357">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F357" t="s">
         <v>1509</v>
@@ -20320,7 +20320,7 @@
         <v>1458</v>
       </c>
       <c r="E358">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F358" t="s">
         <v>1509</v>
@@ -20355,7 +20355,7 @@
         <v>1458</v>
       </c>
       <c r="E359">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F359" t="s">
         <v>1509</v>
@@ -20390,7 +20390,7 @@
         <v>1459</v>
       </c>
       <c r="E360">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F360" t="s">
         <v>1509</v>
@@ -20425,7 +20425,7 @@
         <v>1459</v>
       </c>
       <c r="E361">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F361" t="s">
         <v>1509</v>
@@ -20460,7 +20460,7 @@
         <v>1459</v>
       </c>
       <c r="E362">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F362" t="s">
         <v>1509</v>
@@ -20495,7 +20495,7 @@
         <v>1459</v>
       </c>
       <c r="E363">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F363" t="s">
         <v>1509</v>
@@ -20533,7 +20533,7 @@
         <v>1460</v>
       </c>
       <c r="E364">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F364" t="s">
         <v>1509</v>
@@ -20568,7 +20568,7 @@
         <v>1460</v>
       </c>
       <c r="E365">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F365" t="s">
         <v>1509</v>
@@ -20603,7 +20603,7 @@
         <v>1460</v>
       </c>
       <c r="E366">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F366" t="s">
         <v>1509</v>
@@ -20638,7 +20638,7 @@
         <v>1460</v>
       </c>
       <c r="E367">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F367" t="s">
         <v>1509</v>
@@ -20673,7 +20673,7 @@
         <v>1460</v>
       </c>
       <c r="E368">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F368" t="s">
         <v>1509</v>
@@ -20708,7 +20708,7 @@
         <v>1460</v>
       </c>
       <c r="E369">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F369" t="s">
         <v>1509</v>
@@ -20743,7 +20743,7 @@
         <v>1461</v>
       </c>
       <c r="E370">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F370" t="s">
         <v>1510</v>
@@ -20778,7 +20778,7 @@
         <v>1461</v>
       </c>
       <c r="E371">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F371" t="s">
         <v>1509</v>
@@ -20813,7 +20813,7 @@
         <v>1462</v>
       </c>
       <c r="E372">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F372" t="s">
         <v>1509</v>
@@ -20848,7 +20848,7 @@
         <v>1463</v>
       </c>
       <c r="E373">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F373" t="s">
         <v>1509</v>
@@ -20883,7 +20883,7 @@
         <v>1463</v>
       </c>
       <c r="E374">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F374" t="s">
         <v>1509</v>
@@ -20918,7 +20918,7 @@
         <v>1463</v>
       </c>
       <c r="E375">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F375" t="s">
         <v>1511</v>
@@ -20956,7 +20956,7 @@
         <v>1464</v>
       </c>
       <c r="E376">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F376" t="s">
         <v>1509</v>
@@ -20991,7 +20991,7 @@
         <v>1464</v>
       </c>
       <c r="E377">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F377" t="s">
         <v>1509</v>
@@ -21026,7 +21026,7 @@
         <v>1464</v>
       </c>
       <c r="E378">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F378" t="s">
         <v>1509</v>
@@ -21061,7 +21061,7 @@
         <v>1465</v>
       </c>
       <c r="E379">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F379" t="s">
         <v>1509</v>
@@ -21096,7 +21096,7 @@
         <v>1465</v>
       </c>
       <c r="E380">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F380" t="s">
         <v>1509</v>
@@ -21131,7 +21131,7 @@
         <v>1465</v>
       </c>
       <c r="E381">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F381" t="s">
         <v>1509</v>
@@ -21166,7 +21166,7 @@
         <v>1465</v>
       </c>
       <c r="E382">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F382" t="s">
         <v>1509</v>
@@ -21201,7 +21201,7 @@
         <v>1465</v>
       </c>
       <c r="E383">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F383" t="s">
         <v>1509</v>
@@ -21236,7 +21236,7 @@
         <v>1465</v>
       </c>
       <c r="E384">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F384" t="s">
         <v>1509</v>
@@ -21271,7 +21271,7 @@
         <v>1465</v>
       </c>
       <c r="E385">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F385" t="s">
         <v>1509</v>
@@ -21306,7 +21306,7 @@
         <v>1466</v>
       </c>
       <c r="E386">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F386" t="s">
         <v>1509</v>
@@ -21341,7 +21341,7 @@
         <v>1467</v>
       </c>
       <c r="E387">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F387" t="s">
         <v>1509</v>
@@ -21376,7 +21376,7 @@
         <v>1467</v>
       </c>
       <c r="E388">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F388" t="s">
         <v>1509</v>
@@ -21411,7 +21411,7 @@
         <v>1467</v>
       </c>
       <c r="E389">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F389" t="s">
         <v>1509</v>
@@ -21446,7 +21446,7 @@
         <v>1467</v>
       </c>
       <c r="E390">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F390" t="s">
         <v>1513</v>
@@ -21484,7 +21484,7 @@
         <v>1467</v>
       </c>
       <c r="E391">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F391" t="s">
         <v>1509</v>
@@ -21519,7 +21519,7 @@
         <v>1467</v>
       </c>
       <c r="E392">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F392" t="s">
         <v>1513</v>
@@ -21554,7 +21554,7 @@
         <v>1468</v>
       </c>
       <c r="E393">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F393" t="s">
         <v>1509</v>
@@ -21589,7 +21589,7 @@
         <v>1469</v>
       </c>
       <c r="E394">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F394" t="s">
         <v>1509</v>
@@ -21624,7 +21624,7 @@
         <v>1469</v>
       </c>
       <c r="E395">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F395" t="s">
         <v>1509</v>
@@ -21659,7 +21659,7 @@
         <v>1469</v>
       </c>
       <c r="E396">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F396" t="s">
         <v>1509</v>
@@ -21694,7 +21694,7 @@
         <v>1470</v>
       </c>
       <c r="E397">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F397" t="s">
         <v>1513</v>
@@ -21729,7 +21729,7 @@
         <v>1470</v>
       </c>
       <c r="E398">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F398" t="s">
         <v>1509</v>
@@ -21764,7 +21764,7 @@
         <v>1470</v>
       </c>
       <c r="E399">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F399" t="s">
         <v>1509</v>
@@ -21799,7 +21799,7 @@
         <v>1470</v>
       </c>
       <c r="E400">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F400" t="s">
         <v>1509</v>
@@ -21834,7 +21834,7 @@
         <v>1471</v>
       </c>
       <c r="E401">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F401" t="s">
         <v>1509</v>
@@ -21869,7 +21869,7 @@
         <v>1471</v>
       </c>
       <c r="E402">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F402" t="s">
         <v>1509</v>
@@ -21904,7 +21904,7 @@
         <v>1471</v>
       </c>
       <c r="E403">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F403" t="s">
         <v>1509</v>
@@ -21939,7 +21939,7 @@
         <v>1472</v>
       </c>
       <c r="E404">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F404" t="s">
         <v>1509</v>
@@ -21974,7 +21974,7 @@
         <v>1472</v>
       </c>
       <c r="E405">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F405" t="s">
         <v>1509</v>
@@ -22009,7 +22009,7 @@
         <v>1472</v>
       </c>
       <c r="E406">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F406" t="s">
         <v>1509</v>
@@ -22044,7 +22044,7 @@
         <v>1472</v>
       </c>
       <c r="E407">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F407" t="s">
         <v>1509</v>
@@ -22079,7 +22079,7 @@
         <v>1472</v>
       </c>
       <c r="E408">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F408" t="s">
         <v>1509</v>
@@ -22114,7 +22114,7 @@
         <v>1473</v>
       </c>
       <c r="E409">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F409" t="s">
         <v>1509</v>
@@ -22149,7 +22149,7 @@
         <v>1473</v>
       </c>
       <c r="E410">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F410" t="s">
         <v>1509</v>
@@ -22184,7 +22184,7 @@
         <v>1473</v>
       </c>
       <c r="E411">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F411" t="s">
         <v>1509</v>
@@ -22219,7 +22219,7 @@
         <v>1473</v>
       </c>
       <c r="E412">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F412" t="s">
         <v>1509</v>
@@ -22254,7 +22254,7 @@
         <v>1473</v>
       </c>
       <c r="E413">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F413" t="s">
         <v>1509</v>
@@ -22289,7 +22289,7 @@
         <v>1473</v>
       </c>
       <c r="E414">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F414" t="s">
         <v>1509</v>
@@ -22324,7 +22324,7 @@
         <v>1473</v>
       </c>
       <c r="E415">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F415" t="s">
         <v>1509</v>
@@ -22359,7 +22359,7 @@
         <v>1473</v>
       </c>
       <c r="E416">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F416" t="s">
         <v>1509</v>
@@ -22394,7 +22394,7 @@
         <v>1473</v>
       </c>
       <c r="E417">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F417" t="s">
         <v>1509</v>
@@ -22429,7 +22429,7 @@
         <v>1473</v>
       </c>
       <c r="E418">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F418" t="s">
         <v>1509</v>
@@ -22464,7 +22464,7 @@
         <v>1473</v>
       </c>
       <c r="E419">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F419" t="s">
         <v>1509</v>
@@ -22499,7 +22499,7 @@
         <v>1473</v>
       </c>
       <c r="E420">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F420" t="s">
         <v>1509</v>
@@ -22534,7 +22534,7 @@
         <v>1473</v>
       </c>
       <c r="E421">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F421" t="s">
         <v>1509</v>
@@ -22569,7 +22569,7 @@
         <v>1473</v>
       </c>
       <c r="E422">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F422" t="s">
         <v>1509</v>
@@ -22604,7 +22604,7 @@
         <v>1473</v>
       </c>
       <c r="E423">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F423" t="s">
         <v>1509</v>
@@ -22639,7 +22639,7 @@
         <v>1473</v>
       </c>
       <c r="E424">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F424" t="s">
         <v>1509</v>
@@ -22674,7 +22674,7 @@
         <v>1473</v>
       </c>
       <c r="E425">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F425" t="s">
         <v>1509</v>
@@ -22709,7 +22709,7 @@
         <v>1473</v>
       </c>
       <c r="E426">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F426" t="s">
         <v>1509</v>
@@ -22744,7 +22744,7 @@
         <v>1473</v>
       </c>
       <c r="E427">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F427" t="s">
         <v>1509</v>
@@ -22779,7 +22779,7 @@
         <v>1473</v>
       </c>
       <c r="E428">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F428" t="s">
         <v>1509</v>
@@ -22814,7 +22814,7 @@
         <v>1473</v>
       </c>
       <c r="E429">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F429" t="s">
         <v>1509</v>
@@ -22849,7 +22849,7 @@
         <v>1473</v>
       </c>
       <c r="E430">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F430" t="s">
         <v>1509</v>
@@ -22884,7 +22884,7 @@
         <v>1473</v>
       </c>
       <c r="E431">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F431" t="s">
         <v>1509</v>
@@ -22919,7 +22919,7 @@
         <v>1473</v>
       </c>
       <c r="E432">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F432" t="s">
         <v>1509</v>
@@ -22954,7 +22954,7 @@
         <v>1474</v>
       </c>
       <c r="E433">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F433" t="s">
         <v>1509</v>
@@ -22989,7 +22989,7 @@
         <v>1474</v>
       </c>
       <c r="E434">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F434" t="s">
         <v>1509</v>
@@ -23024,7 +23024,7 @@
         <v>1474</v>
       </c>
       <c r="E435">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F435" t="s">
         <v>1509</v>
@@ -23059,7 +23059,7 @@
         <v>1474</v>
       </c>
       <c r="E436">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F436" t="s">
         <v>1509</v>
@@ -23094,7 +23094,7 @@
         <v>1474</v>
       </c>
       <c r="E437">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F437" t="s">
         <v>1509</v>
@@ -23129,7 +23129,7 @@
         <v>1474</v>
       </c>
       <c r="E438">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F438" t="s">
         <v>1509</v>
@@ -23164,7 +23164,7 @@
         <v>1474</v>
       </c>
       <c r="E439">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F439" t="s">
         <v>1513</v>
@@ -23199,7 +23199,7 @@
         <v>1474</v>
       </c>
       <c r="E440">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F440" t="s">
         <v>1509</v>
@@ -23234,7 +23234,7 @@
         <v>1475</v>
       </c>
       <c r="E441">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F441" t="s">
         <v>1509</v>
@@ -23269,7 +23269,7 @@
         <v>1476</v>
       </c>
       <c r="E442">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F442" t="s">
         <v>1511</v>
@@ -23307,7 +23307,7 @@
         <v>1476</v>
       </c>
       <c r="E443">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F443" t="s">
         <v>1509</v>
@@ -23342,7 +23342,7 @@
         <v>1476</v>
       </c>
       <c r="E444">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F444" t="s">
         <v>1509</v>
@@ -23377,7 +23377,7 @@
         <v>1476</v>
       </c>
       <c r="E445">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F445" t="s">
         <v>1509</v>
@@ -23412,7 +23412,7 @@
         <v>1476</v>
       </c>
       <c r="E446">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F446" t="s">
         <v>1509</v>
@@ -23447,7 +23447,7 @@
         <v>1477</v>
       </c>
       <c r="E447">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F447" t="s">
         <v>1509</v>
@@ -23485,7 +23485,7 @@
         <v>1477</v>
       </c>
       <c r="E448">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F448" t="s">
         <v>1513</v>
@@ -23520,7 +23520,7 @@
         <v>1477</v>
       </c>
       <c r="E449">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F449" t="s">
         <v>1511</v>
@@ -23555,7 +23555,7 @@
         <v>1477</v>
       </c>
       <c r="E450">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F450" t="s">
         <v>1509</v>
@@ -23590,7 +23590,7 @@
         <v>1477</v>
       </c>
       <c r="E451">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F451" t="s">
         <v>1509</v>
@@ -23625,7 +23625,7 @@
         <v>1477</v>
       </c>
       <c r="E452">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F452" t="s">
         <v>1509</v>
@@ -23660,7 +23660,7 @@
         <v>1477</v>
       </c>
       <c r="E453">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F453" t="s">
         <v>1509</v>
@@ -23695,7 +23695,7 @@
         <v>1477</v>
       </c>
       <c r="E454">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F454" t="s">
         <v>1509</v>
@@ -23730,7 +23730,7 @@
         <v>1477</v>
       </c>
       <c r="E455">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F455" t="s">
         <v>1509</v>
@@ -23765,7 +23765,7 @@
         <v>1478</v>
       </c>
       <c r="E456">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F456" t="s">
         <v>1513</v>
@@ -23803,7 +23803,7 @@
         <v>1478</v>
       </c>
       <c r="E457">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F457" t="s">
         <v>1509</v>
@@ -23838,7 +23838,7 @@
         <v>1479</v>
       </c>
       <c r="E458">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F458" t="s">
         <v>1509</v>
@@ -23873,7 +23873,7 @@
         <v>1479</v>
       </c>
       <c r="E459">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F459" t="s">
         <v>1509</v>
@@ -23908,7 +23908,7 @@
         <v>1479</v>
       </c>
       <c r="E460">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F460" t="s">
         <v>1509</v>
@@ -23943,7 +23943,7 @@
         <v>1479</v>
       </c>
       <c r="E461">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F461" t="s">
         <v>1509</v>
@@ -23978,7 +23978,7 @@
         <v>1479</v>
       </c>
       <c r="E462">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F462" t="s">
         <v>1509</v>
@@ -24013,7 +24013,7 @@
         <v>1479</v>
       </c>
       <c r="E463">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F463" t="s">
         <v>1509</v>
@@ -24048,7 +24048,7 @@
         <v>1480</v>
       </c>
       <c r="E464">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F464" t="s">
         <v>1509</v>
@@ -24083,7 +24083,7 @@
         <v>1480</v>
       </c>
       <c r="E465">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F465" t="s">
         <v>1509</v>
@@ -24118,7 +24118,7 @@
         <v>1480</v>
       </c>
       <c r="E466">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F466" t="s">
         <v>1509</v>
@@ -24153,7 +24153,7 @@
         <v>1480</v>
       </c>
       <c r="E467">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F467" t="s">
         <v>1509</v>
@@ -24188,7 +24188,7 @@
         <v>1480</v>
       </c>
       <c r="E468">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F468" t="s">
         <v>1509</v>
@@ -24223,7 +24223,7 @@
         <v>1480</v>
       </c>
       <c r="E469">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F469" t="s">
         <v>1511</v>
@@ -24258,7 +24258,7 @@
         <v>1480</v>
       </c>
       <c r="E470">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F470" t="s">
         <v>1509</v>
@@ -24293,7 +24293,7 @@
         <v>1480</v>
       </c>
       <c r="E471">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F471" t="s">
         <v>1509</v>
@@ -24328,7 +24328,7 @@
         <v>1481</v>
       </c>
       <c r="E472">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F472" t="s">
         <v>1509</v>
@@ -24363,7 +24363,7 @@
         <v>1481</v>
       </c>
       <c r="E473">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F473" t="s">
         <v>1509</v>
@@ -24398,7 +24398,7 @@
         <v>1481</v>
       </c>
       <c r="E474">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F474" t="s">
         <v>1509</v>
@@ -24433,7 +24433,7 @@
         <v>1481</v>
       </c>
       <c r="E475">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F475" t="s">
         <v>1509</v>
@@ -24468,7 +24468,7 @@
         <v>1481</v>
       </c>
       <c r="E476">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F476" t="s">
         <v>1509</v>
@@ -24503,7 +24503,7 @@
         <v>1481</v>
       </c>
       <c r="E477">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F477" t="s">
         <v>1509</v>
@@ -24538,7 +24538,7 @@
         <v>1481</v>
       </c>
       <c r="E478">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F478" t="s">
         <v>1509</v>
@@ -24573,7 +24573,7 @@
         <v>1481</v>
       </c>
       <c r="E479">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F479" t="s">
         <v>1509</v>
@@ -24608,7 +24608,7 @@
         <v>1482</v>
       </c>
       <c r="E480">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F480" t="s">
         <v>1509</v>
@@ -24643,7 +24643,7 @@
         <v>1482</v>
       </c>
       <c r="E481">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F481" t="s">
         <v>1509</v>
@@ -24678,7 +24678,7 @@
         <v>1482</v>
       </c>
       <c r="E482">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F482" t="s">
         <v>1509</v>
@@ -24713,7 +24713,7 @@
         <v>1482</v>
       </c>
       <c r="E483">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F483" t="s">
         <v>1509</v>
@@ -24748,7 +24748,7 @@
         <v>1482</v>
       </c>
       <c r="E484">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F484" t="s">
         <v>1509</v>
@@ -24783,7 +24783,7 @@
         <v>1482</v>
       </c>
       <c r="E485">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F485" t="s">
         <v>1509</v>
@@ -24818,7 +24818,7 @@
         <v>1483</v>
       </c>
       <c r="E486">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F486" t="s">
         <v>1509</v>
@@ -24853,7 +24853,7 @@
         <v>1483</v>
       </c>
       <c r="E487">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F487" t="s">
         <v>1509</v>
@@ -24888,7 +24888,7 @@
         <v>1483</v>
       </c>
       <c r="E488">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F488" t="s">
         <v>1509</v>
@@ -24923,7 +24923,7 @@
         <v>1483</v>
       </c>
       <c r="E489">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F489" t="s">
         <v>1509</v>
@@ -24958,7 +24958,7 @@
         <v>1483</v>
       </c>
       <c r="E490">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F490" t="s">
         <v>1509</v>
@@ -24993,7 +24993,7 @@
         <v>1484</v>
       </c>
       <c r="E491">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F491" t="s">
         <v>1509</v>
@@ -25028,7 +25028,7 @@
         <v>1484</v>
       </c>
       <c r="E492">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F492" t="s">
         <v>1509</v>
@@ -25063,7 +25063,7 @@
         <v>1484</v>
       </c>
       <c r="E493">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F493" t="s">
         <v>1509</v>
@@ -25098,7 +25098,7 @@
         <v>1484</v>
       </c>
       <c r="E494">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F494" t="s">
         <v>1509</v>
@@ -25133,7 +25133,7 @@
         <v>1484</v>
       </c>
       <c r="E495">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F495" t="s">
         <v>1509</v>
@@ -25168,7 +25168,7 @@
         <v>1484</v>
       </c>
       <c r="E496">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F496" t="s">
         <v>1509</v>
@@ -25203,7 +25203,7 @@
         <v>1484</v>
       </c>
       <c r="E497">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F497" t="s">
         <v>1509</v>
@@ -25238,7 +25238,7 @@
         <v>1484</v>
       </c>
       <c r="E498">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F498" t="s">
         <v>1509</v>
@@ -25273,7 +25273,7 @@
         <v>1484</v>
       </c>
       <c r="E499">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F499" t="s">
         <v>1509</v>
@@ -25311,7 +25311,7 @@
         <v>1484</v>
       </c>
       <c r="E500">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F500" t="s">
         <v>1509</v>
@@ -25346,7 +25346,7 @@
         <v>1485</v>
       </c>
       <c r="E501">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F501" t="s">
         <v>1509</v>
@@ -25381,7 +25381,7 @@
         <v>1485</v>
       </c>
       <c r="E502">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F502" t="s">
         <v>1509</v>
@@ -25416,7 +25416,7 @@
         <v>1485</v>
       </c>
       <c r="E503">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F503" t="s">
         <v>1509</v>
@@ -25451,7 +25451,7 @@
         <v>1486</v>
       </c>
       <c r="E504">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F504" t="s">
         <v>1509</v>
@@ -25486,7 +25486,7 @@
         <v>1486</v>
       </c>
       <c r="E505">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F505" t="s">
         <v>1509</v>
@@ -25521,7 +25521,7 @@
         <v>1486</v>
       </c>
       <c r="E506">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F506" t="s">
         <v>1509</v>
@@ -25556,7 +25556,7 @@
         <v>1486</v>
       </c>
       <c r="E507">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F507" t="s">
         <v>1509</v>
@@ -25591,7 +25591,7 @@
         <v>1486</v>
       </c>
       <c r="E508">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F508" t="s">
         <v>1509</v>
@@ -25626,7 +25626,7 @@
         <v>1486</v>
       </c>
       <c r="E509">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F509" t="s">
         <v>1509</v>
@@ -25661,7 +25661,7 @@
         <v>1486</v>
       </c>
       <c r="E510">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F510" t="s">
         <v>1509</v>
@@ -25696,7 +25696,7 @@
         <v>1486</v>
       </c>
       <c r="E511">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F511" t="s">
         <v>1509</v>
@@ -25731,7 +25731,7 @@
         <v>1486</v>
       </c>
       <c r="E512">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F512" t="s">
         <v>1509</v>
@@ -25766,7 +25766,7 @@
         <v>1487</v>
       </c>
       <c r="E513">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F513" t="s">
         <v>1509</v>
@@ -25801,7 +25801,7 @@
         <v>1487</v>
       </c>
       <c r="E514">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F514" t="s">
         <v>1509</v>
@@ -25836,7 +25836,7 @@
         <v>1487</v>
       <